--- a/data/weekly/topic_feeds_week.xlsx
+++ b/data/weekly/topic_feeds_week.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,11 +447,6 @@
           <t>past_days</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>published_dt_utc</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -470,24 +461,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Economic indicators: Key statistics for the UK economy - The House of Commons Library</t>
+          <t>National children’s report to Government influenced by local experiences - North East Lincolnshire Council</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 19:07:30 GMT</t>
+          <t>Tue, 03 Feb 2026 11:08:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFB4VGljZlhGUVdWQUxmc19qYU9VaG02OFVUTUx3cHZ4bDBKbVd4RWJWMnhYYXZZWXJ2cEJXSWNWeUJtQnZRek9nZmN4alpFSWpWd3hhUGpnZ3ZRdFZGN24tWVZRaG83dmItaTc3dEF6RU1CeTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNmItNlgyTnhIUkppVk84b1RfMFh2N3FIRS1BS3ZyRktScGp0VlJqYmttdF9HeGgtVlFDekpOS1RXanJrZlZ5YTI1ZTBTQ1NkaC1qbHF3cUNKZkpOTWZhYklMNzR5WWFOT2xHSDJVcmh0cDRZbmRlMEtZODBQZ1MzNlg3WlA4NW5NSmFpaExlVFpMSXNlejlNaWhfc1laMjBB?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>7</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>46049.796875</v>
       </c>
     </row>
     <row r="3">
@@ -503,24 +491,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>First Annual Report published by the Immigration Advice Authority - GOV.UK</t>
+          <t>UK-India Free Trade Agreement is a significant achievement with a formidable negotiating partner, concludes Committee - UK Parliament</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 13:17:12 GMT</t>
+          <t>Tue, 03 Feb 2026 00:04:30 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNd2daM1B1NkM0bzAwSE5wWWFSRzRiYWtyQjZ6d0NoRlpaVnIzR0tNcDctQXRqMHgycmRVTjZCY0QzcVhxS2hvVHlQSmQ0eks5Tjl4NGx3aGpZOENBR1hTV0JpLVNXejloYUMwMWpENDhMemdqc0hRMS05SlFVNG15ZXRQdHhzRGx6TWV1Ui0xTU5TaXFUQTZobVdBaG02bk5UaUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAJBVV95cUxOa0JjOXpSbUJ5cjA4RXdDSXA0bG9yNGFnb1F5bVdiQXF0dDFWLUttMFUzLUxBbmdVRlZic1VoNEc1NTdfeTZqV1JidHphandNS1hOd2J5S0NxMWRnWkpGckF5a1BOSzJHcTI1VkdyQmFDLVJFS0hGYVhJRHlOOWFBdENxdDlFZFlGcU9MNURQY0JNTi03TkUxbWVvQVd3TnZGSlJJS0RCWFpGaUV1V1ZoM3A0ZnRtaEdBX1gwdmNXZnRUcW50WjZ5WXBzQ19lYTBnQks4NXQxVkJTTDdhMWFOUUtfYTZuMHpMNVlYTjJRSDFWNHZVd0VvbTRtc19GaW9wT3lZM1F1TU1pLWxZZVJFbGNycVU1eVBhNEE1blZueFFsOG1UZ3lkazZIV1NHbFNtdjlrRQ?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>7</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>46051.55361111111</v>
       </c>
     </row>
     <row r="4">
@@ -536,24 +521,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[Report] Annual Terrorism Threat Report 2025 - Pool Reinsurance</t>
+          <t>Sudan, conflict - ETC Situation Report #36 (Reporting period: January 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 15:44:45 GMT</t>
+          <t>Wed, 04 Feb 2026 06:33:07 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQZC1sdjUzTFdSTjI0NS1LNlJlTnBuU1ZhNy1GaWpreDBIYkVUUldMTDJKUDhOZmRoXzA1S0VVZmFOZlUzS3FTemRMU0hiUE1Jc2tQbllvaTEweF9FTW5WR1NuNERyeXozZzVHS29uRUxPWVhfOGRlTjFhM3h2dUpkSkhBWml1LVBjTWk4OW5RUHFzcWZ3SWdrZThtbUJGbU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNX2haNFB0Y21DelpXNTZhMGQyVWxrYzlKVkJhUWFROEJ4WWhZSUNvbjRSb1FMR2NNV3g1VGtyVE53RUxSNVg3a2cxeDBXR1hoNHFTTWNoc3RhYUxHQWQ3X2R6cnBuQy1xUW1sTmE4SXN2Mm5hSGZ0TnJ5VTdKOTRjUi1rc2NlbVNmVEdnX2E5OFdNYml5MTJZNXd5M0JLaFpuQzFlRm9n?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>7</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>46049.65607638889</v>
       </c>
     </row>
     <row r="5">
@@ -569,24 +551,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quicker implementation of pollution laws needed, says report - European Commission</t>
+          <t>Government report warns Ireland lacks access to key EU border-security databases - VisaHQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 10:57:23 GMT</t>
+          <t>Tue, 03 Feb 2026 20:52:20 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNVklCTjRLNzR4UHc3ZHB3WlNCbFVjRVo2b3FLX0hJc2lhaFBKS2trcEg0bHNwRG04NXRaNDR2SXBybkI4bVQ1Z1ExVXM2bG5nbE1LcG9HVU9yTHBQb0JOTkFLTXZQVFN0d3gwZjJxdlhaVE9GZlRUSkUtc1pCRHBlLVotVWFicEU5MGg3NGptbTBCNGV1ZXFoT3dDZFg1QU1kdkdlM2RMRTJjMmV4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQNks4THV6akVUNEIwUjNXVVJ6VEN1aTNDanU1Y0QwalplRVNSSmwxaDhqdWFFb1EwMERKcWxlUk03X2ViNzQwZkRIbEVxOUZBeXZ2UVBDX1c0ZkRJS29UX1JYTzFSQ25hT2pvSWpEek10WGxwcllDNnloWlFXbGs4QnRScmw5Q1lFc3ZDM3ZFZ2tkdEJVWXBsWDAxT0I1cDdqQTA2VHZBNWg0Y1JmMlQ5bW1walQzSjRwaHM1b095NXA?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>7</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>46052.4565162037</v>
       </c>
     </row>
     <row r="6">
@@ -602,24 +581,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ETS Nigeria Conflict Situation Report #109: January 2026 - ReliefWeb</t>
+          <t>Fox Williams cited in Treasury Select Committee report on AI regulation - Fox Williams</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:33:09 GMT</t>
+          <t>Mon, 02 Feb 2026 15:59:28 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOY2RLR1BHd1ZqN1d2c05HS0luYXYyUTB2ZGVhaFp6WFhmVW1yekJtY29oakx1OXc4VjA4bjVNUVdMX09YSldURkVOTjdPaWlmZE02S0xpWVVQVlRHUDZXd0VoYXZtZTFoU0V0VHV1SXBIRnM4aV94UUd2VkdOMGJfTGFBTV9pdDRWMldEcW5HNDl6UXV3b0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONUticHMyRF85OV9QcFRDQm5LV0YwTDc2c2RjZjRFcnpmUXJIcXRVWlIwSWpEdXNpbkp5eUMyZWh2UHNXbHFZcHlIZDJBWkJoQl96ZDAtdUtSc0xodUVGSzh6Q1pDTFdlal9RTmlEUVRZcjRMWXo4TE1feVlCaFJ6RExTR1ZYWHJZRllZMzZJaFhKTy0ydmVIX201Y2pPcHdIZUtVV3BzYm03YzIwbUQzYg?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>7</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>46055.39802083333</v>
       </c>
     </row>
     <row r="7">
@@ -635,24 +611,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cost of clinical negligence revealed in government report - Dentistry UK</t>
+          <t>T&amp;E analysis of the European Commission proposal for the revision of the car CO2 regulation - Transport &amp; Environment</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 11:35:28 GMT</t>
+          <t>Mon, 02 Feb 2026 23:01:39 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYjVwaTN1UkZsRS1raGh3cVF5b1ZSRy1sYnZFM3ZxVDgzYmFUckRQYkpTMlhEbFZmM3c5N0xvbUtETHlIVFZDYVN1M3QtZjBYc00tQmZjbHd1eVRFRFJGZGIybGhzM0x3Z1R3ZUxsX05Mc1NnTHJqT3YydWszZGZQdzg5UkVIVEZvRmpOMDhQSE9QdXEzSzlrYTlIYUpWZ3Iz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNUE5RNUloMElpdDNNNzAtWmNfdHVwalJXLVNiM1VvTkI3a1lOUTA5RlMyR2pxTWFLQWdYMElQWmNDbUlEVFMyU0dIYkRoZXY1WVRCWmEyNy0wdi1PTUUyYjZEWk9CcldMUENFSTBpbXNBd2V3bVI1MjlMZFVwamhWNGctalZLTGtvQkJ1MWRFdVkxR1JNSFd3TzdETFFLUFVIMUx5eEMzYWFVRkFsa3hBUlRoY28xb1ljVlJmX05xWFZBN0RxbWhob1NXczhZVEJTcHE4?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>7</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>46052.48296296296</v>
       </c>
     </row>
     <row r="8">
@@ -668,24 +641,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Novaspace Report Predicts Global Space Economy Market Could Top $1 Trillion by 2034 - Via Satellite</t>
+          <t>Thriving Kids Advisory Group Delivers Final Report - MBS Online</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 21:15:33 GMT</t>
+          <t>Wed, 04 Feb 2026 04:20:18 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOaWNmX19RV0FreC1pNTlDVlZBOWxPOFY4NnNoVWxXM3lkUFdhbEhyVzJBMk9pNnZKTGZaX01zOFN2SmJqLXFvSGVJejBPUjlkWHAwUGlSOU52cnpKd2gxZ0ZSQURBRTh5VXdJc0tTWmw4cGZpWk41b2NEaVlHYzJGMzJxUV84QW5RR0Y4NXlJdmM1MVMzLUFVeXdlblphdHVuNWttb1lHYnJLWnIwS0pGUkxhRlIydUhQSkprUW41X01aOXhLNmJaUEhXX2QxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPQ1lvX0FNbDhia2hlbVhlMnhSb2tKM1l4NlZ3RmZvLV82QzhnWmppcDZCU1dUNjNweE1DUlZOb21fVGlDZE5VaGdmUDE3WnNWNzlFQkktTDZpXy1nX0pFN2RqVXp4clNRdFZpQThsNHk5UVdzaE9tQ1hFblVnX1VkMmJSYjhEenFB?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>7</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>46052.88579861111</v>
       </c>
     </row>
     <row r="9">
@@ -701,24 +671,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>U.S. Military Options in Iran: Means in Search of an End - The Washington Institute</t>
+          <t>Policy analysis: Prospective changes to prevailing wage levels and impacts on international hiring - AIP.ORG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 21:53:13 GMT</t>
+          <t>Tue, 03 Feb 2026 20:36:56 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQRUwtYTRvSmY3M1BWaWRsdmd1bWJ1al9IUHlocURLUmFHei1KTlc1N1dEbjJuaFhGdGpVYjJIVlZ6WEFxdGw4VGx3VWt5dlhGSk1PZHB5MThJdVE4d081RmVLemZ3alkxX0R4V2QzNVlrTlgwYXdmQ3R6bENYRzM3NXBvcDNiNlBDcXhSTXhYb0RodnI4aXUzcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVFZfVmlvaDZhVXNZMjBKSU9aUFFydWxKTFlyRFZ0eU1FOEg4WDY4eGdDQm9FdkJtUVJNQmw3am9DZDRqZHVBeVpMNjlaelo4TWhiR3h0RDBCcUU2V3U3TmVUWVh0bzJvdnpISC1fWE9kSE5fVmhWYmtCS293UXltMnJYWHFaOEhlME1BTW5jVTRfOHNMNl9iMS12clFHSnkzYjVzUFlUR2MwNG12T2FaYWtoMmxfcU9BaVJRdzNGcmZTa2JV?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>7</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>46052.91195601852</v>
       </c>
     </row>
     <row r="10">
@@ -734,57 +701,51 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Report: How Brexit has shaped UK immigration policy - Irish Legal News</t>
+          <t>BetMGM explicitly bans harassment of athletes in policy update - Yogonet</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 13:49:32 GMT</t>
+          <t>Tue, 03 Feb 2026 13:12:32 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPSTFCVXdvOTFjQ28yanVXSDl5dzdtNGhzNkZwbnh3amlaMHlna0dQTEF5TEpGMWxMdDZBNUViekV1ZTMzSjQ1SXFGSGl5NDR6NFhoTVp3dzVqcllsbjZiXzJGcVNsQ056Mk5nM0NuRlh1MXV6VUdnaVJfczN3M1RBcmtvdGdMQ193R0Fjek5QRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORjZNV0FPbUxXU2tKM1lqamYtXzJNV2dSU2djb3hSOF8zVzJUbHJ3UGE2eEV3aGNpNHJUZTJEUlFpNnhHVmFIWm93QThIcUJnSW5QMHhPbFA2Yk9zX0FweGhYR0VZRDI3V20wWkRta1BvZVlkZGNJb3I2dmFpZVQ4TlFjYzhJMFdRZjd4ZDFXZ283T1RqLWhKeDFLcHY1eDIwZlhSRzVZeHhPejJKZ3FiMExjUjhTQU96YnlodjV2aHE?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>7</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>46052.57606481481</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monetary Policy Report Press Conference Opening Statement - Bank of Canada</t>
+          <t>UK investigating first suspected breach of cyber sanctions - The Record from Recorded Future News</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 14:47:31 GMT</t>
+          <t>Tue, 03 Feb 2026 16:46:57 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9sQkNVUmh2OVdwWVhPcXNZdHM3OExHR1c3TnJJRXlVZzBDLXNDODN3ek5vMnNPOFBZQzN4Y09YeExFbkpRVHA0OGs2VUZnd2c2ZkVvdGRrN005N0otVENFSkU0c2RRY2FNODEtQ3hqSkZpb0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQLVYxb29zZ3JfTnpfTHl1TGp3emJHQjNrR2ljZk9Zb2RsRG5mOFJGV0w3dnQxdW5BTjFlRzRnUEhmUjk0SFphWVBSeUo0bWZ4bWRzY3Z4R191QXY2QU1hTmJ1cGthVGwzM201TUtRc2NreUd5Q01HbnZjcHR5alNUQQ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>7</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>46050.61633101852</v>
       </c>
     </row>
     <row r="12">
@@ -800,24 +761,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Logistics Manager Magazine February 2026 - Logistics Manager</t>
+          <t>Vale's transfer window round-up - Port Vale</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:00:25 GMT</t>
+          <t>Tue, 03 Feb 2026 20:02:05 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5WM3c1Um9FY0RtamoxcENreVJvWUpQbWl0ODFqb0VUX0tqTk8xTVM4SmRkc21FLWJJV3pnNVhUcDlUbU5CRHpNWGhNcjRidTVHZ0Qxd09zaWFZV3NIc01mWlpYQ1ZVZ2dYTUtiMEt5ZGRCWVc3dTl2c1pNZ3ozVEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1QTGtyOVQ4Mm9Nc3NxZ3lfRGpxN3diUktMS2Fnc2RhYmdrRl9adEN1N0Q0c3dRUjhrQjVaZU5MOFF1RzFPRi1mYnFBTG8tQVlfYWdRVXh4R3FqQ3ZYVG1sSE5fWlVyUzNsWWdPeQ?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>7</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>46055.50028935185</v>
       </c>
     </row>
     <row r="13">
@@ -833,24 +791,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UK manufacturers recalibrate trade strategies as tariffs bite - Relocate magazine</t>
+          <t>Trump to slash India tariffs after Modi ‘agrees’ to stop buying Russian oil - Financial Times</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:43:42 GMT</t>
+          <t>Mon, 02 Feb 2026 17:18:04 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPNVhoOENKNGhOeVEtZTU1RlB5ZVZ3Zm1Obkw3Xzg3MVFXUnFkZ1ozZmJKZUZKSGhyNmNtMGZfTjRsOHFkLUxUTWMyUzRBbGx3RTRFZU5DQ1ZCODdZSXRTa0V6WmdyeUVqSHA4amw2NEtHNXNmVG1wdEFqOWRPSWlDei1Zcm10a1BvbzQwUi1kb3F6ZWdZeFNXbmV4RS1Gcm9YSkpmUmZBcUw4QnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5DV3FTdThYajVIRFpBZzdyeU9lcENzUVNwUHdUUGJ5VWU2RXdaS2l3SmlwVXJDVUpYQmhvdi01QlpXTVRucEk0XzhFWnRvd0N6UG9TMU1obDJYTXN1UENLMmI5eDNxN2FVWWpzUnFDTGQ?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>7</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>46055.44701388889</v>
       </c>
     </row>
     <row r="14">
@@ -866,24 +821,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Services - GIMA Day Conference 2026: the future of the supply chain for garden products - gardenforum.co.uk</t>
+          <t>Disco Bingo, exclusive port tours and a mini circus – what’s not to like about Love Immingham! - North East Lincolnshire Council</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:04:40 GMT</t>
+          <t>Tue, 03 Feb 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPU3VFMUNRR1duajV0UmZPN3VTeklQYUF6VXlmbmc0RmdXOXpseW5Cd1FTdnBLNS1nQmoxbGNOQjEwWkp2RThUQUZLUlUyYVJwVnhKUFpzV1RPUkZwUDJHYTlpSnltdFNUaXlwT1cwMUpRVnFiVVhLcHFmczVMRUNmV19vbUZPWlg1SllsSTAzQm5HeG05X0NXWk1UVjlDQTd2NUlzaExVU2tLTlpYaHIzM2ZLLXpEQndfQmM4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZDNwUmkxbGNOdFpTdEFhaWNxa2Vmb2ZfcFZHZjBnZVc4OEZxRlkwN2hnTDlKQ2RqdW5VUEdLRm5na2dQeF9BSlZuRW5wTmlGNTBmQk0zeHlRbEZCVjh0bWJNU1dYWlZOSU9IT3ZWQmYzb0MwVVRYdXM1NHhnc0R6eXZnMWxKN190MU9DWGNnZUtJZ2l4YTdhdU42UTdZWHN6ODZLd3BZVXNPcE15YkZZQ0t4ZXpRVFo2?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>7</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>46055.50324074074</v>
       </c>
     </row>
     <row r="15">
@@ -899,24 +851,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Price of consumer goods could surge as shipping costs soar, industry body says - The Guardian</t>
+          <t>Tribunal upholds FCA sanctions against Banque Havilland but slashes fine - Funds Europe</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 13:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 16:07:30 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNM2ZMdGRNWlRFaVVqVHg2Q0Q3X0c1Um5uRFEzRnJselR5czM5OXJZdHdCOVpnUGxtbXo3VUlTekowNkZMaEgyeEtBeDVDUEZfSXhyZG80NlQ4bFp1cnFwTVdCdURyRnk5Zzc0N2doM1BqSFBIY25Jb2dMdUhCclVTZV93XzNsQm9VN1R3VFY3ejB6eVQ4M1ZGRmI4SV9FdEhCcXI0VEdIQVAzVjV6bHBDdmNwZzlzd2c5OVpuNmVaa09vWmdFcjBKQkJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNZGpzd005RFUtY0tMaWRyWV9PdU1MWkJreDRKZ21lbi1yTUItSGItRXE5VDJLNURDQUNqUGpoTEVaaGtiWVMxUjJ0VV9NZFJha0s3aFdjOXlweUR5ckxlR29mUExKUzVydEU4VmJBMWtJb0E4eTdfbXBUYmFobzdHdDgtanp3R2gtZU9mUHdXMlZqdlpVNWRfZHU0ZUZEWGM?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>7</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>46054.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -932,24 +881,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China cuts tariffs on Scotch whisky - The Drinks Business</t>
+          <t>Fortinet: How to Build a Secure Digital Supply Chain - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:56:37 GMT</t>
+          <t>Tue, 03 Feb 2026 21:08:30 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPblMwMm5fMVJQejYzOWRYQ1BWWDhud0tfeTlIdnEzUEZYanRMbWdhQlhVNnprRGs0SVdjNjJtb2p4SUN1emU2ZnZBdl9HTVV6aFFvSUV4bWtsYTVnWjMyNzM3N0xQcVRWelpObUVQb0tUaE0tdkR5SGduMGhXWnpZWWF6SXU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNUmVQOFVwRTZ6MmdWTE5JdVhZZ1lWQV9hWHdDR3FTbzFWWEs2X1JOMDNzMjdfQkNpNndFQ0psSmVMbS1CNENOQXllbUk2MGJDUjRxVVpYb1lWdUZMcVVwdDFSalpLRVVXVklmUm9xTDJ6TXlpdTJ3MXRrSjdObnpseXRDWXo?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>7</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>46055.4559837963</v>
       </c>
     </row>
     <row r="17">
@@ -965,24 +911,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NPA host Agricultural Supply Chain Adjudicator in Lincolnshire - National Pig Association</t>
+          <t>Canada faces ICSID claim over Russia sanctions - Global Arbitration Review</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:49:27 GMT</t>
+          <t>Tue, 03 Feb 2026 22:09:45 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQOFBxVjc5ZFRKY2h4WHFMcmhnbWVBckZHNlpfVk9PVUhhREtMUldwMzd6c1hJUnZPZVRRRklRa1hHek14SHVvWGo0YmdVM1hxQ2g4cWFoNVo0Q2tRc0FUeUNsSnFFc3hXcnRqU2oxMTB4RmU4QkVWSFIxN2kyWjFhLVhPQk4xS3Q2Qk0wd1hXeVFxN1ZLVkxBbmhvVHZFTzJxV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPSzRidXRjaDhZbF9wQmxWYkhYMEJkZlQxRkd6bUIxWHI1dEtZWFhNb29DR0c0VmFKaWo4Tm1tQy1uczAyMlV3YXJfVEc1c3FidXZKWGVwdGpCWlphUThEcUJ1cUZ5a2RBT1FfQ3pmeGtVbVhqUUNENDcwa25rN2NJUXRYZi1hWUNfQm9yUHNKZU83d1p4?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>7</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>46055.45100694444</v>
       </c>
     </row>
     <row r="18">
@@ -998,24 +941,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbia Group appoints Prevention at Sea as compliance partner and rolls out MORSE platform across the fleet - shipmanagementinternational.com</t>
+          <t>Op Chirk: Over thirty arrested in Swansea and Neath Port Talbot - south-wales.police.uk</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:34:37 GMT</t>
+          <t>Tue, 03 Feb 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxObWwwd0JPOVh6Rkp0cmFwckNxZ25TSThzZWtyS0N1dkRGOUV2ODBpUl82djNtZDROVVlmYUNibnpRUW5Cb2pvYnBWRGlLZk1xb2p6YVVqNXdsSWRRRTBFdDdPMWNpZ3JERDlvQzBkQy1qYU0tb2Q0MjQxcm9XZUlpdTc5aWR0OUxnbWV5QS13VDNxdkRMZ00wWm8wVlJENTBRdmZBR0k2dlVnSmNiRnVmZHFzRVktaTNXaU9FZWZ5YkthVHFkUndmWERXdFFYWjk3WU8zUXVFM2NPSlU2OWdDU2FLYXk3Y3NaekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOeHByb0hvOHcySzBpb2liZl9zeUZGdmJLMTl2d0NIRnRYdnhpelNmV0Y5Y2NYS0VBQ1RhMXBrNFVTMXBqZTVaYUExb0pqR3h2NDZuSjFrRDlTZ0lZVmNpSVVlWWhieHFNVGU2em5tbU1QajBONmVQYzROdHFDR2ktWmxfbkZhemFEbFNzbGJzeTlZRzBnOUJiT1dFLUI0YVRLTjlha0xxcmROblpLOW9zT1NxSF9SQjQ1Vm5PWEIya3YwVGd6OHFHZU5ocFRXdw?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>7</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>46055.44070601852</v>
       </c>
     </row>
     <row r="19">
@@ -1031,24 +971,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The North East’s Green Super Port: 18 months on, the opportunity remains vast - North East Bylines</t>
+          <t>What channel is Port Vale v AFC Wimbledon League One match on? TV coverage, live stream and kick-off time - Radio Times</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:12:00 GMT</t>
+          <t>Tue, 03 Feb 2026 14:50:13 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOamgxNERESWJlUy11VUpyMHBVazQzM0tMUXpNRzY3UTk5bXBoV0x2bVZUMkxaUFl1YUFrS3NldGFfY2xuNy1jcjB0amc2UFR0cGlqWWlyQTFpVEVadkY4akJuU2FTeEF1M0FfMXgxejlrbVJvZDhpVFZEcVlVY1N4MFpBaGZnMm5ObmtxemxDWk41V0h4STExZ00wbEhuVWtJQkpha0pHLTI1VG9EdG5wXzBqbm5zY3E4dmpzbUlRekY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNQm45aDF4R01VeW1FTDdRbS1Wb3pTWC1UcUNKdF94aHlWSU83ZEFtcjJKakRudkV6MnBtWEhCTmVCb2UxUkxBa0d1UXlUM2RReVNjNUZwQlZsRnJTaklMdE9tblBCVjB0QlFUODVwWjl2c0lWMWhVQ1hwNERwd1g2VDd3YUYtalk3UGpkeUJ5UExtNE52QmpQR19rZGo?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>7</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>46055.34166666667</v>
       </c>
     </row>
     <row r="20">
@@ -1064,24 +1001,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rising US tariffs: Turbulence and new take-offs - Air Cargo Week</t>
+          <t>Deadline extended for 2026 Everywoman in Transport &amp; Logistics Awards - Fleet News</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:55:45 GMT</t>
+          <t>Tue, 03 Feb 2026 13:05:44 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE8xMHdSSE5PUlNZdE81eU1NcXhLNGluQ2x6VlQ0NnFKdUszZzNmOXV6RUl4ZW8xOWZTVHdMLWUzWVdkVmtmc3RrVTlGaUtnZ0tVR2hRRHhLNWxQQjhyRVJiT2FNOV9aUm5DR0VIbmQwTm5lVzBiR3lUeUpkMnE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOSVk5MHZuNTRobjd2dWdXd2NtNFREXzcwbk9reklJRnRBNnp5RDBVUElzUnpFRTU0ZDF5aGp5WVktUmY0d2V5NlYzZmpqb0JjS05HQjZTRk05ZjhjczhDSXdjTHllR3pteWZXU2ljaHZQdUNDamFvV3ZKdHlyS2JROU5sZ1A0S2dmRVFVVEZUQzNySTNmaklIaDdRUllkN21FbEp4cHBxbw?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>7</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>46055.53871527778</v>
       </c>
     </row>
     <row r="21">
@@ -1097,24 +1031,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mapletree on how European logistics is gaining momentum - Private Equity Real Estate | PERE</t>
+          <t>Report: Late Maycock winner seals three points at Port Vale - AFC Wimbledon</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 02:02:52 GMT</t>
+          <t>Tue, 03 Feb 2026 17:06:53 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQbF9UQXJKSXljNU5GeW9JZmpVZ0ZobUNnTFF5bVFxanRIam4xX2lNMENFeTVJT1Z2WHF1bXI3WHphYXhfd0VQNWx1Z25UVy1WNkFKY0ZmY3hfYTAyYVhJanRnSW44M09CZ2lOcmRIc2czTnY2OVc3UlhFWjc5VGtSYng4QzNxbExj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQWklEWlZuQmxKQjdwbndIRS1peE8tdEJDVkRqZVZkWWNmUUFPSGUybDNsRFRnSEVpTFhYeVpJZUxSQk5LM2hucnRwUFdnNE9sVlJjOUZpQmRsVmRrbENUR0FpX2hCbFRuZ3NMWnJGT2xocjhzX0ZGMGJXMnhmclc2bXdWY0tjd3E4NDFYeTF1TmpFRkh4VktSMUVzOWdBNzljUHI1WTFZcHpGVkdpRzA5dWItZU91TDQ?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>7</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>46055.08532407408</v>
       </c>
     </row>
     <row r="22">
@@ -1130,24 +1061,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>India raises spending and chip investment to head off Donald Trump’s tariffs - Financial Times</t>
+          <t>How The Old Dominion Freight Line ODFL Story Is Shifting As Analysts Rework Expectations - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 11:25:58 GMT</t>
+          <t>Wed, 04 Feb 2026 05:12:00 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBwc3VNWF95ajl5S09iRmxiSnU4TjdWQmtMaGJXNTY0SjJTOHp5bHlzNTUxcnVTWHJNUVZXdVQwc0plVUVRZV9Kejk2ajFHNnRFQ1JWbFYxWWhfMmJoS29fN3cxTUtLNDhMUTdWb3dmZ2o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOeC1zTXRDb1BBSElUMzhrNVEwSWZzemI3S2Vwd2NmaTNZSHk5cGc0NDh2UXR3M0I0WUdwZzBOOWY5eWxUdGFQc0gxX1F6ZmxVeTdlRU9sRC1nSVdXRlp2NWpXcmd0cWRBaHNPUVlsRG5WTkxvNEJreW42VHZYY1VhSE1lOHhSUQ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>7</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>46054.47636574074</v>
       </c>
     </row>
     <row r="23">
@@ -1163,24 +1091,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Apollo appoints Valor as asset manager for logistics portfolio - Logistics Manager</t>
+          <t>Hope and uncertainty as India and US strike long-delayed trade deal - BBC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:21:00 GMT</t>
+          <t>Tue, 03 Feb 2026 06:29:43 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOUUx3a255dUZramdIYndNZmxSMGkwVS1fSy12dW5FWUY5d1ltV0RGbF9jRjdBdldRVXA5RW1SVm9sWUF3emNaYW5QLU1hOWpfZlluX2dPZkxGQTZGdHMwVEJ1LW9WeWk1dHlZOHhsWkk3bTI1alhXRjkzUmlZdDJlaE56R1hrX2FHQ2VXTll2N3BzOElsSTk4alhrZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBoRHZ3eDU2UERBbkZfcHFSSFdicTdPTFdCM2pMQjJORmV6TGFhT3poR2hzamVwN1V1QlF4UDIwMTFDT0gwZUJwb2EyX05Kd1VINnhEdU9fVDIyZw?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>7</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>46055.43125</v>
       </c>
     </row>
     <row r="24">
@@ -1196,24 +1121,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Clarion acquires Mountpark Chartres 2 - Logistics Manager</t>
+          <t>Andre Gray is a Valiant! - Port Vale</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:31:48 GMT</t>
+          <t>Tue, 03 Feb 2026 08:36:50 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9tY2V5UFFHU0pfb0hCa25JNHk5S0JWbXZadk5kU1ZKSWV3QzQtN05HRk5CeHBVeHpQYTdFSVR3UVVIcGVzczJxR2ZEa1dlWjlXcFNaT1E2enVuM0UyUldUai1iU25xSk1PT2NqLUFNWUpUTzI2a043ZHdSYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBmTTI3Q01qcGdCYjR1Qklwa3JNNTNNUlJ0c0VNeGhQMTdVVmVYbGg0aEgxT0x2VDdlcnNLOEYtMDg0THU4MHlCcmRObDNfcnhabjJBTXQzNFdqVm5wWnNfUA?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>7</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>46055.43875</v>
       </c>
     </row>
     <row r="25">
@@ -1229,24 +1151,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wallenius Wilhelmsen starts operating car terminal at Port of Gothenburg - Logistics Manager</t>
+          <t>What do EVITA Trials Mean for DP World's Decarbonisation? - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:24:18 GMT</t>
+          <t>Tue, 03 Feb 2026 20:36:12 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOMzBjYXdWRGJ3QUN4QlgxWjJUeWUtVUxVSzhFbnRDOThwWFRySkJIZjNqUzNMRENVU0gxMzFlVUZqM1Y1dFFJQW9nbTlBQzdxVFdjazJ3XzdxWmgyZEVnblF5NnpscTZueVpuVnotU0Q0aUZTUW81aUM3dkFBSVNSMlMxQnduRUJZekxISnFmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9tRW4wWlhVWlQwdzRYcUpRdS1OSkwtUWh5VFBiN3F3cURlU1BiTjliMFFUVWx1eG5jclBKSE5Ibk1GRFZEaks2VGd0VVdaLXRzeUNleGRqMWZTbUJfcDZxQUp3WjA1a1pVd2lKSjlwSG1CM3lJSWpFVk80Snhadw?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>7</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>46055.391875</v>
       </c>
     </row>
     <row r="26">
@@ -1262,24 +1181,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Why AI-native execution is the next step for supply chains - Logistics Manager</t>
+          <t>Will Cheaper LNG Reshape Europe's Supply Chain Strategy? - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:00:55 GMT</t>
+          <t>Tue, 03 Feb 2026 16:59:23 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOSVEzSlZlTWE4QV9yZlM4QzVlN2pheHJsSjhVSlowVDJUUk9jaGRGT2psZ29OTUdpSENLNkE0VFQ4NjNvdFU4SjFlbXA2WU01M241WEhpMFBTSkxPSmJxTkxHU1pFN3A5SjJ2OEdvNHZRZV91RkZ3bjdDOUYyX2NyLUVaR3NDY3R0UjdtOWlPTDBROFZFZWVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSTFGNkZPaGZVMXlYWFh3NEw0UXdvaWhGMWZ6UjJkdFM0bll1Tmd1OEZ4Y094NDdMLUt2dGdHQVdCY0s4WkFaREVZS2JSdzcxTmNLSHNPNEFidW4wWWhoU3djVXF3WnNaU2k4MjNvYVdLRWZoUjdGdURlSDNzY3NMZFhpVENXem8zUjlCSFl3?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>7</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>46055.37563657408</v>
       </c>
     </row>
     <row r="27">
@@ -1295,24 +1211,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What are tariffs, how do they work and why is Trump using them? - BBC</t>
+          <t>DNB shipping loan book rises in fourth quarter - Tradewinds News</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 10:32:09 GMT</t>
+          <t>Wed, 04 Feb 2026 07:06:25 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBweHdveUp5S2F0aGJwSEs2U2lOMkF6NzRNZTd3bEJUdTQwVjhRX0pjZmFzZ25hRzk4MHE0WW9KVkEtUjIxRUNWbXRzX3pmd1A5UWhyaE5Ja1ZWd9IBX0FVX3lxTE82Y0Q0dVVkNUhXb1o4Tkt6V1AycjA1dmkzbUs3d3JydDktMVNrSnNsNDI1Zk9BdmpMc1BQbGJneThSUDBmUkdUdFhDVTZaTTRGaGlwdDhnR3NPeXhDYW9F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQajdGNldSRzk1V2E1cHVXM3J5NmdVRU9zcFp1NkRxdHYxQ3czUzVpZHY3RmhsNWh3aHZibUcxaGt6Y200c205QXJUUmZDUHhvNU1wN1ZjUXliQnZ4dm5DMV8zaGFQenlyV29PYzF6djJ2NzZjY2YwWTE1RzFXUHN4d29HTERSU3Y4UkZzMkQxeENtVEJsYk83aU9LcjZlZw?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>7</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>46049.43899305556</v>
       </c>
     </row>
     <row r="28">
@@ -1328,24 +1241,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>General Mills: Future-Proofing Sweet Corn Supply Chains - Supply Chain Digital Magazine</t>
+          <t>Sumsub Partners with Fireblocks to Ensure Travel Rule Compliance - Finovate</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:36:53 GMT</t>
+          <t>Tue, 03 Feb 2026 22:27:00 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPSDNHaERCRzBmS2xTYWNEMUQ3UVdfejZycGRHcExYWHVOZm5LSllMVUE0ZElpcEhkd2czakpfbU5BbnowTFFKN1gyZzBZbkVxdWpVVVEzSFU3UFVfUUNnbERBTUF3VmM3Y2oxMG9KLUp5OUtHQU50alNTTmFCQ0ExVXBfcTNiSDR2eHM1X0JZbXFpQ3dN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQOUtVbXppa0hOcUhPTmR4Nm5RWDJtdWRaVnNyTERVdjkwT0NnRE9ObDl5aWRtQnhIZ1JxaG4tOUhPMFhrLXg3d21Ga1pZaE80SVZXdEl0MHViYUNiLXVCYTM5U2pDSmxUOFFad01yZkstSTA0S2Y4czEwSGx3dEQxT3Z3aFRiVGlQcWZxd3lnUQ?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>7</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>46055.44228009259</v>
       </c>
     </row>
     <row r="29">
@@ -1361,24 +1271,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China lifts sanctions on MPs and peers, as Starmer says he hopes Xi will visit UK - BBC</t>
+          <t>Stiffening European sanctions against the Russian oil trade - Brookings</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 13:51:49 GMT</t>
+          <t>Tue, 03 Feb 2026 16:57:39 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5lS2o5QUFSdzNFRFdORmdsd2hKMllEOUVhQ0MwUlp3eHEwSXR1UXlMXzlYZzRvOC1pcTJqSzV3amhQbFl1QU9ETzRWcGxIZy00SWRJVUxuMVRsUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQWlNPcHQ3bkY1alBCeDF6V2FKTzgyZlY5dVNiZjdja2Fnb0RoZThSUHpDaDRKRVQxaTY1U0pKbWU2UHBCU2NnQXd1NVFWRHpmQ1JpWTdhb0w5RVJLN0VPMGFJRU5xclhVaEt3OUNuY1hzRk50bDlXMmVIZ0VTWHAwM2I0Z1ZwM2hIaGl3OEJsUlJVLUVoekhuNl8wYw?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>7</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>46052.57765046296</v>
       </c>
     </row>
     <row r="30">
@@ -1394,24 +1301,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cargo outlook cools in 2026 as supply chain pressures persist - Air Cargo Week</t>
+          <t>P&amp;O Cruises says port fee commission shift brings it 'in line with industry practice' - Travel Weekly - Home</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:42:00 GMT</t>
+          <t>Tue, 03 Feb 2026 15:39:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPdEo1Y2NzWUg1YW5pbXZqSUFfSC1WX3NCdTIwOS1HUnBCR01XNGIzVmJoZ1hMMWhydnhTeW1JRC01RFZEY2RoMGFHOGV0SmZDVF9IUW5kSGNYRXJsLUVGc05YSW1BYVY0bHktT0NTRGI4QWpxTFZNbXplaEtvT09veUFMT1phTDBXSmw1TExhMGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRjA0bjhCMDZERDZCSjBzNWc5N2dHWFN0eFI0b2ZVcm5fZE9sOU5PWWpnOFJYQjJqdUZEZGU2ZGtzWE9jWFhPdFpRa2lHa0RPVE9OdTNiR1FqNjdLVl9MaVZxb0dCQW95dmN5QVFKVk9Mdkd5MmNXNGs5dkFRWXJlVklkQS0teFpQTWd3dFhDUWpqa3UyLVFIVE9JS0JuM0l0OXNhejF3YjhnaXNJN205Tlg0ZXo?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>7</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>46055.4875</v>
       </c>
     </row>
     <row r="31">
@@ -1427,24 +1331,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gold in the age of sanctions: How the Russia-Ukraine war reshaped the global bullion market - New Eastern Europe</t>
+          <t>DP World's EVITA Trial: Decarbonising Logistics with Trucks - Sustainability Magazine</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:49:35 GMT</t>
+          <t>Tue, 03 Feb 2026 17:38:03 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNRTNnYlFDLVFLdGtpM3pQR0d6TEtJczFsRlZrVEVZa0pKcnBuZXVuNGU4X2Q3a0hackJvYnExOTFfZzFXVTJRcGdRakVoUEV5RGpCNk5zalpUNjRSSXNhTmd4aWd2RTBiTWk3YUpXbVpMZW5GanZaRlJqYWJmbHpmemItZEdvbWhfaHhISmFxNVZRWkxXeEdYMkU3YWlxUDlZRG9FNGJ5WEhDdTd2U25VY3p1djFkazU4aXFYdmQ0d1BabFRHOUxTZlBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNSjF0OVBpMWVsWkFoUDZwdUhIYk9HWmVlUmM0ZHgzTnlqQWdCc1BYWi1aaDd3MW16cUpsVXc3RnMxdkJSMEprcEpTbUpzVzdyZFdIOHVySmVrZzE3My0tMlkySHU5Ym80SWhGRGlTTTFZVmdSeHYtcFdNOFZHeHd6SE01LXI2cFRuX1FtemxwMA?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>7</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>46055.53443287037</v>
       </c>
     </row>
     <row r="32">
@@ -1460,24 +1361,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>How AMP8 digital compliance is shaping the water industry - Water Magazine</t>
+          <t>WADA provides update on the compliance status of the Comité National Lutte Antidopage de Côte d'Ivoire - World Anti Doping Agency</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 05:05:04 GMT</t>
+          <t>Tue, 03 Feb 2026 19:28:29 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNT2RfQVZPS1FHeHRURDhWalhPQU43d0RkOGFTTzRxd19BclVwRGtQMlJfUFB5TW5fY294SG13ajVWand6S2Z6a2FCaHFNcTFrQVNJQ0xIbWFOdkRhN2cxbGJ3aVRmVi1tNWt3WUxqUkxuUS1pYk8tWFh6N2ctbXlEYVRQUWd2SFhVNXZiMFVlclgzdkZUU2ZLSEpjdmpuVXpZV2dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNRG1BOFVWVGdHVHZVY3AyUTNIejFZTm1ORUlyWFRIdUhmTmZvc19TTTZVS3B5RDJ3X3VDb095ZWRvMXBjWF9FWmhQUEI3LW1hTkUyN1NjS0ZWYjdXRlZHaU5ialNodkxJUGUwMmhCLVhySTY0MkFrQi1aM21UaFpaRS1mZGNCQy13aVB4ZTVleFlyZVZpdGN5U1E2eHpCTE5sWWhEM2JPYWQ4V0x2R1dVZFNhZ1ZKY0FrLUYzWg?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>7</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>46055.21185185185</v>
       </c>
     </row>
     <row r="33">
@@ -1493,24 +1391,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EU ready to impose sanctions on Kyrgyzstan — report - Eurasianet</t>
+          <t>The Myth That Foreigners Pay Our Tariffs - The Daily Economy</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:56:19 GMT</t>
+          <t>Tue, 03 Feb 2026 11:31:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBWb0tFRFFEc3BtZVhkUV94MWt2MUVzcGNMYmp3eGZHSmk4QmlyTC01U1VjU1JCQU9aM2dsVmMwYzMza1NfRmdHaEJKaGZiOXozMXM5bXVtRVJwb3JmbVhBaF9rRnQ3eTVLQ2lNUVgzcjB2NEI2U3dDX1VXazI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOSWNTSWVzOWxGeHJfTGkyaTgxcy03dEM3VTJMZ2g2d1F2ckZGQkwwSlJ4NXBHcHZvWHZFaUwxM0hyZC16X3ZYSVdoU3hNX1gxMkUxa1NqRFo1X3YzMFVmUEhpMC1jOTVjZnJobUw3dUxPcUpoLWNGN0lfUWZTMGg0S010Yw?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>7</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>46055.4141087963</v>
       </c>
     </row>
     <row r="34">
@@ -1526,24 +1421,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Port of Tyne appoints new Direct of Innovation - porttechnology.org</t>
+          <t>CUBA: Oil sanctions will hit the poorest and weakest warn bishops | Aid to the Church in Need - Aid to the Church in Need</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:45:34 GMT</t>
+          <t>Tue, 03 Feb 2026 16:29:29 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNN05iX2doRUpwajRNSDFMVW1MUnU0d2VsOW1fbTdjR0V5Q1VkRzNHWlZwN1BkbV9SLXlYNF9ZNm1wb09YOUR0MU5jNXRTZHpnbWx0bkpsZWZfdTNiUDBOaW9CbWxxcWotZ3M4b2UtM0lseU1IdUpWaWpDaWpYTFRLeENqNjZhcEp4RzBj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQWlhkWkN4dzFMUjdOaU5FOURSaEpyQnBhQURFZjV2MmdtLXdUdVljaXRnOGloVnYxMm1iYTZrcG9xMlhKdXZrMVdyWHFiNGhlN3VlZDJvSFN6bHppNEc5OGVqRXlYX3dKckdoWVJtZjBVZ1dleTFOczB4MnNNWGl4TEU3eDByRXYzNF9IekFKRHhzdGpFcHF5dFJn?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>7</v>
-      </c>
-      <c r="G34" s="1" t="n">
-        <v>46055.48997685185</v>
       </c>
     </row>
     <row r="35">
@@ -1559,24 +1451,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Transport NorthLink warns of seven days of disruption as freight sailings cancelled - Shetland News</t>
+          <t>Massive Parkside regeneration scheme approved - business-live.co.uk</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:31:32 GMT</t>
+          <t>Wed, 04 Feb 2026 07:21:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNTUJsLUljdDNSNEx4SEFZWTc4TEFkaFFMZzg1ZUlJVEkyMGt0bXNIamlZcXlzSXk3YWVBMkZSZW1Na3hHaWxkVnRCNHVvVmlfV3RndkdxSGswaVcxVV9waWxCVlBTZmFQMlRrZ3R6UkphZHpycUdMQWpQYUpFaVZUU1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOLW1wZ2pQdDJPR0lRWWJBSTNzbDlOdXNNUGdxdE9Lc1FoczRNY0Frcl92TGxMQW4wOTdFSjNKMVhQQTBZcS1YZ3hfblZFTWdvd29Tb0xCdExUSXdiakRXYmp3VVJkcDIyWG1oTzFfSHpndlkyVDVCZ01VTFlBSjYwZ0pnRmRhVGVfd3FQQ3pPM01ybHd1TnhJX3BfdTdXZ9IBowFBVV95cUxOU3pxeEx5WTdVNmExVEhXeTQ4alNXYS1OUkNQWFJDUW8waVJQNVRTQ3hudjNNTUtubW5sMWtPVV9VbkQzN3o3X0dFelZveG5leVlkZm1YQkZjb2RoLUY0S19tR1k3SUdmUGZvck9ZNFlyU28xek5YQXlEZWRrSWJZNEtJdHVfeUlDSjc5OW44MDNJX1M1NTFKUTNHZnBkTjVOS1JV?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>7</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>46055.39689814814</v>
       </c>
     </row>
     <row r="36">
@@ -1592,24 +1481,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Health and Safety at Scale - Logistics Business</t>
+          <t>Two arrested over attempted sabotage of German naval vessels - BBC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:15:24 GMT</t>
+          <t>Tue, 03 Feb 2026 16:30:11 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQZVY5dHhMNlBKYnlkVmRxV1RlZ3hfdDV3T0FzQ1lTajZjaDAtSVV2RVlleUYxZWIxUDR2dXFhSEFtS1VGVy0yTnJQNVgtOERlNTJoWm5fVkFoaVJVajZiVXFhdS1WOFV2bFZKVl9IYjJkWURkWkxyWmxrM3BTQll2aHpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5vUVFxb0Q0Sm9Zdzh4NllUVW9VRllRSEZZVGlSNzZFbzlrUmgtWEpQYnpOeHZHSVZxbnBuNzNjWHU0ZDlpR3I2bzRkenNPMXU1X0ZhaFdFQ0MtZw?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>7</v>
-      </c>
-      <c r="G36" s="1" t="n">
-        <v>46055.46902777778</v>
       </c>
     </row>
     <row r="37">
@@ -1625,24 +1511,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>THIS WEEK: Russian sanctions, Ukrainian loan and US trade deal - EUobserver</t>
+          <t>CK Hutchison launches arbitration over Panama Canal ports contract ruling - Reuters</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 06:00:55 GMT</t>
+          <t>Wed, 04 Feb 2026 00:41:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPZ0RuX1EzcDI4OVJDVTRMbmJMdTRuR3I0X3lDX1NYX3NBcUZDdEZIckxMMDhnYTNDMjhJM3A5UDE0UVpIUnV6clFYWkNOS1J5V3p2a1JkUGt6X19xWE5kZXcxeDB4QlZpNHBVRlJ2TTQ1Vmd2UF9qV1VybEhuME1HdnNMd0pNOVQ5cHlsV2hOUzVVVm9STGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNZzBvWW5tSmtDbmZ5MG5RY0xNZ05lRHh0R1VLeF95VTVPbTNNQUhmcXQ1QjN4NEVYMGJra1pXcFZaR0FUYWNhSjNqMHg5TVJtc3RHak9WSldydkNpQ2Q0c0MzcVpMLWtYZk5PemlEZHZEalJqS2d1cUtOdzNqQkM4WWhad2FiNzVrMW80NmozT2lnaTJuSnM1M0twY3NnYU00UFJLWU1mdEg0VFdlRlNvbFBhdGp4bWNNRVBpR19MaGswaFU?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>7</v>
-      </c>
-      <c r="G37" s="1" t="n">
-        <v>46055.25063657408</v>
       </c>
     </row>
     <row r="38">
@@ -1658,24 +1541,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Net zero readiness in Hospitality, FMCG, Manufacturing, Logistics and Retail - theenergyst.com</t>
+          <t>Johnnie Jackson on Port Vale, Osman Foyo &amp; our supporters - AFC Wimbledon</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:46:56 GMT</t>
+          <t>Tue, 03 Feb 2026 11:23:13 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPcENJelBLS2dmNFotWm5CLVpnY2h1dFhPbTlGYkJNZlRVSnVhNHJBZDFNU3lOMVNxWDRHc2NSYVpzZENlcEJaclRYNTB4TGhSNEM3b2RKMlA3TWxtN3NtMzFKaTNxWVNHUlowaVBGaTFHWnpQTlRSLS1SLW5tdTVJYjV5WjFtQnRodlg1R2V5dnNMWTJnNWlqT1o2al9pVUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNV09XdFc4SjRBREhVS3E0SVN4elRlNlZacVVvU3hjRE5zTEVuUzllUm9tY29KanpoSHRkWEluLVNOMGRqX3NwTUE3WTRKazUyUVRDS1Bfd2VqNmtYSTZZdURUV1Z6ZU1LYlNUYTBOc1hKVTVqbndHSlFHZU5kUU5TSEdqTGQwRm1vYkFhTXM2RXlQOG11VjFVcWM3SkZvNzlzeHcybmlZOVpkX2p5WEhKTVNB?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>7</v>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>46055.44925925926</v>
       </c>
     </row>
     <row r="39">
@@ -1691,24 +1571,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lamb welfare measures will be an “added cost” to supply chain, says NFU - Meat Management</t>
+          <t>The Trump-Modi Trade Deal Won’t Magically Restore U.S.-India Trust - Carnegie Endowment for International Peace</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:56:09 GMT</t>
+          <t>Tue, 03 Feb 2026 21:24:07 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNYUVBWXIzNWlWWGRsbk1lVXE2RnVqMEtNbG9KR0YzbWlVTGJJNnpDaFN3YnRzMExRZlBESGxRem9mSXkxSEgySVpsSkxqM3pLSDFjNHdnckNmN2JtRGxFUWJYVTNYci00ZFdHbnE0bU5ZYUNVMmNGOEgxelc3cDJ4bXBVOGJGMlhOUlVhcGFWTkxLZjFUZU9wT2hOdk16Sl9XSmtpTkZYeXN6S0hDMVhSQzJrbW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQOXNLeDh5cmFqWjlfSUNmTEVwOTA5THBMSjRmcmc3TEoxN2lnaWk3Vk13WEFsWGZDTmlXLVB6OXZiMjVxYm90YVlNSnBNbGFUMm05V3l1VXJkeHlkTkdWNlh3bXA5bzVDZXNndEpqRmM0VkRVLWZUenVlN0dwVzFaQVlTcVRmUzJtUXItR2VhM0xKdG5yT0RUelJBeDNfd2c?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>7</v>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>46055.49732638889</v>
       </c>
     </row>
     <row r="40">
@@ -1724,24 +1601,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>The Compliance Inflection Point: Why Mid-Market US Insurers Are Feeling the Strain - Insurance Edge</t>
+          <t>Panama voids Hong Kong-based firm's canal port contracts - BBC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:02:57 GMT</t>
+          <t>Fri, 30 Jan 2026 09:49:26 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOemlwSW5xR0c5TXk5ZXJtak96NktuWmpaUFRYcDZKWl9XMlg3dmJPLVZwOFVWQ0VuNFFUSWVSMEViZjhOZEpWbTZieXNVWjVwUW9QTGpucmVfQ2xDck55NEhsSzFhc2ItbjNmQkYzdkh4UE0xV05QLVFjM3hvc3BfTUZ3OGZsc1huVmFDVnhVWUVqVWFUc3NRUHN1VVZtRUZlcFZBcW9yTk9XU0l1aDBqX1JkNWRBYnJweW91MQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBQZ1htcTZmXzA5YVBIUGJTQlpRRi11SXRLVUdBRFUxdkZwWnpQU1plZEhRVUNmV1BpS1BqTm1nd3VHM1Z1OG5hNDRxSDYzM2ZtR3FxUUtkYXpwNWti?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>7</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>46055.37704861111</v>
       </c>
     </row>
     <row r="41">
@@ -1757,24 +1631,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Verdion plans €69m Greater Copenhagen urban logistics facility - Green Street News</t>
+          <t>Around 100 flats on 'prime' Port Glasgow site to be demolished after delays - Yahoo News UK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 07:45:57 GMT</t>
+          <t>Wed, 04 Feb 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOWU1GQkF6aWxiaWs2RjVoWTliVE9UcDRBOTE1aWJENE82amxXQXlmcTFpMERCUlUzckluZzA0N2paT09VeWhtVTU4YlpNZkticm8wWWs3UzZ1Q1BRcXA5bzVQd0tJRGJzVHUxdmdhMW4yOE5XNm1vclU3UUIydkkxdG11VDZmVnk3ak1ZZzNBdTNTeXBQTjhwcC1QMV9sMXJX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE92WE44aFUzbURfbkF0d3Iwd0J3WUx1LXlRc3ZOenhTZ2xRVTlnTE12SXl3VlZKQnlQUUZ5VWttLUxzZlpjZjZhUDRGWGdOemZYQ1l3M0VKekNiZ216Nkg2Q2tvS0FiQTlyUXI0bU5HQzMwd0ZNQnNR?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>7</v>
-      </c>
-      <c r="G41" s="1" t="n">
-        <v>46055.32357638889</v>
       </c>
     </row>
     <row r="42">
@@ -1790,24 +1661,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Clarion Partners Europe acquires French logistics facility from Affinius - IPE Real Assets</t>
+          <t>Five critical compliance deadlines food and beverage businesses must prioritise - Lexology</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:33:47 GMT</t>
+          <t>Wed, 04 Feb 2026 03:31:22 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOS1g5VWhPM2VtR3lQSC1sVFRDNmhEVl9IdzYzWUw5QS1sVXgxZHhWc2o0bkR2WUtNTnlsUm45VnZiUV9ZVnlIeGdWbW1jbXhOYzViQlRxSEZtaHJoODQ1ZW96NHFHSWJtUGNqZC1xM1NVWnk4clcyT2VQSVhaRUtWRjdUQnlfWnZLOXM2dlFyaFNtWUQyYndCcDZTWHZXVnFLNWlRdV81NFdfWnUxcHVzMm1lb005R0FsM2g4aFJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd2lPX3RCV25scjFGMmNhcHRwUEU1VUVkeFFqNkJhQk10cU9aREI3U0VleFMxNi1lZnl0SEN6dDFpakRpZlFoV2hWcWZNM1phejBNSlpYcnpzOV9QZFFFTG52SWFLVEhGZFlzTWlKSVVXaWI4RV8yYjlxbnhXRmNoenZpelVIdGU0R2NWcENXRVZqcDdXd3k4Z1pxd3A1TmF3dmR1TllUTlpLREZjZHRPTWRFalJFV0E?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>7</v>
-      </c>
-      <c r="G42" s="1" t="n">
-        <v>46055.48179398148</v>
       </c>
     </row>
     <row r="43">
@@ -1823,24 +1691,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CEO of World’s Largest Container Shipping Company Says ‘No’ to Arctic Shipping - High North News</t>
+          <t>AD Ports Group secures $115m financing for terminal development in Egypt - Baird Maritime</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:50:10 GMT</t>
+          <t>Wed, 04 Feb 2026 05:20:30 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQU1ZCNTRWdUhWN2VyUzZQbmlwSDFFNFlwckhWWVhMazdIR1lFQmhieUxBYjJzLWFUTmdsRkVXdFdndXlVWWtoSDNTUjFhUHBQMmQ0a2RVcVhwR0VmM0tpN1ZVTVlWNE5tV1RHVEZmdjNXa3JqQ3lRbmdOVnFGNndTM1FuX1lnU2p1alBuVTBxT1ppSmwtT2NUX1NETk1PVVN6M3dlSlFLNnMwdGVqWFU0elQxYWc4Z3lWVGVCQm9WQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPMFZzd3VmSldrcTZ4aHlicmtXOGR2QnN1dHhxSGVYcUZrV2hSdXBoMmdHWUxZTXlSU2djZzRVTTQyODZtY3JIN0FEckFtd3dsSzBjbHhuMTlfUl9tQUxOYjZNS1ZPaWJsSXExQUJaVlltYTl5QzJBTVRLSEF4TVVCV2JnMDREWlI5T0xDVjd2SE5aeUVObTZRSXdKZDBkdmYxSTJ5bXNhdWpYYWc0UEszb0dDamhvZWPSAcQBQVVfeXFMT3U1djFaZS0xbE12cU9rN3lPUHdnWXdyRlBqWkltRXpkY2NzWHY2WlZQeW4wWVFjQktqbm5PZlRSamJPZWpXVHZYZkFXUERZN1psaUJ1dGJ0STM5SGxLOWkwNkVnMEt3dGE1bVVmR2RLMW9MbGRBVnFSTEplcjNIQjk1V1B0bm5LV3AtX3B1N2o4OWpkbE01eWs5OVNNNTMzRWJZMVJ3QjdOWnlCQ0RqV2pCY2lzN2t3NXcwSmJBQzB4VWN4Zg?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>7</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>46055.45150462963</v>
       </c>
     </row>
     <row r="44">
@@ -1856,24 +1721,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Skarv Shipping AS selects Oceanly Performance Plus to support automated data integration and digital fleet operations - shipmanagementinternational.com</t>
+          <t>GXO Logistics (GXO) Expected to Beat Earnings Estimates: Should You Buy? - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:34:37 GMT</t>
+          <t>Tue, 03 Feb 2026 15:00:06 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQM2RvOWNMZ0JQblZOSjV3NHN3eldnckFLNldOaVc2cmU2YXRvakdmM2NhSlFXVmpmVnN3MFdrUjJqMGJxaWlXZFM4YVBPY2xBeXVETmVJYm9aMFNJdklfNmlkclNSbjc4X1BxcGluM1NVel9PN3R5VGNQVWJYVWw5T3ZfbjdhQ0UzdFI4QjFOOUs1M0JfNkY5cXVFN2hCNExaMTVBZG5XaW1rQ29MUG5waGdfQUs2OTV3TE9wVmdBeXN1VTUxSnd6NnNPOXBwYlNJS1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOMGZacEpxT1BRYVZZWHJhZVAyMFFqSEhqOUJEQlAwcTcwRXVETm9tQmpsZG1XaGZyMV9TQ0dZREV2VF92VWc0OHJqMVJBRllRODZlTzlIS2hkdzVoZURjS2Z3T0ItNVBCaU4wNHE1eTRidGd6SVZMLWlJb1BpMHZjbUNPU3NwOWc?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>7</v>
-      </c>
-      <c r="G44" s="1" t="n">
-        <v>46055.44070601852</v>
       </c>
     </row>
     <row r="45">
@@ -1889,24 +1751,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Panama voids Hong Kong-based firm's canal port contracts - BBC</t>
+          <t>HighBrook agrees recap of €300m Dutch logistics portfolio - Green Street News</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 13:16:05 GMT</t>
+          <t>Tue, 03 Feb 2026 15:19:06 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAyUDB1T0FCcGI3eV94eS1sRmdVbU1nMk5RdGtydFBzWDJlSWFTRGJQRTltbmd2UG9ZcjJLTnppZFF3b1ZjSTJQM0xfZkRKZ05iNmc2YmRDUVkyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNi1ISjBfR0ozQWl0VGY0REZOUUU0Z0ZYQzRUeGZ6ZV9FSktlWjdwcVROMkRjQXI0Wmc0Q2xvYXRkd3BLck83cWZIWGVGOWxMWU40VENwb0w0R1Zpb1E4SHNtLThKa2dkOUVXRkRaMGJ3b24tU2huY05iWXlmSlNBVWg4LWtiRWdwcWg3U0ZEUkxnY1R6bDFLaTB3?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>7</v>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>46052.55283564814</v>
       </c>
     </row>
     <row r="46">
@@ -1922,24 +1781,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shipping investor J Lauritzen hires new head of research - Tradewinds News</t>
+          <t>What’s next: your complete guide to logistics trends for 2026 - Maersk</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:03:44 GMT</t>
+          <t>Tue, 03 Feb 2026 13:38:45 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPNFZvNVlOdXhWeEVPakxtRTVVVkppb1ZmUjJmRW5mcGNsWkM3OWhpNW1IQldqVmx0VE9WSVlvc2N0TmloNDhHUUlQVlpPN1hzaGx0dkE2dmhqVURaNjU2U3ZyR1l5cnlfcHBCRVRzY0tiZEF1b2x1MjZQYXVDa25GdkVhZmhBOXEzUllVMHU5d0I5Ynl6WkJleWZQQ2ZjYUlhWk5qSHZTd2hRdWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQX044eGlSSEpLTFJpbUdhdlVaaWlmS3BUaXI1VWpKMnU1MXNjMDlVRHZBXzJwOEwwSi00WUE0NnJMX21CbEp2b3RMVkd5WUNiX2N5U0xSUmJXVkR4SGhBb0V5Uzl2YTc5SnY0S3JjWXR6UHBYcDJuMkh0T1dpdDJXRWVEbEhfNXM2VEFGZ2NCMTRaZFNwOEpscno4T3VCWlltTUxRU3pwWnNvSzg?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>7</v>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>46055.46092592592</v>
       </c>
     </row>
     <row r="47">
@@ -1955,24 +1811,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Abuja Pushes for a Modern Logistics Architecture - Air Cargo Week</t>
+          <t>Haskoning acquires port planning and simulation experts - WorldCargo News</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:13:26 GMT</t>
+          <t>Wed, 04 Feb 2026 00:22:31 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1BZENaWFpKQldCdHo0UFpwTFZLdnBLYU5aZFc1TlhSaERkZGNrYVdXVk9KX0ppX0haX01lWUdRQjljV2pCVWFxamlnTmhpbWZTUGNyOGdRSUxWVTN4VlRUQXdYX3IxR2FIQkVrUHJoRzJQMXIxYTZNQTBwOV8wNGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQRklmQVJSd3dyaDFSRF9FWW5jQnYtcEdITW1QM0Q0RktiMTB3UDhwM19xbHNIS3RvOTlkN2dZX25rM01aTW5kRTRXZk9rdTdTaG1GdlhNeEhJWjlHLXM0S0h3ZFM3WUdPaUdRS2llcnZsd0RldDd0Q001R21OcW8taVBMaXVYQWIzVGRRNXZXX0RNT0pOVHBDYW1UNldkYW01T0E?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>7</v>
-      </c>
-      <c r="G47" s="1" t="n">
-        <v>46055.5093287037</v>
       </c>
     </row>
     <row r="48">
@@ -1988,189 +1841,171 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Leyton Orient 0-1 Port Vale - BBC</t>
+          <t>Devante Cole: Luton Town sign experienced Port Vale striker - BBC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sat, 31 Jan 2026 17:03:00 GMT</t>
+          <t>Sat, 31 Jan 2026 13:50:05 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBFZ2R2eks5N1NhX0pmT1JnTEZJQjhSbmJJMUR5Zi1McWV4eVNMSmJWMk4ybDQwRmhJeVlWWml4dGVMOEdSS1pWWWM2MVBkWS1YRFdNVDhGbkltZGlqN09mRXJpc0g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBQVGFONE02cXptWFNtVDR2T2JJTm04QzAxX3BMSC1kVHBvUnRjNk5SZVk1OHdjeVB3WXpjeWhJWjJRX2FpZXJ3Tm4xeDg5ZzlxSGZlZmNRX09JeDhXZnN4WGNzX1lzUFpFbmc?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>7</v>
-      </c>
-      <c r="G48" s="1" t="n">
-        <v>46053.71041666667</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Trump threatens tariffs on Canada planes and nations selling oil to Cuba - BBC</t>
+          <t>Police and Crime Commissioner censured for supporting anti-migrant protests - Searchlight Magazine</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 06:12:07 GMT</t>
+          <t>Tue, 03 Feb 2026 11:34:16 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB1WkVQc0puSWViS1UwYU43WVk1Wi1fcXZVa3hldVc5NE9kV1FZSjdjc0RfUUlieTZnVmJqWGxfcV8xR0pmWHU1dHR4UVRUV0hObkIxSkJQejIzUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQM2M4R2FWQzBlbHpIelJhMVpsQkE4V095dmNlMjFDNHMxOEd3V0g1RTM5SWotbE1IeEpNd1plOWNBSTZ6bWNiV2xzMy1KNjZJVlhoR2ZDSTVBMjJTS1I1NUhNWjhYcEh2RzRUak5nYllpT3lRTk5BMml3OWsyTHR2Rm5hTTJFdTc4X3NFTkJLU0U2bVZlU0NCcUhVU1otS3FxRWtreFE3VjF6d19LeGxRZ0kxUlhvSUU?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>7</v>
-      </c>
-      <c r="G49" s="1" t="n">
-        <v>46052.25841435185</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norwegian court rules sanctions against Russian fishing firm Norebo are valid - SeafoodSource</t>
+          <t>Children and police officers among at least 30 killed in Israeli strikes on Gaza - The Guardian</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:51:44 GMT</t>
+          <t>Sat, 31 Jan 2026 07:33:00 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQY3FfUTVqdHJrN0VGdXMtWjFmUE9UYWtLTzhabFlfLUw3OHRYMzlrZ1JOaWh6NC11LWxGSXk3QlZvb3lzVnBzNmlQVmdBNjZCeEsyeVV5VWNoUWR3dG5qNmNiNUFHeThrOEZkOUNtVGNEZjItTG1QT2xUN2VOYzJ0Vk1kQ2VpMGFqUF9DZTh6bUZhU1NzSVhTdkR4a3NNNFhEYkNEUnNPbW5nc3pvQ3FoRXRpd1lqQ3M1QXdIRUZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPYzV0Y0xxR2lTSU85dzc3TW1wYkVJSzhzQzY3bGRLQ1hsVXpZR0tOeHR5Y2cwRzhZZ3lRT1U1OHZIX3ZyUklUQjE5bllRSF9BWENDMVJ4WDhudTJBTXZYeTlqUmtjbDhkT2N3Y0RvZ19WSkxRckdTWXFQSGw4NE1LNm1UNUVNai1jS3FsRERaeEh5NURYN1E?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>7</v>
-      </c>
-      <c r="G50" s="1" t="n">
-        <v>46055.45259259259</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>APMT open to temporary operation of Panama ports - porttechnology.org</t>
+          <t>Iran police say 139 foreign nationals arrested over protests in Yazd - ایران اینترنشنال</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:55:34 GMT</t>
+          <t>Tue, 03 Feb 2026 10:11:32 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPYWNPVU9TXzUtb21BS2tJdEZPUkhfNFR5T29XRXBaX3llTkhwYVpQNFZPY0w3YUQ5NDktdVdPajNyc1F1Q1c2QTFOc1lqSlZpZWs2c1N2YmpDU1lTT3ZUeENDWnVrcmxnaDI4SzM4NGNEMGdVQ2paV21jLXg2NHIyMzlEZkdSVzZLTUdLZmFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5OLVNjX1hqdFk0NllxYU5uSGN5TmRXTERJSDh1bktUeHZvNC1BaDBzWDVtaUhJbmlWX2Jpekl5WklaZzUzSkhBY1d6VXhmUU5acHc?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>7</v>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>46055.41358796296</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Trump tariffs live updates: EU, India seal trade deal in rebuff to Trump as he threatens S. Korea tariff boost - Yahoo Finance UK</t>
+          <t>Russia resumes strikes on freezing Ukrainian capital ahead of talks - France 24</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:42:00 GMT</t>
+          <t>Tue, 03 Feb 2026 09:46:52 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPRzdWMzRXR1F4eUlpNzNLeGw0QzdFTkRhOFVqLTlubG03MEFqaEtqcHI5U2Nudm9OSm5vUmt3emVGVGVwX3NzZndFUExDY3B6OTBuVE1rUVFsakhxLVZwUW5Gal9pWUZUc19KMnNSSVpocmhHMGo4T1k5SGczanc2WkFteV9hVTRLdUhoVFNNSHZDVERpS1RHejZPTXRFNGlkTUlzS0JHWWdva3FQRnZFQkFLZUVodWZFbVlpRW9ILTliRUwxdHJIcGZ2aFhFbzBtOXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN01uSVNackgwMjE1enhnOVdUWnJQOXZaYkJXQzBscXFaX0tmVkRrb0ZSNjhFTXR4NTJmOE0yQk5TNHZndHV1dkxyRldjZFlDNDhEbW5LMVNzcjdEOGg0VWVsbE5GOTVEZVV1VzZQSGdTLXZEMGREeWg4LUw1MnRIaDNMRjd1eG1BSUs5S2VORE1NTFVRVkI5bnlzZw?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>7</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>46049.69583333333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Crystal International unveils advanced logistics hub in China - Just Style</t>
+          <t>Update after police called to convenience store - Cambs Times</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:57:30 GMT</t>
+          <t>Mon, 02 Feb 2026 11:04:00 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBTLVJYX3pEcmhvNzAwR2tNVUZjQmJGbk54SVpwLVhxOGVrQ1A3NmtfY2NlTFY1Z0Jwdzd6QzhQN19QTnI5Y1h6N3RHUWZNczFDNlVCZXdaQVlSRXhsaTN5N0VSMjY3QUxtWWh3cDA1djRROVd2ME5nQWZjb2dUUVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxORnRnWW9xTkxDMVVISlZvNjZVS0RfZGhhLUU4RFBNZVNsbmExOEJZZHVBZ1IzelZXVl9nOGZFZGQwcTFfaE1YZjlUODVJWExsXzNiVm5DMnpQNGM4RHplZXZRZG5HMHNjaE1VY0VjOGdpd194cU1rUmMzQ3NXV0QyWXBoQkYzMEVVM1A2eFU3VlpkYTA?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>7</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>46055.45659722222</v>
       </c>
     </row>
     <row r="54">
@@ -2186,24 +2021,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Metropolitan Police strikes called off as workers accept new pay offer - Unite the Union</t>
+          <t>Police statement as flag-waving protesters march on Hanley - Stoke-on-Trent Live</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 09:40:32 GMT</t>
+          <t>Mon, 02 Feb 2026 17:36:17 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPZGZLQ1JjVFFWRWJFa01lWUhfRkhfOGd5M3Z6SGRuQUxPcmkwR1N1M3ZYSmxUdjMwRnByb3ViOG1fdGJuS2Uycm1DUDJsNmpFVjJNZEMyU2pyZ1NnREI3dUxVaEIwMk1pSTM4ak5ULXpYZnRtVzFqNEVnSHpPbWpWeFNrOGxfVlAydE9wLWxBTmU0WkY5WEdDeUJ2LUF0MjVnRTc0VWpGZi1SOTVQZ0o0bzRWVW5Ua1FZbjhIM29Sa3p5Q1ZIRE5oOFJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPT1otX0VCaWwyTFVjMkhPU0habVRyTlZTWl9mYzRJX1RvcUZoTTBFbmd2NENQNVJOcW5aajZkLVFRZlZpUVM2MERmUDFCOWp3bFdkX2lseWg3eHByak9HUmlnV29OSlViX1ByNnExQllBQXdXeHRzNU9hc3RlMEY0d3otTjhkTXc0czZ5QVpYckJhNHpCajV5NWJuNG15SEt5NkNuSGNwR23SAa4BQVVfeXFMT29GZ3RWV0xJczVuSG91dVpCS0dXREVJNG0wQUhkU21sYTY4MVItR2pocTdpMC1obWRKeENHNFdkazgyZnpVdzRvZFotcnRpb1lxWk4tbW1hdkxmZ2duTkUyTGcyN2pGWG5iRE9KclhHeVdUUzg0UVVyR1pha2lKdUlYMTViQmF4b1lfc0ZGMlVZNTdEU2NoQU5rb2N0M0p5dGZDVG1USzdCWXJhdmhn?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>7</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>46051.40314814815</v>
       </c>
     </row>
     <row r="55">
@@ -2219,24 +2051,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iranian police detain four unspecified foreigners over unrest - Yahoo News UK</t>
+          <t>Man arrested in connection with physical altercation during Buda high school student walkout, police say - KSAT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:28:46 GMT</t>
+          <t>Wed, 04 Feb 2026 04:41:03 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPekRjSmNra0R3WlRGV2hzZDRMWjNkWEJiNE9Jb1RfOWx2WG45cE15cGwxMXMzMm1FclVYeTlBeE1WQ2cyQkVVQ0kzSDkzUUR2TVhzM0psZEtyOUxVWUxhakllLXhEWXY2U2dJaDNmeF9pTWE0Z3pKMFJtaEhqOVJya0JIY0FBZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS1VuTHpOWGU3M3BEZTVzWU5LbDNILWEwWmJMbGFYdVVraVBMTUI5bXFBRXR6THdDUmd2SHhuQ0dVTTVXbnNQM2NyVnIyamtlMElvMHZJSTBfTnJ3cC05S1ZsMWVSeTY5TnRBSUJCYncwclhMOXdtYXQ1YTB2YVd4Z2R4TW1MNkoxOFpqNjdTdjdPVlpxVTFoM2xqeWtWb0RJZDZYWXdyTnZvUHU3cEN1R0hQaW5aX2NuVTktTXJ5T3BScjN1UWYxcTNtVzY2V3dxRTVlbHJ1SHhjQlNYdUdyXw?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>7</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>46055.47831018519</v>
       </c>
     </row>
     <row r="56">
@@ -2252,24 +2081,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Update after police called to convenience store - Cambs Times</t>
+          <t>Palestine Action Group plans march against Isaac Herzog’s visit despite protest restrictions - The Guardian</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:04:00 GMT</t>
+          <t>Tue, 03 Feb 2026 10:02:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxORnRnWW9xTkxDMVVISlZvNjZVS0RfZGhhLUU4RFBNZVNsbmExOEJZZHVBZ1IzelZXVl9nOGZFZGQwcTFfaE1YZjlUODVJWExsXzNiVm5DMnpQNGM4RHplZXZRZG5HMHNjaE1VY0VjOGdpd194cU1rUmMzQ3NXV0QyWXBoQkYzMEVVM1A2eFU3VlpkYTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPNlhyVnR2VUlxTWpRY2J5M3c4MkpZcGkzNk5iWG5Wajc5QmlvVDVEcDRwd2lVbTJpaFBjR051RERCNmd4dXhibWJtdmJQZjNNT05kMF9vWDRkM0V6X2Z1R0ZEb1ZIOGN5anI4NHFCM0ViQlN6N1BNbXFzZ2tMakZscFg2Y0xseXIwYWxLb0tnSGthaUl5dThmWklCSzdKMi03Y01EUnZn?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>7</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>46055.46111111111</v>
       </c>
     </row>
     <row r="57">
@@ -2285,24 +2111,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Another e-scooter taken into police possession - Fenland Citizen</t>
+          <t>Islamophobia in Europe: Dutch police assault on Muslim women sparks protests, highlights growing crisis - Muslim Network TV</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:33:00 GMT</t>
+          <t>Tue, 03 Feb 2026 15:14:40 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQY0xxNnhKTTZwdUtJdVZNZXBSQ0lwUlpxMDhCUWxhUFBFLXpUaDJMNmF2OW1YY2hWSTJ5Zm1Vbk9mcDl5UjZpWm1Jd1FPYW1mVk5sZV9xc3dlYktqRWlOQTFaUDBBU0JGMVhQZnRkSkMwYV9QWnpsY0RQU1VtRlhWWnJDb0o5WkIyWlZNcTVoTHZvM25keS1BRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNaDVlX294ZEx2MWpIaTc2RUtuM00xbXFNV2xBWWZhUmY5TmVjaXZiYXBXZ1kyQVFrMlNpNldFY0hiVmdrQXNlMnJkeUhnVkdEQWFINS1EdHhrOC1GTGVpeXBqb29MVDZqV2ZMS2xQT05ibFBYS0ZxNHRBWnFVOE5GLVJBaTlOVTdfM0xYaHdURVhYTGVKc2JFVzd2LVhqZGNiZE8xcnZNWlN0MlY2NkYtMWlWWU9CVmJHVkpadlpONHVLMGdYbWU1OFlPSQ?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>7</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>46055.48125</v>
       </c>
     </row>
     <row r="58">
@@ -2318,24 +2141,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Children and police officers among at least 30 killed in Israeli strikes on Gaza - The Guardian</t>
+          <t>NTUCB Cries Foul After Police Deny Protest Permit - Greater Belize Media</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sat, 31 Jan 2026 07:33:00 GMT</t>
+          <t>Wed, 04 Feb 2026 01:51:29 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPYzV0Y0xxR2lTSU85dzc3TW1wYkVJSzhzQzY3bGRLQ1hsVXpZR0tOeHR5Y2cwRzhZZ3lRT1U1OHZIX3ZyUklUQjE5bllRSF9BWENDMVJ4WDhudTJBTXZYeTlqUmtjbDhkT2N3Y0RvZ19WSkxRckdTWXFQSGw4NE1LNm1UNUVNai1jS3FsRERaeEh5NURYN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNMnZiTGxNZjVlM24tYnBTbEV3OC1oc3JvMEE3b1RvY1JTcTNkMEp5Q0xsc3R1MzAtRXZfWGZqb2hnZXRvWjVxVGZzc05kbUE1OXp4bFhWSE9IQmE2SHZvRlkwV2daUUFPTDlsRlcyT2RNUncwWjVkWGx3Nnl2enBFdHQyM2s0OFk?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>7</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>46053.31458333333</v>
       </c>
     </row>
     <row r="59">
@@ -2351,24 +2171,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sussex Police panel says it has "lost confidence" in PCC - BBC</t>
+          <t>Police probe launched after jewellery thieves strike at vulnerable Smethwick woman's home - Express &amp; Star</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 17:19:01 GMT</t>
+          <t>Mon, 02 Feb 2026 08:11:04 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5pSmI0TlhZN3pPMGxjaUIybEp3VUJQU1lWQ014Ykg1TEVCa1d5aGFLSDhlTHZzYXY1SHJLLWcxMGI2eEFlWlhwZnpGVnZYSFpfWFA3THYyWFJjZG5N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNSGdYOGR4YWRSQ0pFc0VxSUdoc3RNUkZ3bXRvdDBuVDBBWWhYLS0td1lPVmtDUWYwZGpqbVZ5RkxrMWQ4SkRqWHhBSkFjWll4QU11cnZKMEtRWTRmNi1xOWRsWTlnSmtkSXN6MVZRT2hCZHBnR2dlbmV1NzZBcWJ5SnJZcDJWNWtENVFkdVNKa2wyRTFkLVJRWDJTSHg2MlZUUDNWY0xOcFBuTkpWUUdRZG0xZzkyeGstTkdVMHF0UGo0UVlzYmNfdGQzMFVKNUtvMHF3UlpRSmJhR211YWFJQTdZVFFXSDJRU1lWNXQwQmxFQjNFMHk0VnFB?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>7</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>46052.72153935185</v>
       </c>
     </row>
     <row r="60">
@@ -2384,24 +2201,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Police probe launched after jewellery thieves strike at vulnerable Smethwick woman's home - Express &amp; Star</t>
+          <t>Russia pounds Ukrainian energy in diplomatic snub, Zelenskiy says - Reuters</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:11:04 GMT</t>
+          <t>Mon, 02 Feb 2026 23:23:20 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNSGdYOGR4YWRSQ0pFc0VxSUdoc3RNUkZ3bXRvdDBuVDBBWWhYLS0td1lPVmtDUWYwZGpqbVZ5RkxrMWQ4SkRqWHhBSkFjWll4QU11cnZKMEtRWTRmNi1xOWRsWTlnSmtkSXN6MVZRT2hCZHBnR2dlbmV1NzZBcWJ5SnJZcDJWNWtENVFkdVNKa2wyRTFkLVJRWDJTSHg2MlZUUDNWY0xOcFBuTkpWUUdRZG0xZzkyeGstTkdVMHF0UGo0UVlzYmNfdGQzMFVKNUtvMHF3UlpRSmJhR211YWFJQTdZVFFXSDJRU1lWNXQwQmxFQjNFMHk0VnFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVlBuNklvRHU5MVg4THZMa2VRMmlRZVpEb2FmX0pNNlJCNXNHbS1CWW5NaG5pbUNLZG05ZDlhcHgwQUV4Tm1mbXVuV2cyaXp5ZGZyNnJkeEJPdC0xR0NYYU8tOWVTX3NXSmNPUHhWSEg2dWlDZEFEYWhCOGdPdWFsMlM1SXYxU1Q1NlhTcFRfLVB0SDM4OGRYVDQxNVNpd0g3?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>7</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>46055.34101851852</v>
       </c>
     </row>
     <row r="61">
@@ -2417,24 +2231,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Police and crime commissioner storms out of hearing after being censured for joining anti-migrant protests in Crowborough - GB News</t>
+          <t>Maple Grove Police Chief Addresses ICE Enforcement and Recent Protest Arrests - CCX Media -</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 15:14:07 GMT</t>
+          <t>Wed, 04 Feb 2026 00:32:02 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNzRfSWt4cFdoY3NpZmJoN3JicjVvcThEaHRCWTdtZW9CUWxNOEVNMURnV05DQ2hGUmJlbUwzbTg1OVZBTkJJaHBZc3dRMUNqTm5rQXBQeDQyMWFIQnh5bHJNWURBeTBJd1Q3OWJzMmNNeVZtbFg4NnZlX0QzQVRNZTdxUThmcjZONG4yaUU0SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOZXN2UHBVaTBoNHljclNnSThxSnhFd1hhWWFBQ191V0s1eFVzdV9EMGE2dzZGT0xqaDlsaHlQRDNVdVhWM25PMzQydGQ2RTdOZXo4X3ZFMXYxMndrYktNSHIycGhxUVY4ZU82RFdKY3JUR1dRaExOWmVfNmVhQURoMkE3X1VzaXBXTVdwcnZXSDlUQkRvNlNnMjBFb0ZZd3RfQ1JRTmphTQ?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>7</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>46054.63480324074</v>
       </c>
     </row>
     <row r="62">
@@ -2450,24 +2261,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Police brace as pro-Palestine and Ukip rallies descend on capital - London Evening Standard</t>
+          <t>ICE-Out Protests in LA w/ LA Times' Gustavo Arellano, plus Capital B's Adam Mahoney on Impact of Freezing Temps - KPFA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sat, 31 Jan 2026 16:01:16 GMT</t>
+          <t>Tue, 03 Feb 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNTmtKeW9taDV6aVJQZkp6ZG45aTNoaE9QMWxDM2o0bmdXTWZYakoySThLamgzMDA1bG84TnhjS2pZdFhncDV4N1Y2MVhnWUMtNV9TN1lPMExhMzFqNXVPeFpCMk1kRHNZTjJETmF4OEFnZ25ETi1XZVhuNWNTUGY4eTFVS2VKQlpCOFY4WkVJb2FoT2JJWkVjVGphT29idF93Zlpnd2ZfQ3FmYU12c18tbXR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11MmFBVWRiMlpkdzd3SFU0aTQ1YnZBd2RJSDhtNWJZZW5XaVhKczVWTG1LUDVkRHVmaXFkWVc1dC1XMXMyMzM5bmZpWXJzNVlPQlVsTU9FYkdZTHhSdml6aS1McDQ?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>7</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>46053.6675462963</v>
       </c>
     </row>
     <row r="63">
@@ -2483,288 +2291,261 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Herts police appeal for information after burglars strike in Bishop’s Stortford - Bishop's Stortford Independent</t>
+          <t>Spokane police chief apologizes for officers wearing masks at protest - The Seattle Times</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 14:59:00 GMT</t>
+          <t>Tue, 03 Feb 2026 19:00:02 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNclZROGF1SmltZGNncGt2VUhoa0E5YURxSngtZ0NwVGZuWk9jajBUSkRyS1NXUGhIYzJvem1nMzNjeHIyTlJzTjRRUWhGT2QwV3dpNEJkN2tZdml3dmc4dnFYWWFSbGx0TWhWa0cxRk1raEV3ekdneTJVTklwa1lKZFRvSDNUdERuaGRZaEhmVmI5X1lQUEF0aXZRLWFvdHliNmVlNTJTYUJHNGo0M2xJcklzaVp0b19IMXlUbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPZHVEUEY5SVQyb3FseU83enJMeHd1S1dzc1NsUUR2aWpPRHBRQ05zQ20zZTBmM1MwYmc1emlYQW05VDg3T2l4bXFNS3k2aHlvOFl6cTctcS1vQnU1dFVGRVFucnVLd3VZbVR5eThXT015cUJLaHIzaWtETlJfUU9rbllnTFdfeU84cXpXdVFuT3Z0UmtGdzVlNWhYS2RCeE5pVV9RVTdXMVkwSFcwSjhFUlZqRUU4QTFYR1ExQWJocw?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>7</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>46052.62430555555</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thousands turn out for national rallies in support of French police force - RFI</t>
+          <t>US stocks drop on fears AI will hit software and analytics groups - Financial Times</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sat, 31 Jan 2026 15:32:04 GMT</t>
+          <t>Tue, 03 Feb 2026 15:51:54 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOeVFhWDVkaDhlV3hzZUF1SGh5VzdFMWJCNW9MbGJMLVZ1M25vS2FfX0x6NHV6ZXBJd2ZoSnhpX0dVQkJfNFp0b2drZ3ZzMXlXaXVVbWQxc2Z3R1VwUWIxNVotaWtfaDdrcUR4M0VpcUxrc281cmdSdjhWbjE4ZU1XTl9xUGI5UEVwR0lROXcwZkRwTUtkdEd2Ti1kRGx4WHNwZHBHa3JRZ2NOYUVLQ2pLdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5uQzVsUF85MERrc09IUk83T0piRjgtQUFvZ2R4c0VyVmxzTlJ2R3BkelNLMWw4eHYxcGMwc3hjSmJsN0tTbGhsNEVQYlJmcWVkaXhxaTk4NW14WDBDbjFFZml4SVFyaGNVbXhqb3licHc?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>7</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46053.64726851852</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eight Arrests made at Demonstration, including Three for Assaulting Police, Queen Street West and Bay Street area (Mahnoor Mohyuddin, Jennifer Vong, Kyle Stephens, Woodrow Fraser-Boychuk, Abe Berglas, Darcy Belanger, Bryn Williams &amp; Charles Kaake - Reddit</t>
+          <t>NHS launches AI and robotic pilot to speed up cancer diagnoses - PublicTechnology</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:33:10 GMT</t>
+          <t>Wed, 04 Feb 2026 01:08:48 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPYlA1UmFxRnlZNXpJODk5X0hOWldUOElDdG1mVXhndl93LUhackpTa1FYZDBjRWR1dmFhc2xrYXMzMFo4WV94OEtZb0ZpYTljNlJYb0RVd1llS0RuWmRHRlA4QUFJaG5QTzBzaDRKUFBBUWNDR1pDdklZUXBvdnVqMmJiMVZydUp1Q0hVV2IydDZQY0F6eGtYdXB1M0w5QU8weWVEag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNYm04ZWFpSkZ1UmgwOTlXVU5TRkJBWjBQeU9PbFNfbDBVVmNpN0ZpT081RUdHemQyVEwwZmJrZXIwYzJSLTJsSGpNcFBmWjJROUVQQlRNaUZrUU90MmphQTQzYi05TV96dGtrT2VFa0hPY1l4YU1pYXlmZ3FrdUdtbmhGQ2xMQkNMU1Y1a2hYc3ZFODZDQVVaSnhhTjJXVTdnMWlIVHFhZlRhYjlPYmJuWHpQeEwwbGotd3JWSTNDZTIzSXAzMURiNDR3?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>7</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46055.52303240741</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Clime Capital Announces March Quarter Dividend Guidance Of 1.35 AU Cents Per Share - TradingView</t>
+          <t>King's robotics and AI specialist helps government upgrade public services - King's College London</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 01:59:00 GMT</t>
+          <t>Tue, 03 Feb 2026 12:59:31 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPaERFNTN6UzRGZkxwdHJpTzVWdm0yOEgzM083aFUwVnZXbEpYbFg2cTFndjF5a2xSX1lFdzBkb3h1TGhIODRfcWh6dUIxdnJJbTFURTQ5dnJxVjFOVHhoZk41dHlrd1VDMi00VWpuSURqaWVQYVBZTHhrV1BFMVBnMkM4NEJVNExLenEycGUwYVBMU0ZldGE3Z2x3SGd2UUtOLXJDX01VYmpJYmNDMTJBcmNuWk9GUnphbHRranNOWWVfbGd1VlZBb1U4cWFmRXJVQWpWdDBEQXd2RVFrN2pTbTNhU2NXXzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQQVJBNEtMQjhaaXJZb25qLUpPZnFHYkpkeVJtdWcwME5NdmlJdG1nWU5sYUZuYVFEMzJsTWItU0kxelRkckI4eVE4dkVoOUtWbkNJaWszYV9VV1FENGphSjhtVU5OcnJnSGtJNFFUYVVYN3ZsTXo2UGhBNGxublktUUV0YzNMdzF1amZkSk05NjRWcVNDa0RUMld3cVZ4WE1DbXc?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>7</v>
-      </c>
-      <c r="G66" s="1" t="n">
-        <v>46055.08263888889</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Man sought by police after thief strikes at North Yorkshire shop - gazetteherald.co.uk</t>
+          <t>‘Technology must enhance, not replace, real-world learning’ - The Hull Story</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sat, 31 Jan 2026 15:15:55 GMT</t>
+          <t>Wed, 04 Feb 2026 06:37:50 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNbm9JWXBPWWJPeG5FaWFVUnk5V1A4U1R6V182OFd2QWZtNzlaZWljd213Z1ZxTm1iR25hRmpvd2hpX1BhNFZpcUpxeGZObGNPb0h4S1lfeExRQnBjTnhITEh3N2pmenZKUWtaNWtmQmJPNXIwaDFZdi1VSXpWZnNSNnU4cFItZjhYVmVVRTNqVWh2TDky?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNm1XOWJDUDBSc09mbEZ0VUFaQ2JwNEdMd0w5a0wxVXczc0RMb09pUlY3ZFB2T3haWHBaR2FTSlB2OEJBN09rRFprMlFfXzBOREtkMkMwb3RGV1I0S3YzenBjOXRUYUdXU2xKS3RIaHZ0T2FMcnIzUmxwdlVYVjJLUGxLcl9BelZldklsNFBqbWNGbFZPNVFQclBGaVA?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>7</v>
-      </c>
-      <c r="G67" s="1" t="n">
-        <v>46053.63605324074</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PPB Monitors Protest Activity, No Arrests Made - City of Portland, Oregon (.gov)</t>
+          <t>UK and Japan strengthen science and technology ties - GOV.UK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 08:17:17 GMT</t>
+          <t>Tue, 03 Feb 2026 09:04:44 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNZEFueFNUZzJZLVlBWWtONDlJdzJuZTNFcUMta2M2SXA4bC12MHpJX1NhRFdVLXMyRWJCNUE3OU5NOUgtejVNRTk0V21ueW1fYUV3WGJIT1J4c0gwV2Q5TUdjY0h4dTJ5V2VNYzdGVXVxZlJKdFNNZEMzbXlNYUgyQXZEa3Mxc0xFbUNxcy1CUVhOejBXYkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQkZQLVZCX0pweG43Y0N0dWNXUXFGaGNsWUN0b0JBb1FFek5FREd3cnJXR0dFRGY4TGloaGlaRlFvMGo5SmxpZmFwVHpxbVdxX1RBTHN2T3dFc0M5Zk1uOTRDU0ktQ2NfRDdPN2xQVmpuanhLRHFIWjhPaHNJRDV1Rm1zVVQ1WlRBOEZrNlRsYw?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>7</v>
-      </c>
-      <c r="G68" s="1" t="n">
-        <v>46054.34533564815</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Police Urges NLC To Cancel Tuesday’s Planned Solidarity Protest - TVC News</t>
+          <t>CURE-ND brings together experts in AI and machine learning - UK DRI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:51:00 GMT</t>
+          <t>Mon, 02 Feb 2026 13:45:51 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQUzc5Q3FUNzJteVlSUEJQekViSS1GRnJ6NFlmd3NVTXRmRzhCVWJfVXNsMk5ENjQ4MDJoOHR0MXZYSzZHbGdQTXlQVGR1dkU1eklxS2wwZFBXbkVybEV2cTl4LVRPNkFXdjE2Z1lySDJEdWdIX0lybnp3R2s5VjlzQkJQVmhubjQxMDBnMmhaUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQUxpOEJSX3VYSW04MTVNYkd1TnJJMXJKUjc2eEpZQ1I3M0hsSTA0dEdaWEc4dUpGQUpvYjRqbFM3akdkZHdzZlhpdmhhcnQ2VnpWb2otYjZjeF9JZ0h3ZTY0SjhDOTBrMVhJVTVXNUQtREczX2xMejB1Q0JKRDNkamFfSGVZMGp2U2t3N3VEaEFZaU1XR2xhQzFYY3RlT3B0OVhZX3RESzI4ZTQyVDZ6T1FxMHZiUQ?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>7</v>
-      </c>
-      <c r="G69" s="1" t="n">
-        <v>46055.53541666667</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Clashes in Turin Injure Over 100 Police During Social Center Eviction Protest - mezha.net</t>
+          <t>Technology and AI - Freeths</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 01:44:25 GMT</t>
+          <t>Tue, 03 Feb 2026 07:37:01 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSVlDdkdjV3ItWWNVWENjVFlDcjFZb19jREVfb1FHVUtvTGZyeHdMY3l5WkMtVFI1MjlCNS13VnNidksxdU0xSk9sRUFwU0IzeTJVRTRmLVBFeXgzZGNsMEhnNTgtb00zUnp3eDVkRWN5aTFMVU4xMTZlUDNMd0d3OU5sNUpXMFRpamhhY2NVOGpmT1M1NEtMcDdlNWwwdHNYNGs2MWJsRFlSd9IBrwFBVV95cUxPa2NMbGltVmNON1BvS1lQMnZ3cFFzWFVtT240Vnl4QkhiN2UwUFhkTGp1Z1ZpRHRkTlhOZjdaVTg5MElzbjV1d1FlYnV6Ym92RG5YMHFja2p6WjFXVzNzb2EtanVmcS1rTUlWcS1peWRfS3dMWjN0ZTdrMWxBX0FDU2tfWWc4bzFjWVFFZXl2cUlOdUV6ZjNfNkZoOEswc1h2UzR6S1RDVUU1WDdjWEtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQMzVSZENscUJaS1laajB3d1dRQ1B5a1N0S0JhM0VySk5GV2JEbXlXWDdSeWhTU2FyQXhnb0Rjajg2WGR0XzhtTDh6TnBEdFF3YnZDZjhLOEJpUFJweGl0d1VNRGNHWENueHFzanNSN3RaamU3aVBoTHV1OE9tcWk2c1RB?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>7</v>
-      </c>
-      <c r="G70" s="1" t="n">
-        <v>46055.07251157407</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Haredi soldier caught in anti-draft protest saved by police - The Jerusalem Post</t>
+          <t>Women in tech and finance at higher risk from AI job losses, report says - The Guardian</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 01:58:48 GMT</t>
+          <t>Wed, 04 Feb 2026 00:03:00 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5xTDZ2R0tKT2N0WmtaUlluNHI5UXpTMjVQeDZodHR1RFNfdERpbjB0eVNiby0tYVJQTDZvbGtpTlRBWWRhQ0dzc2llSERUaEc4VUE4V2pZYmNpa2FpN3B4YjZoZ2ZZbjZOSmF3bzJkVTVWZGJWOXlqYmJvYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNakRQMFJ4NFJDWEU1UnRoVG55QzZjWnl0WW1Kd2czUDgyM1hXVzlNYXM1S2ZtRlRmeTFXMUdMWWhad2taWGpCZUF4UER2ZGRpa3R5aTFycUhyNjZKN0ZzenQ4XzA0ZDdpX2xnaUt1d0I4TkV1VjdadFNQa0ZaNlQ3Qm9QN0hKQ1Vnd1Viamc0anA2UGdQLUQ0S0I1Q3pYXzRnOGc?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>7</v>
-      </c>
-      <c r="G71" s="1" t="n">
-        <v>46054.0825</v>
       </c>
     </row>
     <row r="72">
@@ -2780,24 +2561,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dow to replace 4,500 jobs with automation and AI as shares decline - Packaging Europe</t>
+          <t>Industry suffers lack of joined up AI and digital skills - DecisionMarketing</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:08:32 GMT</t>
+          <t>Tue, 03 Feb 2026 13:49:00 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUG85LWpVTTB1ajhzU3dMMEtCa3NkMDRxbmpjZTV4RmlvZ1dpSlh2VmZZSW40VEV2QzcwTDVaQVltdnpKT0gya19GT3I1VnJFUGNjRkNGNUtobGFCS0RjV2x1NmV5YTQ3bzlYUWxHRl81dnpLVk1vVHlEemtUU0JDeDk0SVhDYXBsSG9pMXBJdnJfOWpPQ3U4NjNVWm1IeEhCT1l6aWUxQ09EaGg0czl5MXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPOEw4RTlNUGI2WDlXMEVBUkJMMlBZZ2VWNnAwbFZIdkJHTEhPbTMyQllzZzZlek5JX2pMQzNxWXQ3a2lTbEdxN253ZEFVM0JNdHZ1dTJrd0UwTWRJNl82YS0wYzlrc2ZPbjl4TkF1bDd6RVc0aWVEWjFhUlp2dHd0VjFNbU9qM3dmYUVKY1VBeXgzMVROd1gtVjY0TGRGdw?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>7</v>
-      </c>
-      <c r="G72" s="1" t="n">
-        <v>46055.46425925926</v>
       </c>
     </row>
     <row r="73">
@@ -2813,24 +2591,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Technology and human rights - Amnesty International UK</t>
+          <t>Nottingham receives funding to develop quantum sensors to improve precision and read-out speed - University of Nottingham</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:19:47 GMT</t>
+          <t>Tue, 03 Feb 2026 16:30:50 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPNHlIOVVoNVd4VmE2V3B1b0JLemxfMTcyYXQxakg2Q0dLekxWLW1nS3Myb3BnNk1TUm9Va1BzR3dSdE93SlRmV2gxN1ZoNmFKSm1YSGF3NUVQOG5qMi1mdnp4WHVBeXJ1MTlrWE42ZkhCaHp1cmhXQlMwMkd4czhaczJXWmxMT0Raa1JKbjhSZy1uUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNaEF1YTRSWm4xM1NnTWJnU0NRVDRVYVlkdTFWRXlJdUY1RWh5QWVQT095VTBzMHFnbkxlbmlqRU5Ha2g0ejJ5ZzFTUE5PMllGUkJyQXRPdzYyNl9MLURSWG50cEYyYUZhN2UyTGFOYlBXRE1lLXU3U1BDYnBaNmJQbDVpV1lLTXJhLVRNTE1BZUktTVF2c01EY3FBNHdXV0pPQWo0R19MOEFZczRqZXpRQk5wZnFqa1lLWlMweDNuR3ZLTEZUYUtV?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>7</v>
-      </c>
-      <c r="G73" s="1" t="n">
-        <v>46055.43040509259</v>
       </c>
     </row>
     <row r="74">
@@ -2846,24 +2621,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>The Telecoms.com Podcast: Ericsson, AI and Nokia - Telecoms</t>
+          <t>Why High-Stakes Decisions Demand a Different Kind of AI - IT Brief UK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:28:13 GMT</t>
+          <t>Tue, 03 Feb 2026 23:35:05 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPTHhsYVpnTHdHNkNEQXR5YTVXeEdDSFh2dE9YLTJsdVdFbDV6MkxuQzJ5Q0xTdEZFb2VaMjlESi1JZDU1QWJpekR4ZExxY196ekhkZ2lJUDZzMnp5MjFrS250eDh5OGRSckRLczFKdjJKYVcyQlhmdEtSWTA2R0VLTTZUa1dhV2dlYXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOYUY4VU01Q0ZDQVF3TnZMN2I2ckMyeXpjRlktczhyS2M5S0Q0YUlOaFNqbDhDQWpTTkUwNlJITlQtaFZ0aTBkSDhwc1d3c00wTXk0ZjRXSDJJb1czVk5PeVQ3eHFTNW84a1hha1V3QndMTDhUeXBZaks5RmwzbTVyeVNDa2F1bDV0NEIw?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>7</v>
-      </c>
-      <c r="G74" s="1" t="n">
-        <v>46055.5195949074</v>
       </c>
     </row>
     <row r="75">
@@ -2879,24 +2651,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NHS trials AI and robotics to speed up lung cancer diagnosis - UKAuthority</t>
+          <t>How agentic AI is transforming financial services - Impact Economist</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:01:03 GMT</t>
+          <t>Wed, 04 Feb 2026 02:29:43 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNVW9sb25UeG1CVzdNOGVXWFRsT1ZBYWhwYkVTYkRZT0E3SURaNHdxeko1ejh5S2xnQThQaWp3TjRrOHM1TE1GcmxXcWFvMWZleFpRZVRNeWpQZW9fZXdBOVZjZTVJTjlUb01YTkRsZWZEQmdheTJ5d2ItdUt4b0JPX3RvZGZWc2JWZU5NRjVSbzNzQlF1Q0JabXRtemtYQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQdk5tYWV3M0t0aEtZRHhmVnI1STNPLXFBTTZPLXFXZENUbkdxMDdSaGE5dUh2dmRkOWpRYnpScHdmeE51SEV2WG91ajZJbUZPaFJLODloZUFtMFAxQkNfN0U1dEVqUUZ6YTFqRnhQZm1SWFRKRk9COUpRWmlTMWRVUWJUamhmdWJ0bUNPMw?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>7</v>
-      </c>
-      <c r="G75" s="1" t="n">
-        <v>46055.3340625</v>
       </c>
     </row>
     <row r="76">
@@ -2912,24 +2681,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Why banks shouldn’t wait for AI to fix the Gen problem - Retail Banker International</t>
+          <t>Liberty Global and Google Cloud strike five-year AI deal - Mobile Europe</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:28:04 GMT</t>
+          <t>Wed, 04 Feb 2026 00:15:55 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPNkJaSEM4djg2STlSalNWM0c3MmhmS1ZNS1c5MG14VUREZzNha25fVXp3VXF0YUczMkRlMEwtVldORHU4TFA1dEtLY3dfeXpmcW5UbHJLR09mX3FYZlFwbmtCbU1GZ3lsMFBUZmhpU2ZHMzlVZUxkSG0wNkRCeFcwQkk1OW5ZUlVaNXFPVktQb1g0djI5ZkQzU0ZKTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY0RJU1NmOVNBNzdrOXdTXzdfZWF1QXpPdlg4ZHFKRU5tUWV3MndBR2lrcl91bHFVZlJtUFRPYmZBX01YeU9FUXhITWtVQXVkc3J5TVpxTWRMY3Z2cjhyZ3dZTVBqZWxkTXA3eEREemRsblBQYi12aGVWZWloVkY5a0lUNll1NzdmdjZ6VzVpS1ZqQQ?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>7</v>
-      </c>
-      <c r="G76" s="1" t="n">
-        <v>46055.39449074074</v>
       </c>
     </row>
     <row r="77">
@@ -2945,24 +2711,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AI and tech adoption in treasury - Private Funds CFO</t>
+          <t>Amazon, Prosus Reach AI, Cloud Deal for Double-Digit Cost Saving - Bloomberg.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 02:00:49 GMT</t>
+          <t>Wed, 04 Feb 2026 04:30:00 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9HX2wxTWg4OXVDNHpST0Z0MGZsRVJZVkVRSHJyWVJKMmk2QVN1Rk9LQmdfSjF1a0h1Vy1tSEpyREJpajlEcWRjZFdYRlZiT1ltYk0wb3hHUm1GejByQ183dTJWMlFXQmVOdDdyVGpjU2lVOFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYlpGRFV0SVRkU0VuQnBMaTRKaUp3VDlGOUswRmNuQmFCVEdnbkNRcFE1NVdKbjdrMmRSanU0M2NxUDVRQjJEZkVJeGtKLVVEYXZwdlJFb0RWaDVRUWhRbGtZbWFsSk4tTmJpNm11UF9PYTdCY0FXc3Jwcl9XRkRCQmIySElkdDNMQThmYnFpbzBYUVgzNjFNTEh4Y3YtTS0wX3BFTjNVWnltMWdHT0laa2xXdw?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>7</v>
-      </c>
-      <c r="G77" s="1" t="n">
-        <v>46055.08390046296</v>
       </c>
     </row>
     <row r="78">
@@ -2978,24 +2741,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IFR position paper on AI in robotics released - International Federation of Robotics</t>
+          <t>Use more AI and video hearings to fix English courts system, report says - Financial Times</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:50:47 GMT</t>
+          <t>Wed, 04 Feb 2026 00:01:01 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1uM2Vnek8zdm5IV1hWem9CYWl1S0czMEJLd3lhNHNlLURxajlQZy1ISzdSd28yblRfeUpKV3ZsYWlPYlJsNGdDalFWMUQyOTVqSmQxMzNqV1Y2SE9UbzRxcjc3RzVRcTc0NG9tYV9JbU5fWVAzemRVMTVhV1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1zU2RFeUxERWhId3lMWDFVbmJTMl96NVhHdndqRkt0VW1JQ2ZSYjJtYWhYS1J4cHc2RHQ0X2tzOVp4ZnoyNDE1eE5Eb0ZJVzdsbjdCdjh5M2pUak1WU1pZbTU3Y000ZlV3QWV0dGh1clA?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>7</v>
-      </c>
-      <c r="G78" s="1" t="n">
-        <v>46055.4102662037</v>
       </c>
     </row>
     <row r="79">
@@ -3011,24 +2771,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>How sustainable funds are navigating AI, defence and financials - Trustnet</t>
+          <t>New robot swabbing technology trialled for the first time at Sellafield - GOV.UK</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:01:33 GMT</t>
+          <t>Tue, 03 Feb 2026 10:41:15 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPRktGQTJJdXpHeldsX3E3NEl3ckx2QjkxU2tIb3lPUF84dEI0a2ZfQjVjbTNMeHpZUFZjdkR2bldWTnpMRmNjMnBkNFZ5Rk05dW5xeEpsTWo1YkRXUjhpYkdEYS1od0dPSmhScjZPRjZsYVBxTzlUbXh1QlVrbVhwaFRyNTB4aEk4V2I3b1dhV1J4VC1vRUdsMmdTUEFFeElqbE1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOd3FSVUNTenVpSFhtWjdBV3JYX2JNRWFhTWZCR2U1Y1FsWlVQQ1FhUjRMVmVwWnlZM2FOMUxJYVgxTk1maEY3RkJpMk9EZjk4Wks5em00UzJBbzRwbUdKUGVkUC1ybkJNc1J1WmtMNGxjMjhiREhzX29JTWQweHZfQ1ZhejluQjdSSzRmVVBGdDNWU0syUUhEd04zMWYyV1IxUWhETlRCejVldw?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>7</v>
-      </c>
-      <c r="G79" s="1" t="n">
-        <v>46055.45940972222</v>
       </c>
     </row>
     <row r="80">
@@ -3044,24 +2801,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Abusers using AI and digital tech to attack and control women, charity warns | Violence against women and girls - The Guardian</t>
+          <t>01.ai's Kai-Fu Lee: Why China will beat the US in consumer AI - Financial Times</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 19:12:00 GMT</t>
+          <t>Wed, 04 Feb 2026 05:00:06 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNalRlb3UyM2w2eHBJQjRDYjNIMmN5Yl9sSDlRRmVDOUdpS0N5b3BHR0RXanJwM1FNd3pGWGw5T1RRYWZJQU9pOGluSUM2V2QxaDVyU3lJTVl1WS1OdzZlbGFQZG9YYzhENldpSy1lM2RrMFB4V01NVlRvUS1aLVpSY2QxTjk0YlN0M1ZuRGFwOURVQWoyQWo2MWdsRTVsY2xmZ0gtVUc4UzJTSXc2V3ZpV1o2YUVRUHc5Y1hSYkd3LWo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE91ZF8xa2FhUFN1cnNHR2lzWlloQTg0TDltLXA3WjVnNktxUWtCaWpFcXlSS2ZrRVJUVGlxOUtOOVkzMGFjMjNWY3lWaGx3MlJSQ25DRHdOX1FzVUwwQzk0SkI1QXJOQVY0dk85MXNhUlY?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>7</v>
-      </c>
-      <c r="G80" s="1" t="n">
-        <v>46052.8</v>
       </c>
     </row>
     <row r="81">
@@ -3077,24 +2831,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Vera van der Burg puts AI and ceramics into "reflective" feedback loop - Dezeen</t>
+          <t>The trillion-dollar question for AI business models - GIS Reports</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:00:00 GMT</t>
+          <t>Wed, 04 Feb 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE5RNF82VUc5cDNNTzhsdHpwbXB6TDBhNW80M2k2Y0NRbFlRYzdoV21GTDNEcko5UDdjbmxIVkgyeHhNWkRCLVJ0SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE94cUluRXhZMVo3ZjhYeHc0N25PUVN0cUl4RDdGeGtuRWVDaEI1dzJUc01pVjJNZnlyTDB4QU5iZ1YtZUtXRGpLbVNuLUU3cktEajkySzR5WGdueDBCMUVmT2p5LTI?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>7</v>
-      </c>
-      <c r="G81" s="1" t="n">
-        <v>46055.375</v>
       </c>
     </row>
     <row r="82">
@@ -3110,24 +2861,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AI 'slop' is transforming social media - and there's a backlash - BBC</t>
+          <t>Tech Secretary: Barnsley can blaze a trail as UK's first Tech Town - GOV.UK</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 06:54:06 GMT</t>
+          <t>Tue, 03 Feb 2026 12:31:33 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9wNDA2bFFUbmx5aDlVcjdxaWE1c1JHZDZTcmxnampFRW5PN19EejRhQklPMkJmeDNYZnlMczE3MWl0M0h2UkhpZUN5b0hoX0RRZzExcTBZUmV3d9IBX0FVX3lxTE9LZjR2U0dKMjJ1WktUTy1JaWFWUkluMWYtSmJBQ0J4QmVuTVhhTUZTUGN5eUZ5UDdGMFZLeHN2TWNPaHZPSGk4LUtlYkpuYVA1Vk9Gd0p3RThuWTNrYXM4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPd0luMnF3ZHJGUFQyMV9VaXM1OENiNjFWVDRQbjRkRWlCeVBvaGxoYmo3Szkxdk04aVlpOEpsazZCZlZMRlNPMk10TnpOeWZOWXViNjNtODZtU3NTWHFZeHRJSnlpaE90Wk1UYXhmeEFwbTRqVmdNWXMwZFVTYmJrRUVUdWN6MDNZY1pwTFVNdjZab2xTMnpZTGNPN1ZhR0pZ?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>7</v>
-      </c>
-      <c r="G82" s="1" t="n">
-        <v>46055.28756944444</v>
       </c>
     </row>
     <row r="83">
@@ -3143,24 +2891,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>“A cloud-enabled, digitally resilient Europe transforms the protection of its citizens, infrastructure and strategic interests” - Thales Group</t>
+          <t>Are jobs getting better? “AI has the potential for a massive productivity uplift” - The London School of Economics and Political Science</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:08:42 GMT</t>
+          <t>Tue, 03 Feb 2026 12:55:05 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQc3lvdXNHRWx4aTVFNFlPbGUyTjB5UlVaN3dhSUhvbXQ5dmF1Tk91REd1QTU4R2VPbGc0b0VEbTZrRlE0cHJWaXVFYmlXaDFDMDhqM3BUOWtNZzJLb0FBSEh3T2pwLWEyTE5ycEpEX19mSmJ4TG40UTIzRVdZTk1IdEpFaWpfVmtoZFRTaXRBREk1YzdNdk1NOVJFRHpzdTJPemlFYmZiWGtuWEJJWVgyaVlDSDBsRjFoaVVUU2tjLU9ZUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeE1EZV9iRnpHTVVPZTR5MDRrOHpKVHI3OEdpN0VobFpEOWlfdFVNQUpqZVN6N1gxS1R6V0J3R29YM2s2LW1meXZ5V2hRbE82Y1lyd0JpY0N2b2RWdFFWcFptNVF3ak4tWmVQUDh1Ym9kZEpqZG1VODF4Q2ktQzBzWXJlakhSQ1Nyc2tqbGxib0xZM19fazMtMW1WM2J5Z0tFUG53X19RaTB1Mm56ZU1hX2g2OGhsYzRnQUtOUlF5VkRndEl2T2FvRw?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>7</v>
-      </c>
-      <c r="G83" s="1" t="n">
-        <v>46055.38104166667</v>
       </c>
     </row>
     <row r="84">
@@ -3176,24 +2921,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AI deepfakes are reshaping cyber risk – and insurance must keep pace - Insurance Business</t>
+          <t>From ‘nerdy’ Gemini to ‘edgy’ Grok: how developers are shaping AI behaviours - The Guardian</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:25:07 GMT</t>
+          <t>Tue, 03 Feb 2026 20:36:00 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNd0JwN0R2S2lhZk02UGFIVWlwODVoZ0NQZTMxZzFURWZURExNbmpXRFlfemNZTWpwNXFidktkSDlSek1EYzlmZzlRSGxoN1dxeG9vcmZYbS1PNU5qTld2RVNQZUNwMXlKcnROQUFXYmtmQUdoVUxxNmV2VlVDRnBSMEZtam1MUzFnd09sRG5IWkVlcW9JNXBzb25qUVo2WjVvRXdxdUt3VnZjbk5vN1hsNVpMTUNQMkUtOVR4QUc3M05NVUZKU2xzNmVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNaFZVa3liZzhLa1dvUk5RVFc3d3h4MDVqbEkzY3lJOUZ0bzN6b0ZQZDVVLUdLTGF3RnFzZHA4aTFwN0Fja0I2WlhoTFYtTmhZa1BJYU9JSldfQ29Cd1B3WktreDR5alJSdUtCU2RRZTB3VGFocDl6eFhINHdIaEJ1VFpqTk1yeHlZZmp5Mk9QUk82dmtRVG5YZktURGx1UjVmZFpSY1BxVlduc0hNRlZJ?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>7</v>
-      </c>
-      <c r="G84" s="1" t="n">
-        <v>46055.47577546296</v>
       </c>
     </row>
     <row r="85">
@@ -3209,24 +2951,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>One Identity names Gihan Munasinghe chief technology officer - IT Brief UK</t>
+          <t>9 indirect tax filing challenges technology can solve - Thomson Reuters tax</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:00:00 GMT</t>
+          <t>Wed, 04 Feb 2026 03:30:35 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOcnhlcVU0RWd5WDI4R0s5d0lvQmdaVHZQeW9QblFnTV8tYmJ2UjlWY1NCckNEWmZiR1lGc19GV3k3ZmMzaF9XV0IwQXBNSEp1N0hTQkhmcW1Wa2ozVmZGUDYzSHh4bFo4UzMwc2FzMmNLTXMzRWw2Y3ZkVHRxYWo4N214NThWRUhHRzN4eHRZbTB1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOMXB2MnJybjVnVGVlR09Rak5vakU1NEs4QmZXWEM0WndUTjRfUTBlb3hVaUxEYVR4ZWpuQ0d2SlVvcnFNN0NXY2swYmV5RHJrSktGZkg5UFM4UFVTTlhUTFVRUmNKNTlpdGZRb0dxZ2pyV0JqaWpPMzItX2RBb1pUZnA3SGk3SEZqNVM0cw?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>7</v>
-      </c>
-      <c r="G85" s="1" t="n">
-        <v>46055.5</v>
       </c>
     </row>
     <row r="86">
@@ -3242,24 +2981,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Breakthrough Power Module Aims to Ease Energy Strain from AI and Data Centers - Telecom Review Africa</t>
+          <t>Aberdeen Science Centre steps into world of AI with new theme - Aberdeen &amp; Grampian Chamber of Commerce</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 05:11:38 GMT</t>
+          <t>Tue, 03 Feb 2026 15:11:50 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOQ293QzEtcl9tQWc2dlJOUG1MSWJwZm1pQXdxVnhiWHo4NEo3TU5YR1hzVXBGRXlQcFY4cDdfTjZPdXZBR3d1UDhXTkVtR1UybFotXzBPOUtDY3FkYndxbU9kODVOQ2RvcVYtM2FEeG80T2xLN1EwUVNZRTJkbzFBOXV5ZGRwRUJXcndkeUpfcDNLRnRxRWkxUHhiRjB6R0k2Zm9KRE1ENVh3TWZkcU5SYU1ja2NTZnJKOG52cndlYVdlN0REY2locnVVaHJLMnkwbXhERkROWTFFMzh3c3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalo5Y3l4UTZST3JaSGp3c2t3cTZZYzNhVUxOMDA4TFFja0QtT21LSHlnZW5vd3VpM3RiN1JEQkFJRFhQZ1FBdHJGOW41c2xlX015aEdYQzZ1ZGdVUEJGYzA1WEZzOEJhWlp4UXhYR2pvTnVWQnNvbnJXMjYzLTg0SG52OWVxRnR2WFVCTEJnWkhSSlB5MnRRbGVaU1haUQ?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>7</v>
-      </c>
-      <c r="G86" s="1" t="n">
-        <v>46055.21641203704</v>
       </c>
     </row>
     <row r="87">
@@ -3275,24 +3011,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EU Selects SUPREME Consortium to Develop The Union’s Superconducting Technology - The Quantum Insider</t>
+          <t>Alphabet (GOOGL) Q4 Earnings Preview: Can AI and cloud momentum sustain the $4 trillion valuation? - marketpulse.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:24:45 GMT</t>
+          <t>Tue, 03 Feb 2026 23:04:00 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNaUNORlkxWXBCMW5YVjZIdHFFck9Yc2VhbGxWMElvaTI2RW01azg1cDBJTWlaclpXZENadEVsNXZiRnNpdUt3QjE5UkVkclByTTNEVXowa1VlTGZ0RlVIaWVIVkwzcjB6b1RVeTlkcjlWMXJrU2psMnNCbm1Fdkg0cW9faGpkVjFZNk1UVE1WejhXTjRfaHdaSUstY0k0UWZjeXNLYWJkbF9SUFRTWm9ZZTNXQ2VaQThROXlFXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPUnl1S1J3dFVvMG9CMEdqcEphckNVTHVkSFFMMmNDb0JaUWhNMFNMM3pvRWZoRng1RmxBSG5UX3VRNFlFdTRjTDA1dngwRXl1OTUxSGhHUlNuelZMWmx3Tzg2YTBvYjFOSEpTMlpZeHU3eDJFWmprZmMzZjdHUDEzOFNhTkFhRkJnQ0JlVzVKWUh5NzJDSk1JSlpELVZyRkVTMW9tdlpuTkZ2akxnYndVbGJvZG16M2VYSWpqNVF5RUhoSzNYTk9qa25n?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>7</v>
-      </c>
-      <c r="G87" s="1" t="n">
-        <v>46055.3921875</v>
       </c>
     </row>
     <row r="88">
@@ -3308,24 +3041,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Betting blind on AI and the scientific mind - The Transmitter</t>
+          <t>Leveraging AI for Optimal Clinical Trial Design in Oncology - OncLive</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 05:00:58 GMT</t>
+          <t>Wed, 04 Feb 2026 00:27:01 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNdWJUT1lZS2tZZEVHXzlBbUJOaVl3Y2VLa3dXblRNcmxsci16YnBrWENIanhRRHFoY1k5VmkyenF6VzdXaGEtRW9WVFlwSXhtTFVHLTdLb1RGVTY0Y2dhZ3dWOHdPZDB1SWFNZnZoR0UyN05TNzQxYmx6eG9QRHROZERYX24tRVg0d0NKTm1OT1RRNU1WUTE0b21zT09UTW04?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPd29OejkxVVNVblpFcUpvbFdIQzAtd1FZaE5GemJURU1jUk9XSUtsbkxTTzNleVFNQmdlTWNtSjhPLTVrTXIxeXVDWHRlNzBBM1NYVTNCYTRCaHI4TlRPRE9UcVJUc3dSUm9QR2R0akU4Um1tWC11bks4X29UVFFCQWdZenhlYzM3NmRlWWk2RzhZdw?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>7</v>
-      </c>
-      <c r="G88" s="1" t="n">
-        <v>46055.20900462963</v>
       </c>
     </row>
     <row r="89">
@@ -3341,24 +3071,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UPS Resets Network To Favour Automation And Higher Margin Deliveries - Yahoo Finance UK</t>
+          <t>Hospitality Tech360 launches programmes tackling leadership, AI and the future of hospitality - hotel magazine</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 01:06:00 GMT</t>
+          <t>Tue, 03 Feb 2026 11:48:24 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNaVo5eHdfOGZhUjJoM0RQeTBpbWNDb0NkdnZKclhQcWtCc2NJUGFmTVBZQmNwcFdibW9QY2JfVjVMTDRiMjNWRkxaU1VPd2hYOWlZSS1GUlJjWFlGMjBfVWZETUVBaUNsUENXVkJ4eDVBNVN6Y2dkNFRVSzBPQXc4dkFqZXNPR2d3QVV4SWRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOTUloLWxxbENQaVVhU1hEcjFNLTdGMWZWSTBNdU81c1o4ZzA3SEZXaWo5aGEySDVZVnJ0cnQ4QkFnWUJXVjZJWndzTGdPQ2hEVlh5MDZrS3IyS0ZYUEZ0MTQ5dmRMSDJuYkEzdzAwVktYOVJqeU1LZmdfNkcxb3ZIYzl6ekNwcmlHU3EzWE0wbnpLb2VIYUVJLW44QmFtQnVqSTNEVWNuX1BXclJhUjhRT1pfbnh4MVozMzFwTUFQckJwdw?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>7</v>
-      </c>
-      <c r="G89" s="1" t="n">
-        <v>46055.04583333333</v>
       </c>
     </row>
     <row r="90">
@@ -3374,24 +3101,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tarabut acquires Servable to add financial AI capabilities - Retail Banker International</t>
+          <t>Musk's SpaceX and xAI merge to make world's most valuable private company - BBC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:43:07 GMT</t>
+          <t>Tue, 03 Feb 2026 09:31:06 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE4zbkhCOEtya20wSGRvRG1UNHkwTGN0NmlmWFNXdUMzOThtTVdaUGhDeFh0T0YtdzlDa2dCdXFHYUkzdUJjb2d5dngySGY2aWl2Vko4Z0s1dUFJbHBUeFZVRGpOR1I3SHVMLTREeUJnS0VDR2NUTXpLbm9BdXBJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAzc09Ibzl2eWJ1OEQ0VTkxakNQV1hxOERGX01GOTNYUW5RNlRwNnVNbzdzSGR3TXJnaTNYTUdkT1doUXdwTko3ZTNJOWxNeXJTampQUVhSRDZlQQ?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>7</v>
-      </c>
-      <c r="G90" s="1" t="n">
-        <v>46055.48827546297</v>
       </c>
     </row>
     <row r="91">
@@ -3407,24 +3131,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Microsoft Q2 2026 Earnings: Can AI and Cloud Keep CX Ahead of the Curve? - CX Today</t>
+          <t>enclaive secures €4.1m to scale confidential computing across multi-cloud - FinTech Global</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:46:47 GMT</t>
+          <t>Tue, 03 Feb 2026 15:22:02 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNUC1EZDJEcjROV0lVNzhneHVKWXk5NEcxZHk3OVZ5ellocGZJUnpTbHI2ZmNBbDVYY19SbS1XWGotdC1ISzE1S3RiT3dqWEFBY0JpUzlndDRCRlJ5SmdfZ2JhSlZQMUJsLUQ5UHA4NGZ3dlVKYmlRbnN6akZKSWZMbWxPWGtOOEVfZ24tMHBNMmZCam5ZeFhlRkkxd001SS1qanpXanNWM2xQQjNVaTRaV2Rvb0hLQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOQmFLR3ItVk1aSW10TjRZWG9wSjk4d05tVHlLekNNVzdGeW1uanh3bGpJRlVoZnVvejY4Umdmelpya0tLMm02QnlrWXpsRDgwZHBPckdTclY5M2tySEVPS29qRVlrT0NucXZoZDV6LWlHci0xeVZMY19CRWlPUDB5OFEwajU5ekJZWWVDelZuaHFMSWFMNDhiM1lCV2E3Q3VDNHpYX3Jsc1dNQnM1?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>7</v>
-      </c>
-      <c r="G91" s="1" t="n">
-        <v>46055.4491550926</v>
       </c>
     </row>
     <row r="92">
@@ -3440,24 +3161,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CANSO Says Greater Airspace Capacity Requires Automation and Strategy - Aviation Week Network</t>
+          <t>IFR position paper on AI in robotics released - International Federation of Robotics</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:39:01 GMT</t>
+          <t>Mon, 02 Feb 2026 09:50:47 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQeEpFajRYUjU3cDhISm9odXVmaF9BU01aZFZxNndTd3AyUnJyZWV1MVdsbjQ5SEt4UlZ4LTJTTFkxdW9lR0xITzY2TFpWQmJiRDhYTzNyQnJhWDNhY3g3bTQwdHVXd3J5ekFtdnlJZ3M4ODU0NWE0VFllMHRBTEpUbTh5OWJBT3cwcllYWHdlZ00yUFNOX3lSNGtKZk40aXpBVzNSVllCeUFmeDkwaVdSM1pFMTZsbEp5SFkwOFpfbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1uM2Vnek8zdm5IV1hWem9CYWl1S0czMEJLd3lhNHNlLURxajlQZy1ISzdSd28yblRfeUpKV3ZsYWlPYlJsNGdDalFWMUQyOTVqSmQxMzNqV1Y2SE9UbzRxcjc3RzVRcTc0NG9tYV9JbU5fWVAzemRVMTVhV1o?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>7</v>
-      </c>
-      <c r="G92" s="1" t="n">
-        <v>46055.5270949074</v>
       </c>
     </row>
     <row r="93">
@@ -3473,24 +3191,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Why are women more sceptical of AI than men? New study sheds light - Euronews.com</t>
+          <t>Perseverance: Nasa's rover makes history with AI-planned trip - BBC</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:30:46 GMT</t>
+          <t>Tue, 03 Feb 2026 14:21:14 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPd285WTNKeFhFUUFjOW1qekVOX1dVeFBuZ1I4aGtZdjhsMFcwck00SGdRdHFkRmk5ZTM1Xzd1MDFtVkZYX29qRVR4RFY0Z21NTDhBRmhaZmV2azI5Uy1oTW9VbDRUS2thS0RYQWtLZDFIXzFiMGNNVjc3LXJNRk5CcTEzalNFQjNPUU1hbmRfcGJlRzZEd2I3c0FBMHFHVWltRDV3aHJBSnRZdWhPbVBfVmhKQVluQ1VCT1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFB5aXNmSUoxVDhEZjdEZ1l3WG84WGYzX2pwbDd2UFRsZFczWDhqRk9aMmZ1bENhZEFPVDFwaWtyV1Q1VVZndjNMVzBDTVlzZ1ZCZDc1QTd4VFZKQzBUVjA3ak5mTdIBaEFVX3lxTE1VOUNha0wtSkpOMV9icjRyeVBqWU4xZ3dWbTlsVnlwcjItOF91VkpITjV5UlFRaE9MT0xCcDU0akJKTm1ZWHB4U01qR29nS3pVMUtabF9XWVIxQ19ZbVdjZXNOVzRHNVRa?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>7</v>
-      </c>
-      <c r="G93" s="1" t="n">
-        <v>46055.35469907407</v>
       </c>
     </row>
     <row r="94">
@@ -3506,24 +3221,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Maxio Report suggests B2B SaaS and AI growth remains strong but has become more selective - Enterprise Times</t>
+          <t>Dow to replace 4,500 jobs with automation and AI as shares decline - Packaging Europe</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 07:14:23 GMT</t>
+          <t>Mon, 02 Feb 2026 11:08:32 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQS1Y4c09NU1JsSUlBMjFudjlEUGlkX19mdWR6Wm5pZ3VpV0NMd0JFTjY4YmtPd1VqWjRzb2E3aGNyMjlxSlBUVm5aMnl5Z1RabC1rNEZpcW1mSURYaUZVVko5dUNkQ2kzekltTDR4dHpTQS1uZFFHN2hWYS0zYnl1NEp5UERRczJwU2pKUnkzakN3c3RZaXM2R3EwX0tXZWgxcUlVRmRwOTc4OGxacmRWbjM3WXNQaUNYcnhwOXptTXpHU2RpRWpNaVEwUEU1UzZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUG85LWpVTTB1ajhzU3dMMEtCa3NkMDRxbmpjZTV4RmlvZ1dpSlh2VmZZSW40VEV2QzcwTDVaQVltdnpKT0gya19GT3I1VnJFUGNjRkNGNUtobGFCS0RjV2x1NmV5YTQ3bzlYUWxHRl81dnpLVk1vVHlEemtUU0JDeDk0SVhDYXBsSG9pMXBJdnJfOWpPQ3U4NjNVWm1IeEhCT1l6aWUxQ09EaGg0czl5MXh3?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>7</v>
-      </c>
-      <c r="G94" s="1" t="n">
-        <v>46055.30165509259</v>
       </c>
     </row>
     <row r="95">
@@ -3539,24 +3251,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tesla cuts car models in shift to robots and AI - BBC</t>
+          <t>How Do Workers Develop Good Judgment in the AI Era? - Harvard Business Review</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 02:35:07 GMT</t>
+          <t>Tue, 03 Feb 2026 13:44:19 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBrMFdIUU1aRzA0bVlsQ2hpQUhralNORFB4S1FfcVUwUEFaQ1o2bDV1VVA4UHhSakpIU2tmRlNjU3lWOFI1UGNkWWdYdTZJUDIxXzRYcUxXZ0tMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1TcXg3M1ljSGhzb2kxLUVYejNnMjdhYVpKeEZUV0F3aV9EOV9pV21MTmpEWE9JR2RQUUFQSVJJZDVxNnZBQ1ZIRDlKOU9Jb25QYVVIX2ZEcGZOWXEtOHZBMXZIV3U4a092VG1UU0hheGpNcl9OZG8weXl0Rm84REk?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>7</v>
-      </c>
-      <c r="G95" s="1" t="n">
-        <v>46051.10771990741</v>
       </c>
     </row>
     <row r="96">
@@ -3572,24 +3281,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Grok, AI and “free speech” – Starmer vs Musk - palatinate.org.uk</t>
+          <t>CNBC Daily Open: Nvidia denies rift with OpenAI, while software and asset management stocks plunge - CNBC</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 20:30:01 GMT</t>
+          <t>Wed, 04 Feb 2026 01:21:00 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9Qa2J6bG5BUjIzZ2k0Zkl6Ynk4a0x3dl9Hbm1yenJMNE1iUFM1cVY4d0hUcmdwYk5XRTB5a3ZjN0h6eldTVU41TkdWV185ZzFLQ0VCZkdkVU9keFZubF9kV0ZsQUdteE5jdDlKdHRpdUdjNXRacVpwMDR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNHpZWElCTU8zN3VlSnNoeUhTZ2tPNWJyQzNzWDZOUldkTlkxcXZSdUZjWEswY3FVbmRCSjV2enRFY0IwVWU1S1JFMG9HV1JfOWtKN2Nla1lEVUtzZFlLb3Y1enowRkhrTlM0LTRDNlFacDZzclp1MGI5a2dmcUdOcjEwek5fREFTdHdnZzZ2M3NqSTAyQVpPMjhUV1pHaUduZ25QZEJ2V29qWmt5aDBhMGZlN3d1dTJEUWlUbjRUckxPVFQwd3Y2Zndib1Qxd9IB0wFBVV95cUxNZzlCQ3JZMnlJMEdPTTB0TThqM29fR3R2S3JTenFIX05YSTZFNlNzQW9RWDRzSU1uM0Jfdk83aWtXVlJsQ2lWTTdXYTh6U0ZPWE4zZHhvOXhxNURSUFVzdlgtUGFNcXJtcWd0U21GamdTbExFMERtVm0xVDZrS1E1VzdkVExPTm5MelQwelB0WmdlaHB2STkzQTEzZ2hsZFZ1M09IMkdORHNHLXdJYjJod205dUpPMC1XU0RQVGZ4M0x2YmtWUjdCbmFLVHZGUGhObE1J?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>7</v>
-      </c>
-      <c r="G96" s="1" t="n">
-        <v>46054.85417824074</v>
       </c>
     </row>
     <row r="97">
@@ -3605,24 +3311,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Can agtech fulfill its promise? World Agri-Tech explores opportunities, challenges for the future - AgTechNavigator.com</t>
+          <t>Dassault Systèmes and NVIDIA Partner to Build Industrial AI Platform Powering Virtual Twins - Dassault Systèmes</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:06:00 GMT</t>
+          <t>Tue, 03 Feb 2026 10:31:12 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNWFFRQ2RucW80azhrWVJ4Y2J2enBFdDJHOTVlcXhnNWtDTmJsOWdadnQ0cUVHNzRXSGhlUGZweUI4RlZGWHA2cFRRRUl6YVhxNzNFYVd1d3dMMFU0LVJXbTA5Zk80ME14ZGhoVjdpVzRXUFZtV0pWb010Z2kwZWliVXV6Z0FkYlBqSmN1b3F6YklmTWxVWWtpVzh0RnhCYWZ3Qm9KLTlrUEFJUnBtdkNrVVpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOb1BjODQ2T1lSRWZJUWFXV2laMjl6dElWODlZa0Y1M295UENQS09BMHR6VHJUTlpRcmFsUmhXclU4bnoxd2NBaHRTQjUtMDRmNG1Ob0QwTkgtaEtiNUFLbUtIUmVZWXFkVFBHUVVPSUF6UWw5N1hyWHJMQ29zeFlHZFduMEUwdjd1UXBFUTFKLXctOWNJWi0zSldSV1ZOTW5EZGJHelUwMFprSUlKLW9XY25kRjBMallKeTI4b0U0amRuYzlyTzhCNjlqS1U?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>7</v>
-      </c>
-      <c r="G97" s="1" t="n">
-        <v>46055.42083333333</v>
       </c>
     </row>
     <row r="98">
@@ -3638,24 +3341,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tesla Recasts Identity As Robotics And AI Platform With Merger Potential - Yahoo Finance UK</t>
+          <t>FormationQ, Cambridge, and IonQ Collaborate on Applied Quantum Work - The Quantum Insider</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 17:10:27 GMT</t>
+          <t>Tue, 03 Feb 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOenZGbUM3RXE4U3Q5RUU5bmZoOC1MelduTGw2Nkl5dWpLZVY1UmNPWnpxQU9Pam1IWGtaYndOcUZWSGt3amdtZk1MQ2hOXzQxeFRETlRFWDd3UkxienlDSWhhTHN2c0hSblNnckdBaUg4V0JOQnlYdjU1VjliMF9aZ3gzNXpvQ3p0RVFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPS0xHRF9WcnY4VkFOSDFLd2RYdFpBVjdfbUJnd1FWRWRDb2JrbjkwbWdLUzc0bkpLc2c5T1pJbnFFc2NZcDRUd0ZKSmNEN3V3dXFFRGVrcXl3NGttZjh5VXJUZ0ZsLXp1dFJiRWJOZWlhREJLaFFTd1RsbGUzby1WTHh4cklCdnlkMXBvWlNDV2lwc2s?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>7</v>
-      </c>
-      <c r="G98" s="1" t="n">
-        <v>46054.71559027778</v>
       </c>
     </row>
     <row r="99">
@@ -3671,783 +3371,411 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Managing the Load: AI and Cognitive Load in Education - Faculty Focus</t>
+          <t>UK-Bulgaria: connecting semiconductor expertise for growth - GOV.UK</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 04:07:18 GMT</t>
+          <t>Mon, 02 Feb 2026 13:59:31 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNNUhwYkZCLS1OQk5FMnVLNThFcE05TGx2M1lEbld3bEdyT3dYdER5b0dwMnJZZW83YlBGRDIxYTRWRXp5eTJHRlRnZ0JwS0FzTHFRV3ZQRV9ZNGVqendFYmN0ekE2REVEblRMX0xWTGlUXzVsWGJLYXFjSkcyaEh4ZGt4SHZXQUU5bUFsWDgtelExVEV5bklDaHZTNk43RDkzNWNTcWwtOGZNYWlLTnY2SXhXNmtPNk9tMVpqWG1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUHdYRDVQYWVLZjR4MnFna1dPMEJYd25Bc3VvdllKVGJ3OXAzcGIzUy1zX3hQUHhfZVdlZExSZWVkVUc1dGF0OG5ncVRpNkp3YlNaaFBKZjczUm1ET3hBMVlRR00xbi1oVTZtS3REQ2tjek42Y1lKQUdTclFzT2dobGhIdE55QjVsVzFqTUJ3U01aZGVISTU0?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
         <v>7</v>
-      </c>
-      <c r="G99" s="1" t="n">
-        <v>46055.17173611111</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>C-suite poses greatest AI risk to businesses, not entry-level - Personnel Today</t>
+          <t>Managing insider threats across the organization - Barracuda Networks Blog</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 05:00:58 GMT</t>
+          <t>Tue, 03 Feb 2026 18:22:09 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBhS2t1cTV0UkhxRmkxdkM0ZmU3eU1JUVR3WG5wY1lkMm1lNGZUZm85VDVYUEFJQnZmVGhKY0dfQkhGWjQ3bDk2bWdZSXRHM3U5ekc4LV9NNGs5MUc1R2owQWwtRlRUSlYwSXluN2VBTVZpS3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPaHVQWllJV0VIT2dJaEtVekhZTWQ3SF9BMTRpeDRGZG13OWR0V0pSSmtHdWtEOXByTTQwNS1yNEJLTi00cXV2eDJ2dzVqSk1KcUhjTFRfT1YzaGVHdTBWcGNWLVUxbGhsTm13MGNzaTRPcndGbTc5b29fWGh6WUg4MVhrdGxkYWJLa0xLdFlKUQ?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
         <v>7</v>
-      </c>
-      <c r="G100" s="1" t="n">
-        <v>46055.20900462963</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AI’s ongoing evolution in corporate travel - PhocusWire</t>
+          <t>Prudential Of Japan Implements Voluntary 90-Day Suspension Of New Sales To Address Previously Disclosed Employee Misconduct - TradingView</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 06:04:25 GMT</t>
+          <t>Tue, 03 Feb 2026 21:17:23 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnRpVmpSMDE0TWZYaXlNalhkMHN6VzdTWGJtbGtXdnd4bUhzZWpQS3dDUFVZaDdteGJxNGUySnBwMkJuemQ0U1ZVVF9XX2U2bktCa3BxcFdKQjBIOVZiUlhldm52YWNBOWpneWpQQWZXMlZvOFRiYXVJTTAxVndtdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxObUF6ZkV6bk03bUlPb0dRR0hsdkZpYm4tM2Y0SU1LaktjWnhHeFBCNzdnSkFsQ0xZTU5ORG1lRDk5elhodjlVV0VmTkxyWE5YWUpuUnpRMndmeVR2NWtDdkM1Tmc2VEtOdEhlT1VNM2ZLdnpHM1NzTUJUaFJtbldJUm0xbzdxV0pjYXpwOFB6MzhLWWlTNkNRbHk4dUtvRWhIdkM4RkE4ajBKNV9jc2pBV1RpY2dJNVJzVmFmNHVURnpvSVpGb055Wk5yS2pLdG43aWpjZFdtR01kbVVxX0k1emg4eXE0U2FBamkwMTIzWldETlVFbWd5UDhjcWZTU1FBTDhsdXhLWVg0UGFOUUs3QTNmY1dEYXBoMEZRUQ?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
         <v>7</v>
-      </c>
-      <c r="G101" s="1" t="n">
-        <v>46055.25306712963</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Deezer opens AI detection tool to rivals - Digital Watch Observatory</t>
+          <t>Treasury Department Cancels Booz Allen Contracts, Citing Past Insider Threat Incident - ASIS International</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:05:00 GMT</t>
+          <t>Wed, 28 Jan 2026 16:07:48 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9ackFocUVZY1ltM2ZxaVpSQWFCcmdGTGVmRkN4WW10LXZJZlVFckQzQnc5RElZWmNvbzhPTEZVbFFLOGdwNm5RcE5ncmt3UkxoUXRRVzluTnlRMndvcXNYNmVQY01XOFpZeVlzck4tSF9TZTIy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQeFBIZGtmYmh5RF83VWFsZHNvdmIxTWx1RUE3Qnc0aGdrT09YVWU5c0tHRmxuWk5YZVpDdGxGMWRCSTN0ekg4Y1pWdkV6U2xzUFFmVlFaUi1fVGJYTlJmamM2Z3Z0WUpBOW9IMWF6X2NVSzRlOFFsTWtXVGFYOTYtLW5haHhMYXBoZ2VtLTVhY0owM0w1bGZtUE91M0EwOVVidU9NRVVKNWNuMXo5VGZzaU5xbmtQUUxqV3UzeG9xeWhGdW15?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
         <v>7</v>
-      </c>
-      <c r="G102" s="1" t="n">
-        <v>46055.33680555555</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kazakhstan to Introduce AI in Water Sector by May, PM Bektenov Says - The Astana Times</t>
+          <t>ReliaQuest Highlights Growing Insider Risk as Threat Actors Target Employees - TipRanks</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:37:49 GMT</t>
+          <t>Mon, 02 Feb 2026 21:12:15 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNT2JBTHhOTmhnTTBtcWQ5NTVCR05aeW5oZnlxNTlyQzVYbllIWHdXX010Y3R5amFnUEN6U3d6Q1R4NVZZMnVhUVJiM3pmWVUyRzl3UTh4WUhwQjV4LUlRZ0k2TmlzUWx5QkhWdl9UbTNvUmRwNUM2VE91a3dCZEpmQlBqMVdSSlNpdnF1RHZKcTZ2UjRBcmRiWjR2ZWV2TFdu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOSFZCR2htd1dUQkRoS0IzS3pTbjdJak92T3ZPOGk0akhSZkRta1hwMVd6dzJETFVIc3B6eS1qU2FNOXNLYV81X1BEbEZEMllGUy14SURmT0RYa1VQQXM4Q0ZSMHlESjdzWGo2NkJrdEp2VGV0N3lmSnhORTI5dGdIZHQtVTFRZXRkcFFvbEhnejFaR2hncS12WXhtS01ud0hwSU0zS084N0JacGFVNXIxZ1dKUEloajFWX1E5WVFOUWh3UQ?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
         <v>7</v>
-      </c>
-      <c r="G103" s="1" t="n">
-        <v>46055.52626157407</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AI in court cases and court cases about AI: eight legal tech stories that you might have missed - The Law Society</t>
+          <t>News - North West council starts crackdown on housing fraud with launch of key amnesty - Inside Housing</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 14:28:45 GMT</t>
+          <t>Tue, 03 Feb 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNdUJSVzJudnlnMlUxOFphSmQyNmoxenBwSnhrWHF1WEc3S2FUSF80R2hGRjRIUWZIaXhkLXBRY0Y4dy1DWC1KM053Smk2dEhqOTc0X1dMY3hCbGhpdmsxR2xZT0tLdVlYejBmcExCZHJxcVRLbWpkWUJjOWctSTI4VWsyNFotb0ZrQS1TM1RURG9HcFpWd3I5UUhWdXRsMFhodWpER1RNVUxhWU5IWEVnaWtvNEVWb1RTQlJHX0RSbFRHdmt4UkF1Q2dxMEQ3SFJUQUVKQW9WcnRpUWtXU3Z0RFpKZlNEOFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdGROQm16bWJmc1kzMUg4NkdDVjRLN241ZlNRZGRyZVJQUVdXcUFEN29teVNuZ2pjZVJPX1RUNUNsamxVUElhbXkxUUYxcGdYcEttTjJtR2pxMVdkU0Y4VGV2aFd2YV85Wi1uSXNaZ3ltYUpUTkxPd2sxUzBINTdpYjJhT2tIbElTUHZzbldFZmxrR0diRHI2VUVKdFVfZE1zSGcxSGZrM2NOLUo3V3VqRTRma0xiVWJYLWR4YkNlQQ?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>7</v>
-      </c>
-      <c r="G104" s="1" t="n">
-        <v>46052.60329861111</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>China, AI and the West’s Free Speech Crackdown | Ash Sarkar Meets Ai Weiwei - Novara Media</t>
+          <t>New phishing attack leverages PDFs and Dropbox - csoonline.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 15:03:30 GMT</t>
+          <t>Tue, 03 Feb 2026 02:32:04 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQVlRxZHhhcHV0NGFidnJRcWZkQnc3WWZLQkNiR1M0T0JSZU9MaGc3VkprNWVvWkZfUVpaaHFxUVFHdkpjdUNWSWRiYno0cXhpOXZNWWF5LWJCV3NzRVJCM1lhbkc1YkFmNUg4ZG9FZ3p4RTJEZUNKeUtIVkh1cDVzTzdMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQUXE3NGNkdHdXeDdMZmg2OEZnVFFaN2szamdjOWkxYkZIdllITHZLRDB1WUYwU2NQaFpEajIyaVJ0SmQ0ci1uVmg3c3BKOHNid2ljQ3hJVjUxVU1OeXZwb2JXZW03YzBuZ2hiWUZuVDZ1TmE3NGpzNE5xbjFOYjZSSmdmeHNaUjVzOVZQaXBsQTBDZ3pwam5WRw?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
         <v>7</v>
-      </c>
-      <c r="G105" s="1" t="n">
-        <v>46054.62743055556</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KPMG warns of gaps between AI ambition and returns - Digital Watch Observatory</t>
+          <t>Ireland’s questionable relationship with social media giants and scam ads - MSN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:00:00 GMT</t>
+          <t>Mon, 02 Feb 2026 00:34:46 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPa0NUQkc4cm94QjhSZ1ppc1Bmb19FUW9RTGNjWDdGUHJncnFpeXNFdkJYS09LTHk2dGRQVUkzb2ZyMGxYOVJyeXlXSzJyMGwyTkdQOVpjX2NDVHMwalNMTkpoWTdPbm1NR1dRRDNKQ1pGbnBBZ1pzOVlRalJCM3dDQ1p3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOY1hlNFR3LU1LUzJRVWpOTmQxZGZKbXdpMVRjZjFGb0lId0N5czhfZHNQUkxMMUxKbDVpTlE2Vi1LZm9iNlpabkVGdnl3dFM2LUtlZkliY1BjYlI3SmR5TXlNMVBqUlktOVJMaVhCUjNmNWxQNUt0WFhwcFVmYmNyVU9NV1F2UFFhWmhXZE5FSDllRkZmZkJpaUYxbkZiQlhFZFpZUlAtakdMOUgxb05OSHI0aTBUT3g5SVVvVWlNVGh5Yzh1TTdRTWVZQVR3UUY2WTJyQU9Da1hZd2hCXzE2Vl9n?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
         <v>7</v>
-      </c>
-      <c r="G106" s="1" t="n">
-        <v>46055.375</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Venture Investment in AI Rises Fivefold in Two Years, Says Latest Report - The Astana Times</t>
+          <t>State adding staff to review nearly 6,000 Medicaid providers in Minnesota for potential fraud - MPR News</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 04:52:40 GMT</t>
+          <t>Tue, 03 Feb 2026 17:32:00 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPVHdSRUZ1LTFkVDJ0VE9td2pIY0xHaThneU82YXFyN2Ric2JQSWpjTHY4WjR5ZDlDbXVMZHpVbTRvLWlTQnl3WlZYYTltYjh2ZGJuYTRkbkNoa0N6ZFV2MEU2RVNNZ0x6b3NoU1ZvdGRiX3QyVmpPNG0wREpJVEZ3VmZ1QS1VRWI3NWN6UXg1em96UTVkdjJVUTZSOXl1ZFF2MHE0ZTFwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNUGlSc0lpXzN2X3VPbTFXazZ0cF93WTRYMURlNW1YQlB1bFYtbGZveS1aN1BpVWxfWVM3T05UckE4eEJVRU40STNtV3FCdjdrZEdpVWdXa0JkeGpSSVhGTUlJRWhYZWRXeG9XTk5wRndmZXQtY0R6bzVITlN5YnhyNWFoQ21oMldRcDdiaVBRN1JjOHhINTVWZ2dHYzVSUUIweTE4Z2ZneDZUeWFIYVd2YQ?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>7</v>
-      </c>
-      <c r="G107" s="1" t="n">
-        <v>46055.20324074074</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Who Answers When We Ask AI About God? - EWTN Vatican</t>
+          <t>Man used social media in Gaffney property listing scam: Police - wspa.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:26:40 GMT</t>
+          <t>Wed, 04 Feb 2026 01:07:14 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB5NklNUjczbU81ZU1UdzdnaGdKak80OFJseVEyX2hKbUY2VVN4VUJBSGtBcUo2NGtTYkIxMDVsUHE0TlRfNlI1ekRScDExMjNDbHdUeVpVbkI4TTBPV3Z2NHpoakN5OVB0LWgzVlBlS0txeGJIN2RqemZfVmlkdDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE02c0VSLXZKdFlTZDVjRmdHYUZiZVdpMXNfYzZXc1h3Wk54Wk9UZkM2bjFwX0tCNnpfcEc1ZUNZeUZsNmQyR2V1Nks4YnhvXzZObC03UUI4eXRyUVM0OVBsT05kbkR3YlFNWUxhSWxB0gFzQVVfeXFMTVpsZE8xWTBvTTFfanFtY2dob3BSWHlYWlZ4UWJuTVVnME9SYzI0eEo5RUJoSnJMOWxxRVE0Sk45cktocTVxSnpvODAtZmJhT2l0dHJEM3FVTzkybEptZGVYYXpUS2RLUnlWMG83aTlFNWtXQQ?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
         <v>7</v>
-      </c>
-      <c r="G108" s="1" t="n">
-        <v>46055.35185185185</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Opinion | Where Is A.I. Taking Us? Eight Leading Thinkers Share Their Visions. - The New York Times</t>
+          <t>CNAS denies the information about the granting of 5000 lei from the social fund: It is a scam - ipn.md</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:03:00 GMT</t>
+          <t>Tue, 03 Feb 2026 10:46:59 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPXy1tbFc5V2p0NVlhcHJUc2FQeFZkS21UMjQ5NXdkcUZib2VndHZOenBpTW5uOGZvYTRoUUZSN2tZT1c3M19XbDEtbkpVY1pPbWJmdmp5RDZuVFZtWDkyb0ZhbExleXl1NnBCVTJWSktzRHhicldUMnFOSmpLOXdLck5waWpnTUktenh4WmRsZExTdkNELXFwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQeUtTOTY5c2w1MjBkLWxRUHRacllZN0x5MlNuNDBJMmZJWW9CZEVPaEdBTzhIUDJIRUhEX1g3bThnYTFXRERpM1FwV1dxei16ZWVPaWhBUld1NlRrRXFRRVQydlRFZkdhMnJvbk0wR2R1Q0RfLWRNb1VxT005eHVkbWJlTDFtcjg2TG5Dd0dmWjZhb21Gdjg0Q2pXMG44LTh6U2ZyTnlZUXJfaXRCdG5mbA?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
         <v>7</v>
-      </c>
-      <c r="G109" s="1" t="n">
-        <v>46055.41875</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>How AI is Revolutionizing Life-Saving Drug Discovery - Pharmaceutical Executive</t>
+          <t>Meta’s social media scam ads cost consumers billions, investigation finds - ClickOnDetroit | WDIV Local 4</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:06:40 GMT</t>
+          <t>Mon, 02 Feb 2026 17:15:21 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOZlkyRDlhc3RUM0EteE5ObTBkSE9IUmZGMzBjX3VYYmZ3bW9oN0x5aWRFYWZfMTdpRmNMZGxYYmNLZjhLZEZLNlNRck8tdXR3X3Y5T3BDV0hubWwwMlE4NFV2Tm9OM0wtcUowUDdpcG5aUVF0TW53QkQ5M1BZLUJVVjJrbEo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNWkZEMG1naVNKampJUHZ3eC13SzVpN2o3NFU0Zmo4NFNwaWVPcHFfV2JDblREaHFzbHdYOUhvMW5oT3BLUXlaVEU2NG5XUG03ZUVheUZlTDliSS1UOUtMUFpXNnVqOTllT3JjQ3NyRmFMSkVNVVh6eHBPV2w0Q1ZwYlBzdDA4VDhSTnZwYThjamM5VTNjMnFSSmdLN0lzZDVIT3RudzZPVVp0VGUyRTFHUjFiRk85U0ZQdTktMWxEMGtjOG8?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
         <v>7</v>
-      </c>
-      <c r="G110" s="1" t="n">
-        <v>46055.46296296296</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Starbucks bets on robots to brew a turnaround and win customers - BBC</t>
+          <t>Scam Alert! Social Media Page Claiming to Be Famous Krabi Hotel Was Found Fake - Thai PBS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 00:11:06 GMT</t>
+          <t>Tue, 03 Feb 2026 10:31:00 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5nSFI2ZTA2QTdDc3FqelRieW9rT0N4OXU1Mmc3YmtLd2V0Si04SmtQdlVqOG50ZEJKR1NnXzA5YmVjQUk0elRaeXZuZi15cl9zYTV0VUFRc1pMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9DeG8wQ20zZHhlcFdCQ2JSRmJHeEdBcjBqalAyQ2g1SGJId2pnWTY5Qjk1dmZkZDJXNDlsb29HWnFOTkpKQnFFSklTNEs2NlZuSTR3QXZWM1F2bGYy?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
         <v>7</v>
-      </c>
-      <c r="G111" s="1" t="n">
-        <v>46055.00770833333</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Is AI killing productivity? - InfoWorld</t>
+          <t>From Social Media Pitch to Loss: Odisha Crime Branch Arrests One in ₹6.16 Crore Cyber Fraud Case - The420.in</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:04:02 GMT</t>
+          <t>Mon, 02 Feb 2026 14:31:27 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFB1VTZOQWpQSWhQbjRZQWZyS0pCbkxuWi1EVHhQSWtKV0RmSTAyeENSVGVrcklaZnJLTUxuaGVBSHJwTnYtWXU5VVlFcGJPVC1qdWQzNzRsUXJram1GdHJCQzVHalV0ZFhZd1ptaWhabUtrd1RoRlNVUFoxZ1V2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE4wTE1raE1pNGg0bzk4Wmc5U3BNQVJiYUtaUHFZZHhmTjJGb3h5b2RzOTh3NGs2UDdVMjdOS2JFUU5UMHFFMGtBSS1fcTBRWGFoNlp4X3BfZ293R1lYVGtDWktTZ2lrck4yVkVDM08yS3RERG11Z1RWcA?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
         <v>7</v>
-      </c>
-      <c r="G112" s="1" t="n">
-        <v>46055.37780092593</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>How technology can help bank Africa’s informal economy - The World Economic Forum</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQY2VyZW5aLWxNNlhIajNPWXJfN0ZCSXh2T0xWSTdpX01yeUxoMGYxVl9tQ0xZdXhZMWJnX3JYMHg3YUkwZXdDdHJRTlNGLWtDM2doendjWTJKZVNmZjFxejlSbEYtalVKX0o0MVVUYjJIZVhNMkZFelIxem5DXzhzemZ2b0QtcHY2ckxrZG0zQ3ZLSnAzbkozOXhkZw?oc=5</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>7</v>
-      </c>
-      <c r="G113" s="1" t="n">
-        <v>46055.33333333334</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>West Midlands AI and coding trainer to open new Dubai base - BBC</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Wed, 28 Jan 2026 06:05:45 GMT</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1XN1BWU1ZLb24yclpFYnFDdmJwcHVXclBCb3EzLW1TZnRVUUE4OHpldEFPTFlobUpjdjBHM0NuakdnMEJyR2oxMjBHZFJPekFNU0tpVXNuMm9QUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>7</v>
-      </c>
-      <c r="G114" s="1" t="n">
-        <v>46050.25399305556</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Did artificial intelligence really drive layoffs at Amazon and other firms? It can be hard to tell - ABC News</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 08:27:13 GMT</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOUnd4UzhaZlNjTEVyRDVIbVgtMFJJcExLR1psMVdtWUxYcktJX05BUkFISUJLdW11Z09DYkg4UHhNVXdPc1NzdVI4VTdDWTBVNE5qSFVWRmU2YUtSSDFSWTJRM0pZWTd6YVRnQTRfcF9lUTE0VHVqX0N4TjFYS0FTSGdfQmxkU0IyekVEdnJjaXlLb2FaMHpLb3pKclJFbkktX3MtTmtlRDdzRWVHYlHSAbMBQVVfeXFMT0lRTjhydFNjTllyUF9qalVtbW8zSVdvSUpJcS1fMlY0a3dFb2VhZWtzZXhXMzdXeXVYUHd5TzNBTDRWcmRHM0l2d21yVkdhZEVLWFA0cGJHWG5hYkNTOHpMNFRhZkpIcktLVnUwUExqSlN0X1BkOHQ4dk1oWGdFS01kOXlKVWxYWGdVMkRnNHlVV2IzWUJVVDE3LXRDWXF3NWViTm9OOXlWOGV6aFVEb0pHOWM?oc=5</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>7</v>
-      </c>
-      <c r="G115" s="1" t="n">
-        <v>46055.35223379629</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>SPIE Photonics West 2026: AI Everywhere | Business | Jan 2026 - Photonics Spectra</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 10:28:00 GMT</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOVER5ekZJMjhVaG1QdWFaMlNMU3R5QjY0U2RkY1JqQllOVDhOcUJQaHJOOEswMks5dmdRWHB0ZlNjV1dRa3BxRlZ0SVgyeXYxaTBQQmRpWEx1M1NfZlh2bmoxaUF3YzkyZnJXWlhDX2o0QlZ0bGdHY0NhNnlvRUZrWFJDR0hkaU5aRnBN?oc=5</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>7</v>
-      </c>
-      <c r="G116" s="1" t="n">
-        <v>46055.43611111111</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>How AI Is Changing the Storied McKinsey Interview - Business Insider</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 10:31:00 GMT</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPTGQyZlRzS3c2MDdEQ1JKaWIzYlFkOHZEY1JKZWx2bkRfRTBLQW9mTGM5ZWk2dmFXQnpVcHA2dEJ3QTBQRkVRQnVJMjhSejFKdTBXbHh3VGlRSGMtcEh1S0hhNnktem5VLWZFTEJGdUI5SXpDUTBHdEF3a0NoUVhSMXJyMk5ac1U?oc=5</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>7</v>
-      </c>
-      <c r="G117" s="1" t="n">
-        <v>46055.43819444445</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Jersey businesses urged to beware of scam financial emails - BBC</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Tue, 27 Jan 2026 16:43:45 GMT</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1pWER4ajJRcUk3NHRXN0pMZkxGbWd4WjYzbnRzQUd2ZkwxNllfMXlFRElwSGpBSEJweHA1eXU0YnRlQldLcWFYdWU5NEFnNGNBcFF4X3RFOERzZ9IBX0FVX3lxTE1QckxlMlhjejd6enltLUl5ZzkyZ1VjeUlwcTJydUNqLUpGRVdVTTZXSkI0d1h0eUVNbS1KR3JHa3dVaVdyby0xWGVaWFJWVWwzRjFXYWwyMWxCTUlwSUxB?oc=5</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>7</v>
-      </c>
-      <c r="G118" s="1" t="n">
-        <v>46049.69704861111</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Email scams go QR - Insurance Business</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Fri, 30 Jan 2026 16:40:04 GMT</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQc2dSdFZPUVZpU29DWG42eFg3S21MdWZMNFdZY2p2cG1ha24tNmh1eWVkZk5Rc0tLYXN4SU1ORmg5WmRjbzQwaHJtMVVxM0gwb1FldUZScHJfXzVkbEp0bS02bkJERnRXMkhWOWxLcWEyYUhFUVJvQ0ZjSTY4MmRhbXVnODNMdmM?oc=5</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>7</v>
-      </c>
-      <c r="G119" s="1" t="n">
-        <v>46052.69449074074</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Scam emails claiming to be from Okotoks Oilers still circulating - OkotoksOnline</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 12:06:07 GMT</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNQ0txZE1iWXdHNlJjNVRKQ3g2SEN3YmJBdWNLTjd6RDJYbFMzYV9lYTJsZ1NUY1pCbmJ2REJ2YUxXQ1FtNXhCa3VCNDJfUmpGMGM4dnlaTTFvMnFXbF9VTlR0NzgxcWxYcGphclFISDFJZi1EVDUwd3BaWmY0NkY4V09wa0dzQ211TXpEV19uY1JSOWFxQlMxQjZ4SG41SjBY?oc=5</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>7</v>
-      </c>
-      <c r="G120" s="1" t="n">
-        <v>46055.50424768519</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>The founder of First Brands, whose bankruptcy rattled Wall Street, charged in multibillion-dollar fraud - Business Insider</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Thu, 29 Jan 2026 23:52:00 GMT</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPVk5Db3pJVzVlQ3c3bTdlaUswdUVFOHNET0I2Y3VfeGxpV011b0x2Zmdwa1JmQVJDdEpSNXBtaXR3NlF6SWc1eVY5dzcyQ1NKOW0yRFF4bEVkS20tcFVibW1sZUY0Q3VISUlQQVJZMEp6RzIwLUpHdkkySURkT3B5RXpyYkw3UW9hbjNRRWpiTFE3VEJvRlRNUFdNejZ5QTUwTHhlbA?oc=5</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>7</v>
-      </c>
-      <c r="G121" s="1" t="n">
-        <v>46051.99444444444</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>1st Circ. Upholds Atty's 7-Year Sentence In Email Fraud Case - Law360</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Fri, 30 Jan 2026 21:32:00 GMT</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxONDFkSVhyb0diX2ZlOWc2UlJjcjNtU2YxX3llS0ptSFBFV1ZScmt5Rkc2dHZoMHJ0TEFFYjc2cDZuc3dxV2N2N3k3S0tMT0NDVXc4R2FVcGUwZV9vUEpBS1FacUtTTlp6QnpuRGEwajROek9veWMzeWVjVUUyRXJoTWtMb3p1SEJRQ1JseG5ON3FGY21hdjZaZFp4SUxKdVZhWjJ0ZkYxQzNXS3RwNFdud3BB0gFeQVVfeXFMTmNOX0NRTVV2VEh3TFlCRjFjWXhoWWN6cUJnZzBuYVM1US1mR0tpb2ptNDFIcElrNC1WaVVZb05XSFc5TG5MVWRTRVhLMnRZcmFMc0tfS01WbFBlLTd1Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>7</v>
-      </c>
-      <c r="G122" s="1" t="n">
-        <v>46052.89722222222</v>
       </c>
     </row>
   </sheetData>

--- a/data/weekly/topic_feeds_week.xlsx
+++ b/data/weekly/topic_feeds_week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>National children’s report to Government influenced by local experiences - North East Lincolnshire Council</t>
+          <t>Importance of Natural Capital to the Scottish Economy – Regional Analysis - The Scottish Government</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:08:00 GMT</t>
+          <t>Mon, 09 Feb 2026 09:01:39 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNmItNlgyTnhIUkppVk84b1RfMFh2N3FIRS1BS3ZyRktScGp0VlJqYmttdF9HeGgtVlFDekpOS1RXanJrZlZ5YTI1ZTBTQ1NkaC1qbHF3cUNKZkpOTWZhYklMNzR5WWFOT2xHSDJVcmh0cDRZbmRlMEtZODBQZ1MzNlg3WlA4NW5NSmFpaExlVFpMSXNlejlNaWhfc1laMjBB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOTEJxbWVpdDlUUHY2c3hNa2huaENGUmtQQ1lfNTFaMDZfZ0xOWW5FaEhEemw2U3BqZS1PR2hMOURLWXNSanVNSEdXUGVNS0ZJcDlnVzlLYjZWYnFOeU9DMHVmQXZydGxKdzhKWmsxaXFxb0RHajMtY2N2YWhyaVdKZUVKcnFucWlOdFROczJyOXpiR3hvTW16RF9aZVg?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UK-India Free Trade Agreement is a significant achievement with a formidable negotiating partner, concludes Committee - UK Parliament</t>
+          <t>Social housing conditions barely improved since pandemic, says Housing Committee - UK Parliament</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 00:04:30 GMT</t>
+          <t>Mon, 09 Feb 2026 00:06:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAJBVV95cUxOa0JjOXpSbUJ5cjA4RXdDSXA0bG9yNGFnb1F5bVdiQXF0dDFWLUttMFUzLUxBbmdVRlZic1VoNEc1NTdfeTZqV1JidHphandNS1hOd2J5S0NxMWRnWkpGckF5a1BOSzJHcTI1VkdyQmFDLVJFS0hGYVhJRHlOOWFBdENxdDlFZFlGcU9MNURQY0JNTi03TkUxbWVvQVd3TnZGSlJJS0RCWFpGaUV1V1ZoM3A0ZnRtaEdBX1gwdmNXZnRUcW50WjZ5WXBzQ19lYTBnQks4NXQxVkJTTDdhMWFOUUtfYTZuMHpMNVlYTjJRSDFWNHZVd0VvbTRtc19GaW9wT3lZM1F1TU1pLWxZZVJFbGNycVU1eVBhNEE1blZueFFsOG1UZ3lkazZIV1NHbFNtdjlrRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxQUHVoc2NrM0xrSmNiNTFIZHNDRzFqZ2xfbVJ0UUZMMzgzTnlhYnNGSENkUE4zS25KS0R0ZGJmaGRPb2MtN2FfdzNLMzFtZWtyYXpDb3pBMjNXS1pzMlpsS2tCclFqeGM2a0k3d2dFaGFLYzFnel9Yd1JFRlU2VkpZaXZvOG9Va1pRaExYWGpoVTAxa0FHMVFfbWYwUk4xUHRWSVVTLW1JN2hUbWZ5eXhFV1Iya0k0U0dhSm9WQmk5UGVRM2JGakJXLWVOLWNDcWJuSlMwQThNSWNTV1dBZ0tmeU00M1NlbWFtQ0t4MEljUTFvS0cxNVYzUmhyQVgwZFZOVnZqcHhkZm8xZGlaSlB5V3NZUEE3NWtW?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sudan, conflict - ETC Situation Report #36 (Reporting period: January 2026) - ReliefWeb</t>
+          <t>I got a copy of the Beveridge Report for my 80th birthday. Every government minister should read it - Big Issue</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 06:33:07 GMT</t>
+          <t>Wed, 11 Feb 2026 04:03:31 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNX2haNFB0Y21DelpXNTZhMGQyVWxrYzlKVkJhUWFROEJ4WWhZSUNvbjRSb1FMR2NNV3g1VGtyVE53RUxSNVg3a2cxeDBXR1hoNHFTTWNoc3RhYUxHQWQ3X2R6cnBuQy1xUW1sTmE4SXN2Mm5hSGZ0TnJ5VTdKOTRjUi1rc2NlbVNmVEdnX2E5OFdNYml5MTJZNXd5M0JLaFpuQzFlRm9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNRTNGMzYxRFl6cVJCZXNhbWlPQ0ptbFhpdXpHSWJFMDVDTXlRcnZ2MlEta1l2c0poMG5od19neGJURDE3enVKVUdqdHdnUmthMjJ5dVUyWXQ1aExHeHlqMUxDb25QYnYxRFBFb0JjU2kzbFRhdXdydV9GamZCd0VieHpBSQ?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Government report warns Ireland lacks access to key EU border-security databases - VisaHQ</t>
+          <t>Policy report: Mapping the EU's long-term budget - The Parliament Magazine</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:52:20 GMT</t>
+          <t>Tue, 10 Feb 2026 16:54:05 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQNks4THV6akVUNEIwUjNXVVJ6VEN1aTNDanU1Y0QwalplRVNSSmwxaDhqdWFFb1EwMERKcWxlUk03X2ViNzQwZkRIbEVxOUZBeXZ2UVBDX1c0ZkRJS29UX1JYTzFSQ25hT2pvSWpEek10WGxwcllDNnloWlFXbGs4QnRScmw5Q1lFc3ZDM3ZFZ2tkdEJVWXBsWDAxT0I1cDdqQTA2VHZBNWg0Y1JmMlQ5bW1walQzSjRwaHM1b095NXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMGZ6b1RSQVkwOUVLQUFlYk5xM2wwMXA0ZXpqb3lTNm1hSm9jVUlqZDBSVmk0UVlpNXlxeFVEZ1A0WHlfTGdVU1JVVUlmdUtZRFdoWngtU0pnZmNXelJTRklfemVCbzRrNzRVT0tXMzJwcVJuNmw1YnRSaGVkcWtycmdValByeHNybWhVTEpGWE1qU1dib1o5TldkZ0tsVkU?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fox Williams cited in Treasury Select Committee report on AI regulation - Fox Williams</t>
+          <t>HCLG Committee report on social housing conditions: LGA statement - Local Government Association</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:59:28 GMT</t>
+          <t>Mon, 09 Feb 2026 08:46:43 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONUticHMyRF85OV9QcFRDQm5LV0YwTDc2c2RjZjRFcnpmUXJIcXRVWlIwSWpEdXNpbkp5eUMyZWh2UHNXbHFZcHlIZDJBWkJoQl96ZDAtdUtSc0xodUVGSzh6Q1pDTFdlal9RTmlEUVRZcjRMWXo4TE1feVlCaFJ6RExTR1ZYWHJZRllZMzZJaFhKTy0ydmVIX201Y2pPcHdIZUtVV3BzYm03YzIwbUQzYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNWxxSjhkQkF0WUZ3d3dzNUxCQ25Nam9rWkhzamg2MUhmRy1vWlpNbjhnRDRibE5aVnQxQ1NGQzJWQ0NaQ0JWX0FoMnlNcHNUbjZxZjdGSEsydWI4LU9PSlctVzBmWGVlSHlSVzYtazM1UXZHQWVNX1VWQnhoSjRBQzh1b3M2TDZjS01INFlaUGw3WU1DbDc4UzRLQ1pJZw?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;E analysis of the European Commission proposal for the revision of the car CO2 regulation - Transport &amp; Environment</t>
+          <t>Ipbes report: Nature loss could spell extinction for businesses - BBC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 23:01:39 GMT</t>
+          <t>Mon, 09 Feb 2026 13:00:55 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNUE5RNUloMElpdDNNNzAtWmNfdHVwalJXLVNiM1VvTkI3a1lOUTA5RlMyR2pxTWFLQWdYMElQWmNDbUlEVFMyU0dIYkRoZXY1WVRCWmEyNy0wdi1PTUUyYjZEWk9CcldMUENFSTBpbXNBd2V3bVI1MjlMZFVwamhWNGctalZLTGtvQkJ1MWRFdVkxR1JNSFd3TzdETFFLUFVIMUx5eEMzYWFVRkFsa3hBUlRoY28xb1ljVlJmX05xWFZBN0RxbWhob1NXczhZVEJTcHE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1DZjdQVC1veG1LU3Biak5NTHVoNTNobEdwOFhRSUNWRm9uY1JHMHFvMXRyNEJ0YlZBanlVUXFaNk1lbGk0aDNQQzJGdkxZOHZZeGxpRnNjWGVScW0z0gFiQVVfeXFMTVRYRk00bkp5Wnk5YmFVTmpON1lQeTFhZkJwYUZhTDltV0tJTWlBS3RrOW81c0hVSEJxYllobXJSVUdwUXYwR09sRWNBU1JyamVjaGtNWG5qN0RkMUg0Q211YkE?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thriving Kids Advisory Group Delivers Final Report - MBS Online</t>
+          <t>Situational Analysis Report for children in conflict with the law in Egypt - ReliefWeb</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 04:20:18 GMT</t>
+          <t>Tue, 10 Feb 2026 12:03:47 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPQ1lvX0FNbDhia2hlbVhlMnhSb2tKM1l4NlZ3RmZvLV82QzhnWmppcDZCU1dUNjNweE1DUlZOb21fVGlDZE5VaGdmUDE3WnNWNzlFQkktTDZpXy1nX0pFN2RqVXp4clNRdFZpQThsNHk5UVdzaE9tQ1hFblVnX1VkMmJSYjhEenFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOOG9HemJ4S244MjBJYm81WG9WUlZyU0lMME5qNzBOMHZ3dVBtSHhfRnhLcGF6b1ZVa3ZnSjMxZ0p5Qml2MkV5MFY1TDBQdW5nWFpTdDVBenhvRFNHazl3UE5hU0J4YUJXZHVQelJTZmxBTkk4SmpVNmZPOEhicFE4R0U1LWdOaUpuZ3VfVWdqSzVMUVdW?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Policy analysis: Prospective changes to prevailing wage levels and impacts on international hiring - AIP.ORG</t>
+          <t>Briefing: delayed elections and council tax rises - The TaxPayers' Alliance</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:36:56 GMT</t>
+          <t>Mon, 09 Feb 2026 08:28:40 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVFZfVmlvaDZhVXNZMjBKSU9aUFFydWxKTFlyRFZ0eU1FOEg4WDY4eGdDQm9FdkJtUVJNQmw3am9DZDRqZHVBeVpMNjlaelo4TWhiR3h0RDBCcUU2V3U3TmVUWVh0bzJvdnpISC1fWE9kSE5fVmhWYmtCS293UXltMnJYWHFaOEhlME1BTW5jVTRfOHNMNl9iMS12clFHSnkzYjVzUFlUR2MwNG12T2FaYWtoMmxfcU9BaVJRdzNGcmZTa2JV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQWnl2NTJwYm9oa2hsRHdsSXlYdFNGZ1RVME91dU1rSkk4RVVEQm1DUF81N2ZOcVRYMkNhcE5TdjZ5eVVBMWhGaWVkd3pfOVNhQzQzTG91S2ZRQzJWWTBSbExhbWVkZXRpcHNuVGR4QmdsbFNLcTNiZ2dWNmZIYm5XVlBnaS0xZw?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BetMGM explicitly bans harassment of athletes in policy update - Yogonet</t>
+          <t>Internal DOE Documents Confirm Climate Report Was Created to Justify Administration Policy - The Equation - Union of Concerned Scientists</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:12:32 GMT</t>
+          <t>Tue, 10 Feb 2026 14:18:01 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORjZNV0FPbUxXU2tKM1lqamYtXzJNV2dSU2djb3hSOF8zVzJUbHJ3UGE2eEV3aGNpNHJUZTJEUlFpNnhHVmFIWm93QThIcUJnSW5QMHhPbFA2Yk9zX0FweGhYR0VZRDI3V20wWkRta1BvZVlkZGNJb3I2dmFpZVQ4TlFjYzhJMFdRZjd4ZDFXZ283T1RqLWhKeDFLcHY1eDIwZlhSRzVZeHhPejJKZ3FiMExjUjhTQU96YnlodjV2aHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOTEVzMVN1MXlMSldHTkdWMnBvV0p5MkhuNXd5MU1aZ1R0c3QyenhYWm9CRFp3THdYYU5XXzJnV2I3S25tRWVfZk5jZmlvRXdfSTRsUThZcHRrUmtkVU9BMTVYenhmcE9mdWljaFBRM3hraC1VSTlZMmRZbWoyaTd1ZU1KN0lSM01hQXhlV2VIcFNUQjZ4NGpjaVFwdlhLSzNJVFZaM3V5QUpOSktad2g4UmpORk80bEMtSkkyNWNXYmgxZ0FtRkJB?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -721,27 +721,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UK investigating first suspected breach of cyber sanctions - The Record from Recorded Future News</t>
+          <t>ICYMI - PBOC pledges loose policy, ample liquidity in Q4 report - investingLive</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:46:57 GMT</t>
+          <t>Wed, 11 Feb 2026 00:27:01 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQLVYxb29zZ3JfTnpfTHl1TGp3emJHQjNrR2ljZk9Zb2RsRG5mOFJGV0w3dnQxdW5BTjFlRzRnUEhmUjk0SFphWVBSeUo0bWZ4bWRzY3Z4R191QXY2QU1hTmJ1cGthVGwzM201TUtRc2NreUd5Q01HbnZjcHR5alNUQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQV1Vvakx4ZHRXUlo2eUZScFhzNjl6emNQZGZoanNaOWZDbXl6Q0cwZzYxbUZGZEF4QUJnNWRUNjVURF9GVW9qSTBsbWs3QURyWWhPaXlWbUlDNGZ5blV1ZVM3SGI1MDF2NXo2dGFIZmoxRExoczBGUWVBUzk3QUJJWVo3cVo0a2Z5enBMM0oxVnRjSzJwU0FqLXNDN1Z5WGtaYzRKNjctYWI3M1Bw0gGyAUFVX3lxTE1nS0w5TVc3R0l4WV9MMDdjdEdzTTVNMjFIeC1DZHp1cWs5REdvdTRVSWxrczhzOWlPQ0VUdm11Q1VKanNINjBPcmJGdWZmZ0xfcUZTTWNqT0k5RnNOWmpaQ2czZFBnTnJZZjAxZ202eUI2Z01vRWZnMGFfRWY3SGJOUnIwU1hxUTlJd0VQUGlmUXg2UW9BM0JkVFJJSG50NXpSemJkdTd5ZjFvSDhZMWU3QWc?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -751,27 +751,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vale's transfer window round-up - Port Vale</t>
+          <t>Global Humanitarian Policy Forum 2025 - Protecting Principles, Norms and Values: Summary Report - ReliefWeb</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:02:05 GMT</t>
+          <t>Sun, 08 Feb 2026 23:25:19 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1QTGtyOVQ4Mm9Nc3NxZ3lfRGpxN3diUktMS2Fnc2RhYmdrRl9adEN1N0Q0c3dRUjhrQjVaZU5MOFF1RzFPRi1mYnFBTG8tQVlfYWdRVXh4R3FqQ3ZYVG1sSE5fWlVyUzNsWWdPeQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPNmpYUGpRU2x6eUZtWkpOMGc4QlNEZEVTdVE3NWVuSjF2V0pQMHRlcURkVUtUbDg4Q1RXMGtwWmdYaFVkaWtqclFWUF92QnJHNzBGQ1MyR1pMTXNoYmZ6VjdhNUpERy1ZZXpaN1hNb2ZacGVPLW1TOGNFSjZybkJoUHI3UDByTmJCTGpwZWUwQngxMk40ekJhNkc2REY2YzhWTi1TUXBuNHNxVXhaY0NkUGdjR3N3S0E2djhwbHI0dFAwNi1j?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -781,27 +781,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trump to slash India tariffs after Modi ‘agrees’ to stop buying Russian oil - Financial Times</t>
+          <t>[Research Report] AMR Policy Update #5: Cancer Care and AMR (Part 2) - 日本医療政策機構</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:18:04 GMT</t>
+          <t>Fri, 06 Feb 2026 07:39:24 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5DV3FTdThYajVIRFpBZzdyeU9lcENzUVNwUHdUUGJ5VWU2RXdaS2l3SmlwVXJDVUpYQmhvdi01QlpXTVRucEk0XzhFWnRvd0N6UG9TMU1obDJYTXN1UENLMmI5eDNxN2FVWWpzUnFDTGQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE51OXpBMkdhdkRGRG1OeVRzMk5PNmpFMEN6Tks2WDdqVXlFRlB4aGlQOHlrLWlQZGpVX3RCLU5ER2JzS3FVcld5V2xBLTRpeE0ycmdUVnpudUI2di1xTWhBR3pJQQ?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -811,27 +811,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Disco Bingo, exclusive port tours and a mini circus – what’s not to like about Love Immingham! - North East Lincolnshire Council</t>
+          <t>OpenAI policy head exits after discrimination allegation: Report - Storyboard18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 03:22:38 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZDNwUmkxbGNOdFpTdEFhaWNxa2Vmb2ZfcFZHZjBnZVc4OEZxRlkwN2hnTDlKQ2RqdW5VUEdLRm5na2dQeF9BSlZuRW5wTmlGNTBmQk0zeHlRbEZCVjh0bWJNU1dYWlZOSU9IT3ZWQmYzb0MwVVRYdXM1NHhnc0R6eXZnMWxKN190MU9DWGNnZUtJZ2l4YTdhdU42UTdZWHN6ODZLd3BZVXNPcE15YkZZQ0t4ZXpRVFo2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPN2ZxVTVMR25DTWhUYy1xQTdhNkFJUFRMYWxaeElsWXhFMHd5X0VqekhrS3IyQWdYQ3RkS1NZX3FhdFM0ZkdsdlJlT2RjejBKdUdPamh3M3lhX2lxMFJvTDVQcDFjRU5vZEl4NUFpTFVJLS04WnF0dVFMdEZUdmpXVExENlJUZm9tS2w4NWZCN2VzSjJ2NXR1cUFRa0hhcWVpUnRkendxb05BZkZkQUhR0gG0AUFVX3lxTE43S19McW4xTWF4OXMwZG5LVUZtS0d4UGtDQ0ZOSHR6SjRFWERKSnpZbnVVb1paWUpjNTF3TndkUXVnV2otQUxuMWx1MzlObVZFbllGekdldXJuWXczRGFHUFJ6OW1mTDlCSUNWYnUwOHYtTm5KY2QtdjAyRmVIdE5YdE45VW41aTUzN25Bc0t0WE5Od1k3amRWS2xSaC1id1dUejRXM3lQdXpNNDY4eWtKbWdoWQ?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -841,27 +841,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tribunal upholds FCA sanctions against Banque Havilland but slashes fine - Funds Europe</t>
+          <t>Euna Solutions Releases “State of AI in the Public Sector” Report, Revealing Where Government Agencies Are Finding Real, Measurable Value from AI - Business Wire</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:07:30 GMT</t>
+          <t>Tue, 10 Feb 2026 15:54:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNZGpzd005RFUtY0tMaWRyWV9PdU1MWkJreDRKZ21lbi1yTUItSGItRXE5VDJLNURDQUNqUGpoTEVaaGtiWVMxUjJ0VV9NZFJha0s3aFdjOXlweUR5ckxlR29mUExKUzVydEU4VmJBMWtJb0E4eTdfbXBUYmFobzdHdDgtanp3R2gtZU9mUHdXMlZqdlpVNWRfZHU0ZUZEWGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxNZFU4aHNKcDBXZDI2aTRQSGswZG1mdFRKM25xVDdqV1lyb2wtdXBVSkZuT2lWRjltY3VBT0ZaRE8xY0lKem5zRlh6Z1g5cF9VbFRORndCSVlRQXhXZUVKRFB1V2ttcF9DbG9NR29YSC1LTVFKTkg0eS11bkRfcTJSc253ZlM2Vjg4X3dhOVFRV3lTQmZERTYxUUdDeE15bXBrV3BQZHdaMnpmeVZjWXQtR1Z2aVF6T2V4OGpUN2JQWjd5aE5mcENwU3U4QjIwcE1aT2NrSE12WUlOX0wwUWl5Z2Y4ZWhvQWJjaFNXYm41M0huR1MxeVl5TVpBckVxRTVDMTZGd1F3RDhnM240a3FKbHFsS2N5X1BCNW5LTVBheXM2RHVH?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -871,27 +871,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fortinet: How to Build a Secure Digital Supply Chain - Supply Chain Digital</t>
+          <t>South Sudan: Conflict in Jonglei State - Flash Update No.6 (as of 10 February 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 21:08:30 GMT</t>
+          <t>Tue, 10 Feb 2026 15:50:57 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNUmVQOFVwRTZ6MmdWTE5JdVhZZ1lWQV9hWHdDR3FTbzFWWEs2X1JOMDNzMjdfQkNpNndFQ0psSmVMbS1CNENOQXllbUk2MGJDUjRxVVpYb1lWdUZMcVVwdDFSalpLRVVXVklmUm9xTDJ6TXlpdTJ3MXRrSjdObnpseXRDWXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPLWFMYzUzOEt3a19BVzRLQThYZFZYM3FNVDZKelBweUhlbTFCcnl2aXkzcTltc3p5TjM1Ym5lWFFsbXJTbjc5Wl9rVThORm1NeGt6MmRCUXpzY3lhRkxEWDZEd0Vpa2FYYmFvYTBqWUxzbHFIa25ZZGxGeGMzOEtLUEFuN3ZxSUQxMzc4bHdqSXVBZDVuRFlHejRvS01oTDVwX3MtRFJFbktnbTROQkE?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Canada faces ICSID claim over Russia sanctions - Global Arbitration Review</t>
+          <t>Sanctions-busting shadow ships are increasing - the big question is what to do about them - BBC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 22:09:45 GMT</t>
+          <t>Wed, 11 Feb 2026 00:17:37 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPSzRidXRjaDhZbF9wQmxWYkhYMEJkZlQxRkd6bUIxWHI1dEtZWFhNb29DR0c0VmFKaWo4Tm1tQy1uczAyMlV3YXJfVEc1c3FidXZKWGVwdGpCWlphUThEcUJ1cUZ5a2RBT1FfQ3pmeGtVbVhqUUNENDcwa25rN2NJUXRYZi1hWUNfQm9yUHNKZU83d1p4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE8tYnJWQ2piRzNBWlg0WUZQZ2NCWnM5VTMzNXJaSFowbUEycXZySGhmMElwSC11SThYU2FLdUxtaFRteFlsM01YTVZMOUtUVVgxX0s0Skkxd056Zw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Op Chirk: Over thirty arrested in Swansea and Neath Port Talbot - south-wales.police.uk</t>
+          <t>US plans Big Tech carve-out from next wave of chip tariffs - Financial Times</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:00:00 GMT</t>
+          <t>Mon, 09 Feb 2026 23:27:26 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOeHByb0hvOHcySzBpb2liZl9zeUZGdmJLMTl2d0NIRnRYdnhpelNmV0Y5Y2NYS0VBQ1RhMXBrNFVTMXBqZTVaYUExb0pqR3h2NDZuSjFrRDlTZ0lZVmNpSVVlWWhieHFNVGU2em5tbU1QajBONmVQYzROdHFDR2ktWmxfbkZhemFEbFNzbGJzeTlZRzBnOUJiT1dFLUI0YVRLTjlha0xxcmROblpLOW9zT1NxSF9SQjQ1Vm5PWEIya3YwVGd6OHFHZU5ocFRXdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE02QlNTMVdWQjVZR09sQ2NhdS13SWtXSmRETzhRdkV1Z3pLZFAzSmRqaTNZTWEwb0pMbUEyNkVfdFlDNVNkZXhfUTlyRkliWUsyZzZtTkcwNE5GUGZvbkQ3azNDRnE3UlZYSzUyLW91RWY?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What channel is Port Vale v AFC Wimbledon League One match on? TV coverage, live stream and kick-off time - Radio Times</t>
+          <t>Tariffs and falling demand leave Scotch distillers under pressure - Business Matters</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 14:50:13 GMT</t>
+          <t>Wed, 11 Feb 2026 07:13:24 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNQm45aDF4R01VeW1FTDdRbS1Wb3pTWC1UcUNKdF94aHlWSU83ZEFtcjJKakRudkV6MnBtWEhCTmVCb2UxUkxBa0d1UXlUM2RReVNjNUZwQlZsRnJTaklMdE9tblBCVjB0QlFUODVwWjl2c0lWMWhVQ1hwNERwd1g2VDd3YUYtalk3UGpkeUJ5UExtNE52QmpQR19rZGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOVkYxY0JNREhERW5tdEo4U1FVS1ktUFJHMGZvRFlBLVU2cXpmLUxka0dncjM3MEpoMWdHZ3UyM0I4SE56R0N0TWZBb2xqWUE0NFdXWHFja21CTFdobUR2ZWJyOXU0bEhaWEhYcWQtR2tyeEVKWGZkX29UUW9UTUQ5NnFZaG1MdVpYY3BScDRMamV5dmsxZzNZ?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Deadline extended for 2026 Everywoman in Transport &amp; Logistics Awards - Fleet News</t>
+          <t>An Invitation Into the world of elevated luxury logistics - Air Cargo Week</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:05:44 GMT</t>
+          <t>Wed, 11 Feb 2026 07:30:23 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOSVk5MHZuNTRobjd2dWdXd2NtNFREXzcwbk9reklJRnRBNnp5RDBVUElzUnpFRTU0ZDF5aGp5WVktUmY0d2V5NlYzZmpqb0JjS05HQjZTRk05ZjhjczhDSXdjTHllR3pteWZXU2ljaHZQdUNDamFvV3ZKdHlyS2JROU5sZ1A0S2dmRVFVVEZUQzNySTNmaklIaDdRUllkN21FbEp4cHBxbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQWEtnY1F2bFNudGFMZ1I5WHJ6M195MXI5U1dSekxlcDREa2tDaDFiWkhaMEpfOGM0ZV9aNGVyd2NKajlYZC1heU5nRUF4TzdMZG1tOWlrcG5HS0ZiOGJTRkxYc2ZQWW9oeG1odVF4MlRlQTFlMklmbl9RaUJMNEFTakpSam9wRk9aeE9B?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Report: Late Maycock winner seals three points at Port Vale - AFC Wimbledon</t>
+          <t>US sanctions officials from Marshall Islands and Palau, citing China fears - Al Jazeera</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 17:06:53 GMT</t>
+          <t>Wed, 11 Feb 2026 02:44:59 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQWklEWlZuQmxKQjdwbndIRS1peE8tdEJDVkRqZVZkWWNmUUFPSGUybDNsRFRnSEVpTFhYeVpJZUxSQk5LM2hucnRwUFdnNE9sVlJjOUZpQmRsVmRrbENUR0FpX2hCbFRuZ3NMWnJGT2xocjhzX0ZGMGJXMnhmclc2bXdWY0tjd3E4NDFYeTF1TmpFRkh4VktSMUVzOWdBNzljUHI1WTFZcHpGVkdpRzA5dWItZU91TDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZ09FUDJUdmZSc3dPc21lenByX3lSaTZicGZFMkdmMXRWSzE1WV9lQ05NMUotZVRKVUpKLWtpSEhsV21DaURxVEJxT2RVcnhNUlRCM3VGc0tyeUs5WENOSVR0NjNrc2dobmFiRVRZSDZkVFM3V2h0U3ZkdjBKbUZnUzlGMnBVaVJ2TGlPMEhQUlVqYjAtamZ3RUROa0U0bk40dS0xWkxaRVhJSnFQLWFkckRlZ1XSAboBQVVfeXFMTWdJNlFOa1RuejF5bWY0aXVFWElHZnVUYjdNaEYtY2NvWW1hY1ZwYnJ0LTRFcHUzU0JGRmt0bzJEaVZPWlZ1M3EwTXB0QUpHR0l4OEhXLVJhbDNqRjlCQ29hNVA2ZDRRVThhNFZBYW5hbjl1TFhwckVtVGRlTHhWSmJDYWhPRFotWERJSElfcTZURGxLZEpESWNhMEEtN1NRNWRoWUNvdnV0c05tRml5LUxTSWI3U0lmTjJR?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How The Old Dominion Freight Line ODFL Story Is Shifting As Analysts Rework Expectations - Yahoo Finance UK</t>
+          <t>EU Considers Sanctions on Georgia’s Kulevi Port Over Russian Oil Links - Organized Crime and Corruption Reporting Project | OCCRP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 05:12:00 GMT</t>
+          <t>Tue, 10 Feb 2026 23:28:27 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOeC1zTXRDb1BBSElUMzhrNVEwSWZzemI3S2Vwd2NmaTNZSHk5cGc0NDh2UXR3M0I0WUdwZzBOOWY5eWxUdGFQc0gxX1F6ZmxVeTdlRU9sRC1nSVdXRlp2NWpXcmd0cWRBaHNPUVlsRG5WTkxvNEJreW42VHZYY1VhSE1lOHhSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOVBUS2Q1MGNTdnZHN3FCcDFqNUpBNU1aeWVJNi1JN1lzdFFNMURJSW5LNWRDSHdpV1BEeGRHUXMzOWdmbzJjMEF2WkhwVEpOcVJqeVNkLXVLbnpBdVNxTVpySVR4Mm5xTUsxSW1fc2lsSGdjZnJlNlBwbG1lTzBtcFpQNEk1bURYT3NSQWsxU1dEby1ELUpsNWg0Z2NJbzNk?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hope and uncertainty as India and US strike long-delayed trade deal - BBC</t>
+          <t>Yorkshire logistics firm invests in new facility with HSBC UK backing - Insider Media Ltd</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:29:43 GMT</t>
+          <t>Wed, 11 Feb 2026 06:03:04 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBoRHZ3eDU2UERBbkZfcHFSSFdicTdPTFdCM2pMQjJORmV6TGFhT3poR2hzamVwN1V1QlF4UDIwMTFDT0gwZUJwb2EyX05Kd1VINnhEdU9fVDIyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQdTlBYkh2Nk04aGRoRXlFel9hNDV6VU5iR05wQW43bWZTem1tRnhKMXhZQ2Z4emt0MWpLZlNxcTRSMDR3QWFWeXQ2bmx4R1VtN1lXc0NYTElncm9NV3JrbkJXbmRveGJMZklWcVZDcEZ2bm1TVXhDbE9qZWtoRHRZQm0zOVQ2V2EzSHJMVm9BRzJldmwzeFQzZEpjRkpEOEhMLWQxZFpHdzlEVTVVSFYzRlVUaw?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Andre Gray is a Valiant! - Port Vale</t>
+          <t>What Does the Descartes Shipping Report Reveal About Trade? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:36:50 GMT</t>
+          <t>Tue, 10 Feb 2026 17:31:51 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBmTTI3Q01qcGdCYjR1Qklwa3JNNTNNUlJ0c0VNeGhQMTdVVmVYbGg0aEgxT0x2VDdlcnNLOEYtMDg0THU4MHlCcmRObDNfcnhabjJBTXQzNFdqVm5wWnNfUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE02NF9uM3ZIMGNyb0ZXNnFJbVlSY2RVd0lPaGJTVktsd3ZHYVZEODhUd0FpbENVWTVSYTUwRkptcWJkbmZyT1FEU0VTY1dFampOZG9ENWQ5bmdCY2tid1hrMDBHeFhfdlZ3d2VmUmlBaWlzZEJNOWc?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What do EVITA Trials Mean for DP World's Decarbonisation? - Supply Chain Digital</t>
+          <t>Broadband social tariffs – how you can save £220 a year - thecanary.co</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:36:12 GMT</t>
+          <t>Tue, 10 Feb 2026 18:10:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9tRW4wWlhVWlQwdzRYcUpRdS1OSkwtUWh5VFBiN3F3cURlU1BiTjliMFFUVWx1eG5jclBKSE5Ibk1GRFZEaks2VGd0VVdaLXRzeUNleGRqMWZTbUJfcDZxQUp3WjA1a1pVd2lKSjlwSG1CM3lJSWpFVk80Snhadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeGNoX0hSSUhKUU85SVJNX3d5UG80MEgxaGt4TEczUk80bUVuWFNBeWd5Y2haY1BpckVfc2ljMC1WNzQzLS1yekE1VWFYZm45REY2cWFaaU5mLXozZnM3MWZ4d0tXclE3Zi1ISmNyYW8zLUZvVG9SOTdvYnpvREs2M3Fkc05TQUg4TjQwMDRWMmV1WXpzMGZGei1oRUhoUQ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Will Cheaper LNG Reshape Europe's Supply Chain Strategy? - Supply Chain Digital</t>
+          <t>US giant buys €65m Milan logistics hub - Green Street News</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:59:23 GMT</t>
+          <t>Wed, 11 Feb 2026 07:47:47 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSTFGNkZPaGZVMXlYWFh3NEw0UXdvaWhGMWZ6UjJkdFM0bll1Tmd1OEZ4Y094NDdMLUt2dGdHQVdCY0s4WkFaREVZS2JSdzcxTmNLSHNPNEFidW4wWWhoU3djVXF3WnNaU2k4MjNvYVdLRWZoUjdGdURlSDNzY3NMZFhpVENXem8zUjlCSFl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNenB2UXFwQWVCVGgyTzFBV25DNW9NZm5jcU9jc0VOVHJTNjQtUXp6VkdDQVpfbFhhVU92SDBBM1dRdUdBSUhaanVYOS1zNmdJa1E4Qmowa1hqVVoyNWZ4UkRnM0pjWG44NFgyTFB5SU5pTUtJbkdKYm5BdGtRQUVrUw?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DNB shipping loan book rises in fourth quarter - Tradewinds News</t>
+          <t>Why Haven’t Tariffs Trashed the Global Economy? Explaining the ‘Global Resilience Puzzle’ - NIESR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 07:06:25 GMT</t>
+          <t>Tue, 10 Feb 2026 09:05:49 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQajdGNldSRzk1V2E1cHVXM3J5NmdVRU9zcFp1NkRxdHYxQ3czUzVpZHY3RmhsNWh3aHZibUcxaGt6Y200c205QXJUUmZDUHhvNU1wN1ZjUXliQnZ4dm5DMV8zaGFQenlyV29PYzF6djJ2NzZjY2YwWTE1RzFXUHN4d29HTERSU3Y4UkZzMkQxeENtVEJsYk83aU9LcjZlZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE0tXzRKOXNVekVwYVRBOFZpamJleGRjUGNlMUJ5NU5XR1ltODdwVVl6eEFXc3hmdXpHWTJORGN4SnpHZUFlRnp3ODdkSEdfUUxUbDJRekpXTURSdm9jLThYbUJHSkhNVXRQT3RFeXNQZURTWFJh?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sumsub Partners with Fireblocks to Ensure Travel Rule Compliance - Finovate</t>
+          <t>Europe’s Russian LNG ban has a shipping loophole - The Parliament Magazine</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 22:27:00 GMT</t>
+          <t>Tue, 10 Feb 2026 16:34:32 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQOUtVbXppa0hOcUhPTmR4Nm5RWDJtdWRaVnNyTERVdjkwT0NnRE9ObDl5aWRtQnhIZ1JxaG4tOUhPMFhrLXg3d21Ga1pZaE80SVZXdEl0MHViYUNiLXVCYTM5U2pDSmxUOFFad01yZkstSTA0S2Y4czEwSGx3dEQxT3Z3aFRiVGlQcWZxd3lnUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNaEs4VWZCQ2hRNklpZzZ6NFFackxWcVVQc2pCQ2RoMThSVUE4OGpQTDNXUnJ5RTUzMlpSU0JiMWVBd1lHZkJreWxfSUkwTlNpN05Xay1CYmpSam93WGxRM29iYmxSZVN1WTZULXhBZDF2MnpvUHBEUUUxdEhFQUxrOTBRWGROcnhaZzNSZ3dESWJtX01pY1k3T3FBZUZsQQ?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stiffening European sanctions against the Russian oil trade - Brookings</t>
+          <t>Dining across the divide: ‘Tariffs are the one thing I agree with Donald Trump on’ - The Guardian</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:57:39 GMT</t>
+          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQWlNPcHQ3bkY1alBCeDF6V2FKTzgyZlY5dVNiZjdja2Fnb0RoZThSUHpDaDRKRVQxaTY1U0pKbWU2UHBCU2NnQXd1NVFWRHpmQ1JpWTdhb0w5RVJLN0VPMGFJRU5xclhVaEt3OUNuY1hzRk50bDlXMmVIZ0VTWHAwM2I0Z1ZwM2hIaGl3OEJsUlJVLUVoekhuNl8wYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVno1bmFoU0l3ZEhfWG5yckFyUE5PVVMzMnpGcHZDTVl4cEExS0ZNQnhDX2ZXTjFpX3V3bWpwcHQwQlVBWUpWSFBKZEpRM1VxRHlxdWRDUUNPOWp4NThyV0I4Y2dIanlsNHRuVXBlQjdtSF8tRGdNRVMyWXFUcXdaNHNaNkJaNEJUS0xfUTZWVjUzM3FSamg0MklpeXZobVdkRnZOVWVKbEZra0ZydHFmUWpHVWxOTVNzaE1HZldJQVFVYmRRRHdWM3lGaS0?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>P&amp;O Cruises says port fee commission shift brings it 'in line with industry practice' - Travel Weekly - Home</t>
+          <t>Bangladesh secures lower US tariffs and exemptions for clothing goods - BBC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:39:00 GMT</t>
+          <t>Tue, 10 Feb 2026 03:26:05 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRjA0bjhCMDZERDZCSjBzNWc5N2dHWFN0eFI0b2ZVcm5fZE9sOU5PWWpnOFJYQjJqdUZEZGU2ZGtzWE9jWFhPdFpRa2lHa0RPVE9OdTNiR1FqNjdLVl9MaVZxb0dCQW95dmN5QVFKVk9Mdkd5MmNXNGs5dkFRWXJlVklkQS0teFpQTWd3dFhDUWpqa3UyLVFIVE9JS0JuM0l0OXNhejF3YjhnaXNJN205Tlg0ZXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE00RDA1ZHRVYXYtTkpxTXZoSTB0ZDRtSTB2VzdNdnVyMGR2NFBKV3JuYXhOang0ZlUzNS05c181WXpmQlNaeEpMUFpSMVdjWEZLNnlOeEtFSlpqdw?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DP World's EVITA Trial: Decarbonising Logistics with Trucks - Sustainability Magazine</t>
+          <t>EU seeks to ban all Russian crypto transactions - Financial Times</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 17:38:03 GMT</t>
+          <t>Tue, 10 Feb 2026 14:02:22 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNSjF0OVBpMWVsWkFoUDZwdUhIYk9HWmVlUmM0ZHgzTnlqQWdCc1BYWi1aaDd3MW16cUpsVXc3RnMxdkJSMEprcEpTbUpzVzdyZFdIOHVySmVrZzE3My0tMlkySHU5Ym80SWhGRGlTTTFZVmdSeHYtcFdNOFZHeHd6SE01LXI2cFRuX1FtemxwMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE4tOFVKeFFXc0tFSUszczJrTzlwU2p6bmJUc0d6dDh5M3dvLWxFSXNKNDUxcjdWN290TWZsdHRqSDVZLWVvUzJVOTAzWmh6c0Z6cmMwSzZGZkRMTnFlOTFXRnRVT1VDd2hPRlo4NkpkREk?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WADA provides update on the compliance status of the Comité National Lutte Antidopage de Côte d'Ivoire - World Anti Doping Agency</t>
+          <t>US imposes new Hezbollah sanctions targeting gold exchange firm - Al Jazeera</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 19:28:29 GMT</t>
+          <t>Wed, 11 Feb 2026 01:14:02 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNRG1BOFVWVGdHVHZVY3AyUTNIejFZTm1ORUlyWFRIdUhmTmZvc19TTTZVS3B5RDJ3X3VDb095ZWRvMXBjWF9FWmhQUEI3LW1hTkUyN1NjS0ZWYjdXRlZHaU5ialNodkxJUGUwMmhCLVhySTY0MkFrQi1aM21UaFpaRS1mZGNCQy13aVB4ZTVleFlyZVZpdGN5U1E2eHpCTE5sWWhEM2JPYWQ4V0x2R1dVZFNhZ1ZKY0FrLUYzWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQZWZDeVNLNFlvSkF2bmw3RWF6Rjg0WXNRM3NGcHlkOTNLR3dTLVNJVUo0eld1ODQxT1ljWFRxTnFYLVlpcWVpR3dZTUhocHpOaDBDeEFmZGNvRXRWSDNrUDRodXlJVVJHcFl1ZFNma01RUDROWXhyNGRQekotNGxac2xINl9YMHlOdmVwXzY0dWZCeDFrYTR5T2p3MlVlNHZvNEt3Wk1KVdIBrAFBVV95cUxQenRYVmlrVjhmLVpBSFdPYUlZZDNqd1U2Y2ZhbnBXcmtKSXNPcm03ak5RM1ctc3ZTUENucnRjUFJhYjROdHVzWHpja3g3bU9IMUdaOVFQM0RFVmZkM19tNFZ3S3lXbGR5czdiMy1qTzNfc0xpemVpOUs3Nk0xQUtISm9TMk1haTRLcWVuZVhzVUwtdHYwdnZodHNNbVBqVnpNaEhxRDcwWGpKVWpT?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The Myth That Foreigners Pay Our Tariffs - The Daily Economy</t>
+          <t>Oil, tariffs and farming: What we still don't know about US-India trade deal - BBC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:31:00 GMT</t>
+          <t>Mon, 09 Feb 2026 09:10:46 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOSWNTSWVzOWxGeHJfTGkyaTgxcy03dEM3VTJMZ2g2d1F2ckZGQkwwSlJ4NXBHcHZvWHZFaUwxM0hyZC16X3ZYSVdoU3hNX1gxMkUxa1NqRFo1X3YzMFVmUEhpMC1jOTVjZnJobUw3dUxPcUpoLWNGN0lfUWZTMGg0S010Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE40MzNfeTZiTi1pV1FnajBXc2RwZ0RtNlNKWWlXUDBtOVhCa3dFNi1PRUVPc0dIVktDZ0FvbDBGYVdBVUJDLUItWFFuMG8zeDhFU0lYaXNnRU9sdw?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CUBA: Oil sanctions will hit the poorest and weakest warn bishops | Aid to the Church in Need - Aid to the Church in Need</t>
+          <t>Shipping giant MSC facilitates trade from Israeli settlements through EU - Al Jazeera</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:29:29 GMT</t>
+          <t>Mon, 09 Feb 2026 10:02:46 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQWlhkWkN4dzFMUjdOaU5FOURSaEpyQnBhQURFZjV2MmdtLXdUdVljaXRnOGloVnYxMm1iYTZrcG9xMlhKdXZrMVdyWHFiNGhlN3VlZDJvSFN6bHppNEc5OGVqRXlYX3dKckdoWVJtZjBVZ1dleTFOczB4MnNNWGl4TEU3eDByRXYzNF9IekFKRHhzdGpFcHF5dFJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOdXd5S1R0TS1hWW43U2ExSnpGcU9wWWxsMFFTbHlPT29oSWRzLWlyQjE2MDZ2ZjlLbXpqaXFfN2dESzRkWGNfVFZSaWlnMzhQbjRRZkJvdkRlQldnc3o1S3hfRHo0WHQybVcwaDFMdHVxT0dzeEo0VGtTMlFFak5JOVdqT0xSbTU3WjRObTlHODdJd19yN0FlYWx4WjRmZ1VUVF9ZaVNPSGw4TDZVVUpBM3VR0gG3AUFVX3lxTE8xaUpIZlg1T2hfU1BDOG9UakJWaGR1VVpNcVltbGxGUkVhTjE4OVFqNzVqbDVmdU10ZzN6Y0QxaUZhLXhka21CUmRYSkpoQmpLM1ZGRDl6UlBCMDBtekthb1NjaFIxTjF0cnpOcmFYWjlvWVFicUFQZzVaMGZaUzVERERISGRHUFVRblg0TTgzbElqWWN0WjdOM2llQ3Zyd2NhM2xPRk4yV0sydFVYT1g1eUx2WURTQQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Massive Parkside regeneration scheme approved - business-live.co.uk</t>
+          <t>Full Fibre ISP Hyperoptic Add Faster and Cheaper UK Broadband Social Tariffs - ISPreview UK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 07:21:00 GMT</t>
+          <t>Wed, 11 Feb 2026 07:38:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOLW1wZ2pQdDJPR0lRWWJBSTNzbDlOdXNNUGdxdE9Lc1FoczRNY0Frcl92TGxMQW4wOTdFSjNKMVhQQTBZcS1YZ3hfblZFTWdvd29Tb0xCdExUSXdiakRXYmp3VVJkcDIyWG1oTzFfSHpndlkyVDVCZ01VTFlBSjYwZ0pnRmRhVGVfd3FQQ3pPM01ybHd1TnhJX3BfdTdXZ9IBowFBVV95cUxOU3pxeEx5WTdVNmExVEhXeTQ4alNXYS1OUkNQWFJDUW8waVJQNVRTQ3hudjNNTUtubW5sMWtPVV9VbkQzN3o3X0dFelZveG5leVlkZm1YQkZjb2RoLUY0S19tR1k3SUdmUGZvck9ZNFlyU28xek5YQXlEZWRrSWJZNEtJdHVfeUlDSjc5OW44MDNJX1M1NTFKUTNHZnBkTjVOS1JV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNcnE4RTdYOFZCWl9sX29sdmI0WXp3ZHhqSHNKQU1JWUJ3bjA3TVlTZGJHb2hvMzIwYlNMU1VlX3pCSHhBVzBDa1VxS1dldkU2RVJOQXNhZlE4cEREUEwxNkNTZXpDVFB2dWJvb3hfSXlUblBlUXNsYk5jbEl1RUhYc0lCQzZwdVN1UEx4UkdyMUszMXpYZnZyc1FQaUMzZmNuTVVaQm5HMHFBWWNmTWxpQVJSUGdhVkxfYjNleEhFNUFRQk9UQXc?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Two arrested over attempted sabotage of German naval vessels - BBC</t>
+          <t>EU financial VAT exemption questioned in European Parliament report - Global VAT Compliance</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:30:11 GMT</t>
+          <t>Wed, 11 Feb 2026 07:04:58 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5vUVFxb0Q0Sm9Zdzh4NllUVW9VRllRSEZZVGlSNzZFbzlrUmgtWEpQYnpOeHZHSVZxbnBuNzNjWHU0ZDlpR3I2bzRkenNPMXU1X0ZhaFdFQ0MtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPNGVzbmZMcGlmMUF0dzFyd2RFWXBrNzVsMnM3Y3pibFRFdldRQUpacnh3Ylc1X0NXTUJlWXI3V0NyY3cxRFF2U29mQ2xqekxkc2ZtdmR5YjRaM21NMDhVaGNmamV1RWpUV2NtWUhzWWdxZUZ1UFhVVkpUZnVsaVE5RlR2VQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CK Hutchison launches arbitration over Panama Canal ports contract ruling - Reuters</t>
+          <t>Businesses with Payroll Urged to Prepare for April 6 ‘R-Day’ Compliance Changes - Business News Wales</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:41:00 GMT</t>
+          <t>Tue, 10 Feb 2026 17:47:52 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNZzBvWW5tSmtDbmZ5MG5RY0xNZ05lRHh0R1VLeF95VTVPbTNNQUhmcXQ1QjN4NEVYMGJra1pXcFZaR0FUYWNhSjNqMHg5TVJtc3RHak9WSldydkNpQ2Q0c0MzcVpMLWtYZk5PemlEZHZEalJqS2d1cUtOdzNqQkM4WWhad2FiNzVrMW80NmozT2lnaTJuSnM1M0twY3NnYU00UFJLWU1mdEg0VFdlRlNvbFBhdGp4bWNNRVBpR19MaGswaFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQOVFaaGJzMXFiX1F5RGthNlBvZE9XNzJiQnhOYlNfdEdTSnZrdXE5T21rTy1JSXJMdm9wRU9yNDFGcHFKSkZpclRNTkFCS1JscnE4WUIyUE8zS3NRaGtHR2QzbGpURUJ6cy0teGt0dUFRclpmSlcyRU9McVdIWXhQaUx1cllKcS1odDlHWHN4VXMwQzVhcE9ZVlNrUFZ4VktpTU9BRzZUYzBUN0pJ?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Johnnie Jackson on Port Vale, Osman Foyo &amp; our supporters - AFC Wimbledon</t>
+          <t>Grant Ward is a Valiant! - Port Vale Football Club</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:23:13 GMT</t>
+          <t>Tue, 10 Feb 2026 06:16:43 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNV09XdFc4SjRBREhVS3E0SVN4elRlNlZacVVvU3hjRE5zTEVuUzllUm9tY29KanpoSHRkWEluLVNOMGRqX3NwTUE3WTRKazUyUVRDS1Bfd2VqNmtYSTZZdURUV1Z6ZU1LYlNUYTBOc1hKVTVqbndHSlFHZU5kUU5TSEdqTGQwRm1vYkFhTXM2RXlQOG11VjFVcWM3SkZvNzlzeHcybmlZOVpkX2p5WEhKTVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1DZE1lMlpmTkRXVl9FZ2VhZnhzaDhCMHEyTFNxRGFfd2N4MUNWN0NlLUU1eHZ2RUtlU0lCdWZkdVdQT3RBeVVkX0JQT0xOQlljeXVDaFdGX0FqaEhCODE1Qw?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The Trump-Modi Trade Deal Won’t Magically Restore U.S.-India Trust - Carnegie Endowment for International Peace</t>
+          <t>Neath Port Talbot parent support scheme to expand across Wales - Wales 247</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 21:24:07 GMT</t>
+          <t>Wed, 11 Feb 2026 06:43:47 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQOXNLeDh5cmFqWjlfSUNmTEVwOTA5THBMSjRmcmc3TEoxN2lnaWk3Vk13WEFsWGZDTmlXLVB6OXZiMjVxYm90YVlNSnBNbGFUMm05V3l1VXJkeHlkTkdWNlh3bXA5bzVDZXNndEpqRmM0VkRVLWZUenVlN0dwVzFaQVlTcVRmUzJtUXItR2VhM0xKdG5yT0RUelJBeDNfd2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOUWhxT3czV29JMldHRWNxVjUyMzBXamgydlJLVUE2Q0l1UXFubExFNk5VZnlZS2ZHYnFOSTFHWDAxTVhELW42RTdpYTRaUC1nR2lQek9JaVhxU1VQa0hDeENvTGFZSHFQX2V0YjlWQmtGbVdzbGRYTHpYODlocXdTajNWWVpQbkZMRVpIb3dUdXpMbkE?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Panama voids Hong Kong-based firm's canal port contracts - BBC</t>
+          <t>Port of Liverpool receives record ADM Shipment - Container News</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 09:49:26 GMT</t>
+          <t>Wed, 11 Feb 2026 05:32:05 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBQZ1htcTZmXzA5YVBIUGJTQlpRRi11SXRLVUdBRFUxdkZwWnpQU1plZEhRVUNmV1BpS1BqTm1nd3VHM1Z1OG5hNDRxSDYzM2ZtR3FxUUtkYXpwNWti?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBkRHZoMmVfSXNWTXdpZjU1aU5vRFFIN0xpZGF0N2xHUC1fTlFYV3lDX1VsOUl4V2pDeE95RnFNMzFHM21tR1RIUmF6SFJQc3FoWUhGSjFkR0hRXzhfYUJ3N1pVTGV1ekJadmdqcnlOMTlBM1JVVmtla2NIWldhdms?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Around 100 flats on 'prime' Port Glasgow site to be demolished after delays - Yahoo News UK</t>
+          <t>Trump Tariffs Face Rebuke as Johnson Fails to Block Votes - Bloomberg.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 06:30:00 GMT</t>
+          <t>Wed, 11 Feb 2026 03:46:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE92WE44aFUzbURfbkF0d3Iwd0J3WUx1LXlRc3ZOenhTZ2xRVTlnTE12SXl3VlZKQnlQUUZ5VWttLUxzZlpjZjZhUDRGWGdOemZYQ1l3M0VKekNiZ216Nkg2Q2tvS0FiQTlyUXI0bU5HQzMwd0ZNQnNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRHFBZGFWMVJiM19UcHU3eVVRQ01GUjBNajA3eTB4OXVfM3BjT3NYV0dmY3FEUlVubXlLbFd3YXJUWWhGQmF0bDgtTXF6aGRiVEoxTG9oWjR0dm96Nnl2bzRDNXUxdzB5SDFsVjU4WXY4V1dKZ09DMTFZOTltT3M0TTZldjVrNWRKX002UzdfSUxQUUc3dktfTjd3amlVSG9jNXJkR3B6a29DUS1MVVRYT2tLTUM?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Five critical compliance deadlines food and beverage businesses must prioritise - Lexology</t>
+          <t>Bespoke tariffs backed to boost community energy schemes - Utility Week</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 03:31:22 GMT</t>
+          <t>Tue, 10 Feb 2026 17:45:25 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd2lPX3RCV25scjFGMmNhcHRwUEU1VUVkeFFqNkJhQk10cU9aREI3U0VleFMxNi1lZnl0SEN6dDFpakRpZlFoV2hWcWZNM1phejBNSlpYcnpzOV9QZFFFTG52SWFLVEhGZFlzTWlKSVVXaWI4RV8yYjlxbnhXRmNoenZpelVIdGU0R2NWcENXRVZqcDdXd3k4Z1pxd3A1TmF3dmR1TllUTlpLREZjZHRPTWRFalJFV0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNmV1c3FsaTY2SFJsTDFrYURIeHlnT2h5cEhVUW8zVzJIQnNiejRkcVFrNDA1RmdzMDNlcXpMSEVCaUlLM3RBZlhXaDRucmRzSmVxMVRfZlJ6ZmNKTmZZTEJRY1d3Y0xZRXhZX09iYmdJZXp3ZUlaWHBVa2YzVWgtYTNjc3hUQV84bF9N0gGXAUFVX3lxTE9XNjF3S29RMTVGcm14Uk1pakZHUXhuTUtRd09NblZoOHJ1aE5Ia2lGbXphNmdPdW1WRG11RWNSWmkySEdHRGFYNGpObnR1bVdyM0pGQTVIZ015LVFWcWJkeUZEYUNFbXZ2V3dGNmNiY0Iza3lXd3hhbG9UTEc5QmtHMGFzcHRoX3pGeExnSTF5UkdqUDFkMVk?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AD Ports Group secures $115m financing for terminal development in Egypt - Baird Maritime</t>
+          <t>EFL Trophy: Stockport, Northampton and Doncaster reach semi-finals - BBC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 05:20:30 GMT</t>
+          <t>Tue, 10 Feb 2026 23:09:17 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPMFZzd3VmSldrcTZ4aHlicmtXOGR2QnN1dHhxSGVYcUZrV2hSdXBoMmdHWUxZTXlSU2djZzRVTTQyODZtY3JIN0FEckFtd3dsSzBjbHhuMTlfUl9tQUxOYjZNS1ZPaWJsSXExQUJaVlltYTl5QzJBTVRLSEF4TVVCV2JnMDREWlI5T0xDVjd2SE5aeUVObTZRSXdKZDBkdmYxSTJ5bXNhdWpYYWc0UEszb0dDamhvZWPSAcQBQVVfeXFMT3U1djFaZS0xbE12cU9rN3lPUHdnWXdyRlBqWkltRXpkY2NzWHY2WlZQeW4wWVFjQktqbm5PZlRSamJPZWpXVHZYZkFXUERZN1psaUJ1dGJ0STM5SGxLOWkwNkVnMEt3dGE1bVVmR2RLMW9MbGRBVnFSTEplcjNIQjk1V1B0bm5LV3AtX3B1N2o4OWpkbE01eWs5OVNNNTMzRWJZMVJ3QjdOWnlCQ0RqV2pCY2lzN2t3NXcwSmJBQzB4VWN4Zg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE01LW14c1UyS0Nrbkh1OEtoMmswYW9qNXEwbTV0Uktsd0JOM2tuTzZnTTZ5OXlna2QwMDZaalhEUDZaRjV3RkZHN3BHRktpMDE4VDB0bzdxQ2ZGY2xzUDRKbmdnOXhoakU?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GXO Logistics (GXO) Expected to Beat Earnings Estimates: Should You Buy? - Yahoo Finance UK</t>
+          <t>Cargo ship towed to shore after engine room fire - BBC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:00:06 GMT</t>
+          <t>Tue, 10 Feb 2026 07:32:05 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOMGZacEpxT1BRYVZZWHJhZVAyMFFqSEhqOUJEQlAwcTcwRXVETm9tQmpsZG1XaGZyMV9TQ0dZREV2VF92VWc0OHJqMVJBRllRODZlTzlIS2hkdzVoZURjS2Z3T0ItNVBCaU4wNHE1eTRidGd6SVZMLWlJb1BpMHZjbUNPU3NwOWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1JdjZkYVdxc0tLMlhXcUFxUDBFd09BYVFGVkYwRU9VSXJoMVh2NWhpSDJXZnlmb1NHZURtWTdaQXd2XzZsN050VGVVZXgwajB2Uk41ZVVJeDc3RDBy?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HighBrook agrees recap of €300m Dutch logistics portfolio - Green Street News</t>
+          <t>Canadian pension giant halts deals with DP World over chief’s Jeffrey Epstein ties - Financial Times</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:19:06 GMT</t>
+          <t>Tue, 10 Feb 2026 20:48:54 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNi1ISjBfR0ozQWl0VGY0REZOUUU0Z0ZYQzRUeGZ6ZV9FSktlWjdwcVROMkRjQXI0Wmc0Q2xvYXRkd3BLck83cWZIWGVGOWxMWU40VENwb0w0R1Zpb1E4SHNtLThKa2dkOUVXRkRaMGJ3b24tU2huY05iWXlmSlNBVWg4LWtiRWdwcWg3U0ZEUkxnY1R6bDFLaTB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1sb29DZlNPY2dXbHAxUVZLQ0xfaFIxREpuT2F1YTRFTlViWl9ZSkpLNmN6dHNfZS1jbDMzSjFSdXNlM0xHWlVTODREeHB4YmVCV2MyZ3pRN1FqSVdIWFhBek0wWEhEbEcxNnYxcS1reGg?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>What’s next: your complete guide to logistics trends for 2026 - Maersk</t>
+          <t>Sanctions Force Russia’s Foreign Trade Down to Soviet-Era Lows - UNITED24 Media</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:38:45 GMT</t>
+          <t>Tue, 10 Feb 2026 20:01:56 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQX044eGlSSEpLTFJpbUdhdlVaaWlmS3BUaXI1VWpKMnU1MXNjMDlVRHZBXzJwOEwwSi00WUE0NnJMX21CbEp2b3RMVkd5WUNiX2N5U0xSUmJXVkR4SGhBb0V5Uzl2YTc5SnY0S3JjWXR6UHBYcDJuMkh0T1dpdDJXRWVEbEhfNXM2VEFGZ2NCMTRaZFNwOEpscno4T3VCWlltTUxRU3pwWnNvSzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNdkptR0liX09lUHNmUUpNQU82MHpnR3lBdWpEV0NNTTFoaFl1akM5amkyMjZ4WjhHaG44Ynp6aWpmOE40eVROSW5CeElFLUhJOHBoUjRZbUUzYTFoMi1Sc1hJYTQtNXAwWlBXbHV5Um92VW9TbXlhNzdETnNPUlNkTnpwNkdtOVFGQXU4RzYxa3hEYXBGdEFVeDFFRERhSnNTajMxNEV0OS0?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Haskoning acquires port planning and simulation experts - WorldCargo News</t>
+          <t>Man who was found to be dealing drugs appears at court for sentencing - East Lothian Courier</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:22:31 GMT</t>
+          <t>Wed, 11 Feb 2026 07:06:06 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQRklmQVJSd3dyaDFSRF9FWW5jQnYtcEdITW1QM0Q0RktiMTB3UDhwM19xbHNIS3RvOTlkN2dZX25rM01aTW5kRTRXZk9rdTdTaG1GdlhNeEhJWjlHLXM0S0h3ZFM3WUdPaUdRS2llcnZsd0RldDd0Q001R21OcW8taVBMaXVYQWIzVGRRNXZXX0RNT0pOVHBDYW1UNldkYW01T0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOcGRObFpXU0dRY25CTE55dnZFU2hGQ3ZDY1ZHZDFIdDlHUmJISldhQXQzeUlaUW5mVUVQc3lDbWpKR19iYzV5Zl9iM0tOcXlVdXdZZnhVbWF2NXJuZUQxcEpyTEU2RktXeDNnNUl5SkdkYnlIZnlOM2sxYzN2NTNTN0tGUHNSMzhya3BsREVEMFBqU091TFFvcEd0UkxDQUJwNkRKQkZHbw?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Devante Cole: Luton Town sign experienced Port Vale striker - BBC</t>
+          <t>Syria’s Future Between Fragmentation and Rival Reconstruction - Manara Magazine</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sat, 31 Jan 2026 13:50:05 GMT</t>
+          <t>Wed, 11 Feb 2026 00:39:40 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBQVGFONE02cXptWFNtVDR2T2JJTm04QzAxX3BMSC1kVHBvUnRjNk5SZVk1OHdjeVB3WXpjeWhJWjJRX2FpZXJ3Tm4xeDg5ZzlxSGZlZmNRX09JeDhXZnN4WGNzX1lzUFpFbmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB0VF9DMWxhR2tkWFViNi1EV0xJSzhtZ0VZSDBZQjF0YkVJY281UTZuMnZ5ZndzdU95UXpoeGN2ckxLQ1FzSGhXeUNXbGZvYXVSU0xlM1BhR2YzeDhzWUZEa2Vod2NHUnN1V0djeEpRSWR0T240aXZaT2NhTDRwSEU?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Police and Crime Commissioner censured for supporting anti-migrant protests - Searchlight Magazine</t>
+          <t>Gabriel Makhlouf sticks to ECB line on rates as US tariffs help keep inflation anchored - The Irish Times</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:34:16 GMT</t>
+          <t>Wed, 11 Feb 2026 06:00:55 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQM2M4R2FWQzBlbHpIelJhMVpsQkE4V095dmNlMjFDNHMxOEd3V0g1RTM5SWotbE1IeEpNd1plOWNBSTZ6bWNiV2xzMy1KNjZJVlhoR2ZDSTVBMjJTS1I1NUhNWjhYcEh2RzRUak5nYllpT3lRTk5BMml3OWsyTHR2Rm5hTTJFdTc4X3NFTkJLU0U2bVZlU0NCcUhVU1otS3FxRWtreFE3VjF6d19LeGxRZ0kxUlhvSUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQQUVrbmpWYTRHSnZreEJmRGFkcjJBQV9iY0lXMWdnUDZ2WE9Td2F5U0g3elNNbG8xMVA2M01SYTliMlJyWE9RYkJjcGF3eUhxem5uMTJYVS1jV1dWa0I0MEdaWW5pUG9jQm90YVBpZ1JzbFlDb0QzY2o0eTR6RmZLZm02ZjJxa3pHbWtoM3ljS182QUtUZWI5Rl9GY3RaazJkV0I2QkpHQTdabW1lUmxtaU1kREhzOXQwdENHa3JsR19ZM181YVZlRGNCMTdEUzh4?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,27 +1891,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Children and police officers among at least 30 killed in Israeli strikes on Gaza - The Guardian</t>
+          <t>Disqualified Somerset driver caught drinking port behind wheel of 4x4 - BBC</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sat, 31 Jan 2026 07:33:00 GMT</t>
+          <t>Mon, 09 Feb 2026 14:29:35 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPYzV0Y0xxR2lTSU85dzc3TW1wYkVJSzhzQzY3bGRLQ1hsVXpZR0tOeHR5Y2cwRzhZZ3lRT1U1OHZIX3ZyUklUQjE5bllRSF9BWENDMVJ4WDhudTJBTXZYeTlqUmtjbDhkT2N3Y0RvZ19WSkxRckdTWXFQSGw4NE1LNm1UNUVNai1jS3FsRERaeEh5NURYN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9EM25TSXZ0TkhsM05Tb1RLTURROU5OMlJ0SFN2MGlYRFMzNkhZS21wa1BFSzYzcFBuYkZ3S21DN2VscXFVTnhyUFBicXk3aEdMME1scmN0ZXZfelV0?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,27 +1921,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iran police say 139 foreign nationals arrested over protests in Yazd - ایران اینترنشنال</t>
+          <t>VW’s Cupra Tavascan first EV to dodge EU’s China tariffs - Automotive World</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:11:32 GMT</t>
+          <t>Wed, 11 Feb 2026 06:30:07 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5OLVNjX1hqdFk0NllxYU5uSGN5TmRXTERJSDh1bktUeHZvNC1BaDBzWDVtaUhJbmlWX2Jpekl5WklaZzUzSkhBY1d6VXhmUU5acHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOOEd1dGJ0Y3ZhT1lHZUQ4SmFQSU15ZVY4QXFpb2RkaG9Ra0pXSlNEdmxqT2VmdXloMlh3MnJRR25aNnJhRjF3SGtWdEpKQjRuRHlRRWoyVWlaMEJRZTN6dG9qaTRCTTZXOUxsMTV4VjR4S3hVdUtvYi1RczRsdEh0RF80WUpwbjJDUGRfNDcyVWkxMVkxQUxZ?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1951,27 +1951,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia resumes strikes on freezing Ukrainian capital ahead of talks - France 24</t>
+          <t>Ukraine Hits Russian Drone Nerve Centers and Logistics Networks - UNITED24 Media</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:46:52 GMT</t>
+          <t>Tue, 10 Feb 2026 16:14:01 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN01uSVNackgwMjE1enhnOVdUWnJQOXZaYkJXQzBscXFaX0tmVkRrb0ZSNjhFTXR4NTJmOE0yQk5TNHZndHV1dkxyRldjZFlDNDhEbW5LMVNzcjdEOGg0VWVsbE5GOTVEZVV1VzZQSGdTLXZEMGREeWg4LUw1MnRIaDNMRjd1eG1BSUs5S2VORE1NTFVRVkI5bnlzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNSE1FdEVRaXkxd1ozVUxMX21kNi1PM3lMcFA5QWZmU3VmZC1fd2ZaY1ZqcExJa0dveUU3RlE0aVMybW95X0tVRS1Meml4R05sX0xWQk5TT3UwOE5vYjQ2Rk0yUVpNeENkaEdrVUJtekctRDZqUkN4OUEtdjhZdmxMYTJHcjJJalJSazJIYmprMms3aWFJUFJJNUluWW41ZV9TMXlTbk9mcmdvQU0?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1981,27 +1981,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Update after police called to convenience store - Cambs Times</t>
+          <t>SeaLead plummets in shipping line rankings - Seatrade Maritime News</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:04:00 GMT</t>
+          <t>Wed, 11 Feb 2026 05:54:57 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxORnRnWW9xTkxDMVVISlZvNjZVS0RfZGhhLUU4RFBNZVNsbmExOEJZZHVBZ1IzelZXVl9nOGZFZGQwcTFfaE1YZjlUODVJWExsXzNiVm5DMnpQNGM4RHplZXZRZG5HMHNjaE1VY0VjOGdpd194cU1rUmMzQ3NXV0QyWXBoQkYzMEVVM1A2eFU3VlpkYTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxObUh3d3FvVThxUl90ZmV2czZldWE3THJsQTBQT29LWUZyZ2hFdmhCdEpNcmNNTGItc0tFdDg1cHJBUWtjSUdnMW1IVkxuZlpNeHNOSWZCQXRfMHRDYUpqcUYtVFhMbWVUcFZIVjZpa2RQcU9CTGdIT1I5WjFmejkxcTNVZ1FhQlAySTlkdlNKNXI?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2011,27 +2011,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Police statement as flag-waving protesters march on Hanley - Stoke-on-Trent Live</t>
+          <t>How AI collaboration transforms governance and compliance - Thomson Reuters Legal Solutions</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:36:17 GMT</t>
+          <t>Tue, 10 Feb 2026 21:13:48 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPT1otX0VCaWwyTFVjMkhPU0habVRyTlZTWl9mYzRJX1RvcUZoTTBFbmd2NENQNVJOcW5aajZkLVFRZlZpUVM2MERmUDFCOWp3bFdkX2lseWg3eHByak9HUmlnV29OSlViX1ByNnExQllBQXdXeHRzNU9hc3RlMEY0d3otTjhkTXc0czZ5QVpYckJhNHpCajV5NWJuNG15SEt5NkNuSGNwR23SAa4BQVVfeXFMT29GZ3RWV0xJczVuSG91dVpCS0dXREVJNG0wQUhkU21sYTY4MVItR2pocTdpMC1obWRKeENHNFdkazgyZnpVdzRvZFotcnRpb1lxWk4tbW1hdkxmZ2duTkUyTGcyN2pGWG5iRE9KclhHeVdUUzg0UVVyR1pha2lKdUlYMTViQmF4b1lfc0ZGMlVZNTdEU2NoQU5rb2N0M0p5dGZDVG1USzdCWXJhdmhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPSG9mcmdjeEFJNU9heTYyMHdzdHIyYlB3S0hJSndwU1pTcnVkOV9XTTJaVmZXMHZPcVUwOUNoQVlJU0w4SHpkM19NZUdCSjE3WjZZYzl2Uml3SE9UQm53YVlMXzh0ODZMY2ZaZF9EdmRjZEl0ekNudEFZRkt0S0JIMDdfMHJzSElFMXNQLTM2bHdXZUJhclBuaXJLQzZMWE8yZm9kcmxsa0otbVY3dGV1T1ZGNDFRUWc?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2041,27 +2041,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Man arrested in connection with physical altercation during Buda high school student walkout, police say - KSAT</t>
+          <t>German Oil Refinery Sounds Alarm Over U.S. Sanctions Risk - Crude Oil Prices Today | OilPrice.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 04:41:03 GMT</t>
+          <t>Tue, 10 Feb 2026 21:30:00 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS1VuTHpOWGU3M3BEZTVzWU5LbDNILWEwWmJMbGFYdVVraVBMTUI5bXFBRXR6THdDUmd2SHhuQ0dVTTVXbnNQM2NyVnIyamtlMElvMHZJSTBfTnJ3cC05S1ZsMWVSeTY5TnRBSUJCYncwclhMOXdtYXQ1YTB2YVd4Z2R4TW1MNkoxOFpqNjdTdjdPVlpxVTFoM2xqeWtWb0RJZDZYWXdyTnZvUHU3cEN1R0hQaW5aX2NuVTktTXJ5T3BScjN1UWYxcTNtVzY2V3dxRTVlbHJ1SHhjQlNYdUdyXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVBocnlscUNIOG01T3hEcU4xczcyVlhiUlVLMzFXd0J3YmdveTR5Ri02NklLVUFoZ3REQ29CSkxrekpoeEtaYkZYX2lUUkFqRFFSY3podWRSN0VGQkNiTTFIWlRZcmNnWng4aDlROEJ3QjBTNVZFendRTm1qclhZN3g1dC1EV09DYm5tOEtjV2pndHRveVVKZTJVY0dfdk4yYUVsU3NrMEZ0SkFjYTRwZdIBtgFBVV95cUxNOGdNSjJTQ29XVnFuNnVSLUdmNmRPYWdDNzE4M25URXNiS3Y2T09Qam55SFRqeHJOSE0yNFk5aHJKUGNNcFBYel84UUtfWG1LTVp5ZWFZUUJORW01SklNSmk2aTR1MkU5bGlrejZ1cHl4TWFNOXIxdm01Sy1rcmtTcXVYT2pYWTdCTDI0NklNMzFvcW9rZ0p6c3R1YVJ2UkFmbFlsTVVTSWV3TENNYkN1ZDNJRTVkQQ?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2071,27 +2071,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palestine Action Group plans march against Isaac Herzog’s visit despite protest restrictions - The Guardian</t>
+          <t>25 wonderful old photos of Fleetwood - port, town and seafont through the years - Blackpool Gazette</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:02:00 GMT</t>
+          <t>Wed, 11 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPNlhyVnR2VUlxTWpRY2J5M3c4MkpZcGkzNk5iWG5Wajc5QmlvVDVEcDRwd2lVbTJpaFBjR051RERCNmd4dXhibWJtdmJQZjNNT05kMF9vWDRkM0V6X2Z1R0ZEb1ZIOGN5anI4NHFCM0ViQlN6N1BNbXFzZ2tMakZscFg2Y0xseXIwYWxLb0tnSGthaUl5dThmWklCSzdKMi03Y01EUnZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxONmN4RjFsUFRtOWZzVjZkQkxsX2F2UjVjWkdTdWZQVXlxb0xDOUxIOTJ3Y0NwT0NGS3dtSktHemRZSVZLbHdHa3Z1S3lUWGR3VTVGSEZiX0hsWlVRN3h3OVJBSGx5R1l2RWZwNUFkWEp1ZnY0Tm1qTTdiWGNrTExiUzNtcFJCV1lJcUF5R1BrUTdGU0xQMkNjdERsOF9jZnFTemRrNGJPaEJHREhvdWlBYzZOSTZXZmJwbkNjSTVnb0RMWjA?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Islamophobia in Europe: Dutch police assault on Muslim women sparks protests, highlights growing crisis - Muslim Network TV</t>
+          <t>Woman, 69, in hospital with broken vertebrae after police allegedly pushed her to the ground at Sydney Herzog protest - The Guardian</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:14:40 GMT</t>
+          <t>Wed, 11 Feb 2026 02:15:00 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNaDVlX294ZEx2MWpIaTc2RUtuM00xbXFNV2xBWWZhUmY5TmVjaXZiYXBXZ1kyQVFrMlNpNldFY0hiVmdrQXNlMnJkeUhnVkdEQWFINS1EdHhrOC1GTGVpeXBqb29MVDZqV2ZMS2xQT05ibFBYS0ZxNHRBWnFVOE5GLVJBaTlOVTdfM0xYaHdURVhYTGVKc2JFVzd2LVhqZGNiZE8xcnZNWlN0MlY2NkYtMWlWWU9CVmJHVkpadlpONHVLMGdYbWU1OFlPSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYnFCY3FhWHY5OU9pdnNRUDJMc1YyaG1iLUxzUHgwQkh3ZUJya2d2SjBpWDU5UXNyMUN6UWlJc3ZFMnhVREJCVTZYSFQ5eUhPQ251Y2tRNm1ONmZqMk1UT2hkNDBhRHNVSk42Nk9VSWxreGlpWVlrYlp3X052b05NWHIwdEdWTW8tbWwtWVpmck83LUE2MGV2SEhENmt4UFBwZnFRTVktYUdSM255b1d6STRJdGx0UnZJODk5bmF5cUl0Zw?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NTUCB Cries Foul After Police Deny Protest Permit - Greater Belize Media</t>
+          <t>Epping: Man in court over alleged racial abuse at protest - essex.police.uk</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 01:51:29 GMT</t>
+          <t>Tue, 10 Feb 2026 17:44:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNMnZiTGxNZjVlM24tYnBTbEV3OC1oc3JvMEE3b1RvY1JTcTNkMEp5Q0xsc3R1MzAtRXZfWGZqb2hnZXRvWjVxVGZzc05kbUE1OXp4bFhWSE9IQmE2SHZvRlkwV2daUUFPTDlsRlcyT2RNUncwWjVkWGx3Nnl2enBFdHQyM2s0OFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOSVFCc2RNS2pkYkRkNTRhWkFrU3loYnV6ODF0X2V6Zmg1QThrdmV4Tkk3eWZOQTFlejFEZXZLV1hyd1cxdnMxa0VSeXFFU2gyVjhRRGxRdFluREhSR2FZYzhBXzd6RzFKMnhBS001LVMwcXVfQlZsSlhJQ1lNR2RicHZDUldUdHBwLUlVSU50ZloxSi1BRnBqNFNUNnlmYmJVUm51V3NuV3FqNkoyU3dSUXpVSncyVUJ5c2NTNkpPQ0U3U19oQmZpajBBOG9aY1g1RGpZNmVtMEptbmxq?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Police probe launched after jewellery thieves strike at vulnerable Smethwick woman's home - Express &amp; Star</t>
+          <t>Australia police defend actions after violence at protest over Israeli president visit - BBC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:11:04 GMT</t>
+          <t>Tue, 10 Feb 2026 09:34:33 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNSGdYOGR4YWRSQ0pFc0VxSUdoc3RNUkZ3bXRvdDBuVDBBWWhYLS0td1lPVmtDUWYwZGpqbVZ5RkxrMWQ4SkRqWHhBSkFjWll4QU11cnZKMEtRWTRmNi1xOWRsWTlnSmtkSXN6MVZRT2hCZHBnR2dlbmV1NzZBcWJ5SnJZcDJWNWtENVFkdVNKa2wyRTFkLVJRWDJTSHg2MlZUUDNWY0xOcFBuTkpWUUdRZG0xZzkyeGstTkdVMHF0UGo0UVlzYmNfdGQzMFVKNUtvMHF3UlpRSmJhR211YWFJQTdZVFFXSDJRU1lWNXQwQmxFQjNFMHk0VnFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE55X3pEekVVX2xLYkhnZjg4VmdvLUlPRFFOUkMxekVsc0ptSXEyMDA0ZkNzS0pNM2lEeGVubWs2Q3JoU2Z6YU1qZzB1cGVVRXViSS1sdW96XzRadw?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia pounds Ukrainian energy in diplomatic snub, Zelenskiy says - Reuters</t>
+          <t>Day 45 the Protests: Nighttime Chants and Intensified Police Presence - Hrana</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 23:23:20 GMT</t>
+          <t>Tue, 10 Feb 2026 22:00:15 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVlBuNklvRHU5MVg4THZMa2VRMmlRZVpEb2FmX0pNNlJCNXNHbS1CWW5NaG5pbUNLZG05ZDlhcHgwQUV4Tm1mbXVuV2cyaXp5ZGZyNnJkeEJPdC0xR0NYYU8tOWVTX3NXSmNPUHhWSEg2dWlDZEFEYWhCOGdPdWFsMlM1SXYxU1Q1NlhTcFRfLVB0SDM4OGRYVDQxNVNpd0g3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTEJ1ZUszLTBIUGVOTWdBV2Y2eVMyZWZfMVlnYnVHMERtV1h4MTFUdGFQTkpOVDNVaFo2WVhOLWJhWTdRYUZHOU40Zkx4ek8wUGNKbVRieU12RVczNlhlUjBRNXdsd2tDeFhIWjY1eTZJUWdIM3JMRDFjOHIxcEtYNmU4NnhQOXU3TWtfRFZJSTNfNzhVajlGWnlB?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Maple Grove Police Chief Addresses ICE Enforcement and Recent Protest Arrests - CCX Media -</t>
+          <t>Antigovernment protests in Albania turn violent, at least 13 arrested - Al Jazeera</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:32:02 GMT</t>
+          <t>Wed, 11 Feb 2026 04:17:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOZXN2UHBVaTBoNHljclNnSThxSnhFd1hhWWFBQ191V0s1eFVzdV9EMGE2dzZGT0xqaDlsaHlQRDNVdVhWM25PMzQydGQ2RTdOZXo4X3ZFMXYxMndrYktNSHIycGhxUVY4ZU82RFdKY3JUR1dRaExOWmVfNmVhQURoMkE3X1VzaXBXTVdwcnZXSDlUQkRvNlNnMjBFb0ZZd3RfQ1JRTmphTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQcmFnaUJZWDY5Q2RObUltcjVpdjBoOFFhZHlubkFhaE5qY0phWHNUNGJNaFJKa29VanVMbnY1OXVZM0VlbkhSc3BpN0R6UjJFQkhJWDc0dVpkTDJJbUNYM004c21yenZtN0tFUVNOVkZjOUU0WkZYNzNaMGJ3eFROWUwwcWYybkdsQjg0YXkyYmdmdGIySkFZSlJvSkFNalpfR2FCc0p1U2xGRXNfOEHSAbMBQVVfeXFMTnVUbzhsUkhMOUNqYUlWaHpac2VpX3Q5b2UzczIxYlVrT0JyR1RqbmxUUmh4YXp3Tzd4UUJWbmNOYUNQSk0xcGs1NzQwZnlMbmtNLTNmMDVhY0ZpTUo0LVU0aG1LMnBQOHZvaUx5cnpKZDBrRlVTZ3plWWgxQXdwQlA4NE1aM0pMOXI1TDlxd0Q0MUtQcFNnb0RQOTYtMmNYTFJQZnpPV2g0ei1qWVphVWxlOGc?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ICE-Out Protests in LA w/ LA Times' Gustavo Arellano, plus Capital B's Adam Mahoney on Impact of Freezing Temps - KPFA</t>
+          <t>Australia politics live: Angus Taylor expected to quit shadow cabinet and launch leadership challenge against Sussan Ley tonight - The Guardian</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 07:01:00 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11MmFBVWRiMlpkdzd3SFU0aTQ1YnZBd2RJSDhtNWJZZW5XaVhKczVWTG1LUDVkRHVmaXFkWVc1dC1XMXMyMzM5bmZpWXJzNVlPQlVsTU9FYkdZTHhSdml6aS1McDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOLUt0Y2hrdDRkSElsTkc3UnlnRmtJbExLMFdOVDdHSEs1VlRsTm9VaWRZOGZjNmJlZjVfWmlrbE1vNXhwWEFUMVY1X01QUGNFOTdxZHdKSDdrdExVV2JaTWlGR2pVaHdqSnZJOEg3dWhTLUhJZGsxR0VOSDdjWHo3aUJPamRVTlNOMXRSSzQzREtPNlRkdUhnamRCQmpKZEF1QU02elB2NGR1UEtDNUMxUGFZWnpidVFxemxDNHhLcklmajduSEJ5dkI3LUVZQVYxaEppYnppM2VaU28tMDktVERLNDhGNkJ2YWNCcDB6UHR5VTdBdXFnMkVKaGg0R1JJ?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spokane police chief apologizes for officers wearing masks at protest - The Seattle Times</t>
+          <t>Police chief orders watch on groups over post-election protests - Nation Thailand</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 19:00:02 GMT</t>
+          <t>Tue, 10 Feb 2026 09:43:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPZHVEUEY5SVQyb3FseU83enJMeHd1S1dzc1NsUUR2aWpPRHBRQ05zQ20zZTBmM1MwYmc1emlYQW05VDg3T2l4bXFNS3k2aHlvOFl6cTctcS1vQnU1dFVGRVFucnVLd3VZbVR5eThXT015cUJLaHIzaWtETlJfUU9rbllnTFdfeU84cXpXdVFuT3Z0UmtGdzVlNWhYS2RCeE5pVV9RVTdXMVkwSFcwSjhFUlZqRUU4QTFYR1ExQWJocw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTFBzQy1WQ1lpNG1aV0hXa0hkY3Q3Wm5zSVplR1loX1d4UW9TLUozZ2J6VWttOEpjOXBfcE9hdUtiNDhuLUNtWVVmVVNEdmw5RXNQYkVMOEQwMHRzSW8tcTVMRUZn?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2311,27 +2311,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US stocks drop on fears AI will hit software and analytics groups - Financial Times</t>
+          <t>Police update after rumours of 'man threatening people with belt' - Cambs Times</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:51:54 GMT</t>
+          <t>Mon, 09 Feb 2026 13:00:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5uQzVsUF85MERrc09IUk83T0piRjgtQUFvZ2R4c0VyVmxzTlJ2R3BkelNLMWw4eHYxcGMwc3hjSmJsN0tTbGhsNEVQYlJmcWVkaXhxaTk4NW14WDBDbjFFZml4SVFyaGNVbXhqb3licHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPemxoenFFcUN2YVFRQThSYzEyS1BtUDlmWnBGelNlWXhlNk0tVVhPaFdTcnZUOEFyTmpDUWhRdUZpTGFzMWhFY0N4V0hJYmZKQkRWUDh5d1hfdEZxRUZfTnl2ajNOQmZxR1BMYm5KVjQ0blp6UDNpVUtJenNGSGFmWnFXbFU0NE5pYllrTm1vNHJwQ0FNMlBtNTBrblA?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2341,27 +2341,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NHS launches AI and robotic pilot to speed up cancer diagnoses - PublicTechnology</t>
+          <t>Despite police crisis and protests, Unión, Colón and Copa go ahead - OneFootball</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 01:08:48 GMT</t>
+          <t>Tue, 10 Feb 2026 17:01:09 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNYm04ZWFpSkZ1UmgwOTlXVU5TRkJBWjBQeU9PbFNfbDBVVmNpN0ZpT081RUdHemQyVEwwZmJrZXIwYzJSLTJsSGpNcFBmWjJROUVQQlRNaUZrUU90MmphQTQzYi05TV96dGtrT2VFa0hPY1l4YU1pYXlmZ3FrdUdtbmhGQ2xMQkNMU1Y1a2hYc3ZFODZDQVVaSnhhTjJXVTdnMWlIVHFhZlRhYjlPYmJuWHpQeEwwbGotd3JWSTNDZTIzSXAzMURiNDR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRDFRaWVYRFZRRmpLZ3YzTXhFZ01uSk0xam9obzdUZS1XODBDaS1Sbl9kYml2NjBWN1ZoY0V0UnlYd2VXSVlCTW5HODBmNGtNZjFGRVQ5VEwtRmt1SElPVWJtLU43bVZLY2Faek90dmZJbXJqZE9MbVhDOE4wSll5R3o5bVhKTmhlWkVnNHY4LXBMb0IyRVN1WEJtLThzWGJiOWdScnJNdDc?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2371,27 +2371,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>King's robotics and AI specialist helps government upgrade public services - King's College London</t>
+          <t>‘Like a pack of wild dogs’: Protester injured in Town Hall clashes calls for officers to be charged - SMH.com.au</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 12:59:31 GMT</t>
+          <t>Tue, 10 Feb 2026 21:20:24 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQQVJBNEtMQjhaaXJZb25qLUpPZnFHYkpkeVJtdWcwME5NdmlJdG1nWU5sYUZuYVFEMzJsTWItU0kxelRkckI4eVE4dkVoOUtWbkNJaWszYV9VV1FENGphSjhtVU5OcnJnSGtJNFFUYVVYN3ZsTXo2UGhBNGxublktUUV0YzNMdzF1amZkSk05NjRWcVNDa0RUMld3cVZ4WE1DbXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOLW82YkxUdVhjdTBFRlRvYU1jcmM4UjhGbmV1LVQzVEZDcTY3NDliWjdDbk9ZQlExZTFNcVVFNTZDcnlUd21rX1Aza1RmNjIwWmJRVWZ4SWZLVVhVSUJ6WHctOEVBbnB1S2VZRkRkZTBTb2hfMzluMFpKUFM2dndBV05vbklETkRSd1JhOHpvamtnMkdWeHJDelRldGY2RGwwUlRzVVA5eUJOX0N5TDNFYUZ3VXNtVHlQR0NPM2VGZ2lVMzUtOEo0QlptMA?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2401,27 +2401,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>‘Technology must enhance, not replace, real-world learning’ - The Hull Story</t>
+          <t>Senegal university student dies after protest clashes with police - Arab News</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 06:37:50 GMT</t>
+          <t>Tue, 10 Feb 2026 08:40:33 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNm1XOWJDUDBSc09mbEZ0VUFaQ2JwNEdMd0w5a0wxVXczc0RMb09pUlY3ZFB2T3haWHBaR2FTSlB2OEJBN09rRFprMlFfXzBOREtkMkMwb3RGV1I0S3YzenBjOXRUYUdXU2xKS3RIaHZ0T2FMcnIzUmxwdlVYVjJLUGxLcl9BelZldklsNFBqbWNGbFZPNVFQclBGaVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1ubjdWQ2F1RzVzeUFJRmRBMHJCRXhXTHpTVWx0bFZrUXBTbU42SUJTcGFFMWJRYWJ3bmpoNHh5TV84T2xaTmlUYTFWZmg4cHJ2aHF0ZTRB?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2431,27 +2431,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UK and Japan strengthen science and technology ties - GOV.UK</t>
+          <t>Meloni blames 'enemies of Italy' for Milan chaos - Inside The Games</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:04:44 GMT</t>
+          <t>Sun, 08 Feb 2026 15:59:32 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQkZQLVZCX0pweG43Y0N0dWNXUXFGaGNsWUN0b0JBb1FFek5FREd3cnJXR0dFRGY4TGloaGlaRlFvMGo5SmxpZmFwVHpxbVdxX1RBTHN2T3dFc0M5Zk1uOTRDU0ktQ2NfRDdPN2xQVmpuanhLRHFIWjhPaHNJRDV1Rm1zVVQ1WlRBOEZrNlRsYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQcUpnUmdPc08zSTQzNnVUSGRGOE1OUWx3MmZqQWlIeHNncFdJS0FGNVVPa0FNUlF0d1NiYjh2Yjd0dW1yeWFxa3JuN2FkeXBGZUM3c2tPX2tuSmpkZ0VjSlhvNGVQUzdlbGtKd0VTS1ZjYUVraV9iZm5oeFVsbE1VaTZvbUFMVnVmN2gyeWtZNA?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CURE-ND brings together experts in AI and machine learning - UK DRI</t>
+          <t>Investors pour billions into Europe’s AI and defence start-ups - Financial Times</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 13:45:51 GMT</t>
+          <t>Tue, 10 Feb 2026 05:00:46 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQUxpOEJSX3VYSW04MTVNYkd1TnJJMXJKUjc2eEpZQ1I3M0hsSTA0dEdaWEc4dUpGQUpvYjRqbFM3akdkZHdzZlhpdmhhcnQ2VnpWb2otYjZjeF9JZ0h3ZTY0SjhDOTBrMVhJVTVXNUQtREczX2xMejB1Q0JKRDNkamFfSGVZMGp2U2t3N3VEaEFZaU1XR2xhQzFYY3RlT3B0OVhZX3RESzI4ZTQyVDZ6T1FxMHZiUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5lS0NTQS1aNEdWbXJ0TzZCck4yU24yYkdIVEtoQ3hUSjJGTE8tbmxhVW1OSzk0a3g5UTJLaHNqSTRIa2JOZ1NkSUpXWkdPbmgyMHpYUDhyVTJYNV80N3F1NG9NMlJQc3lKWGE3SzVmTi0?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Technology and AI - Freeths</t>
+          <t>Durham philosopher brings ethical thinking on AI and democracy to global stage - Durham University</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:37:01 GMT</t>
+          <t>Tue, 10 Feb 2026 11:16:16 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQMzVSZENscUJaS1laajB3d1dRQ1B5a1N0S0JhM0VySk5GV2JEbXlXWDdSeWhTU2FyQXhnb0Rjajg2WGR0XzhtTDh6TnBEdFF3YnZDZjhLOEJpUFJweGl0d1VNRGNHWENueHFzanNSN3RaamU3aVBoTHV1OE9tcWk2c1RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQbF9EZ3B4TnBNWmw5dnBZZ0pPVkZjbzFaVmVOeXVpUVpxVU9MSFkzbFFuOVhuZng1NEdkWkd0MEt3eG1qeW5Lb2FfYjI4eGREU2x3eVhYU0VxSm1ibWNRdm9uSmlyNFRxU19ISVFvVXE5bnpFUU53amFISGFhd0R4WVd0cVVPY1paUFZiUlFnQ0taNklMZHRIUHBSUkh0VktCYlpZMkZpQ2NRRU9KbEtjUkVlMjVPeXBGdEdxcWMtdGRld3MxdHVLTGF2NEhYN0xOT3c?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Women in tech and finance at higher risk from AI job losses, report says - The Guardian</t>
+          <t>Escape the rain and discover the world of robotics and AI at Aberdeen Science Centre this half term - Aberdeen &amp; Grampian Chamber of Commerce</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:03:00 GMT</t>
+          <t>Tue, 10 Feb 2026 14:13:42 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNakRQMFJ4NFJDWEU1UnRoVG55QzZjWnl0WW1Kd2czUDgyM1hXVzlNYXM1S2ZtRlRmeTFXMUdMWWhad2taWGpCZUF4UER2ZGRpa3R5aTFycUhyNjZKN0ZzenQ4XzA0ZDdpX2xnaUt1d0I4TkV1VjdadFNQa0ZaNlQ3Qm9QN0hKQ1Vnd1Viamc0anA2UGdQLUQ0S0I1Q3pYXzRnOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQWnJuUzI2RXhza0dBajFXZU1CT3g0OHh0YkNpWmZQLWNEYnhXNnUxeE54Q2xvM0h0c3ZOU2tNOGtESlVHNFRDSjM4a19DS25pOTF1RWZGLVhGRG5oeUsxaHdxX3FNTkY1OFRWMXRqVzNDTjNyVXlVTTY5dzF5RjltdXFFTGhLU3J1V1NIdWxSVjBZUmxvSU9LREZRelZhUDBSSm5LQW0tTGFYcUU1NEF3Wk03bDllVnFmSFo4LTNjcHA4ZEVVdFROMFVfcGtucHhx?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Industry suffers lack of joined up AI and digital skills - DecisionMarketing</t>
+          <t>Silicon In Focus Podcast: Building Inclusive Tech Teams: Skills, AI, and the Future of Work - Silicon UK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:49:00 GMT</t>
+          <t>Tue, 10 Feb 2026 12:27:10 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPOEw4RTlNUGI2WDlXMEVBUkJMMlBZZ2VWNnAwbFZIdkJHTEhPbTMyQllzZzZlek5JX2pMQzNxWXQ3a2lTbEdxN253ZEFVM0JNdHZ1dTJrd0UwTWRJNl82YS0wYzlrc2ZPbjl4TkF1bDd6RVc0aWVEWjFhUlp2dHd0VjFNbU9qM3dmYUVKY1VBeXgzMVROd1gtVjY0TGRGdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOT2FQc25wdGNXNzJjWEI3RFY1VkVkN0Nvb1M5ZlZQMTh1YVJ0WVhuMWpCNC1iV1o2dXdrSnI0YjZBQ0R0dWxPV0EydVpkSndRdExrek1rblp4SFAzTXJ3OW1SU1paME53LTFGN2hjamIwQXlNQmVDY1VjM3pzN1Q2ejVBd1E5ODN2N3VYQlFnVFh6Qkt3R0Fad3hZMGVLR1BuZFBLR2NyX0xRTl8wb1BxSFpiY25TSXNya0tJQ1YySzIwSzBVSzl1VmN5endpZmNDc042bGFyY9IB3AFBVV95cUxNZ0lyQktSSWR6QWdDRTJLY2xQOWlNYjZ5VkRyRUF5Zm1leFJ3MDdvMmpGS243YjUyNzNST3c5Mjdjc0VKbFNsbEdwaVVhOEFlYnlfejBTM2VES0JLUWZXMURFSE5NSkxLTTdFSnBMZmtjX2VmSFZ4dVJzeTB4a0YwT3k2a0l4SnJVVjRQTDdDNmdneTk1WnZ1RE0zOWVPWnRxdXVnclN5cVN2bjRPMkkxbHk4X0FHa1ZkMkRIR2ZmMzhGaXptZkNkWEplZVVMZkUtM2JRRlBhSFZLdndO?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nottingham receives funding to develop quantum sensors to improve precision and read-out speed - University of Nottingham</t>
+          <t>NEWS: AI Partnership Aims to Speed Up Discovery of New Medicines - Practice Business</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:30:50 GMT</t>
+          <t>Wed, 11 Feb 2026 06:29:01 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNaEF1YTRSWm4xM1NnTWJnU0NRVDRVYVlkdTFWRXlJdUY1RWh5QWVQT095VTBzMHFnbkxlbmlqRU5Ha2g0ejJ5ZzFTUE5PMllGUkJyQXRPdzYyNl9MLURSWG50cEYyYUZhN2UyTGFOYlBXRE1lLXU3U1BDYnBaNmJQbDVpV1lLTXJhLVRNTE1BZUktTVF2c01EY3FBNHdXV0pPQWo0R19MOEFZczRqZXpRQk5wZnFqa1lLWlMweDNuR3ZLTEZUYUtV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQYzUyNXlaeTJ3LTFZb2RhS05tbkQwU0tqTWdPeUpIbVJlSkFOa2JRQmhnV1ViejBNSmRrQTFINjJ0MFpKN1RxNFN4cGhtNUM1XzhFQ0I2R3BqWVNDNHlRdUs2M2lvWTkyRGlJYXFmUElrXzlfT2VVZm9WdVBSVERDNWNKQlRGSHBFX3dybUU0ckhNak9Oc2ZaUzlB?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Why High-Stakes Decisions Demand a Different Kind of AI - IT Brief UK</t>
+          <t>Announcing the shortlist for the AI &amp; Software Development Awards 2026 - Computing UK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 23:35:05 GMT</t>
+          <t>Tue, 10 Feb 2026 14:41:58 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOYUY4VU01Q0ZDQVF3TnZMN2I2ckMyeXpjRlktczhyS2M5S0Q0YUlOaFNqbDhDQWpTTkUwNlJITlQtaFZ0aTBkSDhwc1d3c00wTXk0ZjRXSDJJb1czVk5PeVQ3eHFTNW84a1hha1V3QndMTDhUeXBZaks5RmwzbTVyeVNDa2F1bDV0NEIw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPSDVzNXFfdDltRGFLRDQwWTRyMnZxSXhKOURMQ2VOOUc5RlNkN19PXzVuNU52NTBNTGJlZDU5SnRwY1RkdHdHUlpDNS1samVIQnUwakM3VS1sZUkwZC1vNmctTnJqN2MxTGpHMzdsNjFwOWd6X2RTRXpvY1RNcVNMbm85NUZfMHNTOFRsZg?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>How agentic AI is transforming financial services - Impact Economist</t>
+          <t>CreaTech Network 2026: Exploring Creativity &amp; AI in Entertainment, Heritage, and Open Tools - The University of Manchester</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 02:29:43 GMT</t>
+          <t>Tue, 10 Feb 2026 15:48:14 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQdk5tYWV3M0t0aEtZRHhmVnI1STNPLXFBTTZPLXFXZENUbkdxMDdSaGE5dUh2dmRkOWpRYnpScHdmeE51SEV2WG91ajZJbUZPaFJLODloZUFtMFAxQkNfN0U1dEVqUUZ6YTFqRnhQZm1SWFRKRk9COUpRWmlTMWRVUWJUamhmdWJ0bUNPMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPaHMyWTdfQTNFNzNKcS1zeGIzcW1Pc1RhS3JZV0ZXOV9TMXZvd2l4V2h6aXZSLVYzbmJfd3U5VTloRDk5NW5BaHRyV0NsTnQxeWd5Wld2WFBRMlF2b2c1bGJidGlZWGlFTGQzdzhWc2RtdTZHTEVkYi16UHhyVDZsMWROODZLb3BRRExfTzBURXFLdl9ncm5KM3RrLWxaSzNMMUExYkQ1QW1YV0NNaDlCbTF4TmtCSUZhZmJGRm9rdEMydkFYU1lR?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Liberty Global and Google Cloud strike five-year AI deal - Mobile Europe</t>
+          <t>Former Daily Mail editor tells hacking trial allegations are 'preposterous' - BBC</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:15:55 GMT</t>
+          <t>Tue, 10 Feb 2026 19:30:14 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY0RJU1NmOVNBNzdrOXdTXzdfZWF1QXpPdlg4ZHFKRU5tUWV3MndBR2lrcl91bHFVZlJtUFRPYmZBX01YeU9FUXhITWtVQXVkc3J5TVpxTWRMY3Z2cjhyZ3dZTVBqZWxkTXA3eEREemRsblBQYi12aGVWZWloVkY5a0lUNll1NzdmdjZ6VzVpS1ZqQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5Kelhub0J1VVQ3NHY4a3Uxb3RiS1piWVczSTZWeDBwMnNlMGIwQnRnQTJmdjl1OEZ4V2R3LThRdExnc0lGV2w5M3BGUVA1MzhNZTVLTTRZTC1uQQ?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Amazon, Prosus Reach AI, Cloud Deal for Double-Digit Cost Saving - Bloomberg.com</t>
+          <t>Broadcom Wi Fi 8 Launch Extends AI Networking Story Into Enterprises - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 04:30:00 GMT</t>
+          <t>Wed, 11 Feb 2026 07:09:00 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYlpGRFV0SVRkU0VuQnBMaTRKaUp3VDlGOUswRmNuQmFCVEdnbkNRcFE1NVdKbjdrMmRSanU0M2NxUDVRQjJEZkVJeGtKLVVEYXZwdlJFb0RWaDVRUWhRbGtZbWFsSk4tTmJpNm11UF9PYTdCY0FXc3Jwcl9XRkRCQmIySElkdDNMQThmYnFpbzBYUVgzNjFNTEh4Y3YtTS0wX3BFTjNVWnltMWdHT0laa2xXdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9fbUhucEo2a1Fqcl8wQmJiZDgzZWRwU2dtSWc1c3doVV81LUYtZm1PejlpZDA2RWRnQU5DbE02UWhWcHo1OGo2LURQY1VVeDVHRFpKTDR1S2I0TEVkc1RwZGlXTjlEU1dyZ3N6NzdiRTlsSktLcVVxZ1k0SW4?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Use more AI and video hearings to fix English courts system, report says - Financial Times</t>
+          <t>Hospitality Tech360 puts leadership, AI and people at the heart of hospitality tech - The Caterer</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:01:01 GMT</t>
+          <t>Tue, 10 Feb 2026 14:21:04 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1zU2RFeUxERWhId3lMWDFVbmJTMl96NVhHdndqRkt0VW1JQ2ZSYjJtYWhYS1J4cHc2RHQ0X2tzOVp4ZnoyNDE1eE5Eb0ZJVzdsbjdCdjh5M2pUak1WU1pZbTU3Y000ZlV3QWV0dGh1clA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQVUJLWlFobVJVY1hZSHFobVJaZEZVNXEyUkh6RlpHX2l6emgzbGhHbF9kWmtGLW5QU0k5dm1UcEdyX2dqTXVoamU1TmlhU2tFWmJoZ3Q5aGd6VE1SNlRnZE1QT1JPVkpTVWFiMFNnWWtQQzU0SXRHNkR0LWdENUVjLUZ1VmZfQ1d5MXMtLXg3c3ZkSGJudHdNY3lPUUVmQzl1akgwZ2pBVlV2T1RRTGNnbTU5bzIzUFlX?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New robot swabbing technology trialled for the first time at Sellafield - GOV.UK</t>
+          <t>AI and the future - Atlantic Council</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:41:15 GMT</t>
+          <t>Tue, 10 Feb 2026 11:01:20 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOd3FSVUNTenVpSFhtWjdBV3JYX2JNRWFhTWZCR2U1Y1FsWlVQQ1FhUjRMVmVwWnlZM2FOMUxJYVgxTk1maEY3RkJpMk9EZjk4Wks5em00UzJBbzRwbUdKUGVkUC1ybkJNc1J1WmtMNGxjMjhiREhzX29JTWQweHZfQ1ZhejluQjdSSzRmVVBGdDNWU0syUUhEd04zMWYyV1IxUWhETlRCejVldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQRzhpY0tmc21xVjAyVUJnVHB1MUQydmRNRGVpZUhsWDlkb3BqY3dzOC1PZTUxM0hiVjJmWGxJN2ZBVVU2LVI5aEJmMW1Zb0ZWQ194cmxnMlRFOU1wWndWRGVVTHVBa0dZckdhOVVYQUZmZUU5dlVodlpoenVRa0I2elVORk9aUVZoU0J1ZGJfemhwMnVNX25VeVZ3ZXRjMGhORGdqUnF5TQ?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01.ai's Kai-Fu Lee: Why China will beat the US in consumer AI - Financial Times</t>
+          <t>Microsoft Confirms Saudi Arabia Datacenter Region Available for Customers to Run Cloud Workloads from Q4 2026 - Microsoft Source</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 05:00:06 GMT</t>
+          <t>Tue, 10 Feb 2026 17:35:19 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE91ZF8xa2FhUFN1cnNHR2lzWlloQTg0TDltLXA3WjVnNktxUWtCaWpFcXlSS2ZrRVJUVGlxOUtOOVkzMGFjMjNWY3lWaGx3MlJSQ25DRHdOX1FzVUwwQzk0SkI1QXJOQVY0dk85MXNhUlY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNTTNSejlUVVk4aWRpRG5YNDJzRzhVbHhHNHJfVlNQNEphQ0J3RTJ5WHJwMngzWlRqS1RDdnFzdldkb1VTemhmUDV6d19FYXdocHFoODdUTTNiUDZBbS1nVUFiS2FHQi1TU09ocWVkNXdCLS1mYkl6d1YwMGoxSGNwbmFEUG9GSnN1am9sMVR4bFBKY2VzNVdvWmhlMl9xaDVwOHRacnBGV0NCaGFCS0hfUnFJblNBb1BpbTlVSERXbUxZem9OOUFQT1FENmN3UXhXTzRNbHoxQVFrT2VJdTRDMEQxaHVONGZmWGYxR2RR?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>The trillion-dollar question for AI business models - GIS Reports</t>
+          <t>Drive for AI and data to push tech spend over $6trillion - DecisionMarketing</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 07:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 11:30:00 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE94cUluRXhZMVo3ZjhYeHc0N25PUVN0cUl4RDdGeGtuRWVDaEI1dzJUc01pVjJNZnlyTDB4QU5iZ1YtZUtXRGpLbVNuLUU3cktEajkySzR5WGdueDBCMUVmT2p5LTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOSFNGcm5xUFVCMS12M1pUWG0zZmpxV2ZjZktGRm9WdFhhMnpnQVhoSzE3ZzJDOFktYkpaYVNPRWpKbjBwZEpGQWxCclZZTWtQQ0lVVWs1RXc5MWVQcnJkYjRXY2xGNUtrXzNnbHAyVjdHVXZ1Y1c0RmcxZGVSSHZBV0t6MDVScndqUGV5OFo4aTZDNnd4MEh1d0FpNF8?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tech Secretary: Barnsley can blaze a trail as UK's first Tech Town - GOV.UK</t>
+          <t>BBC set to launch AI Unpacked Week in March - BBC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 12:31:33 GMT</t>
+          <t>Tue, 10 Feb 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPd0luMnF3ZHJGUFQyMV9VaXM1OENiNjFWVDRQbjRkRWlCeVBvaGxoYmo3Szkxdk04aVlpOEpsazZCZlZMRlNPMk10TnpOeWZOWXViNjNtODZtU3NTWHFZeHRJSnlpaE90Wk1UYXhmeEFwbTRqVmdNWXMwZFVTYmJrRUVUdWN6MDNZY1pwTFVNdjZab2xTMnpZTGNPN1ZhR0pZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBZVjlQN3g4Si02WTdkcEswUGxNOUFhd1Y1djNXMFh4N1QzdW1rVG1ZaHg3MlFaRFQycXFCMFpxaF8yd3pFMk9zTXhUcmJyUDlGRWpRNnJjemZJWTZyajNteTlCX3hBdjdDMV9NQnVDbjJCZw?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Are jobs getting better? “AI has the potential for a massive productivity uplift” - The London School of Economics and Political Science</t>
+          <t>AI’s New Bottleneck: Power Supply, Not Chips – Asian Chemical Connections - ICIS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 12:55:05 GMT</t>
+          <t>Wed, 11 Feb 2026 05:37:57 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeE1EZV9iRnpHTVVPZTR5MDRrOHpKVHI3OEdpN0VobFpEOWlfdFVNQUpqZVN6N1gxS1R6V0J3R29YM2s2LW1meXZ5V2hRbE82Y1lyd0JpY0N2b2RWdFFWcFptNVF3ak4tWmVQUDh1Ym9kZEpqZG1VODF4Q2ktQzBzWXJlakhSQ1Nyc2tqbGxib0xZM19fazMtMW1WM2J5Z0tFUG53X19RaTB1Mm56ZU1hX2g2OGhsYzRnQUtOUlF5VkRndEl2T2FvRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMXFXbEVuWlBpNjh2dmJENkRPeTVpUVFVdVU5NW91WXJxaV9sQ1FYNXYyUXdlTHJ3WkxxajZpVWNrYWMwS2hmeEo4SnlDbUZpTGl3Skpyd1NNTHlLd2ZUQTNNVnV5ZHNYSkpUYmtEX05mRzhySTRRRFp6UVVuZ2V1YjV6RlFjck5IUWhjNHpjVW42UTlrcWZTLVhJdG9iNnc?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>From ‘nerdy’ Gemini to ‘edgy’ Grok: how developers are shaping AI behaviours - The Guardian</t>
+          <t>Cadence introduces ChipStack AI tool to automate chip design and verification - New Electronics</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:36:00 GMT</t>
+          <t>Tue, 10 Feb 2026 22:55:09 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNaFZVa3liZzhLa1dvUk5RVFc3d3h4MDVqbEkzY3lJOUZ0bzN6b0ZQZDVVLUdLTGF3RnFzZHA4aTFwN0Fja0I2WlhoTFYtTmhZa1BJYU9JSldfQ29Cd1B3WktreDR5alJSdUtCU2RRZTB3VGFocDl6eFhINHdIaEJ1VFpqTk1yeHlZZmp5Mk9QUk82dmtRVG5YZktURGx1UjVmZFpSY1BxVlduc0hNRlZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQdTRjV2plWTlqb3phX1V0cC1vZm1kWHROTWdWdW11X28tcE9JWUQ0UXNnTzhuU2E2dVlkRjZSaXhLTXRrQVEtZTJTOURaNXZHNG9rcXFLRmZzTURzNTFQcHdYNVV6WEFmM1ZfVDlrbmI3MThBb0tybzF6MUVEdkZoUEMxOXFLcmRNM04xVHpaeWZQeS1jMy1GdGFPUFNzdnF0R3k0LWJwWmV2bnI2bHEwbzBnV2xGTUJiQmUyRjQzWU8?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9 indirect tax filing challenges technology can solve - Thomson Reuters tax</t>
+          <t>GitLab pushes agentic AI to orchestrate software delivery - IT Brief UK</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 03:30:35 GMT</t>
+          <t>Tue, 10 Feb 2026 23:05:00 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOMXB2MnJybjVnVGVlR09Rak5vakU1NEs4QmZXWEM0WndUTjRfUTBlb3hVaUxEYVR4ZWpuQ0d2SlVvcnFNN0NXY2swYmV5RHJrSktGZkg5UFM4UFVTTlhUTFVRUmNKNTlpdGZRb0dxZ2pyV0JqaWpPMzItX2RBb1pUZnA3SGk3SEZqNVM0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOTlA2QTdwVUdWcy1VNGxCMG9EZGJqM0tZVnJBbU1JRWpGX0RxeEFHZnd4VWpvS3Rob3NGNlNUM3pDaXhhcGtDVnV1S19XSndqNzB3NEoxVHM1YnNVdHNrYkpTLUJYS2FlQzZRZWd3TXVoc3lrYmUxTm9qd3ItTm9iVm5oaUZwTFJBRnBNNHZ3?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Aberdeen Science Centre steps into world of AI with new theme - Aberdeen &amp; Grampian Chamber of Commerce</t>
+          <t>The Real Cost of the UK’s ‘Free AI Training for All’ is Democracy - Tech Policy Press</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:11:50 GMT</t>
+          <t>Tue, 10 Feb 2026 21:46:08 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalo5Y3l4UTZST3JaSGp3c2t3cTZZYzNhVUxOMDA4TFFja0QtT21LSHlnZW5vd3VpM3RiN1JEQkFJRFhQZ1FBdHJGOW41c2xlX015aEdYQzZ1ZGdVUEJGYzA1WEZzOEJhWlp4UXhYR2pvTnVWQnNvbnJXMjYzLTg0SG52OWVxRnR2WFVCTEJnWkhSSlB5MnRRbGVaU1haUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSV9sWF9hdE9uTjVQWEJMZllsZjhtS2JKTHhLaHNERXpVR0ZFQnVCVHQwUmVva0JUcDZrZGJlTWEzbW1ERUdPaEF1bHhTT3BTT3Q0X3laWWVOOWloUk9MaUx1OFBJdHFMeERXZGg5UTk0cG9nSHJONEJzV2JETFRaOFRCeTZnaGozSFFvUXpta1I?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Alphabet (GOOGL) Q4 Earnings Preview: Can AI and cloud momentum sustain the $4 trillion valuation? - marketpulse.com</t>
+          <t>Exclusive-ByteDance developing AI chip, in manufacturing talks with Samsung, sources say - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 23:04:00 GMT</t>
+          <t>Wed, 11 Feb 2026 04:47:00 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPUnl1S1J3dFVvMG9CMEdqcEphckNVTHVkSFFMMmNDb0JaUWhNMFNMM3pvRWZoRng1RmxBSG5UX3VRNFlFdTRjTDA1dngwRXl1OTUxSGhHUlNuelZMWmx3Tzg2YTBvYjFOSEpTMlpZeHU3eDJFWmprZmMzZjdHUDEzOFNhTkFhRkJnQ0JlVzVKWUh5NzJDSk1JSlpELVZyRkVTMW9tdlpuTkZ2akxnYndVbGJvZG16M2VYSWpqNVF5RUhoSzNYTk9qa25n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOSm83V3o3YXRmRkduOXRCbkV4a3FHeWpPbnJhc25OekNHQ2ZmdWdqZ24xa2stVTVwei0yTVg1b0kzR244MWR4NG9jUTFMYjFMYkgwNWtDZ2x3V3YwRDNzYVZvSGtQZlBueUh5UFpESUd5eUFjR1FaQ1czVzBSQnNzRGlPc1NaUXJRNy12ZGtxVDM?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Leveraging AI for Optimal Clinical Trial Design in Oncology - OncLive</t>
+          <t>Disciplined Autonomy: How AI and sUAS Will Redefine Security, Safety, Emergency Response, and Military Operations - Small Wars Journal</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:27:01 GMT</t>
+          <t>Wed, 11 Feb 2026 06:05:12 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPd29OejkxVVNVblpFcUpvbFdIQzAtd1FZaE5GemJURU1jUk9XSUtsbkxTTzNleVFNQmdlTWNtSjhPLTVrTXIxeXVDWHRlNzBBM1NYVTNCYTRCaHI4TlRPRE9UcVJUc3dSUm9QR2R0akU4Um1tWC11bks4X29UVFFCQWdZenhlYzM3NmRlWWk2RzhZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1aVlpiQzZqRXpqNjNjRG0tekRpOE85ZlhzelNHVGFIcGw1aE5RSDJYRWZTWU5JUXhkTmpNeUFIX3FIWlAydWh6T1JlQzA5S0dEM0U5NV9WcVIyRFlKQ2xubW55U3BBVVdCNmVrWUNn?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hospitality Tech360 launches programmes tackling leadership, AI and the future of hospitality - hotel magazine</t>
+          <t>AI In Robotics - New Position Paper - IFR International Federation of Robotics</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:48:24 GMT</t>
+          <t>Tue, 10 Feb 2026 06:10:49 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOTUloLWxxbENQaVVhU1hEcjFNLTdGMWZWSTBNdU81c1o4ZzA3SEZXaWo5aGEySDVZVnJ0cnQ4QkFnWUJXVjZJWndzTGdPQ2hEVlh5MDZrS3IyS0ZYUEZ0MTQ5dmRMSDJuYkEzdzAwVktYOVJqeU1LZmdfNkcxb3ZIYzl6ekNwcmlHU3EzWE0wbnpLb2VIYUVJLW44QmFtQnVqSTNEVWNuX1BXclJhUjhRT1pfbnh4MVozMzFwTUFQckJwdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1xNmVSVWNmVUV0cUZUeWF5c2llWVA4X2w3NG14NkNETm9xNkRoU1hySnlnTkdBQWNCSzJ5MXN2eUU2bWpZUU9iUjZFdTZEVHhBc0hULS1QYUJQcnJ0U3dvSElHSkxOeE9NR1pNMXlfaTE4VEhWa1VWbTF0QWJBdw?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Musk's SpaceX and xAI merge to make world's most valuable private company - BBC</t>
+          <t>World Defense Show Day 3: Saudis eye AI, and a local defense giant transforms - Breaking Defense</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:31:06 GMT</t>
+          <t>Tue, 10 Feb 2026 20:07:25 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAzc09Ibzl2eWJ1OEQ0VTkxakNQV1hxOERGX01GOTNYUW5RNlRwNnVNbzdzSGR3TXJnaTNYTUdkT1doUXdwTko3ZTNJOWxNeXJTampQUVhSRDZlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1WQ0lTOW9fbVhrOFk2ZW1jdUZpU1VJM25MUEVlbDlTZ3hiXzAzd0tFWTZTYzVGWXRxT29fRnd4dGZma1FNZkpXSU1za1pnVmFibGsySmhzLXNYc0t0RnlCbEM1azcwaXlkZVJobXpxNXBpSjdN?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>enclaive secures €4.1m to scale confidential computing across multi-cloud - FinTech Global</t>
+          <t>'Introduction to AI and ChatGPT' workshop in Haverfordwest - The Western Telegraph</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:22:02 GMT</t>
+          <t>Wed, 11 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOQmFLR3ItVk1aSW10TjRZWG9wSjk4d05tVHlLekNNVzdGeW1uanh3bGpJRlVoZnVvejY4Umdmelpya0tLMm02QnlrWXpsRDgwZHBPckdTclY5M2tySEVPS29qRVlrT0NucXZoZDV6LWlHci0xeVZMY19CRWlPUDB5OFEwajU5ekJZWWVDelZuaHFMSWFMNDhiM1lCV2E3Q3VDNHpYX3Jsc1dNQnM1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPbHVBanRLX3dTQnNiM3M1SWRSM2tsSy1YRWhHbjdhV3Q3RDBwMHZGQ1ZJcmlTNWVRbnhqX0wzZXpuQ2dRMWZZcmNNNFN0a3k0TUJGTXJIRDF1VGgtSkx0ZERCOWtuWG5FQmxvNU9ubDFCUm55NVpWRDB0Uko3R2F0eVVoNks5czFNXzdRcU1qdkMya3Jtb3JEMW9kWGlIU0drV2xNdlVn?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IFR position paper on AI in robotics released - International Federation of Robotics</t>
+          <t>Airlines' tentative approach to AI - PhocusWire</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:50:47 GMT</t>
+          <t>Wed, 11 Feb 2026 06:04:02 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1uM2Vnek8zdm5IV1hWem9CYWl1S0czMEJLd3lhNHNlLURxajlQZy1ISzdSd28yblRfeUpKV3ZsYWlPYlJsNGdDalFWMUQyOTVqSmQxMzNqV1Y2SE9UbzRxcjc3RzVRcTc0NG9tYV9JbU5fWVAzemRVMTVhV1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE15Q0Q0VVZhY3hXMHcxSzR5REt2dEsycGY3X3d1R1VHRnBCOE1sNDlMRllJX05DYzFCQWZWYmFvRUs3Y0M1QlRqTGF6X0pNcWF0WFNfakUxTzlIZ3Mx?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Perseverance: Nasa's rover makes history with AI-planned trip - BBC</t>
+          <t>Brandwatch and Blackbird.AI to deliver advanced IEAC to NATO - ADS Advance</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 14:21:14 GMT</t>
+          <t>Tue, 10 Feb 2026 15:46:00 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFB5aXNmSUoxVDhEZjdEZ1l3WG84WGYzX2pwbDd2UFRsZFczWDhqRk9aMmZ1bENhZEFPVDFwaWtyV1Q1VVZndjNMVzBDTVlzZ1ZCZDc1QTd4VFZKQzBUVjA3ak5mTdIBaEFVX3lxTE1VOUNha0wtSkpOMV9icjRyeVBqWU4xZ3dWbTlsVnlwcjItOF91VkpITjV5UlFRaE9MT0xCcDU0akJKTm1ZWHB4U01qR29nS3pVMUtabF9XWVIxQ19ZbVdjZXNOVzRHNVRa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPVkFNd3ViOGV3QnRsZXJFbm1nNkJtQzNQVURwOUxMUlJxWGRCZFRmcmZxMERUOC01UU9OY29vMzJfQ1Ftal9obXRzVEVvV3gtSUhGYVpOS3NVd3IwRjUtU1NpbW9tWlpfRFpKX1MtcE9lMHNNMldNYmVCNFh4aWJEVXlnNDNIbXU5ZTNiLWRLcHpWR2U4NVhqLThn?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dow to replace 4,500 jobs with automation and AI as shares decline - Packaging Europe</t>
+          <t>Spotify eyes AI ‘derivatives’ as new revenue stream for artists – says its tech to let fans make remixes and covers is ready - Music Business Worldwide</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:08:32 GMT</t>
+          <t>Tue, 10 Feb 2026 20:17:54 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUG85LWpVTTB1ajhzU3dMMEtCa3NkMDRxbmpjZTV4RmlvZ1dpSlh2VmZZSW40VEV2QzcwTDVaQVltdnpKT0gya19GT3I1VnJFUGNjRkNGNUtobGFCS0RjV2x1NmV5YTQ3bzlYUWxHRl81dnpLVk1vVHlEemtUU0JDeDk0SVhDYXBsSG9pMXBJdnJfOWpPQ3U4NjNVWm1IeEhCT1l6aWUxQ09EaGg0czl5MXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNRWVIcGREN0dDODV5N2gwUGZlVGR0elIzLS15TWJuTkZ4VmxrcTE4eVNRNDhCVzh6XzAyaHFvOHRIWXlQUE1RQkZjOEtyU0xGU0s3azhIYnR6d1ctbXhMMnVZZFNodTFxU3RIcGRhOGVwRFpKN3JKQ1VnWVp5Q2FMWTMtZENnUVdwTTgyeEJNMENaaXFZWXp2d0cyb19SVDNudVA1OERmbGFLT3EteXR3QzJaOHNwMGxVR3BTdU44TTgxXzVMMUZyamFEUUdjd2Uxbks3dGZvaDVQeUpmY3hkYVJSRkt1Ymc1UTQtM2QxN0lNZw?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>How Do Workers Develop Good Judgment in the AI Era? - Harvard Business Review</t>
+          <t>How the use of AI and 'deepfakes' plays a role in the search for Nancy Guthrie - NPR</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:44:19 GMT</t>
+          <t>Tue, 10 Feb 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1TcXg3M1ljSGhzb2kxLUVYejNnMjdhYVpKeEZUV0F3aV9EOV9pV21MTmpEWE9JR2RQUUFQSVJJZDVxNnZBQ1ZIRDlKOU9Jb25QYVVIX2ZEcGZOWXEtOHZBMXZIV3U4a092VG1UU0hheGpNcl9OZG8weXl0Rm84REk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBaVWdvUkFSRWF2V3VKalFvX0x2UDVvT2tVaU5qQ19ZVEFTRV9CQWtNSzdGWV9uZDdZWGhYLXY2NHNYdlJvM0FfN1pXSUNleWdpSE9XVGRSbWx3bDFpc3ZLOF9lUlhHQTJPY2ZtVVFkdEZUc3JSUFB6QW54TQ?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CNBC Daily Open: Nvidia denies rift with OpenAI, while software and asset management stocks plunge - CNBC</t>
+          <t>Experts urge Ofcom to probe AI’s role in fake news after major incidents - AOL.co.uk</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 01:21:00 GMT</t>
+          <t>Wed, 11 Feb 2026 00:01:00 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNHpZWElCTU8zN3VlSnNoeUhTZ2tPNWJyQzNzWDZOUldkTlkxcXZSdUZjWEswY3FVbmRCSjV2enRFY0IwVWU1S1JFMG9HV1JfOWtKN2Nla1lEVUtzZFlLb3Y1enowRkhrTlM0LTRDNlFacDZzclp1MGI5a2dmcUdOcjEwek5fREFTdHdnZzZ2M3NqSTAyQVpPMjhUV1pHaUduZ25QZEJ2V29qWmt5aDBhMGZlN3d1dTJEUWlUbjRUckxPVFQwd3Y2Zndib1Qxd9IB0wFBVV95cUxNZzlCQ3JZMnlJMEdPTTB0TThqM29fR3R2S3JTenFIX05YSTZFNlNzQW9RWDRzSU1uM0Jfdk83aWtXVlJsQ2lWTTdXYTh6U0ZPWE4zZHhvOXhxNURSUFVzdlgtUGFNcXJtcWd0U21GamdTbExFMERtVm0xVDZrS1E1VzdkVExPTm5MelQwelB0WmdlaHB2STkzQTEzZ2hsZFZ1M09IMkdORHNHLXdJYjJod205dUpPMC1XU0RQVGZ4M0x2YmtWUjdCbmFLVHZGUGhObE1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1qODVTVTA4ekN0d2NrQnhrQXgzcXJPR1FRN1VrV1lncWVOOTd6ZkVyWEIxTlF6VTc5MUhiWngxTWowV00xbXJuSmRQc3lWREp1Zmc2UkRSV2MzWWtRenJDZHVuSHFudWZ6dE12SEV5enh4UVZuQWlOWmFBX1hYdw?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dassault Systèmes and NVIDIA Partner to Build Industrial AI Platform Powering Virtual Twins - Dassault Systèmes</t>
+          <t>Is AI getting smarter or just getting better at faking it? - Psychology Today</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:31:12 GMT</t>
+          <t>Tue, 10 Feb 2026 10:58:25 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOb1BjODQ2T1lSRWZJUWFXV2laMjl6dElWODlZa0Y1M295UENQS09BMHR6VHJUTlpRcmFsUmhXclU4bnoxd2NBaHRTQjUtMDRmNG1Ob0QwTkgtaEtiNUFLbUtIUmVZWXFkVFBHUVVPSUF6UWw5N1hyWHJMQ29zeFlHZFduMEUwdjd1UXBFUTFKLXctOWNJWi0zSldSV1ZOTW5EZGJHelUwMFprSUlKLW9XY25kRjBMallKeTI4b0U0amRuYzlyTzhCNjlqS1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOMmZOQXhWQldBVXA4Tmg3OWgzekRseW43cmlZbFFuVUhCTXFnTkFDTGNEYlVyZWdtakZzUlRGUV9OUjN6ZzlCd0JmaW9GNTh4QUlEdXhUSFR4WndVdnZ2SmljZXVQX3ctdlVhc1dmWlpFeC1HLVh5bzgzR3RBcG9YZzJFMWZQSE9aSlFPWXJaamFfSW9WVm5aNW90M0V6ZHdlTHFQUktuaFVSSC050gGyAUFVX3lxTE1LcUZETWdkOW9FUEhIYi0wak1DY3Bncy1XTV9qZVBFejlER1I2MFVyRl9MNUhXUnhndmYxWnJBODFsWnhPZVhFNDFRcUpGVVNEeXVycW5MYVc5cmFDNG9leHZCRVR4SWI1ZHlCUjhQZ2ctUElpX1I4cjZJOEdCYjh4d19Xcmh5TGg1LWR0NE44a1ZxZWhQQS1zZEZ4dXIxeG4yZ3Z3blNHQ0FNWFprNFBhMkE?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FormationQ, Cambridge, and IonQ Collaborate on Applied Quantum Work - The Quantum Insider</t>
+          <t>Empower launches embedded silicon capacitors for next-generation AI and HPC chips - New Electronics</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:30:00 GMT</t>
+          <t>Tue, 10 Feb 2026 22:44:07 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPS0xHRF9WcnY4VkFOSDFLd2RYdFpBVjdfbUJnd1FWRWRDb2JrbjkwbWdLUzc0bkpLc2c5T1pJbnFFc2NZcDRUd0ZKSmNEN3V3dXFFRGVrcXl3NGttZjh5VXJUZ0ZsLXp1dFJiRWJOZWlhREJLaFFTd1RsbGUzby1WTHh4cklCdnlkMXBvWlNDV2lwc2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOQ283d3MwOEE0eDFleTFIM082VVlCS2FWZFNLeExqS1NWNU9MY0FETnpEd2V6ZnAyRTNDSnlxSXVuYVRMbV9fZnp1Vmc3X1dfcTNJUVZ2R1czYnFNVVE2b25OZVpvb2VVdGk2VkZTT01MWnUyRUJUU2JmOS1lT1p0bGREV0pNRzdtVkpEZGtUVjBlaTl2SUZsMjBzeDJxQlFkbk0wNHJLa1JjemlHdnpuYVJ6c0V3c294MlRidTZZRjl3OXJ5OU9lLUw5NmN5RnV6UFVad3VR?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>UK-Bulgaria: connecting semiconductor expertise for growth - GOV.UK</t>
+          <t>No, the human-robot singularity isn’t here. But we must take action to govern AI | Samuel Woolley - The Guardian</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 13:59:31 GMT</t>
+          <t>Tue, 10 Feb 2026 16:17:00 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUHdYRDVQYWVLZjR4MnFna1dPMEJYd25Bc3VvdllKVGJ3OXAzcGIzUy1zX3hQUHhfZVdlZExSZWVkVUc1dGF0OG5ncVRpNkp3YlNaaFBKZjczUm1ET3hBMVlRR00xbi1oVTZtS3REQ2tjek42Y1lKQUdTclFzT2dobGhIdE55QjVsVzFqTUJ3U01aZGVISTU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQeTlqM19rUXVLZHE4Y2RzNVVSUl8zRDBvN2lSWWlHZEJTNW1OQWR0dHp4bVBVZWVpaWpuOU8xemxSOVpZNTV4dXhsZUJKTTZvT282a1FGWlBRZHloNmdrWmtpblliSnpEald1VExmWDFfUUVLdl9ZWXg3M2pWSkxCTURTX3pZSUItdXlLZjJHQl8?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3391,27 +3391,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Managing insider threats across the organization - Barracuda Networks Blog</t>
+          <t>A Silent Arsenal: State Hacking and the Emerging Digital Order - ISPI - Istituto per gli Studi di Politica Internazionale</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 18:22:09 GMT</t>
+          <t>Tue, 10 Feb 2026 10:08:38 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPaHVQWllJV0VIT2dJaEtVekhZTWQ3SF9BMTRpeDRGZG13OWR0V0pSSmtHdWtEOXByTTQwNS1yNEJLTi00cXV2eDJ2dzVqSk1KcUhjTFRfT1YzaGVHdTBWcGNWLVUxbGhsTm13MGNzaTRPcndGbTc5b29fWGh6WUg4MVhrdGxkYWJLa0xLdFlKUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNZGc5ZFZSZUpBcnk1aEFMaTdvVmhoSklrUVlwY2tGUTU1ZU01UTI4X3BDQ05CSjlId3VmZnQwVk0weEhWNEZRUERsUndERTR1Rno0aFJEVFhEdHROZ0lvbnZDZ01oTkdZc1B0d0huMHpKd19oSHUyZC0xdmVXdDZoczJtUFJiTWpqbE1FUm9xQ0pxbWNEYTlzZmVHbHBUNnR4MXV2b0libmZ2TEd5UXc?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3421,27 +3421,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Prudential Of Japan Implements Voluntary 90-Day Suspension Of New Sales To Address Previously Disclosed Employee Misconduct - TradingView</t>
+          <t>The Atlantic’s March Cover: Josh Tyrangiel on AI and the Future of Work—“What’s the Worst That Could Happen?” - The Atlantic</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 21:17:23 GMT</t>
+          <t>Tue, 10 Feb 2026 13:24:16 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxObUF6ZkV6bk03bUlPb0dRR0hsdkZpYm4tM2Y0SU1LaktjWnhHeFBCNzdnSkFsQ0xZTU5ORG1lRDk5elhodjlVV0VmTkxyWE5YWUpuUnpRMndmeVR2NWtDdkM1Tmc2VEtOdEhlT1VNM2ZLdnpHM1NzTUJUaFJtbldJUm0xbzdxV0pjYXpwOFB6MzhLWWlTNkNRbHk4dUtvRWhIdkM4RkE4ajBKNV9jc2pBV1RpY2dJNVJzVmFmNHVURnpvSVpGb055Wk5yS2pLdG43aWpjZFdtR01kbVVxX0k1emg4eXE0U2FBamkwMTIzWldETlVFbWd5UDhjcWZTU1FBTDhsdXhLWVg0UGFOUUs3QTNmY1dEYXBoMEZRUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQa09QUGtfZUZPX3hOOWFkZzU0dkVXeDE1YmY3dGhmV0pMVmlxUnphM2FaajJodXJTOGZzYkstaFhteTg2VmZ6bjJsel82TmEtVUdkLU03dnRrOUJoYnlidW1xczI3eHpaVFRsaUtYTUZDOWV1N0I1ZXlYSHpvYXA2dW1vem50am5jaS10VW9BaWFFVTJmZ2lQeVh0aXhyS3RRbVhj?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3451,27 +3451,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Treasury Department Cancels Booz Allen Contracts, Citing Past Insider Threat Incident - ASIS International</t>
+          <t>AI changes forecasting — But governance still wins - Wolters Kluwer</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 16:07:48 GMT</t>
+          <t>Wed, 11 Feb 2026 05:17:51 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQeFBIZGtmYmh5RF83VWFsZHNvdmIxTWx1RUE3Qnc0aGdrT09YVWU5c0tHRmxuWk5YZVpDdGxGMWRCSTN0ekg4Y1pWdkV6U2xzUFFmVlFaUi1fVGJYTlJmamM2Z3Z0WUpBOW9IMWF6X2NVSzRlOFFsTWtXVGFYOTYtLW5haHhMYXBoZ2VtLTVhY0owM0w1bGZtUE91M0EwOVVidU9NRVVKNWNuMXo5VGZzaU5xbmtQUUxqV3UzeG9xeWhGdW15?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNRnF1SVU0ZEZ3LWk2RVE5eWhteGI1X3lXRG5qb0dxSmVTY1lHSDhPaGNiY2lXeGEwSk5TZUR4cllmYkhSelY5cGpHMDhycTlvOEhJWmpRTkxDLVBDdHhzUGwyUHI5dWY1VlRjR0JLcGQtZVRfRFI5ZWJqczZKd1FLNFVfRkdrX2VtZnRBZTZmRHg2c3hjQUZIZ2ZxTjhQdw?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3481,27 +3481,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ReliaQuest Highlights Growing Insider Risk as Threat Actors Target Employees - TipRanks</t>
+          <t>New National Cancer Plan with AI and robotics focus - UKAuthority</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 21:12:15 GMT</t>
+          <t>Tue, 10 Feb 2026 06:01:26 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOSFZCR2htd1dUQkRoS0IzS3pTbjdJak92T3ZPOGk0akhSZkRta1hwMVd6dzJETFVIc3B6eS1qU2FNOXNLYV81X1BEbEZEMllGUy14SURmT0RYa1VQQXM4Q0ZSMHlESjdzWGo2NkJrdEp2VGV0N3lmSnhORTI5dGdIZHQtVTFRZXRkcFFvbEhnejFaR2hncS12WXhtS01ud0hwSU0zS084N0JacGFVNXIxZ1dKUEloajFWX1E5WVFOUWh3UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPSGtUOGliT2gyd1FIdEQ3YXBOaGJnWk5MbWFNSTk3WURxWjE3SVBnS3Z0ckVORlNvMFVEVnU3TkdLV0EwLU1pbU9BeUg5cTJnXzNqai01SEFiQjZZZDVpNU11Nm0xakxzOWlwbjNZVE44X0dZMFBJTWQ2X3ZVbFlxY2NQcFJXOGZodm1iYXJESmpaZw?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3511,27 +3511,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>News - North West council starts crackdown on housing fraud with launch of key amnesty - Inside Housing</t>
+          <t>AI will boost games not break them, says ‘Clash of Clans’ maker - Financial Times</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:30:00 GMT</t>
+          <t>Tue, 10 Feb 2026 10:00:06 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdGROQm16bWJmc1kzMUg4NkdDVjRLN241ZlNRZGRyZVJQUVdXcUFEN29teVNuZ2pjZVJPX1RUNUNsamxVUElhbXkxUUYxcGdYcEttTjJtR2pxMVdkU0Y4VGV2aFd2YV85Wi1uSXNaZ3ltYUpUTkxPd2sxUzBINTdpYjJhT2tIbElTUHZzbldFZmxrR0diRHI2VUVKdFVfZE1zSGcxSGZrM2NOLUo3V3VqRTRma0xiVWJYLWR4YkNlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9lWDk2MVhfY0JLM1ZwWkVhOHFrY1ZlS3J3RmxZNjBPRG45MS14SHE5eUxnNUs2TGpKNWxjNUF2X1Vha1hFZFFtSS1xY2t5UTh2b1prSHAzVEZsbGhxZUxaNXdqeXY1WlhfZ2d0bDYyeWI?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3541,27 +3541,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New phishing attack leverages PDFs and Dropbox - csoonline.com</t>
+          <t>Are video game developers using AI? Players want to know, but the rules are patchy - The Conversation</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 02:32:04 GMT</t>
+          <t>Tue, 10 Feb 2026 23:19:16 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQUXE3NGNkdHdXeDdMZmg2OEZnVFFaN2szamdjOWkxYkZIdllITHZLRDB1WUYwU2NQaFpEajIyaVJ0SmQ0ci1uVmg3c3BKOHNid2ljQ3hJVjUxVU1OeXZwb2JXZW03YzBuZ2hiWUZuVDZ1TmE3NGpzNE5xbjFOYjZSSmdmeHNaUjVzOVZQaXBsQTBDZ3pwam5WRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNY3RRVGdBMHJDRWlkRkk5NGlVbXk0SlFPZTNWVFVmSEZ5S0VRN3RzODhqT2FqdUxvS2RTcUxkcEcyVHFYYVczUFpvYlpPUVY2Rm4xckFZZnZOOWZBcUdlTmFobVlRODB2TE1nQVZILW9pRVNhZkVrdDJLSk9YaURkVms2RmhJX3B5LXJZTU4yb1hWYUtyVkxBQ1BsQlNmWnoxMFpPR3lwSk1GeWNQbmFhRzdkeXB5QQ?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3571,27 +3571,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ireland’s questionable relationship with social media giants and scam ads - MSN</t>
+          <t>Startup Stage: Altek AI wants to use AI to improve hotel guest communications - PhocusWire</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 00:34:46 GMT</t>
+          <t>Wed, 11 Feb 2026 07:04:12 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOY1hlNFR3LU1LUzJRVWpOTmQxZGZKbXdpMVRjZjFGb0lId0N5czhfZHNQUkxMMUxKbDVpTlE2Vi1LZm9iNlpabkVGdnl3dFM2LUtlZkliY1BjYlI3SmR5TXlNMVBqUlktOVJMaVhCUjNmNWxQNUt0WFhwcFVmYmNyVU9NV1F2UFFhWmhXZE5FSDllRkZmZkJpaUYxbkZiQlhFZFpZUlAtakdMOUgxb05OSHI0aTBUT3g5SVVvVWlNVGh5Yzh1TTdRTWVZQVR3UUY2WTJyQU9Da1hZd2hCXzE2Vl9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9NeHU4UzZmTTZaVGhua1FGcE1OaVY0YTJ3RDVEUE9oTGdtQk1JTlBMLWRkNW1pVWd0bEowbjA3LXpxY1NXRHJxc2RxNFQ3eUNhd1ROb05JaFpKLVU1MFE?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3601,27 +3601,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>State adding staff to review nearly 6,000 Medicaid providers in Minnesota for potential fraud - MPR News</t>
+          <t>University Seminars Explore AI, and Also the Medieval World - Dartmouth</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 17:32:00 GMT</t>
+          <t>Tue, 10 Feb 2026 15:34:27 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNUGlSc0lpXzN2X3VPbTFXazZ0cF93WTRYMURlNW1YQlB1bFYtbGZveS1aN1BpVWxfWVM3T05UckE4eEJVRU40STNtV3FCdjdrZEdpVWdXa0JkeGpSSVhGTUlJRWhYZWRXeG9XTk5wRndmZXQtY0R6bzVITlN5YnhyNWFoQ21oMldRcDdiaVBRN1JjOHhINTVWZ2dHYzVSUUIweTE4Z2ZneDZUeWFIYVd2YQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQ0JIaktHa2FDbFJuNTIxd1d6WXpQYkZsVkxaX1R3c0NwX2dERkwzaHJhdFd2R05MMGpmcEctNjNxVGNoWEx6Vk1YX0VDcXdxUkd0dXdIcnNmaGtYdlhrSTBwTVZJbDBvWmluQU5MOWNUd3ljWHAtWVV2ZndDY1VYeDNrVTZrcTZUQUZ2ek9xd29paVBheVFjWldR?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3631,27 +3631,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Man used social media in Gaffney property listing scam: Police - wspa.com</t>
+          <t>Why the OpenClaw AI agent is a ‘privacy nightmare’ - Northeastern Global News</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 01:07:14 GMT</t>
+          <t>Tue, 10 Feb 2026 20:18:26 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE02c0VSLXZKdFlTZDVjRmdHYUZiZVdpMXNfYzZXc1h3Wk54Wk9UZkM2bjFwX0tCNnpfcEc1ZUNZeUZsNmQyR2V1Nks4YnhvXzZObC03UUI4eXRyUVM0OVBsT05kbkR3YlFNWUxhSWxB0gFzQVVfeXFMTVpsZE8xWTBvTTFfanFtY2dob3BSWHlYWlZ4UWJuTVVnME9SYzI0eEo5RUJoSnJMOWxxRVE0Sk45cktocTVxSnpvODAtZmJhT2l0dHJEM3FVTzkybEptZGVYYXpUS2RLUnlWMG83aTlFNWtXQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1LVENWSG5FZElMZzNVUXplWFIzVmRwdU0xSnBvdFFiWEJfbXJHNDVzLWtXRkREZ1J3RHVwVkdkdDl0UDcyMk96OU5sNnI0Y2dNTTZlSWN0c2hIaFZRb3pBUl9wYnNIdHFHUE1URFBLaE02QQ?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3661,27 +3661,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CNAS denies the information about the granting of 5000 lei from the social fund: It is a scam - ipn.md</t>
+          <t>'Just working towards her pension' - woman settles discrimination case - BBC</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:46:59 GMT</t>
+          <t>Tue, 10 Feb 2026 15:28:20 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQeUtTOTY5c2w1MjBkLWxRUHRacllZN0x5MlNuNDBJMmZJWW9CZEVPaEdBTzhIUDJIRUhEX1g3bThnYTFXRERpM1FwV1dxei16ZWVPaWhBUld1NlRrRXFRRVQydlRFZkdhMnJvbk0wR2R1Q0RfLWRNb1VxT005eHVkbWJlTDFtcjg2TG5Dd0dmWjZhb21Gdjg0Q2pXMG44LTh6U2ZyTnlZUXJfaXRCdG5mbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE96ZmdRbS1uS0tSMVVlZHhZX09Cang2QkNIZEJlaUlrNFBEZXVoM21DQ2VoLS1JVUFYUkxKM2J2cWJtSTBMa3I3V2pFZ0ZuTWMwME1QQkdOZ0d3QQ?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3691,27 +3691,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Meta’s social media scam ads cost consumers billions, investigation finds - ClickOnDetroit | WDIV Local 4</t>
+          <t>Addison Lee partners with Multiverse to build AI and data capability across workforce - taxi-point.co.uk</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:15:21 GMT</t>
+          <t>Tue, 10 Feb 2026 07:19:59 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNWkZEMG1naVNKampJUHZ3eC13SzVpN2o3NFU0Zmo4NFNwaWVPcHFfV2JDblREaHFzbHdYOUhvMW5oT3BLUXlaVEU2NG5XUG03ZUVheUZlTDliSS1UOUtMUFpXNnVqOTllT3JjQ3NyRmFMSkVNVVh6eHBPV2w0Q1ZwYlBzdDA4VDhSTnZwYThjamM5VTNjMnFSSmdLN0lzZDVIT3RudzZPVVp0VGUyRTFHUjFiRk85U0ZQdTktMWxEMGtjOG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNNWszTkZqS2t5a0s4X3V4VkpROHNYQ0ZpU2d1UkZjTEpoaGlyREtDNFhCTHFieGlkaDBxWklyQlpWNmpEcG1JTEVrZW5mNk9Oa0ZEZHNOWmZlRHlXcjBleFlsQ1VvUGV3akY2cW44THlVZnlNNW1jSkhteFA0RW5wYzNIeV9uOWs3TmNFNWs3Zk1DaDZ5bmQ4R2xpTUxka1NKcjM5QmZoZEZmZ1haRUR2bU1rUDA3QU1VZWx3?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3721,27 +3721,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Scam Alert! Social Media Page Claiming to Be Famous Krabi Hotel Was Found Fake - Thai PBS</t>
+          <t>Ransomware hackers say NO to Data Exfiltration and YES to Encryption - Cybersecurity Insiders</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:31:00 GMT</t>
+          <t>Wed, 11 Feb 2026 06:39:52 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9DeG8wQ20zZHhlcFdCQ2JSRmJHeEdBcjBqalAyQ2g1SGJId2pnWTY5Qjk1dmZkZDJXNDlsb29HWnFOTkpKQnFFSklTNEs2NlZuSTR3QXZWM1F2bGYy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZWdaZ2E3Tng1VnBVN01EWnVweTNBQ3lpUk5EYXJvRWIyRWN6T2twWUM4dnZraEEzUW9OejdFN3hYLVczb05zYk9wU3ByaVZ6YU1mR2tuVDBiS3Q4YlR3RnVMVmozSUF5dWtzLXZJUmY2dG82STA1aV9YWUNEN3hrZW1DNkFDeTNTMkJBLThJOWt2b3NXcmhjNFhBcERFSVdYM0l1SVozSk0ySGlL?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3751,30 +3751,540 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>The Modern Insider Threat: Shadow IT, BYOD, and Trade Secrets - Seyfarth Shaw</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 20:21:58 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQVXpXMVN1NDdoTk1QcldHSFlsWFVPa21BZ3JqeUltQVRzdDU4NlBGUlNLUk5EdEp3UWtJYjZDbVY3UE1CSVp3YTNqZzZiZWVIQ003NFNOcXZiMTlFZnRNUWxKdkJya1g5S09XeW1US09sWDl2cFpwenJHc3Vzb0F0NVBWMnFaWXF5cDNjV1Fnb1RHQUltYjhnZWdqU2ZGUFl0TnN1UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>When Employee Misconduct Becomes Marketplace Deception: Court Clarifies Chapter 93A’s Reach - The National Law Review</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 22:17:46 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPWFdfZWZYMFQ5RlQwdVZfR3h2Ty1JYlNqenR4ZS02ZVBsQlMySjJTb01zdzJaUFBKcFdVTTI5LXRjeGVrNVB6aTZyYnVuQkJBZGhJSFlDN205S3E2SjlLbHZNUEN3eFByVVR5TzEzRkxRQnVwWWI4dVFlS1ZOd2R2azhvZ2xrdW5IcE1ZUHI0NE03SjF0ZTU1dUdPMFNSRGp2VzhpVVMxcUdEWFUydTNKTXNKZVFmM2PSAbwBQVVfeXFMTWlLdDQ1TDY4RVA4MWMzTExqb3NmSG5sV1ZiMEx6YnJvengyRjI5V3NDb2taX0lrbFdvY0pBN1UzdDI5NVlFV0pSVi02M1BlMmNNLUxBaDNWYnlLT2ZETE4zRW9jWlFxWG1SZTdad2I3NFlvTHhPS3JqeVBzcDMwYWR5cldpblpLZGRXSEcyT0lOV180VWxEb18zeGtwZmktbDN5bFQ0MlJIcktma3RqeENad0N1R3hkQTNEX2g?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CISA Guidance Emphasizes Insider Threat Readiness - RTO Insider</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 00:27:09 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOZTdrdENmRVJPOUloY0tKMEt0N2JQT2hrZDJmQXZ1cWdlU2FhQTBYbm1USk4yT3JNQ3NieXZuZ3g2aVo2VUNPd2k2YTJ4UFpMSGZiR1dFYzU1TWhNbDNVNmQ2VlcxZ1QySDRRblZ2cHc0eHVRTUh2RWM4bzdPZlladUp5eEFwMkxMelowUw?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SD Public Integrity Unit fields 47 complaints, 4 criminal charges - aberdeennews.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 09:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOZ0o1WjdvUzZQV2YtWTZDc2JMU3RjVWtPUVhvOTlKYUEtY0FzUHJXWUV0eFdtYlZzcTJXSzFNeEJiZjNHQTFvVEZyTkNFa1BVWUlSd2lOa2dkMW1OSUdaSU8zQnItSlk5dXN4T0FJb04zd1ozWHRXdENzTGcxTVp5cWo4MnFZbkxiLWpMc3pMbktGdXZLWVhFc2Q3bUkwc0tHQUE4WV9ZTHoybTFRLXBPaHVkbFVubUlnS09mam9ndEZwOE1fMnBUd180M19YbGZteS1IRGFjN1ZkMlVVOHA3SzhzcDJxa2pieFNYV2dsZVdTQTBfeEIwOF9zaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Insider threat cited in $22M Iowa bank fraud case - American Banker</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 21:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcUhMQm5HVzBqRjVKY2NoYlBDNnB4aTdJYnpnb1R1d1N6empJSHBHRGVGN0NqUVI1QmFackp2VWVub0hCR1EtQVNZOVJSQ3JyUzBqU0ppTWtyMl9STzd4SDFMdmJrZ1VkQkZBSlExTkpOa3JNRmotWkczQ2hsUW5EdWhDUUdVZHVBVFpjeQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>From Social Media Pitch to Loss: Odisha Crime Branch Arrests One in ₹6.16 Crore Cyber Fraud Case - The420.in</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 14:31:27 GMT</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE4wTE1raE1pNGg0bzk4Wmc5U3BNQVJiYUtaUHFZZHhmTjJGb3h5b2RzOTh3NGs2UDdVMjdOS2JFUU5UMHFFMGtBSS1fcTBRWGFoNlp4X3BfZ293R1lYVGtDWktTZ2lrck4yVkVDM08yS3RERG11Z1RWcA?oc=5</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Warning To Under-18s Over Social Media 'Jobs' Scam - West Yorkshire Police</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Sat, 07 Feb 2026 11:08:44 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTHhVUEg2NUt1alJ3azBXbTN3dFNaZzk3YXIwM05PVENXZ2J6THByWHlwR2lybEJWblQ1VHJTRld5eWROQXdueE83SGVzUl9oTjVjUlJwYmt5YlRLa2lkZW42clJWSnVSZGtJdFYyMWc0d29tZXhUQUNVR2tiU2FVNy1kOG1NeksyRjlZd0JIOGJzbzYtc0VDQUFn?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Revealed: 95 billion scam adverts shown to Britons on social media last year - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 15:21:26 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQcFFPNXRBc3UydUZ4c1BqN1pPRVlaZWliNEV4amhiUEwzRlNYM0xac21GUkVjaV81b2ItWEw3VHlPdFZtM2RtbmI4eW5IVVRmZGNvaGNRMmdkRlhXeE9TYzc2aWJhLVoyVUZQSkxaZmRJNl95MWxoNHl5Ti1sWkZ6TVNQZ0ZsTkIy?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Fact Check: Social media posts misstate UK costs of asylum, fraud and tax - Reuters</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 16:09:18 GMT</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNU3pNSUUxZkhySnBMQ3c2YkFIRlU0dTdtZk1ZblVsUENJalM4a212czdVREVIYlhUMTFQNnpTVjJ3WUdMYWdqV0hjM0ZFV01KSUxwa2ZNODg5Mm1wZ1FZbVVNVHFlMng0REFuUEhWSUVtMTczZDdDSjJuWkxMbDZxTURsaXlXalNhVDNUbWFDNTdneExsWnVnYUQ1U0RSMW5SX2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Don't fall for this scam on social media about a deceased Charlotte County deputy - Gulf Coast News and Weather</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 23:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOMGlibF8zWHo0aFFZaTVkanVybG5MYm9uNHBJRjVnWDlBREh2X21Pb1B5d3c5T0FZRmVPQ0tvNTFzN1RTMTVtRmFvUWdaang3V3RFQ1ItRWxmZzVhVkF1U3pnV3FtVWdqcVJTQjhxOFY1YXpMYXpHcXVRTDRLWHpzcGJXenBHZENyR0NPMmd5Yms2ZEJpWDIybGRDR051c0R5QWlv?oc=5</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ESET Threat Report H2 2025: Phishing and Social Engineering pose biggest cybersecurity risks for South African organisations - ZAWYA</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 10:50:43 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOdlRIOHdKYXA3V0l4SWJCNXQyQmVYSUF5WXZmWG52cTRNcTI2cXJwQVoxMzNXd09VQzJYNzBUTldaVEd4cjhuX1cxRVlxM2VhckRINUp5a3JkSmExZXd2bUp4NzNxcEVRQnJ1VG8tblg3NDRGSnNscEc2NlJ1eUg3dFVLcF9wWklpVnVrRTlCa0NDczBveEQtSEk3c2xNSFdvT3VwVHRKU3RQanFpdEx2a1FOOGFhZE9VbnBtcHhLYmpMN29wajQ0UzZYYjVlZW1yZi1wUk1LSUpzclc4OHhkckF3TE9QcWtnaUJDRG9URm1aYmJHSVVZZWZtSHNIOFF0TWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>New scam spotted that uses a calendar invite, deepfakes of CEOs, and a troubleshooting program to create backdoors and data miners - PC Gamer</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 12:37:21 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxNNFJYLXNNVU1lOTRNU3FqcGFidUw1Z0R5ZUtaenE4NEJaLWI0QzFkR3pQOGVSR2t4QzhOckRjWDh4a01jcFF0bXFib2xGejFVWlZkUHZPalVqbEpnQ2hGd25RUVBTVVk0WFItZ2hwQXV0MXpqRzFrMDAxNmR4MHRuUTBkdGpKQlg0Qlp2ZUpUUl81SURydjcxSXRwVjBmWGZrdk50d0JDeDlPaWZqYUhzTWFFZ3ItNUxfbEZaczJxS3NQdTBuMzBlQW5HUkRHdVVfZzBXYV9JNVE4LWplZzRVT0VoR2hwWXE1SV90TUE2MmxMbjVGSDFNNXhtTmZoYWtKQ0IzRUQ2Rlc3WENFNlBhekw0SXYzR3JJZHNWY0ttWVl6YWxwbXZjSTdYZHRJcUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>The anatomy of a small-town scam: How glib talk, social media reels &amp; smalltown dreams fuelled a big scam in UP - The Indian Express</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 02:39:14 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPYnpYSDdLYmZ0Wno3aHc5QVJpWmF4Vzgzc2tJTzE5QmNERE96VWNBVXFPQUdNQWxaaWRsU0N5cDZMYVhsaUpCRDB1a2lrNDhaNTNIUUVKSHBCZlVmNkRqRGhZUkRVYUE0UFB0NTNROXFmLXZaVlRfV3hjbXZqbk9CQkM2LXlZUkN0UWZGd1JHczlsTERNRGU0REpQMWIyUkEyZGdiekNNbWdOdkhwakNsTUtFb0dqOVM5cUtyV1A0Nk1KemtxWjBtc0VmbFZ4c185VlhlV24zbjBDc3c5djF3Tzd30gHoAUFVX3lxTE1RUGJJeDBXajEtQ1VmX1ctcTdrZ1BXMzhTX0RDNGQwR0xRVUwxdTEyWklxRlNFTGppb1I5bWwwZWhwYzdTZWVSRkd0YWd1ZFZUNngzaVF1bXJlaHdEdjg2cnFPWk1QYS15ZWJRN2gyYUJ4TU9UbFN3TGxMMnB1anJaYWY4MDJxeGhGN0ZoZ1ExMEozcllUTm11bUhNX25pbV9yNzlteS0zNGlOYXdvNG84UUUwa0Rtc0FpaDBVbllIZDBaa0JOamdISV9HN1AyZ211RUdVelVKZDdxeHlJU1FlZHRKck9UMVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Romance scam alert: Man dupes woman via social media, Dh194,000 repayment ordered - Gulf News</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 07:56:33 GMT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOWjRwSzljVk1Db3o2NzB4a0hyTW56dmo5RW5zVVRwVnh4UkRBU2xQMloyQWdrSW1hNER5eDdJSlBSMDhlb3dyQURzOUU4NHlxVW5MT2NTLWxWeGlNWjZRM0t4TXdDQWRnSG5RWVFBYXRWdTlOY1VlZ0NwbUpESnk0a1RSQ1lBM2QtakpBeXZLNXgwQ01rOXREcVdBWUNiVDVfSXYzU0JUdzB3SkFPOV82MFFMMVFLYkpVdDU1TDV30gHQAUFVX3lxTE1tSjItbVNNRUNTS0t1UFVkNk9qbmIwX21ZU0d5SjNHVU1JN2I5X0F1QnRxdnNOQlZkLWRCR0Z5UXFWUlpON3YxNXlHZVFxUnpGZTRSS0YxRllRYS1FYnVJVm82Wk5vcWY3MjdiSnpIbkdtaXJRN1hPbzdnN2JMTUtsbHQtSHR6Y3prY2M2emNUNlJYWGIwV2V2d01mMFhBNmZJWWFxVWNkYzVqLW9uSVdhSUJRVUN2RWhzamhrNFdGVzlPTklQNjVSd0JnVVJNYS0?oc=5</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>As Minnesota cracks down on fraud, some lawful social service providers struggle to survive - Star Tribune</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 12:06:39 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9wQUJFY1MxblY2bEN0aG10RVZ1S0RCekpBbTZ0RWIxTnVZY0xZbFdrYWVpZThvV2ZfYjkzVms4Vjg0Y2pkbE91X0ptLWs4NWFSTHhKbXB0VXpXeEMta28zLUNmd2NWUjcyS0RoMlFBdm11Q1FuUjlycGVRSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Who Is Zyan Cabrera? 'Pinay Gold Medalist' Scammers Are Using The Name For Alleged Phishing Scams - International Business Times UK</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 10:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQOVoyNGdZTHg5NnA0QXRfeTlTbzdRNlJWMlVGOU14R2hjTzVVQkR6RzN1TDMyb1MybXNKdHRfbHhmT2RvVTljajVya2pDOVZJQXk2NmxqY09IelE4ZHFnYTRVYkdndHZjYW5VS1dFMzIteEhnVlQxSmdPWWN6a3gyR1NiT1ExdHdRVk1vVkhwQjl3NDFPXzhTLThxQWdnS1I5ZDctZ19hSDNLOHFrZU1mdDNfRTJ5WXht?oc=5</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Oz alleges Maine ‘looks a lot like Minnesota’ regarding entitlement fraud - The Hill</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxONlQyU3Z2b25RMk9UaDhXeUc5bm1oTHlNU0l5aDdubkJoU0hpQkVpbGxHNEVXOWFuWDhHYzdMYlY2dWJ2YmFjS1hyakRjekUzRmFsbTN1ZVZzTDZrRU5VLXVOMWdKQk9DRmJWUDJ5X1RXLWc4YlJ0NFJJU0didXl1RFJLZ9IBiAFBVV95cUxOU1h4b0JPdUhnR0RwTUFiUVVvaGtYVzhhVTJuMTR0d0o0bmdKLU5aX25iZFphQ2hRM19pRU1KX3ZYRW12SGdaMnF3dTVoa0tFZHhKeWRBajZneVhjdFBfZVg2bGs4OXdOYjdmN2xJMVRFR3BpNzZOZzU3di0tV1RvYUtRcG5DaG1I?oc=5</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Hamirpur Judge Falls for Social Media Investment Scam, Loses ₹6 Lakh; Police Register FIR - The420.in</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 05:34:33 GMT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5yQUF2ejV0dG1MOWF1SXoxeXA3bUh0bmJodmh2bVRwaUVMT2s5YVNNcnpQRENRWG1pemJNMHpxOFBfRzEzN2xESUJ0b0lMZXlBQ2RacDdPN3ZzMnVETVd2V0w0cXRSa2tCMUFhaUlfbWQ1Y1ZJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Trump seeks crypto donations in Super Bowl pre-game show ‘AI’ ad; social media says: ‘scam’ | Hindustan Times - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 22:54:45 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOQ3lsVnpYaHp5bXZKR3RMalBKUVlHdTJyRXZpUklwdDNJcHJLa1FpUzJicGZWM3lZNlR2ODUxTHhPNjBLYlgtZmQtWnR1X2tsT1BLOEFlSVl2M1BRVXJ3Ti1Zc25JUFdqNEVrMGhNbW1Bd25ubVZ3cGNOUWNwWlA5N0dHaVU3T3Y0U1N2azZpeXVYM2cxcDgtbVlmNkJYeE9pb2ZPejFTa0M4cGpyWHE0Sk1IN2oybjEtbk1DamY3SjJ6bmFYQzY1N3RVeTRSQ3RmVzBQWjBRbllTNDBIVWd2SV83NUJKRmRpZXphYy1aTdIB9AFBVV95cUxPU05sa3pSSHczVFZPZWE4N2tZRXM4MEtRQTdZLWl3MjlVMjctRWROMlc3Z0xLRlNrZDROWm5FUmtRbjhxS3VqcG5BdlNleXpKcDY3MmxsSUVWb09qUUxhaFNtdUpyQmhtY1Y1NWhLaW1kUzVtN1pEdnhBNE55SDRJWXRBYW1FTTVfbVZ1RmsyZGZOR1V6Q1VjVnFNaVZlMm9acm5uRjIyMTZtamxyeUZFS1J5TldwTFpUSXg0aVNMR1lzSDRLVHZEcDVlRGJoSk81TmJhb1RObmdBb3NsQlFYSUFqYV9ZWlFJclhNTk5SUXNPZDhp?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/weekly/topic_feeds_week.xlsx
+++ b/data/weekly/topic_feeds_week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Importance of Natural Capital to the Scottish Economy – Regional Analysis - The Scottish Government</t>
+          <t>Financial Services Regulation Committee report on the secondary international competitiveness and growth objective - House of Lords Library</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 09:01:39 GMT</t>
+          <t>Tue, 17 Feb 2026 17:06:33 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOTEJxbWVpdDlUUHY2c3hNa2huaENGUmtQQ1lfNTFaMDZfZ0xOWW5FaEhEemw2U3BqZS1PR2hMOURLWXNSanVNSEdXUGVNS0ZJcDlnVzlLYjZWYnFOeU9DMHVmQXZydGxKdzhKWmsxaXFxb0RHajMtY2N2YWhyaVdKZUVKcnFucWlOdFROczJyOXpiR3hvTW16RF9aZVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPZGZabjRpTEJfUjQzam5DeUNmWkUxNWN2M3JWbU9CVGY3SUhFMEwwWmYzY3RrMG9TaHlzMEVtTUZfUy1ObzRyX1p2UTVWRHpMRmVoVjVuNWV3TnkzWGpKM04talFyYkk5VHpFUHp5T3FLYWpvbUJXUjdpekdHWHVVdTU5TTFPUWRKY3lYRVlfTlV0T3BJc3B3V01fZWRuNk9QTUExbHZfYjYxWEk3SHF5aXdsV1drUG9nbllPbmp5bFp1U2hpVXJhTkl2cUxSd055aDR4NVEyUEZ6VFlfVm8wSkRWTUI?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Social housing conditions barely improved since pandemic, says Housing Committee - UK Parliament</t>
+          <t>Training more Britons may not cut net migration or plug skills shortages, study finds - The Guardian</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 00:06:00 GMT</t>
+          <t>Wed, 18 Feb 2026 00:01:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxQUHVoc2NrM0xrSmNiNTFIZHNDRzFqZ2xfbVJ0UUZMMzgzTnlhYnNGSENkUE4zS25KS0R0ZGJmaGRPb2MtN2FfdzNLMzFtZWtyYXpDb3pBMjNXS1pzMlpsS2tCclFqeGM2a0k3d2dFaGFLYzFnel9Yd1JFRlU2VkpZaXZvOG9Va1pRaExYWGpoVTAxa0FHMVFfbWYwUk4xUHRWSVVTLW1JN2hUbWZ5eXhFV1Iya0k0U0dhSm9WQmk5UGVRM2JGakJXLWVOLWNDcWJuSlMwQThNSWNTV1dBZ0tmeU00M1NlbWFtQ0t4MEljUTFvS0cxNVYzUmhyQVgwZFZOVnZqcHhkZm8xZGlaSlB5V3NZUEE3NWtW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQLVNkdkhnT2owWk9QTnV2NmI5M0VKb1RMb3BoakZHa0JBY2lRb2RKX09vYl92cXZ2Yy11TEVILTZpcHpHdnBtQU4wVmJUbWRhTU5WalR5UXNxRXk4cGk1NEZ2SFgtZDBjMHVQSGdtNHFUdEJkb2p1elcyVXBFazgtclR5MlhmTlhnQWZfZTJXenh1MDdadk1Pd29VNzQtd2hRMFg2M2VVelpCWFk?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>I got a copy of the Beveridge Report for my 80th birthday. Every government minister should read it - Big Issue</t>
+          <t>King's expert cited in key government report on security policy - King's College London</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 04:03:31 GMT</t>
+          <t>Tue, 17 Feb 2026 09:27:36 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNRTNGMzYxRFl6cVJCZXNhbWlPQ0ptbFhpdXpHSWJFMDVDTXlRcnZ2MlEta1l2c0poMG5od19neGJURDE3enVKVUdqdHdnUmthMjJ5dVUyWXQ1aExHeHlqMUxDb25QYnYxRFBFb0JjU2kzbFRhdXdydV9GamZCd0VieHpBSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNeDA1QUVjdFlvNzRranJaY1dmbk55dS15X1I2VFpxekhtOTlSN2QtdExiM3BqSWtKb0xVcEpxbGN0ZGNBc1RQbjlOZUt6QXBmdGJJMUgwZ0ttMGg3N2VnUHZqRFFEYnVZZkc5UFBDeXRVMGM1YmhpWV8wMEFvWlJDNkZDV0VKLTZNR3M0dHBJRDVKZmM?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Policy report: Mapping the EU's long-term budget - The Parliament Magazine</t>
+          <t>Update on May 2026 local authority elections - GOV.UK blogs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:54:05 GMT</t>
+          <t>Mon, 16 Feb 2026 14:54:23 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMGZ6b1RSQVkwOUVLQUFlYk5xM2wwMXA0ZXpqb3lTNm1hSm9jVUlqZDBSVmk0UVlpNXlxeFVEZ1A0WHlfTGdVU1JVVUlmdUtZRFdoWngtU0pnZmNXelJTRklfemVCbzRrNzRVT0tXMzJwcVJuNmw1YnRSaGVkcWtycmdValByeHNybWhVTEpGWE1qU1dib1o5TldkZ0tsVkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQRWh5VEc5ZDJuVTd0QVc5RVpYbUFISXlmSEtzazBtT1YxX282b256TWw3ZU5VQ2Nmd21zTGhYR0N4S1R1RTZZOUtneWMxVkxVLWczRS0xYU1XOGw5cUVLdjRudEpGOE1kVmtueUxFdk8waEdnVGZFN2hLNmd3elM1OWtHVWZTSzdBOVNhbnBDY08?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HCLG Committee report on social housing conditions: LGA statement - Local Government Association</t>
+          <t>When Destruction Becomes Policy: What the Munich Security Report Reveals About the Future of Global Governance - Toda Peace Institute</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:46:43 GMT</t>
+          <t>Wed, 18 Feb 2026 01:55:39 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNWxxSjhkQkF0WUZ3d3dzNUxCQ25Nam9rWkhzamg2MUhmRy1vWlpNbjhnRDRibE5aVnQxQ1NGQzJWQ0NaQ0JWX0FoMnlNcHNUbjZxZjdGSEsydWI4LU9PSlctVzBmWGVlSHlSVzYtazM1UXZHQWVNX1VWQnhoSjRBQzh1b3M2TDZjS01INFlaUGw3WU1DbDc4UzRLQ1pJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPT21JTXItbmVPbi1keTkwVnk5MnVGeWlwd19zUlBxVWZOWVdsbnFnVllUQW5RZ3lRdjZfMHJNakxyU2VhaC1LMDZlU3RTSXFTZUdMR2xsVVQ2bkxDXzktVENITDBFQmpMb3p0S2x5alFKVkU2NS1oc25ZaE0xNmFJNl8tVjVacEtCRkNmTFpYT19zVEpKd1U5Sk5GRE9yRDFGWlVET3E5VTF6REI4NllNWnk2Rk1YU01qM3hHa2lMMHpXTGZvdkpYNktPa3ZPU3ZDdFVPamMycW53bXRUV0lOdnBqdmVLdw?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ipbes report: Nature loss could spell extinction for businesses - BBC</t>
+          <t>Australian universities on trial: The Albanese government’s “report card” against dissent - World Socialist Web Site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 13:00:55 GMT</t>
+          <t>Wed, 18 Feb 2026 03:09:13 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1DZjdQVC1veG1LU3Biak5NTHVoNTNobEdwOFhRSUNWRm9uY1JHMHFvMXRyNEJ0YlZBanlVUXFaNk1lbGk0aDNQQzJGdkxZOHZZeGxpRnNjWGVScW0z0gFiQVVfeXFMTVRYRk00bkp5Wnk5YmFVTmpON1lQeTFhZkJwYUZhTDltV0tJTWlBS3RrOW81c0hVSEJxYllobXJSVUdwUXYwR09sRWNBU1JyamVjaGtNWG5qN0RkMUg0Q211YkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE4yUnN3R09ka090aHY4MTZYN1V1cFB4VUYxR2pfUVVaRDF2NlNfaWpWQk05Q3dfYUt4bmtnc0F3WHpXSTRxdlV2d2FFaGZCMzhydUhmYW1FNU9GNlpSSmQ4NWk3MXh6TFRj?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Situational Analysis Report for children in conflict with the law in Egypt - ReliefWeb</t>
+          <t>X prohibits gambling Paid Partnerships in policy update - NEXT.io</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 12:03:47 GMT</t>
+          <t>Tue, 17 Feb 2026 17:32:35 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOOG9HemJ4S244MjBJYm81WG9WUlZyU0lMME5qNzBOMHZ3dVBtSHhfRnhLcGF6b1ZVa3ZnSjMxZ0p5Qml2MkV5MFY1TDBQdW5nWFpTdDVBenhvRFNHazl3UE5hU0J4YUJXZHVQelJTZmxBTkk4SmpVNmZPOEhicFE4R0U1LWdOaUpuZ3VfVWdqSzVMUVdW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQVEdKU0dNb183U0E2WjM0U2RzVkJoN0ZDbnFDSTlmTHhnTGxMWlEzNDk1TTFaLUNxbDlRZXQ0VVlsd2pITXAzYWdEWjhRTl9WNjJnSkRkZDUtOTJVd3VZbkhJZUotSEJ6SFc5dVBCRlowZ050WmxqTFFUcFdXR3lNTzZFWG9zVFR1Sm9Oa0RHakljZw?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Briefing: delayed elections and council tax rises - The TaxPayers' Alliance</t>
+          <t>Japan narrowly avoids a technical recession in 2025, report shows - Euronews.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:28:40 GMT</t>
+          <t>Mon, 16 Feb 2026 11:22:22 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQWnl2NTJwYm9oa2hsRHdsSXlYdFNGZ1RVME91dU1rSkk4RVVEQm1DUF81N2ZOcVRYMkNhcE5TdjZ5eVVBMWhGaWVkd3pfOVNhQzQzTG91S2ZRQzJWWTBSbExhbWVkZXRpcHNuVGR4QmdsbFNLcTNiZ2dWNmZIYm5XVlBnaS0xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNSkVFalJIOUNidnBMWE5QcFJNOXlxSGVMWnhPMEhPTUZOenJIbks2dkxuNFplQWRJVGRRNEZWenhfdDBDeE1oY0Vqd2h1R2NpT1VObGZBdkhCV2FXemR5RWZFNTd2d3pPbWgwOU5jWDlOY29sSk1XcXNRbk5abUVXa3BZNkpoa2cwQ2g1SEtINEd2MFNUWnlDcFM5aU9TY1FrMGxqMXI3ZjYyVVNaZlFXa0hhY1hOeEstMmZCcA?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Internal DOE Documents Confirm Climate Report Was Created to Justify Administration Policy - The Equation - Union of Concerned Scientists</t>
+          <t>“We are seeing free parties rise, mid-tier venues disappear… extraordinary resilience, but resilience is not a policy”: New report into UK electronic music brings mixed news - MusicRadar</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:18:01 GMT</t>
+          <t>Mon, 16 Feb 2026 15:25:04 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOTEVzMVN1MXlMSldHTkdWMnBvV0p5MkhuNXd5MU1aZ1R0c3QyenhYWm9CRFp3THdYYU5XXzJnV2I3S25tRWVfZk5jZmlvRXdfSTRsUThZcHRrUmtkVU9BMTVYenhmcE9mdWljaFBRM3hraC1VSTlZMmRZbWoyaTd1ZU1KN0lSM01hQXhlV2VIcFNUQjZ4NGpjaVFwdlhLSzNJVFZaM3V5QUpOSktad2g4UmpORk80bEMtSkkyNWNXYmgxZ0FtRkJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwJBVV95cUxNVTZJR3p1T0kzd25TcEx4ZXV6ZWpUNi1EQzVsSE92N1ZRSExYYzNZRTNrMmluUE9IbUt6bnhIaFFZb2FJQjZ5UTduQXQ2bk04Z1N3bnJrZ1lfOE5FbWxJN2Y4RmxmWWswcFRSMlo1NGlNblJmS3JqSFRqaUxpMWlHVWpCLVpLOUUxWUc1YXVmMTdMa2JFMlllMnlrR0h5cWFDNGlYQnZkTXlKdV80bWJnN3JnNXh4MjBaUDRxZ25WMG93eVlpeUp3MEpNWHlYcUxWU2xtdHFsejVLdU9jMnpHeWZubW1vd3ZxTjBDc3hfYnZvNFRNdl8zenZ6dWtsd1d5b1V5VDhMZHBPVXBxcDdBSElralBWZ1BFS05fRjVkMmhNZGtROXU1d3BMV25Oc2NfMVd3RkZjczFGX3ZUeWxV?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ICYMI - PBOC pledges loose policy, ample liquidity in Q4 report - investingLive</t>
+          <t>Offshore wind could help support space-based solar, UK government report suggests - Recharge News</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 00:27:01 GMT</t>
+          <t>Mon, 16 Feb 2026 13:19:01 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQV1Vvakx4ZHRXUlo2eUZScFhzNjl6emNQZGZoanNaOWZDbXl6Q0cwZzYxbUZGZEF4QUJnNWRUNjVURF9GVW9qSTBsbWs3QURyWWhPaXlWbUlDNGZ5blV1ZVM3SGI1MDF2NXo2dGFIZmoxRExoczBGUWVBUzk3QUJJWVo3cVo0a2Z5enBMM0oxVnRjSzJwU0FqLXNDN1Z5WGtaYzRKNjctYWI3M1Bw0gGyAUFVX3lxTE1nS0w5TVc3R0l4WV9MMDdjdEdzTTVNMjFIeC1DZHp1cWs5REdvdTRVSWxrczhzOWlPQ0VUdm11Q1VKanNINjBPcmJGdWZmZ0xfcUZTTWNqT0k5RnNOWmpaQ2czZFBnTnJZZjAxZ202eUI2Z01vRWZnMGFfRWY3SGJOUnIwU1hxUTlJd0VQUGlmUXg2UW9BM0JkVFJJSG50NXpSemJkdTd5ZjFvSDhZMWU3QWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQb01lc0E5ZEhZemV3aUIwZDN3U01TdzdsQW9YTk1CbzlyMnIxTnVraVlEcWQ2WTZVb1NVYVZWQlNEbGlNSm9NWXlsdFFpTldrRXNxU04yQWJDSWNqenpnYVpJSHRDTS1PRmxEdnY5QVl0RUhqRmpkcFBnNF9MMUkza2UxU0RsWWtVSmhEUE1pRGh5ZWpqVkRqbnZQa3pWNGoyX0ZJZlFReGIxaWhDa3RIeENHMmR5WjM4RGFJSGxsRENQZXhKRUE?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global Humanitarian Policy Forum 2025 - Protecting Principles, Norms and Values: Summary Report - ReliefWeb</t>
+          <t>Neag School Researchers Seek to Use Innovative Methods and Analysis to Reimagine Special Education Policy - UConn Today</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 23:25:19 GMT</t>
+          <t>Tue, 17 Feb 2026 12:42:43 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPNmpYUGpRU2x6eUZtWkpOMGc4QlNEZEVTdVE3NWVuSjF2V0pQMHRlcURkVUtUbDg4Q1RXMGtwWmdYaFVkaWtqclFWUF92QnJHNzBGQ1MyR1pMTXNoYmZ6VjdhNUpERy1ZZXpaN1hNb2ZacGVPLW1TOGNFSjZybkJoUHI3UDByTmJCTGpwZWUwQngxMk40ekJhNkc2REY2YzhWTi1TUXBuNHNxVXhaY0NkUGdjR3N3S0E2djhwbHI0dFAwNi1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOX0JPRW1qT25FZERFUUhXYndGNDNzbVk3VXNXOFBDZDJnV2hWZkxTWk1tRGJVYTZfbl9IZ0N1blJuOERNb29BdzVIR2IzTFctcklUc3Z4alh5SEZGTGEtQjVvRi1mVlkwQjFZZHhRdXhJeVFmNnBRNG9waXE0SXFweENSbXJuZnNQdFFaVG5RMmVfdjZfRzhBQ3lnUWE0UnAxYlNpN3RxSTh1NzVyOGZTeGFLR3B6ZUhxdDE0QXJmVlM4SXpQRWdmZGxEMVVWYUh1bzhsMQ?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[Research Report] AMR Policy Update #5: Cancer Care and AMR (Part 2) - 日本医療政策機構</t>
+          <t>Update: IMF Official: BOJ Expected to Raise Policy Rate to 1.5% by Two 25-Basis Point Hikes This Year, One Next Year - TradingView</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 07:39:24 GMT</t>
+          <t>Tue, 17 Feb 2026 23:31:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE51OXpBMkdhdkRGRG1OeVRzMk5PNmpFMEN6Tks2WDdqVXlFRlB4aGlQOHlrLWlQZGpVX3RCLU5ER2JzS3FVcld5V2xBLTRpeE0ycmdUVnpudUI2di1xTWhBR3pJQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNODl0SzNmOXRqNWVUci1Jek11TVo4dVBuaXJ5QVVnbHlON00wTm9xeGUyUEpHS2NzaFFPUk9FdnY5R01pYzdTcktSNExhc0ljdFJqemFUQjdOUktmcE1KRXZRcHdxdTM5ZS1XT0pLWVFuRGUxM2s1azdvZmVhRzR4MFBHUnZ2LVNZb0c3NnRCUTU5M1VXLWp2YUZzSkF5NUtTb2ZXMEpaTnlLTlR3ZXJmN2VYdTZRZmQ0SjloaV9Bc1BCUXdJclhPakItN0s5Q3g2LU8zMDgtR0N4Qi1paFl5b243cl9vRjFZOXlPMkhsZFhLQjZrc1ZWWV9qX3NYTDBt?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OpenAI policy head exits after discrimination allegation: Report - Storyboard18</t>
+          <t>Combined policy options needed to remedy plastic waste in U.S., Pew report finds - Waste Dive</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 03:22:38 GMT</t>
+          <t>Tue, 17 Feb 2026 17:42:59 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPN2ZxVTVMR25DTWhUYy1xQTdhNkFJUFRMYWxaeElsWXhFMHd5X0VqekhrS3IyQWdYQ3RkS1NZX3FhdFM0ZkdsdlJlT2RjejBKdUdPamh3M3lhX2lxMFJvTDVQcDFjRU5vZEl4NUFpTFVJLS04WnF0dVFMdEZUdmpXVExENlJUZm9tS2w4NWZCN2VzSjJ2NXR1cUFRa0hhcWVpUnRkendxb05BZkZkQUhR0gG0AUFVX3lxTE43S19McW4xTWF4OXMwZG5LVUZtS0d4UGtDQ0ZOSHR6SjRFWERKSnpZbnVVb1paWUpjNTF3TndkUXVnV2otQUxuMWx1MzlObVZFbllGekdldXJuWXczRGFHUFJ6OW1mTDlCSUNWYnUwOHYtTm5KY2QtdjAyRmVIdE5YdE45VW41aTUzN25Bc0t0WE5Od1k3amRWS2xSaC1id1dUejRXM3lQdXpNNDY4eWtKbWdoWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQaloxWXhRS2JKWmlkM1RvOEpmeWdDRUhRaGNMbmZ2WlVjR21uQXVFN0MtWlBQbHIwRWVlbjhsQnczSXJDYUduMy1sdVZLUm1jVFctbTBFeHFxOFg5ZWlGeVJXa3htbnJ3TDdlcFQyQUhsX19fb2RPeWprRUFQR1d5Y0h1YTctT1RZV2ZsT2lYRTVka3MyU3VMcA?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Euna Solutions Releases “State of AI in the Public Sector” Report, Revealing Where Government Agencies Are Finding Real, Measurable Value from AI - Business Wire</t>
+          <t>OCI Policy Analysis – Tool Overview - Oracle Blogs</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:54:00 GMT</t>
+          <t>Thu, 12 Feb 2026 18:01:44 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxNZFU4aHNKcDBXZDI2aTRQSGswZG1mdFRKM25xVDdqV1lyb2wtdXBVSkZuT2lWRjltY3VBT0ZaRE8xY0lKem5zRlh6Z1g5cF9VbFRORndCSVlRQXhXZUVKRFB1V2ttcF9DbG9NR29YSC1LTVFKTkg0eS11bkRfcTJSc253ZlM2Vjg4X3dhOVFRV3lTQmZERTYxUUdDeE15bXBrV3BQZHdaMnpmeVZjWXQtR1Z2aVF6T2V4OGpUN2JQWjd5aE5mcENwU3U4QjIwcE1aT2NrSE12WUlOX0wwUWl5Z2Y4ZWhvQWJjaFNXYm41M0huR1MxeVl5TVpBckVxRTVDMTZGd1F3RDhnM240a3FKbHFsS2N5X1BCNW5LTVBheXM2RHVH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOdXNpN1o3TmZtQ2hOMVZncUNsYTlEV3ZRaWQwbXN0M0llOFBvZ2VZSFZZZlVUUzU2Umd6V0gtMW5wYjhBVEFSNHRXeldvRnl5a0dsZVQ1VmtnT09XUXMtQ3ZUal8zQ0JCWkJvTGJyRnZvMnFMYUdrc2F6TU55UXItdWtuQXBjZXp2cEE0U19B?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -871,27 +871,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Sudan: Conflict in Jonglei State - Flash Update No.6 (as of 10 February 2026) - ReliefWeb</t>
+          <t>REWE and Cimcorp team to automate fresh supply chain for Berlin supermarkets and stores - Retail Technology Innovation Hub</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:50:57 GMT</t>
+          <t>Wed, 18 Feb 2026 06:16:33 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPLWFMYzUzOEt3a19BVzRLQThYZFZYM3FNVDZKelBweUhlbTFCcnl2aXkzcTltc3p5TjM1Ym5lWFFsbXJTbjc5Wl9rVThORm1NeGt6MmRCUXpzY3lhRkxEWDZEd0Vpa2FYYmFvYTBqWUxzbHFIa25ZZGxGeGMzOEtLUEFuN3ZxSUQxMzc4bHdqSXVBZDVuRFlHejRvS01oTDVwX3MtRFJFbktnbTROQkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRTB4Mll6VnpOUWg0STNVbXlsVTVEMUxkbXFTZmRJcXE2aDc5SU92MWFjWnpnVWMyLTRGbXBYQ3BPLXg0QWlCLUxtWlJabzlxSHlxdURLNGlzdGJkeEEzVGcteXRnUE9ud1BURGRfNkdIU1NqU3FMbkxGZmFBaDFwTWlobURRSHJRUFBOakpGN3dLN1l6bVJRM2JETGhYZ1Bvc0FRdFFJOWM4UXRJaUpyN1c4Qy1sbGZZYmpuaXozOHd5U3NObmZ2b1JyM29IWmh4dWRNaw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sanctions-busting shadow ships are increasing - the big question is what to do about them - BBC</t>
+          <t>Port Marlborough and StraitNZ Bluebridge sign long-term partnership agreement - Shippax</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 00:17:37 GMT</t>
+          <t>Wed, 18 Feb 2026 06:18:54 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE8tYnJWQ2piRzNBWlg0WUZQZ2NCWnM5VTMzNXJaSFowbUEycXZySGhmMElwSC11SThYU2FLdUxtaFRteFlsM01YTVZMOUtUVVgxX0s0Skkxd056Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMG1URHRTMGlEcE56NXFBVjVSN1UxX0p0ZnY0eTMxeWs1Nk1mdTU1TjQySXJrY1E1MjJueUo5WERfaXdhLVVTQnVQWVY2X1lQTTJpVTdBMWtxcGJQbFo4dHJSbWd3VVExOXZfU0NKMzlJUC1WcHZXZWgzNHU3THIyX0FRYzNVbWdnRmhvUVliRi1VT3pxZkMtYmJjR3gwM3BtVDJsaV9ic0V6aTFYSDR2RkZkaU0?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US plans Big Tech carve-out from next wave of chip tariffs - Financial Times</t>
+          <t>Practical insights from the SFO’s refreshed compliance guidance - FT Adviser</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 23:27:26 GMT</t>
+          <t>Wed, 18 Feb 2026 03:06:29 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE02QlNTMVdWQjVZR09sQ2NhdS13SWtXSmRETzhRdkV1Z3pLZFAzSmRqaTNZTWEwb0pMbUEyNkVfdFlDNVNkZXhfUTlyRkliWUsyZzZtTkcwNE5GUGZvbkQ3azNDRnE3UlZYSzUyLW91RWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE4zS1VMMXExdk14RVNlbi1sTDA1OWx6UFBmSVQ3QVMtVHZJdk5pNGhMVDNaYldPWjVWcWJlMTZYOFQycnc4Yy03NkVzczlyS2JRal9TRmZmMGZ4aGVNOWVRUGt1TWw0TTU2RXBrMlBGSDI0QS1xdVIzdE1R?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tariffs and falling demand leave Scotch distillers under pressure - Business Matters</t>
+          <t>Unity from End to End - Logistics Business</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:13:24 GMT</t>
+          <t>Wed, 18 Feb 2026 01:23:49 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOVkYxY0JNREhERW5tdEo4U1FVS1ktUFJHMGZvRFlBLVU2cXpmLUxka0dncjM3MEpoMWdHZ3UyM0I4SE56R0N0TWZBb2xqWUE0NFdXWHFja21CTFdobUR2ZWJyOXU0bEhaWEhYcWQtR2tyeEVKWGZkX29UUW9UTUQ5NnFZaG1MdVpYY3BScDRMamV5dmsxZzNZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE4zeHo1YTlvbkhXdWtxMWJlbWlyRmVRR0wzQS1Oa2tSRGw4RWJKY0ZvYWxfRDU5WmpjaDV6NExaUDAwdkFKQzFZNC1SR1hIeXpsSmFHbW9mcldfVjVhVkJzbzhFSExiTWg1TGtYZVdfNnc1VDdNaTI3UUZB?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>An Invitation Into the world of elevated luxury logistics - Air Cargo Week</t>
+          <t>New £11M fund opens to support jobs, growth and investment in Port Talbot - GOV.UK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:30:23 GMT</t>
+          <t>Tue, 17 Feb 2026 10:12:50 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQWEtnY1F2bFNudGFMZ1I5WHJ6M195MXI5U1dSekxlcDREa2tDaDFiWkhaMEpfOGM0ZV9aNGVyd2NKajlYZC1heU5nRUF4TzdMZG1tOWlrcG5HS0ZiOGJTRkxYc2ZQWW9oeG1odVF4MlRlQTFlMklmbl9RaUJMNEFTakpSam9wRk9aeE9B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMEV3ZzBnTVhqRmxPbVI4WXcwZnZxblRmQlBUQnR2dF8zanJGSXBZVzRsZWRGZG9kTjd5d1V4eTYzVFBBbzNraE12ZHkta0VaeWMzTjdPcW5odDFkOGp3eFg3UEJvU2F6TkxsaFZkVVQ0WVJHTHZ2djBZNW1iZDhzYUNvbzd5M0J0dGxETWdDV3hHOXgzY1o3eWQydUlwNjFfSUZJbzNOTmlCZw?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US sanctions officials from Marshall Islands and Palau, citing China fears - Al Jazeera</t>
+          <t>When Artificial Intelligence Discriminates: Employer Compliance in the Rise of AI Hiring (US) - Employment Law Worldview</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 02:44:59 GMT</t>
+          <t>Tue, 17 Feb 2026 22:09:26 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZ09FUDJUdmZSc3dPc21lenByX3lSaTZicGZFMkdmMXRWSzE1WV9lQ05NMUotZVRKVUpKLWtpSEhsV21DaURxVEJxT2RVcnhNUlRCM3VGc0tyeUs5WENOSVR0NjNrc2dobmFiRVRZSDZkVFM3V2h0U3ZkdjBKbUZnUzlGMnBVaVJ2TGlPMEhQUlVqYjAtamZ3RUROa0U0bk40dS0xWkxaRVhJSnFQLWFkckRlZ1XSAboBQVVfeXFMTWdJNlFOa1RuejF5bWY0aXVFWElHZnVUYjdNaEYtY2NvWW1hY1ZwYnJ0LTRFcHUzU0JGRmt0bzJEaVZPWlZ1M3EwTXB0QUpHR0l4OEhXLVJhbDNqRjlCQ29hNVA2ZDRRVThhNFZBYW5hbjl1TFhwckVtVGRlTHhWSmJDYWhPRFotWERJSElfcTZURGxLZEpESWNhMEEtN1NRNWRoWUNvdnV0c05tRml5LUxTSWI3U0lmTjJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPT2tqTTl0cDZ0REJQRmZVT1VzXzdkLWhlWnRZaEVvM28xeUwwd3V0NUNiUlNKTHZzbWNQMGY1M1JoUm8xXzh0OVNueHRwZS03Z2ZkMk5lbjQ5dG9PSTRaWG9tODR6aGFRNkdKUksxV2VRamdwamxLVk9jeHktS0NfWDU2aTBCcnV4UExrMDZwRXlCOEtpalFSLXZwYmtZLTV0X0RTRS04SjJYbkpFb3Y3YXpLODRaT2d0QXc1YS1USF9VcTgzRXRhamR3?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EU Considers Sanctions on Georgia’s Kulevi Port Over Russian Oil Links - Organized Crime and Corruption Reporting Project | OCCRP</t>
+          <t>HSL Compliance acquires Enitial to add environmental monitoring to its client offering - Water Magazine</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 23:28:27 GMT</t>
+          <t>Wed, 18 Feb 2026 05:05:39 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOVBUS2Q1MGNTdnZHN3FCcDFqNUpBNU1aeWVJNi1JN1lzdFFNMURJSW5LNWRDSHdpV1BEeGRHUXMzOWdmbzJjMEF2WkhwVEpOcVJqeVNkLXVLbnpBdVNxTVpySVR4Mm5xTUsxSW1fc2lsSGdjZnJlNlBwbG1lTzBtcFpQNEk1bURYT3NSQWsxU1dEby1ELUpsNWg0Z2NJbzNk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQeUV6aGZCX1p6SUZ0eWVoVkYtSkE3VE1HUE51bmZLYWVtb1lyYnhUT003b2JiWVhHNS1lbElmdU1QVFhhdEx6T2hnTDExS2FwSmZ5UTEtMVFRV0FzY1NJOXdnVU9fZEZnLTZfWGcyRF80ZnNadmJlM0lRMVVOSFNnanlwbGYtdUQ3Wlpld1J1NXBZa0lTOW5TdDBWWG5jZk5nUEpxSjlINENITTRpY05QQmNrY3JrVEh4emRtVlBIdW50Ukczem1OVzNB?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yorkshire logistics firm invests in new facility with HSBC UK backing - Insider Media Ltd</t>
+          <t>This is the hidden supply chain powering Russia’s war with European tech - Follow the Money - Platform for investigative journalism</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:03:04 GMT</t>
+          <t>Wed, 18 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQdTlBYkh2Nk04aGRoRXlFel9hNDV6VU5iR05wQW43bWZTem1tRnhKMXhZQ2Z4emt0MWpLZlNxcTRSMDR3QWFWeXQ2bmx4R1VtN1lXc0NYTElncm9NV3JrbkJXbmRveGJMZklWcVZDcEZ2bm1TVXhDbE9qZWtoRHRZQm0zOVQ2V2EzSHJMVm9BRzJldmwzeFQzZEpjRkpEOEhMLWQxZFpHdzlEVTVVSFYzRlVUaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNSzhyM0doOWxRVFA0Ym1WTTBNQm9nUUlNaTBGSkhWY284a3Nkc2J4TkhHblRYQ291MVhFS3E1U3dwUmdybjRHN09yaFo3clZpLVhWZkEyTnhTbUYzbTdWb1NLeXRwVFZNc1h0YWZRREstNW5zR3N6aFpXS2R0Q3pSWW5xX0VKNm8?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What Does the Descartes Shipping Report Reveal About Trade? - Supply Chain Digital Magazine</t>
+          <t>‘Economic fighters’: the volunteers helping direct sanctions against Russia - The Guardian</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:31:51 GMT</t>
+          <t>Tue, 17 Feb 2026 05:11:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE02NF9uM3ZIMGNyb0ZXNnFJbVlSY2RVd0lPaGJTVktsd3ZHYVZEODhUd0FpbENVWTVSYTUwRkptcWJkbmZyT1FEU0VTY1dFampOZG9ENWQ5bmdCY2tid1hrMDBHeFhfdlZ3d2VmUmlBaWlzZEJNOWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPX0ZkYmsyOElfU2tuVzcxMTFieWhWMG1lVXl3SmtGbzVUSElWbzE0c29qMEJpdnFnc1Vfb2kxYmRhU1I4aUVPWUJ1bzRyWDF0LVhaUE5PZE5tcnFBOS1yUGhLb2dObFNzLTdfN01VYk5DM2h1VmFZN0NINHBxQl9VQUVkeEI2RndQc1hxdUZadUlCV19GNWtnbFhndGE?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Broadband social tariffs – how you can save £220 a year - thecanary.co</t>
+          <t>Portsmouth Port fears £24m plug-in power system may not be used - BBC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 18:10:00 GMT</t>
+          <t>Tue, 17 Feb 2026 06:16:46 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeGNoX0hSSUhKUU85SVJNX3d5UG80MEgxaGt4TEczUk80bUVuWFNBeWd5Y2haY1BpckVfc2ljMC1WNzQzLS1yekE1VWFYZm45REY2cWFaaU5mLXozZnM3MWZ4d0tXclE3Zi1ISmNyYW8zLUZvVG9SOTdvYnpvREs2M3Fkc05TQUg4TjQwMDRWMmV1WXpzMGZGei1oRUhoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5hSHJyWUp1bDNWdE9ER0owN2NCclBoS1dyZjhxZENTMGJtaFhaM3pDX2hVbE00LVF3bWdfWE05ZmRIQnhDSXVmRG9ET016bEFncFZOWW5RdW1yTWI4?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US giant buys €65m Milan logistics hub - Green Street News</t>
+          <t>French supreme court shields Libyan assets frozen by sanctions - Global Arbitration Review</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:47:47 GMT</t>
+          <t>Tue, 17 Feb 2026 19:24:07 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNenB2UXFwQWVCVGgyTzFBV25DNW9NZm5jcU9jc0VOVHJTNjQtUXp6VkdDQVpfbFhhVU92SDBBM1dRdUdBSUhaanVYOS1zNmdJa1E4Qmowa1hqVVoyNWZ4UkRnM0pjWG44NFgyTFB5SU5pTUtJbkdKYm5BdGtRQUVrUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPeE9lLVpLTURBZzhiajExOHkzMjlIQkxmVnBlcV9lZy1aRTh5QV9FcXhEUWVvR05SODRCRFN3MUlQSlhJM0FacTM0czBiOXdyQ1BNOG90aFhDenBtTEVVU1hkdEdXY0lWdmlNZ1piakpGaWxYdF9qTC1RV1FVRGJIN1JWOHl0WEpJX1Y0RDdKX1Q0UTQ2cER0QlZlLUNWNnZXTXoxcHhn?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Why Haven’t Tariffs Trashed the Global Economy? Explaining the ‘Global Resilience Puzzle’ - NIESR</t>
+          <t>Organisations submit request for UK sanctions against Bahrain Interior Minister - DPG Law</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 09:05:49 GMT</t>
+          <t>Tue, 17 Feb 2026 11:09:57 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE0tXzRKOXNVekVwYVRBOFZpamJleGRjUGNlMUJ5NU5XR1ltODdwVVl6eEFXc3hmdXpHWTJORGN4SnpHZUFlRnp3ODdkSEdfUUxUbDJRekpXTURSdm9jLThYbUJHSkhNVXRQT3RFeXNQZURTWFJh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQbHdVc1dmeUF2V2VFZEJrVEJXMVhyU1dyelZWZlFsZE5YLUtVT1ZrZHdtb1Zid3RjVW1DbzZFaHRKN1p6alFIRXp2Y3JaN2w4azBaRjNFdnF4Z3gzUDdVckhKVjE2TXpaTnV3bnIwWGtyYnlpQUtYTHdpbGU4V2hXVkNYWm5XeEZOcHdfangzV2pZSUFmUXh6VS1QcXNYeWlHVEF3Wg?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe’s Russian LNG ban has a shipping loophole - The Parliament Magazine</t>
+          <t>'Dismal' China exports add to freight trade slump for nation's biggest port - CNBC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:34:32 GMT</t>
+          <t>Tue, 17 Feb 2026 21:41:09 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNaEs4VWZCQ2hRNklpZzZ6NFFackxWcVVQc2pCQ2RoMThSVUE4OGpQTDNXUnJ5RTUzMlpSU0JiMWVBd1lHZkJreWxfSUkwTlNpN05Xay1CYmpSam93WGxRM29iYmxSZVN1WTZULXhBZDF2MnpvUHBEUUUxdEhFQUxrOTBRWGROcnhaZzNSZ3dESWJtX01pY1k3T3FBZUZsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNWm5IT1ZfblNFZS15ZHN4MWVRZ1kwN0R2c3lBa2w4dDFXMTJ4Wm43MjNkY1A2S282MG9zOGx6U1NCRVRuQ3RuMXpVbVlTV1liOUVpUW9yVExYX2dUMG53RFhhMjdqZDFoZlRxcTdDR2h2Wk1peTFlVlY3LXl1VmpwQTZLSmRWeE5QblNwSmx5SlFfU2Zu0gGaAUFVX3lxTE1Nb2lONjdpenhFdVZMSE1EbXJTeG9zdEgxN2Rid2ViOWpSU3BBczJIRnlvVjhDVUdpay1FZ08xQnJfLS1pTE9MMDFydktReUw0VXJiXzB3UGtuMWhyMmxtbmtCNmZPMXBTdGlBTy1hcGhHNHJDTjlOZGdfc25VWEszZDFscGhiNGgtZVZSX0pKRmNfSThRQWpXdGc?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dining across the divide: ‘Tariffs are the one thing I agree with Donald Trump on’ - The Guardian</t>
+          <t>Report: Stevenage 2-1 Port Vale - Stevenage FC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
+          <t>Tue, 17 Feb 2026 19:07:13 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVno1bmFoU0l3ZEhfWG5yckFyUE5PVVMzMnpGcHZDTVl4cEExS0ZNQnhDX2ZXTjFpX3V3bWpwcHQwQlVBWUpWSFBKZEpRM1VxRHlxdWRDUUNPOWp4NThyV0I4Y2dIanlsNHRuVXBlQjdtSF8tRGdNRVMyWXFUcXdaNHNaNkJaNEJUS0xfUTZWVjUzM3FSamg0MklpeXZobVdkRnZOVWVKbEZra0ZydHFmUWpHVWxOTVNzaE1HZldJQVFVYmRRRHdWM3lGaS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPLWZaNlJaSWlncnZ1UkZ0NUtxTmtfYndDb19Fb2o5NThmYnNMdmxLQklDd254SURoekh5Uml3NjVJYUNzNFlRdWVORHhjZVBJbF9Bb0F3MHA2bl9Vb2htak9IZmkyMFA5LXpjTGUxeEdOMTEtMklIRzFwZjVTbVFOMEFQdk1XbjVQZkE?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bangladesh secures lower US tariffs and exemptions for clothing goods - BBC</t>
+          <t>EU 'won't shy away' from new sanctions on Russia if G7 allies fail to reach deal - Euronews.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 03:26:05 GMT</t>
+          <t>Tue, 17 Feb 2026 13:41:58 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE00RDA1ZHRVYXYtTkpxTXZoSTB0ZDRtSTB2VzdNdnVyMGR2NFBKV3JuYXhOang0ZlUzNS05c181WXpmQlNaeEpMUFpSMVdjWEZLNnlOeEtFSlpqdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOQWg1NXQ4dkdJNHRhU0J1S0czdjhpR0NIamVudFZPSFZpZmNxUVpRMmt5dGdTUFoxaWE2R2Q2djVwYlpwZXVNbTNjQ2ZPODliSTB4V2oyNXpaeXUxZjluZEE0bFU1dXRlUnFJdGtxZ19yX0tjWExxZnRqZW5uZjYzZF9SQ19iNUpQTnRhREtBWTNEeW94U2xMQkJLdUpLVkYtWlNORDU4a3d6ZHZLdE9HamtiUUpSanl6emRybXdpNXM?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EU seeks to ban all Russian crypto transactions - Financial Times</t>
+          <t>CLdN set to acquire Samskip’s UK and Ireland freight business - Shipping Telegraph</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:02:22 GMT</t>
+          <t>Wed, 18 Feb 2026 01:55:32 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE4tOFVKeFFXc0tFSUszczJrTzlwU2p6bmJUc0d6dDh5M3dvLWxFSXNKNDUxcjdWN290TWZsdHRqSDVZLWVvUzJVOTAzWmh6c0Z6cmMwSzZGZkRMTnFlOTFXRnRVT1VDd2hPRlo4NkpkREk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNOUUxVlZMWWpmNG9iQ3pKRUVCLVlPaEtmMzY3aVl6YzM5MnFPS1NFM1QtdzN4b1N0WGdOUXNsSmNPekNRbUMyeERyTVYtNGRZYXhVZmZBRTktRmxRZVVNTXUwMjdQZEdFTG9kSVRkWFdDeVAyNU1Oczgwa0lkc2JTYkROMl9XLXZscXJzQTYwdWxOZ3JacUY1bXAwTG9SdGl2TVlrVld1eXZnUzBo?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US imposes new Hezbollah sanctions targeting gold exchange firm - Al Jazeera</t>
+          <t>Egyptian speedy delivery and supply chain tech firm Breadfast bags $50m in pre-Series C funding - Retail Technology Innovation Hub</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 01:14:02 GMT</t>
+          <t>Wed, 18 Feb 2026 06:16:33 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQZWZDeVNLNFlvSkF2bmw3RWF6Rjg0WXNRM3NGcHlkOTNLR3dTLVNJVUo0eld1ODQxT1ljWFRxTnFYLVlpcWVpR3dZTUhocHpOaDBDeEFmZGNvRXRWSDNrUDRodXlJVVJHcFl1ZFNma01RUDROWXhyNGRQekotNGxac2xINl9YMHlOdmVwXzY0dWZCeDFrYTR5T2p3MlVlNHZvNEt3Wk1KVdIBrAFBVV95cUxQenRYVmlrVjhmLVpBSFdPYUlZZDNqd1U2Y2ZhbnBXcmtKSXNPcm03ak5RM1ctc3ZTUENucnRjUFJhYjROdHVzWHpja3g3bU9IMUdaOVFQM0RFVmZkM19tNFZ3S3lXbGR5czdiMy1qTzNfc0xpemVpOUs3Nk0xQUtISm9TMk1haTRLcWVuZVhzVUwtdHYwdnZodHNNbVBqVnpNaEhxRDcwWGpKVWpT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQbDRfeWw0SFFpN0xRUWRsTVRRTTY3ZzRaSGozdEN4NHpIWHFfeUtFbjYzVk9kQjczNTN0QVU0bmhwRnFiSk1mSV9CLTd0OG1KTTY0c2gzZ3FxcWR5a3JPcHFydnIyS0VWcjdjLWxCT3NBcmVPdU1uNEg2cDd4RmVWcDJ4b1dDRTAxREt2MFVHQnJUWDNhRmFJMHhCTEV1eUNkQjJpQzhaSmlLZGg0M0dYYUFmR2dRTUhBdGdUbUdfd3pXd0x3ZUlTcVVrUUpKYTlwNlJlX08tNVEtZmppRVE?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oil, tariffs and farming: What we still don't know about US-India trade deal - BBC</t>
+          <t>Trump tariffs: Irish exports to US soared in 2025 - BBC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 09:10:46 GMT</t>
+          <t>Tue, 17 Feb 2026 14:55:28 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE40MzNfeTZiTi1pV1FnajBXc2RwZ0RtNlNKWWlXUDBtOVhCa3dFNi1PRUVPc0dIVktDZ0FvbDBGYVdBVUJDLUItWFFuMG8zeDhFU0lYaXNnRU9sdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9xa0syQXpfazI4VDEtNU1mOHNRVm5ENk5DUEktcUppeGFTSEdpVnN2V1U4c0lWVHZYM2pQT250cFV1RkpDUDY4WjJpVnlMQWwxNlZDOWxoUWs4QQ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shipping giant MSC facilitates trade from Israeli settlements through EU - Al Jazeera</t>
+          <t>Mondra and inoqo merge with focus on global food system supply chain resilience and sustainability - Retail Technology Innovation Hub</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 10:02:46 GMT</t>
+          <t>Wed, 18 Feb 2026 06:31:55 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOdXd5S1R0TS1hWW43U2ExSnpGcU9wWWxsMFFTbHlPT29oSWRzLWlyQjE2MDZ2ZjlLbXpqaXFfN2dESzRkWGNfVFZSaWlnMzhQbjRRZkJvdkRlQldnc3o1S3hfRHo0WHQybVcwaDFMdHVxT0dzeEo0VGtTMlFFak5JOVdqT0xSbTU3WjRObTlHODdJd19yN0FlYWx4WjRmZ1VUVF9ZaVNPSGw4TDZVVUpBM3VR0gG3AUFVX3lxTE8xaUpIZlg1T2hfU1BDOG9UakJWaGR1VVpNcVltbGxGUkVhTjE4OVFqNzVqbDVmdU10ZzN6Y0QxaUZhLXhka21CUmRYSkpoQmpLM1ZGRDl6UlBCMDBtekthb1NjaFIxTjF0cnpOcmFYWjlvWVFicUFQZzVaMGZaUzVERERISGRHUFVRblg0TTgzbElqWWN0WjdOM2llQ3Zyd2NhM2xPRk4yV0sydFVYT1g1eUx2WURTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQdmVpWTVqSnhQUUprY09SeE1vcFhYN1FrQzdiM1c1Rng1Q0JYa1VMdDRtQ2NlcmpwOFgyZTBFYXJnTU1FR1dIeWhiSUViYmZwNVNxN29jSzZDbnRSRWV6RGZ3eEZoYzBERUpPU3A3ZWxIcWdJWEFkUHFDaFl5REpkWmQzODc3dUhQMlFUcmR2TnBtMkNtbWdRYWhlcVpGQkVjWFZqcFlGbWF3NHZpbE9GYmRhVjVwV1ZDWnpubW5CZlY2cV9jN3kxVDU0NUhHU2kydWpXS0NpMlJwdWcxOGNGb1ZzMA?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Full Fibre ISP Hyperoptic Add Faster and Cheaper UK Broadband Social Tariffs - ISPreview UK</t>
+          <t>Sunderland to face Port Vale or Bristol City in FA Cup fifth round - Sunderland AFC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:38:00 GMT</t>
+          <t>Mon, 16 Feb 2026 21:04:22 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNcnE4RTdYOFZCWl9sX29sdmI0WXp3ZHhqSHNKQU1JWUJ3bjA3TVlTZGJHb2hvMzIwYlNMU1VlX3pCSHhBVzBDa1VxS1dldkU2RVJOQXNhZlE4cEREUEwxNkNTZXpDVFB2dWJvb3hfSXlUblBlUXNsYk5jbEl1RUhYc0lCQzZwdVN1UEx4UkdyMUszMXpYZnZyc1FQaUMzZmNuTVVaQm5HMHFBWWNmTWxpQVJSUGdhVkxfYjNleEhFNUFRQk9UQXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdm54eGl1XzlLSGsyM1Z3d0JZcWV1WXFSRDFPbUROMDdEdkxWYXNzOU5BaWxXRkJ2YzEtMkdVRnUzZWJrbnlCRmR0aFN5ZjQyT3U5S2FOdWhibnJ2V2hSSHpBMmtqVVB6dFFJdXIyT01YdExJTE1iZUs1Zm1BTlNzY25Mc1dyT2g0Z085VjZYZW50SEtzMXRycWpiWUxQYl9aQUplUXFOcjRHSXVPZ2cw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EU financial VAT exemption questioned in European Parliament report - Global VAT Compliance</t>
+          <t>The 2026 supply chain challenge: Global trade disruption - Thomson Reuters tax</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:04:58 GMT</t>
+          <t>Thu, 12 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPNGVzbmZMcGlmMUF0dzFyd2RFWXBrNzVsMnM3Y3pibFRFdldRQUpacnh3Ylc1X0NXTUJlWXI3V0NyY3cxRFF2U29mQ2xqekxkc2ZtdmR5YjRaM21NMDhVaGNmamV1RWpUV2NtWUhzWWdxZUZ1UFhVVkpUZnVsaVE5RlR2VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNkdMUXkyMXRHX0pOcnZSdG53S0FFaDM3SkRLU1Z1djlJYVBKYVpnUGZjaGhuN3MzM1JjM3hPN3Y1ZlJPNlRFaEZ6MVRmUUNGWnpNOFNONnRtekJpblhTSmdfVFpLd2VwWTUwOWtabG55SGlFckxXeTRRYnZST1I2T0MwN1htYTVoOEVGVHNjakRETHVOVXdXMUFjQmg5QTRLY3plYWhPQ0liLWFDTEU4dGtBR3NxZFBuUkI3a0VEZWg?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Businesses with Payroll Urged to Prepare for April 6 ‘R-Day’ Compliance Changes - Business News Wales</t>
+          <t>Corby Logistics Hub Showcases Innovation During VIP Visit - Logistics Business</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:47:52 GMT</t>
+          <t>Tue, 17 Feb 2026 15:03:35 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQOVFaaGJzMXFiX1F5RGthNlBvZE9XNzJiQnhOYlNfdEdTSnZrdXE5T21rTy1JSXJMdm9wRU9yNDFGcHFKSkZpclRNTkFCS1JscnE4WUIyUE8zS3NRaGtHR2QzbGpURUJ6cy0teGt0dUFRclpmSlcyRU9McVdIWXhQaUx1cllKcS1odDlHWHN4VXMwQzVhcE9ZVlNrUFZ4VktpTU9BRzZUYzBUN0pJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQME91M1VzWktyeXJIazQ2Nzk1MDQwRmxVRzRJYmVNSTFlXzBUd3BrSHlXVmx2S0ZodVQ0a3pXT1pQdUxaNklWWml0bTduWFItaUs1a0tUajBuSnB1Z2p2QnVSNmpWa2Q1VlExOWxwa0VuaW9Va3hNV0FaTE50M1ZYMl8ySXAzMWRtSHE0dUpWTVJNT3hmVE5taXlWR2c0U3NPRXc?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Grant Ward is a Valiant! - Port Vale Football Club</t>
+          <t>New payment compliance reporting requirements from January 2026 - Freeths</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:16:43 GMT</t>
+          <t>Tue, 17 Feb 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1DZE1lMlpmTkRXVl9FZ2VhZnhzaDhCMHEyTFNxRGFfd2N4MUNWN0NlLUU1eHZ2RUtlU0lCdWZkdVdQT3RBeVVkX0JQT0xOQlljeXVDaFdGX0FqaEhCODE1Qw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxON2d1eVlYRlRFd3JITEdqVlNnVzlRUGVHZXhyNmpKc0UtenM1ajd1Uzk5TmFoQ3U0Ulc2MGNsWHFFdnpvZEpqQ3UyS0dnbGo5LXVVTkRYZFJrbmpKY0FCUU9Nb0xjUkgzSFNFNjVUWUs1aWpaY1dETUIxNzc0OTRZLUluRFZnbkp3UTlEWHBLUFMzMmFaV1pDN2JvR3JMNUtHWXpzWW5lODZuQjBWZGl0YVlWVTY1eG9mSEpISDh5V0pUS05v?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Neath Port Talbot parent support scheme to expand across Wales - Wales 247</t>
+          <t>Cumberland Council handed enforcement notice by Information Commissioner's Office - Times &amp; Star</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:43:47 GMT</t>
+          <t>Wed, 18 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOUWhxT3czV29JMldHRWNxVjUyMzBXamgydlJLVUE2Q0l1UXFubExFNk5VZnlZS2ZHYnFOSTFHWDAxTVhELW42RTdpYTRaUC1nR2lQek9JaVhxU1VQa0hDeENvTGFZSHFQX2V0YjlWQmtGbVdzbGRYTHpYODlocXdTajNWWVpQbkZMRVpIb3dUdXpMbkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQNjdPS3REZjhQdVlLazFMZkhTVmNiMHI3dVltdmlIRklGRk81dFFNU3QtMGRkLVdkSk1HaHhHc0J5dTRTZ2Y0ZkxMdklna2FCWG9xN3ptY3FWc2EzMEhvVkxNQ0dORTR0TDhsWHlKZmpYZDJjZUNtTlhmZExUQldRZ3lSNVlwYmthc3VyT1pxai15RVdFUlhqSkJXWTQyVWU4bHNVU29jNjVDR3A4OWc?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Port of Liverpool receives record ADM Shipment - Container News</t>
+          <t>Ferry collision damages port and cancels sailings | ITV News - ITVX</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 05:32:05 GMT</t>
+          <t>Tue, 17 Feb 2026 19:56:31 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBkRHZoMmVfSXNWTXdpZjU1aU5vRFFIN0xpZGF0N2xHUC1fTlFYV3lDX1VsOUl4V2pDeE95RnFNMzFHM21tR1RIUmF6SFJQc3FoWUhGSjFkR0hRXzhfYUJ3N1pVTGV1ekJadmdqcnlOMTlBM1JVVmtla2NIWldhdms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOSGdQWWVOWVVxdkZPUUVfd0Z0Zlh4aGhEcWs0MDhSSnhXTWp0WklMcHRudGFvSGlYMEMyYm90Ylcyam12enJheFpHT3EyS2c5bmFINE56RXZpREYwVGZOeXVScG1IcFVGWm9lbkpVTlJqUXk5M0xkSTZ2eko3QjNVM0FSU3FyZVVtV2NwU3VZWXhyM0VBdERmbWln?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trump Tariffs Face Rebuke as Johnson Fails to Block Votes - Bloomberg.com</t>
+          <t>STG Logistics files for Chapter 11 - Financier Worldwide</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 03:46:00 GMT</t>
+          <t>Tue, 17 Feb 2026 15:57:20 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRHFBZGFWMVJiM19UcHU3eVVRQ01GUjBNajA3eTB4OXVfM3BjT3NYV0dmY3FEUlVubXlLbFd3YXJUWWhGQmF0bDgtTXF6aGRiVEoxTG9oWjR0dm96Nnl2bzRDNXUxdzB5SDFsVjU4WXY4V1dKZ09DMTFZOTltT3M0TTZldjVrNWRKX002UzdfSUxQUUc3dktfTjd3amlVSG9jNXJkR3B6a29DUS1MVVRYT2tLTUM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE8wMmVueklqT2Y0M2xYY09fdzh3WXYwOTRlYU0zU1RvV0llcVlkemRNTGZ6UVNSY1lDZkR2cTRVdUFHSXhyblFXUFRINmlqQkc0T2dHem1JSElwcFIxckVhZUJiV0dmRnEyb2V4V3BOazBpbmVrSVIzUw?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bespoke tariffs backed to boost community energy schemes - Utility Week</t>
+          <t>A New Tech Solution To The Freight Fraud Problem - Forbes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:45:25 GMT</t>
+          <t>Tue, 17 Feb 2026 14:41:39 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNmV1c3FsaTY2SFJsTDFrYURIeHlnT2h5cEhVUW8zVzJIQnNiejRkcVFrNDA1RmdzMDNlcXpMSEVCaUlLM3RBZlhXaDRucmRzSmVxMVRfZlJ6ZmNKTmZZTEJRY1d3Y0xZRXhZX09iYmdJZXp3ZUlaWHBVa2YzVWgtYTNjc3hUQV84bF9N0gGXAUFVX3lxTE9XNjF3S29RMTVGcm14Uk1pakZHUXhuTUtRd09NblZoOHJ1aE5Ia2lGbXphNmdPdW1WRG11RWNSWmkySEdHRGFYNGpObnR1bVdyM0pGQTVIZ015LVFWcWJkeUZEYUNFbXZ2V3dGNmNiY0Iza3lXd3hhbG9UTEc5QmtHMGFzcHRoX3pGeExnSTF5UkdqUDFkMVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPenFSdkxCV0ZlWG9sLWMzN1hULUJ6ek4xTTBoMGxmTWdaNzB6dFV3bm41VWxXaEltZWxpN0pzUFREOVlud3ZOQzdZYlVQNEpRa2xBM1B0UE9Ba0djczI2OFo1OTBsbUpweDRRc2k4d2pKVXljRnh1ZThfd01QRFloVFNaX1JlTjZwWFl2aDFiTzV0YUFlMzJ0cVQ2Z01PbUFzVG9r?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EFL Trophy: Stockport, Northampton and Doncaster reach semi-finals - BBC</t>
+          <t>BBA Launches Irish Building Regulations Compliance - Roofing Today</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 23:09:17 GMT</t>
+          <t>Tue, 17 Feb 2026 17:05:34 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE01LW14c1UyS0Nrbkh1OEtoMmswYW9qNXEwbTV0Uktsd0JOM2tuTzZnTTZ5OXlna2QwMDZaalhEUDZaRjV3RkZHN3BHRktpMDE4VDB0bzdxQ2ZGY2xzUDRKbmdnOXhoakU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPcjVMdGZ4cWloZUozV1FjdFVDa2liUDZMaTdFTlFtdGYzN0ZmTWlKNjdaVEFJLW9SZkxkOHJXM09OYktvcWtZZ01kYi1NV1FXOUg5QVRZam1KaXVwQm1Ddmo0WjFlaHVSQ2hFSG1CUDRyV2J6Z1dXZGpqMF9YVTdySG90TUg?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cargo ship towed to shore after engine room fire - BBC</t>
+          <t>UK Financial Sanctions Compliance and Enforcement Update - JD Supra</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 07:32:05 GMT</t>
+          <t>Tue, 17 Feb 2026 19:31:48 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1JdjZkYVdxc0tLMlhXcUFxUDBFd09BYVFGVkYwRU9VSXJoMVh2NWhpSDJXZnlmb1NHZURtWTdaQXd2XzZsN050VGVVZXgwajB2Uk41ZVVJeDc3RDBy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNMU1OSjBya0w0cXlYakw3ZHFIbGFqNk5KODg2MmhRSUVwYUp4QTFpNGVhRDUyMnEyWGI2VlAtQjgtYzQ2bWFhcTBpX2ZUUmx3QW94Uk1wM1ZIYllyUVB1ZzdXaW5SOThXeEs2OFF6S0MxZDRaM0RwT1pfUDhoRnlnSi13RkF3X0k?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Canadian pension giant halts deals with DP World over chief’s Jeffrey Epstein ties - Financial Times</t>
+          <t>Cybersecurity in cross-border logistics operations - Help Net Security</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 20:48:54 GMT</t>
+          <t>Wed, 18 Feb 2026 05:30:17 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1sb29DZlNPY2dXbHAxUVZLQ0xfaFIxREpuT2F1YTRFTlViWl9ZSkpLNmN6dHNfZS1jbDMzSjFSdXNlM0xHWlVTODREeHB4YmVCV2MyZ3pRN1FqSVdIWFhBek0wWEhEbEcxNnYxcS1reGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOUUllYzcweHVqWmxWQlZVZ3RYcFBkUm1WMWxPcnJuVHRZQXQ1RGFRVGxhNkdTN1RlOFhkQTRlQ2V2aTFQMXU0Ni1wU1o5TXM2WndwbEhBSmNqSjFNaF9Zb0dib3RaMjJNWTc2LURNcDhTaWdsM0JrYjJ4NzZXclYtSFFxazk3QnpRWTFZ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sanctions Force Russia’s Foreign Trade Down to Soviet-Era Lows - UNITED24 Media</t>
+          <t>Bashing Trump’s tariffs is slowly becoming a bipartisan sport - Financial Times</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 20:01:56 GMT</t>
+          <t>Mon, 16 Feb 2026 12:31:04 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNdkptR0liX09lUHNmUUpNQU82MHpnR3lBdWpEV0NNTTFoaFl1akM5amkyMjZ4WjhHaG44Ynp6aWpmOE40eVROSW5CeElFLUhJOHBoUjRZbUUzYTFoMi1Sc1hJYTQtNXAwWlBXbHV5Um92VW9TbXlhNzdETnNPUlNkTnpwNkdtOVFGQXU4RzYxa3hEYXBGdEFVeDFFRERhSnNTajMxNEV0OS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5GNzVjWmt1cHAtSllkM0dVZFVoNHZRRTBTTDZ5MWtuRjlWN0xpbmJ4b2Zydjkwb3hwUzJrTjBESmg3WW9IbmlER3lhaHVHNC1OcUZGVnpIUmd2RTVULUlralUzRjF4ay1sZE9Xd3Iwd3o?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Man who was found to be dealing drugs appears at court for sentencing - East Lothian Courier</t>
+          <t>Oman: Asyad Shipping offloads LNG quartet for $110m - Shipping Telegraph</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:06:06 GMT</t>
+          <t>Wed, 18 Feb 2026 01:55:32 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOcGRObFpXU0dRY25CTE55dnZFU2hGQ3ZDY1ZHZDFIdDlHUmJISldhQXQzeUlaUW5mVUVQc3lDbWpKR19iYzV5Zl9iM0tOcXlVdXdZZnhVbWF2NXJuZUQxcEpyTEU2RktXeDNnNUl5SkdkYnlIZnlOM2sxYzN2NTNTN0tGUHNSMzhya3BsREVEMFBqU091TFFvcEd0UkxDQUJwNkRKQkZHbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQYWVpWU9IYktVejNIaXkzMXNMMjh5bUtrSFM1bExLaWtfTDBOZjR6Ull6NmFrSF81M2NQbTNxYzBxTkpJZkZBVkMzWnFteEpVQzZUZ2d3LTJsU0hULUdobzEtZ0dmN2NVTnVSZ0RITTRMb3NxWm9sUzdMRHFGcm5ZamotckYtYzMtMmhpN3VxczJQcVQ3RmpXdU1Ua3VzUktsVUQ4?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Syria’s Future Between Fragmentation and Rival Reconstruction - Manara Magazine</t>
+          <t>How Toyota is Diversifying the Supply Chain Beyond BEVs - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 00:39:40 GMT</t>
+          <t>Tue, 17 Feb 2026 13:37:22 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB0VF9DMWxhR2tkWFViNi1EV0xJSzhtZ0VZSDBZQjF0YkVJY281UTZuMnZ5ZndzdU95UXpoeGN2ckxLQ1FzSGhXeUNXbGZvYXVSU0xlM1BhR2YzeDhzWUZEa2Vod2NHUnN1V0djeEpRSWR0T240aXZaT2NhTDRwSEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOR1BrczEyc2E3eGxtekdKVXdab3E4OU12QmpjbXM2NUNEcHBwSFZ2aU9ZX0czcWhkRGhMeEd2SmVPbnVNbUthUTlVSlg4R21xSjNCdUgxUmd6LXNhM3ZET0tHYUtjVWJLSk5DUFEtbFpiaG1MOTlRN3dCbTEwYlpHckVGRGtVcGM?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gabriel Makhlouf sticks to ECB line on rates as US tariffs help keep inflation anchored - The Irish Times</t>
+          <t>Sphinx Raises $7.1M to Build Every Financial Institution's Last Compliance Hire - Financial IT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:00:55 GMT</t>
+          <t>Tue, 17 Feb 2026 14:07:39 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQQUVrbmpWYTRHSnZreEJmRGFkcjJBQV9iY0lXMWdnUDZ2WE9Td2F5U0g3elNNbG8xMVA2M01SYTliMlJyWE9RYkJjcGF3eUhxem5uMTJYVS1jV1dWa0I0MEdaWW5pUG9jQm90YVBpZ1JzbFlDb0QzY2o0eTR6RmZLZm02ZjJxa3pHbWtoM3ljS182QUtUZWI5Rl9GY3RaazJkV0I2QkpHQTdabW1lUmxtaU1kREhzOXQwdENHa3JsR19ZM181YVZlRGNCMTdEUzh4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSy1ETTdqVzNuZjVYMXRmVE9GUXRwTzFQTUpEOWxJLTU4ME9PeDNYMjdpc1J0TWw1ZjVtWnBNcWhPQTlBblNWZ3hLRDhZYkp1NFdyTVlmUFZyWVVYYVZNaDV5M2oxOWZVaU4tak4zZjUzcHBRWFdtM1IwMExrMUsyTjYySEJGVzhLeXhnOXByQm40M1pfR3NBelFmMkVPMDkyRFhObUxNRlJGVDAxT2cxdWFTMnVmV01mS0hF?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Disqualified Somerset driver caught drinking port behind wheel of 4x4 - BBC</t>
+          <t>New US Trade Deal with Bangladesh Reduces Apparel Tariffs - News By Wire</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 14:29:35 GMT</t>
+          <t>Tue, 17 Feb 2026 19:37:06 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9EM25TSXZ0TkhsM05Tb1RLTURROU5OMlJ0SFN2MGlYRFMzNkhZS21wa1BFSzYzcFBuYkZ3S21DN2VscXFVTnhyUFBicXk3aEdMME1scmN0ZXZfelV0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQV0U2djR0QTI2REZjOUU0YV9oSTZab1hQSmlEU2tTMWE1WXZ6RF9CSEhmS0ZKSU8tMGUtTEd3REF2M0pTZTNJNjNsUjktSDRHMGZpMzFBYXJ3a3RHaUJIR2ZSUU1RRHZSQXN0Y2k2Q0c2VE8xc255RkdpWEc2enA0VDdNeC1iMENv?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VW’s Cupra Tavascan first EV to dodge EU’s China tariffs - Automotive World</t>
+          <t>US sanctions turn International Criminal Court judge’s daily life into a nightmare - AOL.co.uk</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:30:07 GMT</t>
+          <t>Wed, 18 Feb 2026 06:31:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOOEd1dGJ0Y3ZhT1lHZUQ4SmFQSU15ZVY4QXFpb2RkaG9Ra0pXSlNEdmxqT2VmdXloMlh3MnJRR25aNnJhRjF3SGtWdEpKQjRuRHlRRWoyVWlaMEJRZTN6dG9qaTRCTTZXOUxsMTV4VjR4S3hVdUtvYi1RczRsdEh0RF80WUpwbjJDUGRfNDcyVWkxMVkxQUxZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOLW9zd21UU2tuSU81LWhEQlVIWm9FRFZabkFuOHB4NDZYb0ZvdVNUdGluc2RIMmFacExWMy1aMWN0MmN6OHNkeGhoamkxb2ZlaUtwcTBPNk1xaC1hU2ExZHZfUHRDTTdmSTduQjJwbHc4NlQ2c3dmaUdQREtDNi00Z3Y0c0pTaHBXMVE?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ukraine Hits Russian Drone Nerve Centers and Logistics Networks - UNITED24 Media</t>
+          <t>The Salt Supply Chain that will De-Ice North America's Roads - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:14:01 GMT</t>
+          <t>Tue, 17 Feb 2026 12:19:59 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNSE1FdEVRaXkxd1ozVUxMX21kNi1PM3lMcFA5QWZmU3VmZC1fd2ZaY1ZqcExJa0dveUU3RlE0aVMybW95X0tVRS1Meml4R05sX0xWQk5TT3UwOE5vYjQ2Rk0yUVpNeENkaEdrVUJtekctRDZqUkN4OUEtdjhZdmxMYTJHcjJJalJSazJIYmprMms3aWFJUFJJNUluWW41ZV9TMXlTbk9mcmdvQU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbDRsUnBTQ21EUF82TWFvWHdXQ0VzeDQ5SmZnVXVTcVNZOGJnTlp3T25TLUFOeVh5bVg5VnJTYkU2VmZWblJzMUFlaGVuZVYtaDM2Qm12V2tad2N6ZkJSdW53U2d4dUdRbVVyeUxMMDY4WUxFN2lqSHpwaElSdXk4cjQ0a1ByTHRjV0dLTjAyTDFFQ1hJY05LckNLVQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SeaLead plummets in shipping line rankings - Seatrade Maritime News</t>
+          <t>Cabot Properties acquires first logistics asset in Japan - Logistics Manager</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 05:54:57 GMT</t>
+          <t>Tue, 17 Feb 2026 12:17:24 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxObUh3d3FvVThxUl90ZmV2czZldWE3THJsQTBQT29LWUZyZ2hFdmhCdEpNcmNNTGItc0tFdDg1cHJBUWtjSUdnMW1IVkxuZlpNeHNOSWZCQXRfMHRDYUpqcUYtVFhMbWVUcFZIVjZpa2RQcU9CTGdIT1I5WjFmejkxcTNVZ1FhQlAySTlkdlNKNXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNYld5RkFjczhfc1RtUXRFQ254VXFUczZYbG9NWDk0SU1TeFRqLW1laC1lU0JqZC1iMEdWZzRRS0cwRmZjbVI1Y2VTMWFxZjdRVFJQRTQ4SHppNHE1MHlJOFRRSERSQ0pPU3U4SDRST3h1bVEwXzBwZUdLYUlYbi10UU1DdUh3dEhsWkd2a21Uc1Znd2JI?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>How AI collaboration transforms governance and compliance - Thomson Reuters Legal Solutions</t>
+          <t>Safeguarding integrity: ethics and compliance in global business - Financier Worldwide</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 21:13:48 GMT</t>
+          <t>Tue, 17 Feb 2026 15:57:25 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPSG9mcmdjeEFJNU9heTYyMHdzdHIyYlB3S0hJSndwU1pTcnVkOV9XTTJaVmZXMHZPcVUwOUNoQVlJU0w4SHpkM19NZUdCSjE3WjZZYzl2Uml3SE9UQm53YVlMXzh0ODZMY2ZaZF9EdmRjZEl0ekNudEFZRkt0S0JIMDdfMHJzSElFMXNQLTM2bHdXZUJhclBuaXJLQzZMWE8yZm9kcmxsa0otbVY3dGV1T1ZGNDFRUWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOQk1aTTRwY0NfOTI3M0JneUF3WGlINzFMaW9RZzRSOHNIWlBuaXNQZWk0VkZ6U01TanNRWHYwdXJpRTJ3Tm9vV3RES1RzNURfemc1S0EwdGRvVnRJLXA5T0dHaEgtMmVwdjJmMU5aeWx5SzBQU2JaV2wzN0Rmb0FjYWcwa3lZajhXakxKRkV0blg2cHBKZGttaHd2VnRuLVE?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>German Oil Refinery Sounds Alarm Over U.S. Sanctions Risk - Crude Oil Prices Today | OilPrice.com</t>
+          <t>Port Glasgow gran STILL waiting for smart meter months after supplier promised to act - Greenock Telegraph</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 21:30:00 GMT</t>
+          <t>Wed, 18 Feb 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVBocnlscUNIOG01T3hEcU4xczcyVlhiUlVLMzFXd0J3YmdveTR5Ri02NklLVUFoZ3REQ29CSkxrekpoeEtaYkZYX2lUUkFqRFFSY3podWRSN0VGQkNiTTFIWlRZcmNnWng4aDlROEJ3QjBTNVZFendRTm1qclhZN3g1dC1EV09DYm5tOEtjV2pndHRveVVKZTJVY0dfdk4yYUVsU3NrMEZ0SkFjYTRwZdIBtgFBVV95cUxNOGdNSjJTQ29XVnFuNnVSLUdmNmRPYWdDNzE4M25URXNiS3Y2T09Qam55SFRqeHJOSE0yNFk5aHJKUGNNcFBYel84UUtfWG1LTVp5ZWFZUUJORW01SklNSmk2aTR1MkU5bGlrejZ1cHl4TWFNOXIxdm01Sy1rcmtTcXVYT2pYWTdCTDI0NklNMzFvcW9rZ0p6c3R1YVJ2UkFmbFlsTVVTSWV3TENNYkN1ZDNJRTVkQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNbWpqMllJcFdReEJVeXA0cE1uUTJ2dnZ0QkZUcDhhZzA2VkprZU96LTFCOGZtdzBtS0VJRHpaeUg3MUdhMXE2VFZYZjRhOWJDd2NqSE5xLUJoLUJJa2NZT2EteUpiNXFJODVHS3lvZlFnek5CUXZyem9udTctRVJlUDV1dlhHYkNaV21fcjBBVVdhMGU4SWkzYThPbmVybFZBdVFOcDlmc0tzdw?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>25 wonderful old photos of Fleetwood - port, town and seafont through the years - Blackpool Gazette</t>
+          <t>Precarious Work, Precarious Care: Income Instability and Interruptions in Health Care Access - Counterpunch</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:00:00 GMT</t>
+          <t>Wed, 18 Feb 2026 06:59:56 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxONmN4RjFsUFRtOWZzVjZkQkxsX2F2UjVjWkdTdWZQVXlxb0xDOUxIOTJ3Y0NwT0NGS3dtSktHemRZSVZLbHdHa3Z1S3lUWGR3VTVGSEZiX0hsWlVRN3h3OVJBSGx5R1l2RWZwNUFkWEp1ZnY0Tm1qTTdiWGNrTExiUzNtcFJCV1lJcUF5R1BrUTdGU0xQMkNjdERsOF9jZnFTemRrNGJPaEJHREhvdWlBYzZOSTZXZmJwbkNjSTVnb0RMWjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQTGlENDN4RS1ad0c2V0pjUXZxVUd3dzBfVUhzVl95TVdmNy1BRWhVT0FZWnlDbXFod0RLUjJFVzlRaWRUeEhYaHFXUEZwNy1MS1g3ZTN1djdEbnBrX2p2YkVMMGl1bERUVURpb2VPbzZ0d0hGcnlVcnp0RHVWdmRwMGZoVjgwalZlWE9BdDVMU2VVVzQ4LWpJaWNNYmhlbWFScjdUZDg0VHBwbldLN3NwR3FBelZCcVpsUEZOdEVWa3RaOVRUeGQtRDZidw?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2101,27 +2101,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Woman, 69, in hospital with broken vertebrae after police allegedly pushed her to the ground at Sydney Herzog protest - The Guardian</t>
+          <t>Shares in trucking and logistics firms plunge after AI freight tool launch - The Guardian</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 02:15:00 GMT</t>
+          <t>Fri, 13 Feb 2026 10:26:00 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYnFCY3FhWHY5OU9pdnNRUDJMc1YyaG1iLUxzUHgwQkh3ZUJya2d2SjBpWDU5UXNyMUN6UWlJc3ZFMnhVREJCVTZYSFQ5eUhPQ251Y2tRNm1ONmZqMk1UT2hkNDBhRHNVSk42Nk9VSWxreGlpWVlrYlp3X052b05NWHIwdEdWTW8tbWwtWVpmck83LUE2MGV2SEhENmt4UFBwZnFRTVktYUdSM255b1d6STRJdGx0UnZJODk5bmF5cUl0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOUS1ZcWYyVTFBNzl5MHhZMXRBaUtFbDcxcEg3elFISE4tUFhWeS15MlZJQ3RDVVdZY25MN0J1aUhndlh0LWlOVkktYW1aUk01X0MzbzRQQVVEWHRrYW4wTHJFaHVDTzc5T3pmMXNfd2RBRXBFb0tpbERuMk1md0ZnejhGRlY4aWN6MWswZEFiTlBJdzB1OEVyOUVMX3B0M2IxczFzLWU0aWVoY1AyNV9qRFMtVkFkWDA?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2131,27 +2131,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Epping: Man in court over alleged racial abuse at protest - essex.police.uk</t>
+          <t>Quantum Computing Can Solve the Hardest Port Scheduling Problems - The Maritime Executive</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:44:00 GMT</t>
+          <t>Tue, 17 Feb 2026 21:41:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOSVFCc2RNS2pkYkRkNTRhWkFrU3loYnV6ODF0X2V6Zmg1QThrdmV4Tkk3eWZOQTFlejFEZXZLV1hyd1cxdnMxa0VSeXFFU2gyVjhRRGxRdFluREhSR2FZYzhBXzd6RzFKMnhBS001LVMwcXVfQlZsSlhJQ1lNR2RicHZDUldUdHBwLUlVSU50ZloxSi1BRnBqNFNUNnlmYmJVUm51V3NuV3FqNkoyU3dSUXpVSncyVUJ5c2NTNkpPQ0U3U19oQmZpajBBOG9aY1g1RGpZNmVtMEptbmxq?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQYUdvdzZESUh1ai0xM3p6Zkh5M3IxUk03WGxJR0tGYnoyRnAzVW5FTnlhdlFNZnJYbVRSZnJESGRhdEpXZGdvSDVzbk8yZzBaSGgwT2RldlZpT0gyanVyaEhhY0ZURThtZC1GZk5ONEpEazMyUlhnWFc5RU4ydm5fcmNBTm5wQVIzaWhEYmhBVTI1SDBTbkR4VEp5VXNHLVdpeGRZMWM5eHNoZw?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2161,27 +2161,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Australia police defend actions after violence at protest over Israeli president visit - BBC</t>
+          <t>DP World Reshapes Leadership for Supply Chain Resilience - Procurement Magazine</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 09:34:33 GMT</t>
+          <t>Tue, 17 Feb 2026 16:00:59 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE55X3pEekVVX2xLYkhnZjg4VmdvLUlPRFFOUkMxekVsc0ptSXEyMDA0ZkNzS0pNM2lEeGVubWs2Q3JoU2Z6YU1qZzB1cGVVRXViSS1sdW96XzRadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxObkVhcmprd1IycEFIanZHZG41cFRzSU00T0JHTUNPRTZhZTQwTEoyWEFkX3o3V084a3Y2N29fR0l5VlU4RlZQODM4M0l3Znp2Z2owTFhZaVIxLTVCWUc0M3B0aERDUFFIcnhrWHlTeVZKTVR4ejlZeVU5R1ZlT2IyYVY4R2Q1MDROT2dPZg?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2191,27 +2191,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Day 45 the Protests: Nighttime Chants and Intensified Police Presence - Hrana</t>
+          <t>PORT OF LOS ANGELES JANUARY CARGO EASES COMPARED TO ELEVATED 2025 LEVELS - Port of Los Angeles</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 22:00:15 GMT</t>
+          <t>Wed, 18 Feb 2026 07:07:30 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTEJ1ZUszLTBIUGVOTWdBV2Y2eVMyZWZfMVlnYnVHMERtV1h4MTFUdGFQTkpOVDNVaFo2WVhOLWJhWTdRYUZHOU40Zkx4ek8wUGNKbVRieU12RVczNlhlUjBRNXdsd2tDeFhIWjY1eTZJUWdIM3JMRDFjOHIxcEtYNmU4NnhQOXU3TWtfRFZJSTNfNzhVajlGWnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQRzJJUzU4YnVRUlhjcnV6SFd6aHhBWVhNcVlQWnU3TlpvR2pRcHNpa1h4ZzFhQW96ZjJfcXYyamVJNkRqUWM0NU1oZE91dFpvcjl1cnBkU3dvQlVNQkR4bmRYNGJ5WjBueTZWeldDaVhRNGU0bFlPT2tYT2w3U21aWWpna3YzM0k?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2221,27 +2221,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Antigovernment protests in Albania turn violent, at least 13 arrested - Al Jazeera</t>
+          <t>Super Tanker Rates Soar Amid Sanctions, Supply Shifts, and Strategic Hoarding - Crude Oil Prices Today | OilPrice.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 04:17:00 GMT</t>
+          <t>Wed, 18 Feb 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQcmFnaUJZWDY5Q2RObUltcjVpdjBoOFFhZHlubkFhaE5qY0phWHNUNGJNaFJKa29VanVMbnY1OXVZM0VlbkhSc3BpN0R6UjJFQkhJWDc0dVpkTDJJbUNYM004c21yenZtN0tFUVNOVkZjOUU0WkZYNzNaMGJ3eFROWUwwcWYybkdsQjg0YXkyYmdmdGIySkFZSlJvSkFNalpfR2FCc0p1U2xGRXNfOEHSAbMBQVVfeXFMTnVUbzhsUkhMOUNqYUlWaHpac2VpX3Q5b2UzczIxYlVrT0JyR1RqbmxUUmh4YXp3Tzd4UUJWbmNOYUNQSk0xcGs1NzQwZnlMbmtNLTNmMDVhY0ZpTUo0LVU0aG1LMnBQOHZvaUx5cnpKZDBrRlVTZ3plWWgxQXdwQlA4NE1aM0pMOXI1TDlxd0Q0MUtQcFNnb0RQOTYtMmNYTFJQZnpPV2g0ei1qWVphVWxlOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNd3dHMnB4V1B0d1o4S2lqeE12UDFSdjAtSWQxRG1lRFJqcURURU9oeUlCaUkyLWo0UUpMSHpWWllaNXdKZVRsNmN6LVBGRXUtc1E5a1VMd0FndFNDMTZkRVVLM2NUNUhXcm4ybDJ1bHhtLVo2aXFGSXNqWWtYYzE4UXZxbFJabDlNUGRMbkJaa3pNRGZMMWxtaFBvRjNMSEt5b2dEMWhLdjlJcW84RjcyMFE0dDljWHFhbWJTZnFDY1_SAcYBQVVfeXFMUDBtd05oRzAwU3lCVlFhY09wanF2bUVVTWM2TnVLbjctbm8xWjhVaHBSSngwYmstcTF0OWRlVjUtOFdwOURLdmktdUdTQ1hKd1d6dnZMRzRLb01Wd1Jtc0pEREpyeU84ZGVBbGpwcHo2bktja1J2MHZBLUc2RlhWYUd6OVh2amxja2tWZklfeW9GY2wtMGJFaVc0X2tTVTFaMnRhVGxYR2t5eVA0VTFzcE5OS2RtUEJnb3VidkhsMXhEbl9CRUVn?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2251,27 +2251,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Australia politics live: Angus Taylor expected to quit shadow cabinet and launch leadership challenge against Sussan Ley tonight - The Guardian</t>
+          <t>Ellesmere Port woman fined over drunk and disorderly behaviour - Chester Standard</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:01:00 GMT</t>
+          <t>Tue, 17 Feb 2026 14:44:04 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOLUt0Y2hrdDRkSElsTkc3UnlnRmtJbExLMFdOVDdHSEs1VlRsTm9VaWRZOGZjNmJlZjVfWmlrbE1vNXhwWEFUMVY1X01QUGNFOTdxZHdKSDdrdExVV2JaTWlGR2pVaHdqSnZJOEg3dWhTLUhJZGsxR0VOSDdjWHo3aUJPamRVTlNOMXRSSzQzREtPNlRkdUhnamRCQmpKZEF1QU02elB2NGR1UEtDNUMxUGFZWnpidVFxemxDNHhLcklmajduSEJ5dkI3LUVZQVYxaEppYnppM2VaU28tMDktVERLNDhGNkJ2YWNCcDB6UHR5VTdBdXFnMkVKaGg0R1JJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNOUJPRnI3bjBzX1l0bmhfREk1VFRDUEhjVDY0ZE9XTFZZWTEzSFkxSXQteV9sVFpfN3lEdERKQ1ljeWsxdUFhbkNpcGh1WFFGbUxGYmxwU28tUVN1SnVvQkVWTjZkNV9XdTFtSEJMUy00NmxjS2NjMHBPbkFwYmNuc1R5WGNuSFBoNzh2QkxJTHdGSVVwZDBXSkM2MF8tUWVf?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Police chief orders watch on groups over post-election protests - Nation Thailand</t>
+          <t>Arrest made after officer assaulted at Warwick protest - Warwickshire Police</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 09:43:00 GMT</t>
+          <t>Mon, 16 Feb 2026 15:45:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTFBzQy1WQ1lpNG1aV0hXa0hkY3Q3Wm5zSVplR1loX1d4UW9TLUozZ2J6VWttOEpjOXBfcE9hdUtiNDhuLUNtWVVmVVNEdmw5RXNQYkVMOEQwMHRzSW8tcTVMRUZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNSG5sSW9TenItckIzVkpWNHpKMUpQUkZMaERQQVNfcmNaNE51QVJEQUViaWFBc01XT1lTNUQycFhhQ0xIYW4xR3NpR2ZVVUVWR1lhNFBHcUhsNUZ3OE94Y0RLMWx2c0ZsZXNEb0dTRk94YzlZa0g4OUhBczlYYjNDUEhOazZxUk95NjkwdEcteEx4QnhZSVBHVEc0NDIyWk9nY2l2YlZqNGlIM0xWcGd1ZDNCQW9saFpPd1hDVkstRjVnTWQxZmc?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Police update after rumours of 'man threatening people with belt' - Cambs Times</t>
+          <t>Female Israeli soldiers rescued after being chased by ultra-Orthodox men - BBC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 13:00:00 GMT</t>
+          <t>Mon, 16 Feb 2026 07:47:54 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPemxoenFFcUN2YVFRQThSYzEyS1BtUDlmWnBGelNlWXhlNk0tVVhPaFdTcnZUOEFyTmpDUWhRdUZpTGFzMWhFY0N4V0hJYmZKQkRWUDh5d1hfdEZxRUZfTnl2ajNOQmZxR1BMYm5KVjQ0blp6UDNpVUtJenNGSGFmWnFXbFU0NE5pYllrTm1vNHJwQ0FNMlBtNTBrblA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5aN3haeVZSeW01cW1jRmxhaFpGRnFpTmQxUnZJSUU2TXZ2OUxkb1ZMWnhYSUE5MUdOVnRYa2tPTzl0TEozVEpQWkt6MzFRd3NyMHpFYk93V0JPQQ?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Despite police crisis and protests, Unión, Colón and Copa go ahead - OneFootball</t>
+          <t>Eyewitness: London sees a powerful yet incident free day of protest - Police Oracle</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:01:09 GMT</t>
+          <t>Mon, 16 Feb 2026 16:38:22 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRDFRaWVYRFZRRmpLZ3YzTXhFZ01uSk0xam9obzdUZS1XODBDaS1Sbl9kYml2NjBWN1ZoY0V0UnlYd2VXSVlCTW5HODBmNGtNZjFGRVQ5VEwtRmt1SElPVWJtLU43bVZLY2Faek90dmZJbXJqZE9MbVhDOE4wSll5R3o5bVhKTmhlWkVnNHY4LXBMb0IyRVN1WEJtLThzWGJiOWdScnJNdDc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNYjBsd3o3bmFFeWU1a3hsZG1QS0tnaDhvY0EwVkV1bWh1Qzg1eUdldDJGbWEyUHhSYmw5SGRDV1JKSlVELVNzU3FqWWxkZWRaN0pJcmFHOTh6NFlWM0JGeFNPTVpGeWRZTmtyYXJGSnBBLUpTaDhBOVlYSFZPZHlocC00RGg2YU84TmZNb0F6YWNsWTMzdzZfalJfTTY2azNPbU1pZTVINFpNb3J0eTJLQS13?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>‘Like a pack of wild dogs’: Protester injured in Town Hall clashes calls for officers to be charged - SMH.com.au</t>
+          <t>‘It was terrifying’: Australia faces reckoning over brutal police crackdown on pro-Palestine protests - The Independent</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 21:20:24 GMT</t>
+          <t>Tue, 17 Feb 2026 05:25:00 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOLW82YkxUdVhjdTBFRlRvYU1jcmM4UjhGbmV1LVQzVEZDcTY3NDliWjdDbk9ZQlExZTFNcVVFNTZDcnlUd21rX1Aza1RmNjIwWmJRVWZ4SWZLVVhVSUJ6WHctOEVBbnB1S2VZRkRkZTBTb2hfMzluMFpKUFM2dndBV05vbklETkRSd1JhOHpvamtnMkdWeHJDelRldGY2RGwwUlRzVVA5eUJOX0N5TDNFYUZ3VXNtVHlQR0NPM2VGZ2lVMzUtOEo0QlptMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTy0wZ1RhcWs1Ny1iVm5lQUJaeWc0X0VwWmNVVTdNcGl1cmVkd3JpRUtEeWlNRzBjVmdYbkZYNXp1bGZLbGlCZUZjNGk4bGplZWRRZEhZQXpPRVN2dm4zR2p1TW9kV1BGZ09WZmNuVWRWQV9tVDgxQVdmYzhZNUZSemlMUm15YndZWW1rajRrY2o2dFNzMFd6SVVzX0dGcXNBN2swbVZwakg0U1E1enJiOVFmSjBSdw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Senegal university student dies after protest clashes with police - Arab News</t>
+          <t>BOOKOFF Strikes Strategic Capital and Business Alliance with ITOCHU to Accelerate Reuse Expansion - TipRanks</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 08:40:33 GMT</t>
+          <t>Wed, 18 Feb 2026 06:59:49 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1ubjdWQ2F1RzVzeUFJRmRBMHJCRXhXTHpTVWx0bFZrUXBTbU42SUJTcGFFMWJRYWJ3bmpoNHh5TV84T2xaTmlUYTFWZmg4cHJ2aHF0ZTRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQTnZZZjljVUFHRjFWR1ozLVM4ODZxcHBhTTEtRXpocEg5LVg3Nnp4eHNkNVVTaWNsWDcxRkhTOGw5MWZUcXBiT3FxcWxxdzlJMUdlMWJfOHpuUHRjU0ZtMXlBVHJPQ0R2WWpfYjRjQWxpVG5rSmNGN2VHcl9kYTNJYmNjb2pXbENuazQ4cy00QzRQM1FDMm9xV1puR2ZVSEl5YUJia1Z1ODlWajVxXzVnSC1QRFMzLS1KOHd3bzY1dzd0eHZKNkFNVENOTkNlck1wQ0dUYUNxb05MZWIyT291cUV3WQ?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Meloni blames 'enemies of Italy' for Milan chaos - Inside The Games</t>
+          <t>HungryPanda delivery drivers say police contacted family back home - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 15:59:32 GMT</t>
+          <t>Tue, 17 Feb 2026 18:35:47 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQcUpnUmdPc08zSTQzNnVUSGRGOE1OUWx3MmZqQWlIeHNncFdJS0FGNVVPa0FNUlF0d1NiYjh2Yjd0dW1yeWFxa3JuN2FkeXBGZUM3c2tPX2tuSmpkZ0VjSlhvNGVQUzdlbGtKd0VTS1ZjYUVraV9iZm5oeFVsbE1VaTZvbUFMVnVmN2gyeWtZNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQUnJZOEtrVXRZOWZHZVNac1daSzctQlhoVVkxUjlPNlRnYVlQREkyU1NzbElyb3ZLLVJ5aS1yNDE4cFR5MnRpLTJYaHg0TjdhVjR6YlBFczBQZ21rUFhCU3dNZzVuMXQ4T01sMkhLRkp5OGRiZ3lNNmx2QU92MVlSNE12akJVcmthdU1IWXdIYjZaWlRPc1RLNXBIaWpwUWNCaFlJNzAweWM2TUE?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2461,27 +2461,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Investors pour billions into Europe’s AI and defence start-ups - Financial Times</t>
+          <t>Police body launch legal challenge to century-long ban on joining unions that could open the door to strikes - The Irish Sun</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:00:46 GMT</t>
+          <t>Tue, 17 Feb 2026 21:02:15 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5lS0NTQS1aNEdWbXJ0TzZCck4yU24yYkdIVEtoQ3hUSjJGTE8tbmxhVW1OSzk0a3g5UTJLaHNqSTRIa2JOZ1NkSUpXWkdPbmgyMHpYUDhyVTJYNV80N3F1NG9NMlJQc3lKWGE3SzVmTi0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE91d0tqTFFRUW1uREFlak5jV3NraUQzSVVveTVFSHZzd3JDUjkzV05oNmNzdjM0MFpIQ1Y1cENtbTJwQ2ZrMC10NHBoenNQMTB2SUstYlVvY0lkdzhjX3VoMlFPa0JwRDcyU3c?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2491,27 +2491,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Durham philosopher brings ethical thinking on AI and democracy to global stage - Durham University</t>
+          <t>Sydney's post-Bondi attack protest restrictions come to an end - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 11:16:16 GMT</t>
+          <t>Mon, 16 Feb 2026 23:22:53 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQbF9EZ3B4TnBNWmw5dnBZZ0pPVkZjbzFaVmVOeXVpUVpxVU9MSFkzbFFuOVhuZng1NEdkWkd0MEt3eG1qeW5Lb2FfYjI4eGREU2x3eVhYU0VxSm1ibWNRdm9uSmlyNFRxU19ISVFvVXE5bnpFUU53amFISGFhd0R4WVd0cVVPY1paUFZiUlFnQ0taNklMZHRIUHBSUkh0VktCYlpZMkZpQ2NRRU9KbEtjUkVlMjVPeXBGdEdxcWMtdGRld3MxdHVLTGF2NEhYN0xOT3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPbE5YbTFGVEt4bmdrRXh3eHFTS25HV0ZQclVYOEd2WTdXdFJxZ0VaYVkyd01hcEpGX2xzXzY2YnZfMHFDeFlGcjFvZ2FDRVdhRlBmaFZ3N29kaDRSRmFKZktvcnFpdjdTQkpfM01ZUUVqTnY0cGthZEhCQkxrQVdSRGFDWmdNcUhNWXJRMWxnUGxjaWducUtPVGR6Ml82NWNPZ3NaMmtQM3BPSms?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2521,27 +2521,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Escape the rain and discover the world of robotics and AI at Aberdeen Science Centre this half term - Aberdeen &amp; Grampian Chamber of Commerce</t>
+          <t>Germany news: Right-wing violence rises in 2025 - DW.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:13:42 GMT</t>
+          <t>Sat, 14 Feb 2026 10:25:32 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQWnJuUzI2RXhza0dBajFXZU1CT3g0OHh0YkNpWmZQLWNEYnhXNnUxeE54Q2xvM0h0c3ZOU2tNOGtESlVHNFRDSjM4a19DS25pOTF1RWZGLVhGRG5oeUsxaHdxX3FNTkY1OFRWMXRqVzNDTjNyVXlVTTY5dzF5RjltdXFFTGhLU3J1V1NIdWxSVjBZUmxvSU9LREZRelZhUDBSSm5LQW0tTGFYcUU1NEF3Wk03bDllVnFmSFo4LTNjcHA4ZEVVdFROMFVfcGtucHhx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxON2VNUEgwczBBeW9sR21HWWNoc0V6MU1yN2J1QTJVM3BqcDVMOHRtam1McGEwV3lzWW90S2pSV1k3d3pvcDhoTkJRZ2NyZFNMTGw2UVhzUlQxemxDWHhmWkV6bTdRNU1CSkh2VlBzUGc5Z2Rlb09Yb29UdjRwMDREWXVLeG1RWHJaWXc?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2551,27 +2551,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Silicon In Focus Podcast: Building Inclusive Tech Teams: Skills, AI, and the Future of Work - Silicon UK</t>
+          <t>Vehicle fatally strikes pedestrian on Seward Highway in Fairview, police say - Anchorage Daily News</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 12:27:10 GMT</t>
+          <t>Wed, 18 Feb 2026 03:56:59 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOT2FQc25wdGNXNzJjWEI3RFY1VkVkN0Nvb1M5ZlZQMTh1YVJ0WVhuMWpCNC1iV1o2dXdrSnI0YjZBQ0R0dWxPV0EydVpkSndRdExrek1rblp4SFAzTXJ3OW1SU1paME53LTFGN2hjamIwQXlNQmVDY1VjM3pzN1Q2ejVBd1E5ODN2N3VYQlFnVFh6Qkt3R0Fad3hZMGVLR1BuZFBLR2NyX0xRTl8wb1BxSFpiY25TSXNya0tJQ1YySzIwSzBVSzl1VmN5endpZmNDc042bGFyY9IB3AFBVV95cUxNZ0lyQktSSWR6QWdDRTJLY2xQOWlNYjZ5VkRyRUF5Zm1leFJ3MDdvMmpGS243YjUyNzNST3c5Mjdjc0VKbFNsbEdwaVVhOEFlYnlfejBTM2VES0JLUWZXMURFSE5NSkxLTTdFSnBMZmtjX2VmSFZ4dVJzeTB4a0YwT3k2a0l4SnJVVjRQTDdDNmdneTk1WnZ1RE0zOWVPWnRxdXVnclN5cVN2bjRPMkkxbHk4X0FHa1ZkMkRIR2ZmMzhGaXptZkNkWEplZVVMZkUtM2JRRlBhSFZLdndO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxObF9UakYtRy1xMldIbi11dTI1YnBRbUZnRHk2Ulh4aW9RVzBJam1BNzVmSUdzejNSOWYybVU4TmVlaGpETGxzbWppaTZtYmV3WFE0NmE5dDFfUkR5em9nWmY3ZTBfR1M5NkZheVB4aHVwak5Qc0lpc1ZHTnhRZ1lPOWFOcGRSc3BVZTVOdG9XRDIwb0lQdjBuaGtZcGotVGdqRE94VUpVMm1ERlJfWWxUVkpqUF9lblBmZ1djYWJkM3RFRWtYZXNjMg?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2581,27 +2581,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NEWS: AI Partnership Aims to Speed Up Discovery of New Medicines - Practice Business</t>
+          <t>Synagogue protest 'buffer zone' legislation undergoing revision in NYC as police chief Jessica Tisch says she 'has concerns' - Jewish Telegraphic Agency</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:29:01 GMT</t>
+          <t>Tue, 17 Feb 2026 19:14:46 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQYzUyNXlaeTJ3LTFZb2RhS05tbkQwU0tqTWdPeUpIbVJlSkFOa2JRQmhnV1ViejBNSmRrQTFINjJ0MFpKN1RxNFN4cGhtNUM1XzhFQ0I2R3BqWVNDNHlRdUs2M2lvWTkyRGlJYXFmUElrXzlfT2VVZm9WdVBSVERDNWNKQlRGSHBFX3dybUU0ckhNak9Oc2ZaUzlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQM2pRUzh0Q0pETmh2YnQxaDFtaEdFNDFybl9acEhyemNGZU52bVBNY1J5UmRUU3pxRTFSTXo0eHFYMDVNd3JaYXB4MFF1aGtodjJ5cVFCQlhxRzdDWXBHcldOaXBDYWFZaFdpejZRTVpwa2RGY0ZPamJRWHJyMzZiZ2kwVjE0SXVRM2dFT05odmtlbFFQMjN0VHhBSEMtRkg3YW53cTlTdjZ1NVM0MmYyMzhqaWVlQUNhZ2ZFeXRhQWlVSUhvXy1ZNC1JWm9wZUdXQnB1eFVuWGVjWEVoYlhNeWY2VmhYeG5VeGc?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2611,27 +2611,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Announcing the shortlist for the AI &amp; Software Development Awards 2026 - Computing UK</t>
+          <t>The beatings will continue until social cohesion improves - The Australia Institute</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:41:58 GMT</t>
+          <t>Sat, 14 Feb 2026 22:35:49 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPSDVzNXFfdDltRGFLRDQwWTRyMnZxSXhKOURMQ2VOOUc5RlNkN19PXzVuNU52NTBNTGJlZDU5SnRwY1RkdHdHUlpDNS1samVIQnUwakM3VS1sZUkwZC1vNmctTnJqN2MxTGpHMzdsNjFwOWd6X2RTRXpvY1RNcVNMbm85NUZfMHNTOFRsZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOcnBocWpIa2FTTy1LSUs4cE9EdUFoenRJb2dnSDBfNE0xTEozbWJCNjRTbFZ2OURuLXpwMW92ZWllZXlxQ2dVMEVfcTA5ZzZwdUhxNVRjS0k2RnYxN0xuY1huOElhZXFIeGVDU0FUM243OHl6TFViemlkaHdXZ2FMMnM4X0pwQWhUWVA1WWxxSl92UERCcHVONWFCZEx6Zw?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2641,27 +2641,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CreaTech Network 2026: Exploring Creativity &amp; AI in Entertainment, Heritage, and Open Tools - The University of Manchester</t>
+          <t>SVG Police makes major drug haul after US boat strike - St Vincent Times</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:48:14 GMT</t>
+          <t>Tue, 17 Feb 2026 12:47:47 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPaHMyWTdfQTNFNzNKcS1zeGIzcW1Pc1RhS3JZV0ZXOV9TMXZvd2l4V2h6aXZSLVYzbmJfd3U5VTloRDk5NW5BaHRyV0NsTnQxeWd5Wld2WFBRMlF2b2c1bGJidGlZWGlFTGQzdzhWc2RtdTZHTEVkYi16UHhyVDZsMWROODZLb3BRRExfTzBURXFLdl9ncm5KM3RrLWxaSzNMMUExYkQ1QW1YV0NNaDlCbTF4TmtCSUZhZmJGRm9rdEMydkFYU1lR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxORjdRSTFJcGM2cXV6N0ZhSTZZdG1mUmUxQXdJbWQ2eGxKR0VLSXFZOE1aWkwybEVrb3VwVzN1c2NrRkhmQzlzLVNkMjcwZ3ZQcUhYandtRXJIZms5eF9DWXJKY1N4clNfTTljMkMtY0R1YVdNeU1GdktBcENMaFFrMVVtSUJVajNBd1ZQY2l3?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2671,27 +2671,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Former Daily Mail editor tells hacking trial allegations are 'preposterous' - BBC</t>
+          <t>Arion Bank Sets March AGM to Vote on Dividend, Capital Cut and Share Buybacks - TipRanks</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 19:30:14 GMT</t>
+          <t>Mon, 16 Feb 2026 20:05:23 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5Kelhub0J1VVQ3NHY4a3Uxb3RiS1piWVczSTZWeDBwMnNlMGIwQnRnQTJmdjl1OEZ4V2R3LThRdExnc0lGV2w5M3BGUVA1MzhNZTVLTTRZTC1uQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNY2xOUXVIVFNZaEV1SDQ2ejlReVp1SF9TMTFCU09LWkNZYUpLVExCX3NTRWJrUUtJOUZVT2Q0bXFVNEU3WDZ3RXExTWZQdjBrTkFiQmk1TFRRdXJGbXc5SElZUExhTDVyNkNUVVk3SlVhOUtqMVNrYS1POWRSQ01JcTJGT3Y5ekdEeVRUVE9jUzhPcFBONHdwSG5NTnZLWlNaeDVEZTNRSktKZ3cyUUZsREVMX05QODd3dEgzOVI4S2NGYUxJRWR3?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2701,27 +2701,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Broadcom Wi Fi 8 Launch Extends AI Networking Story Into Enterprises - Yahoo Finance UK</t>
+          <t>Gaithersburg police chief to retire in March - DC News Now</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:09:00 GMT</t>
+          <t>Wed, 18 Feb 2026 03:05:40 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9fbUhucEo2a1Fqcl8wQmJiZDgzZWRwU2dtSWc1c3doVV81LUYtZm1PejlpZDA2RWRnQU5DbE02UWhWcHo1OGo2LURQY1VVeDVHRFpKTDR1S2I0TEVkc1RwZGlXTjlEU1dyZ3N6NzdiRTlsSktLcVVxZ1k0SW4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOVGpZbFE4cFVKSzM5VDhrTEotV05YMzZmU1cyUk40RWlOYk1LU0NvQ0xLU0ZSUVJBbThFMGNJbnIza2VwaDY2RTRpamJpVmc5NXpIM1Q3TUpKYlBkdU54eVVsSTlpUWVoOTNHX3JhYUFqSmpDdUNWRzA0SVlGeHl1bW1uX2JNV29oUlF1VmJCdjhjZzZBalY4TnRld3ljdl9sU0xZTF9PRThsVWtLRzk4YW01Z2bSAboBQVVfeXFMTmZGZFVCS2NLWFVhMGxiRnRseWdDTnlFcjlkcTlqTzVkczNpVEZmOXNoX0xadEtNdVlxTHFDMWhveTFiaVJjU2UyeHFYLV9IS0dXaXRfQ3ptSUdzX05JZkU3X1VIb0hqa2ZEbzE0ZGo4SThXRHhDQU5WSkdNZ1NoRE1kTGpBbHVRMlA3cWdrYmJucFhNaEpvSFB3R2xuQzhRU0VwS3ZRcTNLOGpjRy1VcEdwbWhjdTJqWmh3?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2731,27 +2731,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hospitality Tech360 puts leadership, AI and people at the heart of hospitality tech - The Caterer</t>
+          <t>Police Disperse CHP Protest Against Proposed Bridge Privatization; Three Detained - PA Turkey</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:21:04 GMT</t>
+          <t>Wed, 18 Feb 2026 01:24:14 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQVUJLWlFobVJVY1hZSHFobVJaZEZVNXEyUkh6RlpHX2l6emgzbGhHbF9kWmtGLW5QU0k5dm1UcEdyX2dqTXVoamU1TmlhU2tFWmJoZ3Q5aGd6VE1SNlRnZE1QT1JPVkpTVWFiMFNnWWtQQzU0SXRHNkR0LWdENUVjLUZ1VmZfQ1d5MXMtLXg3c3ZkSGJudHdNY3lPUUVmQzl1akgwZ2pBVlV2T1RRTGNnbTU5bzIzUFlX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNa201cFlMZXpqOVNucFh1dXBvclVKeWp1Z1I1czJFWXJvRDlaY2NDVWpJelBsMjM0QzIzM0FoWXdCcTNuaFFSVjdsMmozdTVhWER6LXRjQ2FxREExTXE4QllIRFQ1TElHeG5TLUxMczc3NUhZb19OSGlyZkR3aFlUYVlocjBLOGZtdm03NjgySEZfZ0w1ZS1JdUhyMjZ6NGRmSHRrbmtUQXhBZTVwbWhjanBOY0x0RGVMa1pYTU8tTQ?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2761,27 +2761,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AI and the future - Atlantic Council</t>
+          <t>Police pursuit results in crash that causes RTS bus to strike pedestrian - Spectrum News</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 11:01:20 GMT</t>
+          <t>Tue, 17 Feb 2026 17:39:00 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQRzhpY0tmc21xVjAyVUJnVHB1MUQydmRNRGVpZUhsWDlkb3BqY3dzOC1PZTUxM0hiVjJmWGxJN2ZBVVU2LVI5aEJmMW1Zb0ZWQ194cmxnMlRFOU1wWndWRGVVTHVBa0dZckdhOVVYQUZmZUU5dlVodlpoenVRa0I2elVORk9aUVZoU0J1ZGJfemhwMnVNX25VeVZ3ZXRjMGhORGdqUnF5TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOcnd0N2dzbzVNTTJiNEpKRUVtYUk5WmNmUm41eHNBSUVsTGIwR0VWd0xEYzg0c2RvajVoSnd3enU0ZTZDcGJzMUhaU0RZVTNpS2lqOWNHY2NoZG1OeWp2U0cxeTJmX0xBNmNUZ3E2QmRDSmFab2hGQUY0SmVRRWNBUVVpaW9BTG5GU0lSeEpRX2lKd2pMdEEzOFpmMnluOFdJbzN6b2FLeTdtRW5WcnJyQmdqLUF5bTVGSHZQdGdsdHBwb2lsTnZKM3F0cDN1RGxYaGdjOFNpeFE?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2791,27 +2791,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Microsoft Confirms Saudi Arabia Datacenter Region Available for Customers to Run Cloud Workloads from Q4 2026 - Microsoft Source</t>
+          <t>Today in History: March 3, Rodney King beaten by Los Angeles police - Norwalk Hour</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:35:19 GMT</t>
+          <t>Mon, 16 Feb 2026 20:40:39 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNTTNSejlUVVk4aWRpRG5YNDJzRzhVbHhHNHJfVlNQNEphQ0J3RTJ5WHJwMngzWlRqS1RDdnFzdldkb1VTemhmUDV6d19FYXdocHFoODdUTTNiUDZBbS1nVUFiS2FHQi1TU09ocWVkNXdCLS1mYkl6d1YwMGoxSGNwbmFEUG9GSnN1am9sMVR4bFBKY2VzNVdvWmhlMl9xaDVwOHRacnBGV0NCaGFCS0hfUnFJblNBb1BpbTlVSERXbUxZem9OOUFQT1FENmN3UXhXTzRNbHoxQVFrT2VJdTRDMEQxaHVONGZmWGYxR2RR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPU2JpTGxDek5qMi1ZZV9NWWp2MWVadjJhTUdKbXNXSDNiLVZ3RXVzbk8weU43LUs3Sk1MY2pMY0FxM3ZUbTdlUGVHWWFxS1lEZ2dfTVNzQWUtVHhzWHY1Rmt2M2pUelVGZVRfYW1CcHNhNmt0Y3BNREhlVVpzenU2YWx0S1dHY0x4d28yNWJ5bldycTJNaTRmRDFhRzU?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2821,27 +2821,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Drive for AI and data to push tech spend over $6trillion - DecisionMarketing</t>
+          <t>‘Excessive and disproportionate’: Police criticize feds’ tear gas tactics at Portland ICE protests - OregonLive.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 11:30:00 GMT</t>
+          <t>Tue, 17 Feb 2026 16:50:00 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOSFNGcm5xUFVCMS12M1pUWG0zZmpxV2ZjZktGRm9WdFhhMnpnQVhoSzE3ZzJDOFktYkpaYVNPRWpKbjBwZEpGQWxCclZZTWtQQ0lVVWs1RXc5MWVQcnJkYjRXY2xGNUtrXzNnbHAyVjdHVXZ1Y1c0RmcxZGVSSHZBV0t6MDVScndqUGV5OFo4aTZDNnd4MEh1d0FpNF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQQWlNdExvelZ6cGpvcW1WVGtKa1djdFRfWmRqZGl4RVAyR0FLR24xQ3BNWVB0YjI0b2ZBbks5UHdJaXZ5NUxqXzNzTVhveVZkYkhrbnJGYXRHeXJTbzhKbGhBWjV4Zk1uaEtqOElQd0ltT2U5eDdKMkV4Njl4RjBzRXFmZV9qRUdubFFaQkJPNUwyUlh4bjNxbnRRN0Y0LXJpSkJiS3B6LXJuTEk1NG1GSEE5d1VaaTZfVXBkbnpYMWY0Q2hzRGY4VkpRcU80SEh2NS1xdktNNNIB6wFBVV95cUxNY3p2RlZISG1IdlhwWGJubTdESVo0TWFnVXp5aW1YWnY4bldFSWJ2YXdUeERUVWV2UXpEWE9lVGxCXzZ4LXIyYkhQeWtkdUtVZmJiZndBd2hhVFVDMjdSaHczNVRJamJIM0M5N242VTJIWk5MMkdWYzEtc21mT2ZubXZSNzU4WnV4V1JIXzNsRmxST1NoNWNBUXE4RHQxU3RORjhsWEpzZ3FpN09oZWRhMGc1UEJ4Qk1LSDdiZjExT0pQQnk5Y01MVEJBQVIyWVAxUVFnRnFUdTJMeFVvZm9wSGs5SXBWQ1ZMM1ZN?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2851,27 +2851,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BBC set to launch AI Unpacked Week in March - BBC</t>
+          <t>Criminals strike amid police vigil: Officer's mother, jewellery shop targeted in Bhubaneswar - The New Indian Express</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 09:00:00 GMT</t>
+          <t>Wed, 18 Feb 2026 03:40:48 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBZVjlQN3g4Si02WTdkcEswUGxNOUFhd1Y1djNXMFh4N1QzdW1rVG1ZaHg3MlFaRFQycXFCMFpxaF8yd3pFMk9zTXhUcmJyUDlGRWpRNnJjemZJWTZyajNteTlCX3hBdjdDMV9NQnVDbjJCZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNTm1ocEdYUm5felVSXzYzblhSNUxobDdpMXJGNm9oZFJaLXZCUWM2ekd5MmI1QVJFWE5Ma0lzd2NDRXpqMGwxWVJUdGhxM3kyRklYU2FCS21pTlZKVHVWWUpmWkdvTHdCY1dfWGhfU3k4bTFQQm1DSWQwWmttQW1veFFyT0VUVWU4TEVoZTZrOFljSFJVMVhhRV9WOGp0V2N4WEwxS0lOTTk4ekYzRFJ5Q2I5UmdnNjF5aUg4b3RUTUVBc1FSbXVtcERmTnJGM252Q3hCSHpDNjNKa3daeXU3NlNWNXo5WThW0gH2AUFVX3lxTE1OU1p2VVpfTmdzWnBjNnNxbHVpaVloeVN2OENoRjgzRDZmSmJZNnVYZnhocUw1SEdTNS1DdDd0NDZDUU10OHMwMWh6OGt0ZUtVQ2JqakRYam1ycmRoSFNxMUlSN2tsU2cyQVh3YWs1bWh1Z0ViM1ltZS1LMktfeXpBVFpxclp5RjRlZE5oRFlfanpBWkgyelZ5aDdBRnFzZ0RYd3dJckZyVEN2M28ydC1KUDR0dVBnUHZaUUJnMGhJVUZhdXFLWG5CVXlERk9aU0RNRExXNF9CNlJsRkNrNTh1NUVNRU5XVlltai1DQmNwTVdrU25RUQ?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AI’s New Bottleneck: Power Supply, Not Chips – Asian Chemical Connections - ICIS</t>
+          <t>Why AI and leadership choices will define law firm profitability in 2026 - Legal Futures</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 05:37:57 GMT</t>
+          <t>Wed, 18 Feb 2026 00:19:20 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMXFXbEVuWlBpNjh2dmJENkRPeTVpUVFVdVU5NW91WXJxaV9sQ1FYNXYyUXdlTHJ3WkxxajZpVWNrYWMwS2hmeEo4SnlDbUZpTGl3Skpyd1NNTHlLd2ZUQTNNVnV5ZHNYSkpUYmtEX05mRzhySTRRRFp6UVVuZ2V1YjV6RlFjck5IUWhjNHpjVW42UTlrcWZTLVhJdG9iNnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5BNUtiU3lGQzAzbHRBNzZ1c1JiRXZNSnRTb3p1ZmVFT1h5SHpYcTktYkdXQUR6TlU5cEN2UHBaRFpzbXItVWJaNG1Cem9NV0UydFE?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cadence introduces ChipStack AI tool to automate chip design and verification - New Electronics</t>
+          <t>Relatedness and positive attitudes drive trust in AI and its developers - Phys.org</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 22:55:09 GMT</t>
+          <t>Tue, 17 Feb 2026 21:23:44 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQdTRjV2plWTlqb3phX1V0cC1vZm1kWHROTWdWdW11X28tcE9JWUQ0UXNnTzhuU2E2dVlkRjZSaXhLTXRrQVEtZTJTOURaNXZHNG9rcXFLRmZzTURzNTFQcHdYNVV6WEFmM1ZfVDlrbmI3MThBb0tybzF6MUVEdkZoUEMxOXFLcmRNM04xVHpaeWZQeS1jMy1GdGFPUFNzdnF0R3k0LWJwWmV2bnI2bHEwbzBnV2xGTUJiQmUyRjQzWU8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9wdV9TUXB5eDVLVWVmVDMxQ3Z1eHpDQ200U0g0Yzh2TnlQZW1NZFJRWUVGcEZVNU0tS20xeXlvckdWa1dRcnBmcU5Wc3ZiUGJDUi1oU0pITlF5eDZieTB5NDlobktaNm5ZWTVteUJ6NWZPS1c0RVdz?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GitLab pushes agentic AI to orchestrate software delivery - IT Brief UK</t>
+          <t>AI and legal privilege: no confidentiality or privilege where third-party commercial AI system used - Burges Salmon</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 23:05:00 GMT</t>
+          <t>Tue, 17 Feb 2026 14:21:49 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOTlA2QTdwVUdWcy1VNGxCMG9EZGJqM0tZVnJBbU1JRWpGX0RxeEFHZnd4VWpvS3Rob3NGNlNUM3pDaXhhcGtDVnV1S19XSndqNzB3NEoxVHM1YnNVdHNrYkpTLUJYS2FlQzZRZWd3TXVoc3lrYmUxTm9qd3ItTm9iVm5oaUZwTFJBRnBNNHZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPSG5rNm5ta2QwU1dULThNUzFjSTczdDhOem1vbFRvWTBvQXNKTnM4aFpuX2YwYkx2TlhYTFVCdGx4c0JFRFY3ZGZFSVVjVHpObk5tNG9UQ1I1ckxHWHIwaUlHR2xma1E2WDFCOHRyd04wVjRCQmtIU1lualQ1TDhjcmNGRFQ1SXlaTFlEbU9jVHRCNndRM3VVbVloTmxzSnhCWHBRS2tJUWtqdDlGUVJwRXNiN2NqSmlHdjlSLUtuNVNBSWJkQkE?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>The Real Cost of the UK’s ‘Free AI Training for All’ is Democracy - Tech Policy Press</t>
+          <t>Regulating AI and enforcing privacy laws through landmark cases and regulatory practice - Financier Worldwide</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 21:46:08 GMT</t>
+          <t>Tue, 17 Feb 2026 15:57:32 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSV9sWF9hdE9uTjVQWEJMZllsZjhtS2JKTHhLaHNERXpVR0ZFQnVCVHQwUmVva0JUcDZrZGJlTWEzbW1ERUdPaEF1bHhTT3BTT3Q0X3laWWVOOWloUk9MaUx1OFBJdHFMeERXZGg5UTk0cG9nSHJONEJzV2JETFRaOFRCeTZnaGozSFFvUXpta1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdFhBcjUzWVMtSWJud1U3RkplY2NLZjZEdmRPaHY5ZnB6VmtpcW5IVUtROWtqckFoMDM0ZzBVaTZvd09XYWw1MkEzeHRsaGpuNERoR2pBNExpczNQNEs0N21PWUxWNmtrZURoajJQcjl3c2dnR0ZiNE82NElhdm5sYTlnNzZrNjJSTDRod1FaVThUMFFKRk9sUUlZR0FqVHN3UV9mY2NNOW1wdXhhLXZ2RHRlWGJ1UG5yWW54SmdFRQ?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Exclusive-ByteDance developing AI chip, in manufacturing talks with Samsung, sources say - Yahoo Finance UK</t>
+          <t>New technology and medicines to combat drug and alcohol addiction - GOV.UK</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 04:47:00 GMT</t>
+          <t>Mon, 16 Feb 2026 14:30:10 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOSm83V3o3YXRmRkduOXRCbkV4a3FHeWpPbnJhc25OekNHQ2ZmdWdqZ24xa2stVTVwei0yTVg1b0kzR244MWR4NG9jUTFMYjFMYkgwNWtDZ2x3V3YwRDNzYVZvSGtQZlBueUh5UFpESUd5eUFjR1FaQ1czVzBSQnNzRGlPc1NaUXJRNy12ZGtxVDM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSklZSWNINFN1MUg4WnB2NmdUaFIxR1hoOHN4TWdvRUp2ZDZMOEJsRzFrV09weF9qRGwwb2tlOWlNdEZtNlVTbWZSN2xEVTBCcjZnNUNyWmhwV2pPVXNzN05EYU9iT0tHVktFb1l0X3BuVVQ3TE1obnRzUm4wbjc3YjdpYWV0eGJUVEFHTWFBZWczWlQ5NFE?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Disciplined Autonomy: How AI and sUAS Will Redefine Security, Safety, Emergency Response, and Military Operations - Small Wars Journal</t>
+          <t>Spotlight on AI and cyber security at Telford College event - FE News</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:05:12 GMT</t>
+          <t>Tue, 17 Feb 2026 13:18:05 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1aVlpiQzZqRXpqNjNjRG0tekRpOE85ZlhzelNHVGFIcGw1aE5RSDJYRWZTWU5JUXhkTmpNeUFIX3FIWlAydWh6T1JlQzA5S0dEM0U5NV9WcVIyRFlKQ2xubW55U3BBVVdCNmVrWUNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQbU1rSVVnWFk1VUtMV3ZmVWlCUzd0VFFMR1lDVEc4SnhyOWxDZlJxV1BaOXRlNl9iU1d5Nlh1YlRqSmh0Z25DSEJFUFFMRGpnZFZ1c1lDRmJMdU84VUtzb1RlOTlodkxBTDRENlJRdDFsU3V5OTQxd2hEWC1weEh0cl9pSHEybE9aZ1diWEgxZlJJa0wweHRR?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AI In Robotics - New Position Paper - IFR International Federation of Robotics</t>
+          <t>Risk without borders: the malicious use of AI and the EU AI Act’s global reach - Real Instituto Elcano</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:10:49 GMT</t>
+          <t>Tue, 17 Feb 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1xNmVSVWNmVUV0cUZUeWF5c2llWVA4X2w3NG14NkNETm9xNkRoU1hySnlnTkdBQWNCSzJ5MXN2eUU2bWpZUU9iUjZFdTZEVHhBc0hULS1QYUJQcnJ0U3dvSElHSkxOeE9NR1pNMXlfaTE4VEhWa1VWbTF0QWJBdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPS0E0ZHppWEljRDdldThNRTNWa29fMUE2YnFJaUpNdEVzLW1pM2hTYnRFcjI5X0lMUWpmODZ2cVJOdkxRcFpfa2RTQ2hPYTZNSXB4SHNiM0RSYjRsU1B2YmtjaWZCR2p1R1p5dGRqMmtERlNFMmlibGdYTWhmc0VveG1TVldlNHVISi1Ecm5VTVNzRjF4X1Q4ODBzSy1vRlU3VUROd2J6QV9oV0pNbVZscXhmbnY5ci1oTy1ESjFybG54cGM?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>World Defense Show Day 3: Saudis eye AI, and a local defense giant transforms - Breaking Defense</t>
+          <t>Agents urged not to use outside firms to tailor websites for AI - Estate Agent Today</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 20:07:25 GMT</t>
+          <t>Wed, 18 Feb 2026 00:10:10 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1WQ0lTOW9fbVhrOFk2ZW1jdUZpU1VJM25MUEVlbDlTZ3hiXzAzd0tFWTZTYzVGWXRxT29fRnd4dGZma1FNZkpXSU1za1pnVmFibGsySmhzLXNYc0t0RnlCbEM1azcwaXlkZVJobXpxNXBpSjdN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPZG1RSldnM2FpdDVhRnBWSXFwbnJlMjY1SUUxZmF5TDZFLVJaR2FmbjlYWUZIZzN5aTNJaFdfRmhJcS1PQU1MWXFEdTVhZTY4ajFwVDdxZFRmV05tS1VpODJLNGNyaE5sTlZudk10ZVhKLXdJa29vaEI4OXNqRFBObWVON3NYRVNEdVFyMXEtV25mV2JZVHVCQWxxNGdwU095MnhkdTI3SWQ1aW1fQ1RNN1dMUmU3MS1pVVc4ZnRB?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>'Introduction to AI and ChatGPT' workshop in Haverfordwest - The Western Telegraph</t>
+          <t>Claims that AI can help fix climate dismissed as greenwashing - The Guardian</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:00:00 GMT</t>
+          <t>Tue, 17 Feb 2026 08:34:00 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPbHVBanRLX3dTQnNiM3M1SWRSM2tsSy1YRWhHbjdhV3Q3RDBwMHZGQ1ZJcmlTNWVRbnhqX0wzZXpuQ2dRMWZZcmNNNFN0a3k0TUJGTXJIRDF1VGgtSkx0ZERCOWtuWG5FQmxvNU9ubDFCUm55NVpWRDB0Uko3R2F0eVVoNks5czFNXzdRcU1qdkMya3Jtb3JEMW9kWGlIU0drV2xNdlVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNVkhjWktRSVpwRmxYa05yZ3FYU2x3OFRkR1BWZWpoWDdncHczMWE2NzEydjZmMGo0eTRTQWtXRWpOQkpTWTVRQVU1ZVNQX0x0YTBuUnNzN1Nmell5R1JxellLSkx6aWRrb3d6MjF1VWlRN3hNUHZlMFNzZDhCWlBWMG5IUEgydVNvd1FpS2RQODhBSTdwU09VelBobFRNbEVaZzRaaDlRRWlhc2RkNHJYZG54ckZ4NFE?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Airlines' tentative approach to AI - PhocusWire</t>
+          <t>Brokers should beware consumer AI and hike data security: Mortgage Brain - Mortgage Strategy</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:04:02 GMT</t>
+          <t>Tue, 17 Feb 2026 09:58:50 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE15Q0Q0VVZhY3hXMHcxSzR5REt2dEsycGY3X3d1R1VHRnBCOE1sNDlMRllJX05DYzFCQWZWYmFvRUs3Y0M1QlRqTGF6X0pNcWF0WFNfakUxTzlIZ3Mx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQVE16OER3VGZLdC0xZmVsTEVpOVBoQUpGcmw0RWlzQ2NZNFdGdU56VktpTFhVX3JZT0EtSW9NQ0txS2tlZS1ucnc4WFl6LV9WTWM1WjZlZnl0Y1hBX3BLOE0tZVdoOUZHWW9RZW9hX210TlRwSlNIWnl2eTUzR2F6elVEV2RBVnNXbW5BQW1CaFBCU1NDVEdDMXNIUVpMVmJ2anZKQW5MOUR3N2t0R1Z0ZHRn?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brandwatch and Blackbird.AI to deliver advanced IEAC to NATO - ADS Advance</t>
+          <t>Donald Trump’s AI push fuels revolt in Maga heartlands - Financial Times</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:46:00 GMT</t>
+          <t>Wed, 18 Feb 2026 05:00:44 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPVkFNd3ViOGV3QnRsZXJFbm1nNkJtQzNQVURwOUxMUlJxWGRCZFRmcmZxMERUOC01UU9OY29vMzJfQ1Ftal9obXRzVEVvV3gtSUhGYVpOS3NVd3IwRjUtU1NpbW9tWlpfRFpKX1MtcE9lMHNNMldNYmVCNFh4aWJEVXlnNDNIbXU5ZTNiLWRLcHpWR2U4NVhqLThn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5EVUIyMVloOTlUc1hjMTlLTGR5RWU1SFFKdGx5UDZQa0IyOUcyWlJNR05HV3FEX2s4eWtvMm9mMW5NWVdWUGtHWHFtdmg4Q09MZDRpN2dfVGc2RkhsQ3loRGpGTzVOb1hrZXZZRVBpckU?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spotify eyes AI ‘derivatives’ as new revenue stream for artists – says its tech to let fans make remixes and covers is ready - Music Business Worldwide</t>
+          <t>Ramco Systems Introduces Chia, an Enterprise-Grade Conversational AI Agent for Better Customer Experience - PR Newswire UK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 20:17:54 GMT</t>
+          <t>Wed, 18 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNRWVIcGREN0dDODV5N2gwUGZlVGR0elIzLS15TWJuTkZ4VmxrcTE4eVNRNDhCVzh6XzAyaHFvOHRIWXlQUE1RQkZjOEtyU0xGU0s3azhIYnR6d1ctbXhMMnVZZFNodTFxU3RIcGRhOGVwRFpKN3JKQ1VnWVp5Q2FMWTMtZENnUVdwTTgyeEJNMENaaXFZWXp2d0cyb19SVDNudVA1OERmbGFLT3EteXR3QzJaOHNwMGxVR3BTdU44TTgxXzVMMUZyamFEUUdjd2Uxbks3dGZvaDVQeUpmY3hkYVJSRkt1Ymc1UTQtM2QxN0lNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOZTA3WmdIcTE4QUtwTzdkV2NBcGh4WlMxU2QzYW81bjloSkxSZjZoc2NnSXkwWFMycUE5WWswajNvU2R3eGg2RWlFeG93YmxwdnlINXByanIzTEtHeHlrVVllUzl0aEF6SnhuQkRWUVN3OEpMclMwTXFIdmFsVVFxS0pZSUFPQVQ1T0tadjhGcERfd3plQjluWmNnZl9yUHVwWFZrVFU1NjVsZTlEenFWUkdjaWFDNVJHRURUa1E4OWVXdWtUb3p2dGlDNTUwOWtBcTF2U29rbHc0VENMZ05MV09qUDNwOTFVYkc1UV9qTU9XZ0J5?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>How the use of AI and 'deepfakes' plays a role in the search for Nancy Guthrie - NPR</t>
+          <t>Google Cloud partnership pioneers next generation of consumer goods technologies - Unilever</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 10:00:00 GMT</t>
+          <t>Tue, 17 Feb 2026 14:12:00 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBaVWdvUkFSRWF2V3VKalFvX0x2UDVvT2tVaU5qQ19ZVEFTRV9CQWtNSzdGWV9uZDdZWGhYLXY2NHNYdlJvM0FfN1pXSUNleWdpSE9XVGRSbWx3bDFpc3ZLOF9lUlhHQTJPY2ZtVVFkdEZUc3JSUFB6QW54TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPX044Rm10MlNjTkswYU5yU3NPS0VkWDVlQk5RTjRPUkgwRnBLTUE2aTg0Y01hQlRFZVgtZU1WLW51SWxBV0tzYlJyRlVmeEZwR09kZjBpbG5JaU1VdmRGNzluNWJfN3piZkpiUFhENm5KYUU1Z3B4MGlXZlYyYlNqX0xjd0pMakhjRU9GRVVIaTdtNjNENE1Nckd0c0lMOGxNbDFlNFB4cjZWckdSSUFyeHVrbC1mbkVub1FzZ01MUzhKSnZxRmo0NXVJMVZyeVRrMXJ4S2x2dWR5WGxOc2FDNw?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Experts urge Ofcom to probe AI’s role in fake news after major incidents - AOL.co.uk</t>
+          <t>Private Credit, Tech Issuance fuelled by AI, and Increasing Leverage Among Key Driving Factors Impacting Credit Market Liquidity in 2026 according to S&amp;P Global Ratings - S&amp;P Global</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 00:01:00 GMT</t>
+          <t>Tue, 17 Feb 2026 22:46:18 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1qODVTVTA4ekN0d2NrQnhrQXgzcXJPR1FRN1VrV1lncWVOOTd6ZkVyWEIxTlF6VTc5MUhiWngxTWowV00xbXJuSmRQc3lWREp1Zmc2UkRSV2MzWWtRenJDZHVuSHFudWZ6dE12SEV5enh4UVZuQWlOWmFBX1hYdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxOd08zb2JqSmJqVEFBMms1VXRFNFRKNV9pd2s5MExwTkFHV3NBZ2luM0pEYkF2czI1TnlOdXVKcDRTb0lkYnNRZjBGZlQ2ZjFmczk2NkRKenY3LWZraVhPQmFJQ3lsOTM1S1UwYlJMZllSUzBGWTFfYVcyTVo4eWxlMVJlaXNDY3lzcnJCak4yMEp0cFV5ZHYwN01tQ3BpSXlrbGxDc2JNU1I3Z1pmcUpaUjRSUGh4X1prc1pJOUpuTUdreENpdXlnc1JONUN1ZE94R2ZJU3lrQWYwZ2dvTTU4dTB4cHlkUEhxT1NYd0h5ZHdUR2NtUHFEOTBYMzdaaUNfSXh5dEd0SVYyb2ZkWFE5WjlaV25pRFVXZjFCVkhHdGZ3cVRIMHpSbTIzeFFiVk0?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Is AI getting smarter or just getting better at faking it? - Psychology Today</t>
+          <t>Why AI Adoption Stalls, According to Industry Data - Harvard Business Review</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 10:58:25 GMT</t>
+          <t>Tue, 17 Feb 2026 13:45:36 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOMmZOQXhWQldBVXA4Tmg3OWgzekRseW43cmlZbFFuVUhCTXFnTkFDTGNEYlVyZWdtakZzUlRGUV9OUjN6ZzlCd0JmaW9GNTh4QUlEdXhUSFR4WndVdnZ2SmljZXVQX3ctdlVhc1dmWlpFeC1HLVh5bzgzR3RBcG9YZzJFMWZQSE9aSlFPWXJaamFfSW9WVm5aNW90M0V6ZHdlTHFQUktuaFVSSC050gGyAUFVX3lxTE1LcUZETWdkOW9FUEhIYi0wak1DY3Bncy1XTV9qZVBFejlER1I2MFVyRl9MNUhXUnhndmYxWnJBODFsWnhPZVhFNDFRcUpGVVNEeXVycW5MYVc5cmFDNG9leHZCRVR4SWI1ZHlCUjhQZ2ctUElpX1I4cjZJOEdCYjh4d19Xcmh5TGg1LWR0NE44a1ZxZWhQQS1zZEZ4dXIxeG4yZ3Z3blNHQ0FNWFprNFBhMkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBUcE5UaWlJb0R3bU1RLXVvZzYtclB3M0tRajVITW9ZSXZTbFlfOWRwMHNmdGpveC00ZWtVRVpMS25odTJ3Wm95Snh5N2NVLTVITUxNUko0b3JMdFh2YzBDRDcyOUgxazM1TTlGRi1CdkNyYldQUl9RUjZjcDBZdw?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Empower launches embedded silicon capacitors for next-generation AI and HPC chips - New Electronics</t>
+          <t>Cloud and rain forecast by Met Office for Portishead this week - North Somerset Times</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 22:44:07 GMT</t>
+          <t>Wed, 18 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOQ283d3MwOEE0eDFleTFIM082VVlCS2FWZFNLeExqS1NWNU9MY0FETnpEd2V6ZnAyRTNDSnlxSXVuYVRMbV9fZnp1Vmc3X1dfcTNJUVZ2R1czYnFNVVE2b25OZVpvb2VVdGk2VkZTT01MWnUyRUJUU2JmOS1lT1p0bGREV0pNRzdtVkpEZGtUVjBlaTl2SUZsMjBzeDJxQlFkbk0wNHJLa1JjemlHdnpuYVJ6c0V3c294MlRidTZZRjl3OXJ5OU9lLUw5NmN5RnV6UFVad3VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZVAyYUxyV2txQWhOY2VQYUt0T0QwRGFySUdmZ25zQjBWdVpvalVTRTJla0l4Z19KQ2J0UWlaUGM0UkRNODA2Tmw2T056Y01HbEVyVDdNVklqOVhUTUJMTXJYaGYyNzNBam5XdE1COFQwdWR1ZjBrMkJxSjJtMVlxaHFRUHFwVVI5cWYyb2NfeXBUXzFubWhhcDNrbXFxYjB2UWVj?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>No, the human-robot singularity isn’t here. But we must take action to govern AI | Samuel Woolley - The Guardian</t>
+          <t>We need to act with urgency to address the growing AI divide - The Official Microsoft Blog</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:17:00 GMT</t>
+          <t>Tue, 17 Feb 2026 23:33:39 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQeTlqM19rUXVLZHE4Y2RzNVVSUl8zRDBvN2lSWWlHZEJTNW1OQWR0dHp4bVBVZWVpaWpuOU8xemxSOVpZNTV4dXhsZUJKTTZvT282a1FGWlBRZHloNmdrWmtpblliSnpEald1VExmWDFfUUVLdl9ZWXg3M2pWSkxCTURTX3pZSUItdXlLZjJHQl8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQOG9fTzA1aTZ4ZlJlVERDNnI0SWtvVVRJWjNnU2JnWUpyMm5sWEhOWUVGNDFJaXZ5YzI4VnFNN1o4Um15NTFSam1QRHBjbHpycjZzM2FUWXVMWnNZRzVXck5kWXNRUG80RlBuVTVINURrY1dZWmJvMHRnTzdVQ0g3YUNWMHRTc2hVX0k2ZTF6SnZTZ2VzUFhYbGVoNlRSOEJfWEhPU3pmSlhMUQ?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>A Silent Arsenal: State Hacking and the Emerging Digital Order - ISPI - Istituto per gli Studi di Politica Internazionale</t>
+          <t>FSS Future-Proofs Middle East Payments with Scalable, Sovereign Cloud Infrastructure - PR Newswire UK</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 10:08:38 GMT</t>
+          <t>Wed, 18 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNZGc5ZFZSZUpBcnk1aEFMaTdvVmhoSklrUVlwY2tGUTU1ZU01UTI4X3BDQ05CSjlId3VmZnQwVk0weEhWNEZRUERsUndERTR1Rno0aFJEVFhEdHROZ0lvbnZDZ01oTkdZc1B0d0huMHpKd19oSHUyZC0xdmVXdDZoczJtUFJiTWpqbE1FUm9xQ0pxbWNEYTlzZmVHbHBUNnR4MXV2b0libmZ2TEd5UXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOMnJsa25nU0I5cFM2enY1dFM1MURGT0VsNUJkT0VVOFVTSmxLU3M4NzhuWUpUMXIzRnNYTGs3Q1lVcF8yNFd1cDlVNFBkUDJjSnZ5dDZzcGxYbEMyQm1HNlhIVnVhM0VpVW1ma3RvVUpDN0FhVERTMHByTXR3WkY3M3c3am9NQWFSWjdHTzh2czRtWXVqR1F4eWdkTGFSS0V1YVI0cms1UkdBMEpmOEZnRUMzREZWODV6aUJTVklaRVYzMUpYcTVpcW5hLWEzY2RWQUotdE9fOTg?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>The Atlantic’s March Cover: Josh Tyrangiel on AI and the Future of Work—“What’s the Worst That Could Happen?” - The Atlantic</t>
+          <t>AI’s workplace revolution is here – and anxiety is rising with it - The Guardian</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 13:24:16 GMT</t>
+          <t>Tue, 17 Feb 2026 15:39:00 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQa09QUGtfZUZPX3hOOWFkZzU0dkVXeDE1YmY3dGhmV0pMVmlxUnphM2FaajJodXJTOGZzYkstaFhteTg2VmZ6bjJsel82TmEtVUdkLU03dnRrOUJoYnlidW1xczI3eHpaVFRsaUtYTUZDOWV1N0I1ZXlYSHpvYXA2dW1vem50am5jaS10VW9BaWFFVTJmZ2lQeVh0aXhyS3RRbVhj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOWFQ5bThLYTdnMVhyMENWblE3RHluTFpIX00zQ0w1V1JpcXBmTHBqTHlIb2Z2NmZwUDFvRDBsY3JPc3h6OVlGazVzcDZJaFl1VU1Kb3BKTW5NWEdaWjg3c2xkajloRXBtaTFHSmxBdUsxUWFPOHk1SHY5MGVZU1RBV2lEWGphUzlKQWMyRVlvckUyaG8?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AI changes forecasting — But governance still wins - Wolters Kluwer</t>
+          <t>Guest Post — 2026 Global Strategy Briefing For Boards on Quantum And AI - The Quantum Insider</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 05:17:51 GMT</t>
+          <t>Mon, 16 Feb 2026 09:18:20 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNRnF1SVU0ZEZ3LWk2RVE5eWhteGI1X3lXRG5qb0dxSmVTY1lHSDhPaGNiY2lXeGEwSk5TZUR4cllmYkhSelY5cGpHMDhycTlvOEhJWmpRTkxDLVBDdHhzUGwyUHI5dWY1VlRjR0JLcGQtZVRfRFI5ZWJqczZKd1FLNFVfRkdrX2VtZnRBZTZmRHg2c3hjQUZIZ2ZxTjhQdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNG5vdXE5VHNLZ3BtYUZqc0ZLbXlITjNjMU5EN1VOcFhnekk3bjVZRkdLR0NZMW5aeUZpQV9FVkVCVzhmUFJYdDRuNU91cHMwd21lMUYtbk00anIxMzk4R0UyM3pEczRwZmwyZlVVMmxxSm1wdVNHdWJmNjR1aE9rb2o1cENLWUF3ZnlSNFBObDFiMlFHRkh1dmN5QldodEQ3cmpJdlRhbmV2bk4zTXpVZg?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New National Cancer Plan with AI and robotics focus - UKAuthority</t>
+          <t>Could India challenge tech boss power at Delhi AI Impact Summit? - BBC</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:01:26 GMT</t>
+          <t>Tue, 17 Feb 2026 11:35:09 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPSGtUOGliT2gyd1FIdEQ3YXBOaGJnWk5MbWFNSTk3WURxWjE3SVBnS3Z0ckVORlNvMFVEVnU3TkdLV0EwLU1pbU9BeUg5cTJnXzNqai01SEFiQjZZZDVpNU11Nm0xakxzOWlwbjNZVE44X0dZMFBJTWQ2X3ZVbFlxY2NQcFJXOGZodm1iYXJESmpaZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBPSEtXQ0trd3o5V1lQbDF0NFhZN0NNdjRBNWo1U2RkcWhiV1E0bVZNa0Rmb1lxNkhkNExfMU5NOUUzNV9xWlFpbzIzU3g4WmIzYnh0NUl2S1dmdw?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AI will boost games not break them, says ‘Clash of Clans’ maker - Financial Times</t>
+          <t>How one chemist is using AI and robots to automate lab experiments - Scientific American</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 10:00:06 GMT</t>
+          <t>Tue, 17 Feb 2026 11:00:00 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9lWDk2MVhfY0JLM1ZwWkVhOHFrY1ZlS3J3RmxZNjBPRG45MS14SHE5eUxnNUs2TGpKNWxjNUF2X1Vha1hFZFFtSS1xY2t5UTh2b1prSHAzVEZsbGhxZUxaNXdqeXY1WlhfZ2d0bDYyeWI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQV3BWSTFCUGg1UTE1cXl1aXF2RjMwQzJiSnRnR0w2dXV5anhrajNDaFBTS3MxMkJFQlZDRlotbmF6cVVYUEhGN1kzdS1hLXo0TjdyTUxhVWJNQWllRXRDSzRtZ2FBa0pYRWxqVTdzRDE4c21SaFNiNFFSWW42OHpOQ21aZU0wTHp0bDZscmJDRGx4TWZHSzVTM0M3ejVIVlNmZnFyWUtDQVZ2VGpSN2Nz?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Are video game developers using AI? Players want to know, but the rules are patchy - The Conversation</t>
+          <t>BoE AI roundtables reveal constraints to responsible adoption - TheBanker.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 23:19:16 GMT</t>
+          <t>Tue, 17 Feb 2026 11:26:53 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNY3RRVGdBMHJDRWlkRkk5NGlVbXk0SlFPZTNWVFVmSEZ5S0VRN3RzODhqT2FqdUxvS2RTcUxkcEcyVHFYYVczUFpvYlpPUVY2Rm4xckFZZnZOOWZBcUdlTmFobVlRODB2TE1nQVZILW9pRVNhZkVrdDJLSk9YaURkVms2RmhJX3B5LXJZTU4yb1hWYUtyVkxBQ1BsQlNmWnoxMFpPR3lwSk1GeWNQbmFhRzdkeXB5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5yMVpQSzBVY0VxTVF5NTNOZ01jZVZVNUN6T2xQNFRPOGJXaEsyRHluT3Y3OXYyeFlIOGk2T1VCWmFVZldxT21NQ2gzU2taMm9NRlBDaUQ4YjBaQkJfRm81RWh4b21jZWFBOFZVbEJIRmhSZjJUN0VnT2pn?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Startup Stage: Altek AI wants to use AI to improve hotel guest communications - PhocusWire</t>
+          <t>Alphabet (GOOGL) AI, Cloud, and Waymo Provide Multi-Layered Growth Optionality - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:04:12 GMT</t>
+          <t>Tue, 17 Feb 2026 13:23:48 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9NeHU4UzZmTTZaVGhua1FGcE1OaVY0YTJ3RDVEUE9oTGdtQk1JTlBMLWRkNW1pVWd0bEowbjA3LXpxY1NXRHJxc2RxNFQ3eUNhd1ROb05JaFpKLVU1MFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPSFFDOWhDSWVmdEtXajVhRDkxd0FQZS1ESUtFZS10ejg2QVRhVUpsMjJHUHRNNDRfaGlILXE2Y0ZKaDdkMUhKaVBZdHN5NGY5V3RPMDZOc3M2OFVGaG0taE8tbXo0Zmg2dnk4eF9KT0swOThOQm52dU8xNXZySENWS2p6SGg?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>University Seminars Explore AI, and Also the Medieval World - Dartmouth</t>
+          <t>Musk is wrong about AI and retirement: You still need to save. - The Japan Times</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:34:27 GMT</t>
+          <t>Wed, 18 Feb 2026 03:45:00 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQ0JIaktHa2FDbFJuNTIxd1d6WXpQYkZsVkxaX1R3c0NwX2dERkwzaHJhdFd2R05MMGpmcEctNjNxVGNoWEx6Vk1YX0VDcXdxUkd0dXdIcnNmaGtYdlhrSTBwTVZJbDBvWmluQU5MOWNUd3ljWHAtWVV2ZndDY1VYeDNrVTZrcTZUQUZ2ek9xd29paVBheVFjWldR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOZTB5REU3NGxjeG9pZlUzek02bTFmanFpMnhERUJIdXJQc0dyOS1GbDdsd210LURDUGVDUkkzUGhycFh2OGk2MWlnTktoSEp4UnhiOWVia091U1JMN05US0NROTVJdFZJZEdQWXBwMmxGVVU4MkdMNW9fNUc1NG5FX1RZNWpFcW1kR0F3eWNMc0FxVnhJeU9J?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Why the OpenClaw AI agent is a ‘privacy nightmare’ - Northeastern Global News</t>
+          <t>‘Agentic with a small a’: CMOs are adopting AI more slowly than it’s evolving - Digiday</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 20:18:26 GMT</t>
+          <t>Wed, 18 Feb 2026 05:02:14 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1LVENWSG5FZElMZzNVUXplWFIzVmRwdU0xSnBvdFFiWEJfbXJHNDVzLWtXRkREZ1J3RHVwVkdkdDl0UDcyMk96OU5sNnI0Y2dNTTZlSWN0c2hIaFZRb3pBUl9wYnNIdHFHUE1URFBLaE02QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxON3BXX0t4OWMtU19KRk9tTXBXazk0UFhpUTd0b3Z1aFZUS0Jra0pZSXRpX1FLNUpoQ1d4dGZyX3NWalhGTnFuVUh0V2dHZTlSTTNpMXV4RjJMRnpMTm1OTU9nZjlpaXRSYy10eVZCYTFFYldTTGpmZjNmMkEzVklGOGVlWlBDVWZuNWd1Z3VLTmxuUUJhVzh6YXJja1RGNmRTdFFqT2taRQ?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>'Just working towards her pension' - woman settles discrimination case - BBC</t>
+          <t>How AI, Cost Pressures and Reskilling are Transforming Talent Strategies - aon.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:28:20 GMT</t>
+          <t>Tue, 17 Feb 2026 18:34:36 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE96ZmdRbS1uS0tSMVVlZHhZX09Cang2QkNIZEJlaUlrNFBEZXVoM21DQ2VoLS1JVUFYUkxKM2J2cWJtSTBMa3I3V2pFZ0ZuTWMwME1QQkdOZ0d3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQbkQtT2dxX0hKejd3X3gzcmJuSTIxS1hBVUdocU5ncHVwcnhUTkMtSnNURV95UmFSLVl4aEhQQWpaQ2NST1FqY3ppNDNVZVNMWHlYT0JnUldmUEF1WjNyMXZXYnhfa3gzUWJyLW9Jem9iQXBrR3RtQ2JzSkVwdlVIYXNZR2tLTXdSUk9KNl9JZkNIdWp5LUJ5bF9tazUxV0lwRDZrSWFJOGdDUXNSQmR2VWlR?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Addison Lee partners with Multiverse to build AI and data capability across workforce - taxi-point.co.uk</t>
+          <t>Questions About AI in Shareholder Engagement Meetings - Wilson Sonsini</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 07:19:59 GMT</t>
+          <t>Wed, 18 Feb 2026 01:14:11 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNNWszTkZqS2t5a0s4X3V4VkpROHNYQ0ZpU2d1UkZjTEpoaGlyREtDNFhCTHFieGlkaDBxWklyQlpWNmpEcG1JTEVrZW5mNk9Oa0ZEZHNOWmZlRHlXcjBleFlsQ1VvUGV3akY2cW44THlVZnlNNW1jSkhteFA0RW5wYzNIeV9uOWs3TmNFNWs3Zk1DaDZ5bmQ4R2xpTUxka1NKcjM5QmZoZEZmZ1haRUR2bU1rUDA3QU1VZWx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPaVlnb2FkT3VBSVdhdVc4TUdpVE9nSklldUlZa3ZHWE9EMTZIZjZHa0lLZlRsT2VUSF9VSEtMTlgzREFrYnhuOHZ6Tnc4V1VxTUNhUmVVMWo1VTUyTWV5OUIxNl9ndGlVOHJQY0FuN3NvTW85Wk5VdXdJSTRwRU44WVdFZHJDWElJb1lTSmFiaGl5M2pJWlE?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3721,27 +3721,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ransomware hackers say NO to Data Exfiltration and YES to Encryption - Cybersecurity Insiders</t>
+          <t>Bournemouth University receives over £500,000 to improve AI reliability - Bournemouth Echo</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:39:52 GMT</t>
+          <t>Wed, 18 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZWdaZ2E3Tng1VnBVN01EWnVweTNBQ3lpUk5EYXJvRWIyRWN6T2twWUM4dnZraEEzUW9OejdFN3hYLVczb05zYk9wU3ByaVZ6YU1mR2tuVDBiS3Q4YlR3RnVMVmozSUF5dWtzLXZJUmY2dG82STA1aV9YWUNEN3hrZW1DNkFDeTNTMkJBLThJOWt2b3NXcmhjNFhBcERFSVdYM0l1SVozSk0ySGlL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQTEVwX1JiRHpPc0xFWTU5RWRGTkxleDRkT09wZml5NkFQalBhdUNGOEl2R0xGYWFHZS15LXB4QjdwWEJiUFEyRDYwMW50U3NiLWhKNzYwOXE4QVl3aDdCRG1UekpQODJUdlk2dHQ0a0JkZk9SSWFtZ3k0aGFVMThmVEhLNkZaNU8zN2dlUlVqUm5sQ1M4T3QwZl9GTnZTU1d5X0pOYnpRTQ?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3751,27 +3751,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>The Modern Insider Threat: Shadow IT, BYOD, and Trade Secrets - Seyfarth Shaw</t>
+          <t>FinovateEurope 2026: From AI Hype to Operational Reality - Finovate</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 20:21:58 GMT</t>
+          <t>Tue, 17 Feb 2026 20:57:44 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQVXpXMVN1NDdoTk1QcldHSFlsWFVPa21BZ3JqeUltQVRzdDU4NlBGUlNLUk5EdEp3UWtJYjZDbVY3UE1CSVp3YTNqZzZiZWVIQ003NFNOcXZiMTlFZnRNUWxKdkJya1g5S09XeW1US09sWDl2cFpwenJHc3Vzb0F0NVBWMnFaWXF5cDNjV1Fnb1RHQUltYjhnZWdqU2ZGUFl0TnN1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPcW83OHFpSGRVNVFTa01rZVhvR0UtenIxUUx0V1ZTQW5FUU5KbXFVdmtZVk12cnFqTGItd2FEVXRSMGlqaThQN3VUSFZrUG1TV2IyVWkzeV81Um0yaU1ZbnBoTUxhU3hVR0lxYm9GX2Fvdm95STlGa3BWRVNXZm5LdjBybw?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3781,27 +3781,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>When Employee Misconduct Becomes Marketplace Deception: Court Clarifies Chapter 93A’s Reach - The National Law Review</t>
+          <t>HIVE Digital posts record Q3 revenue of $93.1M, expands AI and Bitcoin operations - Proactive Investors</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 22:17:46 GMT</t>
+          <t>Tue, 17 Feb 2026 17:55:00 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPWFdfZWZYMFQ5RlQwdVZfR3h2Ty1JYlNqenR4ZS02ZVBsQlMySjJTb01zdzJaUFBKcFdVTTI5LXRjeGVrNVB6aTZyYnVuQkJBZGhJSFlDN205S3E2SjlLbHZNUEN3eFByVVR5TzEzRkxRQnVwWWI4dVFlS1ZOd2R2azhvZ2xrdW5IcE1ZUHI0NE03SjF0ZTU1dUdPMFNSRGp2VzhpVVMxcUdEWFUydTNKTXNKZVFmM2PSAbwBQVVfeXFMTWlLdDQ1TDY4RVA4MWMzTExqb3NmSG5sV1ZiMEx6YnJvengyRjI5V3NDb2taX0lrbFdvY0pBN1UzdDI5NVlFV0pSVi02M1BlMmNNLUxBaDNWYnlLT2ZETE4zRW9jWlFxWG1SZTdad2I3NFlvTHhPS3JqeVBzcDMwYWR5cldpblpLZGRXSEcyT0lOV180VWxEb18zeGtwZmktbDN5bFQ0MlJIcktma3RqeENad0N1R3hkQTNEX2g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNWC1XVUVWUzN3VllfcFNJanlOOVFNWWFrZmFMQWRDV1I2U09EZzdYS3JUdTF0b1B3OG5YTFJ0R1hMZ29WbTlfLUtiQzh3LVBZTWtGN3U0Smx2RkJOWXFWbmV1cVh4bE53T0tZTlJWa2ZCNDVXSEhXYXdIbGx4VUIzUFQxRTJhSTF5TU9DR2U3WDVzUVVIYVhVRk5xdVBTYlVzeVl5d2wwd0h6cjhFeUExT242VVM5dzNHNC1TdkR6WFJsNWhTT3ZXLXNLbmtiWHkyLXBVTUFRTE44MlU?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3811,27 +3811,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CISA Guidance Emphasizes Insider Threat Readiness - RTO Insider</t>
+          <t>AI fueled massive surge in fraud losses last year, study finds - Supply Chain Dive</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 00:27:09 GMT</t>
+          <t>Wed, 18 Feb 2026 00:43:27 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOZTdrdENmRVJPOUloY0tKMEt0N2JQT2hrZDJmQXZ1cWdlU2FhQTBYbm1USk4yT3JNQ3NieXZuZ3g2aVo2VUNPd2k2YTJ4UFpMSGZiR1dFYzU1TWhNbDNVNmQ2VlcxZ1QySDRRblZ2cHc0eHVRTUh2RWM4bzdPZlladUp5eEFwMkxMelowUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOanZVdmZhU2hXZEVkWW9FcmYxYk1ha3JVZVoxaWxlMFRxSFlmRDhCUmQ5Uk0ydlBiYVRYdTJVZDE1S3VuYzAxSm8wakZYUU9EMGNaN2xrSGtVLW83NnhoMWdxV0pzZ1dJTmZYQVZmWVBFZmRncG1XS05SMkRJRUZPTFRmMi1OdHNkbHc3ZFZoZWpWd2k5QXdNWkRwUng?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3841,27 +3841,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SD Public Integrity Unit fields 47 complaints, 4 criminal charges - aberdeennews.com</t>
+          <t>Can the government trust AI to answer citizens’ questions? - Civil Service World</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 09:01:00 GMT</t>
+          <t>Tue, 17 Feb 2026 13:03:29 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOZ0o1WjdvUzZQV2YtWTZDc2JMU3RjVWtPUVhvOTlKYUEtY0FzUHJXWUV0eFdtYlZzcTJXSzFNeEJiZjNHQTFvVEZyTkNFa1BVWUlSd2lOa2dkMW1OSUdaSU8zQnItSlk5dXN4T0FJb04zd1ozWHRXdENzTGcxTVp5cWo4MnFZbkxiLWpMc3pMbktGdXZLWVhFc2Q3bUkwc0tHQUE4WV9ZTHoybTFRLXBPaHVkbFVubUlnS09mam9ndEZwOE1fMnBUd180M19YbGZteS1IRGFjN1ZkMlVVOHA3SzhzcDJxa2pieFNYV2dsZVdTQTBfeEIwOF9zaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQamZxMm16UkF5RmQxSFJPMDNlVFhkTzFEZ21CZVNPQk1DNURrRU02bHB4VS1TWkVOTXFoUkI0NHAyQnRLTE9lN0llYzM2TUc1M2oyZHl0V01rOGduN082MHVsYThPeHBLRTl3VlFKYUpORXVuX3U4RllzSDQtOWQtc3dxS2pQUGtmTlpLX0hsNDJxTld0aGZfWUEyVWtCVVZlR3AwR0tIQW1sRm9w?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3871,27 +3871,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Insider threat cited in $22M Iowa bank fraud case - American Banker</t>
+          <t>B2i Digital Supports AI &amp; Technology Virtual Investor Conference as Official Marketing Partner | Corporate - EQS News</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 21:22:00 GMT</t>
+          <t>Tue, 17 Feb 2026 23:11:12 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcUhMQm5HVzBqRjVKY2NoYlBDNnB4aTdJYnpnb1R1d1N6empJSHBHRGVGN0NqUVI1QmFackp2VWVub0hCR1EtQVNZOVJSQ3JyUzBqU0ppTWtyMl9STzd4SDFMdmJrZ1VkQkZBSlExTkpOa3JNRmotWkczQ2hsUW5EdWhDUUdVZHVBVFpjeQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNelVMOTVEWGVFSS1QVjB5NkZ6c1NoZS0wMTlDYTlPckFoM050d0JHck90RGI0ZmdIdWVqMlNfRE1TQkdabVlQTFBBRHhkOUZ1Zk5JRlota1J3bG5EZXE0MUp3MmYwLXlVM0xuMG43X284YVh4VzNLdExhZVJqdW44N0hXRmxDa3MwNTl0SVRZc3hmUzc2dTRHcFY4dFNZd3l6dG9CdG9uRzJvWWNuLS02ZTlQdVJJLXhCS1NQUjFKUHBRRTh6YVEzMmhqQ2VNWWtGX2ZWTURHeC1OWVRNZGZlaDExUGVZMlNSd2RsazJ6QVFkM3pxNVF0U0xpdTBMaUNjaHk4YmlMcw?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3901,27 +3901,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Warning To Under-18s Over Social Media 'Jobs' Scam - West Yorkshire Police</t>
+          <t>Meta Builds AI Infrastructure With NVIDIA - NVIDIA Investor Relations</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 11:08:44 GMT</t>
+          <t>Wed, 18 Feb 2026 05:44:17 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTHhVUEg2NUt1alJ3azBXbTN3dFNaZzk3YXIwM05PVENXZ2J6THByWHlwR2lybEJWblQ1VHJTRld5eWROQXdueE83SGVzUl9oTjVjUlJwYmt5YlRLa2lkZW42clJWSnVSZGtJdFYyMWc0d29tZXhUQUNVR2tiU2FVNy1kOG1NeksyRjlZd0JIOGJzbzYtc0VDQUFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQMkprQWZPNzUydGVZX0IzeXVEWkd4VVBsVHlzRk1LaGRlcjVOYXFhbmVmNlRHRHMzNGhTMHFmTnN2azlpcXRsd015YVJBMnVNVjRpWFJSalNQZ3Ryc0hNTThMOW1QTEY4S1VlWlMwZktPcnJLdzNiRGhPelg3R3JKUVlWUGxWM3VWN3ROY1RTaVZNbVFsNVJyQ2FkYk5mZGhMZ1NqejlOYkdReU5TeXpUeFdKS2o?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3931,27 +3931,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Revealed: 95 billion scam adverts shown to Britons on social media last year - Yahoo Finance UK</t>
+          <t>AI Compliance Monitoring in UC: What Works, and What Backfires - UC Today</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:21:26 GMT</t>
+          <t>Wed, 18 Feb 2026 05:54:21 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQcFFPNXRBc3UydUZ4c1BqN1pPRVlaZWliNEV4amhiUEwzRlNYM0xac21GUkVjaV81b2ItWEw3VHlPdFZtM2RtbmI4eW5IVVRmZGNvaGNRMmdkRlhXeE9TYzc2aWJhLVoyVUZQSkxaZmRJNl95MWxoNHl5Ti1sWkZ6TVNQZ0ZsTkIy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNLUEzWWpMZm15dUV0SVlmYVF5Y2pJaGx6Y1FCYTBtRnZrZnZxdGkxTzV4eVNtZFhvUDE0RHJfLXBBVGctc0h4ZjZKakNTSEhvWlZua0xPTUZqWlRSeUNHbzk3RzI5TldWSnAwank3Qkhnakg1cHU5enJDRHFVODdYc05qYzh1RmM?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3961,27 +3961,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fact Check: Social media posts misstate UK costs of asylum, fraud and tax - Reuters</t>
+          <t>Spain steps into 5G Advanced with MasOrange and Ericsson - telecomtv.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:09:18 GMT</t>
+          <t>Tue, 17 Feb 2026 17:24:41 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNU3pNSUUxZkhySnBMQ3c2YkFIRlU0dTdtZk1ZblVsUENJalM4a212czdVREVIYlhUMTFQNnpTVjJ3WUdMYWdqV0hjM0ZFV01KSUxwa2ZNODg5Mm1wZ1FZbVVNVHFlMng0REFuUEhWSUVtMTczZDdDSjJuWkxMbDZxTURsaXlXalNhVDNUbWFDNTdneExsWnVnYUQ1U0RSMW5SX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOMFZXMkg3QW1nNG1BSG5aWS1ibmd0Z2xPUVZvQ0RSOXVIRUtBT2ZoV2Q3eG94eFpMMVlDSWk5eW9oT3BQeThQWlhWenc5eGlVa3BHMldBWDlkQktvbmhEc2tXc2lFUzUwV1hZTk43NHktUjhtRjZiZmRKRUdtNjNfUjIxclIwdElTc0FwSkFWX3N1NGpKbmVVT2VGOGR1T2VFcGfSAacBQVVfeXFMTW14ZHFsQ2NGcm0wR3lSVGI4eWZTZU5iVzdJZWR5dzdGazNGSTdGZjViRUpEalNvNDEtaXhhYWQ2QTFyWnBDRU5wWWFlRk02T2E4a0xSZ05nRjZpS2FIRWRQblpsbzFNWE1rbThZQUMwOTlCNFJ0M1VYX296OVVqdXZraGZWSjJuYTFzY1hDYTJQREhWTFB0MjhpN29RTWU4UDUxQl9senM?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -3991,27 +3991,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Don't fall for this scam on social media about a deceased Charlotte County deputy - Gulf Coast News and Weather</t>
+          <t>AI and tech stocks trading lower 'due to high capital costs' - BBC</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 23:04:00 GMT</t>
+          <t>Tue, 17 Feb 2026 17:35:24 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOMGlibF8zWHo0aFFZaTVkanVybG5MYm9uNHBJRjVnWDlBREh2X21Pb1B5d3c5T0FZRmVPQ0tvNTFzN1RTMTVtRmFvUWdaang3V3RFQ1ItRWxmZzVhVkF1U3pnV3FtVWdqcVJTQjhxOFY1YXpMYXpHcXVRTDRLWHpzcGJXenBHZENyR0NPMmd5Yms2ZEJpWDIybGRDR051c0R5QWlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQekhjVTVueTE5NDZLVGt5YVZmYzE3WFVqemp6RDBqZVF2QnJUTUdQeV9RT2NlLU83V0VxZWtLNnZabzlCOU1tSGVvN0h3WG5KV2VwbEF2U3JnamliTFZmVnBQTll1WVQ3OHlYVDBTNDJqQ0VmaVRWaVFMbVpEODB2SF9TQUg1QXMxdWZjZXpnOFFOQmhrdm9JUmxGVGhBZ0xi?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4021,27 +4021,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ESET Threat Report H2 2025: Phishing and Social Engineering pose biggest cybersecurity risks for South African organisations - ZAWYA</t>
+          <t>AI and Uncertainty Are Gnawing at the Edges of the Job Market - FE News</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 10:50:43 GMT</t>
+          <t>Tue, 17 Feb 2026 04:04:20 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOdlRIOHdKYXA3V0l4SWJCNXQyQmVYSUF5WXZmWG52cTRNcTI2cXJwQVoxMzNXd09VQzJYNzBUTldaVEd4cjhuX1cxRVlxM2VhckRINUp5a3JkSmExZXd2bUp4NzNxcEVRQnJ1VG8tblg3NDRGSnNscEc2NlJ1eUg3dFVLcF9wWklpVnVrRTlCa0NDczBveEQtSEk3c2xNSFdvT3VwVHRKU3RQanFpdEx2a1FOOGFhZE9VbnBtcHhLYmpMN29wajQ0UzZYYjVlZW1yZi1wUk1LSUpzclc4OHhkckF3TE9QcWtnaUJDRG9URm1aYmJHSVVZZWZtSHNIOFF0TWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOTW9MMVd3b2Y0cTZFR0FpS0hOTzA4RzNqVFFKMnhDQTV2dE5xRzFqWFdQZ3BhMGp6VmFlT1hVbjUwVXBmUUItNHpLQUNBTXQzTzBzeUJUNF9kT2I1Uk5ZdFNvTFd5N3g4NW43M1FUaE8xWHpLQzJ5WVVJV3FEUE9fbkJpZWxNOGpSaGZVZjVzaWRIZXZGaUNRZnZ6dm5rdw?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4051,27 +4051,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New scam spotted that uses a calendar invite, deepfakes of CEOs, and a troubleshooting program to create backdoors and data miners - PC Gamer</t>
+          <t>The Future Of Artificial Intelligence: Physical AI and Humanoid Robotics Are The Next Industrial Frontier - FII Institute</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 12:37:21 GMT</t>
+          <t>Tue, 17 Feb 2026 07:35:09 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxNNFJYLXNNVU1lOTRNU3FqcGFidUw1Z0R5ZUtaenE4NEJaLWI0QzFkR3pQOGVSR2t4QzhOckRjWDh4a01jcFF0bXFib2xGejFVWlZkUHZPalVqbEpnQ2hGd25RUVBTVVk0WFItZ2hwQXV0MXpqRzFrMDAxNmR4MHRuUTBkdGpKQlg0Qlp2ZUpUUl81SURydjcxSXRwVjBmWGZrdk50d0JDeDlPaWZqYUhzTWFFZ3ItNUxfbEZaczJxS3NQdTBuMzBlQW5HUkRHdVVfZzBXYV9JNVE4LWplZzRVT0VoR2hwWXE1SV90TUE2MmxMbjVGSDFNNXhtTmZoYWtKQ0IzRUQ2Rlc3WENFNlBhekw0SXYzR3JJZHNWY0ttWVl6YWxwbXZjSTdYZHRJcUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPZjI0SWR2NTJER3NDT29KRmZuenZ0QTZGWm5Mdy1BWGNKTjd5T21iNHpPY3BJeTRIWEtWcFlLYVgzczUyb29CRkMzNFpsR2tKUTBpOTlJc3JLUHM2YXp4eU9LRkhFdEZFTVhueXhkUy05bGZXNnBZRk1WZDdRR0loVV9xaGR5eGFVTlp1Q1NvdFFVWjdxbGVDVkxxWmtlS3ZidlBJeTJMVTRYanlwMFVTWkxZR3AwSWd1UFRseGxDWkZsTFJSLWNCZjN4TENXS29JMTMweGFTemVQUQ?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -4081,27 +4081,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>The anatomy of a small-town scam: How glib talk, social media reels &amp; smalltown dreams fuelled a big scam in UP - The Indian Express</t>
+          <t>Dassault Systèmes Reveals the Future of Scalable AI for Connected Industries at MWC 2026 - Dassault Systèmes</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 02:39:14 GMT</t>
+          <t>Tue, 17 Feb 2026 15:33:48 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPYnpYSDdLYmZ0Wno3aHc5QVJpWmF4Vzgzc2tJTzE5QmNERE96VWNBVXFPQUdNQWxaaWRsU0N5cDZMYVhsaUpCRDB1a2lrNDhaNTNIUUVKSHBCZlVmNkRqRGhZUkRVYUE0UFB0NTNROXFmLXZaVlRfV3hjbXZqbk9CQkM2LXlZUkN0UWZGd1JHczlsTERNRGU0REpQMWIyUkEyZGdiekNNbWdOdkhwakNsTUtFb0dqOVM5cUtyV1A0Nk1KemtxWjBtc0VmbFZ4c185VlhlV24zbjBDc3c5djF3Tzd30gHoAUFVX3lxTE1RUGJJeDBXajEtQ1VmX1ctcTdrZ1BXMzhTX0RDNGQwR0xRVUwxdTEyWklxRlNFTGppb1I5bWwwZWhwYzdTZWVSRkd0YWd1ZFZUNngzaVF1bXJlaHdEdjg2cnFPWk1QYS15ZWJRN2gyYUJ4TU9UbFN3TGxMMnB1anJaYWY4MDJxeGhGN0ZoZ1ExMEozcllUTm11bUhNX25pbV9yNzlteS0zNGlOYXdvNG84UUUwa0Rtc0FpaDBVbllIZDBaa0JOamdISV9HN1AyZ211RUdVelVKZDdxeHlJU1FlZHRKck9UMVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOUThMT1VEVzBYanpzOFJTYjBTUUZPaHVIQ2xLVmptRGprWWVfSXM4ZkI5ZWpIVTgtM3B5Snk0NVB2S1lHUk0tLVVPY3Nuc0hGWVFUZllkS0Q3WHBOWnlCdzNPYUxfZ2VmVm82d2F2ODg2dkRRWG1lYjI0MEwwVFkwMXBuVWNDYWpPcldJSm8yOE80YVV6MWxiS0ZEUHJoNWItRHFRMlRVVkh0YVhwZ1hEM25LUzlkTnM?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4111,27 +4111,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romance scam alert: Man dupes woman via social media, Dh194,000 repayment ordered - Gulf News</t>
+          <t>Too little, too concentrated: why AI start-up funding in Africa needs rethinking - The Conversation</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 07:56:33 GMT</t>
+          <t>Tue, 17 Feb 2026 16:05:39 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOWjRwSzljVk1Db3o2NzB4a0hyTW56dmo5RW5zVVRwVnh4UkRBU2xQMloyQWdrSW1hNER5eDdJSlBSMDhlb3dyQURzOUU4NHlxVW5MT2NTLWxWeGlNWjZRM0t4TXdDQWRnSG5RWVFBYXRWdTlOY1VlZ0NwbUpESnk0a1RSQ1lBM2QtakpBeXZLNXgwQ01rOXREcVdBWUNiVDVfSXYzU0JUdzB3SkFPOV82MFFMMVFLYkpVdDU1TDV30gHQAUFVX3lxTE1tSjItbVNNRUNTS0t1UFVkNk9qbmIwX21ZU0d5SjNHVU1JN2I5X0F1QnRxdnNOQlZkLWRCR0Z5UXFWUlpON3YxNXlHZVFxUnpGZTRSS0YxRllRYS1FYnVJVm82Wk5vcWY3MjdiSnpIbkdtaXJRN1hPbzdnN2JMTUtsbHQtSHR6Y3prY2M2emNUNlJYWGIwV2V2d01mMFhBNmZJWWFxVWNkYzVqLW9uSVdhSUJRVUN2RWhzamhrNFdGVzlPTklQNjVSd0JnVVJNYS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVGZRMGZpdldHT2NRaEpRcjJtNWs1XzZINExCSFllR052cVl2bkxqWVR5TmNaeXF0a2ZjeHE5Q092OTBLdUhWVUY3TmhiclVtS0xlNjNtRHNCLUtmb1pDT0JYelNxZnlpVnlzczRNS1dLRURFZ2Nzc1RNbEhLSmFYLWk0MGtxX0JwUDdWM1VWdWFBTlcwdEFkM3RPN3YxQ3JIUVhDc1BjNHBMdnd4cGdlWDMxNA?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -4141,27 +4141,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>As Minnesota cracks down on fraud, some lawful social service providers struggle to survive - Star Tribune</t>
+          <t>Is AI sovereignty possible? Balancing autonomy and interdependence - Brookings</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 12:06:39 GMT</t>
+          <t>Tue, 17 Feb 2026 18:36:19 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9wQUJFY1MxblY2bEN0aG10RVZ1S0RCekpBbTZ0RWIxTnVZY0xZbFdrYWVpZThvV2ZfYjkzVms4Vjg0Y2pkbE91X0ptLWs4NWFSTHhKbXB0VXpXeEMta28zLUNmd2NWUjcyS0RoMlFBdm11Q1FuUjlycGVRSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQcU1qSkxCQmNQLTVySWVlNWktaGRmZ2UyVU1yR2ROaHltS0hwY0QwQ1VnLUh5RlhLa0hGUXRIRlV5cVpiUGpmYkRraVlTTEpydTFrVzlwSVBoZ3hjQ3dtaHhXQnJvZ0RtZmNyaFZoUTlubG5RRE81VjJHTkF6YUZUZWFvcUtrUWVKdGdVVmQ0b2tMTzJScGZ3ZWFTY296cms0YXVF?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -4171,27 +4171,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Who Is Zyan Cabrera? 'Pinay Gold Medalist' Scammers Are Using The Name For Alleged Phishing Scams - International Business Times UK</t>
+          <t>NTT DATA and Saal.ai Announce Strategic Collaboration to Advance Enterprise AI at Scale - NTT, Inc.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 10:23:00 GMT</t>
+          <t>Tue, 17 Feb 2026 10:06:16 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQOVoyNGdZTHg5NnA0QXRfeTlTbzdRNlJWMlVGOU14R2hjTzVVQkR6RzN1TDMyb1MybXNKdHRfbHhmT2RvVTljajVya2pDOVZJQXk2NmxqY09IelE4ZHFnYTRVYkdndHZjYW5VS1dFMzIteEhnVlQxSmdPWWN6a3gyR1NiT1ExdHdRVk1vVkhwQjl3NDFPXzhTLThxQWdnS1I5ZDctZ19hSDNLOHFrZU1mdDNfRTJ5WXht?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPa1JFdzZxaTdPZWtUTVlYNnRBZ2tCZzJKRXNiN2NNS256dWdfemRMeUtub2ktakZpakNLd2FTem5RRVRpbUpUNGcwWnRTcGpURjF0d3ZndzhmZ00zbmRvVVZZNWRYdDZEUUdyNHdHNHJCNHVKMWRETlVLRmtvUTBwMXNOaGxTMjE4Vzk0b3Q2Y1hxb0ZySE1Ebkd6RkJoaUdNekFxMlZVYjVzbC1kNlJ6ZzZrUUxXWDNOS3Z1cFpqd2pQMVZUYWRUeVpR?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4201,27 +4201,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Oz alleges Maine ‘looks a lot like Minnesota’ regarding entitlement fraud - The Hill</t>
+          <t>The future of European cybersecurity: Why ENISA’s recent expansion matters - GLOBSEC</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
+          <t>Tue, 17 Feb 2026 14:45:01 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxONlQyU3Z2b25RMk9UaDhXeUc5bm1oTHlNU0l5aDdubkJoU0hpQkVpbGxHNEVXOWFuWDhHYzdMYlY2dWJ2YmFjS1hyakRjekUzRmFsbTN1ZVZzTDZrRU5VLXVOMWdKQk9DRmJWUDJ5X1RXLWc4YlJ0NFJJU0didXl1RFJLZ9IBiAFBVV95cUxOU1h4b0JPdUhnR0RwTUFiUVVvaGtYVzhhVTJuMTR0d0o0bmdKLU5aX25iZFphQ2hRM19pRU1KX3ZYRW12SGdaMnF3dTVoa0tFZHhKeWRBajZneVhjdFBfZVg2bGs4OXdOYjdmN2xJMVRFR3BpNzZOZzU3di0tV1RvYUtRcG5DaG1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOXy1lRTBLMGJ4a21QMm9yOGRGVURGb05FZWNKNjdGb19UbXNkTm45MGhqMERKcDV6YmxIRGVrUDRGSmZPTDlqMExUVUVGUEtUd3g3aWFQSlFiQmFTNU53RVpXbjNFN3lHYUMtVDR5QkxUU1BQbHFlSmlFWFZSWG9oQ3FR?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -4231,27 +4231,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hamirpur Judge Falls for Social Media Investment Scam, Loses ₹6 Lakh; Police Register FIR - The420.in</t>
+          <t>The New Insider Risk: AI Changes How Data Moves Inside the Enterprise - HackerNoon</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 05:34:33 GMT</t>
+          <t>Wed, 18 Feb 2026 02:18:55 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5yQUF2ejV0dG1MOWF1SXoxeXA3bUh0bmJodmh2bVRwaUVMT2s5YVNNcnpQRENRWG1pemJNMHpxOFBfRzEzN2xESUJ0b0lMZXlBQ2RacDdPN3ZzMnVETVd2V0w0cXRSa2tCMUFhaUlfbWQ1Y1ZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNNWxWc0RsQzItaUFfVl9QeEZWQVFENmJwYkRwSjFpNHFrOEJpbDc5T3BvNTN1eTZpcWdzcWxXaW9aUjh1VEFjaUV3akdibTVxNGtnNTU4djQ5UEZFTE1sU3d1LXNJa1RFWWEwUnVhSTJ3NWJ0LW92ME9fSWdhbm1sLURRcTVaRlA2STdjRUtkejlRenphVVE?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4261,30 +4261,330 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Comment: Four insider-risk trends engineering must watch in 2026 - The Engineer</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 14:19:51 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZUt4ZEFMeEh3YW9faTZ1LS04aW4wZ0ZFc0JFdjRXZ0x3LU00aHRTR2ZXenM4N3F0dE5QeTZ3dG5GX08zR3YyRGlzZTR2cXlfamdXM3FRVjhRdXNxQUc5Q1VuOWFIdmJTYTVQRDFXTVdIdTg4Z3RrZWlIeGNlX0E5cGpBVFQyazF0VFRaTnZUX2dVdnM0Z25ZdHNuMnJ6c0RmbEtz?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Cybersecurity and insider threat risks - Nixon Peabody</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 02:43:12 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNOGRJSldlcFBxR2s4bzg0SjJTanZVRV9BSnUzaWtxaTVkc1BvbUhmMThnUHRyTEYxYzhrQmZiSGxYcUIzSWV2eGxsQ3VCZ05SRG1kSHNJRXBVZ244VTRhYXE4VVJtQnVKWUpENFV3QVlVOEhXNGl3bkp1OWVsLWRHbUw3WjROdkJkSkx1N3oxQXNyeld3Skhjelpn?oc=5</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Trump seeks crypto donations in Super Bowl pre-game show ‘AI’ ad; social media says: ‘scam’ | Hindustan Times - Hindustan Times</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Sun, 08 Feb 2026 22:54:45 GMT</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOQ3lsVnpYaHp5bXZKR3RMalBKUVlHdTJyRXZpUklwdDNJcHJLa1FpUzJicGZWM3lZNlR2ODUxTHhPNjBLYlgtZmQtWnR1X2tsT1BLOEFlSVl2M1BRVXJ3Ti1Zc25JUFdqNEVrMGhNbW1Bd25ubVZ3cGNOUWNwWlA5N0dHaVU3T3Y0U1N2azZpeXVYM2cxcDgtbVlmNkJYeE9pb2ZPejFTa0M4cGpyWHE0Sk1IN2oybjEtbk1DamY3SjJ6bmFYQzY1N3RVeTRSQ3RmVzBQWjBRbllTNDBIVWd2SV83NUJKRmRpZXphYy1aTdIB9AFBVV95cUxPU05sa3pSSHczVFZPZWE4N2tZRXM4MEtRQTdZLWl3MjlVMjctRWROMlc3Z0xLRlNrZDROWm5FUmtRbjhxS3VqcG5BdlNleXpKcDY3MmxsSUVWb09qUUxhaFNtdUpyQmhtY1Y1NWhLaW1kUzVtN1pEdnhBNE55SDRJWXRBYW1FTTVfbVZ1RmsyZGZOR1V6Q1VjVnFNaVZlMm9acm5uRjIyMTZtamxyeUZFS1J5TldwTFpUSXg0aVNMR1lzSDRLVHZEcDVlRGJoSk81TmJhb1RObmdBb3NsQlFYSUFqYV9ZWlFJclhNTk5SUXNPZDhp?oc=5</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Suffolk social worker fraudster handed suspended sentence - BBC</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 15:48:29 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFByeTUyaUYxWjhiMVJjeHNTVXhyTHdqaDZ2bzhhTVJTSVZwVXR1eTdMZnk4WWdMV2x0bnlxY3V6LS01S1lXSW42VkplZG9fRGlfQ2k1TkpMTUlwZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>‘Fake Flex’ Trend Raises Alarm Over AI-Driven Fraud and Social Media Illusions - Koreabizwire</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 03:37:14 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONGF1eUN5eU9EZzg4U04tXzViQlVYUjk4Q3d3TzZha1lPRWJQd0VLd3ViSC10OGQ2VG1Xc1JGdVFDTk1tNFJRNVN2aE9ySjdaWThtSDdUaGtmZHRBYUstdzlQdVpSUDFUaC1mY3ppM2hva3NfQnkwU0E5ekhKYkhLMmlJbENDd2otcWs2NjZSejFMNnluMkl3aGNjMENzak1sOVdBV1BGenZUZ0k?oc=5</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Egypt arrests woman over alleged Hajj visa scam - Gulf News</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 12:46:30 GMT</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSFdvWExQTGR0LWljZEdBZ0ZiUkw2MFQ0OVdQeU9wNmxzR0lBMm1vMkZCQnRZMVJwSUc3RUpqZ2ZFMzdPTlJodjBQOENodmNsMG0yT0NLYmJld1JOU2t3Qkp3d2lPeC1aempuV2x4Nk9pb1JvWHdBSlMwYkszZ2FtZlNwZ0s4cGJHZWMwa3J5bVBESkI5M0HSAagBQVVfeXFMTXdmczVEOU01RW05YUdNdHpsRVU0WnRuOGoydmNwdVFEYkkzSThhREdTOW5KUF9HdlZyd3dHNlJ4b3pzR0xScDVrdnBQOXVvelB3WmFqT1ZmVFpXUGdxQzNodmlsR080YnJFaWNqUEQ3dDRYUHd5WTdlbVltUHVtYm1taHJMTG1hZzEtamp0NmViLVljR0JTcklqSlZ2bUZmRGZkN1pROURt?oc=5</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Desmond calls for review of social service fraud safeguards after California scandals - Times of San Diego</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 02:23:45 GMT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWXBsVWZJaTEydGs0Q2NZTDVEajZjWDlPSnRjblVEcjR4RUVGRDRESEJRRVZSUFFVTllZNUE2M0pLQlJKWF9oQm50OHFESElBclRlY0tWWG5sRTFGNTRjcHhHelF3eE1xNTdWUnJ1V3FRNVFGVmNvQmlKNFJpRU5EeFBGaTJPZzhfS1dCMVlnRmV1cU1GY0lmcEpUN2EwUHBZbUNDOVJXUGxyME5iTGFZSkN5WE01Y0V1SUJ5UzNn?oc=5</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>How a Social Media Tip Turned into a ₹45 Lakh Online Fraud - Open Magazine</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 11:34:08 GMT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPZlcyellrSDRMb21hUXVVc2xEQWxDY3AwTENkNk5uN0dYa1RfRlMydFJBUU80cHpxcXVXcS13ZXN3cVdjX2tBeEdLbnQ3Q3JBQTJSaS00Y1hIcFNrZ0FsVXVjT0VwY3FVN1BMZ3JLSGxRTWlad2pmU3FCX05OZVV6Vl9kRHlRNGhOVWVERjBiTDFTMlJWb0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Why is Revolut so interested in the number of Irish social media users getting scammed? - The Journal</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 07:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9rcnNfWWZVNE5pSmVma2ptZ0ctdlZOank3T3hDcTRQcXJzNHB0Y3hXMVhGTTE0ZmJGT2k4RDZCY2FlSXFlUXltMGlQd3NMZU55akt4dnIyc2xzYTFGMVpjT1VRZUdFSFgzZnFUblV3ampxYWVwOWxqN3QyeGVMcjg?oc=5</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Payroll fraud: social engineering and identity theft target employee paychecks - SC Media</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 00:17:10 GMT</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNRDg0TFo2VkhXMTNRWGRSWFV2TEdQeng1QXFONGdvNzhobXBUa1o5a0ExeDFvUi1IUnBHVG1SczRSeUVTZk5pWm0ta2lHVHlLQ08wRlBGZ2JtY2FNUmIwUUlUU3RYNGgtWHctaVdMZmltQVNDWmUxTW52UkZZaHo1MktWQ3BQRGM1aVM2Uy01UG53bDU5ZGE5RWljSElubnpBc3NCS01QVkRSTWs?oc=5</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Durban vehicle sale fraud syndicate busted: Two arrested for social media fake deals - themercury.co.za</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 10:46:59 GMT</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNQjN2OUl5WEhyY0gyemRhbVljY0J2aWh6cVl1cGdENjRPbzA5VTc5eFRGb05fUVQxWHFqYVdmbm9zTjNpd0htWERhWkMzd3kxYW5pREc5Tm9NR0lLRlgwYWM1eHJmYjFWcnprSFBtS3NPbjllTVk2WDhhQU1DeEZnV0ZaN01lZ3Z5aElZOVh6eUlfeWpHVFNGRjRvZVpkOGF3UGpjcnhYaUpqN3FSR2F1aUZrWWU1TnkzMVlkY0c5RFZHMGM?oc=5</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Minnesota investigators are halting payments earlier and longer when fraud is suspected - Star Tribune</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 19:00:04 GMT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNVmNTY05ncnFfUG5BVF85dXBBQWtBYkhtX3c0MEpZODlLVmFKYU85QmpwQzdwaVlSaWpUVl9LMEV6T3lOWk11d0lNeFNXMWFaLW83OGdScDhTYjJobmM0SHRtSU5CWm9OWTQ2cTNzcjNfX01DVXYwVmFaWWs4SnhuRHNQVnhxOEhfcnR2N0NWV0NPZlJTZU9MUEt6Sl9ta2VkX3RLUlRYbG5fVE5iTHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/weekly/topic_feeds_week.xlsx
+++ b/data/weekly/topic_feeds_week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,22 +456,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services Regulation Committee report on the secondary international competitiveness and growth objective - House of Lords Library</t>
+          <t>UK announces biggest sanctions package against Russia four years on from full-scale invasion of Ukraine - GOV.UK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 17:06:33 GMT</t>
+          <t>Tue, 24 Feb 2026 08:18:31 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPZGZabjRpTEJfUjQzam5DeUNmWkUxNWN2M3JWbU9CVGY3SUhFMEwwWmYzY3RrMG9TaHlzMEVtTUZfUy1ObzRyX1p2UTVWRHpMRmVoVjVuNWV3TnkzWGpKM04talFyYkk5VHpFUHp5T3FLYWpvbUJXUjdpekdHWHVVdTU5TTFPUWRKY3lYRVlfTlV0T3BJc3B3V01fZWRuNk9QTUExbHZfYjYxWEk3SHF5aXdsV1drUG9nbllPbmp5bFp1U2hpVXJhTkl2cUxSd055aDR4NVEyUEZ6VFlfVm8wSkRWTUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNZVN0OGM0bndZWHRIUHBtNDNqdnl3Y1NtSlBsQ0w4bHJXUl9tbGh2M1FUWWgzQTlOcUp5c0loRGRWVGVBLThWWEE1TjhVZkxvLTQwZzJGRV9DNDJqRS1MWHlKQ0VnWkJlRy1WQ01oU2NJWlZLR0l3dDlSV3NlTnpJdmVJMDQxeER6R3FyU0hoZGJsR2hVZWtlYmJjeFNNX3duRnlkQ0pYMUlvX1JINDVxdnJaNmFUT2dVMlgxYy14NHVWMm5ETUJhSEVEYVhrbVRkNGc?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -486,22 +486,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Training more Britons may not cut net migration or plug skills shortages, study finds - The Guardian</t>
+          <t>Reform’s Danny Kruger criticises UK’s ‘totally unregulated sexual economy’ - The Guardian</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 00:01:00 GMT</t>
+          <t>Wed, 25 Feb 2026 02:30:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQLVNkdkhnT2owWk9QTnV2NmI5M0VKb1RMb3BoakZHa0JBY2lRb2RKX09vYl92cXZ2Yy11TEVILTZpcHpHdnBtQU4wVmJUbWRhTU5WalR5UXNxRXk4cGk1NEZ2SFgtZDBjMHVQSGdtNHFUdEJkb2p1elcyVXBFazgtclR5MlhmTlhnQWZfZTJXenh1MDdadk1Pd29VNzQtd2hRMFg2M2VVelpCWFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPSm9ScG0zTHVYZnFxYjBTdFQyejJvaXpPOUE3Tk90UlNEUUNtNjJlVTlsM3VPZHEwSXVOaW1VZmx3QkZTd1RQN1cwOUhLOUJwZFlCSVUwZV9zbVBGMGVzUTYwUFh4VmtJb0Z3cDZVclpkRkM0dEVMRU05UERVWVVMcXhUREp6Y09iSmtBb1lOSDdpb2tzVV9XdlFuUFVnMDdnYWZvalJKdVBMdw?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -516,22 +516,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>King's expert cited in key government report on security policy - King's College London</t>
+          <t>Business insights and impact on the UK economy: 19 February 2026 - Office for National Statistics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 09:27:36 GMT</t>
+          <t>Thu, 19 Feb 2026 11:07:41 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNeDA1QUVjdFlvNzRranJaY1dmbk55dS15X1I2VFpxekhtOTlSN2QtdExiM3BqSWtKb0xVcEpxbGN0ZGNBc1RQbjlOZUt6QXBmdGJJMUgwZ0ttMGg3N2VnUHZqRFFEYnVZZkc5UFBDeXRVMGM1YmhpWV8wMEFvWlJDNkZDV0VKLTZNR3M0dHBJRDVKZmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPRmNaTjRnbDlNUjAwVUU1d2Vjd0VFeE9HN253VlRicWpTV1huOUZMTmQ2RGZybmUzNjdaOUh1UnJkQVFqdktaYUFSNGVCT1JqaFFiZnJNX05vVklSLUZDRVhwbV9lSWhZbTRQSlBEQjJrZzJjLXVRQXBWajFJSmZiV2ZraFhCOHNiNk5raGRPS09vd1MzMDVTTHJtTnBVWmF2MFNfcHZZUVJpV1I0Q2NZeHFyT3drd2xIdmhEMTB3cE5WTjVFZlZWeXR1MGRfaHluZGs0VA?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -546,22 +546,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Update on May 2026 local authority elections - GOV.UK blogs</t>
+          <t>EU ethnic minorities in the UK: an overview - Migration Observatory</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 14:54:23 GMT</t>
+          <t>Mon, 23 Feb 2026 14:32:20 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQRWh5VEc5ZDJuVTd0QVc5RVpYbUFISXlmSEtzazBtT1YxX282b256TWw3ZU5VQ2Nmd21zTGhYR0N4S1R1RTZZOUtneWMxVkxVLWczRS0xYU1XOGw5cUVLdjRudEpGOE1kVmtueUxFdk8waEdnVGZFN2hLNmd3elM1OWtHVWZTSzdBOVNhbnBDY08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOVDdmLWl3WHFCbi1ESFJROXV3RFFaZFhMNGwxQlQtVGl1dVlHT2s0WGlVOWlMOWJDend4ZGFESnhDQ3hvYVhmWWk4LUxZUXl1akx5N1pOT2NEbjNuWFAtOHRFQkN3WmtQcUNLSGdoVGptWXh3c3JZb2dnLWJjSDd4aWcwdF9TdURPYzkyekFCbDJTeXVBclZQdk5tYk15dnBMZG9Z?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -576,22 +576,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>When Destruction Becomes Policy: What the Munich Security Report Reveals About the Future of Global Governance - Toda Peace Institute</t>
+          <t>Mental health of children affected by armed conflict: experts call for global commitment and funding - BMJ Group</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 01:55:39 GMT</t>
+          <t>Tue, 24 Feb 2026 14:01:36 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPT21JTXItbmVPbi1keTkwVnk5MnVGeWlwd19zUlBxVWZOWVdsbnFnVllUQW5RZ3lRdjZfMHJNakxyU2VhaC1LMDZlU3RTSXFTZUdMR2xsVVQ2bkxDXzktVENITDBFQmpMb3p0S2x5alFKVkU2NS1oc25ZaE0xNmFJNl8tVjVacEtCRkNmTFpYT19zVEpKd1U5Sk5GRE9yRDFGWlVET3E5VTF6REI4NllNWnk2Rk1YU01qM3hHa2lMMHpXTGZvdkpYNktPa3ZPU3ZDdFVPamMycW53bXRUV0lOdnBqdmVLdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQcm9MaUM0T1c0eHN2MG1waVlIR1hUcjNLWlZESFVKa0E1cDA0SW16djJWNUxpUzg3c05ma2VTd0JwMXVTU0ZjU0p6SVVIX0FzTXZFNkRuR1ItTDk0djRmc0VwSWx0WlRhVVJWQmhTaUJ4RTlGdW1aSmpxcEg3S3kzWGlzb2dlb0hTQkk5anBIUmpPR3dXSFFfT2ZfRmFRN0NkN3UzdHkzZW5hOE81YTRtYjl5UmR3SDFsWGtpWmtB?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -606,22 +606,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australian universities on trial: The Albanese government’s “report card” against dissent - World Socialist Web Site</t>
+          <t>The Day in Trade: Supreme Court tariff fallout continues, ‘landmark’ UK sanctions package and UKEF urged to expand support as UK goods’ exports drop - The Chartered Institute of Export &amp; International Trade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 03:09:13 GMT</t>
+          <t>Tue, 24 Feb 2026 12:04:58 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE4yUnN3R09ka090aHY4MTZYN1V1cFB4VUYxR2pfUVVaRDF2NlNfaWpWQk05Q3dfYUt4bmtnc0F3WHpXSTRxdlV2d2FFaGZCMzhydUhmYW1FNU9GNlpSSmQ4NWk3MXh6TFRj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPN2Zya3FRUFhJQTNBeFFuSThYOEdNcF9sWlZIaDY2c0ZBU2ZLemlhSVNjcmRtVnRBM3FfYzM0LWJkZWxKLVUtX1N4OU5KTm5YUHdpYV9UY3R4dmJpdUNBMDBid2t5MmJQT1hBYWtsZE0yNmVFcVNLRG05bU1DaFBsRjluaC12SVc2OUNlM19Jay1DTm05QkpvMUtSUS1rTnBqZGJES3JSU1JYSXZXVHA3OE5RUXRCNG1sRVpLX1BUaWQ3VTJvZ21YUTZYS0NMLS11bmNRLXhsZDg0SlZxU2VvSV93NktXS0wxYVltTnFHRnVMS1F0a09TOWI5WWhnSFI0TnJ3TWVRRE9qVXhrLU0ydDBhTzZ5akxkcVE?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -636,22 +636,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>X prohibits gambling Paid Partnerships in policy update - NEXT.io</t>
+          <t>Ukraine war latest: UK and Ukraine respond to Moscow's 'absurd' nuclear bomb claim - as Trump sets new peace deal deadline - Sky News</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 17:32:35 GMT</t>
+          <t>Wed, 25 Feb 2026 07:22:17 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQVEdKU0dNb183U0E2WjM0U2RzVkJoN0ZDbnFDSTlmTHhnTGxMWlEzNDk1TTFaLUNxbDlRZXQ0VVlsd2pITXAzYWdEWjhRTl9WNjJnSkRkZDUtOTJVd3VZbkhJZUotSEJ6SFc5dVBCRlowZ050WmxqTFFUcFdXR3lNTzZFWG9zVFR1Sm9Oa0RHakljZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOeUtvMTh2UXpkaTMzanZhdXR1a0ZNLVJLZFp0b0FEV2RzY3FfVG8xbG43Yl8tS2VxT1E1NjVzX2NNY0JqX0llRHp6bVpGSEUxM01feWdMMU9QSEt2TkJiVWtBRWc1Snc3dTU3SS1tV2RGclZRSkMzNVF6QXdjRVR2a0lOQjg0LVFJSF81dlM3UENqWS03RE5NNUFmYXpzdi1ERlJ1cW41a3pDNjNrUWVhVVNJU0puLS1QVmhQTjZwSUdiWE9KWm4tVA?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -666,22 +666,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan narrowly avoids a technical recession in 2025, report shows - Euronews.com</t>
+          <t>Celebrating 250 million: Empowering communities to enable the global AI economy - The Official Microsoft Blog</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 11:22:22 GMT</t>
+          <t>Tue, 24 Feb 2026 14:05:40 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNSkVFalJIOUNidnBMWE5QcFJNOXlxSGVMWnhPMEhPTUZOenJIbks2dkxuNFplQWRJVGRRNEZWenhfdDBDeE1oY0Vqd2h1R2NpT1VObGZBdkhCV2FXemR5RWZFNTd2d3pPbWgwOU5jWDlOY29sSk1XcXNRbk5abUVXa3BZNkpoa2cwQ2g1SEtINEd2MFNUWnlDcFM5aU9TY1FrMGxqMXI3ZjYyVVNaZlFXa0hhY1hOeEstMmZCcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaG9FdXMxcExScVp1dFZ5cWl2bFQ1TUdJQnV2U09pbndYUEdUYWN2dVRyck55eF82N3BFa2NFUGp0Z2w1anNaenFlLXlfLUVJYjR6RHhRa0xYVXRqNWdyZThiYWtSUFpsMFpybzlodlEyMWM4MW0yUmR6T3lRNDNfVDdvRklpSl9KcHQ1Vk1ablFLQ2RFdjliOUVlQ0ZLSXZsM2dielY2M3d6ZkFx?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -696,22 +696,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>“We are seeing free parties rise, mid-tier venues disappear… extraordinary resilience, but resilience is not a policy”: New report into UK electronic music brings mixed news - MusicRadar</t>
+          <t>Consumer price inflation, UK: January 2026 - Office for National Statistics</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 15:25:04 GMT</t>
+          <t>Wed, 18 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwJBVV95cUxNVTZJR3p1T0kzd25TcEx4ZXV6ZWpUNi1EQzVsSE92N1ZRSExYYzNZRTNrMmluUE9IbUt6bnhIaFFZb2FJQjZ5UTduQXQ2bk04Z1N3bnJrZ1lfOE5FbWxJN2Y4RmxmWWswcFRSMlo1NGlNblJmS3JqSFRqaUxpMWlHVWpCLVpLOUUxWUc1YXVmMTdMa2JFMlllMnlrR0h5cWFDNGlYQnZkTXlKdV80bWJnN3JnNXh4MjBaUDRxZ25WMG93eVlpeUp3MEpNWHlYcUxWU2xtdHFsejVLdU9jMnpHeWZubW1vd3ZxTjBDc3hfYnZvNFRNdl8zenZ6dWtsd1d5b1V5VDhMZHBPVXBxcDdBSElralBWZ1BFS05fRjVkMmhNZGtROXU1d3BMV25Oc2NfMVd3RkZjczFGX3ZUeWxV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPMkZvSkhVdERGWjJIU1A2eVF2MDh6VG4ySXJfOGlaR3VfN29VWENoT1BTTWVHMGZES1lCU0tEb0tUUDI0QXNxaHV1WHNIOWZiZzBWbWlkcjA5bGZKclZhZXp6aTVJREFZLUhBUzI2cXB0dDhJQjFkdGZ0bG9uOUpoTE5nVnl0dWF4aEltNmsxX3NSaXV0X01VcjJlNDJselh3c0E?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -726,22 +726,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Offshore wind could help support space-based solar, UK government report suggests - Recharge News</t>
+          <t>Europe is underfunding female innovators and paying an economic price - Euractiv</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 13:19:01 GMT</t>
+          <t>Wed, 25 Feb 2026 02:29:11 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQb01lc0E5ZEhZemV3aUIwZDN3U01TdzdsQW9YTk1CbzlyMnIxTnVraVlEcWQ2WTZVb1NVYVZWQlNEbGlNSm9NWXlsdFFpTldrRXNxU04yQWJDSWNqenpnYVpJSHRDTS1PRmxEdnY5QVl0RUhqRmpkcFBnNF9MMUkza2UxU0RsWWtVSmhEUE1pRGh5ZWpqVkRqbnZQa3pWNGoyX0ZJZlFReGIxaWhDa3RIeENHMmR5WjM4RGFJSGxsRENQZXhKRUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNamZhdXAxeG1zYUlSamZTbHJQemV0dERkUTNybnNqOUxqd2xwRlNybzVGX05WVWhXX01zUC1pdnNOVmlVSEJfZDlhTm1zSWhTTHJBSWhnYVUxQkNRRTJtUkJ6QnR5ekRDY183U0VGUk9uX3k2YnNVMU12MUVjTkt2aVFYTFpfVVQtQTUzVVQtTEtRblVVUWx1eTd1S1l4QlowZFE?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -756,22 +756,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Neag School Researchers Seek to Use Innovative Methods and Analysis to Reimagine Special Education Policy - UConn Today</t>
+          <t>UK Shares Flat Amid Russian Sanctions, US Tariff Uncertainty; Convatec Rallies - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 12:42:43 GMT</t>
+          <t>Tue, 24 Feb 2026 16:49:05 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOX0JPRW1qT25FZERFUUhXYndGNDNzbVk3VXNXOFBDZDJnV2hWZkxTWk1tRGJVYTZfbl9IZ0N1blJuOERNb29BdzVIR2IzTFctcklUc3Z4alh5SEZGTGEtQjVvRi1mVlkwQjFZZHhRdXhJeVFmNnBRNG9waXE0SXFweENSbXJuZnNQdFFaVG5RMmVfdjZfRzhBQ3lnUWE0UnAxYlNpN3RxSTh1NzVyOGZTeGFLR3B6ZUhxdDE0QXJmVlM4SXpQRWdmZGxEMVVWYUh1bzhsMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNdktXRHgxMGxROU12VmZBWHAxRlV4T28yeDllSHNEMTZNRFJLWGZQQ21Dc0RCc3RFNHFfTjBOVXVPbzJwUnNtQy1nZnBfWU5NQXp4UFBFSFR2U2JfblZ6aEtsQ1Byb1JMTUNTZkVqLTVKVk9scTZBRktIWGNZY05XYjZ3?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -786,22 +786,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Update: IMF Official: BOJ Expected to Raise Policy Rate to 1.5% by Two 25-Basis Point Hikes This Year, One Next Year - TradingView</t>
+          <t>New awards recognise contribution to UK economy by manufacturers, border innovators, customs professionals, and food and drink traders - The Chartered Institute of Export &amp; International Trade</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 23:31:00 GMT</t>
+          <t>Tue, 24 Feb 2026 10:59:07 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNODl0SzNmOXRqNWVUci1Jek11TVo4dVBuaXJ5QVVnbHlON00wTm9xeGUyUEpHS2NzaFFPUk9FdnY5R01pYzdTcktSNExhc0ljdFJqemFUQjdOUktmcE1KRXZRcHdxdTM5ZS1XT0pLWVFuRGUxM2s1azdvZmVhRzR4MFBHUnZ2LVNZb0c3NnRCUTU5M1VXLWp2YUZzSkF5NUtTb2ZXMEpaTnlLTlR3ZXJmN2VYdTZRZmQ0SjloaV9Bc1BCUXdJclhPakItN0s5Q3g2LU8zMDgtR0N4Qi1paFl5b243cl9vRjFZOXlPMkhsZFhLQjZrc1ZWWV9qX3NYTDBt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxOWFZVQ3JubUNKSEpqNkYzYjc0dFd5WFRUVVNVSzExdzRXMXktZF9BamZrVW1KZnpFS1NhX1lSSjBQeWtqU0hFSWhnY0UwemhrVlgwWklOTVR1OHg5ODR0bUxBRVliWk5RSmp4XzZFYm5UbXNvcVQ4Sy1xQVFkbGF1elZ1Wnl1Y2J3YmJwazdNR1BDcEF2Q2tKTlJEWHJ0dkJPenFiaVZLLUNBVGtGc1N2ZFQ3anFlb2phTXdFY21Wd3pkOVdGbHhFczdLcTFfY21oaWpwMHZEeFg3cm95M0pHbnQ5b3NoTk5sNUxELWRGOG5PUjU4MkZ5SWpxNUhzalFpVmVIMi1JUEVhUjdrWU9uN3phM045TG50Q3JJVQ?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -816,22 +816,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Combined policy options needed to remedy plastic waste in U.S., Pew report finds - Waste Dive</t>
+          <t>Manufacturing industries: Economic indicators - The House of Commons Library</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 17:42:59 GMT</t>
+          <t>Fri, 20 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQaloxWXhRS2JKWmlkM1RvOEpmeWdDRUhRaGNMbmZ2WlVjR21uQXVFN0MtWlBQbHIwRWVlbjhsQnczSXJDYUduMy1sdVZLUm1jVFctbTBFeHFxOFg5ZWlGeVJXa3htbnJ3TDdlcFQyQUhsX19fb2RPeWprRUFQR1d5Y0h1YTctT1RZV2ZsT2lYRTVka3MyU3VMcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFAtZERLN3pVemh0UV9uR2FtVnQwS21TbTM3R3dUQUxfNllGOWFJRTVBUElnLXlOdkJCVUZkYTdTTVJfTDQxOFFFRXE4bFg4SDZwaW8tUHJnMUVCN1BIV2ttLXpKT2V5NThwM2pBc0lacm5JZw?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -846,22 +846,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OCI Policy Analysis – Tool Overview - Oracle Blogs</t>
+          <t>UK Government Seeks Evidence on Ownership and Control in Financial Sanctions Regulations - Crowell &amp; Moring LLP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 18:01:44 GMT</t>
+          <t>Mon, 23 Feb 2026 20:00:20 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOdXNpN1o3TmZtQ2hOMVZncUNsYTlEV3ZRaWQwbXN0M0llOFBvZ2VZSFZZZlVUUzU2Umd6V0gtMW5wYjhBVEFSNHRXeldvRnl5a0dsZVQ1VmtnT09XUXMtQ3ZUal8zQ0JCWkJvTGJyRnZvMnFMYUdrc2F6TU55UXItdWtuQXBjZXp2cEE0U19B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNQVJkUkdmY1ZQNTJVSG1wMlVyaUZHVGFMUG82YndueGZjRkdTYUJhcU9xMlJ1N3hvRUx6NW1CdXBCMF9HZ09zU3VYRjlTZW5WTlVIckZlb0Z1LUxHSW1fSGxpeW9aNlU2bGpzemJTcjNFakxxNjFMYzBaVHp0dkJsRklmV2NMeU5OT1FtN2hwSHJTM2k5UjFTclg4VHNjemo3dko3VXU1T0JTbWZxczdvdXJySlpWMXlKTXA1Ri1TQTJGTjhYMno2LWIwek9STU5ib21wcg?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -871,27 +871,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>REWE and Cimcorp team to automate fresh supply chain for Berlin supermarkets and stores - Retail Technology Innovation Hub</t>
+          <t>Disinformation was ‘central accelerant’ in Leicester Hindu-Muslim clashes, inquiry finds - The Guardian</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:16:33 GMT</t>
+          <t>Mon, 23 Feb 2026 12:20:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRTB4Mll6VnpOUWg0STNVbXlsVTVEMUxkbXFTZmRJcXE2aDc5SU92MWFjWnpnVWMyLTRGbXBYQ3BPLXg0QWlCLUxtWlJabzlxSHlxdURLNGlzdGJkeEEzVGcteXRnUE9ud1BURGRfNkdIU1NqU3FMbkxGZmFBaDFwTWlobURRSHJRUFBOakpGN3dLN1l6bVJRM2JETGhYZ1Bvc0FRdFFJOWM4UXRJaUpyN1c4Qy1sbGZZYmpuaXozOHd5U3NObmZ2b1JyM29IWmh4dWRNaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQNWZXcDE2ekwydGQxTFNVS2NoTmVMY2dtRUtaWS1yd2sxNUJQZFBsQU5lc2lNdm92X1d2WFdFQ21vbFJrVXRlMXN2czdpNXVKVVNLZ1dqZGt3UnRQVkRQQ2FsUy1xQ0VKNkw5ZG84eXA4akk5czRRa3RFWURuYlFXR0pVZzlUN2dUT3JIRGw2aGVkY0F0ak5KRGZna0lRcjg?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -901,27 +901,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Port Marlborough and StraitNZ Bluebridge sign long-term partnership agreement - Shippax</t>
+          <t>CLIA reveals cruise tourism contributed €64.1b to Europe’s economy - Seatrade Cruise News</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:18:54 GMT</t>
+          <t>Tue, 24 Feb 2026 18:44:31 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMG1URHRTMGlEcE56NXFBVjVSN1UxX0p0ZnY0eTMxeWs1Nk1mdTU1TjQySXJrY1E1MjJueUo5WERfaXdhLVVTQnVQWVY2X1lQTTJpVTdBMWtxcGJQbFo4dHJSbWd3VVExOXZfU0NKMzlJUC1WcHZXZWgzNHU3THIyX0FRYzNVbWdnRmhvUVliRi1VT3pxZkMtYmJjR3gwM3BtVDJsaV9ic0V6aTFYSDR2RkZkaU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQYjBCWXJDejBfNHM3cW5KUHROdm1rWDJQV0duaE5jRUQ1aWlWM2tTTUpISTZDUVFFcS1XeVNMbk1kVGxCb3dfQi14Nk5XbVZ2VUlFejNZWjVwUng4NXdQVUlWQ1NrTTZTajBsUXkzZjFiR2hmNGFScEIzYW5IZ3hobzVUZmgyMEs0UFZFeHIyb3hleUxCOERUMEs1Vk80eUs3dFhOYlRReU9WQVV4RUZ4U3VzVU5fcTZIU3BVazJra1k?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -931,27 +931,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Practical insights from the SFO’s refreshed compliance guidance - FT Adviser</t>
+          <t>Russia's invasion of Ukraine four years ago launched Europe's biggest conflict since WWII. Marking the anniversary, leaders from Germany, France and the UK praised Ukrainian resilience and reaffirmed their support. Read more: https://p.dw.com/p/59GbS - facebook.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 03:06:29 GMT</t>
+          <t>Wed, 25 Feb 2026 03:20:57 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE4zS1VMMXExdk14RVNlbi1sTDA1OWx6UFBmSVQ3QVMtVHZJdk5pNGhMVDNaYldPWjVWcWJlMTZYOFQycnc4Yy03NkVzczlyS2JRal9TRmZmMGZ4aGVNOWVRUGt1TWw0TTU2RXBrMlBGSDI0QS1xdVIzdE1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNTnc3TWRuVzIyTE92eUdsQ2EzUFp3MG9BWTZEUWxRbk00dXpvVlExTXAwUC1DSk5JWUVLNGFnTG1GUElKUXBZXzA2S3Rha3hDSXlRUXg4d19vbzBCRk5MaVlzcld0WkpmN0JRVXhiRkxnTFFYQUZrNjNVdFp3dHFtZWpmZS1kNnJqUkVKTlN1aHZxaGN1eWl0cTdRd0dPU0xJaklfRlNmMWpNN29YODhPcWFlcWdGYndvWGFBdDVaOTZYMXBMcE8xLUVoWkpDWnlDcWtBUDJ5d0M1ZHRRdzhhdw?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -961,27 +961,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unity from End to End - Logistics Business</t>
+          <t>When is the Spring Statement and what might be in it? - BBC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 01:23:49 GMT</t>
+          <t>Mon, 23 Feb 2026 13:02:11 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE4zeHo1YTlvbkhXdWtxMWJlbWlyRmVRR0wzQS1Oa2tSRGw4RWJKY0ZvYWxfRDU5WmpjaDV6NExaUDAwdkFKQzFZNC1SR1hIeXpsSmFHbW9mcldfVjVhVkJzbzhFSExiTWg1TGtYZVdfNnc1VDdNaTI3UUZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5LclFOMDZoWmdObk15SllmNWxqNmdZM1hrTmx1c1JVeG1wMC0teGh5QlFVTDNaS0JKTG1xWXRkMW9tUkM2NnAySW9XcGMwUXktZVhuUVZZMjB3dw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -991,27 +991,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New £11M fund opens to support jobs, growth and investment in Port Talbot - GOV.UK</t>
+          <t>Gen Z influencers trade Europe for Dubai’s booming content economy - Euronews.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 10:12:50 GMT</t>
+          <t>Wed, 25 Feb 2026 07:00:59 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMEV3ZzBnTVhqRmxPbVI4WXcwZnZxblRmQlBUQnR2dF8zanJGSXBZVzRsZWRGZG9kTjd5d1V4eTYzVFBBbzNraE12ZHkta0VaeWMzTjdPcW5odDFkOGp3eFg3UEJvU2F6TkxsaFZkVVQ0WVJHTHZ2djBZNW1iZDhzYUNvbzd5M0J0dGxETWdDV3hHOXgzY1o3eWQydUlwNjFfSUZJbzNOTmlCZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQZk5CMEx5ck5NamgyME5jVERoWktZMnc0aURRRlgwcHB4aDBGTktwdldSOU5hS0VDbDdqVEtDSlFFb0pqZGUwU3JNZ2psaFNSZklJZmx4eV9oTl9JNzJMWmh1dDE1TzBOcnlaTUFXdVRHX0tZZERRQ0lVN2RRd3Z4d0tuT3Y4SzRqOEFyaHNHXzBrdTdBR2FNdURzZ21LZW1sYkJCVVo5SVk4dktPUmtJ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1021,27 +1021,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>When Artificial Intelligence Discriminates: Employer Compliance in the Rise of AI Hiring (US) - Employment Law Worldview</t>
+          <t>NTIA Hosts NSW Night Time Economy Minister as Global Demand for Dedicated Government Leadership Accelerates - Caterer, Licensee and Hotelier News</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 22:09:26 GMT</t>
+          <t>Tue, 24 Feb 2026 11:26:36 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPT2tqTTl0cDZ0REJQRmZVT1VzXzdkLWhlWnRZaEVvM28xeUwwd3V0NUNiUlNKTHZzbWNQMGY1M1JoUm8xXzh0OVNueHRwZS03Z2ZkMk5lbjQ5dG9PSTRaWG9tODR6aGFRNkdKUksxV2VRamdwamxLVk9jeHktS0NfWDU2aTBCcnV4UExrMDZwRXlCOEtpalFSLXZwYmtZLTV0X0RTRS04SjJYbkpFb3Y3YXpLODRaT2d0QXc1YS1USF9VcTgzRXRhamR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYm9ySHhZY2U5LUI5ZVgyTmY5VWoteG5CVkZDMmZteHRXS1R2RUY0X2o1Q2VtWHA1RXIyUEw4alkzOEVtQTIzcGktZVlOc0dMZFNuN0J1RC1ScHdIem11RVRGYmdxX0ExcEM0dTlRTFNsS2otbFFtN3hFY0t1YnRhOVRZWk43YUQ3eVlVUUZvemt1TS1fT2NfbVFQUzByZmxFeEtvSmNNeW5jYzFicXFQeF8zQXdQYlpDaVZXLXVKeEdhYW04emZSOThOamZMampvSmc?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1051,27 +1051,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HSL Compliance acquires Enitial to add environmental monitoring to its client offering - Water Magazine</t>
+          <t>Maybe the global economy isn't all about AI - Reuters</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:05:39 GMT</t>
+          <t>Wed, 25 Feb 2026 07:10:59 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQeUV6aGZCX1p6SUZ0eWVoVkYtSkE3VE1HUE51bmZLYWVtb1lyYnhUT003b2JiWVhHNS1lbElmdU1QVFhhdEx6T2hnTDExS2FwSmZ5UTEtMVFRV0FzY1NJOXdnVU9fZEZnLTZfWGcyRF80ZnNadmJlM0lRMVVOSFNnanlwbGYtdUQ3Wlpld1J1NXBZa0lTOW5TdDBWWG5jZk5nUEpxSjlINENITTRpY05QQmNrY3JrVEh4emRtVlBIdW50Ukczem1OVzNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOWUlIdUZfQ2s1T2pVS1lMUGtTenRpUk9neDVGVXNIaHVhRzVxazJRZlhFbS1CVVN1dTZ2Y3FpMFlkMVpITUJldDROdGh3Wkl0NTlYQlpKOWdXcWFJQnBFZkFFeDJnSXhQcUlUZEZvZzRSNVI3N3hSSVQtM3pSR190cXpZWlFMdFNNVUE?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>This is the hidden supply chain powering Russia’s war with European tech - Follow the Money - Platform for investigative journalism</t>
+          <t>Belgian diamonds lose US tariffs exemption - Financial Times</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:00:00 GMT</t>
+          <t>Wed, 25 Feb 2026 05:00:38 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNSzhyM0doOWxRVFA0Ym1WTTBNQm9nUUlNaTBGSkhWY284a3Nkc2J4TkhHblRYQ291MVhFS3E1U3dwUmdybjRHN09yaFo3clZpLVhWZkEyTnhTbUYzbTdWb1NLeXRwVFZNc1h0YWZRREstNW5zR3N6aFpXS2R0Q3pSWW5xX0VKNm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE11VUU1UlgyRmtDV1lWUDU2VnFfWUlPMmpHczZINHVybnZCWllEQmRoZ2hNNjFOUTQyZ29oTlZWTVpRMVEwYkdLLXhSSmo0Rmp3aUh4TUxmRjVDcFlEamtPT3A5ekE1VjVjcFFkNTZXTUM?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>‘Economic fighters’: the volunteers helping direct sanctions against Russia - The Guardian</t>
+          <t>Trump's new global tariff comes into effect at 10% - BBC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 05:11:00 GMT</t>
+          <t>Tue, 24 Feb 2026 17:35:52 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPX0ZkYmsyOElfU2tuVzcxMTFieWhWMG1lVXl3SmtGbzVUSElWbzE0c29qMEJpdnFnc1Vfb2kxYmRhU1I4aUVPWUJ1bzRyWDF0LVhaUE5PZE5tcnFBOS1yUGhLb2dObFNzLTdfN01VYk5DM2h1VmFZN0NINHBxQl9VQUVkeEI2RndQc1hxdUZadUlCV19GNWtnbFhndGE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBvYkhFUWNZNXVOTkNzQXkwelRtcjN0WUZiTVpkNm5GRWdpbm5Tc0lGNU5jXzRVRURrYnN4WDRGSmlGdFlySWJFbjZXWEdLYjB2MWFFQ05HSUFSdw?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portsmouth Port fears £24m plug-in power system may not be used - BBC</t>
+          <t>Northampton Town 0-1 Port Vale - BBC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 06:16:46 GMT</t>
+          <t>Tue, 24 Feb 2026 21:47:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5hSHJyWUp1bDNWdE9ER0owN2NCclBoS1dyZjhxZENTMGJtaFhaM3pDX2hVbE00LVF3bWdfWE05ZmRIQnhDSXVmRG9ET016bEFncFZOWW5RdW1yTWI4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9DeEtPQUQ5alJGYVlPT1otTjlndVAzTkdFdTVEMFltWEFrUEY5WDV0WFpPQjJXcG5CMWhwY1R6RTRwMFA2U0F3VFZSUXY2WEJzQWtLc0JSOV9RRXpfbG9sclA5LWI?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>French supreme court shields Libyan assets frozen by sanctions - Global Arbitration Review</t>
+          <t>US-UK trade deal still stands, says Business Secretary – latest updates - The Telegraph</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 19:24:07 GMT</t>
+          <t>Tue, 24 Feb 2026 17:36:01 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPeE9lLVpLTURBZzhiajExOHkzMjlIQkxmVnBlcV9lZy1aRTh5QV9FcXhEUWVvR05SODRCRFN3MUlQSlhJM0FacTM0czBiOXdyQ1BNOG90aFhDenBtTEVVU1hkdEdXY0lWdmlNZ1piakpGaWxYdF9qTC1RV1FVRGJIN1JWOHl0WEpJX1Y0RDdKX1Q0UTQ2cER0QlZlLUNWNnZXTXoxcHhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQN19PNDVjZnFEZ0JjQ1FZUS1tVkJiNUdqdlJVQ1dFYnVfVFZ0bVp5eFA0YVR1VXE4TDFWVmRTYk9aR3Y0Z05aanV4SnlvWU5OZU9kU3dQTDFONlY2d05nWFJaQVpSSHc3Tk5sWEozWUJhMzYwc3plZ3dZdWRnZ3k2TjJOZmNwckNyVU5YMWhNX2NORmNENnVvWlFMZFlSMV9JZUxqM0dn?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Organisations submit request for UK sanctions against Bahrain Interior Minister - DPG Law</t>
+          <t>Your energy bill from April: what’s changing - GOV.UK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 11:09:57 GMT</t>
+          <t>Wed, 25 Feb 2026 07:19:37 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQbHdVc1dmeUF2V2VFZEJrVEJXMVhyU1dyelZWZlFsZE5YLUtVT1ZrZHdtb1Zid3RjVW1DbzZFaHRKN1p6alFIRXp2Y3JaN2w4azBaRjNFdnF4Z3gzUDdVckhKVjE2TXpaTnV3bnIwWGtyYnlpQUtYTHdpbGU4V2hXVkNYWm5XeEZOcHdfangzV2pZSUFmUXh6VS1QcXNYeWlHVEF3Wg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQajBJM3lfTU5jVUViTDFCREp2eHVObVltdWw1eS1UUGwxVFJQckIxLTNlalhBR2FNSkZMUF9RLS1lSjJKbjM5RXpsTGd4UXNkcDdNVVFJeTlzT3FFSEtDcTRYQWJPT3NpUlJLNUo1SldNdldhZGU1cGJqNDZwM2NqQjVCQQ?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'Dismal' China exports add to freight trade slump for nation's biggest port - CNBC</t>
+          <t>Panama hands canal ports control to Maersk and MSC after ejecting Hong Kong group - Financial Times</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 21:41:09 GMT</t>
+          <t>Tue, 24 Feb 2026 14:10:56 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNWm5IT1ZfblNFZS15ZHN4MWVRZ1kwN0R2c3lBa2w4dDFXMTJ4Wm43MjNkY1A2S282MG9zOGx6U1NCRVRuQ3RuMXpVbVlTV1liOUVpUW9yVExYX2dUMG53RFhhMjdqZDFoZlRxcTdDR2h2Wk1peTFlVlY3LXl1VmpwQTZLSmRWeE5QblNwSmx5SlFfU2Zu0gGaAUFVX3lxTE1Nb2lONjdpenhFdVZMSE1EbXJTeG9zdEgxN2Rid2ViOWpSU3BBczJIRnlvVjhDVUdpay1FZ08xQnJfLS1pTE9MMDFydktReUw0VXJiXzB3UGtuMWhyMmxtbmtCNmZPMXBTdGlBTy1hcGhHNHJDTjlOZGdfc25VWEszZDFscGhiNGgtZVZSX0pKRmNfSThRQWpXdGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5pSDRMZnZ5dTd3cXhaRElCMkM4a2RVX1huMjVzVmp2a3JFLUFDUk9vbURkMWRYWklsTm12cGgwSlE3Wno5RWVlMEJ3WXdwVDZPZ2xLdlF4YTVza2ExWVJHM0JzUDFxLUxOMHJHRmhtZUo?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Report: Stevenage 2-1 Port Vale - Stevenage FC</t>
+          <t>NR buys Barking hub for international freight - modernrailways.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 19:07:13 GMT</t>
+          <t>Wed, 25 Feb 2026 07:38:25 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPLWZaNlJaSWlncnZ1UkZ0NUtxTmtfYndDb19Fb2o5NThmYnNMdmxLQklDd254SURoekh5Uml3NjVJYUNzNFlRdWVORHhjZVBJbF9Bb0F3MHA2bl9Vb2htak9IZmkyMFA5LXpjTGUxeEdOMTEtMklIRzFwZjVTbVFOMEFQdk1XbjVQZkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQbFAyaFR3VC1acW14Wkl6Uk1ENHJIRVJpNHQyYXNpam9zOVdtdGFTYlViejdTOU50LXp4R3NBZ0hWSEZ0VmZQcDVXVnFINXBwU2pwRUkyUXMxWWVZaHFTbjVrOTdjRnVURW1JZlVrVGJNNzgtdHdxTXVFY0luaE1HTW94S0hjdWs?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EU 'won't shy away' from new sanctions on Russia if G7 allies fail to reach deal - Euronews.com</t>
+          <t>Central Asia’s Foreign Policy Agenda: Balancing Between Sanctions and Cooperation - Bloomsbury Intelligence and Security Institute (BISI)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 13:41:58 GMT</t>
+          <t>Wed, 25 Feb 2026 06:03:54 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOQWg1NXQ4dkdJNHRhU0J1S0czdjhpR0NIamVudFZPSFZpZmNxUVpRMmt5dGdTUFoxaWE2R2Q2djVwYlpwZXVNbTNjQ2ZPODliSTB4V2oyNXpaeXUxZjluZEE0bFU1dXRlUnFJdGtxZ19yX0tjWExxZnRqZW5uZjYzZF9SQ19iNUpQTnRhREtBWTNEeW94U2xMQkJLdUpLVkYtWlNORDU4a3d6ZHZLdE9HamtiUUpSanl6emRybXdpNXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQb0pKM2FmVU9jYVNiN1NfY2xGZ1J0M29jdzBacTJjYVNnZ2I0LTdDV09xLUlROGhYWDYtNE84aVJvRmZQOWJ5UEJXZ21YMDhpWnRtUnp0NlBJWGV0cTZIMFJMRDdjeUY4Z3hYUzBYbzhhWXZNYUI5Z0ZnLUkwOTczRTlycmIwWmRMcHlSTVN0YUhkTk9odnF0QVR1VHAyc0szVUFtcDU2VTlkTTQ?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLdN set to acquire Samskip’s UK and Ireland freight business - Shipping Telegraph</t>
+          <t>Footwear brands navigate uncertainty after latest tariffs flip-flop - Modern Retail</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 01:55:32 GMT</t>
+          <t>Wed, 25 Feb 2026 05:01:24 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNOUUxVlZMWWpmNG9iQ3pKRUVCLVlPaEtmMzY3aVl6YzM5MnFPS1NFM1QtdzN4b1N0WGdOUXNsSmNPekNRbUMyeERyTVYtNGRZYXhVZmZBRTktRmxRZVVNTXUwMjdQZEdFTG9kSVRkWFdDeVAyNU1Oczgwa0lkc2JTYkROMl9XLXZscXJzQTYwdWxOZ3JacUY1bXAwTG9SdGl2TVlrVld1eXZnUzBo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOWTFOc0tqOUZma1A2Vjg5cGJrZEg5d3VCR3RJZWh2bmRQVmh3ZXVoZXRaTjlZT29sUU56UWd6eDZiLVhTTkNLQVdidEg0UjB6UENyNzktX183cmd3dmNIWFZWUkR3UDNUVWY5ZWdlVnBjX21ubWJJa0JpdXJISEJjMVZPcEZkMjUzUFRUaHRwM0ttUkl1bGZzbTd3R1RvR211SFFGYklVa21wXzA?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egyptian speedy delivery and supply chain tech firm Breadfast bags $50m in pre-Series C funding - Retail Technology Innovation Hub</t>
+          <t>Climate risk compliance note outlines data providers’ duty of care to conveyancers - Today's Conveyancer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:16:33 GMT</t>
+          <t>Wed, 25 Feb 2026 05:00:46 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQbDRfeWw0SFFpN0xRUWRsTVRRTTY3ZzRaSGozdEN4NHpIWHFfeUtFbjYzVk9kQjczNTN0QVU0bmhwRnFiSk1mSV9CLTd0OG1KTTY0c2gzZ3FxcWR5a3JPcHFydnIyS0VWcjdjLWxCT3NBcmVPdU1uNEg2cDd4RmVWcDJ4b1dDRTAxREt2MFVHQnJUWDNhRmFJMHhCTEV1eUNkQjJpQzhaSmlLZGg0M0dYYUFmR2dRTUhBdGdUbUdfd3pXd0x3ZUlTcVVrUUpKYTlwNlJlX08tNVEtZmppRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPTFYySmo2THE2WEdJaUNuOFdhWV8ydGJJZVZmT2lkTGtTNncwVkpEbmxRZXhBV240Vk1XQ24taERFbVVpdkhGRVY5M3B5eFJSTmNPWmQzakNBM1FpU0o4UFFxeXZubFlfZHBYWno0V2FWYTk4ejNEMzdoTm1Cd1hhUi10V0tqTlVqWkNsWEZmVkdMM1pjUTltckJXZ19XSHlDX0ZramFNNWd0aWd5Rm5hOFhrN3Q?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Trump tariffs: Irish exports to US soared in 2025 - BBC</t>
+          <t>India and US defer trade talks after Supreme Court's tariff ruling - BBC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 14:55:28 GMT</t>
+          <t>Mon, 23 Feb 2026 08:20:01 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9xa0syQXpfazI4VDEtNU1mOHNRVm5ENk5DUEktcUppeGFTSEdpVnN2V1U4c0lWVHZYM2pQT250cFV1RkpDUDY4WjJpVnlMQWwxNlZDOWxoUWs4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5STDlHa012NkU5QVpuckpRZmFZM2k1ME11UGZjZU51T2NndjdNalhaQy1rdVkycGdQVFZydDFlUU1EWlh1c1ZCTHBaUXZZb1NSYVZUNmJncFc5UQ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mondra and inoqo merge with focus on global food system supply chain resilience and sustainability - Retail Technology Innovation Hub</t>
+          <t>Compliance challenges with EU and UK nitrites/nitrates rules - Food Manufacture</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:31:55 GMT</t>
+          <t>Wed, 25 Feb 2026 07:30:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQdmVpWTVqSnhQUUprY09SeE1vcFhYN1FrQzdiM1c1Rng1Q0JYa1VMdDRtQ2NlcmpwOFgyZTBFYXJnTU1FR1dIeWhiSUViYmZwNVNxN29jSzZDbnRSRWV6RGZ3eEZoYzBERUpPU3A3ZWxIcWdJWEFkUHFDaFl5REpkWmQzODc3dUhQMlFUcmR2TnBtMkNtbWdRYWhlcVpGQkVjWFZqcFlGbWF3NHZpbE9GYmRhVjVwV1ZDWnpubW5CZlY2cV9jN3kxVDU0NUhHU2kydWpXS0NpMlJwdWcxOGNGb1ZzMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPUjdhS2RkVWNCU3dMTnFqRWFSbnNSVld2a0NWSlVjbWtpeEhWMkxnWDljMjI1c1AxZkN1Skc2SW05dTY4UjF0c3h5bmZiSENmSXpKZDdvUWh6NTRLLUFOTkhEMVdRVzNlU29YbDB6REFCWVE0emw2ZUdrWmpFb3VVYXo3VlBNWnpUUk1mdkFrYi1fN0VyX0NlYVF4NjRUaFNtSnMwNnRENmJ4OG1hdHlGblBxYw?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunderland to face Port Vale or Bristol City in FA Cup fifth round - Sunderland AFC</t>
+          <t>‘Simpler’ FCA insurance priorities raise bar on Consumer Duty compliance - Insurance Business</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 21:04:22 GMT</t>
+          <t>Wed, 25 Feb 2026 04:52:15 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdm54eGl1XzlLSGsyM1Z3d0JZcWV1WXFSRDFPbUROMDdEdkxWYXNzOU5BaWxXRkJ2YzEtMkdVRnUzZWJrbnlCRmR0aFN5ZjQyT3U5S2FOdWhibnJ2V2hSSHpBMmtqVVB6dFFJdXIyT01YdExJTE1iZUs1Zm1BTlNzY25Mc1dyT2g0Z085VjZYZW50SEtzMXRycWpiWUxQYl9aQUplUXFOcjRHSXVPZ2cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNcEVCTU5OTklHVGFiVGhPVndsUUR5azZCaHdvWWY3T2xYcG1EZWpRaXNQNDRCVzFKa2M2RmF0Tm1sQnFXdng0ekR5Skl0YTcwOGt4RVRRTEI1YU54bWQwQzlvTVJWc3NvYlJRNGZqZGlMcXlTWnEwX19sZmdSeXRCdE5QT3pZb2RXSU0wNTRzdjJ1XzNpRjlyRHNJUDRVR2IzV1JOb3M2WjRwcVBIT09sckFwVWExaUdNSHE1RmxlR3ZmQ2dxZmg1aWs0NWY3MmV3Vkk0all3Vkc?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>The 2026 supply chain challenge: Global trade disruption - Thomson Reuters tax</t>
+          <t>UK Hits Russian Oil Fleet with Biggest Sanctions in Years - Rigzone</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 08:00:00 GMT</t>
+          <t>Wed, 25 Feb 2026 06:46:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNkdMUXkyMXRHX0pOcnZSdG53S0FFaDM3SkRLU1Z1djlJYVBKYVpnUGZjaGhuN3MzM1JjM3hPN3Y1ZlJPNlRFaEZ6MVRmUUNGWnpNOFNONnRtekJpblhTSmdfVFpLd2VwWTUwOWtabG55SGlFckxXeTRRYnZST1I2T0MwN1htYTVoOEVGVHNjakRETHVOVXdXMUFjQmg5QTRLY3plYWhPQ0liLWFDTEU4dGtBR3NxZFBuUkI3a0VEZWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPaUEta0ZQT28zeU52dzlzbXBQbERQUmdBR2lfUXVBYVp4RFJpcUFTNF8xd1FWYzBLVlBZVHB1MmZhN1pTZE85bURfRjBYdmlabGF1NWtNVUtZMjR6ZjJ0S2M1WXFTdG5OR0NueFUzd1Y3c0ZRMk9lUnBQNDdoZFM3TEFjdmgzMUYxaVNSamZZNTBDZ1J4cERmVHRPUTRPVlJBVnJEZnJ6T1h3Umpwckw0RlF6MkJneGs4ajJ3?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Corby Logistics Hub Showcases Innovation During VIP Visit - Logistics Business</t>
+          <t>State of the Union 2026: Top moments from Trump's speech - BBC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 15:03:35 GMT</t>
+          <t>Wed, 25 Feb 2026 05:19:40 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQME91M1VzWktyeXJIazQ2Nzk1MDQwRmxVRzRJYmVNSTFlXzBUd3BrSHlXVmx2S0ZodVQ0a3pXT1pQdUxaNklWWml0bTduWFItaUs1a0tUajBuSnB1Z2p2QnVSNmpWa2Q1VlExOWxwa0VuaW9Va3hNV0FaTE50M1ZYMl8ySXAzMWRtSHE0dUpWTVJNT3hmVE5taXlWR2c0U3NPRXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5wdk93ZHRVWHowZEt4eEQ5bVo4LTVsWUNBVlB5dFcxZ25SSmpwR3RIWFJsdTZoUzFKNVVpSDRyTk9vNFpVNDRPTzYzM0V4azdVbGp0T0lvT284UQ?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New payment compliance reporting requirements from January 2026 - Freeths</t>
+          <t>Tech can make supply chain ends meet - SeaNews.co.uk</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 12:00:00 GMT</t>
+          <t>Tue, 24 Feb 2026 17:16:46 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxON2d1eVlYRlRFd3JITEdqVlNnVzlRUGVHZXhyNmpKc0UtenM1ajd1Uzk5TmFoQ3U0Ulc2MGNsWHFFdnpvZEpqQ3UyS0dnbGo5LXVVTkRYZFJrbmpKY0FCUU9Nb0xjUkgzSFNFNjVUWUs1aWpaY1dETUIxNzc0OTRZLUluRFZnbkp3UTlEWHBLUFMzMmFaV1pDN2JvR3JMNUtHWXpzWW5lODZuQjBWZGl0YVlWVTY1eG9mSEpISDh5V0pUS05v?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBGNVhhcmx3MUNQd3llZGNwTXpRQ3RFTFRCcFRrTlMybXJiSDRTVUtxRTNKdUdJcDJfdmdPbGlBRk56T3JYMVprTnBkR183NDl4dG41U1NzajJ0M1I0ZHRrQkgxTWtXZHRUZTRLRWxINHJ1WEdrRlE?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cumberland Council handed enforcement notice by Information Commissioner's Office - Times &amp; Star</t>
+          <t>'Pupils locked me in a room' claims striking teacher - BBC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:00:00 GMT</t>
+          <t>Tue, 24 Feb 2026 18:56:30 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQNjdPS3REZjhQdVlLazFMZkhTVmNiMHI3dVltdmlIRklGRk81dFFNU3QtMGRkLVdkSk1HaHhHc0J5dTRTZ2Y0ZkxMdklna2FCWG9xN3ptY3FWc2EzMEhvVkxNQ0dORTR0TDhsWHlKZmpYZDJjZUNtTlhmZExUQldRZ3lSNVlwYmthc3VyT1pxai15RVdFUlhqSkJXWTQyVWU4bHNVU29jNjVDR3A4OWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5YOXFxUnMxLWtjWENWeTJ2UUcxc2VhYmFEM1MwdGh5LTlkRDlwdG9MSGFRdk1yUFY3d2pDclpFMzl4NjRGUHdZNm5KQ1U5RFB4ZVV3enhiNlNBeFJ5?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ferry collision damages port and cancels sailings | ITV News - ITVX</t>
+          <t>'Burned and destroyed': Locals and tourists describe Mexico unrest - BBC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 19:56:31 GMT</t>
+          <t>Tue, 24 Feb 2026 03:19:30 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOSGdQWWVOWVVxdkZPUUVfd0Z0Zlh4aGhEcWs0MDhSSnhXTWp0WklMcHRudGFvSGlYMEMyYm90Ylcyam12enJheFpHT3EyS2c5bmFINE56RXZpREYwVGZOeXVScG1IcFVGWm9lbkpVTlJqUXk5M0xkSTZ2eko3QjNVM0FSU3FyZVVtV2NwU3VZWXhyM0VBdERmbWln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBYcWJDZXFTU0hsZGxtOHNVQm41V3ZMV1hkR2poN3M1R2RQLXgtbFdqQVpJNnZ0akNUTGYya1k2RzhrZ3JwaVNvZVJiUGxwTGhyOVd2RExWOXlLUQ?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>STG Logistics files for Chapter 11 - Financier Worldwide</t>
+          <t>Dortmund fan groups boycott Atalanta rematch after "incomprehensible" police checks - OneFootball</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 15:57:20 GMT</t>
+          <t>Tue, 24 Feb 2026 18:03:45 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE8wMmVueklqT2Y0M2xYY09fdzh3WXYwOTRlYU0zU1RvV0llcVlkemRNTGZ6UVNSY1lDZkR2cTRVdUFHSXhyblFXUFRINmlqQkc0T2dHem1JSElwcFIxckVhZUJiV0dmRnEyb2V4V3BOazBpbmVrSVIzUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOaWpyMnJaMEkxdzRrV193YWpYbVJ6YlVoY1lHcHFKZHhpc0dmWDU5dUxzTVg3ajZWYzIxLVpzWWV2WXFkZTdHSmlYTmZhdFpaRGNFdS0xWWZXWEpIWEMyQnBhZlRxUGJiVTBYVnJtSjkweV9ORDVnU2hrMGFxelNFSzZDLXAtSHBQZGNzSVdOV1JXTTRwLU1EcW82TFFIV3ZRRDRrZ0prLWhETi1kZVRjRjBjbDRFWVZ3QXNrWWRtbw?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1651,27 +1651,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A New Tech Solution To The Freight Fraud Problem - Forbes</t>
+          <t>7 March: International Day of Remembrance for Fallen Police Officers - Interpol</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 14:41:39 GMT</t>
+          <t>Fri, 20 Feb 2026 15:30:35 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPenFSdkxCV0ZlWG9sLWMzN1hULUJ6ek4xTTBoMGxmTWdaNzB6dFV3bm41VWxXaEltZWxpN0pzUFREOVlud3ZOQzdZYlVQNEpRa2xBM1B0UE9Ba0djczI2OFo1OTBsbUpweDRRc2k4d2pKVXljRnh1ZThfd01QRFloVFNaX1JlTjZwWFl2aDFiTzV0YUFlMzJ0cVQ2Z01PbUFzVG9r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPMlI5ZnV1aXpsUnBBaEd4X0lKaWlVX0dBd3drWDhTaFZWaGRIMUlqcWdpWTRsUzJnQWU3Mm55VnBPYVdfeWpNeTlTbjNwOW9jZlYtcmQ5QTJmcDM4RUtfVkJYdy0xdEhldm1MVElhUnRrdnJmZVdURk1rYnNyWW1IUlBkbjdHZFhIMGJkdVVJQnpNLVlVNzNHWDFEbnJ1UQ?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1681,27 +1681,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BBA Launches Irish Building Regulations Compliance - Roofing Today</t>
+          <t>28 March - Roots Street Carnival at Rotherham Town Centre - Rotherham Metropolitan Borough Council</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 17:05:34 GMT</t>
+          <t>Wed, 18 Feb 2026 16:23:31 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPcjVMdGZ4cWloZUozV1FjdFVDa2liUDZMaTdFTlFtdGYzN0ZmTWlKNjdaVEFJLW9SZkxkOHJXM09OYktvcWtZZ01kYi1NV1FXOUg5QVRZam1KaXVwQm1Ddmo0WjFlaHVSQ2hFSG1CUDRyV2J6Z1dXZGpqMF9YVTdySG90TUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQRlJVam9TRmFhWnRfMmx1Y2hIQmNvdThaLV8tbDJKMy1DdWxsa2xRZy14VmxCcE9iS1luYnQxb0t4MjJsTk12Sm5raUNCQVp4OVQ2QVdIeGxEaUE4UktZTHhJNUEyWUsxRXNSdW9BcVdXNUYxRDllY0VGOUdzR1h5UjByU2tFTWtrSUdSejZkTl9tVUN5cVdhMnl0QTk5eXRaeE5UbA?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,27 +1711,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UK Financial Sanctions Compliance and Enforcement Update - JD Supra</t>
+          <t>Tennis officials draft in extra security for tournament in Mexico as civil unrest intensifies amid cartel violence - Daily Mail</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 19:31:48 GMT</t>
+          <t>Tue, 24 Feb 2026 21:48:22 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNMU1OSjBya0w0cXlYakw3ZHFIbGFqNk5KODg2MmhRSUVwYUp4QTFpNGVhRDUyMnEyWGI2VlAtQjgtYzQ2bWFhcTBpX2ZUUmx3QW94Uk1wM1ZIYllyUVB1ZzdXaW5SOThXeEs2OFF6S0MxZDRaM0RwT1pfUDhoRnlnSi13RkF3X0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQeW16NjZTX2FpUm03Umd1X2pCcmdFUGdRM2NEMkVjOEhmM1dIYk9BU1pteUJDb2VZX1hENzl5REx4bHVmU21HYVVCcDVSNG1wbVZ4aGxWeGRkaG1KVkdLOVF5M2JkUzdxaGVxNUxvZHBpVHYzSVllYnNSbmtJZm9jdnA5ZUdFd2NGVW1nUll5X0FPazVtUVN2X3lRdTZsaG81THZrNlRRUVdxV2FlX0ozNHFVUEYxZWJzdjVnTUNDTE1MODTSAcgBQVVfeXFMTVhTVFhVU3hkUXdTU0ppR0dmS0E0aWZGa2w5VHlKUWZvQy1sdU9uMEF4eWNZMExCV0NLMEkxSkNYSWp1ZUltdW1jZk5qNGhnTmdTaVkxdjFpS1ZaQnRlMWdfTlhoVXMtYUI1ZXFzV2VJbmFWd1VhRkJ3aTJBWVFfX1BBN2ZLZWE0OGNDZlNjVHV2MENFYjFOazNDT1VwV0t3enNselhYTGFPaW1ZNXNmNUdzSEhxU2Q4dlM5TlB3MHZrN0Vld3FILXQ?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,27 +1741,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cybersecurity in cross-border logistics operations - Help Net Security</t>
+          <t>UK’s food system a ‘tinderbox’ for social unrest which could lead to violence, experts warn - The Independent</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:30:17 GMT</t>
+          <t>Mon, 23 Feb 2026 16:43:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOUUllYzcweHVqWmxWQlZVZ3RYcFBkUm1WMWxPcnJuVHRZQXQ1RGFRVGxhNkdTN1RlOFhkQTRlQ2V2aTFQMXU0Ni1wU1o5TXM2WndwbEhBSmNqSjFNaF9Zb0dib3RaMjJNWTc2LURNcDhTaWdsM0JrYjJ4NzZXclYtSFFxazk3QnpRWTFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaG1wXzlHVzZNc1NzS0pDd19SQS1DbjN1VHJmTi1aY3ExZEU3WGI4eWpZaGtfMnZydmpISW5kXzU4b1FTMHdhRnVDX3JqaVRwSHZnRFloZm1OX2dBREtQT2d1U3VYRGEzamNLSHFLZDQ4M0ZoS2o5Z3RJTEVIQzJJTWlvckFEYXJLMG1tbnpXdmlLTEVNUG9PMzROQQ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,27 +1771,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bashing Trump’s tariffs is slowly becoming a bipartisan sport - Financial Times</t>
+          <t>At least 2 Quakertown students released after protest clash with police; DA investigating response - FOX 29 Philadelphia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 12:31:04 GMT</t>
+          <t>Tue, 24 Feb 2026 22:57:58 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5GNzVjWmt1cHAtSllkM0dVZFVoNHZRRTBTTDZ5MWtuRjlWN0xpbmJ4b2Zydjkwb3hwUzJrTjBESmg3WW9IbmlER3lhaHVHNC1OcUZGVnpIUmd2RTVULUlralUzRjF4ay1sZE9Xd3Iwd3o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQamh3V2I5OVk3VGZSeDFwSkREREM0V2ZhOEE1UUZtWmFYTm04cFRfYUF0ZF9pbDNHa3RjNzVLN1dnOFBnazJPTzNUQTdQU25ldVJneWZIdWdYeEV5cjlJbnY3VWNaNHhYRXdabVFFeGlhYXI2N01ZSnhrYmNwSGJ3TzUzcGxQNUJJQVg3UlEzOUNlVGN4MjRoS1c0WkRDMHE1OVBaaEl2ZnFKSHNrZG9tTHhQVTEtVkHSAbwBQVVfeXFMUG9xbElqM0RKMGsxRUtHWnhQTWloaElQOFZOS0VFLWtPNktTNmgyaXpYLVdfSy0tNXBSMF8xVHZtbWRaS3NUdm1MbU5FQ3JTcXppdnR6Wkdia1lzWUN6S3A1dUwtb1FRcHJ4YWtFX0JyTlJkNk5WT1FWd0lJQ1pTYzAxd2lHSW9xMnd3ejVaYVNOOXZldDBleWlCZkhPeVJHay1jRElGVUdaVGs1cGJaU2pjVG5SZkJqdlk1SHI?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1801,27 +1801,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman: Asyad Shipping offloads LNG quartet for $110m - Shipping Telegraph</t>
+          <t>Norfolk school for autistic children's staff strike over assaults - BBC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 01:55:32 GMT</t>
+          <t>Tue, 24 Feb 2026 14:36:20 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQYWVpWU9IYktVejNIaXkzMXNMMjh5bUtrSFM1bExLaWtfTDBOZjR6Ull6NmFrSF81M2NQbTNxYzBxTkpJZkZBVkMzWnFteEpVQzZUZ2d3LTJsU0hULUdobzEtZ0dmN2NVTnVSZ0RITTRMb3NxWm9sUzdMRHFGcm5ZamotckYtYzMtMmhpN3VxczJQcVQ3RmpXdU1Ua3VzUktsVUQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9mcHRUNVlQblIxazIxR1FnTS11ck1yZXU0N2o4ZFd5OU1XUU41azlGVVduMlRSeUJXNlNTOHJtb3dNQUd2MnV6Y3pINURlb3g1dVpaeEJwZHB6R05H?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1831,27 +1831,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>How Toyota is Diversifying the Supply Chain Beyond BEVs - Supply Chain Digital Magazine</t>
+          <t>Mexico hunts 23 inmates sprung from jail during wave of violence - BBC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 13:37:22 GMT</t>
+          <t>Tue, 24 Feb 2026 13:43:53 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOR1BrczEyc2E3eGxtekdKVXdab3E4OU12QmpjbXM2NUNEcHBwSFZ2aU9ZX0czcWhkRGhMeEd2SmVPbnVNbUthUTlVSlg4R21xSjNCdUgxUmd6LXNhM3ZET0tHYUtjVWJLSk5DUFEtbFpiaG1MOTlRN3dCbTEwYlpHckVGRGtVcGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBRQkQtSzREazRWZ1BhMDhsSmFhZnEtZjJkVmpUTUFJODZOQW4wVV94Q01KWDRuMnp4V3BvQThvVDBqX3RQV3V0cWtSeEp0Q1VGU3RVNW1YWDlBdw?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sphinx Raises $7.1M to Build Every Financial Institution's Last Compliance Hire - Financial IT</t>
+          <t>'Significant failings' during city disorder - report - BBC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 14:07:39 GMT</t>
+          <t>Mon, 23 Feb 2026 15:08:12 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSy1ETTdqVzNuZjVYMXRmVE9GUXRwTzFQTUpEOWxJLTU4ME9PeDNYMjdpc1J0TWw1ZjVtWnBNcWhPQTlBblNWZ3hLRDhZYkp1NFdyTVlmUFZyWVVYYVZNaDV5M2oxOWZVaU4tak4zZjUzcHBRWFdtM1IwMExrMUsyTjYySEJGVzhLeXhnOXByQm40M1pfR3NBelFmMkVPMDkyRFhObUxNRlJGVDAxT2cxdWFTMnVmV01mS0hF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1meU0taEROVnhCNWVra0VjSDVPR1A1RkRYdjJYWjdPVjFOQlkyUS10RExJVktzbTZoZmJLRzdSeXUtT3lFaUhqUDV6Wng1cmN5YmpselNRSFZoUQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,27 +1891,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New US Trade Deal with Bangladesh Reduces Apparel Tariffs - News By Wire</t>
+          <t>BBC's Will Grant on the atmosphere in Mexico following unrest - BBC</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 19:37:06 GMT</t>
+          <t>Tue, 24 Feb 2026 06:25:07 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQV0U2djR0QTI2REZjOUU0YV9oSTZab1hQSmlEU2tTMWE1WXZ6RF9CSEhmS0ZKSU8tMGUtTEd3REF2M0pTZTNJNjNsUjktSDRHMGZpMzFBYXJ3a3RHaUJIR2ZSUU1RRHZSQXN0Y2k2Q0c2VE8xc255RkdpWEc2enA0VDdNeC1iMENv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE5GWVN3UlJ1QnVVMml2STZuZlItMHpNelhEZjVHdDB1VldhbGplZ3YtNUxrMDJMRFFMV0N4NllvSHpvQjNKSHhfSUItYUtxUVdJTjhQWlNhNA?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,27 +1921,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US sanctions turn International Criminal Court judge’s daily life into a nightmare - AOL.co.uk</t>
+          <t>Argentina approves Milei's radical labour reform amid nationwide strike, clashes - TRT World</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:31:00 GMT</t>
+          <t>Fri, 20 Feb 2026 06:50:42 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOLW9zd21UU2tuSU81LWhEQlVIWm9FRFZabkFuOHB4NDZYb0ZvdVNUdGluc2RIMmFacExWMy1aMWN0MmN6OHNkeGhoamkxb2ZlaUtwcTBPNk1xaC1hU2ExZHZfUHRDTTdmSTduQjJwbHc4NlQ2c3dmaUdQREtDNi00Z3Y0c0pTaHBXMVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBmd2RlSE9mRExMdDhvMllHeE5YNDhiWHEzdUxfeFAtWlV5LXlRbVh1aVV0cElwQlpMcjN4VmJmSWc1Sm1yQjIwTUxtSFNISDgzcmMxMGNId1PSAV5BVV95cUxOSVFtZVlMZUNYTzBubGtCSDhZakNjTDdpUm44VmdLZXZvNXg0NHlUaFI2S0E5LU5vZGwwWTFkaXAwdUJrQVh0Vm56NXZnaFd3ZFhiWmNSdURndDJSNWFn?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1951,27 +1951,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>The Salt Supply Chain that will De-Ice North America's Roads - Supply Chain Digital Magazine</t>
+          <t>Man beaten by police at Town Hall protest slammed by magistrate - SMH.com.au</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 12:19:59 GMT</t>
+          <t>Tue, 24 Feb 2026 04:30:00 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbDRsUnBTQ21EUF82TWFvWHdXQ0VzeDQ5SmZnVXVTcVNZOGJnTlp3T25TLUFOeVh5bVg5VnJTYkU2VmZWblJzMUFlaGVuZVYtaDM2Qm12V2tad2N6ZkJSdW53U2d4dUdRbVVyeUxMMDY4WUxFN2lqSHpwaElSdXk4cjQ0a1ByTHRjV0dLTjAyTDFFQ1hJY05LckNLVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdTltZXRQSGQ5OXFiVjdqLWFxcUh5RkhwUDlpc1VjMTA5N2pLclJNYXF2YVRQTVkzLXNKcWlZLUxHLUVIZDhTZmNMYUxPdmQxdzlob3NfYV9zZk8yWDdXTExYSVFIQjFvdC14YTVXV2RqTnhqQXVhb1VTaHNkYkplYWVreFVFVTdtVmdfQ0tad2FCWmJuek5tR282Yi0zNGs1M2lBakdBdXgyNnZXeFhCb2dWQ0VseGtaYUMyYQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1981,27 +1981,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cabot Properties acquires first logistics asset in Japan - Logistics Manager</t>
+          <t>March 1 Will Be A Great Day For Spider-Man Fans Ahead Of Brand New Day's Release - Screen Rant</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 12:17:24 GMT</t>
+          <t>Tue, 24 Feb 2026 14:53:03 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNYld5RkFjczhfc1RtUXRFQ254VXFUczZYbG9NWDk0SU1TeFRqLW1laC1lU0JqZC1iMEdWZzRRS0cwRmZjbVI1Y2VTMWFxZjdRVFJQRTQ4SHppNHE1MHlJOFRRSERSQ0pPU3U4SDRST3h1bVEwXzBwZUdLYUlYbi10UU1DdUh3dEhsWkd2a21Uc1Znd2JI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQU25oTHVVdjJ6WWQtWGEwSVFCWUd4dEgwWndlY01iVFVkOVgwbUN1NDk1aWNLWUdKRWZEdFhjcnpjYV9ReVRsWDNHQzlZSDNYb3BOQ3RtQy1PcDV6Qy1rV0ZPaWdHRDNSdzFYLVVwV0xRSDVKQlBzQlZUWjV2VFZ1N1RXR05lR3hVa2JEczBYdw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2011,27 +2011,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Safeguarding integrity: ethics and compliance in global business - Financier Worldwide</t>
+          <t>Teens arrested in Quakertown ICE protest charged with aggravated assault - Inquirer.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 15:57:25 GMT</t>
+          <t>Tue, 24 Feb 2026 14:36:53 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOQk1aTTRwY0NfOTI3M0JneUF3WGlINzFMaW9RZzRSOHNIWlBuaXNQZWk0VkZ6U01TanNRWHYwdXJpRTJ3Tm9vV3RES1RzNURfemc1S0EwdGRvVnRJLXA5T0dHaEgtMmVwdjJmMU5aeWx5SzBQU2JaV2wzN0Rmb0FjYWcwa3lZajhXakxKRkV0blg2cHBKZGttaHd2VnRuLVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNLVJGa2V1REVFZHNKVEJnNTBGLVNkT1prRjB1YVUyTlpiLWZtOE9QelpZdUVVb0JTcHo5dkFUOFpfRDhBTE9pREJSOEU4QjRRb0s3VHVmUVBhU1drNWZRelF6RUhLUjhwcFNjSGdWSWFuMkNZbTd3Z0g5a2lUWnpsYlNJNUpBT0QzQVF6d0l3?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2041,27 +2041,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Port Glasgow gran STILL waiting for smart meter months after supplier promised to act - Greenock Telegraph</t>
+          <t>DU students protest, as 'police beat journalists' - The Financial Express | First Financial Daily of Bangladesh</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:30:00 GMT</t>
+          <t>Wed, 25 Feb 2026 05:46:17 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNbWpqMllJcFdReEJVeXA0cE1uUTJ2dnZ0QkZUcDhhZzA2VkprZU96LTFCOGZtdzBtS0VJRHpaeUg3MUdhMXE2VFZYZjRhOWJDd2NqSE5xLUJoLUJJa2NZT2EteUpiNXFJODVHS3lvZlFnek5CUXZyem9udTctRVJlUDV1dlhHYkNaV21fcjBBVVdhMGU4SWkzYThPbmVybFZBdVFOcDlmc0tzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxORXZIM2hoVjljQXd2bm56UnNHVFhhUTBTZXVOT2JDcWpOVDN6NlFjTndsSmZYb19LM3pVaHVvLU9LQUZnOEpKWkhVa083bFgwbnN6WFVMdUpQYU14MHBhdkNZb1EwaS1vOGhrT2gtZHhuOGpiLTJzWV93bkp1RWRlMGN0RXhnTHlZZjdGOU1YRVBWQWxv?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2071,27 +2071,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Precarious Work, Precarious Care: Income Instability and Interruptions in Health Care Access - Counterpunch</t>
+          <t>Oregon residents, expats recount unrest following cartel violence in Mexico - Oregon Public Broadcasting - OPB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:59:56 GMT</t>
+          <t>Tue, 24 Feb 2026 03:57:19 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQTGlENDN4RS1ad0c2V0pjUXZxVUd3dzBfVUhzVl95TVdmNy1BRWhVT0FZWnlDbXFod0RLUjJFVzlRaWRUeEhYaHFXUEZwNy1MS1g3ZTN1djdEbnBrX2p2YkVMMGl1bERUVURpb2VPbzZ0d0hGcnlVcnp0RHVWdmRwMGZoVjgwalZlWE9BdDVMU2VVVzQ4LWpJaWNNYmhlbWFScjdUZDg0VHBwbldLN3NwR3FBelZCcVpsUEZOdEVWa3RaOVRUeGQtRDZidw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNM29jWHY0VGZSM0diazNCTjJZX3BCeVRaRERUZFpRVVdWVm1OQURORFNPMHdmSEd2WHA1OVR0ejZuelRtdG1KalMyRzdvWXRNMi1lRkgtM0dRWEpSSnpXb2xwdmtaZWt1NU5aRXZ5eVc2aHRhUVVhcTlycGcycTJlVW1YYjV0NVAxYW1EczJSOA?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2101,27 +2101,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Shares in trucking and logistics firms plunge after AI freight tool launch - The Guardian</t>
+          <t>What is physical AI, and how can you invest in it? - MoneyWeek</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 10:26:00 GMT</t>
+          <t>Wed, 25 Feb 2026 06:01:59 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOUS1ZcWYyVTFBNzl5MHhZMXRBaUtFbDcxcEg3elFISE4tUFhWeS15MlZJQ3RDVVdZY25MN0J1aUhndlh0LWlOVkktYW1aUk01X0MzbzRQQVVEWHRrYW4wTHJFaHVDTzc5T3pmMXNfd2RBRXBFb0tpbERuMk1md0ZnejhGRlY4aWN6MWswZEFiTlBJdzB1OEVyOUVMX3B0M2IxczFzLWU0aWVoY1AyNV9qRFMtVkFkWDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBWeV9PTHZVQ3RGVDF6Qi1iTDdpN2dNZzI5LUtLUVd0ZkdmWjJKRGJMYlAtY1pnWnNUaDRZNGl6MllJNkNtNmRBNlVfLWhLTF9iNDZmZFdMUEdPZzFOUDdxZlVQRTVmeURVNDlTaTNOOEt5bFZ0Tmc?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2131,27 +2131,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Quantum Computing Can Solve the Hardest Port Scheduling Problems - The Maritime Executive</t>
+          <t>The Forces Shaping European Credit: Data, Automation and the Rise of the Multi-Asset Trader - Tradeweb</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 21:41:00 GMT</t>
+          <t>Tue, 24 Feb 2026 22:45:08 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQYUdvdzZESUh1ai0xM3p6Zkh5M3IxUk03WGxJR0tGYnoyRnAzVW5FTnlhdlFNZnJYbVRSZnJESGRhdEpXZGdvSDVzbk8yZzBaSGgwT2RldlZpT0gyanVyaEhhY0ZURThtZC1GZk5ONEpEazMyUlhnWFc5RU4ydm5fcmNBTm5wQVIzaWhEYmhBVTI1SDBTbkR4VEp5VXNHLVdpeGRZMWM5eHNoZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQRFAyZDUzR3lBRnJLZUNmLXlBQy1XUFFQNXpCb2tWd3o1cHRRY3A4OWJqb1owVW5RRHltLVVJMmpZQThwajJteXpBZVJXWHVVcUhPVGpUb0lvdlA1WmFQQk5qazJpWGJ5b0Z5MldqVjZXNUo4V254MWhTWEM0WEFSUnZFdlFKeFBmTXZyUHZhVmVnd3dSYnJYTVotRFlrcHJEdnRRbE5MSFlvLWNTZE43VTVuNDltY1FPaHBLbVFMWTI1U1AtWTZINXkzMU9zWmFlQXRNOTJZc2JkYTNRSDV1RWRtWWJ0TFU?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2161,27 +2161,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DP World Reshapes Leadership for Supply Chain Resilience - Procurement Magazine</t>
+          <t>US software and private capital shares hit with fresh wave of selling - Financial Times</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 16:00:59 GMT</t>
+          <t>Mon, 23 Feb 2026 16:33:09 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxObkVhcmprd1IycEFIanZHZG41cFRzSU00T0JHTUNPRTZhZTQwTEoyWEFkX3o3V084a3Y2N29fR0l5VlU4RlZQODM4M0l3Znp2Z2owTFhZaVIxLTVCWUc0M3B0aERDUFFIcnhrWHlTeVZKTVR4ejlZeVU5R1ZlT2IyYVY4R2Q1MDROT2dPZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9lNTRrX3ZVY2lMaThqZ0pQR1pJS2tsZXRMZVBiSUxleS1PdHZQZFNvTS1vcS1nNmpxSHUtYVVDTUs0NTFfUWNUbmRudklJckM1TFdkbENXLWtPTUVocTVPemI3NjhObnZWZlF5ZmhiR1M?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2191,27 +2191,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PORT OF LOS ANGELES JANUARY CARGO EASES COMPARED TO ELEVATED 2025 LEVELS - Port of Los Angeles</t>
+          <t>NHS pilot of AI scripting tech reduced admin time for 87% of users - Home | Digital Health</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 07:07:30 GMT</t>
+          <t>Wed, 25 Feb 2026 07:32:37 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQRzJJUzU4YnVRUlhjcnV6SFd6aHhBWVhNcVlQWnU3TlpvR2pRcHNpa1h4ZzFhQW96ZjJfcXYyamVJNkRqUWM0NU1oZE91dFpvcjl1cnBkU3dvQlVNQkR4bmRYNGJ5WjBueTZWeldDaVhRNGU0bFlPT2tYT2w3U21aWWpna3YzM0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZF9rM3JlUWRpZGtqT2xudlk1UFVkX2NXWWtPaUZObGZJVjhNTVNRa0ZwX0pmUV9jbzdUVjFidTYyQUs3c2NzbVJoa1pCTU9XYktCVHpsZ0tHdkN3MTBtc3hvR2o3NHViQ0NTOUZlVlpmWGlaSUFpWVkzRG9ULXRMVUhwQWJDYWdrOGpONmlYSEFSU0ZJZmVlSVZMSEt1NVFEMUFuZ3F0NA?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2221,27 +2221,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Super Tanker Rates Soar Amid Sanctions, Supply Shifts, and Strategic Hoarding - Crude Oil Prices Today | OilPrice.com</t>
+          <t>US threatens Anthropic with deadline in dispute on AI safeguards - BBC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 00:00:00 GMT</t>
+          <t>Tue, 24 Feb 2026 22:58:46 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNd3dHMnB4V1B0d1o4S2lqeE12UDFSdjAtSWQxRG1lRFJqcURURU9oeUlCaUkyLWo0UUpMSHpWWllaNXdKZVRsNmN6LVBGRXUtc1E5a1VMd0FndFNDMTZkRVVLM2NUNUhXcm4ybDJ1bHhtLVo2aXFGSXNqWWtYYzE4UXZxbFJabDlNUGRMbkJaa3pNRGZMMWxtaFBvRjNMSEt5b2dEMWhLdjlJcW84RjcyMFE0dDljWHFhbWJTZnFDY1_SAcYBQVVfeXFMUDBtd05oRzAwU3lCVlFhY09wanF2bUVVTWM2TnVLbjctbm8xWjhVaHBSSngwYmstcTF0OWRlVjUtOFdwOURLdmktdUdTQ1hKd1d6dnZMRzRLb01Wd1Jtc0pEREpyeU84ZGVBbGpwcHo2bktja1J2MHZBLUc2RlhWYUd6OVh2amxja2tWZklfeW9GY2wtMGJFaVc0X2tTVTFaMnRhVGxYR2t5eVA0VTFzcE5OS2RtUEJnb3VidkhsMXhEbl9CRUVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1fTFA4Rlp2MzdLREk3VG1Ka05wWGNEWG9yczh3RXUtQTJSemtSTkE0bjVYMm5uNFIwVWZJdTk3bW9TOHhuR2p4UzFMUjVFS3N6ODh3bkFqVnNSUQ?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2251,27 +2251,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ellesmere Port woman fined over drunk and disorderly behaviour - Chester Standard</t>
+          <t>IBM 2026 X-Force Threat Index: AI-Driven Attacks are Escalating as Basic Security Gaps Leave Enterprises Exposed - IBM Newsroom</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 14:44:04 GMT</t>
+          <t>Wed, 25 Feb 2026 05:01:26 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNOUJPRnI3bjBzX1l0bmhfREk1VFRDUEhjVDY0ZE9XTFZZWTEzSFkxSXQteV9sVFpfN3lEdERKQ1ljeWsxdUFhbkNpcGh1WFFGbUxGYmxwU28tUVN1SnVvQkVWTjZkNV9XdTFtSEJMUy00NmxjS2NjMHBPbkFwYmNuc1R5WGNuSFBoNzh2QkxJTHdGSVVwZDBXSkM2MF8tUWVf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOZXFEZm03WHYzcmZWVWlYTVRnanEwSnlxaVJaNkZDdUxPUzVKTGZCeUxTbU4wakkxNUJjR01TSFRZTjZmLXlUQ2dmR0g1SU53OWo0T2J3MFhsODZvblpGdzdPV1RTWEx2QjNZS3VKbTZNS0RDZXhyZ2FjSDFaVzhyamVnaUNKd3ZQUjZEdDVrQ240Q0FtOTFoUzNaSE90Qk5ldFlKNXJXUG1ZZUxlZEk4TVd1azBrVWpWcDBhVUQxbnhscTk0ODFSTHhFcG1HM2FONU5HZV90RERrWG5LSU4zUQ?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2281,27 +2281,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arrest made after officer assaulted at Warwick protest - Warwickshire Police</t>
+          <t>Agentic AI and the rise of in silico team science in biomedical research - Nature</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 15:45:00 GMT</t>
+          <t>Tue, 24 Feb 2026 10:20:10 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNSG5sSW9TenItckIzVkpWNHpKMUpQUkZMaERQQVNfcmNaNE51QVJEQUViaWFBc01XT1lTNUQycFhhQ0xIYW4xR3NpR2ZVVUVWR1lhNFBHcUhsNUZ3OE94Y0RLMWx2c0ZsZXNEb0dTRk94YzlZa0g4OUhBczlYYjNDUEhOazZxUk95NjkwdEcteEx4QnhZSVBHVEc0NDIyWk9nY2l2YlZqNGlIM0xWcGd1ZDNCQW9saFpPd1hDVkstRjVnTWQxZmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFBtWEdvbEZoVWFiN3huUnM4TDJ3YW1YVjRfWG16dWF0dzU0M2MycnNPZ0xkTDhheDFlVWtwZm5VaG0yVEtMeXUyNGoxcnFJaWo0TTVZVElFaVdJMm1Qb0J3?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2311,27 +2311,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Female Israeli soldiers rescued after being chased by ultra-Orthodox men - BBC</t>
+          <t>OpenClaw, operational AI and the SaaS stress test - The Drum</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:47:54 GMT</t>
+          <t>Tue, 24 Feb 2026 19:03:18 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5aN3haeVZSeW01cW1jRmxhaFpGRnFpTmQxUnZJSUU2TXZ2OUxkb1ZMWnhYSUE5MUdOVnRYa2tPTzl0TEozVEpQWkt6MzFRd3NyMHpFYk93V0JPQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSGZxbzZFUnU1bUdxQWR2cVQwdUZFS3Nwc29RM0ZLekJ2b1hnSU5zMWVOWXpaeDBiRkhGd1BEVkJJMW1MZTktLUtsTVhaRGE5ZlVWRVpEQWpKR2dsZERNWnlWQlo3ZDRjNVhQR0tGNUtnZExkT0haTE9oR1hfNGlxMHJyVzNFUQ?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2341,27 +2341,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eyewitness: London sees a powerful yet incident free day of protest - Police Oracle</t>
+          <t>Agentic AI for Warehouse Processes - Logistics Business</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 16:38:22 GMT</t>
+          <t>Wed, 25 Feb 2026 01:26:39 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNYjBsd3o3bmFFeWU1a3hsZG1QS0tnaDhvY0EwVkV1bWh1Qzg1eUdldDJGbWEyUHhSYmw5SGRDV1JKSlVELVNzU3FqWWxkZWRaN0pJcmFHOTh6NFlWM0JGeFNPTVpGeWRZTmtyYXJGSnBBLUpTaDhBOVlYSFZPZHlocC00RGg2YU84TmZNb0F6YWNsWTMzdzZfalJfTTY2azNPbU1pZTVINFpNb3J0eTJLQS13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOYVRHeUd0WmFDdXNlbjdUMjZZMFluYmJGaksxdk5sSFRBQW9KZmFIYjhManlOOEQxV25UWnVjV0VmZmJfODdGSTBjRVE4M3Z5TFBZN3hLaW9fRWNoaElyNEVudUYzN0wwb2JFOGJwcjZFMlprVXJyZl9yVkVRNzh6WTI0aTRndGdEaERKdA?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2371,27 +2371,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>‘It was terrifying’: Australia faces reckoning over brutal police crackdown on pro-Palestine protests - The Independent</t>
+          <t>Enhancing maritime cybersecurity with technology and policy - MIT News</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 05:25:00 GMT</t>
+          <t>Wed, 25 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTy0wZ1RhcWs1Ny1iVm5lQUJaeWc0X0VwWmNVVTdNcGl1cmVkd3JpRUtEeWlNRzBjVmdYbkZYNXp1bGZLbGlCZUZjNGk4bGplZWRRZEhZQXpPRVN2dm4zR2p1TW9kV1BGZ09WZmNuVWRWQV9tVDgxQVdmYzhZNUZSemlMUm15YndZWW1rajRrY2o2dFNzMFd6SVVzX0dGcXNBN2swbVZwakg0U1E1enJiOVFmSjBSdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRnkwQVZjVGhaN004UTBBSC1IbndpNkU0aHdiempUN0h5VXlackRsWHlSM1U5c2NoU3Y3aU5Rd2lyYkFhNHBsejg1TjNRZmNGNnoxY0x4Uy1sVExWMWZzT2lnTDc0cTlYb2tfX2dZTmRwUGR4OWJmX1ZjLS1QcDdWR0VrSmsyeEVVWlJtcGhoLW0wbnhVMjN5bDF4SlhWWkFBQWZ0bw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2401,27 +2401,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BOOKOFF Strikes Strategic Capital and Business Alliance with ITOCHU to Accelerate Reuse Expansion - TipRanks</t>
+          <t>Artists and writers are often hesitant to disclose they’ve collaborated with AI – and those fears may be justified - The Conversation</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:59:49 GMT</t>
+          <t>Tue, 24 Feb 2026 13:48:50 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQTnZZZjljVUFHRjFWR1ozLVM4ODZxcHBhTTEtRXpocEg5LVg3Nnp4eHNkNVVTaWNsWDcxRkhTOGw5MWZUcXBiT3FxcWxxdzlJMUdlMWJfOHpuUHRjU0ZtMXlBVHJPQ0R2WWpfYjRjQWxpVG5rSmNGN2VHcl9kYTNJYmNjb2pXbENuazQ4cy00QzRQM1FDMm9xV1puR2ZVSEl5YUJia1Z1ODlWajVxXzVnSC1QRFMzLS1KOHd3bzY1dzd0eHZKNkFNVENOTkNlck1wQ0dUYUNxb05MZWIyT291cUV3WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNbXNZUTJUWFFiOFlIaUg3TWlfd29jWm9RMGRhTDRYRzJla0lfR3puc0hycHhzMUJMWjVUQWlBRk1oSjk2Vno0ZEFMaExxdzF6dno1eHJvNjFnZGpyLS1BS1ZiQUdlSnI3SnJkakljWmR3VG5UenQtRkFoODNhVV85eVoxQ2V1XzQ3VzNqTHdsMVNSU0dLRFYzMGNmMmdGQTA3UnoxX0xTV2NkWU15dWZLSWhzVDZ3ZDl4T0xZV1NCdHNKdUtzNzlVd2E4eFJnSlFub2wyMU1fSXQ1LXdQazZZ?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2431,27 +2431,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HungryPanda delivery drivers say police contacted family back home - Australian Broadcasting Corporation</t>
+          <t>AI is changing travel companies’ hiring mindset - PhocusWire</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 18:35:47 GMT</t>
+          <t>Wed, 25 Feb 2026 06:04:20 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQUnJZOEtrVXRZOWZHZVNac1daSzctQlhoVVkxUjlPNlRnYVlQREkyU1NzbElyb3ZLLVJ5aS1yNDE4cFR5MnRpLTJYaHg0TjdhVjR6YlBFczBQZ21rUFhCU3dNZzVuMXQ4T01sMkhLRkp5OGRiZ3lNNmx2QU92MVlSNE12akJVcmthdU1IWXdIYjZaWlRPc1RLNXBIaWpwUWNCaFlJNzAweWM2TUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOVVV1MlBwb3V1d2p4enM4UndxR09FazBDd0VlblUxdmxlX3lkYXhCUXNJaWU2QjhsVXgwTk93YWh6QVFUQ0hOR1ZsZXZzZUp6STYzYnhaNzd5MWJCUVJkVHk0eHBwdGtiSVpVLVdSUmN5cVpYUXcwUnZvY2V3cWhtVA?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2461,27 +2461,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Police body launch legal challenge to century-long ban on joining unions that could open the door to strikes - The Irish Sun</t>
+          <t>Israel to invest in more AI infrastructure - BICOM - Britain Israel Communications and Research Centre</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 21:02:15 GMT</t>
+          <t>Tue, 24 Feb 2026 12:56:41 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE91d0tqTFFRUW1uREFlak5jV3NraUQzSVVveTVFSHZzd3JDUjkzV05oNmNzdjM0MFpIQ1Y1cENtbTJwQ2ZrMC10NHBoenNQMTB2SUstYlVvY0lkdzhjX3VoMlFPa0JwRDcyU3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBjSTExTlJxcHA2dzZtNWpRSzJOOHlsRHdnSGx5UUdfZnNadUtoVG1SNEtRb3pEcG96dldTRlVKaFRUd2ZNeVlUMmtQVUV5RlpiMVo3ZXJibE1XMmRPd3oteVM2NUMxWXRJSGxvZVU3VG1sSEYxWEZN?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2491,27 +2491,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sydney's post-Bondi attack protest restrictions come to an end - Australian Broadcasting Corporation</t>
+          <t>How Romania’s growth shift and AI are reshaping the job market - ING THINK economic and financial analysis | ING THINK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 23:22:53 GMT</t>
+          <t>Tue, 24 Feb 2026 09:49:38 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPbE5YbTFGVEt4bmdrRXh3eHFTS25HV0ZQclVYOEd2WTdXdFJxZ0VaYVkyd01hcEpGX2xzXzY2YnZfMHFDeFlGcjFvZ2FDRVdhRlBmaFZ3N29kaDRSRmFKZktvcnFpdjdTQkpfM01ZUUVqTnY0cGthZEhCQkxrQVdSRGFDWmdNcUhNWXJRMWxnUGxjaWducUtPVGR6Ml82NWNPZ3NaMmtQM3BPSms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNRnJSUGhUakZEdGdDdVpxRXR4a2szRXZncUhwSHFmeHdOeGdYSnNPTFIyM3BOYlJCTDA3WDJyT2IydXFsNTNrd1YyVmduWTVoamhSN01iMVdhb3BzTEdiNzlyNTB5SklESzBfVWlwLV9ZOHhnSVMwbWVzeEQyRUxyZWxHUzk0MGt6T2FDck91MVVLU0lsSnc?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2521,27 +2521,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany news: Right-wing violence rises in 2025 - DW.com</t>
+          <t>Flexzo Ai and Island Doctors Announce Multi-Site Partnership to Deploy AI-Driven Workforce Automation Across Florida - PR Newswire UK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 10:25:32 GMT</t>
+          <t>Tue, 24 Feb 2026 15:12:00 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxON2VNUEgwczBBeW9sR21HWWNoc0V6MU1yN2J1QTJVM3BqcDVMOHRtam1McGEwV3lzWW90S2pSV1k3d3pvcDhoTkJRZ2NyZFNMTGw2UVhzUlQxemxDWHhmWkV6bTdRNU1CSkh2VlBzUGc5Z2Rlb09Yb29UdjRwMDREWXVLeG1RWHJaWXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOLXlVUXQ0N0NFS0Vfak10SHlqRHNpalZfRGFhTWV4RGQ1THpYNC1zM29rMjJlMzd1bUhRUEdrYnk2UnRSM2Z5RHI3Tk9lOFFrQVZOclE3Ty0zNlhrdF9VUm9STVFSYnJJZ0ZQcDB3bUt6ejc0eXlEVWN4cE5MRVdQOHNnb3lFNkk4N2gxUHJYTkkwempBcHprZDBPcDM5ZnE4b3BZV2JsUEJrZ0VJaXhRUlJVR3BqQ0Vnb3VRZnphN2VjUUlYa3BoLUNWZjgydmdZRHc1UjA2UEVwYjgxV3RvRHNvdVp1cXZjSnFvYmVYZlJpRVdCNGk3ZVFoeTV0VnRWcXE1Xw?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2551,27 +2551,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Vehicle fatally strikes pedestrian on Seward Highway in Fairview, police say - Anchorage Daily News</t>
+          <t>AI and Alternative Data: Why the UAE is Redefining Financial Inclusion - The Fintech Times</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 03:56:59 GMT</t>
+          <t>Tue, 24 Feb 2026 09:42:51 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxObF9UakYtRy1xMldIbi11dTI1YnBRbUZnRHk2Ulh4aW9RVzBJam1BNzVmSUdzejNSOWYybVU4TmVlaGpETGxzbWppaTZtYmV3WFE0NmE5dDFfUkR5em9nWmY3ZTBfR1M5NkZheVB4aHVwak5Qc0lpc1ZHTnhRZ1lPOWFOcGRSc3BVZTVOdG9XRDIwb0lQdjBuaGtZcGotVGdqRE94VUpVMm1ERlJfWWxUVkpqUF9lblBmZ1djYWJkM3RFRWtYZXNjMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNOGMyTGtaTEI1RnNoN0p2SDVvcTQ3VlN0SE1nUFZHTG5URi1FSWJpSVp0bEF4b01sa0xzSHljbkNWakViZEhEVDY5ZkF5dTltNFpwSG96M21JLW54WGc2Um1uSlZmN1B0UmxhcEk5OEVkNlVPTndfSXd1SXNWa0dfelVyNnp1d2U0eDVrX2E2enF1QkFRNWxlbm1neVoxcEE?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2581,27 +2581,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Synagogue protest 'buffer zone' legislation undergoing revision in NYC as police chief Jessica Tisch says she 'has concerns' - Jewish Telegraphic Agency</t>
+          <t>Telcos told to step up as AI, sovereignty and APIs reshape B2B demand - Mobile Europe</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 19:14:46 GMT</t>
+          <t>Wed, 25 Feb 2026 00:47:56 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQM2pRUzh0Q0pETmh2YnQxaDFtaEdFNDFybl9acEhyemNGZU52bVBNY1J5UmRUU3pxRTFSTXo0eHFYMDVNd3JaYXB4MFF1aGtodjJ5cVFCQlhxRzdDWXBHcldOaXBDYWFZaFdpejZRTVpwa2RGY0ZPamJRWHJyMzZiZ2kwVjE0SXVRM2dFT05odmtlbFFQMjN0VHhBSEMtRkg3YW53cTlTdjZ1NVM0MmYyMzhqaWVlQUNhZ2ZFeXRhQWlVSUhvXy1ZNC1JWm9wZUdXQnB1eFVuWGVjWEVoYlhNeWY2VmhYeG5VeGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQVl9VYl9vWDAwd1lWQWdxc0c0Z19DUEQxT0RrZzZxZ3VMbTh5Mm9mdUd2M0xhVDVXbTJNSzFkdUItc2hwSWtFZVFzelh3QXhscWlMWFFNOHhGVTB6RFNCX1hJVXgwMGJJMWpfaGRaNlFPbFVqbTdTM1lzc1RVXzBWWnpsZUdMUjVobGdvdEtMU0tTa3JVTkhxTGdhUTNuQWtqX2c?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2611,27 +2611,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>The beatings will continue until social cohesion improves - The Australia Institute</t>
+          <t>Today’s AI Has Plenty of Tools. What Companies Need is a Builder. - IBM Newsroom</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 22:35:49 GMT</t>
+          <t>Tue, 24 Feb 2026 21:51:15 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOcnBocWpIa2FTTy1LSUs4cE9EdUFoenRJb2dnSDBfNE0xTEozbWJCNjRTbFZ2OURuLXpwMW92ZWllZXlxQ2dVMEVfcTA5ZzZwdUhxNVRjS0k2RnYxN0xuY1huOElhZXFIeGVDU0FUM243OHl6TFViemlkaHdXZ2FMMnM4X0pwQWhUWVA1WWxxSl92UERCcHVONWFCZEx6Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUG5SRE4xWC1OOXJDS0dhbFdxQXo3UmpNaEEwOU1hbW5ZOW9lMHFpcHpQcWpKRUFGV0M2SnhBTnJXRW9Hb2tjTS1lTXBQaWZTbmQtcDlTcFV3MEVqU2RaWjZ3b3oyYkNuQjk0cmtZVldTN0pxWHZpZllsTjR5b1JDTURtby1ZVlEtQkFrY0N5djd4ejRJYnh3?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2641,27 +2641,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SVG Police makes major drug haul after US boat strike - St Vincent Times</t>
+          <t>Jeffery warns education secretary the UK is getting it wrong on skills, AI and early careers - Recruiter.co.uk</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 12:47:47 GMT</t>
+          <t>Tue, 24 Feb 2026 13:19:14 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxORjdRSTFJcGM2cXV6N0ZhSTZZdG1mUmUxQXdJbWQ2eGxKR0VLSXFZOE1aWkwybEVrb3VwVzN1c2NrRkhmQzlzLVNkMjcwZ3ZQcUhYandtRXJIZms5eF9DWXJKY1N4clNfTTljMkMtY0R1YVdNeU1GdktBcENMaFFrMVVtSUJVajNBd1ZQY2l3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbnlLLTg5bTZqb0tuOFVtaF8ybjUwcXJLNTRDanRNLUF6cUVDWE5Rek16bTdjcDhwNEVCanZ2TTFyTWdNcjNxUmktSmE1enRGY3RSMWh1bVV3eEhHVk0xSEMxOWRBN0ZaNk5ZVWRHV3hLN2lkdE1WZEk0U0JwQm8zQzVzRWt4aGE4WlBkN1VIQUlnazZkUElXcHpZZWlNVmJaTVFIYkNMbDRJMVUtVGNyMTBDckgwWVd4SnE1amFidw?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2671,27 +2671,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arion Bank Sets March AGM to Vote on Dividend, Capital Cut and Share Buybacks - TipRanks</t>
+          <t>Using Artificial Intelligence to Predict Chronic Disease Through Diet and Multi-Omics Data - News-Medical</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 20:05:23 GMT</t>
+          <t>Tue, 24 Feb 2026 23:34:01 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNY2xOUXVIVFNZaEV1SDQ2ejlReVp1SF9TMTFCU09LWkNZYUpLVExCX3NTRWJrUUtJOUZVT2Q0bXFVNEU3WDZ3RXExTWZQdjBrTkFiQmk1TFRRdXJGbXc5SElZUExhTDVyNkNUVVk3SlVhOUtqMVNrYS1POWRSQ01JcTJGT3Y5ekdEeVRUVE9jUzhPcFBONHdwSG5NTnZLWlNaeDVEZTNRSktKZ3cyUUZsREVMX05QODd3dEgzOVI4S2NGYUxJRWR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMW1FbGpzSGpzakJuLTJoampxNUlsUzlXb1UtQkNXRl8zLUlTWEJXWEtSQVNtSlhPbWxvaDZOMjd1TnZiR2dfMzJhMmQ5bFRtNTRQWTZPSlVyekFvQVBWRGY2Y0NZY09TT1pmRXoxeWJBRzNiWDVxRUc1Z1NNTmo5a2hXWUlpUDFwTzBYVzRQellnRG9QSzgxN0NvTW9LQkhZald4ODEzaXk0MXJCaFZiZ0FxVDVIeG9OQk41aHZacGpTWUpYZjl2SU5DWQ?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2701,27 +2701,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Gaithersburg police chief to retire in March - DC News Now</t>
+          <t>Automation: China Accomplishes Unmanned Operation of a Container Ship - SeaNews.co.uk</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 03:05:40 GMT</t>
+          <t>Tue, 24 Feb 2026 20:31:13 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOVGpZbFE4cFVKSzM5VDhrTEotV05YMzZmU1cyUk40RWlOYk1LU0NvQ0xLU0ZSUVJBbThFMGNJbnIza2VwaDY2RTRpamJpVmc5NXpIM1Q3TUpKYlBkdU54eVVsSTlpUWVoOTNHX3JhYUFqSmpDdUNWRzA0SVlGeHl1bW1uX2JNV29oUlF1VmJCdjhjZzZBalY4TnRld3ljdl9sU0xZTF9PRThsVWtLRzk4YW01Z2bSAboBQVVfeXFMTmZGZFVCS2NLWFVhMGxiRnRseWdDTnlFcjlkcTlqTzVkczNpVEZmOXNoX0xadEtNdVlxTHFDMWhveTFiaVJjU2UyeHFYLV9IS0dXaXRfQ3ptSUdzX05JZkU3X1VIb0hqa2ZEbzE0ZGo4SThXRHhDQU5WSkdNZ1NoRE1kTGpBbHVRMlA3cWdrYmJucFhNaEpvSFB3R2xuQzhRU0VwS3ZRcTNLOGpjRy1VcEdwbWhjdTJqWmh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPeTJieEhYMUxaSkx5WkR0dThoX3duNEMwTENSSHF2a1NQT3U0TEh0NnVaNTlyYWltd2VhbjFmTTRqUmdaSTNZNTNyci1GNGRBbGtjTE1fa0swNzJwZWdnZGtac0pXZmNkZ1BIdVZ4VVpJVU1nbVI3VFF0bktES1dqY0JRWXhiWjllaGt5U2pPWkk0azVNalRZTlpJV1hKV3JZdm9TRS1wNEY?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2731,27 +2731,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Police Disperse CHP Protest Against Proposed Bridge Privatization; Three Detained - PA Turkey</t>
+          <t>Blue Planet’s Kailem Anderson on the need for data and AI standards - TM Forum</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 01:24:14 GMT</t>
+          <t>Tue, 24 Feb 2026 16:46:36 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNa201cFlMZXpqOVNucFh1dXBvclVKeWp1Z1I1czJFWXJvRDlaY2NDVWpJelBsMjM0QzIzM0FoWXdCcTNuaFFSVjdsMmozdTVhWER6LXRjQ2FxREExTXE4QllIRFQ1TElHeG5TLUxMczc3NUhZb19OSGlyZkR3aFlUYVlocjBLOGZtdm03NjgySEZfZ0w1ZS1JdUhyMjZ6NGRmSHRrbmtUQXhBZTVwbWhjanBOY0x0RGVMa1pYTU8tTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPUEtlc2VlTW85cGpvSjc5R1dhcTFRRGEzSFhWaWFZMnV6RXpsWEVzUUFNMGwxUkx0dldXdFZNaVVtQm50WTlEcHQ2ajdMUV9ndWpMbkUwemZ2ZFVfWEQ4dmJ5ZUIxbVI3Y09vT1oteFBRWWJoNVlLdzNqMmJ2a1h6eUp6bGFacXJfZHc3aUZSa0ZjQUJWa1EycGl4dUc2eE5Ic01ILXFFWlBmOWhYWnp1eG9PMFQ?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2761,27 +2761,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Police pursuit results in crash that causes RTS bus to strike pedestrian - Spectrum News</t>
+          <t>Anlife: what does an unusual evolution simulator have to say about AI? - The Guardian</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 17:39:00 GMT</t>
+          <t>Tue, 24 Feb 2026 18:40:00 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOcnd0N2dzbzVNTTJiNEpKRUVtYUk5WmNmUm41eHNBSUVsTGIwR0VWd0xEYzg0c2RvajVoSnd3enU0ZTZDcGJzMUhaU0RZVTNpS2lqOWNHY2NoZG1OeWp2U0cxeTJmX0xBNmNUZ3E2QmRDSmFab2hGQUY0SmVRRWNBUVVpaW9BTG5GU0lSeEpRX2lKd2pMdEEzOFpmMnluOFdJbzN6b2FLeTdtRW5WcnJyQmdqLUF5bTVGSHZQdGdsdHBwb2lsTnZKM3F0cDN1RGxYaGdjOFNpeFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQWmp2VUlxdklJUGxCbS10V05SY050ekxsYUFTWHJwVTBzTklRUkE2RDdYZkc5QUxtWVNiVC1XRWR4Y3FxZDVKR1RyVUhpMWR6Vk14eGVHdlhDVGQ1dDFTWFZmQ0x6UWhGd3UtNGlvMFRDOTR3T0pybHhncTZ3N0dxVC1rOTVKcHd6aU1Fd203RkpNbmVJbUo5VDR2RS1MUUhTeU5jRGVqUG9BcF9obkdMR2M4d1c?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2791,27 +2791,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Today in History: March 3, Rodney King beaten by Los Angeles police - Norwalk Hour</t>
+          <t>How Colt Technology is Meeting Growing AI Demand - AI Magazine</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 20:40:39 GMT</t>
+          <t>Wed, 25 Feb 2026 07:33:29 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPU2JpTGxDek5qMi1ZZV9NWWp2MWVadjJhTUdKbXNXSDNiLVZ3RXVzbk8weU43LUs3Sk1MY2pMY0FxM3ZUbTdlUGVHWWFxS1lEZ2dfTVNzQWUtVHhzWHY1Rmt2M2pUelVGZVRfYW1CcHNhNmt0Y3BNREhlVVpzenU2YWx0S1dHY0x4d28yNWJ5bldycTJNaTRmRDFhRzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE04YkFDQ0RxMGd6aGtJbDdBVVNsaklOOGxfVXlleV8tZ1Z6QXBHaV94WGZjOFRMc2FQVXBZYk52OFh3Wms5cXB1Nk9oMF9aRmdtT0Z3b2RhclhYQkhVTzE0YUdwMDNZdVVxTmJ1Vm1GQ0c?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2821,27 +2821,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>‘Excessive and disproportionate’: Police criticize feds’ tear gas tactics at Portland ICE protests - OregonLive.com</t>
+          <t>The ‘extreme and improbable’ economics of Citrini’s AI report - Financial Times</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 16:50:00 GMT</t>
+          <t>Tue, 24 Feb 2026 15:30:29 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQQWlNdExvelZ6cGpvcW1WVGtKa1djdFRfWmRqZGl4RVAyR0FLR24xQ3BNWVB0YjI0b2ZBbks5UHdJaXZ5NUxqXzNzTVhveVZkYkhrbnJGYXRHeXJTbzhKbGhBWjV4Zk1uaEtqOElQd0ltT2U5eDdKMkV4Njl4RjBzRXFmZV9qRUdubFFaQkJPNUwyUlh4bjNxbnRRN0Y0LXJpSkJiS3B6LXJuTEk1NG1GSEE5d1VaaTZfVXBkbnpYMWY0Q2hzRGY4VkpRcU80SEh2NS1xdktNNNIB6wFBVV95cUxNY3p2RlZISG1IdlhwWGJubTdESVo0TWFnVXp5aW1YWnY4bldFSWJ2YXdUeERUVWV2UXpEWE9lVGxCXzZ4LXIyYkhQeWtkdUtVZmJiZndBd2hhVFVDMjdSaHczNVRJamJIM0M5N242VTJIWk5MMkdWYzEtc21mT2ZubXZSNzU4WnV4V1JIXzNsRmxST1NoNWNBUXE4RHQxU3RORjhsWEpzZ3FpN09oZWRhMGc1UEJ4Qk1LSDdiZjExT0pQQnk5Y01MVEJBQVIyWVAxUVFnRnFUdTJMeFVvZm9wSGs5SXBWQ1ZMM1ZN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBOaXF3SWl0bldPSmtHMm52X3J0dXdtWEtESFhwNXRTUnBMTW9nTFg1S2hDa19jemdaQlFSZTZSUTg1LTNFVzI5WWVzMjIzdHd1MUczUEh0RzYwMm9aNFpWWldHOFlJN0gyTi1US2h1VGg?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2851,27 +2851,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Criminals strike amid police vigil: Officer's mother, jewellery shop targeted in Bhubaneswar - The New Indian Express</t>
+          <t>AI and the future of work: The jobs you’re not hearing about - BBC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 03:40:48 GMT</t>
+          <t>Mon, 23 Feb 2026 17:26:08 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNTm1ocEdYUm5felVSXzYzblhSNUxobDdpMXJGNm9oZFJaLXZCUWM2ekd5MmI1QVJFWE5Ma0lzd2NDRXpqMGwxWVJUdGhxM3kyRklYU2FCS21pTlZKVHVWWUpmWkdvTHdCY1dfWGhfU3k4bTFQQm1DSWQwWmttQW1veFFyT0VUVWU4TEVoZTZrOFljSFJVMVhhRV9WOGp0V2N4WEwxS0lOTTk4ekYzRFJ5Q2I5UmdnNjF5aUg4b3RUTUVBc1FSbXVtcERmTnJGM252Q3hCSHpDNjNKa3daeXU3NlNWNXo5WThW0gH2AUFVX3lxTE1OU1p2VVpfTmdzWnBjNnNxbHVpaVloeVN2OENoRjgzRDZmSmJZNnVYZnhocUw1SEdTNS1DdDd0NDZDUU10OHMwMWh6OGt0ZUtVQ2JqakRYam1ycmRoSFNxMUlSN2tsU2cyQVh3YWs1bWh1Z0ViM1ltZS1LMktfeXpBVFpxclp5RjRlZE5oRFlfanpBWkgyelZ5aDdBRnFzZ0RYd3dJckZyVEN2M28ydC1KUDR0dVBnUHZaUUJnMGhJVUZhdXFLWG5CVXlERk9aU0RNRExXNF9CNlJsRkNrNTh1NUVNRU5XVlltai1DQmNwTVdrU25RUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9WSHdMNGgyam5MVmptOXVBVEphTHI1LThIQXdNNERlWnRqeVhJb3Nzb1ZWcnp1ZXFVWkMzQ3hjN2dUMVcwRDVFTldnR3IwTW9vU2MwcUNkemg5YjA?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Why AI and leadership choices will define law firm profitability in 2026 - Legal Futures</t>
+          <t>Clearview AI and the expansion of US border security - Bloomsbury Intelligence and Security Institute (BISI)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 00:19:20 GMT</t>
+          <t>Mon, 23 Feb 2026 06:03:53 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5BNUtiU3lGQzAzbHRBNzZ1c1JiRXZNSnRTb3p1ZmVFT1h5SHpYcTktYkdXQUR6TlU5cEN2UHBaRFpzbXItVWJaNG1Cem9NV0UydFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPZVh6QjRpNG11SU1SZGg5ZEhnVzJrTU52WWtQTFFDRlVSSEhDcHA2dzJvemFSUFpOcU1zdkk2Ullwb0pfX1pTN2ZtRGh2ZHBXU3Y2SmNTV1FRNmJPMVJGZ0ppQndHNnhqN1haTG5TNEhfNUhKdGNXdlgxSnFVZm9HNS1fVTZrYzQ?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Relatedness and positive attitudes drive trust in AI and its developers - Phys.org</t>
+          <t>Nokia and KDDI demonstrate quantum-safe optical transport for secure AI and data center infrastructure - Nokia</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 21:23:44 GMT</t>
+          <t>Mon, 23 Feb 2026 02:00:00 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9wdV9TUXB5eDVLVWVmVDMxQ3Z1eHpDQ200U0g0Yzh2TnlQZW1NZFJRWUVGcEZVNU0tS20xeXlvckdWa1dRcnBmcU5Wc3ZiUGJDUi1oU0pITlF5eDZieTB5NDlobktaNm5ZWTVteUJ6NWZPS1c0RVdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNV054MjhuSEZoOExaOXdUOERIaVBPQzlYLVJoeUxTUVBWX2dfNU02aThmWnBPRVBoYUVQREFDejBHY1FsSWlWaDVVQ2FNN1UxOGxnZXFQRUExWTJCT1FYMUE2b0lJQjlXNjlRVXE1dFh4UGt6T3JteXByYkdLNFZIVXlrUFY1UjJyZTdQYU1rZGNQdmw5MnBsNi1kS1BqSE1yNVdYS1JQVmlyWlVYVGtNZkRrTVN3cl9OSlVWbWpjZklaUGlVek13N0JzTV9sVFk?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AI and legal privilege: no confidentiality or privilege where third-party commercial AI system used - Burges Salmon</t>
+          <t>The Intersection of AI and Attorney-Client Privilege—A Cautionary Tale - Ogletree</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 14:21:49 GMT</t>
+          <t>Tue, 24 Feb 2026 15:35:48 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPSG5rNm5ta2QwU1dULThNUzFjSTczdDhOem1vbFRvWTBvQXNKTnM4aFpuX2YwYkx2TlhYTFVCdGx4c0JFRFY3ZGZFSVVjVHpObk5tNG9UQ1I1ckxHWHIwaUlHR2xma1E2WDFCOHRyd04wVjRCQmtIU1lualQ1TDhjcmNGRFQ1SXlaTFlEbU9jVHRCNndRM3VVbVloTmxzSnhCWHBRS2tJUWtqdDlGUVJwRXNiN2NqSmlHdjlSLUtuNVNBSWJkQkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOcUlVeGdVODB0VEx5OTBHeEI2QkVnalZVdWRQNkN6UjRRS0c5dFVSZjMzYUVOcFR0TUYwMFJhUjlhRXBsU1dSeDNMMWpzVHZROW1iSmFFWG02Y1pNR3UwRzl0LVduVlhCeHRDZ2VMN2tMRVhZaU5LT1B5OWd1M2ViWS1qWlRSN1NaenNTRnNNdjhwaWpoNnhheEhNWUZPRWJ1MVVOeFB1em9wNHV4UnNyRk9DakZXT2stQl95LW9Baw?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Regulating AI and enforcing privacy laws through landmark cases and regulatory practice - Financier Worldwide</t>
+          <t>Building an AI-Ready America: Teaching in the AI age - The Official Microsoft Blog</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 15:57:32 GMT</t>
+          <t>Tue, 24 Feb 2026 19:00:42 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdFhBcjUzWVMtSWJud1U3RkplY2NLZjZEdmRPaHY5ZnB6VmtpcW5IVUtROWtqckFoMDM0ZzBVaTZvd09XYWw1MkEzeHRsaGpuNERoR2pBNExpczNQNEs0N21PWUxWNmtrZURoajJQcjl3c2dnR0ZiNE82NElhdm5sYTlnNzZrNjJSTDRod1FaVThUMFFKRk9sUUlZR0FqVHN3UV9mY2NNOW1wdXhhLXZ2RHRlWGJ1UG5yWW54SmdFRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPVDlQTDU1ejV2amlqaEhfQ2REX3FsSTB4NWIxUllnVHNMWmcxaFNJaTJWaWtZdEFvcW54NXRqODhVUjAweWxRcmFmbTZWTFhVQzRFN2ZvRlZPMExwV3o5UFJ5N09ld3BfTWt2MWc4Zl9nbGdtUFFIVHZneFNjc0pxUXhB?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New technology and medicines to combat drug and alcohol addiction - GOV.UK</t>
+          <t>Coventry University Group’s India Hub strengthens research partnerships through collaboration in AI, clean tech and healthcare - coventry.ac.uk</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 14:30:10 GMT</t>
+          <t>Tue, 24 Feb 2026 09:58:34 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSklZSWNINFN1MUg4WnB2NmdUaFIxR1hoOHN4TWdvRUp2ZDZMOEJsRzFrV09weF9qRGwwb2tlOWlNdEZtNlVTbWZSN2xEVTBCcjZnNUNyWmhwV2pPVXNzN05EYU9iT0tHVktFb1l0X3BuVVQ3TE1obnRzUm4wbjc3YjdpYWV0eGJUVEFHTWFBZWczWlQ5NFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNb1RCOXY4VkUtVmVfWThlM0I4NzV6anpqSUpVRkZxUzU1N051MUtYb1V6RDhkaXpLTlFvY1VINW15UFdjdHdWcUk1S1VXS1VTamx5Y09SREF5TTg4OXZiekYybjZqV2M5X0FhR19ScEQ5T2duM004S0FrU00wSDRjOGhoTHo0Z3A0X3g4WFVpaEpDd00?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spotlight on AI and cyber security at Telford College event - FE News</t>
+          <t>AI is simultaneously aiding and replacing workers, wage data suggest - Federal Reserve Bank of Dallas</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 13:18:05 GMT</t>
+          <t>Tue, 24 Feb 2026 15:56:15 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQbU1rSVVnWFk1VUtMV3ZmVWlCUzd0VFFMR1lDVEc4SnhyOWxDZlJxV1BaOXRlNl9iU1d5Nlh1YlRqSmh0Z25DSEJFUFFMRGpnZFZ1c1lDRmJMdU84VUtzb1RlOTlodkxBTDRENlJRdDFsU3V5OTQxd2hEWC1weEh0cl9pSHEybE9aZ1diWEgxZlJJa0wweHRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBQOWtReHktSFJSOVo1ekpaWTdNLUxUODBpUmdqd0h1OVRsOVVxdG9kR1ZaRmlCQzhIUWlNVTFtNGJLdkFRaE5PR0p1azBoVktPT3hoZl9VV21fOE5Ud256djQtTWk?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Risk without borders: the malicious use of AI and the EU AI Act’s global reach - Real Instituto Elcano</t>
+          <t>Wolverhampton AI and coding firm's 'pride' at business award - BBC</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 10:00:00 GMT</t>
+          <t>Fri, 20 Feb 2026 06:12:36 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPS0E0ZHppWEljRDdldThNRTNWa29fMUE2YnFJaUpNdEVzLW1pM2hTYnRFcjI5X0lMUWpmODZ2cVJOdkxRcFpfa2RTQ2hPYTZNSXB4SHNiM0RSYjRsU1B2YmtjaWZCR2p1R1p5dGRqMmtERlNFMmlibGdYTWhmc0VveG1TVldlNHVISi1Ecm5VTVNzRjF4X1Q4ODBzSy1vRlU3VUROd2J6QV9oV0pNbVZscXhmbnY5ci1oTy1ESjFybG54cGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE95d1Vfd1h1NEw4VHUwN3BnRkFoUmNqQ0hxVjdmVDFsNnZnMHBKNGNzVEREd2FlZzVJU2Q2MndnQUFXTE9zdkV3WkFQLVJQOFFjMktSQjNiU0dHUQ?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Agents urged not to use outside firms to tailor websites for AI - Estate Agent Today</t>
+          <t>Citizens’ CIO on the ethos that led the bank into the cloud and beyond - Tearsheet</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 00:10:10 GMT</t>
+          <t>Tue, 24 Feb 2026 13:56:29 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPZG1RSldnM2FpdDVhRnBWSXFwbnJlMjY1SUUxZmF5TDZFLVJaR2FmbjlYWUZIZzN5aTNJaFdfRmhJcS1PQU1MWXFEdTVhZTY4ajFwVDdxZFRmV05tS1VpODJLNGNyaE5sTlZudk10ZVhKLXdJa29vaEI4OXNqRFBObWVON3NYRVNEdVFyMXEtV25mV2JZVHVCQWxxNGdwU095MnhkdTI3SWQ1aW1fQ1RNN1dMUmU3MS1pVVc4ZnRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNR2NRNzV0eTdvMElEWnlVb0xvbVlRMTRNcU1wNlpDUXhHV0pqWGlQQ3V5LWdxTWFzYUo1djZ1OVNUdURZVUJ3dVlGNnFmcHdJMDRiNk1nVm5pNEJ1ZDlvV1NIN3RFRzNXa19WZnVmSnVsRGw0MFF3YWFfXzlreTBfbFJyV2RlMmhQRExxWmpreUtyZkFmNTBJaElJSkxQb25n?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Claims that AI can help fix climate dismissed as greenwashing - The Guardian</t>
+          <t>AI Is Upending Marketing on Two Fronts - Harvard Business Review</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 08:34:00 GMT</t>
+          <t>Mon, 23 Feb 2026 13:49:41 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNVkhjWktRSVpwRmxYa05yZ3FYU2x3OFRkR1BWZWpoWDdncHczMWE2NzEydjZmMGo0eTRTQWtXRWpOQkpTWTVRQVU1ZVNQX0x0YTBuUnNzN1Nmell5R1JxellLSkx6aWRrb3d6MjF1VWlRN3hNUHZlMFNzZDhCWlBWMG5IUEgydVNvd1FpS2RQODhBSTdwU09VelBobFRNbEVaZzRaaDlRRWlhc2RkNHJYZG54ckZ4NFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE40Szh6eEVXajluSmo3U2VlZkN3bkFWa2o3UW51bXVaRmZLMlRXX3BacDYyMXNNZjlwbHVNVEs3N2l5X3RYbjlHYkYwYzMtRFNNZFRaOWRTLUtGQy03SllpSmRlQ2VMMHlwZ3ZNLXpXZw?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brokers should beware consumer AI and hike data security: Mortgage Brain - Mortgage Strategy</t>
+          <t>Track AI and Thematic Funding Flows in Private Markets - S&amp;P Global</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 09:58:50 GMT</t>
+          <t>Tue, 24 Feb 2026 23:19:06 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQVE16OER3VGZLdC0xZmVsTEVpOVBoQUpGcmw0RWlzQ2NZNFdGdU56VktpTFhVX3JZT0EtSW9NQ0txS2tlZS1ucnc4WFl6LV9WTWM1WjZlZnl0Y1hBX3BLOE0tZVdoOUZHWW9RZW9hX210TlRwSlNIWnl2eTUzR2F6elVEV2RBVnNXbW5BQW1CaFBCU1NDVEdDMXNIUVpMVmJ2anZKQW5MOUR3N2t0R1Z0ZHRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQU3R4MjBtZk9iLU1CbG9DMlViWnJnXzByc0Y4Y1RVbjhkQk0tYWpzbjRQMl80eXBraHRPNzZKNFJVX194eHpscnY2SDViLUJmUjZ0TnVUOEt6ZERTMzdPV3BnSFZNY2UzNFNzU3JJV2J3WE5SZzhLSEpWQl95dUNtcnU3d1luV3ZYM1ZMMnVDTVNoY0U0bFRQMHNYRC1WUGs2QUlFa2ZVeHZ1RmpzWmRaMWRld1RLblNoR3dYd2lHMTU?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Donald Trump’s AI push fuels revolt in Maga heartlands - Financial Times</t>
+          <t>Ex-Mail on Sunday editor says allowing hacking and blagging of senior politician would have been ‘crazy’ - The Independent</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:00:44 GMT</t>
+          <t>Tue, 24 Feb 2026 16:09:00 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5EVUIyMVloOTlUc1hjMTlLTGR5RWU1SFFKdGx5UDZQa0IyOUcyWlJNR05HV3FEX2s4eWtvMm9mMW5NWVdWUGtHWHFtdmg4Q09MZDRpN2dfVGc2RkhsQ3loRGpGTzVOb1hrZXZZRVBpckU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNMzd0S3RULWswY0thUUY3TkxrUkxfT1c1Z3dicXRLRkpKVDVRYXFmM3dta2JhWElJaU00bHh5MVlUeVhBQ0toQWFjYm1tTTBBb1RVX1ZrQ1lFVUNNNU9YWHJHSjJkVXpobVdVVndHTndZWW00aGp2dkxwTGRLZW9SQnV0Z1JIdm9JN3FNM1VyUW4wWkdTczR3?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ramco Systems Introduces Chia, an Enterprise-Grade Conversational AI Agent for Better Customer Experience - PR Newswire UK</t>
+          <t>Sam Altman defends AI’s energy toll by saying it also takes a lot to ‘train a human’ - The Guardian</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:00:00 GMT</t>
+          <t>Mon, 23 Feb 2026 16:38:00 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOZTA3WmdIcTE4QUtwTzdkV2NBcGh4WlMxU2QzYW81bjloSkxSZjZoc2NnSXkwWFMycUE5WWswajNvU2R3eGg2RWlFeG93YmxwdnlINXByanIzTEtHeHlrVVllUzl0aEF6SnhuQkRWUVN3OEpMclMwTXFIdmFsVVFxS0pZSUFPQVQ1T0tadjhGcERfd3plQjluWmNnZl9yUHVwWFZrVFU1NjVsZTlEenFWUkdjaWFDNVJHRURUa1E4OWVXdWtUb3p2dGlDNTUwOWtBcTF2U29rbHc0VENMZ05MV09qUDNwOTFVYkc1UV9qTU9XZ0J5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQYklFLThXLVhsMDkzaFVUcF9HZVVVU0xWdGN0WUE3ZlpfeGZrQ2xQWjV1WUFaSTdHSzV1dU1heTc0bVFTUXNQa2J0N01MVTFKOVB6dHo2Zkp3X1hOZVp5OVVDU0xLanlrWHhfdVVfeTVMc0lNTldxVkZLRk03VUY3Ulh6V2V1UUpXejRvOVdmUzFPX1VoM0E?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Google Cloud partnership pioneers next generation of consumer goods technologies - Unilever</t>
+          <t>HDRO co-authors cutting-edge research using AI and satellite imagery to estimate HDI at a highly granular local level - United Nations Development Programme</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 14:12:00 GMT</t>
+          <t>Mon, 23 Feb 2026 18:36:28 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPX044Rm10MlNjTkswYU5yU3NPS0VkWDVlQk5RTjRPUkgwRnBLTUE2aTg0Y01hQlRFZVgtZU1WLW51SWxBV0tzYlJyRlVmeEZwR09kZjBpbG5JaU1VdmRGNzluNWJfN3piZkpiUFhENm5KYUU1Z3B4MGlXZlYyYlNqX0xjd0pMakhjRU9GRVVIaTdtNjNENE1Nckd0c0lMOGxNbDFlNFB4cjZWckdSSUFyeHVrbC1mbkVub1FzZ01MUzhKSnZxRmo0NXVJMVZyeVRrMXJ4S2x2dWR5WGxOc2FDNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPMEgzNjZqVjVmRzNyekhKWVUwOEU4YjI4UUtwVlkzNExld3hSN0VaNUUtb1hFcGQ2VTN2aGJwckVRbGcycm5hUW41dmNKeERYNnlwTldXb01kdk1OQWJ6eGtSdnoxYUZIWUlTb0NBeUZuYmJjSklON1RrX3phVGJwaVgyTzZTSlRzcWoyMTdGRUtHdlRTcnU5emdCUGEzZmktMTUzX0FmWlRaSlBLVzcwNHdrSVJYVHdf?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Private Credit, Tech Issuance fuelled by AI, and Increasing Leverage Among Key Driving Factors Impacting Credit Market Liquidity in 2026 according to S&amp;P Global Ratings - S&amp;P Global</t>
+          <t>AI Governance: Three Lessons from the Global Digital Compact - unfoundation.org</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 22:46:18 GMT</t>
+          <t>Tue, 24 Feb 2026 22:11:51 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxOd08zb2JqSmJqVEFBMms1VXRFNFRKNV9pd2s5MExwTkFHV3NBZ2luM0pEYkF2czI1TnlOdXVKcDRTb0lkYnNRZjBGZlQ2ZjFmczk2NkRKenY3LWZraVhPQmFJQ3lsOTM1S1UwYlJMZllSUzBGWTFfYVcyTVo4eWxlMVJlaXNDY3lzcnJCak4yMEp0cFV5ZHYwN01tQ3BpSXlrbGxDc2JNU1I3Z1pmcUpaUjRSUGh4X1prc1pJOUpuTUdreENpdXlnc1JONUN1ZE94R2ZJU3lrQWYwZ2dvTTU4dTB4cHlkUEhxT1NYd0h5ZHdUR2NtUHFEOTBYMzdaaUNfSXh5dEd0SVYyb2ZkWFE5WjlaV25pRFVXZjFCVkhHdGZ3cVRIMHpSbTIzeFFiVk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPZVdwTXRHNG5XZmNpMEZfSVhYMDJaSnlSMmRFdkEtVWxCbHRnZ1FhX0lLZkZSS0UyRlZJb0VPZnN2SlRkZDFUTG1xZUZIZ08xVEJ3bURqS0RRRThGUEswOTBYT0V3b1lOelIweTVmM3F1enFKVkQxQ3M0VnU4MC1kSGJPTFdFNzN4OFhGTGxKRU1IT29YQnpBOUZzOA?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Why AI Adoption Stalls, According to Industry Data - Harvard Business Review</t>
+          <t>AI upheaval forces software industry to ask if this is an ‘adapt or die’ moment - Financial Times</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 13:45:36 GMT</t>
+          <t>Tue, 24 Feb 2026 05:01:05 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBUcE5UaWlJb0R3bU1RLXVvZzYtclB3M0tRajVITW9ZSXZTbFlfOWRwMHNmdGpveC00ZWtVRVpMS25odTJ3Wm95Snh5N2NVLTVITUxNUko0b3JMdFh2YzBDRDcyOUgxazM1TTlGRi1CdkNyYldQUl9RUjZjcDBZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1INkRweExVcThnUGJxeWxBZXFKdkFLX2R3YVFPX2NRQUdpb0V0SGU5Rm5pMmJ0SUxPUHVEUWpwUlJPSkpQLXdCV00taDlTUlpPNG9URWMybXlJVFdsQnctSXVsTnJUalFHc3FzcE9iQlg?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cloud and rain forecast by Met Office for Portishead this week - North Somerset Times</t>
+          <t>Travel platforms that survive won’t choose between AI and people. They’ll need both. - webintravel.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:00:00 GMT</t>
+          <t>Tue, 24 Feb 2026 13:26:18 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZVAyYUxyV2txQWhOY2VQYUt0T0QwRGFySUdmZ25zQjBWdVpvalVTRTJla0l4Z19KQ2J0UWlaUGM0UkRNODA2Tmw2T056Y01HbEVyVDdNVklqOVhUTUJMTXJYaGYyNzNBam5XdE1COFQwdWR1ZjBrMkJxSjJtMVlxaHFRUHFwVVI5cWYyb2NfeXBUXzFubWhhcDNrbXFxYjB2UWVj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNLUZfQUJHN0ltOGFQeHlWVDRLcXhJcDBWb1JGT3ExS0JNXzBwSDZZV1hNSmMwTnMxQ1dBeURucVh1UThPYl9CY2puZnlzeHl6c1VRT1VLR0dfaVcxLURGMmFsOUpWMzNFd1NGcXR3VzBnc1ZWS2h1Qjk4ZndOT3Q1azZCOTY3OF9TNjR6MG9yNkVUakNtMFo5OC1feGVoandKZjFiTERia1RGRHotQWc?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>We need to act with urgency to address the growing AI divide - The Official Microsoft Blog</t>
+          <t>I hacked ChatGPT and Google's AI - and it only took 20 minutes - BBC</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 23:33:39 GMT</t>
+          <t>Wed, 18 Feb 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQOG9fTzA1aTZ4ZlJlVERDNnI0SWtvVVRJWjNnU2JnWUpyMm5sWEhOWUVGNDFJaXZ5YzI4VnFNN1o4Um15NTFSam1QRHBjbHpycjZzM2FUWXVMWnNZRzVXck5kWXNRUG80RlBuVTVINURrY1dZWmJvMHRnTzdVQ0g3YUNWMHRTc2hVX0k2ZTF6SnZTZ2VzUFhYbGVoNlRSOEJfWEhPU3pmSlhMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOV0dONVVvLXFTREpTMGVLdTJuN0ZiaHpZZDU4enFRd1M4TDQxQjcxLXFnY05CNkQ1MXRRQVRMalg2TTRJZUdUYU9ka1hfTWZqaUsybUFlMjJzTlEwY3l4bDRoRmZrYklXTldFSkFvUUNfZXl4ZDgzUjNqTk16UlIweGZueFREbnNoS3NaR0toYmdMNFl4NlN0ck5LQS1CNVVUVFRPVDFB?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FSS Future-Proofs Middle East Payments with Scalable, Sovereign Cloud Infrastructure - PR Newswire UK</t>
+          <t>US AI giant accuses Chinese rivals of mass data theft - The Guardian</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 06:00:00 GMT</t>
+          <t>Tue, 24 Feb 2026 00:31:00 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOMnJsa25nU0I5cFM2enY1dFM1MURGT0VsNUJkT0VVOFVTSmxLU3M4NzhuWUpUMXIzRnNYTGs3Q1lVcF8yNFd1cDlVNFBkUDJjSnZ5dDZzcGxYbEMyQm1HNlhIVnVhM0VpVW1ma3RvVUpDN0FhVERTMHByTXR3WkY3M3c3am9NQWFSWjdHTzh2czRtWXVqR1F4eWdkTGFSS0V1YVI0cms1UkdBMEpmOEZnRUMzREZWODV6aUJTVklaRVYzMUpYcTVpcW5hLWEzY2RWQUotdE9fOTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBjSTZTNVNoNVFnbl80ejNOdUJvQTdpNXlmWFBqM3NaTXRsWU4wbkRFYmRYSktIT002YWdUampiV18tUXBMR1BhMW5aWU5jN0RKWnV0cnp4enZ2bjg5aUNKTjlPLWs1ODBPeVh0bExuMjNXTlVEeEEtTTltdHA?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AI’s workplace revolution is here – and anxiety is rising with it - The Guardian</t>
+          <t>How Generative AI and OpenTelemetry Transform Observability - Bank Information Security</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 15:39:00 GMT</t>
+          <t>Tue, 24 Feb 2026 13:28:31 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOWFQ5bThLYTdnMVhyMENWblE3RHluTFpIX00zQ0w1V1JpcXBmTHBqTHlIb2Z2NmZwUDFvRDBsY3JPc3h6OVlGazVzcDZJaFl1VU1Kb3BKTW5NWEdaWjg3c2xkajloRXBtaTFHSmxBdUsxUWFPOHk1SHY5MGVZU1RBV2lEWGphUzlKQWMyRVlvckUyaG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNZlVqTGI3TTRIc2Q5UlhRaHdmY3BTWnhleDdCX2U4MG5hZkRXOEFjZHB4cUZWd28xVFh2TUFKUkt4ZTVFdWRZRnBnYUQxZGpJeExrRTBWVnNQb1FvTDBoanJ5ZnZtRXV4ckFRbW5udmdHQnI5OFdMSVRzbUtpa09EekVRaTgtYlNVZjFGLWYzOEh4eGM3Z0wzcEc0aDlJLTFHSEJR?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Guest Post — 2026 Global Strategy Briefing For Boards on Quantum And AI - The Quantum Insider</t>
+          <t>Document management: the missing link in AI adoption - Economist Impact</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 09:18:20 GMT</t>
+          <t>Tue, 24 Feb 2026 12:08:35 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNG5vdXE5VHNLZ3BtYUZqc0ZLbXlITjNjMU5EN1VOcFhnekk3bjVZRkdLR0NZMW5aeUZpQV9FVkVCVzhmUFJYdDRuNU91cHMwd21lMUYtbk00anIxMzk4R0UyM3pEczRwZmwyZlVVMmxxSm1wdVNHdWJmNjR1aE9rb2o1cENLWUF3ZnlSNFBObDFiMlFHRkh1dmN5QldodEQ3cmpJdlRhbmV2bk4zTXpVZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOTVhWSlU0ek5USndoRnA4YWdVdUVQN0xPSFg2TWhJYVNvNDkteWw2TEpiMFdfa0h0Y3lMU1FBTHFRbG05NDdDTGNTV0w3YXp4a2pidFhJX2J3Nk14WUc5MGF2Vk5pLUpjUVJXdy1ya1A3SlhvRGdLb1NJX2NhRjRfalQtT3RoSmtkLUsxTk1pLWNHUkxsZTRz?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Could India challenge tech boss power at Delhi AI Impact Summit? - BBC</t>
+          <t>ISIS teaching recruits how to use AI ‘responsibly’ - politico.eu</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 11:35:09 GMT</t>
+          <t>Mon, 23 Feb 2026 12:02:00 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBPSEtXQ0trd3o5V1lQbDF0NFhZN0NNdjRBNWo1U2RkcWhiV1E0bVZNa0Rmb1lxNkhkNExfMU5NOUUzNV9xWlFpbzIzU3g4WmIzYnh0NUl2S1dmdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNZ0pqNzVBV0phcTZwS1JHVnB1MHN3ZFpBWTJaeU1JX0NZcVJvWHFWcjBFSGh6TWhiOHhES0hrcVp1S0x5Tm9CMXBSRHZDWkQtY2RFNG9WRUV4ZkdSZkNqUEtwXzhSM1U0YUxfd0Qxczh2Qm5hbGNRUXpZN1dNdEFfcWptLXZCVFNQ?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>How one chemist is using AI and robots to automate lab experiments - Scientific American</t>
+          <t>How Teens Use and View AI - Pew Research Center</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 11:00:00 GMT</t>
+          <t>Tue, 24 Feb 2026 14:52:52 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQV3BWSTFCUGg1UTE1cXl1aXF2RjMwQzJiSnRnR0w2dXV5anhrajNDaFBTS3MxMkJFQlZDRlotbmF6cVVYUEhGN1kzdS1hLXo0TjdyTUxhVWJNQWllRXRDSzRtZ2FBa0pYRWxqVTdzRDE4c21SaFNiNFFSWW42OHpOQ21aZU0wTHp0bDZscmJDRGx4TWZHSzVTM0M3ejVIVlNmZnFyWUtDQVZ2VGpSN2Nz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1yRkUwZ2RkcENYZURtNmYyTW5XenJzczlSX2xaXzNiRldjV2JhamYwN3V1UXVCZHc2NWFTd3lCNFBPSmp4OWplQnlKWkdpYmtCU25QTHV0ZWozcnFXc0kzenBoMVBWUWNlV0JqWkpvcHRod2FJWGN4WW42RjdNNHc?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3541,27 +3541,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BoE AI roundtables reveal constraints to responsible adoption - TheBanker.com</t>
+          <t>Former council worker jailed for nearly £900,000 theft - LocalGov.co.uk</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 11:26:53 GMT</t>
+          <t>Thu, 19 Feb 2026 13:20:03 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5yMVpQSzBVY0VxTVF5NTNOZ01jZVZVNUN6T2xQNFRPOGJXaEsyRHluT3Y3OXYyeFlIOGk2T1VCWmFVZldxT21NQ2gzU2taMm9NRlBDaUQ4YjBaQkJfRm81RWh4b21jZWFBOFZVbEJIRmhSZjJUN0VnT2pn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQWkxBN21jTUU0YU54SjRKWXdCZnphbGR0VDAyWDl2a3Z6SVNqamZ3aG5pYnZHQmRaOUVfWllRcEQxQU5yQkJuNDFDZ3FfYjZqTGFTdTc5RXB0UmhqcnZKZ0kyNE9xa3NSWHpacVZFOHhlYWJxTTd1QUZ5ZE9aQW9QUzZDcDc0T0RYa1JVd2N3?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3571,27 +3571,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Alphabet (GOOGL) AI, Cloud, and Waymo Provide Multi-Layered Growth Optionality - Yahoo Finance UK</t>
+          <t>Man jailed for 30 months after driving test fraud - BBC</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 13:23:48 GMT</t>
+          <t>Fri, 20 Feb 2026 16:57:22 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPSFFDOWhDSWVmdEtXajVhRDkxd0FQZS1ESUtFZS10ejg2QVRhVUpsMjJHUHRNNDRfaGlILXE2Y0ZKaDdkMUhKaVBZdHN5NGY5V3RPMDZOc3M2OFVGaG0taE8tbXo0Zmg2dnk4eF9KT0swOThOQm52dU8xNXZySENWS2p6SGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5yV041SVMwTGtxa3VpaFlaN2RJdWlfa3RYMjl4MjFTZFl6SFBUcTZkWmRoSU9lNmhsZkNBME9qM3RCNldodUFXNlNKbU55S0VGWE81QWJWZWFmUQ?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3601,27 +3601,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Musk is wrong about AI and retirement: You still need to save. - The Japan Times</t>
+          <t>Two more convicted over mass UK car crash data theft - DecisionMarketing</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 03:45:00 GMT</t>
+          <t>Thu, 19 Feb 2026 13:19:00 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOZTB5REU3NGxjeG9pZlUzek02bTFmanFpMnhERUJIdXJQc0dyOS1GbDdsd210LURDUGVDUkkzUGhycFh2OGk2MWlnTktoSEp4UnhiOWVia091U1JMN05US0NROTVJdFZJZEdQWXBwMmxGVVU4MkdMNW9fNUc1NG5FX1RZNWpFcW1kR0F3eWNMc0FxVnhJeU9J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQRFcxX1pGcHVobG56SV9fNnVLTVhrTU4yZmhzTFBlajBEaXVJcGpOYVZxdmpLZzFieURpNWw2a3hrVXRlb3pRYkJOQkx2Y2twWk9LSkJjOTZWOS1TVlZvVDY5VGJFMnNEdjUzZ25qSTFvUFVYWHFkZ2pTVGtja3NJc3JrWkw1Vm40eWJGVnJ6SXFWV3ZOSU15Xw?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3631,27 +3631,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>‘Agentic with a small a’: CMOs are adopting AI more slowly than it’s evolving - Digiday</t>
+          <t>Accountant sentenced for stealing £26,000 from food bank - Third Sector</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:02:14 GMT</t>
+          <t>Tue, 24 Feb 2026 08:20:13 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxON3BXX0t4OWMtU19KRk9tTXBXazk0UFhpUTd0b3Z1aFZUS0Jra0pZSXRpX1FLNUpoQ1d4dGZyX3NWalhGTnFuVUh0V2dHZTlSTTNpMXV4RjJMRnpMTm1OTU9nZjlpaXRSYy10eVZCYTFFYldTTGpmZjNmMkEzVklGOGVlWlBDVWZuNWd1Z3VLTmxuUUJhVzh6YXJja1RGNmRTdFFqT2taRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOUHY2VG9lbTZUR3M0aVEyZGt6dXlDb0xldlBZLXA0Z0MwRTFtV25XRk1xbmowTWVEbERZajkwZnNGTElZSTEwMTEyNW9yeWN6ZWhtTkxsWldlUjhnOWZSYjBmTXlOaEYzUmZZZ0UyeUd4Umh4SkRLNGdCTU9zV1Q1cWRScWVVZ3NZcFpqb1llTllpOHRId1RZQ0U2a1I4YzEw?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3661,27 +3661,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>How AI, Cost Pressures and Reskilling are Transforming Talent Strategies - aon.com</t>
+          <t>Bulgarian tech employee sentenced for Russia exports - Global Investigations Review</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 18:34:36 GMT</t>
+          <t>Thu, 19 Feb 2026 21:29:03 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQbkQtT2dxX0hKejd3X3gzcmJuSTIxS1hBVUdocU5ncHVwcnhUTkMtSnNURV95UmFSLVl4aEhQQWpaQ2NST1FqY3ppNDNVZVNMWHlYT0JnUldmUEF1WjNyMXZXYnhfa3gzUWJyLW9Jem9iQXBrR3RtQ2JzSkVwdlVIYXNZR2tLTXdSUk9KNl9JZkNIdWp5LUJ5bF9tazUxV0lwRDZrSWFJOGdDUXNSQmR2VWlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOVW10QlBWQ0RfYXVIZ0NjZi1qbENpZTZyWUJkY3U2emd5dzFhbk50bV8wRmtXM2g2dm95bkNITUhUZjJvQ1JJU3lsNThxanl6azEyUnhGSHdSMDBTakh6OEREc01EMElxbTJJWncwdWpSbEl0SEh4OHlYR1NseVdNdjQwOTZKdDRCcURaVk1KSDdDejNYcWlVXzlQTEhTdG5MNjdVTzViVWo5ak1LRWpn?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3691,27 +3691,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Questions About AI in Shareholder Engagement Meetings - Wilson Sonsini</t>
+          <t>Ukrainian National Sentenced to 5 Years in North Korea IT Worker Fraud Case - The Hacker News</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 01:14:11 GMT</t>
+          <t>Fri, 20 Feb 2026 09:52:00 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPaVlnb2FkT3VBSVdhdVc4TUdpVE9nSklldUlZa3ZHWE9EMTZIZjZHa0lLZlRsT2VUSF9VSEtMTlgzREFrYnhuOHZ6Tnc4V1VxTUNhUmVVMWo1VTUyTWV5OUIxNl9ndGlVOHJQY0FuN3NvTW85Wk5VdXdJSTRwRU44WVdFZHJDWElJb1lTSmFiaGl5M2pJWlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQN1JuYW5xeVRrQ1B0bURicUNhMjBYV3ozeWVJM3lzTUY1cS1oVW1oelRBMVdCU2NKeGpJRzk5NlU2bk1XcTN2bmhpMEd0a0pLQWlFZmhCZnlGVVVLTUVZYWlhclpBaVlLMUgzalo4OExKMm1SSlhxYjFBSXJvWXhlQzhZX1k?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3721,27 +3721,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bournemouth University receives over £500,000 to improve AI reliability - Bournemouth Echo</t>
+          <t>St Helens woman created 'false invoices' to steal more than £120k from employer - St Helens Star</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:00:00 GMT</t>
+          <t>Fri, 20 Feb 2026 17:00:00 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQTEVwX1JiRHpPc0xFWTU5RWRGTkxleDRkT09wZml5NkFQalBhdUNGOEl2R0xGYWFHZS15LXB4QjdwWEJiUFEyRDYwMW50U3NiLWhKNzYwOXE4QVl3aDdCRG1UekpQODJUdlk2dHQ0a0JkZk9SSWFtZ3k0aGFVMThmVEhLNkZaNU8zN2dlUlVqUm5sQ1M4T3QwZl9GTnZTU1d5X0pOYnpRTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNllPaWxzRFptblNLWVJOdTBKMFJsX2ZNZXpRZ21OaHZoM3k5dTVXZmg0TGRRN2k5c0JMX3hYem1PS0FlZVQ5NlozQ2RwZE55d3ZvaVd0RVFqV2lLMEcxWnFnVlgySnNYWDAzV0s3X2trTXR3YlZFc3lXMGV4VUt2N1hLYTV2ZGJPVmZmNWtrUGRJWEpqVWdWRTlR?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3751,27 +3751,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FinovateEurope 2026: From AI Hype to Operational Reality - Finovate</t>
+          <t>'It nearly took the company down': Trusted employee took nearly £50,000 from landscape garden business - Hartlepool Mail</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 20:57:44 GMT</t>
+          <t>Sat, 21 Feb 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPcW83OHFpSGRVNVFTa01rZVhvR0UtenIxUUx0V1ZTQW5FUU5KbXFVdmtZVk12cnFqTGItd2FEVXRSMGlqaThQN3VUSFZrUG1TV2IyVWkzeV81Um0yaU1ZbnBoTUxhU3hVR0lxYm9GX2Fvdm95STlGa3BWRVNXZm5LdjBybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQNjB5bENCVjU0QmRsTWQ3WWpiLXJXY2dsM2FidHlLbUZqVFZjdGc1dXBqNDNTUWhCMFNTTGItLXA1dDJMbklPTk5CRTJydTdDdHV0QUhhS1JuMFByOHN1WERHMlpxODYyb1hoNk01UEdaSG4yX0d0VUJ1LXZOZ052T0tLc19FMGRmSlNQcWFSbW5weTN0WXRtOTNZT0xUX2hzT3RMTEZ0eXU4aVZWNWNrSEE5Nzgta1A5dEhDYWhET0s5NzR6ZEpiekN3?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3781,27 +3781,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HIVE Digital posts record Q3 revenue of $93.1M, expands AI and Bitcoin operations - Proactive Investors</t>
+          <t>Greggs thief dubbed ‘Hamster’ by staff avoids jail after 38 raids in six weeks - The Sun</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 17:55:00 GMT</t>
+          <t>Wed, 18 Feb 2026 19:57:00 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNWC1XVUVWUzN3VllfcFNJanlOOVFNWWFrZmFMQWRDV1I2U09EZzdYS3JUdTF0b1B3OG5YTFJ0R1hMZ29WbTlfLUtiQzh3LVBZTWtGN3U0Smx2RkJOWXFWbmV1cVh4bE53T0tZTlJWa2ZCNDVXSEhXYXdIbGx4VUIzUFQxRTJhSTF5TU9DR2U3WDVzUVVIYVhVRk5xdVBTYlVzeVl5d2wwd0h6cjhFeUExT242VVM5dzNHNC1TdkR6WFJsNWhTT3ZXLXNLbmtiWHkyLXBVTUFRTE44MlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxON1hYbmx6SzU5c3pmSy1jUGJXbVhGNWtYTld1ZllIcnU4c21xdnNPT3hLc3dvV1E0Rlk3czZqcm9KbHhQUWtvcWxyekY1cW91SjhFbUwwU2VscjFKNTM1SjJYUE02WmJIRlc5RDdyclN4amVpeWlpbWNBaUNTZjRRb1d2Tk5PbThuZDBKVk9Kbw?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3811,27 +3811,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AI fueled massive surge in fraud losses last year, study finds - Supply Chain Dive</t>
+          <t>Former Maryland correctional employee, business owner sentenced for fraud scheme - CBS News</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 00:43:27 GMT</t>
+          <t>Wed, 18 Feb 2026 16:18:56 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOanZVdmZhU2hXZEVkWW9FcmYxYk1ha3JVZVoxaWxlMFRxSFlmRDhCUmQ5Uk0ydlBiYVRYdTJVZDE1S3VuYzAxSm8wakZYUU9EMGNaN2xrSGtVLW83NnhoMWdxV0pzZ1dJTmZYQVZmWVBFZmRncG1XS05SMkRJRUZPTFRmMi1OdHNkbHc3ZFZoZWpWd2k5QXdNWkRwUng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNQS1mM2RaTEVDbk40UE1VN0RKNjR2bGU4VXpEYUhCN1RsRy1ialpLX09pdWVGZ0pQU1Y5TzcxOUdsVjhhY3hvaTNzNDlxUWh0SGNUT1p0cEJYNy1qZ0VScDRZM0ZyTjRDdHVZVm5TN3BRTzA4bVlkS1FqMUVPNUg3MFRnbGl2NVFuODFDYld3MGF2WHNmcXVyZ0pGaDIxREUwTERR?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3841,27 +3841,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Can the government trust AI to answer citizens’ questions? - Civil Service World</t>
+          <t>Indian American Optum director Karan Gupta convicted in $1.2 million US ‘ghost employee scam’ - The Indian Express</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 13:03:29 GMT</t>
+          <t>Fri, 20 Feb 2026 10:21:27 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQamZxMm16UkF5RmQxSFJPMDNlVFhkTzFEZ21CZVNPQk1DNURrRU02bHB4VS1TWkVOTXFoUkI0NHAyQnRLTE9lN0llYzM2TUc1M2oyZHl0V01rOGduN082MHVsYThPeHBLRTl3VlFKYUpORXVuX3U4RllzSDQtOWQtc3dxS2pQUGtmTlpLX0hsNDJxTld0aGZfWUEyVWtCVVZlR3AwR0tIQW1sRm9w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQnJrTmlXMjFfRWlCVDBnNEVZaHFwMk4xTS1jeEpwbDhSU0hiMGctOFpzTlFjZzFFNXBJdmxDaWN5X0VvaXB2eTBCbTFUQmFvTnFaTUZPS0lBMkcySzZRdGpzOEVHSGRlQW5qcUJCalR6X21FLUlrM2V6SnFaS1Zpc3ZvN1RoQ2laaGxwaXhDVVlNUi10SHF0c3AySmpyT0ZkcndaY1BhVUlYUTZiUUZud0JLdzVxS0RxZ3dUb1R2UzRNdG1xWnlGQUo5X3ExNUl2Uk5j0gHaAUFVX3lxTE9zSVFndVRkSmxvOGZKNk04U1BJOGZzVDJkdWlPWGY1X3M1cElZVWpVX3ppSU82NFhvRGxWd0ZfZWUzMFhFYUVEVUhUVFBpZi1ocDU5X2RrOVJsVG5ZbEFMdE5kZHF5bGFvT1dfTU5XYWhmSU5oY1I1M29WUXAzX01VMWl2NnVISmVxTjhBTE82T2tyOGYzNHVGSkRkUDd3R1M5bE9QZHN0cGMydlkxNUxDRHVxdnVPZDBycjhfSWJoOExlc3VtWGdGNE4tNEZNYjFZN0hpeUl3bHpB?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3871,27 +3871,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B2i Digital Supports AI &amp; Technology Virtual Investor Conference as Official Marketing Partner | Corporate - EQS News</t>
+          <t>Dolores Ingram murder: Man sentenced for brutal killing of 82-year-old mother in Bucks County - 6abc Philadelphia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 23:11:12 GMT</t>
+          <t>Thu, 19 Feb 2026 03:27:03 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNelVMOTVEWGVFSS1QVjB5NkZ6c1NoZS0wMTlDYTlPckFoM050d0JHck90RGI0ZmdIdWVqMlNfRE1TQkdabVlQTFBBRHhkOUZ1Zk5JRlota1J3bG5EZXE0MUp3MmYwLXlVM0xuMG43X284YVh4VzNLdExhZVJqdW44N0hXRmxDa3MwNTl0SVRZc3hmUzc2dTRHcFY4dFNZd3l6dG9CdG9uRzJvWWNuLS02ZTlQdVJJLXhCS1NQUjFKUHBRRTh6YVEzMmhqQ2VNWWtGX2ZWTURHeC1OWVRNZGZlaDExUGVZMlNSd2RsazJ6QVFkM3pxNVF0U0xpdTBMaUNjaHk4YmlMcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNQ05KWXQ1MGQ4TmdXMXlhclpjRGRqb09wVDlXQWdDVGRBbThXSWJSM29xdkNvQ2FocnhKYnFjWDd5UTNROFg1SkxBNXc1QXZ4VGxJQkxxQUd2VlVtMjJDUDRTMXdLeFBqZFkwYlI3b3RBc0ZId0N3SEZMUXVLbWFfTmZETkVIVk5rYTZLSFZqdF9PUngyNnU1NUhqZHRNOG1keHlUZDZWS0hMVU9NZWpPanJDSkvSAboBQVVfeXFMT2Z6eG1XTUEzT2k5TE1iVl9GbGotLUREc2VvSHA3YlVlaDR6S2hmMDFQemQxdFEtZlpKX0FkTFpyRDhhUmRXdHYwdE9HUG5ZcFU5aGJkYWNwMDJ1QmJoYzlxc1Vib2VpNXZLRUdNWmFHNVVCcmlBMldkYVhaNkZwZElpb3BMSGNLOFRjVkZnWjZJZlNsV0Q2Y1NnTnZPVjFPZXNod3BnWk9oQ3k1TEdlRktHZFYybmFMay1n?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3901,27 +3901,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Meta Builds AI Infrastructure With NVIDIA - NVIDIA Investor Relations</t>
+          <t>Former Jefferson Parish corrections officer sentenced for $80,000 payroll fraud - NOLA.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:44:17 GMT</t>
+          <t>Wed, 18 Feb 2026 21:30:00 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQMkprQWZPNzUydGVZX0IzeXVEWkd4VVBsVHlzRk1LaGRlcjVOYXFhbmVmNlRHRHMzNGhTMHFmTnN2azlpcXRsd015YVJBMnVNVjRpWFJSalNQZ3Ryc0hNTThMOW1QTEY4S1VlWlMwZktPcnJLdzNiRGhPelg3R3JKUVlWUGxWM3VWN3ROY1RTaVZNbVFsNVJyQ2FkYk5mZGhMZ1NqejlOYkdReU5TeXpUeFdKS2o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxORjk1WkJnN256dHhmZ0NEUjMway14T1cybVE3cGU2YW1iUFBLWkxZdHRSa2N3V1ZTdDJwb2VzMl9lYkYtYWF2SkMtZnNyN09GN05ZT19DbloxT19MbWE0QUswanA1anE0RE1qVDNrMmhSNEpBekJiekluZmZDWXNmTE1qTjVuMTJNZC00cTRkWFJjcVBiOEhpUUFPbVNJcVRNUURfN2NQX3AtXzVtZC1zUUs3QzbSAboBQVVfeXFMTmNJRzdUVlFHc3VaV3VVQzlGRjNUTmJ6c0R3MlA1QTZSNk9GbGk5OThVcWk0a083S2dSb2JPZzBkLXpXUjNpQldSZ0RVRm1VRTI1c1RaY0h1ZXdaeEJEN2Z2Z3I0WkVUQUtTbDd5WFg4VEtIcEpnNDNNMEY3aDhoNGhuSmtBTXJPcWxjRlo3THpFZDJfeUJHU2RJWGpEbG43VXQ3YWZUR2hXNWlhQ0x3M29zZmZZWGpRaUN3?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3931,27 +3931,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AI Compliance Monitoring in UC: What Works, and What Backfires - UC Today</t>
+          <t>Court jails bank employee for investment fraud in Kano - MSN</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:54:21 GMT</t>
+          <t>Thu, 19 Feb 2026 01:43:39 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNLUEzWWpMZm15dUV0SVlmYVF5Y2pJaGx6Y1FCYTBtRnZrZnZxdGkxTzV4eVNtZFhvUDE0RHJfLXBBVGctc0h4ZjZKakNTSEhvWlZua0xPTUZqWlRSeUNHbzk3RzI5TldWSnAwank3Qkhnakg1cHU5enJDRHFVODdYc05qYzh1RmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPdW95UHRhdmN2OXZuX052bG9YRTQtcW1vSndpU25qUHppSnQwY1lyRFptYjVKMWR6cXdLRUFPT1NKQnZSNHctb29BQWxWQmJLREtyS01jUnFRTEFnbU9aV09pX3J3eTd2bmhUbmJsdU8xLXhrRWEySUpuVDNkckZWWnhmbDFickhRVXVjYUdpOVlsSFZ1X2dpRWtTa0NGN185aHVKbmhB?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3961,27 +3961,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain steps into 5G Advanced with MasOrange and Ericsson - telecomtv.com</t>
+          <t>Former Hawaii Public Safety employee pleads guilty to theft, misconduct - Hawaii News Now</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 17:24:41 GMT</t>
+          <t>Tue, 24 Feb 2026 01:29:00 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOMFZXMkg3QW1nNG1BSG5aWS1ibmd0Z2xPUVZvQ0RSOXVIRUtBT2ZoV2Q3eG94eFpMMVlDSWk5eW9oT3BQeThQWlhWenc5eGlVa3BHMldBWDlkQktvbmhEc2tXc2lFUzUwV1hZTk43NHktUjhtRjZiZmRKRUdtNjNfUjIxclIwdElTc0FwSkFWX3N1NGpKbmVVT2VGOGR1T2VFcGfSAacBQVVfeXFMTW14ZHFsQ2NGcm0wR3lSVGI4eWZTZU5iVzdJZWR5dzdGazNGSTdGZjViRUpEalNvNDEtaXhhYWQ2QTFyWnBDRU5wWWFlRk02T2E4a0xSZ05nRjZpS2FIRWRQblpsbzFNWE1rbThZQUMwOTlCNFJ0M1VYX296OVVqdXZraGZWSjJuYTFzY1hDYTJQREhWTFB0MjhpN29RTWU4UDUxQl9senM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQQ2NQd0l4WWlpUkxuX2tZVEdFSTdXNERyUjlkYXJGSE5OUXZWWVpUc292c1Z3elQtTENnRG1PTFRKaDk4VmZ3enZrX3VKeFQ3cG9uWTE3ZklvOHJjVFFsRlFWUm1BOGRRemJuQVl3cVlZVzFCMVZHbXRGaUJCNkZCZjhVXzh0ODJQN0pIYmEzZG1fZjRsd2hHNzNwZ0xnNXVJaHI5Rkt4SDBQN2tUdWfSAcIBQVVfeXFMT25TVm1ScDJVdVN3cWhmeGJGUE9fcjdGMDRKTDZDTXVFdzFWYmYwaVI1MjVYU2YyaWlpcnBWRFY4eEhGY2NMRTZsMGVsRzc3Q2V5LXZ0c29RaFdDTlVVWloxNnQxaWIwZkRZTERnVnFidGRzSEsyMXdzcFZJcm5GdU5WNno0N0ZoNGtpYlkyY3RJYnhVb29jOWZhd2hIdXE4OXhGeU1ic0hxOGJYR2JwWmotS29QOXUyZWl3LTFldHdXdWc?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -3991,27 +3991,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AI and tech stocks trading lower 'due to high capital costs' - BBC</t>
+          <t>How Charlotte Post Office worker who stole $8m in checks got a 6-month sentence - Charlotte Observer</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 17:35:24 GMT</t>
+          <t>Wed, 18 Feb 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQekhjVTVueTE5NDZLVGt5YVZmYzE3WFVqemp6RDBqZVF2QnJUTUdQeV9RT2NlLU83V0VxZWtLNnZabzlCOU1tSGVvN0h3WG5KV2VwbEF2U3JnamliTFZmVnBQTll1WVQ3OHlYVDBTNDJqQ0VmaVRWaVFMbVpEODB2SF9TQUg1QXMxdWZjZXpnOFFOQmhrdm9JUmxGVGhBZ0xi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE95LXFwWlJvV09DdGxZN0Y2cUxSY0tlZ3UtTTN5a3c2bEF2WEVnZXd1RE1ibjNHTXh4YVk2M01kUm5LOGk1WlFpSm9hdFhjbjhxNW1RNExiQTNreTJMdmgwSDM4SEtmdWEyMUd5XzFua0NRZnFmWnpyRHlneVfSAXxBVV95cUxNRDJ5czFtblZ6YllYZTd4VUJpaXNuaFpjZXdfVG9mZ24xdTlwZnQyQVRQT3dEMVFqSHBOSWpjMm15Y0QzUjk3OS1nTmN4YTZfdVZnNXVQZnZKeGJUSjNMYWFPLVRPOWZVdzQxUjhDSlZ1dGwza1VlSE5XVXVh?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4021,27 +4021,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AI and Uncertainty Are Gnawing at the Edges of the Job Market - FE News</t>
+          <t>Woman accused of embezzling San Diego County grant money to fund lavish lifestyle - NBC 7 San Diego</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 04:04:20 GMT</t>
+          <t>Thu, 19 Feb 2026 18:07:21 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOTW9MMVd3b2Y0cTZFR0FpS0hOTzA4RzNqVFFKMnhDQTV2dE5xRzFqWFdQZ3BhMGp6VmFlT1hVbjUwVXBmUUItNHpLQUNBTXQzTzBzeUJUNF9kT2I1Uk5ZdFNvTFd5N3g4NW43M1FUaE8xWHpLQzJ5WVVJV3FEUE9fbkJpZWxNOGpSaGZVZjVzaWRIZXZGaUNRZnZ6dm5rdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNN0w3cjNreEQ1dkxjcVV5Y0pyVHQ5RU5ncUhfU192eHpGMlpTU3FYU1dYU0prNk1UbGhSTnlvNUs5MExvUmQ0NTRQZllDQVJDdzA4MDNPRlJZZFlRMHpnUmM1dTV0OW9OMDdjb2VLUFV3RWFQN01fd0pPTlJXdDRjSTJESk0zMWp2QlkyMlBPeTVnRlhoZXM0VHhtV1VtWXRqaHVMTEpHaTV4RzQtYXNhRGNHQk5WOGRtcHdrM3JtZ1hUX18tNlp0RdIB0AFBVV95cUxNNmtEeWNGT0VSWThFSkRabFZUNXVVWjAyWUM4N1hwU0M0eENMeVBnc3R6VExIQ2VvYmdvb2RiWVJ1dXhFUGU4SnRFd0pwNWhNeHh1UURvQWRobjBfcGFGTENUSnpEZEFnbEpHVzRuMkpCMGEzT0d4YWQ1TGJaeHVtVWFiZmVoOVUta2pJcWMtOWdEdDNFbG9WczJYd1Bsalh6NmF6cjM1RFYzeUJJbndNTnhhR1hXdktOSmJ3dDdoXzg3TktSUF9JaHJ0QUFqYmhG?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4051,27 +4051,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>The Future Of Artificial Intelligence: Physical AI and Humanoid Robotics Are The Next Industrial Frontier - FII Institute</t>
+          <t>Sunset Mesa employee reiterates request for second re-sentencing - The Grand Junction Daily Sentinel</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 07:35:09 GMT</t>
+          <t>Wed, 18 Feb 2026 14:16:01 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPZjI0SWR2NTJER3NDT29KRmZuenZ0QTZGWm5Mdy1BWGNKTjd5T21iNHpPY3BJeTRIWEtWcFlLYVgzczUyb29CRkMzNFpsR2tKUTBpOTlJc3JLUHM2YXp4eU9LRkhFdEZFTVhueXhkUy05bGZXNnBZRk1WZDdRR0loVV9xaGR5eGFVTlp1Q1NvdFFVWjdxbGVDVkxxWmtlS3ZidlBJeTJMVTRYanlwMFVTWkxZR3AwSWd1UFRseGxDWkZsTFJSLWNCZjN4TENXS29JMTMweGFTemVQUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNTHlWNVpERE13dU5EVktjT3NnYi1aRHdSZHUwZ0FHczBFNThZUzBXNkFjai1MNnFoeUJ4ZkZDYVRPX1NqNHROYk9vRW9EOTN0UzBEMHRmWkFTMUxhYXl4MjlMX19kYXVGMmZzcnVqMV8teVFhTXhLQ3pucWx0SzQ2WWtEWHBKa3NtV0lhblk1bmJ4M2JCS0ZHOThPejhFaTFjamUxNEwwaTVGM1dVUl84eHNXanl4RmJjQUkzSVJFS0k1U2JwXy1LQTJDa0oyajRlXzZQTk40V2tqcEhKMUhMT2RSeUxxUFgwaTRjRmhMbTI5dFpOWGfSAfsBQVVfeXFMTmJRakdVX2RkNjV2R0IxTTduMVpTdHEyc0lJTThucE1fYkJtNlEtSGdvQnl0TFRNV2otUFlHaElzRzFOaTNYNFN6YTlJSGxGUDlRZTlELWxlTFdCTnRvVHNGOWpLLUhVYk1oLXFQclJ4dWg3ekFEQXJ2MjVoMkFRbXU4d1ZDc3F5c2dOY3B0TkYzYUUwWGhsN3RaaVFleEl0RVZXaDNoNVFETk1QNGd1dkhwblNhM1lxRE9sMjJOb1VDb041Y2gwZ2hBYnJ4M3VIU1lTdGRmNVUtV1YwbExrUzcycFozWWJDVG94RHE1ZG44TWhwT0E3bDVYNzQ?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -4081,27 +4081,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dassault Systèmes Reveals the Future of Scalable AI for Connected Industries at MWC 2026 - Dassault Systèmes</t>
+          <t>Former USPS worker pleads guilty to stealing thousands in charity fee mail fraud - KIRO 7 News Seattle</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 15:33:48 GMT</t>
+          <t>Sat, 21 Feb 2026 03:59:00 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOUThMT1VEVzBYanpzOFJTYjBTUUZPaHVIQ2xLVmptRGprWWVfSXM4ZkI5ZWpIVTgtM3B5Snk0NVB2S1lHUk0tLVVPY3Nuc0hGWVFUZllkS0Q3WHBOWnlCdzNPYUxfZ2VmVm82d2F2ODg2dkRRWG1lYjI0MEwwVFkwMXBuVWNDYWpPcldJSm8yOE80YVV6MWxiS0ZEUHJoNWItRHFRMlRVVkh0YVhwZ1hEM25LUzlkTnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOUUcyS0xCSEFhRVdZSEsycGt4X2s4ZjVUSEZUV3B3cEtWRDFkQU16d2lVOEZySFkxRFI4aU1FMU1kM0wyR3lCRGNUb1lhbnhOT1poTFVHXzl1aG9SNFdOdVRBTGlSb0tRQWlMRV9oelJkOUcxZzZJazBKa2xPRmM5a3Ewc01lUkNkcXhxYks0RDhEMGZZTUFVRk5rclc2TEVQZkhnVTNWNHowbUItNUtDUkZ0UkFGcGVfRWE5Ym1CUjVIQzRPdXRUVjdqZDJlS1Yy0gHkAUFVX3lxTE1DZ3VXYUJ2ZkpKQXMxNTRaWTVJdXB0dnphZ1NzajlLMWVWaDYxWW9Db1ZvdnBoQkl3ek84M2FpUldOSTJwbzN5a0tScXFrZDUwMXdxYUM1MlNIU1ZsUXV5ek9yVTROaVpleGs3b2cxWXh1V0xUM2dSVXMwSlo0aC1tbWl6VWtQOUVFWnk4Y016R2p0MFRtS2ZCdldzR3NzT1BndHM1bW1XYnYxem1zT1c2c2t6cGdNbnJucFNyTkZ3LVlaWDl2ZjBMTTlqN3poeHJZdDVQVHA3bkN6OUR2ZXZvVlpLRg?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4111,27 +4111,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Too little, too concentrated: why AI start-up funding in Africa needs rethinking - The Conversation</t>
+          <t>Plain Township veteran sentenced for stealing from Cleveland VA - Canton Repository</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 16:05:39 GMT</t>
+          <t>Sat, 21 Feb 2026 15:07:00 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVGZRMGZpdldHT2NRaEpRcjJtNWs1XzZINExCSFllR052cVl2bkxqWVR5TmNaeXF0a2ZjeHE5Q092OTBLdUhWVUY3TmhiclVtS0xlNjNtRHNCLUtmb1pDT0JYelNxZnlpVnlzczRNS1dLRURFZ2Nzc1RNbEhLSmFYLWk0MGtxX0JwUDdWM1VWdWFBTlcwdEFkM3RPN3YxQ3JIUVhDc1BjNHBMdnd4cGdlWDMxNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRFJkN2xIYUdRTk1Zd1FIdVJCb3J5WnRlaTZWcmFVaFBPVE9tR3VVcGF3RW9BbC1kUHFmenp0UEhtTWxNbDZURjlvWTVSRHZabXJlRWJiU0tMNjdsWUNscUotZWdXencyc0NhRzdMQ05LVFJGZlRNMnJ1M203M0c1U1dwaDVOMWtsN25wcWEzS0h6YTRwLXZSc1ZQMVg4aFBFOWhnQ0U4eW9rOTJDRkg4M20zZ2hPNGNWbGNJZld3Ujh6V0owbWpQLXVn?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -4141,27 +4141,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Is AI sovereignty possible? Balancing autonomy and interdependence - Brookings</t>
+          <t>Ex-federal employee learns punishment for stealing nearly $200K from VA in Ohio - 95.3 and 101.1 FM The Eagle</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 18:36:19 GMT</t>
+          <t>Tue, 24 Feb 2026 21:10:15 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQcU1qSkxCQmNQLTVySWVlNWktaGRmZ2UyVU1yR2ROaHltS0hwY0QwQ1VnLUh5RlhLa0hGUXRIRlV5cVpiUGpmYkRraVlTTEpydTFrVzlwSVBoZ3hjQ3dtaHhXQnJvZ0RtZmNyaFZoUTlubG5RRE81VjJHTkF6YUZUZWFvcUtrUWVKdGdVVmQ0b2tMTzJScGZ3ZWFTY296cms0YXVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUzNRaEhsUGcxdy1BVGNYSmg2UTIyMlQxelZVSGZCNlJEVkYyTktuamhNeTFfZndSd1Fzd05IOVZIMUpzTnIwTHlkdWxMcU8tY1lkZGVQaWt3TmlSU3dqaVlSR3ZxODd5VkE4Y2lzNGZBa1FmaWFtemhyMzVTZUFtRFZQSE1DTlluSlpSeGgzT2RCQjBFMUlmZzVnRWdDRFVDODRDbFNUU3liWmljM1BLeERwSnZkM0wwaHhRY0JuUGlieFpGRWVqR0h6R1p6Z9IB4gFBVV95cUxPNGoycWJVTkJkdWx6b1ZqNEpFdVE5WWRHdHVoaHo2OVJRSHJQTlZkS1gtUWJyaTljT0owQkVPalNkUC00d2tRV2NtcHJIRzZQeFhUQnlDYWJnR0NEeEVRTnZrTDBCc3BtQy1KSm12OGhDbjJXSWQ5aVpxbXd2eFRUNWlwWWZsMDdMMkJJRExFZlk3MXZ0N0R5Z2NVWTJmR0tLbkRNUUVVcVo5TXlCa25VN1MyZTBWU3NOcUFJQkRSeVBHRXZVbFdMN0cyMlBaTzR3eks5RTMxSks0b3hnVFJKTXln?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -4171,27 +4171,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NTT DATA and Saal.ai Announce Strategic Collaboration to Advance Enterprise AI at Scale - NTT, Inc.</t>
+          <t>LG Energy Solution Ex-Employee Sentenced for Trade Secret Leak - 조선일보</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 10:06:16 GMT</t>
+          <t>Sun, 22 Feb 2026 03:37:11 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPa1JFdzZxaTdPZWtUTVlYNnRBZ2tCZzJKRXNiN2NNS256dWdfemRMeUtub2ktakZpakNLd2FTem5RRVRpbUpUNGcwWnRTcGpURjF0d3ZndzhmZ00zbmRvVVZZNWRYdDZEUUdyNHdHNHJCNHVKMWRETlVLRmtvUTBwMXNOaGxTMjE4Vzk0b3Q2Y1hxb0ZySE1Ebkd6RkJoaUdNekFxMlZVYjVzbC1kNlJ6ZzZrUUxXWDNOS3Z1cFpqd2pQMVZUYWRUeVpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOOEFtZVNsM3hPOEhzQk1NTjVRYzE1NGRQSWlyX0RwaFZJcjdTZndQdkhvbkprSGFfNFNQSmYydmpLaDdwcmUtNFhGamFXdDlaMy1kWnlHSVBCT2RvUzk0OEozUFhoSjdQaDNwQ3NPZjN3V2QwZzZlbExHZE1XQWNDQTFkNm9GQXpf?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4201,27 +4201,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>The future of European cybersecurity: Why ENISA’s recent expansion matters - GLOBSEC</t>
+          <t>Texas man sentenced for part in stolen car scheme discovered after Leon County traffic stop - WCTV</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 14:45:01 GMT</t>
+          <t>Mon, 23 Feb 2026 19:08:00 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOXy1lRTBLMGJ4a21QMm9yOGRGVURGb05FZWNKNjdGb19UbXNkTm45MGhqMERKcDV6YmxIRGVrUDRGSmZPTDlqMExUVUVGUEtUd3g3aWFQSlFiQmFTNU53RVpXbjNFN3lHYUMtVDR5QkxUU1BQbHFlSmlFWFZSWG9oQ3FR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNUllzSEM3MmxJVThpZjBjSEVpSk1LWUFLZ25wMkhDa2lxVjJ3cFlhM2ZGZVBVUGJWcVNfanE0bjVJMEtKVTFtUFhUMUZ6RXpLYUlwSEJ2am9hYjEtZjdFRjZHWjZVNTNWV2w0RXpJUEkxSlFHVEpWZVR4dEVrUzVJZ0JmOHJFbnR0ckJRbDV1d3c2UHBReVdSLXZQbUFlRTVJY295WHZUbVdROHY0d0oxRE1wRmFQYTg?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -4236,22 +4236,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>The New Insider Risk: AI Changes How Data Moves Inside the Enterprise - HackerNoon</t>
+          <t>Attorney General Raoul Obtains Restitution From State Employee Who Pleaded Guilty To PPP Loan Fraud - RiverBender.com</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 02:18:55 GMT</t>
+          <t>Tue, 24 Feb 2026 17:52:00 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNNWxWc0RsQzItaUFfVl9QeEZWQVFENmJwYkRwSjFpNHFrOEJpbDc5T3BvNTN1eTZpcWdzcWxXaW9aUjh1VEFjaUV3akdibTVxNGtnNTU4djQ5UEZFTE1sU3d1LXNJa1RFWWEwUnVhSTJ3NWJ0LW92ME9fSWdhbm1sLURRcTVaRlA2STdjRUtkejlRenphVVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNR1VtZ1dnZWt5d2FSUmIydm44TTNpM0U3cUhMMDMxVmRWdUNMRGRvSVVfUElScmEyWWozWlNkdW9kSVd6b0lxem43TUduVzhGYksyS2gtOUtfV3QxVmxuSklZZVYtT3gtcUhSQmJZaHVtaWpBX2M4MzdyQkhVQ2FybjRiNnBTUWRPZlZyY2NScXpxdUNBOHRmTENvUGpRU2I4WXY5MWVVY1hnYjhZa28yS2VLV0RpenE0NGtGSFp3Sm5WQnNrZ3VqVlJGOGFsUVd2TXJCMXQ0N0JlQjRzN292aDJB?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Comment: Four insider-risk trends engineering must watch in 2026 - The Engineer</t>
+          <t>KeyBank elder fraud victims recover $2M in sweeping scam - Cleveland.com</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 14:19:51 GMT</t>
+          <t>Wed, 18 Feb 2026 16:48:00 GMT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZUt4ZEFMeEh3YW9faTZ1LS04aW4wZ0ZFc0JFdjRXZ0x3LU00aHRTR2ZXenM4N3F0dE5QeTZ3dG5GX08zR3YyRGlzZTR2cXlfamdXM3FRVjhRdXNxQUc5Q1VuOWFIdmJTYTVQRDFXTVdIdTg4Z3RrZWlIeGNlX0E5cGpBVFQyazF0VFRaTnZUX2dVdnM0Z25ZdHNuMnJ6c0RmbEtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNamxYYy1qR0Jsc1JSODdWNUc0YkZremM1TnVwUHlIUGVaMG5BaXR6R2c5YkJCOGlXa2tlOUdPWUg2dGxRWE03T3ZDY1VDNVhpZDVOMURYVFM4bGRrek1SY3Fnd0IxMHl3ZXUzcUZMYmdPbWpFdXJmTE1pNnhURlVtdHlkZ19QYm1xeU9VT0pveVR4SHpLMG5KbFk4d21zTk120gG0AUFVX3lxTE9EX2R0N3dLUG1vanhiRGlUNkJxNFZaUTVMTldKZWV4UHRFUGpXQ0hZbTJQRkRWWlJJck45dDUxS1VKRUJTNndPZUNsbHBnQ2xlT3FZaVV3LXRrWElDYjZTamRpYmF4YTRqel9UaEU4OVdZcmczd0tua1VEY2lETFEwdkZhTXJqNjNGYUo0NVZIRHB0LV9xTWppdjZDOU5iSUV4ZTBtY040WF8xQ1NSakxyaXJ2Vg?oc=5</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -4296,22 +4296,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cybersecurity and insider threat risks - Nixon Peabody</t>
+          <t>Notary sentenced to 57 months in prison for real estate fraud scheme - WBBJ TV</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 02:43:12 GMT</t>
+          <t>Fri, 20 Feb 2026 16:53:26 GMT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNOGRJSldlcFBxR2s4bzg0SjJTanZVRV9BSnUzaWtxaTVkc1BvbUhmMThnUHRyTEYxYzhrQmZiSGxYcUIzSWV2eGxsQ3VCZ05SRG1kSHNJRXBVZ244VTRhYXE4VVJtQnVKWUpENFV3QVlVOEhXNGl3bkp1OWVsLWRHbUw3WjROdkJkSkx1N3oxQXNyeld3Skhjelpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSDJ2MFZtYmtjdGgyNzd4N25IR2NuMlh0bTJ4cG1KUFQ5NkFUeXN2SEdwX1BXRlpySWp4Wm80NnVMQnRqWmJUa2FUS3VqMk42NFY3WmhpdkpoRkNPakVKcVdmb2g1bmVIX3plbDdOTXh0UXlWeXVqNzFIblV6WV9EQkoxVU5qRFc3X1ZaNzBrdURUei00Z1NKR3BRM2kwRjRmbURtV1Rn?oc=5</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4321,27 +4321,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Suffolk social worker fraudster handed suspended sentence - BBC</t>
+          <t>Davis-Monthan airman indicted in plot to defraud the military of millions in medical equipment - Task &amp; Purpose</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 15:48:29 GMT</t>
+          <t>Sun, 22 Feb 2026 17:39:08 GMT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFByeTUyaUYxWjhiMVJjeHNTVXhyTHdqaDZ2bzhhTVJTSVZwVXR1eTdMZnk4WWdMV2x0bnlxY3V6LS01S1lXSW42VkplZG9fRGlfQ2k1TkpMTUlwZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1sVmxKTEJ6RHJfRnhScjVtcXU2anpfb210NE5uMGprYzBBdGJINUp4T25LVGNtRFBSTFlWWDhxM3liR1ZMeXh5LXQxRFpBTnc1eEhTdVE3YWpNeDk3cjFjVm5Xam1rc2tWTllvaGtnRExtWWtPMThhblF0MHM?oc=5</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4351,27 +4351,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>‘Fake Flex’ Trend Raises Alarm Over AI-Driven Fraud and Social Media Illusions - Koreabizwire</t>
+          <t>Former Commanders Sentenced for Martial Law Insurrection - 조선일보</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 03:37:14 GMT</t>
+          <t>Thu, 19 Feb 2026 23:06:43 GMT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONGF1eUN5eU9EZzg4U04tXzViQlVYUjk4Q3d3TzZha1lPRWJQd0VLd3ViSC10OGQ2VG1Xc1JGdVFDTk1tNFJRNVN2aE9ySjdaWThtSDdUaGtmZHRBYUstdzlQdVpSUDFUaC1mY3ppM2hva3NfQnkwU0E5ekhKYkhLMmlJbENDd2otcWs2NjZSejFMNnluMkl3aGNjMENzak1sOVdBV1BGenZUZ0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQWkd0QncwbHloZlRxa0hHRllVYVF4TnN3bTgyUDVyRG4xU2FtWnVEMnZ0NGFFUmtZYUhYRGpyOUZOdDRIVU5COTdqOWtmS2RNS3FWUW9yeTVpajJVM2pPdmhmb2Jzdnp3Uy03VVJBZ3BBSDNoSVFGRGdEb3ZuUDZvcXhJR2N5Vm8w?oc=5</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4381,27 +4381,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Egypt arrests woman over alleged Hajj visa scam - Gulf News</t>
+          <t>Man sentenced to 16 months in prison for threatening downtown Lawrence restaurant worker - Lawrence Journal-World</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 12:46:30 GMT</t>
+          <t>Tue, 24 Feb 2026 18:04:00 GMT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSFdvWExQTGR0LWljZEdBZ0ZiUkw2MFQ0OVdQeU9wNmxzR0lBMm1vMkZCQnRZMVJwSUc3RUpqZ2ZFMzdPTlJodjBQOENodmNsMG0yT0NLYmJld1JOU2t3Qkp3d2lPeC1aempuV2x4Nk9pb1JvWHdBSlMwYkszZ2FtZlNwZ0s4cGJHZWMwa3J5bVBESkI5M0HSAagBQVVfeXFMTXdmczVEOU01RW05YUdNdHpsRVU0WnRuOGoydmNwdVFEYkkzSThhREdTOW5KUF9HdlZyd3dHNlJ4b3pzR0xScDVrdnBQOXVvelB3WmFqT1ZmVFpXUGdxQzNodmlsR080YnJFaWNqUEQ3dDRYUHd5WTdlbVltUHVtYm1taHJMTG1hZzEtamp0NmViLVljR0JTcklqSlZ2bUZmRGZkN1pROURt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQcV9qbGlkTno3UTd2NkRkNlVNNm9LeGtqUWxiUEtyZG1YUlF4YUgyVkF1Y2VwRmZRTnJZTl9mc28xODVzbVplNVpQMlBsSGwyUVQ3UWdTc05YV0NMZ1FXeWZ1SlM4bGctY3IwSkotU1ktRHFQaHp6SFNGbkhnWV9vSm83MGNMcjMzSHFkUnJOSjBUNjI0dDVhdDVZVEo5SHhvaUpoMlU0SnM4Z0dTeE8xbklFM3R5QWJCMVdoVVdiVHVEUDE3RGoyMmlwMWJYQUZrOE1WRjZIbmlRSW1rVWc?oc=5</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -4411,27 +4411,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Desmond calls for review of social service fraud safeguards after California scandals - Times of San Diego</t>
+          <t>Capital Region tow company owner, used car dealer sentenced in theft scheme - Times Union</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 02:23:45 GMT</t>
+          <t>Tue, 24 Feb 2026 22:56:47 GMT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWXBsVWZJaTEydGs0Q2NZTDVEajZjWDlPSnRjblVEcjR4RUVGRDRESEJRRVZSUFFVTllZNUE2M0pLQlJKWF9oQm50OHFESElBclRlY0tWWG5sRTFGNTRjcHhHelF3eE1xNTdWUnJ1V3FRNVFGVmNvQmlKNFJpRU5EeFBGaTJPZzhfS1dCMVlnRmV1cU1GY0lmcEpUN2EwUHBZbUNDOVJXUGxyME5iTGFZSkN5WE01Y0V1SUJ5UzNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPQWpLYmxYemh5VkhPc3pvRWNqbjN1VVVBbEl4cnBmbm1yaDhmYl91WWIyYWZDbjR4WXJjNjUxTG9FQl8zeEt5OE5nZzJqbWJOWGZfVkxMQ1RKWEVkUjlWTUNlZi00Z3hPTGU4SjdIdHlyVlJnLTBsbWI5ampGM1o5YmhZODlZdzY3Z1U4OGtpOVBWRjJRRUVhck0zbUJ6TGZ1LXJuaVZR?oc=5</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4441,27 +4441,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>How a Social Media Tip Turned into a ₹45 Lakh Online Fraud - Open Magazine</t>
+          <t>Bookkeeper Sentenced for Embezzling More Than $550,000 From Employer - edhat</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 11:34:08 GMT</t>
+          <t>Mon, 23 Feb 2026 21:51:57 GMT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPZlcyellrSDRMb21hUXVVc2xEQWxDY3AwTENkNk5uN0dYa1RfRlMydFJBUU80cHpxcXVXcS13ZXN3cVdjX2tBeEdLbnQ3Q3JBQTJSaS00Y1hIcFNrZ0FsVXVjT0VwY3FVN1BMZ3JLSGxRTWlad2pmU3FCX05OZVV6Vl9kRHlRNGhOVWVERjBiTDFTMlJWb0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPTDJuSW9mOFhPNmExZDVHLVZDOGduR1NYNVJEeW1fSnA4SXN2TWtVUzI4aFFwaVAwOTFTdmdUZ2tSVEljUC1hdlRDbTZ4WDlILXVjWWo5MGFUVzVMTGtOVWdlNXE1Zk8xMUd2dXFnZGZfQkw1RFlWX0ZlaEpERE9LaE42SXFTVDgyUDlkeGRIalg3Nnh6U044NzVXZUFndVNmLVFCOA?oc=5</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4471,27 +4471,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Why is Revolut so interested in the number of Irish social media users getting scammed? - The Journal</t>
+          <t>Man sentenced to 8 years for elderly fraud scheme - WDTN.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 07:01:00 GMT</t>
+          <t>Tue, 24 Feb 2026 11:00:07 GMT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9rcnNfWWZVNE5pSmVma2ptZ0ctdlZOank3T3hDcTRQcXJzNHB0Y3hXMVhGTTE0ZmJGT2k4RDZCY2FlSXFlUXltMGlQd3NMZU55akt4dnIyc2xzYTFGMVpjT1VRZUdFSFgzZnFUblV3ampxYWVwOWxqN3QyeGVMcjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOLThyVnh4VXpmdHRMaUNvWENwZ2MtaDh6ZHU3azRnODRDT0ZDMV8xUmVoc1FRX1l6Nm81WkM1MEVSdGc4RjdNZDN1NnQyMFNTMDVJaUo1bFc5emt2VjFSenNTNTBHS2pxY1hZUWZVeDBrZWNadll2S1VpV3k1ZDVRLWJmSEN1aFnSAYcBQVVfeXFMTi04clZ4eFV6ZnR0TGlDb1hDcGdjLWg4emR1N2s0Zzg0Q09GQzFfMVJlaHNRUV9ZejZvNVpDNTBFUnRnOEY3TWQzdTZ0MjBTUzA1SWlKNWxXOXprdlYxUnpzUzUwR0tqcWNYWVFmVXgwa2VjWnZZdktVaVd5NWQ1US1iZkhDdWhZ?oc=5</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4501,27 +4501,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Payroll fraud: social engineering and identity theft target employee paychecks - SC Media</t>
+          <t>Jacksonville woman sentenced to 18 months, ordered to pay $1.8M in tax fraud case - 104.5 WOKV</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 00:17:10 GMT</t>
+          <t>Thu, 19 Feb 2026 02:13:00 GMT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNRDg0TFo2VkhXMTNRWGRSWFV2TEdQeng1QXFONGdvNzhobXBUa1o5a0ExeDFvUi1IUnBHVG1SczRSeUVTZk5pWm0ta2lHVHlLQ08wRlBGZ2JtY2FNUmIwUUlUU3RYNGgtWHctaVdMZmltQVNDWmUxTW52UkZZaHo1MktWQ3BQRGM1aVM2Uy01UG53bDU5ZGE5RWljSElubnpBc3NCS01QVkRSTWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPT2xFQlFLY0M4SURLSGh6Qnpudl9nTkZCMUVmcGJLQ3BOekJVYjVHTmlSQzFUQ1ZkRFBCTHQzNGVkQjZ5dS1jbkZLa2JYaWhKMFR1UzVUYkdKeW1rUWI5NjhTNjM4a2llQ0dZUkxLVER3WUJIWkhBYU5OOGV0Q3d4TnNlTDJOUDJwbHJ6bUh5emJ6WXNwOWJpVnRTNVRxMDQ0WXFaSHpnMlFwRS1LRWFVV01qYnl1ZWdORnZ1bjRYZll0clRDR19aeA?oc=5</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -4531,27 +4531,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Durban vehicle sale fraud syndicate busted: Two arrested for social media fake deals - themercury.co.za</t>
+          <t>Former NFL player convicted in nearly $200M Medicare fraud scheme - InsuranceNewsNet</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 10:46:59 GMT</t>
+          <t>Fri, 20 Feb 2026 14:02:49 GMT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNQjN2OUl5WEhyY0gyemRhbVljY0J2aWh6cVl1cGdENjRPbzA5VTc5eFRGb05fUVQxWHFqYVdmbm9zTjNpd0htWERhWkMzd3kxYW5pREc5Tm9NR0lLRlgwYWM1eHJmYjFWcnprSFBtS3NPbjllTVk2WDhhQU1DeEZnV0ZaN01lZ3Z5aElZOVh6eUlfeWpHVFNGRjRvZVpkOGF3UGpjcnhYaUpqN3FSR2F1aUZrWWU1TnkzMVlkY0c5RFZHMGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZGpxbVNyMHBHcTZ1eHRxRmhjVVlRM2FrN1kzb1VmMExUa1JXVmJQclJoVXBYV2JROUN6d2RlS1NXcm5ySkYxYTJ4M2hhTUtYOFVwVmN3ZzdfeW5ySmZSMlAySGR4M2pCV2RzQXhIMURfTTFGaHdzRGxwSVAxaFRlck1hSEx5a2xKVG5FR1dWVHQ3bkNwRHg3OUlBVERoTGRWay1JMDA2bw?oc=5</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -4561,30 +4561,840 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Local woman found with stolen truck sentenced - The Keene Sentinel</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 19:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOQUc1dHNQbUUzM2VTY3N3dzk4VUl5M0RIZmZUUzdvSl9pSy1VdlFQMk52ZkxzZWFheFJ4ZGstQnYyRV9hLUNSc0sxSnBvMVVqbTZLSWlYanlkbU50OUloZFR3bXhtYnJfZ2Jyd0dhb3NXN3l3SjRIQkVWdnVYdVU5c2xxZzE0dEd2U3pMbHpLWXJZcVdtcFhUS2hMY1lvUzc3enVfbG9sT3JVUkZsRkEtemE0UV9QelNrM0hRakhiNnpQYm5kaUh1ZTJjWkhnSnAyQmRRQmdn?oc=5</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Nigerian, Matthew Akande, ordered to pay $1.39m after U.S. tax fraud conviction - Nairametrics</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Sun, 22 Feb 2026 08:32:14 GMT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYTJqMTVXbVpjUFlWWXpOQWR2Ylp0ZEQ0S2c0SHNUY3VIV3RFam9tcUdlVU5WVkdScUZ1RExHVFJJT0JuWUNnOU93a3RodTBuRF85V2xTMnF4ZzBOTDZTTUNaTWlmU3M4bU9TeHZWd1J4d3BMcWx1blpGOF9ZWWR0czdCZGJzck5ScmUwYm4zQ1VxWDBtNnp0TUQyRnB4eEVpcXh3b19pdzN6RmE0LVR2cllB?oc=5</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Overstayed student visa, duped elderly for $6M: Indian sentenced in US fraud schemes - The Financial Express</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Sun, 22 Feb 2026 04:53:34 GMT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQaE9QYUtNeXVWekpNLThfZVlNcUZHY2w1WUdXVTIyQjhDTUIyWG45dVdoMk5ySFVMcGtRbENLWS1kb2wyX2lkeW5qOXpGblJXYVZ6cUxSY3lqVjNNVmt1amNBR3BLSC1WREdKR1VtUnFINWlhekI5cXg4THdCeVpFVzV6UHhMZnZYMmFsd0RVSHNId2NhZnZhbldsaFB2TlVfTU8waWZoV1ZQMU1Ga0FHN01GTFl2ZDRCNzQ2eHJ0WEZ2VERwU0JxZ0JESENIVHMxd3RSM25CY1dNQdIB4AFBVV95cUxNcUkxOWZoczBiZ0Fxa1BYLUdjVDVrZFRrSmZpU0xlOFR0Zl9faTYxTWFLQWhiUXhoS1FIU0c5NnpGTXhGX2Q3TWVkWWIzcmZzRGhxeFVPWVROaXZCTFBmMm5zbkE0ckNfMUpFWllsOGRISmRfREUwTWpIUXNFX3JqR2JhYnBBVXRWZERqdWZvLU1MZVR5dFB6WkpCRUdRTzdsSzJoeXZOY2liaE5HUndtMzBCOXhhUFJwcld1QmVUbFdZNzlTQ2dWb3VPOGl6VU1mV1B4TjNrWVRUZUVhVG5oXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Former Northeast Ohio municipal court clerk sentenced on federal program theft charges - Mahoning Matters</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sat, 21 Feb 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1lSDU2OU1UdWw4eDhCLXB6WWlUNXR1enp1b0JZWjRWcXZHcXlnZVY0UXdIRVA0UUhVNWhsekJZbHh4eTRpRUJocFlJYWtkMHZhdWJWTmJjRjktM0kxd1JVZWI4M0JVbUtlc0JFbVBnSVIwZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Minnesota investigators are halting payments earlier and longer when fraud is suspected - Star Tribune</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Mon, 16 Feb 2026 19:00:04 GMT</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNVmNTY05ncnFfUG5BVF85dXBBQWtBYkhtX3c0MEpZODlLVmFKYU85QmpwQzdwaVlSaWpUVl9LMEV6T3lOWk11d0lNeFNXMWFaLW83OGdScDhTYjJobmM0SHRtSU5CWm9OWTQ2cTNzcjNfX01DVXYwVmFaWWs4SnhuRHNQVnhxOEhfcnR2N0NWV0NPZlJTZU9MUEt6Sl9ta2VkX3RLUlRYbG5fVE5iTHc?oc=5</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Charity workers accused of fraud and ‘unauthorised absence’ awarded £96k for unfair dismissal - People Management</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 13:17:05 GMT</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNUGVMd1Zrb0dwTUZJNUdBUDdkMjZ2RDA4VnJyZjR6bThNYTFBT1cwZlNMc0x2anR1TmZQMzB3WWdMOFFtLUJEM05qZVNnTlRVWmtfb3pqMHRMVkJIam00Z0F5LXNwRDBWV0hQYnc4d3hyZmI4Nk5kcnhTYWhiaWlrMjdYS0xRNWFIWTRleTJSTHpRVmNzMEZKb2FPU1lBV1ByVzNIcW5nTTdZaUl1Y3lzNFlUSGE0WmJpVU5zZTl5ajVhZEdadWpJWHZB?oc=5</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Spoofing, Smishing and Deepfakes: To Stop Scams, Consumers Need Stronger Protections - Bank Policy Institute</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 19:22:10 GMT</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQZ19wYkp5T0pERmlCVDQwQVFEcTNvSXlNN0tQaDlpMmR1Tlc2a3Q5TE1JUjB6WEhDcWpDSlpORGp2WTQ5SlhQRExtdC1mNU5BeWRScE0td3ZtT1NlUXJGeXpaWkI4bGMteUtMR0lDSjN0aFdiSjJLamdfdl9TVUt4SnFaWlZLSlNxRXl2V2pwZS1xcVkza2dzdXpudFM1cU0?oc=5</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Parents urged to stop one online habit that could put their children at risk - Greenock Telegraph</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 05:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPazIzNWNaWHZVYzdieXZYSEEwNmlweVZkVVNxdEZ0LWFsbG1kbUUyak9BUGotUmtVWFlqanlEbjg3YVB6VjlQeUxUTjgwSkVzZEVDQXRxdzFHZnJCc04zV1Z4ZUdONkdtaHVXYVJFSFFvZE1wUzY5c0o1UVVRVzA2WHRUNGtiZl9wNTNWZk9mbnBIakZIX3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NEWS: US ‘Dark Bank’ suspect extradited to France in €1bn money laundering case - AML Intelligence</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 10:07:36 GMT</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPc3EzUzNkS3k1NVJOeUNoYlZNVWFlQXBkLTJEX2F2ZHY1UVBwTkRZdVFseThMS2VvOEpyMVQwODBWX0I3eUY2ekozNWkxTGE2TWxrczZiSDI1ZzVTTzItZGN2bTNLWXdHenp2SmRNNENTZWxvV1VXOExaY1BtNFRzaTlKLU11RGJWbU5YbzBheDRkYjZhMTRWcHZrazFBek9UZGtKWUdKWGlIUVdHQ3dUdEtiV0swYnpQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Understanding Medicaid Home Care Amid CMS Focus on Potential Fraud and Abuse - KFF</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 19:21:11 GMT</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQOFpQa1M0RDBBLXAzdTcwS0hlUE92MWZNQy1xbjlyUXN0RUY1dXFkQzFPZEFWMzFqUFFmZFRjYWZXLWt6Mmx1OGtUZE05dHdtaGxtaXJpNnZPdmlKVWJ4dExlWVgtdUtiSkRENVBKXzFPckFUb2RaX3pZUUF4c1lzdW9xMU5aZlY4cUYyWEh3bGVjUERTWXVkd2x1d0xIZ19DaGVkMDI1eS1OUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Seafood fraud detection gaps persist despite new technologies - intrafish.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 06:36:40 GMT</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNXZCOW9sRVJpMUpsQW9tal9JZi1jZ3BmU2xUcENCdkRjejlNbjkxVVM5dUlHWDA5MThoRHpERVRoc3pUSmNLQjBBb1FOazYxby1EcmtCa0lLcGFMRndnWFU2cFBHSFo3cS1fNnFjSDBkVG5tYm5ZSXM3UFJ3VTlXUmlCUDhVdG1SVDUtTWh2RzFUaVBKaFg3TFlfNS13UGxTUWdVN0NpeU8?oc=5</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AI agent speeds up fraud alert reviews - FinTech Global</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 10:10:38 GMT</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBjZGVKRTJRZV8ybzlaLVlGbWstRk1yZjgwNEtYa01yVXlPZ2FPbGZRSXRMcEUyZWF5elVXZlp3ZFV4T0RjV3UyZDhmT3JVcjVnZ3ZiWFRTWlVzTUQyNTRYVjRWaXRLTmJLdk0zMllEOWh0ZHN4aGJmaS10QkRXQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>KnowBe4 unveils AI tool for autonomous phishing training - SecurityBrief Australia</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 22:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxONHJYTi1OcWR6OVgybUhXWFNTbl9YeHQ1ZDhEU3BxbFpGZUFyT2lETW5fNk5zanFYT3QzODNnckJTRUdLMmgzT2hUT0VEOE14dVFfSDBQMkFOemlPdjJPeFV1OXVSc0YxMDdSa0p4NTBzTVNpZTBoVVAxRC03QVBxeHFsM0U5VWNuR1JYcUJFWnlRcHdWaVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Morocco Arrests Dutch National Wanted for Fraud, Money Laundering - Morocco World News</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 20:17:25 GMT</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOdUEtNWZzdzlBOXpPdzNmZkRoN2w4ZTdrQUtORW82R3hRRzJhYUFncjJOdUZVYjVxUDFrRGp6SElyTXE0WUd2N1dWNUFSdEwtRERWbVhRbzI2UGVWWGNZZUtJZVhHLXA1VVJMczZhZkVpUHQwTlZPc2FvQ0QyY25OSHVHMEUtenhYSk9aTmdtNUx0cFp0WjUzbmJEY1ZZUWVVSDhtZ2FzRlAzN2M4RWFuLVNiOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>FATF warns of rising cyber-enabled fraud and widening money laundering, terrorist financing, and... - lokmattimes.com</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 07:32:33 GMT</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOVDlmQmJSTmhNcXRoSnlCT1c0YmVBZU5tR1l0eWl6cEtmQk5jbzAtangzZ0lMTHFYdUd2eWNwWUxBNUgxZ084b2VTTkIyRThSdmdYOUlTRVFKa2lETlY1LVk2Smd1YXhPbkxXMkQ2YUJQYm1NWVZ0eTM2MndLaFVlZ29TaFU0RzIxT3paSXR3NlUweXdMeEVndlZaLTRneW40VXRQZmlodUtoNTliRnFiWm5Hb2h5cU1QR2d1QlZkejkxYmRKS2dZcU5VT1JyRThYTGkzWmRpMEJ0YVFLYTFzcGptQXlUZ04tM3M2T3U3RW5RbU9WSFlCcjZCZ9IBgAJBVV95cUxNdWZ3MXFYUFNkajQzMG1OeTdMSVJkdXRVSTlQeGpDbm5ZcUIzTklwZ3B6djZncTEwdGZrYWE1cVFNa04wMmk2MkZYQm15WFV4X3p5Rk0wcWxyeVh1YWpXVzBtRkFzcV8tMEdRamstU2hsSkg0MXpaS1NGOUx3c0pfODhJRWZmYjB5RG5WdjNYWFVqbEVNN19GaEtfVnZQUVdBLXd5RlZZR0VNc2N5aVBLRTZJdF9YaVlUdDM1eUVSX3libVZleHhxQ0ZqU1hjY2tpYzBwY09uaHcyUUhJUWVlZDdFM3Vicm1tQ2FzMWFsREpvY0VDaFEtYXdpS1VTQklK?oc=5</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Fideo Intelligence Launches Verify for Payments to Combat Synthetic Identity Fraud and Strengthen Real-Time Fraud Prevention - Business Wire</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxNOUpia1gxcDQ2dnIxUnhjUW9HdXJ6ejBzQUd0QzZfcjlVR2ViOF92aFlpSmNjbHgtRlhpR3E2c21ERTFpUks2M3lLb0NJeXByOTd5YU94YXItbVpnbHEzcFkxSFNUR2tHYjFEakdDR2dhZXY5M1JSbDZaUEJTVnFOdWEtTzZRUXl6XzAxZFUyMlZkRHBQbi1EQ3Q4X2hSdndubHB1dE11djM5d21CR3ZqRTdmQ1kzQThqQlhTZkJhUWYxTVlGTnFWcktkZmN5VXRUdjdRdWpHU3NwX2RHV2NvdE55bXBTRU14aXlIQlBMb0llOFphbEpDV3V5ZWVNYWZuSmpKUGJXWFVUVDNacHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Cyber fraud rises on global crime lists - Royal Gazette | Bermuda</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 21:55:43 GMT</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPclJoSHgwZnpFTk5CRlRTeWNSVUhoVXRIbG1faWVjeHNFcFJlSHFoRFZUYU9fMlF0RXR1LXdOc0ZhSFl1eWJ2SFlzSzhWcjFRZDB4WXlZVDZDQ0hPNUpDek1vQUVrcWNjYzk4UUotUzJpdWdWeHFSejhrQXpUaHNYb1lCWGQ3RndhUXFteWdhVVptNEdPenoySkJzNmlScEV5NkstZFhFWUVlNzZsSUU5azJ3QVdkc1lkeHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Barcelona member’s complaint accuses Joan Laporta of money laundering, tax fraud and criminal organisation - OneFootball</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 08:40:21 GMT</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQa1dhamhnUGlRTV9PQ2FJYUVldGhwMFVUbjlyZ0ZxT1V2eUc2NF83M3ZPc2NqYjV3YUU1dWljdUx2WnNJc2lKN2lnb3NHVGFQTnN5bkhvZXU5MjNjUDU5VldEal9pel9uak5hemp3b1lZNTNqdEhnbXNxams1czltUTVWaVY2dEs0ckY0cUxnbkpaZzBHX2FEQUV6NTFCZnloYjcwTkN6VUVhYTJDSFRON3Nsb3UtcmloX0JtaVIzVlR6N2RGVHZCcDZQX0Z0S1hodkg2RFFpRUdoTjE4Z0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Trump Targets Democratic States on Fraud and Voting in Speech Touting Economic Gains - Governing</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 06:04:11 GMT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQc1h5clc5RHlwbU5vS3BrV3BBcXFDTWFfYmhRamdGTzF0NW9EdHN4T2ZzZ3Z2bGN2clduUmd5Y0l6ZVlJcmFGa3g0WFNrSVBpZmlqQU56bFlxWFhvN3c4eUVEVmpHNVk1RkdVLS1rMUtYNTY5MEFKMHFXdGRZY2R6YjM4aTlDVnV2NzJhbUw1eWVDa3hrQ3J1Zlh1UjY4TkJEVHQ1Mkl1bGNVd2dJVnpvdHdJZWx4ZUkwQ2ZJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>BankThink: FinCEN Should Reassert Its Control Over Anti-Money-Laundering Policy - Bank Policy Institute</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 12:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNLTVxbWRBaG9oNG5KemFEckt2UnczNVdTY3VpbG0zRHBIaU1ONVdCLUF2cW5aLVVscHhnaFFhQ0RFaV9tYllLNE9naXNOdVpHLWNHV3JyWnlVejdUVU4xQlFaNnFDS2JKNGtyX3A1NmJfaUIyVkdjaHpzdERjdFVEeTlKREVLRWUtN2IxbzJZZlpLTVJPcldIN3lwUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Protect Yourself Against Romance Scams - U.S. Immigration and Customs Enforcement (.gov)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Fri, 20 Feb 2026 18:07:16 GMT</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE53bzBaQWRrZTh2RmdGdkZEVjZ2VUdMQ3JSRWdvY2R3d3o3QkdqMUFrNUNUVlhTcEZaV3V6bmkwLVVSdVJ2X3FfQnFKWUFNQi0zamlPanB5MGo5TkNPaGpiZzZKN3pGS1d5NHJqZEtmUG02Z0RFOEJDQlVrcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Phishing campaign targets freight and logistics orgs in the US, Europe - BleepingComputer</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 23:57:58 GMT</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPRmduVjRQQ1RPc09HbGRvUnEyZkEtX1FGcnBfd21ONExYV1JUTXB2aDdvOFRNdklRR1Y1YmRGRkZRSUhPMVRGclV6ZXJFR0lnSVF5WVZGaGFUU04zS2lCYURqeDk4LTZJTDljUzRwM3JLbkRya3RHWGprZ0tlb2VyUk5yTTExZExnbVdtU0JLRzlZNnotWW5iajNoSjdRdFJ4N3JwUjBxWGhTMFJxcC14TldqQWFYcVRv0gG-AUFVX3lxTE9UbkdrV0VVRmE0LWVxWUJVaDdvYjBzNTd3ZFg3LTRFWTlyT2Y4bHJwby1KM1BZVjNnalRmLW5qYzBZZDJnQldRWEtNeENNcVExTDd6VU9odUxSUFNoNzlYTHg2NGlxTkdITTVEMV9pNkFkWWZvZmRjZzlVejU1R09zbGpIS19zWlRRQnRYSEt1eXdkSlQwdWpCdXRQVFVLVVh4elQySWFaUE9nN2tON1JFWnI4bFA3bFhXVlF6bEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Trump’s ‘war on fraud’ announcement recalls plan for assistant attorney general who answers to Vance - Democracy Docket</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 05:37:30 GMT</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOM2xYb21TY21XS0dRT0JmS2tuV0tDX1l0UFFnV2tUTUVaTHBWOWtwSUUtc0M5Nnh5eUk0a0lkc1NZTWZyWHVZU0JVR09LY1Npckw4NjN1ZHZfUG9ZalZxLTFRLTU3WTZjNS1DX283YW9ZRkRaOWM5dlZmRDZ6TmFYZUN5Sk1EZm9tNkxzUWR0eWVfc1M3bEg1SXZQMkFwLW5zcHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Contini clan controls San Giovanni Bosco hospital in Naples: arrests for fraud and corruption - Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 07:04:16 GMT</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPYS1ZWEduNExOR0xxdl82dTZCZDVXLTZXMWI2REtsWFJNNjZDa2I2WmFyZ1FuM1NFckp4NXpRZmpQNE1raG01cVRUSlI3TWlnaVBoaEgxSUJfek1JdnRVcGJDa01xWS10SFhnVnBZb2pZSnBxaFd3VWVyNjRNaWFXbTBKN3lCVkxnT19tVzh6eWhFQ3BGY215TjlzTkdnSW9udTZLc2tXSzBtTDd1S3RtcGhId0loSFRMTTFlZXYweFpteVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DOJ-Office of Cybercrime Joins Global Effort to Tackle Financial Fraud through Open-Source Technology - Doj.gov.ph</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 01:37:13 GMT</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQdExXeC14ZWFnN1U1eXBnYnl3TzVYYTVwSU04M1h1ZG0wX0lzMnh2ZlhDcm53amw0TXBKaG1SaGRiX1Y3NFUyUUVNVnJCTXBKTFBFempkSWFYLVdTVWRtQ216WUxmX1lNV0h2ZjZQNU9GRGR3OFhwcEJQal82R1JuZnRWRm5QaXhHbG1jdWExT3NadmtwRkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ex-Motley Rice Lawyer Pleads Guilty to Fraud, Money Laundering - Bloomberg Law News</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 21:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOeWljbWd6UDJaWUtqbDUtNlJwQ0h2TTJ2Q0lmOTNVcUU5TV90SzVwSzhoNWRuZUxjU21UUElUVm1KbEFOMEVKY1YzcHRpSG93VU1PZHpVRmg3YUdNRkhvVmZfRTB4bjhRYktwM3RqZi1BTG5iczN4YWxVWnI5dlF4TFJNYmRHcUppelpRTXYwVWx6aS1ZSU05cDctU2ptRk1wZXE3UjRscmxQZFQzQVd2OTJjVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Woman reported missing in New Haven arrested in California for bank fraud, officials say - New Haven Register</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 01:16:16 GMT</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUjdLRUtPalY1ZEJBcndIWGFhUmxYV1BhZ0JEbmxPQmI3VjBGZ1FscHl1XzQ3R1ItS2wwVWlwRGVITkk3ZHFRaUVxQUFzWW1kNHNkVzVUWnlGdU03R3pzRHV6V1ZvOGJ0OTJCU3FYNU1IcUw1VkpkWWhrYmdYbFdxQ1RWcU5XUEdUcDlTZWpldHVFSi1kZVBXLVZMaFQzUTNOWW53?oc=5</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ireland Sees Alarming Rise in Fraud Offences as Traditional Crimes Decline - International Business Times UK</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 15:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5CdGVKOEYzMFRLUDNPMmx4emh3bGhWX0llVjVLQS1IdUZfWmVhbndqUlU4UkJseE5HX3NZbUtMMVByRmd2UlNYMWE3WHUwVU5INGZkS19BWWFrMHA5aVJyWUo1ODhvVlZjZXZYRnM5ZjkzUnlT?oc=5</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ENFORCEMENT—S.D.N.Y.: SEC obtains penalties in COVID-related corporate fraud (Feb 24, 2026) - VitalLaw.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 01:16:25 GMT</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPb253OFZrMnVzQXBsVHo3M3dZXzFZSFAzNmNuck9ObjlYeF9HM29ZTHgyYm1FbTEwRzhWN2pld1NkTGtWMGlJN2Flb05fTHM1aGEyMnRwTkJrSl9Ic01Zd0JmRGg3WGJKQ1pWQ0h5V2wwR2xGVkRrVWNWSks1RFFmdFVEZThmZm9haFVhbkdOby1tZ1phVk1NYVVtaGQwaTBmR3poT3hYM2R5VlRGQldGQlNXWWZ0RTVkX1REZk5ObVUxSkJGZjdmem51UWk1RXZKbENnTW9Dc3pZQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/weekly/topic_feeds_week.xlsx
+++ b/data/weekly/topic_feeds_week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UK announces biggest sanctions package against Russia four years on from full-scale invasion of Ukraine - GOV.UK</t>
+          <t>Spring Forecast 2026: The right economic plan for Britain - GOV.UK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 08:18:31 GMT</t>
+          <t>Tue, 03 Mar 2026 13:10:37 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNZVN0OGM0bndZWHRIUHBtNDNqdnl3Y1NtSlBsQ0w4bHJXUl9tbGh2M1FUWWgzQTlOcUp5c0loRGRWVGVBLThWWEE1TjhVZkxvLTQwZzJGRV9DNDJqRS1MWHlKQ0VnWkJlRy1WQ01oU2NJWlZLR0l3dDlSV3NlTnpJdmVJMDQxeER6R3FyU0hoZGJsR2hVZWtlYmJjeFNNX3duRnlkQ0pYMUlvX1JINDVxdnJaNmFUT2dVMlgxYy14NHVWMm5ETUJhSEVEYVhrbVRkNGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOdnQ3YVN2OE1HQW5ySUZWSUNEQ1NxQV9lejRlOGpwbWlacDBCeTh3ZlZNOTZBSVRabjhraFVoZVRoclQ4ZzFFMUhzVFh0bU52S3NZR1d2VWQxXzV2dXRvWk43MHI3UHB6UjI3WHJHSV9wOWJqWUhYYUJTNHBFbTdMQVFjRmR5bnRhM0FmdFJqNFJEaGYtT1E?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reform’s Danny Kruger criticises UK’s ‘totally unregulated sexual economy’ - The Guardian</t>
+          <t>UK lifts Russia-linked sanctions on British accountant - Financial Times</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 02:30:00 GMT</t>
+          <t>Tue, 03 Mar 2026 18:04:31 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPSm9ScG0zTHVYZnFxYjBTdFQyejJvaXpPOUE3Tk90UlNEUUNtNjJlVTlsM3VPZHEwSXVOaW1VZmx3QkZTd1RQN1cwOUhLOUJwZFlCSVUwZV9zbVBGMGVzUTYwUFh4VmtJb0Z3cDZVclpkRkM0dEVMRU05UERVWVVMcXhUREp6Y09iSmtBb1lOSDdpb2tzVV9XdlFuUFVnMDdnYWZvalJKdVBMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9wMGpiRGp2dEh3cWRfWFRteWZuTmhWcjNuMFkySzhZYU1iSzEwR2wwdEZReGNqeEpyNFlEY0lSUWx6VDExcVpIUnZ6S3YxNGN4RGllT2Q0RnlHNDhSTjJPOUcyeHczdVBrYk1SQW1jVjc?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Business insights and impact on the UK economy: 19 February 2026 - Office for National Statistics</t>
+          <t>Alert: NCSC advises UK organisations to take action following conflict in the Middle East - National Cyber Security Centre</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 11:07:41 GMT</t>
+          <t>Mon, 02 Mar 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPRmNaTjRnbDlNUjAwVUU1d2Vjd0VFeE9HN253VlRicWpTV1huOUZMTmQ2RGZybmUzNjdaOUh1UnJkQVFqdktaYUFSNGVCT1JqaFFiZnJNX05vVklSLUZDRVhwbV9lSWhZbTRQSlBEQjJrZzJjLXVRQXBWajFJSmZiV2ZraFhCOHNiNk5raGRPS09vd1MzMDVTTHJtTnBVWmF2MFNfcHZZUVJpV1I0Q2NZeHFyT3drd2xIdmhEMTB3cE5WTjVFZlZWeXR1MGRfaHluZGs0VA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOclp2OTdKYlV2NEFZOGlPV3VSUkNnWWpkelNWXzBxV1R5N1pxS1phZkQzdXd4R3NTMjhIOXdyZDVoa0ttNW1ZOGVYRzBNS0VaeXJxUkFvLTRlcjFsODdYZy1YQWRLSVlwTUhhRjZZcVBYVEtlNnYwWkFiVi05bV9zVHBWS0p1MG1jV3RpRVJvejREeEU0eTBaVVlqcjZwVl9YeUtabnNTYw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EU ethnic minorities in the UK: an overview - Migration Observatory</t>
+          <t>UK borrowing costs jump again on fears Iran conflict will curb growth - The Guardian</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 14:32:20 GMT</t>
+          <t>Tue, 03 Mar 2026 22:26:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOVDdmLWl3WHFCbi1ESFJROXV3RFFaZFhMNGwxQlQtVGl1dVlHT2s0WGlVOWlMOWJDend4ZGFESnhDQ3hvYVhmWWk4LUxZUXl1akx5N1pOT2NEbjNuWFAtOHRFQkN3WmtQcUNLSGdoVGptWXh3c3JZb2dnLWJjSDd4aWcwdF9TdURPYzkyekFCbDJTeXVBclZQdk5tYk15dnBMZG9Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcjlMSEpiRG1jSTM0U05Cb21ubDc0YjZhTm9KY2x6TkVnc3pOUlB0UGdtNzRBMEhJSU1xZWloWDdyMGJJSFE4R3dJLThzUHJZd0FvSG56MEgzSXdha181YjY0ZzBoeER0RUM1M01XZjdiUlh6R1hOQmxzRXdDUkZWQlVhVU5VUGVma3NVcERXYlBVb0VRUldKbmZpaXRuQzRzQjdMdENpaHI2enJCYXlCOG5NaWJnaG5mWUE?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mental health of children affected by armed conflict: experts call for global commitment and funding - BMJ Group</t>
+          <t>Low carbon and renewable energy economy, UK: 2024 - Office for National Statistics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:01:36 GMT</t>
+          <t>Wed, 25 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQcm9MaUM0T1c0eHN2MG1waVlIR1hUcjNLWlZESFVKa0E1cDA0SW16djJWNUxpUzg3c05ma2VTd0JwMXVTU0ZjU0p6SVVIX0FzTXZFNkRuR1ItTDk0djRmc0VwSWx0WlRhVVJWQmhTaUJ4RTlGdW1aSmpxcEg3S3kzWGlzb2dlb0hTQkk5anBIUmpPR3dXSFFfT2ZfRmFRN0NkN3UzdHkzZW5hOE81YTRtYjl5UmR3SDFsWGtpWmtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQSmgtUlpKWTZybFlTb0Jvc0szVFQ3Smd5U1RIQ1lKSjMxbUJhRzZWNlgzMFFHZ09kTkRBVXpFUFljNk9TYWhXT3FmazRVSGh4Z3pmZWRBRFoxVHhGUktpV3pnUXo0Sm5RRnhCclVrRWw4ak1RTk5YYVdFQll0TTlxMzRZUlBKZTZvZlE?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Day in Trade: Supreme Court tariff fallout continues, ‘landmark’ UK sanctions package and UKEF urged to expand support as UK goods’ exports drop - The Chartered Institute of Export &amp; International Trade</t>
+          <t>Gas and oil prices soar and shares tumble on fears conflict could escalate - BBC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 12:04:58 GMT</t>
+          <t>Tue, 03 Mar 2026 21:44:31 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPN2Zya3FRUFhJQTNBeFFuSThYOEdNcF9sWlZIaDY2c0ZBU2ZLemlhSVNjcmRtVnRBM3FfYzM0LWJkZWxKLVUtX1N4OU5KTm5YUHdpYV9UY3R4dmJpdUNBMDBid2t5MmJQT1hBYWtsZE0yNmVFcVNLRG05bU1DaFBsRjluaC12SVc2OUNlM19Jay1DTm05QkpvMUtSUS1rTnBqZGJES3JSU1JYSXZXVHA3OE5RUXRCNG1sRVpLX1BUaWQ3VTJvZ21YUTZYS0NMLS11bmNRLXhsZDg0SlZxU2VvSV93NktXS0wxYVltTnFHRnVMS1F0a09TOWI5WWhnSFI0TnJ3TWVRRE9qVXhrLU0ydDBhTzZ5akxkcVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAtaUk4QzE0N0R4ejdKczZYVHVNSmVWbVgxTEZTTGhqMHJHbHhWcm1rUXhJdy1OR3U5WGRlZlo3Y05HT2h1QzN0eE55Tm9ydUdkRjFhc3lGNkZNUQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine war latest: UK and Ukraine respond to Moscow's 'absurd' nuclear bomb claim - as Trump sets new peace deal deadline - Sky News</t>
+          <t>Lower net migration could hold back UK growth potential, OBR finds - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:22:17 GMT</t>
+          <t>Tue, 03 Mar 2026 15:57:38 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOeUtvMTh2UXpkaTMzanZhdXR1a0ZNLVJLZFp0b0FEV2RzY3FfVG8xbG43Yl8tS2VxT1E1NjVzX2NNY0JqX0llRHp6bVpGSEUxM01feWdMMU9QSEt2TkJiVWtBRWc1Snc3dTU3SS1tV2RGclZRSkMzNVF6QXdjRVR2a0lOQjg0LVFJSF81dlM3UENqWS03RE5NNUFmYXpzdi1ERlJ1cW41a3pDNjNrUWVhVVNJU0puLS1QVmhQTjZwSUdiWE9KWm4tVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPYnVwZld5UzdDX2JJeFVnODd3N0UyRFZqcUlIekgxWGNoSHo1MmpiNUJ6LVJZa085aVVuV0FGWVhKNTd1TC14eTVIZjRjc2stYklud01EWXpIR0h1NXpYYVJNOE9KX1VJSjE4bDlZYWRCUTFEazZLNE0tYzVJdGFoWUtpYmQ0UQ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Celebrating 250 million: Empowering communities to enable the global AI economy - The Official Microsoft Blog</t>
+          <t>Conflict in the Middle East: Martin Lewis' 'get off the Energy Price Cap' mini-briefing - Money Saving Expert</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:05:40 GMT</t>
+          <t>Tue, 03 Mar 2026 19:33:15 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaG9FdXMxcExScVp1dFZ5cWl2bFQ1TUdJQnV2U09pbndYUEdUYWN2dVRyck55eF82N3BFa2NFUGp0Z2w1anNaenFlLXlfLUVJYjR6RHhRa0xYVXRqNWdyZThiYWtSUFpsMFpybzlodlEyMWM4MW0yUmR6T3lRNDNfVDdvRklpSl9KcHQ1Vk1ablFLQ2RFdjliOUVlQ0ZLSXZsM2dielY2M3d6ZkFx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOakJvMDQ1TFlpLUlHRk9xc0NReTg0R0ZEdHBjMjRRem8yU2ktTWctbFZ5NERtV0dRSk9iRGJ3dGlxZEZrVzFrSGtCcHdBaDNjSDFTYmJPelVXLWZVaDdTMV8tVVpWdmxaZm95NDVMVE5iUUdfSFB3OXFnTlNhbWlQaHZkYWJLSWpDQXl2bi04Szc?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Consumer price inflation, UK: January 2026 - Office for National Statistics</t>
+          <t>Increase in young women out of jobs market costing UK economy billions, report finds - People Management</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 08:00:00 GMT</t>
+          <t>Tue, 03 Mar 2026 15:08:41 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPMkZvSkhVdERGWjJIU1A2eVF2MDh6VG4ySXJfOGlaR3VfN29VWENoT1BTTWVHMGZES1lCU0tEb0tUUDI0QXNxaHV1WHNIOWZiZzBWbWlkcjA5bGZKclZhZXp6aTVJREFZLUhBUzI2cXB0dDhJQjFkdGZ0bG9uOUpoTE5nVnl0dWF4aEltNmsxX3NSaXV0X01VcjJlNDJselh3c0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNaUh6d2NUN3MtVWl6c2I1Z0NJbGtkWGRHanJZemstRmQtVnJkUkxVMlFzYjRmeVJTVEYzNHRvR2tHaEtLV3N4M1YyX192TlRsQnFRRTc5bzBITWFpUDFVUEc4OE44MVE3Z2l5c0RRTmZtZVBfSU9BczlldHBpOWt1WUtqQ0pYXzRNZUVQRXRjMmhCcHo4NWRLLVF6MDAyWWVrZDhnZXUwY0lNT1pnbGpLb1RXTFB5VmFXTGgxX2VHOEtRUQ?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe is underfunding female innovators and paying an economic price - Euractiv</t>
+          <t>Urgent call to protect civilians and respect international law amid escalating regional conflict following US and Israeli attacks on Iran - Amnesty International</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 02:29:11 GMT</t>
+          <t>Tue, 03 Mar 2026 16:19:54 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNamZhdXAxeG1zYUlSamZTbHJQemV0dERkUTNybnNqOUxqd2xwRlNybzVGX05WVWhXX01zUC1pdnNOVmlVSEJfZDlhTm1zSWhTTHJBSWhnYVUxQkNRRTJtUkJ6QnR5ekRDY183U0VGUk9uX3k2YnNVMU12MUVjTkt2aVFYTFpfVVQtQTUzVVQtTEtRblVVUWx1eTd1S1l4QlowZFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOUG9tcllZVkhVa3l6bDl5WUxkY3FpdDlyamQweGV4SVFCTDY0bmNIZlRtbF83TW9XR3BHVC1uTXpPVFVhVVZPb1Y5YVdDMXg1bWU4MkNqWF9rSlo1b0Z5MXNkVGFSMGpEZnpISWJtRExMbHQwNDRadnlXdTV2RkhLSElJSkVQMnhncm5BcmdXUjI2S0w2VWUxS0EwbFNEelN6QnF0T0x4dlhRVmZSOHNBWlJPbkc1SkIzSlRUbVphWkNJMlZSOXh0N1VwVEY5eG1tUDJXSXNKWDZqUXIwc3NUcFZ5czg5TURWNzZVSGs1aGRrM3g3clczSFdoQUhiRnZMczZKcXdfdnlJcWxYWFhxZVVXaw?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UK Shares Flat Amid Russian Sanctions, US Tariff Uncertainty; Convatec Rallies - Yahoo Finance UK</t>
+          <t>Stranded abroad or travel disrupted due to conflict in the Middle East? Your rights explained - Money Saving Expert</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 16:49:05 GMT</t>
+          <t>Tue, 03 Mar 2026 22:25:15 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNdktXRHgxMGxROU12VmZBWHAxRlV4T28yeDllSHNEMTZNRFJLWGZQQ21Dc0RCc3RFNHFfTjBOVXVPbzJwUnNtQy1nZnBfWU5NQXp4UFBFSFR2U2JfblZ6aEtsQ1Byb1JMTUNTZkVqLTVKVk9scTZBRktIWGNZY05XYjZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxObHBFa3RhaWlJSF9FelZtOGo5S3JiVVJYdFVmby1oYXgxeHlXUzdYOTNjaWt1M1BQcTRIdHAxSmxEOUllRkNudDI0dU5uZ1NzZnNIQkROY2Ffbl8xV2VJR0E2YXNTb0FiRVctZUFOenNJSWNBd0RBSDdrcXRfNWY0eUZlbXB1cWdfU1E?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New awards recognise contribution to UK economy by manufacturers, border innovators, customs professionals, and food and drink traders - The Chartered Institute of Export &amp; International Trade</t>
+          <t>Starmer seeks to carve out distinct UK approach to this conflict - BBC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 10:59:07 GMT</t>
+          <t>Mon, 02 Mar 2026 18:05:54 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxOWFZVQ3JubUNKSEpqNkYzYjc0dFd5WFRUVVNVSzExdzRXMXktZF9BamZrVW1KZnpFS1NhX1lSSjBQeWtqU0hFSWhnY0UwemhrVlgwWklOTVR1OHg5ODR0bUxBRVliWk5RSmp4XzZFYm5UbXNvcVQ4Sy1xQVFkbGF1elZ1Wnl1Y2J3YmJwazdNR1BDcEF2Q2tKTlJEWHJ0dkJPenFiaVZLLUNBVGtGc1N2ZFQ3anFlb2phTXdFY21Wd3pkOVdGbHhFczdLcTFfY21oaWpwMHZEeFg3cm95M0pHbnQ5b3NoTk5sNUxELWRGOG5PUjU4MkZ5SWpxNUhzalFpVmVIMi1JUEVhUjdrWU9uN3phM045TG50Q3JJVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFA3WEcxYlZOY2JJTlp2cjdRMk5jaFZyaFdPcVB6VWhET21abHFMLU4xVXlHUU5NbDJhV21iMW92dmp4SDgwNTNzcU9DVE85UThqM1l0WFhZQ21pQQ?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manufacturing industries: Economic indicators - The House of Commons Library</t>
+          <t>‘Simply not true’ UK is being dragged into Iraq-style conflict, says foreign secretary - The Guardian</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 08:00:00 GMT</t>
+          <t>Mon, 02 Mar 2026 09:08:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFAtZERLN3pVemh0UV9uR2FtVnQwS21TbTM3R3dUQUxfNllGOWFJRTVBUElnLXlOdkJCVUZkYTdTTVJfTDQxOFFFRXE4bFg4SDZwaW8tUHJnMUVCN1BIV2ttLXpKT2V5NThwM2pBc0lacm5JZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdVRucEtOYm5tSEV6SjhmVjI5RnAtWDdOTHpIMmFrRGJ0NTJEcEhJUU1NUGUzZGtqdUgtUGVuVnNwR2kxZVNRZzFYN1VCczI0QzFRem8wblg0OERVOXJPR2pzMFFWdXZlYXAwSm5QRzlwWkxFdFFHaXF6S1pkTm5kWmFVaTd6ZnhzNGdMUEJDNk95QQ?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UK Government Seeks Evidence on Ownership and Control in Financial Sanctions Regulations - Crowell &amp; Moring LLP</t>
+          <t>Why Europe's leaders have struggled to speak as one on Iran - BBC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 20:00:20 GMT</t>
+          <t>Tue, 03 Mar 2026 16:26:21 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNQVJkUkdmY1ZQNTJVSG1wMlVyaUZHVGFMUG82YndueGZjRkdTYUJhcU9xMlJ1N3hvRUx6NW1CdXBCMF9HZ09zU3VYRjlTZW5WTlVIckZlb0Z1LUxHSW1fSGxpeW9aNlU2bGpzemJTcjNFakxxNjFMYzBaVHp0dkJsRklmV2NMeU5OT1FtN2hwSHJTM2k5UjFTclg4VHNjemo3dko3VXU1T0JTbWZxczdvdXJySlpWMXlKTXA1Ri1TQTJGTjhYMno2LWIwek9STU5ib21wcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5kNDU2TGZJTGQwSEgtc3VKR2cxWGxFVWZlRmFBdkdYdXRFY3BZcGwxU0I4XzlLNUw5SDkyNThZWjlOTmp4cmN4WDVwSnBxNG01ejhCeFYyMVpBQQ?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Disinformation was ‘central accelerant’ in Leicester Hindu-Muslim clashes, inquiry finds - The Guardian</t>
+          <t>Boy, 12, stranded in Middle East amid conflict - BBC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 12:20:00 GMT</t>
+          <t>Tue, 03 Mar 2026 17:53:14 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQNWZXcDE2ekwydGQxTFNVS2NoTmVMY2dtRUtaWS1yd2sxNUJQZFBsQU5lc2lNdm92X1d2WFdFQ21vbFJrVXRlMXN2czdpNXVKVVNLZ1dqZGt3UnRQVkRQQ2FsUy1xQ0VKNkw5ZG84eXA4akk5czRRa3RFWURuYlFXR0pVZzlUN2dUT3JIRGw2aGVkY0F0ak5KRGZna0lRcjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE40WEJGanBXMXlpbTA4THJta216Qk15QTA5TVhTQkRCS291Rzc0M2J2a0FzeXVYOVVIS1pwSzdhWm1weXNkZ0NjM3JHRVdxVkRjbkdRYjRnbDAzd05N?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLIA reveals cruise tourism contributed €64.1b to Europe’s economy - Seatrade Cruise News</t>
+          <t>Stock markets slump amid Iran war as gas prices jump 30% to three-year high - The Guardian</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 18:44:31 GMT</t>
+          <t>Tue, 03 Mar 2026 10:21:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQYjBCWXJDejBfNHM3cW5KUHROdm1rWDJQV0duaE5jRUQ1aWlWM2tTTUpISTZDUVFFcS1XeVNMbk1kVGxCb3dfQi14Nk5XbVZ2VUlFejNZWjVwUng4NXdQVUlWQ1NrTTZTajBsUXkzZjFiR2hmNGFScEIzYW5IZ3hobzVUZmgyMEs0UFZFeHIyb3hleUxCOERUMEs1Vk80eUs3dFhOYlRReU9WQVV4RUZ4U3VzVU5fcTZIU3BVazJra1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQcnJ3cHZTM2tqVndJMW42dUY2MFVtc25mc1VOMWpEV2xxUG1YNUtxbzd4WXZvYnlGRGRENnpkbGZEdFFJY2hQLUxtTEYyZTlwR1Q4aGh0c3hwOXFNalVQYVg2VDVfVVkzZTdSUHhXYnlsT2JBSW90ZzZobFZhbzM0dVVLR242YVJrQzlvUy11Q09OZEFBcDdPc1hvSlFlZUFERnU2Nw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia's invasion of Ukraine four years ago launched Europe's biggest conflict since WWII. Marking the anniversary, leaders from Germany, France and the UK praised Ukrainian resilience and reaffirmed their support. Read more: https://p.dw.com/p/59GbS - facebook.com</t>
+          <t>Market news - investments.halifax.co.uk</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 03:20:57 GMT</t>
+          <t>Tue, 03 Mar 2026 17:21:35 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNTnc3TWRuVzIyTE92eUdsQ2EzUFp3MG9BWTZEUWxRbk00dXpvVlExTXAwUC1DSk5JWUVLNGFnTG1GUElKUXBZXzA2S3Rha3hDSXlRUXg4d19vbzBCRk5MaVlzcld0WkpmN0JRVXhiRkxnTFFYQUZrNjNVdFp3dHFtZWpmZS1kNnJqUkVKTlN1aHZxaGN1eWl0cTdRd0dPU0xJaklfRlNmMWpNN29YODhPcWFlcWdGYndvWGFBdDVaOTZYMXBMcE8xLUVoWkpDWnlDcWtBUDJ5d0M1ZHRRdzhhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPQmZwR1Juai1oNHE5MkltUHFCRGtJajJXQ3JPQ0hJeDNGRUVCVDRaNDBvR0tidnZPSjJidEZvcHhLUW5IalN6SF9VRnBKTXVpWHc1aWRlZ3RKUVE0YWZUeEgwWjN2TzQwQlFwd1k4UENsYk1FcDRVcjd5SU9QMWdDT2tObVNFb3JIckllNjdVLTdLM05ZZUptdHJyRQ?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>When is the Spring Statement and what might be in it? - BBC</t>
+          <t>US sanctions Rwanda's army for violating Trump-brokered DR Congo peace deal - BBC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 13:02:11 GMT</t>
+          <t>Tue, 03 Mar 2026 10:28:07 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5LclFOMDZoWmdObk15SllmNWxqNmdZM1hrTmx1c1JVeG1wMC0teGh5QlFVTDNaS0JKTG1xWXRkMW9tUkM2NnAySW9XcGMwUXktZVhuUVZZMjB3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE96SHc2NTdhNW1HQmIwMDFpMEx5ZGpERndvdmVtbXZUOWhsclI4REE1T1pCZmZiQVdTQ0FZcnMwSGxyRjBYT2NveUFqUDZReFU2dzV0LVg4R1ExUDBD?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -991,27 +991,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gen Z influencers trade Europe for Dubai’s booming content economy - Euronews.com</t>
+          <t>£271 million to clean up shipping and power coastal communities - GOV.UK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:00:59 GMT</t>
+          <t>Tue, 03 Mar 2026 16:25:46 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQZk5CMEx5ck5NamgyME5jVERoWktZMnc0aURRRlgwcHB4aDBGTktwdldSOU5hS0VDbDdqVEtDSlFFb0pqZGUwU3JNZ2psaFNSZklJZmx4eV9oTl9JNzJMWmh1dDE1TzBOcnlaTUFXdVRHX0tZZERRQ0lVN2RRd3Z4d0tuT3Y4SzRqOEFyaHNHXzBrdTdBR2FNdURzZ21LZW1sYkJCVVo5SVk4dktPUmtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQNmZNaFViTXFSQ3BWZmk3eThXM2lZS1dXUFo4Sk9sbkJjSVVYa2dZNDBjcTlHczZHZ293bTZuRXZWbjZTQTJzamRvN2x0UzRCWjV3MHc4cDJDZm5sTmpIY2MwMVlscVpsWWlveGNmZTE5YkZHcGpfTFI0VHR2WUVQaHh0ZUhldUk1S01yMjVMMzNyU0l5NEZ6ejllcWZMQQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1021,27 +1021,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NTIA Hosts NSW Night Time Economy Minister as Global Demand for Dedicated Government Leadership Accelerates - Caterer, Licensee and Hotelier News</t>
+          <t>Maritime and ports businesses push for global shipping climate deal - Financial Times</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 11:26:36 GMT</t>
+          <t>Wed, 04 Mar 2026 05:00:23 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYm9ySHhZY2U5LUI5ZVgyTmY5VWoteG5CVkZDMmZteHRXS1R2RUY0X2o1Q2VtWHA1RXIyUEw4alkzOEVtQTIzcGktZVlOc0dMZFNuN0J1RC1ScHdIem11RVRGYmdxX0ExcEM0dTlRTFNsS2otbFFtN3hFY0t1YnRhOVRZWk43YUQ3eVlVUUZvemt1TS1fT2NfbVFQUzByZmxFeEtvSmNNeW5jYzFicXFQeF8zQXdQYlpDaVZXLXVKeEdhYW04emZSOThOamZMampvSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5ILWNVd1JISmNfNmhCRXduaTlicllHVmhoM2N3Y2o3cW5lQ3RwRWplQlljd1dyQmt2MG4zT2Z2ZmdfZGtBTTRMQXRINlNFVUdmS2ZuZloyalMzUDJYT2E1SGRadHFuZUpaM3p0ZzduTGo?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1051,27 +1051,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Maybe the global economy isn't all about AI - Reuters</t>
+          <t>Gallagher flags widening protection gap as UK supply chain shocks intensify - Insurance Business</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:10:59 GMT</t>
+          <t>Wed, 04 Mar 2026 07:10:46 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOWUlIdUZfQ2s1T2pVS1lMUGtTenRpUk9neDVGVXNIaHVhRzVxazJRZlhFbS1CVVN1dTZ2Y3FpMFlkMVpITUJldDROdGh3Wkl0NTlYQlpKOWdXcWFJQnBFZkFFeDJnSXhQcUlUZEZvZzRSNVI3N3hSSVQtM3pSR190cXpZWlFMdFNNVUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNUVJ2TU1FUTNURlAwTEJIOHVpV2pmUHJZWEhPeGx5NUtHaGFFVGNxQWhNM2F3dTBQZTF6bXpPa2VxemJvVFp1MXBIdmFyd19uYTNEYWMydUdkOWQ3NVhWZXd4STFCbjQzdnZidE4xZ3JKcG5TVTNGX0pWVTdSeFRxQjBpQW1ZQ2lGM3N4a2FYdFZKS1JwdEZWc2tESzAtNE9DUi1MeWl2b1Rtek9tdExwXzNZZkx1aEY3Qkl6bEZZaWJJRXA2RHhaamltRUVkWFphZjkzcXVxbEtlN2pMNXE0?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgian diamonds lose US tariffs exemption - Financial Times</t>
+          <t>Match Gallery: Defeat at Port Vale - Bristol City FC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 05:00:38 GMT</t>
+          <t>Tue, 03 Mar 2026 23:52:20 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE11VUU1UlgyRmtDV1lWUDU2VnFfWUlPMmpHczZINHVybnZCWllEQmRoZ2hNNjFOUTQyZ29oTlZWTVpRMVEwYkdLLXhSSmo0Rmp3aUh4TUxmRjVDcFlEamtPT3A5ekE1VjVjcFFkNTZXTUM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5NZTRSOUdDOFM3M1dSTUI0QV9mOTFzNEsySGozekNxa0ZGSGYyTVF3OWJXdzRGMU1yakpqYzlkcjBSNmxPQm0yc2FCbHMxM0M3MG96Q01hczd4UkxjcmJISW0wSjc1SWctRFpUZWUyNVdsejg?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trump's new global tariff comes into effect at 10% - BBC</t>
+          <t>China calls for vessels in strait of Hormuz to be protected amid soaring shipping costs - The Guardian</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 17:35:52 GMT</t>
+          <t>Tue, 03 Mar 2026 16:13:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBvYkhFUWNZNXVOTkNzQXkwelRtcjN0WUZiTVpkNm5GRWdpbm5Tc0lGNU5jXzRVRURrYnN4WDRGSmlGdFlySWJFbjZXWEdLYjB2MWFFQ05HSUFSdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNbDJyQUJRelZJdEpYdGtiOHFxTkZhTHgtMGVyT254RWlNbWFFNWUtdWtGLXg0Tm1SSUhDSi0zSjR5aWZmZXFudnRFQ2xDU0V4ZUROQ3g3aVR6OHlNelRKY043NXpkLVcwU1hzS0UxUUVKNDVJbnpta1dpaWNGMEFuWFpSZGZqbWN3NlQzOVZISmlOU19vV0ZaVmY4T3Rxa0NTaU50ZDdqTW9kaEE1eEtqTFJ3bWltUS02RFJUQ29B?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Northampton Town 0-1 Port Vale - BBC</t>
+          <t>US manufacturing growth slows to seven-month low as tariffs and weather hit exports - The Manufacturer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 21:47:00 GMT</t>
+          <t>Wed, 04 Mar 2026 02:22:06 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9DeEtPQUQ5alJGYVlPT1otTjlndVAzTkdFdTVEMFltWEFrUEY5WDV0WFpPQjJXcG5CMWhwY1R6RTRwMFA2U0F3VFZSUXY2WEJzQWtLc0JSOV9RRXpfbG9sclA5LWI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNa3JPOUxodlFnNHpaN1RvVXVOVVhqUjJoR1JMNG13WVU4UFZQdGFxXzg4NElBdFFmbFdJSU1McGE2ZHpoa3o0SnBtV2pJZkZqblFORUJrQl9VQVJ4MkFja0N3b0Jib05yQmFRV08yTWVaN3g0eDZxNVRFMEVuOGk1SWxSbFFJQngwcE5VMl9Cc3J1Y2d0Sk9KR1BIM29FZEVOV2lMMHFOMHlTazVoRzBBV0RHVUUxakFvM3oxOEl2UkYwSDg?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US-UK trade deal still stands, says Business Secretary – latest updates - The Telegraph</t>
+          <t>Taxi zones with different tariffs may be scrapped - BBC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 17:36:01 GMT</t>
+          <t>Tue, 03 Mar 2026 13:45:04 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQN19PNDVjZnFEZ0JjQ1FZUS1tVkJiNUdqdlJVQ1dFYnVfVFZ0bVp5eFA0YVR1VXE4TDFWVmRTYk9aR3Y0Z05aanV4SnlvWU5OZU9kU3dQTDFONlY2d05nWFJaQVpSSHc3Tk5sWEozWUJhMzYwc3plZ3dZdWRnZ3k2TjJOZmNwckNyVU5YMWhNX2NORmNENnVvWlFMZFlSMV9JZUxqM0dn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1HNHdrVm1leW95RXBnMDg3M3FxZE1iVkdZME01NmViRFdVSmJON3pKREFkbHJ6cWVUQ243RzNHYVh4UnFmMzZaLVhVWmZ5dlZacGlsaGxZRVY3Wmda?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Your energy bill from April: what’s changing - GOV.UK</t>
+          <t>US could owe €110bn in tariff refunds after court rejects Trump delay - Euronews.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:19:37 GMT</t>
+          <t>Tue, 03 Mar 2026 16:54:38 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQajBJM3lfTU5jVUViTDFCREp2eHVObVltdWw1eS1UUGwxVFJQckIxLTNlalhBR2FNSkZMUF9RLS1lSjJKbjM5RXpsTGd4UXNkcDdNVVFJeTlzT3FFSEtDcTRYQWJPT3NpUlJLNUo1SldNdldhZGU1cGJqNDZwM2NqQjVCQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQS3JXNjRITHVvaVdEenRPYTVWUXJfaWlUSmRGSndHa1MzcFZpajdnbzJiS3dWdUV3c0FubWU1WjlLRDE0VVVxWWVUOHpKYTVwdElNNjF3U3BwOFRBZkdsSGVmRUYzUjlIamRkUmhnczkxN2V5Z0lQRE1mX0hnZEktVm5WQXBBSXBuWmd3X2dEN1lfUUVCeXF3S0dLNkFCdXN3b0VkdDZ2MkhvcURXSWdKcUl3NmRxcjN1WEE?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Panama hands canal ports control to Maersk and MSC after ejecting Hong Kong group - Financial Times</t>
+          <t>How Resilient is the Global Food Supply Chain? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:10:56 GMT</t>
+          <t>Tue, 03 Mar 2026 17:48:13 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5pSDRMZnZ5dTd3cXhaRElCMkM4a2RVX1huMjVzVmp2a3JFLUFDUk9vbURkMWRYWklsTm12cGgwSlE3Wno5RWVlMEJ3WXdwVDZPZ2xLdlF4YTVza2ExWVJHM0JzUDFxLUxOMHJHRmhtZUo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBLRE9JdmhxT3JhY1Nzcnk5M2pneG1ld0JUM1dpMURwX3pRbXJ2RmtYcVJsektHaFFCTW11WmY0S2dpMGsyVVM1V0MyMXVDdXhiakx3ek82WXJzWjNlZXB2SXpFNW95V3JnU19Kd1ZYWW1LOVh3d2xsdXFn?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NR buys Barking hub for international freight - modernrailways.com</t>
+          <t>US sanctions Rwanda's army for violating Trump-brokered DR Congo peace deal - BBC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:38:25 GMT</t>
+          <t>Tue, 03 Mar 2026 10:30:12 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQbFAyaFR3VC1acW14Wkl6Uk1ENHJIRVJpNHQyYXNpam9zOVdtdGFTYlViejdTOU50LXp4R3NBZ0hWSEZ0VmZQcDVXVnFINXBwU2pwRUkyUXMxWWVZaHFTbjVrOTdjRnVURW1JZlVrVGJNNzgtdHdxTXVFY0luaE1HTW94S0hjdWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5WN2psQ3ZEYUlaNzVHVTZXQVRIU1BjT1h6Nm9ZaHE4a0dlUnF4LXJCcE4xa3NybWEzTExleU5TWDVvcDhKMm9GQ1NiZnhmajJZU24xS01lYXpfQQ?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Central Asia’s Foreign Policy Agenda: Balancing Between Sanctions and Cooperation - Bloomsbury Intelligence and Security Institute (BISI)</t>
+          <t>CSconnected announces £1m investment in final call to supply chain development programme - The Manufacturer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 06:03:54 GMT</t>
+          <t>Wed, 04 Mar 2026 02:22:06 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQb0pKM2FmVU9jYVNiN1NfY2xGZ1J0M29jdzBacTJjYVNnZ2I0LTdDV09xLUlROGhYWDYtNE84aVJvRmZQOWJ5UEJXZ21YMDhpWnRtUnp0NlBJWGV0cTZIMFJMRDdjeUY4Z3hYUzBYbzhhWXZNYUI5Z0ZnLUkwOTczRTlycmIwWmRMcHlSTVN0YUhkTk9odnF0QVR1VHAyc0szVUFtcDU2VTlkTTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxORm9Sc2V0Qmh2Q0RPMFlDcTlHM01OT3dKRlBmNkU4c3llZWZrX21XR1BQZnBldXowSktrNjV1cFBJemsxZG1PWEM3WlVwbzAzUXFZMG81bFRsekdhdEZMZzZuSFVvMF8wdHNoQnJKVGxYcHZtX1pJQ0o3eFhkbXdDbHlYVUpSSlB4WVBmRHlPUzZtdjF2TGF3YzRvNmRrQ2VJNWI1Zlh1dldLZDNSemh0YVhHT1dSSURFeTRHSEw2Q3VPUzluOWUwbw?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Footwear brands navigate uncertainty after latest tariffs flip-flop - Modern Retail</t>
+          <t>Watch: How the US-Israel war with Iran is jeopardising shipping - BBC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 05:01:24 GMT</t>
+          <t>Tue, 03 Mar 2026 18:49:50 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOWTFOc0tqOUZma1A2Vjg5cGJrZEg5d3VCR3RJZWh2bmRQVmh3ZXVoZXRaTjlZT29sUU56UWd6eDZiLVhTTkNLQVdidEg0UjB6UENyNzktX183cmd3dmNIWFZWUkR3UDNUVWY5ZWdlVnBjX21ubWJJa0JpdXJISEJjMVZPcEZkMjUzUFRUaHRwM0ttUkl1bGZzbTd3R1RvR211SFFGYklVa21wXzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFA2YkExZkVTazFHSjR6dW56UE5EeDFDbVlHZ1ctei1yaDJ6dmZ1c3d3MkNTWFJCWEdKQlh0cTNpaXNkOEljbXJlbWdEbDdnWTB4T1o2QjF6MA?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Climate risk compliance note outlines data providers’ duty of care to conveyancers - Today's Conveyancer</t>
+          <t>Maritime insurers cancel war risk cover in Gulf as Iran conflict disrupts shipping - The Guardian</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 05:00:46 GMT</t>
+          <t>Mon, 02 Mar 2026 17:37:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPTFYySmo2THE2WEdJaUNuOFdhWV8ydGJJZVZmT2lkTGtTNncwVkpEbmxRZXhBV240Vk1XQ24taERFbVVpdkhGRVY5M3B5eFJSTmNPWmQzakNBM1FpU0o4UFFxeXZubFlfZHBYWno0V2FWYTk4ejNEMzdoTm1Cd1hhUi10V0tqTlVqWkNsWEZmVkdMM1pjUTltckJXZ19XSHlDX0ZramFNNWd0aWd5Rm5hOFhrN3Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNSkZrQzBKdlNHNnVZUWotb1NvQnVqMUF5eHFYam1aX2ZHYjQxSnc3R1lIeU9QRE5nQTRaVTBDOTNURXpxMHRyZlBCTmMwZERXM2NMbEZvcm1VUUk0WDR1cjRLNm92ZU8zbERrOGxrekx5cDAtbXF2U19tcnM1XzNPSGREX29Nd0FnUUdxYzV0eFZhVXlHMzczdFRZNTlEWmtLZWFjTnpWSzVRVG5vRXZuUjRBLUdnUFFR?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>India and US defer trade talks after Supreme Court's tariff ruling - BBC</t>
+          <t>DHL to build carbon-neutral logistics center in Germany - Parcel and Postal Technology International</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 08:20:01 GMT</t>
+          <t>Tue, 03 Mar 2026 17:00:21 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5STDlHa012NkU5QVpuckpRZmFZM2k1ME11UGZjZU51T2NndjdNalhaQy1rdVkycGdQVFZydDFlUU1EWlh1c1ZCTHBaUXZZb1NSYVZUNmJncFc5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPRWNCblRxc1piOWV3NW1CWlVNVEFyTEN0M0JIVm1vOWlvSTZ2ODY4akRlMk5uV2tfaEF2ajNMSU1lOGhOOXlpSGlQNV93OE5fazc2WTQ5emxST2dPN2ZFRDg2QWlNNUl5akNjUlI4OTBOQ3lFS1h1XzlCaE1zdERIcENFSzN0dnB1NDgyY210U05BM0l5cDA4Mmtib09Lakw0Uko2VVJxRDlOU1doejRVT3Fqck90MGpyOVNwUTl4dXEyV0NaTThTM19NcVdidjRYWjNuYUdWdXpNQndPOGc?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Compliance challenges with EU and UK nitrites/nitrates rules - Food Manufacture</t>
+          <t>Hormuz crisis ignites Chinese shipping stocks and futures - Lloyd's List</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:30:00 GMT</t>
+          <t>Tue, 03 Mar 2026 13:09:02 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPUjdhS2RkVWNCU3dMTnFqRWFSbnNSVld2a0NWSlVjbWtpeEhWMkxnWDljMjI1c1AxZkN1Skc2SW05dTY4UjF0c3h5bmZiSENmSXpKZDdvUWh6NTRLLUFOTkhEMVdRVzNlU29YbDB6REFCWVE0emw2ZUdrWmpFb3VVYXo3VlBNWnpUUk1mdkFrYi1fN0VyX0NlYVF4NjRUaFNtSnMwNnRENmJ4OG1hdHlGblBxYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOZGpqUTl2akJlMkQyTGc3NHZVOGtaYVJhMy1vWE42SWNhb0FVWTJmdkY5aDc3N2VsY0FhbEd2b3I2dnBsdThSdXlaa2ZBRGNhS0x6dkREQmNMVEx5NGYtaVAwYVp5VDQ5bkZZY2VEaWNERmVKclN1Um9jeWhwZ0tfeUQ0cVQ3ekh1WXlYTDI5WjFiNloxNS11cmZ3?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>‘Simpler’ FCA insurance priorities raise bar on Consumer Duty compliance - Insurance Business</t>
+          <t>Retail fears rise over Middle East war supply chain costs impact - Retail Week</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 04:52:15 GMT</t>
+          <t>Wed, 04 Mar 2026 06:39:05 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNcEVCTU5OTklHVGFiVGhPVndsUUR5azZCaHdvWWY3T2xYcG1EZWpRaXNQNDRCVzFKa2M2RmF0Tm1sQnFXdng0ekR5Skl0YTcwOGt4RVRRTEI1YU54bWQwQzlvTVJWc3NvYlJRNGZqZGlMcXlTWnEwX19sZmdSeXRCdE5QT3pZb2RXSU0wNTRzdjJ1XzNpRjlyRHNJUDRVR2IzV1JOb3M2WjRwcVBIT09sckFwVWExaUdNSHE1RmxlR3ZmQ2dxZmg1aWs0NWY3MmV3Vkk0all3Vkc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNVlNCSzhWOXJ1Z3kzRkpzWG42YmhsNThVZmJVM0tpd2NqaVlVRk9PMldPMFg5VGhVRkN4VjZMSkRKTS15SmlzdnBzcE55TjdRZXBOLUJfZVRYU3c4SHN6MWxUMmRRbWNaT0tZTGZuTkNLbV90LUJOV3M5Z2p5ZmpYVmpySXYzejRIem52dDd0RjNvXzlUXzhnbVkwUzd6UlhCVURoVzNhM3I3MmVsWWhobHdUOTBBQlJJSGF1MENn?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UK Hits Russian Oil Fleet with Biggest Sanctions in Years - Rigzone</t>
+          <t>Explosion after drone appears to strike fuel tank in Oman's Duqm port - Sky News</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 06:46:00 GMT</t>
+          <t>Tue, 03 Mar 2026 12:05:24 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPaUEta0ZQT28zeU52dzlzbXBQbERQUmdBR2lfUXVBYVp4RFJpcUFTNF8xd1FWYzBLVlBZVHB1MmZhN1pTZE85bURfRjBYdmlabGF1NWtNVUtZMjR6ZjJ0S2M1WXFTdG5OR0NueFUzd1Y3c0ZRMk9lUnBQNDdoZFM3TEFjdmgzMUYxaVNSamZZNTBDZ1J4cERmVHRPUTRPVlJBVnJEZnJ6T1h3Umpwckw0RlF6MkJneGs4ajJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZzlFdFo2czdMbU93Qi0tODFoejhBaFQzRVM4a2lvTldwMzZ2X1lDZWZiUFdqU2lXajNzTnZNVWFPZlF0ay1IYWc3Ql9DM3h4dmNSREdjeXVvRk9nekpXZkg3dGZsWFNuWWtxdktrOXVDRXF6WDdNdGRXZTd6aXV6WWxTeEdSa2t4d3J0aWVRYWFiRzUtbl9WdHRXZmN3ODlla1dOY0JOMA?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>State of the Union 2026: Top moments from Trump's speech - BBC</t>
+          <t>Tanker heads to UAE port via Strait of Hormuz to load oil, sources say - Reuters</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 05:19:40 GMT</t>
+          <t>Wed, 04 Mar 2026 04:58:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5wdk93ZHRVWHowZEt4eEQ5bVo4LTVsWUNBVlB5dFcxZ25SSmpwR3RIWFJsdTZoUzFKNVVpSDRyTk9vNFpVNDRPTzYzM0V4azdVbGp0T0lvT284UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNR3hOX3BhQzEyT2xKd3dlcmFMLWp1ZmJuRjNPeXNNQ19HaE1KeG5aT3V1cm41S2FDWkY0RVFnWkhHVUVWYVRGVXNIQURzcVZVNGh5aGVHZmRBbk9Qb0p3aFhNeEdaQk1DVVk3TUlGRjVGY2ZZMnVGQWd2ak1tQzc2WXVRTHFUR3dWNm1XbEFCX0hRcWNHUm1ZN3paVFU2dlNuX0xwMllFUjBFYllqcHVhc0ppODI?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tech can make supply chain ends meet - SeaNews.co.uk</t>
+          <t>'Trump introduces new tariffs as legally shaky as those struck down by the Supreme Court' - Le Monde.fr</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 17:16:46 GMT</t>
+          <t>Tue, 03 Mar 2026 15:49:34 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBGNVhhcmx3MUNQd3llZGNwTXpRQ3RFTFRCcFRrTlMybXJiSDRTVUtxRTNKdUdJcDJfdmdPbGlBRk56T3JYMVprTnBkR183NDl4dG41U1NzajJ0M1I0ZHRrQkgxTWtXZHRUZTRLRWxINHJ1WEdrRlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQb1NPVE9JWWZCVS1FNDk0SUpqZkxGSnZ5VXA1aG9mVTdraDV2SUpCbVF1Z2lLTmx2WFpaRWtCeWItQWZ1NjRRQVRraG1mUm9sNXE2NFN0c0RkMGVoOGhaOEV1Tm85cF9GNHBrZ29pYlhZdVA2bUN4YVhUSHVXQ3UxRWZfMDdZTkZ4WGtxVEtKNWQyMkpYalhGbVp2OEZOOW83a3MxSm52TmlkV3RWcDZHVy1YQzVxTXk5UVNvNXp6aFV1QUN6bkVyQmZjYVRxVWJMaXctM3BmZFJyYlNqM2dBenlMeHE4SU9iSTNhUQ?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>'Pupils locked me in a room' claims striking teacher - BBC</t>
+          <t>Romania and Ukraine: cooperation based on logistics and investments - GMK Center</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 18:56:30 GMT</t>
+          <t>Wed, 04 Mar 2026 06:00:47 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5YOXFxUnMxLWtjWENWeTJ2UUcxc2VhYmFEM1MwdGh5LTlkRDlwdG9MSGFRdk1yUFY3d2pDclpFMzl4NjRGUHdZNm5KQ1U5RFB4ZVV3enhiNlNBeFJ5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZVZ4enhqYTI1RHNhUWRFQms1LWZqUGFSQ2NPc2NXV28yRHZCWTRXbVZWUnNYWDEyOEVJTG45Q0l4VVdHcFFhYzdNTzVWSEJ3T0l0OTlxQlV0UTNlRVFSYmtZN2lBWWdMWkhqQ1pENVl4VE1Odk84cEV3eWFYSVRfSE81eGpCQVFVTGlRNVVOVktFX2JpN09kVmI5a9IBoAFBVV95cUxNZlAxaFBScXNtdlhjeEttenVrMGhBWVVaUExhWXMtR3NSUnVHakpURVVlNjNuNWZXSk1YcmVUcFlUVlFfblk1ZDlXNlMyXzVIRUlNbTBra19GQTBuOEhyaFNETEZZRDNiLXMtZGV4OWRaSFp2WTFIdGJzZHhGTTBGRmJSWlB4cnZldGFjZ2ZFVzdfMTNTaGtCSEotdVgwZS00?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>'Burned and destroyed': Locals and tourists describe Mexico unrest - BBC</t>
+          <t>Small businesses left confused over state of Trump’s tariffs: ‘The level of uncertainty is crazy’ - The Independent</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 03:19:30 GMT</t>
+          <t>Tue, 03 Mar 2026 19:35:00 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBYcWJDZXFTU0hsZGxtOHNVQm41V3ZMV1hkR2poN3M1R2RQLXgtbFdqQVpJNnZ0akNUTGYya1k2RzhrZ3JwaVNvZVJiUGxwTGhyOVd2RExWOXlLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNMEJ6bGE4VGRlVGZWTHVCTUk3dUhtUDlZR0UxaFV5X1NWc1V2d1dPbzRZNjg0R0tpMzhodDgyQldtT3UtNU5zWVMtaDdUbk1tVl91R2NaS25RYUtmZlgtR0pDNGMtX1JzNzgtN29wOHBELWplXzV5WG5SNFFrdFIzbV9zS1EzV204MUJlUFFWLUM2ZG82QTRQZ3pYSTFRd2tuTXVCUWk5VmNsTXc?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dortmund fan groups boycott Atalanta rematch after "incomprehensible" police checks - OneFootball</t>
+          <t>Marine radar testing facility proposal for 1000 sqm plot at Ramsgate Port - The Isle of Thanet News</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 18:03:45 GMT</t>
+          <t>Tue, 03 Mar 2026 19:15:57 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOaWpyMnJaMEkxdzRrV193YWpYbVJ6YlVoY1lHcHFKZHhpc0dmWDU5dUxzTVg3ajZWYzIxLVpzWWV2WXFkZTdHSmlYTmZhdFpaRGNFdS0xWWZXWEpIWEMyQnBhZlRxUGJiVTBYVnJtSjkweV9ORDVnU2hrMGFxelNFSzZDLXAtSHBQZGNzSVdOV1JXTTRwLU1EcW82TFFIV3ZRRDRrZ0prLWhETi1kZVRjRjBjbDRFWVZ3QXNrWWRtbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQRHNkZElfSU9nQWJBSEZpcGxXOGlIM01nc3E5MVFsMmJlT0pqYjUtMHg0MlZNUVJINlBhZ044U2pqOXB4a1RjWTRuMzJRQUt5LUVPM1ZENVkzSWxoZjhCdlVtMURncmFOekZPamQ3NzNMalByempqWTlzMmxONUFNNXY0anJhN2x3R1dzUldXSWVhWmdDamVEZkJzUVhEWUQ3cWtEMS1MU2JFeEI4eFJ0MmcwVlFySVJi?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1651,27 +1651,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7 March: International Day of Remembrance for Fallen Police Officers - Interpol</t>
+          <t>The oil price surge is just one symptom of a supply chain network that is not fit for this age of global tensions - The Conversation</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 15:30:35 GMT</t>
+          <t>Mon, 02 Mar 2026 16:50:08 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPMlI5ZnV1aXpsUnBBaEd4X0lKaWlVX0dBd3drWDhTaFZWaGRIMUlqcWdpWTRsUzJnQWU3Mm55VnBPYVdfeWpNeTlTbjNwOW9jZlYtcmQ5QTJmcDM4RUtfVkJYdy0xdEhldm1MVElhUnRrdnJmZVdURk1rYnNyWW1IUlBkbjdHZFhIMGJkdVVJQnpNLVlVNzNHWDFEbnJ1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQSjNtRDNzc05sU21PdTVCVjFRaTNQRkJJa1puT2hUeHk2R29sNU1BbUtaYnRQanBEUnBsczgxRG9IN1VlMkkybl9zZndVeHFGclFRcG8zX2lKa3RHZWNMLWNHamstNWNuSnpVODkwc0pWVG90cjRsb1FBcVo1X0ROZGRpRjVaMElTb1pFTGNNWXliLU1pZW1ISTBwWE1DMFo2LVNSM01UblA1OXkxQWx5d0dDV2dLLUUxbFdZUmtSQkhkbS1VeFFnWFJhUDFxZlFtbTdJQ1FSVDMxQ0ppNTdZTkln?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1681,27 +1681,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>28 March - Roots Street Carnival at Rotherham Town Centre - Rotherham Metropolitan Borough Council</t>
+          <t>US tariffs on Norwegian seafood could top $120m, refunds may take years, analyst says - intrafish.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 16:23:31 GMT</t>
+          <t>Wed, 04 Mar 2026 05:22:29 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQRlJVam9TRmFhWnRfMmx1Y2hIQmNvdThaLV8tbDJKMy1DdWxsa2xRZy14VmxCcE9iS1luYnQxb0t4MjJsTk12Sm5raUNCQVp4OVQ2QVdIeGxEaUE4UktZTHhJNUEyWUsxRXNSdW9BcVdXNUYxRDllY0VGOUdzR1h5UjByU2tFTWtrSUdSejZkTl9tVUN5cVdhMnl0QTk5eXRaeE5UbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQcnVLT0luNHJHMHlieVpmOG9zZVI5WG5MWXRzd2JsLVlBZFRlb0drMXNXMWFmYnhjUUR2YTFGX1pMVV9lOEhRS3FMMnhjdHNpTWpSSmNyR3lEQmFvNXJ1V2VIcEpVLTZWVWQxczVyNWlhZmlIQ1pFWHhEb0tsY2hUb0RmbmNrSE9EMWN2bUZNcS1YX0pnTmFGVklOMjJlN0NvQWV4dUswSk1wRHhjM3drSjhxVmlySkRMSUdaUWNrejIwZGV5?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,27 +1711,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tennis officials draft in extra security for tournament in Mexico as civil unrest intensifies amid cartel violence - Daily Mail</t>
+          <t>Trump ponders Plans B to D after his favourite tariffs are taken away - Financial Times</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 21:48:22 GMT</t>
+          <t>Mon, 02 Mar 2026 12:31:03 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQeW16NjZTX2FpUm03Umd1X2pCcmdFUGdRM2NEMkVjOEhmM1dIYk9BU1pteUJDb2VZX1hENzl5REx4bHVmU21HYVVCcDVSNG1wbVZ4aGxWeGRkaG1KVkdLOVF5M2JkUzdxaGVxNUxvZHBpVHYzSVllYnNSbmtJZm9jdnA5ZUdFd2NGVW1nUll5X0FPazVtUVN2X3lRdTZsaG81THZrNlRRUVdxV2FlX0ozNHFVUEYxZWJzdjVnTUNDTE1MODTSAcgBQVVfeXFMTVhTVFhVU3hkUXdTU0ppR0dmS0E0aWZGa2w5VHlKUWZvQy1sdU9uMEF4eWNZMExCV0NLMEkxSkNYSWp1ZUltdW1jZk5qNGhnTmdTaVkxdjFpS1ZaQnRlMWdfTlhoVXMtYUI1ZXFzV2VJbmFWd1VhRkJ3aTJBWVFfX1BBN2ZLZWE0OGNDZlNjVHV2MENFYjFOazNDT1VwV0t3enNselhYTGFPaW1ZNXNmNUdzSEhxU2Q4dlM5TlB3MHZrN0Vld3FILXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBuZ3hqNTRvYU0tVGlsWm1nbjMwWFl6cDZsa2Mxb0w1VjV6cXpyQlRnWk1XSDNXcGZjbDdpTFQwNlpyU3k1UV9RRjU5aHV2Y2NpSVMzOTQ1VlJjc25rYXU1RGtfSDMwdkIyaTVieE5oMGU?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,27 +1741,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UK’s food system a ‘tinderbox’ for social unrest which could lead to violence, experts warn - The Independent</t>
+          <t>US sanctions reveal Iran’s growing reliance on Turkish companies to expand drone and missile programs - Nordic Monitor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 16:43:00 GMT</t>
+          <t>Tue, 03 Mar 2026 23:34:51 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaG1wXzlHVzZNc1NzS0pDd19SQS1DbjN1VHJmTi1aY3ExZEU3WGI4eWpZaGtfMnZydmpISW5kXzU4b1FTMHdhRnVDX3JqaVRwSHZnRFloZm1OX2dBREtQT2d1U3VYRGEzamNLSHFLZDQ4M0ZoS2o5Z3RJTEVIQzJJTWlvckFEYXJLMG1tbnpXdmlLTEVNUG9PMzROQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQdlgxQkxPMmhpUGgtMDVGaFNSQ2d2QnpJdnl6SzliZkpfT2R2djIzbWxVRldwelFYcWpUTEFxem83T21yUU5hcG1iZU04eFIxa3BSTkQ5aEhUanljdzRSLUJXUEQ4ekRCRGo1UmxZY01iZEJVTlZuWFRacUJZS0tINkpIc2d3Vjg2QVI4SlZxM3cwYWc4RGkyWkszM1lBZi1POUdhbDZlOU9vU3lzVzZicjdnaUw3SHZ1QzlTU1FPdEgwT0dEN2F1aDllWQ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,27 +1771,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>At least 2 Quakertown students released after protest clash with police; DA investigating response - FOX 29 Philadelphia</t>
+          <t>'We have to win, this must be our standard' - BBC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 22:57:58 GMT</t>
+          <t>Tue, 03 Mar 2026 23:10:54 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQamh3V2I5OVk3VGZSeDFwSkREREM0V2ZhOEE1UUZtWmFYTm04cFRfYUF0ZF9pbDNHa3RjNzVLN1dnOFBnazJPTzNUQTdQU25ldVJneWZIdWdYeEV5cjlJbnY3VWNaNHhYRXdabVFFeGlhYXI2N01ZSnhrYmNwSGJ3TzUzcGxQNUJJQVg3UlEzOUNlVGN4MjRoS1c0WkRDMHE1OVBaaEl2ZnFKSHNrZG9tTHhQVTEtVkHSAbwBQVVfeXFMUG9xbElqM0RKMGsxRUtHWnhQTWloaElQOFZOS0VFLWtPNktTNmgyaXpYLVdfSy0tNXBSMF8xVHZtbWRaS3NUdm1MbU5FQ3JTcXppdnR6Wkdia1lzWUN6S3A1dUwtb1FRcHJ4YWtFX0JyTlJkNk5WT1FWd0lJQ1pTYzAxd2lHSW9xMnd3ejVaYVNOOXZldDBleWlCZkhPeVJHay1jRElGVUdaVGs1cGJaU2pjVG5SZkJqdlk1SHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBNaUtrZjJ0cTVyYUZsdlN6Z0REVXBsbUU2Ykp4SE5UVmR4dzlSeWxiVlM5bFlJR3hrMF9oYk9QOEVDeEh2dUNiV1FQbndyR2lQakpyU1ZqXzBwTVJ6OWhXb3phaUhwQWc?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1801,27 +1801,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norfolk school for autistic children's staff strike over assaults - BBC</t>
+          <t>Report: MSC and BlackRock Push to Complete Hutchison Deal for Port Ops - The Maritime Executive</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:36:20 GMT</t>
+          <t>Wed, 04 Mar 2026 00:35:35 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9mcHRUNVlQblIxazIxR1FnTS11ck1yZXU0N2o4ZFd5OU1XUU41azlGVVduMlRSeUJXNlNTOHJtb3dNQUd2MnV6Y3pINURlb3g1dVpaeEJwZHB6R05H?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQeW5aVC1HSExCWFdqcWd2aEctY0VNMFFFZ2I0dTF2Y095RFpiaC1mWWZLU2JQRkVWVFpEWVFjYXM5dm1fSUV6T3VXeEZad2xFYkZ1SDg1ZTlOUU96YTE2NkZrdXU0dHlPQ2RzWUc5Ql9Ec21Od01EczlIMWlXZXR3TkFvaDdMWDhERERRa0ZvYTh3N1dMUzM1OXlDOW9iXzI1cklIZEU1MWUzMU1w?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1831,27 +1831,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mexico hunts 23 inmates sprung from jail during wave of violence - BBC</t>
+          <t>Moomin and Pippi Longstocking get supply chain transparency upgrade - Retail Times</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 13:43:53 GMT</t>
+          <t>Tue, 03 Mar 2026 19:28:50 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBRQkQtSzREazRWZ1BhMDhsSmFhZnEtZjJkVmpUTUFJODZOQW4wVV94Q01KWDRuMnp4V3BvQThvVDBqX3RQV3V0cWtSeEp0Q1VGU3RVNW1YWDlBdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNZWlMbXpNODRpcnQ3X0pLNzdtOENPeGRMOE9ORzVoLThhWXpLUVVwYzFQcmNqVS15WnlyTC1DZEd5blluS3V0M2Z4TWt5ODlpTmFIY2FkR2FzNmJPUGp4ZEN1WGJDdC1ENVFWSW5Na3lMb0hac0pDdUl6TlpCWF9QQ1dRcnFpSENGMHdFMEJ2UXh4LU9JdGJJSGN3?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>'Significant failings' during city disorder - report - BBC</t>
+          <t>Shipping between Red Sea and Europe &amp; North Africa? A Contingency Surcharge (CSU) is coming up - Hapag-Lloyd</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 15:08:12 GMT</t>
+          <t>Mon, 02 Mar 2026 12:27:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1meU0taEROVnhCNWVra0VjSDVPR1A1RkRYdjJYWjdPVjFOQlkyUS10RExJVktzbTZoZmJLRzdSeXUtT3lFaUhqUDV6Wng1cmN5YmpselNRSFZoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNWGk0RWRDd0Y5eXg0ci0tU0poOGhkTUhfcjJnMlZBMjY3WkY2MnJObzNIckVqd3BCMUVFelpvakVRU3JVel9fUjMxU0ItaTBidlBHZ2h3cWIySUkyRjh6WXBDaWhGemFzXzAtZ3oybkxtX2xPVmUzOGpDRDR5aEo0VlRMM201VWxqdjJyaW1DVklOOGVfZlZLUUtHWFFvdllWRnBlWHgtbDVuVXZ3VXFSZVlNanQ2N1g2YXpLNERGMFktbktiZGxmRXZyaFVtbHc?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,27 +1891,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BBC's Will Grant on the atmosphere in Mexico following unrest - BBC</t>
+          <t>Ellesmere Port man who harassed supermarket staff faces sentence report - Chester Standard</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 06:25:07 GMT</t>
+          <t>Wed, 04 Mar 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE5GWVN3UlJ1QnVVMml2STZuZlItMHpNelhEZjVHdDB1VldhbGplZ3YtNUxrMDJMRFFMV0N4NllvSHpvQjNKSHhfSUItYUtxUVdJTjhQWlNhNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPLW5qN1JNaUNYNW1qaWFRVG5FaWJ4QmRRNnRnS28yZHBsZW11bVBwdkhqa2V6TDFmc0NyX3JCR3FKVi1WNXdWRWtFSWdsNGtXRHIwV1Azb214a1d0VWpKUjlidE1SWmxSaGJVWVA3QXk4MkJLdGRzVWU1SU5nMmJkMl8tcklpNUM2MFpUSkw3ckpHemJGb2hjSElUbFBKbE5JNGc?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina approves Milei's radical labour reform amid nationwide strike, clashes - TRT World</t>
+          <t>Met police commander denies Jewish group’s legal threats led to ban on Palestine march to BBC - Morning Star | The People’s Daily</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 06:50:42 GMT</t>
+          <t>Wed, 04 Mar 2026 04:21:57 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBmd2RlSE9mRExMdDhvMllHeE5YNDhiWHEzdUxfeFAtWlV5LXlRbVh1aVV0cElwQlpMcjN4VmJmSWc1Sm1yQjIwTUxtSFNISDgzcmMxMGNId1PSAV5BVV95cUxOSVFtZVlMZUNYTzBubGtCSDhZakNjTDdpUm44VmdLZXZvNXg0NHlUaFI2S0E5LU5vZGwwWTFkaXAwdUJrQVh0Vm56NXZnaFd3ZFhiWmNSdURndDJSNWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQSnkzWFJTTHJTZmFYSFcxSjhvS05lNHY3QzBiUzBhckxyRGN0eXJyaHpqUFQycnNvUktwMllValZkTXBfNVBiYlBfeVhzUXBiUkhUSGtvOEkxT3FOTGxld3FlLXNialNSdUlYQUFITUtKem9VaW5telY2NHhnNzlDb2FRZVBuTzNyQ1pxVVlVMWtGZmQtSE04U3lQMXh2b3lOcllyS1Y5eGFqbjctd1VZV0ZoQnk3ejBHRi1PUUxMQlhnRVdvNmc?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Man beaten by police at Town Hall protest slammed by magistrate - SMH.com.au</t>
+          <t>Video. Israeli strike hits Beirut hotel as Israel-Hezbollah clashes escalate - Euronews.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 04:30:00 GMT</t>
+          <t>Wed, 04 Mar 2026 07:24:02 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdTltZXRQSGQ5OXFiVjdqLWFxcUh5RkhwUDlpc1VjMTA5N2pLclJNYXF2YVRQTVkzLXNKcWlZLUxHLUVIZDhTZmNMYUxPdmQxdzlob3NfYV9zZk8yWDdXTExYSVFIQjFvdC14YTVXV2RqTnhqQXVhb1VTaHNkYkplYWVreFVFVTdtVmdfQ0tad2FCWmJuek5tR282Yi0zNGs1M2lBakdBdXgyNnZXeFhCb2dWQ0VseGtaYUMyYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRFFSbnNKT3ZVRzBQSk1DQVZ3b1pWWUlMVGdENjRwUUpISGlQZy1EZk5YYTByV3JEOFI1eXBGRmpqM3lhR2p3NUQ5TjJyazIySzE1LWUyemNZaUVJa2RXM1BhR0pFM0NJWHRQdUQwWDZ5cVh6UXJsd244dnpEN2JqSTdtRVBUcFlOZ1dyZWxfcFA4TmgzUzFUeXo3VzhOWmpOSDkzVFU0RmxYUXdodGRTYw?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>March 1 Will Be A Great Day For Spider-Man Fans Ahead Of Brand New Day's Release - Screen Rant</t>
+          <t>Women reflect on safety five years after Sarah Everard's murder - BBC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:53:03 GMT</t>
+          <t>Tue, 03 Mar 2026 06:12:07 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQU25oTHVVdjJ6WWQtWGEwSVFCWUd4dEgwWndlY01iVFVkOVgwbUN1NDk1aWNLWUdKRWZEdFhjcnpjYV9ReVRsWDNHQzlZSDNYb3BOQ3RtQy1PcDV6Qy1rV0ZPaWdHRDNSdzFYLVVwV0xRSDVKQlBzQlZUWjV2VFZ1N1RXR05lR3hVa2JEczBYdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1pZXFlaHcweDZva01MbDNMTURzNVd4YzVQOHFoaDBHUk1yMDktZUhoNWlUclIzV1ViVkV1ZThWQkpkRUFOVXNjakhFWjEzYm00ZFBzQjlNekhWWVdQ?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Teens arrested in Quakertown ICE protest charged with aggravated assault - Inquirer.com</t>
+          <t>The Times Luxury cartoon: March 2, 2026 - The Times</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:36:53 GMT</t>
+          <t>Mon, 02 Mar 2026 04:00:00 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNLVJGa2V1REVFZHNKVEJnNTBGLVNkT1prRjB1YVUyTlpiLWZtOE9QelpZdUVVb0JTcHo5dkFUOFpfRDhBTE9pREJSOEU4QjRRb0s3VHVmUVBhU1drNWZRelF6RUhLUjhwcFNjSGdWSWFuMkNZbTd3Z0g5a2lUWnpsYlNJNUpBT0QzQVF6d0l3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipANBVV95cUxQY3d2X1A4S2szQWVoVjdrLXdpVEpmZ211YVhMaFVyZzM0d1BDbnI2ay1WTXBsdW94S2RLMlRieThDRGRyVE9nY2NLNUxYRGNyVk5jaXZsU1ZJUmdBdHdaNlJZQl9YNWY4dENJRW5qeGpzT09QM2JWMmUxM0xYX2pyaWdnQ1k5Y0N0LVNvbmVZRG0tcmtmUklhTzhiRlgyNkRwRGx5bS1sbVFSZGJFMDFkeWRDek16aVo5bUowTm5QYnRaczQxc3c5MGlrTmlXaUprdEYyQ0VtbTh1anVCb3BvakJOT250ZUxHQmZoNDRiOHFHS095eV96eVc1bUdnVmZyUGhaRTJPQmxXVW9EdGJJSjM2Z0EzZXdJSkgzUEItbjdRMjdkSHZDRXk4MU9qOV9Qd25rbVJYSU1JczNjMGhZLTJYVlp4VEF5aHhBYmJpVW5sVDFXZEcwNWFxUTBEejhFMWFmRld0SjlXWmU0Zi0zVXpsX2Z2b2pTaFpGWm5NQUsxLUtERlA4VUNMVUUxQnVYTHhON1BFSGI0NUZFRl92UXFmT1Y?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DU students protest, as 'police beat journalists' - The Financial Express | First Financial Daily of Bangladesh</t>
+          <t>Cumbria Police reveal speed camera van locations for March 3 - Times &amp; Star</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 05:46:17 GMT</t>
+          <t>Tue, 03 Mar 2026 07:10:00 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxORXZIM2hoVjljQXd2bm56UnNHVFhhUTBTZXVOT2JDcWpOVDN6NlFjTndsSmZYb19LM3pVaHVvLU9LQUZnOEpKWkhVa083bFgwbnN6WFVMdUpQYU14MHBhdkNZb1EwaS1vOGhrT2gtZHhuOGpiLTJzWV93bkp1RWRlMGN0RXhnTHlZZjdGOU1YRVBWQWxv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOaGl5Zk9YNW9vSnBLei1yUVUtdmd4anQySzBqcWF6Wnp4cHhHYzg0X3htUnZsZ0t4VnQ4WXlsc3d3R0k2ZUpzS1QwdWxWUlNscmo2TEwxX1d3ZVdRVjl1UWNPT2xXdjZsRjV2MHNVT1lHdFBkOUR0UXNCLW9hclN0OUJjUUx5b09GVG1jUzJ4dUN3YTdSa3ljeHVrbXliTmQzMmFVdnpGOA?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oregon residents, expats recount unrest following cartel violence in Mexico - Oregon Public Broadcasting - OPB</t>
+          <t>Suspect Arrested in Greece for Spying on U.S. Military Ships in Crete - Мілітарний</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 03:57:19 GMT</t>
+          <t>Tue, 03 Mar 2026 11:19:17 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNM29jWHY0VGZSM0diazNCTjJZX3BCeVRaRERUZFpRVVdWVm1OQURORFNPMHdmSEd2WHA1OVR0ejZuelRtdG1KalMyRzdvWXRNMi1lRkgtM0dRWEpSSnpXb2xwdmtaZWt1NU5aRXZ5eVc2aHRhUVVhcTlycGcycTJlVW1YYjV0NVAxYW1EczJSOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNa3ZyWllxTjdubWR5Q0dkVnVQQ3lic3RsZW9ybktxcElDZ2ZxRzJ1TUluaGhLZ1VKN2pnbFRVY3gtZ0FWSnJLMUtfOXdjeEhTcGJZaENNUWFGelJmT3RNZ2luZFhIOFZ4aVBFNkxEaGhJem02SmZhdEtPU2I3RUREb1BHY0lTQzF1N0I1dWNaejJJNTVZem84LWw5LTQxV19ESUE?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2101,27 +2101,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>What is physical AI, and how can you invest in it? - MoneyWeek</t>
+          <t>Call for witnesses - Fatal pedestrian strike - Pinelands - NT Police, Fire &amp; Emergency Services</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 06:01:59 GMT</t>
+          <t>Tue, 03 Mar 2026 23:55:31 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBWeV9PTHZVQ3RGVDF6Qi1iTDdpN2dNZzI5LUtLUVd0ZkdmWjJKRGJMYlAtY1pnWnNUaDRZNGl6MllJNkNtNmRBNlVfLWhLTF9iNDZmZFdMUEdPZzFOUDdxZlVQRTVmeURVNDlTaTNOOEt5bFZ0Tmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNM0VvNjUxelU0QjNjR3owZzZyMTVKdFN6NVBLSGNLczNzYThwU3pKUG1YV2h5bE1OWkdDSnpINXZobmlVdWthVVJua0RUS1JwUjNRLVpTb3ZhX3FPTjlReWlSV19uY1NrcU1WYW5BS0cwSW1mTkI5VWxjdXZ5UGl6bk1FXzRLT21ZS0pNNzZ3?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2131,27 +2131,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Forces Shaping European Credit: Data, Automation and the Rise of the Multi-Asset Trader - Tradeweb</t>
+          <t>Nio to Launch Firefly Sub-Brand in Thailand on March 5 - eletric-vehicles.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 22:45:08 GMT</t>
+          <t>Tue, 03 Mar 2026 20:25:08 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQRFAyZDUzR3lBRnJLZUNmLXlBQy1XUFFQNXpCb2tWd3o1cHRRY3A4OWJqb1owVW5RRHltLVVJMmpZQThwajJteXpBZVJXWHVVcUhPVGpUb0lvdlA1WmFQQk5qazJpWGJ5b0Z5MldqVjZXNUo4V254MWhTWEM0WEFSUnZFdlFKeFBmTXZyUHZhVmVnd3dSYnJYTVotRFlrcHJEdnRRbE5MSFlvLWNTZE43VTVuNDltY1FPaHBLbVFMWTI1U1AtWTZINXkzMU9zWmFlQXRNOTJZc2JkYTNRSDV1RWRtWWJ0TFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWnBjaG1qOEd4S01TZ3p6RVZuaUhOcnE2OTJvYjc2QngweEJRNzZLM2xkc3JxbVhiWndUNGZIY0RtX21fdF85RWdUbHZKN3FMN09uSkt2Skh5eW4zZ3lzaW0yVDAxTE9vMXRJV2pHQk04TVRDSWlDd084M1Z1andXd2dPUW9iUlo4US1SUDlpQkRmOXFKaHhwN1hWb0s?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2161,27 +2161,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US software and private capital shares hit with fresh wave of selling - Financial Times</t>
+          <t>Daily News- March 3, 2026 - Riley County Police Department</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 16:33:09 GMT</t>
+          <t>Tue, 03 Mar 2026 20:51:08 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9lNTRrX3ZVY2lMaThqZ0pQR1pJS2tsZXRMZVBiSUxleS1PdHZQZFNvTS1vcS1nNmpxSHUtYVVDTUs0NTFfUWNUbmRudklJckM1TFdkbENXLWtPTUVocTVPemI3NjhObnZWZlF5ZmhiR1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBkTlRKZWM1eHFFZ2J3bTY1QWpXV0gzQTlVclRCaGlGSWFSVUpqdXhUSnc5VFY5RWQ0ZXl3dm10TS1oVXF4b1FwajhfZmpwa0JRN280TVVXV0l6c0tXU2JaZnRLNzMyR3duN1E?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2191,27 +2191,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NHS pilot of AI scripting tech reduced admin time for 87% of users - Home | Digital Health</t>
+          <t>Arlington Police Department's 'On Call' Newsletter for March 2026 - City of Arlington (.gov)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:32:37 GMT</t>
+          <t>Tue, 03 Mar 2026 22:27:08 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZF9rM3JlUWRpZGtqT2xudlk1UFVkX2NXWWtPaUZObGZJVjhNTVNRa0ZwX0pmUV9jbzdUVjFidTYyQUs3c2NzbVJoa1pCTU9XYktCVHpsZ0tHdkN3MTBtc3hvR2o3NHViQ0NTOUZlVlpmWGlaSUFpWVkzRG9ULXRMVUhwQWJDYWdrOGpONmlYSEFSU0ZJZmVlSVZMSEt1NVFEMUFuZ3F0NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNelpOTm52Vm05X096T1ZBclAxOXVFemdDX1BCRkNDRmlGQmU4VlJveFVWTS1Pc2RBNWdFYnVYMVk0WnFJQXJwTzB6RWFDV3liS0NVNGVGM3A0U0Mxb0RwQ1JKTGZ3eTdIcUEzUTloRWJ0a04yUzNlQ1hfZEJ3N0JORC1YVFhaNTNOd0pFaFlBeUNIMGN1Nm5ESE9xZGpfdmdtWi11YmNSR3ZUMjUzRk0tOXJyN2ttQQ?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2221,27 +2221,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US threatens Anthropic with deadline in dispute on AI safeguards - BBC</t>
+          <t>UEFA knockout draws set to shape Europe’s big March clashes | Daily Sabah - Daily Sabah</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 22:58:46 GMT</t>
+          <t>Thu, 26 Feb 2026 09:28:33 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1fTFA4Rlp2MzdLREk3VG1Ka05wWGNEWG9yczh3RXUtQTJSemtSTkE0bjVYMm5uNFIwVWZJdTk3bW9TOHhuR2p4UzFMUjVFS3N6ODh3bkFqVnNSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxORS1IUmtXQTBqdHAxZGxGSnJaZVFUckZQMWs1VWVod2RPVFV2ODgtTmJfMVVOSDZnX1BaeGkwZ3I1ZWZTcVF0dnJQYlhxWWRhLVpzQjQ0ZXA5dk81RGZMQWhWN2p3ZEJnejdHNEVTdHJPYWc2d3FJZVB0SmZKTEgyQm1NclZROFotRDlEN1NoRTJpX252M3JuSWJ2ekZWNklvZkNj0gGoAUFVX3lxTE1BdjJreXJMajZicTE1UnlmSS05aVJ4VFAzN1N4SGhGbWFpOUpmbllEeHBGVXVFU3hhYnhvTUItVjI1Ulh0R2pzaTd4ZWplanBGYTJ0cTF2eHRBUS1aM2F5Q3RNdThocGMtU2k3V0pfd3l0dDNFYWtjSjRycXpTdDlnMDBJQml6VTQtaUJoMUtmTkFIa3NCYU03N2dhRFlJRG5wRDJBS3c1Tw?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2251,27 +2251,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IBM 2026 X-Force Threat Index: AI-Driven Attacks are Escalating as Basic Security Gaps Leave Enterprises Exposed - IBM Newsroom</t>
+          <t>Champaign Police Invite Residents to Coffee with a Cop on March 11! - City of Champaign (.gov)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 05:01:26 GMT</t>
+          <t>Tue, 03 Mar 2026 16:06:59 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOZXFEZm03WHYzcmZWVWlYTVRnanEwSnlxaVJaNkZDdUxPUzVKTGZCeUxTbU4wakkxNUJjR01TSFRZTjZmLXlUQ2dmR0g1SU53OWo0T2J3MFhsODZvblpGdzdPV1RTWEx2QjNZS3VKbTZNS0RDZXhyZ2FjSDFaVzhyamVnaUNKd3ZQUjZEdDVrQ240Q0FtOTFoUzNaSE90Qk5ldFlKNXJXUG1ZZUxlZEk4TVd1azBrVWpWcDBhVUQxbnhscTk0ODFSTHhFcG1HM2FONU5HZV90RERrWG5LSU4zUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTFh4VnRoSDZ3Tk1kNFRqdEhmbFBJaml0anFCTEdwNU02TWl6dUNseWVnNVZRckR3VXZNNGRJVHRRTGtCdVctR1NFVk9nOGxLZjk0cjNTMU15Y1l2REdaaXlDWjNSTTRTd3NoMDM2MmFQal9qTGQxRE1BNTZmdlRFUDl6RHJFbG1abndMbWVyeEs2TGlBbHVVWFZwQ3hhVk83OW56bA?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2281,27 +2281,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Agentic AI and the rise of in silico team science in biomedical research - Nature</t>
+          <t>March with the AGM: Elevate Retail Strategy with Insight-Driven Webinars - The Golf Wire</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 10:20:10 GMT</t>
+          <t>Tue, 03 Mar 2026 21:33:50 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFBtWEdvbEZoVWFiN3huUnM4TDJ3YW1YVjRfWG16dWF0dzU0M2MycnNPZ0xkTDhheDFlVWtwZm5VaG0yVEtMeXUyNGoxcnFJaWo0TTVZVElFaVdJMm1Qb0J3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1pTHcxTmtkT0MySms0b3dCbHh0TktoTmFuSzRFZTZoYXVKaWw5YmhncjZlOF8zQmhvX0VGM1I0eXdNTkZCV1ZiY0FPQVFWSENVMnJwX2d3?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2311,27 +2311,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OpenClaw, operational AI and the SaaS stress test - The Drum</t>
+          <t>Prineville police log, March 10 - Central Oregonian</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 19:03:18 GMT</t>
+          <t>Wed, 04 Mar 2026 05:01:58 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSGZxbzZFUnU1bUdxQWR2cVQwdUZFS3Nwc29RM0ZLekJ2b1hnSU5zMWVOWXpaeDBiRkhGd1BEVkJJMW1MZTktLUtsTVhaRGE5ZlVWRVpEQWpKR2dsZERNWnlWQlo3ZDRjNVhQR0tGNUtnZExkT0haTE9oR1hfNGlxMHJyVzNFUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5rbGI1NVZvakVIZ0VmS1JWdVV5OWVlU2FZMFlBZUFpUzJUNzhzdnFhSTZfWmE2eWF2WDRnTlJfbktxZnhUOF9aN3cxLU02aHJ3WGVWdjYxVGZEVHRrelI4R1F6M0NzMldVRXlhWTR4dVVWR2p3VlFrZWJpOA?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2341,27 +2341,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Agentic AI for Warehouse Processes - Logistics Business</t>
+          <t>Cairns Overnight Crime Wrap – 4 March - Queensland Police News</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 01:26:39 GMT</t>
+          <t>Tue, 03 Mar 2026 21:17:00 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOYVRHeUd0WmFDdXNlbjdUMjZZMFluYmJGaksxdk5sSFRBQW9KZmFIYjhManlOOEQxV25UWnVjV0VmZmJfODdGSTBjRVE4M3Z5TFBZN3hLaW9fRWNoaElyNEVudUYzN0wwb2JFOGJwcjZFMlprVXJyZl9yVkVRNzh6WTI0aTRndGdEaERKdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOXzZkR0tOcEJDUlBwTGw5eEt1QlhISXRTYXJnWDMzSkoyMVczWmZ2NUdGaDVpdk50TlBnamVNM19JV3c0SVh2d3JVY0NJY2pWMlZWRmQwUUxFT1k2T2hIOW1KVkE5VEtRLXBQQjRLT09xRExpMzQ1QXFiM2xlMERvR0ZFeGlHNWp4V01SSg?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2371,27 +2371,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Enhancing maritime cybersecurity with technology and policy - MIT News</t>
+          <t>South Fulton police seek help in March murder of teen - FOX 5 Atlanta</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 05:00:00 GMT</t>
+          <t>Tue, 03 Mar 2026 23:10:16 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRnkwQVZjVGhaN004UTBBSC1IbndpNkU0aHdiempUN0h5VXlackRsWHlSM1U5c2NoU3Y3aU5Rd2lyYkFhNHBsejg1TjNRZmNGNnoxY0x4Uy1sVExWMWZzT2lnTDc0cTlYb2tfX2dZTmRwUGR4OWJmX1ZjLS1QcDdWR0VrSmsyeEVVWlJtcGhoLW0wbnhVMjN5bDF4SlhWWkFBQWZ0bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPdEFETUY3d3lMMWdMS2hwYUNQR09yVlhZektyMzZRSHpGbldrVFVKZlRvUlVESjJMN1dRV3dyanVxQW40aUxNSUNESjJOZUNSLWlCWWdtSnpXV1lmSk0xbnVUazhQUnF0R0traFF6dHRBc2hNdFFyRFdBWWI1U3l5MlF1X3Z1SzTSAYwBQVVfeXFMT3Nvd2tKYi0xclo1eFcxSHhZLW8zeTVSdmZ2MmNGYjAtM1dqd3NqMkdtWjNGejJ6TVhla2k2TEhVYVpWTTFuUG9HaVRQYzdXLWFqOV9zRkxDejg3UUZ6NnJuME1aNEJCdnVDS2JZU0VObGtaZDJkREJ6SWE5dEFUSW9nUnA1VXRyRkpLX0Q?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2401,27 +2401,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Artists and writers are often hesitant to disclose they’ve collaborated with AI – and those fears may be justified - The Conversation</t>
+          <t>Today in History: March 3, Rodney King beaten by Los Angeles police - SooLeader.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 13:48:50 GMT</t>
+          <t>Tue, 03 Mar 2026 16:43:38 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNbXNZUTJUWFFiOFlIaUg3TWlfd29jWm9RMGRhTDRYRzJla0lfR3puc0hycHhzMUJMWjVUQWlBRk1oSjk2Vno0ZEFMaExxdzF6dno1eHJvNjFnZGpyLS1BS1ZiQUdlSnI3SnJkakljWmR3VG5UenQtRkFoODNhVV85eVoxQ2V1XzQ3VzNqTHdsMVNSU0dLRFYzMGNmMmdGQTA3UnoxX0xTV2NkWU15dWZLSWhzVDZ3ZDl4T0xZV1NCdHNKdUtzNzlVd2E4eFJnSlFub2wyMU1fSXQ1LXdQazZZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPWGRlamZvOTJCazZ3NWlzUjZyQlBaTWE3bmlqQlR4NUJxMHltSnAtdmJFeWxiS2I1QWtNVXVIYUNtd0lsZGhTbFFJbzlPSU8zSl9QV0F0WVdDelRaQVVnNW5oSkZTcXFLS2ltVzNVaUtYc1JPc2ZtUWplaEFudU05cG9fSWNqQWpjU2gyUGlldkpiWXduZUlhT0V1U3NzQmhSa0tEM3FnUzZmc0x5ckxPbQ?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2431,27 +2431,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AI is changing travel companies’ hiring mindset - PhocusWire</t>
+          <t>VIDEO: Aftermath of air strike on Iranian police station in Tehran - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 06:04:20 GMT</t>
+          <t>Mon, 02 Mar 2026 18:48:33 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOVVV1MlBwb3V1d2p4enM4UndxR09FazBDd0VlblUxdmxlX3lkYXhCUXNJaWU2QjhsVXgwTk93YWh6QVFUQ0hOR1ZsZXZzZUp6STYzYnhaNzd5MWJCUVJkVHk0eHBwdGtiSVpVLVdSUmN5cVpYUXcwUnZvY2V3cWhtVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPT3ljaTU5bHI3aUVTVmNyRnNDZzh5Wm5uNlhQWllPMG9pQWhzb2NBQm4zNXNUZFNwSjlFLWszUWlSMjE5aTFackxfdU9TcXUwOFFzdDNlclBzNzJoMVRCczBVckpLdEtLM1JGeG85NlhpZTFtS29Ld002WmlMWkJZMnMwQ3U4YW1ycHNWUlpBa0hXU2thWXhEOVFpd1dmdERibzR5UjZJd281OTN0?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Israel to invest in more AI infrastructure - BICOM - Britain Israel Communications and Research Centre</t>
+          <t>Teacher v chatbot: my journey into the classroom in the age of AI - The Guardian</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 12:56:41 GMT</t>
+          <t>Tue, 03 Mar 2026 12:16:00 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBjSTExTlJxcHA2dzZtNWpRSzJOOHlsRHdnSGx5UUdfZnNadUtoVG1SNEtRb3pEcG96dldTRlVKaFRUd2ZNeVlUMmtQVUV5RlpiMVo3ZXJibE1XMmRPd3oteVM2NUMxWXRJSGxvZVU3VG1sSEYxWEZN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUC1XWU43OXNTY1VvUkVlRDhsaGxEdk9BdFdBTE5uS0xWdHVBSllScHlFQmdIdUNTYmQ4LWx6SzFjU2N6NEIxTVZOcml2S1ZJSkZwQ3dWV0VUbmpveklwcjV4ZHd1TXVzSnZ1NnVaVkw1b2YtMnB1MW9wNHdqTlJ0LUdWU3VmNHpKY2VtT3B2NENqbmtRWWc0ODdwUTRfQ1ZsWHFPaHpVNzZyLURaNFo0VVZQTzBsME5KWkZROWFxYnJHU1FwbmE4aVlfN3BDOU95endUMGNSZXY?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>How Romania’s growth shift and AI are reshaping the job market - ING THINK economic and financial analysis | ING THINK</t>
+          <t>AI helping farmer with data about bees and crops - BBC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 09:49:38 GMT</t>
+          <t>Wed, 04 Mar 2026 06:09:54 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNRnJSUGhUakZEdGdDdVpxRXR4a2szRXZncUhwSHFmeHdOeGdYSnNPTFIyM3BOYlJCTDA3WDJyT2IydXFsNTNrd1YyVmduWTVoamhSN01iMVdhb3BzTEdiNzlyNTB5SklESzBfVWlwLV9ZOHhnSVMwbWVzeEQyRUxyZWxHUzk0MGt6T2FDck91MVVLU0lsSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBTSDlJOFd2ZDR6N1ZUOHA3MnBZMU15UUQ0ajhXNTkyNy1vNDR4dVFmaG5Gd0t5cjR5R1c1QjRpdzVSbTAzalQxcTR3ZGp5X2ZsM05jOHEzeFhKWUJw?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Flexzo Ai and Island Doctors Announce Multi-Site Partnership to Deploy AI-Driven Workforce Automation Across Florida - PR Newswire UK</t>
+          <t>AI and privilege: Assessing recent court rulings - Data Protection Report</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 15:12:00 GMT</t>
+          <t>Wed, 04 Mar 2026 01:19:40 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOLXlVUXQ0N0NFS0Vfak10SHlqRHNpalZfRGFhTWV4RGQ1THpYNC1zM29rMjJlMzd1bUhRUEdrYnk2UnRSM2Z5RHI3Tk9lOFFrQVZOclE3Ty0zNlhrdF9VUm9STVFSYnJJZ0ZQcDB3bUt6ejc0eXlEVWN4cE5MRVdQOHNnb3lFNkk4N2gxUHJYTkkwempBcHprZDBPcDM5ZnE4b3BZV2JsUEJrZ0VJaXhRUlJVR3BqQ0Vnb3VRZnphN2VjUUlYa3BoLUNWZjgydmdZRHc1UjA2UEVwYjgxV3RvRHNvdVp1cXZjSnFvYmVYZlJpRVdCNGk3ZVFoeTV0VnRWcXE1Xw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZkRWZmxlLXBYNTFsNjJiS0VOVC1NbkNzYy1BNGFDVDYxenpPYW1HVW9PR3NWZFJMSU8zeXN0QW14NUZXclBYdERibTYyX2tUZ2h3a2p2a090OUlydEpZV2RRVW5WZWVNRVc3RXYzVUx5ZUY1TG5fdjNqSS1jSkF4ekZNVHR0aGNDMWdfcEdVd3Y0bm5VMHhhbQ?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AI and Alternative Data: Why the UAE is Redefining Financial Inclusion - The Fintech Times</t>
+          <t>OpenAI changes deal with US military after backlash - BBC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 09:42:51 GMT</t>
+          <t>Tue, 03 Mar 2026 19:37:28 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNOGMyTGtaTEI1RnNoN0p2SDVvcTQ3VlN0SE1nUFZHTG5URi1FSWJpSVp0bEF4b01sa0xzSHljbkNWakViZEhEVDY5ZkF5dTltNFpwSG96M21JLW54WGc2Um1uSlZmN1B0UmxhcEk5OEVkNlVPTndfSXd1SXNWa0dfelVyNnp1d2U0eDVrX2E2enF1QkFRNWxlbm1neVoxcEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1vckNhRkttVzdBZWFOVHhwVWlSVmpsLUc3bmZGRkRseXhfQUZxa0FPTFpzMXFBcFJEbUlocnBpSEFEV0RUVV9GUnYzTlhJTHY1bkNFcjBKdUdidw?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Telcos told to step up as AI, sovereignty and APIs reshape B2B demand - Mobile Europe</t>
+          <t>AI and GDPR Monthly Update - Dentons</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 00:47:56 GMT</t>
+          <t>Tue, 03 Mar 2026 11:05:11 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQVl9VYl9vWDAwd1lWQWdxc0c0Z19DUEQxT0RrZzZxZ3VMbTh5Mm9mdUd2M0xhVDVXbTJNSzFkdUItc2hwSWtFZVFzelh3QXhscWlMWFFNOHhGVTB6RFNCX1hJVXgwMGJJMWpfaGRaNlFPbFVqbTdTM1lzc1RVXzBWWnpsZUdMUjVobGdvdEtMU0tTa3JVTkhxTGdhUTNuQWtqX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQcVIwOW5TSFR0VXpsV0tKSGdMcUdKR1I4UDFnTjhWSHBycXowdTNJTzBHcEVCLUxHcnI0RFVGd2thd2dOWnotQmJXZ1lBeXVKeXcyVHAyU3ZtdjlFMUlLVVpPdy13OGxpdzJhMzJCeXJCdzZMM1pGOVVORTNXNnJGZk4wYzloQjdmMGkxRzN6c3NiLWFQWTV6aENQQzZlamhCUHkyNTVmQk9ybmV6T2g5bEEtYTR6eDVILVJLTUR3YlpNS200a2RfQTRuZUdnLXhNcTRVUlpua1lIRVVTSEtHbjlkekVGcFpSS1FWc0ctUVlLWFhLdHJ1bnY4V0V3bkhNS3RYOFN4b2w1Z3lO?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Today’s AI Has Plenty of Tools. What Companies Need is a Builder. - IBM Newsroom</t>
+          <t>AI and the Future of Proxy Research: How New Tools Are Reshaping Stewardship Workflows - The Harvard Law School Forum on Corporate Governance</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 21:51:15 GMT</t>
+          <t>Tue, 03 Mar 2026 15:56:43 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUG5SRE4xWC1OOXJDS0dhbFdxQXo3UmpNaEEwOU1hbW5ZOW9lMHFpcHpQcWpKRUFGV0M2SnhBTnJXRW9Hb2tjTS1lTXBQaWZTbmQtcDlTcFV3MEVqU2RaWjZ3b3oyYkNuQjk0cmtZVldTN0pxWHZpZllsTjR5b1JDTURtby1ZVlEtQkFrY0N5djd4ejRJYnh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQdm5yTmxoRnRUQXdFd3VkSzZtYThndS1TS1JGcTlGRXR4OVZzSkwyR3Z6UFFIMUk2X2k5djdTSWxrSEZEQ2JTX2pnNmtLc3Y2QU5lMlJKZ3lFeTlvMXY0dFF1MGUwUjRtLXdGNDdubWc4bG1FaVpVdFJwMS1pNnMySGFZRVlEZXVzVnZVMkZQVkZMYkhsTnpZLWhuUUNKTWtwd1VrZVcxZVZ4MDludFBHSEpMYnRhekc4WUo3eWpMa2JXUjFualM3eg?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jeffery warns education secretary the UK is getting it wrong on skills, AI and early careers - Recruiter.co.uk</t>
+          <t>WFW advises Vantage on partnership with Altarea to develop French AI and cloud data centre campus - Watson Farley &amp; Williams</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 13:19:14 GMT</t>
+          <t>Tue, 03 Mar 2026 14:06:32 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbnlLLTg5bTZqb0tuOFVtaF8ybjUwcXJLNTRDanRNLUF6cUVDWE5Rek16bTdjcDhwNEVCanZ2TTFyTWdNcjNxUmktSmE1enRGY3RSMWh1bVV3eEhHVk0xSEMxOWRBN0ZaNk5ZVWRHV3hLN2lkdE1WZEk0U0JwQm8zQzVzRWt4aGE4WlBkN1VIQUlnazZkUElXcHpZZWlNVmJaTVFIYkNMbDRJMVUtVGNyMTBDckgwWVd4SnE1amFidw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPOUt1ZlBoUm1pajFxMVpsQ1UtWEliLW53bE5Hd2xGRHhIWXg5SVozaGxWSjB2eERyV1V0ZFRKMmwzYzhKbjNFUXRiaTRtV0V0QmZpcUJwZElWd0dhelgyOW1jTkx0ek1TMUVnUkxnb2RNMGlzUHNsZ1pYQ3NFNkJ4TnZVdmNuN29sY1FLRko1R0VsVEw0eXkxbWh2RU9QdU0xYVdnUWI4TTR1MVhBWlp0WWJBZ3FKd2QxNXptOGtwbVV2UQ?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Using Artificial Intelligence to Predict Chronic Disease Through Diet and Multi-Omics Data - News-Medical</t>
+          <t>12 Quotes About AI—And How It Makes Us Better - Forbes</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 23:34:01 GMT</t>
+          <t>Sun, 01 Mar 2026 12:30:00 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMW1FbGpzSGpzakJuLTJoampxNUlsUzlXb1UtQkNXRl8zLUlTWEJXWEtSQVNtSlhPbWxvaDZOMjd1TnZiR2dfMzJhMmQ5bFRtNTRQWTZPSlVyekFvQVBWRGY2Y0NZY09TT1pmRXoxeWJBRzNiWDVxRUc1Z1NNTmo5a2hXWUlpUDFwTzBYVzRQellnRG9QSzgxN0NvTW9LQkhZald4ODEzaXk0MXJCaFZiZ0FxVDVIeG9OQk41aHZacGpTWUpYZjl2SU5DWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNaGgwRFROcWFfbHRwX0owS1AxaElGRzhUUFFJbHREbGs4ai15Qno0VS1sUmI4MUpaSGhLYWJ0dnBxeDN3Nm9IR2pnQ3VVZFZRYzVWNUdtbXU2S2t2Vm95ZlJ2RmhTTm91OS1UeDhFSGlUS3N4dTVLVWxfRTJpYjZqdWFZSjNQd0xoV0hWSVI3SjFYRzFEV1RJZEpLSGd3ZUcyMXc?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Automation: China Accomplishes Unmanned Operation of a Container Ship - SeaNews.co.uk</t>
+          <t>Physical AI: Intelligence in motion - PwC</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 20:31:13 GMT</t>
+          <t>Tue, 03 Mar 2026 16:27:04 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPeTJieEhYMUxaSkx5WkR0dThoX3duNEMwTENSSHF2a1NQT3U0TEh0NnVaNTlyYWltd2VhbjFmTTRqUmdaSTNZNTNyci1GNGRBbGtjTE1fa0swNzJwZWdnZGtac0pXZmNkZ1BIdVZ4VVpJVU1nbVI3VFF0bktES1dqY0JRWXhiWjllaGt5U2pPWkk0azVNalRZTlpJV1hKV3JZdm9TRS1wNEY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQU1EySGR2Mll4NjJVRTJ4T1Z2VUF1aDhHX0Z3clNqN3JUZHNOdWdjczNDOVFyS1VWV0pyZEFvZnVCTEtqdGpvbnZaRXNXYVgzWWFWUnpvXzQ2c1ZXNnJUcmZlcUl1d1I5WUVicmlDMkZILV9xcHBVenNwSE56YUZOZ21DYzdOY2N3VklqNm12S1hRc3h1bF9rODk4ME5YOC1TWGJkdnUwbw?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Blue Planet’s Kailem Anderson on the need for data and AI standards - TM Forum</t>
+          <t>Europe unites to build sovereign cloud and AI infrastructure to stop reliance on US - Euronews.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 16:46:36 GMT</t>
+          <t>Tue, 03 Mar 2026 15:11:57 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPUEtlc2VlTW85cGpvSjc5R1dhcTFRRGEzSFhWaWFZMnV6RXpsWEVzUUFNMGwxUkx0dldXdFZNaVVtQm50WTlEcHQ2ajdMUV9ndWpMbkUwemZ2ZFVfWEQ4dmJ5ZUIxbVI3Y09vT1oteFBRWWJoNVlLdzNqMmJ2a1h6eUp6bGFacXJfZHc3aUZSa0ZjQUJWa1EycGl4dUc2eE5Ic01ILXFFWlBmOWhYWnp1eG9PMFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPOWtqZFVRVG1vTFhvRzh6QXRvcWp5UGR5R2ZqM3N3VGdnd21aMVFGTHdZUkdDY1Y1Ul9seXJVY01uSEt5TXJqcGF0ZzdleTgtUWZ0Q0ROQ2NiTm9PVUdBZmtMUmlGeW5la1JPd1p1OGF4R2k2ZlRtcDZwajk4cTZBakN6UEZmMlk1cTl3cmZxM0ZaeTBwZG9OYnV1NFBnVmJxUFoxOWs4b21objZkdG5WY1JNNG1vUWdkNzdpQXMyRUJBdw?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Anlife: what does an unusual evolution simulator have to say about AI? - The Guardian</t>
+          <t>The AI Law Professor: When AI makes lawyers work more, not less - Thomson Reuters</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 18:40:00 GMT</t>
+          <t>Wed, 04 Mar 2026 00:36:34 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQWmp2VUlxdklJUGxCbS10V05SY050ekxsYUFTWHJwVTBzTklRUkE2RDdYZkc5QUxtWVNiVC1XRWR4Y3FxZDVKR1RyVUhpMWR6Vk14eGVHdlhDVGQ1dDFTWFZmQ0x6UWhGd3UtNGlvMFRDOTR3T0pybHhncTZ3N0dxVC1rOTVKcHd6aU1Fd203RkpNbmVJbUo5VDR2RS1MUUhTeU5jRGVqUG9BcF9obkdMR2M4d1c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQMW9JNGRVUHdiZ004RkltOHluQ3U1ajYxenlkS3I2eUljbGZLNWZURnhlY2hxWDVlWENackFYN1pDekk4dldvRWsxaHhxejNDQU9vdlVVa18xZXZUY3VrbkdJS2FJTC02YUFOQ1dHUGRMOFZfZ3VMUm5hbGo0eHFjUmdBRk4tbmZvMkR5STBLMEtLX1FpQ3lvVHg4ckRySTBUT3FTRzFhMHY1NlU?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>How Colt Technology is Meeting Growing AI Demand - AI Magazine</t>
+          <t>New GTDC Research Details Distribution's Influence on AI, Cloud and Hyperscaler Sales and Adoption - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:33:29 GMT</t>
+          <t>Tue, 03 Mar 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE04YkFDQ0RxMGd6aGtJbDdBVVNsaklOOGxfVXlleV8tZ1Z6QXBHaV94WGZjOFRMc2FQVXBZYk52OFh3Wms5cXB1Nk9oMF9aRmdtT0Z3b2RhclhYQkhVTzE0YUdwMDNZdVVxTmJ1Vm1GQ0c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQVzFFaWR5TjNwU010bDNWVjJISE5hZTVkNVRVX1lqUWMwMHVraDZpUHE2M09Lbl9rYklQdmJhQzFRWHZMMnZqMWtmX3daTUJ1Ylo0MHhDbGFsR0pjZ1p6dF9aOW55eDdkRkh4OVY2UUhxLXZrX2RESWtKWkI3SGp1V2UwbUpsT3BTV01paG5NMXd2eHRqOVI3MG5R?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>The ‘extreme and improbable’ economics of Citrini’s AI report - Financial Times</t>
+          <t>Generative AI and Privilege: Practical Lessons from Two Early Decisions and What Comes Next - Sidley</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 15:30:29 GMT</t>
+          <t>Tue, 03 Mar 2026 15:05:33 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBOaXF3SWl0bldPSmtHMm52X3J0dXdtWEtESFhwNXRTUnBMTW9nTFg1S2hDa19jemdaQlFSZTZSUTg1LTNFVzI5WWVzMjIzdHd1MUczUEh0RzYwMm9aNFpWWldHOFlJN0gyTi1US2h1VGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQY2RIaHVnZ3duaEVjZkEwN016RzRvYTZLbzBRcFI1cDBmb1hHR3F1aWZqcGNyaFJTOHZLOHJiUGZwSktvTk5QZG9VQ3JoN1MwT2VoQnFPUXBYSFZFVjItM0p3aFc1VDNhRGVUaElFa3VMRHh3OEFRYmdyTy16WUdOS181c043X21lakt5OC1TSXlDNmxfWXhnX1Y2RE1WX3dDYmhVTkJ5eEFpTGl2UFBYODdYVW1PcVBVeFNqaC1tNksxLW04TkFLZTluUmoydw?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AI and the future of work: The jobs you’re not hearing about - BBC</t>
+          <t>Guernésiais translations generated by AI 'could be wrong' - BBC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 17:26:08 GMT</t>
+          <t>Wed, 04 Mar 2026 06:11:59 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9WSHdMNGgyam5MVmptOXVBVEphTHI1LThIQXdNNERlWnRqeVhJb3Nzb1ZWcnp1ZXFVWkMzQ3hjN2dUMVcwRDVFTldnR3IwTW9vU2MwcUNkemg5YjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBiRUNkaVNpQmY3QjlwSEJjLVJlV2hJNU16dnFuQUtIc0VrMlRiMHA3R0N0eU5PT2FMVGxUV0lCZ0hCR0o5OVpGallVbmJrNWd6YWh5QUdtbFRyWVVr?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Clearview AI and the expansion of US border security - Bloomsbury Intelligence and Security Institute (BISI)</t>
+          <t>The highs and lows of AI in the tattoo industry - BBC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 06:03:53 GMT</t>
+          <t>Wed, 04 Mar 2026 06:13:41 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPZVh6QjRpNG11SU1SZGg5ZEhnVzJrTU52WWtQTFFDRlVSSEhDcHA2dzJvemFSUFpOcU1zdkk2Ullwb0pfX1pTN2ZtRGh2ZHBXU3Y2SmNTV1FRNmJPMVJGZ0ppQndHNnhqN1haTG5TNEhfNUhKdGNXdlgxSnFVZm9HNS1fVTZrYzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5KeUZVVU1RMlJ0VW9IcDMyRmpweUl2MUdiUmJqVVVlTHVuamV4VlV5WGVGZ1lHMHlzRTFRUXgtaGtMVkgyMGxBWmthejVwU3FFMDBxWURYdHRPQQ?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nokia and KDDI demonstrate quantum-safe optical transport for secure AI and data center infrastructure - Nokia</t>
+          <t>Trump is using AI to fight his wars – this is a dangerous turning point | Chris Stokel-Walker - The Guardian</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 02:00:00 GMT</t>
+          <t>Tue, 03 Mar 2026 14:44:00 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNV054MjhuSEZoOExaOXdUOERIaVBPQzlYLVJoeUxTUVBWX2dfNU02aThmWnBPRVBoYUVQREFDejBHY1FsSWlWaDVVQ2FNN1UxOGxnZXFQRUExWTJCT1FYMUE2b0lJQjlXNjlRVXE1dFh4UGt6T3JteXByYkdLNFZIVXlrUFY1UjJyZTdQYU1rZGNQdmw5MnBsNi1kS1BqSE1yNVdYS1JQVmlyWlVYVGtNZkRrTVN3cl9OSlVWbWpjZklaUGlVek13N0JzTV9sVFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSUhSdkZvNzBqbWtsSldTYWhnX2t4b0YwbWxjeXlTbjc1cWZNYjNlSVh2dkx6ekhHZ0Nkc3dDNnFMSWxZRlBOaXlmeUdrLU45eGM4MktFZ2Qwdmg3SU10Vk5rYVlIWGQ1aTF3RllvR1RSOUZSWVZQbXF1ZEYwMjRlbVBibDB1YkVxb0pTSzRJWUhJZWxLWVphVDVidk1KTkI1ZEEyMG9CVQ?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>The Intersection of AI and Attorney-Client Privilege—A Cautionary Tale - Ogletree</t>
+          <t>Goldman finds ‘no meaningful relationship between AI and productivity at the economy-wide level,’ but a 30% boost for 2 specific use cases - Yahoo Finance</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 15:35:48 GMT</t>
+          <t>Tue, 03 Mar 2026 14:35:53 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOcUlVeGdVODB0VEx5OTBHeEI2QkVnalZVdWRQNkN6UjRRS0c5dFVSZjMzYUVOcFR0TUYwMFJhUjlhRXBsU1dSeDNMMWpzVHZROW1iSmFFWG02Y1pNR3UwRzl0LVduVlhCeHRDZ2VMN2tMRVhZaU5LT1B5OWd1M2ViWS1qWlRSN1NaenNTRnNNdjhwaWpoNnhheEhNWUZPRWJ1MVVOeFB1em9wNHV4UnNyRk9DakZXT2stQl95LW9Baw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNZVJja01kbXQ3UHZMV1M2cTNNQVJFZnZNbVo0X3BFY2p5ODdEMFhUdmtvY2FmbW0tMGs5bUNfdXhYLWtPYW1NSm44SElXRHhVYnRaeFdScllXanNvSTV2UEpHZ2hvczZlMHIyUFNUajktbjBFY2VSb3ZNeU56UXQyMERobzQ0WjMwSkxlOElOaw?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Building an AI-Ready America: Teaching in the AI age - The Official Microsoft Blog</t>
+          <t>News Corp is essentially an AI ‘input company’, chief executive says, after US$150m deal with Meta - The Guardian</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 19:00:42 GMT</t>
+          <t>Wed, 04 Mar 2026 03:12:00 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPVDlQTDU1ejV2amlqaEhfQ2REX3FsSTB4NWIxUllnVHNMWmcxaFNJaTJWaWtZdEFvcW54NXRqODhVUjAweWxRcmFmbTZWTFhVQzRFN2ZvRlZPMExwV3o5UFJ5N09ld3BfTWt2MWc4Zl9nbGdtUFFIVHZneFNjc0pxUXhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5OMnpYb2t4OWl4dXBTdnNFSFViM3VDSjJuVjFlbXEyZ1FIdXY5NV9ITUR1d2lFNG5aQlZ1WkNUakxQZTFMa1RrZDBobGJkdTM5b3l2eENBWUFMNHJJbHRfQk5Ua1BFbk04WkJhZTY3bXNmRzZORlZ1QkpNVDEzblk?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Coventry University Group’s India Hub strengthens research partnerships through collaboration in AI, clean tech and healthcare - coventry.ac.uk</t>
+          <t>Mentions of AI in BBC 500 Word stories increases - BBC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 09:58:34 GMT</t>
+          <t>Mon, 02 Mar 2026 16:55:52 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNb1RCOXY4VkUtVmVfWThlM0I4NzV6anpqSUpVRkZxUzU1N051MUtYb1V6RDhkaXpLTlFvY1VINW15UFdjdHdWcUk1S1VXS1VTamx5Y09SREF5TTg4OXZiekYybjZqV2M5X0FhR19ScEQ5T2duM004S0FrU00wSDRjOGhoTHo0Z3A0X3g4WFVpaEpDd00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBmRTJPQUtmdW56a3RXUkNRU3JlLWlKSFJFRTZvTUhjNnAyYVJuOUtSZHhOZ2xGelF4bHFNeU94NmpjWnFvQ0stallGY2k4aHNRUHN3Y08tWVAzQQ?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AI is simultaneously aiding and replacing workers, wage data suggest - Federal Reserve Bank of Dallas</t>
+          <t>Pitch to Pitch: JD Cymru Premier Technology &amp; Innovation Programme - FAW</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 15:56:15 GMT</t>
+          <t>Tue, 03 Mar 2026 16:45:21 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBQOWtReHktSFJSOVo1ekpaWTdNLUxUODBpUmdqd0h1OVRsOVVxdG9kR1ZaRmlCQzhIUWlNVTFtNGJLdkFRaE5PR0p1azBoVktPT3hoZl9VV21fOE5Ud256djQtTWk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNOHQ2ZzFnQ3RfWU42a2hjSXJicVpMSUtsbk5DNkFZcVBnc21FSEVvTk5UVDdZSXdnMlRsZFdoSGVGT05oSGR1NlRFRXVDRVZCOXJtamJvVFhyRFRNTzNEVXpZbzItOWZLSFlqaGxKYXI2LUNQdm5aQ1l6VC0xZDRoRzU1RHdIaEkxMEJVeXhhcFVycDVsdFI0SXhLUVBlQUx2OGNz?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wolverhampton AI and coding firm's 'pride' at business award - BBC</t>
+          <t>AI and the distribution of income between capital and labour - CEPR</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 06:12:36 GMT</t>
+          <t>Tue, 03 Mar 2026 00:05:41 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE95d1Vfd1h1NEw4VHUwN3BnRkFoUmNqQ0hxVjdmVDFsNnZnMHBKNGNzVEREd2FlZzVJU2Q2MndnQUFXTE9zdkV3WkFQLVJQOFFjMktSQjNiU0dHUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOc1VHY2dHWGpaQ09ydFFHcHloSm11aFdYejduN2dGRVJLMThfbEdvTFF3TndYcEtVbENFNG41bzZPdENzdHBwYTMtbmMyTkpFMlltaDFjaWIxU2xDcEltcnpIQlpSOGFoUUZjbTR0TXVwMmhuOG5QcWJOUEU2bk5NazhFeVM3ZUFJZUhoUQ?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Citizens’ CIO on the ethos that led the bank into the cloud and beyond - Tearsheet</t>
+          <t>Former Daily Mail showbusiness editor denies hacking Sadie Frost's voicemails - BBC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 13:56:29 GMT</t>
+          <t>Tue, 03 Mar 2026 20:17:47 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNR2NRNzV0eTdvMElEWnlVb0xvbVlRMTRNcU1wNlpDUXhHV0pqWGlQQ3V5LWdxTWFzYUo1djZ1OVNUdURZVUJ3dVlGNnFmcHdJMDRiNk1nVm5pNEJ1ZDlvV1NIN3RFRzNXa19WZnVmSnVsRGw0MFF3YWFfXzlreTBfbFJyV2RlMmhQRExxWmpreUtyZkFmNTBJaElJSkxQb25n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBMaXppaVJRR3p1VUVCaEdrLWRkSDNpbHJ5TzFzQjFGYzVWTmdjN2d2S3NKcWZ6RTRydHRzQWxoTjJ4WUVPYVZqcVFiSkJWSjNNY2N0anNrNDhWZw?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AI Is Upending Marketing on Two Fronts - Harvard Business Review</t>
+          <t>Telefónica presents the ‘SOC of the Future’ to strengthen companies' cyber resilience with AI - telefonica.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 13:49:41 GMT</t>
+          <t>Tue, 03 Mar 2026 10:42:54 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE40Szh6eEVXajluSmo3U2VlZkN3bkFWa2o3UW51bXVaRmZLMlRXX3BacDYyMXNNZjlwbHVNVEs3N2l5X3RYbjlHYkYwYzMtRFNNZFRaOWRTLUtGQy03SllpSmRlQ2VMMHlwZ3ZNLXpXZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOaW1rYjBwSmNWc1RJS3RiU3FmX2xUMXVaVDRzMWgyMTRDd0NtalZKTmo4NkdwcFFJVHpKN2VZSjROcldQQlJ4Z2tXcnVpVGt0YUZTWjEyNGdiaGtkVHJGUXFlV2thSTFOWlNmd2s3Ulp4a1pHZ2pBY29PWHJEMXhDQy04N182WThwejhVUzVvanBPSFdwSWNkLXQ0YXZvOVFXRGo4SWpoaVVEYVB3NVVDVzMteFN2d2hnd1hMM2dJNjJNZ0lpSkpfVWItOUg?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Track AI and Thematic Funding Flows in Private Markets - S&amp;P Global</t>
+          <t>AI could be giving US lethal edge in Iran war - but there are dangers - Sky News</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 23:19:06 GMT</t>
+          <t>Tue, 03 Mar 2026 19:45:34 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQU3R4MjBtZk9iLU1CbG9DMlViWnJnXzByc0Y4Y1RVbjhkQk0tYWpzbjRQMl80eXBraHRPNzZKNFJVX194eHpscnY2SDViLUJmUjZ0TnVUOEt6ZERTMzdPV3BnSFZNY2UzNFNzU3JJV2J3WE5SZzhLSEpWQl95dUNtcnU3d1luV3ZYM1ZMMnVDTVNoY0U0bFRQMHNYRC1WUGs2QUlFa2ZVeHZ1RmpzWmRaMWRld1RLblNoR3dYd2lHMTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPa1NZZ3hfeXF1d0NpOVY0UHZYYS1UNFlXWHVnem4yOTJlaEpGUm00dWc4eWxIUm9MajRNTnMzYjdwdG1XMXdLaWU4U054MnZibHVqaXNjeXRWMERMRW1MbE1jSE5Qc2Zqdnd2YTRfRnJUQnFZSzVsSlM2a1dXS1FPLWRRNWd4cllOdzZFc0ZDaVBVOFd2aV9LbzJ5MXdHWVRxbXJwQjh3?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ex-Mail on Sunday editor says allowing hacking and blagging of senior politician would have been ‘crazy’ - The Independent</t>
+          <t>Major funding boost for Cardiff biotech firm using AI to design drugs - Wales 247</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 16:09:00 GMT</t>
+          <t>Wed, 04 Mar 2026 06:56:11 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNMzd0S3RULWswY0thUUY3TkxrUkxfT1c1Z3dicXRLRkpKVDVRYXFmM3dta2JhWElJaU00bHh5MVlUeVhBQ0toQWFjYm1tTTBBb1RVX1ZrQ1lFVUNNNU9YWHJHSjJkVXpobVdVVndHTndZWW00aGp2dkxwTGRLZW9SQnV0Z1JIdm9JN3FNM1VyUW4wWkdTczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQVVJpRlpJdlNWdmZCemQtNDlPMXpGZXhhZlpPM2JTOXdBbE5rcHlRdmVRem1JcjA2blNQQW1JVmszR0tZRkhDRjJHNW9DRHZQeXlxazZqckJTVEs1NE13M1hiWjA2Nkp4bmtodFk4aUcyaERQTVdpNGpWVEdudlVKRGFtNV9tM1RRRmx0YVBBdkJmanB2SU5jMkNpQ1M?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sam Altman defends AI’s energy toll by saying it also takes a lot to ‘train a human’ - The Guardian</t>
+          <t>How AI is already reshaping working conditions - UN News</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 16:38:00 GMT</t>
+          <t>Wed, 04 Mar 2026 03:00:00 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQYklFLThXLVhsMDkzaFVUcF9HZVVVU0xWdGN0WUE3ZlpfeGZrQ2xQWjV1WUFaSTdHSzV1dU1heTc0bVFTUXNQa2J0N01MVTFKOVB6dHo2Zkp3X1hOZVp5OVVDU0xLanlrWHhfdVVfeTVMc0lNTldxVkZLRk03VUY3Ulh6V2V1UUpXejRvOVdmUzFPX1VoM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1wbWZrbjdDanhYRzRqb2E2eldtRjR0Y19tMUYtQmtrUVVJQ1RJaE5EX1lKV21YMndadjBMRUY0dEJTajhhQjgwZW0wT2g2THlPaXZQbWcyRQ?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HDRO co-authors cutting-edge research using AI and satellite imagery to estimate HDI at a highly granular local level - United Nations Development Programme</t>
+          <t>How Collaboration Can Enable Action on AI and Mental Health - Tech Policy Press</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 18:36:28 GMT</t>
+          <t>Tue, 03 Mar 2026 14:29:28 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPMEgzNjZqVjVmRzNyekhKWVUwOEU4YjI4UUtwVlkzNExld3hSN0VaNUUtb1hFcGQ2VTN2aGJwckVRbGcycm5hUW41dmNKeERYNnlwTldXb01kdk1OQWJ6eGtSdnoxYUZIWUlTb0NBeUZuYmJjSklON1RrX3phVGJwaVgyTzZTSlRzcWoyMTdGRUtHdlRTcnU5emdCUGEzZmktMTUzX0FmWlRaSlBLVzcwNHdrSVJYVHdf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPeGgtOUhMcHlwYkdrNkVpdmI5NVNLTGxFUl9UWjBuLXVKeFplbWNxR3VPWFFJX1FJbmpUbDJHR0RRbmJNdlJSQzlFMy05Q3pOTFFRVVJBRnpuLWowdmdmZFdoZmhkVnlSTjFOWHpwal80ekdrck9UamlGVDN6bUoxM3hUeGZZbGcwTVN3MXNjY004bnc?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AI Governance: Three Lessons from the Global Digital Compact - unfoundation.org</t>
+          <t>UAE Central Bank publishes responsible AI guidance for financial sector - Pinsent Masons</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 22:11:51 GMT</t>
+          <t>Tue, 03 Mar 2026 11:31:17 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPZVdwTXRHNG5XZmNpMEZfSVhYMDJaSnlSMmRFdkEtVWxCbHRnZ1FhX0lLZkZSS0UyRlZJb0VPZnN2SlRkZDFUTG1xZUZIZ08xVEJ3bURqS0RRRThGUEswOTBYT0V3b1lOelIweTVmM3F1enFKVkQxQ3M0VnU4MC1kSGJPTFdFNzN4OFhGTGxKRU1IT29YQnpBOUZzOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNTluMEJPNzE1ZkY1WEZRaE9pRjJoMU9zUmNNVWRTTC1qemswOFR5LWNNTmxsbVZVNFo2UHhXUmZSNjVBblR2UmNKa3lxS0Nnb0hNYkRYcG91bUtIS1k5clJhU18wVnJ5ZS0xTy1DaEVaSjk2UkpRbEpsY2Y1TmVMMWxWZ1lKWnowbFpIMjkyWmVFVDRuU1c4azJWSkNKdTNkRGc?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AI upheaval forces software industry to ask if this is an ‘adapt or die’ moment - Financial Times</t>
+          <t>Enhancing breast imaging with AI - healthcare-in-europe.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 05:01:05 GMT</t>
+          <t>Wed, 04 Mar 2026 05:30:11 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1INkRweExVcThnUGJxeWxBZXFKdkFLX2R3YVFPX2NRQUdpb0V0SGU5Rm5pMmJ0SUxPUHVEUWpwUlJPSkpQLXdCV00taDlTUlpPNG9URWMybXlJVFdsQnctSXVsTnJUalFHc3FzcE9iQlg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOc2hEM0U4cm5WUWFHcDhDY2prZDZ3bFZJb2k3SFd2TFdSbWFnWTQ4akx3b3VnMGgyU2Fqa1BySUdlNm5yd3JiUEVadjJpYU9GMzdvcWZ6WWF0WGpUMGJkZzVIRmFMUnJ5RGw4THBCNVRqdGVUME5zc19iQ3VCdlhCX2UweUw?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Travel platforms that survive won’t choose between AI and people. They’ll need both. - webintravel.com</t>
+          <t>How a band of engineers anticipated the cloud and remade the internet - Princeton University</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 13:26:18 GMT</t>
+          <t>Tue, 03 Mar 2026 22:33:01 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNLUZfQUJHN0ltOGFQeHlWVDRLcXhJcDBWb1JGT3ExS0JNXzBwSDZZV1hNSmMwTnMxQ1dBeURucVh1UThPYl9CY2puZnlzeHl6c1VRT1VLR0dfaVcxLURGMmFsOUpWMzNFd1NGcXR3VzBnc1ZWS2h1Qjk4ZndOT3Q1azZCOTY3OF9TNjR6MG9yNkVUakNtMFo5OC1feGVoandKZjFiTERia1RGRHotQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNbGE2SXVCT0x3SXlxYjNaSmtLS0VQTFJwd2JuVEtBZHVDa3FUc0lwVDZjbVpCSmhhdlI5aldYM0hmaV9VUmwwcjU3R0xpR1dCT1Jmc1J1bERXZlVUMF9jYnRDX05ZaUFlanJmX3RndFBTZXFLTmJxQkotZDlNUlV0MzU1cUxuUjIzeUZYN1JOX3NHSGhDd3p2dkdZWU9yVFE?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>I hacked ChatGPT and Google's AI - and it only took 20 minutes - BBC</t>
+          <t>The Future of local government technology: AI, robotics, and agile platforms - The MJ</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 10:00:00 GMT</t>
+          <t>Mon, 02 Mar 2026 09:08:19 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOV0dONVVvLXFTREpTMGVLdTJuN0ZiaHpZZDU4enFRd1M4TDQxQjcxLXFnY05CNkQ1MXRRQVRMalg2TTRJZUdUYU9ka1hfTWZqaUsybUFlMjJzTlEwY3l4bDRoRmZrYklXTldFSkFvUUNfZXl4ZDgzUjNqTk16UlIweGZueFREbnNoS3NaR0toYmdMNFl4NlN0ck5LQS1CNVVUVFRPVDFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQbU9BY3htNThpdnJ1SzBDVnp3Z2FNRXZhTFBLaWJ5QWRYSVB2aU5oWDZZQ0Z1OFl5OENKS2RnYzYxLWt0cmk2cUkzZHZVWV9lQlU4bFhZeC14Yk0xOE5zV2xSOHJuRHZXSC1ZRWJWeFVVcHVtMGRMd3RtTkw1dGRoVHJiaS1RXzNDbTZMc3I5OA?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US AI giant accuses Chinese rivals of mass data theft - The Guardian</t>
+          <t>AI slop: Can players and football clubs do anything about it? - BBC</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 00:31:00 GMT</t>
+          <t>Mon, 02 Mar 2026 07:48:48 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBjSTZTNVNoNVFnbl80ejNOdUJvQTdpNXlmWFBqM3NaTXRsWU4wbkRFYmRYSktIT002YWdUampiV18tUXBMR1BhMW5aWU5jN0RKWnV0cnp4enZ2bjg5aUNKTjlPLWs1ODBPeVh0bExuMjNXTlVEeEEtTTltdHA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE43ZlRmM21lM0YxTERaczdob1IwM0lZWUUzTWZyTmt1ZzRPcUcwZlhCZmFGZlQwYkZoeEVEMFlsT0U1d3RiRDBBQjZzeFRrYnpVSHhzN0NYV1VMM3hGY3cwSmM5bFVNQUU?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>How Generative AI and OpenTelemetry Transform Observability - Bank Information Security</t>
+          <t>We’re Still Early to AI — And Your Team Needs More Help Than You Think - SaaStr</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 13:28:31 GMT</t>
+          <t>Mon, 02 Mar 2026 17:43:14 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNZlVqTGI3TTRIc2Q5UlhRaHdmY3BTWnhleDdCX2U4MG5hZkRXOEFjZHB4cUZWd28xVFh2TUFKUkt4ZTVFdWRZRnBnYUQxZGpJeExrRTBWVnNQb1FvTDBoanJ5ZnZtRXV4ckFRbW5udmdHQnI5OFdMSVRzbUtpa09EekVRaTgtYlNVZjFGLWYzOEh4eGM3Z0wzcEc0aDlJLTFHSEJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPay1ubTBPajhKWkhpN3FkWldaWmF4NG40VkxrMTEtcHYzWWY5S3g2NzRfY0c2OW5tOUtPS3M4MjhaeVhSaHRfZnNBbUVhRW5wVVNnNk9MUlphcXpsbDVIaTRnM2JEUHQwSWQzc2JneGwtdC1WMkIyN3RfNjE4NnVkMlFDOUxIRmhnX002OThjNGxGV3FRVGc?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Document management: the missing link in AI adoption - Economist Impact</t>
+          <t>How architects use and will use AI in 2026 and beyond - Royal Institute of British Architects Journal</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 12:08:35 GMT</t>
+          <t>Mon, 02 Mar 2026 15:11:14 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOTVhWSlU0ek5USndoRnA4YWdVdUVQN0xPSFg2TWhJYVNvNDkteWw2TEpiMFdfa0h0Y3lMU1FBTHFRbG05NDdDTGNTV0w3YXp4a2pidFhJX2J3Nk14WUc5MGF2Vk5pLUpjUVJXdy1ya1A3SlhvRGdLb1NJX2NhRjRfalQtT3RoSmtkLUsxTk1pLWNHUkxsZTRz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQQVBIeTJGZ1VPeHRkOHJfWHVKcExoZ2hwZzhkTkU1Q1lUTE9TRFIyNi1PTDRtV21DSWwtTmdZWDlpRGhaZE84ZkdQbnltaGRmQ3lHbHk4Y2t3VmttUzJLT0FWM1lidDB4ckNUdFpiSjFrMTF3LTRacnktVzZaOTJJa25lLWRrMk15aWUzS01fMHE1RTg?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ISIS teaching recruits how to use AI ‘responsibly’ - politico.eu</t>
+          <t>RS Group expands portfolio with acquisition of BPX Group - allthingsbusiness.co.uk</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 12:02:00 GMT</t>
+          <t>Tue, 03 Mar 2026 11:29:05 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNZ0pqNzVBV0phcTZwS1JHVnB1MHN3ZFpBWTJaeU1JX0NZcVJvWHFWcjBFSGh6TWhiOHhES0hrcVp1S0x5Tm9CMXBSRHZDWkQtY2RFNG9WRUV4ZkdSZkNqUEtwXzhSM1U0YUxfd0Qxczh2Qm5hbGNRUXpZN1dNdEFfcWptLXZCVFNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPUEJXYzRoR3IzenkxZ3Qtck9ZaWtPbGdIWFZOXy1RUk9pcXFVbnp5Mzd1SkhrT2RwdkV5MGotZ1Jia0VfaHJUVUlQTGYtNTM0OFhUWXhKZDBUTVVDWVBjaXByQmRnODJwYlY1X1dnSURqaHJCMTN5blZEZHNNVnNpRXEtRFJQT3NmOENScEdLNzVaaDM2c084eUl2bUZVaHBuUUtUdFdJWTRfckk?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>How Teens Use and View AI - Pew Research Center</t>
+          <t>Women in IP Speaker Series: AI-Copyright Collision: Latest Developments &amp; Hot Topics - Jones Day</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:52:52 GMT</t>
+          <t>Tue, 03 Mar 2026 22:35:46 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1yRkUwZ2RkcENYZURtNmYyTW5XenJzczlSX2xaXzNiRldjV2JhamYwN3V1UXVCZHc2NWFTd3lCNFBPSmp4OWplQnlKWkdpYmtCU25QTHV0ZWozcnFXc0kzenBoMVBWUWNlV0JqWkpvcHRod2FJWGN4WW42RjdNNHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUkZZejZIdGJNcHVjR19DZXItMmxXay1xZ1pqREVkZV9rdldMY0YyTkJNdWhLWVYwc2dqS3FhTkd3aEVVc3Mxb1hVa1l0bk9uVFFTQWhWVF9ZRkcwNjBxczlMTERrTnU5Zm9IejJaZlRHXzlCU0hmMzFkNVhwYTNjWjc1U0FtWVoxQWtySkkwbmpHZ0FCZjd5bXRQQXdtNHJKclpmNWw2OTZUSFo1WkFWSDBKVHZNcFR4WGFLUTVVWmJucms?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3541,27 +3541,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Former council worker jailed for nearly £900,000 theft - LocalGov.co.uk</t>
+          <t>From algorithms to atoms: How artificial intelligence is accelerating the discovery of next-generation energy materials - EurekAlert!</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 13:20:03 GMT</t>
+          <t>Wed, 04 Mar 2026 03:15:36 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQWkxBN21jTUU0YU54SjRKWXdCZnphbGR0VDAyWDl2a3Z6SVNqamZ3aG5pYnZHQmRaOUVfWllRcEQxQU5yQkJuNDFDZ3FfYjZqTGFTdTc5RXB0UmhqcnZKZ0kyNE9xa3NSWHpacVZFOHhlYWJxTTd1QUZ5ZE9aQW9QUzZDcDc0T0RYa1JVd2N3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5zYVBaWDltYjFPUlRWWkZrOEtnRDVJUWpDUnM5dWZKeVVjRGUyREp4TV9IVW9UZGU0RTdYbnc0NGoxVDFOQ2hKcXRUNldkNy11aEZJcDA2YWFRb1c3?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3571,27 +3571,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Man jailed for 30 months after driving test fraud - BBC</t>
+          <t>How AI Damages Work Relationships—and Where It Can Actually Help - Harvard Business Review</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 16:57:22 GMT</t>
+          <t>Mon, 02 Mar 2026 13:12:15 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5yV041SVMwTGtxa3VpaFlaN2RJdWlfa3RYMjl4MjFTZFl6SFBUcTZkWmRoSU9lNmhsZkNBME9qM3RCNldodUFXNlNKbU55S0VGWE81QWJWZWFmUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQU0x1enNLWXdGdm00bnIyMTZ4aklTV2VtRy1icGQtVkNwamhPWEVYUUJlWUltWUFNTFhwY1BhZXFCS1A1ejFqOVRmUGZmblZ0VjlIRktSU21Tc2VaRnJ6OUNlWHpNUFFsRU9jbi1sbWMxNWhqWmRCMW9rb1c0QmZJeTZfYzZ4SG5xazRGS2daa3BpZw?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3601,27 +3601,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Two more convicted over mass UK car crash data theft - DecisionMarketing</t>
+          <t>AI reality in the UK and Europe moves from pilot to production – EXL - Insurance Times</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 13:19:00 GMT</t>
+          <t>Tue, 03 Mar 2026 15:15:47 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQRFcxX1pGcHVobG56SV9fNnVLTVhrTU4yZmhzTFBlajBEaXVJcGpOYVZxdmpLZzFieURpNWw2a3hrVXRlb3pRYkJOQkx2Y2twWk9LSkJjOTZWOS1TVlZvVDY5VGJFMnNEdjUzZ25qSTFvUFVYWHFkZ2pTVGtja3NJc3JrWkw1Vm40eWJGVnJ6SXFWV3ZOSU15Xw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPQXdGVnRRWVV5SWxrcWlfaURsNTFEa0k1eVdHbmVYdjZvVF85X2FKV2ppN2kxR3g1U2hVNHdvdUVTYWpaNVFhbk82aGpLenlGSWtEMHllb3hmdGxLOWlEYWFVYzl4R3VrR1Blanktdm9tcThxZnZENVBVSUNlUjJBOTQ5NkxSY0hwZDNnYjJ1ZmdKLUJyT0I0R3VwbmRvS1pFLVVnRWI0YjJQUUpjYXRyeUs4SXRORklWOGd0TlMzdTB6cjZySjBn?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3631,27 +3631,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Accountant sentenced for stealing £26,000 from food bank - Third Sector</t>
+          <t>Exploring Agentic AI and its Implementation into MS Research - NeurologyLive</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 08:20:13 GMT</t>
+          <t>Mon, 02 Mar 2026 18:33:51 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOUHY2VG9lbTZUR3M0aVEyZGt6dXlDb0xldlBZLXA0Z0MwRTFtV25XRk1xbmowTWVEbERZajkwZnNGTElZSTEwMTEyNW9yeWN6ZWhtTkxsWldlUjhnOWZSYjBmTXlOaEYzUmZZZ0UyeUd4Umh4SkRLNGdCTU9zV1Q1cWRScWVVZ3NZcFpqb1llTllpOHRId1RZQ0U2a1I4YzEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOG5UZS1DQXM3Q2ctZDEzQXZfNFZZWlk1MjhyY3kzNG90WkM3U3ZKTUFvUHJ2dzNlaTUxdEdfcnVGdjdzeXc3ZlkyWHdZOG93VF9BTTA4VVhESW5UX2pGSXJpSlRPNEc3SWZQcVVUSUhsek1oX2JjUHp3azg4WHZoOW1nT1NacTRLMGc?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3661,27 +3661,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bulgarian tech employee sentenced for Russia exports - Global Investigations Review</t>
+          <t>What 2 MIT experts are thinking about AI and work - MIT Sloan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 21:29:03 GMT</t>
+          <t>Mon, 02 Mar 2026 16:58:09 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOVW10QlBWQ0RfYXVIZ0NjZi1qbENpZTZyWUJkY3U2emd5dzFhbk50bV8wRmtXM2g2dm95bkNITUhUZjJvQ1JJU3lsNThxanl6azEyUnhGSHdSMDBTakh6OEREc01EMElxbTJJWncwdWpSbEl0SEh4OHlYR1NseVdNdjQwOTZKdDRCcURaVk1KSDdDejNYcWlVXzlQTEhTdG5MNjdVTzViVWo5ak1LRWpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbFowdnl4MTZsVkVfMTVUel9tQnpvekdLSWVtVjVJMGx6bTZxcHVISEhqeTQ1dXlPZWxPTDV1N3AwdFlKOFpnRDdhU1ZaVFhRNUczZVVsRFMxZGhzd0VnbkVKblZsenNhaUljUVp3TWFGNC1PY19yeGdIOWhBNllZVHdlcjV1cXBTVGNrSTk5WFNHbFFPQkt4eW83QQ?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3691,27 +3691,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ukrainian National Sentenced to 5 Years in North Korea IT Worker Fraud Case - The Hacker News</t>
+          <t>Leading the AI Revolution: 2026 Trends and Insights from Saudi Arabia &amp; UAE - Deloitte</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 09:52:00 GMT</t>
+          <t>Wed, 04 Mar 2026 04:59:04 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQN1JuYW5xeVRrQ1B0bURicUNhMjBYV3ozeWVJM3lzTUY1cS1oVW1oelRBMVdCU2NKeGpJRzk5NlU2bk1XcTN2bmhpMEd0a0pLQWlFZmhCZnlGVVVLTUVZYWlhclpBaVlLMUgzalo4OExKMm1SSlhxYjFBSXJvWXhlQzhZX1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOTE0yLWRGX2hrU1NVR3ViT01RdGJRc0VKenpiVlg0UnBFNjhxVlRnUFNQaUtKNVpqVi1lWEFRZlI4VzM5UDNGWGlTbEY1d1I5TzNqNGNjOVpaR3lCY3FiTWViZ3lYaklnLVBCNGk1Z2Y4VHhqT0JxRVNNOXdYLVFiTW1HajNpeUtJTUF1VWNGckVOM0dyNm91TzZfbmVHTXJTRVZXZUlB?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3721,27 +3721,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>St Helens woman created 'false invoices' to steal more than £120k from employer - St Helens Star</t>
+          <t>Samsung Advances Galaxy AI and Its Connected Ecosystem at MWC 2026 - PR Newswire UK</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 17:00:00 GMT</t>
+          <t>Tue, 03 Mar 2026 10:07:00 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNllPaWxzRFptblNLWVJOdTBKMFJsX2ZNZXpRZ21OaHZoM3k5dTVXZmg0TGRRN2k5c0JMX3hYem1PS0FlZVQ5NlozQ2RwZE55d3ZvaVd0RVFqV2lLMEcxWnFnVlgySnNYWDAzV0s3X2trTXR3YlZFc3lXMGV4VUt2N1hLYTV2ZGJPVmZmNWtrUGRJWEpqVWdWRTlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQQnM4MzlJSjdEVzVXLTFvdGFaMXZZVGM3VFVCVU91YUplUEo0ekhuUm1sMWh0a1hhZzJmbEI4bjNTZXJnYmNpTk5nelpBRXhVMzhNQXBfdk9fSFBYejByZ2RrVlV6aHBsbVpkSzZpMk4zMTNYYjNwUnUtM2J2SjdKbFc4d3ZkVW5vUGN2WmUwWFNYOGhxZUxHMGJXeTdlZXVOZmNNVXBCX0hRUklab0kwYVpJN293N3ZOZk8ycTBKcFRYQQ?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3751,27 +3751,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>'It nearly took the company down': Trusted employee took nearly £50,000 from landscape garden business - Hartlepool Mail</t>
+          <t>Mobile sector must speed up 5G and confront AI challenges, says GSMA Chief - Mobilenewscwp.co.uk</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sat, 21 Feb 2026 07:00:00 GMT</t>
+          <t>Mon, 02 Mar 2026 14:40:20 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQNjB5bENCVjU0QmRsTWQ3WWpiLXJXY2dsM2FidHlLbUZqVFZjdGc1dXBqNDNTUWhCMFNTTGItLXA1dDJMbklPTk5CRTJydTdDdHV0QUhhS1JuMFByOHN1WERHMlpxODYyb1hoNk01UEdaSG4yX0d0VUJ1LXZOZ052T0tLc19FMGRmSlNQcWFSbW5weTN0WXRtOTNZT0xUX2hzT3RMTEZ0eXU4aVZWNWNrSEE5Nzgta1A5dEhDYWhET0s5NzR6ZEpiekN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxORkc5SmhUZF9TQUlzWEM0cGtTTmJFNE1hakJqNWdWUHpxLWRtZ1JGQy1YZ1NVcDRPb3VneXFFN25BeFJ0NzJoQ2Q3QWJkc0VoZXpGdDNIdFBwR1YyaFhpbEtYZTlaeExISWZPRGk2aUpLdlNCN0dNdFN2ZU1QU3NOSnR1TGk1eHZLbFRZeFBXS2FRUHZZMWNOX1hiMGppcmpFejRpdVZtSHNFaEE5ZTVxUW0wLU1LUQ?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3781,27 +3781,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Greggs thief dubbed ‘Hamster’ by staff avoids jail after 38 raids in six weeks - The Sun</t>
+          <t>Telcos rebrand as cloud providers during MWC - verdict.co.uk</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 19:57:00 GMT</t>
+          <t>Tue, 03 Mar 2026 17:29:49 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxON1hYbmx6SzU5c3pmSy1jUGJXbVhGNWtYTld1ZllIcnU4c21xdnNPT3hLc3dvV1E0Rlk3czZqcm9KbHhQUWtvcWxyekY1cW91SjhFbUwwU2VscjFKNTM1SjJYUE02WmJIRlc5RDdyclN4amVpeWlpbWNBaUNTZjRRb1d2Tk5PbThuZDBKVk9Kbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPYkFMX1lnQ0RWdDNZdTI0MEw2Mm51MS1nYkpmOEtJN1o0SU50UWlUVlZrN1NTelRJcnVMMXFVS2J3Yy1kZDVaUFhvb0c3c3BWZzlud3B3Y2RaamItT2tZclRYTDJKMU1HZlRnMm1hd0ozZGx2UWtWS19GcDRSR0hGbTNUdUVTUjVqOWpKMkh0eHg?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3811,27 +3811,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Former Maryland correctional employee, business owner sentenced for fraud scheme - CBS News</t>
+          <t>Merck &amp; Co. picks Tempus' AI models for new oncology data deal - FirstWord Pharma</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 16:18:56 GMT</t>
+          <t>Tue, 03 Mar 2026 18:49:42 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNQS1mM2RaTEVDbk40UE1VN0RKNjR2bGU4VXpEYUhCN1RsRy1ialpLX09pdWVGZ0pQU1Y5TzcxOUdsVjhhY3hvaTNzNDlxUWh0SGNUT1p0cEJYNy1qZ0VScDRZM0ZyTjRDdHVZVm5TN3BRTzA4bVlkS1FqMUVPNUg3MFRnbGl2NVFuODFDYld3MGF2WHNmcXVyZ0pGaDIxREUwTERR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1HSEVRV3NvN3VQZlVQUFlJekRVZnkzNnlna2tlQUExMWVjUXQ3SnBQeXczRXJjNnF0bUdTMVVjMEVsZkVFckdpZEVZR1Z3VDEyUGI4?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Indian American Optum director Karan Gupta convicted in $1.2 million US ‘ghost employee scam’ - The Indian Express</t>
+          <t>Former Rockhill Women’s Care employee sentenced for fraud - FOX4KC.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 10:21:27 GMT</t>
+          <t>Tue, 03 Mar 2026 20:31:33 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQnJrTmlXMjFfRWlCVDBnNEVZaHFwMk4xTS1jeEpwbDhSU0hiMGctOFpzTlFjZzFFNXBJdmxDaWN5X0VvaXB2eTBCbTFUQmFvTnFaTUZPS0lBMkcySzZRdGpzOEVHSGRlQW5qcUJCalR6X21FLUlrM2V6SnFaS1Zpc3ZvN1RoQ2laaGxwaXhDVVlNUi10SHF0c3AySmpyT0ZkcndaY1BhVUlYUTZiUUZud0JLdzVxS0RxZ3dUb1R2UzRNdG1xWnlGQUo5X3ExNUl2Uk5j0gHaAUFVX3lxTE9zSVFndVRkSmxvOGZKNk04U1BJOGZzVDJkdWlPWGY1X3M1cElZVWpVX3ppSU82NFhvRGxWd0ZfZWUzMFhFYUVEVUhUVFBpZi1ocDU5X2RrOVJsVG5ZbEFMdE5kZHF5bGFvT1dfTU5XYWhmSU5oY1I1M29WUXAzX01VMWl2NnVISmVxTjhBTE82T2tyOGYzNHVGSkRkUDd3R1M5bE9QZHN0cGMydlkxNUxDRHVxdnVPZDBycjhfSWJoOExlc3VtWGdGNE4tNEZNYjFZN0hpeUl3bHpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNbV9MWTdDSEZsdEpOd3d4SXNNUU5GU2VrVlBWc01aS2x2YXVYSy05UDR6RDROV19ocm9rLVg0VldsallmRFQ3OUd4LXNaa0pULUk3WWN6M1F4Sm9OTjlmUDZDNFRsa1hPYjZEZXlIX09ZcjViU0ZiNXdicWlRZWoycUwwZ05uMFRi0gGOAUFVX3lxTE8xT1M0ODRpSDJLZkFoY05BZ01lR1hpLTRsUnBLc214TF9IaXM4OXVHVDMxOFJ0cTFEcEt5dl9wX2JWclNWbjRQOVBqbmxJbGkya1R6c3psaDI1X290RWNYaVVVRmtuZi1IMnRhQkVoeUowckVDYWZzTHNXaDBYLU41QlZreU9xX0ExWG5kOEE?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dolores Ingram murder: Man sentenced for brutal killing of 82-year-old mother in Bucks County - 6abc Philadelphia</t>
+          <t>Defense Contractor Employee Jailed for Selling 8 Zero-Days to Russian Broker - The Hacker News</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 03:27:03 GMT</t>
+          <t>Wed, 25 Feb 2026 08:49:00 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNQ05KWXQ1MGQ4TmdXMXlhclpjRGRqb09wVDlXQWdDVGRBbThXSWJSM29xdkNvQ2FocnhKYnFjWDd5UTNROFg1SkxBNXc1QXZ4VGxJQkxxQUd2VlVtMjJDUDRTMXdLeFBqZFkwYlI3b3RBc0ZId0N3SEZMUXVLbWFfTmZETkVIVk5rYTZLSFZqdF9PUngyNnU1NUhqZHRNOG1keHlUZDZWS0hMVU9NZWpPanJDSkvSAboBQVVfeXFMT2Z6eG1XTUEzT2k5TE1iVl9GbGotLUREc2VvSHA3YlVlaDR6S2hmMDFQemQxdFEtZlpKX0FkTFpyRDhhUmRXdHYwdE9HUG5ZcFU5aGJkYWNwMDJ1QmJoYzlxc1Vib2VpNXZLRUdNWmFHNVVCcmlBMldkYVhaNkZwZElpb3BMSGNLOFRjVkZnWjZJZlNsV0Q2Y1NnTnZPVjFPZXNod3BnWk9oQ3k1TEdlRktHZFYybmFMay1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNU2YtVWUzRkRELTRfMjFGbk9uT2U0dXJmUDBtV1FuN3BzWUhRSFJIX005Y3RaUkhCM1BPTmxjQkZ3QUd3S2g1LWlCV0N5TFRBUmVfdnZLU2wwb21aVjFaa3BDX21tdk90V0xCYzRXQm1teUhGenpjUl9vRmRRUHNCM0x0QQ?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Former Jefferson Parish corrections officer sentenced for $80,000 payroll fraud - NOLA.com</t>
+          <t>Ex-Home Depot worker from Covington gets prison in $4M gift card scam - FOX 5 Atlanta</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 21:30:00 GMT</t>
+          <t>Thu, 26 Feb 2026 18:24:37 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxORjk1WkJnN256dHhmZ0NEUjMway14T1cybVE3cGU2YW1iUFBLWkxZdHRSa2N3V1ZTdDJwb2VzMl9lYkYtYWF2SkMtZnNyN09GN05ZT19DbloxT19MbWE0QUswanA1anE0RE1qVDNrMmhSNEpBekJiekluZmZDWXNmTE1qTjVuMTJNZC00cTRkWFJjcVBiOEhpUUFPbVNJcVRNUURfN2NQX3AtXzVtZC1zUUs3QzbSAboBQVVfeXFMTmNJRzdUVlFHc3VaV3VVQzlGRjNUTmJ6c0R3MlA1QTZSNk9GbGk5OThVcWk0a083S2dSb2JPZzBkLXpXUjNpQldSZ0RVRm1VRTI1c1RaY0h1ZXdaeEJEN2Z2Z3I0WkVUQUtTbDd5WFg4VEtIcEpnNDNNMEY3aDhoNGhuSmtBTXJPcWxjRlo3THpFZDJfeUJHU2RJWGpEbG43VXQ3YWZUR2hXNWlhQ0x3M29zZmZZWGpRaUN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPRFB4aDlXTWdDMDZ3MVpKT0lNa1lDSWJPRWJZZXBNTmloWDktdkpFQnBEcHZJdWJHeWhZNXFmOXRSOVhQeGViS042SEV2QU5QRVJUei1lZTJKRk5XQkpsbC1QcTRLTDR1SzBxYXhBYWZXNWpDX2UtNHlpa0FkVXd3U2RuUVYtT1NNelBEN1VndkpFTEFvT2R3dEdmcHNrQmvSAaQBQVVfeXFMUFZVNlFOSEgxU254bGZHb3p0NnBVbUdIMmEwWldCczhMUGxNZEtid21HSnhxM0FyX21JMUFlUUFqazZicG9YQXUwS2U0VVJTbmdlckgtZVJiS1I1c0tqTTVQMVRWakxXWDB3M2JUYl9uclpnaEROSTgwb3AteU1kVEVYNlpfNWQteV9kOHI4ZlRiYVdyemJuMjJwX3FGYlprSmJwQWM?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Court jails bank employee for investment fraud in Kano - MSN</t>
+          <t>Former KC postal worker pleads guilty to depositing stolen checks in 2023 - Kansas City Star</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 01:43:39 GMT</t>
+          <t>Fri, 27 Feb 2026 22:34:44 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPdW95UHRhdmN2OXZuX052bG9YRTQtcW1vSndpU25qUHppSnQwY1lyRFptYjVKMWR6cXdLRUFPT1NKQnZSNHctb29BQWxWQmJLREtyS01jUnFRTEFnbU9aV09pX3J3eTd2bmhUbmJsdU8xLXhrRWEySUpuVDNkckZWWnhmbDFickhRVXVjYUdpOVlsSFZ1X2dpRWtTa0NGN185aHVKbmhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBHWG1ucWtpaTdzVUJlMHI2eXJaR1F5V0dtYkJuR3B3ejNSclRnbkRkRmRpNGZoaFMtdk1YLW5lVUxmbmZuU09xVHl5VW5hYlkzdkw2U05MaGY3eTV5cDE0V2JfLVJjTWdIVmNaM3hIOGFfaDjSAXNBVV95cUxObUlZRF9NN0N6RWhqdjA5cVR0cXJBdDFfOUF1ZzJSNHppM3RsZl9RQUgtX0pRZEdzMWZzeFdhSlp6bTFiM3NNN2p0cjI3Qm1raWdHN09kdjNUaEFjcGhDZ1RPMWRzcVEtX0dZcTBjNkxNWTkw?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Former Hawaii Public Safety employee pleads guilty to theft, misconduct - Hawaii News Now</t>
+          <t>Former employee of small Arizona town ordered to pay $194K in restitution - 12News</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 01:29:00 GMT</t>
+          <t>Thu, 26 Feb 2026 16:09:00 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQQ2NQd0l4WWlpUkxuX2tZVEdFSTdXNERyUjlkYXJGSE5OUXZWWVpUc292c1Z3elQtTENnRG1PTFRKaDk4VmZ3enZrX3VKeFQ3cG9uWTE3ZklvOHJjVFFsRlFWUm1BOGRRemJuQVl3cVlZVzFCMVZHbXRGaUJCNkZCZjhVXzh0ODJQN0pIYmEzZG1fZjRsd2hHNzNwZ0xnNXVJaHI5Rkt4SDBQN2tUdWfSAcIBQVVfeXFMT25TVm1ScDJVdVN3cWhmeGJGUE9fcjdGMDRKTDZDTXVFdzFWYmYwaVI1MjVYU2YyaWlpcnBWRFY4eEhGY2NMRTZsMGVsRzc3Q2V5LXZ0c29RaFdDTlVVWloxNnQxaWIwZkRZTERnVnFidGRzSEsyMXdzcFZJcm5GdU5WNno0N0ZoNGtpYlkyY3RJYnhVb29jOWZhd2hIdXE4OXhGeU1ic0hxOGJYR2JwWmotS29QOXUyZWl3LTFldHdXdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQakttbkxBT2JyNEhCRUZwRndkOEFUSkMtWFBuaXJXVFNLV29zYU9RV0xLMW9hTXRHQTlKbGlnZk9UQ01yQnctRzlBSmxEUmFCMXV6SDM2OWVJRTJxbFJqUXEtOTgtVUlaN2dIelRiOWpzS0hXaWdfZkxXTnFwYkJYXzBCVm9MZjg2WjI1bFlyNlJ6V2hlbGZ3YWpJX0dvQ0otRHFoQlA0OC1LMUtLMEJpM3B3MHRNX0pOTlgxaGR5TkFVb2sweDVuYXhXMWxhWmM3alE0cm8tb21namxZU2cxMGgwOE5mSnpjUXBYNA?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>How Charlotte Post Office worker who stole $8m in checks got a 6-month sentence - Charlotte Observer</t>
+          <t>Former employee of South Lake Tahoe construction company sentenced after embezzling more than $1.4M - South Tahoe Now</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 10:00:00 GMT</t>
+          <t>Fri, 27 Feb 2026 20:01:59 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE95LXFwWlJvV09DdGxZN0Y2cUxSY0tlZ3UtTTN5a3c2bEF2WEVnZXd1RE1ibjNHTXh4YVk2M01kUm5LOGk1WlFpSm9hdFhjbjhxNW1RNExiQTNreTJMdmgwSDM4SEtmdWEyMUd5XzFua0NRZnFmWnpyRHlneVfSAXxBVV95cUxNRDJ5czFtblZ6YllYZTd4VUJpaXNuaFpjZXdfVG9mZ24xdTlwZnQyQVRQT3dEMVFqSHBOSWpjMm15Y0QzUjk3OS1nTmN4YTZfdVZnNXVQZnZKeGJUSjNMYWFPLVRPOWZVdzQxUjhDSlZ1dGwza1VlSE5XVXVh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNX05mUGJPNUlQTDJTakJSMzFlWllaTjk2c0pSazlSS0tnLVFFUTJETGRFUVF4OFRMVkNfM2dpOVdqZGNXR0xEbk5LelNJVEdpNE1NeEFuMVZUOFFCeFJEUUd2dnhrY2Z0OEZoUnAtNUlTcVhCWThBODdRdzVnZnNWdUE0YWt4cERNTnBhaDR2Rkw1YWV2Q09QczE3V1l0MnlZeHU4WmRkeDhoYjBpa1EzTmlOT0V6cUV5Q3VmSHpuMHF2X0pLUmNGTVl5cUpfcjlW?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Woman accused of embezzling San Diego County grant money to fund lavish lifestyle - NBC 7 San Diego</t>
+          <t>Former Hadeed Motors employee gets five years for fraud - Antigua Observer Newspaper</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 18:07:21 GMT</t>
+          <t>Tue, 03 Mar 2026 01:58:29 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNN0w3cjNreEQ1dkxjcVV5Y0pyVHQ5RU5ncUhfU192eHpGMlpTU3FYU1dYU0prNk1UbGhSTnlvNUs5MExvUmQ0NTRQZllDQVJDdzA4MDNPRlJZZFlRMHpnUmM1dTV0OW9OMDdjb2VLUFV3RWFQN01fd0pPTlJXdDRjSTJESk0zMWp2QlkyMlBPeTVnRlhoZXM0VHhtV1VtWXRqaHVMTEpHaTV4RzQtYXNhRGNHQk5WOGRtcHdrM3JtZ1hUX18tNlp0RdIB0AFBVV95cUxNNmtEeWNGT0VSWThFSkRabFZUNXVVWjAyWUM4N1hwU0M0eENMeVBnc3R6VExIQ2VvYmdvb2RiWVJ1dXhFUGU4SnRFd0pwNWhNeHh1UURvQWRobjBfcGFGTENUSnpEZEFnbEpHVzRuMkpCMGEzT0d4YWQ1TGJaeHVtVWFiZmVoOVUta2pJcWMtOWdEdDNFbG9WczJYd1Bsalh6NmF6cjM1RFYzeUJJbndNTnhhR1hXdktOSmJ3dDdoXzg3TktSUF9JaHJ0QUFqYmhG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNOURpUm12MFVSTlJGVEExNXNuOXRqMUhVWmprYkxTZkJZTlRwWVBJWnF4UUVJZWVHWXdPaE9PYTlPNE10bkJ4ck9WQ292VjRFZk9HOTlUQnJudDRsSXhvNGdIUG9XTktITjlHTVlSaFpkckZKNTd4Uy1kWXNucW9RUVJVanBOTVE0WU9nTA?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sunset Mesa employee reiterates request for second re-sentencing - The Grand Junction Daily Sentinel</t>
+          <t>Former head of security accused of stealing comic books from FSU’s Strozier Library sentenced to prison - WCTV</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 14:16:01 GMT</t>
+          <t>Thu, 26 Feb 2026 20:35:00 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNTHlWNVpERE13dU5EVktjT3NnYi1aRHdSZHUwZ0FHczBFNThZUzBXNkFjai1MNnFoeUJ4ZkZDYVRPX1NqNHROYk9vRW9EOTN0UzBEMHRmWkFTMUxhYXl4MjlMX19kYXVGMmZzcnVqMV8teVFhTXhLQ3pucWx0SzQ2WWtEWHBKa3NtV0lhblk1bmJ4M2JCS0ZHOThPejhFaTFjamUxNEwwaTVGM1dVUl84eHNXanl4RmJjQUkzSVJFS0k1U2JwXy1LQTJDa0oyajRlXzZQTk40V2tqcEhKMUhMT2RSeUxxUFgwaTRjRmhMbTI5dFpOWGfSAfsBQVVfeXFMTmJRakdVX2RkNjV2R0IxTTduMVpTdHEyc0lJTThucE1fYkJtNlEtSGdvQnl0TFRNV2otUFlHaElzRzFOaTNYNFN6YTlJSGxGUDlRZTlELWxlTFdCTnRvVHNGOWpLLUhVYk1oLXFQclJ4dWg3ekFEQXJ2MjVoMkFRbXU4d1ZDc3F5c2dOY3B0TkYzYUUwWGhsN3RaaVFleEl0RVZXaDNoNVFETk1QNGd1dkhwblNhM1lxRE9sMjJOb1VDb041Y2gwZ2hBYnJ4M3VIU1lTdGRmNVUtV1YwbExrUzcycFozWWJDVG94RHE1ZG44TWhwT0E3bDVYNzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQbm82R2NUcW03Qk04Yzd2R19FcnJrSFFYZkxmd2V0RGRVbmxibWpUdVRJUnZJQUtKUl8tcFlXNjRkSmZtRlJLa3ZYa3NLRmNFd3N3bGdUalpfUzdSdlN6Z3NGMTlySHUtRk5mdldHUXFBMUJkeEJvVENpVFlmby10WFlTcjd4MlN6NFMxckUwd2IxUjR5dE5XUHlCUHlrd2VLTnpWYWwyaFFPOURETDN1RTdqSFdhN1JVWHdaZw?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Former USPS worker pleads guilty to stealing thousands in charity fee mail fraud - KIRO 7 News Seattle</t>
+          <t>Woman sentenced for defrauding Town of Parker - AZ Family</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Sat, 21 Feb 2026 03:59:00 GMT</t>
+          <t>Thu, 26 Feb 2026 19:22:00 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOUUcyS0xCSEFhRVdZSEsycGt4X2s4ZjVUSEZUV3B3cEtWRDFkQU16d2lVOEZySFkxRFI4aU1FMU1kM0wyR3lCRGNUb1lhbnhOT1poTFVHXzl1aG9SNFdOdVRBTGlSb0tRQWlMRV9oelJkOUcxZzZJazBKa2xPRmM5a3Ewc01lUkNkcXhxYks0RDhEMGZZTUFVRk5rclc2TEVQZkhnVTNWNHowbUItNUtDUkZ0UkFGcGVfRWE5Ym1CUjVIQzRPdXRUVjdqZDJlS1Yy0gHkAUFVX3lxTE1DZ3VXYUJ2ZkpKQXMxNTRaWTVJdXB0dnphZ1NzajlLMWVWaDYxWW9Db1ZvdnBoQkl3ek84M2FpUldOSTJwbzN5a0tScXFrZDUwMXdxYUM1MlNIU1ZsUXV5ek9yVTROaVpleGs3b2cxWXh1V0xUM2dSVXMwSlo0aC1tbWl6VWtQOUVFWnk4Y016R2p0MFRtS2ZCdldzR3NzT1BndHM1bW1XYnYxem1zT1c2c2t6cGdNbnJucFNyTkZ3LVlaWDl2ZjBMTTlqN3poeHJZdDVQVHA3bkN6OUR2ZXZvVlpLRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQV20tZ3JXYWhOOXdfTi1ROHpHUTdzWUt5UUV2STJKYnhkb21XaURobGVYZjlOUUUwMzhodTFNaW8tNjZvVmExbFk5N2U1M1FYVldUY2JKM29WSXRFaTdzRW1ISmwtVXRUcmM4OUQ3RHc2cXV6MHFONS03eE9URGtrSlI2VGJ5OUVz?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4121,17 +4121,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Plain Township veteran sentenced for stealing from Cleveland VA - Canton Repository</t>
+          <t>Former Arizona AG official takes plea deal in diamond bracelet theft scheme - AZ Family</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Sat, 21 Feb 2026 15:07:00 GMT</t>
+          <t>Wed, 04 Mar 2026 01:02:00 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRFJkN2xIYUdRTk1Zd1FIdVJCb3J5WnRlaTZWcmFVaFBPVE9tR3VVcGF3RW9BbC1kUHFmenp0UEhtTWxNbDZURjlvWTVSRHZabXJlRWJiU0tMNjdsWUNscUotZWdXencyc0NhRzdMQ05LVFJGZlRNMnJ1M203M0c1U1dwaDVOMWtsN25wcWEzS0h6YTRwLXZSc1ZQMVg4aFBFOWhnQ0U4eW9rOTJDRkg4M20zZ2hPNGNWbGNJZld3Ujh6V0owbWpQLXVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNbk9EMmhtTWhUeFJ6MnM4aWVkTElDN1lFQlZiOUNiM1hSRXNTeFNQdEtXU05Cb21BRFFmbWhUQlRJTTBacHhtQl93NmpleGNTUkdxSjZrVl9sLU9CcEdJYXdJcFlhY3JpNURDRk5LU0xvV0E0X0xqWkR4ZkRzVWR3dG9CaWhWeHlqMkZGUGYyNTFIQjlXSW56Y1kxSVVIMGxRaC1IOXl3aHUtVVF6ZFE?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ex-federal employee learns punishment for stealing nearly $200K from VA in Ohio - 95.3 and 101.1 FM The Eagle</t>
+          <t>eThekwini contractor worker found guilty of cable theft amid crackdown on infrastructure crime - IOL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 21:10:15 GMT</t>
+          <t>Thu, 26 Feb 2026 23:45:52 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUzNRaEhsUGcxdy1BVGNYSmg2UTIyMlQxelZVSGZCNlJEVkYyTktuamhNeTFfZndSd1Fzd05IOVZIMUpzTnIwTHlkdWxMcU8tY1lkZGVQaWt3TmlSU3dqaVlSR3ZxODd5VkE4Y2lzNGZBa1FmaWFtemhyMzVTZUFtRFZQSE1DTlluSlpSeGgzT2RCQjBFMUlmZzVnRWdDRFVDODRDbFNUU3liWmljM1BLeERwSnZkM0wwaHhRY0JuUGlieFpGRWVqR0h6R1p6Z9IB4gFBVV95cUxPNGoycWJVTkJkdWx6b1ZqNEpFdVE5WWRHdHVoaHo2OVJRSHJQTlZkS1gtUWJyaTljT0owQkVPalNkUC00d2tRV2NtcHJIRzZQeFhUQnlDYWJnR0NEeEVRTnZrTDBCc3BtQy1KSm12OGhDbjJXSWQ5aVpxbXd2eFRUNWlwWWZsMDdMMkJJRExFZlk3MXZ0N0R5Z2NVWTJmR0tLbkRNUUVVcVo5TXlCa25VN1MyZTBWU3NOcUFJQkRSeVBHRXZVbFdMN0cyMlBaTzR3eks5RTMxSks0b3hnVFJKTXln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOZ0pENHZmLTJOWlNPSTdieXdUcFQ3TWNfLTk2R2pSdnNCYk9ySTQ2V3p3bG9VM3dFLUREVHVkeG1HSXhJdVpWT2Z4Qkd0UWVKYnNlekl0SDNMYzFZVnBIQkdMUF85aUZwOUVYa0NRczgtdlFycmJweG55T0hzSThYSGw4dWEzZ3JVTF9xdjNIVzRQU1JSSW5SZ3BwWDdHTnhCaWtIMDBmNW00SVRnUFAyNi1ZMC1YcDFIUU5sdTVORlI3NDQ2aVpaVXg2T1lMYThrVGlZ?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -4171,27 +4171,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LG Energy Solution Ex-Employee Sentenced for Trade Secret Leak - 조선일보</t>
+          <t>A smarter approach to tackling fraud: Lessons for government from a review of the MoD - Civil Service World</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sun, 22 Feb 2026 03:37:11 GMT</t>
+          <t>Tue, 03 Mar 2026 14:27:48 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOOEFtZVNsM3hPOEhzQk1NTjVRYzE1NGRQSWlyX0RwaFZJcjdTZndQdkhvbkprSGFfNFNQSmYydmpLaDdwcmUtNFhGamFXdDlaMy1kWnlHSVBCT2RvUzk0OEozUFhoSjdQaDNwQ3NPZjN3V2QwZzZlbExHZE1XQWNDQTFkNm9GQXpf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOR25zZmFDWUZma29yZFlEdDh3SnpSS2FEclpCQ3N6UHhuc3g3bzFybzlNdGZ4Rjl2RFZVMlVyeWJBdE1GQVFyd3J4dEpOQjE2ZGFRN0tVbWN5Zm9QOXpKLXlaU0g5RFROSW0yX00zWTFYSEt1U3RnTlUzVDZueWpwdFVGYkdtLWpxY0lza0Y5T19HaTJyT3pIR08ycWMtSGJMV0dia3V6UHY1N0M3Z2JVUnNGTG11SndudGJiUGZzYXNVVXBGdTFPYjg0UHJSbG0xQ1YyRQ?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4201,27 +4201,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Texas man sentenced for part in stolen car scheme discovered after Leon County traffic stop - WCTV</t>
+          <t>Portsmouth woman pleads guilty to £280,000 holiday and events fraud - Portsmouth City Council</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 19:08:00 GMT</t>
+          <t>Fri, 27 Feb 2026 14:13:34 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNUllzSEM3MmxJVThpZjBjSEVpSk1LWUFLZ25wMkhDa2lxVjJ3cFlhM2ZGZVBVUGJWcVNfanE0bjVJMEtKVTFtUFhUMUZ6RXpLYUlwSEJ2am9hYjEtZjdFRjZHWjZVNTNWV2w0RXpJUEkxSlFHVEpWZVR4dEVrUzVJZ0JmOHJFbnR0ckJRbDV1d3c2UHBReVdSLXZQbUFlRTVJY295WHZUbVdROHY0d0oxRE1wRmFQYTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNdU85czFsS0FqcHJsRm9DSTQxTU5CdWxRT2ZsTV92MGVkR3V0YWNjaS13SVQzME8xOVE4b1ZhZVRpUW9PMWV5dUFHejFsM3AzNE1VTE1aOUZzMXlLZFNKZUFudUwzRFRiNFJXRmNHY19sYTNybmFmOENnSnY3eUNFWWk1cmgyVEx5WTUwM0ladjJWdW5YVFdmZHdUWmM?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -4231,27 +4231,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Attorney General Raoul Obtains Restitution From State Employee Who Pleaded Guilty To PPP Loan Fraud - RiverBender.com</t>
+          <t>Customs and VAT fraud are reshaping the criminal ecosystem in the EU, with €45 billion in estimated damage uncovered by EPPO - European Public Prosecutor's Office (EPPO)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 17:52:00 GMT</t>
+          <t>Mon, 02 Mar 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNR1VtZ1dnZWt5d2FSUmIydm44TTNpM0U3cUhMMDMxVmRWdUNMRGRvSVVfUElScmEyWWozWlNkdW9kSVd6b0lxem43TUduVzhGYksyS2gtOUtfV3QxVmxuSklZZVYtT3gtcUhSQmJZaHVtaWpBX2M4MzdyQkhVQ2FybjRiNnBTUWRPZlZyY2NScXpxdUNBOHRmTENvUGpRU2I4WXY5MWVVY1hnYjhZa28yS2VLV0RpenE0NGtGSFp3Sm5WQnNrZ3VqVlJGOGFsUVd2TXJCMXQ0N0JlQjRzN292aDJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQX2JlLXF2dFdsVzV1WnYwRGlOQzNaUkl6ZS1TUUJsUDU3bFJTRWNzNG1OMWlYQTdMOWxBeFIyZjRMUlVxUEVDWEwwSnYzNWFKT0FYQ2xYcXJCTExWU2dJcTFmTVZVYnF6LThMUUo2Z1ZFUVJIRE9IekdOdl9FUWZfWTlDa3F1TGNqN1ItcUtLWDlfWWR4UXV4VGowbjZ2ZXpuRXB4MWVKQmF0S003T1pGLVZsek9WU1Jzd01nN1RqdlNmWHN4ejNz?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4261,27 +4261,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KeyBank elder fraud victims recover $2M in sweeping scam - Cleveland.com</t>
+          <t>Careers Breakfast: Law, Financial Fraud and Cryptocurrency - The King's School Chester</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 16:48:00 GMT</t>
+          <t>Fri, 27 Feb 2026 16:35:11 GMT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNamxYYy1qR0Jsc1JSODdWNUc0YkZremM1TnVwUHlIUGVaMG5BaXR6R2c5YkJCOGlXa2tlOUdPWUg2dGxRWE03T3ZDY1VDNVhpZDVOMURYVFM4bGRrek1SY3Fnd0IxMHl3ZXUzcUZMYmdPbWpFdXJmTE1pNnhURlVtdHlkZ19QYm1xeU9VT0pveVR4SHpLMG5KbFk4d21zTk120gG0AUFVX3lxTE9EX2R0N3dLUG1vanhiRGlUNkJxNFZaUTVMTldKZWV4UHRFUGpXQ0hZbTJQRkRWWlJJck45dDUxS1VKRUJTNndPZUNsbHBnQ2xlT3FZaVV3LXRrWElDYjZTamRpYmF4YTRqel9UaEU4OVdZcmczd0tua1VEY2lETFEwdkZhTXJqNjNGYUo0NVZIRHB0LV9xTWppdjZDOU5iSUV4ZTBtY040WF8xQ1NSakxyaXJ2Vg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUHNtWmJ2M3lEd0tNUjZpbWdzWExkSGo0eGR1WHNja241UVdMVTgxQkp6cE5FTmFveWNGYWliOGNLMnM2aDVsVy11cnFIdV9xQWlvU3RJd1NTdm1GT2h4ZFdrRHVXU3pYTFFWRVV4a3ZHZlprZzdDb0l5cXphcUhCZmNPOUYwTzA3X2JtZFdBb0pHdlk?oc=5</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -4291,27 +4291,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Notary sentenced to 57 months in prison for real estate fraud scheme - WBBJ TV</t>
+          <t>AccessPay taps PayPoint to enhance payment fraud controls - IBS Intelligence</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 16:53:26 GMT</t>
+          <t>Wed, 04 Mar 2026 06:05:56 GMT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSDJ2MFZtYmtjdGgyNzd4N25IR2NuMlh0bTJ4cG1KUFQ5NkFUeXN2SEdwX1BXRlpySWp4Wm80NnVMQnRqWmJUa2FUS3VqMk42NFY3WmhpdkpoRkNPakVKcVdmb2g1bmVIX3plbDdOTXh0UXlWeXVqNzFIblV6WV9EQkoxVU5qRFc3X1ZaNzBrdURUei00Z1NKR3BRM2kwRjRmbURtV1Rn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQeVM3dXk1QmFPMXdDeGJKN3Q2S09NUlQtUk5Gcy1KVF95Ni1kYV82cDVLRlVJYml2WW12MnpNSDdHSk1fdGswMXhWTUU1Vk0xdTg4b014NVZUYVdMdkZVZ0paVTJyRGFhWUoxdDZnanViX1lpa3RmX3ZxejlGQjBTV1Q2Q2ZSRzNuVW9EakNpRmJBLS16R2tybnV0RHM?oc=5</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4321,27 +4321,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Davis-Monthan airman indicted in plot to defraud the military of millions in medical equipment - Task &amp; Purpose</t>
+          <t>DataVisor Report Reveals "AI Readiness Gap" Between Rising AI-Driven Fraud and Financial Institutions' Defense Capabilities - Business Wire</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Sun, 22 Feb 2026 17:39:08 GMT</t>
+          <t>Tue, 03 Mar 2026 19:39:00 GMT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1sVmxKTEJ6RHJfRnhScjVtcXU2anpfb210NE5uMGprYzBBdGJINUp4T25LVGNtRFBSTFlWWDhxM3liR1ZMeXh5LXQxRFpBTnc1eEhTdVE3YWpNeDk3cjFjVm5Xam1rc2tWTllvaGtnRExtWWtPMThhblF0MHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNZENlbVp2TzhKeExabFRDMmE3ZXBIeExKc284MVFYWmVyeHFrTFBHMlZKRGRLVllaVm13NmlKcWNjRm9GT3dZWWpFbGVTbXNhTmVWd09pVnhFbkk1UTRfSlFyWVhnSlF6TDhEbElwOW14dDNnVXNvZ1I4ZmFBdnQ3VWY3OVl0b1NCWVRUOWRfSldrVjZEUklRclJldi0xVzRINmlRVm5GTm0tRWhTTzNHb2libC1BT2d5Rk50QmZYaFBzU1YzMjZ1eFYxd2gwZkVEUzQwUFNQZXpxRURPd3FINFlMYW9zcTZtTHB2c0luRjk0dk1JSFRzV19YWmZXS1F3OWlnX0JDSlo?oc=5</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4351,27 +4351,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Former Commanders Sentenced for Martial Law Insurrection - 조선일보</t>
+          <t>FRAUD AND MANIPULATION—S.D.N.Y.: Investors again fail to nail token developers, but on state law claims this time - VitalLaw.com</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 23:06:43 GMT</t>
+          <t>Wed, 04 Mar 2026 01:15:03 GMT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQWkd0QncwbHloZlRxa0hHRllVYVF4TnN3bTgyUDVyRG4xU2FtWnVEMnZ0NGFFUmtZYUhYRGpyOUZOdDRIVU5COTdqOWtmS2RNS3FWUW9yeTVpajJVM2pPdmhmb2Jzdnp3Uy03VVJBZ3BBSDNoSVFGRGdEb3ZuUDZvcXhJR2N5Vm8w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQeHlPOXZFLWRqVjJpSnRBZHdWdWJ2Y3ZxUl9fNk16NUx1NjZCWXFfeUEwb2k5Z3UtVF9nWUhLLWhLUXljM0E0dWVYbDZXbW5oZjNzMS1pdm51bVlrbzJDMl9yWWFldVlwdklRYVZQT2xfRnAwbUN4UFdNYVZPbUlCM0pFX2EyNTRtUGVEREd6WUx5S3oyMVhEV0RPRGlMSktFd2tYeFRlTUl6VXJjNkx6TmlTU2lSU1VndUdpbXpfVXBGVURTcC1wQnRXQ081WWk5aFhDNVlvcnFtVkVBZDJkc3BlVFdMZmZRYnhObWprZnBvdUlnYW03RC05ZVoxUGxkMHRxZ0RJSGhZZw?oc=5</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4381,27 +4381,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Man sentenced to 16 months in prison for threatening downtown Lawrence restaurant worker - Lawrence Journal-World</t>
+          <t>Saudi introduces tougher controls to prevent food fortification fraud - FoodNavigator-Asia.com</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 18:04:00 GMT</t>
+          <t>Wed, 04 Mar 2026 02:32:21 GMT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQcV9qbGlkTno3UTd2NkRkNlVNNm9LeGtqUWxiUEtyZG1YUlF4YUgyVkF1Y2VwRmZRTnJZTl9mc28xODVzbVplNVpQMlBsSGwyUVQ3UWdTc05YV0NMZ1FXeWZ1SlM4bGctY3IwSkotU1ktRHFQaHp6SFNGbkhnWV9vSm83MGNMcjMzSHFkUnJOSjBUNjI0dDVhdDVZVEo5SHhvaUpoMlU0SnM4Z0dTeE8xbklFM3R5QWJCMVdoVVdiVHVEUDE3RGoyMmlwMWJYQUZrOE1WRjZIbmlRSW1rVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPUFFDWnR5YlJjaGJwd1JpYmNlS1dTbEo4YnVONzNWRVhMeHFhVWktOHFQV2xlbTZ2NjNSMU1oREZOZXJ2Nkh5UzJpLUR4M3FWLUVPemh0N1VTel90RElfRldMR2lSRGppa0plZE4yVmRRZ0ZjdTM5YmQ5cXM1b1N3ZC1JY0xYV2tCNWRoZ3JpU3JEdFJiWlFCdGNaSm5fN1RYUl91Wm00RVVzYms1aHVkV1VRa2hMSldlbDlESXlPU3NjZw?oc=5</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -4411,27 +4411,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Capital Region tow company owner, used car dealer sentenced in theft scheme - Times Union</t>
+          <t>Cops provide scam prevention advice to residents at Eaglesham care home - Barrhead News</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 22:56:47 GMT</t>
+          <t>Tue, 03 Mar 2026 15:43:52 GMT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPQWpLYmxYemh5VkhPc3pvRWNqbjN1VVVBbEl4cnBmbm1yaDhmYl91WWIyYWZDbjR4WXJjNjUxTG9FQl8zeEt5OE5nZzJqbWJOWGZfVkxMQ1RKWEVkUjlWTUNlZi00Z3hPTGU4SjdIdHlyVlJnLTBsbWI5ampGM1o5YmhZODlZdzY3Z1U4OGtpOVBWRjJRRUVhck0zbUJ6TGZ1LXJuaVZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPWVZsZ3pLNU03cGRiUDQ5NkJ2LTNTam9JUVpNQlNHQ3RicS1ETnI4clNmYV9xR0JaaDdEOXhDMUk3a3BFY0ViM3FxWjlWblgtbGRqeFVNQklrZlJmNDFiRG8yc2hmU1ZNbU1DOHljT1RCOEN2ckxiSk9hZlAtUWl2bDRFaEUyeDB5WG90MWw0cnY3RmozRklSU3Y2RFVGQjM4?oc=5</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4441,27 +4441,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bookkeeper Sentenced for Embezzling More Than $550,000 From Employer - edhat</t>
+          <t>OAuth redirection abuse enables phishing and malware delivery - Microsoft</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 21:51:57 GMT</t>
+          <t>Mon, 02 Mar 2026 19:29:53 GMT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPTDJuSW9mOFhPNmExZDVHLVZDOGduR1NYNVJEeW1fSnA4SXN2TWtVUzI4aFFwaVAwOTFTdmdUZ2tSVEljUC1hdlRDbTZ4WDlILXVjWWo5MGFUVzVMTGtOVWdlNXE1Zk8xMUd2dXFnZGZfQkw1RFlWX0ZlaEpERE9LaE42SXFTVDgyUDlkeGRIalg3Nnh6U044NzVXZUFndVNmLVFCOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOdkllUUR4WDdMc1V1RHRodnJKRFRaZW5mREE5cnZoT1dndHA2RUE3Szd2cGJRcjJkb3BFMkJDenplSE1McUpwVlhTNUJaX05kT0VXTnM1WHl6d2V3bzJBN2R3VERlRHB0dHJ5TVNFZXhIWFc2U1FxN0RwNGVlUlBrRnMtd0ZnNHFDSnk2Y3FCQUg5Nms1RDZZSTBoSVpLT2tZVnpTajJyeG5OYk9wSnZPRlh5UHFnUQ?oc=5</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4471,27 +4471,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Man sentenced to 8 years for elderly fraud scheme - WDTN.com</t>
+          <t>Taiwan indicts 62 over suspected scam centre operator Prince Group - Reuters</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 11:00:07 GMT</t>
+          <t>Wed, 04 Mar 2026 03:26:00 GMT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOLThyVnh4VXpmdHRMaUNvWENwZ2MtaDh6ZHU3azRnODRDT0ZDMV8xUmVoc1FRX1l6Nm81WkM1MEVSdGc4RjdNZDN1NnQyMFNTMDVJaUo1bFc5emt2VjFSenNTNTBHS2pxY1hZUWZVeDBrZWNadll2S1VpV3k1ZDVRLWJmSEN1aFnSAYcBQVVfeXFMTi04clZ4eFV6ZnR0TGlDb1hDcGdjLWg4emR1N2s0Zzg0Q09GQzFfMVJlaHNRUV9ZejZvNVpDNTBFUnRnOEY3TWQzdTZ0MjBTUzA1SWlKNWxXOXprdlYxUnpzUzUwR0tqcWNYWVFmVXgwa2VjWnZZdktVaVd5NWQ1US1iZkhDdWhZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQnNLT1l0bU15UHlKaTlhdExxUklFWTVNWVZPOC11MnhxWDR2cEpITU92QW9tMGl0d2Nnc2U4X3VhQVlicEhDSkpxQkl5Mm5DUVZFUVR6TTJsUUEyTzduNTRnTjNBUXJQdGRFQ2c3dGdEM283YlhHNjc4VHY3bXl3aFdKTHF5cWZWOWd2b3BRZzc5RTFIdnZpRmtJN3Fud2ZWUXJ3UG1laTdpS2l5b3hnMkFKdk8?oc=5</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4501,27 +4501,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jacksonville woman sentenced to 18 months, ordered to pay $1.8M in tax fraud case - 104.5 WOKV</t>
+          <t>Quarter of UK fraud trials likely to be tried without jury, justice minister says - MLex</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 02:13:00 GMT</t>
+          <t>Tue, 03 Mar 2026 17:52:00 GMT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPT2xFQlFLY0M4SURLSGh6Qnpudl9nTkZCMUVmcGJLQ3BOekJVYjVHTmlSQzFUQ1ZkRFBCTHQzNGVkQjZ5dS1jbkZLa2JYaWhKMFR1UzVUYkdKeW1rUWI5NjhTNjM4a2llQ0dZUkxLVER3WUJIWkhBYU5OOGV0Q3d4TnNlTDJOUDJwbHJ6bUh5emJ6WXNwOWJpVnRTNVRxMDQ0WXFaSHpnMlFwRS1LRWFVV01qYnl1ZWdORnZ1bjRYZll0clRDR19aeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPVDlmbDZhb1dzQzVCYmN6S1hKbUJoVFh3cWNaSFI5T1Frd19Qa3FYOTZHRTBMeEIxZFpLUm1CVHp0MTRDZGpNczVsa2lPZzVlQWcxMG1hUWFndFZwa2JtMUY5UF9wVEkzV2N5cWdkTF9oR0RDOVUyX1o4dnJqdDZVTW1tbm03cHB2MG9sTl9lYkg4TWNOVm5BeUZ1ak82TE1VOWhQUnM3ekdSTTBPTVNKT1Rxak40eVBJX2Fabmd6d3HSAVpBVV95cUxQNU1oT0p2Z01Fb015MEtaVkI4MS1UOWJSUTBPUy1mcEFkOHFnVkhkV0VqbmF0UHFwclJlZ2hBWmhSX2hLTnZVN01NUmR0eThEeTcyekVYeFhybkE?oc=5</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -4531,27 +4531,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Former NFL player convicted in nearly $200M Medicare fraud scheme - InsuranceNewsNet</t>
+          <t>AI is baseline in fraud and AML, but complexity drives higher costs - CRN Asia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 14:02:49 GMT</t>
+          <t>Tue, 03 Mar 2026 18:51:43 GMT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZGpxbVNyMHBHcTZ1eHRxRmhjVVlRM2FrN1kzb1VmMExUa1JXVmJQclJoVXBYV2JROUN6d2RlS1NXcm5ySkYxYTJ4M2hhTUtYOFVwVmN3ZzdfeW5ySmZSMlAySGR4M2pCV2RzQXhIMURfTTFGaHdzRGxwSVAxaFRlck1hSEx5a2xKVG5FR1dWVHQ3bkNwRHg3OUlBVERoTGRWay1JMDA2bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQnI4LTFHdXNXbXlmV3FtUHVIcDJlOV9WS2x6T0ZUQU51c1liZHh1Y3p2anlMZVRyUzR4eHJ2VnNXaDRacS1hd1VGWTBHRUJpMENIMmpZalR1LU8taGdjMkpXd2l1U09nNGxnNUNYR3pibllaalNRRDZtb0tma3gzUGtIUm84Zw?oc=5</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -4561,27 +4561,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Local woman found with stolen truck sentenced - The Keene Sentinel</t>
+          <t>MoneyLion Now Offers Members Scam and Identity Protection Powered by LifeLock – Company Announcement - Financial Times</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 19:20:00 GMT</t>
+          <t>Mon, 02 Mar 2026 14:00:00 GMT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOQUc1dHNQbUUzM2VTY3N3dzk4VUl5M0RIZmZUUzdvSl9pSy1VdlFQMk52ZkxzZWFheFJ4ZGstQnYyRV9hLUNSc0sxSnBvMVVqbTZLSWlYanlkbU50OUloZFR3bXhtYnJfZ2Jyd0dhb3NXN3l3SjRIQkVWdnVYdVU5c2xxZzE0dEd2U3pMbHpLWXJZcVdtcFhUS2hMY1lvUzc3enVfbG9sT3JVUkZsRkEtemE0UV9QelNrM0hRakhiNnpQYm5kaUh1ZTJjWkhnSnAyQmRRQmdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOSFd5eGNNTldhQUpnUVBtaDZOcV9TUjZ5QkRDYTJwc25ZdnFUQlItbGZRLVctS2ZjajQ3SHpMNnF6WGNWb2pWanl5S00zaWctUUgtZmZHMGszTjRvSmVneFlsTno0WnQ0R2JaaFlSYTN0SFNmN3ZGb2NYNkM2dWh2dkg3SktfYWJ2eklUVjBQNW9YNzMtVmhwVw?oc=5</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -4591,27 +4591,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Nigerian, Matthew Akande, ordered to pay $1.39m after U.S. tax fraud conviction - Nairametrics</t>
+          <t>Two people arrested in waste packaging fraud and money laundering probe - Sky News</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sun, 22 Feb 2026 08:32:14 GMT</t>
+          <t>Wed, 25 Feb 2026 12:32:14 GMT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYTJqMTVXbVpjUFlWWXpOQWR2Ylp0ZEQ0S2c0SHNUY3VIV3RFam9tcUdlVU5WVkdScUZ1RExHVFJJT0JuWUNnOU93a3RodTBuRF85V2xTMnF4ZzBOTDZTTUNaTWlmU3M4bU9TeHZWd1J4d3BMcWx1blpGOF9ZWWR0czdCZGJzck5ScmUwYm4zQ1VxWDBtNnp0TUQyRnB4eEVpcXh3b19pdzN6RmE0LVR2cllB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVTRQcVZNakQxZDFYdHlFTDNpM1p5ODl1cmlPSV9UdUhTenhFc05FbFctcU1KMGE5Wk82NkQyMGVwV25Nc1kzZ095M0VibV9BSjlHbkZQbl9ZSy14eHJ2ZUJjaHROM0Z6NkVBQ2wyNnZwNVcwbGtHRTFibnQ0WG8wQTJGZ1V4WGJNOWx4bnNRWWI3d3VVMUtxSGtQN1drcVFFNDlILVNSYnFTaEE?oc=5</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -4621,27 +4621,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Overstayed student visa, duped elderly for $6M: Indian sentenced in US fraud schemes - The Financial Express</t>
+          <t>The Dark Side of Luxury Brands: Fraud and Laundering - eSecurity Planet</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sun, 22 Feb 2026 04:53:34 GMT</t>
+          <t>Mon, 02 Mar 2026 20:36:39 GMT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQaE9QYUtNeXVWekpNLThfZVlNcUZHY2w1WUdXVTIyQjhDTUIyWG45dVdoMk5ySFVMcGtRbENLWS1kb2wyX2lkeW5qOXpGblJXYVZ6cUxSY3lqVjNNVmt1amNBR3BLSC1WREdKR1VtUnFINWlhekI5cXg4THdCeVpFVzV6UHhMZnZYMmFsd0RVSHNId2NhZnZhbldsaFB2TlVfTU8waWZoV1ZQMU1Ga0FHN01GTFl2ZDRCNzQ2eHJ0WEZ2VERwU0JxZ0JESENIVHMxd3RSM25CY1dNQdIB4AFBVV95cUxNcUkxOWZoczBiZ0Fxa1BYLUdjVDVrZFRrSmZpU0xlOFR0Zl9faTYxTWFLQWhiUXhoS1FIU0c5NnpGTXhGX2Q3TWVkWWIzcmZzRGhxeFVPWVROaXZCTFBmMm5zbkE0ckNfMUpFWllsOGRISmRfREUwTWpIUXNFX3JqR2JhYnBBVXRWZERqdWZvLU1MZVR5dFB6WkpCRUdRTzdsSzJoeXZOY2liaE5HUndtMzBCOXhhUFJwcld1QmVUbFdZNzlTQ2dWb3VPOGl6VU1mV1B4TjNrWVRUZUVhVG5oXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxObE80bVlYYVJsNHRieWUyVVNQM3FJNWt6WWlJUmtvQXo1RndyMURjMlh2SkVFd3dmWWxPNEFtV2pxLW9ueFQ0b1VaeTA5ck1XTVZENmpGZHg1RXR2Y0xHeXZnQkp6ckxvX3JqamRMY3RZQmtUbWpfUHI5dE5XQmwxLUJwUThNUmM4RFl3N194bEJoMFM0QVMw?oc=5</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -4651,27 +4651,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Former Northeast Ohio municipal court clerk sentenced on federal program theft charges - Mahoning Matters</t>
+          <t>Interpol-Listed Scam Suspect Arrested in Morocco - Morocco World News</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sat, 21 Feb 2026 10:00:00 GMT</t>
+          <t>Tue, 03 Mar 2026 18:11:59 GMT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1lSDU2OU1UdWw4eDhCLXB6WWlUNXR1enp1b0JZWjRWcXZHcXlnZVY0UXdIRVA0UUhVNWhsekJZbHh4eTRpRUJocFlJYWtkMHZhdWJWTmJjRjktM0kxd1JVZWI4M0JVbUtlc0JFbVBnSVIwZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQcTF2c2hkNVV1emJtOGJJSmdxd3hhVUJvNUZVU3dleERPUkhPbURlNGRGQUJwUnFWVXgySEx5Rmc4Q0N0QzBrMXRiTHBPZHkxdkxjYmxJeFZIY0NMZGdxbGg0ZTZVRGhvdkJ4ampYT3J1d1pPOVNvdWJMNmdCLTNsUFVfSnhwT0c5M3RMT1JQR21xN0dDbVQyQ2FJRS1ZZw?oc=5</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Charity workers accused of fraud and ‘unauthorised absence’ awarded £96k for unfair dismissal - People Management</t>
+          <t>Man admits several counts of fraud and wearing military uniform without permission - Manx Radio</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 13:17:05 GMT</t>
+          <t>Tue, 03 Mar 2026 18:07:00 GMT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNUGVMd1Zrb0dwTUZJNUdBUDdkMjZ2RDA4VnJyZjR6bThNYTFBT1cwZlNMc0x2anR1TmZQMzB3WWdMOFFtLUJEM05qZVNnTlRVWmtfb3pqMHRMVkJIam00Z0F5LXNwRDBWV0hQYnc4d3hyZmI4Nk5kcnhTYWhiaWlrMjdYS0xRNWFIWTRleTJSTHpRVmNzMEZKb2FPU1lBV1ByVzNIcW5nTTdZaUl1Y3lzNFlUSGE0WmJpVU5zZTl5ajVhZEdadWpJWHZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOS1N6Z1lGNWdJYlc4TVdSMUwxNzhweEN1Mm9rNU9Ta3R0MG8yVmxIY2ZjUTVqcGQ1N3RGbTh4c0JqYjJ5bzYxdExVWWRVWWJIR2lrd3VWSkpXUGhTX1B1dTZSaXlJUUxGQ3N1SzI2aGlrWEtWVkRWS1dtdmUzSFVnb1dwQ2l0N09NNEM3UkRNZE9KNEx1MGtKVW4tNUlmSy1LWDh1QzdoMHJCMkx6bExrXzVsMTJ1Mm5LQjBodHZZRWo5V1JsNHozR0NLNA?oc=5</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spoofing, Smishing and Deepfakes: To Stop Scams, Consumers Need Stronger Protections - Bank Policy Institute</t>
+          <t>Stablecoins account for most illicit crypto activity, FATF says - CoinDesk</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 19:22:10 GMT</t>
+          <t>Tue, 03 Mar 2026 18:00:02 GMT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQZ19wYkp5T0pERmlCVDQwQVFEcTNvSXlNN0tQaDlpMmR1Tlc2a3Q5TE1JUjB6WEhDcWpDSlpORGp2WTQ5SlhQRExtdC1mNU5BeWRScE0td3ZtT1NlUXJGeXpaWkI4bGMteUtMR0lDSjN0aFdiSjJLamdfdl9TVUt4SnFaWlZLSlNxRXl2V2pwZS1xcVkza2dzdXpudFM1cU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNdV9ISWFHUmxHNkxLZEJwZTI5cXNEajVCX1JJdGFmYnpPeUlTSXA5d1lRMGxQX05EMDAxTkpWUHRnbUJSV3FLLWZmVHVjYXhYVUR4V3ZlVnlaTEVPUUFUMkc3N2xuZ1pSN29vOExNd0xkdEZtQU16QXlKMUpGT0NUQUVxbHEzVnNGZUNPeWdha1lxU0g1QmxIUmFMajJCWXlHdGZrbk1od0lCQjg4aDRhRDJhOHhyTzNvS0ZXT1FQOTNhbHRqanJQYTl2WHRqQ28zY3NtQzhZZUFWZDQzNE1FeFl6NEQ0Uy1WNXh2bkNB?oc=5</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Parents urged to stop one online habit that could put their children at risk - Greenock Telegraph</t>
+          <t>Study Finds AI Is Fueling An Alarming Surge In Sophisticated Phishing Scams - HotHardware</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 05:52:00 GMT</t>
+          <t>Tue, 03 Mar 2026 18:35:00 GMT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPazIzNWNaWHZVYzdieXZYSEEwNmlweVZkVVNxdEZ0LWFsbG1kbUUyak9BUGotUmtVWFlqanlEbjg3YVB6VjlQeUxUTjgwSkVzZEVDQXRxdzFHZnJCc04zV1Z4ZUdONkdtaHVXYVJFSFFvZE1wUzY5c0o1UVVRVzA2WHRUNGtiZl9wNTNWZk9mbnBIakZIX3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9Vc3F3OWh0bllfVmtBY2d3b1lnZ1RKb1pkYUdRMmdUallYZ0Fya0NUSER3NjFMRk5GM3FIejZxOXlJTHk4cDJtOHJBUE9QT01SNlNsYW1CN2ZheDc2cGhVc2dnX2tHRDJWQ1VsUlcybFFSTHNEX2JHREpDMXA?oc=5</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NEWS: US ‘Dark Bank’ suspect extradited to France in €1bn money laundering case - AML Intelligence</t>
+          <t>Payments, Fraud and AI: Why Retailers Can’t Afford to Ignore AML in 2026 - Retail TouchPoints</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 10:07:36 GMT</t>
+          <t>Mon, 02 Mar 2026 14:23:00 GMT</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPc3EzUzNkS3k1NVJOeUNoYlZNVWFlQXBkLTJEX2F2ZHY1UVBwTkRZdVFseThMS2VvOEpyMVQwODBWX0I3eUY2ekozNWkxTGE2TWxrczZiSDI1ZzVTTzItZGN2bTNLWXdHenp2SmRNNENTZWxvV1VXOExaY1BtNFRzaTlKLU11RGJWbU5YbzBheDRkYjZhMTRWcHZrazFBek9UZGtKWUdKWGlIUVdHQ3dUdEtiV0swYnpQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQZ2NHMGJ6cFVfNE1fQl9xeU1rbHhLLVpHMVVEQXp4dTVVczlsRkRjNHEweWZhQkRPenNnMkpGSDVEQ1Y0WjI5M0dvOHB0SWE5TExWcFFySnFhNDVlQnRMTHltRWVSbmVTczN2Zmp1RjV5ZElGT3V3QXhNM1R3VnZTYjNISGliaGpRblR6LWZvbERmM1QydElqdlNoYnNDSUlaT0VNWW1tZTFFbHJVbUtvSF9DelNlQ21yeDRvZHFFSjJ3NDlycEtWaUlKZmZwZw?oc=5</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Understanding Medicaid Home Care Amid CMS Focus on Potential Fraud and Abuse - KFF</t>
+          <t>Tonypandy man given community order for fraud and driving offences. - aberdareonline.co.uk</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 19:21:11 GMT</t>
+          <t>Mon, 02 Mar 2026 16:41:41 GMT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQOFpQa1M0RDBBLXAzdTcwS0hlUE92MWZNQy1xbjlyUXN0RUY1dXFkQzFPZEFWMzFqUFFmZFRjYWZXLWt6Mmx1OGtUZE05dHdtaGxtaXJpNnZPdmlKVWJ4dExlWVgtdUtiSkRENVBKXzFPckFUb2RaX3pZUUF4c1lzdW9xMU5aZlY4cUYyWEh3bGVjUERTWXVkd2x1d0xIZ19DaGVkMDI1eS1OUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNOHF6cXJ4RkJQTGxxb1BMeGRnakVFQkFZSUowV0FsdGtOZjRWY1ItWWkxU2pUVXJoc1ZWeEY2RTVVeHJVQnBKM0RIZTlvb1EycndxV1ZhUGtRclc4RnJEV2daQmhLekN6bUVLcElZaHZmel9IYkJrVk1hcTVob2FxY3FtVHMxWlNTbzk2MmhFRXBTODFjcmpvbGpLRkVKOU4xY253emdFWkJyME1XN0JTcA?oc=5</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Seafood fraud detection gaps persist despite new technologies - intrafish.com</t>
+          <t>Mafia accused of using Naples hospital for fraud and illegal transport of corpses - The Guardian</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 06:36:40 GMT</t>
+          <t>Thu, 26 Feb 2026 15:06:00 GMT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNXZCOW9sRVJpMUpsQW9tal9JZi1jZ3BmU2xUcENCdkRjejlNbjkxVVM5dUlHWDA5MThoRHpERVRoc3pUSmNLQjBBb1FOazYxby1EcmtCa0lLcGFMRndnWFU2cFBHSFo3cS1fNnFjSDBkVG5tYm5ZSXM3UFJ3VTlXUmlCUDhVdG1SVDUtTWh2RzFUaVBKaFg3TFlfNS13UGxTUWdVN0NpeU8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPRE5MaXFTSlp6eU5qQVpUbUt2LUpOZUh0a0pFZ2pXM3M2a1RVel9FVm4yckhMcG5DN2NtcDhURjR2OHBldXVBZDFLaHlZT2tySmxIQ3ZFNDA4RmhOSGNyQlJaUmFrLUwwR2RmOFJWcU9Ga05HdjdmWHo4ZHZKckJpOUtielFVa0s5YWlhdkFPWmpaX21rRk93WkkwVGNJazhB?oc=5</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AI agent speeds up fraud alert reviews - FinTech Global</t>
+          <t>Police issue alert on officer-impersonation scam | Salisbury And Avon | In Print &amp; Online - Salisbury &amp; Avon Gazette</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 10:10:38 GMT</t>
+          <t>Tue, 03 Mar 2026 08:55:46 GMT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBjZGVKRTJRZV8ybzlaLVlGbWstRk1yZjgwNEtYa01yVXlPZ2FPbGZRSXRMcEUyZWF5elVXZlp3ZFV4T0RjV3UyZDhmT3JVcjVnZ3ZiWFRTWlVzTUQyNTRYVjRWaXRLTmJLdk0zMllEOWh0ZHN4aGJmaS10QkRXQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQZlZDZWFaT2xVcmZtb0Y4bzBpZFBFeG1jVkRlQUloSmRrWFduOTZmcFNIZGxFdjdaWjZlX09YaGEyVHpPZHBGbk1vdnZ5aGFEWk9jbC1jMVVndDYtbHU5c2NhOEpFYWs3VGYxamIzY1cyc2xiM1pSUVRUOUx5ZzBGS0VBeUtMYVU?oc=5</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4901,17 +4901,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>KnowBe4 unveils AI tool for autonomous phishing training - SecurityBrief Australia</t>
+          <t>This new phishing campaign uses a fake Google Account security page to steal passcodes and more - TechRadar</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 22:09:00 GMT</t>
+          <t>Tue, 03 Mar 2026 12:25:00 GMT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxONHJYTi1OcWR6OVgybUhXWFNTbl9YeHQ1ZDhEU3BxbFpGZUFyT2lETW5fNk5zanFYT3QzODNnckJTRUdLMmgzT2hUT0VEOE14dVFfSDBQMkFOemlPdjJPeFV1OXVSc0YxMDdSa0p4NTBzTVNpZTBoVVAxRC03QVBxeHFsM0U5VWNuR1JYcUJFWnlRcHdWaVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPSnhXX2Fsdk1DRmhGYklyRVNXM2s4SWNIalVFdVp5ZllJLTdZTWVzMlNSXzdRUDY0TGM5cXNSSlNpMGhLV0JhZjZ4VzkwUV85NzBhSFhWX05kUGlMWTJicFNfUnNGelNTV3pqbVZMd0xPb0ZvcTByQXpSUExULUdpdVF2NDdfaXhaQUFnY1VOLTBOeWo5V1E2OTlmb2hLYnF1R2liZjgyWUFFdUJaOUE5eXgtODdVRHMyU2Q0dVpkMGtXWXpHWHhmN2xVYXBabUE?oc=5</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Morocco Arrests Dutch National Wanted for Fraud, Money Laundering - Morocco World News</t>
+          <t>Thailand seeks arrest of foreigner accused of $30 million cross-border fraud - The Japan Times</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 20:17:25 GMT</t>
+          <t>Tue, 03 Mar 2026 06:21:00 GMT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOdUEtNWZzdzlBOXpPdzNmZkRoN2w4ZTdrQUtORW82R3hRRzJhYUFncjJOdUZVYjVxUDFrRGp6SElyTXE0WUd2N1dWNUFSdEwtRERWbVhRbzI2UGVWWGNZZUtJZVhHLXA1VVJMczZhZkVpUHQwTlZPc2FvQ0QyY25OSHVHMEUtenhYSk9aTmdtNUx0cFp0WjUzbmJEY1ZZUWVVSDhtZ2FzRlAzN2M4RWFuLVNiOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPSkxVS2lwMXZZck9LZERDckhQNlhLT3FvRTlYXzVWOW1pajNVTTZsX3BWd2R6cWwzR3lnYzJYNVRtd3pTN1FCN3MtMnZ5TXAyTjdRdWpNQWFfYVVTcEhHOXhpeThPQm5kS2NLZmlCUXBFcWZ5bjZJRlNwRkthRHFOOWdjamsydk5VektOUzNGbmdtX05iVm9UdktJN0RMWTRsdC02WlVrY0tEQW1w?oc=5</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FATF warns of rising cyber-enabled fraud and widening money laundering, terrorist financing, and... - lokmattimes.com</t>
+          <t>62 indicted for laundering over NT$10.7bn for Cambodia scam centers - Taipei Times</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:32:33 GMT</t>
+          <t>Tue, 03 Mar 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOVDlmQmJSTmhNcXRoSnlCT1c0YmVBZU5tR1l0eWl6cEtmQk5jbzAtangzZ0lMTHFYdUd2eWNwWUxBNUgxZ084b2VTTkIyRThSdmdYOUlTRVFKa2lETlY1LVk2Smd1YXhPbkxXMkQ2YUJQYm1NWVZ0eTM2MndLaFVlZ29TaFU0RzIxT3paSXR3NlUweXdMeEVndlZaLTRneW40VXRQZmlodUtoNTliRnFiWm5Hb2h5cU1QR2d1QlZkejkxYmRKS2dZcU5VT1JyRThYTGkzWmRpMEJ0YVFLYTFzcGptQXlUZ04tM3M2T3U3RW5RbU9WSFlCcjZCZ9IBgAJBVV95cUxNdWZ3MXFYUFNkajQzMG1OeTdMSVJkdXRVSTlQeGpDbm5ZcUIzTklwZ3B6djZncTEwdGZrYWE1cVFNa04wMmk2MkZYQm15WFV4X3p5Rk0wcWxyeVh1YWpXVzBtRkFzcV8tMEdRamstU2hsSkg0MXpaS1NGOUx3c0pfODhJRWZmYjB5RG5WdjNYWFVqbEVNN19GaEtfVnZQUVdBLXd5RlZZR0VNc2N5aVBLRTZJdF9YaVlUdDM1eUVSX3libVZleHhxQ0ZqU1hjY2tpYzBwY09uaHcyUUhJUWVlZDdFM3Vicm1tQ2FzMWFsREpvY0VDaFEtYXdpS1VTQklK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFAwZDJLb3hpbHZ0Rnd6UkJyVmdEdW55YTYxRmZwYWJ0UmlzTDlsNUZpV2xlZWVTd2ktRTlMNktsS09rNTM3a1lsWnpSWHU0N01uQWtZRDhJQXJ6b1VDY296WVZNSFdXR2dwUnZJejZvSDZTVXd6b1JNRDJn?oc=5</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Fideo Intelligence Launches Verify for Payments to Combat Synthetic Identity Fraud and Strengthen Real-Time Fraud Prevention - Business Wire</t>
+          <t>Romance scam victim gets $200K back after Westminster police investigation - Denver7</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:00:00 GMT</t>
+          <t>Wed, 04 Mar 2026 00:16:19 GMT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxNOUpia1gxcDQ2dnIxUnhjUW9HdXJ6ejBzQUd0QzZfcjlVR2ViOF92aFlpSmNjbHgtRlhpR3E2c21ERTFpUks2M3lLb0NJeXByOTd5YU94YXItbVpnbHEzcFkxSFNUR2tHYjFEakdDR2dhZXY5M1JSbDZaUEJTVnFOdWEtTzZRUXl6XzAxZFUyMlZkRHBQbi1EQ3Q4X2hSdndubHB1dE11djM5d21CR3ZqRTdmQ1kzQThqQlhTZkJhUWYxTVlGTnFWcktkZmN5VXRUdjdRdWpHU3NwX2RHV2NvdE55bXBTRU14aXlIQlBMb0llOFphbEpDV3V5ZWVNYWZuSmpKUGJXWFVUVDNacHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNWHkzeDAwaGp3UTdZRWU5N1dyQXRIbGl6Y1k5Tk4zU1V4b3VZbTB5MjBodFduYW1qZXZzb3FCdEpsYkJPVzFTUkY0S2dnYTk2elJpbnpmSE1OOFRMNHFqRzZlMXVDWHRkN2x6dE50VVFpT1JoZFhxNURIS0x3NWpVT1RmM3VWbjZNR1lfU2tHR1lkVUI3M3RWRnlGMXpnQVNKQnc4NVNIWlU3S3JD?oc=5</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -5021,17 +5021,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cyber fraud rises on global crime lists - Royal Gazette | Bermuda</t>
+          <t>Avon financial adviser indicted on fraud charges tied to $3.3M ‘free-riding’ scheme - Hartford Business Journal</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 21:55:43 GMT</t>
+          <t>Tue, 03 Mar 2026 20:13:36 GMT</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPclJoSHgwZnpFTk5CRlRTeWNSVUhoVXRIbG1faWVjeHNFcFJlSHFoRFZUYU9fMlF0RXR1LXdOc0ZhSFl1eWJ2SFlzSzhWcjFRZDB4WXlZVDZDQ0hPNUpDek1vQUVrcWNjYzk4UUotUzJpdWdWeHFSejhrQXpUaHNYb1lCWGQ3RndhUXFteWdhVVptNEdPenoySkJzNmlScEV5NkstZFhFWUVlNzZsSUU5azJ3QVdkc1lkeHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPOHpMLU1OejB0RFdITVlHNl9STTVNQTd1aGtVMk9vTUVvZ21kOEF6MWJ4UEt1enlvTkNLUlo3WTdyQThzVEMtQ0VtcG8tS2VHMHJWQkJBV2lZVnhsM2tIMlp0dVhCd3E0b1YtVV9KRmIzMl9FV1kxckNpd2VzTHBwZHBSM3hBM0NHaVlyZHR3eWQ3aVdkYy1ncnNZY1lzeEEzanRkLV92ZGExQ0ppdDFUd2QtNGtnNllNNGc?oc=5</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -5051,350 +5051,20 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Barcelona member’s complaint accuses Joan Laporta of money laundering, tax fraud and criminal organisation - OneFootball</t>
+          <t>3 NY men facing 100s of counts of fraud-related charges in Greenwich, police say - Greenwich Time</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 08:40:21 GMT</t>
+          <t>Tue, 03 Mar 2026 16:25:57 GMT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQa1dhamhnUGlRTV9PQ2FJYUVldGhwMFVUbjlyZ0ZxT1V2eUc2NF83M3ZPc2NqYjV3YUU1dWljdUx2WnNJc2lKN2lnb3NHVGFQTnN5bkhvZXU5MjNjUDU5VldEal9pel9uak5hemp3b1lZNTNqdEhnbXNxams1czltUTVWaVY2dEs0ckY0cUxnbkpaZzBHX2FEQUV6NTFCZnloYjcwTkN6VUVhYTJDSFRON3Nsb3UtcmloX0JtaVIzVlR6N2RGVHZCcDZQX0Z0S1hodkg2RFFpRUdoTjE4Z0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQX1JJTEg1UnNRVnZBYkZ2elpsZjMwSGJLTndySWtCb2hMbGpXVF9mWVltd25lLWVhbVBWSTN0Q1BRcnFYM3R2aU52NmN4SThZWXdIbzMwSjlqbEJrY2VuOGYxSklJN201Yi1HM2kzNDNTUGhwSVFHNXZHRWNNS1Fpd3NSd01WTTRiWVBHT001V3RzSk9Wd3dGVVJnS1B5enl5N0VWR3Z3?oc=5</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Trump Targets Democratic States on Fraud and Voting in Speech Touting Economic Gains - Governing</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 06:04:11 GMT</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQc1h5clc5RHlwbU5vS3BrV3BBcXFDTWFfYmhRamdGTzF0NW9EdHN4T2ZzZ3Z2bGN2clduUmd5Y0l6ZVlJcmFGa3g0WFNrSVBpZmlqQU56bFlxWFhvN3c4eUVEVmpHNVk1RkdVLS1rMUtYNTY5MEFKMHFXdGRZY2R6YjM4aTlDVnV2NzJhbUw1eWVDa3hrQ3J1Zlh1UjY4TkJEVHQ1Mkl1bGNVd2dJVnpvdHdJZWx4ZUkwQ2ZJ?oc=5</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>BankThink: FinCEN Should Reassert Its Control Over Anti-Money-Laundering Policy - Bank Policy Institute</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Mon, 23 Feb 2026 12:30:00 GMT</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNLTVxbWRBaG9oNG5KemFEckt2UnczNVdTY3VpbG0zRHBIaU1ONVdCLUF2cW5aLVVscHhnaFFhQ0RFaV9tYllLNE9naXNOdVpHLWNHV3JyWnlVejdUVU4xQlFaNnFDS2JKNGtyX3A1NmJfaUIyVkdjaHpzdERjdFVEeTlKREVLRWUtN2IxbzJZZlpLTVJPcldIN3lwUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Protect Yourself Against Romance Scams - U.S. Immigration and Customs Enforcement (.gov)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Fri, 20 Feb 2026 18:07:16 GMT</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE53bzBaQWRrZTh2RmdGdkZEVjZ2VUdMQ3JSRWdvY2R3d3o3QkdqMUFrNUNUVlhTcEZaV3V6bmkwLVVSdVJ2X3FfQnFKWUFNQi0zamlPanB5MGo5TkNPaGpiZzZKN3pGS1d5NHJqZEtmUG02Z0RFOEJDQlVrcw?oc=5</t>
-        </is>
-      </c>
-      <c r="F158" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Phishing campaign targets freight and logistics orgs in the US, Europe - BleepingComputer</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Tue, 24 Feb 2026 23:57:58 GMT</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPRmduVjRQQ1RPc09HbGRvUnEyZkEtX1FGcnBfd21ONExYV1JUTXB2aDdvOFRNdklRR1Y1YmRGRkZRSUhPMVRGclV6ZXJFR0lnSVF5WVZGaGFUU04zS2lCYURqeDk4LTZJTDljUzRwM3JLbkRya3RHWGprZ0tlb2VyUk5yTTExZExnbVdtU0JLRzlZNnotWW5iajNoSjdRdFJ4N3JwUjBxWGhTMFJxcC14TldqQWFYcVRv0gG-AUFVX3lxTE9UbkdrV0VVRmE0LWVxWUJVaDdvYjBzNTd3ZFg3LTRFWTlyT2Y4bHJwby1KM1BZVjNnalRmLW5qYzBZZDJnQldRWEtNeENNcVExTDd6VU9odUxSUFNoNzlYTHg2NGlxTkdITTVEMV9pNkFkWWZvZmRjZzlVejU1R09zbGpIS19zWlRRQnRYSEt1eXdkSlQwdWpCdXRQVFVLVVh4elQySWFaUE9nN2tON1JFWnI4bFA3bFhXVlF6bEE?oc=5</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Trump’s ‘war on fraud’ announcement recalls plan for assistant attorney general who answers to Vance - Democracy Docket</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 05:37:30 GMT</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOM2xYb21TY21XS0dRT0JmS2tuV0tDX1l0UFFnV2tUTUVaTHBWOWtwSUUtc0M5Nnh5eUk0a0lkc1NZTWZyWHVZU0JVR09LY1Npckw4NjN1ZHZfUG9ZalZxLTFRLTU3WTZjNS1DX283YW9ZRkRaOWM5dlZmRDZ6TmFYZUN5Sk1EZm9tNkxzUWR0eWVfc1M3bEg1SXZQMkFwLW5zcHc?oc=5</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Contini clan controls San Giovanni Bosco hospital in Naples: arrests for fraud and corruption - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 07:04:16 GMT</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPYS1ZWEduNExOR0xxdl82dTZCZDVXLTZXMWI2REtsWFJNNjZDa2I2WmFyZ1FuM1NFckp4NXpRZmpQNE1raG01cVRUSlI3TWlnaVBoaEgxSUJfek1JdnRVcGJDa01xWS10SFhnVnBZb2pZSnBxaFd3VWVyNjRNaWFXbTBKN3lCVkxnT19tVzh6eWhFQ3BGY215TjlzTkdnSW9udTZLc2tXSzBtTDd1S3RtcGhId0loSFRMTTFlZXYweFpteVU?oc=5</t>
-        </is>
-      </c>
-      <c r="F161" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>DOJ-Office of Cybercrime Joins Global Effort to Tackle Financial Fraud through Open-Source Technology - Doj.gov.ph</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 01:37:13 GMT</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQdExXeC14ZWFnN1U1eXBnYnl3TzVYYTVwSU04M1h1ZG0wX0lzMnh2ZlhDcm53amw0TXBKaG1SaGRiX1Y3NFUyUUVNVnJCTXBKTFBFempkSWFYLVdTVWRtQ216WUxmX1lNV0h2ZjZQNU9GRGR3OFhwcEJQal82R1JuZnRWRm5QaXhHbG1jdWExT3NadmtwRkE?oc=5</t>
-        </is>
-      </c>
-      <c r="F162" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Ex-Motley Rice Lawyer Pleads Guilty to Fraud, Money Laundering - Bloomberg Law News</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Tue, 24 Feb 2026 21:25:00 GMT</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOeWljbWd6UDJaWUtqbDUtNlJwQ0h2TTJ2Q0lmOTNVcUU5TV90SzVwSzhoNWRuZUxjU21UUElUVm1KbEFOMEVKY1YzcHRpSG93VU1PZHpVRmg3YUdNRkhvVmZfRTB4bjhRYktwM3RqZi1BTG5iczN4YWxVWnI5dlF4TFJNYmRHcUppelpRTXYwVWx6aS1ZSU05cDctU2ptRk1wZXE3UjRscmxQZFQzQVd2OTJjVQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Woman reported missing in New Haven arrested in California for bank fraud, officials say - New Haven Register</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 01:16:16 GMT</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUjdLRUtPalY1ZEJBcndIWGFhUmxYV1BhZ0JEbmxPQmI3VjBGZ1FscHl1XzQ3R1ItS2wwVWlwRGVITkk3ZHFRaUVxQUFzWW1kNHNkVzVUWnlGdU03R3pzRHV6V1ZvOGJ0OTJCU3FYNU1IcUw1VkpkWWhrYmdYbFdxQ1RWcU5XUEdUcDlTZWpldHVFSi1kZVBXLVZMaFQzUTNOWW53?oc=5</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Ireland Sees Alarming Rise in Fraud Offences as Traditional Crimes Decline - International Business Times UK</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Mon, 23 Feb 2026 15:11:00 GMT</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5CdGVKOEYzMFRLUDNPMmx4emh3bGhWX0llVjVLQS1IdUZfWmVhbndqUlU4UkJseE5HX3NZbUtMMVByRmd2UlNYMWE3WHUwVU5INGZkS19BWWFrMHA5aVJyWUo1ODhvVlZjZXZYRnM5ZjkzUnlT?oc=5</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>ENFORCEMENT—S.D.N.Y.: SEC obtains penalties in COVID-related corporate fraud (Feb 24, 2026) - VitalLaw.com</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 01:16:25 GMT</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPb253OFZrMnVzQXBsVHo3M3dZXzFZSFAzNmNuck9ObjlYeF9HM29ZTHgyYm1FbTEwRzhWN2pld1NkTGtWMGlJN2Flb05fTHM1aGEyMnRwTkJrSl9Ic01Zd0JmRGg3WGJKQ1pWQ0h5V2wwR2xGVkRrVWNWSks1RFFmdFVEZThmZm9haFVhbkdOby1tZ1phVk1NYVVtaGQwaTBmR3poT3hYM2R5VlRGQldGQlNXWWZ0RTVkX1REZk5ObVUxSkJGZjdmem51UWk1RXZKbENnTW9Dc3pZQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F166" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/weekly/topic_feeds_week.xlsx
+++ b/data/weekly/topic_feeds_week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spring Forecast 2026: The right economic plan for Britain - GOV.UK</t>
+          <t>UK-EU SPS Agreement - Legislation in scope - GOV.UK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 13:10:37 GMT</t>
+          <t>Mon, 09 Mar 2026 08:34:48 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOdnQ3YVN2OE1HQW5ySUZWSUNEQ1NxQV9lejRlOGpwbWlacDBCeTh3ZlZNOTZBSVRabjhraFVoZVRoclQ4ZzFFMUhzVFh0bU52S3NZR1d2VWQxXzV2dXRvWk43MHI3UHB6UjI3WHJHSV9wOWJqWUhYYUJTNHBFbTdMQVFjRmR5bnRhM0FmdFJqNFJEaGYtT1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOM3QzWjRWSUdFekNmZWUyOG5Od01hZUo2enVJMV8yVUliLUhxSk4xUXBDQzJpZ1Y0Y0k0eXNrSEtTYjFQbTc0V3BlYnFBc3dHMVEzWnpZLWFXWHV2Nk1zX3Z2b0NiVEEwb2NzVU01VEJJZzJwTy1tTXFGaE5TS2pZSA?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UK lifts Russia-linked sanctions on British accountant - Financial Times</t>
+          <t>UK Music Launches Welsh Music Manifesto to Turbocharge Economy, Drive Tourism and Tear Down Export Barriers Ahead of Key Elections - UK Music</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 18:04:31 GMT</t>
+          <t>Wed, 11 Mar 2026 06:11:15 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9wMGpiRGp2dEh3cWRfWFRteWZuTmhWcjNuMFkySzhZYU1iSzEwR2wwdEZReGNqeEpyNFlEY0lSUWx6VDExcVpIUnZ6S3YxNGN4RGllT2Q0RnlHNDhSTjJPOUcyeHczdVBrYk1SQW1jVjc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQdl9NcldjSmZKRUttYlExQ25VQWVkSGxxMDhCYVd3TlhtaUhfZlhMaXE2VF93R2lkNVJYdDNGYlktQkhCeThIXy0teGtVVm80WEJ0R1lUaU5SMm5kOFlXRU5pb2lXMm5veEVGRXIzNG1yUEdic1c4Tlg2a2FVNjJtbmUyT0dSam9sQzNtaGFnazRpbXNZN09vU25mRzlpUS0tdWxSNUotTXRta0QtRUFYUHo3OWpOTURkRmxvM1VkVFZwbWE3MzgwcWk5Q0xfTHdpc3JqTDNlLUxBaXNxSHdBZVRkUDVuLUNpYjFoT3NIWlo?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alert: NCSC advises UK organisations to take action following conflict in the Middle East - National Cyber Security Centre</t>
+          <t>PM warns of impact of Iran conflict on UK economy - BBC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 12:00:00 GMT</t>
+          <t>Mon, 09 Mar 2026 17:21:24 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOclp2OTdKYlV2NEFZOGlPV3VSUkNnWWpkelNWXzBxV1R5N1pxS1phZkQzdXd4R3NTMjhIOXdyZDVoa0ttNW1ZOGVYRzBNS0VaeXJxUkFvLTRlcjFsODdYZy1YQWRLSVlwTUhhRjZZcVBYVEtlNnYwWkFiVi05bV9zVHBWS0p1MG1jV3RpRVJvejREeEU0eTBaVVlqcjZwVl9YeUtabnNTYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBYQjlxc1p2aEJLNVc1YVByMFRZTjF6Sl84ZERKaTcyNk1sOFNVS1dCZVdYbE1Cc1VNNkQyVHZidGVNZXFrSUVocVV4NUw0c0wxdWJyR1ZINkh3dw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UK borrowing costs jump again on fears Iran conflict will curb growth - The Guardian</t>
+          <t>From Tehran to Europe: Terrorism Risks After the Killing of Iran’s Ayatollah - International Centre for Counter-Terrorism - ICCT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 22:26:00 GMT</t>
+          <t>Mon, 09 Mar 2026 09:04:20 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcjlMSEpiRG1jSTM0U05Cb21ubDc0YjZhTm9KY2x6TkVnc3pOUlB0UGdtNzRBMEhJSU1xZWloWDdyMGJJSFE4R3dJLThzUHJZd0FvSG56MEgzSXdha181YjY0ZzBoeER0RUM1M01XZjdiUlh6R1hOQmxzRXdDUkZWQlVhVU5VUGVma3NVcERXYlBVb0VRUldKbmZpaXRuQzRzQjdMdENpaHI2enJCYXlCOG5NaWJnaG5mWUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNM0VjRlhYS2dnM1JWZVhRZzBNRUlrdGFTMElrSWZfZmxLSm0xakVyT0JFS3c2anFFQVRYM3JUUXRGOFF3VWtGc1NrLUdWd3BCdWU1d1gtV3ZQQmhpOFFhR3BlbWF6UTMxUTQ0WVJ1cDdTZ21kUjhFZEtDTVZIYzlCV0IyR3J2UFE5YWstejFaS0I?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Low carbon and renewable energy economy, UK: 2024 - Office for National Statistics</t>
+          <t>War in Iran – NFU raises concerns over impact on fuel and fertiliser - NFUonline</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 08:00:00 GMT</t>
+          <t>Tue, 10 Mar 2026 17:19:34 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQSmgtUlpKWTZybFlTb0Jvc0szVFQ3Smd5U1RIQ1lKSjMxbUJhRzZWNlgzMFFHZ09kTkRBVXpFUFljNk9TYWhXT3FmazRVSGh4Z3pmZWRBRFoxVHhGUktpV3pnUXo0Sm5RRnhCclVrRWw4ak1RTk5YYVdFQll0TTlxMzRZUlBKZTZvZlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB2NEQtUjRWZW9USjgxTmk1NUJsNmxnU2NzVk5Rb3lsTlBRUUtrMVU4UG5hSkotbjVTUk4tYU1Gb2hZalBTWmNIS0k1NFBGLVZHWjJiTXRBQkdCYzg0SzlQXzFlckdSWG5GZ1lFR1VxY0JJa2VHM2Q1WmpTUWgxanc?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gas and oil prices soar and shares tumble on fears conflict could escalate - BBC</t>
+          <t>Navigating the New Era of National Security, Geopolitics &amp; Global Trade - Baker McKenzie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 21:44:31 GMT</t>
+          <t>Tue, 10 Mar 2026 13:53:51 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAtaUk4QzE0N0R4ejdKczZYVHVNSmVWbVgxTEZTTGhqMHJHbHhWcm1rUXhJdy1OR3U5WGRlZlo3Y05HT2h1QzN0eE55Tm9ydUdkRjFhc3lGNkZNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNVTl2S1BKeW81VlI4d3dHOE5naVdJVE5GYTFIUUJkaV9FQzcyY2JfY2JiRnd0SU95R1VZRS1VSzYxanJLUmoxV0Z6eDR5T0gxUEhxbDlPaTNZTndmMVRST0ptUkpxeTZyWHJ3LUppSGFCNnZPZTk3cklTVm54aFpoWS1ONG5tRXlGWnpXUUlBR1VyVTJTZXpKQXRKaUIzSXNrcTA4YWY0VEs?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lower net migration could hold back UK growth potential, OBR finds - Yahoo Finance UK</t>
+          <t>Energy price volatility and the global economy - OMFIF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 15:57:38 GMT</t>
+          <t>Tue, 10 Mar 2026 12:14:07 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPYnVwZld5UzdDX2JJeFVnODd3N0UyRFZqcUlIekgxWGNoSHo1MmpiNUJ6LVJZa085aVVuV0FGWVhKNTd1TC14eTVIZjRjc2stYklud01EWXpIR0h1NXpYYVJNOE9KX1VJSjE4bDlZYWRCUTFEazZLNE0tYzVJdGFoWUtpYmQ0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBtQkFmanNvYU1RMUFvMzZYT0Nzc1hYdzRVRFRueGdFYVdDeHMtVEpvMkhpZUMtSVBWM1M1YjVkWS1lMkZvWHBTVHNlcExPN3p4bHgwNDRaSkNTbF81eXZ3b0lwbXhudnNvNExSSHZRMFVPaFFCOEkw?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conflict in the Middle East: Martin Lewis' 'get off the Energy Price Cap' mini-briefing - Money Saving Expert</t>
+          <t>Impact of Middle East conflict on UK energy prices: Will CP2030 prevent another energy crisis? - Solar Power Portal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 19:33:15 GMT</t>
+          <t>Tue, 10 Mar 2026 11:12:52 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOakJvMDQ1TFlpLUlHRk9xc0NReTg0R0ZEdHBjMjRRem8yU2ktTWctbFZ5NERtV0dRSk9iRGJ3dGlxZEZrVzFrSGtCcHdBaDNjSDFTYmJPelVXLWZVaDdTMV8tVVpWdmxaZm95NDVMVE5iUUdfSFB3OXFnTlNhbWlQaHZkYWJLSWpDQXl2bi04Szc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPVWVGeWJkZFNnVXprSndMSUhoSDFsTXdLakdYdHk5bXI3TlpzUk1qTHMtOHZQazVSQnN0ckZkS25QZFpLTXY5cXRSR1RpeTktT2ZNWUVDTXhvcnEybnV1bW96bEtfaDd5VW45NXh3Vnh6aUh2d3RadnFpWGEzcjdkUUkwRTZMbnBRZ2ZpYmtQbHA0c2dYTGhweWtBYkZVU1NzTmh0eG9NR3o3TjFnSG95RGxTb193LU5NNk9fUUx2SXhMMUFKTzdGS3p4VDlLNlR1VXRzbHpVMWdvUQ?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Increase in young women out of jobs market costing UK economy billions, report finds - People Management</t>
+          <t>New analysis reveals £43bn annual Open Banking opportunity for the UK economy - Open Banking Expo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 15:08:41 GMT</t>
+          <t>Tue, 10 Mar 2026 12:28:43 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNaUh6d2NUN3MtVWl6c2I1Z0NJbGtkWGRHanJZemstRmQtVnJkUkxVMlFzYjRmeVJTVEYzNHRvR2tHaEtLV3N4M1YyX192TlRsQnFRRTc5bzBITWFpUDFVUEc4OE44MVE3Z2l5c0RRTmZtZVBfSU9BczlldHBpOWt1WUtqQ0pYXzRNZUVQRXRjMmhCcHo4NWRLLVF6MDAyWWVrZDhnZXUwY0lNT1pnbGpLb1RXTFB5VmFXTGgxX2VHOEtRUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNSjJ2SWVQQklJNFlaeUtLd3ZVa2ZyWXlqMlpEeDh3Ri1fRk5ZQ29UdWJjdVlwRFNsTUdWUmtwaXVyY1IxSlppYmJSb0lxYW1tWU5UR1B1ZkpQM3owdXBsRmVGSEVmdXdDYWFDT2tkUEtPMkYyQXF1VjZadkVMZTdidGUxNXZHeUpLVFRrNmRvVk4tUEVQS25HbVZFbnBrTk8yVEdUYXVyN2EycmhoS25PYnQtNWE?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Urgent call to protect civilians and respect international law amid escalating regional conflict following US and Israeli attacks on Iran - Amnesty International</t>
+          <t>Conflict in the Middle East could impact petrol, diesel and grocery prices in the UK - facebook.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:19:54 GMT</t>
+          <t>Wed, 11 Mar 2026 06:43:59 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOUG9tcllZVkhVa3l6bDl5WUxkY3FpdDlyamQweGV4SVFCTDY0bmNIZlRtbF83TW9XR3BHVC1uTXpPVFVhVVZPb1Y5YVdDMXg1bWU4MkNqWF9rSlo1b0Z5MXNkVGFSMGpEZnpISWJtRExMbHQwNDRadnlXdTV2RkhLSElJSkVQMnhncm5BcmdXUjI2S0w2VWUxS0EwbFNEelN6QnF0T0x4dlhRVmZSOHNBWlJPbkc1SkIzSlRUbVphWkNJMlZSOXh0N1VwVEY5eG1tUDJXSXNKWDZqUXIwc3NUcFZ5czg5TURWNzZVSGs1aGRrM3g3clczSFdoQUhiRnZMczZKcXdfdnlJcWxYWFhxZVVXaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxObmZWY281UGI1Wjk4N29QVnNQTUF5UzBULVFldC1SVXJuVjM0T2FXLXVIemRBenJnaDFrU1dYdHFVVWR3OUlGWi1jbVlrMTJ5S0JpNGRUUG1ody10WENTRDNtc2hneFlQeTIzeS1PYUdkR3lKVzdENUZIdTIydmd0N2x1THp4dVdFVXAtX2RHZ1ZzLXV0TnpER0dNR3hqVzJnQUduWVIycXdmSnhURmc1dzA1ZnFrcl9MMEE5M3I1WWRzZFRKbmxlMm1XOHlPUG5nSVNaVkhtM3lodkZyb2l4VXdEVC1TUQ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Stranded abroad or travel disrupted due to conflict in the Middle East? Your rights explained - Money Saving Expert</t>
+          <t>Inside the Russian explosives plot that targeted the UK - BBC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 22:25:15 GMT</t>
+          <t>Wed, 11 Mar 2026 06:00:08 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxObHBFa3RhaWlJSF9FelZtOGo5S3JiVVJYdFVmby1oYXgxeHlXUzdYOTNjaWt1M1BQcTRIdHAxSmxEOUllRkNudDI0dU5uZ1NzZnNIQkROY2Ffbl8xV2VJR0E2YXNTb0FiRVctZUFOenNJSWNBd0RBSDdrcXRfNWY0eUZlbXB1cWdfU1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE52cUN1OU9yS0NQNUp2TzdIX09pVFk5WnExTTBmazVBbFJyaHRhZkd4cDB5aWhCZTN5dlhjal9qa0tSeFF0TXN0eWp6Q2Z1Szc5Z2VCcnFHTGROQQ?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Starmer seeks to carve out distinct UK approach to this conflict - BBC</t>
+          <t>Calls grow for Reeves to ditch fuel tax hike over Iran - BBC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 18:05:54 GMT</t>
+          <t>Tue, 10 Mar 2026 17:34:01 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFA3WEcxYlZOY2JJTlp2cjdRMk5jaFZyaFdPcVB6VWhET21abHFMLU4xVXlHUU5NbDJhV21iMW92dmp4SDgwNTNzcU9DVE85UThqM1l0WFhZQ21pQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9VbkRlLTIzV1lRb1JuTndvQzdDZUJsWFlSWkxDaG5nbE50R0JJQnJqNWVVU01tb2g3bUlWa1F1a2pwU3NDblJoMnVIM3lzVmN2QlZIVjhtQnFPdw?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>‘Simply not true’ UK is being dragged into Iraq-style conflict, says foreign secretary - The Guardian</t>
+          <t>Cornwall navy air squadron 'maintaining readiness' in conflict - BBC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 09:08:00 GMT</t>
+          <t>Tue, 10 Mar 2026 13:44:40 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdVRucEtOYm5tSEV6SjhmVjI5RnAtWDdOTHpIMmFrRGJ0NTJEcEhJUU1NUGUzZGtqdUgtUGVuVnNwR2kxZVNRZzFYN1VCczI0QzFRem8wblg0OERVOXJPR2pzMFFWdXZlYXAwSm5QRzlwWkxFdFFHaXF6S1pkTm5kWmFVaTd6ZnhzNGdMUEJDNk95QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5DRk8xOGRFQW04YzFNME8zRzNxZzRmLU4xR1FiUVNJSUxXVnF3OFlnYTR4M3NJaWdGRVpzOUpmVmRRMHdibVpkR1J1Sk5sWTZpUngtdEFCWTVlZw?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Why Europe's leaders have struggled to speak as one on Iran - BBC</t>
+          <t>Three US bombers land at RAF Fairford amid conflict with Iran - BBC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:26:21 GMT</t>
+          <t>Mon, 09 Mar 2026 14:29:35 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5kNDU2TGZJTGQwSEgtc3VKR2cxWGxFVWZlRmFBdkdYdXRFY3BZcGwxU0I4XzlLNUw5SDkyNThZWjlOTmp4cmN4WDVwSnBxNG01ejhCeFYyMVpBQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5RT0lBclVKSTNoYVA0TEM1NUdNXzJjM0RBdmczVDhnWmlkV0MwcWR2c2ZRcXFvT2EzVHc3Z1dkVEZEZmlzU0RhTnV0Tm9aOHROZ2JldWZ4Z2NRZw?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boy, 12, stranded in Middle East amid conflict - BBC</t>
+          <t>Iran conflict steers global real estate into uncertain waters - Property Week</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 17:53:14 GMT</t>
+          <t>Tue, 10 Mar 2026 14:13:19 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE40WEJGanBXMXlpbTA4THJta216Qk15QTA5TVhTQkRCS291Rzc0M2J2a0FzeXVYOVVIS1pwSzdhWm1weXNkZ0NjM3JHRVdxVkRjbkdRYjRnbDAzd05N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQeVlKRWgtOVFKMlAwWHJ3aFZzU1NsSTdzel9MSE1idnpMYXZTMXBjbUxadjZVQ1BZZUswbHFEcFF3Vlo2NXJwOEl0OG1YWjl3NTBlLXJYbnY5c2xNaWJNRUZKWE16bmd4TXFQcVIydE85NDBtd29US1lXU3Fzd0MwbS1kTVhmQm5DcG1BVHpQOXhDLWlvenNLUzBIaGUzOVI2?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stock markets slump amid Iran war as gas prices jump 30% to three-year high - The Guardian</t>
+          <t>Trump is bombing the global economy An inflationary downturn looms - UnHerd</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 10:21:00 GMT</t>
+          <t>Wed, 11 Mar 2026 00:38:46 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQcnJ3cHZTM2tqVndJMW42dUY2MFVtc25mc1VOMWpEV2xxUG1YNUtxbzd4WXZvYnlGRGRENnpkbGZEdFFJY2hQLUxtTEYyZTlwR1Q4aGh0c3hwOXFNalVQYVg2VDVfVVkzZTdSUHhXYnlsT2JBSW90ZzZobFZhbzM0dVVLR242YVJrQzlvUy11Q09OZEFBcDdPc1hvSlFlZUFERnU2Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1QLXBQb2xTbFAycGVxa2k5UlRYUkY4cklxLUJsbFhDeTl1MTVHM2t5ODBBLWdfb3htQXdzSGplaF8zaFRwcWxNNzBtN3dCdUN0Smt6NWlqX1V6d1hyVktmRGFSRVdGVlZWd0dEMTA4LXB1cDZPbk9BSXltZWE5SEU?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Market news - investments.halifax.co.uk</t>
+          <t>UK MP calls for additional sanctions against Georgian officials - JAMnews</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 17:21:35 GMT</t>
+          <t>Tue, 10 Mar 2026 15:39:17 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPQmZwR1Juai1oNHE5MkltUHFCRGtJajJXQ3JPQ0hJeDNGRUVCVDRaNDBvR0tidnZPSjJidEZvcHhLUW5IalN6SF9VRnBKTXVpWHc1aWRlZ3RKUVE0YWZUeEgwWjN2TzQwQlFwd1k4UENsYk1FcDRVcjd5SU9QMWdDT2tObVNFb3JIckllNjdVLTdLM05ZZUptdHJyRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPaEVDUnJSTVpQSVBEcUUwSF9kbW84Y3ZmX1NuNDF6ZDhGYnV1bFRlZjIxZ2paRkpIRXRPSVJqTHhsaE1IOXlrTFhRanhaRE8tMjZZSXpfR1RWeVdEY0t5RkpKOHVnUzhOYXZLc0hqZWdYOUNVRDNJQXJxRGllTC1uZW91Z1hFSVB1Z2t4TWJR?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US sanctions Rwanda's army for violating Trump-brokered DR Congo peace deal - BBC</t>
+          <t>Wider Europe Briefing: Hungary, Slovakia Toying With Russia Sanctions Renewal - Radio Free Europe/Radio Liberty</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 10:28:07 GMT</t>
+          <t>Tue, 10 Mar 2026 11:06:54 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE96SHc2NTdhNW1HQmIwMDFpMEx5ZGpERndvdmVtbXZUOWhsclI4REE1T1pCZmZiQVdTQ0FZcnMwSGxyRjBYT2NveUFqUDZReFU2dzV0LVg4R1ExUDBD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNSVhsUm5jSFBKUzhlbGFMajZCbkR2X1gwN1hDQmY5d2k2T0ZrRk56MDBwTTBZZUMwTjlaN2pCdEVJQXRSOHRyMG9DVExySjZoYnBBVmRZWlRtZlg0LVp1THJEQUJrczdvdGF5YUhvZGpZbzVHanJjT1R3eDVhNGZ4ek4zcjZYTGVEaEZfcEg0ek1za0hzanhkY0NVeU16bzFrMVIyd21mYVhsU0txLUFtZ1pWa9IBtgFBVV95cUxNUzlPYTI4RmdzSHdnaFRqd3JoLVYwaE5Gblk0OHctOTlHa0c5dlQ5NkpwMXhILXpqOEZPWFVTNklERnZoN2FmNnJhOVRLeGdEejdBek5NNks5ZzRicTcwNlFjUVJ1SS1hTnN6Q3hqUlhWYmZJSlBXZkFOMDIxQ081X1d2MEd0WUQwY0pYdG1pMmgxUUpUZGVzLWRjSHBjNTMwa2JQVHRhTlZDcVpDNFRQWjE3Q0ozZw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -991,27 +991,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£271 million to clean up shipping and power coastal communities - GOV.UK</t>
+          <t>Trump Generating His Own Fog Of Disinformation About Iran War - HuffPost UK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:25:46 GMT</t>
+          <t>Wed, 11 Mar 2026 06:14:37 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQNmZNaFViTXFSQ3BWZmk3eThXM2lZS1dXUFo4Sk9sbkJjSVVYa2dZNDBjcTlHczZHZ293bTZuRXZWbjZTQTJzamRvN2x0UzRCWjV3MHc4cDJDZm5sTmpIY2MwMVlscVpsWWlveGNmZTE5YkZHcGpfTFI0VHR2WUVQaHh0ZUhldUk1S01yMjVMMzNyU0l5NEZ6ejllcWZMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOY2VVX3hZb2dhSVBfWVNoTEFYckNJdDBWcmpXRm5waHp4aUN5dlZRTmtxbkU0UFUtc0FmdlJBVnB2Z3lKZlpMa01OdlloNktmeXdqVDFZeFFVMFh5N1JINGpDZXlhbTF1aTR0S21NbGdkb2Utb0JrQ3d5YUxVRWVNSXJsTHVNX2xwbmstVmN6dENXbTJtdVVyMXp4UW5yOUc4amYxS1ZUQVRwd2NBa1phaVhodE54YkFYTnhuNkVxTEJ6TF9ZNmg00gHOAUFVX3lxTE5RYW9KS1A5eV9KNmRmcGhKVlR3NFVnTTg1S1B0dTdveFVUdGhrOXl4ek9WS0ktd0VoY2NyeGlNQ2JDNzk5aS1kcVc1N19mWUNpcEstTHVrT1U3VUV3b0Yxd3hKZndBY05ac0s5WGFpZjNxbHNVSEkzdTBDTVByVXZrY0p0SjlfaW9BOGdDc1E4QjFJd3lqckZfeU5OTFNBSGoyVUR1dHlLRU4xOHJsdlZVY1l4S0c1bmFkTVpNaXBPZWNPZHVHc0h5UWJUb0ln?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1021,27 +1021,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Maritime and ports businesses push for global shipping climate deal - Financial Times</t>
+          <t>Pound Sterling Higher as Trump Signals Conflict Could End Soon - CurrencyNews.co.uk</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 05:00:23 GMT</t>
+          <t>Tue, 10 Mar 2026 19:01:02 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5ILWNVd1JISmNfNmhCRXduaTlicllHVmhoM2N3Y2o3cW5lQ3RwRWplQlljd1dyQmt2MG4zT2Z2ZmdfZGtBTTRMQXRINlNFVUdmS2ZuZloyalMzUDJYT2E1SGRadHFuZUpaM3p0ZzduTGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOLWtueUFVYzRCVjNXd0RhNHJGaTRHMWNzSHJHelVJS2ZCTDFCUTN1UU5DNzZBOUxlSFF3WGtycFZfb1M0SkVid2JYUHVKNzNrZml2bFJaOVhDdDdoRUg5RWVNaUpEb0l0MkVUeXN4eW82STg1LXowcEt1QzBsajMtd0RlQjdxQWhrZUVMYWd2Y3dZTHo0TnZLVnFWRTdlSk00WlhIMzRKSEE5NTU2N1I2TkR1ZDJNNE1MdFAw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1051,27 +1051,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gallagher flags widening protection gap as UK supply chain shocks intensify - Insurance Business</t>
+          <t>Oil Price Spike Could Crash Global Economy - Novara Media</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 07:10:46 GMT</t>
+          <t>Mon, 09 Mar 2026 19:37:48 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNUVJ2TU1FUTNURlAwTEJIOHVpV2pmUHJZWEhPeGx5NUtHaGFFVGNxQWhNM2F3dTBQZTF6bXpPa2VxemJvVFp1MXBIdmFyd19uYTNEYWMydUdkOWQ3NVhWZXd4STFCbjQzdnZidE4xZ3JKcG5TVTNGX0pWVTdSeFRxQjBpQW1ZQ2lGM3N4a2FYdFZKS1JwdEZWc2tESzAtNE9DUi1MeWl2b1Rtek9tdExwXzNZZkx1aEY3Qkl6bEZZaWJJRXA2RHhaamltRUVkWFphZjkzcXVxbEtlN2pMNXE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNaExfeldpU0ZtSzVZNkZlWGg0N3R0ZllBRFRDYllzZ0lhdnFPUTlLS05Tdm5KVkNpYlFVN3AxYW01WTZRdndITFc0cDZXMjhnNzdsejM2Q2drU21PZmE1TkZUeXMxT05ocXV3eThuSHBIanZ0c3lkTWtOQkp6TjA4ZzFHb0I?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Match Gallery: Defeat at Port Vale - Bristol City FC</t>
+          <t>Iran war cost will be passed to consumers, shipping giant boss tells BBC - BBC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 23:52:20 GMT</t>
+          <t>Wed, 11 Mar 2026 00:27:15 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5NZTRSOUdDOFM3M1dSTUI0QV9mOTFzNEsySGozekNxa0ZGSGYyTVF3OWJXdzRGMU1yakpqYzlkcjBSNmxPQm0yc2FCbHMxM0M3MG96Q01hczd4UkxjcmJISW0wSjc1SWctRFpUZWUyNVdsejg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5kZWUxX1NsWHNaOFpaYnZveFdKWUdTXzVJbkVjRWdwVmNja1U5SDJSdG1Hb0hnaF9FVUlNMG1KUzItU0lVZFZrNXpIb0l2ZkJPX2k4UlpQbjBJQQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China calls for vessels in strait of Hormuz to be protected amid soaring shipping costs - The Guardian</t>
+          <t>China warns Maersk and MSC over high freight rates from Iran war - Financial Times</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:13:00 GMT</t>
+          <t>Tue, 10 Mar 2026 11:36:51 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNbDJyQUJRelZJdEpYdGtiOHFxTkZhTHgtMGVyT254RWlNbWFFNWUtdWtGLXg0Tm1SSUhDSi0zSjR5aWZmZXFudnRFQ2xDU0V4ZUROQ3g3aVR6OHlNelRKY043NXpkLVcwU1hzS0UxUUVKNDVJbnpta1dpaWNGMEFuWFpSZGZqbWN3NlQzOVZISmlOU19vV0ZaVmY4T3Rxa0NTaU50ZDdqTW9kaEE1eEtqTFJ3bWltUS02RFJUQ29B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBPVU93VDJRcVZOSk1IVWN3MWZYcFdMUWRsVHhDZDFaNnI2eEZNc2pER1ZvX2pzUlBxT05mWXVVRXVzLXh5V0JYX1QtUFdjVkhhOWROYXlVSUVtcW5aaGlkMGZxWG5udUFrOXExSzBTZ1I?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US manufacturing growth slows to seven-month low as tariffs and weather hit exports - The Manufacturer</t>
+          <t>VW to cut 50,000 jobs by 2030 amid Trump tariffs and falling Chinese sales - The Guardian</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 02:22:06 GMT</t>
+          <t>Wed, 11 Mar 2026 02:30:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNa3JPOUxodlFnNHpaN1RvVXVOVVhqUjJoR1JMNG13WVU4UFZQdGFxXzg4NElBdFFmbFdJSU1McGE2ZHpoa3o0SnBtV2pJZkZqblFORUJrQl9VQVJ4MkFja0N3b0Jib05yQmFRV08yTWVaN3g0eDZxNVRFMEVuOGk1SWxSbFFJQngwcE5VMl9Cc3J1Y2d0Sk9KR1BIM29FZEVOV2lMMHFOMHlTazVoRzBBV0RHVUUxakFvM3oxOEl2UkYwSDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSHBiZThPYTc3WXFDZkpVbFk2dVYtQ25pWXlUc2RXS1VaR3lXWlR1a3VITUZQa0ZwNERZVFRlUVpHcHV3dFJLNDN3SUR3X1ZELWpiNWpIRDRvVnJ6cmZPVFFzYk5SWXoyN2xUU1piX0RXSWtWUXFNMW9RaXpWRVJBXzYtcF9lSVRDVUFNcEFkdmhxNHYzUUhzek91b1JYZzNiTkRZ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Taxi zones with different tariffs may be scrapped - BBC</t>
+          <t>Building Rail Baltica: A €1.13bn Supply Chain Milestone - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 13:45:04 GMT</t>
+          <t>Tue, 10 Mar 2026 17:40:24 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1HNHdrVm1leW95RXBnMDg3M3FxZE1iVkdZME01NmViRFdVSmJON3pKREFkbHJ6cWVUQ243RzNHYVh4UnFmMzZaLVhVWmZ5dlZacGlsaGxZRVY3Wmda?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPeUE4N3hjcWptUDdRUlJLYkg3b2tFRXBlZW44ZmU4WXY3YkZneDIweE1fVGoxVkQ1cnF1Y2gxaTlIaEt0OVNDRjFReE00eGI2ODlTdkdhUWVvOEdoLWZlRHlmWXVqVkxVb0dfNWxncFlYSzdlTnM1bG5zR245TFVXVQ?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US could owe €110bn in tariff refunds after court rejects Trump delay - Euronews.com</t>
+          <t>UK manufacturers to save millions of pounds a year as government removes offshore wind energy tariffs - GOV.UK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:54:38 GMT</t>
+          <t>Tue, 10 Mar 2026 16:05:37 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQS3JXNjRITHVvaVdEenRPYTVWUXJfaWlUSmRGSndHa1MzcFZpajdnbzJiS3dWdUV3c0FubWU1WjlLRDE0VVVxWWVUOHpKYTVwdElNNjF3U3BwOFRBZkdsSGVmRUYzUjlIamRkUmhnczkxN2V5Z0lQRE1mX0hnZEktVm5WQXBBSXBuWmd3X2dEN1lfUUVCeXF3S0dLNkFCdXN3b0VkdDZ2MkhvcURXSWdKcUl3NmRxcjN1WEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOUDZONnRkT1RuR3lqR2JTQTlWVlFwOHFob0tjbHNoSWhQVFJjdWtKT2JMZHotanZBcVgzNE16QzlyZDFyMm5ONldsRnZjMkNwNHFhanhvRE5HamI0TGQ2bHdkTG5jcjg3TGZzSWJFLTZ1YXpVV1lMTFBkRzcyR2dhS0dNVHBLLW1vZm4tV0FycE9ZbzhENWJyN01ld2pzSmx4YjhSeUk3clhmTjdmMnZ5bG9tMEluLTFfVGtxajN6cnUxVFcwWTlxc2VwMGdhZmc1cEE?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How Resilient is the Global Food Supply Chain? - Supply Chain Digital Magazine</t>
+          <t>Timelapse shows fall in shipping traffic since start of Iran war - BBC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 17:48:13 GMT</t>
+          <t>Tue, 10 Mar 2026 20:36:01 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBLRE9JdmhxT3JhY1Nzcnk5M2pneG1ld0JUM1dpMURwX3pRbXJ2RmtYcVJsektHaFFCTW11WmY0S2dpMGsyVVM1V0MyMXVDdXhiakx3ek82WXJzWjNlZXB2SXpFNW95V3JnU19Kd1ZYWW1LOVh3d2xsdXFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1QSnEwRWlWZjRZMk9VOTZwUWpObHAwcTF3VEp0WGZ3YlZ6UUd4RS10QXhjOVd6UUZ5dGxJUFFaS2UxUTBWZGIyUlgwLUxaZlU4Z19PdEU4UWRqUQ?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US sanctions Rwanda's army for violating Trump-brokered DR Congo peace deal - BBC</t>
+          <t>Gatekeepers publish updated reports on DMA compliance - Digital Markets Act</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 10:30:12 GMT</t>
+          <t>Mon, 09 Mar 2026 13:36:27 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5WN2psQ3ZEYUlaNzVHVTZXQVRIU1BjT1h6Nm9ZaHE4a0dlUnF4LXJCcE4xa3NybWEzTExleU5TWDVvcDhKMm9GQ1NiZnhmajJZU24xS01lYXpfQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOLXduVk5qTTAyMzRDSW9hREEwUHhZQmR1MGtrMm9ZYlhYQ1VSeF9wUVFSQWNIQWVvRDdXSHQzUGNQN1RjeUNFTDBwZnRWUmVkUWtyOEZFcm9hWnB2WDczcDRmblo3S29hSnZpNjg1WFdvcXd6ZXJEdlVVMU5lcUN2OG1GQlFpNzZuVENRYTFsb3hybG8tdlIwUUJYd3Vqb1BPWjhBZU1QejM?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CSconnected announces £1m investment in final call to supply chain development programme - The Manufacturer</t>
+          <t>Derby suspends Pakistan and Bangladesh recruitment as UK compliance pressures grow - The PIE News</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 02:22:06 GMT</t>
+          <t>Wed, 11 Mar 2026 02:48:45 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxORm9Sc2V0Qmh2Q0RPMFlDcTlHM01OT3dKRlBmNkU4c3llZWZrX21XR1BQZnBldXowSktrNjV1cFBJemsxZG1PWEM3WlVwbzAzUXFZMG81bFRsekdhdEZMZzZuSFVvMF8wdHNoQnJKVGxYcHZtX1pJQ0o3eFhkbXdDbHlYVUpSSlB4WVBmRHlPUzZtdjF2TGF3YzRvNmRrQ2VJNWI1Zlh1dldLZDNSemh0YVhHT1dSSURFeTRHSEw2Q3VPUzluOWUwbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa3JONzdZdHc5ZHliZHFJbFFWUllSaXFyU2stbmg4QzdXZVp1bUxGNk1OejlaQ0liMnBrQld0ZEFaR0dpYXhETHRxSUt0YVZ1YTZXaU5PRExwUC1oZ1B4NXhTd1gzaVB1bFVQVnZqb0ZNbkJwVkpobmF0S3pYb3VnZm1RQl9BYkhSQzNHWnFGWGZHY2YzVnZlODhnWkJMdHoyU2hhNWJfbkRJQQ?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Watch: How the US-Israel war with Iran is jeopardising shipping - BBC</t>
+          <t>Trump's 'show some guts' comment problematic for shipping - Seatrade Maritime News</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 18:49:50 GMT</t>
+          <t>Wed, 11 Mar 2026 06:18:56 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFA2YkExZkVTazFHSjR6dW56UE5EeDFDbVlHZ1ctei1yaDJ6dmZ1c3d3MkNTWFJCWEdKQlh0cTNpaXNkOEljbXJlbWdEbDdnWTB4T1o2QjF6MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMThXX2lLUkdfQmdZS2djNTl2cjJwclVPcm5VaVI1SVF5ZEZzaDUwYXFpYXlmNF9VNmpzTFppQzhia2xlOGlVendHMENITlhmTE00VXQ2LThqNWhRX1ZEMHF2RlBBQkk4ZVYwOUhwaDZoSXdGZm5xcVV6dFlEVFU3cHFnQ1VlVGV5dDh5blZMbFowTWE1RjM0a2kzZHlGYzA?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Maritime insurers cancel war risk cover in Gulf as Iran conflict disrupts shipping - The Guardian</t>
+          <t>'Self-defeating': EU and US clash over Russia sanctions relief as prices soar - Euronews.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 17:37:00 GMT</t>
+          <t>Tue, 10 Mar 2026 14:04:57 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNSkZrQzBKdlNHNnVZUWotb1NvQnVqMUF5eHFYam1aX2ZHYjQxSnc3R1lIeU9QRE5nQTRaVTBDOTNURXpxMHRyZlBCTmMwZERXM2NMbEZvcm1VUUk0WDR1cjRLNm92ZU8zbERrOGxrekx5cDAtbXF2U19tcnM1XzNPSGREX29Nd0FnUUdxYzV0eFZhVXlHMzczdFRZNTlEWmtLZWFjTnpWSzVRVG5vRXZuUjRBLUdnUFFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNbzlRa3ZSWlZKeE9hMGJVcDhoaWhQTGdQLXRiY2NIY3hiZVNQVm1WZVpSVGZzTF9PT3hRSjA1Qnd1d3RkbHQzelhYOEMyU0ZLQmg5eWd3dlgybjd2eGFGZUtGNG9VdHF4OFBrUmJUSmRPc0x0TkUzVE5tbEhXWlpUSWprNm1ucXpLN20zdnV2Nkw1UGJsRm1JYVFBc0ZJWjZOOFY2dmZxTHdZbkdPODctTXFpTk9wSWc5U1pScw?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DHL to build carbon-neutral logistics center in Germany - Parcel and Postal Technology International</t>
+          <t>Trump’s tariffs mean more cost-cutting at Volkswagen - politico.eu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 17:00:21 GMT</t>
+          <t>Tue, 10 Mar 2026 16:46:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPRWNCblRxc1piOWV3NW1CWlVNVEFyTEN0M0JIVm1vOWlvSTZ2ODY4akRlMk5uV2tfaEF2ajNMSU1lOGhOOXlpSGlQNV93OE5fazc2WTQ5emxST2dPN2ZFRDg2QWlNNUl5akNjUlI4OTBOQ3lFS1h1XzlCaE1zdERIcENFSzN0dnB1NDgyY210U05BM0l5cDA4Mmtib09Lakw0Uko2VVJxRDlOU1doejRVT3Fqck90MGpyOVNwUTl4dXEyV0NaTThTM19NcVdidjRYWjNuYUdWdXpNQndPOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNY3pkXzNDT1JvbzRJaFE0WnEtMVpVWDZUbXp5cDQ0X1lDbEFiZmF5V2t0VmQ2SU95QmFSbjY1cjdKZWhGYWI1U01CS2RYYkg3VFQ1QjZsV1RNa1ZjYVd1TmpZaDdMZ2NKZTBnbWQ3aVlaaXZRclZRRTdHQUxQMmN1WTdxbzBuZ0ZETU9GbURNalNVQUJL?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hormuz crisis ignites Chinese shipping stocks and futures - Lloyd's List</t>
+          <t>How Osprey Approach is supporting Hannays Solicitors’ long-term compliance and operational confidence - Legal Futures</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 13:09:02 GMT</t>
+          <t>Wed, 11 Mar 2026 00:01:06 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOZGpqUTl2akJlMkQyTGc3NHZVOGtaYVJhMy1vWE42SWNhb0FVWTJmdkY5aDc3N2VsY0FhbEd2b3I2dnBsdThSdXlaa2ZBRGNhS0x6dkREQmNMVEx5NGYtaVAwYVp5VDQ5bkZZY2VEaWNERmVKclN1Um9jeWhwZ0tfeUQ0cVQ3ekh1WXlYTDI5WjFiNloxNS11cmZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQaV9VOUY0M2Y3SWE0OXROSWpoSWlQRlNYWHhtbTdUeGVmR04zbDB1SzdsNDlWREN0WHNpTER2MmhrWkg2YXZ6SV9Jd3pBLTlFYUJJbFVkT1d0MGttZDM3enNOLU5HMTJsNzdaM3RqMFllWWpmWDBYZzFKaDJrcktxNDFIS21UQkZtZUJldlo1OXB1RndZa2FWNUtfejhwemh2ajhhZm55WkRCcHhlXzQ1V2hfcWdVZzd0ZVlKWjRoa1YwZzNpSlRMVmpScUo3cU1lc0EtQUxtVDl0NENCQUtR?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Retail fears rise over Middle East war supply chain costs impact - Retail Week</t>
+          <t>David Squires on … FA Cup magic for Port Vale and a close call for Mikel Arteta - The Guardian</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 06:39:05 GMT</t>
+          <t>Tue, 10 Mar 2026 17:32:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNVlNCSzhWOXJ1Z3kzRkpzWG42YmhsNThVZmJVM0tpd2NqaVlVRk9PMldPMFg5VGhVRkN4VjZMSkRKTS15SmlzdnBzcE55TjdRZXBOLUJfZVRYU3c4SHN6MWxUMmRRbWNaT0tZTGZuTkNLbV90LUJOV3M5Z2p5ZmpYVmpySXYzejRIem52dDd0RjNvXzlUXzhnbVkwUzd6UlhCVURoVzNhM3I3MmVsWWhobHdUOTBBQlJJSGF1MENn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNYXExNW9fQzdPeHkxUEI5LXV3b3BUSGZNbzduQkZvOG5aQ21EMVFxRVlSWjY1ejRjRVBUZnRucGJ5bnJNTmNDOEJIblJlSGxQb2M0UTdWOVR2RG8wNG5VUm81SXRQelI1WWV5aW1WcUlHUmZYNTM3Y2xfT3BjUDBiNWtKbnhDWWhSU1VQVWVmTlFzb1F6MTJvX2l3ZVJLaFRUTmR1eXM2MFQxRXpZLUlwQk9IbUg2NHJp?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Explosion after drone appears to strike fuel tank in Oman's Duqm port - Sky News</t>
+          <t>BBC visits key Dubai port in Iran's firing line - BBC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 12:05:24 GMT</t>
+          <t>Tue, 10 Mar 2026 17:07:01 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZzlFdFo2czdMbU93Qi0tODFoejhBaFQzRVM4a2lvTldwMzZ2X1lDZWZiUFdqU2lXajNzTnZNVWFPZlF0ay1IYWc3Ql9DM3h4dmNSREdjeXVvRk9nekpXZkg3dGZsWFNuWWtxdktrOXVDRXF6WDdNdGRXZTd6aXV6WWxTeEdSa2t4d3J0aWVRYWFiRzUtbl9WdHRXZmN3ODlla1dOY0JOMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9UblRfY0pUamFVODFzVkFEMTI5OGRaN3lDNnlncG9pMUpGTzBqQU11YUNmak85dGFvd0NnczVxWmQtOVA2QXVBbkszc01YbGJuV0ZmQ1BDUQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tanker heads to UAE port via Strait of Hormuz to load oil, sources say - Reuters</t>
+          <t>Senate Democrats introduce bill to shield small businesses from Trump’s new tariffs - The Guardian</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 04:58:00 GMT</t>
+          <t>Tue, 10 Mar 2026 17:53:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNR3hOX3BhQzEyT2xKd3dlcmFMLWp1ZmJuRjNPeXNNQ19HaE1KeG5aT3V1cm41S2FDWkY0RVFnWkhHVUVWYVRGVXNIQURzcVZVNGh5aGVHZmRBbk9Qb0p3aFhNeEdaQk1DVVk3TUlGRjVGY2ZZMnVGQWd2ak1tQzc2WXVRTHFUR3dWNm1XbEFCX0hRcWNHUm1ZN3paVFU2dlNuX0xwMllFUjBFYllqcHVhc0ppODI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPdmNzMTJNejdma0JqY0NqMW56QUJxUUlGMW84MUFaM0VxNGJhclpzX0F2enAwUzhYVWhXUnBneUdULUJFR21Eb2lDa3JqSF95UC02SE5SMENua0J3ckpVLUVzUWJnU3VSLVVpQ0hzUXhjOVYyMGdHLThPYWRWYTBMSzZFZS1IQVZzMXF3YjRrT2NMbUhDQmx4VmoxcjdrYWFTV2c?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>'Trump introduces new tariffs as legally shaky as those struck down by the Supreme Court' - Le Monde.fr</t>
+          <t>‘I was absolutely gobsmacked’: Port Vale fans react to unexpected win against Sunderland - The Guardian</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 15:49:34 GMT</t>
+          <t>Mon, 09 Mar 2026 20:08:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQb1NPVE9JWWZCVS1FNDk0SUpqZkxGSnZ5VXA1aG9mVTdraDV2SUpCbVF1Z2lLTmx2WFpaRWtCeWItQWZ1NjRRQVRraG1mUm9sNXE2NFN0c0RkMGVoOGhaOEV1Tm85cF9GNHBrZ29pYlhZdVA2bUN4YVhUSHVXQ3UxRWZfMDdZTkZ4WGtxVEtKNWQyMkpYalhGbVp2OEZOOW83a3MxSm52TmlkV3RWcDZHVy1YQzVxTXk5UVNvNXp6aFV1QUN6bkVyQmZjYVRxVWJMaXctM3BmZFJyYlNqM2dBenlMeHE4SU9iSTNhUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQk85QktYaFdrZElYT0Zzb2RrY1IyMmpGa2Z1aVFHcnNpTFpUeUdNOHVta2xKWlhGQy05dVp2bHVaWks4RmhxWkEwcVZxNjJZZEtqTHRhQnpnX1VuLVkzUk5ZQzNqaHlOc2N6OThJRFhBRWl6WWkzZWJ3Nk4xeDJyN2JoRXRvUmtPUTJRQw?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania and Ukraine: cooperation based on logistics and investments - GMK Center</t>
+          <t>China exports surge despite Trump tariffs - BBC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 06:00:47 GMT</t>
+          <t>Tue, 10 Mar 2026 06:16:02 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZVZ4enhqYTI1RHNhUWRFQms1LWZqUGFSQ2NPc2NXV28yRHZCWTRXbVZWUnNYWDEyOEVJTG45Q0l4VVdHcFFhYzdNTzVWSEJ3T0l0OTlxQlV0UTNlRVFSYmtZN2lBWWdMWkhqQ1pENVl4VE1Odk84cEV3eWFYSVRfSE81eGpCQVFVTGlRNVVOVktFX2JpN09kVmI5a9IBoAFBVV95cUxNZlAxaFBScXNtdlhjeEttenVrMGhBWVVaUExhWXMtR3NSUnVHakpURVVlNjNuNWZXSk1YcmVUcFlUVlFfblk1ZDlXNlMyXzVIRUlNbTBra19GQTBuOEhyaFNETEZZRDNiLXMtZGV4OWRaSFp2WTFIdGJzZHhGTTBGRmJSWlB4cnZldGFjZ2ZFVzdfMTNTaGtCSEotdVgwZS00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5JUEJwZVE3UFFZeFVFYV9BUHBBdVE4YTdoX2JIODJTSWEwaTFJcmZBLW9oTjliSjNrV1g4M3BhR2t5SXFqdUVKcmladG96U1U1Nlo2VHhOcDlTdw?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Small businesses left confused over state of Trump’s tariffs: ‘The level of uncertainty is crazy’ - The Independent</t>
+          <t>United Kingdom: Additional Compliance Obligations Introduced in Updated Sponsor Guidance - Fragomen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 19:35:00 GMT</t>
+          <t>Tue, 10 Mar 2026 20:55:06 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNMEJ6bGE4VGRlVGZWTHVCTUk3dUhtUDlZR0UxaFV5X1NWc1V2d1dPbzRZNjg0R0tpMzhodDgyQldtT3UtNU5zWVMtaDdUbk1tVl91R2NaS25RYUtmZlgtR0pDNGMtX1JzNzgtN29wOHBELWplXzV5WG5SNFFrdFIzbV9zS1EzV204MUJlUFFWLUM2ZG82QTRQZ3pYSTFRd2tuTXVCUWk5VmNsTXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQOTdZQkVSdkpfSjE5V0NDejN5dzdQblZJYVpoVFNsa1FoV1BDMFprUVRoc3BHSVJNdXNta01adE9GcFJMN1dUZzl6blRFNnJ4VlppVllGMmw4OTJzVGNDZFphSmNYRElsNnBwZUM1WHppRU9YTXdObnRaOUJkTFdScUhKalBrM3p5Y2FGQlFDekZrUC1uSV9JM0N6a2RoMTNiTEZDZ0JKVDcxeFhJQ0FOM3kyR1ktdGpJMDFEOGxBTUNEZlJV?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Marine radar testing facility proposal for 1000 sqm plot at Ramsgate Port - The Isle of Thanet News</t>
+          <t>Putin gives Trump easy way out of confused Iran war strategy – and he might take it - The Independent</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 19:15:57 GMT</t>
+          <t>Wed, 11 Mar 2026 04:01:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQRHNkZElfSU9nQWJBSEZpcGxXOGlIM01nc3E5MVFsMmJlT0pqYjUtMHg0MlZNUVJINlBhZ044U2pqOXB4a1RjWTRuMzJRQUt5LUVPM1ZENVkzSWxoZjhCdlVtMURncmFOekZPamQ3NzNMalByempqWTlzMmxONUFNNXY0anJhN2x3R1dzUldXSWVhWmdDamVEZkJzUVhEWUQ3cWtEMS1MU2JFeEI4eFJ0MmcwVlFySVJi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNemVuYVN2aFREVzlSX1ZPQ0VESXVMTWhZMkNVejhDZVpicmRzSWZaQkJGTzh4MExXMmxHWUVZN3E2OHVoSnNGb2ZiOC1TVkxiSm5sek9jaHpVZmFpQ0Myck16NktrZ056ZjVJbHFJSE9oeVI0VGdvSmxneVcyOF9HWEwtT1JrTlB3R2pmcm11YmE0YjExbUZUT2ZfS0F4d0hwLW1ZZnZ4bXBKN3IwYjVsOE5KalZNVm8?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>The oil price surge is just one symptom of a supply chain network that is not fit for this age of global tensions - The Conversation</t>
+          <t>Argan lets 32,000 sq m at Île-de-France logistics site - Green Street News</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 16:50:08 GMT</t>
+          <t>Wed, 11 Mar 2026 07:22:27 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQSjNtRDNzc05sU21PdTVCVjFRaTNQRkJJa1puT2hUeHk2R29sNU1BbUtaYnRQanBEUnBsczgxRG9IN1VlMkkybl9zZndVeHFGclFRcG8zX2lKa3RHZWNMLWNHamstNWNuSnpVODkwc0pWVG90cjRsb1FBcVo1X0ROZGRpRjVaMElTb1pFTGNNWXliLU1pZW1ISTBwWE1DMFo2LVNSM01UblA1OXkxQWx5d0dDV2dLLUUxbFdZUmtSQkhkbS1VeFFnWFJhUDFxZlFtbTdJQ1FSVDMxQ0ppNTdZTkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPM2dYektqUE5ScWtfWlZfMW9ORVVCWW5EVGtJanl6UXhkUi1OSWhBRFk5OENXemxTS1BXQ01fQTZEMnRvR043anlCNm9hbEhNcy1IMmM2MGhhNDA0V0hjbGU4Qlo3RGhVZ1BhZXFQbVN2QkpqbjkxWXlSZEQ2c2ZUY01EYjI4UU1WNlZLTlg2bllOdXR6?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US tariffs on Norwegian seafood could top $120m, refunds may take years, analyst says - intrafish.com</t>
+          <t>US Navy tells shipping industry Hormuz escorts not possible for now - Reuters</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 05:22:29 GMT</t>
+          <t>Tue, 10 Mar 2026 20:01:58 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQcnVLT0luNHJHMHlieVpmOG9zZVI5WG5MWXRzd2JsLVlBZFRlb0drMXNXMWFmYnhjUUR2YTFGX1pMVV9lOEhRS3FMMnhjdHNpTWpSSmNyR3lEQmFvNXJ1V2VIcEpVLTZWVWQxczVyNWlhZmlIQ1pFWHhEb0tsY2hUb0RmbmNrSE9EMWN2bUZNcS1YX0pnTmFGVklOMjJlN0NvQWV4dUswSk1wRHhjM3drSjhxVmlySkRMSUdaUWNrejIwZGV5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOWXN5RnJ0RUQ1ZDlvLWtGbUViVXV5NXdiZ0RWOHV5UVd4aEdhVTF3YUpuV0U2endhTndKNW5PVWVlVEcyam16dGNuMHR6M1lySXlUM2tVUnNlMzRKb2h2LTRxMzRQY2dxUzM0X0xkQ3ZJZEFZeWU4VXpPTjJ6XzlUcG1QRVFzQWJTSFFaX0dzVnlUam8zeHViSF90RTFRV2FMX2RtQjJnZGxMbG5VaEwzakU2eU9UdmRP?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Trump ponders Plans B to D after his favourite tariffs are taken away - Financial Times</t>
+          <t>Strike Paralyzes Shipping at Antwerp and Other Belgian Ports - The Maritime Executive</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 12:31:03 GMT</t>
+          <t>Tue, 10 Mar 2026 23:06:38 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBuZ3hqNTRvYU0tVGlsWm1nbjMwWFl6cDZsa2Mxb0w1VjV6cXpyQlRnWk1XSDNXcGZjbDdpTFQwNlpyU3k1UV9RRjU5aHV2Y2NpSVMzOTQ1VlJjc25rYXU1RGtfSDMwdkIyaTVieE5oMGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNXB2eDVOU191QU0tMzhKbHN6T1lyVzRIYW8tUlRaOG1CTWxvaUY1R00zQUNpRWc2RTlwVXVmREE1cWpEYkpZa29DaHR5SGtlTnhCNXNud2hHanAwWG56TjZFZFpWSFJzZ3ZFT1c2cEYtMk9WN3k1WUNjODFtOF9jWUV6ZHN1NGt6LVZwbkhjZGFEbjQxYzVGZ1ZMU1ZKajMx?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US sanctions reveal Iran’s growing reliance on Turkish companies to expand drone and missile programs - Nordic Monitor</t>
+          <t>'Extraordinary reasons' for port disruption affecting rugby fans' return ferries - BBC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 23:34:51 GMT</t>
+          <t>Sun, 08 Mar 2026 18:42:48 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQdlgxQkxPMmhpUGgtMDVGaFNSQ2d2QnpJdnl6SzliZkpfT2R2djIzbWxVRldwelFYcWpUTEFxem83T21yUU5hcG1iZU04eFIxa3BSTkQ5aEhUanljdzRSLUJXUEQ4ekRCRGo1UmxZY01iZEJVTlZuWFRacUJZS0tINkpIc2d3Vjg2QVI4SlZxM3cwYWc4RGkyWkszM1lBZi1POUdhbDZlOU9vU3lzVzZicjdnaUw3SHZ1QzlTU1FPdEgwT0dEN2F1aDllWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE00aWhqRTM5bDg5WDdEaF8wTWVIODZuRmU3WTlMbkVidXluQ0szNy0zeWJVUWVQeWlTXzUtWXU0aFdjbEpUQXBxb2FidXBTekFRMzByck50TWdVVTFT?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>'We have to win, this must be our standard' - BBC</t>
+          <t>Anthropic sues US Defense Department over ‘supply chain risk’ designation - Jurist</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 23:10:54 GMT</t>
+          <t>Wed, 11 Mar 2026 04:29:40 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBNaUtrZjJ0cTVyYUZsdlN6Z0REVXBsbUU2Ykp4SE5UVmR4dzlSeWxiVlM5bFlJR3hrMF9oYk9QOEVDeEh2dUNiV1FQbndyR2lQakpyU1ZqXzBwTVJ6OWhXb3phaUhwQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZGE5S1p1R0ltZU80UG5pVHh4X2ZTaEFXZWktSmRUS05kT1p0YUY1Um9RNWd0Q1Q5NElMOGdseTBtTU9ScndvQk5SclhQbHpkVE9ZZFV5ZG1oZEpHblRyYlcyc3BuV2JvV2F6SXNmbm9vN201ZFc4QlVVWmxPWHRoYnNoMEVVU3JFTEh5WFFOZkV6aUR4ZTIwUlY1V2RkdTY1YV95amppU1B6b0xE?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Report: MSC and BlackRock Push to Complete Hutchison Deal for Port Ops - The Maritime Executive</t>
+          <t>ROSHIN group and Agility Logistics to develop Jeddah-based park - Logistics Manager</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 00:35:35 GMT</t>
+          <t>Tue, 10 Mar 2026 16:22:32 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQeW5aVC1HSExCWFdqcWd2aEctY0VNMFFFZ2I0dTF2Y095RFpiaC1mWWZLU2JQRkVWVFpEWVFjYXM5dm1fSUV6T3VXeEZad2xFYkZ1SDg1ZTlOUU96YTE2NkZrdXU0dHlPQ2RzWUc5Ql9Ec21Od01EczlIMWlXZXR3TkFvaDdMWDhERERRa0ZvYTh3N1dMUzM1OXlDOW9iXzI1cklIZEU1MWUzMU1w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQTjRhTGJIc1NVT2VaM1dfcE40aHdzeHBLVWR4NXJlWld1cktNbkJKS3JzYUp0clA4anBGN1EyT3A0UGk3RXZ0a2FVWFRqS3RwOWlxbFJSRnlwMnV6bDNPMnM0RnZfSXpYel9YM0NoallmMzZuX1NGV0FmZlM3Y196UnY1S2RhRUQ4QXdFdjRBT0FSOGluU19JNW9VSmwtZw?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Moomin and Pippi Longstocking get supply chain transparency upgrade - Retail Times</t>
+          <t>With Trump’s Tariffs Overturned, Who Gets Refunds? - Bloomberg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 19:28:50 GMT</t>
+          <t>Tue, 10 Mar 2026 18:48:36 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNZWlMbXpNODRpcnQ3X0pLNzdtOENPeGRMOE9ORzVoLThhWXpLUVVwYzFQcmNqVS15WnlyTC1DZEd5blluS3V0M2Z4TWt5ODlpTmFIY2FkR2FzNmJPUGp4ZEN1WGJDdC1ENVFWSW5Na3lMb0hac0pDdUl6TlpCWF9QQ1dRcnFpSENGMHdFMEJ2UXh4LU9JdGJJSGN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNNVpaVE1GS0I5SnVyaDMxQ09ySHY4OGNlSTBSM2tLMTlHbmhTX2o2TWFUSjZ5VEdiVWVBU0dIdW9XeDJRQ0ppXzMtYUZieHhiWExMb2dxWnJrbmNiVUlGMFhCdGNNaDlSbnl3d0pCYk55cWlpUFdvd0NLclBVZjNGcVpTODV3T2JyNkNMckNJLTJrOEstMkY3bnlaazBTZk9kTmo0Mm5GS3M5dlR3VkVUWHZ5UHZNaWJlOHRPM20yTFgxZ2s?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shipping between Red Sea and Europe &amp; North Africa? A Contingency Surcharge (CSU) is coming up - Hapag-Lloyd</t>
+          <t>Elevating Compliance Readiness in a Rapidly Evolving Insurance Regulatory Landscape - SIA Partners</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 12:27:00 GMT</t>
+          <t>Tue, 10 Mar 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNWGk0RWRDd0Y5eXg0ci0tU0poOGhkTUhfcjJnMlZBMjY3WkY2MnJObzNIckVqd3BCMUVFelpvakVRU3JVel9fUjMxU0ItaTBidlBHZ2h3cWIySUkyRjh6WXBDaWhGemFzXzAtZ3oybkxtX2xPVmUzOGpDRDR5aEo0VlRMM201VWxqdjJyaW1DVklOOGVfZlZLUUtHWFFvdllWRnBlWHgtbDVuVXZ3VXFSZVlNanQ2N1g2YXpLNERGMFktbktiZGxmRXZyaFVtbHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNU1lRVWc5eWF5Vm9JSnBjeldsdEV4ajhaT2VldVNLczZyZUZ1WlJfV21MUnUwWDAxaFZGQWFSY2tLUDFnQ2U5NHo3SjU1dFQ1X3lzeHFtZE9KUTkxcmpzOHFuZXJEZm1tdENaOGYzY0o4ZVl0VFcyVXI0N0VrWUttTVZLQUg1ejRFZkhlaUR5WWJmMC1nSWlZVFFfMGRsTjhORXAwZWd5QURYTm02TXprbVNUenhuTEhLUlR4Vi1uVXIyUQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ellesmere Port man who harassed supermarket staff faces sentence report - Chester Standard</t>
+          <t>People Moves: Hormel Foods' Will Bonifant - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 06:00:00 GMT</t>
+          <t>Tue, 10 Mar 2026 16:30:31 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPLW5qN1JNaUNYNW1qaWFRVG5FaWJ4QmRRNnRnS28yZHBsZW11bVBwdkhqa2V6TDFmc0NyX3JCR3FKVi1WNXdWRWtFSWdsNGtXRHIwV1Azb214a1d0VWpKUjlidE1SWmxSaGJVWVA3QXk4MkJLdGRzVWU1SU5nMmJkMl8tcklpNUM2MFpUSkw3ckpHemJGb2hjSElUbFBKbE5JNGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPS0NrbE9MdXUyVlJLd3E1NEthT2V4VFJ4YU5hd3JfbWZyMktUMlk2TlNCZUZLYUJqX2VZNU9MT1BQRndVVDMzeWY4REF5bUJsUG5pQlBNUmwzRjBCbnRQblh6QXQxN3hyWl9IOGc4TkNBTUwxWHNRQm5KTk1DN1dBNg?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,27 +1921,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Met police commander denies Jewish group’s legal threats led to ban on Palestine march to BBC - Morning Star | The People’s Daily</t>
+          <t>Slovakia’s Fico threatens existing EU sanctions on Russia, as Hungary vetoes new ones - EUobserver</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 04:21:57 GMT</t>
+          <t>Tue, 10 Mar 2026 16:56:17 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQSnkzWFJTTHJTZmFYSFcxSjhvS05lNHY3QzBiUzBhckxyRGN0eXJyaHpqUFQycnNvUktwMllValZkTXBfNVBiYlBfeVhzUXBiUkhUSGtvOEkxT3FOTGxld3FlLXNialNSdUlYQUFITUtKem9VaW5telY2NHhnNzlDb2FRZVBuTzNyQ1pxVVlVMWtGZmQtSE04U3lQMXh2b3lOcllyS1Y5eGFqbjctd1VZV0ZoQnk3ejBHRi1PUUxMQlhnRVdvNmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOaHBicU1QXzMzbUFxWTJ5cFhwZzRiM2p4b1czVUttcGtEM0dLZnUxTmpOdkY5OFlrUjBTUXZuWFRkcFVfeVhNbk9NVWNHVnY5NWtVdlVnR1cxRkhBczVXVXRlMGxpeFQ3UU91V0hFU0c0VTBPYXUzZWNLUk1FOVFBRU5qa2hTa1dOVHVRcWV3NWJLRFFiVHI5YldFdWs1aWVuRWtPRlkwNGQ3aWxnYy1xdHNtV1g?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1951,27 +1951,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Video. Israeli strike hits Beirut hotel as Israel-Hezbollah clashes escalate - Euronews.com</t>
+          <t>Electronics Supply Chain Outlook - S&amp;P Global</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 07:24:02 GMT</t>
+          <t>Tue, 10 Mar 2026 23:23:35 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRFFSbnNKT3ZVRzBQSk1DQVZ3b1pWWUlMVGdENjRwUUpISGlQZy1EZk5YYTByV3JEOFI1eXBGRmpqM3lhR2p3NUQ5TjJyazIySzE1LWUyemNZaUVJa2RXM1BhR0pFM0NJWHRQdUQwWDZ5cVh6UXJsd244dnpEN2JqSTdtRVBUcFlOZ1dyZWxfcFA4TmgzUzFUeXo3VzhOWmpOSDkzVFU0RmxYUXdodGRTYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPV3YxRVhYRFVyWDc2WDlwaURvalphZlI4MjU4clRrdGJfUDhjZEl1d2dMRUJTNDlIVTBoWFZDT1VjQmZGTE5DWG1PaFNkeHVWT0hBbi1iZ0RuZnZ0bHFoUUVaU2dXbm9oUU9DN1lQNUs5Um15SHhhQjNBbHU5SzhCcjQ2REpWVXZSdFhHejdMR1lLSWdvYl9DOVNIbWxybFhGZ0JwRnVCa0pEYi1WSUx6ag?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1981,27 +1981,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Women reflect on safety five years after Sarah Everard's murder - BBC</t>
+          <t>PHOTO OF THE DAY: TSHD Albatros arrives at Port of Devonport - Dredging Today</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 06:12:07 GMT</t>
+          <t>Wed, 11 Mar 2026 07:10:31 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1pZXFlaHcweDZva01MbDNMTURzNVd4YzVQOHFoaDBHUk1yMDktZUhoNWlUclIzV1ViVkV1ZThWQkpkRUFOVXNjakhFWjEzYm00ZFBzQjlNekhWWVdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPUFFQV2Z5WmNqZVNLNWtLTFZPMDhmVnN2ZEU4R19vZlZvTDVib0F2TEZULWNidGhfeC1Yb2lkRFdDbUtTV1NncWhaclBvUjJxVHVGSEkyM1FZbENuajlxRjdsWlM4RDJhWmhWcm9fZ3RLcjdpRHQ1YllpbzNYeFd1RG1wdXRHRFJvMVN2R0lCM010QXhMLUlhTXhMRXY2eEtMQzJJ?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2011,27 +2011,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>The Times Luxury cartoon: March 2, 2026 - The Times</t>
+          <t>Shipping containers to host pop-up art galleries in Southampton - Daily Echo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 04:00:00 GMT</t>
+          <t>Wed, 11 Mar 2026 03:30:00 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipANBVV95cUxQY3d2X1A4S2szQWVoVjdrLXdpVEpmZ211YVhMaFVyZzM0d1BDbnI2ay1WTXBsdW94S2RLMlRieThDRGRyVE9nY2NLNUxYRGNyVk5jaXZsU1ZJUmdBdHdaNlJZQl9YNWY4dENJRW5qeGpzT09QM2JWMmUxM0xYX2pyaWdnQ1k5Y0N0LVNvbmVZRG0tcmtmUklhTzhiRlgyNkRwRGx5bS1sbVFSZGJFMDFkeWRDek16aVo5bUowTm5QYnRaczQxc3c5MGlrTmlXaUprdEYyQ0VtbTh1anVCb3BvakJOT250ZUxHQmZoNDRiOHFHS095eV96eVc1bUdnVmZyUGhaRTJPQmxXVW9EdGJJSjM2Z0EzZXdJSkgzUEItbjdRMjdkSHZDRXk4MU9qOV9Qd25rbVJYSU1JczNjMGhZLTJYVlp4VEF5aHhBYmJpVW5sVDFXZEcwNWFxUTBEejhFMWFmRld0SjlXWmU0Zi0zVXpsX2Z2b2pTaFpGWm5NQUsxLUtERlA4VUNMVUUxQnVYTHhON1BFSGI0NUZFRl92UXFmT1Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNY3d5R2RocW1Pd2Qzd0EzbXYwOC04M1h4M2tjRFdROGFEd0JEMlhVWTZTc3RxZWhaTTZyN1VtOVNpYkoyUUtnaUlndkhpNTZPM1dDcUI2aDVxbHBTWU1YeU1PRXVRSlhRRFpseWpSeDZ2Y2UxRFhCYU4yS1ZVOW5CUW5xWWR0RHNTdEdQQzdBaGtYTVJ6QXRleVVaM3hWdG1x?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2041,27 +2041,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cumbria Police reveal speed camera van locations for March 3 - Times &amp; Star</t>
+          <t>Cosco suspends Balboa port calls amid escalating Panama dispute - Lloyd's List</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 07:10:00 GMT</t>
+          <t>Wed, 11 Mar 2026 07:39:45 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOaGl5Zk9YNW9vSnBLei1yUVUtdmd4anQySzBqcWF6Wnp4cHhHYzg0X3htUnZsZ0t4VnQ4WXlsc3d3R0k2ZUpzS1QwdWxWUlNscmo2TEwxX1d3ZVdRVjl1UWNPT2xXdjZsRjV2MHNVT1lHdFBkOUR0UXNCLW9hclN0OUJjUUx5b09GVG1jUzJ4dUN3YTdSa3ljeHVrbXliTmQzMmFVdnpGOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeXhxLXZUZlV0ZFVIQV9sNGJmY1NZMmV3eW1qbVlmOWRiVkw2V01ha3Y0UG9tV0tLUFhuNnE4MXZEWU5XTXRUcGhmUzBTbUdUVDdlTUt2U2V6d0hmNEwxcm0tQXlWOTM2c0pVbTFHbGpQTXRUTGNUMWlYTGJPNThZNmFLSVlxQVpUYmt0cnR4dnNoS3g2OVJGQnJUZTZLajlkQmc?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2071,27 +2071,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Suspect Arrested in Greece for Spying on U.S. Military Ships in Crete - Мілітарний</t>
+          <t>Middle East port operational update: Tuesday, March 10 - Lloyd's List</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 11:19:17 GMT</t>
+          <t>Tue, 10 Mar 2026 16:50:25 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNa3ZyWllxTjdubWR5Q0dkVnVQQ3lic3RsZW9ybktxcElDZ2ZxRzJ1TUluaGhLZ1VKN2pnbFRVY3gtZ0FWSnJLMUtfOXdjeEhTcGJZaENNUWFGelJmT3RNZ2luZFhIOFZ4aVBFNkxEaGhJem02SmZhdEtPU2I3RUREb1BHY0lTQzF1N0I1dWNaejJJNTVZem84LWw5LTQxV19ESUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQdWlsdVItcllmZFJwZFBxTEJ0Mzg5MnEwSFhsN0h6ZFpKeVRZYmZHX2dpLS1VdUlEN1ZxbUtrN2Ywc08tVFNIWUd2aUlhYUwxZWFmeWJKZDVfWVBOWUhlYnpZRUZ4OU55T2hCLXRUc2NYd3ZMWG5NcmVzVm9FaFVDdWVtSDA4b3laeUZHcjdVNkw5VzA?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2101,27 +2101,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Call for witnesses - Fatal pedestrian strike - Pinelands - NT Police, Fire &amp; Emergency Services</t>
+          <t>HMS Dragon FINALLY leaves port after Keir's dither &amp; delay over Iran crisis - The Sun</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 23:55:31 GMT</t>
+          <t>Tue, 10 Mar 2026 16:18:00 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNM0VvNjUxelU0QjNjR3owZzZyMTVKdFN6NVBLSGNLczNzYThwU3pKUG1YV2h5bE1OWkdDSnpINXZobmlVdWthVVJua0RUS1JwUjNRLVpTb3ZhX3FPTjlReWlSV19uY1NrcU1WYW5BS0cwSW1mTkI5VWxjdXZ5UGl6bk1FXzRLT21ZS0pNNzZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPUFE0RjVjN00wVk5EWUt1UmxaZlVrSEwtbnJwQnp5dU1UUURZN2VpME1ES3M0eTBvb21ZRDZXUDAtRFZVcElTWDE1SHhXQk5tcG5YQUxpdXBaU3lSZ0FyTnc0N1JER3RrWFo1aVBIdWRMZ0FodkJDZzlaa1FQZE9NVWw1YlJUNXM?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2131,27 +2131,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nio to Launch Firefly Sub-Brand in Thailand on March 5 - eletric-vehicles.com</t>
+          <t>Lifeline for seafarers given fresh boost - Daily Echo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 20:25:08 GMT</t>
+          <t>Wed, 11 Mar 2026 03:30:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWnBjaG1qOEd4S01TZ3p6RVZuaUhOcnE2OTJvYjc2QngweEJRNzZLM2xkc3JxbVhiWndUNGZIY0RtX21fdF85RWdUbHZKN3FMN09uSkt2Skh5eW4zZ3lzaW0yVDAxTE9vMXRJV2pHQk04TVRDSWlDd084M1Z1andXd2dPUW9iUlo4US1SUDlpQkRmOXFKaHhwN1hWb0s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNRmpsWVBJVFZrU2dtVWlseWpXMVlOeWZOYm44SzVlNnFOc0I1enR5Rkt2UnFkaTFEeG1vZThJYzdjdHVIejhtMkZ4WFZlQkFIVG9ESmpBalRYRjYxLUFHSVdvYlpaT1pnQ0hMaHBfUHYtYTdVdTV5R2N4OVFyNXMyQWRBZlk3Q1MzY0QtTFpXTGU2M3JLNmQ2UThLbFZ4TXg4aGNyb0xB?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2161,27 +2161,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Daily News- March 3, 2026 - Riley County Police Department</t>
+          <t>Port Glasgow care home given 'weak' rating as inspectors raise ongoing concerns - Greenock Telegraph</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 20:51:08 GMT</t>
+          <t>Wed, 11 Mar 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBkTlRKZWM1eHFFZ2J3bTY1QWpXV0gzQTlVclRCaGlGSWFSVUpqdXhUSnc5VFY5RWQ0ZXl3dm10TS1oVXF4b1FwajhfZmpwa0JRN280TVVXV0l6c0tXU2JaZnRLNzMyR3duN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPTElGZklZUVpsYm9yZVp0dkYyaTdOM3UybDI0RWNGUXlyVVV3ckxBeU9yUGhZd1lvd3N3V2RzVGV3ZmhLWUhYaWFDWUUtMUE1Q3hHNUIxNkpPbHNQblFGazVyWVNfdW5oOWJoM3JXZXljX291QTJJR0VQT1phVHJmdmo2VktWZUZEN2lmU1hodzA3WU1jZkloYnVTU2pDQnhXYmctYQ?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2191,27 +2191,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Arlington Police Department's 'On Call' Newsletter for March 2026 - City of Arlington (.gov)</t>
+          <t>Seatrade Maritime Club Round Table sets scene for CMA Shipping discussions - Seatrade Maritime News</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 22:27:08 GMT</t>
+          <t>Tue, 10 Mar 2026 19:12:54 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNelpOTm52Vm05X096T1ZBclAxOXVFemdDX1BCRkNDRmlGQmU4VlJveFVWTS1Pc2RBNWdFYnVYMVk0WnFJQXJwTzB6RWFDV3liS0NVNGVGM3A0U0Mxb0RwQ1JKTGZ3eTdIcUEzUTloRWJ0a04yUzNlQ1hfZEJ3N0JORC1YVFhaNTNOd0pFaFlBeUNIMGN1Nm5ESE9xZGpfdmdtWi11YmNSR3ZUMjUzRk0tOXJyN2ttQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOU3MxQV9RSl9yQTJuZVEtRmFJLU15TDhCR0dOMGZ6RkdKaXNnYzdzbnFyZ2VkOVZtQjNSSW1qdFNNTktuVGhaQktBaTExR1p6cU5iczVHSUJReDVhOGd6OGFzdW01N2ljYUpOS0RSN1RJS0hOMU9qelZsTnZOZkpJMU5IbEs1V3lkRkswRU1hSTUwczBDVU40dk1zOHNsUS14aWQzQjZMaHM3SHlpSWwtUU1wTnQ2Y24yQ2hj?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2221,27 +2221,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UEFA knockout draws set to shape Europe’s big March clashes | Daily Sabah - Daily Sabah</t>
+          <t>KPMG appoints Silvia Zamorano as legal compliance partner - Iberian Lawyer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 09:28:33 GMT</t>
+          <t>Tue, 10 Mar 2026 14:04:04 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxORS1IUmtXQTBqdHAxZGxGSnJaZVFUckZQMWs1VWVod2RPVFV2ODgtTmJfMVVOSDZnX1BaeGkwZ3I1ZWZTcVF0dnJQYlhxWWRhLVpzQjQ0ZXA5dk81RGZMQWhWN2p3ZEJnejdHNEVTdHJPYWc2d3FJZVB0SmZKTEgyQm1NclZROFotRDlEN1NoRTJpX252M3JuSWJ2ekZWNklvZkNj0gGoAUFVX3lxTE1BdjJreXJMajZicTE1UnlmSS05aVJ4VFAzN1N4SGhGbWFpOUpmbllEeHBGVXVFU3hhYnhvTUItVjI1Ulh0R2pzaTd4ZWplanBGYTJ0cTF2eHRBUS1aM2F5Q3RNdThocGMtU2k3V0pfd3l0dDNFYWtjSjRycXpTdDlnMDBJQml6VTQtaUJoMUtmTkFIa3NCYU03N2dhRFlJRG5wRDJBS3c1Tw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPcWZJemZQcXF1cnZtTDZXeUlES2pOcTBWc09CWmloWTdCdUFMTndlbmZsaC1NcV9TQW5xWXdDbDM1QndXRDBIVUdhSVNzbEppcTNRQkNEdDRRNS1VeWxLdkc2QmhlU2JKZWNOSkVqdXgxVElwVFAxUWRGaWkxS3pWb3JXc21xRVpOaHg5YUpiaE5rWExLTm1iRg?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Champaign Police Invite Residents to Coffee with a Cop on March 11! - City of Champaign (.gov)</t>
+          <t>Government approves Met request to ban Al Quds Day march - BBC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:06:59 GMT</t>
+          <t>Wed, 11 Mar 2026 04:14:17 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTFh4VnRoSDZ3Tk1kNFRqdEhmbFBJaml0anFCTEdwNU02TWl6dUNseWVnNVZRckR3VXZNNGRJVHRRTGtCdVctR1NFVk9nOGxLZjk0cjNTMU15Y1l2REdaaXlDWjNSTTRTd3NoMDM2MmFQal9qTGQxRE1BNTZmdlRFUDl6RHJFbG1abndMbWVyeEs2TGlBbHVVWFZwQ3hhVk83OW56bA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBpUVlhQjA0c3V1Q3R1b3hnbGV6MkhJSjdHdVZYdkxKT3JTTE45aExDNlB0TTBjbWdpVDIzaklIbUpYYjkwQnhWbmFWVmN0WXNhVDRNNHZQZkIydw?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>March with the AGM: Elevate Retail Strategy with Insight-Driven Webinars - The Golf Wire</t>
+          <t>War expands to central Beirut as Israeli strike kills Iranians in luxury hotel - BBC</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 21:33:50 GMT</t>
+          <t>Tue, 10 Mar 2026 16:31:23 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1pTHcxTmtkT0MySms0b3dCbHh0TktoTmFuSzRFZTZoYXVKaWw5YmhncjZlOF8zQmhvX0VGM1I0eXdNTkZCV1ZiY0FPQVFWSENVMnJwX2d3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5hMlZyWUl3V3hjaWtlZlV0UV9IRFBtQWY4cHB4LVRMcFZoWTJDa1JOMFM5bmhSbFRXWXhrbG9jUHVEVzFYcHVpT3lvVGlpN0FHR0VoN01xWXNHcTNP?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prineville police log, March 10 - Central Oregonian</t>
+          <t>Man arrested with Samurai sword – police thank public - Leicestershire Police</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 05:01:58 GMT</t>
+          <t>Sat, 07 Mar 2026 18:00:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5rbGI1NVZvakVIZ0VmS1JWdVV5OWVlU2FZMFlBZUFpUzJUNzhzdnFhSTZfWmE2eWF2WDRnTlJfbktxZnhUOF9aN3cxLU02aHJ3WGVWdjYxVGZEVHRrelI4R1F6M0NzMldVRXlhWTR4dVVWR2p3VlFrZWJpOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUTloR2JZcXg2YWZQMXBNRGl0cDBIOGpRb2V2bEg0YWM3ZHU1d0Y2QTc3YzRtR1NraW1Jamxiakw3Wjc0a3NvRmFSOUVjVkNpN2ZmYzVHZEdQdUZkZ2pCX1NpdlFDUmlsNS1uc3Awd0VpS3BqUFBMTjdLLXMzTGEzeEg4dHVJd1JIOTRQWFpOYnA4dHA4ZkNZdXRwQlNLSXdLcXJQWHZabnpLcHA3UUpsQU5NT0VpV01YdXpHLUY2S2drYTlYb2NDaElXT2JET29pMUFpc0Z5UWVSUQ?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cairns Overnight Crime Wrap – 4 March - Queensland Police News</t>
+          <t>Three teenage boys arrested in connection with Hythe business burglaries - hampshire.police.uk</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 21:17:00 GMT</t>
+          <t>Mon, 09 Mar 2026 13:27:00 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOXzZkR0tOcEJDUlBwTGw5eEt1QlhISXRTYXJnWDMzSkoyMVczWmZ2NUdGaDVpdk50TlBnamVNM19JV3c0SVh2d3JVY0NJY2pWMlZWRmQwUUxFT1k2T2hIOW1KVkE5VEtRLXBQQjRLT09xRExpMzQ1QXFiM2xlMERvR0ZFeGlHNWp4V01SSg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQYlVCN2I1aHV5TjI5eTd0aUhFM3ZuSDI0RlpfV2tzdDZFaWRfUnc3aHJhSV9zWGsyY2EyMllIVW15eGJNbmQ1OGZIWG50bWhMYlh1eGs3TlVJbURWdmxNTjE4cW1Ocy1OREwyTjVTYVg4SzN2OW02b1pCTUNucE8xQk9xTGJzWlptMkVIM2pjVzNfQkhIbm1Sc2NPXzVFandYaW1kYmdVLTJ0cURyWWpIN0VsSlYxM0ZfRUMwY21QSVU2dXMyNmJvY2tfY0JSSUtQa2ZEcG51blNwSjZ6aHJj?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Fulton police seek help in March murder of teen - FOX 5 Atlanta</t>
+          <t>Bellerivestrasse Threat Cleared After Zurich Police Sweep – March 11 - Meyka</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 23:10:16 GMT</t>
+          <t>Wed, 11 Mar 2026 03:13:17 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPdEFETUY3d3lMMWdMS2hwYUNQR09yVlhZektyMzZRSHpGbldrVFVKZlRvUlVESjJMN1dRV3dyanVxQW40aUxNSUNESjJOZUNSLWlCWWdtSnpXV1lmSk0xbnVUazhQUnF0R0traFF6dHRBc2hNdFFyRFdBWWI1U3l5MlF1X3Z1SzTSAYwBQVVfeXFMT3Nvd2tKYi0xclo1eFcxSHhZLW8zeTVSdmZ2MmNGYjAtM1dqd3NqMkdtWjNGejJ6TVhla2k2TEhVYVpWTTFuUG9HaVRQYzdXLWFqOV9zRkxDejg3UUZ6NnJuME1aNEJCdnVDS2JZU0VObGtaZDJkREJ6SWE5dEFUSW9nUnA1VXRyRkpLX0Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTVAzUnNEQm5pRmV3U1N5bFRWdGM5YW5MYXpMMG1haDE0NklsTmF5T3ZPQTZWaVZYS3R3VTJkQlRsbWZMSEZGcmwxdFVZM29ORjVJODFhRHd1NjhfQ3BGU1l4dW5FTHBwbTBJMV9wT0lJc2FVbnB6VVNlbFhJSXVaWnFWU1ZQR194SUhPVkNKYzNZUklSZGgyZ01pcw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Today in History: March 3, Rodney King beaten by Los Angeles police - SooLeader.com</t>
+          <t>Suspected drink-driver arrested at Ramsgate Travelodge - The Isle of Thanet News</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:43:38 GMT</t>
+          <t>Tue, 10 Mar 2026 09:47:37 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPWGRlamZvOTJCazZ3NWlzUjZyQlBaTWE3bmlqQlR4NUJxMHltSnAtdmJFeWxiS2I1QWtNVXVIYUNtd0lsZGhTbFFJbzlPSU8zSl9QV0F0WVdDelRaQVVnNW5oSkZTcXFLS2ltVzNVaUtYc1JPc2ZtUWplaEFudU05cG9fSWNqQWpjU2gyUGlldkpiWXduZUlhT0V1U3NzQmhSa0tEM3FnUzZmc0x5ckxPbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNSk1lLVd0SExkLVlLTDFjR1BmSWhOVzFaeGxhdGRGZVZMSExmTEloWmVMTFhYTjV1Z0dIWTNoVlpFVW5jNmZQR00xSnoxMlB0LVV2M2hhbU9Yc3RKbUFNRUtkcXVLc3ZTOHJBM1RvbXd5NnV5eFBqQ1o0alVUS3FvWUZoMThaNDRZcXFTUTB1MG9zX3ptSXpyOFd1em9ZZVE?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VIDEO: Aftermath of air strike on Iranian police station in Tehran - Australian Broadcasting Corporation</t>
+          <t>Pro-Iran ‘hate march’ BANNED by Home Office after Met Police request over 'disorder' concerns - The Sun</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 18:48:33 GMT</t>
+          <t>Tue, 10 Mar 2026 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPT3ljaTU5bHI3aUVTVmNyRnNDZzh5Wm5uNlhQWllPMG9pQWhzb2NBQm4zNXNUZFNwSjlFLWszUWlSMjE5aTFackxfdU9TcXUwOFFzdDNlclBzNzJoMVRCczBVckpLdEtLM1JGeG85NlhpZTFtS29Ld002WmlMWkJZMnMwQ3U4YW1ycHNWUlpBa0hXU2thWXhEOVFpd1dmdERibzR5UjZJd281OTN0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNa1pEdFdzMGlUMEYybU9ITnZndVZiUDJFYlU0MF95eEo5b3VUdlg0eXBDVjRzQnZ5c25iRHBVdHlseGFhaElyUXZrbXFFd1JaYkVNaUNmdjYtQmZpSUN4aUZBTUdwYVFOUjJZRU1BNkMwNFpGTFdoQzR0Tjc3bHZfZG43LVg?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2461,27 +2461,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Teacher v chatbot: my journey into the classroom in the age of AI - The Guardian</t>
+          <t>Hannah Spencer: Green MP gets police escort from violent demo - BBC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 12:16:00 GMT</t>
+          <t>Mon, 09 Mar 2026 13:55:11 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUC1XWU43OXNTY1VvUkVlRDhsaGxEdk9BdFdBTE5uS0xWdHVBSllScHlFQmdIdUNTYmQ4LWx6SzFjU2N6NEIxTVZOcml2S1ZJSkZwQ3dWV0VUbmpveklwcjV4ZHd1TXVzSnZ1NnVaVkw1b2YtMnB1MW9wNHdqTlJ0LUdWU3VmNHpKY2VtT3B2NENqbmtRWWc0ODdwUTRfQ1ZsWHFPaHpVNzZyLURaNFo0VVZQTzBsME5KWkZROWFxYnJHU1FwbmE4aVlfN3BDOU95endUMGNSZXY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5ENmpkakx4NFpSMGhKcUpySHZ0c3E0TFFsQ285NUYyZTRlcF9pT3Q0R0xIdjVqNXlVWlBIOGJ5bnRlMWp5dHdpaDNwOFFXd0t6RTJJajhhUUM4RVhI?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2491,27 +2491,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AI helping farmer with data about bees and crops - BBC</t>
+          <t>Police called following reports of women 'screaming for help' at Crewe park - Crewe Nub News</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 06:09:54 GMT</t>
+          <t>Mon, 09 Mar 2026 22:44:01 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBTSDlJOFd2ZDR6N1ZUOHA3MnBZMU15UUQ0ajhXNTkyNy1vNDR4dVFmaG5Gd0t5cjR5R1c1QjRpdzVSbTAzalQxcTR3ZGp5X2ZsM05jOHEzeFhKWUJw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOVTg0RGY3RHRzNUpydjlEcmpjX1dRN2xEUzVvZW51TzJoYW5WQmpua09GNkJPcWhNMVFibVY5Z0pQbVVKV09BTFBBa09TOVBuRzROWWViX0VUNmEySXoweTl5cExyWXpBNkpTVzcxMDlUbUNGZi0ya2dXNW83Ylp5OVYxWHB2WUE1NkQwZHE4QU9ycFRzN3pENDN4bVhWMUlSLVAwU0ZmdDNVRjdpNm55TndQMWYwNS1MaTdF?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2521,27 +2521,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AI and privilege: Assessing recent court rulings - Data Protection Report</t>
+          <t>Santa Rosa prepares for March 28 No Kings protest as police expect record crowds - Northern California Public Media</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 01:19:40 GMT</t>
+          <t>Wed, 11 Mar 2026 01:03:18 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZkRWZmxlLXBYNTFsNjJiS0VOVC1NbkNzYy1BNGFDVDYxenpPYW1HVW9PR3NWZFJMSU8zeXN0QW14NUZXclBYdERibTYyX2tUZ2h3a2p2a090OUlydEpZV2RRVW5WZWVNRVc3RXYzVUx5ZUY1TG5fdjNqSS1jSkF4ekZNVHR0aGNDMWdfcEdVd3Y0bm5VMHhhbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxORzNGeS1yMVpWeHBWUEtoRnBRU2d3b3BxMy1Qd29hN25iNTdrQnFwZjhsaHZ4WXc1UnBJRk1zcVpLaGFtd2c4dFZ1bXlxZmZhdWFmY1RoT05OLTRGRjBIcDBVVzFZSFVSMVU4NGlaeV9naHM2bHo1OWs1eDNLLWZEQWdLZ0ZhVEtDTTg0NUUtSVc1Nzh5Yk45TjhoUGFOdU1jLTNHVUxGZ1Z2Q3YzVFNBQXhBR1d6NEZtb0V2ZDBWSQ?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2551,27 +2551,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OpenAI changes deal with US military after backlash - BBC</t>
+          <t>REMINDER: Seattle Police sponsoring 'Our City Our Safety' community conversation March 11 - Westside Seattle</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 19:37:28 GMT</t>
+          <t>Tue, 10 Mar 2026 19:56:27 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1vckNhRkttVzdBZWFOVHhwVWlSVmpsLUc3bmZGRkRseXhfQUZxa0FPTFpzMXFBcFJEbUlocnBpSEFEV0RUVV9GUnYzTlhJTHY1bkNFcjBKdUdidw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOZ0ljOGJ6RkhYd0FtUkZRaWFsLXNKZ0pxM0tidG5LZ3pCTHJ0c1ZPZGR0NzROcTFocGhhQ2RZYWdQeU5KU2pMYXdkWS0teWpfYkltOGtCUVdSZUF0d0hiUjFGNDh2RmJvaHZUc3VvdE1YemFSNmJOYU1xd2UydFFZMEJKb1NnYUU4YkNUa0lkeXdqX1BpWnRKOGIyUkU4SUx1ckd1SFNXSnNkaDRzOF9xYl8xeUExR1RlY3pkODF5Q3I?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2581,27 +2581,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AI and GDPR Monthly Update - Dentons</t>
+          <t>City police calls – March 11 - The Republic News</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 11:05:11 GMT</t>
+          <t>Wed, 11 Mar 2026 04:03:00 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQcVIwOW5TSFR0VXpsV0tKSGdMcUdKR1I4UDFnTjhWSHBycXowdTNJTzBHcEVCLUxHcnI0RFVGd2thd2dOWnotQmJXZ1lBeXVKeXcyVHAyU3ZtdjlFMUlLVVpPdy13OGxpdzJhMzJCeXJCdzZMM1pGOVVORTNXNnJGZk4wYzloQjdmMGkxRzN6c3NiLWFQWTV6aENQQzZlamhCUHkyNTVmQk9ybmV6T2g5bEEtYTR6eDVILVJLTUR3YlpNS200a2RfQTRuZUdnLXhNcTRVUlpua1lIRVVTSEtHbjlkekVGcFpSS1FWc0ctUVlLWFhLdHJ1bnY4V0V3bkhNS3RYOFN4b2w1Z3lO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1KeWdVTDlKUmxyN1k4UGZKSENMazE1Y3BGd0d5VWREUzNSX3dVUTZWc0NVejkzWWtBR3NaajJsVUNrZGJIWlcxT3RKNmlpRWsyZndzYTNfZ0VHalFGMmZfWTZHZnZYcFpaeGNKN0t6NkdLSkhrbGxj?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2611,27 +2611,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AI and the Future of Proxy Research: How New Tools Are Reshaping Stewardship Workflows - The Harvard Law School Forum on Corporate Governance</t>
+          <t>Man dies after March 9 shooting in Wilmington’s Hedgeville area - Delawareonline.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 15:56:43 GMT</t>
+          <t>Tue, 10 Mar 2026 18:50:00 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQdm5yTmxoRnRUQXdFd3VkSzZtYThndS1TS1JGcTlGRXR4OVZzSkwyR3Z6UFFIMUk2X2k5djdTSWxrSEZEQ2JTX2pnNmtLc3Y2QU5lMlJKZ3lFeTlvMXY0dFF1MGUwUjRtLXdGNDdubWc4bG1FaVpVdFJwMS1pNnMySGFZRVlEZXVzVnZVMkZQVkZMYkhsTnpZLWhuUUNKTWtwd1VrZVcxZVZ4MDludFBHSEpMYnRhekc4WUo3eWpMa2JXUjFualM3eg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNTHlYUXZDRXFVV21rdVM2WTRTQmgybWh0amhncmRMbnA2c1BiNkdQVVQwZTVNeTZqMG0ySEZRUDlSaFNGQVpFeFdmWXowbThNejRFZFN2ZjY3ckh0VzJQbHoxNVdENi1Qd0FSUEVLc1M1UndDeU9nTVBtVl9VcS1XLTY0UWFOZUI5aW1KUDRLZ0o4REpmSGtnZElQN2IxZEVJYldUNjZJb3hBdkpRMjh1bm4tX0I2RENkZ3pGaUZ1SjJwQUwwUVFmRHNhcnZUNGk2Q2c?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2641,27 +2641,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WFW advises Vantage on partnership with Altarea to develop French AI and cloud data centre campus - Watson Farley &amp; Williams</t>
+          <t>Gracie Mansion terror plot: Mamdani urges broad rejection of violence as another bomb scare rattles Upper East Side - amNewYork</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:06:32 GMT</t>
+          <t>Tue, 10 Mar 2026 20:50:33 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPOUt1ZlBoUm1pajFxMVpsQ1UtWEliLW53bE5Hd2xGRHhIWXg5SVozaGxWSjB2eERyV1V0ZFRKMmwzYzhKbjNFUXRiaTRtV0V0QmZpcUJwZElWd0dhelgyOW1jTkx0ek1TMUVnUkxnb2RNMGlzUHNsZ1pYQ3NFNkJ4TnZVdmNuN29sY1FLRko1R0VsVEw0eXkxbWh2RU9QdU0xYVdnUWI4TTR1MVhBWlp0WWJBZ3FKd2QxNXptOGtwbVV2UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOSlJkUC1rOUR5ZTZaNnhoRVZwR1gtcWhXeXNFeGpjWXJabXd3WV96S1YyTThNSGxNMkF1NlJIblllVjhSVTZLMzNxRFN2Wkh0YlVVejRFd0NpV3F5RFhRTFlYdVpidHhxWDFWaFFMVGQxUVhKQlRYOE4wd1lRc202OHJ3?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2671,27 +2671,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12 Quotes About AI—And How It Makes Us Better - Forbes</t>
+          <t>Man arrested for allegedly attacking deputy in Victorville - KTLA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 12:30:00 GMT</t>
+          <t>Wed, 11 Mar 2026 04:26:28 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNaGgwRFROcWFfbHRwX0owS1AxaElGRzhUUFFJbHREbGs4ai15Qno0VS1sUmI4MUpaSGhLYWJ0dnBxeDN3Nm9IR2pnQ3VVZFZRYzVWNUdtbXU2S2t2Vm95ZlJ2RmhTTm91OS1UeDhFSGlUS3N4dTVLVWxfRTJpYjZqdWFZSjNQd0xoV0hWSVI3SjFYRzFEV1RJZEpLSGd3ZUcyMXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOTXU3OWRRTGlTYWI4ZTZXWENjZExPOXF3NXRVajJFWmVTQ1k1MXNSNThKeV9IaWxjdlJMNE1LRlE2a1MwTUJwV0lQcFozeWlZRkV4RDZrdjJ4Z3k4Und4SENaRUNCMWpyTkJsbDNzZFFDa0FKMmlQMzNLNDN6Y0ctQ3RUREd3bVYtbWd0LUNCYkhkSDB1OXV5cTVMZ9IBoAFBVV95cUxNTEZxLS1OTV9rYndkWFJjSzh0WDZScmJ2ZEpHOUZfbDd3LWJKd0pJQllxaUNiUG5WVUVPOHZvdUtNM18zalB5VEVMSFZ3c1NVZW5DRnFsOGdNM3p4UldSdTI3b3QwQW1BejlIVDFNVXlxQXhqakduOGVLNUJKTG8xM0RXVWtteGdsVHJQdFNldzMydTRkcEJCalgwbkRlYXA2?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2701,27 +2701,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Physical AI: Intelligence in motion - PwC</t>
+          <t>Loudonville police reports for March 1-7 - Ashland Source</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:27:04 GMT</t>
+          <t>Tue, 10 Mar 2026 19:51:47 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQU1EySGR2Mll4NjJVRTJ4T1Z2VUF1aDhHX0Z3clNqN3JUZHNOdWdjczNDOVFyS1VWV0pyZEFvZnVCTEtqdGpvbnZaRXNXYVgzWWFWUnpvXzQ2c1ZXNnJUcmZlcUl1d1I5WUVicmlDMkZILV9xcHBVenNwSE56YUZOZ21DYzdOY2N3VklqNm12S1hRc3h1bF9rODk4ME5YOC1TWGJkdnUwbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOXFqQlEwSVpwWUtSQTljVm41RDZMVTZLU09wSndpeFBYUGZOdTNoU0N0R1hjLXdyazhRaVFuUXF6OGE5aUt2N2swa3RMX2RrMjZKdFpXdHdkV0hSMFBQN0JodE9LVjVlWlBFZ2s2cDFqWGFUVXhMTmdpclRvSXlCQ2ZfNGFmSFhibGc?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Europe unites to build sovereign cloud and AI infrastructure to stop reliance on US - Euronews.com</t>
+          <t>Innovation in the NHS: personalised medicine and AI inquiry launched - UK Parliament</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 15:11:57 GMT</t>
+          <t>Mon, 09 Mar 2026 09:03:27 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPOWtqZFVRVG1vTFhvRzh6QXRvcWp5UGR5R2ZqM3N3VGdnd21aMVFGTHdZUkdDY1Y1Ul9seXJVY01uSEt5TXJqcGF0ZzdleTgtUWZ0Q0ROQ2NiTm9PVUdBZmtMUmlGeW5la1JPd1p1OGF4R2k2ZlRtcDZwajk4cTZBakN6UEZmMlk1cTl3cmZxM0ZaeTBwZG9OYnV1NFBnVmJxUFoxOWs4b21objZkdG5WY1JNNG1vUWdkNzdpQXMyRUJBdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOeEJqVjRGRUthQWw0XzhDSVdFVEhmUVdzekRBSEJabk9KT3dPdHFEZmRPcHhuc2tPdjIydFhHcVc1cWFyRVJ2cm1lbm5PYlJMXzh2UklhcmgybkhxeE96Mkc0NjQ4MTkxb1ZzQVZzOFhiM0JXOGVUSlQ5UHFXLUdhc1Q3RDdRSk9JNzNXR3MzZHMyS19GUjg3X0E5bG94bWlYSXdFVnNYaW9ZQ09Yc1c3Y0JJZGdMb3NTS1pHX2k4SU80ZVU0UENrOFBoSDFxLUdSUU1FOTJsWVVrODRYdXRoMDg0SGtNOWY0d0FES1FMc1ZkQQ?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>The AI Law Professor: When AI makes lawyers work more, not less - Thomson Reuters</t>
+          <t>‘I wish I could push ChatGPT off a cliff’: professors scramble to save critical thinking in an age of AI - The Guardian</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 00:36:34 GMT</t>
+          <t>Tue, 10 Mar 2026 22:28:00 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQMW9JNGRVUHdiZ004RkltOHluQ3U1ajYxenlkS3I2eUljbGZLNWZURnhlY2hxWDVlWENackFYN1pDekk4dldvRWsxaHhxejNDQU9vdlVVa18xZXZUY3VrbkdJS2FJTC02YUFOQ1dHUGRMOFZfZ3VMUm5hbGo0eHFjUmdBRk4tbmZvMkR5STBLMEtLX1FpQ3lvVHg4ckRySTBUT3FTRzFhMHY1NlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQRmJSV0FMd0UxbWVoczdlQUpBbFlaRUVDUUNRTWRaZWlMcEM0Ml9za1lUWjNiYmZ1cC1SaEQ4Qm1DTnZLNEdYTXc4ZGZmaFR1TUhPUVFGT0NSUmxzbG9ZclU3S19uajktVGhkT21vWmNYc3pBY0g0VlZKNS1XTTJnMXlPXzljWUQ4bkttZmlpdVk1YkhaZktQeThncTZlN1Rpdi1SV2l2NA?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New GTDC Research Details Distribution's Influence on AI, Cloud and Hyperscaler Sales and Adoption - Yahoo Finance UK</t>
+          <t>AI and the Commission and Facilitation of International Crimes: On Accountability Gaps and the Minab School Strike - EJIL: Talk!</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 15:00:00 GMT</t>
+          <t>Mon, 09 Mar 2026 06:56:06 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQVzFFaWR5TjNwU010bDNWVjJISE5hZTVkNVRVX1lqUWMwMHVraDZpUHE2M09Lbl9rYklQdmJhQzFRWHZMMnZqMWtmX3daTUJ1Ylo0MHhDbGFsR0pjZ1p6dF9aOW55eDdkRkh4OVY2UUhxLXZrX2RESWtKWkI3SGp1V2UwbUpsT3BTV01paG5NMXd2eHRqOVI3MG5R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQSWxmVjQzNW85MnFTUUxrZ1hYc1hncmNhbmc0V1o3RFJ1Z0tjQU1XNUdfdTY0Q2MtT3dKNFZjYWpHNGFfRnFhcW5UMzIwTzlsWlpTVDFUMHNMcHV3TXpPUXM0bU9GQ2hvYmQ4NEplQ3NnTFZIMzVJcHU2ckR4SG9udHpCNy1PVHBNSzBsMzNmeXhPUW1kcHE3ZHBRS3VqTkdvREpUNlhuelp6S0tJQi1UcURhbTI0VlctYUcwNW52cC1vVFdYY1FvemJHcUtyMzYzMWt1bnFB?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Generative AI and Privilege: Practical Lessons from Two Early Decisions and What Comes Next - Sidley</t>
+          <t>Newgen Software and G-ABLE Group Announce Strategic Partnership to Advance Digital Transformation Across APAC - PR Newswire UK</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 15:05:33 GMT</t>
+          <t>Wed, 11 Mar 2026 02:00:00 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQY2RIaHVnZ3duaEVjZkEwN016RzRvYTZLbzBRcFI1cDBmb1hHR3F1aWZqcGNyaFJTOHZLOHJiUGZwSktvTk5QZG9VQ3JoN1MwT2VoQnFPUXBYSFZFVjItM0p3aFc1VDNhRGVUaElFa3VMRHh3OEFRYmdyTy16WUdOS181c043X21lakt5OC1TSXlDNmxfWXhnX1Y2RE1WX3dDYmhVTkJ5eEFpTGl2UFBYODdYVW1PcVBVeFNqaC1tNksxLW04TkFLZTluUmoydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxQX2ExNkNpdmI5ZU9QTlZabnZMVGRyUjZlaDBOeWFOLV9qOGRyY0lEOFBjOW1FajBkbnFWOVBsbXpLOXkxNVNNcnAzWHhyaFBLQkducEFORU10SDI3MG5DaldUOTJ6bTFPOUR3bzQ5UGlXMkJrZnB3SlFSMlNwUXM4ZzhMVGhrSURseGFfZ180Z09aalk3eHFLcDBsa2V3Tmw1aFBqQ21iZUJwSkQzbk1lYUdPbHg4d0xwakRWa2tDT0RpY2R5NnBJNnBaeDlxVElXeW9ZZDlva1dtX3RmeU9ZSXg1LTdwWmtTbnlhT2pGUW5VWUYzSUN1R2ZDWQ?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Guernésiais translations generated by AI 'could be wrong' - BBC</t>
+          <t>The rise of DeepTech in the UK - businesscloud.co.uk</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 06:11:59 GMT</t>
+          <t>Wed, 11 Mar 2026 07:25:49 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBiRUNkaVNpQmY3QjlwSEJjLVJlV2hJNU16dnFuQUtIc0VrMlRiMHA3R0N0eU5PT2FMVGxUV0lCZ0hCR0o5OVpGallVbmJrNWd6YWh5QUdtbFRyWVVr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBpWXd5dGNnWVNCbTNCaGxabmlTdlZpZWxjV1VWTVY4QVd6YWVXQkpzYXhqdlJ3WjJ4b2NjREpweVJPaHhHUWlHSG84WG1nNmRpVzlEei1KdUNZMzJxMEtGdUV0bzUxMDJrdjdWRXlHd0RPdw?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>The highs and lows of AI in the tattoo industry - BBC</t>
+          <t>Lords Committee report warns of Generative AI risks to creatives - Fieldfisher</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 06:13:41 GMT</t>
+          <t>Tue, 10 Mar 2026 15:42:05 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5KeUZVVU1RMlJ0VW9IcDMyRmpweUl2MUdiUmJqVVVlTHVuamV4VlV5WGVGZ1lHMHlzRTFRUXgtaGtMVkgyMGxBWmthejVwU3FFMDBxWURYdHRPQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNUmZqOV9pVVdKZ1ZFaWRTRHllaGl4Yjd0aUxVeXhCbTExZFhsaDJVRVVPOVNRTE9XZlRSRTlOQ1Z3Tkpvbko4cmRqejMyNmlmeUd2d0ItVHBHMkJHWnAzSVFqMzRkS3k1NU1KUm5BRVl6RWk4MFQzamY3cHJvcHUzX3pfYk9mQmd0TS14TUl3TXZQUEZVdF9mZlpCeUt5b1M3YWJ0c1FEUEM3QndDZ2ExWC1WRzZBb2hmWmdUajFBQTZYUkl4bXpvTUNpM3I0VkNQNTh4LVB3?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trump is using AI to fight his wars – this is a dangerous turning point | Chris Stokel-Walker - The Guardian</t>
+          <t>Neura Robotics and Qualcomm enter strategic collaboration to advance physical AI and cognitive robotics - telecomtv.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 GMT</t>
+          <t>Tue, 10 Mar 2026 15:38:36 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSUhSdkZvNzBqbWtsSldTYWhnX2t4b0YwbWxjeXlTbjc1cWZNYjNlSVh2dkx6ekhHZ0Nkc3dDNnFMSWxZRlBOaXlmeUdrLU45eGM4MktFZ2Qwdmg3SU10Vk5rYVlIWGQ1aTF3RllvR1RSOUZSWVZQbXF1ZEYwMjRlbVBibDB1YkVxb0pTSzRJWUhJZWxLWVphVDVidk1KTkI1ZEEyMG9CVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOdFpoRGlUYXA2TXQtVW1oU3RDRlhVZEdQUWF6WkVqRFJTNl9FTnFBSXFaSW1qX0JwYThGODVWLVpUQzZ1bzBILTlCTVFMdDZPWWFHdm1aMmhZVU92N2ZOLUpoVmxaaGxiZlNGLW1zbEloRXRBT3Vta25WRTJidVo5WkxQeERpMGlOTUd3dWJ4WmxzUmxTekZPUmE5eHpJN2JZTXlDeXpheTFvM2g0TkpiQlgteWhXR2xjSDRLQXloRVFOSkZ4aG5jRzJIOHRXOXpSTjJzZnhmMjZfTmFNbWdzR2RTN2UxeDZ6Qkpac1B6YkN6OS1yQXFmMDZEWGpwUllD0gGGAkFVX3lxTE95VDB1czRVNzgyTlpTNGtjbl9HUkRONXR6RmlTQmNRcldzVERSc2NBVHFZOVVXZnBmWHhxam5JTXp2blgzQm9LWmxNOWhEZDBzRFRJeFNHZnRKLXhhTTV3dHpZVkJJejM4Z25mcEhpclpacXY0SmMxbVlYUGZxaTVNTWN5VWtNUlp6TVhRTmJldGZkNHpfS3RlQVdmcE93NVJidm5yMy1xdWd2YjhfeEFxYWlWQXBBSmI5V2ZUVTFTM21Idlk2b0ZhNW5TbHVWZldPOXNuSWZjNE1Xd3Zqb2I3bFdBeHI1V25Rb0dCNC1FYmFvNTlpR2xucDFTdk5GSzNxYUJ6S1E?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Goldman finds ‘no meaningful relationship between AI and productivity at the economy-wide level,’ but a 30% boost for 2 specific use cases - Yahoo Finance</t>
+          <t>Research on AI and the labor market is still in the first inning - Peterson Institute for International Economics</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:35:53 GMT</t>
+          <t>Tue, 10 Mar 2026 13:00:00 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNZVJja01kbXQ3UHZMV1M2cTNNQVJFZnZNbVo0X3BFY2p5ODdEMFhUdmtvY2FmbW0tMGs5bUNfdXhYLWtPYW1NSm44SElXRHhVYnRaeFdScllXanNvSTV2UEpHZ2hvczZlMHIyUFNUajktbjBFY2VSb3ZNeU56UXQyMERobzQ0WjMwSkxlOElOaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObFBXRGRVRS1Ba2NQdXB4dV9rVVVDZk5haTRtNkpGWmNRZmRWWUdJbVd4YjlfcjNJaGxJOU03ZHNLOG5BMkpOX0JiRWR5by1fbW54Q2JIM2ZEa3NQQ2xiZzJBYlpSRWtrejI0dnh3dGt1Wkl3SnFGZjRDb0M3ZlBOUndkaHpDTEdqS2tvLV90YllMQ1BZSmdGN1RZTzdOMzA?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>News Corp is essentially an AI ‘input company’, chief executive says, after US$150m deal with Meta - The Guardian</t>
+          <t>UNESCO and African Network of Judicial Trainers lead regional action on AI and Justice - UNESCO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 03:12:00 GMT</t>
+          <t>Tue, 10 Mar 2026 17:31:19 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5OMnpYb2t4OWl4dXBTdnNFSFViM3VDSjJuVjFlbXEyZ1FIdXY5NV9ITUR1d2lFNG5aQlZ1WkNUakxQZTFMa1RrZDBobGJkdTM5b3l2eENBWUFMNHJJbHRfQk5Ua1BFbk04WkJhZTY3bXNmRzZORlZ1QkpNVDEzblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOalZaOFN1a2czd3FuemtldzJPeWdXbFZPNUVPUE53RmNJUTVOaDVUVkVQS2luS3ZCempUYndSbnpST1VKZ3F2OWQ3SkhBSXAyVldtYlU4Rkk2d2pwYXZJdkxHbXF4MzY5Nm5mRmMxQlM3aFN3Wkhabkg2elFwbVRQclVKTmxZVUNWOUI0Mi1CY0FVMnlubUlWdk1fWUJqZklFU3hfTVJpcEc1RWhfZ2J2ZUlVUU02Zw?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mentions of AI in BBC 500 Word stories increases - BBC</t>
+          <t>AI and digital infrastructure are rewiring global finance - India Is Ready - LSEG</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 16:55:52 GMT</t>
+          <t>Mon, 09 Mar 2026 07:20:06 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBmRTJPQUtmdW56a3RXUkNRU3JlLWlKSFJFRTZvTUhjNnAyYVJuOUtSZHhOZ2xGelF4bHFNeU94NmpjWnFvQ0stallGY2k4aHNRUHN3Y08tWVAzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNRHMyeGtVaXUxdWxEcmdleTFCcVhMdUZySFZEanBSbkVKM2s3cXQtU2IzYjF0ZHJEVFBpM2dLZFBNVldsZUF0Uk54X0x6TzlZLWR2S0ltYlpSZ2htSWRlaUgwak5GeVh6VG9ZUDZvRS1GM3UwLS1FOEo2N2h0WUxIV25KTzdwR1pPaXlzQ1I1NjNoTl8xOU43S3U2dzJ3Y1c5NDRTWjJ0Sjc?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pitch to Pitch: JD Cymru Premier Technology &amp; Innovation Programme - FAW</t>
+          <t>PAC digs into government’s ‘curiously specific’ claims of AI benefits - PublicTechnology</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:45:21 GMT</t>
+          <t>Wed, 11 Mar 2026 01:15:21 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNOHQ2ZzFnQ3RfWU42a2hjSXJicVpMSUtsbk5DNkFZcVBnc21FSEVvTk5UVDdZSXdnMlRsZFdoSGVGT05oSGR1NlRFRXVDRVZCOXJtamJvVFhyRFRNTzNEVXpZbzItOWZLSFlqaGxKYXI2LUNQdm5aQ1l6VC0xZDRoRzU1RHdIaEkxMEJVeXhhcFVycDVsdFI0SXhLUVBlQUx2OGNz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNZVZOMUN3Q1dvMjFpMnBycDJPTWJLQi1BUnJXSldMS2ZXYVVQLWIxbWJqb2ZZZjR1SlgtLVhVVEZKUXZCdkdrNVlId3JaU0V5ZGhJUjluWEI4S2FMc0JVQzhEcDhhZ291NjhpN0NyellEanJDRXJ3bTV1MlVGdmxMRU9fZFRDUm5HaDRBeDY0YnhrdUJWMjAwS09fQWNzVFkxMmNTLXFSSXlHNXBzbTlESlVOMlVUeUNGa0k1WjAwMFJKc2JUX1RRNzE1ZmVvLVV2?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AI and the distribution of income between capital and labour - CEPR</t>
+          <t>Google report warns identity is weak link in cloud - IT Brief UK</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 00:05:41 GMT</t>
+          <t>Wed, 11 Mar 2026 03:47:00 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOc1VHY2dHWGpaQ09ydFFHcHloSm11aFdYejduN2dGRVJLMThfbEdvTFF3TndYcEtVbENFNG41bzZPdENzdHBwYTMtbmMyTkpFMlltaDFjaWIxU2xDcEltcnpIQlpSOGFoUUZjbTR0TXVwMmhuOG5QcWJOUEU2bk5NazhFeVM3ZUFJZUhoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWDA2UGhSWlRHYWVKY29MaElHYWNwNkR3WC1mWVNKMFp6WEdqWGZZRHd6c2czWGZBSjc5Vi14ZllMdzVjZ0FhODI3Tk44bk8xMnNOZEMzLUZvX3lISXBzRkFmZWpfdFloQjFXaE5GaXdpQ0o4VnNyLU9pa1JCYlEyY3IzNjg?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Former Daily Mail showbusiness editor denies hacking Sadie Frost's voicemails - BBC</t>
+          <t>Google Research and Synaptics debut Coral Dev Board for multimodal Edge AI development - New Electronics</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 20:17:47 GMT</t>
+          <t>Wed, 11 Mar 2026 07:09:42 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBMaXppaVJRR3p1VUVCaEdrLWRkSDNpbHJ5TzFzQjFGYzVWTmdjN2d2S3NKcWZ6RTRydHRzQWxoTjJ4WUVPYVZqcVFiSkJWSjNNY2N0anNrNDhWZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOTTNnWjFWWWwxTm50NmJQOTlieGlqOTBZdzdIRk45T3JYWW42ajdLbjVPTGxZNmd2NjA1cnQ4eEpadHFJaGFvRmtuaTByTzRWenBmQ3FzaDFQb3NTVWRGNW9EWVhBcmlRdV93QTNWR0N2YzdsdEpKd0Vua00tVjdJUEZjUnVQS0xSOElieFM0d3liYkY0WTYxMkpRcWc1OXo5MzdKcG9nWmMyS24xQlcyb1pOdnZxUWlKTmZpNFdSdnBPck1oQnh3X3U5cTg?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Telefónica presents the ‘SOC of the Future’ to strengthen companies' cyber resilience with AI - telefonica.com</t>
+          <t>What is physical AI and how it is defining the next platform shift? - Arm Newsroom</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 10:42:54 GMT</t>
+          <t>Tue, 10 Mar 2026 16:00:40 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOaW1rYjBwSmNWc1RJS3RiU3FmX2xUMXVaVDRzMWgyMTRDd0NtalZKTmo4NkdwcFFJVHpKN2VZSjROcldQQlJ4Z2tXcnVpVGt0YUZTWjEyNGdiaGtkVHJGUXFlV2thSTFOWlNmd2s3Ulp4a1pHZ2pBY29PWHJEMXhDQy04N182WThwejhVUzVvanBPSFdwSWNkLXQ0YXZvOVFXRGo4SWpoaVVEYVB3NVVDVzMteFN2d2hnd1hMM2dJNjJNZ0lpSkpfVWItOUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9OX2dSRV9RZWxfX1R2VWFuTzI0OExsN3VDbWk4a2RwbDYxczQ4TGRqVDBDaE9mZnNXOWV4T0I1dHMzSlZoOEM4TW00ZFRMaWdzTFlZZlhLcjVLdWJCNVE?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AI could be giving US lethal edge in Iran war - but there are dangers - Sky News</t>
+          <t>UK Supreme Court reshapes the approach to patentability of AI inventions, and beyond - Mishcon de Reya LLP</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 19:45:34 GMT</t>
+          <t>Tue, 10 Mar 2026 20:32:06 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPa1NZZ3hfeXF1d0NpOVY0UHZYYS1UNFlXWHVnem4yOTJlaEpGUm00dWc4eWxIUm9MajRNTnMzYjdwdG1XMXdLaWU4U054MnZibHVqaXNjeXRWMERMRW1MbE1jSE5Qc2Zqdnd2YTRfRnJUQnFZSzVsSlM2a1dXS1FPLWRRNWd4cllOdzZFc0ZDaVBVOFd2aV9LbzJ5MXdHWVRxbXJwQjh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNRTlyR2UzdnNlMjVMQkh0X1FGLXdPcmVTZlpmTEpJRUNGNk1yMjVwMGZZMExRN0lzclJJb21NUng2Ry1YVHFDMVdhYm10Z2hTSkhEX3RHQ2JUTkFseWt2RkpoVHBQMjI2WWhvb0VlX2ZMbkg4ZWVMRFlubFVjcFh1YW1Vb3RwN01rVTZVYU9sRG5WaGZUcXIxRGNWVmpaUnFVQXd3R28tTzc2Q05KWGxiZnRB?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Major funding boost for Cardiff biotech firm using AI to design drugs - Wales 247</t>
+          <t>Flintshire families learn about artificial intelligence through hands on workshops - Wales 247</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 06:56:11 GMT</t>
+          <t>Wed, 11 Mar 2026 06:20:43 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQVVJpRlpJdlNWdmZCemQtNDlPMXpGZXhhZlpPM2JTOXdBbE5rcHlRdmVRem1JcjA2blNQQW1JVmszR0tZRkhDRjJHNW9DRHZQeXlxazZqckJTVEs1NE13M1hiWjA2Nkp4bmtodFk4aUcyaERQTVdpNGpWVEdudlVKRGFtNV9tM1RRRmx0YVBBdkJmanB2SU5jMkNpQ1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPNm0xbnNLcVI4dWd4SUFVMVVsMTlfR2lCVE83N0JJZURiSHNtU0h5R0lOSWV4M1hCT2I4ZW4xUERmUl9ieGlJZXR0aXVrYW0zaUJlUy0xNjdOc2lxOEwzeHNWcWZMQlNuVXUzMnM4TnVpRTc4bkZsNWNmZnFQYVFIZ3dBWE5oUWlvdjVsRU5SRldXMmRZekpzYnllcGozUk1ncmZ1c1pMN0c5eGdqY1E?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>How AI is already reshaping working conditions - UN News</t>
+          <t>AI and genetics reveal new insights into human language development - News-Medical</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 03:00:00 GMT</t>
+          <t>Wed, 11 Mar 2026 02:59:00 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1wbWZrbjdDanhYRzRqb2E2eldtRjR0Y19tMUYtQmtrUVVJQ1RJaE5EX1lKV21YMndadjBMRUY0dEJTajhhQjgwZW0wT2g2THlPaXZQbWcyRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNemgweXRhYThtT2piT1U5WlhRQlV2SS1xdVhXbHBlRzRWUWdNY3NpZDlCTUozcF9jNHQ4bWNXMHJhSXJBOHFETEhlX2ljbUk3UmJUSUJrcHQzNGU0RWJzaVBKSjl2M2RtYVhRb3dhbUMtRG5ScVg0SlYtQV81THRxeGxXUHFVdG45czEyVGFwUHYzTVZOcGhub3A2TEgxR2FMWkFYemVCd2ZpQ2lkM3RSa3hwRHQtUQ?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>How Collaboration Can Enable Action on AI and Mental Health - Tech Policy Press</t>
+          <t>UNESCO Supports Training on Drones, AI and GIS to Strengthen Disaster Reporting in the Caribbean - UNESCO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:29:28 GMT</t>
+          <t>Tue, 10 Mar 2026 20:30:10 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPeGgtOUhMcHlwYkdrNkVpdmI5NVNLTGxFUl9UWjBuLXVKeFplbWNxR3VPWFFJX1FJbmpUbDJHR0RRbmJNdlJSQzlFMy05Q3pOTFFRVVJBRnpuLWowdmdmZFdoZmhkVnlSTjFOWHpwal80ekdrck9UamlGVDN6bUoxM3hUeGZZbGcwTVN3MXNjY004bnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPVDNwNzI0a1c5em1FRWF1UHR0RDZJaDRTZzhyRTU4WmxfZFcxZnM2R2NVYlZQdENUVTVHelBOajhsUUU2VWxKRUVYdGxIc0M2S25lUkJ3TkI3MWpQRVV5R2ppdmU4b1hPczdac0ZSM0lESjNrbk5SZnhmTFZwTWVGdkRMaDc4UjdHWWV4RV9rWFlYc2xSMzhRblJSVUtReWdISjBqTG45RUx0NVRoYTljQ3h5cXV6WnU3?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>UAE Central Bank publishes responsible AI guidance for financial sector - Pinsent Masons</t>
+          <t>AI and copyright: House of Lords Committee sets out 'licensing-first' approach - Mishcon de Reya LLP</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 11:31:17 GMT</t>
+          <t>Mon, 09 Mar 2026 14:26:25 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNTluMEJPNzE1ZkY1WEZRaE9pRjJoMU9zUmNNVWRTTC1qemswOFR5LWNNTmxsbVZVNFo2UHhXUmZSNjVBblR2UmNKa3lxS0Nnb0hNYkRYcG91bUtIS1k5clJhU18wVnJ5ZS0xTy1DaEVaSjk2UkpRbEpsY2Y1TmVMMWxWZ1lKWnowbFpIMjkyWmVFVDRuU1c4azJWSkNKdTNkRGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQdkpRdTlZaHYtUEJzdFFzc1NBY2RxVkhMTENoOWlBdU1MbWpsTTVXRVV2RVdFS3ZzX3hnLUxvNV9yc25kUmRxVXZlMVlEVjJHRWRJYWRlUGlqNUtzcjQyY3piT0toc3VoM1ZFWXdaV0NESFY2bzVSdFFybkdMM0JOQUNCcXVPTFl0SXpFa0lrcEw3VnJ1cVVLV1l2d05UV0ItWE9iZ3h1Zw?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Enhancing breast imaging with AI - healthcare-in-europe.com</t>
+          <t>Human-in-the-Loop or Loophole? Targeting AI and Legal Accountability - Small Wars Journal</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 05:30:11 GMT</t>
+          <t>Wed, 11 Mar 2026 06:03:13 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOc2hEM0U4cm5WUWFHcDhDY2prZDZ3bFZJb2k3SFd2TFdSbWFnWTQ4akx3b3VnMGgyU2Fqa1BySUdlNm5yd3JiUEVadjJpYU9GMzdvcWZ6WWF0WGpUMGJkZzVIRmFMUnJ5RGw4THBCNVRqdGVUME5zc19iQ3VCdlhCX2UweUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5pMmhVcTFMNkZTQjdUaHdYQWZiWEhfMmdqMVBWSTUtTFotNGJlUENVM2pPUXZnQXJMWUdCbmtCeVFOTlh4VzZvNVpkSFdRU1VzY0QzX2xteExGdDBFV2tJUFd1ZlllbFJad1E?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>How a band of engineers anticipated the cloud and remade the internet - Princeton University</t>
+          <t>Supreme Court Denies Review in AI Authorship Case - Mayer Brown</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 22:33:01 GMT</t>
+          <t>Tue, 10 Mar 2026 22:42:53 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNbGE2SXVCT0x3SXlxYjNaSmtLS0VQTFJwd2JuVEtBZHVDa3FUc0lwVDZjbVpCSmhhdlI5aldYM0hmaV9VUmwwcjU3R0xpR1dCT1Jmc1J1bERXZlVUMF9jYnRDX05ZaUFlanJmX3RndFBTZXFLTmJxQkotZDlNUlV0MzU1cUxuUjIzeUZYN1JOX3NHSGhDd3p2dkdZWU9yVFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQTWliUUpVOXZXMXl6REl2RGZuUmkzYUJRV2FUMHg3RXlWNEVyVmpneng1UjZyZjIyTFN0OENPXzJpN2U1R1FKR1JqTzlyWTZiY1FYWnd0b2ttdDZYYWlZenA0ZDlyU2RHenpORWdJR0tTVkRfblNfaHA2a0NpWWZwajFPZHk0TEFLaGgtYnNiT3M2eElNVmVuVnEtbjFnSm9IWDNlMFFMM3VDWTdrTXc?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>The Future of local government technology: AI, robotics, and agile platforms - The MJ</t>
+          <t>Reshaping the legal industry – document automation &amp; ALSPs in an era of AI - Wolters Kluwer</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 09:08:19 GMT</t>
+          <t>Tue, 10 Mar 2026 16:11:58 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQbU9BY3htNThpdnJ1SzBDVnp3Z2FNRXZhTFBLaWJ5QWRYSVB2aU5oWDZZQ0Z1OFl5OENKS2RnYzYxLWt0cmk2cUkzZHZVWV9lQlU4bFhZeC14Yk0xOE5zV2xSOHJuRHZXSC1ZRWJWeFVVcHVtMGRMd3RtTkw1dGRoVHJiaS1RXzNDbTZMc3I5OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNRWhKYWZBczFXcUQxaDJnTHdnVTg1U05EOU91aXpoVTZkMXN0LUdwRFZhN2xGM0lxMTlTNE1PRXEzUVZjbGVPb05kelB0eDZnalFUa1RGRzdSam9oc09CWE8tblVxaXRlY2pReTVfZzFiY19LUXNISlBucDBvMjVJVFJCUC1mMVNGOUE?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AI slop: Can players and football clubs do anything about it? - BBC</t>
+          <t>Turbulent techno-politics: a leadership imperative for Chartered Managers in the AI era - CMI</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:48:48 GMT</t>
+          <t>Tue, 10 Mar 2026 18:59:19 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE43ZlRmM21lM0YxTERaczdob1IwM0lZWUUzTWZyTmt1ZzRPcUcwZlhCZmFGZlQwYkZoeEVEMFlsT0U1d3RiRDBBQjZzeFRrYnpVSHhzN0NYV1VMM3hGY3cwSmM5bFVNQUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOR09HOXhmZ3UtY1NGRm9qQ05tTXlJaFFGblU3TVhOQWtDT1MwaXdqUmhvNVoxZ0FEVlNReTA3VDhXNXViLTZMUUNiZWFKTl82OHZjYzE2WFpob1NOaWhDa3FvaVRXZnptb3djU1Fua3JFR0REeXVveU8weTNKajVCZ3VBRnlxWWpzelZTMm1TLXVIRUoxRWV1RTVPUmd1ZzRUdWdIWm5SSU9xN0RiTmk3TTNhMTR4NGVGY0g2dm1LY1JMUVJkZnk2MUJ4MzVmand3NG1UdVBtNzVsZGxCWWJJ?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>We’re Still Early to AI — And Your Team Needs More Help Than You Think - SaaStr</t>
+          <t>TrustInSoft unveils AI‑enhanced software verification features in April 2026 release - New Electronics</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 17:43:14 GMT</t>
+          <t>Wed, 11 Mar 2026 06:54:40 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPay1ubTBPajhKWkhpN3FkWldaWmF4NG40VkxrMTEtcHYzWWY5S3g2NzRfY0c2OW5tOUtPS3M4MjhaeVhSaHRfZnNBbUVhRW5wVVNnNk9MUlphcXpsbDVIaTRnM2JEUHQwSWQzc2JneGwtdC1WMkIyN3RfNjE4NnVkMlFDOUxIRmhnX002OThjNGxGV3FRVGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNdF9KQUx4UmtreWhZNkhwZE0zUFVqdm5fdndUdUprYk4wTmZFSDk4bktJdWxZSER5MDlHUHowci04a0tWRjlIMDRpVjlneDJTbk5zWGxIQVVOemNLOHVManU4bVBoS0YwQ1ZZUXIyRjhtZllhcHRFQnI3dzBSVE91YmRwbEhvNGZmNHpDTzczLU5jdGhDeXl2TWc0WlF2TWxYQnhYRk04ZnNpcVFXNTI3a1JoTGNYeHpTb1NMUW1pZkwxbFZqNTBLVVB3?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>How architects use and will use AI in 2026 and beyond - Royal Institute of British Architects Journal</t>
+          <t>AI and its discontents, with Decca Muldowney - New Internationalist Magazine</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 15:11:14 GMT</t>
+          <t>Tue, 10 Mar 2026 10:14:39 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQQVBIeTJGZ1VPeHRkOHJfWHVKcExoZ2hwZzhkTkU1Q1lUTE9TRFIyNi1PTDRtV21DSWwtTmdZWDlpRGhaZE84ZkdQbnltaGRmQ3lHbHk4Y2t3VmttUzJLT0FWM1lidDB4ckNUdFpiSjFrMTF3LTRacnktVzZaOTJJa25lLWRrMk15aWUzS01fMHE1RTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNExPNWkzTkFWbDJGR2FaMnJGSEJMQlJWazFSNEkxQS1SVmtDYnFYaEdxWWVlaV9ZbXByNXlsdVJONkhXemZmbGZTeG9iamI4Yk9iZ0hEbGNvSzI5LU1XdGRzbHNhUXkzdG8zTG9vMXRMdFllU19USTl6WE5zTTZINTJJRjY5UlBwcHgtRG5B?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>RS Group expands portfolio with acquisition of BPX Group - allthingsbusiness.co.uk</t>
+          <t>Careers Breakfast: AI and Machine Learning - The King's School Chester</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 11:29:05 GMT</t>
+          <t>Fri, 06 Mar 2026 16:55:29 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPUEJXYzRoR3IzenkxZ3Qtck9ZaWtPbGdIWFZOXy1RUk9pcXFVbnp5Mzd1SkhrT2RwdkV5MGotZ1Jia0VfaHJUVUlQTGYtNTM0OFhUWXhKZDBUTVVDWVBjaXByQmRnODJwYlY1X1dnSURqaHJCMTN5blZEZHNNVnNpRXEtRFJQT3NmOENScEdLNzVaaDM2c084eUl2bUZVaHBuUUtUdFdJWTRfckk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9DSXhkcVpsOE5BdHJia1h3SGp6a244UFN3MDN4MzhqNjdxNU5YYVo4Uk0xNkxndEVVT0JCOWVYU0RKWi11S0FpSU5iVDgwbEx5Y1Y1czFzU3pmT3dMSWJqOXV0MFVNazRPeXBITzVZajh1dDR4NFREdUtxby1Kczg?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Women in IP Speaker Series: AI-Copyright Collision: Latest Developments &amp; Hot Topics - Jones Day</t>
+          <t>Indra Group anticipates the future of smart mobility with connected vehicle technology and digital infrastructures - Indra Group</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 22:35:46 GMT</t>
+          <t>Tue, 10 Mar 2026 15:57:49 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUkZZejZIdGJNcHVjR19DZXItMmxXay1xZ1pqREVkZV9rdldMY0YyTkJNdWhLWVYwc2dqS3FhTkd3aEVVc3Mxb1hVa1l0bk9uVFFTQWhWVF9ZRkcwNjBxczlMTERrTnU5Zm9IejJaZlRHXzlCU0hmMzFkNVhwYTNjWjc1U0FtWVoxQWtySkkwbmpHZ0FCZjd5bXRQQXdtNHJKclpmNWw2OTZUSFo1WkFWSDBKVHZNcFR4WGFLUTVVWmJucms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNX0dRRXBCN3d1eVlMS3VENndJRUpkTDZrN1FSNTZGNzdEVzExY01DVGZUX3ZDN2JNdjg3eGJqX3ZVODBrYkEzYUxHQXRtOUtNSUJBTTZ3TFlscTVZTmtHaWp0WGJuOTFwOVBWdVB0U05pN3ptQ0xNSmdfUDZfeTQ2UDdnclhiZjBteXVzYjkxdFJoTnNORlV2UXJWaGdUbzh6MWdvaUdUNS1mSjJwZ1A2Vk1UYTVid09OcUwyS0xtSzhGX2JZZDk4eDlDYTAtUWFfZ19WV3AydWVWWGh6RmtybUtMSQ?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>From algorithms to atoms: How artificial intelligence is accelerating the discovery of next-generation energy materials - EurekAlert!</t>
+          <t>M&amp;A Discovery in the AI Era: Generative AI Communications and Outputs May Become Litigation Ammunition - Mayer Brown</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 03:15:36 GMT</t>
+          <t>Tue, 10 Mar 2026 18:01:50 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5zYVBaWDltYjFPUlRWWkZrOEtnRDVJUWpDUnM5dWZKeVVjRGUyREp4TV9IVW9UZGU0RTdYbnc0NGoxVDFOQ2hKcXRUNldkNy11aEZJcDA2YWFRb1c3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPYWNCSXp6RHlsQmR5c2loaTNNejVYbmxPU2piM05UQlN1akZsYzBoYWJnakFobnFaQlkxNGdWOFo5aTdfQkNodEFiLWthTlZwVUdGVmlKQ2xLVGZWSGE5Z2pRZC1ZM1N3V1NkcjZ6YXlqNDE5Sm5scDdUY2dFZFZaYWNScjVVaWNSOGp2TkY4czJabmg0Z2RSTDRsaVotWF8tdk1kWXRkcnFBa0FaNkxyYWVjVHJ5VjZNNlpHdUhVcGp6QVFiT2FWZHFzTGhTVTRNVUNNd0ZRTW4yR3FSaGlMaGQ5TkVhSUhZdy1hd01ZS1BGQQ?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>How AI Damages Work Relationships—and Where It Can Actually Help - Harvard Business Review</t>
+          <t>How AI can identify breast cancer 'better' than a doctor but there's a catch - Sky News</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 13:12:15 GMT</t>
+          <t>Tue, 10 Mar 2026 19:37:14 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQU0x1enNLWXdGdm00bnIyMTZ4aklTV2VtRy1icGQtVkNwamhPWEVYUUJlWUltWUFNTFhwY1BhZXFCS1A1ejFqOVRmUGZmblZ0VjlIRktSU21Tc2VaRnJ6OUNlWHpNUFFsRU9jbi1sbWMxNWhqWmRCMW9rb1c0QmZJeTZfYzZ4SG5xazRGS2daa3BpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPcUJEUXVrX2dRQzFGNXVIT29DOWUtTlRMRzFDYk1LRmRqUmFmQUFjMWlkcUNyOGdCaVdHRXMzMjBtQ0REc1Q1OUVfa3I0V3JrWXhXdF9XT3JpUXBoRFExQnRkdGdtLXVNQzM3bHRfdlRkb1hCRGdDaWxlZkxLR2VEa2d1dDVhd05ocENlMENtZ2Vwb0VteXhlWF8wNEI?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AI reality in the UK and Europe moves from pilot to production – EXL - Insurance Times</t>
+          <t>How AI is changing the game in what we know about our horses - Horse &amp; Hound</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 15:15:47 GMT</t>
+          <t>Tue, 10 Mar 2026 17:25:44 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPQXdGVnRRWVV5SWxrcWlfaURsNTFEa0k1eVdHbmVYdjZvVF85X2FKV2ppN2kxR3g1U2hVNHdvdUVTYWpaNVFhbk82aGpLenlGSWtEMHllb3hmdGxLOWlEYWFVYzl4R3VrR1Blanktdm9tcThxZnZENVBVSUNlUjJBOTQ5NkxSY0hwZDNnYjJ1ZmdKLUJyT0I0R3VwbmRvS1pFLVVnRWI0YjJQUUpjYXRyeUs4SXRORklWOGd0TlMzdTB6cjZySjBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE83WkM1NmloX0hmSVcxUDlMSmJKRDRsR3E5U0JwMmNjNFB2Y0dQUkNCQjdNOWxFcXQ0Vlh0QWZ0R2x3T1ZGLUJEY0JqZTh3UnpNNE4xeG1ZQTNtUzFfVnF3bzJaclVCOW1CWGQ5b2RGVjl6Zw?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Exploring Agentic AI and its Implementation into MS Research - NeurologyLive</t>
+          <t>ITA and Trenitalia forge partnership for AI-driven intermodal travel - Business Travel News Europe</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 18:33:51 GMT</t>
+          <t>Tue, 10 Mar 2026 18:26:44 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOG5UZS1DQXM3Q2ctZDEzQXZfNFZZWlk1MjhyY3kzNG90WkM3U3ZKTUFvUHJ2dzNlaTUxdEdfcnVGdjdzeXc3ZlkyWHdZOG93VF9BTTA4VVhESW5UX2pGSXJpSlRPNEc3SWZQcVVUSUhsek1oX2JjUHp3azg4WHZoOW1nT1NacTRLMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOSV82ZS0ybnhfdTlLdFhqWlIybGxwblFuRkUyM2JEajJuUGk2RlVLdnh4b3dpZG1XUmJScTNsY1NFb1dMX1FRMFhrQWNfdTl5Ql95UEI3QWtPVzJLT1VjQzVHdWFYQW9yYzNRMVVXWFk4S09mTUNScjJKMVA0VS0xTERpNzN5aEJEVHI3NUl0MkRIN21na18zMlg0aGFOeUZUMTlfdGI1dHMwUk1NRkhlTEZwUFRtMzg?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>What 2 MIT experts are thinking about AI and work - MIT Sloan</t>
+          <t>America’s Endangered AI - Foreign Affairs</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 16:58:09 GMT</t>
+          <t>Wed, 11 Mar 2026 04:00:00 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbFowdnl4MTZsVkVfMTVUel9tQnpvekdLSWVtVjVJMGx6bTZxcHVISEhqeTQ1dXlPZWxPTDV1N3AwdFlKOFpnRDdhU1ZaVFhRNUczZVVsRFMxZGhzd0VnbkVKblZsenNhaUljUVp3TWFGNC1PY19yeGdIOWhBNllZVHdlcjV1cXBTVGNrSTk5WFNHbFFPQkt4eW83QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9tLTZlSWQzSEZpVkJBaUhrTHZmeXVfUXY2MW5IaDAtdVQxV0gwbkdNNTRzQ0VNckpuQTBmbDc4bFJKWVQ2NVVzbEttZlNVSHR3dEp4OEZQNWhzRHpVbTUtckVoQjFfS2JaZXJfNTBBQWhWYkFwRVE?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Leading the AI Revolution: 2026 Trends and Insights from Saudi Arabia &amp; UAE - Deloitte</t>
+          <t>ABB Robotics Partners with NVIDIA to Deliver Industrial-Grade Physical AI at Scale - ABB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 04:59:04 GMT</t>
+          <t>Mon, 09 Mar 2026 16:29:15 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOTE0yLWRGX2hrU1NVR3ViT01RdGJRc0VKenpiVlg0UnBFNjhxVlRnUFNQaUtKNVpqVi1lWEFRZlI4VzM5UDNGWGlTbEY1d1I5TzNqNGNjOVpaR3lCY3FiTWViZ3lYaklnLVBCNGk1Z2Y4VHhqT0JxRVNNOXdYLVFiTW1HajNpeUtJTUF1VWNGckVOM0dyNm91TzZfbmVHTXJTRVZXZUlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE5pT2QyY2IxOUluVzMxQTREWVVxV2h4NFM5dWlwR1E5aXNjY3dIT1psMjctcVRuWHNBb3pVay1xOHcteFc1NTRnZFJVUkJvb3dyYXBJ?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Samsung Advances Galaxy AI and Its Connected Ecosystem at MWC 2026 - PR Newswire UK</t>
+          <t>University of Bristol lays out a case for swarm robotics - Logistics Manager</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 10:07:00 GMT</t>
+          <t>Tue, 10 Mar 2026 14:37:57 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQQnM4MzlJSjdEVzVXLTFvdGFaMXZZVGM3VFVCVU91YUplUEo0ekhuUm1sMWh0a1hhZzJmbEI4bjNTZXJnYmNpTk5nelpBRXhVMzhNQXBfdk9fSFBYejByZ2RrVlV6aHBsbVpkSzZpMk4zMTNYYjNwUnUtM2J2SjdKbFc4d3ZkVW5vUGN2WmUwWFNYOGhxZUxHMGJXeTdlZXVOZmNNVXBCX0hRUklab0kwYVpJN293N3ZOZk8ycTBKcFRYQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQbzFzZ1hldkFfOTRqd0lmVXJKbElCU1Znc1VtRExzS2RucE1wYjM4VGhGeWdlWWF1X25pdGxRQVFhZHFJeVMtRG50aHpheVNHb0xtUm9KMWM3aWxNcEtaRGZLYUxDeHBjbWFTRW1tVWdFWnRiMnJxQmVqNWJ5cVhSaUY2U1E2NlIzY0hvVXVmYXllVHFt?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mobile sector must speed up 5G and confront AI challenges, says GSMA Chief - Mobilenewscwp.co.uk</t>
+          <t>How are Britons using AI at work? - YouGov</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 14:40:20 GMT</t>
+          <t>Tue, 10 Mar 2026 11:15:26 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxORkc5SmhUZF9TQUlzWEM0cGtTTmJFNE1hakJqNWdWUHpxLWRtZ1JGQy1YZ1NVcDRPb3VneXFFN25BeFJ0NzJoQ2Q3QWJkc0VoZXpGdDNIdFBwR1YyaFhpbEtYZTlaeExISWZPRGk2aUpLdlNCN0dNdFN2ZU1QU3NOSnR1TGk1eHZLbFRZeFBXS2FRUHZZMWNOX1hiMGppcmpFejRpdVZtSHNFaEE5ZTVxUW0wLU1LUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1ZbWVkSzduZW9GRWR0R1VBVXVJalBhTDFONUNaOWU4bk5XTkhFc2hjbDB0TUw0Y3U0UW5PTUVLTExNQU5BUDlRcndKZG50UHB4cld1bDdJaWt4eUhfQkIxQTh1YVduczU1ZEp5eF9ma0oza2J2bFZIZHRDNWM?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Telcos rebrand as cloud providers during MWC - verdict.co.uk</t>
+          <t>Emerging economies and the future of global digital governance: data, AI and transnational cooperation - The International Institute for Strategic Studies</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 17:29:49 GMT</t>
+          <t>Mon, 09 Mar 2026 12:19:34 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPYkFMX1lnQ0RWdDNZdTI0MEw2Mm51MS1nYkpmOEtJN1o0SU50UWlUVlZrN1NTelRJcnVMMXFVS2J3Yy1kZDVaUFhvb0c3c3BWZzlud3B3Y2RaamItT2tZclRYTDJKMU1HZlRnMm1hd0ozZGx2UWtWS19GcDRSR0hGbTNUdUVTUjVqOWpKMkh0eHg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQN2szZHRZTVQwaUpKaUZ4akxDSHFDTkZQZG1teGtOV002WUdQdXF6ZHZRZ2UteG5LSlJ2T0x5bFJYNXFpNmMwOUtkUlJYd1FBd2lud0FzSkZra2tKMnhFREdYczM1OFZ2SklsMGdsRXFWcGpYX1M2UGIzclQ4ekJRdmg4VWJKNE5JZEFlODBOSE9JQUNmaHNjVWRaSWxKdXdYOGVmeFVmVEdsMzRhaTJFUHlJbHZmSS1PUTNjRE93bDlqQk5KbnB4NUp1ZUpSSWlBZVNmd0laT2UybU0yMVlSS3hHYzNjN0MtclNPenN2UVVvYU5C?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Merck &amp; Co. picks Tempus' AI models for new oncology data deal - FirstWord Pharma</t>
+          <t>Bridge the Gap from Design to Production with Manufacturing Engineering - Dassault Systèmes</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 18:49:42 GMT</t>
+          <t>Tue, 10 Mar 2026 17:48:11 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1HSEVRV3NvN3VQZlVQUFlJekRVZnkzNnlna2tlQUExMWVjUXQ3SnBQeXczRXJjNnF0bUdTMVVjMEVsZkVFckdpZEVZR1Z3VDEyUGI4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE15Sl9vZktJTEZDbjV5RWZVcVNSR1pGLWhSd0REUUY1TnVpdTdrU2ZBcVVFNHJYVktxTUlMX09vZ1BzblphbUhqUGR5SjJBMDFTZm10TlVvV2tMalRJbk5aRlJ1MDU?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3841,27 +3841,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Former Rockhill Women’s Care employee sentenced for fraud - FOX4KC.com</t>
+          <t>Generative AI changes how employees spend their time - MIT Sloan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 20:31:33 GMT</t>
+          <t>Tue, 10 Mar 2026 14:22:00 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNbV9MWTdDSEZsdEpOd3d4SXNNUU5GU2VrVlBWc01aS2x2YXVYSy05UDR6RDROV19ocm9rLVg0VldsallmRFQ3OUd4LXNaa0pULUk3WWN6M1F4Sm9OTjlmUDZDNFRsa1hPYjZEZXlIX09ZcjViU0ZiNXdicWlRZWoycUwwZ05uMFRi0gGOAUFVX3lxTE8xT1M0ODRpSDJLZkFoY05BZ01lR1hpLTRsUnBLc214TF9IaXM4OXVHVDMxOFJ0cTFEcEt5dl9wX2JWclNWbjRQOVBqbmxJbGkya1R6c3psaDI1X290RWNYaVVVRmtuZi1IMnRhQkVoeUowckVDYWZzTHNXaDBYLU41QlZreU9xX0ExWG5kOEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMGpXSWd4X1QxV1BJMGlaUEpFa2FyZThPOGxTN0w1QjJrWFZvSGpfUndIc2d0WWRjeUgxQ2taSDVLWkRyOVlfdWtHVFhZSl9CV3pPTmd5M2F1cUV3SzRBWlpuYy10UEVlNXJXamx0TTJqN0pOMkpBUVF6RUhjQWNSQ29uemNvVGdQYUY5THV2UWJlelNHSDVRblZmRWhiSlU?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3871,27 +3871,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Defense Contractor Employee Jailed for Selling 8 Zero-Days to Russian Broker - The Hacker News</t>
+          <t>Precisely and Matillion Partner to Accelerate Data Modernization and Agentic AI Readiness | Corporate - EQS News</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 08:49:00 GMT</t>
+          <t>Tue, 10 Mar 2026 13:10:27 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNU2YtVWUzRkRELTRfMjFGbk9uT2U0dXJmUDBtV1FuN3BzWUhRSFJIX005Y3RaUkhCM1BPTmxjQkZ3QUd3S2g1LWlCV0N5TFRBUmVfdnZLU2wwb21aVjFaa3BDX21tdk90V0xCYzRXQm1teUhGenpjUl9vRmRRUHNCM0x0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSUV5bkpkcnp2VmZIaFpBeGVDY2lBTDJaM1VzYXBBNDd2NkxteERNMnpUTXZzRU9uQ0Y5SGJsRUFQZGYzbTcwVEdpVXlYa2dYVGw4clk2d1ZsalgwRVJNMlVQRTJkYnBHSW9jOTNMam1kRkNKUjdIMERCd3pNbkpkTGk3bWZOcVFBWjQ2TUZtLXhoQUNLYndldDVxSFRHZnpIbG1BWXYxYlF5UUNJSElYdHBBMG1xOVFjWER5cU5ZVXdCM0tQQzBnRWNEcS10R1VoYk5sTUIzTG44dmZmaGdSUDhaQ2pDOUhvYXAtNXFiQWd6eUZ3dEp4Zkd1bjd3Zw?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3901,27 +3901,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ex-Home Depot worker from Covington gets prison in $4M gift card scam - FOX 5 Atlanta</t>
+          <t>To What End? When Technology and Media Seduce Politicians Into Taking Military Action - Small Wars Journal</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 18:24:37 GMT</t>
+          <t>Tue, 10 Mar 2026 13:22:57 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPRFB4aDlXTWdDMDZ3MVpKT0lNa1lDSWJPRWJZZXBNTmloWDktdkpFQnBEcHZJdWJHeWhZNXFmOXRSOVhQeGViS042SEV2QU5QRVJUei1lZTJKRk5XQkpsbC1QcTRLTDR1SzBxYXhBYWZXNWpDX2UtNHlpa0FkVXd3U2RuUVYtT1NNelBEN1VndkpFTEFvT2R3dEdmcHNrQmvSAaQBQVVfeXFMUFZVNlFOSEgxU254bGZHb3p0NnBVbUdIMmEwWldCczhMUGxNZEtid21HSnhxM0FyX21JMUFlUUFqazZicG9YQXUwS2U0VVJTbmdlckgtZVJiS1I1c0tqTTVQMVRWakxXWDB3M2JUYl9uclpnaEROSTgwb3AteU1kVEVYNlpfNWQteV9kOHI4ZlRiYVdyemJuMjJwX3FGYlprSmJwQWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPVk12Qnl1WERCdzA1WVVIUFZaSWZiTkZ3em1VRnVWUzI2OUVkMzdxcjNhUlV3bHdVaWh4NlRnY3E0ZUVhN1hlWUd6TGhRV1hqcE1VUHU5ZGF6TmRmMElySjhuMGViVldHc1V1YzlnTzlrN0JHcDd3UGVUYndJd01IVm5oaFlJb0RESXh5bm94TmRybWtTWWJmMmFQaDhhQQ?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3931,27 +3931,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Former KC postal worker pleads guilty to depositing stolen checks in 2023 - Kansas City Star</t>
+          <t>The Quiet Transformations: How AI Is Rewriting the Logic of Progress - Allianz.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 22:34:44 GMT</t>
+          <t>Tue, 10 Mar 2026 08:42:05 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBHWG1ucWtpaTdzVUJlMHI2eXJaR1F5V0dtYkJuR3B3ejNSclRnbkRkRmRpNGZoaFMtdk1YLW5lVUxmbmZuU09xVHl5VW5hYlkzdkw2U05MaGY3eTV5cDE0V2JfLVJjTWdIVmNaM3hIOGFfaDjSAXNBVV95cUxObUlZRF9NN0N6RWhqdjA5cVR0cXJBdDFfOUF1ZzJSNHppM3RsZl9RQUgtX0pRZEdzMWZzeFdhSlp6bTFiM3NNN2p0cjI3Qm1raWdHN09kdjNUaEFjcGhDZ1RPMWRzcVEtX0dZcTBjNkxNWTkw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQUmJIdkV4aUhxQWJ6eUt0bWxhRF93WlY3RHJsZnpxR2pJQlJVSTd3U0xrOWY3bXFhYW5SNFcxTWtNbHVJZWJkUTNhUjM3MzV6bGRJWWFoLWp5UWFfcHNTTDJWQzAwSkZJa0NXVGhqMTJQa2NHeXlSdXd2eEphdDBwTXBGWFBGU2ZnTE9kV3BCck5uRmdncVBIbU5rLWt1eDlsS1l4WHU1XzViN0JVSnhtTjk4RDA?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3961,27 +3961,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Former employee of small Arizona town ordered to pay $194K in restitution - 12News</t>
+          <t>Has AI Ended Thought Leadership? - Harvard Business Review</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 16:09:00 GMT</t>
+          <t>Mon, 09 Mar 2026 12:18:53 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQakttbkxBT2JyNEhCRUZwRndkOEFUSkMtWFBuaXJXVFNLV29zYU9RV0xLMW9hTXRHQTlKbGlnZk9UQ01yQnctRzlBSmxEUmFCMXV6SDM2OWVJRTJxbFJqUXEtOTgtVUlaN2dIelRiOWpzS0hXaWdfZkxXTnFwYkJYXzBCVm9MZjg2WjI1bFlyNlJ6V2hlbGZ3YWpJX0dvQ0otRHFoQlA0OC1LMUtLMEJpM3B3MHRNX0pOTlgxaGR5TkFVb2sweDVuYXhXMWxhWmM3alE0cm8tb21namxZU2cxMGgwOE5mSnpjUXBYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE84bkJtenp6SDNsY0x0WVhQNFlERW9VLVJsUUdxQ2FsWW9RRzV5TWxqdU5ZZ19Sa2tDdHVYeVBWemJMS3p0VGpVVGZZMTA1THFNeE9hVXduZ0dJaFF5LTRtTUI1YXJhUQ?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -3991,27 +3991,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Former employee of South Lake Tahoe construction company sentenced after embezzling more than $1.4M - South Tahoe Now</t>
+          <t>Furniture.com was built for SEO. Now it’s trying to crack AI search - Modern Retail</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 20:01:59 GMT</t>
+          <t>Wed, 11 Mar 2026 05:38:13 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNX05mUGJPNUlQTDJTakJSMzFlWllaTjk2c0pSazlSS0tnLVFFUTJETGRFUVF4OFRMVkNfM2dpOVdqZGNXR0xEbk5LelNJVEdpNE1NeEFuMVZUOFFCeFJEUUd2dnhrY2Z0OEZoUnAtNUlTcVhCWThBODdRdzVnZnNWdUE0YWt4cERNTnBhaDR2Rkw1YWV2Q09QczE3V1l0MnlZeHU4WmRkeDhoYjBpa1EzTmlOT0V6cUV5Q3VmSHpuMHF2X0pLUmNGTVl5cUpfcjlW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQNEFYSWhHZnZkZGpXUFJfNHdWZUNvdmMwSjNqS09FeWl2YTk0dzdqTXhxVEVPZ3FNQVp5cXlWX0dZY3VTR1JfOEdoMlJBcWdWZklCQjRqLUFmYVVvUFN5MkJOLWowV3QyLUlQZnZfaDZGT0VIeHFDS0FkbVJTWWwzZ1RudHRvZnZSWUl4Q2V4TjE2M2ZuT3kwZjhtTk9BSmtNSW56NUJFSG0zRHNva0U4VVh4QmtfMFJXaUlRX21OTDhkMjByTmNNWW1ad1lXcTU1Rjh3ZjZFT29fTE1GUnFmaXhBZTlKT19jQVpfWVVBQ2NzMWkxNEM0dTBrYnh2c1lhSlE?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4021,27 +4021,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Former Hadeed Motors employee gets five years for fraud - Antigua Observer Newspaper</t>
+          <t>How AI firm Anthropic wound up in the Pentagon’s crosshairs - The Guardian</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 01:58:29 GMT</t>
+          <t>Mon, 09 Mar 2026 11:02:00 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNOURpUm12MFVSTlJGVEExNXNuOXRqMUhVWmprYkxTZkJZTlRwWVBJWnF4UUVJZWVHWXdPaE9PYTlPNE10bkJ4ck9WQ292VjRFZk9HOTlUQnJudDRsSXhvNGdIUG9XTktITjlHTVlSaFpkckZKNTd4Uy1kWXNucW9RUVJVanBOTVE0WU9nTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOLXdKSXF4WFl2cGEyR1lrTTBLNXVwNE53WEFBdFhDLUtQUUhFdmxtZ2xYT3lpVmJmbXN1T3JjRDV1WHJFakZvUFlFVnpTTWZNUDJBRDB3VmZta1NMWjVTdmJza1NiMWNob1VVNmJwc3VUZjNWZFdBQnNvYlotNHFVWW8wb0VFdlFXOW1kWFl6NW1JUFIxNF9UNw?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Former head of security accused of stealing comic books from FSU’s Strozier Library sentenced to prison - WCTV</t>
+          <t>Man sentenced for assaulting police officer and theft - westmercia.police.uk</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 20:35:00 GMT</t>
+          <t>Fri, 06 Mar 2026 11:26:00 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQbm82R2NUcW03Qk04Yzd2R19FcnJrSFFYZkxmd2V0RGRVbmxibWpUdVRJUnZJQUtKUl8tcFlXNjRkSmZtRlJLa3ZYa3NLRmNFd3N3bGdUalpfUzdSdlN6Z3NGMTlySHUtRk5mdldHUXFBMUJkeEJvVENpVFlmby10WFlTcjd4MlN6NFMxckUwd2IxUjR5dE5XUHlCUHlrd2VLTnpWYWwyaFFPOURETDN1RTdqSFdhN1JVWHdaZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNMGQ1VzVHSVhZNjR5VXVtMVZpWFpuSFR6a0dBWG5GeFdLZWhxQ1phSDVUR3hiMmxWQTRmN0RoVExuOEFiNEtVdzRKNDdRazlaVzF5WTM4cndaaDR1cmRucTFLd0ZEbUR1VGdQRWRiSzFpTEZnSTBfcVM1NlBoVkJjVHpHcTh2NFhaNFpaUEVubDNpZ0ktNGhQRW1ranJtTW1oUmZIWVVKZTVsbVdYaXlWY1VWel9mUjVOV1NoUA?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Woman sentenced for defrauding Town of Parker - AZ Family</t>
+          <t>Royal Albert Hall worker stole £40k of equipment - BBC</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 19:22:00 GMT</t>
+          <t>Wed, 04 Mar 2026 14:48:42 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQV20tZ3JXYWhOOXdfTi1ROHpHUTdzWUt5UUV2STJKYnhkb21XaURobGVYZjlOUUUwMzhodTFNaW8tNjZvVmExbFk5N2U1M1FYVldUY2JKM29WSXRFaTdzRW1ISmwtVXRUcmM4OUQ3RHc2cXV6MHFONS03eE9URGtrSlI2VGJ5OUVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBfNlZBWGRQWVZmRkFSTjg2b2ZFdWtDZXByVE13bW5xa1JPc2ItcDA1VHNsTkdPNERVcF9NUVR0cXktZmtNZHdzbDBWLWRTLWRWOTk4czR4SkRHY0Nm?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4121,17 +4121,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Former Arizona AG official takes plea deal in diamond bracelet theft scheme - AZ Family</t>
+          <t>Ex-Employee Sentenced to 2.5 Years for Stealing Ship Part Blueprints - MSN</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 01:02:00 GMT</t>
+          <t>Tue, 10 Mar 2026 01:23:10 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNbk9EMmhtTWhUeFJ6MnM4aWVkTElDN1lFQlZiOUNiM1hSRXNTeFNQdEtXU05Cb21BRFFmbWhUQlRJTTBacHhtQl93NmpleGNTUkdxSjZrVl9sLU9CcEdJYXdJcFlhY3JpNURDRk5LU0xvV0E0X0xqWkR4ZkRzVWR3dG9CaWhWeHlqMkZGUGYyNTFIQjlXSW56Y1kxSVVIMGxRaC1IOXl3aHUtVVF6ZFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwJBVV95cUxNU0pKSVpVTWZDRTM1S2ZyWWcyUGpCVm1yV1FXYXQtcVdBRnJvbVdxajZIaDJXQ0hJRXRjY3NON3l6Z2g3eEYta0tJUGdQeE16U2MxcHhQM2ZraVg1ai1mZUpwcWNlaHRRdzY3UWxvWmxUZ0lLdDZRNUxoSGJUdVlEZFRKcFkwajJtdGJrQXhXeWw1bDVGTDhTMnNSSHNMSVhWd1JIR3RXWnlTcWRYeEJ6TVFzNmZzVkhhRFJBbkdhTVNJSGFkeF8telBfaDJZaDNQdlN5Y2dvTU5sRG1WYUJmSXlmc0ljYnFhM19BTEJqVnl2c0d2cVJFSmtqblpnU29JajRIQTJkOUFQcGRueXFiRG9obm5TTVhLVE95Um94ZnNiY1RVdG9VMjE5TFBfYkpQdzh6WTZoMUVqdlJKYVN6VWhGOGJiNGdIOFFjMFZ5bw?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>eThekwini contractor worker found guilty of cable theft amid crackdown on infrastructure crime - IOL</t>
+          <t>Court sentences former BEB employee to probation for $700,000 fraud - UA.NEWS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 23:45:52 GMT</t>
+          <t>Tue, 10 Mar 2026 10:58:36 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOZ0pENHZmLTJOWlNPSTdieXdUcFQ3TWNfLTk2R2pSdnNCYk9ySTQ2V3p3bG9VM3dFLUREVHVkeG1HSXhJdVpWT2Z4Qkd0UWVKYnNlekl0SDNMYzFZVnBIQkdMUF85aUZwOUVYa0NRczgtdlFycmJweG55T0hzSThYSGw4dWEzZ3JVTF9xdjNIVzRQU1JSSW5SZ3BwWDdHTnhCaWtIMDBmNW00SVRnUFAyNi1ZMC1YcDFIUU5sdTVORlI3NDQ2aVpaVXg2T1lMYThrVGlZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOS1llU0tCNWc1OXRDTHVEZkwtLUJrTjJLbW4wZm1ydFlYWTFpTXpDNnYwTl9BUU5NdmtwM2hrbEgzRWNCSlhlS0dubVhUVlp3RmVEdmRNNVRlUGFyTmJzVXpVamZ2Wm84akV2TmdncENnUzhmbHpHYzRaNTRMZ1dSR0VHc2c3NXdkQkpZM2s0R0s0SmhEajRpOW1YRjAycDE2RlJZRHJSZzY3dE0x?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -4171,27 +4171,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>A smarter approach to tackling fraud: Lessons for government from a review of the MoD - Civil Service World</t>
+          <t>Former Lee Health employee gets jail after theft of heart monitors - The News-Press</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:27:48 GMT</t>
+          <t>Fri, 06 Mar 2026 15:08:00 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOR25zZmFDWUZma29yZFlEdDh3SnpSS2FEclpCQ3N6UHhuc3g3bzFybzlNdGZ4Rjl2RFZVMlVyeWJBdE1GQVFyd3J4dEpOQjE2ZGFRN0tVbWN5Zm9QOXpKLXlaU0g5RFROSW0yX00zWTFYSEt1U3RnTlUzVDZueWpwdFVGYkdtLWpxY0lza0Y5T19HaTJyT3pIR08ycWMtSGJMV0dia3V6UHY1N0M3Z2JVUnNGTG11SndudGJiUGZzYXNVVXBGdTFPYjg0UHJSbG0xQ1YyRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNREtNYmpjNkxoMmJiNEJXUlBtUldJYlRNNDJVbzVjVTVXRGNrT1FEek9qVl9PRXFuTjBVcHh4X2V5OVlmQnB6bVdtVXRTYkVKV2E4OEN2LTJpbU0tcFA3c1JtTXFuYXc2dWhDc0ZtX1NVRlprQzdvV1hkNkEySlQxVGNyc1Q3andDVDREQVkxS0xiUGcwVGhJb0NDdXVPVlpiendRSmFBMnplT2lLSHlOWHAyODVvalUzVGZmemg0SFA?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4201,27 +4201,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portsmouth woman pleads guilty to £280,000 holiday and events fraud - Portsmouth City Council</t>
+          <t>Board of Dentistry denies reinstatement for VB dentist convicted of opioid fraud - WTKR</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 14:13:34 GMT</t>
+          <t>Thu, 05 Mar 2026 12:03:14 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNdU85czFsS0FqcHJsRm9DSTQxTU5CdWxRT2ZsTV92MGVkR3V0YWNjaS13SVQzME8xOVE4b1ZhZVRpUW9PMWV5dUFHejFsM3AzNE1VTE1aOUZzMXlLZFNKZUFudUwzRFRiNFJXRmNHY19sYTNybmFmOENnSnY3eUNFWWk1cmgyVEx5WTUwM0ladjJWdW5YVFdmZHdUWmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxORk5ObTc5VVhhc1VsTmNCMzBzWW4tcmRidThUTmllamFUenhmV1N5UzA1SkdTUHZrOHdUbkEtUl9zOGltWnVQOF9uUkwwWXFYR3lJOV9ham5HN0E1bk02Y2VoSnBXSDFlT1k2YzdSUUJteTB4RlBOVDFsTHFLS2lQUWtZSjlYMXpmcmNKOVlrR2NOc1lkMUdURzZpVEJ2cnktbmw3WkdDWjZyTjdIeENWSWVVZkU3bXlEY2MzeGx3a3ZnWEVoOU1BNVJqUk5MTHdXSWswdQ?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -4231,27 +4231,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Customs and VAT fraud are reshaping the criminal ecosystem in the EU, with €45 billion in estimated damage uncovered by EPPO - European Public Prosecutor's Office (EPPO)</t>
+          <t>Trump pardons wipe nearly $2 billion in victim repayment and taxpayer recovery for Medicare and tax fraud, and more - California State Portal | CA.gov</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 12:00:00 GMT</t>
+          <t>Thu, 05 Mar 2026 16:01:12 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQX2JlLXF2dFdsVzV1WnYwRGlOQzNaUkl6ZS1TUUJsUDU3bFJTRWNzNG1OMWlYQTdMOWxBeFIyZjRMUlVxUEVDWEwwSnYzNWFKT0FYQ2xYcXJCTExWU2dJcTFmTVZVYnF6LThMUUo2Z1ZFUVJIRE9IekdOdl9FUWZfWTlDa3F1TGNqN1ItcUtLWDlfWWR4UXV4VGowbjZ2ZXpuRXB4MWVKQmF0S003T1pGLVZsek9WU1Jzd01nN1RqdlNmWHN4ejNz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9NYjhGMmZIbkdOaEYxejBmN2VaME1jUVBxODlLZkVkbExkU29HR21adzdNMWZlbTFWc3FyMlI5SnJIYlQ1eHF3ZFBqdXJGN3NobDczU3drcHdlNFZXREsw?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4261,27 +4261,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Careers Breakfast: Law, Financial Fraud and Cryptocurrency - The King's School Chester</t>
+          <t>Akron man sentenced to prison for rape of hotel worker - Cleveland.com</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:35:11 GMT</t>
+          <t>Wed, 11 Mar 2026 02:36:00 GMT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUHNtWmJ2M3lEd0tNUjZpbWdzWExkSGo0eGR1WHNja241UVdMVTgxQkp6cE5FTmFveWNGYWliOGNLMnM2aDVsVy11cnFIdV9xQWlvU3RJd1NTdm1GT2h4ZFdrRHVXU3pYTFFWRVV4a3ZHZlprZzdDb0l5cXphcUhCZmNPOUYwTzA3X2JtZFdBb0pHdlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOQXVIbUhURUNsTlhXMFVIV2NiOThPZTNhY3pvV3dnTURNdzhnUGVWVjRGMTFQR3R3MWdpM1lrYkg5SHlPWjBEYXZRelN5ckpUYVdLRDhYRU5FakJSc1I3ZkNsSURHam92STcxSjJoaTFiNzVwWkhnMW5DdEZuR0lKR3JTZXlSY0lqSEluTkhjeDNKdjNzWW9acnp6Vkh0d0hxbHA3ZDhvc05hOFk?oc=5</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -4291,27 +4291,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AccessPay taps PayPoint to enhance payment fraud controls - IBS Intelligence</t>
+          <t>Former IRS employee from Mass. gets prison time for tax fraud and Social Security fraud - Boston 25 News</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 06:05:56 GMT</t>
+          <t>Sat, 07 Mar 2026 01:35:00 GMT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQeVM3dXk1QmFPMXdDeGJKN3Q2S09NUlQtUk5Gcy1KVF95Ni1kYV82cDVLRlVJYml2WW12MnpNSDdHSk1fdGswMXhWTUU1Vk0xdTg4b014NVZUYVdMdkZVZ0paVTJyRGFhWUoxdDZnanViX1lpa3RmX3ZxejlGQjBTV1Q2Q2ZSRzNuVW9EakNpRmJBLS16R2tybnV0RHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxObF9sOEZKWGI2WHNKTWRqMWlFSVJBdVlpWnpPN1JUUE51SXhHN3RsZXlCV2JOaEgzcWJ1djZTNDNrbXZqeElhZnBIbmZrSjNfWW51dU5kMUl2RENfTFFDbnZ6SXlJVXU2dDZzUnBGZGRTQXNrNDNkby1MWmRnMU1nb2dtd1lNYXVjcmF4SGNNZFBGbThzM0E1cG9oWVJodjBsRVl3ZWZnRXg1YThOZm9DUWFtdWYtZFY0aWp1TURmVmxSallMY2NiUnVtdTZ3WG1aWkHSAeYBQVVfeXFMTmJmTWhZdEhVQXVsMlU4aFhtaDkwNHVGOW1nbFFzWXp2QzdfYWVvcmctVUx2eFF5TElTcF80TFlQYV91aXNCWERXSmlkVEItaEZlb1hFVl9ZNjdDWEJEcXJlMGk5VVkzZGhsVjVuUzlfZV9nVmVoQTZ2RGZYbnNCdjItSnJYNUJPc0pleDZUWWJlS1QwUjRRVml6bVAySUt2dUpqSGNDZXRfLXpQWXljNjNvbzJTSGFVZC1IQU42MzhxZlN3SldIRUhNY01DWlUzNmU3TzFPOTdKbTdRV0NoczVmazlpY3c?oc=5</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4321,27 +4321,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DataVisor Report Reveals "AI Readiness Gap" Between Rising AI-Driven Fraud and Financial Institutions' Defense Capabilities - Business Wire</t>
+          <t>Fake invoices and personas: Liv Eat contractor sentenced for $65,000 fraud - The Advocate | Burnie, TAS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 19:39:00 GMT</t>
+          <t>Thu, 05 Mar 2026 05:37:26 GMT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNZENlbVp2TzhKeExabFRDMmE3ZXBIeExKc284MVFYWmVyeHFrTFBHMlZKRGRLVllaVm13NmlKcWNjRm9GT3dZWWpFbGVTbXNhTmVWd09pVnhFbkk1UTRfSlFyWVhnSlF6TDhEbElwOW14dDNnVXNvZ1I4ZmFBdnQ3VWY3OVl0b1NCWVRUOWRfSldrVjZEUklRclJldi0xVzRINmlRVm5GTm0tRWhTTzNHb2libC1BT2d5Rk50QmZYaFBzU1YzMjZ1eFYxd2gwZkVEUzQwUFNQZXpxRURPd3FINFlMYW9zcTZtTHB2c0luRjk0dk1JSFRzV19YWmZXS1F3OWlnX0JDSlo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQLV9HUENOWDdYQmxRZU9rd0ZNM3VMS01LaEUxSkNmdk1feVh6S3pRSThCX3M0Wk9wcWd6WW90azE5RUFGdEpCMnFGNXJJNDhHMGFTblRpRDZOTGhWMmtPbkRtcGV0T0Y0S3lveHlYOUZDUmNhOXFBbko5aGZKaXhrUVY3THRTSmVwcTg3LXlfY09VSzY3YzdZV2MwZVZGcWlXbTB0R3lIS0Z4SDlxYXc?oc=5</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4351,27 +4351,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FRAUD AND MANIPULATION—S.D.N.Y.: Investors again fail to nail token developers, but on state law claims this time - VitalLaw.com</t>
+          <t>Pennsylvania man convicted of fraud for voting twice for President Donald Trump in 2020 election - 6abc Philadelphia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 01:15:03 GMT</t>
+          <t>Thu, 05 Mar 2026 11:57:27 GMT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQeHlPOXZFLWRqVjJpSnRBZHdWdWJ2Y3ZxUl9fNk16NUx1NjZCWXFfeUEwb2k5Z3UtVF9nWUhLLWhLUXljM0E0dWVYbDZXbW5oZjNzMS1pdm51bVlrbzJDMl9yWWFldVlwdklRYVZQT2xfRnAwbUN4UFdNYVZPbUlCM0pFX2EyNTRtUGVEREd6WUx5S3oyMVhEV0RPRGlMSktFd2tYeFRlTUl6VXJjNkx6TmlTU2lSU1VndUdpbXpfVXBGVURTcC1wQnRXQ081WWk5aFhDNVlvcnFtVkVBZDJkc3BlVFdMZmZRYnhObWprZnBvdUlnYW03RC05ZVoxUGxkMHRxZ0RJSGhZZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5LanRvaTlGYmF6YW96OGNhbGhNQzZvd0d4bVU0SUMzU1JkMlRjQUdra2RhMEpHSFBGQWo3bWJETDNfcjJIQU9DdkpabHBZVFBoUXYzRFd0S0xUWkJCZHBIUUgtVjlRcWs3SW1WYdIBckFVX3lxTE5NekxaMG5KMlREWEpDY2wwN0I2dzdrLWRkbVZXa2pUQnZxazNRNXc3NmxpbkFmSnZCb2ZsRnp3VWItMTRkc2xpS2k4YnpEVW00TXh4VkQxZVRJUnh6TUlienBtaHBvYkNvVFpIQy1iX21NUQ?oc=5</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4381,27 +4381,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Saudi introduces tougher controls to prevent food fortification fraud - FoodNavigator-Asia.com</t>
+          <t>DOJ: Former CFO sentenced to two years in prison for $35 million theft from start-up tech firm - KIRO 7 News Seattle</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 02:32:21 GMT</t>
+          <t>Fri, 06 Mar 2026 16:21:23 GMT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPUFFDWnR5YlJjaGJwd1JpYmNlS1dTbEo4YnVONzNWRVhMeHFhVWktOHFQV2xlbTZ2NjNSMU1oREZOZXJ2Nkh5UzJpLUR4M3FWLUVPemh0N1VTel90RElfRldMR2lSRGppa0plZE4yVmRRZ0ZjdTM5YmQ5cXM1b1N3ZC1JY0xYV2tCNWRoZ3JpU3JEdFJiWlFCdGNaSm5fN1RYUl91Wm00RVVzYms1aHVkV1VRa2hMSldlbDlESXlPU3NjZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQTm1JT1I3cVNvdmg5YUsyMVJXODFrd0Fnb01JQ1hRR0xtSUZUTTdDVDRZUUswMjlZMENYVTZoU2Z5dFM4RC1mazVlSklkbjFPUUlrVkZDcmhMQ0ZyRTNYVXBRWXJCRkNzQlNGNDZ0VFlESXJQeWd0aGlXdzZ0OGk3cHd1ZUgyb09nTkJFUzM1bzlFWjBtNzhlYmJSU3E2OW5NbTB0YzlTZFVPZDh1Tmh5R0Fnc0NVeVFsMlNPeUtib29QOTRlSWZpNGhaRmJFWUcyamlHetIB6AFBVV95cUxQVlljVkQtOVhGUW9Sc3ZULWZsQUhMRkN1ODZtempLSFMyM2hhczJZZjh4NmdHVHdvdlZPNjJCZnFSeFFSbXkzd3QzenFuazJMODBpeG1VN0JtaUJrSmdEWklDZHNXanp4bGZudGN5dFRyNnpBanJBRXZEelBUTDR3RmFha1Jlb1RJVjlJbnJ4eGVZYVVCTlYxMnd6QTJLbzlxSUFQVktzUWFQR3ZINldvb2k3TDE0SlZ1RklzX2JGekoyYjJ0ekpCNjRkSXVZMWVxZVFoSmEtYnEtN3p0VWtnbG5wU0hVTDI0?oc=5</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -4411,27 +4411,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cops provide scam prevention advice to residents at Eaglesham care home - Barrhead News</t>
+          <t>Construction worker handed suspended sentence for violent theft - MaltaToday</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 15:43:52 GMT</t>
+          <t>Thu, 05 Mar 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPWVZsZ3pLNU03cGRiUDQ5NkJ2LTNTam9JUVpNQlNHQ3RicS1ETnI4clNmYV9xR0JaaDdEOXhDMUk3a3BFY0ViM3FxWjlWblgtbGRqeFVNQklrZlJmNDFiRG8yc2hmU1ZNbU1DOHljT1RCOEN2ckxiSk9hZlAtUWl2bDRFaEUyeDB5WG90MWw0cnY3RmozRklSU3Y2RFVGQjM4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNOVItNEtKUWdOSnIzWXB3REtGWUJsUkZGOVJJUE1yTVBjaDhfbjNkcy05MXAyOGVJRWN6aDdkV1R3UU9GaWp0WVpBLU02elR2RVhuMnJGWHk0aE80UHYzZUdWNDV2VGZfT1FVUkxoblFtdFRoRDlLR3FTYkNDZ1NHOXhVcGJYMHR5UXJhU1dkeVdQcU9helZYaUJBTFJfbmU4ZWJpWlM5X2RSTzlMblF6ckZPNWNGbkZDaXN5WFBFWQ?oc=5</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4441,27 +4441,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OAuth redirection abuse enables phishing and malware delivery - Microsoft</t>
+          <t>Former Springfield postal worker sentenced for after-hours post office burglary, mail theft - KY3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 19:29:53 GMT</t>
+          <t>Wed, 04 Mar 2026 19:09:00 GMT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOdkllUUR4WDdMc1V1RHRodnJKRFRaZW5mREE5cnZoT1dndHA2RUE3Szd2cGJRcjJkb3BFMkJDenplSE1McUpwVlhTNUJaX05kT0VXTnM1WHl6d2V3bzJBN2R3VERlRHB0dHJ5TVNFZXhIWFc2U1FxN0RwNGVlUlBrRnMtd0ZnNHFDSnk2Y3FCQUg5Nms1RDZZSTBoSVpLT2tZVnpTajJyeG5OYk9wSnZPRlh5UHFnUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPVmFSWUhBbWJyWk9xWUZReW4yN2hBSVR4c3VlM1B2c2dBNUdreU94dF94TDhBR2p3NmllRGh0S0NXM3ZmY1M3a3laMmpLS0pObG91NG13Q0dQSEVWcDNzUVQ2ZlZBcDB5MTlwbW5fTExlSnp3UVotY081REtkNmVBTUtMSEdKZlVHZndqelpwZ1ZsU2FvZEpsakc4ZXdoT0k5MV9NYnUzRUZNQTlzanZia2tKbGNYVS01V2fSAc4BQVVfeXFMTXpzOHBwWFJVTU13M3lScG1sbVpuQkU4dkZqMEJBRDZkZTNyUFY5a0JQT2RpUTd4TnJSRmdJeVRqWV9kYXI1ZnRhVTItNTZjTC1KUVhGY3FYNENEV0ZzRE1sQXEzMUZPUldndHBYMmVkOHp5U1JSZXk5LWYtWEJpdTlaN0U3OXl3VHBJVmlmZ3l3OGNyUXg2bW4zYTJsWTB1dmRMYTRSTmFrV3cxTDRQV0lrQXZIYzR4U1VoTkhRY2hiT05pYVhQcmtXczJSNnc?oc=5</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4471,27 +4471,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Taiwan indicts 62 over suspected scam centre operator Prince Group - Reuters</t>
+          <t>Man convicted of assaulting Norfolk hospital staff - norfolkneradio.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 03:26:00 GMT</t>
+          <t>Sat, 07 Mar 2026 15:38:00 GMT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQnNLT1l0bU15UHlKaTlhdExxUklFWTVNWVZPOC11MnhxWDR2cEpITU92QW9tMGl0d2Nnc2U4X3VhQVlicEhDSkpxQkl5Mm5DUVZFUVR6TTJsUUEyTzduNTRnTjNBUXJQdGRFQ2c3dGdEM283YlhHNjc4VHY3bXl3aFdKTHF5cWZWOWd2b3BRZzc5RTFIdnZpRmtJN3Fud2ZWUXJ3UG1laTdpS2l5b3hnMkFKdk8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQYnp5QWx3MmJXN24xc1l3cDQxcEV0MkVtMktiRnNUNk1Jd3luUVVBck1KaUJGNkJRMmNaakhNbTM2MVJMUC1yN1VHUDFXWUxIRGw5Mkpma3l2dXNDTVgzN1NMeU0yaE5pVGtkMmdkZlZnWmU4NVpNbVNTdmwtcFNzaEZSSnNFd2RFcXhBcmZTZVFHQ3h1bkYtQkFlT2UtM1BUSDVzSGFTby1EUVpScEdhV2dIc0c1aFUzb2o2SjNjZzJwT2dqbldiMEpaN0hsYldSVVE?oc=5</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4501,27 +4501,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Quarter of UK fraud trials likely to be tried without jury, justice minister says - MLex</t>
+          <t>Former Costa Mesa postal supervisor sentenced to year in home confinement for thefts of checks, money orders - Los Angeles Times</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 17:52:00 GMT</t>
+          <t>Mon, 09 Mar 2026 18:08:31 GMT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPVDlmbDZhb1dzQzVCYmN6S1hKbUJoVFh3cWNaSFI5T1Frd19Qa3FYOTZHRTBMeEIxZFpLUm1CVHp0MTRDZGpNczVsa2lPZzVlQWcxMG1hUWFndFZwa2JtMUY5UF9wVEkzV2N5cWdkTF9oR0RDOVUyX1o4dnJqdDZVTW1tbm03cHB2MG9sTl9lYkg4TWNOVm5BeUZ1ak82TE1VOWhQUnM3ekdSTTBPTVNKT1Rxak40eVBJX2Fabmd6d3HSAVpBVV95cUxQNU1oT0p2Z01Fb015MEtaVkI4MS1UOWJSUTBPUy1mcEFkOHFnVkhkV0VqbmF0UHFwclJlZ2hBWmhSX2hLTnZVN01NUmR0eThEeTcyekVYeFhybkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdldIbzNPMXhsY19hZzFaZlYxOFpPZ3hPZGE1Wmx0bm9uRHBsUmxKYmlDWlFFbW1qQVhNWk5UMHNpNTNER2pybXBLV2Q1VkxxWUVYZ2NvcThKU3pZOTU1YWZaY3BnbUZ0azJPU2Z5VU5ocDBGdzNRWnk1SGJrdUhIejR5MkdmcnZ4dnZPYV9GVXV6WXRRUFFKaDFrZDdQb3pha0gzaU9mVXQ4T09YNVM5NnNKT2o4dmt2eUJBUDRqa2FvU3JzQUYxSjg1b2lmcC1Hd01r?oc=5</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -4531,27 +4531,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AI is baseline in fraud and AML, but complexity drives higher costs - CRN Asia</t>
+          <t>Motorola rival ordered to pay $50M fine for stealing trade secrets - Crain's Chicago Business</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 18:51:43 GMT</t>
+          <t>Tue, 10 Mar 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQnI4LTFHdXNXbXlmV3FtUHVIcDJlOV9WS2x6T0ZUQU51c1liZHh1Y3p2anlMZVRyUzR4eHJ2VnNXaDRacS1hd1VGWTBHRUJpMENIMmpZalR1LU8taGdjMkpXd2l1U09nNGxnNUNYR3pibllaalNRRDZtb0tma3gzUGtIUm84Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPRGxQSDd5bFB1NnV1Uy1OTU8zWEJkeTZWVUxRdEVIbTdYaDM3c3lIYy1kdXk4dHEtWXRxTnpzdnZtQzFYZ3BPWksyOGs3RzFYbElGc1hvRURmRjhxLW9UdTlBejJqTUl4b1BYZE9VamEzbTVxSXFaTDhSSEE4TmhYekNHeHFPRmpMamN1eW1iM0JYWG5YZkFCQWdR?oc=5</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -4561,27 +4561,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MoneyLion Now Offers Members Scam and Identity Protection Powered by LifeLock – Company Announcement - Financial Times</t>
+          <t>Ohio man convicted of three crimes connected to stolen credit card scheme - The Norfolk Daily News</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 14:00:00 GMT</t>
+          <t>Sat, 07 Mar 2026 15:26:00 GMT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOSFd5eGNNTldhQUpnUVBtaDZOcV9TUjZ5QkRDYTJwc25ZdnFUQlItbGZRLVctS2ZjajQ3SHpMNnF6WGNWb2pWanl5S00zaWctUUgtZmZHMGszTjRvSmVneFlsTno0WnQ0R2JaaFlSYTN0SFNmN3ZGb2NYNkM2dWh2dkg3SktfYWJ2eklUVjBQNW9YNzMtVmhwVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQd2F3eW1Lc1lRZU9IdEVXRDRiYmloQ3hpQW5mTGk2X29ja3lPV1FoNTNQOVlwdXFnaktrSmw4SGxyWHRlWUd2SllhUmswQVJqRThkMi1TSUZlWjFQRHdCalE1Nk9vUHNSc3R3bFB1LXFtRFB0aktQWl90WWFFUEFSQktwRDVnMHd4NmxoMW5jOEdNczc0VkZCZFhZUVNIanNiTEJLTEFDSU1WQnRVcmxzRVVSd0JpOVdTMWdWLWdJekJVT0tKVzlpaDhJZ25WVDB0aWthcGVFeFJNbXJaWXppd3EyWkVvNFJrMTFXNGtxUWM?oc=5</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -4591,27 +4591,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Two people arrested in waste packaging fraud and money laundering probe - Sky News</t>
+          <t>Former Missouri House speaker sentenced for pandemic fraud - KMOV</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 12:32:14 GMT</t>
+          <t>Mon, 09 Mar 2026 21:15:00 GMT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVTRQcVZNakQxZDFYdHlFTDNpM1p5ODl1cmlPSV9UdUhTenhFc05FbFctcU1KMGE5Wk82NkQyMGVwV25Nc1kzZ095M0VibV9BSjlHbkZQbl9ZSy14eHJ2ZUJjaHROM0Z6NkVBQ2wyNnZwNVcwbGtHRTFibnQ0WG8wQTJGZ1V4WGJNOWx4bnNRWWI3d3VVMUtxSGtQN1drcVFFNDlILVNSYnFTaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZlUwYVBoYnBxSGpGQVBuNFMtNlFRbDRTZU16VUJ4UkJ5NkRNajBucmRCQjMwNU05R1JJa2xkRDlsN0pYOVJqUjloZXo3b09SZ3h5dVJaSlJJM3hyempZV2NCTHlFVmdVZ0VxeHptZmVMUEczYXpBazBDd1pWY3BRekZOUG5FNFdocXBCM1h2TUFQeG1MWDNOMFNR0gGuAUFVX3lxTE1XQUNSLUZ6RXZHdjgwMVgzbXBJZzNJUFRGLWl3dUtuTjBvWXF0eU1RVThBNGpaOVNXblFsV3hIU05ONFExeGhtN3kzSE1wWEtNQlF1dUY5bjBjaUZ1blpIcHp3MU9nTUo1OW9aMmk2dGN4d1ZidlEwaEltQjBKVF9lMGFCWWZFa0tJWFdSSlZTM05pMGszSUN6UThYcnpUZzJUdTdWVUUzR2Zmc0VCQQ?oc=5</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -4621,27 +4621,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>The Dark Side of Luxury Brands: Fraud and Laundering - eSecurity Planet</t>
+          <t>De Pere man convicted of federal fraud seeks court relief - WBAY</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 20:36:39 GMT</t>
+          <t>Tue, 10 Mar 2026 20:44:00 GMT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxObE80bVlYYVJsNHRieWUyVVNQM3FJNWt6WWlJUmtvQXo1RndyMURjMlh2SkVFd3dmWWxPNEFtV2pxLW9ueFQ0b1VaeTA5ck1XTVZENmpGZHg1RXR2Y0xHeXZnQkp6ckxvX3JqamRMY3RZQmtUbWpfUHI5dE5XQmwxLUJwUThNUmM4RFl3N194bEJoMFM0QVMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNdHNxWkdVV0pUWUpPQUdLeHNfcVJpYnZmakJlQ0pLOEZXNDF5aDZYRnMtVmcxb0EwQjdXcGpla0dSYUNQQnhjZEItUVBySDlhOUFoZmpaN1dEckFVcjQtOFBUQThQVDBpcW1pbFRSTzBxQ2p3amRGWlNBdHNGRU9yMjRlYzlmTU81SWZqWTJndUPSAaQBQVVfeXFMT29ad0ZNWlVJcUZOTzJldm8wTXpVSmtfOWhZbl9CWEhhaEJKOVo5NEFUbFNKallrbUE4SnZxcDlmNk1hRFNvcWEtWVhLQTBfSWo0ZEtteTAwTXRWUjh2Y2ZwMnlvaXN5bXhIQTBITjdTdUF5c2dWbThUbGdWTWJvME9PeEhubkh1cUpJOWI1aV82MUJDc1JsZXF4YVFaem1OSTcyWGU?oc=5</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -4651,27 +4651,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Interpol-Listed Scam Suspect Arrested in Morocco - Morocco World News</t>
+          <t>Former Yuma school employee convicted of stealing $86K in public funds - KVOA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 18:11:59 GMT</t>
+          <t>Fri, 06 Mar 2026 18:34:17 GMT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQcTF2c2hkNVV1emJtOGJJSmdxd3hhVUJvNUZVU3dleERPUkhPbURlNGRGQUJwUnFWVXgySEx5Rmc4Q0N0QzBrMXRiTHBPZHkxdkxjYmxJeFZIY0NMZGdxbGg0ZTZVRGhvdkJ4ampYT3J1d1pPOVNvdWJMNmdCLTNsUFVfSnhwT0c5M3RMT1JQR21xN0dDbVQyQ2FJRS1ZZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxQSlBsLURMb0VJdDdVaFEwV3h6d3h4UFN1MDBWNWtvZS0wUUpTNEQ2cnhyLVR3bGtrQXZsLVd6VmktRU1iR0JBWGhabFRLTDYwbUszMXZoc09NNjd5QmV1TmxhZGFaSTZMNkNldTFxRWxoWDFVMzRJa25teU9FUEtwU1pWTGM5dXlTblBmLUpuR1dlODVQV0dEOTBFdjVjY0dPT1ZjemdES0Fva0pmMkxyZUJMUldyZFlmWE02QVh4eUxQdW1laVhfV01aeFNabWYybTI2TTFMQ2FxcVQ3aWNMVV9ZbXZKUQ?oc=5</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -4681,27 +4681,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Man admits several counts of fraud and wearing military uniform without permission - Manx Radio</t>
+          <t>Three executives plead guilty in $528M pre-IPO investment fraud - Brooklyn Eagle</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 18:07:00 GMT</t>
+          <t>Fri, 06 Mar 2026 18:08:57 GMT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOS1N6Z1lGNWdJYlc4TVdSMUwxNzhweEN1Mm9rNU9Ta3R0MG8yVmxIY2ZjUTVqcGQ1N3RGbTh4c0JqYjJ5bzYxdExVWWRVWWJIR2lrd3VWSkpXUGhTX1B1dTZSaXlJUUxGQ3N1SzI2aGlrWEtWVkRWS1dtdmUzSFVnb1dwQ2l0N09NNEM3UkRNZE9KNEx1MGtKVW4tNUlmSy1LWDh1QzdoMHJCMkx6bExrXzVsMTJ1Mm5LQjBodHZZRWo5V1JsNHozR0NLNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGlnbDVaNk9qeEg5c1RNQXRlVUt3S2hkVmNmMFpoTXU3Y0J4bW9sbDB5RThKWnBRQm5GNEcteDlRc2lvd2NpZnY4ODFnLUNjb2diNXJ3V2ZiLWxKdkpmWG9TdjM5RmxUSTJua1JXdGRZUzJMOVhFbHFDakI3TTdwUkNXMzVqZl9wb3hiZFBIcVYwWGUtRm1nS0ZTYWQ?oc=5</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -4711,27 +4711,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Stablecoins account for most illicit crypto activity, FATF says - CoinDesk</t>
+          <t>Abdullah Alwan, Mughith Faisal and Basheer Faisal: Three men sentenced in Phoenix for defrauding Amazon o - The Times of India</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 18:00:02 GMT</t>
+          <t>Sat, 07 Mar 2026 14:31:00 GMT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNdV9ISWFHUmxHNkxLZEJwZTI5cXNEajVCX1JJdGFmYnpPeUlTSXA5d1lRMGxQX05EMDAxTkpWUHRnbUJSV3FLLWZmVHVjYXhYVUR4V3ZlVnlaTEVPUUFUMkc3N2xuZ1pSN29vOExNd0xkdEZtQU16QXlKMUpGT0NUQUVxbHEzVnNGZUNPeWdha1lxU0g1QmxIUmFMajJCWXlHdGZrbk1od0lCQjg4aDRhRDJhOHhyTzNvS0ZXT1FQOTNhbHRqanJQYTl2WHRqQ28zY3NtQzhZZUFWZDQzNE1FeFl6NEQ0Uy1WNXh2bkNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxPUkdnV1JKcWhnbEd6SHlDaXc3UkVUY3liLVN3U0tlRmRqQW5GRnZXWU5mMl81T2hER1BSRVRLN0plSEh1c2lXV3BLbFZFUXNtZERBU1Y0dDhOc2s5bGhNNmRxM1YwMWNvamNibUZkYy1uNEFnY2hEcGVFRXhNVHdDX1gtbUEzUFVheks4QzFaR1QtdlhtZzRmdnVUdEs3ektZSWZ1c194dWRkOUJhX0pxMU1ONk11NERQbWZQNjV5SUdNdVQwWGxQbjN6LWhremVCemcxcFJrTlpETUdxNXNPZlFKSUw1cXVNa1kyV3k5dmVxY0I2YTJyYktVeUJlVDdCellCbW14bkE5aEZnZENnWm8zMjNya2V4YnE5MktPclHSAaYCQVVfeXFMUDh2M2dWUUdod3BJN1pUUVpDQU05b0JLTV9iUVRGQmhBZ2VnZzV5ZzFiYmpYRDJOSTRfbHdmQzZoX2RHZUFSTkJiYW1FUkJYdXpGRDBoZWhuVlBjN3FWWGowQXZOVTNyV2Q0VVZOTTN4cmMxcE9rQ2VkQ0FKRjJQSy1RTl9sanJxVzBFUU1XbDE1ejk4dkdsTzJiQVVXamhmNzZFdm5VbGlHZDUxcU9Nb2tEb0VkdTNmZGpXanhlYlU4VllhdG9YdVQxc3lnQUthbHVaaVRzSU1PU21LUUxoaFU3a2ZfLU5MUDdsR1gzNDMxTFJETFN1WTRKSm85Z09jSTF0cFp3Q3A0SnAwZDB2SnRmRFlJdFhmTXdEX3NENjFQNmJadVZ3?oc=5</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4741,27 +4741,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Study Finds AI Is Fueling An Alarming Surge In Sophisticated Phishing Scams - HotHardware</t>
+          <t>Mexican national living in country illegally pleads, sentenced for federal fraud crime - WV News</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 18:35:00 GMT</t>
+          <t>Tue, 10 Mar 2026 18:20:00 GMT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9Vc3F3OWh0bllfVmtBY2d3b1lnZ1RKb1pkYUdRMmdUallYZ0Fya0NUSER3NjFMRk5GM3FIejZxOXlJTHk4cDJtOHJBUE9QT01SNlNsYW1CN2ZheDc2cGhVc2dnX2tHRDJWQ1VsUlcybFFSTHNEX2JHREpDMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOVmpFdnNzQnd5NmgzZDRvNHdMVDVfblh3SFc4eG5hNmY2VlFldS1SS2RjN1B1RTV2ZkUxejBWU0JveEdjVk5VRS1BY3FrdDlyRmVaOTg0MHZ1RklmTlBLSWZGUU5NdDREX1hGUEZoVjNPN3g0WVI0RVpHeXNUMXEzakU4dTBfNkIxdWN1Sktmb3NFdEpzd3lyemJFc0dvMV9Jc0Foa25nZjFLY0kyNElWTlY0Y253dDhWS3E5aDVucGp6eE1BZ0h0SjB3ZkNWZDFETnp0Szd1QmY1VW1wcUZxcmhpRWxXMlNGYkc4R1lTNGgyX0N2RUdlRHdJMFVjRWc?oc=5</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4771,27 +4771,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Payments, Fraud and AI: Why Retailers Can’t Afford to Ignore AML in 2026 - Retail TouchPoints</t>
+          <t>Former Arizona attorney general employee pleads guilty in jewelry theft case - KVOA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 14:23:00 GMT</t>
+          <t>Wed, 04 Mar 2026 22:43:00 GMT</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQZ2NHMGJ6cFVfNE1fQl9xeU1rbHhLLVpHMVVEQXp4dTVVczlsRkRjNHEweWZhQkRPenNnMkpGSDVEQ1Y0WjI5M0dvOHB0SWE5TExWcFFySnFhNDVlQnRMTHltRWVSbmVTczN2Zmp1RjV5ZElGT3V3QXhNM1R3VnZTYjNISGliaGpRblR6LWZvbERmM1QydElqdlNoYnNDSUlaT0VNWW1tZTFFbHJVbUtvSF9DelNlQ21yeDRvZHFFSjJ3NDlycEtWaUlKZmZwZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNV3czNENtZkJ5YWw0Unp0YXhwS2gxMElGS2VuaDdaR2Q2OHRlZU1UYWxDSkZGUS1BdnFqZkxHSFhLTkhhMzZjend2T0h4ZUE5Nm1aT25BZy1oZGJ3Qlh3UEFzajJVb04xSUFSb01RQm9pZTR2QUdEeXJxN25LY04yRl9ZbE1USlROLTU5aWJhTnZSNEdIdEJabnhIVVdudHRMSDd1anpyV280V0RUU1VlRXNtZFloYkhnX19KcDZTeEh6RDhva2hyeHZEeDJWTVdjQmdlaExLdjgzUFBINVZUN2Z0RDBMeWpIT1NITEZJdw?oc=5</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -4801,27 +4801,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tonypandy man given community order for fraud and driving offences. - aberdareonline.co.uk</t>
+          <t>Hawaii couple convicted in nationwide tax fraud conspiracy - Hawaii News Now</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 16:41:41 GMT</t>
+          <t>Mon, 09 Mar 2026 20:44:00 GMT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNOHF6cXJ4RkJQTGxxb1BMeGRnakVFQkFZSUowV0FsdGtOZjRWY1ItWWkxU2pUVXJoc1ZWeEY2RTVVeHJVQnBKM0RIZTlvb1EycndxV1ZhUGtRclc4RnJEV2daQmhLekN6bUVLcElZaHZmel9IYkJrVk1hcTVob2FxY3FtVHMxWlNTbzk2MmhFRXBTODFjcmpvbGpLRkVKOU4xY253emdFWkJyME1XN0JTcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOWDM5R2twSFd6LVQwS0tNRHdZQTlJMVJEV3A3dXJlZUZjS0MybWlIeG53b3lZaExSRU1QU2EtUUV5UUdEMncyLTBiUkEtQ1VoVVYybjZSRjNEU3puM2hSMGdUN3VOM0R4d05pRUhjQnhYTEFlb213M1prelJaeXV0cmtpYUNJY3hhMkFRZWhHbi1YYUQ1ZUttdWVQN0VGd9IBsgFBVV95cUxOTDhVbzJ4WHgxbDdpUU5mNXdEeWVra0xfQ2lYYU9oU2xYQlVMd3IxbFdrdmRoTkM5c0hwNVJtTVVXQzhLamZCdU9EZkVuMHJTZlFRbjQ2SGs0c2F6YWd4TjhtcEFSdms0dUt6NG9NNDNTOEVORldnRVpEaWc3QUFXWlZPRXVKUUdwOEJZbXNHSVpZNGdGMUFUMGtQdEVSTHFHY0JGeXFyMWdKR0NoNEcyQW9R?oc=5</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4831,27 +4831,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Mafia accused of using Naples hospital for fraud and illegal transport of corpses - The Guardian</t>
+          <t>Former USPS mail carrier pleads guilty to stealing mail - WGRZ</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 15:06:00 GMT</t>
+          <t>Tue, 10 Mar 2026 18:32:00 GMT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPRE5MaXFTSlp6eU5qQVpUbUt2LUpOZUh0a0pFZ2pXM3M2a1RVel9FVm4yckhMcG5DN2NtcDhURjR2OHBldXVBZDFLaHlZT2tySmxIQ3ZFNDA4RmhOSGNyQlJaUmFrLUwwR2RmOFJWcU9Ga05HdjdmWHo4ZHZKckJpOUtielFVa0s5YWlhdkFPWmpaX21rRk93WkkwVGNJazhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZUN0V2dPM3p6UGZ3ckQwWHc1UWtBTmtmeHVrNkRHWU51Vy1DVGJGRnBZRWVJSnpFTHMtbzE4eTB6UUJSVmtKZjJNMHdTcG5PaFI1NEZqME1pQ1NVTTVYRmpaZGxXOGdaeENmYURfQmN2RGdDaUNuQTZ2ekRxNS1jVlpqRlpCWjNldWJLMTVUXzNqcUR6c1I1WXhvaEhKeC1TTUNoTHJnT0JTbFFobU9ZWmhtaEdNdWVRSGwyUEw1SlNsZENtTEliUXpn?oc=5</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4861,27 +4861,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Police issue alert on officer-impersonation scam | Salisbury And Avon | In Print &amp; Online - Salisbury &amp; Avon Gazette</t>
+          <t>CT man who prompted Amber Alert to be sentenced for stealing $370,000 in federal benefits - New Haven Register</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 08:55:46 GMT</t>
+          <t>Mon, 09 Mar 2026 15:39:09 GMT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQZlZDZWFaT2xVcmZtb0Y4bzBpZFBFeG1jVkRlQUloSmRrWFduOTZmcFNIZGxFdjdaWjZlX09YaGEyVHpPZHBGbk1vdnZ5aGFEWk9jbC1jMVVndDYtbHU5c2NhOEpFYWs3VGYxamIzY1cyc2xiM1pSUVRUOUx5ZzBGS0VBeUtMYVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNWmJGeXFCUE9vSVE3RW9JMm94SDdEQmhhWHhFck5SVWc1cVJ5dGNTTFVUaThrckJJTzNneFdwbXNZcERlR3ZJZTFZVjlVZzN0dkptTW1IdlBJVmNsRFN1SDJwbVZFaXVUN3dmU3JBcTBndXhjOHNpeHltOVYyUTdGbXY3Q1ZYcHB0LUIzd0dzeHRleFJ4ZzJIUmZUX1k4YnZCekVvYQ?oc=5</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4891,27 +4891,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>This new phishing campaign uses a fake Google Account security page to steal passcodes and more - TechRadar</t>
+          <t>Three Arizona men sentenced for $4.5M Amazon logistics fraud scheme - KVOA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 12:25:00 GMT</t>
+          <t>Thu, 05 Mar 2026 04:03:38 GMT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPSnhXX2Fsdk1DRmhGYklyRVNXM2s4SWNIalVFdVp5ZllJLTdZTWVzMlNSXzdRUDY0TGM5cXNSSlNpMGhLV0JhZjZ4VzkwUV85NzBhSFhWX05kUGlMWTJicFNfUnNGelNTV3pqbVZMd0xPb0ZvcTByQXpSUExULUdpdVF2NDdfaXhaQUFnY1VOLTBOeWo5V1E2OTlmb2hLYnF1R2liZjgyWUFFdUJaOUE5eXgtODdVRHMyU2Q0dVpkMGtXWXpHWHhmN2xVYXBabUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOT081NmZsRk5pTFJhY1Q0cEl0Nm5sVzVhbExKNC1iUklEczBpaFpzV2ZLaE5EVjFXOFBPbVNwdFB3ZkUteW9xSlhuNzJaTlFGQlFmcW5MVU9IUjlaWmFNWnE2Z0hCS2YwczdkQTBmWHl2cTNyY0cxVkVlQ3VrTVRFVzBYSXlkVzUzVWNtUUhuOV9LbUljU0FBcG9IRHQzSGRJVFBSUEhpNmRHLVZubEU0bGxFZU50a0wzWVgtNXlhU1Y3Yldla1VMQVNXbUNnMU1CMVBjbFhxZUUzOTFwSV94czNn?oc=5</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4921,27 +4921,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Thailand seeks arrest of foreigner accused of $30 million cross-border fraud - The Japan Times</t>
+          <t>Former Pittston church worker gets prison for theft - Wilkes-Barre Citizens' Voice</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 06:21:00 GMT</t>
+          <t>Wed, 04 Mar 2026 18:38:48 GMT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPSkxVS2lwMXZZck9LZERDckhQNlhLT3FvRTlYXzVWOW1pajNVTTZsX3BWd2R6cWwzR3lnYzJYNVRtd3pTN1FCN3MtMnZ5TXAyTjdRdWpNQWFfYVVTcEhHOXhpeThPQm5kS2NLZmlCUXBFcWZ5bjZJRlNwRkthRHFOOWdjamsydk5VektOUzNGbmdtX05iVm9UdktJN0RMWTRsdC02WlVrY0tEQW1w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPclVvU1lHbWpDbEYxZ1RhanJqRWcwN2o1U3FMWmNzenFobWxvYXU4VF9QM0ZzT0FTUTBmZklwaS1rSl9PNk14cno0VVFncXRCaVVhRUlnWklsRExQMzN1SVNHc0VISVpaQ2Y2Wl9wclM0bDdHN2puWWJYbFlSbjVzMU9nVk9mZENXUFpkcmM1YW05SHF3SmZkZw?oc=5</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4951,27 +4951,27 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>62 indicted for laundering over NT$10.7bn for Cambodia scam centers - Taipei Times</t>
+          <t>Advisor convicted of defrauding NBA players through viatical life sales - InsuranceNewsNet</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 16:00:00 GMT</t>
+          <t>Wed, 04 Mar 2026 15:38:23 GMT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFAwZDJLb3hpbHZ0Rnd6UkJyVmdEdW55YTYxRmZwYWJ0UmlzTDlsNUZpV2xlZWVTd2ktRTlMNktsS09rNTM3a1lsWnpSWHU0N01uQWtZRDhJQXJ6b1VDY296WVZNSFdXR2dwUnZJejZvSDZTVXd6b1JNRDJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPelBCY2JUc1E2blhqT0F2Q0loQTdOWWZJbTZUalVMT3RVUWN6YWZBbnFsSFlWWHI2VGJ5c1I4bzI4Q05NMC1xQUgwMEcyNDgwUHZHLXlIZjRZTC12bVAxOFFrcW5wQl9qN0ZmM3lVc0ZQemowRmM1RU1lQXRid2VrM0lQelQ3VXkxRU9IdEFYdnJBSDE2aEo2MDh4MklTb2tCeDlDMXJ3aWZ6dkNDMGdVYg?oc=5</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4981,27 +4981,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Romance scam victim gets $200K back after Westminster police investigation - Denver7</t>
+          <t>Why a convicted ex-lawyer turned on others in New Orleans staged crash scheme during trial - NOLA.com</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 00:16:19 GMT</t>
+          <t>Sat, 07 Mar 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNWHkzeDAwaGp3UTdZRWU5N1dyQXRIbGl6Y1k5Tk4zU1V4b3VZbTB5MjBodFduYW1qZXZzb3FCdEpsYkJPVzFTUkY0S2dnYTk2elJpbnpmSE1OOFRMNHFqRzZlMXVDWHRkN2x6dE50VVFpT1JoZFhxNURIS0x3NWpVT1RmM3VWbjZNR1lfU2tHR1lkVUI3M3RWRnlGMXpnQVNKQnc4NVNIWlU3S3JD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPOXRLVU5pYmgySF9UOEpyN2VON085UVppaDRwUVdpMC1oTEZUMXZ5SUU3Uzlkd2czUnY3RTEtb1REUl9seVJ4bkdJSmhiWDFMaVF2WkQtc0o2Wmt3Y0ZldTlpSG9XRW9LNjZscGIwUEM2ZnV4YkJvUV85aUFyekViZEZrVmZCaHVCRVhGdWhXVHotWmdWWVlTSlZkbjFsWkJSejRrbWIzNWx0aWpLWWxfRnp0MkdMRV9MZlBZcmNYbktuSkxuWUHSAcsBQVVfeXFMT2hONVh5Rmo2eVBJTk1OeU95ZEpiSGVGLVI0ekctanZrZlBqWDVlLXM2R3A1LW43bVZvVVVKR3NvRzFBRDJKbWtLV1VyaFNNSnRCczBJS0NkZHh4WHZxOHVUZy1MZlBWS2hpeExEYkl6WWdKY2ZWZVNlcHc0UjhaS0NiUFRZS3JkX0M5cUk5SFRKVkhIQkdKQ3Q4UDRhM1lGTUdKYTRUV21QUmVHbURDa2tVTkJocDkzMmhsYjFsWGZ1Wm5yYU5fREdBQTA?oc=5</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -5011,27 +5011,27 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avon financial adviser indicted on fraud charges tied to $3.3M ‘free-riding’ scheme - Hartford Business Journal</t>
+          <t>Jail for former bank employee who gave scammer data on over 1,000 customers in Singapore - The Star</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 20:13:36 GMT</t>
+          <t>Tue, 10 Mar 2026 10:51:00 GMT</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPOHpMLU1OejB0RFdITVlHNl9STTVNQTd1aGtVMk9vTUVvZ21kOEF6MWJ4UEt1enlvTkNLUlo3WTdyQThzVEMtQ0VtcG8tS2VHMHJWQkJBV2lZVnhsM2tIMlp0dVhCd3E0b1YtVV9KRmIzMl9FV1kxckNpd2VzTHBwZHBSM3hBM0NHaVlyZHR3eWQ3aVdkYy1ncnNZY1lzeEEzanRkLV92ZGExQ0ppdDFUd2QtNGtnNllNNGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNTl8zUUtGeXZFdEFWWVJSdnBZeDJhc18xLXhLUHdNUS1CaVNzTUpiV3cwaXpMQWdIb2dFQkRjWWlzbDl1dTVuR2UwM0t5RjVINERsTzgtNk9JN1kxaGtLSzRfYmVIUllHTXVQX0JDNXJGbDJTWTFUeDlObEx5QnFobkpGSWhWN280elRXV0RUMWxvekExcW0tblpQSUgybExRdlJtWFFoSHBWR1Y4WFQteVJwMEoxN0J6Sm0tdHJxeWNTT2c5cE5LZnFUY1VtSUZVUGhzRW9oRFFaVzlqOGNDbEkzTDg?oc=5</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -5041,30 +5041,900 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Trumbull trucking company owner pleads guilty to wire fraud in $3.5M Amazon fraud scheme - New Haven Register</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Fri, 06 Mar 2026 20:37:42 GMT</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQYzNQQnF0SFRyR21pZFlLOGwtUGl6R2RBa0VoQl9SZmxMcUxJSnBuWTY3SU5uc3dFWEVVZHhONmo2V2tTN2dhVTRuN0NydFZ2YUdlaWpFbXVlamhLZUJjOW5iaW53SkNGVWFLR1pROHVBMm5keEVRbm8yNnFpMFI4UlE5RzRyRGNuaUVVYTBsQVdXbzVfQXZ4dzFLQ3N5RWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Jamestown man sentenced for taking, selling water meters - Jamestown Sun</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Sat, 07 Mar 2026 12:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQM2xwQUFTcGdMdF9UdUlnZC04ckt4cVV3TzZVcWVIOXc3MUUybUgzTUh2Z3ZrR211RTdPSE1VeTdaLUczSHVsRnUtQmxfc2JzMnloZGhHdjVZWGJXSk9mNl9zZ0tUX3AtY2Y3LWpMZ2xsWVQtNDBfbTE1YXJ0U0ZpR2JJRjZNeGRQTnVNbVJwbGFIdlBPcS1hQTQwRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Portsmouth man sentenced to more than 2 years in prison for auto loan fraud - 13newsnow.com</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Thu, 05 Mar 2026 19:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPLWRKT19KVU1LWmpiUGFsSXBpUVlvZFRPbGg4RTZIVHVTWWJQdUxiNERCbERMTm9KY1BySWtrRUpMN3JtRFg4OGRybkU1QVBsUGhORUVkR3c5T3oyUFB0aFhrRnB5amEzRWQ3aUpQaW9oVG1sa1Y2djlVaFY2YURmZk5ibWgxaHFnd05sQXpVM3ZVUkRjZXRiU2dWRVZVaXJub1laUFN3alRDQ1U3LW9nRG5jWURQLTZSVGk1cWRRS1BuTkwzaG1Nd1lDWGpIaUNPNTZpUk96bk81WXY2V3JrTHBEenJyQ05vV3BCQ0ZKckRfT0dwS3VCLXUzWXNKM09EdFFXM2RDYl83aFU?oc=5</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Woman, 31, an ex-UOB staff, gives over 1,000 customers' data to scammers, gets 1 year &amp; 24 weeks' jail - Mothership</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 17:46:43 GMT</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1RM2Nzc014cDdSTTZSOU1Bb1lIc2g3QVBHcktMSFl4Q0FVeDNkLU1jaU52cU5ia3RtTzVpNl9ZYW9GRjhNSzdmUHRwMk1TeDRmTC1sRHZzTWVNQlc3RXNJeVpfMHlqS3A4TWlORQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Sandy man sentenced for stealing $65K from storage units - KPTV</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 16:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQQzA3Ym9zQkZReWs4UkRUdlYxNlAtSUFUbURBOWxIY050c2h4dVg2RDVxbTR1Qkc0OHFPNDd2cWhROHptWGliVnJYZWNTWTZBcHIxZnJJclBpdk13WWpxQWo0Z012VnBVSDdmQXpLcldvYko4U21Ba0JQS0N3U24ybUpBOHZJT0E1ZXY2dGM0QlViU2xiLTdkRzJ30gGaAUFVX3lxTFBDMDdib3NCRlF5azhSRFR2VjE2UC1JQVRtREE5bEhjTnRzaHh1WDZENXFtNHVCRzQ4cU80N3ZxaFE4em1YaWJWclhlY1NZNkFwcjFmcklyUGl2TXdZanFBajRnTXZWcFVIN2ZBektyV29iSjhTbUFrQlBLQ3dTbjJtSkE4dklPQTVldjZ0YzRCVWJTbGItN2RHMnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Medicaid fraud scheme leads to prison terms for owner and staff at substance abuse facility - Roanoke-Chowan News-Herald</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Thu, 05 Mar 2026 20:28:49 GMT</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOQ1lxb0d5VFFOU1gteTkxVkpQSTFyOXlEbVZnT2JUNjJhT2VSaHoxTzBXQ1UxZjhtSzBFX3U2SzA2UFMxTjB2QzRVTjB3TnlBOTYxWmVGR2VDa3J2T1JqYlhNUi1ZR0ZCUXZFeVluczVmeUFMQjlKalNGVTUzajRZNjNtVDFJb1BZMEhWMHB4b2ozZVJkM3NvZGRNWGVCMkRXLTV6RHlhZXpTTV9pb2xJTkgwb2lyeXloS2lWQlctUUw4YTRqc3hoUF9KbVl3c0VJcXdMckZ1dkZzUi1XMlhN?oc=5</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>3 NY men facing 100s of counts of fraud-related charges in Greenwich, police say - Greenwich Time</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Tue, 03 Mar 2026 16:25:57 GMT</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQX1JJTEg1UnNRVnZBYkZ2elpsZjMwSGJLTndySWtCb2hMbGpXVF9mWVltd25lLWVhbVBWSTN0Q1BRcnFYM3R2aU52NmN4SThZWXdIbzMwSjlqbEJrY2VuOGYxSklJN201Yi1HM2kzNDNTUGhwSVFHNXZHRWNNS1Fpd3NSd01WTTRiWVBHT001V3RzSk9Wd3dGVVJnS1B5enl5N0VWR3Z3?oc=5</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Fraud Strategy launch - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 20:07:01 GMT</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE50d1drWUlDMC1UZFNFby1ha0dpdVZoaUJha2ljVHhMUDNjYjgxZHJfeFBEMXRLaTdpZzU3U1RyczVXOXRMZ3FUcVlyemNzQlk5T2luZElVSXo3T2c0UkhFLWI1OU5uVGRFSlNfXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>The impact of AI on online fraud in London - London City Hall</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 12:59:53 GMT</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcDBkOXFCYTJhX3AxSGI0bkZ3M2RCN3BzWGFIeExLSXJyVlhoN1JFMHBqSmhPTTdMYmFtQVhMZk1PMEVCZHlfSlhObGtMRHF3VHZBU3F1TXc5Y1E2Mnp4a0xUdTZqNkltTnNJcUNFSDlURlVFM0dzTFpmMEFLSmpxTUsyNzFaS0Fma3dQekJmMTU1LVAxZHlva1NhNTJqZHZNY09CMmJQVFEwYjNjMDNVUU5LZHJHRzhwc2pFTXhLOHI?oc=5</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>NEWS: World law enforcement chiefs set for EAFCS2026 to enhance fight against fraud and financial crime - AML Intelligence</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 01:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPbEpJZ1oxd1NrS0xMY1RuaFk4V2ZvaEdVUFN5VkJUaU9vNThuUG43N29aTU1Fb2xKNmhmd3pyQTNxQ3ZwYng1ZG5BWFNOTVpEUkhqLTJRZndnazJLTEEtN20wOFgzU1dGOVBQeFpRWE1oLXhsYWVEaVNLenotUEdMOXNkbVk4NTZoNGRyRzl0ZHhISUVZQU4yNFE3TUJzOGtrVi1oajJ6NXNkUTlHUVpkYmxyOVhSdXA2b3JQdkZhbVdEUWF5aHUyUnJYQm1tZ3M3eTlWVGI3WS1hX1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>The consequences of targeting Universal Credit fraud and error - The London School of Economics and Political Science</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 20:22:02 GMT</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNaGdkUWR2cVFRelhZZHhkdUxhNnNHUkdnM2gtNGN0M2FxVTItb0pfVVYwdDdxeWFDSlA3a2lYenZqclV6SU5LRWhZajRxTE0waHgwRkFRMmlZVWxPbzY5Y3kwY1NhM2RURUtadTRYNHBoU3lEQS1FWlZuQVMzWUoxRW1mZGhRTnBZZGczUGcyNlFfM0FhbE5hMzZxbUZxU0V1VGtSMFdER3M?oc=5</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Fraud prevention successes save council more than £420,000 - One Welwyn Hatfield</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 11:05:09 GMT</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWEZEN0lMT25QLTNHSlA5UW5QMlhHX1N4UXcwM0xnMWRzcHNiQzJrdWNiQU83cXA1dE5nd1FwR0NCX2x3Y2NuTU9qMENITnpPRGhCWkkxMjNDQTZSWGdSTDFIR1RTM1dnMEM1XzBEMGtmek1pak92SlkzNHg5a09Mc2hYRTNoMlFXOG1wSGdxMlBGRU9GU0VZUlVIYVN0OGk2R2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Internet fraud in Ghana: Immigration arrest 93 Nigerians in Ghana ova alleged internet fraud and oda crimes - BBC</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 15:02:55 GMT</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE55SHJjRXZQWG54S3FVTTVNb01iN3JxckhmbGY5YnBTWE9MNm1PdzYxMmF4MWtHeVhnU0VfemJBMVhpNFVqSVVOSDROOGxzZlRYbW41dDBndEVjS19U0gFiQVVfeXFMTmx1ckRmWWF5cHRmZ0pFaHlCa05tU1pjRkEzMXJMQlY3eDRmS0dGVm5ra2RnM2Z1VWxtcUtJX0NMU2JoOXc5NXpuay1oUE5vbW9jY244Sk5GZkp2Wm9mbnhtSFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AI helps Virgin Media O2 detect and flag 1 billion suspected scam and spam calls to customers - Virgin Media O2</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Fri, 06 Mar 2026 10:03:36 GMT</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNeUtibERmTVVnam9UdTdiQXprX1JJWnNSU1NCQmJsdkZxXzhVaTFrcndXQ3NZUTA1VnVaYjVMdzVIaW9YS0lRblBHRk96NjZuX0NYR01WblVHbDd1SkJsQ084S1haalg5X0I1V0l1aTRJTmJLUkRBSm1CcjlUamJPZVJ5YzNsVzhfMEhYUFBzR0JpaUJzUnFVVHpCUzhZcGt1bnQ0OXRZUURXakYwcFhjdVF6aFlxZzdSbWF5LUJ1UXdXczBEWEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Disrupting fraud and strengthening support for victims - new strategy released | New technical rescue PPE rolled out to firefighters in the North West - Emergency Services Times</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwRBVV95cUxObWhhbGt2Vm1KbUVmLUEyQTY0QndBMWlHc2Q2anRyY01FWmRFSGxUQk5NcEktc1BnMHJJVloyc3dwODFlZDZEWWM0OGlxcy1vTWhtTkpKaWJ5VWloQm5fR0xIblM1M3BzeFFOcXU5ZHBpMG5MZk9Ua0IyM1NiQks2RmVWUG02TU9WcGlaRFRGc0lEUDhmakhGc1NfRW4wWC1DRFlFUmZCTGdSLVhYYWQ1UmdDakdkcU9NQ1BOUGh5X0ZBWklSNl9xb19pbHBNSkMzLXp3a1kzTk5rVlladU5uVkRpX080eXFzWXlmcHQyRjdRalRYUkl2ODVmcWQ1blA1WjVyWW02WFdTV0tjZkNBVzUxSUlKeXhmeld1MHdMWHVnQ2dFdkRkX2NVNTRWc0RqZFU5R3laMnQxVEkwM0g0Nms3UWJoZlpZdHY0WmdjbVI4TEhHVDczUlFQYWhFcGdBNWZ1UlJITURSempHcnJCQ2tBclF3anh2MlFiby1pQU90aVdpb0I4a21hNDl3eUpndFBCcVpnZU9tM3MzWUIxVUg4QkxRTFltMXkwSHNwSF9aRks1MTU0SVNSUlZUYUw1OTlMN1Njb2VRalkwQmJmaVhiMWxZbzFOVkEwTDdWS3piWWx1TGtrd0x2YU1LYmFxSkhLc1lHaERudEpmemZtMWlnWDVCUjhzTlBkY055MlhQRXpYMlI2anBCcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Judge strikes out taxi driver’s fraud claims against law firm - Legal Futures</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 00:21:26 GMT</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE82bVhpektPLWZzMmx3Z0tiakxuZTBqTWhJMXpVQi1PLXRRLWJvbHNVVFFqN3NIampXbW9NTS1KMUdTNGgta05NWWk3bFg1Q085YVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>EU launches AI platform to detect food fraud and contamination - Digital Watch Observatory</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 12:16:32 GMT</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE55bWdScnlwNC1uLUxqOGJmT1JFMmlyZHhpV2IybjZ1YjJhY1QzTGZteERpVV9IT0RnUWw4ZFZicFFaUzljTWpDRUtVMFRVQW44OXI2d05fS0Q5dWx0NjBCUks1TWZxXzgtN2o0ZGg3MHk4RTF5MnhBVGRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>The Tycoon Who Had a Secret Life as an Alleged Scam Kingpin - Bloomberg</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 23:00:03 GMT</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOb0h4NWtWbHpmY2RCWHd2cDVLM0JmSjBPSUlnMVV2UXluck5SZmNVcTdSaTdlRnZRVHYzb09aRXBZSllyTGktMUlBQmlGUllRSjBUMzlDR2NlQXN3T1piX1JzMTlwZGZQa0ZFcXlvQVFhWmFrSkJmdW1IT2NCbWFGeDk1MXJWLU1IQTQ5a0k1NmpSY2tlS21pRHhtMEFCWl9VbnpnS2lGd3VxeE92RkctemRwUnVFdklOcS05T2FVNkN2WlhFRTlwcQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Telstra partners with major banks to boost early fraud detection - Telecompaper</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 06:33:15 GMT</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVkwyUFRtN0ZKSXN6R1BscWxXWm5LWkw3M3U4MV83dnEzT3hHdXI2clI3TS1yYVdhTHVCeFROVzBHWVdZX1hkWDNJbTU2dEZLdnA5WjBFWWY0U0hFajA5cXJnbDJYRndza1g4ZjJfZFhRbUt5enVXMVpEUmVCbGZVeVV4WUpvTGRxU3E0NkNINHhpUDVvbmhURjFFaWlCdXd0b1JSV1lTWlFlakU?oc=5</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Signal and WhatsApp accounts targeted in phishing campaign - Malwarebytes</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 11:23:24 GMT</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPM2RJU2EwQXVuMG1DUEdsMDNodWwzZWxyVEpSWlZaQlEtLXpJMW9BUXZyXzFjYmJERVNNaFl3TlhmRE94VWx1MFUyMnV2U0Z1Z0tKNnB0WXM1MG4xNUdnZnZfNEVTcDBXdS1wdDl3WndCU0F3VG1CNzg3ZzJab3JXQlhNbHJSRDdHTlY3c09XaHJEZGFmakVIU3gzbTlzeW9HLTIzWXp5Yy0?oc=5</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Telltale signs a bank message is a scam (and the simple trick to banish them) - Yahoo News UK</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 11:35:16 GMT</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQWXFaNzNDZlVvYWlwSlduT0ZtYkZacl9wd19abU9hUkgxVjlXX2xxRm1TdS1DTDFISWx0NWVvVDFEbVp2X1ZHN0dpdGU2RjJVWVpDYjV3M3JzSWloMmt6aFJySWVrcnRSaURyZllBRnZOWnpsaEM5YURyQkx3Ung4UjJGc202M0hjbktGTWN6Q0FiWmxNMmd0T29pTjlhX2g3OUJ5ZXlYRHhxeG1lYTVHSXdUYnZnOUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>MoD perm sec pledges anti-fraud performance will improve - Civil Service World</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 12:29:26 GMT</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNcU5pWUNjLTh4anlBOS1QOWY3anA4V1E4SFRuc2ExU18yMWJTT1p3cHgwOGFMNm5oV19LTTFQcXZyU2d1QUJzZHFDZFZIQjVScGlnb2VBS3ZWTWJteFFKOElKWERRX3dZVUpFSUhBdkxIaVFFNHI1TWswVUYtR3ZjVTNoQk1PaEt1RjBUQmVydFNUQUNPdDFKQ0MteHBkejhqNXVsa3RIcFVpRklDYVpqbjRkTXJTNU9aZi1JQVlR?oc=5</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>China’s selective anti-scam campaign poses a paradox for Southeast Asia - East Asia Forum</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 11:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQNG1kVGJkZldlN3hrUUdrUGlxZE1KSWp1Q0ZGZnJtMnIxSlV3cWM2TlFiU1YwQ3pXa2c4OVBMN1lVR3k2QnI5YW80N2RMVmlCWnJHN1ZyaU5Ed3A1Qmw1aUNPVW1FdTBpMUR2bGVrQlI3aDc2RGtCTFdqcGQ1dGYtTmh2bjVTSjhQUlJ4SkxqOXRPUmd0RFNvdXV6X0lHV3l0RzFpTlBmeXRXMlJp?oc=5</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Belgium, the Netherlands and Luxembourg sign treaty to combat social fraud more efficiently - belganewsagency.eu</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 12:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVURxbzZQN3NiTTBLU0hXVzUtYks1VUdZenhxRE80TUJ3MzgtMFhWeTRhaEd6X01jenIyeDlRRHB0ZnpoOGQ3MUdMSVcwSjV2Q2hoNV9FQzNRTmVocWVXVTA4a3pTNzFhX0FiT3UtUERjWHVwT185WHlnSkdrZDRWZ0lGbGt5MjRIMkthWnBYeFk1Y09TczZZUWZRb1dDY3R2TTlwUnZLRnhPN1VMTk5xcWZEQVBVQ3lEMC1hdHRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>New SurxRAT Android Malware Uses AI To Automate Phishing and Steal Data - cyberpress.org</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 07:20:58 GMT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5aZVlJVm5WMnFiVVN2ekplODlYN2RBcUNQRDNoWVNoU1VEWUU2UUdjVFVUbWY0MHJMUXNaNkVOdmdmajFjOVdkaml4WWFfLUdKdmtkMHVvYU50akRtUkl5YkJQYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Synthetic Identity Fraud: Key Risks and Practical Protections - CLA (CliftonLarsonAllen)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 22:08:15 GMT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQUkFlbG01WmwyTWNjVGlud3o5VFlqdFhnMDltVHg1R1NoQm5hOXRqblg2X18wVVJRdzVQak1wMWhwUHhjN2FnV2ItY2w1WTNfVG5NN3hCQTRFMDVVcll2MVJfUWFub24xamlCaFNzblFmcm41LVNQRm5LM1RwTGpKX0hB?oc=5</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>A Massachusetts man has been sentenced to federal prison for bank fraud and money laundering, the U.S. Attorney said. - facebook.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 00:00:19 GMT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPLWpvR3dqWE1BcDZvNkFmTFAyU3htUFFYSWJDNVZGZngyRUIydTNYX3NxWHdZWkw5RFhxeUhXRDJ0SEhRNGt4TXFjZ1FfTDFHdk9BTHRsb3BwRjFkbFZ1SzJraHQxb2JFR2RPdkRwcUx5MUtDSkY5ejQwdVdVWnhrbG1IbHlxbU94N3ZTWEYtRTNWelVqUUlRcWU5NTdrOGlvSkt5NnJpampaVHpOaGZtXzVDWmlrYkxnSmhKcm10bTVNdzNBby1XaGFQX2dIYklXZzQ2a1FlWGZaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Judge drops money laundering charges against former FirstEnergy execs - Cleveland.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 01:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQTGExV3lkNkFkb1dkVW4xNmZxSEJyYU1xOGRJTjBDcGFoRzlKbHdNVzNkZk5mZ1ZjdFZPTHlVQ0p4TG5fQTVVc1ViQ01sb0FhMnc5UjhNN1B4V1dxVEhld0RleTJXVFAxUGJvbjhrSjFjZkZfbzBodmxyWDhXQ1FYNlZ3WEVTYWtUcF9KNm9jZ1lxa043UExVVGEwN0tqT2V4MDZlS3YxbFI1UzBHeU1YTmJSa2c2WndX0gHMAUFVX3lxTFBubW5WZWlTMzhpanpBeG9VQ3lkSWZzVkcwc0d5bE50WmJiVGE5MS00ZDEwUEJtQXR1LTlwRjMwcmVUUUR1TXgtTG9QVEVZVjRMbS1YOXJaVk5md1RuSGJ1SUdiVFNQbEVLMDFVNUdmWEhIM0JPNEJ3UEY3VEdfa2dlNkdwN3B0SFJpcHd5Q2dqR2QzUGdSSmFwcGdkaTF5emk3N1JOWXNvNUlyX1B6WUtVbm5UT0N0ZDNrYTNlVEpBeVRxMERFUmZMdHVEUA?oc=5</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ghanaian national pleads guilty in $100 million romance scam and BEC fraud ring - SC Media</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 23:43:05 GMT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxONWdMakdaeW1mYl9zWnVON0lTT3Q1akNORmthZHowcS1idmR3RTVPZ3dKcHNwMFJFb0Jqa2laOFVhck4zNUxlMTZXYjVFQlNPdWNMcTJhYVpXdG92aGoxZExkTG9Xdk5YaGExWEFLZFlsMTU3M3E3d291eU1CLThPSnlFangyQWdxVVU4ekw3ZEhrc3poWU9tU2tnZWRNVFlGTkZzMmxDNXdxOThN?oc=5</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Crypto Hacks Drop in February as Phishing and Wallet Scams Surge - Crypto News Australia</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 04:56:39 GMT</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxORXdpaGJBVUxQc1NTSTU3aGg2S0l5TEs2SHZNNnRfdnRKM3owaDNsTjBEMEt2SXdQUDlrNXZxQXdyWDN3UGRLemRtOHFISTg3aDdHaGJEa1d1b20yb2FwdzhUMnQwNmEyRFZGVURtSDUwN2pqaEFPR3BrNVdxN1EtSnVCU2gwMEFSRTNIQVNhbXNneDFJaTN3NnMwZUdESmJmN0dlZUVR?oc=5</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Radial Selects Riskified to Power Payment Fraud and Refund/Return Protection for Merchant Client Portfolio - Business Wire</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQeUpaQmNJZE5yV1ZCOFZpUlFMc19KV3c4U01EcUZWWlpDUkRZZVMzeGdmLXp6ZnNMVmQwcDgxSXNLYWFFTEd0UmQ5Uk9nM2JZTlktZXVQdk9WclFaN2N2SmVjNnVjbHBKTlljYzh3dzJtM002SGNHY3lVaUhieldUNTdEbUR5Qlh5TGExNXphNGktN1hpdm5ST2NZd2doc21HSGwxdm9xeDFpQm5MRVo4RWRnSHowT2FqZXlYWG8tV0dISHkzMDFaUE9ZSXNqUGM3Nmtxdm9sdzc2RlRKb2kwZlc2ejlZeG1NS3BKNlNWZFNXSVVH?oc=5</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/weekly/topic_feeds_week.xlsx
+++ b/data/weekly/topic_feeds_week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UK-EU SPS Agreement - Legislation in scope - GOV.UK</t>
+          <t>UK nationals fleeing Middle East reach 100,000 as evacuation efforts continue - The Guardian</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 08:34:48 GMT</t>
+          <t>Wed, 18 Mar 2026 02:30:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOM3QzWjRWSUdFekNmZWUyOG5Od01hZUo2enVJMV8yVUliLUhxSk4xUXBDQzJpZ1Y0Y0k0eXNrSEtTYjFQbTc0V3BlYnFBc3dHMVEzWnpZLWFXWHV2Nk1zX3Z2b0NiVEEwb2NzVU01VEJJZzJwTy1tTXFGaE5TS2pZSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPaEllUFJEOEM1a212cnhlZW9xOUFaclB3QW01UzFmM0tYcC14UlhYLWtLblJ6NXhZaHJvZXVsdVhzMTZ6Yi1kVnh3ZWVnaW1lWXF6eVpNdC03UkZtVHo4MXFRQlFtRmtITGVhVEppbU5FOUhjT2tidWpfaHItUUNhdXctT2F0OHdSbE5CTWpMR1RFYkFOaGt2MkZQZmZsOHZYeE9NaTlGbmF1Zw?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UK Music Launches Welsh Music Manifesto to Turbocharge Economy, Drive Tourism and Tear Down Export Barriers Ahead of Key Elections - UK Music</t>
+          <t>Chancellor’s growth plan sets key principles for UK-EU alignment - GOV.UK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:11:15 GMT</t>
+          <t>Tue, 17 Mar 2026 15:14:38 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQdl9NcldjSmZKRUttYlExQ25VQWVkSGxxMDhCYVd3TlhtaUhfZlhMaXE2VF93R2lkNVJYdDNGYlktQkhCeThIXy0teGtVVm80WEJ0R1lUaU5SMm5kOFlXRU5pb2lXMm5veEVGRXIzNG1yUEdic1c4Tlg2a2FVNjJtbmUyT0dSam9sQzNtaGFnazRpbXNZN09vU25mRzlpUS0tdWxSNUotTXRta0QtRUFYUHo3OWpOTURkRmxvM1VkVFZwbWE3MzgwcWk5Q0xfTHdpc3JqTDNlLUxBaXNxSHdBZVRkUDVuLUNpYjFoT3NIWlo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPcndnQUtMZUFBcTlRZ1l6V1VrV2VYNGUyRDZiX2I1ZkJVUTFTNG11Vm4wX0NuY2hDdkxlNE1NbzZEa2VVRERhdHRpYzN4X19XT0tIRzlJSk1aTDJLMDlDT0pDNGFxV3o5ejU0WDBQNUdNcnNDQTZwMXpVVlc4UEJkZEhyb0xGOUtvZ2lWb282UFFCT2xiYWd2YWJ0dzgtaHc?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PM warns of impact of Iran conflict on UK economy - BBC</t>
+          <t>Worlds Apart: British Muslim Attitudes on the Iran Conflict - Policy Exchange</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 17:21:24 GMT</t>
+          <t>Tue, 17 Mar 2026 22:02:46 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBYQjlxc1p2aEJLNVc1YVByMFRZTjF6Sl84ZERKaTcyNk1sOFNVS1dCZVdYbE1Cc1VNNkQyVHZidGVNZXFrSUVocVV4NUw0c0wxdWJyR1ZINkh3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPUlBqNmtxUHhsajRJVy1EZ0xKeEdqbGdxeWVXdWloYmw4YUV3bnMxZFNOdFpvWEREUjZoZk5sekd5UWNjU3U5Q2FRbDZhdkRzYkhWUUh5cUFjQUI0elQzcGJhcWc4bVdhUDBmMnhVQ0l5UnNqNzd4dTJsTFQxOHpUbmwxd09YaVoxRnVzNGpka2NjenVFaU5Eb1pxMFN2SzJEYnQ0?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>From Tehran to Europe: Terrorism Risks After the Killing of Iran’s Ayatollah - International Centre for Counter-Terrorism - ICCT</t>
+          <t>UK returns from conflict zones: Why individuals and employers must seek tax advice - BDO UK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 09:04:20 GMT</t>
+          <t>Tue, 17 Mar 2026 13:46:58 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNM0VjRlhYS2dnM1JWZVhRZzBNRUlrdGFTMElrSWZfZmxLSm0xakVyT0JFS3c2anFFQVRYM3JUUXRGOFF3VWtGc1NrLUdWd3BCdWU1d1gtV3ZQQmhpOFFhR3BlbWF6UTMxUTQ0WVJ1cDdTZ21kUjhFZEtDTVZIYzlCV0IyR3J2UFE5YWstejFaS0I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOX0tiQm5Rbm1lUS1OanlIVWw4eDBwUEl4bXFFVlVoTXI0UHRZdklpOUZsU1dqN1ZBcUl2aHk1QkJrMVViWWdQWXU1WjhrZ09OTmxhWUFxMENLSEpvMUxvWWtPc2hPdHdOOU9mRU03LUZZbXpiWTg0dmUtNWpOZVZVSmVDdlEydlFxTEpja2tsQnRjUFRqRjRWMEJCQXhqVTVKd2dWRnBCZWdtZHkyd0JQY2N2T2NnakhWY2FFMGI3OGR6dUpGck9iM3I3OXdWNVRodHhjX0lVcVhsM0FqcHVnNg?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>War in Iran – NFU raises concerns over impact on fuel and fertiliser - NFUonline</t>
+          <t>US eases sanctions on Russian oil What should EU UK and Australian businesses look out for - twobirds.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:19:34 GMT</t>
+          <t>Mon, 16 Mar 2026 11:54:50 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB2NEQtUjRWZW9USjgxTmk1NUJsNmxnU2NzVk5Rb3lsTlBRUUtrMVU4UG5hSkotbjVTUk4tYU1Gb2hZalBTWmNIS0k1NFBGLVZHWjJiTXRBQkdCYzg0SzlQXzFlckdSWG5GZ1lFR1VxY0JJa2VHM2Q1WmpTUWgxanc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPQ3RuMEllZTJKZjB5Mm55U3M1OTl3MmJub3JnNXVLT1VtT2lpMngxV3o1NW9JY0NMLUgtMFJ6OE9pajFyU1Fjb3ZMcWw4WjN0MEhSRWZKeFhDTk5vNkE3Zmo4WG9tc3ZWMVlncUVSWVFnRVg0UVExVVhwSlFRTWJaNmo5Nk5sbkFpUmlEbkhxQmRCTVN6WTBodEhRcHd3d0hYcWlaVWVsV3kwdndoQ0dmeVA2RWtjNVBodENuY2lLNTFHM05ZSmtqRHQ5c0RWd182dGIxTVZYbGExcHc?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Navigating the New Era of National Security, Geopolitics &amp; Global Trade - Baker McKenzie</t>
+          <t>Service industries: Economic indicators - The House of Commons Library</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 13:53:51 GMT</t>
+          <t>Fri, 13 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNVTl2S1BKeW81VlI4d3dHOE5naVdJVE5GYTFIUUJkaV9FQzcyY2JfY2JiRnd0SU95R1VZRS1VSzYxanJLUmoxV0Z6eDR5T0gxUEhxbDlPaTNZTndmMVRST0ptUkpxeTZyWHJ3LUppSGFCNnZPZTk3cklTVm54aFpoWS1ONG5tRXlGWnpXUUlBR1VyVTJTZXpKQXRKaUIzSXNrcTA4YWY0VEs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE43d1RyejhtY3NLbXNmSVB5NXF5a2swMkt0eWJqanA5d01Iak1zNFMtTVJjczRiWnFsRjJZdmc3UnFQSzhWcTBMck1iWUhEdUdmNXYweFZNSE1ud2VEYVZKUTM1dVlKZDBfemZCN2RqdGhpQQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Energy price volatility and the global economy - OMFIF</t>
+          <t>UK’s Supercomputer Delivers £8 to Economy for Every £1 Spent - digit.fyi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 12:14:07 GMT</t>
+          <t>Wed, 18 Mar 2026 01:12:58 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBtQkFmanNvYU1RMUFvMzZYT0Nzc1hYdzRVRFRueGdFYVdDeHMtVEpvMkhpZUMtSVBWM1M1YjVkWS1lMkZvWHBTVHNlcExPN3p4bHgwNDRaSkNTbF81eXZ3b0lwbXhudnNvNExSSHZRMFVPaFFCOEkw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNX0xwckNMaW1aalZGNlotUVBpbWFiSDVsLU15OU03RzllZ0ZacTJyMEJKOFF5dnJ6dEJhSFZUMWdzbDdaTDBfM2dMS2Fnd29XTmxuQ2dOR01oMUhJazB0aEJtcGg4QjYxemt0UzFiSlVUeVpuRGtVTkhaZkFiMEs0WFdpbFZCQWc?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Impact of Middle East conflict on UK energy prices: Will CP2030 prevent another energy crisis? - Solar Power Portal</t>
+          <t>Chancellor bets on AI and devolution to boost UK economy - ITVX</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 11:12:52 GMT</t>
+          <t>Tue, 17 Mar 2026 17:30:57 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPVWVGeWJkZFNnVXprSndMSUhoSDFsTXdLakdYdHk5bXI3TlpzUk1qTHMtOHZQazVSQnN0ckZkS25QZFpLTXY5cXRSR1RpeTktT2ZNWUVDTXhvcnEybnV1bW96bEtfaDd5VW45NXh3Vnh6aUh2d3RadnFpWGEzcjdkUUkwRTZMbnBRZ2ZpYmtQbHA0c2dYTGhweWtBYkZVU1NzTmh0eG9NR3o3TjFnSG95RGxTb193LU5NNk9fUUx2SXhMMUFKTzdGS3p4VDlLNlR1VXRzbHpVMWdvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPRnNEMDZsVGNKVS1JMHhUeFRsMFdJbjF0MWswZU9SZ0x5aXN2bHg1dHpNeXBnaTBYaV9WUkp4emg2bjNfWmV3aEFnN18wekZiU0FRQ3N4NjB1dVlua29BeHUzZWc2bF9Oa3hIWEk4dkJxa3h1RlBVRGlkVUxTbG9iTjlXZVZtRkNULXZqSEdDdnpyUjlJMldnZVhzLXFJb21ubXY5M2tJc1pGdlNPU0RXUTNn?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New analysis reveals £43bn annual Open Banking opportunity for the UK economy - Open Banking Expo</t>
+          <t>Cyber-attacks against the EU and its member states: Council sanctions three entities and two individuals - consilium.europa.eu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 12:28:43 GMT</t>
+          <t>Mon, 16 Mar 2026 13:14:37 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNSjJ2SWVQQklJNFlaeUtLd3ZVa2ZyWXlqMlpEeDh3Ri1fRk5ZQ29UdWJjdVlwRFNsTUdWUmtwaXVyY1IxSlppYmJSb0lxYW1tWU5UR1B1ZkpQM3owdXBsRmVGSEVmdXdDYWFDT2tkUEtPMkYyQXF1VjZadkVMZTdidGUxNXZHeUpLVFRrNmRvVk4tUEVQS25HbVZFbnBrTk8yVEdUYXVyN2EycmhoS25PYnQtNWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQUGlyZEJMWTdQNm8yWG11TEhnOGY5YTVhaEZxQWRZaGs3WTN0bmVkVW14NTdFTVlQdkd3TjNJTHY3NGVnR0ZXMDZkM0doalRqdXJNaWJUeE1xbWxsRXNxZmdBQ3NlR2EzemJPcEJWVm5QUDBnckRoaENVMXB4TDhrRUZxT1VkWnJhU1pQZXFDZWJUTDZWeXpDaVp3c2Q0QWNGWVZLQjBORXVhTHd1MkJTeXNCUzNCZ0V3dnVjY19PanZPOWFUVnVtZUprbFotd3p0ZkFyWWNoUVBvclF2eXpBblhfdjczc2trQ0RQQnM2UjEwa1pEdERlT1BOUjdLWU5u?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conflict in the Middle East could impact petrol, diesel and grocery prices in the UK - facebook.com</t>
+          <t>Iran conflict shines a light on UK’s ‘stretched’ naval capabilities: Analysts - Breaking Defense</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:43:59 GMT</t>
+          <t>Tue, 17 Mar 2026 16:58:50 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxObmZWY281UGI1Wjk4N29QVnNQTUF5UzBULVFldC1SVXJuVjM0T2FXLXVIemRBenJnaDFrU1dYdHFVVWR3OUlGWi1jbVlrMTJ5S0JpNGRUUG1ody10WENTRDNtc2hneFlQeTIzeS1PYUdkR3lKVzdENUZIdTIydmd0N2x1THp4dVdFVXAtX2RHZ1ZzLXV0TnpER0dNR3hqVzJnQUduWVIycXdmSnhURmc1dzA1ZnFrcl9MMEE5M3I1WWRzZFRKbmxlMm1XOHlPUG5nSVNaVkhtM3lodkZyb2l4VXdEVC1TUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPZklQOTJaMVAzSEk4MnY2OVoyWlJEMVdDTGdWLU11RlB5eW4tUGVkRkVqTHNXUG52VGFCM05UNF91UVQwZExmVTU0Q2VBSHF4MndVZnVTWDBZdlg0Z2FuZUlTZlFiSVJSVzFkcVNNTjZ5UWdQT1NBeHRfR2V6NDFFNnJ1SW10UG0yVHA5aEtQT3ItYnROM3ctLThiSEpsZTgyUXJMM0c0UmxBdGNSMWpF?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inside the Russian explosives plot that targeted the UK - BBC</t>
+          <t>Joint statement on the escalating conflict between Israel and Hezbollah: 16 March 2026 - GOV.UK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:00:08 GMT</t>
+          <t>Mon, 16 Mar 2026 20:38:42 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE52cUN1OU9yS0NQNUp2TzdIX09pVFk5WnExTTBmazVBbFJyaHRhZkd4cDB5aWhCZTN5dlhjal9qa0tSeFF0TXN0eWp6Q2Z1Szc5Z2VCcnFHTGROQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOWWdCRVQtTXJaR2pXblhBdndUTVpaam14TWRRUWp4MmpHSjBxSjRmbzE0ODJjZjMxWHVNUlpMS3I4QktVRXVsSGdKWVY5VkljbDZQaU5RYXU0a2wzS1dzTmREbF9FVF85UzVKWEwwazNvMVZtN1E1bUFrcENubE43eWFWNlctbTBjQmVGUzFKVTk3LVpGMkUxcWhGeTJWYS1PWkcxVUJvWXZVc2NQcEVfWkM5aUFHV3RBZmxCZA?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Calls grow for Reeves to ditch fuel tax hike over Iran - BBC</t>
+          <t>Isolated and exposed: can New Zealand’s fragile economic recovery withstand the global oil shock? - The Guardian</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:34:01 GMT</t>
+          <t>Wed, 18 Mar 2026 02:09:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9VbkRlLTIzV1lRb1JuTndvQzdDZUJsWFlSWkxDaG5nbE50R0JJQnJqNWVVU01tb2g3bUlWa1F1a2pwU3NDblJoMnVIM3lzVmN2QlZIVjhtQnFPdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPbFpqZ3p3Zm03bkZ5VklMektoWHZUZXd5NGp0NS1FVjVmMGVkLUMtZEoxRnM2d3phOGROSzN1azVpNU52aVBDUDk2elZnM1ZuSDZtZ19rT3JURF93bjZoYUNYRWYycXNSbk5yTk5YdXUwX08tdHZtamhKaFczaEFaT2c1SDFydC10ZTdz?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cornwall navy air squadron 'maintaining readiness' in conflict - BBC</t>
+          <t>Track UK's latest migration numbers - including asylum, visas and small boats - BBC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 13:44:40 GMT</t>
+          <t>Thu, 12 Mar 2026 12:34:01 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5DRk8xOGRFQW04YzFNME8zRzNxZzRmLU4xR1FiUVNJSUxXVnF3OFlnYTR4M3NJaWdGRVpzOUpmVmRRMHdibVpkR1J1Sk5sWTZpUngtdEFCWTVlZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9abkk0V2VWNThMdjNsdG1OMWYteGRuZWpJSmRBeE05TkVScDRxWHpsOTBBbldicVRxVnFWWjV6WkFBTjdZcUQwMVZoMHl5d1E4X0RyVFJIeEh0UQ?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Three US bombers land at RAF Fairford amid conflict with Iran - BBC</t>
+          <t>Europe must prepare for drone strikes by terrorists and criminals, warns Zelenskyy - The Guardian</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 14:29:35 GMT</t>
+          <t>Tue, 17 Mar 2026 19:38:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5RT0lBclVKSTNoYVA0TEM1NUdNXzJjM0RBdmczVDhnWmlkV0MwcWR2c2ZRcXFvT2EzVHc3Z1dkVEZEZmlzU0RhTnV0Tm9aOHROZ2JldWZ4Z2NRZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNcDdDLS1xRk5oUWFpLS1Teno2QVA5X0dSODdWWVNTRjRLVHRLcHpEVm4zbFRvSUJKeUhWcDNyOGNoNXJwNWNHemtWVEtDSm56Y3hxNWlubUpkS0ZpSGdWRjYzQTJSRllUUXNaMEhjZjlNbW44SnQzQ3pFQmVDZXF0dHpQRmNNOGhsdXh2NjhUbC1FLUJodTdOQlJPck94c19kdGtrUF93?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran conflict steers global real estate into uncertain waters - Property Week</t>
+          <t>Reform council seeks to declare migration emergency - BBC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:13:19 GMT</t>
+          <t>Sun, 15 Mar 2026 12:17:33 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQeVlKRWgtOVFKMlAwWHJ3aFZzU1NsSTdzel9MSE1idnpMYXZTMXBjbUxadjZVQ1BZZUswbHFEcFF3Vlo2NXJwOEl0OG1YWjl3NTBlLXJYbnY5c2xNaWJNRUZKWE16bmd4TXFQcVIydE85NDBtd29US1lXU3Fzd0MwbS1kTVhmQm5DcG1BVHpQOXhDLWlvenNLUzBIaGUzOVI2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5NZ2lnUndTOHktMGJKb19zRkpoUnFQMmFQQm05YnNuTjd3anNoc0RCZjQzREp5ekRUWVVFME9yUVNiX195Z1JRODhSRWVGLWVKWk1mV2FkZWRrUQ?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trump is bombing the global economy An inflationary downturn looms - UnHerd</t>
+          <t>Spotlight on Sanctions - Norton Rose Fulbright</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 00:38:46 GMT</t>
+          <t>Mon, 16 Mar 2026 15:59:47 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1QLXBQb2xTbFAycGVxa2k5UlRYUkY4cklxLUJsbFhDeTl1MTVHM2t5ODBBLWdfb3htQXdzSGplaF8zaFRwcWxNNzBtN3dCdUN0Smt6NWlqX1V6d1hyVktmRGFSRVdGVlZWd0dEMTA4LXB1cDZPbk9BSXltZWE5SEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNUJMY3JVcjY4U1gtT0tHSFVxa1lONlJWNnVZWGRkbjR1RDNNNTJISi1tOHp1cW53UWlfRUxmcUFSa0ZUM2FXWk5lZVYxTENJeWdmWXFaWTdCLTdROVRnMHV2RWVXQnZrbEtQRVA2S1JJdGhvSnZvNURfcDZnNWF5SlVkemtWRW9rWU9VU0NPMzlvQzFFV2l5Uw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UK MP calls for additional sanctions against Georgian officials - JAMnews</t>
+          <t>Iran and Russia are 'brothers in hatred', Zelensky tells MPs - BBC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:39:17 GMT</t>
+          <t>Tue, 17 Mar 2026 18:26:19 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPaEVDUnJSTVpQSVBEcUUwSF9kbW84Y3ZmX1NuNDF6ZDhGYnV1bFRlZjIxZ2paRkpIRXRPSVJqTHhsaE1IOXlrTFhRanhaRE8tMjZZSXpfR1RWeVdEY0t5RkpKOHVnUzhOYXZLc0hqZWdYOUNVRDNJQXJxRGllTC1uZW91Z1hFSVB1Z2t4TWJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1OZjBtbENiWFlFZ3VieVNYdDUyaGV1ZXVBSFZyeWFZZ0dwV0ZPeE82dHg1a25ZTGtUMV9fU1ZjWnVjc0dEc05leFYycmpmdzJzUm5DNVk0cDZaQQ?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wider Europe Briefing: Hungary, Slovakia Toying With Russia Sanctions Renewal - Radio Free Europe/Radio Liberty</t>
+          <t>Geopolitics &amp; portfolio risk in UK private equity - The Lawyer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 11:06:54 GMT</t>
+          <t>Tue, 17 Mar 2026 11:27:47 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNSVhsUm5jSFBKUzhlbGFMajZCbkR2X1gwN1hDQmY5d2k2T0ZrRk56MDBwTTBZZUMwTjlaN2pCdEVJQXRSOHRyMG9DVExySjZoYnBBVmRZWlRtZlg0LVp1THJEQUJrczdvdGF5YUhvZGpZbzVHanJjT1R3eDVhNGZ4ek4zcjZYTGVEaEZfcEg0ek1za0hzanhkY0NVeU16bzFrMVIyd21mYVhsU0txLUFtZ1pWa9IBtgFBVV95cUxNUzlPYTI4RmdzSHdnaFRqd3JoLVYwaE5Gblk0OHctOTlHa0c5dlQ5NkpwMXhILXpqOEZPWFVTNklERnZoN2FmNnJhOVRLeGdEejdBek5NNks5ZzRicTcwNlFjUVJ1SS1hTnN6Q3hqUlhWYmZJSlBXZkFOMDIxQ081X1d2MEd0WUQwY0pYdG1pMmgxUUpUZGVzLWRjSHBjNTMwa2JQVHRhTlZDcVpDNFRQWjE3Q0ozZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNTzhoMjRoZmxWNEJNdDJ5d3hqYlhjYWR2aXpNTl9iQ1BtcmE0MlFLbzJCeGl1YWU1N1psaVVCMUJVcVNzLUdjMENJc1VDVEdyaThrcmVKeTM2Q1pDSzRLdGx3Vi1RdFdMMkJma1RNQTNpOVE0UVVUa2JVMmNpOGJpS21YSDJPNUZXRGxz?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trump Generating His Own Fog Of Disinformation About Iran War - HuffPost UK</t>
+          <t>Cancellations mount as Middle East conflict disrupts global travel and events - micebook.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:14:37 GMT</t>
+          <t>Tue, 17 Mar 2026 10:57:57 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOY2VVX3hZb2dhSVBfWVNoTEFYckNJdDBWcmpXRm5waHp4aUN5dlZRTmtxbkU0UFUtc0FmdlJBVnB2Z3lKZlpMa01OdlloNktmeXdqVDFZeFFVMFh5N1JINGpDZXlhbTF1aTR0S21NbGdkb2Utb0JrQ3d5YUxVRWVNSXJsTHVNX2xwbmstVmN6dENXbTJtdVVyMXp4UW5yOUc4amYxS1ZUQVRwd2NBa1phaVhodE54YkFYTnhuNkVxTEJ6TF9ZNmg00gHOAUFVX3lxTE5RYW9KS1A5eV9KNmRmcGhKVlR3NFVnTTg1S1B0dTdveFVUdGhrOXl4ek9WS0ktd0VoY2NyeGlNQ2JDNzk5aS1kcVc1N19mWUNpcEstTHVrT1U3VUV3b0Yxd3hKZndBY05ac0s5WGFpZjNxbHNVSEkzdTBDTVByVXZrY0p0SjlfaW9BOGdDc1E4QjFJd3lqckZfeU5OTFNBSGoyVUR1dHlLRU4xOHJsdlZVY1l4S0c1bmFkTVpNaXBPZWNPZHVHc0h5UWJUb0ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOcld2T3JDR2dzclVGT0FOeG5qcUpYZkhVY1BPUjE3RmhPcVR2aGhnVkRucGJDTUUzQlEyLTRNXzVSamFRRlY3RmFBRVRyMGgtRzVDeDZQVHNXVU9lTUFISnNUdDZwMU1wZEVHTEI1NExzMHN1dmpDb3loNlNRY2dzUm1YZDNJZzB2Q1JEZ1FuMWdackFodG1TcmJYd050OVBXR3p0OUtRUzN1MWdTUmtFRlFta3RUQQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pound Sterling Higher as Trump Signals Conflict Could End Soon - CurrencyNews.co.uk</t>
+          <t>£140bn experience economy takes spotlight at InnovateX - avinteractive.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 19:01:02 GMT</t>
+          <t>Tue, 17 Mar 2026 16:51:57 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOLWtueUFVYzRCVjNXd0RhNHJGaTRHMWNzSHJHelVJS2ZCTDFCUTN1UU5DNzZBOUxlSFF3WGtycFZfb1M0SkVid2JYUHVKNzNrZml2bFJaOVhDdDdoRUg5RWVNaUpEb0l0MkVUeXN4eW82STg1LXowcEt1QzBsajMtd0RlQjdxQWhrZUVMYWd2Y3dZTHo0TnZLVnFWRTdlSk00WlhIMzRKSEE5NTU2N1I2TkR1ZDJNNE1MdFAw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPaVZFTi13ajhNY0FCTUJmR2dKa1M1dlloTHQ0bkJMbWV2MGFPem5zcmdLSXFOWEhWZTE5bHBMUXJHU3VzQlVLMng4dm5nTjdxSndnNE9TaEVTV0ZBSVRVVzdqeFhZcER1NDgtS1dQemdReHhnYnJxN0gxdTEteDZYZlVTWWVMZUVKdG5iemRCdGxSendMaDEwbURodmNBdVlFRG9rN1o2R2Q0NjBJWUh6N3E5QlZGMWlfWURCbC13dw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oil Price Spike Could Crash Global Economy - Novara Media</t>
+          <t>'One in, one out' migration deal: 377 migrants returned to France, 380 admitted to the UK - InfoMigrants</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 19:37:48 GMT</t>
+          <t>Tue, 17 Mar 2026 12:38:47 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNaExfeldpU0ZtSzVZNkZlWGg0N3R0ZllBRFRDYllzZ0lhdnFPUTlLS05Tdm5KVkNpYlFVN3AxYW01WTZRdndITFc0cDZXMjhnNzdsejM2Q2drU21PZmE1TkZUeXMxT05ocXV3eThuSHBIanZ0c3lkTWtOQkp6TjA4ZzFHb0I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNV9hbl91OEZCOFZ3dm5SX0ZIa2JWRTFfZ21qUmZKSENaNEhiNF90SlNlYmVEVTJvQ2NxRGFCcjBmR3piOGlocG5ncFUzalFCcWZBaUxQcHFOaDRZV3RhVmdBTmZ5MnBmRldBSGN4aTRWYmZyOU9LME5nckEwd2stcGs2d1I3TzlwOWdGRTdZa3pSZlY0anpEejZValRqQlNqazRKUUlZYmNJQWoxT0FWTjBHeE5VR2VYUC0wTjJXSndKVkZ3SkE?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1081,27 +1081,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iran war cost will be passed to consumers, shipping giant boss tells BBC - BBC</t>
+          <t>Sanctions and Export Controls Round-Up: Latest Enforcement and Policy Updates - BCL Solicitors</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 00:27:15 GMT</t>
+          <t>Mon, 16 Mar 2026 10:34:55 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5kZWUxX1NsWHNaOFpaYnZveFdKWUdTXzVJbkVjRWdwVmNja1U5SDJSdG1Hb0hnaF9FVUlNMG1KUzItU0lVZFZrNXpIb0l2ZkJPX2k4UlpQbjBJQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOdVl0dTNyemp6NjVOWE1iYVhncVBWVTJmLUhpUjJZUWhIWkQ3R25QZUtNUVh2cjdNR2d4enhiX0ladVgyb0gxM3ZvSWItZUlqbm55bmtuOS1YTUpfd2k5djhhajJkdzh0VEEwbk8yODF6a2VGTFplM0RsVFktdHhIMUp1YXNBZTJreDN0cV9BcVRfeHcyN1c4LTVlVkVJaTdvQzVv?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1111,27 +1111,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China warns Maersk and MSC over high freight rates from Iran war - Financial Times</t>
+          <t>UK announces new £2 billion “Quantum Leap” in hopes of transforming the economy and technology - Open Access Government</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 11:36:51 GMT</t>
+          <t>Tue, 17 Mar 2026 11:39:02 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBPVU93VDJRcVZOSk1IVWN3MWZYcFdMUWRsVHhDZDFaNnI2eEZNc2pER1ZvX2pzUlBxT05mWXVVRXVzLXh5V0JYX1QtUFdjVkhhOWROYXlVSUVtcW5aaGlkMGZxWG5udUFrOXExSzBTZ1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPSk9oMWh4YV9zMm9Db2lFdlkzOWl6aVpvMVdFZXYxbmFfWC1RUlFLaWZJZHJKLXBuRXhpS0lQTFhPcnNmMzZDaWpyQUwzUEx1VnZrUXdsOXBCaXg4VkJuNkZ5TW5OWW51c2xzbG1xNS1OemFVdkF5SkFkUDJpdzJxQTJ5YjEtM1FTVzBWTURfWG9QZXl1b3kyZGtFVTN1WGNjQUNpWjlRazlCRFYzMUN0SXFPQ29NSGNBLVRmcUN5clhCcGpuOUZFUlhMNXVNOUxFNnc?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1141,27 +1141,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VW to cut 50,000 jobs by 2030 amid Trump tariffs and falling Chinese sales - The Guardian</t>
+          <t>Vulnerable funding in the global economy - UB - Universitat de Barcelona</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 02:30:00 GMT</t>
+          <t>Mon, 16 Mar 2026 12:07:05 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSHBiZThPYTc3WXFDZkpVbFk2dVYtQ25pWXlUc2RXS1VaR3lXWlR1a3VITUZQa0ZwNERZVFRlUVpHcHV3dFJLNDN3SUR3X1ZELWpiNWpIRDRvVnJ6cmZPVFFzYk5SWXoyN2xUU1piX0RXSWtWUXFNMW9RaXpWRVJBXzYtcF9lSVRDVUFNcEFkdmhxNHYzUUhzek91b1JYZzNiTkRZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxONWx1VDFEU05Ia3pGS1hFNERFZ2VMOTlsaUhKakVjdkk2Z3oybjRkWXVkbGNXZHdab2NzR0NoVnQ4cU4ybzdNR0ctSGMwMktPQktqcUx3bjJKazJXXzN2cTNoZFJibzhYOGhsSHlWcXFQNTU5aFdsN05vVHREV2RCUUlmcw?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1171,27 +1171,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Building Rail Baltica: A €1.13bn Supply Chain Milestone - Supply Chain Digital Magazine</t>
+          <t>The new expat investor: What intermediaries need to know about the wealth migration wave - mpamag.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:40:24 GMT</t>
+          <t>Tue, 17 Mar 2026 14:00:12 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPeUE4N3hjcWptUDdRUlJLYkg3b2tFRXBlZW44ZmU4WXY3YkZneDIweE1fVGoxVkQ1cnF1Y2gxaTlIaEt0OVNDRjFReE00eGI2ODlTdkdhUWVvOEdoLWZlRHlmWXVqVkxVb0dfNWxncFlYSzdlTnM1bG5zR245TFVXVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNcVpCWTBVQWJUM19EVmhfblNDQzFmVDJsLXBMWnNwaVhKYVYwMnFDZUcwN3JXVWszMzM0ZkVHUFIzeHVMUE9rMmN2VEZ2elVHMjVrb1FiQ2VOMUN1c3hnY090ak1UWUNwLVkwZjFwZU1fWDNRdklWSXNXN1c1RGc0Y0M3ZzdlLTNscmVHWkJxMWpPUzRzc3RqU2JTY1BGcDJ1blAtYk5PM2tQQlQ5aHlVNUlQeGJCbVpmN0ExRFhpRGtvWTg2N0lwT0pKanJYYXhSR29Zd0lGV2tCWGpvWlVR?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1201,27 +1201,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UK manufacturers to save millions of pounds a year as government removes offshore wind energy tariffs - GOV.UK</t>
+          <t>Brand Protection Congress Europe: addressing counterfeiting and IP protection in the digital economy - Managing Intellectual Property</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:05:37 GMT</t>
+          <t>Tue, 17 Mar 2026 14:28:40 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOUDZONnRkT1RuR3lqR2JTQTlWVlFwOHFob0tjbHNoSWhQVFJjdWtKT2JMZHotanZBcVgzNE16QzlyZDFyMm5ONldsRnZjMkNwNHFhanhvRE5HamI0TGQ2bHdkTG5jcjg3TGZzSWJFLTZ1YXpVV1lMTFBkRzcyR2dhS0dNVHBLLW1vZm4tV0FycE9ZbzhENWJyN01ld2pzSmx4YjhSeUk3clhmTjdmMnZ5bG9tMEluLTFfVGtxajN6cnUxVFcwWTlxc2VwMGdhZmc1cEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOejFuWnZucFZkUDZYSktYZVR5V0tJcUw0S2c0YjU4SUpYeTJkSjZGRGdkUjh6dzhmYzhmRjBZSC16blktOVFUUVd3cXlzT1N4ckNENi1iSjlmbzE1NFBpUzVjZ2FfRHk0N3RaNGhWWnBadjVRSHNsYlUxZWRpRUN6Nm9pa0ozdC0yTjJnWWxmYmJVeDl0WmhuM0lnLVVRZExwZTZmX1VUR1RSNzJrUGl3NjktQjRnWHRWSTRtaWM3RlBsRUhzMzBVUXpZMm16aUdMcTJiajZqN1BxNjl1dmJZYTlGVGJOdi1pajcya05VR1p0Nk0xMFdhS3J0a21XNXkzdWQxLQ?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1231,27 +1231,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Timelapse shows fall in shipping traffic since start of Iran war - BBC</t>
+          <t>Week three of the Iran–US conflict: oil market volatility, infrastructure attacks, and CSC’s energy outlook - Marex</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 20:36:01 GMT</t>
+          <t>Tue, 17 Mar 2026 09:37:58 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1QSnEwRWlWZjRZMk9VOTZwUWpObHAwcTF3VEp0WGZ3YlZ6UUd4RS10QXhjOVd6UUZ5dGxJUFFaS2UxUTBWZGIyUlgwLUxaZlU4Z19PdEU4UWRqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPbHFyQ0dHQlV5bUF0VW8tSld1aEVZSXlYS1hIVWdpaENqQjRydFZtQXNNSExaOExuZV8temJnT0pwdFg5ZjVaUGRpZGNsX2ZfTWR0bWdjUXgta2kyMkhxYmFfNXZ1Vzludm9JSnJ4WGlSamFIR3p1X2tmZWJ2LUxQeXFXM0NIbEVxXzVWVXZGdUY3TDg?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1261,27 +1261,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gatekeepers publish updated reports on DMA compliance - Digital Markets Act</t>
+          <t>New report reveals Black music’s staggering worth to UK economy - Rolling Stone UK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 13:36:27 GMT</t>
+          <t>Tue, 17 Mar 2026 11:58:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOLXduVk5qTTAyMzRDSW9hREEwUHhZQmR1MGtrMm9ZYlhYQ1VSeF9wUVFSQWNIQWVvRDdXSHQzUGNQN1RjeUNFTDBwZnRWUmVkUWtyOEZFcm9hWnB2WDczcDRmblo3S29hSnZpNjg1WFdvcXd6ZXJEdlVVMU5lcUN2OG1GQlFpNzZuVENRYTFsb3hybG8tdlIwUUJYd3Vqb1BPWjhBZU1QejM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQSU9FdGlsOVRNYzhpMy0zVktCOW9BX2gwR08yNUt1VXh5bXJsX3ZpeWNGTmNFSjBYcDZ1Z09UMTBGZWs1ZVdkQ0RURC1EYXM3UjNlRDhSc1hQZURMSVpfRTZMNDV3cTNOWUJGZHBIRGppeW9EblAtV19UUWFSYXhFWEhEejJhNGxUU0Rkd2ZpUDlBWHFTNXp6WHRvbFdIWVRHX3ZCclJyMTFIQQ?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1291,27 +1291,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Derby suspends Pakistan and Bangladesh recruitment as UK compliance pressures grow - The PIE News</t>
+          <t>Tata Steel UK’s support for circular economy initiative - SteelRadar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 02:48:45 GMT</t>
+          <t>Wed, 18 Mar 2026 07:36:19 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa3JONzdZdHc5ZHliZHFJbFFWUllSaXFyU2stbmg4QzdXZVp1bUxGNk1OejlaQ0liMnBrQld0ZEFaR0dpYXhETHRxSUt0YVZ1YTZXaU5PRExwUC1oZ1B4NXhTd1gzaVB1bFVQVnZqb0ZNbkJwVkpobmF0S3pYb3VnZm1RQl9BYkhSQzNHWnFGWGZHY2YzVnZlODhnWkJMdHoyU2hhNWJfbkRJQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMnpCZ0szR0J0X0l1OF9ROExaZDFDWjZPZlE2bldDUEIyaDF4cHpkaFQtUXZhZTNibmVHQTZMT0ZNdXViUjNiZ0FSUHMyU2xCcG5rLXg1bnRYTzdYcTFVTWZGOUFTZU9YbDFaVHVQYmpQVVdNMnNCMVMyRWpWVGREREEyNUlWdWxkSnQ1Z1NOX0R6MC1tM2c?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trump's 'show some guts' comment problematic for shipping - Seatrade Maritime News</t>
+          <t>Iran conflict turns shipping market into ‘wild west’ - Financial Times</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:18:56 GMT</t>
+          <t>Wed, 18 Mar 2026 05:00:27 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMThXX2lLUkdfQmdZS2djNTl2cjJwclVPcm5VaVI1SVF5ZEZzaDUwYXFpYXlmNF9VNmpzTFppQzhia2xlOGlVendHMENITlhmTE00VXQ2LThqNWhRX1ZEMHF2RlBBQkk4ZVYwOUhwaDZoSXdGZm5xcVV6dFlEVFU3cHFnQ1VlVGV5dDh5blZMbFowTWE1RjM0a2kzZHlGYzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9zb3J4Szl2T2ZXWVJGdkdvY1AxM3FWZE1tb0dzZ1FEYnZBRlhuZkFBcnI4dnF4eXlIRjJ1d3o2Zm55TEdMNEhkMXRFS01lOGVvNjBiM3ZSSFpBYVJVQXVFZ2xCWHJZTkc0QzdhaUdjV24?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>'Self-defeating': EU and US clash over Russia sanctions relief as prices soar - Euronews.com</t>
+          <t>Blackpool 3-2 Port Vale | League One Highlights - Sky Sports</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:04:57 GMT</t>
+          <t>Tue, 17 Mar 2026 21:53:35 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNbzlRa3ZSWlZKeE9hMGJVcDhoaWhQTGdQLXRiY2NIY3hiZVNQVm1WZVpSVGZzTF9PT3hRSjA1Qnd1d3RkbHQzelhYOEMyU0ZLQmg5eWd3dlgybjd2eGFGZUtGNG9VdHF4OFBrUmJUSmRPc0x0TkUzVE5tbEhXWlpUSWprNm1ucXpLN20zdnV2Nkw1UGJsRm1JYVFBc0ZJWjZOOFY2dmZxTHdZbkdPODctTXFpTk9wSWc5U1pScw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPZnJLNDVGMHlsOGVZdERVRU1oX1dYUUJRdlpUazVQUFVnV2htclFyeDdSMUVzR043a0ZPTGdYc0RDY2VuRVExWVJNN2dZTG94QmxGZVNqeE9iaXZ4b2pQd2Fmdm84VEhVYVByREF2N3drRW14bG1QTWhROGZYUmxIMFA1a2xQaC1NTW1MSnd1eVVSSjR0a1hmQXJqQmhjd0RUSHg4?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Trump’s tariffs mean more cost-cutting at Volkswagen - politico.eu</t>
+          <t>Iran: Council sanctions an additional 16 persons and three entities over serious human rights violations - consilium.europa.eu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:46:00 GMT</t>
+          <t>Mon, 16 Mar 2026 14:25:51 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNY3pkXzNDT1JvbzRJaFE0WnEtMVpVWDZUbXp5cDQ0X1lDbEFiZmF5V2t0VmQ2SU95QmFSbjY1cjdKZWhGYWI1U01CS2RYYkg3VFQ1QjZsV1RNa1ZjYVd1TmpZaDdMZ2NKZTBnbWQ3aVlaaXZRclZRRTdHQUxQMmN1WTdxbzBuZ0ZETU9GbURNalNVQUJL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOR3NJbE0yM0dQMzNXODF1QmhSUmVZWERaaVF0UUQ2Y0R1N1k0LWx6dno5Qk1vTUloclF5SFhZdTlsYU9XLTJiSENWWUctNmNaU1VhUjRkUU1rLW9PZmRlU0lJUUdJZlloam5HUl91a2d3Q1hPVXlSdTFhWmlfb2FuU0E2MElULUZaU09sa0FpVHQtYVNTQklkdlMxVEV1Z0JHRWNGU0NQZXpFZXAzTzV2YjZUUWY0SzJ5blc5N2xub3ZwTXo4XzFvTzBvZDN6ODEtalhhRjhEdE9vX1ZtX3FyYTFVZ2RjVnhndk8wT1RRczItWmZGSjZJakx4MjJOUVU3?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>How Osprey Approach is supporting Hannays Solicitors’ long-term compliance and operational confidence - Legal Futures</t>
+          <t>Freight sector concern over port access charges as it calls for fair treatment - Rail Magazine</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 00:01:06 GMT</t>
+          <t>Wed, 18 Mar 2026 06:04:18 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQaV9VOUY0M2Y3SWE0OXROSWpoSWlQRlNYWHhtbTdUeGVmR04zbDB1SzdsNDlWREN0WHNpTER2MmhrWkg2YXZ6SV9Jd3pBLTlFYUJJbFVkT1d0MGttZDM3enNOLU5HMTJsNzdaM3RqMFllWWpmWDBYZzFKaDJrcktxNDFIS21UQkZtZUJldlo1OXB1RndZa2FWNUtfejhwemh2ajhhZm55WkRCcHhlXzQ1V2hfcWdVZzd0ZVlKWjRoa1YwZzNpSlRMVmpScUo3cU1lc0EtQUxtVDl0NENCQUtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNUlQ2QVdMbWlvT2FtdEZEVS1MRWg1UEQzcXZLR3lFRWpWNHk5eUJUS0UtNGFqbC1XNFk2Y0xUWVRsVVprY3k4Nmh3NzNtWDlJeXdMdzA5eGJhVG40TGlmMUxzbTN3ZWpOR3VTZnBvVk12RVQ1b2QtZm1NdTFXMVJ1V1RLdDBnbTRINFBVQ2NiS2dxN0hSdmlPRk5scjNQcGpfTWtBdHJBVmJNYjNxcmV0SHB3?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>David Squires on … FA Cup magic for Port Vale and a close call for Mikel Arteta - The Guardian</t>
+          <t>UK to raise steel tariffs to 50 percent in new sector strategy this week - politico.eu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:32:00 GMT</t>
+          <t>Mon, 16 Mar 2026 15:33:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNYXExNW9fQzdPeHkxUEI5LXV3b3BUSGZNbzduQkZvOG5aQ21EMVFxRVlSWjY1ejRjRVBUZnRucGJ5bnJNTmNDOEJIblJlSGxQb2M0UTdWOVR2RG8wNG5VUm81SXRQelI1WWV5aW1WcUlHUmZYNTM3Y2xfT3BjUDBiNWtKbnhDWWhSU1VQVWVmTlFzb1F6MTJvX2l3ZVJLaFRUTmR1eXM2MFQxRXpZLUlwQk9IbUg2NHJp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNNWg2MkowZHVxeEgzOVRvYUpSMmc0LXJLSF9jUjdlQU9nRjZIVjBGZmpCelc0YzcwX2JaVjZuSXNIRzFiZ1JKakM2eDk1aHZvc3JvSVZDVTY0cFBPYXRRbERZTG5xT3c1VEsySHdwSndoQVhrTk11ZmlKMmlhZ0ZEekVQSFdlaFEwX3VNRU9rdGJEUFE3WUhYdUNta1pYVDZCZGdXWThyUkNEQm8?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BBC visits key Dubai port in Iran's firing line - BBC</t>
+          <t>Boots inks logistics deal with XPO Logistics to support healthcare and online operations - Retail Technology Innovation Hub</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:07:01 GMT</t>
+          <t>Wed, 18 Mar 2026 05:35:58 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9UblRfY0pUamFVODFzVkFEMTI5OGRaN3lDNnlncG9pMUpGTzBqQU11YUNmak85dGFvd0NnczVxWmQtOVA2QXVBbkszc01YbGJuV0ZmQ1BDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPVmNRaWlfSG42V2h0eFRaendCaWtBWUZ2RUlIa0l2bHJ5dlRGYmJ0WjVMcFczclNacjlzejJoRlpfdVFyT0xQRFE1SGR1US1IZmxwZ1lSNzRGbHRiNGg5WFJXOFFDb1E2STZta3ZIQXJXX2JzaGVUM2ViVUpIcHltT0JiVXgyZGx0UlJiT0k4d2RMX181akk3TUtCWTlyTlV0SVRJeG8yNEloZjBmMlZoWHRiX2E5UkpBeVRIMjJmNmRycGVCOWgxMEVlY1l4Ui1WYjk2RnVB?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Senate Democrats introduce bill to shield small businesses from Trump’s new tariffs - The Guardian</t>
+          <t>Trump's tariffs were supposed to help manufacturers. But instead, they're hurting - The Independent</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:53:00 GMT</t>
+          <t>Wed, 18 Mar 2026 04:03:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPdmNzMTJNejdma0JqY0NqMW56QUJxUUlGMW84MUFaM0VxNGJhclpzX0F2enAwUzhYVWhXUnBneUdULUJFR21Eb2lDa3JqSF95UC02SE5SMENua0J3ckpVLUVzUWJnU3VSLVVpQ0hzUXhjOVYyMGdHLThPYWRWYTBMSzZFZS1IQVZzMXF3YjRrT2NMbUhDQmx4VmoxcjdrYWFTV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPYVdTVnBwbjVRcGZqbElTbHZVazI2aDZ0YW9la3BLa08zRTFaU244eWhYd2lOUl9SSzdHbFg2QXdkT05LdHZ5NTJjNVd3VlRIdllRRGYyT3AzMkFFNzdpUDVvaDRaOERhblpNWUUxbTZxREVEcVBrQl9uWTY5bG9FU05YVXh6SDl1WEY1OC15QnJFNV8xYVd6TzlZYw?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>‘I was absolutely gobsmacked’: Port Vale fans react to unexpected win against Sunderland - The Guardian</t>
+          <t>Trump claims he has ‘absolute right’ to impose new tariffs after supreme court blow - The Guardian</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 20:08:00 GMT</t>
+          <t>Mon, 16 Mar 2026 17:23:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQk85QktYaFdrZElYT0Zzb2RrY1IyMmpGa2Z1aVFHcnNpTFpUeUdNOHVta2xKWlhGQy05dVp2bHVaWks4RmhxWkEwcVZxNjJZZEtqTHRhQnpnX1VuLVkzUk5ZQzNqaHlOc2N6OThJRFhBRWl6WWkzZWJ3Nk4xeDJyN2JoRXRvUmtPUTJRQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPMG0wek9EX2kxNmpZZDJJckt4LVdsQllPemwxM0dXYzByanJaZjdmSTFLVFlaNXFkVUc1T3BzbElSRHhZMF81LXhLblp2VGN0NThhRFJZZnZyanYtdzVYa3dsVHg5TG5PeXN3b05tbUItSmpFS1IwMkR4akhIcW9LclZBTkdmMFJuUmsyclVsYjdSTklKNGNiMmZqaThsSkdmTFQxSGx3?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China exports surge despite Trump tariffs - BBC</t>
+          <t>Jon Brady: Port Vale boss slams 'joke' pitch for 'breaking' players - BBC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 06:16:02 GMT</t>
+          <t>Mon, 16 Mar 2026 13:22:12 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5JUEJwZVE3UFFZeFVFYV9BUHBBdVE4YTdoX2JIODJTSWEwaTFJcmZBLW9oTjliSjNrV1g4M3BhR2t5SXFqdUVKcmladG96U1U1Nlo2VHhOcDlTdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFA5YzZmUzdQREVYNWM0a2gwbWNiMFFCdlZweVJBTmlqWG9yWHJrVk00RlZ3akd3S1I3bUJ4UVd5aUJOUWhTN0M4b25OYjFfazNNQ0NHYkpzN1hrTl9HWE5nQS01RE54M2M?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>United Kingdom: Additional Compliance Obligations Introduced in Updated Sponsor Guidance - Fragomen</t>
+          <t>Greek exports to US unchanged despite tariffs - eKathimerini.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 20:55:06 GMT</t>
+          <t>Wed, 18 Mar 2026 01:00:31 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQOTdZQkVSdkpfSjE5V0NDejN5dzdQblZJYVpoVFNsa1FoV1BDMFprUVRoc3BHSVJNdXNta01adE9GcFJMN1dUZzl6blRFNnJ4VlppVllGMmw4OTJzVGNDZFphSmNYRElsNnBwZUM1WHppRU9YTXdObnRaOUJkTFdScUhKalBrM3p5Y2FGQlFDekZrUC1uSV9JM0N6a2RoMTNiTEZDZ0JKVDcxeFhJQ0FOM3kyR1ktdGpJMDFEOGxBTUNEZlJV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPb3k2cERab2x1VG9NRjJ3SnplT1U1VEFrU1AwS054TnhHb05SUENlaVVjc0tVV3MyMEFuTHo0blNmTzZ5MlBWZmR4SU92WUlOLWltdXlSMks1aEYtbTBzZjIzVWFXd19vTk9YQnRkbnpTQU5ldGRIa29WU2taNC1lUzF3QWJ4XzdBdnpDVV9wckVEUWl6dGc?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Putin gives Trump easy way out of confused Iran war strategy – and he might take it - The Independent</t>
+          <t>Russia’s war of aggression against Ukraine: EU extends individual listings over Ukraine's territorial integrity for a further six months - consilium.europa.eu</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 04:01:00 GMT</t>
+          <t>Sat, 14 Mar 2026 15:32:49 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNemVuYVN2aFREVzlSX1ZPQ0VESXVMTWhZMkNVejhDZVpicmRzSWZaQkJGTzh4MExXMmxHWUVZN3E2OHVoSnNGb2ZiOC1TVkxiSm5sek9jaHpVZmFpQ0Myck16NktrZ056ZjVJbHFJSE9oeVI0VGdvSmxneVcyOF9HWEwtT1JrTlB3R2pmcm11YmE0YjExbUZUT2ZfS0F4d0hwLW1ZZnZ4bXBKN3IwYjVsOE5KalZNVm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwJBVV95cUxQU3lQaVplSWRXSGF5S3c3MjQ0dnZLS3g0UGMxTEYwU2EtMkVGNnRyYXRQOGtFaVg4UElBeUcydU80LUU0RXZ5SHVZVlhJaEw0aF82d1FDX1c3X1BRdXZYYmtFbmtET3ozQ1hyVGpaN2QxME5KQ05obXZlTzA4bHNZcnRzQzRyZGROUEY4aTJtWkExbklJRXFSUVphMlJQSVN0ZzNUeG5OdVhRdG9ieGdUc2JfaTg2dDFKRG83c3FhUGRPcE51QnVRU1l5eHNQNjJPRVlsZTViQ2hqSlNpTHQyclFxYklvamY4STE5QThveFp1Y05YbjJOZjF3ZzkyNjFDcldJbUYzZHRkSzE5R1BMUmxmdk1GXzhFaUU1d1lxSVRBaXlSV3NSc1hPOA?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argan lets 32,000 sq m at Île-de-France logistics site - Green Street News</t>
+          <t>Q4 Rundown: United Parcel Service (NYSE:UPS) Vs Other Air Freight and Logistics Stocks - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 07:22:27 GMT</t>
+          <t>Wed, 18 Mar 2026 00:42:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPM2dYektqUE5ScWtfWlZfMW9ORVVCWW5EVGtJanl6UXhkUi1OSWhBRFk5OENXemxTS1BXQ01fQTZEMnRvR043anlCNm9hbEhNcy1IMmM2MGhhNDA0V0hjbGU4Qlo3RGhVZ1BhZXFQbVN2QkpqbjkxWXlSZEQ2c2ZUY01EYjI4UU1WNlZLTlg2bllOdXR6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNYS0yUms3aUdNUmNaRGxjUHZUbnJmWDNUbUk0SW5Ca1dDdFFLeGJFVFI5Y0YwbERvcF9HcWQ2UnNHdnA1ZjdTNlJ2X2VJQVh4ci1TUXB3NlhBcFcxQXhwUnFIR0hza0s5b0RsVC14NHBVaGo4aF9oTEJydVU4aTY2M2dhTDc?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US Navy tells shipping industry Hormuz escorts not possible for now - Reuters</t>
+          <t>Crispin Odey’s former compliance head accuses him of falsifying minutes of key meeting - Financial Times</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 20:01:58 GMT</t>
+          <t>Tue, 17 Mar 2026 16:58:47 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOWXN5RnJ0RUQ1ZDlvLWtGbUViVXV5NXdiZ0RWOHV5UVd4aEdhVTF3YUpuV0U2endhTndKNW5PVWVlVEcyam16dGNuMHR6M1lySXlUM2tVUnNlMzRKb2h2LTRxMzRQY2dxUzM0X0xkQ3ZJZEFZeWU4VXpPTjJ6XzlUcG1QRVFzQWJTSFFaX0dzVnlUam8zeHViSF90RTFRV2FMX2RtQjJnZGxMbG5VaEwzakU2eU9UdmRP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNWmJDLXp3ODFrVGlYRFhnVzgzbVhEaTN1b0RCaWNUbWdWTkhZNXptM1huaWJSdWQ5UVZpazE2TW9GZVV0VWhkSk1xckM1MzR0dVpiYkw0SDJWN3lLcW8wSl92MEhzNHhBSjdOaEJCMTA0eXZtQTY3aklZRDlwZk1XZmYwZTk?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Strike Paralyzes Shipping at Antwerp and Other Belgian Ports - The Maritime Executive</t>
+          <t>US to Ease Venezuela Sanctions to Unlock More Oil Amid Iran War - Bloomberg.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 23:06:38 GMT</t>
+          <t>Tue, 17 Mar 2026 20:18:46 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNXB2eDVOU191QU0tMzhKbHN6T1lyVzRIYW8tUlRaOG1CTWxvaUY1R00zQUNpRWc2RTlwVXVmREE1cWpEYkpZa29DaHR5SGtlTnhCNXNud2hHanAwWG56TjZFZFpWSFJzZ3ZFT1c2cEYtMk9WN3k1WUNjODFtOF9jWUV6ZHN1NGt6LVZwbkhjZGFEbjQxYzVGZ1ZMU1ZKajMx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOeXdHc1ZqUEl6RXJKbXhVT1pmUklWd3RfVDh5bFJYNHYzMmNQN29TMXdZN1BuTFROZ0NWM2FxVnZyZG9TdGVjTERqSlJJaU9BeU1GOHhra2hmUUM2NTk1UHlLWTdXOXU3dEk5c1BwWnVkbDJCdzA1bl9oQlNxZEZwWEwyZVN4bTlCajd4a2tnOEtudFJVTHd4ZERfTGlUd1ZvTm93Rl8wTlpnUmJBemVUbXMyRHE?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>'Extraordinary reasons' for port disruption affecting rugby fans' return ferries - BBC</t>
+          <t>How Latin America’s New Consumers Are Rewriting Logistics - Maersk</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 18:42:48 GMT</t>
+          <t>Wed, 18 Mar 2026 07:16:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE00aWhqRTM5bDg5WDdEaF8wTWVIODZuRmU3WTlMbkVidXluQ0szNy0zeWJVUWVQeWlTXzUtWXU0aFdjbEpUQXBxb2FidXBTekFRMzByck50TWdVVTFT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPXzRDUkJHZ2I4X2Z1UG85eUN5QjRoU3FSZVItX05VTlNfT2pCbThrRFRrMXR6UW1rYllZRnlUT0ZJSTFXdElYcDlrV0xYSTktUUNsbkNoWmtaeVNUZVpISG5ZZnJ5SlZHLXpvSS15Qy1jTGhadG8tZDdEdWdWVDFUYjMxQmJHZnZn?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Anthropic sues US Defense Department over ‘supply chain risk’ designation - Jurist</t>
+          <t>Morrisons Ruby Port – 75cl Bottle, Rich Fruity Flavor With Cherry &amp; Chocolate Notes, Perfect With Cheese - ruhrkanal.news</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 04:29:40 GMT</t>
+          <t>Wed, 18 Mar 2026 07:20:37 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZGE5S1p1R0ltZU80UG5pVHh4X2ZTaEFXZWktSmRUS05kT1p0YUY1Um9RNWd0Q1Q5NElMOGdseTBtTU9ScndvQk5SclhQbHpkVE9ZZFV5ZG1oZEpHblRyYlcyc3BuV2JvV2F6SXNmbm9vN201ZFc4QlVVWmxPWHRoYnNoMEVVU3JFTEh5WFFOZkV6aUR4ZTIwUlY1V2RkdTY1YV95amppU1B6b0xE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNS2hXa25TZTdKVnZqbVNiMnhNOVBhaExvX29ycllqOUJEN213MDA1NzJEanNQYUNnODBrVTdScTVZREdRaHFoQXJfUTRRRGZ3LWZvcVVJYjRQOTZZSEJQUUw5YjJkNExVZDRydmpMYkZlZlphdzFyNVpHVkx5WXFrNkhaUDBZNXNmSjdMWDhOLWQ?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ROSHIN group and Agility Logistics to develop Jeddah-based park - Logistics Manager</t>
+          <t>The era of US dominance in economic warfare is over - Financial Times</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:22:32 GMT</t>
+          <t>Tue, 17 Mar 2026 15:22:36 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQTjRhTGJIc1NVT2VaM1dfcE40aHdzeHBLVWR4NXJlWld1cktNbkJKS3JzYUp0clA4anBGN1EyT3A0UGk3RXZ0a2FVWFRqS3RwOWlxbFJSRnlwMnV6bDNPMnM0RnZfSXpYel9YM0NoallmMzZuX1NGV0FmZlM3Y196UnY1S2RhRUQ4QXdFdjRBT0FSOGluU19JNW9VSmwtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBFUEw1bWxsUlpOeXh1YUJEem9GLUpPZXB3eGI0emZIR05DemtUMDJ1b0FUR3FDVDM5VXdqYTBzRFNpaTR5RnJ6d1F5RmZkdE5fbWdWb1lkMEJWLVQzY3UtWFlGVWdUOHJSS3ljUXlSZlk?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>With Trump’s Tariffs Overturned, Who Gets Refunds? - Bloomberg</t>
+          <t>Fifa sanctions Nigeria and DR Congo over World Cup play-off - BBC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:48:36 GMT</t>
+          <t>Mon, 16 Mar 2026 18:13:30 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNNVpaVE1GS0I5SnVyaDMxQ09ySHY4OGNlSTBSM2tLMTlHbmhTX2o2TWFUSjZ5VEdiVWVBU0dIdW9XeDJRQ0ppXzMtYUZieHhiWExMb2dxWnJrbmNiVUlGMFhCdGNNaDlSbnl3d0pCYk55cWlpUFdvd0NLclBVZjNGcVpTODV3T2JyNkNMckNJLTJrOEstMkY3bnlaazBTZk9kTmo0Mm5GS3M5dlR3VkVUWHZ5UHZNaWJlOHRPM20yTFgxZ2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE11enpKejlEd2UyNVA1X2VwVk9oZWRMLUpjSmtsc2o4R051OHhJUVhORVhXZzRnaWUxNGlEeGl1OGh6dXY5N3dISHhPdE5nTkFkMXFIbU01dVl3RTJCQlU1X2IwUDVaSEk?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Elevating Compliance Readiness in a Rapidly Evolving Insurance Regulatory Landscape - SIA Partners</t>
+          <t>Chinese shipyard to build freight vessels for Northern Isles - BBC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 12:00:00 GMT</t>
+          <t>Tue, 17 Mar 2026 13:50:59 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNU1lRVWc5eWF5Vm9JSnBjeldsdEV4ajhaT2VldVNLczZyZUZ1WlJfV21MUnUwWDAxaFZGQWFSY2tLUDFnQ2U5NHo3SjU1dFQ1X3lzeHFtZE9KUTkxcmpzOHFuZXJEZm1tdENaOGYzY0o4ZVl0VFcyVXI0N0VrWUttTVZLQUg1ejRFZkhlaUR5WWJmMC1nSWlZVFFfMGRsTjhORXAwZWd5QURYTm02TXprbVNUenhuTEhLUlR4Vi1uVXIyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5sbWI1TllwQ0lfQmM5Nkk1SzU0TXBTNDJzd294STlxZjJXOWJRZElQaFZfVy16WVE2bzVqU0Y4WU1QemFjZDZzX0ktOVhBcFNDVVJKMjFnSnM3REt0?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>People Moves: Hormel Foods' Will Bonifant - Supply Chain Digital Magazine</t>
+          <t>Hubbis Appoints Andrew Chow as Strategic Adviser to Strengthen Compliance and Regulatory Offering - Hubbis</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:30:31 GMT</t>
+          <t>Wed, 18 Mar 2026 06:01:18 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPS0NrbE9MdXUyVlJLd3E1NEthT2V4VFJ4YU5hd3JfbWZyMktUMlk2TlNCZUZLYUJqX2VZNU9MT1BQRndVVDMzeWY4REF5bUJsUG5pQlBNUmwzRjBCbnRQblh6QXQxN3hyWl9IOGc4TkNBTUwxWHNRQm5KTk1DN1dBNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNVkdja24wUjBJOVFiM1VwVk5xeGpJNVJia2J5STBlMS1Hc1prQVd3Q0FFZnBfNUhqel94YUpQREMxbDkwazRneTYyUHZNYmdyQzI4bS1IbU50dzdkVGRmSUpRWmh5N3dYbWRhSlhPM3JqeFRnRkFlNjBVX2U3S2E4Y3ZDb0N5aFBJeTlWenlIX08tRWx5WXUxelNoV3ZHZ1ZGTExVYkZvRGx5VnRuel95R3hlVEwwUmZSV2FpdW1pRUFRTkE?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Slovakia’s Fico threatens existing EU sanctions on Russia, as Hungary vetoes new ones - EUobserver</t>
+          <t>Trump's tariffs lead to production increase at Lochaber smelter - BBC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:56:17 GMT</t>
+          <t>Fri, 13 Mar 2026 08:51:27 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOaHBicU1QXzMzbUFxWTJ5cFhwZzRiM2p4b1czVUttcGtEM0dLZnUxTmpOdkY5OFlrUjBTUXZuWFRkcFVfeVhNbk9NVWNHVnY5NWtVdlVnR1cxRkhBczVXVXRlMGxpeFQ3UU91V0hFU0c0VTBPYXUzZWNLUk1FOVFBRU5qa2hTa1dOVHVRcWV3NWJLRFFiVHI5YldFdWs1aWVuRWtPRlkwNGQ3aWxnYy1xdHNtV1g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5XX2FJM1lVbkJSeXhkbl8zVGRFNXlUb3dRNERKMXBMNDZiSXZVUDE2WEtva1ByZW10bVFEQ0lOczRFSl82anRDaG83RDA5UFhTMXhreHpYbmUtZw?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Electronics Supply Chain Outlook - S&amp;P Global</t>
+          <t>Poll on EU tariffs on imported electric vehicles - news.cgtn.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 23:23:35 GMT</t>
+          <t>Wed, 18 Mar 2026 05:47:43 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPV3YxRVhYRFVyWDc2WDlwaURvalphZlI4MjU4clRrdGJfUDhjZEl1d2dMRUJTNDlIVTBoWFZDT1VjQmZGTE5DWG1PaFNkeHVWT0hBbi1iZ0RuZnZ0bHFoUUVaU2dXbm9oUU9DN1lQNUs5Um15SHhhQjNBbHU5SzhCcjQ2REpWVXZSdFhHejdMR1lLSWdvYl9DOVNIbWxybFhGZ0JwRnVCa0pEYi1WSUx6ag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUzFwaU1oOWp1U3BDU2NtT21yNHpBcGdjbFlxX0psdTBkMl9SMnRYMXJZdFdESUhtbDNPcDc4OWR3MmRoRjA5bXNtUnRkYVdzYUNiX29xT25PT083b3pzbjdHV2RNOUdpbTU5MDBNMjVWVGVCMWRrbmdmOHBTa3JIaVhaWWRJQ2tFYk5HeWdqSDBRVldlYXFxa1hveHJZTnBUeEIxYXdYd1lldw?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PHOTO OF THE DAY: TSHD Albatros arrives at Port of Devonport - Dredging Today</t>
+          <t>Seven in 10 Americans say Trump tariffs have cost them more money - The Guardian</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 07:10:31 GMT</t>
+          <t>Fri, 13 Mar 2026 17:37:00 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPUFFQV2Z5WmNqZVNLNWtLTFZPMDhmVnN2ZEU4R19vZlZvTDVib0F2TEZULWNidGhfeC1Yb2lkRFdDbUtTV1NncWhaclBvUjJxVHVGSEkyM1FZbENuajlxRjdsWlM4RDJhWmhWcm9fZ3RLcjdpRHQ1YllpbzNYeFd1RG1wdXRHRFJvMVN2R0lCM010QXhMLUlhTXhMRXY2eEtMQzJJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFAxUXNyeUhpNHhfSHk5QVRhWXBGbUdhdmo1cUNhMk9Ha01aMm9OQVROa1M4NHhpcG5XV01CMnZfelhSS24zam9pMnl5LV9OWDRzR1dKY25vbWptZmttYUEwa29JME9XaVdmMXZObkJsNVlGcDhn?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Shipping containers to host pop-up art galleries in Southampton - Daily Echo</t>
+          <t>Cost of clearing up 40 wrecked shipping containers revealed - The Argus</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 03:30:00 GMT</t>
+          <t>Wed, 18 Mar 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNY3d5R2RocW1Pd2Qzd0EzbXYwOC04M1h4M2tjRFdROGFEd0JEMlhVWTZTc3RxZWhaTTZyN1VtOVNpYkoyUUtnaUlndkhpNTZPM1dDcUI2aDVxbHBTWU1YeU1PRXVRSlhRRFpseWpSeDZ2Y2UxRFhCYU4yS1ZVOW5CUW5xWWR0RHNTdEdQQzdBaGtYTVJ6QXRleVVaM3hWdG1x?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQWHhwSTIwdE9oWnBQQVZiYmZLWVlka2tDUzJsclN4c0Nzc3QxRnYtczB5T1I3THRVVFlHSTdnV25GdDV4YWlBSGtXOVhJb1lmbWpYRHRua0VEQ3gxYlI1YVZGWEpGVG16V0xRSlZ1U1JmaXllU0J0RkRwUlhXZWg4SlZYckVTZl9Qb1haQ3U5Y1VldmZxNzNMdFZENA?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cosco suspends Balboa port calls amid escalating Panama dispute - Lloyd's List</t>
+          <t>US easing of Russia oil sanctions faces pushback from other leaders - BBC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 07:39:45 GMT</t>
+          <t>Fri, 13 Mar 2026 16:38:02 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeXhxLXZUZlV0ZFVIQV9sNGJmY1NZMmV3eW1qbVlmOWRiVkw2V01ha3Y0UG9tV0tLUFhuNnE4MXZEWU5XTXRUcGhmUzBTbUdUVDdlTUt2U2V6d0hmNEwxcm0tQXlWOTM2c0pVbTFHbGpQTXRUTGNUMWlYTGJPNThZNmFLSVlxQVpUYmt0cnR4dnNoS3g2OVJGQnJUZTZLajlkQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5ZUzhYTzcybjRfTExSNXBDRFh4ek5OMXliUjZnSElvTHRjT1Z3TjRhbXdCcGtaOER5TE9ZYVlvWFF4aS03TEp1bkRFZ1BGcEo4QkRmNVI5cDEzQQ?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Middle East port operational update: Tuesday, March 10 - Lloyd's List</t>
+          <t>Space boom strains supply chain, industry report warns - SpaceNews</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:50:25 GMT</t>
+          <t>Tue, 17 Mar 2026 19:08:32 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQdWlsdVItcllmZFJwZFBxTEJ0Mzg5MnEwSFhsN0h6ZFpKeVRZYmZHX2dpLS1VdUlEN1ZxbUtrN2Ywc08tVFNIWUd2aUlhYUwxZWFmeWJKZDVfWVBOWUhlYnpZRUZ4OU55T2hCLXRUc2NYd3ZMWG5NcmVzVm9FaFVDdWVtSDA4b3laeUZHcjdVNkw5VzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQWVJpZUNHdjVZQk90cUpkZzVscmlYQl9Ra3lva09iQkppUVhFdWl0bWRtSVFVc240NVdRMkNMRVZOdkotS3E3cUtaaW5rQlBPNFBJU2c1d1BDa21nNGhIbFhoaGRfUy12ejJ5d3FabUxqTVVZRnJiSnhzbkpoWktHMlBR?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HMS Dragon FINALLY leaves port after Keir's dither &amp; delay over Iran crisis - The Sun</t>
+          <t>US diesel tops $5 a gallon in worrying sign for shipping, food costs and construction - The Independent</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:18:00 GMT</t>
+          <t>Wed, 18 Mar 2026 01:14:00 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPUFE0RjVjN00wVk5EWUt1UmxaZlVrSEwtbnJwQnp5dU1UUURZN2VpME1ES3M0eTBvb21ZRDZXUDAtRFZVcElTWDE1SHhXQk5tcG5YQUxpdXBaU3lSZ0FyTnc0N1JER3RrWFo1aVBIdWRMZ0FodkJDZzlaa1FQZE9NVWw1YlJUNXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQaUpOR1NNNThHaDFQVlN5eFRnQzVZRlN3S2hOY1RmZXFoQUlrS2lnMjNtQkw1eFZic19QRTB4RXNlQWNzNWVHMjhPWi1POThTdTluVEcybkNRTDM0SjJlOE9QY3Rpb2NmbFFpc2lTY01yeXZVQWF4NmtuNWFuaG9EX1RsNlRzWVB1RlB1SFNaQ3F1cUx0TlNNWGdILXdDdEM4Q3NidQ?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lifeline for seafarers given fresh boost - Daily Echo</t>
+          <t>EU sanctions Iran group that hacked Charlie Hebdo - politico.eu</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 03:30:00 GMT</t>
+          <t>Mon, 16 Mar 2026 15:24:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNRmpsWVBJVFZrU2dtVWlseWpXMVlOeWZOYm44SzVlNnFOc0I1enR5Rkt2UnFkaTFEeG1vZThJYzdjdHVIejhtMkZ4WFZlQkFIVG9ESmpBalRYRjYxLUFHSVdvYlpaT1pnQ0hMaHBfUHYtYTdVdTV5R2N4OVFyNXMyQWRBZlk3Q1MzY0QtTFpXTGU2M3JLNmQ2UThLbFZ4TXg4aGNyb0xB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNQTdRNjN0Zi1GRklEQUtrZVlOSHRQb1BJS3Y5SUxhWmFzNUpzVjRpM01rQmVCVEFCOTVxNmhoSVhGalVfX09aay1EbzBrWjF1Q2c5OWRDSC1mdXRxelVtaTRFTmhjcHJ2TXQ2MUo0LVloTEU5ZGFlQkUxcnFSak53UkJaYw?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Port Glasgow care home given 'weak' rating as inspectors raise ongoing concerns - Greenock Telegraph</t>
+          <t>Perth's biggest logistics offering in five years hits the market - Green Street News</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:30:00 GMT</t>
+          <t>Tue, 17 Mar 2026 21:47:45 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPTElGZklZUVpsYm9yZVp0dkYyaTdOM3UybDI0RWNGUXlyVVV3ckxBeU9yUGhZd1lvd3N3V2RzVGV3ZmhLWUhYaWFDWUUtMUE1Q3hHNUIxNkpPbHNQblFGazVyWVNfdW5oOWJoM3JXZXljX291QTJJR0VQT1phVHJmdmo2VktWZUZEN2lmU1hodzA3WU1jZkloYnVTU2pDQnhXYmctYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOR1F0ckJBZ1NYYjN5VDJZMV9wTFRmQk91dEx0b1ppUWJRSHctWTZveGFpaHF3T0JIU0dxWmdTNDVGVzVYcy1PQ3RldEdDc3laSU5qWUVBMFBxYllQUUdIZkliNjhiVUJaN3dmYlZaMU1aUUt6R29lTzRpWEs2X1YyQ25PVXRrOXZqU2JJ?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seatrade Maritime Club Round Table sets scene for CMA Shipping discussions - Seatrade Maritime News</t>
+          <t>Iran hits key UAE oil port and Dubai airport - BBC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 19:12:54 GMT</t>
+          <t>Mon, 16 Mar 2026 12:43:32 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOU3MxQV9RSl9yQTJuZVEtRmFJLU15TDhCR0dOMGZ6RkdKaXNnYzdzbnFyZ2VkOVZtQjNSSW1qdFNNTktuVGhaQktBaTExR1p6cU5iczVHSUJReDVhOGd6OGFzdW01N2ljYUpOS0RSN1RJS0hOMU9qelZsTnZOZkpJMU5IbEs1V3lkRkswRU1hSTUwczBDVU40dk1zOHNsUS14aWQzQjZMaHM3SHlpSWwtUU1wTnQ2Y24yQ2hj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5mOFdVeWRDSm12RzJwU2ZhWkRGRVNxaUZoOU8wTVZaUDJLYVlUb3JXM203YzVlSTNsc0pyZHZOb09ZUUdQX3BzUjVSOHVmcFZabktCMG8zN2lPQQ?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KPMG appoints Silvia Zamorano as legal compliance partner - Iberian Lawyer</t>
+          <t>Traffic starts trickling through Strait of Hormuz: Who's moving through and who's still stranded or diverting - CNBC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:04:04 GMT</t>
+          <t>Wed, 18 Mar 2026 04:55:43 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPcWZJemZQcXF1cnZtTDZXeUlES2pOcTBWc09CWmloWTdCdUFMTndlbmZsaC1NcV9TQW5xWXdDbDM1QndXRDBIVUdhSVNzbEppcTNRQkNEdDRRNS1VeWxLdkc2QmhlU2JKZWNOSkVqdXgxVElwVFAxUWRGaWkxS3pWb3JXc21xRVpOaHg5YUpiaE5rWExLTm1iRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOdzB6MU80MEF2U3ZQemV0RUtyVG85T19SN1FnZ01uZ3ZsQk50RXZGVzVSV21rV2p6eDQ5T0pEYmE4NU1OT2dYcFpXdTd0SFV1NEl4UGVmb1dVR2paVE02MFNfbzhOaWVCZGNTZHdYZG9iMTM0STF6bmZ4bXV3QTVPN1ZDZTc1SC1ESU5lVTJSdFVnTTRKVmlKMlhfLW9PcmlrcUN1OdIBqgFBVV95cUxOU3Y4QWE3aU5FTjU3OHVyWXFfTk1ZY0Jxd3VtNlVoeGhwMXlrZW56THo3RmEwV0Mxam9UemRrY2VkR2t5M21tcDZxdExhZHplYjJqRkY2LUl3WWRzcmlxTFg4LVZvaHE1UGFDcFlSRHRpZHRWU21reDhIMHNlTVNfRW9Pb3FKeXZJSVNrdnBXek15Ti1Sd0tvNWYwSHkzM3l3cklSaXN3S0djUQ?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2251,27 +2251,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Government approves Met request to ban Al Quds Day march - BBC</t>
+          <t>Carrier Protests and Border Checks Paralyse Poland–Ukraine Freight Corridors - VisaHQ</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 04:14:17 GMT</t>
+          <t>Tue, 17 Mar 2026 23:07:04 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBpUVlhQjA0c3V1Q3R1b3hnbGV6MkhJSjdHdVZYdkxKT3JTTE45aExDNlB0TTBjbWdpVDIzaklIbUpYYjkwQnhWbmFWVmN0WXNhVDRNNHZQZkIydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNSjcta3N1SlU5NWRucHhmbHVsTUVna0xsZ3Y0aWkxRkVSSlQ2WDN6aGlzRkxLVmotUkhYNUwwdTQzNG54RFBMTVdxU0lGOVBlOXZlX3N5T0NmelpxUkR5STh2NlBlUmt6azZJVHVpU0NYTFU0Ym1nV2pCb0tOU3RvWFJic1h1OExCejJFN3gtaHlZRTJ6bHhtdXNqVHRtRm10dHcwZkcwU0JzZFplYnZvSzZJWWtFWG1pd0gw?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2281,27 +2281,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>War expands to central Beirut as Israeli strike kills Iranians in luxury hotel - BBC</t>
+          <t>AFCON statement in full as Morocco named champions and Senegal sanctions confirmed - The Mirror</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:31:23 GMT</t>
+          <t>Tue, 17 Mar 2026 22:43:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5hMlZyWUl3V3hjaWtlZlV0UV9IRFBtQWY4cHB4LVRMcFZoWTJDa1JOMFM5bmhSbFRXWXhrbG9jUHVEVzFYcHVpT3lvVGlpN0FHR0VoN01xWXNHcTNP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPYTB0YllzdHJFVjQtZW5TSERPamVnWXhCeDRPdlJiV2JxcE04dWFOWEJHQ0ppVG9pQVNDZ0pFNm5vRHBJQW9CbGRrLUs4aVhSRlU5b3JxZVFXNXAtMlE4SVdrcmU3cEpqMW1MVWNXQS0teWhsS1Y2Ulh5UUVEdGpLOENLTFBkdFZjcTJldnNXLXdmQnN3ZFZr0gGcAUFVX3lxTE1XSzlkRWk0V2RWN2hFSnd5WjdjRE5adHZOTHpvOXdEaTl5Vm1xb05ILS1YeE04bnpObUVlMkd5RzlxM2dObXZZd096ai16ODVYd2tQMXNUVTNqT0dHQ2RpZFRNTTR1MHJyMHZvbmRMZEdWYThfTDJJcGJDaUZYRmZGaWk4OFJWZWJjS2xQdklqaW5PdWhPY3NkZDBSQg?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Man arrested with Samurai sword – police thank public - Leicestershire Police</t>
+          <t>Information which resulted in two Cardiff schools being closed is now being investigated as malicious communications - south-wales.police.uk</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sat, 07 Mar 2026 18:00:00 GMT</t>
+          <t>Tue, 17 Mar 2026 13:06:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUTloR2JZcXg2YWZQMXBNRGl0cDBIOGpRb2V2bEg0YWM3ZHU1d0Y2QTc3YzRtR1NraW1Jamxiakw3Wjc0a3NvRmFSOUVjVkNpN2ZmYzVHZEdQdUZkZ2pCX1NpdlFDUmlsNS1uc3Awd0VpS3BqUFBMTjdLLXMzTGEzeEg4dHVJd1JIOTRQWFpOYnA4dHA4ZkNZdXRwQlNLSXdLcXJQWHZabnpLcHA3UUpsQU5NT0VpV01YdXpHLUY2S2drYTlYb2NDaElXT2JET29pMUFpc0Z5UWVSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNcEZkUWRPYzczaWJzUllrQ3M0R2dTWEVJZWFpT2gyMWstVy1oNG1nVmJBSXI4RGMtQm5DNEZhNEM5X3VlSWppd2hIMkZkZFJEeVEzeGpDa3FwR1p1aDBGU01McVRjTDhaMFE4UU9LOW5VZVREOUJwWDRqdy1VQ0trWUtxSFdlQkJlaWdUMzFzWFV6cXVRYmxOQmNqMXoyYkJoUFBUbk94RUdsenBxbkY0WkNjMnluTFdxUDF4Rl9IZjNIYTJ6MUtfUENxNnBLT1ZrWVppUy13SGdNVzZKbUVxQ1l3YklSWFJ5OGNCZjRZT0RnSXVnT3RCeXVNMWVGQjJKd2dqZWlidk8wNFVQQVNsOVJB?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Three teenage boys arrested in connection with Hythe business burglaries - hampshire.police.uk</t>
+          <t>Five arrested over alleged gutter cleaning fraud - staffordshire.police.uk</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 13:27:00 GMT</t>
+          <t>Tue, 17 Mar 2026 11:00:00 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQYlVCN2I1aHV5TjI5eTd0aUhFM3ZuSDI0RlpfV2tzdDZFaWRfUnc3aHJhSV9zWGsyY2EyMllIVW15eGJNbmQ1OGZIWG50bWhMYlh1eGs3TlVJbURWdmxNTjE4cW1Ocy1OREwyTjVTYVg4SzN2OW02b1pCTUNucE8xQk9xTGJzWlptMkVIM2pjVzNfQkhIbm1Sc2NPXzVFandYaW1kYmdVLTJ0cURyWWpIN0VsSlYxM0ZfRUMwY21QSVU2dXMyNmJvY2tfY0JSSUtQa2ZEcG51blNwSjZ6aHJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPUGlsZ09VTThJQVQ3NzI1T3Axd2cySS05WHFSUGxBUUcwTTNlZVVZdUhtZkdheGdEZkhQbDd5aFRCUVYzSzUxYXNheVdVcVFlazBBanVZcmxGc2JkQUtMWW9qQjZ0cUNWemc5eFVnRTZoUkU5eG5pRWVoZ1pYTG1lN0M1WVpvT0R2WjRqSEVrYkVWSnEtQ2pkOHd0VGhxTFFZbjVHcjhuZkRaa1lTeEtYTXVJZF9nRG5EQnVETw?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bellerivestrasse Threat Cleared After Zurich Police Sweep – March 11 - Meyka</t>
+          <t>Investigation into the death of a man in his 40s in Whitby town centre - North Yorkshire Police</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 03:13:17 GMT</t>
+          <t>Mon, 16 Mar 2026 18:01:00 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTVAzUnNEQm5pRmV3U1N5bFRWdGM5YW5MYXpMMG1haDE0NklsTmF5T3ZPQTZWaVZYS3R3VTJkQlRsbWZMSEZGcmwxdFVZM29ORjVJODFhRHd1NjhfQ3BGU1l4dW5FTHBwbTBJMV9wT0lJc2FVbnB6VVNlbFhJSXVaWnFWU1ZQR194SUhPVkNKYzNZUklSZGgyZ01pcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPcjhMUWhFcWZFdTJqMFNmM3pkM0NvWnFiT3hpcVd0dlpzUTIzTEJkSndZSG9xZnN5QWdtaU84dEV1UlZ3cF9VUVNOQ0FoV2NtLUxsWnpFQnV6Y2x1UUhYMERXb1daZ2dubGx2bUVmdzRUc2tkSGlLOVRaLVVRaHVya3BpZDhGR2c0YnV6LXdtQ0ZTN3FaM3YzN1BLMWx5a1FJWG93X2xhdlVwdmFLSFVpU0VOclhXWmNZbXdNd1NqWVJERWRNaGRSVmJnZzVvY19xUUVVR0FlQ0dzTWNEclQ5LXlTaTZJa0lfcDJ0eA?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Suspected drink-driver arrested at Ramsgate Travelodge - The Isle of Thanet News</t>
+          <t>Man arrested after alleged hate crime at Bristol protest - BBC</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 09:47:37 GMT</t>
+          <t>Fri, 13 Mar 2026 09:01:14 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNSk1lLVd0SExkLVlLTDFjR1BmSWhOVzFaeGxhdGRGZVZMSExmTEloWmVMTFhYTjV1Z0dIWTNoVlpFVW5jNmZQR00xSnoxMlB0LVV2M2hhbU9Yc3RKbUFNRUtkcXVLc3ZTOHJBM1RvbXd5NnV5eFBqQ1o0alVUS3FvWUZoMThaNDRZcXFTUTB1MG9zX3ptSXpyOFd1em9ZZVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBmcmxUV1JITGtmMURRRzFoSHpsLTNaOERrQmlOanFFV01qaVdCUkw3Q2FoV2l3dFNHSTQxSFFnNkdXenlBZWNoRWZMZHVvajZ5ZnFCbzVoSmJZZG41?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pro-Iran ‘hate march’ BANNED by Home Office after Met Police request over 'disorder' concerns - The Sun</t>
+          <t>Teenage boy arrested following stabbing incident in Cirencester - gloucestershire.police.uk</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 21:00:00 GMT</t>
+          <t>Mon, 16 Mar 2026 12:08:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNa1pEdFdzMGlUMEYybU9ITnZndVZiUDJFYlU0MF95eEo5b3VUdlg0eXBDVjRzQnZ5c25iRHBVdHlseGFhaElyUXZrbXFFd1JaYkVNaUNmdjYtQmZpSUN4aUZBTUdwYVFOUjJZRU1BNkMwNFpGTFdoQzR0Tjc3bHZfZG43LVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQSmwxRFBsaVp1d3E5VlVfd1NvWmQtN2s1NDVFbzhpNXJaa3JVcmJpRlhoeExGa2JMTElZNk55NjZNTGNFY1h6SmlRLWFna1N5OWxvM1M3amhDV1Z2VU1jbXhfY2Q1aUJSOW9yX3ItUnhZNzJBZGNLeTZPQl9UOXc5UTY4M01OdDI1SkctNlZvVGxiUGlxSEZ0S2lKV0hoQnNvRGNFS2c5VXRFNlF3a0gxTXN0Tjl3bUl2akxMZnlQeFplVTNGc1dCb2JvWXdxWWc?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hannah Spencer: Green MP gets police escort from violent demo - BBC</t>
+          <t>Israeli strike on Gaza police kills officers - Al Jazeera</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 13:55:11 GMT</t>
+          <t>Mon, 16 Mar 2026 09:03:34 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5ENmpkakx4NFpSMGhKcUpySHZ0c3E0TFFsQ285NUYyZTRlcF9pT3Q0R0xIdjVqNXlVWlBIOGJ5bnRlMWp5dHdpaDNwOFFXd0t6RTJJajhhUUM4RVhI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPRG1RVmhUd1hRamdQR1VxS3V3Y1IzUXF1dEtrWkxJZnhlbjA2SGl6ZkQ1YUw0MENkYnprRGI5dkZZa3BvNVc2NkZ0REUtSkJFV21QZTczcEFvQU0zRTNadXRQSk9RQ0MtTUhGaU1hX014SHFySGxqX01qRU1qN3hqR3RadHJpajF3SWt5X2N1WWxRSTM2LTlOVkV5d9IBoAFBVV95cUxNWFdzMEotOVB0U19reTZLS0JWdzBDdG10M2xxT3A2TDNUeVpqdmtTSlRzQUVwUDFiaUJjNmNjRnY5TXU4UWQwR3QtMEg4cjFpcWs2djUwUVVsSERoYzdlWkJBVWdzNlIzRTBZR05BMDFJbEtLNjBldVM2LWdkSzNmVmVmT0FkQ21FMGp6MW5IX2RUa243MHVZMHc3ZkctTXli?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Police called following reports of women 'screaming for help' at Crewe park - Crewe Nub News</t>
+          <t>The Times Luxury Cartoon: March 16, 2026 - The Times</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 22:44:01 GMT</t>
+          <t>Mon, 16 Mar 2026 04:05:00 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOVTg0RGY3RHRzNUpydjlEcmpjX1dRN2xEUzVvZW51TzJoYW5WQmpua09GNkJPcWhNMVFibVY5Z0pQbVVKV09BTFBBa09TOVBuRzROWWViX0VUNmEySXoweTl5cExyWXpBNkpTVzcxMDlUbUNGZi0ya2dXNW83Ylp5OVYxWHB2WUE1NkQwZHE4QU9ycFRzN3pENDN4bVhWMUlSLVAwU0ZmdDNVRjdpNm55TndQMWYwNS1MaTdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgNBVV95cUxPQmxMczRCLTFYa0NRWTBwbVAwZjdMdUdWS2tFV3c0SHIzYi01NUNrOVJ0bThocXpUWTA0QnhnaU1UTHd0V1Q5bXRJVHlQbW96REpyLWVwMVFoR1RNbzNOWUlhNk56a0NiaGtZdmtITy1ZOVpDaEFoREc5WUdmbWpjOEgwYWYxOEJfb1BUSTRMN2xlbFpCeHZqWDlGckpIZmVfYWpSZHFfNVB2ZDZUaXRzek1lMGJvVXdLZWdPVzBPTTFTQ1BKUlhjdE9NbnJ0dW1kV3I3NGF4V2RHVFlZOEYwNU5vZ3VIUjhSaUZwZV9icVp5OElPY3FqSlBvMmJESzVrbUZpYkg5UXJSTVV6UDdjUUVYV1VWYmZyTHlhcUVLQ2VudVhLTVBiSmQyUGpHTUgtb0JZVjJtYkVFOGNHdGdSbV8zaHRRaERKSnc4ZzlwNy1nZTJlcm1sRGpBMGhIaDEyaUNvbkZzUVdGQzhBd2ZUYlcwbzVVVDgtRmxzTUMwa1FmTHh4TW5ZOUpPMGR4Tko5dkF1dHFJc0VOWTBkTlpVa1Y3Z0NMZw?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santa Rosa prepares for March 28 No Kings protest as police expect record crowds - Northern California Public Media</t>
+          <t>One week into Natomas Unified teachers strike: Parents fed up, one arrested - capradio.org</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 01:03:18 GMT</t>
+          <t>Wed, 18 Mar 2026 00:01:16 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxORzNGeS1yMVpWeHBWUEtoRnBRU2d3b3BxMy1Qd29hN25iNTdrQnFwZjhsaHZ4WXc1UnBJRk1zcVpLaGFtd2c4dFZ1bXlxZmZhdWFmY1RoT05OLTRGRjBIcDBVVzFZSFVSMVU4NGlaeV9naHM2bHo1OWs1eDNLLWZEQWdLZ0ZhVEtDTTg0NUUtSVc1Nzh5Yk45TjhoUGFOdU1jLTNHVUxGZ1Z2Q3YzVFNBQXhBR1d6NEZtb0V2ZDBWSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNMmpzenJQR0puWEtMMlptT2JrRlFNVXBGRmQ1b0dJbFlGWlY1V0hvUjBtemZZcjRMUF9xOXZmY2xJRHBrN0hCY0MwUTR2RGVvSUI3b3BwQWVpNmF3SXVxcG5XNWRJQ2xOVjBMUmJzakFKR3UwbERaZFR3eWNOX3VWZm1JMlVpWlU1OHF4dV90TDFBdGhBZ1VlMUlYdGpjU24wU0MxUkY2cy1ITDB3RXFWQnZ6dnNGV09hLUFF?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REMINDER: Seattle Police sponsoring 'Our City Our Safety' community conversation March 11 - Westside Seattle</t>
+          <t>Police investigate 'death to the IDF' chants led by Bobby Vylan at rally - BBC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 19:56:27 GMT</t>
+          <t>Sun, 15 Mar 2026 16:25:32 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOZ0ljOGJ6RkhYd0FtUkZRaWFsLXNKZ0pxM0tidG5LZ3pCTHJ0c1ZPZGR0NzROcTFocGhhQ2RZYWdQeU5KU2pMYXdkWS0teWpfYkltOGtCUVdSZUF0d0hiUjFGNDh2RmJvaHZUc3VvdE1YemFSNmJOYU1xd2UydFFZMEJKb1NnYUU4YkNUa0lkeXdqX1BpWnRKOGIyUkU4SUx1ckd1SFNXSnNkaDRzOF9xYl8xeUExR1RlY3pkODF5Q3I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFB5NzZOaXBfM1hDU2RQa3hGM2RXcUxkcElIZmcwTjRDc2hjbjRFNU1LWk0xSXlWdHRTenl6TWdyaVRfRUx5cEE1cFpCTFNVRXZnR1NPT09LYVhsWUxP?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>City police calls – March 11 - The Republic News</t>
+          <t>Eugene Police to host hiring workshop on March 21 at headquarters - KVAL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 04:03:00 GMT</t>
+          <t>Wed, 18 Mar 2026 06:24:08 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1KeWdVTDlKUmxyN1k4UGZKSENMazE1Y3BGd0d5VWREUzNSX3dVUTZWc0NVejkzWWtBR3NaajJsVUNrZGJIWlcxT3RKNmlpRWsyZndzYTNfZ0VHalFGMmZfWTZHZnZYcFpaeGNKN0t6NkdLSkhrbGxj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSGE2S1VuaHZ6N3h5eElwWkZ0NzdJVklHQkJZWHR4MW8xajVTODZHMWxzaldGX0NDaVNRT0wycVdnejIwMjNycG54SVhhTkJUNmZacjhEVU1OazFLbHFJTWpLYUs4bU1zamNrOXE2X0M1b09qWnk2UXR2RHZNWF9hRDNRQTFBOG15YUVFaV95QWtZTVFhcEpmZg?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Man dies after March 9 shooting in Wilmington’s Hedgeville area - Delawareonline.com</t>
+          <t>Baywatch icon Alexandra Paul ARRESTED again after animal rights protest saw her free beagles from lab breeders - Daily Mail</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:50:00 GMT</t>
+          <t>Tue, 17 Mar 2026 01:41:00 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNTHlYUXZDRXFVV21rdVM2WTRTQmgybWh0amhncmRMbnA2c1BiNkdQVVQwZTVNeTZqMG0ySEZRUDlSaFNGQVpFeFdmWXowbThNejRFZFN2ZjY3ckh0VzJQbHoxNVdENi1Qd0FSUEVLc1M1UndDeU9nTVBtVl9VcS1XLTY0UWFOZUI5aW1KUDRLZ0o4REpmSGtnZElQN2IxZEVJYldUNjZJb3hBdkpRMjh1bm4tX0I2RENkZ3pGaUZ1SjJwQUwwUVFmRHNhcnZUNGk2Q2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVm9MT1VFS2h0bWZKaEVWdlp1YUVyd2pwVF9HOUkwQnVjMUcxS045a3M5N3Vqc2tJdmRZYmVyc3hyaHJFSnprSGxqR1RLczFnZzlfU3ZpcHZkUkdkNlVmRTFnd3NfcEpXdmVGazk1UnJaRlM0SXB0N1NhT05URGF4bDRGdFFPV184NC1NWmhoemh4WHc5ZzQtRC1UQzljQlRJUmxBT2hQdzV5Z25KV3N6OWdSazjSAboBQVVfeXFMTXozOTktTGxQVzVvbms3M2xRUUJuRUpNNWxKdFdUd3lOWV9UZGVleGlTSGR3RXBjeTJVemx1SEdFV0J6LTFfbTgzZDAyb0NzVmgyaUV2XzE3eXVRU0l5eXNHemJIOHFBbGdDci1tMXlGemNFOEQxdU5jdlBidS1rWXFDVkh3eVAxOEtEaVVoNnRZcmJEeHdsRlpmN0JEY05Gd2xQdkNlYkswbHRZRDFaY001cGxpNS1OZ0Vn?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gracie Mansion terror plot: Mamdani urges broad rejection of violence as another bomb scare rattles Upper East Side - amNewYork</t>
+          <t>UK Police to host law enforcement training March 19 - UKNow</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 20:50:33 GMT</t>
+          <t>Mon, 16 Mar 2026 08:00:34 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOSlJkUC1rOUR5ZTZaNnhoRVZwR1gtcWhXeXNFeGpjWXJabXd3WV96S1YyTThNSGxNMkF1NlJIblllVjhSVTZLMzNxRFN2Wkh0YlVVejRFd0NpV3F5RFhRTFlYdVpidHhxWDFWaFFMVGQxUVhKQlRYOE4wd1lRc202OHJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQNXhiOC1OS3JTTmNDWl9aSmpTNDhsbWE2NWYzY3VuYlJwVGVZcExsSmJpdlZkVXRvOHg3U2d4RzJmeUF6NkE4WG8waDdJRUFkcXcyWHA0RHVtdFkybmlqTXV5NTduNmlIUlQ4ZnJ6M3FCMVUtN3B3OWFKZGpmT1BEZ2ZZeDMydDBS?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Man arrested for allegedly attacking deputy in Victorville - KTLA</t>
+          <t>Home Secretary grants police request to ban Al Quds Day march - Police Oracle</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 04:26:28 GMT</t>
+          <t>Wed, 11 Mar 2026 10:42:14 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOTXU3OWRRTGlTYWI4ZTZXWENjZExPOXF3NXRVajJFWmVTQ1k1MXNSNThKeV9IaWxjdlJMNE1LRlE2a1MwTUJwV0lQcFozeWlZRkV4RDZrdjJ4Z3k4Und4SENaRUNCMWpyTkJsbDNzZFFDa0FKMmlQMzNLNDN6Y0ctQ3RUREd3bVYtbWd0LUNCYkhkSDB1OXV5cTVMZ9IBoAFBVV95cUxNTEZxLS1OTV9rYndkWFJjSzh0WDZScmJ2ZEpHOUZfbDd3LWJKd0pJQllxaUNiUG5WVUVPOHZvdUtNM18zalB5VEVMSFZ3c1NVZW5DRnFsOGdNM3p4UldSdTI3b3QwQW1BejlIVDFNVXlxQXhqakduOGVLNUJKTG8xM0RXVWtteGdsVHJQdFNldzMydTRkcEJCalgwbkRlYXA2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNQXVWRDBRd2JNRkc2UDA1Qy1oUkw4T21TT3RuWGw1c1pJVlNwOVpaSzFwY21Xd09LenJOMkppZHo4bkxqNjU2d0k0Z2tTcG1jS1diYzFWNEdrOFFWSlBGNGpBZXlMT1VPMDNOcTdnUm02UUU4RzMyN0l4MjhTUjB1SVlITGxmbUtBNDV5QU1xZnBaSWw5T29NdTYzaWNZTlJoWnNsUDczVDFZNFk?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Loudonville police reports for March 1-7 - Ashland Source</t>
+          <t>Norfolk Police need your help to identify commercial burglary suspect - City of Norfolk (.gov)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 19:51:47 GMT</t>
+          <t>Tue, 17 Mar 2026 15:49:45 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOXFqQlEwSVpwWUtSQTljVm41RDZMVTZLU09wSndpeFBYUGZOdTNoU0N0R1hjLXdyazhRaVFuUXF6OGE5aUt2N2swa3RMX2RrMjZKdFpXdHdkV0hSMFBQN0JodE9LVjVlWlBFZ2s2cDFqWGFUVXhMTmdpclRvSXlCQ2ZfNGFmSFhibGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5ITlFMLVNuTzRuc2s5NlY4Vm5XTHJjUjBaTVRia2RiMnMxVTBWeVV3dklsRjFBVjVuTVAzMkl5TnpfUk4wNDV2OFQ0ZmRJRDhaNXBIbmlkcmZLZw?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2731,27 +2731,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Innovation in the NHS: personalised medicine and AI inquiry launched - UK Parliament</t>
+          <t>Alabama guard Aden Holloway arrested on felony drug charge days before NCAA tournament - Los Angeles Times</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 09:03:27 GMT</t>
+          <t>Tue, 17 Mar 2026 19:15:45 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOeEJqVjRGRUthQWw0XzhDSVdFVEhmUVdzekRBSEJabk9KT3dPdHFEZmRPcHhuc2tPdjIydFhHcVc1cWFyRVJ2cm1lbm5PYlJMXzh2UklhcmgybkhxeE96Mkc0NjQ4MTkxb1ZzQVZzOFhiM0JXOGVUSlQ5UHFXLUdhc1Q3RDdRSk9JNzNXR3MzZHMyS19GUjg3X0E5bG94bWlYSXdFVnNYaW9ZQ09Yc1c3Y0JJZGdMb3NTS1pHX2k4SU80ZVU0UENrOFBoSDFxLUdSUU1FOTJsWVVrODRYdXRoMDg0SGtNOWY0d0FES1FMc1ZkQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOd0h2NkR0WmJRYm94eVA4MHBUMmU3bUhUZlRFd001aVBFcE9nNzQ0V1pXaUtjMXdqbjZRTEJJYkhKa0pZWVotX1ZFY0pEWTlYUWpfcmROcjNMdjYtN3NUYkdrdWwtR29WT2FwdEgyQUFhbkFqMGNDNzBlbHRGNG9ValV3TXN6Y0I1b0hVbUFjRlZCUlpTVmdnSXBJWkZUMzFfeUswRHZCOWUtMGJjU1hCTnpySC1MYlN6eTM0SHM2b3M2b0tyTlY1Y2R5RXlGcU0?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2761,27 +2761,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>‘I wish I could push ChatGPT off a cliff’: professors scramble to save critical thinking in an age of AI - The Guardian</t>
+          <t>Surrey Police vehicle involved in morning collision, no injuries reported - Peace Arch News</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 22:28:00 GMT</t>
+          <t>Tue, 17 Mar 2026 22:34:32 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQRmJSV0FMd0UxbWVoczdlQUpBbFlaRUVDUUNRTWRaZWlMcEM0Ml9za1lUWjNiYmZ1cC1SaEQ4Qm1DTnZLNEdYTXc4ZGZmaFR1TUhPUVFGT0NSUmxzbG9ZclU3S19uajktVGhkT21vWmNYc3pBY0g0VlZKNS1XTTJnMXlPXzljWUQ4bkttZmlpdVk1YkhaZktQeThncTZlN1Rpdi1SV2l2NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQcHZxT2NfNkZVSXBpbVpKc0NYWFFpX19BUTdTcmtXckRuWjlGSHdDdk1mdEl1aUVUWDRfWUZpbmM1emdhWFJEd1FIbjUtbVdzaU5sS2ZLT2Z2SjRKRUFGa3JESWVOVUxKejJhTXZRQ3ZuY0VkeTNqMkNEVFZ3ZFBBTUg3UnNVZDhsRFBrZW5RWm1ReXh6RnptWVNoZ3pKQ2dMZEJta0RmMlNvMlJFekhr?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2791,27 +2791,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AI and the Commission and Facilitation of International Crimes: On Accountability Gaps and the Minab School Strike - EJIL: Talk!</t>
+          <t>Trump demands NATO and China police the Strait of Hormuz. So far they aren't joining - NPR</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 06:56:06 GMT</t>
+          <t>Mon, 16 Mar 2026 10:05:59 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQSWxmVjQzNW85MnFTUUxrZ1hYc1hncmNhbmc0V1o3RFJ1Z0tjQU1XNUdfdTY0Q2MtT3dKNFZjYWpHNGFfRnFhcW5UMzIwTzlsWlpTVDFUMHNMcHV3TXpPUXM0bU9GQ2hvYmQ4NEplQ3NnTFZIMzVJcHU2ckR4SG9udHpCNy1PVHBNSzBsMzNmeXhPUW1kcHE3ZHBRS3VqTkdvREpUNlhuelp6S0tJQi1UcURhbTI0VlctYUcwNW52cC1vVFdYY1FvemJHcUtyMzYzMWt1bnFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQRFdvSGxmM01ST1JyV3hvNkxTeTBsd0R0SUZ6MFVYX2lSNjUyQTBaX2xrUDU0QUxWR1pHU2JEZGJQTmdkTEFxc0JETWxXSGpOeWtfcGZ6U1ZVSUk4QjVSZko0Q19nd29zOFhHa1VqaWRQd3hUVWxMWWh2bWtJT25MZ2xJSUVhZ0ZkVlNubVotZXlCZw?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2821,27 +2821,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Newgen Software and G-ABLE Group Announce Strategic Partnership to Advance Digital Transformation Across APAC - PR Newswire UK</t>
+          <t>Police, fire blotter (March 16) - State-Journal</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 02:00:00 GMT</t>
+          <t>Wed, 18 Mar 2026 03:27:28 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxQX2ExNkNpdmI5ZU9QTlZabnZMVGRyUjZlaDBOeWFOLV9qOGRyY0lEOFBjOW1FajBkbnFWOVBsbXpLOXkxNVNNcnAzWHhyaFBLQkducEFORU10SDI3MG5DaldUOTJ6bTFPOUR3bzQ5UGlXMkJrZnB3SlFSMlNwUXM4ZzhMVGhrSURseGFfZ180Z09aalk3eHFLcDBsa2V3Tmw1aFBqQ21iZUJwSkQzbk1lYUdPbHg4d0xwakRWa2tDT0RpY2R5NnBJNnBaeDlxVElXeW9ZZDlva1dtX3RmeU9ZSXg1LTdwWmtTbnlhT2pGUW5VWUYzSUN1R2ZDWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5XcTNfTTFidFJqbThZSlBGMTFRdW1tbjVjWkVlS0o4WS1pT1NMLXEyR28yX0ZhOEEyM290cHVWQlZ1NTBMZWwxdl9iZk8tVm9yU3dpMmZPZmdlcUIzQW0xZUowNmd1bjc2VkJaaHd6dmJmVjQwMllZ?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>The rise of DeepTech in the UK - businesscloud.co.uk</t>
+          <t>UK will win AI race as Chancellor sets out economic ‘big choices’ - GOV.UK</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 07:25:49 GMT</t>
+          <t>Tue, 17 Mar 2026 11:14:30 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBpWXd5dGNnWVNCbTNCaGxabmlTdlZpZWxjV1VWTVY4QVd6YWVXQkpzYXhqdlJ3WjJ4b2NjREpweVJPaHhHUWlHSG84WG1nNmRpVzlEei1KdUNZMzJxMEtGdUV0bzUxMDJrdjdWRXlHd0RPdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNS2Q1REU1YlB5VFo4Q0stclFISkpVc3p1Qk5UVDQ0b093Mnp2dERSQWVxNHhLaGx0LVpya0I3Rkw1dzVaX3luYm80QkV1ZHVBTHFkV1VVUmUwNHV5blhfc2xWZnNWQVRSY3dNaXZuR1Q1NUdmTUlycUJVZ0V0NnFabFlrSmVwQU9rWmQxRGwxb3poU3lSMDZoX3dGQXdFd00?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lords Committee report warns of Generative AI risks to creatives - Fieldfisher</t>
+          <t>Salesforce reckons software and debt do mix after all - Financial Times</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:42:05 GMT</t>
+          <t>Tue, 17 Mar 2026 14:42:40 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNUmZqOV9pVVdKZ1ZFaWRTRHllaGl4Yjd0aUxVeXhCbTExZFhsaDJVRVVPOVNRTE9XZlRSRTlOQ1Z3Tkpvbko4cmRqejMyNmlmeUd2d0ItVHBHMkJHWnAzSVFqMzRkS3k1NU1KUm5BRVl6RWk4MFQzamY3cHJvcHUzX3pfYk9mQmd0TS14TUl3TXZQUEZVdF9mZlpCeUt5b1M3YWJ0c1FEUEM3QndDZ2ExWC1WRzZBb2hmWmdUajFBQTZYUkl4bXpvTUNpM3I0VkNQNTh4LVB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOYThHVlRPVjlNaUROeGlrMmJMdjBQS2wtaVNyNk40MG43UWZMU1JRcVpNenVNM25xRmZFQWxSeG1pUE1jcjNUbGJSbkxpNjdCQ0w2eUc4VWV4ZzdLcDhLX2tpT2hkb0xDWEN4ZEFiR3RLSDM4WkJ0bi1rMU1VM3hvdzUzWEE?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Neura Robotics and Qualcomm enter strategic collaboration to advance physical AI and cognitive robotics - telecomtv.com</t>
+          <t>AI and cyber security: risks and opportunities for organisations - Financier Worldwide</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:38:36 GMT</t>
+          <t>Tue, 17 Mar 2026 15:53:40 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOdFpoRGlUYXA2TXQtVW1oU3RDRlhVZEdQUWF6WkVqRFJTNl9FTnFBSXFaSW1qX0JwYThGODVWLVpUQzZ1bzBILTlCTVFMdDZPWWFHdm1aMmhZVU92N2ZOLUpoVmxaaGxiZlNGLW1zbEloRXRBT3Vta25WRTJidVo5WkxQeERpMGlOTUd3dWJ4WmxzUmxTekZPUmE5eHpJN2JZTXlDeXpheTFvM2g0TkpiQlgteWhXR2xjSDRLQXloRVFOSkZ4aG5jRzJIOHRXOXpSTjJzZnhmMjZfTmFNbWdzR2RTN2UxeDZ6Qkpac1B6YkN6OS1yQXFmMDZEWGpwUllD0gGGAkFVX3lxTE95VDB1czRVNzgyTlpTNGtjbl9HUkRONXR6RmlTQmNRcldzVERSc2NBVHFZOVVXZnBmWHhxam5JTXp2blgzQm9LWmxNOWhEZDBzRFRJeFNHZnRKLXhhTTV3dHpZVkJJejM4Z25mcEhpclpacXY0SmMxbVlYUGZxaTVNTWN5VWtNUlp6TVhRTmJldGZkNHpfS3RlQVdmcE93NVJidm5yMy1xdWd2YjhfeEFxYWlWQXBBSmI5V2ZUVTFTM21Idlk2b0ZhNW5TbHVWZldPOXNuSWZjNE1Xd3Zqb2I3bFdBeHI1V25Rb0dCNC1FYmFvNTlpR2xucDFTdk5GSzNxYUJ6S1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQcUsxdF9IN2NlOTJ4elBmUlA5Y2pGSlJXSk5TT3RjUzYyVzZrcHJhdWVwVW9XWElkQXItZWxIZTJKNzloUG5rY25qVEg4YmhMX0ZqRGwxbzN5SmJHcXdyTlZveVZYSlFVWEU0S1BJcy05NTZMSlFsOXpNMGJUSWJVLUNLR2FOb0IyNGlfT2JIcWROUXJhcVpQRUphdmktcFE?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Research on AI and the labor market is still in the first inning - Peterson Institute for International Economics</t>
+          <t>Government probes use of AI in children’s social care - PublicTechnology</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 13:00:00 GMT</t>
+          <t>Wed, 18 Mar 2026 01:15:56 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObFBXRGRVRS1Ba2NQdXB4dV9rVVVDZk5haTRtNkpGWmNRZmRWWUdJbVd4YjlfcjNJaGxJOU03ZHNLOG5BMkpOX0JiRWR5by1fbW54Q2JIM2ZEa3NQQ2xiZzJBYlpSRWtrejI0dnh3dGt1Wkl3SnFGZjRDb0M3ZlBOUndkaHpDTEdqS2tvLV90YllMQ1BZSmdGN1RZTzdOMzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNZ2E0cnlDdllXbzRGYlVLUVZiTVpMWjZUQU5fbWJabG4tLVhYYnRjWnRUUGlralRjM0J3dmlaVXZqX1lTSDJXb01PMmxIc296dkl2YkFzbUl2aEhoNXVVWUp1Y2VjaEN4UVpNMl9LTmxFaTgxcXVFYXRVTUZaa19XdV9tMDlpOWo2d3pzSVlMTXR3NnVpeDZfUElXc1FVLVVaS09tWHdxbVFjUjQwVmhaZTAzblgyenhvT2sxUQ?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>UNESCO and African Network of Judicial Trainers lead regional action on AI and Justice - UNESCO</t>
+          <t>What could ‘AI-native’ stores look like? - FashionNetwork France</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:31:19 GMT</t>
+          <t>Wed, 18 Mar 2026 04:56:08 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOalZaOFN1a2czd3FuemtldzJPeWdXbFZPNUVPUE53RmNJUTVOaDVUVkVQS2luS3ZCempUYndSbnpST1VKZ3F2OWQ3SkhBSXAyVldtYlU4Rkk2d2pwYXZJdkxHbXF4MzY5Nm5mRmMxQlM3aFN3Wkhabkg2elFwbVRQclVKTmxZVUNWOUI0Mi1CY0FVMnlubUlWdk1fWUJqZklFU3hfTVJpcEc1RWhfZ2J2ZUlVUU02Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNRXdxckY4ajhzTDVId2hCMmVQcHphZDI3N2lFQjhkMk9IV0F0NTFQUDhEU2d4MEk1R0tVQ3FKdGdPQ3lhcmhBMTltUnhUTXUwM2VRNkJrcGJLeElWZTk4RXQ2VkI4c1pZSTZqa0hvYl93dWNDQU5USWFBRHQxN3NTOEExZklKam5iVjdVdFBGaw?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AI and digital infrastructure are rewiring global finance - India Is Ready - LSEG</t>
+          <t>Siemens introduces AI agent to automate semiconductor and PCB design workflows - New Electronics</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:20:06 GMT</t>
+          <t>Wed, 18 Mar 2026 00:02:45 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNRHMyeGtVaXUxdWxEcmdleTFCcVhMdUZySFZEanBSbkVKM2s3cXQtU2IzYjF0ZHJEVFBpM2dLZFBNVldsZUF0Uk54X0x6TzlZLWR2S0ltYlpSZ2htSWRlaUgwak5GeVh6VG9ZUDZvRS1GM3UwLS1FOEo2N2h0WUxIV25KTzdwR1pPaXlzQ1I1NjNoTl8xOU43S3U2dzJ3Y1c5NDRTWjJ0Sjc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQVm1KNi1hM18xRnBwOEh5V0FIbXdOS1RocWFvbGkwTnRDd3lrN0RUblQ3RFRscjZCQUhRUlR5eWFjU2JQQmhFVDcxU1VYX1BjM2NmVlNxZm5tSkQ3eVdRQXlDUDFTZlpiUm5BbWRPd1BCNXgxNWRyOFJnSDlMUC1KcEJHMlBMOGw4b3NiNnRqdENYUmd6dnlVcnZRRHBCVk5QUDlVcldvWHN4UlJ0cFh1dUhBLWIxQ204NGQzTzVHQkF0dw?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PAC digs into government’s ‘curiously specific’ claims of AI benefits - PublicTechnology</t>
+          <t>MWC 2026: adaptive devices, agentic AI, and always-on companions - verdict.co.uk</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 01:15:21 GMT</t>
+          <t>Tue, 17 Mar 2026 14:22:10 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNZVZOMUN3Q1dvMjFpMnBycDJPTWJLQi1BUnJXSldMS2ZXYVVQLWIxbWJqb2ZZZjR1SlgtLVhVVEZKUXZCdkdrNVlId3JaU0V5ZGhJUjluWEI4S2FMc0JVQzhEcDhhZ291NjhpN0NyellEanJDRXJ3bTV1MlVGdmxMRU9fZFRDUm5HaDRBeDY0YnhrdUJWMjAwS09fQWNzVFkxMmNTLXFSSXlHNXBzbTlESlVOMlVUeUNGa0k1WjAwMFJKc2JUX1RRNzE1ZmVvLVV2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOS3U5NWhyQ1U2VDVrTkFjUDRLbU02cFIwYlZPZEh0NHZMVTE1Z1NRTF9jS2tGdzducXNUU1lLb1JLRm5naGVMbmhzcjN2SmhfLTltMDlPUzdaQjh5bXZlVU9obF9Zc2JHU3JZTi1YMV9ad2lETlZldW1GdVRIckxJMHJFUkI0UQ?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Google report warns identity is weak link in cloud - IT Brief UK</t>
+          <t>Majority of European businesses now use AI, but startups signal early warning on scaling challenges - About Amazon Europe</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 03:47:00 GMT</t>
+          <t>Tue, 17 Mar 2026 23:11:01 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWDA2UGhSWlRHYWVKY29MaElHYWNwNkR3WC1mWVNKMFp6WEdqWGZZRHd6c2czWGZBSjc5Vi14ZllMdzVjZ0FhODI3Tk44bk8xMnNOZEMzLUZvX3lISXBzRkFmZWpfdFloQjFXaE5GaXdpQ0o4VnNyLU9pa1JCYlEyY3IzNjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOMlBMTE9pTmtyVGFjbGpobVIzWnRZWXpWbFgwX3hwY0tFbzVzdjkxZ2NyekZQQW0yUi05ODNZdDNtVFBLSXg5aTRHalliWDlaQnItRnR0M2xyQVVkUWdJTV8zNmxNUVVWc1ppNXNDeWYybldPRWNnbFhTOHNnZ2wyc1FYY3JTM0tLQWw4cl9tQ3BGbjh1NEVvcExIcnNMTDBBLUNUczcycGFrM21MaU53eDU3cmpoUUFPcGdPb3RwMnlTR2QxMm9HN05wNTYybkNlcTF2QTVvUTg?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Google Research and Synaptics debut Coral Dev Board for multimodal Edge AI development - New Electronics</t>
+          <t>Europe Has an Edge in Developing Applications for AI - Goldman Sachs</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 07:09:42 GMT</t>
+          <t>Tue, 17 Mar 2026 19:00:25 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOTTNnWjFWWWwxTm50NmJQOTlieGlqOTBZdzdIRk45T3JYWW42ajdLbjVPTGxZNmd2NjA1cnQ4eEpadHFJaGFvRmtuaTByTzRWenBmQ3FzaDFQb3NTVWRGNW9EWVhBcmlRdV93QTNWR0N2YzdsdEpKd0Vua00tVjdJUEZjUnVQS0xSOElieFM0d3liYkY0WTYxMkpRcWc1OXo5MzdKcG9nWmMyS24xQlcyb1pOdnZxUWlKTmZpNFdSdnBPck1oQnh3X3U5cTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPZk5XNFRtYlNUb0ZhU0w3UGVhVXZqTXh5aDVxUmlIdDJnZUtKVDlXaXQwLWlTLVpudFYzcHdPRGlIZmViUERYWDRCOUJTcVNyWEN5LXYzdEdveTB0ekxETmpoUzV2MHJWR0Fna04xclBZWVpjNnF6SElPYXMyM3BwUUtSRFp1S1NraFFKYWJTN3BDT2ZURDU4NjJDaTRGMFFW?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>What is physical AI and how it is defining the next platform shift? - Arm Newsroom</t>
+          <t>The AI stories we tell – and the ones we don't - Journalism UK</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:00:40 GMT</t>
+          <t>Tue, 17 Mar 2026 18:55:43 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9OX2dSRV9RZWxfX1R2VWFuTzI0OExsN3VDbWk4a2RwbDYxczQ4TGRqVDBDaE9mZnNXOWV4T0I1dHMzSlZoOEM4TW00ZFRMaWdzTFlZZlhLcjVLdWJCNVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBXWkZIVEhlazM2WXRwRUFubjVod1FhN3BLVGhCekx5TzdVNVYwZ2F2U3dnVUgwNno4Q0pwRkc1TWI1MDhfSmhPT05wSVRFLVMwOWhsNXl5Sy1kSTFJOXpjUElQSFpuT05lcDZCcnlEOUc2ZFdIWklVU2JCNTUzUQ?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UK Supreme Court reshapes the approach to patentability of AI inventions, and beyond - Mishcon de Reya LLP</t>
+          <t>Node4 reaches Nerdio Gold Partner status in six months - TECHNOLOGY RESELLER</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 20:32:06 GMT</t>
+          <t>Wed, 18 Mar 2026 07:39:17 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNRTlyR2UzdnNlMjVMQkh0X1FGLXdPcmVTZlpmTEpJRUNGNk1yMjVwMGZZMExRN0lzclJJb21NUng2Ry1YVHFDMVdhYm10Z2hTSkhEX3RHQ2JUTkFseWt2RkpoVHBQMjI2WWhvb0VlX2ZMbkg4ZWVMRFlubFVjcFh1YW1Vb3RwN01rVTZVYU9sRG5WaGZUcXIxRGNWVmpaUnFVQXd3R28tTzc2Q05KWGxiZnRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOR1RsaDNDMlBwMXNIdWhHcnkxQzFncjdEOXhYLVdVYXVHTGd0ZkpOdjV1NmJEeHFhdGswZnhFaHdiMnVmY1d4QUVmcndJTGNXUmFSR2c1dUc4bElPQld3QkRVN0FIYlpMdnd4WDRRenhBR0QzOURyRzJDemR4dWlXRGdYSjlKc0g5cTBQdlZB?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Flintshire families learn about artificial intelligence through hands on workshops - Wales 247</t>
+          <t>Press release: AI at work - New LRD union guide to shape its future - Labour Research</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:20:43 GMT</t>
+          <t>Tue, 17 Mar 2026 16:19:31 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPNm0xbnNLcVI4dWd4SUFVMVVsMTlfR2lCVE83N0JJZURiSHNtU0h5R0lOSWV4M1hCT2I4ZW4xUERmUl9ieGlJZXR0aXVrYW0zaUJlUy0xNjdOc2lxOEwzeHNWcWZMQlNuVXUzMnM4TnVpRTc4bkZsNWNmZnFQYVFIZ3dBWE5oUWlvdjVsRU5SRldXMmRZekpzYnllcGozUk1ncmZ1c1pMN0c5eGdqY1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQQ3A0MTNDNGVjdmNXSDJIUWpDNWhJLVliVVdwaGd0WEUxYXJxd3ZMUkI4V2I3cUhDZTBORHhVOWpERzJNX0ozSTV6MHdweEVoV2gya3pNcGZ1WnhvLWVZTUNpWHJBcHNrQTdEVThSbWNCSGRMc1JBOUNCd3FGS2pNT0c2cWt4cjBiSHVRZ01nSQ?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AI and genetics reveal new insights into human language development - News-Medical</t>
+          <t>Global Underwater Hub launches underwater robotics and Autonomy Forum ahead of 2026 annual conference - Aberdeen &amp; Grampian Chamber of Commerce</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 02:59:00 GMT</t>
+          <t>Tue, 17 Mar 2026 13:00:34 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNemgweXRhYThtT2piT1U5WlhRQlV2SS1xdVhXbHBlRzRWUWdNY3NpZDlCTUozcF9jNHQ4bWNXMHJhSXJBOHFETEhlX2ljbUk3UmJUSUJrcHQzNGU0RWJzaVBKSjl2M2RtYVhRb3dhbUMtRG5ScVg0SlYtQV81THRxeGxXUHFVdG45czEyVGFwUHYzTVZOcGhub3A2TEgxR2FMWkFYemVCd2ZpQ2lkM3RSa3hwRHQtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPNFlWdEQ5cG9WRW1WZnhETlRWR21Uci02Smtxdk5XTzlyUm1pbHExVnplcGFyaE8wVWtJWG10cWVwbk1LMTM4bG0yQXVEei0wcmhqMTJpX295QzctZ3VDU3hYaXNFaEdCVms0b0JuSjNxQkxHbUhjSlR6am5JemZYbXdkZFRnUTlBblRCTldxQ2xqaDE5SnplYmRMYWFBR3g2bFk4ZEFIcmNTZVVnV0hxc0ZtcEFObkRhS1d2c3lGTDRTclhTbXk2SlRGeWtycTlOZC1B?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>UNESCO Supports Training on Drones, AI and GIS to Strengthen Disaster Reporting in the Caribbean - UNESCO</t>
+          <t>Cadbury's Phil Warfield: Inspiring Generosity, AI Adoption And LHF Creative - Creative Salon</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 20:30:10 GMT</t>
+          <t>Wed, 18 Mar 2026 07:19:59 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPVDNwNzI0a1c5em1FRWF1UHR0RDZJaDRTZzhyRTU4WmxfZFcxZnM2R2NVYlZQdENUVTVHelBOajhsUUU2VWxKRUVYdGxIc0M2S25lUkJ3TkI3MWpQRVV5R2ppdmU4b1hPczdac0ZSM0lESjNrbk5SZnhmTFZwTWVGdkRMaDc4UjdHWWV4RV9rWFlYc2xSMzhRblJSVUtReWdISjBqTG45RUx0NVRoYTljQ3h5cXV6WnU3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNWW9qeXJDck5INS1HSk1FY1JtWHJfVmNua3h2SXQ4aUlVYjhpNTVoNGYxMDBucWRnclM5MVdWaVhCd1dNcm9ZTC1PVk5GYlNmVzIzZ2VYandJUjhxek1UQmpFTW04Nk45VWNyQ1pJUUlEVm54NVAzTnZvLXpHdXJiR25mSXlTZWlWT2JZSWFqRGRzWnVsQ3pMQV8ybE5GQ2JBWFREN0tjYmk?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AI and copyright: House of Lords Committee sets out 'licensing-first' approach - Mishcon de Reya LLP</t>
+          <t>Are the winds changing on the AI and copyright debate? (via Passle) - Slaughter and May</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 14:26:25 GMT</t>
+          <t>Mon, 16 Mar 2026 15:04:05 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQdkpRdTlZaHYtUEJzdFFzc1NBY2RxVkhMTENoOWlBdU1MbWpsTTVXRVV2RVdFS3ZzX3hnLUxvNV9yc25kUmRxVXZlMVlEVjJHRWRJYWRlUGlqNUtzcjQyY3piT0toc3VoM1ZFWXdaV0NESFY2bzVSdFFybkdMM0JOQUNCcXVPTFl0SXpFa0lrcEw3VnJ1cVVLV1l2d05UV0ItWE9iZ3h1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQdk5KZUo1WmtQNkJOeFpVRzFNOTEtM3RFSk5aNFNlTHM1VkprcWRkMGpTTlFnYUxoZmtZOE1Jb3RjM2dieXVoUHQ3amF1YXB0aUJNN0tsZkhncE9PcUhNZUtEOThBVlctQ0JBMndnZWtxR20zRGlKYm44VklsdWhQWVNyZm94eXFPMElUcXRMWjF5Y01SRnhHa2EzbHJmTlljaGw4Rw?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Human-in-the-Loop or Loophole? Targeting AI and Legal Accountability - Small Wars Journal</t>
+          <t>Mayors to gain more spending power under Reeves tax plans - BBC</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:03:13 GMT</t>
+          <t>Tue, 17 Mar 2026 18:26:30 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5pMmhVcTFMNkZTQjdUaHdYQWZiWEhfMmdqMVBWSTUtTFotNGJlUENVM2pPUXZnQXJMWUdCbmtCeVFOTlh4VzZvNVpkSFdRU1VzY0QzX2xteExGdDBFV2tJUFd1ZlllbFJad1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9hdkZCcndvNDBEdXdna1hGOU9ySlFvWHFCVDd5dDJKeF8zQjdiTnl0Z3hjakNWM1dnYjRaTmV0QXNlTGxGSndaaE45X1BMbVExZS1RRVFJS0ViQQ?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Supreme Court Denies Review in AI Authorship Case - Mayer Brown</t>
+          <t>AI workflows keep marketers too busy for the day job - DecisionMarketing</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 22:42:53 GMT</t>
+          <t>Tue, 17 Mar 2026 15:38:00 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQTWliUUpVOXZXMXl6REl2RGZuUmkzYUJRV2FUMHg3RXlWNEVyVmpneng1UjZyZjIyTFN0OENPXzJpN2U1R1FKR1JqTzlyWTZiY1FYWnd0b2ttdDZYYWlZenA0ZDlyU2RHenpORWdJR0tTVkRfblNfaHA2a0NpWWZwajFPZHk0TEFLaGgtYnNiT3M2eElNVmVuVnEtbjFnSm9IWDNlMFFMM3VDWTdrTXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVlVYazlMMEtHdXVTbEw1WnREYXJVZlQ5UGI1dEhWdUNZOFVJY0xWQUVXTzRQNi1FT2NNb0NjeDFhUFVhYThnRkxYQU10eVpoaGRKclkybW5UNmRSam9BVExQU3BxUWhYZnpHYklxWTBQMHVRT2lPUzZnLU9BTFdPQkNyczVaWl91VTQ3cmNFemlOM0N2ektVaEJac1BRVEE?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Reshaping the legal industry – document automation &amp; ALSPs in an era of AI - Wolters Kluwer</t>
+          <t>Taiwan - a critical technology hub - New Electronics</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:11:58 GMT</t>
+          <t>Wed, 18 Mar 2026 00:02:45 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNRWhKYWZBczFXcUQxaDJnTHdnVTg1U05EOU91aXpoVTZkMXN0LUdwRFZhN2xGM0lxMTlTNE1PRXEzUVZjbGVPb05kelB0eDZnalFUa1RGRzdSam9oc09CWE8tblVxaXRlY2pReTVfZzFiY19LUXNISlBucDBvMjVJVFJCUC1mMVNGOUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNTGN1MGh3SlhEbm84YkM5cjAxRVFISkJVVUR0U2ZtNXltZXAyRUU1aGFyd3RFTzNRanc1OWJvN2E1cXg3YzdaS1ZZalhVSm5JbjVMeUhjMkk2aURSaFl4UXJRbVdIVVlETFJiaFd6bm9HZ3NuS3RySU43RXlhdFFtVw?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turbulent techno-politics: a leadership imperative for Chartered Managers in the AI era - CMI</t>
+          <t>AI and Big Data in Surgery: Emerging Evidence from the Frontline - European Medical Journal</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:59:19 GMT</t>
+          <t>Tue, 17 Mar 2026 07:35:54 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOR09HOXhmZ3UtY1NGRm9qQ05tTXlJaFFGblU3TVhOQWtDT1MwaXdqUmhvNVoxZ0FEVlNReTA3VDhXNXViLTZMUUNiZWFKTl82OHZjYzE2WFpob1NOaWhDa3FvaVRXZnptb3djU1Fua3JFR0REeXVveU8weTNKajVCZ3VBRnlxWWpzelZTMm1TLXVIRUoxRWV1RTVPUmd1ZzRUdWdIWm5SSU9xN0RiTmk3TTNhMTR4NGVGY0g2dm1LY1JMUVJkZnk2MUJ4MzVmand3NG1UdVBtNzVsZGxCWWJJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNZVJxUTM1ejlNc29mYndhdFl4NUVBeFlPR3VuQ3Z6QTBpdUFFb3RmWExZa3lSMi1CcV9NWHlNcndYQmNfRDJvVExLT1BTWER0VEZSdnlSZjY1WjZ5d3NwRzhJVHhULU95VjVZM1h0TEgtdGVZNjFSZTh4RUlkTVRQWDhUZzRJOVFzRmRSNWg4ZEVFZk9NMW5TRTBONXJWdEdNLUpVZm41c25ZT3U1Q2hJeG03ZHc5emc5dk1QVEREVnBkMjI0WGcwY193aw?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TrustInSoft unveils AI‑enhanced software verification features in April 2026 release - New Electronics</t>
+          <t>India's outsourcing industry is worth $300bn. Can it survive AI? - BBC</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:54:40 GMT</t>
+          <t>Tue, 17 Mar 2026 01:12:50 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNdF9KQUx4UmtreWhZNkhwZE0zUFVqdm5fdndUdUprYk4wTmZFSDk4bktJdWxZSER5MDlHUHowci04a0tWRjlIMDRpVjlneDJTbk5zWGxIQVVOemNLOHVManU4bVBoS0YwQ1ZZUXIyRjhtZllhcHRFQnI3dzBSVE91YmRwbEhvNGZmNHpDTzczLU5jdGhDeXl2TWc0WlF2TWxYQnhYRk04ZnNpcVFXNTI3a1JoTGNYeHpTb1NMUW1pZkwxbFZqNTBLVVB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4wTHVnbzFpczd5Wk84XzJjRGZmX1JYX2I4M09UeDFtLXpDVUZYTTBvXzl3akhHLUpHWDFqN2RDMTRTLS01bWtnTktlYUFxZ2x5VlMyblRFY0lydw?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AI and its discontents, with Decca Muldowney - New Internationalist Magazine</t>
+          <t>7 Factors That Drive Returns on AI Investments, According to a New Survey - Harvard Business Review</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 10:14:39 GMT</t>
+          <t>Tue, 17 Mar 2026 22:26:19 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNExPNWkzTkFWbDJGR2FaMnJGSEJMQlJWazFSNEkxQS1SVmtDYnFYaEdxWWVlaV9ZbXByNXlsdVJONkhXemZmbGZTeG9iamI4Yk9iZ0hEbGNvSzI5LU1XdGRzbHNhUXkzdG8zTG9vMXRMdFllU19USTl6WE5zTTZINTJJRjY5UlBwcHgtRG5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPYmVERHhJMlQtMG1pRllpSHR6emdaMlBkV3FOc2xGZk9hZVcxX3NPaGt1alFPLUI1SVlDdURXdU1ndzRSeEV2eUcwTmtPbVoxRGFfeFlGYzRlSnVNWmF5TC1ZZnU0TGhqcDJDbWFKc1M3U215YzVBM0Z2NGU0bTVIUUoxdFZsUjYtM2Y5TlVUd1QteTMzeGFheHBMTjc?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Careers Breakfast: AI and Machine Learning - The King's School Chester</t>
+          <t>IBM Completes Acquisition of Confluent, Making Real Time Data the Engine of Enterprise AI and Agents - IBM Newsroom</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 16:55:29 GMT</t>
+          <t>Tue, 17 Mar 2026 13:13:18 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9DSXhkcVpsOE5BdHJia1h3SGp6a244UFN3MDN4MzhqNjdxNU5YYVo4Uk0xNkxndEVVT0JCOWVYU0RKWi11S0FpSU5iVDgwbEx5Y1Y1czFzU3pmT3dMSWJqOXV0MFVNazRPeXBITzVZajh1dDR4NFREdUtxby1Kczg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPUHFyR1R1NHJSZjA1T0diQUZybERvZ0RqU0YzQXpYbEdvQkhaVTN6QlJtYXRHMjVPLTFPQ2VYWnpHd05rc1JmWFVkOG5hMDUyX3YtWDdUcEhKMWw4WWxvNWtOLUtacVA5c3JrckR1eEJ5ZmQ5VjVMbDVTWXJSMk1iZU9za0dtbGI3RGo0N1Ftb0hjbEpfYm9FQWtrc21mMEhFb1lYNldNa1RDMmVaU19ON0hDX09PN2ZpeTJlMktEblhGQUVsVnFjeTlBNm1SQ2lwTHc?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Indra Group anticipates the future of smart mobility with connected vehicle technology and digital infrastructures - Indra Group</t>
+          <t>What's On | Alien Intelligence: AI and Architecture - Architectural Association</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:57:49 GMT</t>
+          <t>Fri, 13 Mar 2026 06:35:34 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNX0dRRXBCN3d1eVlMS3VENndJRUpkTDZrN1FSNTZGNzdEVzExY01DVGZUX3ZDN2JNdjg3eGJqX3ZVODBrYkEzYUxHQXRtOUtNSUJBTTZ3TFlscTVZTmtHaWp0WGJuOTFwOVBWdVB0U05pN3ptQ0xNSmdfUDZfeTQ2UDdnclhiZjBteXVzYjkxdFJoTnNORlV2UXJWaGdUbzh6MWdvaUdUNS1mSjJwZ1A2Vk1UYTVid09OcUwyS0xtSzhGX2JZZDk4eDlDYTAtUWFfZ19WV3AydWVWWGh6RmtybUtMSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPVkNIak15Ni1hWkh3cTY5R0Z3SERSYkVOQ18xT1FmbXhpVWhPY0VKSlh6QnBzVnNBcWtnTzNiUWNyRHZJNXRmVFE2ZFNEalhKcDNyWFJkZnlZMzhINV9vaENmb25yMWxGamxCMFZXMjVlVlFzN3pjbjRtT2ZDWmxpcUQ2dkpPRHdB?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>M&amp;A Discovery in the AI Era: Generative AI Communications and Outputs May Become Litigation Ammunition - Mayer Brown</t>
+          <t>Khalifa University is actively building technology capacity - University World News</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:01:50 GMT</t>
+          <t>Wed, 18 Mar 2026 07:03:10 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPYWNCSXp6RHlsQmR5c2loaTNNejVYbmxPU2piM05UQlN1akZsYzBoYWJnakFobnFaQlkxNGdWOFo5aTdfQkNodEFiLWthTlZwVUdGVmlKQ2xLVGZWSGE5Z2pRZC1ZM1N3V1NkcjZ6YXlqNDE5Sm5scDdUY2dFZFZaYWNScjVVaWNSOGp2TkY4czJabmg0Z2RSTDRsaVotWF8tdk1kWXRkcnFBa0FaNkxyYWVjVHJ5VjZNNlpHdUhVcGp6QVFiT2FWZHFzTGhTVTRNVUNNd0ZRTW4yR3FSaGlMaGQ5TkVhSUhZdy1hd01ZS1BGQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE53WHAwU2hqa292UzUwZ2RfdWlrOXVkTGZOcFVVWDZxZmxjV3lCRW1fVWcxOGI0TDRmQ1hITHJxSXBhdEl1aHc1X29FNUNaUzlwdVdEM2kwcEpTbHhza2txaTk2ckdwUHZGWFFQd0ZHa1BPOVJ0c2Zj?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>How AI can identify breast cancer 'better' than a doctor but there's a catch - Sky News</t>
+          <t>CISO Redefined: Navigating Transactions and the Cybersecurity Landscape - FTI Consulting</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 19:37:14 GMT</t>
+          <t>Tue, 17 Mar 2026 20:22:24 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPcUJEUXVrX2dRQzFGNXVIT29DOWUtTlRMRzFDYk1LRmRqUmFmQUFjMWlkcUNyOGdCaVdHRXMzMjBtQ0REc1Q1OUVfa3I0V3JrWXhXdF9XT3JpUXBoRFExQnRkdGdtLXVNQzM3bHRfdlRkb1hCRGdDaWxlZkxLR2VEa2d1dDVhd05ocENlMENtZ2Vwb0VteXhlWF8wNEI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOV3VZVFRsNzBsX2QwSXpGeGR6aXBDOW9Nb2FXaEtlbmdtV04wU29LWFFLQU92T3otbFgtRHVodktOcGU2bXNWQ3VUQzc0dFRkRHZ5Z2VmaUM2dGpUV1gtVlg1eTJrRlc5U1FBN2VsWGZUSmF0anpjOFQ4MDJrc1JxYUlHMGwyc0lmczgtQkFEbVBBTmdfN1dTRjRTUE9XRDUzdHJtZi1Wek5USjNFUVE?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>How AI is changing the game in what we know about our horses - Horse &amp; Hound</t>
+          <t>How technology supports long-term care at different stages of life - telefonica.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:25:44 GMT</t>
+          <t>Tue, 17 Mar 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE83WkM1NmloX0hmSVcxUDlMSmJKRDRsR3E5U0JwMmNjNFB2Y0dQUkNCQjdNOWxFcXQ0Vlh0QWZ0R2x3T1ZGLUJEY0JqZTh3UnpNNE4xeG1ZQTNtUzFfVnF3bzJaclVCOW1CWGQ5b2RGVjl6Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOajdmQ3FrRWRWMzg0V2xpUFZaTVJGUmc1TG5oZnRySnJuX21vVmlFYll3MHdJMldHaHJNdU91NzdUaFFSa09rTEh3a1VsaUxKblNiUzVwNVVNTlc5SFBZVmJGU0Ezc3hXcXBkMFpWODkzTTV5MUVOOGRzNkMtbzE2VXU1b244cURubjRYaDJBazB5XzBFMjRXMGsxbERocE83c01J?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ITA and Trenitalia forge partnership for AI-driven intermodal travel - Business Travel News Europe</t>
+          <t>Singapore opens new entry path in bid to lure AI and tech leaders - Pinsent Masons</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:26:44 GMT</t>
+          <t>Tue, 17 Mar 2026 12:11:39 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOSV82ZS0ybnhfdTlLdFhqWlIybGxwblFuRkUyM2JEajJuUGk2RlVLdnh4b3dpZG1XUmJScTNsY1NFb1dMX1FRMFhrQWNfdTl5Ql95UEI3QWtPVzJLT1VjQzVHdWFYQW9yYzNRMVVXWFk4S09mTUNScjJKMVA0VS0xTERpNzN5aEJEVHI3NUl0MkRIN21na18zMlg0aGFOeUZUMTlfdGI1dHMwUk1NRkhlTEZwUFRtMzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOWTFKRFc5RjNjUHRFbG50S3RwSDFHZXRCd0lnYzJVWUFndjgzb09Ua2RlREVTN1hiQm5PTW1QZ0pEOFdZUlVSTktma3A2X1FHT1hLbHctRXZmWlZhcWJIdkJHUTlMQ0lURFRkMEJrd1FXRVdnNGJEQWNyZDRzdWdqVkxTSVhUb0dtZ3JWd0dlcjFUXzVOdFVuUkJFTmhWbU0?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>America’s Endangered AI - Foreign Affairs</t>
+          <t>Rachel Reeves puts £2,500,000,000 towards AI and quantum tech in bid for growth - Metro.co.uk</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 04:00:00 GMT</t>
+          <t>Tue, 17 Mar 2026 13:47:00 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9tLTZlSWQzSEZpVkJBaUhrTHZmeXVfUXY2MW5IaDAtdVQxV0gwbkdNNTRzQ0VNckpuQTBmbDc4bFJKWVQ2NVVzbEttZlNVSHR3dEp4OEZQNWhzRHpVbTUtckVoQjFfS2JaZXJfNTBBQWhWYkFwRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNeEwxemVpR01CZVlpM1c0eS1pUFItV3BqbW9kbXNrSEZ4TE95UG1XMWNOd3BGUjhlZU5YcWdjcS1oTnVpTkVHeHBNcVNJeU5fMDVnWmFzenMzbDQyVUgxSUw2aDVJay1ZeDVoendlQ1NoUm9XbEZGVmE4OWVIbjlYcVRYZDFNa1B2OXBIUlBPUjFRZ1BLd2c2dUw1SmF0QjlCSnpqbzN4dUhabDBZ0gGyAUFVX3lxTE0tc2xITWphZkQ2N1AweGw3TG5VMFpVdmtDWTBGdFIwZ1RWdTN2UHNQd3VvaUlrQnRZTzRLa2lOamxCdk4xSEpCUkplM2Fyb3RsZWFTTm41UUNNcmtEQzFaNnBrc2lrU0pVS20xb1JiUjlmSmd6U242YzRZX2c0Vk5meXhiOHdEcnQ2N0lrQXNoREgtN1JZTkNpMVNOUE9fNWpuQzdtTTNZeVVITEN4T1JKalE?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ABB Robotics Partners with NVIDIA to Deliver Industrial-Grade Physical AI at Scale - ABB</t>
+          <t>See which jobs are most threatened by AI and who may be able to adapt - The Washington Post</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 16:29:15 GMT</t>
+          <t>Mon, 16 Mar 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE5pT2QyY2IxOUluVzMxQTREWVVxV2h4NFM5dWlwR1E5aXNjY3dIT1psMjctcVRuWHNBb3pVay1xOHcteFc1NTRnZFJVUkJvb3dyYXBJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQLW5fTVYyUm9aS2hCUXU4WGxvZXlkM1FibGRRTDFKZlJNOWJsdDlvMlBzNVRKSmtsXzEwVGFHS1k0VFNhQ0pDeS1zZ3BrcUdFYTFCNkdXVUhPY3FTNVJzZ2EyTVhPZUx3c3VOSkRGNzc1Q2oxOVR2NEFXWjRBbmZrcGVkZ0laQjl5bmFzUnYxNkx5a2ZaMzhj?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>University of Bristol lays out a case for swarm robotics - Logistics Manager</t>
+          <t>Understanding the Complexities in Managing Risk for Artificial Intelligence: The Challenges for Senior Management - Hubbis</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:37:57 GMT</t>
+          <t>Wed, 18 Mar 2026 03:35:44 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQbzFzZ1hldkFfOTRqd0lmVXJKbElCU1Znc1VtRExzS2RucE1wYjM4VGhGeWdlWWF1X25pdGxRQVFhZHFJeVMtRG50aHpheVNHb0xtUm9KMWM3aWxNcEtaRGZLYUxDeHBjbWFTRW1tVWdFWnRiMnJxQmVqNWJ5cVhSaUY2U1E2NlIzY0hvVXVmYXllVHFt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOOEZKQzlXdUxSWTJwRl9oRUFGc0ZmZk9GY3VtXzFMOS16bm1OdGFGbzhIRU9PRGxQSnVtZXhPOWFpekhvUlJ3aEw2anVKQ2JaTE9LTmREYjhnRmR3YXhETmQ2SEU2TmJFU0N1VUZQZlJ3S18xcFN6aEo1S0dqVzY4TUhvQUV6d0lQbHpGd0hYUFEtNW9sX0VXeUtoWlVfckFnREJiNnZOYUhlUDNPTlBpQ3BYRHE1b2RtRFAyUlVWeHY4Q2x2aC1EbzIxRUh3ZXFidkF2ODhrUjhQQXM?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>How are Britons using AI at work? - YouGov</t>
+          <t>Hefring and Ecomar integrate monitoring technology with electric propulsion - Smart Maritime Network</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 11:15:26 GMT</t>
+          <t>Wed, 18 Mar 2026 07:42:43 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1ZbWVkSzduZW9GRWR0R1VBVXVJalBhTDFONUNaOWU4bk5XTkhFc2hjbDB0TUw0Y3U0UW5PTUVLTExNQU5BUDlRcndKZG50UHB4cld1bDdJaWt4eUhfQkIxQTh1YVduczU1ZEp5eF9ma0oza2J2bFZIZHRDNWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQRHJ4SXNvSVhWYnJJckRoMnBHNE5XeE5ZNVJhY0dNQ0ZoYXc0WnA1S0VHa1ItN3NlcVlJMzRvc2Itb0I0UEJBSFVxejVtZkcxNzc3TFIyQ0dNeGszVzBGdnBMaDVQQVpvWk4zVE5tOC0tcjRycDhickc5WXQ5YmdxdWFIaUlRNXdmSjg1VnROaFo5a1RKWk50dm1QZUN0S2RvQk5kVGVVR2dmenFpWWpNdDJSYmZJbVdmS0dKNA?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Emerging economies and the future of global digital governance: data, AI and transnational cooperation - The International Institute for Strategic Studies</t>
+          <t>Propertymark CEO discusses market resilience, AI and the future of home moving with fellow property guru Phil Spencer - Essex-TV</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 12:19:34 GMT</t>
+          <t>Tue, 17 Mar 2026 18:09:01 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQN2szZHRZTVQwaUpKaUZ4akxDSHFDTkZQZG1teGtOV002WUdQdXF6ZHZRZ2UteG5LSlJ2T0x5bFJYNXFpNmMwOUtkUlJYd1FBd2lud0FzSkZra2tKMnhFREdYczM1OFZ2SklsMGdsRXFWcGpYX1M2UGIzclQ4ekJRdmg4VWJKNE5JZEFlODBOSE9JQUNmaHNjVWRaSWxKdXdYOGVmeFVmVEdsMzRhaTJFUHlJbHZmSS1PUTNjRE93bDlqQk5KbnB4NUp1ZUpSSWlBZVNmd0laT2UybU0yMVlSS3hHYzNjN0MtclNPenN2UVVvYU5C?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNV1dLSXBrS0dXdzNsSmF5c2xKZjFRUkNTOU5NMFBHQ2Q5UGxpTjBTOGFZWTlveFdsaEJhZXN6Qk1ycnR4ZlB5SldHNnhiNFBPNlR0VFdoaFVPTHBMRTB0ZjA1c2VQM0FxMG1qVUlnY1lpc0Z0QW1lY0VwUkd1RnE1NkU2M044d3BsTE1rbWdwNGdOUXpiZGZJYnI3QkhCYzB5Sk1MSnJIMlFxREtoSU9zcGNZVWVxYjlHMTd5UzhQaGY3Q19hMGk5elphN3lTbzJNXzMxRHVzWQ?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bridge the Gap from Design to Production with Manufacturing Engineering - Dassault Systèmes</t>
+          <t>Vera CPU by NVIDIA accelerates large-scale AI workloads - Digital Watch Observatory</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:48:11 GMT</t>
+          <t>Wed, 18 Mar 2026 07:26:00 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE15Sl9vZktJTEZDbjV5RWZVcVNSR1pGLWhSd0REUUY1TnVpdTdrU2ZBcVVFNHJYVktxTUlMX09vZ1BzblphbUhqUGR5SjJBMDFTZm10TlVvV2tMalRJbk5aRlJ1MDU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1tMnZxaHI3N1k0bElEN2JyT2hfOGJuV0djLU1IakNkY1lIdzBCdG9fS3h6cG9XenNId2FJV2hkNUkyTF85aEF6YzFNQWQzM1VnNVRwQ0FabERsbXYxSVBvLXdmTGptTVowZVpQS2x1ZDNRMnBx?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Generative AI changes how employees spend their time - MIT Sloan</t>
+          <t>[Interview] Growth Through HVAC: Samsung Leads the Market With AI and Hyperconnected Solutions - samsung.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:22:00 GMT</t>
+          <t>Wed, 18 Mar 2026 02:02:38 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMGpXSWd4X1QxV1BJMGlaUEpFa2FyZThPOGxTN0w1QjJrWFZvSGpfUndIc2d0WWRjeUgxQ2taSDVLWkRyOVlfdWtHVFhZSl9CV3pPTmd5M2F1cUV3SzRBWlpuYy10UEVlNXJXamx0TTJqN0pOMkpBUVF6RUhjQWNSQ29uemNvVGdQYUY5THV2UWJlelNHSDVRblZmRWhiSlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOOUdxRmxleFp0ZXBvUjV5ZnpCYmxRY1B1LXVJWnFwWlpPOWFzMzdOczJRWGQ1ejd6R2ZsZmVmVmpkdXRzRmRTeWFyR29CLXVZSWtVZWdxdWk1UE05cTVud0lLc3Jtc29DZWc0RkVnZnVUQUlDREdzNHkxbjIteUw0QWxWYnRIY00zQTFZOExnLUd4SHBkb1VGY2tPZ0E1Z1lXNERHckJLNHhxU1FsZUE4R04xWEYzZnBmQ2Jz?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Precisely and Matillion Partner to Accelerate Data Modernization and Agentic AI Readiness | Corporate - EQS News</t>
+          <t>Debt investors offloading exposure to software companies is latest sign of pain - Reuters</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 13:10:27 GMT</t>
+          <t>Tue, 17 Mar 2026 14:42:07 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSUV5bkpkcnp2VmZIaFpBeGVDY2lBTDJaM1VzYXBBNDd2NkxteERNMnpUTXZzRU9uQ0Y5SGJsRUFQZGYzbTcwVEdpVXlYa2dYVGw4clk2d1ZsalgwRVJNMlVQRTJkYnBHSW9jOTNMam1kRkNKUjdIMERCd3pNbkpkTGk3bWZOcVFBWjQ2TUZtLXhoQUNLYndldDVxSFRHZnpIbG1BWXYxYlF5UUNJSElYdHBBMG1xOVFjWER5cU5ZVXdCM0tQQzBnRWNEcS10R1VoYk5sTUIzTG44dmZmaGdSUDhaQ2pDOUhvYXAtNXFiQWd6eUZ3dEp4Zkd1bjd3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQeHV5SWNHd2hFUHd2NDlVZzZrUTlCZ3BuTGUwUFFXaGhfcGo2QmtFbXlWQ3djaGl5UkZOOThpNkJfWldMVTZHWldrTG9CR05HTEJWQW5YOHpyOWl1V29lQkpWWm1JTmFzX24ta1p5enBmMG9EQ2VTdlZWMVM5RW1SUF9PbVdBc1RfV2VoNVBDc25qZUlmUm1BUm1sbFhIaEhPVk1Eakx2Uy1YSndqOW52anp4dFVWaFFDZGlrSDlyaVNQVVo0?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>To What End? When Technology and Media Seduce Politicians Into Taking Military Action - Small Wars Journal</t>
+          <t>EU delays tech sovereignty package with AI and Chips Act 2 - Digital Watch Observatory</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 13:22:57 GMT</t>
+          <t>Tue, 17 Mar 2026 12:27:57 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPVk12Qnl1WERCdzA1WVVIUFZaSWZiTkZ3em1VRnVWUzI2OUVkMzdxcjNhUlV3bHdVaWh4NlRnY3E0ZUVhN1hlWUd6TGhRV1hqcE1VUHU5ZGF6TmRmMElySjhuMGViVldHc1V1YzlnTzlrN0JHcDd3UGVUYndJd01IVm5oaFlJb0RESXh5bm94TmRybWtTWWJmMmFQaDhhQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1RbzRGTGRJZ1JyRlRrdTliLWlRVEFHZGdvOEhrRENJVGN2QnlXWDh6S1dFb0pobkFQVFBKcjRvX2VpQnZVeGtrc2ZBbXF5NW5YR3h6ZF9YYzRMU25fUy1SUg?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>The Quiet Transformations: How AI Is Rewriting the Logic of Progress - Allianz.com</t>
+          <t>Microsoft considers legal action over $50 billion Amazon-OpenAI cloud deal, FT reports - Reuters</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 08:42:05 GMT</t>
+          <t>Wed, 18 Mar 2026 05:07:00 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQUmJIdkV4aUhxQWJ6eUt0bWxhRF93WlY3RHJsZnpxR2pJQlJVSTd3U0xrOWY3bXFhYW5SNFcxTWtNbHVJZWJkUTNhUjM3MzV6bGRJWWFoLWp5UWFfcHNTTDJWQzAwSkZJa0NXVGhqMTJQa2NHeXlSdXd2eEphdDBwTXBGWFBGU2ZnTE9kV3BCck5uRmdncVBIbU5rLWt1eDlsS1l4WHU1XzViN0JVSnhtTjk4RDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNVFQ4bDFHenlqSFctZWJoMVFBeG54NGlPeXdpNkNGbHVfLXRiLV9VQ0RjMWozRTZWbDBwemoxN0FoUEtJdVF6WkZidDlZQlc5c05Ba09RN2o2U2taejRSMk9NcGc5enVkZGpZU2cyalBrRjJNMTdmSVpRdF96dXRjTkxLbDhHOFFpalVoYUp0LWJtdGE1bnhvcUhQa2g3TVdFWVlRam8zcE5aNS1MTy1vbUhRV1pXQzlDcWFLLQ?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Has AI Ended Thought Leadership? - Harvard Business Review</t>
+          <t>Kering Taps Former Auto Exec as Chief Digital, AI and IT Officer - WWD</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 12:18:53 GMT</t>
+          <t>Tue, 17 Mar 2026 17:33:34 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE84bkJtenp6SDNsY0x0WVhQNFlERW9VLVJsUUdxQ2FsWW9RRzV5TWxqdU5ZZ19Sa2tDdHVYeVBWemJMS3p0VGpVVGZZMTA1THFNeE9hVXduZ0dJaFF5LTRtTUI1YXJhUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOelVFMVR3QXdKTW83LV94MVhuQ0lPR2ZiNnZtVWFmdElSSEptd2Z5OWR4QzBmcC01Vm5ENFdYSl9xcGtQRll1V2FUbDY4Wkp4YWRFdXV5R1hremdDUWFYX2NLT1dBbjVHeHl2bGs5YTlvMVJSZ0hxck5EdjREVUNUaXJtVE9hUHkwQlg1c3Vsbkc0eXJ2eUNmcGZPNGxkRG1VS1NxUnY4bXhJUQ?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Furniture.com was built for SEO. Now it’s trying to crack AI search - Modern Retail</t>
+          <t>Tim Cook talks Apple's 50th anniversary, future of AI and privacy - Good Morning America</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 05:38:13 GMT</t>
+          <t>Tue, 17 Mar 2026 13:58:41 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQNEFYSWhHZnZkZGpXUFJfNHdWZUNvdmMwSjNqS09FeWl2YTk0dzdqTXhxVEVPZ3FNQVp5cXlWX0dZY3VTR1JfOEdoMlJBcWdWZklCQjRqLUFmYVVvUFN5MkJOLWowV3QyLUlQZnZfaDZGT0VIeHFDS0FkbVJTWWwzZ1RudHRvZnZSWUl4Q2V4TjE2M2ZuT3kwZjhtTk9BSmtNSW56NUJFSG0zRHNva0U4VVh4QmtfMFJXaUlRX21OTDhkMjByTmNNWW1ad1lXcTU1Rjh3ZjZFT29fTE1GUnFmaXhBZTlKT19jQVpfWVVBQ2NzMWkxNEM0dTBrYnh2c1lhSlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOXzhGYjlENkhCbFZ5ZE12aFJCRWtUb2g1TnZ3VW1Yd0FidjVsbGQ4Z2FKaGJoMnFjWDRjNEtrX3VOVTEtMW9salNHdWZGWHNYWlJlYjE2V1BaSUxGUW5lTDVHRGdWLWUtajNxS2YxbzJyYk1wbnJmRTUwbnpzUHhta3hhSWdBQ3c0VHZoMXo2aWE0a0t0SmJDT2FOXy1udE9pTnU0bVJGU1RmUmfSAbABQVVfeXFMUEFqdmwtWjFUdGRicUMtRHA1WEtnZzRBdG13c3Z4SmNQQWpac29oRnRIUXU2RktfdEVkM1hxU0VBSk5xYk5nUFZtYy1tX09ocDIzaGNINXVxelNiazh0WVprc3l1MDB6a3dvSlo2Q1hVR2cwU1NJcHN2MGlLaDltaV9RbVlncU0yNDI5cVJ6NzR4NkZhS0lWU1AyY28tc1c5bk1yREktUmgxQm52NXlqTlU?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>How AI firm Anthropic wound up in the Pentagon’s crosshairs - The Guardian</t>
+          <t>Elevate Quantum And Partners Launch Nation’s First Quantum Open Architecture System in Record Time - The Quantum Insider</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 11:02:00 GMT</t>
+          <t>Tue, 17 Mar 2026 07:08:23 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOLXdKSXF4WFl2cGEyR1lrTTBLNXVwNE53WEFBdFhDLUtQUUhFdmxtZ2xYT3lpVmJmbXN1T3JjRDV1WHJFakZvUFlFVnpTTWZNUDJBRDB3VmZta1NMWjVTdmJza1NiMWNob1VVNmJwc3VUZjNWZFdBQnNvYlotNHFVWW8wb0VFdlFXOW1kWFl6NW1JUFIxNF9UNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNVFJ4OC1aVXp2RVNKLWFoOEdINzdzcnlSODlPNWozb053NkJCR0I3YXZhdHBoRzZfeEdwd0J2T19ndS1BSHNxR1N4aXZISVp4eldfU1lsZFhSalFwcmROQm1ONUlNVWFsVEh2dUdPZTlJTnhHTzYxMFItTGFXYWN1LWVqTm5ZX0JQNm93b2lLRVl2UGZZMUZLNF8zN1NXNFYyZ1dxOVV4Q1AyamZxU1RDYVhQYk9SdFF6WmJCZUtmTDl4bXZoNW9lblNoSFZTVDNHRnBDMDJR?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Man sentenced for assaulting police officer and theft - westmercia.police.uk</t>
+          <t>Three men convicted following robbery of mobile phones in Sittingbourne - Kent Police</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 11:26:00 GMT</t>
+          <t>Wed, 11 Mar 2026 14:15:00 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNMGQ1VzVHSVhZNjR5VXVtMVZpWFpuSFR6a0dBWG5GeFdLZWhxQ1phSDVUR3hiMmxWQTRmN0RoVExuOEFiNEtVdzRKNDdRazlaVzF5WTM4cndaaDR1cmRucTFLd0ZEbUR1VGdQRWRiSzFpTEZnSTBfcVM1NlBoVkJjVHpHcTh2NFhaNFpaUEVubDNpZ0ktNGhQRW1ranJtTW1oUmZIWVVKZTVsbVdYaXlWY1VWel9mUjVOV1NoUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNUEFQNjhaYW03S3hqNF85MTRPWlJteEdaTmxmOG1fRDY5Z2FBZFF1bjFfS2ZuVGxzaDhsRnlwNlh0SGdWclE2RURHWjZCRDQ1QlpQOWxOTVdaZ2ZlMWxSekFRV3h2SEFGWHQySTRZZWhhTDVRa3ZCWHVsZEd2NnhxMXNyT1lQZ0M1NUJKcGJLLUI2NE5UeUphRDV1QXJ6MzFrSUZkeXRVUlpNX0VMdkVnakZDTFBIcHZ2N2M3QXl0UXpwWk0wSkRBYVh3?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Royal Albert Hall worker stole £40k of equipment - BBC</t>
+          <t>'I was pursued for fraud for having two council jobs at once' - BBC</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 14:48:42 GMT</t>
+          <t>Thu, 12 Mar 2026 05:55:27 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBfNlZBWGRQWVZmRkFSTjg2b2ZFdWtDZXByVE13bW5xa1JPc2ItcDA1VHNsTkdPNERVcF9NUVR0cXktZmtNZHdzbDBWLWRTLWRWOTk4czR4SkRHY0Nm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9uN2tBVGJ5b2YxakV5SVo1aDhHQld6eXhPd0xWUmNBTU10Q09ydFNTSGllc2lvaTZZMWY1UW5KTEJwV2FqZGF0NWJVZ3h1OVpsaG5WdkdvZld0NFVV?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4121,17 +4121,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ex-Employee Sentenced to 2.5 Years for Stealing Ship Part Blueprints - MSN</t>
+          <t>Man jailed for shoplifting and abusing staff in Aldershot | News - Greatest Hits Radio (Surrey &amp; East Hampshire) - Rayo</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 01:23:10 GMT</t>
+          <t>Mon, 16 Mar 2026 12:53:33 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwJBVV95cUxNU0pKSVpVTWZDRTM1S2ZyWWcyUGpCVm1yV1FXYXQtcVdBRnJvbVdxajZIaDJXQ0hJRXRjY3NON3l6Z2g3eEYta0tJUGdQeE16U2MxcHhQM2ZraVg1ai1mZUpwcWNlaHRRdzY3UWxvWmxUZ0lLdDZRNUxoSGJUdVlEZFRKcFkwajJtdGJrQXhXeWw1bDVGTDhTMnNSSHNMSVhWd1JIR3RXWnlTcWRYeEJ6TVFzNmZzVkhhRFJBbkdhTVNJSGFkeF8telBfaDJZaDNQdlN5Y2dvTU5sRG1WYUJmSXlmc0ljYnFhM19BTEJqVnl2c0d2cVJFSmtqblpnU29JajRIQTJkOUFQcGRueXFiRG9obm5TTVhLVE95Um94ZnNiY1RVdG9VMjE5TFBfYkpQdzh6WTZoMUVqdlJKYVN6VWhGOGJiNGdIOFFjMFZ5bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNWWh1YVNDUW1NVmVaZThxdDBjbE93cUFNUzREQWdhU2xMSGRXd0NHWURDVEtpZ0N5TXZpU0ljOGprN2VuUExscG9mdGNrN1pKclo5WDNXWUVyUGdIYlFwSnQzY1Jzc2pBWGYwRmp4RGRsSVRFSUdTNXE3b0pBZFNlOV9ta3RuLU1rekhxVmJPRFFidFRNM0tQSktfQzBUR2toOFNsZ1dJNWdSdm45VGpDX0g2dmNSdEVWcGVEM2s3ZEpaZw?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Court sentences former BEB employee to probation for $700,000 fraud - UA.NEWS</t>
+          <t>Congleton man sentenced for theft after repeatedly stealing from the same store - Cheshire's Silk 106.9</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 10:58:36 GMT</t>
+          <t>Tue, 17 Mar 2026 22:35:13 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOS1llU0tCNWc1OXRDTHVEZkwtLUJrTjJLbW4wZm1ydFlYWTFpTXpDNnYwTl9BUU5NdmtwM2hrbEgzRWNCSlhlS0dubVhUVlp3RmVEdmRNNVRlUGFyTmJzVXpVamZ2Wm84akV2TmdncENnUzhmbHpHYzRaNTRMZ1dSR0VHc2c3NXdkQkpZM2s0R0s0SmhEajRpOW1YRjAycDE2RlJZRHJSZzY3dE0x?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNdFFUY0k4WUlzVkpQXzFVU1B5aUVNV0pjODZmMlNSSzU4b1JzN1RDWjBQM0FnXy13SzloSjNBN1FHWGk5WV94NDBEVWVpNk5UUGNTNlFqdTF0MUpkZnZmODliem1BUHB2b1lWM1I1elNXQWFNc3VaRTNVQzl1d3RNVm0wUUdoSzJVdjFTNmNxYlRIT1dpOVo0S2RfbVF4MWtkaDlQMG5oeHlLNFFSR2ZBZXVVSHJaUlVIdm0xdld3?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Former Lee Health employee gets jail after theft of heart monitors - The News-Press</t>
+          <t>A former Royal Albert Hall worker is convicted of stealing audio equipment worth more than 40.000 pounds - Digital AV Magazine</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 15:08:00 GMT</t>
+          <t>Mon, 16 Mar 2026 11:18:31 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNREtNYmpjNkxoMmJiNEJXUlBtUldJYlRNNDJVbzVjVTVXRGNrT1FEek9qVl9PRXFuTjBVcHh4X2V5OVlmQnB6bVdtVXRTYkVKV2E4OEN2LTJpbU0tcFA3c1JtTXFuYXc2dWhDc0ZtX1NVRlprQzdvV1hkNkEySlQxVGNyc1Q3andDVDREQVkxS0xiUGcwVGhJb0NDdXVPVlpiendRSmFBMnplT2lLSHlOWHAyODVvalUzVGZmemg0SFA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOUHdkMnJSNDZqQW8xRm5Ha2hmeVFuN3RvZ1pwczBoUjlTZDNfY0Z6R3cxNHNuMlRUeVRxQzBlLXVuNWdXQVkxa29zWldpblBFN0t2SDhkVjg3TXRIRWxKZDdOSkpUUl8xMWQyek8yY3JESk05bzU5M0hOTzdwYVpGRl9iQ1E0Tml5VFJrVDZjTTBwNTBKTWNFMUNDSWRsTzY4STdhRmJoa25vSTNHTW9r?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Board of Dentistry denies reinstatement for VB dentist convicted of opioid fraud - WTKR</t>
+          <t>'Prolific' shoplifter who assaulted worker at Co-op in Reading jailed - Reading Chronicle</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 12:03:14 GMT</t>
+          <t>Fri, 13 Mar 2026 16:36:52 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxORk5ObTc5VVhhc1VsTmNCMzBzWW4tcmRidThUTmllamFUenhmV1N5UzA1SkdTUHZrOHdUbkEtUl9zOGltWnVQOF9uUkwwWXFYR3lJOV9ham5HN0E1bk02Y2VoSnBXSDFlT1k2YzdSUUJteTB4RlBOVDFsTHFLS2lQUWtZSjlYMXpmcmNKOVlrR2NOc1lkMUdURzZpVEJ2cnktbmw3WkdDWjZyTjdIeENWSWVVZkU3bXlEY2MzeGx3a3ZnWEVoOU1BNVJqUk5MTHdXSWswdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxONXZ1djUxdTliQ1RPM0hYeFhTTHRFR2dtNFVCbE9ackgwSUlzd0EwdmtMQmwxTXVNanNaVkMtMF9vNDRhOXNjZGVIUlFHS3hzWDc1czJST1EtX2hqOS1haFZSMGUzeU5XUFdQNk9rSlo2b0thQVpUNThWZXhoM1pQT2liaW1HSzVKeWFSUWNWbGdiUDZWVUxVNVZxWGpKdm8?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Trump pardons wipe nearly $2 billion in victim repayment and taxpayer recovery for Medicare and tax fraud, and more - California State Portal | CA.gov</t>
+          <t>Hunt for two convicted Londoners after over £50,000 worth of phones stolen from shop - Yahoo News UK</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 16:01:12 GMT</t>
+          <t>Wed, 11 Mar 2026 14:44:23 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9NYjhGMmZIbkdOaEYxejBmN2VaME1jUVBxODlLZkVkbExkU29HR21adzdNMWZlbTFWc3FyMlI5SnJIYlQ1eHF3ZFBqdXJGN3NobDczU3drcHdlNFZXREsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE40Sk1hTGlTQTZDTUQtcDhncVpKVWl2Z0RQWVE4Qm1EbGswUW9UMnFRR0NvaE9RSGpxS3FTVENVaGhIQ2R0UGc4R05WZTNURnUyWTVRSEFFMjduS2hJeUZEelp0S183bk4tN29waFNBeTJSU0xuaUcyS2ZWSHNNeVk?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Akron man sentenced to prison for rape of hotel worker - Cleveland.com</t>
+          <t>Logistics Employee Sentenced for Stealing 120 Million Won in Electronics - 조선일보</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 02:36:00 GMT</t>
+          <t>Sun, 15 Mar 2026 06:36:59 GMT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOQXVIbUhURUNsTlhXMFVIV2NiOThPZTNhY3pvV3dnTURNdzhnUGVWVjRGMTFQR3R3MWdpM1lrYkg5SHlPWjBEYXZRelN5ckpUYVdLRDhYRU5FakJSc1I3ZkNsSURHam92STcxSjJoaTFiNzVwWkhnMW5DdEZuR0lKR3JTZXlSY0lqSEluTkhjeDNKdjNzWW9acnp6Vkh0d0hxbHA3ZDhvc05hOFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQTks4Znd0TE5tX0JBcnNJbmVTYjY2NG01UVhma29KT09VTFJXNWZvNm4tUzlzMmRJUkxrQ21BbFZQLUx0YnpvVTNsWGJIUmlUNXljNDRkRnVIel84V1UtWjFRbUFvVXRjc3RWWm1jcVN6XzJlN3h6Sm5JU1gtSmpRNTd0RWFiYmxh?oc=5</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Former IRS employee from Mass. gets prison time for tax fraud and Social Security fraud - Boston 25 News</t>
+          <t>Couple who stole disabled NC Chick-fil-A worker’s phone sentenced after his death - Charlotte Observer</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sat, 07 Mar 2026 01:35:00 GMT</t>
+          <t>Thu, 12 Mar 2026 21:43:00 GMT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxObF9sOEZKWGI2WHNKTWRqMWlFSVJBdVlpWnpPN1JUUE51SXhHN3RsZXlCV2JOaEgzcWJ1djZTNDNrbXZqeElhZnBIbmZrSjNfWW51dU5kMUl2RENfTFFDbnZ6SXlJVXU2dDZzUnBGZGRTQXNrNDNkby1MWmRnMU1nb2dtd1lNYXVjcmF4SGNNZFBGbThzM0E1cG9oWVJodjBsRVl3ZWZnRXg1YThOZm9DUWFtdWYtZFY0aWp1TURmVmxSallMY2NiUnVtdTZ3WG1aWkHSAeYBQVVfeXFMTmJmTWhZdEhVQXVsMlU4aFhtaDkwNHVGOW1nbFFzWXp2QzdfYWVvcmctVUx2eFF5TElTcF80TFlQYV91aXNCWERXSmlkVEItaEZlb1hFVl9ZNjdDWEJEcXJlMGk5VVkzZGhsVjVuUzlfZV9nVmVoQTZ2RGZYbnNCdjItSnJYNUJPc0pleDZUWWJlS1QwUjRRVml6bVAySUt2dUpqSGNDZXRfLXpQWXljNjNvbzJTSGFVZC1IQU42MzhxZlN3SldIRUhNY01DWlUzNmU3TzFPOTdKbTdRV0NoczVmazlpY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE0wOG90Q2tFdTdRYXhnaFFRZE56Qy1GcTZzeEYzVlVnRkNUM0x1OTZXM1djSTExWTFhdU9LQ3A0dzg5Qm15TUxXcXg1dnZaZHdtZVRYN1Jycy14OTBldE5uNXBYdUUxOTI3WGZMSElad3ZlR0hmRHlDR2luelDSAXxBVV95cUxPWkk0NjcxaEZGbl9ob0pOT2lyWmNheTVCQ3NTZ0FTd3ZzdTYyZEJRZGk0anRpSDVvVjk1c2ptY1YzUXBZTF9tSmdVcWY3dm9rNVplQjQya3cxaHVDWE9CYjlndk5tNWkydHBnWVVfODZLaUNDTlhhblFxcDFz?oc=5</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fake invoices and personas: Liv Eat contractor sentenced for $65,000 fraud - The Advocate | Burnie, TAS</t>
+          <t>Stellenbosch law firm employee gets seven years for R13 million fraud - IOL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 05:37:26 GMT</t>
+          <t>Sun, 15 Mar 2026 15:27:29 GMT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQLV9HUENOWDdYQmxRZU9rd0ZNM3VMS01LaEUxSkNmdk1feVh6S3pRSThCX3M0Wk9wcWd6WW90azE5RUFGdEpCMnFGNXJJNDhHMGFTblRpRDZOTGhWMmtPbkRtcGV0T0Y0S3lveHlYOUZDUmNhOXFBbko5aGZKaXhrUVY3THRTSmVwcTg3LXlfY09VSzY3YzdZV2MwZVZGcWlXbTB0R3lIS0Z4SDlxYXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNRHE4R2pGdmpjM2dKUDlpSjZHLTdDdUZ2Z0NKdjl1RTBfVHNfVHRadE03ZzQ4akxYNDRPdEJhOVBwZldwR2NWNzBnNzljVWU4cmg5M1lpb19vR1hDRTc5SGVfMEs5VVh5QmxHXzNJZEZsRnJWOEFOb1VLbDB2amQyZFVqZmlUQVg3ZkIzeWxjSEhrYnk0Yk4zc1Jla3pSaFRsekRab2YyUjJhREl1Q0xGNGFYT2V6dzBfRFVvRHRB?oc=5</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pennsylvania man convicted of fraud for voting twice for President Donald Trump in 2020 election - 6abc Philadelphia</t>
+          <t>Dental employee gets 4 years in prison - DrBicuspid.com</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 11:57:27 GMT</t>
+          <t>Thu, 12 Mar 2026 06:05:30 GMT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5LanRvaTlGYmF6YW96OGNhbGhNQzZvd0d4bVU0SUMzU1JkMlRjQUdra2RhMEpHSFBGQWo3bWJETDNfcjJIQU9DdkpabHBZVFBoUXYzRFd0S0xUWkJCZHBIUUgtVjlRcWs3SW1WYdIBckFVX3lxTE5NekxaMG5KMlREWEpDY2wwN0I2dzdrLWRkbVZXa2pUQnZxazNRNXc3NmxpbkFmSnZCb2ZsRnp3VWItMTRkc2xpS2k4YnpEVW00TXh4VkQxZVRJUnh6TUlienBtaHBvYkNvVFpIQy1iX21NUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdnF4MzV2ODNETWEwcV9vZjFrUURnM1Y0Yy00LUJQVmdWQnZOU001b0Y4eDV1ZWwzYnN4ZFBpWTVQelJncldlZDlKOFdfVmEyZ1ZMdlQ3cDdiU2ZlMlFua3Rsai1VR0NSQ3BDLWRkV1FLV2RMUlU2T01YbGdyNTZBNmVkR2ZhOHE1OTZCUUQxbDVuSmZhRFl1VVU2eFJ4VUNhY0dWdkRjV3lPWGNFSnYtYg?oc=5</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DOJ: Former CFO sentenced to two years in prison for $35 million theft from start-up tech firm - KIRO 7 News Seattle</t>
+          <t>Elkins doctor sentenced for nearly $2.5M in tax fraud stolen from employee payroll - WDTV 5</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 16:21:23 GMT</t>
+          <t>Tue, 17 Mar 2026 18:02:00 GMT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQTm1JT1I3cVNvdmg5YUsyMVJXODFrd0Fnb01JQ1hRR0xtSUZUTTdDVDRZUUswMjlZMENYVTZoU2Z5dFM4RC1mazVlSklkbjFPUUlrVkZDcmhMQ0ZyRTNYVXBRWXJCRkNzQlNGNDZ0VFlESXJQeWd0aGlXdzZ0OGk3cHd1ZUgyb09nTkJFUzM1bzlFWjBtNzhlYmJSU3E2OW5NbTB0YzlTZFVPZDh1Tmh5R0Fnc0NVeVFsMlNPeUtib29QOTRlSWZpNGhaRmJFWUcyamlHetIB6AFBVV95cUxQVlljVkQtOVhGUW9Sc3ZULWZsQUhMRkN1ODZtempLSFMyM2hhczJZZjh4NmdHVHdvdlZPNjJCZnFSeFFSbXkzd3QzenFuazJMODBpeG1VN0JtaUJrSmdEWklDZHNXanp4bGZudGN5dFRyNnpBanJBRXZEelBUTDR3RmFha1Jlb1RJVjlJbnJ4eGVZYVVCTlYxMnd6QTJLbzlxSUFQVktzUWFQR3ZINldvb2k3TDE0SlZ1RklzX2JGekoyYjJ0ekpCNjRkSXVZMWVxZVFoSmEtYnEtN3p0VWtnbG5wU0hVTDI0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQcW9SbHpqc1RHbnZqbXhzUWtYcmxKQkJEX2hPYURqa0hKajFnc1hxUElsNXA3N2VWZm41UXVYNzl0RzU4VmRpbGVTa29MTmlock13UEdWZ3FXRDBtVXRZUXhmQlB4ZVhpYlVZa0duRTZqLUg5TGRRMXZfVDVqZ2s5OF9WTdIBlwFBVV95cUxNVEJsaF8ydDFlYS1TR250TGt2QV9scVNDaG5tazRnVjg1bndWUE5OSElLQ2RfMU1IelpBV3FTQW5KU2ZpUHg2M2twSE1ITVVoRjRET3EzMjQ2dzhtWm5xZUFsbkRvQXFKRGEtTVpNNzNVNUU4ODVsOUF6bmQ1UGVMSUotVXFZQno5T2pLMHRXMmFwalBxTnNB?oc=5</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -4421,17 +4421,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Construction worker handed suspended sentence for violent theft - MaltaToday</t>
+          <t>Two Indian-origin brothers convicted for healthcare, visa fraud in US - Scroll.in</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 15:00:00 GMT</t>
+          <t>Tue, 17 Mar 2026 07:07:00 GMT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNOVItNEtKUWdOSnIzWXB3REtGWUJsUkZGOVJJUE1yTVBjaDhfbjNkcy05MXAyOGVJRWN6aDdkV1R3UU9GaWp0WVpBLU02elR2RVhuMnJGWHk0aE80UHYzZUdWNDV2VGZfT1FVUkxoblFtdFRoRDlLR3FTYkNDZ1NHOXhVcGJYMHR5UXJhU1dkeVdQcU9helZYaUJBTFJfbmU4ZWJpWlM5X2RSTzlMblF6ckZPNWNGbkZDaXN5WFBFWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNSk5MdkltNHFoNGZ3MFpoU1ZCVnVIYjlIRnNzSXA4QlhvWjZYeGJkSjZMX3BDS0lXRVFvTmZpVXJMY0U1aVY1R3hobk94S1FFSktRcXBsZThDeTRTUkJxQ1I4WnhNaWYzYXM0UTlDeXExUXVFRFIxWEtER0JuMXpRYTZFMTRNem5sREczRXpETlFBeE9QYmcwNlBWWkxHX2hBc2s40gGoAUFVX3lxTE5yYWhIcTRuWURkSjlHejB3aVY2blVJYnRwTDNzbGpIV3prY0dISTE1Y1VaOFVvZkRLN0QtTzVjamJiRFluaXlhdl9IZVl6UU40Y2VaQTNKckdhSnhBUzFmNjNFY2lwRDFDT0Y5MElhelJsaUNSWXlGT0lINDJyaW10SklSbDdRZFVHdFhnOG1mUXpZdGxjazVRNm5SaGlabTl0bkZZTkRzVw?oc=5</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Former Springfield postal worker sentenced for after-hours post office burglary, mail theft - KY3</t>
+          <t>Ex-Home Depot worker from Covington gets prison in $4M gift card scam - AOL.com</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 19:09:00 GMT</t>
+          <t>Thu, 12 Mar 2026 22:50:05 GMT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPVmFSWUhBbWJyWk9xWUZReW4yN2hBSVR4c3VlM1B2c2dBNUdreU94dF94TDhBR2p3NmllRGh0S0NXM3ZmY1M3a3laMmpLS0pObG91NG13Q0dQSEVWcDNzUVQ2ZlZBcDB5MTlwbW5fTExlSnp3UVotY081REtkNmVBTUtMSEdKZlVHZndqelpwZ1ZsU2FvZEpsakc4ZXdoT0k5MV9NYnUzRUZNQTlzanZia2tKbGNYVS01V2fSAc4BQVVfeXFMTXpzOHBwWFJVTU13M3lScG1sbVpuQkU4dkZqMEJBRDZkZTNyUFY5a0JQT2RpUTd4TnJSRmdJeVRqWV9kYXI1ZnRhVTItNTZjTC1KUVhGY3FYNENEV0ZzRE1sQXEzMUZPUldndHBYMmVkOHp5U1JSZXk5LWYtWEJpdTlaN0U3OXl3VHBJVmlmZ3l3OGNyUXg2bW4zYTJsWTB1dmRMYTRSTmFrV3cxTDRQV0lrQXZIYzR4U1VoTkhRY2hiT05pYVhQcmtXczJSNnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE0zeXYwaG5KaC1JcEVjTmVreHdwWWRBS2E1ZXR3Nk1GdF9SUFRSSDIzV1ozY3JaeGVUVWtNcDVpdXpZSVBnMGFNLWxoRXQ1WFMzbHg0XzNubmJoS0VSUS01V3Nyd3hrY29xdE1DdnlKYmJwOTNMbFI4RDNHZWJRSTg?oc=5</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Man convicted of assaulting Norfolk hospital staff - norfolkneradio.com</t>
+          <t>Tenant Sentenced to 22 Months in Prison for Stealing $65K From Units at Sandy, OR, Self-Storage Facility - Inside Self-Storage</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sat, 07 Mar 2026 15:38:00 GMT</t>
+          <t>Mon, 16 Mar 2026 22:34:22 GMT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQYnp5QWx3MmJXN24xc1l3cDQxcEV0MkVtMktiRnNUNk1Jd3luUVVBck1KaUJGNkJRMmNaakhNbTM2MVJMUC1yN1VHUDFXWUxIRGw5Mkpma3l2dXNDTVgzN1NMeU0yaE5pVGtkMmdkZlZnWmU4NVpNbVNTdmwtcFNzaEZSSnNFd2RFcXhBcmZTZVFHQ3h1bkYtQkFlT2UtM1BUSDVzSGFTby1EUVpScEdhV2dIc0c1aFUzb2o2SjNjZzJwT2dqbldiMEpaN0hsYldSVVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOaWJjQlhnRnY3QkJ5dHNGcnRoamRDZUo4WmVORkpkWll0a1puVlRfWklnTEhsUzBRUVlrSVJkVHZOMWtQMURWUTlhS1otd25pNHlCYmxtekZVcU9wa0EzSWZBQThrSW9BbVpEeVBqNmJNbUkydVNqNEtWanl0SEFBQzE3aDdpdXFsbUZVdFVGYl9Na2Q3bnVFdGFfbEdVQWN1bnRNRkd5cjFxa0xYUFBWY3Z1TmEta05PUlN6aElUbGNvME00Q2sxbzVTMkFOX0tGeXZZWGFfb3RkaWd4TUlMSXFUOVRYNk1jVVJiSDNyWTlQUnRS?oc=5</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Former Costa Mesa postal supervisor sentenced to year in home confinement for thefts of checks, money orders - Los Angeles Times</t>
+          <t>Swoyersville woman sentenced for theft from credit union - Times Leader</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 18:08:31 GMT</t>
+          <t>Tue, 17 Mar 2026 19:31:00 GMT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdldIbzNPMXhsY19hZzFaZlYxOFpPZ3hPZGE1Wmx0bm9uRHBsUmxKYmlDWlFFbW1qQVhNWk5UMHNpNTNER2pybXBLV2Q1VkxxWUVYZ2NvcThKU3pZOTU1YWZaY3BnbUZ0azJPU2Z5VU5ocDBGdzNRWnk1SGJrdUhIejR5MkdmcnZ4dnZPYV9GVXV6WXRRUFFKaDFrZDdQb3pha0gzaU9mVXQ4T09YNVM5NnNKT2o4dmt2eUJBUDRqa2FvU3JzQUYxSjg1b2lmcC1Hd01r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOUHg3bXQxZ3FvT1hOU3pwOFp1SlM2V1N6UG9ITTBkdGFJSXdIZGZtcE9Bb0FyVTJwSEVnYlJWamtVdlpTemsySk82UTFiMl91Rl9sYkJwNzJORElCdzRxSmMzQ3g4dzJ5VWxzS0dWSGp6S2VkTkM0SzdDaUtyb3FLbzdneWFJNWVKYWFNdHdJT3NnQTZ1QXloMTZCMG1MZw?oc=5</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Motorola rival ordered to pay $50M fine for stealing trade secrets - Crain's Chicago Business</t>
+          <t>Local HVAC business's former employee sentenced to 8 years for $600K embezzlement scheme - KEZI</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 12:00:00 GMT</t>
+          <t>Wed, 11 Mar 2026 17:54:00 GMT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPRGxQSDd5bFB1NnV1Uy1OTU8zWEJkeTZWVUxRdEVIbTdYaDM3c3lIYy1kdXk4dHEtWXRxTnpzdnZtQzFYZ3BPWksyOGs3RzFYbElGc1hvRURmRjhxLW9UdTlBejJqTUl4b1BYZE9VamEzbTVxSXFaTDhSSEE4TmhYekNHeHFPRmpMamN1eW1iM0JYWG5YZkFCQWdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxNaWZXWEV0bmk2ZVp1ejV3WThSRmZmV3NqVy1NeWZtaV9LMFpfOWs4Wlc1R0F4MTNKd0ljNk9qVlJObm5yUjBkVTAyZF9qeUlsUDZFQ2hKMFJ1aGowY3RPbU9VTHJsVlVEbjlneG4wUGoxU1F3TmlYbjhDRFBPaFVSMnlUNnhYQ2h6SWhONEJKUm55SUppRjYtLTdSeVM5Rm56Z3B5aTVYTU5OcVNtVTJHZ21XbzMxN1JLeGxqUGdCMU9QSk5qa2MzUndsRk5Cdy00cmRXMGFtdFppSXVBaUFWWDNoRVZHZWRKWk1lS2pxd3J4RzR3RHlkTEVxUTc?oc=5</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ohio man convicted of three crimes connected to stolen credit card scheme - The Norfolk Daily News</t>
+          <t>For robbing New Orleans postal worker with gun, man sentenced to 12 years in federal prison - NOLA.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sat, 07 Mar 2026 15:26:00 GMT</t>
+          <t>Wed, 11 Mar 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQd2F3eW1Lc1lRZU9IdEVXRDRiYmloQ3hpQW5mTGk2X29ja3lPV1FoNTNQOVlwdXFnaktrSmw4SGxyWHRlWUd2SllhUmswQVJqRThkMi1TSUZlWjFQRHdCalE1Nk9vUHNSc3R3bFB1LXFtRFB0aktQWl90WWFFUEFSQktwRDVnMHd4NmxoMW5jOEdNczc0VkZCZFhZUVNIanNiTEJLTEFDSU1WQnRVcmxzRVVSd0JpOVdTMWdWLWdJekJVT0tKVzlpaDhJZ25WVDB0aWthcGVFeFJNbXJaWXppd3EyWkVvNFJrMTFXNGtxUWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQLW9UdUpoek52MnJJWWVkWURzazVUQ045MzhPcHdrTVBJR0E3X1REVWVXRHotQ2R6M2Jxdk5YcHVFS1lHMUpHWl9JVXZMQm1pam1Eb3hmaTh1ZElJRkJ5VzljZWp1RGliUHI4Z004SEt3MHd0QURGc1VPanpLRkhia08wT0tLY1pVQWhJYmNjOThPcF9xdWtUa3psZnNzeFdDNlhOdDk5bmNoWUZ4cmdveHBSdVZPTWY2N3dmMHJKNkFjcVRxRlVTQTF6Q2gtR1MtZzZISnZqWGptSkVuS05EWXBZM0FHTEoxYTRmZlhDdDBkbjFLMmkzN2Nn0gH_AUFVX3lxTFBoUlFWdW1sRGJEWVVNenNSRWc4TUFSNlloLVR0RFdKY1haNFBsUUNRNWlSa216RkdyS2pTUXpLSVY4R1dzbUR2cFJnN004bWVoZUJCMUxjNElqM2pYVGpYTEpncXRzTUlmeDN2XzdBS2tVMWZ3S2xzY3ptaVBhNGM5TWUyYWhaX2dRVlpGY3BHMlVxbG0tWkprM01DWFdubmR6OHg2clhkWGR1R1BTT3Y0OUVGX2U1ck5wRzVMOVU3OGlPVjF3d1lZaDhGRjlrRERsQjJDTTVFZEVIZ1BlY2JXQmJpV3dJVXJOcENDRnk3LTh6cUs0RnpHeFZlUVlhcw?oc=5</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Former Missouri House speaker sentenced for pandemic fraud - KMOV</t>
+          <t>Alabama dentist sentenced after setting fire to his own office in insurance fraud scheme - Yellowhammer News</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 21:15:00 GMT</t>
+          <t>Fri, 13 Mar 2026 15:30:26 GMT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZlUwYVBoYnBxSGpGQVBuNFMtNlFRbDRTZU16VUJ4UkJ5NkRNajBucmRCQjMwNU05R1JJa2xkRDlsN0pYOVJqUjloZXo3b09SZ3h5dVJaSlJJM3hyempZV2NCTHlFVmdVZ0VxeHptZmVMUEczYXpBazBDd1pWY3BRekZOUG5FNFdocXBCM1h2TUFQeG1MWDNOMFNR0gGuAUFVX3lxTE1XQUNSLUZ6RXZHdjgwMVgzbXBJZzNJUFRGLWl3dUtuTjBvWXF0eU1RVThBNGpaOVNXblFsV3hIU05ONFExeGhtN3kzSE1wWEtNQlF1dUY5bjBjaUZ1blpIcHp3MU9nTUo1OW9aMmk2dGN4d1ZidlEwaEltQjBKVF9lMGFCWWZFa0tJWFdSSlZTM05pMGszSUN6UThYcnpUZzJUdTdWVUUzR2Zmc0VCQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVC1XRU9TNXBMLVR2SUVycHdybUFKaU5ZWFJXdmdpRW9MYVR0SlNFbEZfTDlTZ1hFTmd3dVpaRUJVOHFoZTVJeUs2bnp3TGZqd213SFc5SUxYcmFkRnZObW9JY2JYLVFTQkpYR2Nyb1hYQW1NZW1iRS1SZXE2ZThvdU5jd29nWjlUSG1BXzFkaWoya2FSSmNHTTZBMWNEdGhiMVIwRFE0RXN1Q2E4UFFteDFUemp2Z2RlRmc?oc=5</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>De Pere man convicted of federal fraud seeks court relief - WBAY</t>
+          <t>Former employee sentenced for stealing cash from defunct credit union - 28/22 News</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 20:44:00 GMT</t>
+          <t>Tue, 17 Mar 2026 22:18:29 GMT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNdHNxWkdVV0pUWUpPQUdLeHNfcVJpYnZmakJlQ0pLOEZXNDF5aDZYRnMtVmcxb0EwQjdXcGpla0dSYUNQQnhjZEItUVBySDlhOUFoZmpaN1dEckFVcjQtOFBUQThQVDBpcW1pbFRSTzBxQ2p3amRGWlNBdHNGRU9yMjRlYzlmTU81SWZqWTJndUPSAaQBQVVfeXFMT29ad0ZNWlVJcUZOTzJldm8wTXpVSmtfOWhZbl9CWEhhaEJKOVo5NEFUbFNKallrbUE4SnZxcDlmNk1hRFNvcWEtWVhLQTBfSWo0ZEtteTAwTXRWUjh2Y2ZwMnlvaXN5bXhIQTBITjdTdUF5c2dWbThUbGdWTWJvME9PeEhubkh1cUpJOWI1aV82MUJDc1JsZXF4YVFaem1OSTcyWGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQTzlTQlA3eHd5ODFsVWZlYy1DLVQ0MlJLVE8wYVBlc2xVbG5xTkluZG4xNzk1MmJ4WXpaMC1yOHdSR0JRZllFRjN4dlVYZjh3Wk1qTENTNnFJUTRrWVpReXBzRWMxWVlPWHp6SU1kUGFYRUpyaGVJNHVuS29pNnRIeERqOHB2bUIwY0RwVl9wa1M0UEtGRExMbDRLeE50Tlg0NHk0dTBnQS11N1lpUEdTSFZzQW5xbG9r0gG4AUFVX3lxTFBPOVNCUDd4d3k4MWxVZmVjLUMtVDQyUktUTzBhUGVzbFVsbnFOSW5kbjE3OTUyYnhZelowLXI4d1JHQlFmWUVGM3h2VVhmOHdaTWpMQ1M2cUlRNGtZWlF5cHNFYzFZWU9YenpJTWRQYVhFSnJoZUk0dW5Lb2k2dEh4RGo4cHZtQjBjRHBWX3BrUzRQS0ZETExsNEt4TnROWDQ0eTR1MGdBLXU3WWlQR1NIVnNBbnFsb2s?oc=5</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Former Yuma school employee convicted of stealing $86K in public funds - KVOA</t>
+          <t>Employee triggered a major alarm at the Lindt Museum - sentenced - blue News</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 18:34:17 GMT</t>
+          <t>Wed, 18 Mar 2026 06:46:00 GMT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxQSlBsLURMb0VJdDdVaFEwV3h6d3h4UFN1MDBWNWtvZS0wUUpTNEQ2cnhyLVR3bGtrQXZsLVd6VmktRU1iR0JBWGhabFRLTDYwbUszMXZoc09NNjd5QmV1TmxhZGFaSTZMNkNldTFxRWxoWDFVMzRJa25teU9FUEtwU1pWTGM5dXlTblBmLUpuR1dlODVQV0dEOTBFdjVjY0dPT1ZjemdES0Fva0pmMkxyZUJMUldyZFlmWE02QVh4eUxQdW1laVhfV01aeFNabWYybTI2TTFMQ2FxcVQ3aWNMVV9ZbXZKUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOX0tFcUhzNS1CVG5XZnNIeXJ3ejZ2b1AxLWowS0lydE14NUV3TzBDd3ZIOElmYTRVUmktWldIOTFDOFd6eFo4ZzlLdlc0SVVsV05yZDlPRWtiUFhnUUhLWWJyWjhsci1NeGY5dTJULTB5b1BLUDNxUnRaanBWTjZOR2ZDX2xzQ0w2ckVQS0VLbkFQY1BqNXhTYTFDUzNwMlQ5c0FTaEFBN0dYWkF1eTBaZzlfVmZEOWxYYnc?oc=5</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Three executives plead guilty in $528M pre-IPO investment fraud - Brooklyn Eagle</t>
+          <t>Westchester Construction Boss ‘Convicted Of Scamming Workers Is Re-Arrested For $50,000 In Wage Theft’ - WNY Labor Today</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 18:08:57 GMT</t>
+          <t>Tue, 17 Mar 2026 20:23:47 GMT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGlnbDVaNk9qeEg5c1RNQXRlVUt3S2hkVmNmMFpoTXU3Y0J4bW9sbDB5RThKWnBRQm5GNEcteDlRc2lvd2NpZnY4ODFnLUNjb2diNXJ3V2ZiLWxKdkpmWG9TdjM5RmxUSTJua1JXdGRZUzJMOVhFbHFDakI3TTdwUkNXMzVqZl9wb3hiZFBIcVYwWGUtRm1nS0ZTYWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPdE1QUnQzT2R4a3BsVW81aFV3UU55VmpHNThvd2tPeGpYYUZUd0UtUlkzSmIxMFZlQ1VpTElEcmN3SkJYejNQWEFtRDFRdXljOGpVV2VGR3c4MjJyMHdYU29LM1lmbzgzWUxBWEQ1MWVLX09SdlpGOWFpT2thOEExODR5UktVdmNfa0ZKc3JEMzZoLUtXcjRJZk5HbnNqZFVTazdtRndNZWEwYXZocjdrLWJDclNDeFhYLXZqc3Y4WHpVU0hZVll4cC1MR0xsY3Brak5NQXR3UUxhZFplSVVsaFA5XzgwLXcwNFd1ekZuc1U0TmE1WmFfUmJwQXBmajBpanc?oc=5</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Abdullah Alwan, Mughith Faisal and Basheer Faisal: Three men sentenced in Phoenix for defrauding Amazon o - The Times of India</t>
+          <t>CAUGHT ON CAM: MKE woman convicted of battery of officer, retail theft after intense Wauwatosa mall incident - TMJ4 News</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Sat, 07 Mar 2026 14:31:00 GMT</t>
+          <t>Tue, 17 Mar 2026 00:30:43 GMT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxPUkdnV1JKcWhnbEd6SHlDaXc3UkVUY3liLVN3U0tlRmRqQW5GRnZXWU5mMl81T2hER1BSRVRLN0plSEh1c2lXV3BLbFZFUXNtZERBU1Y0dDhOc2s5bGhNNmRxM1YwMWNvamNibUZkYy1uNEFnY2hEcGVFRXhNVHdDX1gtbUEzUFVheks4QzFaR1QtdlhtZzRmdnVUdEs3ektZSWZ1c194dWRkOUJhX0pxMU1ONk11NERQbWZQNjV5SUdNdVQwWGxQbjN6LWhremVCemcxcFJrTlpETUdxNXNPZlFKSUw1cXVNa1kyV3k5dmVxY0I2YTJyYktVeUJlVDdCellCbW14bkE5aEZnZENnWm8zMjNya2V4YnE5MktPclHSAaYCQVVfeXFMUDh2M2dWUUdod3BJN1pUUVpDQU05b0JLTV9iUVRGQmhBZ2VnZzV5ZzFiYmpYRDJOSTRfbHdmQzZoX2RHZUFSTkJiYW1FUkJYdXpGRDBoZWhuVlBjN3FWWGowQXZOVTNyV2Q0VVZOTTN4cmMxcE9rQ2VkQ0FKRjJQSy1RTl9sanJxVzBFUU1XbDE1ejk4dkdsTzJiQVVXamhmNzZFdm5VbGlHZDUxcU9Nb2tEb0VkdTNmZGpXanhlYlU4VllhdG9YdVQxc3lnQUthbHVaaVRzSU1PU21LUUxoaFU3a2ZfLU5MUDdsR1gzNDMxTFJETFN1WTRKSm85Z09jSTF0cFp3Q3A0SnAwZDB2SnRmRFlJdFhmTXdEX3NENjFQNmJadVZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOMTNqMno0RVBCTDhqV0pPOE1fMk0yYnFOMGFzek5pekt5Um9zTVE4S1FiYzZQd0F4TDRoLWxBa28wNUpSbU54Mmd2VE5KS1BrRm1BZ2w4WnE2WUkxaEREWlVWTHdhTGtaRjFSQVQ0YkpHcUZTSzV6UFdvdGNwNGFCYjYwTGVmSXVmaUNhcmpwWEZxd1dQMnRRX3Q2WWlhUkVRUmtyd1EwNHB2SVR0WGVYVHRNMk5ST3ZCQk9ZUDN0bFhaRVFxUHJWbVgxYkgtQ0dvTU0zeTRkSWlNTnpaakxPc2Nkaw?oc=5</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mexican national living in country illegally pleads, sentenced for federal fraud crime - WV News</t>
+          <t>Maine prison official pleads guilty to spending nearly $2.4M in theft and bribery case - Piscataquis Observer</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:20:00 GMT</t>
+          <t>Mon, 16 Mar 2026 20:39:25 GMT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOVmpFdnNzQnd5NmgzZDRvNHdMVDVfblh3SFc4eG5hNmY2VlFldS1SS2RjN1B1RTV2ZkUxejBWU0JveEdjVk5VRS1BY3FrdDlyRmVaOTg0MHZ1RklmTlBLSWZGUU5NdDREX1hGUEZoVjNPN3g0WVI0RVpHeXNUMXEzakU4dTBfNkIxdWN1Sktmb3NFdEpzd3lyemJFc0dvMV9Jc0Foa25nZjFLY0kyNElWTlY0Y253dDhWS3E5aDVucGp6eE1BZ0h0SjB3ZkNWZDFETnp0Szd1QmY1VW1wcUZxcmhpRWxXMlNGYkc4R1lTNGgyX0N2RUdlRHdJMFVjRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQLWljLWdyMDh1d0hUVHFCaFdtSHJwOGN2VXJHZXFWZnBVN2xhMlRUYWExU01WSTZRaTdrV1Ftd3FNU1JtaVFzVW5ZV2FCQkZFS19oNnNrdHMyY3JRUDNWR0RxSm5tLUpjMWs3ZHdSTGhSbHRxUjloNHIwOGFBcURyRGFETzB0cm5uRERzWkJzZ3hIam5paGMwaE1TdmxQVW53ZU1nVW5WOXhDOVppRkQwcWdId3lJUGRxUnBXeFQwNXRCeDdN?oc=5</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Former Arizona attorney general employee pleads guilty in jewelry theft case - KVOA</t>
+          <t>Former sex abuse charity worker sentenced after passing sensitive material to prisoner - Civil Society Media</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 22:43:00 GMT</t>
+          <t>Wed, 11 Mar 2026 13:24:30 GMT</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNV3czNENtZkJ5YWw0Unp0YXhwS2gxMElGS2VuaDdaR2Q2OHRlZU1UYWxDSkZGUS1BdnFqZkxHSFhLTkhhMzZjend2T0h4ZUE5Nm1aT25BZy1oZGJ3Qlh3UEFzajJVb04xSUFSb01RQm9pZTR2QUdEeXJxN25LY04yRl9ZbE1USlROLTU5aWJhTnZSNEdIdEJabnhIVVdudHRMSDd1anpyV280V0RUU1VlRXNtZFloYkhnX19KcDZTeEh6RDhva2hyeHZEeDJWTVdjQmdlaExLdjgzUFBINVZUN2Z0RDBMeWpIT1NITEZJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNUVtamhsS296RWVLMm1nU2ZpQkNRejN3TFZ0dEtGeloydzNPZEJzQkhaNzMxejJFWmRyX2wtUERjQThfNl9ZbzQxaFlwRTNNcTJETlE5NnlMd1gwN045bVlvSWZaRFJqZl9uYkpwOGhoMloxS3RXVUstcldGbk5mWVc4Y3ROcnhjemtzTVR1QjJfR09URWVpcy1jZGoxdDRBb1JRT1RxUG14WjRFUmRPS3poZk8zZy0tekN5VzdyQkRrbHJVWWc?oc=5</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Hawaii couple convicted in nationwide tax fraud conspiracy - Hawaii News Now</t>
+          <t>DStv pirates sentenced as MultiChoice raids intensify - ITWeb</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 20:44:00 GMT</t>
+          <t>Thu, 12 Mar 2026 12:05:00 GMT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOWDM5R2twSFd6LVQwS0tNRHdZQTlJMVJEV3A3dXJlZUZjS0MybWlIeG53b3lZaExSRU1QU2EtUUV5UUdEMncyLTBiUkEtQ1VoVVYybjZSRjNEU3puM2hSMGdUN3VOM0R4d05pRUhjQnhYTEFlb213M1prelJaeXV0cmtpYUNJY3hhMkFRZWhHbi1YYUQ1ZUttdWVQN0VGd9IBsgFBVV95cUxOTDhVbzJ4WHgxbDdpUU5mNXdEeWVra0xfQ2lYYU9oU2xYQlVMd3IxbFdrdmRoTkM5c0hwNVJtTVVXQzhLamZCdU9EZkVuMHJTZlFRbjQ2SGs0c2F6YWd4TjhtcEFSdms0dUt6NG9NNDNTOEVORldnRVpEaWc3QUFXWlZPRXVKUUdwOEJZbXNHSVpZNGdGMUFUMGtQdEVSTHFHY0JGeXFyMWdKR0NoNEcyQW9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSkFkdGtuSkFERVJiNlJZMHY1RnZDYkpPZlN5dUpLemplSGt4cURHLW5PbFBpTEtYc3M2dGVIS1UyajhqQkJwVXBNUVViNmJZNUNHUjJJdDlFZ3RyLXNjSU1MN0pwZ043R09nM244Si14Y1ppX056YUdqc1dTSF9LaUJobDBRTDJOYjRnYzA2b19yakRHVEdhZWNjSWtsbU1sWGpiUg?oc=5</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Former USPS mail carrier pleads guilty to stealing mail - WGRZ</t>
+          <t>Petal pharmacy owner pleads guilty to tax fraud involving employee paychecks - WDAM-TV</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:32:00 GMT</t>
+          <t>Wed, 11 Mar 2026 15:31:00 GMT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZUN0V2dPM3p6UGZ3ckQwWHc1UWtBTmtmeHVrNkRHWU51Vy1DVGJGRnBZRWVJSnpFTHMtbzE4eTB6UUJSVmtKZjJNMHdTcG5PaFI1NEZqME1pQ1NVTTVYRmpaZGxXOGdaeENmYURfQmN2RGdDaUNuQTZ2ekRxNS1jVlpqRlpCWjNldWJLMTVUXzNqcUR6c1I1WXhvaEhKeC1TTUNoTHJnT0JTbFFobU9ZWmhtaEdNdWVRSGwyUEw1SlNsZENtTEliUXpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPZGZ5V2VWRmxxZXpOQ0xkY0FCMmh5eDU3WU8tQmlUNENEMHlwSTdLemhKTWFvRU11cGUzckt2MVoyVm1HdjgyQm1DbERxVVg2N3ZWX1hZUzc5cXJ2NlJaRzJmQll5c3ZNaFhkQkhoUGRiZWtsYlh0eGEyUk9KTzNkWlp1dEl4UDNReU14VzBLcWI4aDJDUU5zUldyZ0d6czE1QzFEaVJmeVZhUdIBvgFBVV95cUxNWmw2T2NWUXV4REdVYTdBNHZia0lXQmQ1OEpNd0txT1ZtYkhSWkgxVjRDVERUZ1dGcS14MEJleTRwYllCb05Qc2ZnTk9Od3hONDZXSlREUGhDd0xOcm1hUE9PSUtiRWppSjV0R1VfUVM3QS1RV3dla2hQUkFuT05CSFJYYWV2ZWYzVElFbjEtbGN4MGZWdXY1M2lSblZYY214VVloY0dpVE5UVWZnd21qZ0JINk9iMkFCbnJhYnNB?oc=5</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CT man who prompted Amber Alert to be sentenced for stealing $370,000 in federal benefits - New Haven Register</t>
+          <t>Man sentenced in mail theft case - paxtonmedia.com</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 15:39:09 GMT</t>
+          <t>Fri, 13 Mar 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNWmJGeXFCUE9vSVE3RW9JMm94SDdEQmhhWHhFck5SVWc1cVJ5dGNTTFVUaThrckJJTzNneFdwbXNZcERlR3ZJZTFZVjlVZzN0dkptTW1IdlBJVmNsRFN1SDJwbVZFaXVUN3dmU3JBcTBndXhjOHNpeHltOVYyUTdGbXY3Q1ZYcHB0LUIzd0dzeHRleFJ4ZzJIUmZUX1k4YnZCekVvYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOYmpvRzZTM3EteGJxaGlXcFY4ZkVXSTI5cG5aRTVtcjBoUEJMVFpUcllQN1lKX3ZaSXE0Sk9sYzAwT3BhX09BQUNkbHRxa0RwVFlUZ3JFUU15U0ZSVjNlWXVNNUNaRUVYcnNnWmpKRjBmWW1vb0pFTlpYbDFpU0JMZDdiR2RfWFpZNmxaQVY0a0s5NlJ0WnBCUkJseUJCN3BtdnpIUG5YbVdwelJiSnpURDFLZ3J5TEVNajRGLVU0Y3VRSHRxZGlnYQ?oc=5</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4901,17 +4901,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Three Arizona men sentenced for $4.5M Amazon logistics fraud scheme - KVOA</t>
+          <t>Former Hillsborough Township School Employee Sentenced to Probation for Embezzlement and Theft of School Funds - TAPinto</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 04:03:38 GMT</t>
+          <t>Thu, 12 Mar 2026 16:50:10 GMT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOT081NmZsRk5pTFJhY1Q0cEl0Nm5sVzVhbExKNC1iUklEczBpaFpzV2ZLaE5EVjFXOFBPbVNwdFB3ZkUteW9xSlhuNzJaTlFGQlFmcW5MVU9IUjlaWmFNWnE2Z0hCS2YwczdkQTBmWHl2cTNyY0cxVkVlQ3VrTVRFVzBYSXlkVzUzVWNtUUhuOV9LbUljU0FBcG9IRHQzSGRJVFBSUEhpNmRHLVZubEU0bGxFZU50a0wzWVgtNXlhU1Y3Yldla1VMQVNXbUNnMU1CMVBjbFhxZUUzOTFwSV94czNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxPMXl5bFliZW5Kczc3b2dIcGpGcHJxYVV3aGo0cjdOWmlDdFFHQnFrQnByTFRtSTA1bWJMeVVMRHFYNVZMc2lDeGpRWVFwSG5jT1NlY1IzTkxiU25oR1NrWFVfdGQxVmUyVGU5Y0Z5WTBJUW9ycFRzRWtnUnJreFpHUG50Z3M3Y2taVV8zWUNtajBES3h4V2pmbllYdXZqb1hVb3JWWXduUzVJV2I2MVA3dW5odGV4aHVxV29qUWZCd2pXbzdsV2xmd21ydDBvck90d0I4WE1jMVBWRHA4Tjg5ZVJ2SHY5ejlRZVJNanRSM0xXV2h5YlZ3dlNZWEdfaU9BblB0UTVYanZuSlhOTktmbVVDSDhzQQ?oc=5</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Former Pittston church worker gets prison for theft - Wilkes-Barre Citizens' Voice</t>
+          <t>Habitual fraud Steve Farzam takes plea deal in latest case of impersonating public safety worker - Santa Monica Daily Press</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 18:38:48 GMT</t>
+          <t>Wed, 11 Mar 2026 21:11:48 GMT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPclVvU1lHbWpDbEYxZ1RhanJqRWcwN2o1U3FMWmNzenFobWxvYXU4VF9QM0ZzT0FTUTBmZklwaS1rSl9PNk14cno0VVFncXRCaVVhRUlnWklsRExQMzN1SVNHc0VISVpaQ2Y2Wl9wclM0bDdHN2puWWJYbFlSbjVzMU9nVk9mZENXUFpkcmM1YW05SHF3SmZkZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPR1NpVEpkWlY4Tm9MZU04UXdxc1VsbTlHWkVhRUxGYlRONkFhbVdyLTR1anpHTlZ5bDBQNGJDOEk1ODRoZFBwclNXcU9aeXhtTXppTlM0U2dYT2Ria2g1b0d1bkp4RjlaU0VjeGVYdW1VVkFzUXRxNjRtbVM3NkZ3eU5uNXNYZi0xMmdDS1VGdTdub2gtdE1HTUFwck0tcFdReXRvQ0Vmc3o0V2xpQm1uT0lGc0RhalNPVnc?oc=5</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Advisor convicted of defrauding NBA players through viatical life sales - InsuranceNewsNet</t>
+          <t>A Jamaican national was previously deported after drug, assault convictions. Now it’s passport fraud - Hartford Courant</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 15:38:23 GMT</t>
+          <t>Wed, 11 Mar 2026 09:47:19 GMT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPelBCY2JUc1E2blhqT0F2Q0loQTdOWWZJbTZUalVMT3RVUWN6YWZBbnFsSFlWWHI2VGJ5c1I4bzI4Q05NMC1xQUgwMEcyNDgwUHZHLXlIZjRZTC12bVAxOFFrcW5wQl9qN0ZmM3lVc0ZQemowRmM1RU1lQXRid2VrM0lQelQ3VXkxRU9IdEFYdnJBSDE2aEo2MDh4MklTb2tCeDlDMXJ3aWZ6dkNDMGdVYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNcEl2U2FVQzFCZjctWnJrZjQ3eXhNVElLekpwZVFidV9tc25lYWkweVBXdy1PUEpTTUI3bjRvRlplRERTT3g4cWpCZUV3YmpNLUIyZWpGekQ5dTBLMkE1WXVlMVVZYVVwclU5TmV6QjRMQmg3RUdPWWJINElhbUIyRnpsd1pSdXZoRTBuMDFxbTY1Q21oeTBtM0ZWYzdkZ284MXk1SlFEdklPR0hLWGh2aWZkck1sYzNIUm56ODltODlVVE1PZENfbUpJeFJZZw?oc=5</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Why a convicted ex-lawyer turned on others in New Orleans staged crash scheme during trial - NOLA.com</t>
+          <t>Baltimore County CEO sentenced to 18 months for stealing $2 million in employee payroll taxes - CBS News</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Sat, 07 Mar 2026 10:00:00 GMT</t>
+          <t>Sun, 15 Mar 2026 03:35:38 GMT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPOXRLVU5pYmgySF9UOEpyN2VON085UVppaDRwUVdpMC1oTEZUMXZ5SUU3Uzlkd2czUnY3RTEtb1REUl9seVJ4bkdJSmhiWDFMaVF2WkQtc0o2Wmt3Y0ZldTlpSG9XRW9LNjZscGIwUEM2ZnV4YkJvUV85aUFyekViZEZrVmZCaHVCRVhGdWhXVHotWmdWWVlTSlZkbjFsWkJSejRrbWIzNWx0aWpLWWxfRnp0MkdMRV9MZlBZcmNYbktuSkxuWUHSAcsBQVVfeXFMT2hONVh5Rmo2eVBJTk1OeU95ZEpiSGVGLVI0ekctanZrZlBqWDVlLXM2R3A1LW43bVZvVVVKR3NvRzFBRDJKbWtLV1VyaFNNSnRCczBJS0NkZHh4WHZxOHVUZy1MZlBWS2hpeExEYkl6WWdKY2ZWZVNlcHc0UjhaS0NiUFRZS3JkX0M5cUk5SFRKVkhIQkdKQ3Q4UDRhM1lGTUdKYTRUV21QUmVHbURDa2tVTkJocDkzMmhsYjFsWGZ1Wm5yYU5fREdBQTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOclhIM2ZCQlVrX05ubnk3UHBiSEloT3IybUZ5aTlYYjUtQjBHMk9UUEpuNHh2a1EzWHJrVnVDSnJTQ1oxUW4td05JRF9LcXFZb2ZZR1NRWENkby1ySnVpbU5XRjdWblkyZGpJM3R4dlVXQ24waDhpSU1sSENhVm5OMk9YYm9iVGZFdl9QZHFUT0R3QWVZcDNJSWU5YTZicHlOeDlCZ3d3bw?oc=5</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -5021,17 +5021,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jail for former bank employee who gave scammer data on over 1,000 customers in Singapore - The Star</t>
+          <t>Randolph Woman Pleads Guilty To Mail Theft - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 10:51:00 GMT</t>
+          <t>Wed, 11 Mar 2026 11:42:02 GMT</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNTl8zUUtGeXZFdEFWWVJSdnBZeDJhc18xLXhLUHdNUS1CaVNzTUpiV3cwaXpMQWdIb2dFQkRjWWlzbDl1dTVuR2UwM0t5RjVINERsTzgtNk9JN1kxaGtLSzRfYmVIUllHTXVQX0JDNXJGbDJTWTFUeDlObEx5QnFobkpGSWhWN280elRXV0RUMWxvekExcW0tblpQSUgybExRdlJtWFFoSHBWR1Y4WFQteVJwMEoxN0J6Sm0tdHJxeWNTT2c5cE5LZnFUY1VtSUZVUGhzRW9oRFFaVzlqOGNDbEkzTDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFAxU1lBemNMbEVCNG9ZV3RJWHJLY2U3NzROZEYzT3haUzgwQl9fYzFNd3lLcnVWVlpVcFhZQWlYZzExOHJUVlhKUUp4LUFtdk1OWDNhZ1lwNG83VXBLOUxOTG1kZllKMVBuRjVGSG12UEYxTGFG?oc=5</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Trumbull trucking company owner pleads guilty to wire fraud in $3.5M Amazon fraud scheme - New Haven Register</t>
+          <t>Former USPS employees plead guilty to stealing mail, fraudulently filing PPP loans, authorities say - 11Alive.com</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 20:37:42 GMT</t>
+          <t>Fri, 13 Mar 2026 23:56:00 GMT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQYzNQQnF0SFRyR21pZFlLOGwtUGl6R2RBa0VoQl9SZmxMcUxJSnBuWTY3SU5uc3dFWEVVZHhONmo2V2tTN2dhVTRuN0NydFZ2YUdlaWpFbXVlamhLZUJjOW5iaW53SkNGVWFLR1pROHVBMm5keEVRbm8yNnFpMFI4UlE5RzRyRGNuaUVVYTBsQVdXbzVfQXZ4dzFLQ3N5RWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPMnZ4U1Q0Q1ZPY3lWMVp6UFBSRmhIS3dwdzNPSUhfLS1sN2pEQzhOTkRxMU1XcjhXR2YxQlhNeDNyWjNab25uRXFla0RJLVAtSFRZbG1tellCSHUwU2pYVEQ5WHN3bUdvdGUxNV9VdFpDNVBwbDk2Vll3X3NTTmdtY1BQRWIwM2ljN2Y4MTdHaGVVdV9rTEd2OS1JZUx0ZTFjeGxMOHJlUTlScXgtNHVPdlRER1NuUU5GTktKc3J4d2N3aV9GM2FCYXIzc3pxMlRvVmdGYXJ5dWJnYWxuVzBYWmxrTktwejRkMGtqV08za2d5bFloc3c?oc=5</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -5081,17 +5081,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Jamestown man sentenced for taking, selling water meters - Jamestown Sun</t>
+          <t>Two including ex-bank employee get five-year jail in bank fraud case - lokmattimes.com</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Sat, 07 Mar 2026 12:48:00 GMT</t>
+          <t>Tue, 17 Mar 2026 11:38:04 GMT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQM2xwQUFTcGdMdF9UdUlnZC04ckt4cVV3TzZVcWVIOXc3MUUybUgzTUh2Z3ZrR211RTdPSE1VeTdaLUczSHVsRnUtQmxfc2JzMnloZGhHdjVZWGJXSk9mNl9zZ0tUX3AtY2Y3LWpMZ2xsWVQtNDBfbTE1YXJ0U0ZpR2JJRjZNeGRQTnVNbVJwbGFIdlBPcS1hQTQwRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQUlJNdHB0bTZ2RnVQY3ZEc01FTGVOdElBQUFkdXRiVWRXd3QxZ1VQOWJLamJKUVYzeGVTdE9KcWhJdWFfZGQxSFB3REEzY2JNTWZoYWRTQm9FeWVfdHowOUN0a1pvSlRpejN3ejJpcXQweUNWT2NZczFaOGxZaEhrSkNycWtfTVdYM0Y2eHBaWWZwb3NtWlJwZjJVR0RPaGhFVUpRZlZiR0lMQdIBrwFBVV95cUxPSXJHOUlUa2RuZGNPSFhRZlFJa200ZUVqNlFBZnRqSHlGVmsxbEpMVkFEVnlvQ3ltWGFkYlVnQVF1V1pPdWNKemtaN0xDaFpkYVB4OG05R2p5a2RLcDZ5MUd0aXIxMERjdlFmdTdxZkdMWW10Nnc4ekI1RFVZNjAzS2lvV2RDdm12aFhXSkJGNmdsS1Q4UmFZcllSTUdPWGZlVThaeTgtNW1QYUJaWWVv?oc=5</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -5111,17 +5111,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portsmouth man sentenced to more than 2 years in prison for auto loan fraud - 13newsnow.com</t>
+          <t>The only Glenn Valley worker charged with identity theft sentenced to one year in prison - Omaha World-Herald</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 19:57:00 GMT</t>
+          <t>Fri, 13 Mar 2026 18:24:22 GMT</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPLWRKT19KVU1LWmpiUGFsSXBpUVlvZFRPbGg4RTZIVHVTWWJQdUxiNERCbERMTm9KY1BySWtrRUpMN3JtRFg4OGRybkU1QVBsUGhORUVkR3c5T3oyUFB0aFhrRnB5amEzRWQ3aUpQaW9oVG1sa1Y2djlVaFY2YURmZk5ibWgxaHFnd05sQXpVM3ZVUkRjZXRiU2dWRVZVaXJub1laUFN3alRDQ1U3LW9nRG5jWURQLTZSVGk1cWRRS1BuTkwzaG1Nd1lDWGpIaUNPNTZpUk96bk81WXY2V3JrTHBEenJyQ05vV3BCQ0ZKckRfT0dwS3VCLXUzWXNKM09EdFFXM2RDYl83aFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOc2k5VjZfZTBCV3dxVlZuUHJKeHJqMGhnNU5jd1VrUUVULWt0UzFCV3UwOHZUMDZKbnR5Y0xBdTJHamFUamhpdllvdHRBZXFaQlRPWlFEZEs1MnA2RlhjWWl5Y21aOEpyUkNrc3ZqOWVZQ1FlUkFJZkRQSFRTQ2xFU0NpTWJBZTZST2psTm84QmZESzZ4aEE?oc=5</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Woman, 31, an ex-UOB staff, gives over 1,000 customers' data to scammers, gets 1 year &amp; 24 weeks' jail - Mothership</t>
+          <t>Fake Name, Fake Paychecks, Fake Drowning Stint, Real Taxpayer Money – Connecticut Man Sentenced To 57 Months On Multi-Decade Fraud Charges - The Maine Wire</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 17:46:43 GMT</t>
+          <t>Tue, 17 Mar 2026 16:18:24 GMT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1RM2Nzc014cDdSTTZSOU1Bb1lIc2g3QVBHcktMSFl4Q0FVeDNkLU1jaU52cU5ia3RtTzVpNl9ZYW9GRjhNSzdmUHRwMk1TeDRmTC1sRHZzTWVNQlc3RXNJeVpfMHlqS3A4TWlORQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOX0lQX2p0dTVKRlJOaFNGNi0td3R5RDVjOTdZQ0tKbE5IX2Y3NHRwbFdIcnQxNlBka3FkbG02ZmpSWVd3S3ZpalZrMllMamlva1pseUh4RUwxc2lpdEFMX0ZzdlFkUnlmVDF3eFY0MFY2c0xQOXI4Sy1CM3BsSlJZcGkzTWxQMWxnaHFJa09IMHViNzdYZXoxal9uQy1MOS05b3hrWGJjN0JEbEljMDFrR25YN2g2ZDJLQ3FYVXBiM0g1YlAwVlZYaXQ5eXNpWGJmMlAtend2NTFDU2c2anJScGt6RmU4cGI3YWNwY3ZhbnBBZjIxRUUxTE5nVmF0c1B0?oc=5</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sandy man sentenced for stealing $65K from storage units - KPTV</t>
+          <t>Former Weott Water District Employee Pleads Guilty to Grand Theft; District Operator Says Restitution Falls Far Short - Redheaded Blackbelt</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 16:19:00 GMT</t>
+          <t>Thu, 12 Mar 2026 07:02:23 GMT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQQzA3Ym9zQkZReWs4UkRUdlYxNlAtSUFUbURBOWxIY050c2h4dVg2RDVxbTR1Qkc0OHFPNDd2cWhROHptWGliVnJYZWNTWTZBcHIxZnJJclBpdk13WWpxQWo0Z012VnBVSDdmQXpLcldvYko4U21Ba0JQS0N3U24ybUpBOHZJT0E1ZXY2dGM0QlViU2xiLTdkRzJ30gGaAUFVX3lxTFBDMDdib3NCRlF5azhSRFR2VjE2UC1JQVRtREE5bEhjTnRzaHh1WDZENXFtNHVCRzQ4cU80N3ZxaFE4em1YaWJWclhlY1NZNkFwcjFmcklyUGl2TXdZanFBajRnTXZWcFVIN2ZBektyV29iSjhTbUFrQlBLQ3dTbjJtSkE4dklPQTVldjZ0YzRCVWJTbGItN2RHMnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOZzdyaFpTNXRQWTlweG9SMFJaUHJFdlo1Y0FBVmd3aC1Sc2lzTGNlX0ticlF2Y1NScjEzdVV3cWZWTkRjQm8tZl9mVHZmNjJ2NklhZzBqM2lOMkpFWHdsclIyWkV6TFFWS2N5N0FJd0pLUU00MV9jdXpmRmNOTjNTSE1MbTZ4VWJfdVNFUFExRHF4dElNSHR5R2VmZU14M1VqbHhoeUQzS09kdGdqdjhVZmtUdWRwSzE3M3lnc2g3LUh0VHFrRDFjZ1BTU2cxNW4xdm9hZTlPMlhlc2oteWdoZWNR?oc=5</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -5201,17 +5201,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Medicaid fraud scheme leads to prison terms for owner and staff at substance abuse facility - Roanoke-Chowan News-Herald</t>
+          <t>Former Steinhoff auditor sentenced to R2 million fine in fraud saga - novanews.co.za</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 20:28:49 GMT</t>
+          <t>Fri, 13 Mar 2026 03:10:00 GMT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOQ1lxb0d5VFFOU1gteTkxVkpQSTFyOXlEbVZnT2JUNjJhT2VSaHoxTzBXQ1UxZjhtSzBFX3U2SzA2UFMxTjB2QzRVTjB3TnlBOTYxWmVGR2VDa3J2T1JqYlhNUi1ZR0ZCUXZFeVluczVmeUFMQjlKalNGVTUzajRZNjNtVDFJb1BZMEhWMHB4b2ozZVJkM3NvZGRNWGVCMkRXLTV6RHlhZXpTTV9pb2xJTkgwb2lyeXloS2lWQlctUUw4YTRqc3hoUF9KbVl3c0VJcXdMckZ1dkZzUi1XMlhN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQZWNEWi1nUUVrWlAycHRVRWRqNUFyX0s0RjRZMnVVT0hMZ3lhYVFpN1pjSmExbzJuQk91Q0JpNk1CLU9LTTZaQURhQVdYSm5jVEF6amI4Q2JOQVBndjRSYUluTkt6OGQ3WWpvOHdONTdXWng5eHdkWTJ2akotcG1tTHdVa0VzYVdLcVlyb1cxTlJfSGY3aFE?oc=5</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -5221,27 +5221,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Fraud Strategy launch - GOV.UK</t>
+          <t>Seasonal Worker at Old Faithful Sentenced to 12 Months for Assault - Montana Outdoor</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 20:07:01 GMT</t>
+          <t>Tue, 17 Mar 2026 14:01:27 GMT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE50d1drWUlDMC1UZFNFby1ha0dpdVZoaUJha2ljVHhMUDNjYjgxZHJfeFBEMXRLaTdpZzU3U1RyczVXOXRMZ3FUcVlyemNzQlk5T2luZElVSXo3T2c0UkhFLWI1OU5uVGRFSlNfXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOT1gxOVdXZU5zckVuaFlicHoyZWdmeDI0TnhvY3lHVm41dlR2R3ViQUNCSGJjWTJJR1dFeWNWeWV2S2s2aGdtVWJvUVhUM2VqcjR6X0NDaHhrNHhLdGp5OHhtdFNWQnpGSEZlTHJlVWZ3VnVCRnZpS2dkdndTSlBwUjNYdlhwYi1SeUFMQkt6bU5PQnBteE9KRlpoYVJsSEl2V0EzWmxIaFFtdw?oc=5</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -5251,27 +5251,27 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>The impact of AI on online fraud in London - London City Hall</t>
+          <t>US$186 000 ghost‑worker fraud at United Refineries - heraldonline.co.zw</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 12:59:53 GMT</t>
+          <t>Mon, 16 Mar 2026 21:14:32 GMT</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcDBkOXFCYTJhX3AxSGI0bkZ3M2RCN3BzWGFIeExLSXJyVlhoN1JFMHBqSmhPTTdMYmFtQVhMZk1PMEVCZHlfSlhObGtMRHF3VHZBU3F1TXc5Y1E2Mnp4a0xUdTZqNkltTnNJcUNFSDlURlVFM0dzTFpmMEFLSmpxTUsyNzFaS0Fma3dQekJmMTU1LVAxZHlva1NhNTJqZHZNY09CMmJQVFEwYjNjMDNVUU5LZHJHRzhwc2pFTXhLOHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPYjZ1X3EyVXVUWjlaZVc3OHJ3UFVkclBHbXpDaTlNcWlUeVI4bE1hMGJxX3IwWGxKTWp5QU5pY0RmZ0RzcEIwVS1lSHo5VzQ2bG50REszT09jU1d1UnhWMjExVWJwcThRV3dGNmIwanVCWVoyVGo1NXRBWFFWVGc0WE44UUlqdDZW?oc=5</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NEWS: World law enforcement chiefs set for EAFCS2026 to enhance fight against fraud and financial crime - AML Intelligence</t>
+          <t>Investigation Black Forest: EPPO carries out searches on suspicion of customs fraud involving the imports of aluminium from China | European Public Prosecutor’s Office - European Public Prosecutor’s Office</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 01:12:00 GMT</t>
+          <t>Tue, 17 Mar 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPbEpJZ1oxd1NrS0xMY1RuaFk4V2ZvaEdVUFN5VkJUaU9vNThuUG43N29aTU1Fb2xKNmhmd3pyQTNxQ3ZwYng1ZG5BWFNOTVpEUkhqLTJRZndnazJLTEEtN20wOFgzU1dGOVBQeFpRWE1oLXhsYWVEaVNLenotUEdMOXNkbVk4NTZoNGRyRzl0ZHhISUVZQU4yNFE3TUJzOGtrVi1oajJ6NXNkUTlHUVpkYmxyOVhSdXA2b3JQdkZhbVdEUWF5aHUyUnJYQm1tZ3M3eTlWVGI3WS1hX1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPMnhnVk1nWFptRF9QaV9ZVHpFMldkMmRXdTVzSWlUUkZyMUYxZlNGWVJabF9kQUljNU0zQ2V5WHgzdlRULWZoZEJjdlZ0LVRIc3RVbm5tbW1CQmtIY1NIT2U1SVp5c0RJTVNwa2psLUxSRWNWdV9NVGJJS3NZdDh6Z2ozaWlFNkd1QzgyQTBadkxkUmZQN2xoYlFWMGtKUWkycUtCU0U1RDBPT3Y5Vm5ia2c0Q1A4bFNXMUdlUVZrdkNScVVLREE?oc=5</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>The consequences of targeting Universal Credit fraud and error - The London School of Economics and Political Science</t>
+          <t>Global Fraud Summit keynote speech - GOV.UK</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 20:22:02 GMT</t>
+          <t>Mon, 16 Mar 2026 13:56:51 GMT</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNaGdkUWR2cVFRelhZZHhkdUxhNnNHUkdnM2gtNGN0M2FxVTItb0pfVVYwdDdxeWFDSlA3a2lYenZqclV6SU5LRWhZajRxTE0waHgwRkFRMmlZVWxPbzY5Y3kwY1NhM2RURUtadTRYNHBoU3lEQS1FWlZuQVMzWUoxRW1mZGhRTnBZZGczUGcyNlFfM0FhbE5hMzZxbUZxU0V1VGtSMFdER3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9Fd1J1bTBtTG1nb3FHMmxjZlp6OXdwVWVodkZPTU9YT3RBSXhoQzZQcTdZbXROMGQxRGRYRWVTMENzSVhZbmZvbHNwTTdmTlVWeTNvMFI2NFJoWGFMYk5LRlVxTS1jRWJ2bDc4Nm9rbWhJNDBIdGhyTWV2dVpwUQ?oc=5</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -5351,17 +5351,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Fraud prevention successes save council more than £420,000 - One Welwyn Hatfield</t>
+          <t>Coherent Solutions Releases Research on AI-driven Fraud Prevention in Banking and Finance and the Best AI Models for Banks - PA Media</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 11:05:09 GMT</t>
+          <t>Tue, 17 Mar 2026 14:17:17 GMT</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWEZEN0lMT25QLTNHSlA5UW5QMlhHX1N4UXcwM0xnMWRzcHNiQzJrdWNiQU83cXA1dE5nd1FwR0NCX2x3Y2NuTU9qMENITnpPRGhCWkkxMjNDQTZSWGdSTDFIR1RTM1dnMEM1XzBEMGtmek1pak92SlkzNHg5a09Mc2hYRTNoMlFXOG1wSGdxMlBGRU9GU0VZUlVIYVN0OGk2R2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOaHFXN0ZWTG5aUFBGNjNqSmdJT2FqeW1MN3gyZ21adzdEZFRYRjg5a0JGOGx3QW5fbjNuY05UYVBpVXFrUUt3cHVBLS1pREEtNUpsMXFiQ2Jhd0w3a1lHNTctMWpnX2dGN1NHUE5jUk1ZUVNsakxTNzFaX05fZXZibU5QTVYxOHlDdFAyaF9pZ1VKLWZLbVgwTUZwdzlkU3lrVkR3MlljaGR1UXFIR29GaHhVWnVyU2o0a01USjZESEZnU08zTk1yMDRnU3ZkMC1YLTJKaHlmOWtLZDl5X0ZPNXVFd0xGcDJMMnBnR0xqM2Rta0VGSUdaUGxDVXg0c3FOUEgxSQ?oc=5</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -5381,17 +5381,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Internet fraud in Ghana: Immigration arrest 93 Nigerians in Ghana ova alleged internet fraud and oda crimes - BBC</t>
+          <t>UK launches new anti-fraud strategy - Pinsent Masons</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:02:55 GMT</t>
+          <t>Mon, 16 Mar 2026 14:54:33 GMT</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE55SHJjRXZQWG54S3FVTTVNb01iN3JxckhmbGY5YnBTWE9MNm1PdzYxMmF4MWtHeVhnU0VfemJBMVhpNFVqSVVOSDROOGxzZlRYbW41dDBndEVjS19U0gFiQVVfeXFMTmx1ckRmWWF5cHRmZ0pFaHlCa05tU1pjRkEzMXJMQlY3eDRmS0dGVm5ra2RnM2Z1VWxtcUtJX0NMU2JoOXc5NXpuay1oUE5vbW9jY244Sk5GZkp2Wm9mbnhtSFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNYWl2RUVrX1Z0QkdIUTRfRGtjTGhUMTdzcloyNTlhRXBzWkROUEQwbm5la1VBcHRJak1GQWs2U09NcXJnb0VCQTdITFo0V2NRSzRmYlZPUGMyaE45QW9ZNlI2LXZIcS1tUjZ5Ml9PQ2haTEZtZXFqbDVKcHQybGNzdWF0QWY?oc=5</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AI helps Virgin Media O2 detect and flag 1 billion suspected scam and spam calls to customers - Virgin Media O2</t>
+          <t>VIPRE email security integrates with Microsoft Defender - IT Brief UK</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 10:03:36 GMT</t>
+          <t>Tue, 17 Mar 2026 16:54:00 GMT</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNeUtibERmTVVnam9UdTdiQXprX1JJWnNSU1NCQmJsdkZxXzhVaTFrcndXQ3NZUTA1VnVaYjVMdzVIaW9YS0lRblBHRk96NjZuX0NYR01WblVHbDd1SkJsQ084S1haalg5X0I1V0l1aTRJTmJLUkRBSm1CcjlUamJPZVJ5YzNsVzhfMEhYUFBzR0JpaUJzUnFVVHpCUzhZcGt1bnQ0OXRZUURXakYwcFhjdVF6aFlxZzdSbWF5LUJ1UXdXczBEWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNzI4NVZHc2I0cExfSzBaSVczcUMtQlVKaFFjT3JaTVV4Yy1HSGl1MVk2SEVrMDhmUzJYTGV3VHpGa1c2dHF2MEhLVzJ0NE11WVNER0t2dnZnLTlRSEhSSHdNVC01OEM5ajQ0UEh2U1N0dDZtbEh5LWxRdG8ydnZVeEpVaVY2LUhmd0dv?oc=5</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Disrupting fraud and strengthening support for victims - new strategy released | New technical rescue PPE rolled out to firefighters in the North West - Emergency Services Times</t>
+          <t>Impersonation Fraud: Woman scammed out of £17k travelled across UK to try to find them - BBC</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 05:00:00 GMT</t>
+          <t>Tue, 17 Mar 2026 00:00:38 GMT</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwRBVV95cUxObWhhbGt2Vm1KbUVmLUEyQTY0QndBMWlHc2Q2anRyY01FWmRFSGxUQk5NcEktc1BnMHJJVloyc3dwODFlZDZEWWM0OGlxcy1vTWhtTkpKaWJ5VWloQm5fR0xIblM1M3BzeFFOcXU5ZHBpMG5MZk9Ua0IyM1NiQks2RmVWUG02TU9WcGlaRFRGc0lEUDhmakhGc1NfRW4wWC1DRFlFUmZCTGdSLVhYYWQ1UmdDakdkcU9NQ1BOUGh5X0ZBWklSNl9xb19pbHBNSkMzLXp3a1kzTk5rVlladU5uVkRpX080eXFzWXlmcHQyRjdRalRYUkl2ODVmcWQ1blA1WjVyWW02WFdTV0tjZkNBVzUxSUlKeXhmeld1MHdMWHVnQ2dFdkRkX2NVNTRWc0RqZFU5R3laMnQxVEkwM0g0Nms3UWJoZlpZdHY0WmdjbVI4TEhHVDczUlFQYWhFcGdBNWZ1UlJITURSempHcnJCQ2tBclF3anh2MlFiby1pQU90aVdpb0I4a21hNDl3eUpndFBCcVpnZU9tM3MzWUIxVUg4QkxRTFltMXkwSHNwSF9aRks1MTU0SVNSUlZUYUw1OTlMN1Njb2VRalkwQmJmaVhiMWxZbzFOVkEwTDdWS3piWWx1TGtrd0x2YU1LYmFxSkhLc1lHaERudEpmemZtMWlnWDVCUjhzTlBkY055MlhQRXpYMlI2anBCcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9VM1R4VkN2TVp6dUxoRWs3R200eDlzcFZmZlBWRGE5UkU0bmhDenM2RDZ2dF9ZUmdlSVB5cTdteER1OEo3ajJJT1kyYWJmLUJjRUJtOUFpOE1QQQ?oc=5</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Judge strikes out taxi driver’s fraud claims against law firm - Legal Futures</t>
+          <t>Three men accused of 'illegitimate payments' over migrant work visas - EDP24</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 00:21:26 GMT</t>
+          <t>Mon, 16 Mar 2026 13:23:16 GMT</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE82bVhpektPLWZzMmx3Z0tiakxuZTBqTWhJMXpVQi1PLXRRLWJvbHNVVFFqN3NIampXbW9NTS1KMUdTNGgta05NWWk3bFg1Q085YVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxONkJzTnpSWk5DQ2hkeDFXTnhCcEIyX21qZmpIQ1VXcDkxSWF1X0c0cXBQd2lUWU5vc1YtY1dfS0ZfWVYtODZSX2sxODZJSzZnSjQ0MTluU21HOHRRcTcxaGJUOU9hbnJZX0M0OUNVRk12MmFKZEIxRnFkb1pLaWJ3YTVSY1Iyb2hUSmpVdGtvdk5YVzB2cm16VV9R?oc=5</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>EU launches AI platform to detect food fraud and contamination - Digital Watch Observatory</t>
+          <t>FRAUD AND MANIPULATION—Trump signs E.O. formally launches task force to eliminate federal benefit fraud - VitalLaw.com</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 12:16:32 GMT</t>
+          <t>Wed, 18 Mar 2026 00:10:36 GMT</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE55bWdScnlwNC1uLUxqOGJmT1JFMmlyZHhpV2IybjZ1YjJhY1QzTGZteERpVV9IT0RnUWw4ZFZicFFaUzljTWpDRUtVMFRVQW44OXI2d05fS0Q5dWx0NjBCUks1TWZxXzgtN2o0ZGg3MHk4RTF5MnhBVGRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQSlBDS3ZBYU5LWV9hanl1Y2tVaUpOakt5OWRNVXFTd09QMlB5Qmx4Y3BZQ0pDZzlyRHQ0SFJCQmM4MGN6UVhBZUxxbXBGYXJQYWl4czdna1o2R3hCem1zaW41c2xmb0dLVnZURzlVMWhoQXloSzVRcWlKdExITzdVcXJfbWpISndSaUJqd1BFZTU5WW1OYkVIaXRFV2p5Q2xkdVZjSmFobkdkNmpMRlYwQmZzNFZ6NDZDanR5V0FTNjJPR3VaY2puNDJOdTFYZFJNNDkyUmFmUTdXbXh6ai1QX3BwU1Q5aWNmaEhUWGZvYjRUM1A2WmJzTm1vNjR3aW8?oc=5</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5531,17 +5531,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>The Tycoon Who Had a Secret Life as an Alleged Scam Kingpin - Bloomberg</t>
+          <t>Oversight and Intelligence Subcommittee Chairman Cory Mills Delivers Opening Remarks at Hearing on Waste, Fraud, and Abuse in Foreign Assistance - House.gov</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 23:00:03 GMT</t>
+          <t>Tue, 17 Mar 2026 20:27:06 GMT</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOb0h4NWtWbHpmY2RCWHd2cDVLM0JmSjBPSUlnMVV2UXluck5SZmNVcTdSaTdlRnZRVHYzb09aRXBZSllyTGktMUlBQmlGUllRSjBUMzlDR2NlQXN3T1piX1JzMTlwZGZQa0ZFcXlvQVFhWmFrSkJmdW1IT2NCbWFGeDk1MXJWLU1IQTQ5a0k1NmpSY2tlS21pRHhtMEFCWl9VbnpnS2lGd3VxeE92RkctemRwUnVFdklOcS05T2FVNkN2WlhFRTlwcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxPcXFMMVdlQmZOWE4zUFVrR3Bvamx1UWdROUdZbzZKU3dXNzJoQXBkeVFTTVpKUUhwSml0TGxtSXRmbkhOenZ0aWNWM1UwaXk5TFhJUWpwS296M1hpcGtzaW5GR09MaWZkMnpubWR0Tm0tSTdmZFJ5cVk4NWppZTF4OFBzOTRzX3FraldwU2lQVHQxaWVIellXSEpqNnNaTjRkWExzSlRvS2RoR29uOGlzTVBwRTFaLTVNenQ2dDFac3I1VTNadG9meDA3M3Z1cmVWTlk2MXJ2eGlBZjZiY29WUDFibXQ2bVpPdy1jQkNYMXhlVUo2ZVpHY2lUTURxOUJmdWtmMnp3ajhkMlZ0RG1aMHpuM1NQazZCSV9zMUtEQ2k?oc=5</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5561,17 +5561,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Telstra partners with major banks to boost early fraud detection - Telecompaper</t>
+          <t>The Trump administration has opened the door to waste, fraud and abuse and put national security at risk - Citizens for Responsibility and Ethics in Washington</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 06:33:15 GMT</t>
+          <t>Tue, 17 Mar 2026 17:38:18 GMT</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVkwyUFRtN0ZKSXN6R1BscWxXWm5LWkw3M3U4MV83dnEzT3hHdXI2clI3TS1yYVdhTHVCeFROVzBHWVdZX1hkWDNJbTU2dEZLdnA5WjBFWWY0U0hFajA5cXJnbDJYRndza1g4ZjJfZFhRbUt5enVXMVpEUmVCbGZVeVV4WUpvTGRxU3E0NkNINHhpUDVvbmhURjFFaWlCdXd0b1JSV1lTWlFlakU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPNFhqSmhoWmhlVWhSYmpXdDRPTWQtMERSNVVMWGU0ZGxKQi1TSUxyNVR3dk1NdDViRTJOYUtaU1Zzc0NtRXhLWTdGdVBsd21HSmVxX2M0V0JGdFhHQVE5ZTdyWFdqUVRTZ1FHMnFtR2tMeGp3UVhSTjJoandsTGJPVEhZV3pIeGtIY0VqM3NkLU9UWlpMYi1rSmpOR2RQLTl4ZnNsaVhXeU5FOXM1a1RCNjl1aVBZV1dXRDA2VzE0bzBrTW9jemFsYUZiNzZHcUp2WkRQT1hQcVk1WktJcFU2ZXQ0X215UmNUdVlFbjhOTlExRkk?oc=5</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Signal and WhatsApp accounts targeted in phishing campaign - Malwarebytes</t>
+          <t>Google, Meta, Microsoft Among Signatories of Pact to Combat Scams - SecurityWeek</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 11:23:24 GMT</t>
+          <t>Tue, 17 Mar 2026 12:10:52 GMT</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPM2RJU2EwQXVuMG1DUEdsMDNodWwzZWxyVEpSWlZaQlEtLXpJMW9BUXZyXzFjYmJERVNNaFl3TlhmRE94VWx1MFUyMnV2U0Z1Z0tKNnB0WXM1MG4xNUdnZnZfNEVTcDBXdS1wdDl3WndCU0F3VG1CNzg3ZzJab3JXQlhNbHJSRDdHTlY3c09XaHJEZGFmakVIU3gzbTlzeW9HLTIzWXp5Yy0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNT2ZoYjVadGRvNEVGSHVDMWV4QksyYU90aWVWeW8yMk5Ud05OaFpoOHptQ1habVRoSXE0SE9CV2tpRnViOVB2ZnZCc0llUDJpRmNTejJDN2JIeTJaRS14Rmwxb0xlSFRjWDFCZncyZkxtQ0RxdDB0VHpDdENISGVBd081X0VXRlZDeHRLTktMQmQ5YlBabklXSdIBngFBVV95cUxQMXJBZ1EwbGF0N2swMGE2amlHQTZ1SjdDTTdWTzk3RktKdFV0cmMxWHlKZW9Yc18xX2o0MTJ4Qi1ETE9MVVVIYUhveHk0ZVZuWHlUTEZ3YnVGWkVOM2ttdnlKSGdRM0xhU3FkVXh6X1dlOFRZdVV4WnJVNmxDdFN2QzBjVF8xcEZobFFYeUhSMXFGN1lNcFhmR19kMXMtdw?oc=5</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5621,17 +5621,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Telltale signs a bank message is a scam (and the simple trick to banish them) - Yahoo News UK</t>
+          <t>Anaconda woman shares her story of elder fraud, and how to protect yourself - NonStop Local Billings</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 11:35:16 GMT</t>
+          <t>Tue, 17 Mar 2026 23:53:00 GMT</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQWXFaNzNDZlVvYWlwSlduT0ZtYkZacl9wd19abU9hUkgxVjlXX2xxRm1TdS1DTDFISWx0NWVvVDFEbVp2X1ZHN0dpdGU2RjJVWVpDYjV3M3JzSWloMmt6aFJySWVrcnRSaURyZllBRnZOWnpsaEM5YURyQkx3Ung4UjJGc202M0hjbktGTWN6Q0FiWmxNMmd0T29pTjlhX2g3OUJ5ZXlYRHhxeG1lYTVHSXdUYnZnOUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOUUJhTEtHUG8tdTRzQTVXN2NLbUNTYkRLbmlFX0M0dFBiaGwwT3Z6WE12R04xc1p2VHR4R2dKaGs2YV93anpZRURMSHRMbTFCNENVZVlrSFQ1bXVfcHFxM2N4TThKMzdFSUVqYnJta0h1RTdieVh4R2RDeDIyM1RYclJyYlBHbzM4bkJzX2lPWnJ1S2V5VDFnTzBuZ3JPaWhWNEt4TDJFNzEyYkdlc1R6TGlmOWVBRDcyb04xbktrNlpGZm9VME1lX1Z4ZW5vS0hsNHAxaWFTRXZtREQ0dWR3cUJDY243Zw?oc=5</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5651,17 +5651,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>MoD perm sec pledges anti-fraud performance will improve - Civil Service World</t>
+          <t>Ex-Shire of Coorow executive charged with fraud and corruption - ABC News</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 12:29:26 GMT</t>
+          <t>Wed, 18 Mar 2026 06:36:12 GMT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNcU5pWUNjLTh4anlBOS1QOWY3anA4V1E4SFRuc2ExU18yMWJTT1p3cHgwOGFMNm5oV19LTTFQcXZyU2d1QUJzZHFDZFZIQjVScGlnb2VBS3ZWTWJteFFKOElKWERRX3dZVUpFSUhBdkxIaVFFNHI1TWswVUYtR3ZjVTNoQk1PaEt1RjBUQmVydFNUQUNPdDFKQ0MteHBkejhqNXVsa3RIcFVpRklDYVpqbjRkTXJTNU9aZi1JQVlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOY0w2Z25ZZWw4ZHZDd2M5UmZxLVRDeHFaR2FCNEp4WlFnX0U5U2R0bzZiSHNxN25kQVNMVnV0MjYyOHFidFZraXNmOS02YVlfdXFYZm9Ca2xaSkh5Sld6UjFIMUVBSC0tY2owSFZSNExBQ1FXRnJ4Tmt3QWNCVmdHVG5ZQjdwN0ZHSFVHeEhjUHJRMlpNQ0lfUjZYMm5BeFBOV2NadDdR?oc=5</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>China’s selective anti-scam campaign poses a paradox for Southeast Asia - East Asia Forum</t>
+          <t>Scots crooks stole nearly £9m in huge VAT scam – splashing dirty cash on gold bullion - The Scottish Sun</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 11:00:00 GMT</t>
+          <t>Mon, 16 Mar 2026 23:03:00 GMT</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQNG1kVGJkZldlN3hrUUdrUGlxZE1KSWp1Q0ZGZnJtMnIxSlV3cWM2TlFiU1YwQ3pXa2c4OVBMN1lVR3k2QnI5YW80N2RMVmlCWnJHN1ZyaU5Ed3A1Qmw1aUNPVW1FdTBpMUR2bGVrQlI3aDc2RGtCTFdqcGQ1dGYtTmh2bjVTSjhQUlJ4SkxqOXRPUmd0RFNvdXV6X0lHV3l0RzFpTlBmeXRXMlJp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNaXBfM282Nzl5R1A3TkM4T2NkSHVjdS0xM3o1N2ZTWUxQWWZnUTNrSVdHYkk2bWFBT3FzZ3pqSFVZLUtPemxsMFQtWC1tVzEwSng4NHpoY0M0YlhqdnN0czNUWk80M3N2VXZZbFNQN1o5Zk9GbUFOYTVXVHozbTNpc1R2RGdPU3JxWlh4Zm1LYkZoYUV0TFh1cw?oc=5</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5711,17 +5711,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belgium, the Netherlands and Luxembourg sign treaty to combat social fraud more efficiently - belganewsagency.eu</t>
+          <t>Ted DiBiase Jr. welfare fraud trial: Judge denies motion to dismiss as defense begins case - WLBT</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 12:40:00 GMT</t>
+          <t>Wed, 18 Mar 2026 03:19:00 GMT</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVURxbzZQN3NiTTBLU0hXVzUtYks1VUdZenhxRE80TUJ3MzgtMFhWeTRhaEd6X01jenIyeDlRRHB0ZnpoOGQ3MUdMSVcwSjV2Q2hoNV9FQzNRTmVocWVXVTA4a3pTNzFhX0FiT3UtUERjWHVwT185WHlnSkdrZDRWZ0lGbGt5MjRIMkthWnBYeFk1Y09TczZZUWZRb1dDY3R2TTlwUnZLRnhPN1VMTk5xcWZEQVBVQ3lEMC1hdHRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNbV9wWFl6TGFpTHpxbzVFOXp6WWV5bUdvZGxGd1dEUkdIMHNUSnZ0dks1SlJuWXZQb3llMEVjMVozWUNob051VVFUSFNrbEx5c3p0R2YzYkFfcmFnb1FsOEt3U3ZUMDdmR2FBZDB0TGNtNjRRQnpuYVRUX1J6TldYQ01INTVHdkJHUzd2cTlXNWlfZFJuUlpsaVJWVEVETkRfdFBQUWxOWWRvb1lKaUFwY0pXZlFXd9IBygFBVV95cUxOWjNEbUlQWTk5UmpnM0xiZ20xMEhIMjB1ZlBMa0xkSmNCUTBoV3pCQWRUc1ljaVVJaGgtaGRHNmdHbUg0elVJWjFob1NPNG13X0w2QmRDckNPUy01QWFEVkFZWExwbW53QUVoRHF6TFdsRGFwSXMtNFVsUmg0dlYxQU5vUk9jXzJ1cmhsR1BBM0JxLXA4MWRRQUQ3VWl1S1dFQmVMekQxYzlFZ3A5alBMYmJBcUJaeGNMT3ZrSVlYSVRDS1NwcXJUY2J3?oc=5</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>New SurxRAT Android Malware Uses AI To Automate Phishing and Steal Data - cyberpress.org</t>
+          <t>Jail time imposed as Albanese Government cracks down on NDIS fraud - MBS Online</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 07:20:58 GMT</t>
+          <t>Wed, 18 Mar 2026 06:18:07 GMT</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5aZVlJVm5WMnFiVVN2ekplODlYN2RBcUNQRDNoWVNoU1VEWUU2UUdjVFVUbWY0MHJMUXNaNkVOdmdmajFjOVdkaml4WWFfLUdKdmtkMHVvYU50akRtUkl5YkJQYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQVFM4VmRRNThpUjN4SFdmNl94RC04a0dsTk9tR0RObnJ1SllQSl8wb3JfdWlyTkJRdVZMaHdkSEs4MlcyNTU0UTNTNFBKY1BMUm5rSEtNQzg4SGRxcmhxUG5idU4zdTY2V3ktSnoxM0dxcWdENmxLaEYtU3dsNjBXejlfWUlkckpUYXdqWUxZQ1VIbDU1cDduYk9rLVZIM1ZjMFl2ZmNKOF9VN3p1TjA4NDJNMUtYUWlzVk9FTVIzazdWZGhmY3NOR1NGZTBCRzFaU2ZMM3pNNGo2cWZjN09rbXpvNVdRNVFv?oc=5</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Synthetic Identity Fraud: Key Risks and Practical Protections - CLA (CliftonLarsonAllen)</t>
+          <t>International police launch Operation Atlantic to combat crypto approval phishing scams - CoinDesk</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 22:08:15 GMT</t>
+          <t>Mon, 16 Mar 2026 12:54:51 GMT</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQUkFlbG01WmwyTWNjVGlud3o5VFlqdFhnMDltVHg1R1NoQm5hOXRqblg2X18wVVJRdzVQak1wMWhwUHhjN2FnV2ItY2w1WTNfVG5NN3hCQTRFMDVVcll2MVJfUWFub24xamlCaFNzblFmcm41LVNQRm5LM1RwTGpKX0hB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPbWJuWG80cy1mSmxYbmVSdUNjZ2VibENib2g2STA5dnNvSGl1Z2JWdVk2QXZkOXJ5V2xwV0llc2JGdml2X2szTDg4RkhRaHZsN01ZamdlbFVMalpFSU0yb0d0WG1TOS0wUE1zTl84d2wtV0JIRWwzQlBiUFJhZkU4VTlkNkRzX0Zwa0k1SlFrVWZHTlI3TGZDaVpzeFMyd0kxdHQ3MUt6ZXA5b2tOYkZJa0pCZF9WNmdEcGJLLXJnYUhNNFk?oc=5</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5801,17 +5801,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>A Massachusetts man has been sentenced to federal prison for bank fraud and money laundering, the U.S. Attorney said. - facebook.com</t>
+          <t>Georgia resident indicted for targeting athletes in a fraud, sex trafficking scheme - The National News Desk</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 00:00:19 GMT</t>
+          <t>Tue, 17 Mar 2026 13:41:53 GMT</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPLWpvR3dqWE1BcDZvNkFmTFAyU3htUFFYSWJDNVZGZngyRUIydTNYX3NxWHdZWkw5RFhxeUhXRDJ0SEhRNGt4TXFjZ1FfTDFHdk9BTHRsb3BwRjFkbFZ1SzJraHQxb2JFR2RPdkRwcUx5MUtDSkY5ejQwdVdVWnhrbG1IbHlxbU94N3ZTWEYtRTNWelVqUUlRcWU5NTdrOGlvSkt5NnJpampaVHpOaGZtXzVDWmlrYkxnSmhKcm10bTVNdzNBby1XaGFQX2dIYklXZzQ2a1FlWGZaZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOZHRBRm9yQlJyVk53eTdQOXZHc2lRT1hSdEdoV1M4eUdISWFsUHVSLTdCdll2czFQVFBYaVl0WnRLd3FBbktXY0ZrdENKcy1fdG9sWWgza05qRnNBeDNtSGVmU3loUEYwOURDdXJNeHo1cHFtcms1WUNpVUw5VnFyR3ZmdzE2VUJnX1JPN0V3ZzdVZTdWSmJrRE5aUmhvbjMxaUpGWllDYmdkSFNWaWdwZlY4c2U1ckRjSkVEUEZXOWc3cmQ0UDZuUjM4MzN0bzVDNGFwWEJIVFNSODlmeHVBdkhYNS1VOENEN1dMX3ljUDhDdw?oc=5</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5831,17 +5831,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Judge drops money laundering charges against former FirstEnergy execs - Cleveland.com</t>
+          <t>West Virginia doctor sentenced to prison for tax fraud and obstruction, prosecutors say - WCHS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 01:41:00 GMT</t>
+          <t>Tue, 17 Mar 2026 18:42:58 GMT</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQTGExV3lkNkFkb1dkVW4xNmZxSEJyYU1xOGRJTjBDcGFoRzlKbHdNVzNkZk5mZ1ZjdFZPTHlVQ0p4TG5fQTVVc1ViQ01sb0FhMnc5UjhNN1B4V1dxVEhld0RleTJXVFAxUGJvbjhrSjFjZkZfbzBodmxyWDhXQ1FYNlZ3WEVTYWtUcF9KNm9jZ1lxa043UExVVGEwN0tqT2V4MDZlS3YxbFI1UzBHeU1YTmJSa2c2WndX0gHMAUFVX3lxTFBubW5WZWlTMzhpanpBeG9VQ3lkSWZzVkcwc0d5bE50WmJiVGE5MS00ZDEwUEJtQXR1LTlwRjMwcmVUUUR1TXgtTG9QVEVZVjRMbS1YOXJaVk5md1RuSGJ1SUdiVFNQbEVLMDFVNUdmWEhIM0JPNEJ3UEY3VEdfa2dlNkdwN3B0SFJpcHd5Q2dqR2QzUGdSSmFwcGdkaTF5emk3N1JOWXNvNUlyX1B6WUtVbm5UT0N0ZDNrYTNlVEpBeVRxMERFUmZMdHVEUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOb0JJLUhPa1JNS2V6b3VEbUMwRWl2Z3dCNjJIazVGdlJDeFhfb0ZJQnV2RzVjNC05SWhnWVZLSXI4TDlxb0FXTkVpSm1WODVVeGhibU5PdmtuUnNNVHROYXVxcWd6X2YtalNoNnJSaHVWSkRlanpaTzZQY0RzQ3FwcEdkeU40LTJqMVFhX2hkNHlZMVlweHV0TGJyTDNvOVJsN0hIaENhVC1zdDVnSEtKQk5BMll2Y2s?oc=5</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ghanaian national pleads guilty in $100 million romance scam and BEC fraud ring - SC Media</t>
+          <t>Medicare freezes new supplier enrollment as Russian‑linked Texas fraud case unfolds - CBS News</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 23:43:05 GMT</t>
+          <t>Wed, 18 Mar 2026 03:23:35 GMT</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxONWdMakdaeW1mYl9zWnVON0lTT3Q1akNORmthZHowcS1idmR3RTVPZ3dKcHNwMFJFb0Jqa2laOFVhck4zNUxlMTZXYjVFQlNPdWNMcTJhYVpXdG92aGoxZExkTG9Xdk5YaGExWEFLZFlsMTU3M3E3d291eU1CLThPSnlFangyQWdxVVU4ekw3ZEhrc3poWU9tU2tnZWRNVFlGTkZzMmxDNXdxOThN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNRGtEVlRKLW5LMTFNTU9XcERZQzhEYU1vcDdtNVF4ZlFveWp4bTRLT05FemU1R1NJTDJ3LUZpWGYxc3BHN2VibkJMZXRQRUFpb21FeDBCS09SZ3FKLVRQak91cmNobDByQmFfS1NBS2VjWE45STFvd09vZTdybmJRZEFYVlNUWGo3aF81UmcwT2cwUHVydVloSzBSOUlmLURfdHhTeGZDdFItdDg0d3ZWNXpEOUZkdmR1RVpJ?oc=5</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5891,50 +5891,20 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Crypto Hacks Drop in February as Phishing and Wallet Scams Surge - Crypto News Australia</t>
+          <t>Skullcandy Taps AI to Fight Fraud, Reduce Decline Rates - Consumer Goods Technology</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 04:56:39 GMT</t>
+          <t>Tue, 17 Mar 2026 15:12:10 GMT</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxORXdpaGJBVUxQc1NTSTU3aGg2S0l5TEs2SHZNNnRfdnRKM3owaDNsTjBEMEt2SXdQUDlrNXZxQXdyWDN3UGRLemRtOHFISTg3aDdHaGJEa1d1b20yb2FwdzhUMnQwNmEyRFZGVURtSDUwN2pqaEFPR3BrNVdxN1EtSnVCU2gwMEFSRTNIQVNhbXNneDFJaTN3NnMwZUdESmJmN0dlZUVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPbmQ0UzZtTzIwdzZyV1hzTTdzWHZyY3JlQXU5ekN5WnpYcnZDV3NYWTNtaHE1T3htcERLMFN4R3AteEE2WlQ2dGVsMENDd2lfeEQ5a0hZVEdVWkRWeTRCZ2dnTV9ua2J0MFl5ekhOMFF4VmVzdDZTQ0xIRzdGRWRLVEktVQ?oc=5</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Radial Selects Riskified to Power Payment Fraud and Refund/Return Protection for Merchant Client Portfolio - Business Wire</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Mon, 09 Mar 2026 14:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQeUpaQmNJZE5yV1ZCOFZpUlFMc19KV3c4U01EcUZWWlpDUkRZZVMzeGdmLXp6ZnNMVmQwcDgxSXNLYWFFTEd0UmQ5Uk9nM2JZTlktZXVQdk9WclFaN2N2SmVjNnVjbHBKTlljYzh3dzJtM002SGNHY3lVaUhieldUNTdEbUR5Qlh5TGExNXphNGktN1hpdm5ST2NZd2doc21HSGwxdm9xeDFpQm5MRVo4RWRnSHowT2FqZXlYWG8tV0dISHkzMDFaUE9ZSXNqUGM3Nmtxdm9sdzc2RlRKb2kwZlc2ejlZeG1NS3BKNlNWZFNXSVVH?oc=5</t>
-        </is>
-      </c>
-      <c r="F184" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/weekly/topic_feeds_week.xlsx
+++ b/data/weekly/topic_feeds_week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UK nationals fleeing Middle East reach 100,000 as evacuation efforts continue - The Guardian</t>
+          <t>Changes to UK visa and settlement rules after the 2025 immigration white paper - The House of Commons Library</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 02:30:00 GMT</t>
+          <t>Fri, 20 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPaEllUFJEOEM1a212cnhlZW9xOUFaclB3QW01UzFmM0tYcC14UlhYLWtLblJ6NXhZaHJvZXVsdVhzMTZ6Yi1kVnh3ZWVnaW1lWXF6eVpNdC03UkZtVHo4MXFRQlFtRmtITGVhVEppbU5FOUhjT2tidWpfaHItUUNhdXctT2F0OHdSbE5CTWpMR1RFYkFOaGt2MkZQZmZsOHZYeE9NaTlGbmF1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBXb3hZSG02UTNOZXFvbVV6aHdkZ1FBcTI5QmlrYnFCX0ZnQ0MyOGFULTlkZ2N1UGloZHd3N0xkT3J6VE1KRFdfN3RxLVV5Q3BEbmhwTVJ2Zld6M2owTTNuZDZnQVZ3cXp5X0ktakVGUEJna29h?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chancellor’s growth plan sets key principles for UK-EU alignment - GOV.UK</t>
+          <t>Time to Pay Up: Government unveils toughest crackdown on late payments in over 25 years - GOV.UK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:14:38 GMT</t>
+          <t>Tue, 24 Mar 2026 00:08:20 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPcndnQUtMZUFBcTlRZ1l6V1VrV2VYNGUyRDZiX2I1ZkJVUTFTNG11Vm4wX0NuY2hDdkxlNE1NbzZEa2VVRERhdHRpYzN4X19XT0tIRzlJSk1aTDJLMDlDT0pDNGFxV3o5ejU0WDBQNUdNcnNDQTZwMXpVVlc4UEJkZEhyb0xGOUtvZ2lWb282UFFCT2xiYWd2YWJ0dzgtaHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNMkRMZUptbzJNdV9UaXJtMWlreTM5WUJ4Y2FseGp3SDVqS083a05XckRPTzdwNjAxYy1iZE91ejhDM3Nfbk85SWJrdTM5Y2Nfb2R0VExCdVdrWmJneGhEYk1TWkZhTnJBdmVVUUo1QlY5VVhoTE1abzlkTUM4alNrcnA3MFZBcDkwdi1VV0RrN2NRZUFPZ21MR0ExZ2ctUE9kYmhwS3R5amJWbmlWVEhpNk1IUUY2RV84aW1sMHh3?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Worlds Apart: British Muslim Attitudes on the Iran Conflict - Policy Exchange</t>
+          <t>BlackRock boss Larry Fink warns of global recession if oil price hits $150 - BBC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 22:02:46 GMT</t>
+          <t>Wed, 25 Mar 2026 08:04:43 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPUlBqNmtxUHhsajRJVy1EZ0xKeEdqbGdxeWVXdWloYmw4YUV3bnMxZFNOdFpvWEREUjZoZk5sekd5UWNjU3U5Q2FRbDZhdkRzYkhWUUh5cUFjQUI0elQzcGJhcWc4bVdhUDBmMnhVQ0l5UnNqNzd4dTJsTFQxOHpUbmwxd09YaVoxRnVzNGpka2NjenVFaU5Eb1pxMFN2SzJEYnQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE50SEhfNnhMQzB0aWFPLUVHcEFyaVA5M2NmWVFEWE0yZmQ4OHg4N3RNd2cxQmtPRFU1a0lKeGFxTzI2UXo1RGlJc3pYN29VRTk1UnhVNm5ZN3NMZw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UK returns from conflict zones: Why individuals and employers must seek tax advice - BDO UK</t>
+          <t>UK inflation held at 3% before global energy price hit from Iran war - The Guardian</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 13:46:58 GMT</t>
+          <t>Wed, 25 Mar 2026 08:03:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOX0tiQm5Rbm1lUS1OanlIVWw4eDBwUEl4bXFFVlVoTXI0UHRZdklpOUZsU1dqN1ZBcUl2aHk1QkJrMVViWWdQWXU1WjhrZ09OTmxhWUFxMENLSEpvMUxvWWtPc2hPdHdOOU9mRU03LUZZbXpiWTg0dmUtNWpOZVZVSmVDdlEydlFxTEpja2tsQnRjUFRqRjRWMEJCQXhqVTVKd2dWRnBCZWdtZHkyd0JQY2N2T2NnakhWY2FFMGI3OGR6dUpGck9iM3I3OXdWNVRodHhjX0lVcVhsM0FqcHVnNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQdW9RdlgtdU5kbjBhME9Ca2RXVkVWd0ViSF83UjBJcU1zXzFvU1cwaEVpMTVfenVzaklZRnZnajlqVzZGU2JjdGdjX0liaFdKZHhYckRVNWdrSXZGZm0ydFVGMHNQalRZajZQY0JBckxSSW5zbUdtX2pvWTNjTkl6X1M3eU1QYWlKRDZEaE9oUTlfVGxWQ0VjQQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US eases sanctions on Russian oil What should EU UK and Australian businesses look out for - twobirds.com</t>
+          <t>Keir Starmer to bring forward EU rules legislation in King’s Speech - Financial Times</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 11:54:50 GMT</t>
+          <t>Mon, 23 Mar 2026 05:00:48 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPQ3RuMEllZTJKZjB5Mm55U3M1OTl3MmJub3JnNXVLT1VtT2lpMngxV3o1NW9JY0NMLUgtMFJ6OE9pajFyU1Fjb3ZMcWw4WjN0MEhSRWZKeFhDTk5vNkE3Zmo4WG9tc3ZWMVlncUVSWVFnRVg0UVExVVhwSlFRTWJaNmo5Nk5sbkFpUmlEbkhxQmRCTVN6WTBodEhRcHd3d0hYcWlaVWVsV3kwdndoQ0dmeVA2RWtjNVBodENuY2lLNTFHM05ZSmtqRHQ5c0RWd182dGIxTVZYbGExcHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPeHlkN3MwSjVheHB2eXhXRktOY3BxYUhaUHE5Y0ZEZUNuUGQ4UWRwQWpuZWtseEVNY0UxQWxZMmxGVlM0aTBOQnlBQWI5OUZVV3lrLU9ManFQQW9icW1CVjV3dkpjdzFMTDZNZ09wZFBNc3N1NEVSYmhJLVdOSG9tdzhfbGU?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Service industries: Economic indicators - The House of Commons Library</t>
+          <t>ECJ advocate general advises on Yemen sanctions - Global Arbitration Review</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 07:00:00 GMT</t>
+          <t>Tue, 24 Mar 2026 21:29:17 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE43d1RyejhtY3NLbXNmSVB5NXF5a2swMkt0eWJqanA5d01Iak1zNFMtTVJjczRiWnFsRjJZdmc3UnFQSzhWcTBMck1iWUhEdUdmNXYweFZNSE1ud2VEYVZKUTM1dVlKZDBfemZCN2RqdGhpQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPc1FBcFpJdnNsekIwTG1fVkZ1X0RoLTlyaUVDZW1DZm52VlBFMHBfOVdVNFpBblpFWHRwY002U0tKZC1Mdy1JcDdIM1VJY2xhOWg4bmlCbEk0dF95R3p2NlFoN04zdFhBblg5cV8wdWgwaG5BaUhQTDFaYTMyZDlKWVFUYW5vUG1uclZTUVdCTlpLUQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UK’s Supercomputer Delivers £8 to Economy for Every £1 Spent - digit.fyi</t>
+          <t>Middle East Conflict: Situational Updates and Implications for Global Mobility - Newland Chase</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 01:12:58 GMT</t>
+          <t>Tue, 24 Mar 2026 10:28:13 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNX0xwckNMaW1aalZGNlotUVBpbWFiSDVsLU15OU03RzllZ0ZacTJyMEJKOFF5dnJ6dEJhSFZUMWdzbDdaTDBfM2dMS2Fnd29XTmxuQ2dOR01oMUhJazB0aEJtcGg4QjYxemt0UzFiSlVUeVpuRGtVTkhaZkFiMEs0WFdpbFZCQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBnZEN5U3QxTHpnZUV0RVA1dFpHUzMyM05BTEREOUc0LXppakp6YVdTRnZzU1VFbWdVVGFKbXA5MWhnVDV4ZFVvQkRSOUMtT2pLY3NQdHliYlRJM1EtTGVJM090X0MyWmtHdWNFUUNR?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chancellor bets on AI and devolution to boost UK economy - ITVX</t>
+          <t>Russian Sanctions Spark Investigation at a Global Bank - FTI Consulting</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 17:30:57 GMT</t>
+          <t>Tue, 24 Mar 2026 15:39:55 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPRnNEMDZsVGNKVS1JMHhUeFRsMFdJbjF0MWswZU9SZ0x5aXN2bHg1dHpNeXBnaTBYaV9WUkp4emg2bjNfWmV3aEFnN18wekZiU0FRQ3N4NjB1dVlua29BeHUzZWc2bF9Oa3hIWEk4dkJxa3h1RlBVRGlkVUxTbG9iTjlXZVZtRkNULXZqSEdDdnpyUjlJMldnZVhzLXFJb21ubXY5M2tJc1pGdlNPU0RXUTNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPb2hNR29yQl9Lc3EzWkRVa1RKOTJhN0JVM3pDcWxUMEdqTDBKMnZSb0hhMGVWR2IwRHREWlZ6OHg1aFNMdjhOcVlnX0xjNHZ3MnV6NllHYTRDc2dxdk1rTEFzM2tHel9NSFFPeWdKamdkQ0drMmtYNWY0Q0toRFMzUE1MVm84eTNBVHNOdldDR2xJQ1JqLUktQ1dGc3NSRU1zUFhj?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyber-attacks against the EU and its member states: Council sanctions three entities and two individuals - consilium.europa.eu</t>
+          <t>How the Iran Conflict Could Drive a New Wave of Terrorism in the West - Vision of Humanity</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 13:14:37 GMT</t>
+          <t>Wed, 25 Mar 2026 00:46:12 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQUGlyZEJMWTdQNm8yWG11TEhnOGY5YTVhaEZxQWRZaGs3WTN0bmVkVW14NTdFTVlQdkd3TjNJTHY3NGVnR0ZXMDZkM0doalRqdXJNaWJUeE1xbWxsRXNxZmdBQ3NlR2EzemJPcEJWVm5QUDBnckRoaENVMXB4TDhrRUZxT1VkWnJhU1pQZXFDZWJUTDZWeXpDaVp3c2Q0QWNGWVZLQjBORXVhTHd1MkJTeXNCUzNCZ0V3dnVjY19PanZPOWFUVnVtZUprbFotd3p0ZkFyWWNoUVBvclF2eXpBblhfdjczc2trQ0RQQnM2UjEwa1pEdERlT1BOUjdLWU5u?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOOG1aa181cGxYSHU4QjllaUk3R1dnZlpHREpCd084d2Fid3BnaFNieGhoclVGdWVWTk42R0F4Q2pnaU11Y0hjbDYwRmlQRVA1M0VSSi0tazN0UG54S1pnY3Z1bm12bmd2VGpqblpiN2xFTXJLUG8wdTVEeWhTYnlQUHFLM3M4Z1lwWEdSWmFzV1VBeWNFYUM5a1NCMC1MS0xJR1puTUN3?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran conflict shines a light on UK’s ‘stretched’ naval capabilities: Analysts - Breaking Defense</t>
+          <t>‘The UK’s 'impact economy' definition must put ownership first’ - Pioneers Post</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 16:58:50 GMT</t>
+          <t>Mon, 23 Mar 2026 11:31:00 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPZklQOTJaMVAzSEk4MnY2OVoyWlJEMVdDTGdWLU11RlB5eW4tUGVkRkVqTHNXUG52VGFCM05UNF91UVQwZExmVTU0Q2VBSHF4MndVZnVTWDBZdlg0Z2FuZUlTZlFiSVJSVzFkcVNNTjZ5UWdQT1NBeHRfR2V6NDFFNnJ1SW10UG0yVHA5aEtQT3ItYnROM3ctLThiSEpsZTgyUXJMM0c0UmxBdGNSMWpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOSDVfQUdKUFlfczFGQ3NPbmpadUdiR3VvWUFYWXFSUnFTbXhWODc5MHBPUVZPbXFVaExWNWtPT3Bzd3ROR2Q3bG1SZjd4RW9wMG1rY1FNem9yMjJUMXlzRmdZN0RsaHZoNk5hakxyRGRibjluOGllNVl2aGpkejd5ZDA5R2YxMkVKWU5BYjFSMXc2LXQxRjdhSjVDYkx6ZURmYTd0bTlhRzdwZGVZTUFYSmln?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Joint statement on the escalating conflict between Israel and Hezbollah: 16 March 2026 - GOV.UK</t>
+          <t>Iran conflict jolts UK mortgages: fixed rates jump, lenders pull deals - mpamag.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 20:38:42 GMT</t>
+          <t>Tue, 24 Mar 2026 16:10:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOWWdCRVQtTXJaR2pXblhBdndUTVpaam14TWRRUWp4MmpHSjBxSjRmbzE0ODJjZjMxWHVNUlpMS3I4QktVRXVsSGdKWVY5VkljbDZQaU5RYXU0a2wzS1dzTmREbF9FVF85UzVKWEwwazNvMVZtN1E1bUFrcENubE43eWFWNlctbTBjQmVGUzFKVTk3LVpGMkUxcWhGeTJWYS1PWkcxVUJvWXZVc2NQcEVfWkM5aUFHV3RBZmxCZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOeWdNZlFZempuVXQtMm84eUhfSm5tRTlLTjFfa0w5ZXpQUGZoM1hhX0dVMDloMXEyOVZTNXdaUzg4UUVSZTFPWWdQQXc2Q3k0N2VPWFEtXzlfbEJXNmdycEJ2NTlOekZQQWpoS3VpYjlIOVVDVklSME5qenFBZVNrSGpDbDZFemJNZ3dyYnctOFpHS1FHX0ZxdDdfZXBoVi1aTjFBTXBQcHpvbDBHakNDbjFKOGg?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Isolated and exposed: can New Zealand’s fragile economic recovery withstand the global oil shock? - The Guardian</t>
+          <t>Iran conflict: TUC calls for emergency taskforce to protect UK from economic shock - Wired-gov.net</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 02:09:00 GMT</t>
+          <t>Tue, 24 Mar 2026 16:34:55 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPbFpqZ3p3Zm03bkZ5VklMektoWHZUZXd5NGp0NS1FVjVmMGVkLUMtZEoxRnM2d3phOGROSzN1azVpNU52aVBDUDk2elZnM1ZuSDZtZ19rT3JURF93bjZoYUNYRWYycXNSbk5yTk5YdXUwX08tdHZtamhKaFczaEFaT2c1SDFydC10ZTdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPOUZ6Qm1Wd19JTXNnR25temJURzdBWUJDTGl3emhlZ0J1N2tETS1HTFp3QmctdjRDYUxJOHVnWHNkUTUzMlNFdjZsNXpYTTVoQWNyWUJ4aEUxa1JOdEVNRmR4VDc5cDJpZHA5OHpmNzhzNm9leVphWDFyNUctUzNsUTVpRkc2NTVsdlFuOEs2SFdYWnZ2SWNEaWcwcV9wRWxWOHBYSUxVWjNVUVh0cXhud1A5NlNNdG54VUI0b3hEN1VrWnZHWGNLLUJlTDFVNGgyd2tMREtVYXlDOW80VGRZa0NR?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Track UK's latest migration numbers - including asylum, visas and small boats - BBC</t>
+          <t>UK's Starmer, Saudi crown prince discussed ongoing Middle East conflict, Downing Street says - Reuters</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 12:34:01 GMT</t>
+          <t>Tue, 24 Mar 2026 21:52:24 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9abkk0V2VWNThMdjNsdG1OMWYteGRuZWpJSmRBeE05TkVScDRxWHpsOTBBbldicVRxVnFWWjV6WkFBTjdZcUQwMVZoMHl5d1E4X0RyVFJIeEh0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNNkRCeVVXUV9tMlk0Sm0zWTJ4eUlKcWZQUlhwdm83cjN4X3lTNDhmTDBCRDEwNmtKOFRXT1pfX01YbC1NWTNJOFdabFBGaDMzbkNQRTR1MzZzbVBOSnFkVExPUWZIUlIxM0hsSzVUSXdsRlNIdldzUXQ5UmF4c2tqR3liSDNMOFltX0xnbDVnT2o1WERYYmJDdlE1ay1RR2lKVEkxQ19RTnRLRk5uWHhsd205VHd6QnROeGxDdF9sVQ?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe must prepare for drone strikes by terrorists and criminals, warns Zelenskyy - The Guardian</t>
+          <t>UK energy supplier flags growing debt burden as Iran conflict drives up prices - Financial Times</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 19:38:00 GMT</t>
+          <t>Mon, 23 Mar 2026 05:00:28 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNcDdDLS1xRk5oUWFpLS1Teno2QVA5X0dSODdWWVNTRjRLVHRLcHpEVm4zbFRvSUJKeUhWcDNyOGNoNXJwNWNHemtWVEtDSm56Y3hxNWlubUpkS0ZpSGdWRjYzQTJSRllUUXNaMEhjZjlNbW44SnQzQ3pFQmVDZXF0dHpQRmNNOGhsdXh2NjhUbC1FLUJodTdOQlJPck94c19kdGtrUF93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQYVJSOU9DSmdSaHJBWFRScC16c2k2Y2huNkFRdjRPdVIwdVQtSlVtRkFBVFFMUVR4TmtxWnZvUkQxdWNvTEZHMGdkQmJicjVzZVlSdGE2dFBJWUQ5SWJ1R3Znci1RVlByb1V0cm9pMTdKWl81dnVSaGVKRGRjekgtaUFtcHE?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reform council seeks to declare migration emergency - BBC</t>
+          <t>Trump’s sanctions against a UN human rights expert show free speech is dying | - The Guardian</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sun, 15 Mar 2026 12:17:33 GMT</t>
+          <t>Tue, 24 Mar 2026 15:57:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5NZ2lnUndTOHktMGJKb19zRkpoUnFQMmFQQm05YnNuTjd3anNoc0RCZjQzREp5ekRUWVVFME9yUVNiX195Z1JRODhSRWVGLWVKWk1mV2FkZWRrUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPSTBSNHhhb3piU1QtZFBBVmhlM25Ya2pCOVRyQUlxOG9rSFJUR3lmYXlhRHREUmRkYU82WE45S25GaGN5cGJicTZvVlBRSU5rcW5tSzh3WEdWRVFuT01kaWJxVVIydV9aV2pHZFZWZ2N3NjRvYWVWLWdMcWt5Z3RMRkZYZEhwaWNGSHFJU0FRMUM5RVdFRlhYaWJ5TTk3Q0xOWjNKcHFNNA?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spotlight on Sanctions - Norton Rose Fulbright</t>
+          <t>Philippines declares national energy emergency in wake of Iran conflict - BBC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 15:59:47 GMT</t>
+          <t>Tue, 24 Mar 2026 13:02:54 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNUJMY3JVcjY4U1gtT0tHSFVxa1lONlJWNnVZWGRkbjR1RDNNNTJISi1tOHp1cW53UWlfRUxmcUFSa0ZUM2FXWk5lZVYxTENJeWdmWXFaWTdCLTdROVRnMHV2RWVXQnZrbEtQRVA2S1JJdGhvSnZvNURfcDZnNWF5SlVkemtWRW9rWU9VU0NPMzlvQzFFV2l5Uw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE11RjAwNTZLQTE3MjFWeTJ3ajdlUFliZlNqaENFUlRub1NDT2FZdzl1VjEyV3hkS0MwczZFc3FZTjNDM05sNGJveGRXV3NsQWJ4RWFhRkdpb21Wc3NM?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran and Russia are 'brothers in hatred', Zelensky tells MPs - BBC</t>
+          <t>Reeves plans energy bill help for those 'who need it most' - BBC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 18:26:19 GMT</t>
+          <t>Tue, 24 Mar 2026 14:52:24 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1OZjBtbENiWFlFZ3VieVNYdDUyaGV1ZXVBSFZyeWFZZ0dwV0ZPeE82dHg1a25ZTGtUMV9fU1ZjWnVjc0dEc05leFYycmpmdzJzUm5DNVk0cDZaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE42S3FVTnhnUEVSTEFuaGpJaFRkc19ER0xNeGJiV2dTd1V1S2Ffdk9RNkplempHaUNpa3owQTRNSHg3d3hqYVdEM0Vkb3FCanJoQ09jTGFfQWpHTmI3?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Geopolitics &amp; portfolio risk in UK private equity - The Lawyer</t>
+          <t>Middle East conflict risks pushing UK food inflation above 8%, warns IGD - Retail Gazette</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 11:27:47 GMT</t>
+          <t>Wed, 25 Mar 2026 08:56:05 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNTzhoMjRoZmxWNEJNdDJ5d3hqYlhjYWR2aXpNTl9iQ1BtcmE0MlFLbzJCeGl1YWU1N1psaVVCMUJVcVNzLUdjMENJc1VDVEdyaThrcmVKeTM2Q1pDSzRLdGx3Vi1RdFdMMkJma1RNQTNpOVE0UVVUa2JVMmNpOGJpS21YSDJPNUZXRGxz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQMm9tN1M0MERYdzdmU3gzOFREcThRVjFraGVGc2lFRkF6alVnNkVYeU1SdUN4c0Q0bGxzNGRWOWZrRzFRcmZLTnRJNHFVRncyMktXRU5uSDNhRzdtNmhWZ3JkRkJPR1J4c0hkeHJBSW40N3MyYzZ3YkpFQ1BiaDhycGU3bHJ2d1RuNnhOdEV2bnNLY0h1QWdVRDR3bVZrdHIzN3UyVGNkdGV5SjliOXMtZFFEcUNzbG8?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cancellations mount as Middle East conflict disrupts global travel and events - micebook.</t>
+          <t>Keir Starmer’s policy on the Iran war is a recipe for catastrophe - Al Jazeera</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 10:57:57 GMT</t>
+          <t>Tue, 24 Mar 2026 14:28:47 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOcld2T3JDR2dzclVGT0FOeG5qcUpYZkhVY1BPUjE3RmhPcVR2aGhnVkRucGJDTUUzQlEyLTRNXzVSamFRRlY3RmFBRVRyMGgtRzVDeDZQVHNXVU9lTUFISnNUdDZwMU1wZEVHTEI1NExzMHN1dmpDb3loNlNRY2dzUm1YZDNJZzB2Q1JEZ1FuMWdackFodG1TcmJYd050OVBXR3p0OUtRUzN1MWdTUmtFRlFta3RUQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQWGx2REwtcnpQWjlsWnF0ZkdNRkp6Mnlxa0pEbHJ2MFFraDhhUVVDMll2T1B4clZQYmttU0hNN2ROYTdkcTE3MG8wdEdudTc3dHIzNEcta0NqR1ExMGlUNUsxZ3Y3SzRlOGdDUnIxenFqcW1FT21oMEhiVjJ0aGFUVVVIQnkyUDRtX0t5YTNBSVQ3Y01MODVTSUNGVzM2eUdqREQxX3E4cjdMVXNqcUHSAbMBQVVfeXFMTThrV21mZ01hMjdraDFFZ2RwTTEwQkh0YWhGaEpLQ2tnWXl3NnZmRFdCQzU3cThyaDRBdFBiamx6LVlWTFpXTWhrWUFzbGYyLWZiZUhraVpzaGhwQTdmbXlhOURaWFdLa25PWDZMazBaNWs3RkNvOEV6VlF3NzZUeVNibmp4YXl5V01KQjByUVYtUUFVVkc4dHZuSTd2VVcwdXpub3kyNlZacjlxQ1VsSDU5THM?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£140bn experience economy takes spotlight at InnovateX - avinteractive.com</t>
+          <t>PM warns against 'false comfort' of thinking Iran war will end quickly - BBC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 16:51:57 GMT</t>
+          <t>Mon, 23 Mar 2026 19:10:55 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPaVZFTi13ajhNY0FCTUJmR2dKa1M1dlloTHQ0bkJMbWV2MGFPem5zcmdLSXFOWEhWZTE5bHBMUXJHU3VzQlVLMng4dm5nTjdxSndnNE9TaEVTV0ZBSVRVVzdqeFhZcER1NDgtS1dQemdReHhnYnJxN0gxdTEteDZYZlVTWWVMZUVKdG5iemRCdGxSendMaDEwbURodmNBdVlFRG9rN1o2R2Q0NjBJWUh6N3E5QlZGMWlfWURCbC13dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9RZ3EzbENWYVF2NFdMOHgtOHhjZGtXSFozTTd1MnlJUkFYMThMdWx1Tk84RHVNaElocFV2VDVQbGVXTTRiVDRTUlZsbkdERDB4Y0JpeWN0UXY5QQ?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'One in, one out' migration deal: 377 migrants returned to France, 380 admitted to the UK - InfoMigrants</t>
+          <t>Gulf study interest falls 30% as conflict reshapes student demand - The PIE News</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 12:38:47 GMT</t>
+          <t>Tue, 24 Mar 2026 13:53:18 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNV9hbl91OEZCOFZ3dm5SX0ZIa2JWRTFfZ21qUmZKSENaNEhiNF90SlNlYmVEVTJvQ2NxRGFCcjBmR3piOGlocG5ncFUzalFCcWZBaUxQcHFOaDRZV3RhVmdBTmZ5MnBmRldBSGN4aTRWYmZyOU9LME5nckEwd2stcGs2d1I3TzlwOWdGRTdZa3pSZlY0anpEejZValRqQlNqazRKUUlZYmNJQWoxT0FWTjBHeE5VR2VYUC0wTjJXSndKVkZ3SkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQYjVtUFF2emZkRUQtc0pBTktNejNnckkxRmk0Y1VvUVJQSUhmTVFVY2o3dm51d3hqNmZJOGZKUEo5aDMxRWZaNmJNSXdNX1pOeHRhc05helA0WjFxQ0k5NHY2aTdwcjYwZGZFRW1OQjZvVHZmbWlyOHY2NTYxT1JGYi1razZYcjZpYTg0TjZaTFVhZw?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sanctions and Export Controls Round-Up: Latest Enforcement and Policy Updates - BCL Solicitors</t>
+          <t>Tuesday briefing: With the horror of conflict throughout the globe, how likely is world war three? - The Guardian</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:34:55 GMT</t>
+          <t>Tue, 24 Mar 2026 06:32:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOdVl0dTNyemp6NjVOWE1iYVhncVBWVTJmLUhpUjJZUWhIWkQ3R25QZUtNUVh2cjdNR2d4enhiX0ladVgyb0gxM3ZvSWItZUlqbm55bmtuOS1YTUpfd2k5djhhajJkdzh0VEEwbk8yODF6a2VGTFplM0RsVFktdHhIMUp1YXNBZTJreDN0cV9BcVRfeHcyN1c4LTVlVkVJaTdvQzVv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOclE5SHJqc2dGZ1ZUYVpvUjc5QlRsT1lkcExBUUxwTXg0S0h3SF84ZzF4ZTZvaVJtcHktOHo3QVE4b21MajlLWVBJODhTOW1NVzJ1dVVzU3BaWnp5bWl6bUdySzNhX2ZQS1NVVG5QSzJVbDdkejVJTE1YT09ZanI0LVNWaTdVeU9vczFOTDl3RVdzV3pGM3NGRlMzYm1tMC1seUhWV3JGbXY0YjI3bmszTU4ydnRxVHFvLXhOVDNubDdDbUlNWVhGQ3lRNzVPMDV1enpheTFCOEE?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UK announces new £2 billion “Quantum Leap” in hopes of transforming the economy and technology - Open Access Government</t>
+          <t>Denmark's PM Mette Frederiksen, tenacious and tough on migration - Yahoo News UK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 11:39:02 GMT</t>
+          <t>Wed, 25 Mar 2026 01:18:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPSk9oMWh4YV9zMm9Db2lFdlkzOWl6aVpvMVdFZXYxbmFfWC1RUlFLaWZJZHJKLXBuRXhpS0lQTFhPcnNmMzZDaWpyQUwzUEx1VnZrUXdsOXBCaXg4VkJuNkZ5TW5OWW51c2xzbG1xNS1OemFVdkF5SkFkUDJpdzJxQTJ5YjEtM1FTVzBWTURfWG9QZXl1b3kyZGtFVTN1WGNjQUNpWjlRazlCRFYzMUN0SXFPQ29NSGNBLVRmcUN5clhCcGpuOUZFUlhMNXVNOUxFNnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPV05XWXc5VUlDdUVEZF9TeVNNaTYxZDZ0ZDV6b012bmRnb0VNam5BSEFvTl9tLVlNWEtCbFpuRUVXYWtqQVd0d3Zpci01NjhvZml2Q1I1X2VMRzZWcW5IZ21kRVozTDEtRjk3TGRmNjI4alhYNUtnU2FlSEVsaFRjVTdWa2NDU3c?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vulnerable funding in the global economy - UB - Universitat de Barcelona</t>
+          <t>Cari’s Legal Exchange — Iran Sanctions: Implications For Global Trade (Video) - Mondaq</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 12:07:05 GMT</t>
+          <t>Wed, 25 Mar 2026 09:11:20 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxONWx1VDFEU05Ia3pGS1hFNERFZ2VMOTlsaUhKakVjdkk2Z3oybjRkWXVkbGNXZHdab2NzR0NoVnQ4cU4ybzdNR0ctSGMwMktPQktqcUx3bjJKazJXXzN2cTNoZFJibzhYOGhsSHlWcXFQNTU5aFdsN05vVHREV2RCUUlmcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNa21ZcnpFcFVtLTQ1VUE5NUpuR29WaUhlU3pQQjNZNzUyZG5iQ3I5aWItRmdRWlpzMnJySGxPdWlYWWVXMzBjVF9xTzUtMWhrREtBRmhoUmRWa293Ynd2OEhpeTg3MTF1RTk0UmtGcmw5cHd4bUNkbDdVSDd2TjlEZGpUZG9RS3BITTNEcHl3U2VnbTh5c0xuSF9ZUkNKMXFkeGptR3pzZEJnYWdFNV9yV200Qkp4VlZERFl4VE9sOGcyV2pldEdWY0FUSHVBNDJzZG90eHdlMHVPelhwUUJBZmZWNkJDbTVMZlBCeER3OA?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The new expat investor: What intermediaries need to know about the wealth migration wave - mpamag.com</t>
+          <t>Asia’s economy projected to grow 4.5% in 2026, with global GDP share nearing 50% - Human Resources Online</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 14:00:12 GMT</t>
+          <t>Wed, 25 Mar 2026 08:40:14 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNcVpCWTBVQWJUM19EVmhfblNDQzFmVDJsLXBMWnNwaVhKYVYwMnFDZUcwN3JXVWszMzM0ZkVHUFIzeHVMUE9rMmN2VEZ2elVHMjVrb1FiQ2VOMUN1c3hnY090ak1UWUNwLVkwZjFwZU1fWDNRdklWSXNXN1c1RGc0Y0M3ZzdlLTNscmVHWkJxMWpPUzRzc3RqU2JTY1BGcDJ1blAtYk5PM2tQQlQ5aHlVNUlQeGJCbVpmN0ExRFhpRGtvWTg2N0lwT0pKanJYYXhSR29Zd0lGV2tCWGpvWlVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNUJyVnhjQVZ0Y2Q1SVVvNndOMk9sV2NxOUlDM3lBOFVKMW41QVRzZGtTekRaSU9hTjBSalJPSlZTcWYtWXZVR1FLcEpERlR0TEZQS2hmRUpmR3pUTEE1b1FZQUZ6U2NCOTA4SnBsQ0c0bWdPLXlRVUNhZ3I4d1BNNkdoaWU3R1BJRm1oQVE4U2FFNGxMRGxLMDUtc3BMNnZPOFFPc1lfS1c3YTVxbUhBdmxCQks?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brand Protection Congress Europe: addressing counterfeiting and IP protection in the digital economy - Managing Intellectual Property</t>
+          <t>Global Terrorism Index 2026: Morocco, a sanctuary of stability in the face of transnational challenges - Atalayar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 14:28:40 GMT</t>
+          <t>Wed, 25 Mar 2026 08:47:03 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOejFuWnZucFZkUDZYSktYZVR5V0tJcUw0S2c0YjU4SUpYeTJkSjZGRGdkUjh6dzhmYzhmRjBZSC16blktOVFUUVd3cXlzT1N4ckNENi1iSjlmbzE1NFBpUzVjZ2FfRHk0N3RaNGhWWnBadjVRSHNsYlUxZWRpRUN6Nm9pa0ozdC0yTjJnWWxmYmJVeDl0WmhuM0lnLVVRZExwZTZmX1VUR1RSNzJrUGl3NjktQjRnWHRWSTRtaWM3RlBsRUhzMzBVUXpZMm16aUdMcTJiajZqN1BxNjl1dmJZYTlGVGJOdi1pajcya05VR1p0Nk0xMFdhS3J0a21XNXkzdWQxLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxPQURIZU1YQ05GWm1xTE1wNjlBM3BfRHFlamZoZEZZcHVFT3FGeFZ4UDl0dnlCbkExVDEzMktHbm44LXBpd3FGU1MxaTNCNExoMVpvUDYta0VldnB0SFBUVVAwSXB4Q204WTQ0NFRaOFg1bHMza1B6WU01RFRXT3l4OVlaaWs2elpkTTZocmVneExiM1BkYkk0Rl9zc3VhWXFzdzZva2F2Q2YwNy1pSHpxQ2FDbDVqTG5xOWFMOXlCUHlfWnpSZEo3WXdaRU8ycjBZeXFiUklfWERMUzdFekp3ZXEzQ01DbGNtQjkwRno0WWJOWmhqZ1F5UFpuMUQ3LUZucFVFZtIBigJBVV95cUxOMnlMOU00R1FXWHdjc2VXWEtyanU2bkw1OXExRGtBcUpSR2xOMVkzZnVWLXQyTjF6dEwyaVJNZF9MeVVBZVNQaVRsTmU1NTNEYXl1elV3UExDdURPcmFad1RpbTR4MHQ2cF8yZkdlSFZvbzN4bGVqdnhKR3dpOWFLNVJvWW1xNGd3ZHFHczlkVEJJNjJyY3dJay15XzFJTC0zcHZZcmhsVVNrYS1oQ3NPemZwMnM2b0N2T3Fscm0yQkpoMmp4QzI5aDd0QV9nYXdMXzZhSkJNaWc5TU1iZTJ1NlBGWkFvSndxamFHV0p0ZUx2VHFRV05IVnB1M2hXdUxDV25GeG12Q3VEdw?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Week three of the Iran–US conflict: oil market volatility, infrastructure attacks, and CSC’s energy outlook - Marex</t>
+          <t>Kuwait says Strait of Hormuz closure is beyond catastrophic, will trigger domino effect across global economy - CNBC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 09:37:58 GMT</t>
+          <t>Tue, 24 Mar 2026 18:18:54 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPbHFyQ0dHQlV5bUF0VW8tSld1aEVZSXlYS1hIVWdpaENqQjRydFZtQXNNSExaOExuZV8temJnT0pwdFg5ZjVaUGRpZGNsX2ZfTWR0bWdjUXgta2kyMkhxYmFfNXZ1Vzludm9JSnJ4WGlSamFIR3p1X2tmZWJ2LUxQeXFXM0NIbEVxXzVWVXZGdUY3TDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOc0o0a2UwV0t0Wm1vc25hXzBkd0ZuaUJaaWNuTDBmcFRMak1Ga3hLYmtLb2pCNHpTWWlyUmR4cndUWjA3SHVUUVFfZHdLZzluRVI4RTRoMlhXY2RuM1l2Y21VdDV2RkNmZnRFdU9aZUtTa2tBaTRQWjJXelFmSVQ0bNIBhgFBVV95cUxNMHk0eXIxQjVaaHRNZE5ZSmJPSDBqT1l3YnZKdzNxdXo3ZS10Q0l0d0hQVDdqU0FEeTBMOEZIQ09HVHhaTlo2SFhXNl9KQTVRVjhpZ29Wenlhd2s1MmxHY21aN01GLUtHMlRsV0FfaElKUHQtY3pZcXloSjFhLW5jalJxQm55Zw?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New report reveals Black music’s staggering worth to UK economy - Rolling Stone UK</t>
+          <t>China's growth buoying regional, global economy - China Daily</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 11:58:00 GMT</t>
+          <t>Tue, 24 Mar 2026 16:21:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQSU9FdGlsOVRNYzhpMy0zVktCOW9BX2gwR08yNUt1VXh5bXJsX3ZpeWNGTmNFSjBYcDZ1Z09UMTBGZWs1ZVdkQ0RURC1EYXM3UjNlRDhSc1hQZURMSVpfRTZMNDV3cTNOWUJGZHBIRGppeW9EblAtV19UUWFSYXhFWEhEejJhNGxUU0Rkd2ZpUDlBWHFTNXp6WHRvbFdIWVRHX3ZCclJyMTFIQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9naUg3ckRzYzF3cGZ5MHN2VDlHRnNLakZ6THhVQjFvSXhJQnhiZ0RnSTgwQVpGYkszUzF6ZnRGTlQteFpDeWY2bl9KWkh5YmNvb3NLdm4xVTV0WEVxZ3EwempMMGtzelpDckstTzBpYkNxY2RHNXI0NGFxZFlfUQ?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tata Steel UK’s support for circular economy initiative - SteelRadar</t>
+          <t>Nigeria signs digital deal with Finland as Europe backs Africa’s tech talent push with €23million funding - Business Insider Africa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 07:36:19 GMT</t>
+          <t>Wed, 25 Mar 2026 08:06:12 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMnpCZ0szR0J0X0l1OF9ROExaZDFDWjZPZlE2bldDUEIyaDF4cHpkaFQtUXZhZTNibmVHQTZMT0ZNdXViUjNiZ0FSUHMyU2xCcG5rLXg1bnRYTzdYcTFVTWZGOUFTZU9YbDFaVHVQYmpQVVdNMnNCMVMyRWpWVGREREEyNUlWdWxkSnQ1Z1NOX0R6MC1tM2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQMGhyM0hTVDlQNGxSZHQ3ZFR4LUZBRnZPaFpVczFJa2psSkRlMS1WTGhja1VhVWNOVTRNM2pTOXZ4dEVrbFc1UGU5SWprdDNSSjlrXzI5Y1ZtYTBnVENPWndoc2Q0ZlJFQVJCdkNiTzI0cmZzRW5QMzIxTjhrV0gtZG9jLVhON082NzZkeTRXYkMyMWNTTE5WZTloem91d0pwekE0aENqLVpiQ0c1TW04aGZ2NThJQkhuNGNwMnpmcVhBQXB5QVE?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1321,27 +1321,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran conflict turns shipping market into ‘wild west’ - Financial Times</t>
+          <t>International Energy Agency head says global economy faces ‘major, major threat’ from Iran war - AP News</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 05:00:27 GMT</t>
+          <t>Mon, 23 Mar 2026 08:02:00 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9zb3J4Szl2T2ZXWVJGdkdvY1AxM3FWZE1tb0dzZ1FEYnZBRlhuZkFBcnI4dnF4eXlIRjJ1d3o2Zm55TEdMNEhkMXRFS01lOGVvNjBiM3ZSSFpBYVJVQXVFZ2xCWHJZTkc0QzdhaUdjV24?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNYWpXa0N2MzNVRGRWcV9kZFdEUHpqUmpjRGhSN0lub0ZLdndYLUpsTW8wWFZ4WFhMLVYyV3FsdlpnaFNLdW1ZTWhqVll3aXI1cVRCVnREU0lkMTktcmY5N1Z5X0EtOHZLUkVUNkhycXA5NWZRVzJyZ3ZjZld4V0NfSFdMNzRtWldkQzktdzFtaWxJclJqNW1oa2RfOGVFLUxLRWd1cHZoQ0w1Zw?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1351,27 +1351,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Blackpool 3-2 Port Vale | League One Highlights - Sky Sports</t>
+          <t>ACCC monitoring impact on domestic aviation amid Middle East conflict - ACCC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 21:53:35 GMT</t>
+          <t>Mon, 23 Mar 2026 22:31:09 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPZnJLNDVGMHlsOGVZdERVRU1oX1dYUUJRdlpUazVQUFVnV2htclFyeDdSMUVzR043a0ZPTGdYc0RDY2VuRVExWVJNN2dZTG94QmxGZVNqeE9iaXZ4b2pQd2Fmdm84VEhVYVByREF2N3drRW14bG1QTWhROGZYUmxIMFA1a2xQaC1NTW1MSnd1eVVSSjR0a1hmQXJqQmhjd0RUSHg4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNVlZWVGFuc3A2SW01cUNfekJ1MzR3MVFqa05SVkVHRUIyUk1Dczh1THhNZl9PNVBPajdXc3BFOUg5aGpCbFlMQW84azlqQUlmMkFsRUJYVWdrdjViQ05DblFWY0d5NDNJODAySGIzT0lOOXgzbmxsWTB3NFJndnctRVRzZTlzcmRzWFVBbmgyQWVNQW0xUUdiNE02aVhUaFVoX254akhSVFN0RXM?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1381,27 +1381,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran: Council sanctions an additional 16 persons and three entities over serious human rights violations - consilium.europa.eu</t>
+          <t>Nepali traders make global shocks from Iran conflict a pretext to jack up prices - The Kathmandu Post</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 14:25:51 GMT</t>
+          <t>Wed, 25 Mar 2026 01:18:50 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOR3NJbE0yM0dQMzNXODF1QmhSUmVZWERaaVF0UUQ2Y0R1N1k0LWx6dno5Qk1vTUloclF5SFhZdTlsYU9XLTJiSENWWUctNmNaU1VhUjRkUU1rLW9PZmRlU0lJUUdJZlloam5HUl91a2d3Q1hPVXlSdTFhWmlfb2FuU0E2MElULUZaU09sa0FpVHQtYVNTQklkdlMxVEV1Z0JHRWNGU0NQZXpFZXAzTzV2YjZUUWY0SzJ5blc5N2xub3ZwTXo4XzFvTzBvZDN6ODEtalhhRjhEdE9vX1ZtX3FyYTFVZ2RjVnhndk8wT1RRczItWmZGSjZJakx4MjJOUVU3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOS3g0ejA5UFM5VjVCVVhHRm0zNTBXakZKSjhJalhrZEwxVFVzbjQ5QThHVjJyaU1UeXAzQUpkdGVvUkp4Y21nS2FBNkJJb0phQlVUeDhZenhuWFRpbXNra0FHbWtvSGdUQVZRYXJRLTFoc29VcTVuSThiN2FYazExLUhXUW9zTmZQSjhWVmY5X3IzVGVPTm1adWp2Z3dlVHVhWFAwajBDU05oQXdqSjRKN2R2dDhoS1RSY3ZXUFo3UEk?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Freight sector concern over port access charges as it calls for fair treatment - Rail Magazine</t>
+          <t>Mar 25, 2026: DHL Supply Chain and iglo extend their exclusive logistics partnership - DHL Group</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:04:18 GMT</t>
+          <t>Wed, 25 Mar 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNUlQ2QVdMbWlvT2FtdEZEVS1MRWg1UEQzcXZLR3lFRWpWNHk5eUJUS0UtNGFqbC1XNFk2Y0xUWVRsVVprY3k4Nmh3NzNtWDlJeXdMdzA5eGJhVG40TGlmMUxzbTN3ZWpOR3VTZnBvVk12RVQ1b2QtZm1NdTFXMVJ1V1RLdDBnbTRINFBVQ2NiS2dxN0hSdmlPRk5scjNQcGpfTWtBdHJBVmJNYjNxcmV0SHB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOeU81VE8wZ1hwVWQ5ZWxMeU4zMTVuSkxmREdEUjJGNzRjNWdJUVRQUjQ4VUU5UVZnRVowOHpNX1VGemMwY01OdU9aeVFsRlhyaVA2ZnRLOUV2NEVfRXc0UHNGT3J0cXc4bERLYXdESXloZXhpT1V1R1lNSWRIckRmb294NVJLZHZYUWxQRnB3eTZBbU9KT0hnbDFvd19vTXVRSzJhMEVjMHBoZkJPS3NGLXAzVGRGQWZia2FVcHZGNFU5ZzJUNUFoMUJKYThkMFBndUE?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UK to raise steel tariffs to 50 percent in new sector strategy this week - politico.eu</t>
+          <t>Doncaster Rovers 1-0 Port Vale | League One highlights - Sky Sports</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 15:33:00 GMT</t>
+          <t>Tue, 24 Mar 2026 22:16:25 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNNWg2MkowZHVxeEgzOVRvYUpSMmc0LXJLSF9jUjdlQU9nRjZIVjBGZmpCelc0YzcwX2JaVjZuSXNIRzFiZ1JKakM2eDk1aHZvc3JvSVZDVTY0cFBPYXRRbERZTG5xT3c1VEsySHdwSndoQVhrTk11ZmlKMmlhZ0ZEekVQSFdlaFEwX3VNRU9rdGJEUFE3WUhYdUNta1pYVDZCZGdXWThyUkNEQm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxON1ZXaUQwajF6Q3IybWoycFFaajN2WWNLRU5TMktKVUhWbnlYQUZoZklyekJad1RPcjVQVjJ6SWVrR3cyVFVGaGJIM2RpNUtuREJ3QjVyTVJmbG1rSUlkaVh3b0pVV1ZKTzRIaGRWUHZFRUxpZVlyZmVqLWIxVXc4T0t6MVpCd1FUUHJ2NWpxR1hPRzlETFBmdVNVR2ozQkd6cXJFYVJnN1pFYm9H?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boots inks logistics deal with XPO Logistics to support healthcare and online operations - Retail Technology Innovation Hub</t>
+          <t>Contract signed for freight flex vessels - Shippax</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 05:35:58 GMT</t>
+          <t>Wed, 25 Mar 2026 05:55:41 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPVmNRaWlfSG42V2h0eFRaendCaWtBWUZ2RUlIa0l2bHJ5dlRGYmJ0WjVMcFczclNacjlzejJoRlpfdVFyT0xQRFE1SGR1US1IZmxwZ1lSNzRGbHRiNGg5WFJXOFFDb1E2STZta3ZIQXJXX2JzaGVUM2ViVUpIcHltT0JiVXgyZGx0UlJiT0k4d2RMX181akk3TUtCWTlyTlV0SVRJeG8yNEloZjBmMlZoWHRiX2E5UkpBeVRIMjJmNmRycGVCOWgxMEVlY1l4Ui1WYjk2RnVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNQVdqNy1ZY0JuYlViQUtDT2ZDT2lTb3d5NW5hV3NLVDNFVlR0Qmp5QWhpdjZzTlJMY1I0MTQ2LUpUTTR0LXE4aXdzaTlaUHJBUmotNS1CYVRKZzRxa0ZibzliV1ZWbVNJb2JWcUNWbHprbmNQMTRtRXpjUkNtVWxqZkxVZw?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trump's tariffs were supposed to help manufacturers. But instead, they're hurting - The Independent</t>
+          <t>Interactive content - The role of tech in Awaab’s Law compliance - Inside Housing</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 04:03:00 GMT</t>
+          <t>Wed, 25 Mar 2026 07:07:39 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPYVdTVnBwbjVRcGZqbElTbHZVazI2aDZ0YW9la3BLa08zRTFaU244eWhYd2lOUl9SSzdHbFg2QXdkT05LdHZ5NTJjNVd3VlRIdllRRGYyT3AzMkFFNzdpUDVvaDRaOERhblpNWUUxbTZxREVEcVBrQl9uWTY5bG9FU05YVXh6SDl1WEY1OC15QnJFNV8xYVd6TzlZYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSUdLWG93LUFwRGp4cnBfTXRpZVhyaENnc24xSjlUNmNNZVhtdWM4ZjY3aXNCa2ZwV2NxUDZvVlYzc2k5N1JaUXU1cUpYbkpXVE5JOU1FeGpaODNYWDhJY2dvMGpmNlZpQWx2NWRVZnZUR1RUcUttLUVoamk0a0ZER3M2VDJwb25hN0FNN21JTnV6TzlsVnJtUA?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trump claims he has ‘absolute right’ to impose new tariffs after supreme court blow - The Guardian</t>
+          <t>FIREPOWER: Supply chain issues ‘biggest hindrance’ for defence industry scale-up - Euractiv</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 17:23:00 GMT</t>
+          <t>Wed, 25 Mar 2026 08:47:40 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPMG0wek9EX2kxNmpZZDJJckt4LVdsQllPemwxM0dXYzByanJaZjdmSTFLVFlaNXFkVUc1T3BzbElSRHhZMF81LXhLblp2VGN0NThhRFJZZnZyanYtdzVYa3dsVHg5TG5PeXN3b05tbUItSmpFS1IwMkR4akhIcW9LclZBTkdmMFJuUmsyclVsYjdSTklKNGNiMmZqaThsSkdmTFQxSGx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxORTl6cUhSelFrTjM4MHl1SlpYdHlTWHYtSWU5MnFxQ2V6a1Rab0dNRzVtWkpSMmJadDl0cHI2dDFNY0haZC1QRndldXRNaVZMVTk1cUJBQk9VVWlPUWJfb1pQZHJNaTcybzZlcFhYcUlZbGZhQmZ4Y1ctNGJ4MDZsdXlnbTI1Xzh4bWRpWTJ1WlYtdFFBNnpjM0xGZWUtLWtzR0l2azVnMFY2bDUy?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jon Brady: Port Vale boss slams 'joke' pitch for 'breaking' players - BBC</t>
+          <t>Subsidising the supply chain: How China’s industrial policy shapes export competitiveness - CEPR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 13:22:12 GMT</t>
+          <t>Wed, 25 Mar 2026 00:05:49 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFA5YzZmUzdQREVYNWM0a2gwbWNiMFFCdlZweVJBTmlqWG9yWHJrVk00RlZ3akd3S1I3bUJ4UVd5aUJOUWhTN0M4b25OYjFfazNNQ0NHYkpzN1hrTl9HWE5nQS01RE54M2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNTkVZVkJsUzZBUlpDMHdRaFUyY0p6M0JIWFZieDlrVVN2OGIwWFZ4QlFZRXNiSGZEbDh5WE5TeXlMa19lbXktTU1vX0YxLWpaMkZQZUp2MmNnZkVXYTRHNjBlM2YxS2ttcThWeTMyVzNKV1BZSUxSc0thVU0zQlhBb1pmVWR2X3dZUVRHLVgtYjFCSDBZUjdQLXlWNk1xZ1VkUVhmdlpoeEh1dE10Z1paV0dGVjc?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Greek exports to US unchanged despite tariffs - eKathimerini.com</t>
+          <t>Companies House disciplines over 100 staff for compliance breaches - Introducer Today</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 01:00:31 GMT</t>
+          <t>Wed, 25 Mar 2026 00:07:10 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPb3k2cERab2x1VG9NRjJ3SnplT1U1VEFrU1AwS054TnhHb05SUENlaVVjc0tVV3MyMEFuTHo0blNmTzZ5MlBWZmR4SU92WUlOLWltdXlSMks1aEYtbTBzZjIzVWFXd19vTk9YQnRkbnpTQU5ldGRIa29WU2taNC1lUzF3QWJ4XzdBdnpDVV9wckVEUWl6dGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOdW5BcVBncnVzUDZYRGw3ZGNTOFpDQlVhVVJYTnZ6a181TEFwUFg2elRleHNldzBvQzhTNUVDYXhkRkE5UzlYUEt6bFZTV2VyNDJDTjJNRTdnUkJFVmg4XzJBY2JnREJBcGtLR214QzVWT1o2ZTFYRTlSOW1EbkJQV1ljZmFVclNsLTVxSF9aNTRUeHRDQmUyb25IamxXYmw4blluTVFkYVlUZDZxNy1mYUxZd1AtOXFUb2lpTHVXdDg?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia’s war of aggression against Ukraine: EU extends individual listings over Ukraine's territorial integrity for a further six months - consilium.europa.eu</t>
+          <t>Berry supply chain must collaborate - Hort News</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sat, 14 Mar 2026 15:32:49 GMT</t>
+          <t>Wed, 25 Mar 2026 07:03:43 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwJBVV95cUxQU3lQaVplSWRXSGF5S3c3MjQ0dnZLS3g0UGMxTEYwU2EtMkVGNnRyYXRQOGtFaVg4UElBeUcydU80LUU0RXZ5SHVZVlhJaEw0aF82d1FDX1c3X1BRdXZYYmtFbmtET3ozQ1hyVGpaN2QxME5KQ05obXZlTzA4bHNZcnRzQzRyZGROUEY4aTJtWkExbklJRXFSUVphMlJQSVN0ZzNUeG5OdVhRdG9ieGdUc2JfaTg2dDFKRG83c3FhUGRPcE51QnVRU1l5eHNQNjJPRVlsZTViQ2hqSlNpTHQyclFxYklvamY4STE5QThveFp1Y05YbjJOZjF3ZzkyNjFDcldJbUYzZHRkSzE5R1BMUmxmdk1GXzhFaUU1d1lxSVRBaXlSV3NSc1hPOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1WMFI2S19IcnRZMnBhaGZPalplZko1cHlXekwzS01lXzV2MERtcXJuNVlaZVZCTTdfY19NX3FlWkUxSjFSXzBfVDVsc3ZzVWZtcVhiQlBVdjFkQkwtbTF1a01aQUVncmpX?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Q4 Rundown: United Parcel Service (NYSE:UPS) Vs Other Air Freight and Logistics Stocks - Yahoo Finance UK</t>
+          <t>McLaughlin &amp; Harvey lands key role in Scottish port upgrade - geplus.co.uk</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 00:42:00 GMT</t>
+          <t>Wed, 25 Mar 2026 06:33:45 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNYS0yUms3aUdNUmNaRGxjUHZUbnJmWDNUbUk0SW5Ca1dDdFFLeGJFVFI5Y0YwbERvcF9HcWQ2UnNHdnA1ZjdTNlJ2X2VJQVh4ci1TUXB3NlhBcFcxQXhwUnFIR0hza0s5b0RsVC14NHBVaGo4aF9oTEJydVU4aTY2M2dhTDc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNnVfT2F4UXFXUkFBZDdoSVl4NWViREZ0MnI3QzlSSVJFVlpKbFNzZmxfS1hGYnlhQng2QW9fU1dVV2NTMW00WWRwUlBoZURtRnVCSFBuakRSYVVjUVdtWDNkNko0WG5fQzRDcHZEWUwzcVFzSjZ3WDM5SDlVaDByNkJhbGRJdGJjNllWdVQ1eERIU3NOelRjZWhjWEhvT0ww?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Crispin Odey’s former compliance head accuses him of falsifying minutes of key meeting - Financial Times</t>
+          <t>News | M&amp;S logistics warehouse deal underlines confidence in Bristol - CoStar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 16:58:47 GMT</t>
+          <t>Wed, 25 Mar 2026 07:02:28 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNWmJDLXp3ODFrVGlYRFhnVzgzbVhEaTN1b0RCaWNUbWdWTkhZNXptM1huaWJSdWQ5UVZpazE2TW9GZVV0VWhkSk1xckM1MzR0dVpiYkw0SDJWN3lLcW8wSl92MEhzNHhBSjdOaEJCMTA0eXZtQTY3aklZRDlwZk1XZmYwZTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPZzRNaFU2TFlaTjRWaVczaUVIMnNrdVJhQ1dXMklLR1A3RW1Kd0piM1pYS25pN080X0VNcHkxRk5Pa2xHWjJlOU00TXd6cGlXS0luNzU1aElSbWRscm9jc3ZWQ2hVUm9RUk5rVC0tN0djSm83REhWbkR3blhsdVpyUlM3azJheUtMUWQzXzZIMXlic3NDMXFKVHRRaWlUWXg2ZmpKRA?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US to Ease Venezuela Sanctions to Unlock More Oil Amid Iran War - Bloomberg.com</t>
+          <t>UK-based sports retailer Stadium to build in-house logistics hub in Sweden - FashionNetwork France</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 20:18:46 GMT</t>
+          <t>Tue, 24 Mar 2026 18:32:14 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOeXdHc1ZqUEl6RXJKbXhVT1pmUklWd3RfVDh5bFJYNHYzMmNQN29TMXdZN1BuTFROZ0NWM2FxVnZyZG9TdGVjTERqSlJJaU9BeU1GOHhra2hmUUM2NTk1UHlLWTdXOXU3dEk5c1BwWnVkbDJCdzA1bl9oQlNxZEZwWEwyZVN4bTlCajd4a2tnOEtudFJVTHd4ZERfTGlUd1ZvTm93Rl8wTlpnUmJBemVUbXMyRHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNM21RNEhWaGpDMkNVMlpqSW9jZ2hyNGVIVU1NNG0zVGN1NlVMUFh5NnZLQ19hQVNtSDZUN1dONUg4UFh2Y19QYldiQzdLc1FDdWtpZzctQjZ6eTZBRHRGME0tR2g2dG5oSXpiZ3E1LWotRjZRQWVVMzAwb0cwRDY3LURHeWVfLVZkaFlOMUZWV0E1MzU4d2Q5MnE2dFozLTcyalFudlktaExZTDRtZFBHdnBEdHZCN3QydFZ1ZU5MTQ?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>How Latin America’s New Consumers Are Rewriting Logistics - Maersk</t>
+          <t>Cocaine worth £80m found in ceramics load at Thurrock port - BBC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 07:16:00 GMT</t>
+          <t>Wed, 25 Mar 2026 06:18:56 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPXzRDUkJHZ2I4X2Z1UG85eUN5QjRoU3FSZVItX05VTlNfT2pCbThrRFRrMXR6UW1rYllZRnlUT0ZJSTFXdElYcDlrV0xYSTktUUNsbkNoWmtaeVNUZVpISG5ZZnJ5SlZHLXpvSS15Qy1jTGhadG8tZDdEdWdWVDFUYjMxQmJHZnZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9oYWdfTGxTYW94OXVWb2xlaTVSWm1TcFFsaGV0R29fQ2M0SERCMk85Y0o4Q3VSMXdmbll4TGpVV0Nibm5uTllRWUloYWhURGpVQXl1b090cGF2Zw?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morrisons Ruby Port – 75cl Bottle, Rich Fruity Flavor With Cherry &amp; Chocolate Notes, Perfect With Cheese - ruhrkanal.news</t>
+          <t>Russia reports fire at Baltic Sea port of Ust-Luga after Ukrainian drone attack - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 07:20:37 GMT</t>
+          <t>Wed, 25 Mar 2026 08:20:05 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNS2hXa25TZTdKVnZqbVNiMnhNOVBhaExvX29ycllqOUJEN213MDA1NzJEanNQYUNnODBrVTdScTVZREdRaHFoQXJfUTRRRGZ3LWZvcVVJYjRQOTZZSEJQUUw5YjJkNExVZDRydmpMYkZlZlphdzFyNVpHVkx5WXFrNkhaUDBZNXNmSjdMWDhOLWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPOWRGNU90YXFCN2NlVXk1S1ZaM1ltY29sWlo2cXM5Rkp3TUhFeUQ1NENHd2pzTzdPeVQycGJTX1dXc0FoanVUZFlDcHhNX01mbnpzYjdTV3E1RWVFMnFBUHNyUU9TdXE1eXFhNDJPcHFjaVBoQzJZeGtpb3lhcVJtVVRwdGV3ZExtOS04bU9Ud0hjdUktaENXQWIwUXNTaG1RYVE5RkZnUnFFWE1Jc0s5aVFkVlhILW1JQ1E?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>The era of US dominance in economic warfare is over - Financial Times</t>
+          <t>Saudi logistics group returns for a sixth Posidonia - eKathimerini.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:22:36 GMT</t>
+          <t>Tue, 24 Mar 2026 21:50:47 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBFUEw1bWxsUlpOeXh1YUJEem9GLUpPZXB3eGI0emZIR05DemtUMDJ1b0FUR3FDVDM5VXdqYTBzRFNpaTR5RnJ6d1F5RmZkdE5fbWdWb1lkMEJWLVQzY3UtWFlGVWdUOHJSS3ljUXlSZlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZjJFdHVPT1VkSFRPR3hLWXQ1V0xDb0piaVdYTUJuM3JaYmh3azlGeW1ub3RLSWlIbmFrNi1YN0x2c013MFc0MXZEa1dnekRFdVVvbllralZ0WGdpRm9ibFlXOEdIX2ZoWHJFa3N3Rk0zckxSdFNwcXFaY0I4UUtpUE5FQWM0VnJUcVBxbnkxSDl2dlU5bktTM29BU204Zw?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fifa sanctions Nigeria and DR Congo over World Cup play-off - BBC</t>
+          <t>Irish metals refinery is in supply chain that feeds Russian war machine, records suggest - The Guardian</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 18:13:30 GMT</t>
+          <t>Tue, 24 Mar 2026 16:58:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE11enpKejlEd2UyNVA1X2VwVk9oZWRMLUpjSmtsc2o4R051OHhJUVhORVhXZzRnaWUxNGlEeGl1OGh6dXY5N3dISHhPdE5nTkFkMXFIbU01dVl3RTJCQlU1X2IwUDVaSEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNMTFjTWR2ckd0a2J5cXhoTXh1aGNLRWljWHhxTnJRVFgydmxoci1UY2Z4T3haRUtDclh2X09CX0RfdHFnak9RRHY1UTQ0MWgtVGNrTHBPeE5CWlVZZ1lJb0hFTnp0d0NzS0VYcTJXS2pnQkpCdmllT25jdGEyNmVxcDVDWV96VHZpaVUycm5ST00tc1YxcXo5dDQ5U3ZuS0dObjVGSm9haHhDcUxtT2l0cC1FOFpyMUNfNkNfNDlPd2dvcHgzWUZNMzlBUEQ1Zw?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chinese shipyard to build freight vessels for Northern Isles - BBC</t>
+          <t>IFS.ai Logistics to Plug Transport Management Hole - ERP Today</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 13:50:59 GMT</t>
+          <t>Wed, 25 Mar 2026 06:03:38 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5sbWI1TllwQ0lfQmM5Nkk1SzU0TXBTNDJzd294STlxZjJXOWJRZElQaFZfVy16WVE2bzVqU0Y4WU1QemFjZDZzX0ktOVhBcFNDVVJKMjFnSnM3REt0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1WcFFFSWhGTXExRGdRUS1KVW43c3h3UGhBSlhoYlk5ZE5ENmNUUUpjaVJFRVYzNl9kZGIteXM2OHFZd2MtSU9kVUd2RE55bzI3eGpJV0RrMGV1RHJrbGFBWURORkk3dWJYMDlQTkwtc3g2RHNkWVpjMw?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hubbis Appoints Andrew Chow as Strategic Adviser to Strengthen Compliance and Regulatory Offering - Hubbis</t>
+          <t>Jewellery retailer Pandora enlists Hardis Supply Chain for warehouse management system project - Retail Technology Innovation Hub</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:01:18 GMT</t>
+          <t>Wed, 25 Mar 2026 05:32:14 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNVkdja24wUjBJOVFiM1VwVk5xeGpJNVJia2J5STBlMS1Hc1prQVd3Q0FFZnBfNUhqel94YUpQREMxbDkwazRneTYyUHZNYmdyQzI4bS1IbU50dzdkVGRmSUpRWmh5N3dYbWRhSlhPM3JqeFRnRkFlNjBVX2U3S2E4Y3ZDb0N5aFBJeTlWenlIX08tRWx5WXUxelNoV3ZHZ1ZGTExVYkZvRGx5VnRuel95R3hlVEwwUmZSV2FpdW1pRUFRTkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPQTM2VFEzWTFoVXNlNXUyV1VFTkZYV2M5MlpDTEJRcHM2OGswY2dXRFhOTVNHSVd6SmZ1VnFON3JIaUVpTHA0VGhid1BjbVpENGp0N1JyekJ1VUVEYkZjaVgyX1FzdU9OMkdOQ2VPUVV5R052OEdjRkc1d21EQ0FPNUNSSzlWakE1bzFfRVdMSl9CRjlHVkIzNTVySzVDbmxwSS1RcTJiQWhwY1hiY3NMbW9vNjBlekpCY1ZMNjNMTXUzQmR0MndDNFc5T0R0NU1ubVdvbEZvVHI2VXZJN0E?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Trump's tariffs lead to production increase at Lochaber smelter - BBC</t>
+          <t>Greene King Opens New Consolidated Depot To Serve Its Northwest Pubs and Optimise Supply Chain Efficiencies - British Guild of Beer Writers</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 08:51:27 GMT</t>
+          <t>Wed, 25 Mar 2026 07:30:43 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5XX2FJM1lVbkJSeXhkbl8zVGRFNXlUb3dRNERKMXBMNDZiSXZVUDE2WEtva1ByZW10bVFEQ0lOczRFSl82anRDaG83RDA5UFhTMXhreHpYbmUtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQalBRa1JUQlN5czNfV2JtTmQzUG1jbWVXejJweEVLY2xVN0ZNMElObEFCSS1ZZ1c2S1VUTXMxc3hFUGd3RXIzVHdVZnRKVUh1cVVnRjJuR1Bkb2M1b0cxWUVoOWhnbk5KZ1FtVTRmbEk5dFZmMzFnbUVLUE9tMF9PZ3ZmY2hZQllBaXlvTHNrY0toVC1wR2g0bXpMOTd6S1ZXdXdiUEk5TEFmMUlHNnhHYkhTVjQyMnRkc3hvaDJkZjd0dVBJXzdIOVpyTGM0UQ?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poll on EU tariffs on imported electric vehicles - news.cgtn.com</t>
+          <t>Stablecoins go mainstream, but compliance hasn’t caught up - Electronic Payments International</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 05:47:43 GMT</t>
+          <t>Wed, 25 Mar 2026 03:44:12 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUzFwaU1oOWp1U3BDU2NtT21yNHpBcGdjbFlxX0psdTBkMl9SMnRYMXJZdFdESUhtbDNPcDc4OWR3MmRoRjA5bXNtUnRkYVdzYUNiX29xT25PT083b3pzbjdHV2RNOUdpbTU5MDBNMjVWVGVCMWRrbmdmOHBTa3JIaVhaWWRJQ2tFYk5HeWdqSDBRVldlYXFxa1hveHJZTnBUeEIxYXdYd1lldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOcl9BNHg2Q1lHcnpqN2pJTGR1N2xER0V2bXlYYTdSeDJkSWpWY1ZheUU3WlhXbEFHb2E2bUdlem1PdWo1MjFPVGZVa2VaWDIyMjJSQVVFSlhIaXI4TkhManZUdThiWXhfZE4xMTVXRVJLWXlYQndseW90MVhzNHBkVGpWSVBwY3owODJ2YWFmU3RvUENZS0pIQXNzcXB5VHR5aE1QZGMzMXdsbzVwVGZHUw?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seven in 10 Americans say Trump tariffs have cost them more money - The Guardian</t>
+          <t>French bill to push shippers into zero-emission road freight - Trans.INFO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 17:37:00 GMT</t>
+          <t>Wed, 25 Mar 2026 04:05:54 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFAxUXNyeUhpNHhfSHk5QVRhWXBGbUdhdmo1cUNhMk9Ha01aMm9OQVROa1M4NHhpcG5XV01CMnZfelhSS24zam9pMnl5LV9OWDRzR1dKY25vbWptZmttYUEwa29JME9XaVdmMXZObkJsNVlGcDhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5DLUpKZGZnZ29vWmF6T19wd3hKRG5zU25kaGRSdjR6LUNoaDlHWGZZNm1pb1NhQldVZV90SE1jNGdOY1o3OEpXNElzckc4WUlIOFY0Z0I1NElZV2FsRXVBVFZ6cGg?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cost of clearing up 40 wrecked shipping containers revealed - The Argus</t>
+          <t>Middle East instability raises immediate inflation concerns - Furniture News</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 05:00:00 GMT</t>
+          <t>Wed, 25 Mar 2026 09:36:14 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQWHhwSTIwdE9oWnBQQVZiYmZLWVlka2tDUzJsclN4c0Nzc3QxRnYtczB5T1I3THRVVFlHSTdnV25GdDV4YWlBSGtXOVhJb1lmbWpYRHRua0VEQ3gxYlI1YVZGWEpGVG16V0xRSlZ1U1JmaXllU0J0RkRwUlhXZWg4SlZYckVTZl9Qb1haQ3U5Y1VldmZxNzNMdFZENA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPaUhJQUxyYy1NckFWV01BRnRxc0JRZVlJTG93WGNJNlk4X3FlUUZPZFY5UUpHWG52cDVLOGFVM3BmcDhVVGhUUUs1ZlN1aW9JV3YySVh1R2t5M0Z4ZWQyQTlnVzRPdXYwYVdQanFlaHZXUm8zNzZQVElOR2ZOTVpLNXo1UmZ0SlN6Wnp0ZmlaSkh2NWwx?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US easing of Russia oil sanctions faces pushback from other leaders - BBC</t>
+          <t>To break the pattern of rigid higher education leadership we must move away from compliance and towards curiosity - Wonkhe</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 16:38:02 GMT</t>
+          <t>Wed, 25 Mar 2026 05:05:56 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5ZUzhYTzcybjRfTExSNXBDRFh4ek5OMXliUjZnSElvTHRjT1Z3TjRhbXdCcGtaOER5TE9ZYVlvWFF4aS03TEp1bkRFZ1BGcEo4QkRmNVI5cDEzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQc3I3U0twTUhheFNXVWwwQldUc0NfX2FrT05uU1FTdXQzRGdQbnBCUUpzWm5FWk5RbkdHaHowSWhMRmlBbWFsX2YtNTJGeXJkYzFwbmFwRjVlcEk0V3FPaFFRSzVRanRYR3lUd1BPY09BSnh3bEFoTWozWndIVjFZaHV6blYwYmZrVERRZDVNbDduWm5JZ2haZW1UOTVVVHhuMk9Ca2s0akRZTzJpVFRSbWRXOFdzc2lvYjJZaWJXTVNOb0xUYnBVSmxfTmRfVndtVk90SFlB?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Space boom strains supply chain, industry report warns - SpaceNews</t>
+          <t>Uncertainty complicates efforts to prioritise shipping investments amid today’s decarbonisation regulations – yet delaying action is not a viable strategy, Wärtsilä survey finds - Wärtsilä</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 19:08:32 GMT</t>
+          <t>Wed, 25 Mar 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQWVJpZUNHdjVZQk90cUpkZzVscmlYQl9Ra3lva09iQkppUVhFdWl0bWRtSVFVc240NVdRMkNMRVZOdkotS3E3cUtaaW5rQlBPNFBJU2c1d1BDa21nNGhIbFhoaGRfUy12ejJ5d3FabUxqTVVZRnJiSnhzbkpoWktHMlBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wJBVV95cUxPZHZZcUlmUEZQc2pjUzhRbndZcE1hUlMyT0hFZUEycHRXUDdfRnpZTU8zS0haWFF3b0pQVXp1VVZKVzlMUEFDbXRwQnZnTjZfaDY5Qk5XaEdRTXlfbldtWC0xNnRpdDJPdzJRSVN1Q3FmRXVmclIxWmtZT29CSldETzU2b0UwQ1MteFJoT0hFZGFnajhaWXM3aEFCOU9KNEVQcTBPNnlERTM2UnUwbUt6YlFLLVFLRG1hSFhua1hsLTVSRWhDTE5TTHFSWW9CcmYxRHJwdlJJM0JabHA2a2dKeWtHdHNLMjhFbkNkLVpKOThYSHk5MjR2SlNNN19PbEQxTUxGdHZoc1FnSnNyRE02djVXblBlVmY0YjY2Um11VWFPczAtaGFHQ1RIc0g0Q3l3M1Z4QTlOZlJOTDd0RWlCekpzdG02NFAtLTV0OGt2bWo3NzQ?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US diesel tops $5 a gallon in worrying sign for shipping, food costs and construction - The Independent</t>
+          <t>Western powers were unable to secure shipping in the Red Sea. Hormuz will be harder - Reuters</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 01:14:00 GMT</t>
+          <t>Wed, 25 Mar 2026 06:02:00 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQaUpOR1NNNThHaDFQVlN5eFRnQzVZRlN3S2hOY1RmZXFoQUlrS2lnMjNtQkw1eFZic19QRTB4RXNlQWNzNWVHMjhPWi1POThTdTluVEcybkNRTDM0SjJlOE9QY3Rpb2NmbFFpc2lTY01yeXZVQWF4NmtuNWFuaG9EX1RsNlRzWVB1RlB1SFNaQ3F1cUx0TlNNWGdILXdDdEM4Q3NidQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxObXYyUE82WTFKZGx3dy1aLWtwQkJHQ0xtaTdYX1U2b2Nnclp0VmdYY1kwa0lEUEk3dVJDdmdQYXNQeHJmV3hhUExNalF6UHJTLUhhTDlnM3NYZmZQOGswQWpncm9ycjJxN1NvMmc0S1pGa0pJWFBhNjFLTlZ6c1JidTU1bGdaRHRIektUaS1oZlFtZUNBOVUzelJpRTZrckdXTzhOMHBqZnp0M0Jhd1ZvMndEU0NIbEJ6ZjZXTDFXQjNyQQ?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EU sanctions Iran group that hacked Charlie Hebdo - politico.eu</t>
+          <t>Why is General Motors Investing US$1bn into Mexico? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 15:24:00 GMT</t>
+          <t>Tue, 24 Mar 2026 17:23:15 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNQTdRNjN0Zi1GRklEQUtrZVlOSHRQb1BJS3Y5SUxhWmFzNUpzVjRpM01rQmVCVEFCOTVxNmhoSVhGalVfX09aay1EbzBrWjF1Q2c5OWRDSC1mdXRxelVtaTRFTmhjcHJ2TXQ2MUo0LVloTEU5ZGFlQkUxcnFSak53UkJaYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOQ2lPaDNDSEJVTTdGczZNME9HeFlTbGdDTjBNNUxYRWREeXMtYkVZQzltaUlFOEI2aFdvdUtsZWhOUWRqY1hUYVMzTTRKazBpUWtWUWtBVE5mWElhYzVTT2V3T294akxJOFJIaVJINE1EZldOeXdEbjNFTjhYM1BfNm5B?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Perth's biggest logistics offering in five years hits the market - Green Street News</t>
+          <t>Elliptic selected as compliance partner for Solana Developer Platform - Elliptic</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 21:47:45 GMT</t>
+          <t>Tue, 24 Mar 2026 19:11:48 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOR1F0ckJBZ1NYYjN5VDJZMV9wTFRmQk91dEx0b1ppUWJRSHctWTZveGFpaHF3T0JIU0dxWmdTNDVGVzVYcy1PQ3RldEdDc3laSU5qWUVBMFBxYllQUUdIZkliNjhiVUJaN3dmYlZaMU1aUUt6R29lTzRpWEs2X1YyQ25PVXRrOXZqU2JJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNM05nQjJLM3hxTF9aNmphU21SN09qNkh3QTZ0YjVTbFI2Z2lhRlFINHNBY0ZmVEp1aGVNNFR6bjVBbmVIMzZKQUZHaDJ6b0ExcEVraVJGY3VjbTZTMnF0VjhjZHNkVUVVYS14dDZLaFZIdWMtb2gwUU9XSF9JTElzTElrUXVBWXRBdnB3VllUZXZ4MWhqcExrOWwwd2VSbV9rc1AwNWxNMHYyUQ?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iran hits key UAE oil port and Dubai airport - BBC</t>
+          <t>Shell shipping boss Karrie Trauth steps up at UK Chamber - Tradewinds News</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 12:43:32 GMT</t>
+          <t>Wed, 25 Mar 2026 08:48:44 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5mOFdVeWRDSm12RzJwU2ZhWkRGRVNxaUZoOU8wTVZaUDJLYVlUb3JXM203YzVlSTNsc0pyZHZOb09ZUUdQX3BzUjVSOHVmcFZabktCMG8zN2lPQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVE5TN0dNMVM2Z1lieFpZWVItaEdfOUdKVE83SVE4NHdKWlk3Y0tLWUxfVHZKMVpFbzJoZk90STFqYmUzeElZWnFKZFNFdkdodjg1TkxrdkRxMnRNNXFLc1BZcDVlZ2F6TTBUWURBc1FTNmNXMC1SZk5rNE9Ib0JpUFY5Tzc0enRndG5jRzZsOEoyRzAxYUdQVGZIX3dVbjgtajZEdlFpaU5Odw?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Traffic starts trickling through Strait of Hormuz: Who's moving through and who's still stranded or diverting - CNBC</t>
+          <t>Ohio Mayors visit Ellesmere Port - Chester's Dee Radio</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 04:55:43 GMT</t>
+          <t>Wed, 25 Mar 2026 03:25:45 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOdzB6MU80MEF2U3ZQemV0RUtyVG85T19SN1FnZ01uZ3ZsQk50RXZGVzVSV21rV2p6eDQ5T0pEYmE4NU1OT2dYcFpXdTd0SFV1NEl4UGVmb1dVR2paVE02MFNfbzhOaWVCZGNTZHdYZG9iMTM0STF6bmZ4bXV3QTVPN1ZDZTc1SC1ESU5lVTJSdFVnTTRKVmlKMlhfLW9PcmlrcUN1OdIBqgFBVV95cUxOU3Y4QWE3aU5FTjU3OHVyWXFfTk1ZY0Jxd3VtNlVoeGhwMXlrZW56THo3RmEwV0Mxam9UemRrY2VkR2t5M21tcDZxdExhZHplYjJqRkY2LUl3WWRzcmlxTFg4LVZvaHE1UGFDcFlSRHRpZHRWU21reDhIMHNlTVNfRW9Pb3FKeXZJSVNrdnBXek15Ti1Sd0tvNWYwSHkzM3l3cklSaXN3S0djUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE8wZlJjMnNmZV9PRTRJS2k1bkRQRjJDeHVRMFdNeHE4RVdsRU85NDkwTmZsekNBY29oQnp0aS02NENJbXg1SUxDM2FFVDdZV25LMXpURlp4Rm5RLUJIbTNSdFZlRlpDWGdiSWdHaV9EWHFnTy1nVXdGd1F5VC1hUQ?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Carrier Protests and Border Checks Paralyse Poland–Ukraine Freight Corridors - VisaHQ</t>
+          <t>‘Decision intelligence at speed is the breakthrough shipping needs’ - Splash247</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 23:07:04 GMT</t>
+          <t>Wed, 25 Mar 2026 05:48:16 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNSjcta3N1SlU5NWRucHhmbHVsTUVna0xsZ3Y0aWkxRkVSSlQ2WDN6aGlzRkxLVmotUkhYNUwwdTQzNG54RFBMTVdxU0lGOVBlOXZlX3N5T0NmelpxUkR5STh2NlBlUmt6azZJVHVpU0NYTFU0Ym1nV2pCb0tOU3RvWFJic1h1OExCejJFN3gtaHlZRTJ6bHhtdXNqVHRtRm10dHcwZkcwU0JzZFplYnZvSzZJWWtFWG1pd0gw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNeE84ck1UTkRNRDRxOV9MMy10ck5IaTl0YjY2NGZGajNMV2g1aHNzNm9tOV9XRFk1MUE0dXB3MGM4RnJOZHg3ZG5HTm1TVWZ1d2M4U2xRYTB0RlJLbEVVWjNSbnBsMHlTV0ZoYjR2XzZySk1EcmliY3lzVHNNclVlYXd4dm5aT2RFaVZ5bE9reGI4dw?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AFCON statement in full as Morocco named champions and Senegal sanctions confirmed - The Mirror</t>
+          <t>Ellesmere Port MP launches petition over stalled shopping centre investment - Chester's Dee Radio</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 22:43:00 GMT</t>
+          <t>Wed, 25 Mar 2026 03:25:45 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPYTB0YllzdHJFVjQtZW5TSERPamVnWXhCeDRPdlJiV2JxcE04dWFOWEJHQ0ppVG9pQVNDZ0pFNm5vRHBJQW9CbGRrLUs4aVhSRlU5b3JxZVFXNXAtMlE4SVdrcmU3cEpqMW1MVWNXQS0teWhsS1Y2Ulh5UUVEdGpLOENLTFBkdFZjcTJldnNXLXdmQnN3ZFZr0gGcAUFVX3lxTE1XSzlkRWk0V2RWN2hFSnd5WjdjRE5adHZOTHpvOXdEaTl5Vm1xb05ILS1YeE04bnpObUVlMkd5RzlxM2dObXZZd096ai16ODVYd2tQMXNUVTNqT0dHQ2RpZFRNTTR1MHJyMHZvbmRMZEdWYThfTDJJcGJDaUZYRmZGaWk4OFJWZWJjS2xQdklqaW5PdWhPY3NkZDBSQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNOVVvekhNNXZ4c2tGZFh6MTJlNmVvbThqVGJKNWR6UEFfWE1XNE14OVd1c1k4NnRYU1J0ZjV4MS1XZmNRZnNDQUtoYXR6S3ExM21UdjhxM3lSSU9YaFZ0aXFvZXRlNjdiZ01aLWM3eGpGTlNZQ2RUdmo5a0c1OGZtNDk5U3V6S19CcnMyclNBcG1Ea0dmUUJXTmpvRjh3NW5wdHplaFhQV3JrZkowUmktQ2tqZC00Mlk?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2311,27 +2311,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Information which resulted in two Cardiff schools being closed is now being investigated as malicious communications - south-wales.police.uk</t>
+          <t>Kenya flower industry bleeds as Iran war disrupts shipments, drives up freight costs - TRT World</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 13:06:00 GMT</t>
+          <t>Wed, 25 Mar 2026 09:21:46 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNcEZkUWRPYzczaWJzUllrQ3M0R2dTWEVJZWFpT2gyMWstVy1oNG1nVmJBSXI4RGMtQm5DNEZhNEM5X3VlSWppd2hIMkZkZFJEeVEzeGpDa3FwR1p1aDBGU01McVRjTDhaMFE4UU9LOW5VZVREOUJwWDRqdy1VQ0trWUtxSFdlQkJlaWdUMzFzWFV6cXVRYmxOQmNqMXoyYkJoUFBUbk94RUdsenBxbkY0WkNjMnluTFdxUDF4Rl9IZjNIYTJ6MUtfUENxNnBLT1ZrWVppUy13SGdNVzZKbUVxQ1l3YklSWFJ5OGNCZjRZT0RnSXVnT3RCeXVNMWVGQjJKd2dqZWlidk8wNFVQQVNsOVJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBoY0hGWTQ2ejJhd3VXQnl5VThaRVZVUzBCRXllSkVaV3lYMFp1LVVhOG1VYWhpZGlZdlJxNC1COVNoRjAtRFF2NXdXbEZfSUZBWkZzZVp2YW3SAV5BVV95cUxQOUdhbFlzemdlbTlpUkpKZ29YVWtxTUlSM0Y5aUVsRXdQbzVFanFXOTlpUnVQMDgxeHBINW1aTlhUaHRKMk9tOFZFQWM5Vi1VN1hoODRYX19XMFo1Q1Z3?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2341,27 +2341,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Five arrested over alleged gutter cleaning fraud - staffordshire.police.uk</t>
+          <t>Neath Port Talbot Council Approves Capital Programme for 2026–2029 - Business News Wales</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 11:00:00 GMT</t>
+          <t>Tue, 24 Mar 2026 21:39:59 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPUGlsZ09VTThJQVQ3NzI1T3Axd2cySS05WHFSUGxBUUcwTTNlZVVZdUhtZkdheGdEZkhQbDd5aFRCUVYzSzUxYXNheVdVcVFlazBBanVZcmxGc2JkQUtMWW9qQjZ0cUNWemc5eFVnRTZoUkU5eG5pRWVoZ1pYTG1lN0M1WVpvT0R2WjRqSEVrYkVWSnEtQ2pkOHd0VGhxTFFZbjVHcjhuZkRaa1lTeEtYTXVJZF9nRG5EQnVETw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNbF9QUkNZRHdSRXFHVzVJeS1aOVRyN1k4MGNRZ25kc2tnQzFkRUVjb09CUUE4VGVfTlFiTmdkSFNNRE93aXFuUXNUMHdMQkV6em5HMWxtMU9wM2xoc3J2UDc5WXlMOFBTSXdQOEhCdmNLQk9rdzVab09aX2NLdk9nQkYxZXN0UEJkd2FIazVjcVlDMmNfZVE5YUtzbnJmdw?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2371,27 +2371,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Investigation into the death of a man in his 40s in Whitby town centre - North Yorkshire Police</t>
+          <t>War with Iran drives big swings in shipping stock prices - Lloyd's List</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 18:01:00 GMT</t>
+          <t>Tue, 24 Mar 2026 22:44:41 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPcjhMUWhFcWZFdTJqMFNmM3pkM0NvWnFiT3hpcVd0dlpzUTIzTEJkSndZSG9xZnN5QWdtaU84dEV1UlZ3cF9VUVNOQ0FoV2NtLUxsWnpFQnV6Y2x1UUhYMERXb1daZ2dubGx2bUVmdzRUc2tkSGlLOVRaLVVRaHVya3BpZDhGR2c0YnV6LXdtQ0ZTN3FaM3YzN1BLMWx5a1FJWG93X2xhdlVwdmFLSFVpU0VOclhXWmNZbXdNd1NqWVJERWRNaGRSVmJnZzVvY19xUUVVR0FlQ0dzTWNEclQ5LXlTaTZJa0lfcDJ0eA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNMURCdFJKQkNUckNPdmRIS3BLd3pDU1htUUJ4bEFyUkExcVppQy04R2Z6U19aamY5Y2ljRWllRGNWZ2dUalR4NDVsTUdfOS1pcWc0VXM3UTJJTDZSS2pJdmsxemdTcWRrQnF1Vk9FakpkRTlvUnNsVGdfQ1poTU4xbldJVVB1OUYwbnRDbzN5ZDV1eHpFZ01WcQ?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2401,27 +2401,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Man arrested after alleged hate crime at Bristol protest - BBC</t>
+          <t>Promotion: How this Suffolk team guards the nation’s food supply - East Anglian Daily Times</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 09:01:14 GMT</t>
+          <t>Wed, 25 Mar 2026 09:20:54 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBmcmxUV1JITGtmMURRRzFoSHpsLTNaOERrQmlOanFFV01qaVdCUkw3Q2FoV2l3dFNHSTQxSFFnNkdXenlBZWNoRWZMZHVvajZ5ZnFCbzVoSmJZZG41?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNU3BCcTJycEJtdFRLWjAxSlR4Z1pjRURQSjBaSW5HY3YwcmotaXNNNExCalFibTRLRnJqSVNrNy0wRnNoelNweWY2WFBTSHdHdzRzSHBjSVlkUDdGTWw1bmx2eWRIYk5GY2JyLWxOVmhmZnZvNTVMVF8wX05rUTg4dXc1SHFvTkZIblpOd2V1bnByeDRNQUtfYg?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2431,27 +2431,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Teenage boy arrested following stabbing incident in Cirencester - gloucestershire.police.uk</t>
+          <t>Brentford announce fan behaviour sanctions for first half of 2025/26 season - Brentford FC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 12:08:00 GMT</t>
+          <t>Mon, 23 Mar 2026 16:00:23 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQSmwxRFBsaVp1d3E5VlVfd1NvWmQtN2s1NDVFbzhpNXJaa3JVcmJpRlhoeExGa2JMTElZNk55NjZNTGNFY1h6SmlRLWFna1N5OWxvM1M3amhDV1Z2VU1jbXhfY2Q1aUJSOW9yX3ItUnhZNzJBZGNLeTZPQl9UOXc5UTY4M01OdDI1SkctNlZvVGxiUGlxSEZ0S2lKV0hoQnNvRGNFS2c5VXRFNlF3a0gxTXN0Tjl3bUl2akxMZnlQeFplVTNGc1dCb2JvWXdxWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOVXV6WDhzRzdIa0VybWNiUnBneHdDblRLT3lQSFZRLXBPeENvaHFvSTNGOTVQV1BydWI4SG0xLWl1d182SzBRTE5veUNNTXlFVnNSR1QxZ3FaX1JLWWpyN1RMQzZLUVgyT3hQTTFCWFNMRFJkS3hUTHZBTzNiSTduTnJId1NMYnJVbEQzNzNLeV9LVVBhRERQVUFJczRQdGZmNDI1U1hKbG5zcWdNNVJrZVdpRlRmSk85YktZ?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2461,27 +2461,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Israeli strike on Gaza police kills officers - Al Jazeera</t>
+          <t>MEDLOG Inaugurates Integrated Logistics Park in Saudi Arabia to Support Vision 2030 - LM - Logistics Manager</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 09:03:34 GMT</t>
+          <t>Wed, 25 Mar 2026 07:14:29 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPRG1RVmhUd1hRamdQR1VxS3V3Y1IzUXF1dEtrWkxJZnhlbjA2SGl6ZkQ1YUw0MENkYnprRGI5dkZZa3BvNVc2NkZ0REUtSkJFV21QZTczcEFvQU0zRTNadXRQSk9RQ0MtTUhGaU1hX014SHFySGxqX01qRU1qN3hqR3RadHJpajF3SWt5X2N1WWxRSTM2LTlOVkV5d9IBoAFBVV95cUxNWFdzMEotOVB0U19reTZLS0JWdzBDdG10M2xxT3A2TDNUeVpqdmtTSlRzQUVwUDFiaUJjNmNjRnY5TXU4UWQwR3QtMEg4cjFpcWs2djUwUVVsSERoYzdlWkJBVWdzNlIzRTBZR05BMDFJbEtLNjBldVM2LWdkSzNmVmVmT0FkQ21FMGp6MW5IX2RUa243MHVZMHc3ZkctTXli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZWg5MFdBb3V0M3pucUFwMVRSbjBVUi1NR1JRQUhWRVJKbzlBa280MlhGLXdCQnNZQmhHbVI3UG9DQzJBV0ZjZ0FaS19JcDlyaTNWY0FLMmxTZGgwdG1aWjBDQ1hXdWt2NEprOUpDLUxJS0FGWWJUbGdRelU1Q3Q2akVKQzF6VDJIWGkwTmF4dlV0QW1xWnptXzd1NXlsSE82MmZRYXVQQXZsaEtuTS1RMUhuZmg?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2491,27 +2491,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>The Times Luxury Cartoon: March 16, 2026 - The Times</t>
+          <t>Hutchison Ports unit pushes Panama arbitration claim past $2bn after ‘unlawful’ port takeover - Tradewinds News</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 04:05:00 GMT</t>
+          <t>Wed, 25 Mar 2026 02:38:35 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgNBVV95cUxPQmxMczRCLTFYa0NRWTBwbVAwZjdMdUdWS2tFV3c0SHIzYi01NUNrOVJ0bThocXpUWTA0QnhnaU1UTHd0V1Q5bXRJVHlQbW96REpyLWVwMVFoR1RNbzNOWUlhNk56a0NiaGtZdmtITy1ZOVpDaEFoREc5WUdmbWpjOEgwYWYxOEJfb1BUSTRMN2xlbFpCeHZqWDlGckpIZmVfYWpSZHFfNVB2ZDZUaXRzek1lMGJvVXdLZWdPVzBPTTFTQ1BKUlhjdE9NbnJ0dW1kV3I3NGF4V2RHVFlZOEYwNU5vZ3VIUjhSaUZwZV9icVp5OElPY3FqSlBvMmJESzVrbUZpYkg5UXJSTVV6UDdjUUVYV1VWYmZyTHlhcUVLQ2VudVhLTVBiSmQyUGpHTUgtb0JZVjJtYkVFOGNHdGdSbV8zaHRRaERKSnc4ZzlwNy1nZTJlcm1sRGpBMGhIaDEyaUNvbkZzUVdGQzhBd2ZUYlcwbzVVVDgtRmxzTUMwa1FmTHh4TW5ZOUpPMGR4Tko5dkF1dHFJc0VOWTBkTlpVa1Y3Z0NMZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNVWVIM0Y4OU0wRnAxTEstRkREdTZyTU9oem1qT3V3UHQzdnhsb3NmNWpWSWVvNGEwVjZtd1BhMk9UWHoyRTZIS254R0c0Z3hOak1LTVc5MlVNLWljVUFTZ1VaYk5CRk5GbnE1dXhKeWo4bE5lc1ZxanczTmg1eWFBcGJlRUtzNmdLNjBSOXhXeFlEa1BQYWVFZFVUOWd3UkhCY2ZXdnZya3VlcEdaM01MbzJ6dHFBTTVDRGxDc09wc21yZ2wwc1B5NlVRaUtSOVllM0FDOWF3?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2521,27 +2521,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>One week into Natomas Unified teachers strike: Parents fed up, one arrested - capradio.org</t>
+          <t>Man who caused 'permanent damage' in Ellesmere Port pub fight told to expect jail - Chester Standard</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 00:01:16 GMT</t>
+          <t>Wed, 25 Mar 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNMmpzenJQR0puWEtMMlptT2JrRlFNVXBGRmQ1b0dJbFlGWlY1V0hvUjBtemZZcjRMUF9xOXZmY2xJRHBrN0hCY0MwUTR2RGVvSUI3b3BwQWVpNmF3SXVxcG5XNWRJQ2xOVjBMUmJzakFKR3UwbERaZFR3eWNOX3VWZm1JMlVpWlU1OHF4dV90TDFBdGhBZ1VlMUlYdGpjU24wU0MxUkY2cy1ITDB3RXFWQnZ6dnNGV09hLUFF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYzBkYWRsamVQdjQxRnI2Z3U0RWgzQlVpLU5KRXVvR0ZjMjBpOEFEQWhVTXM1dnR2NDY2MDNlZnM5UDlOZ2lqSGZCNTZjZk53c0JfQXA4cm8tV1BHbjFfTTdhMzdPMWZ3ZlhuUmVUUXNFRGV0OVhXOElNN0pUODRvc242M0xBRXBFSDdnbmM5dVBFRWRab09FQVlJT0x3QjJx?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2551,27 +2551,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Police investigate 'death to the IDF' chants led by Bobby Vylan at rally - BBC</t>
+          <t>£1bn boost to drive UK shift to electric trucks and vans - AirQualityNews</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sun, 15 Mar 2026 16:25:32 GMT</t>
+          <t>Wed, 25 Mar 2026 09:09:27 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFB5NzZOaXBfM1hDU2RQa3hGM2RXcUxkcElIZmcwTjRDc2hjbjRFNU1LWk0xSXlWdHRTenl6TWdyaVRfRUx5cEE1cFpCTFNVRXZnR1NPT09LYVhsWUxP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPdmRDNEZ2QW9iQ1gxME4yLWdmZ0VPd1d4eTYxZ2Z4aXpNdzg3YUpaRmItZTJUN3NCLTFuS0dBNndwRXhlcG0zVWVQMzdYTVRKN3NSSTJYU3J1SUR3cXloU19jZDFNdGRhZkQ5R1NmaGtTNElDQUUySkpUNzcyeWttTVBGdEJPM1lsWjh5dGVGUlMzZmNRNFZNa0pGbnN5RlFaQkNJa3lvN1Bxdw?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eugene Police to host hiring workshop on March 21 at headquarters - KVAL</t>
+          <t>Man arrested on suspicion of murder following incident in Crumpsall - Greater Manchester Police</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:24:08 GMT</t>
+          <t>Tue, 24 Mar 2026 21:23:00 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSGE2S1VuaHZ6N3h5eElwWkZ0NzdJVklHQkJZWHR4MW8xajVTODZHMWxzaldGX0NDaVNRT0wycVdnejIwMjNycG54SVhhTkJUNmZacjhEVU1OazFLbHFJTWpLYUs4bU1zamNrOXE2X0M1b09qWnk2UXR2RHZNWF9hRDNRQTFBOG15YUVFaV95QWtZTVFhcEpmZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQN19OTTlBUE9NNUdYRElZT3IxTkZKYWo1Rkt0SVNjdTItRHRkdWtCbWJXQ2NNbVlEaGVyanMyZmxER3BJeUFCMWY5bkxBbjVuUnkya2V1U1Y1MW12aUk1NkhnZ1Y1NXo1eHFMLVNHeld1QlRubFF1SW1melBiTkVicXBNYzRIYlV5YXBnYVNVdUhvZ0QtcnNSYmotc3JnYWptR0hxSFhCR1NMQ09XVjBtNi1vdW82eGkza3NzYw?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Baywatch icon Alexandra Paul ARRESTED again after animal rights protest saw her free beagles from lab breeders - Daily Mail</t>
+          <t>Appeal for witnesses following sexual assault – Buckingham - thamesvalley.police.uk</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 01:41:00 GMT</t>
+          <t>Tue, 24 Mar 2026 12:20:00 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVm9MT1VFS2h0bWZKaEVWdlp1YUVyd2pwVF9HOUkwQnVjMUcxS045a3M5N3Vqc2tJdmRZYmVyc3hyaHJFSnprSGxqR1RLczFnZzlfU3ZpcHZkUkdkNlVmRTFnd3NfcEpXdmVGazk1UnJaRlM0SXB0N1NhT05URGF4bDRGdFFPV184NC1NWmhoemh4WHc5ZzQtRC1UQzljQlRJUmxBT2hQdzV5Z25KV3N6OWdSazjSAboBQVVfeXFMTXozOTktTGxQVzVvbms3M2xRUUJuRUpNNWxKdFdUd3lOWV9UZGVleGlTSGR3RXBjeTJVemx1SEdFV0J6LTFfbTgzZDAyb0NzVmgyaUV2XzE3eXVRU0l5eXNHemJIOHFBbGdDci1tMXlGemNFOEQxdU5jdlBidS1rWXFDVkh3eVAxOEtEaVVoNnRZcmJEeHdsRlpmN0JEY05Gd2xQdkNlYkswbHRZRDFaY001cGxpNS1OZ0Vn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNczM5cEV5X2VTUWVQNkZMZi0zOEhHVFNFOEh3WTBYblVhYnZ2aTlNNlZxQzhuS0pzNGgwaTNwM0FVV083bjhhempHb3Bob3VRWG1qYW9xZ2RsSUxrc1dkOFRGOXEwejQzdllvbDhsQVFFcHZEY3U2VE9xV1VCdTlrSUNRQURZdHZreGZRX3F5OC1iZDJSUU5UWGMyWWt5R1dFMDBpTVZvVWwtRWFyd2U5TU5taDNPVnVPdzZzWUkwd3haUWY2Zmh4ZjRESHctT0NOZldIR2tR?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>UK Police to host law enforcement training March 19 - UKNow</t>
+          <t>March UK retail sales fall, further decline expected - Retail Insight Network</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 08:00:34 GMT</t>
+          <t>Wed, 25 Mar 2026 09:14:30 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQNXhiOC1OS3JTTmNDWl9aSmpTNDhsbWE2NWYzY3VuYlJwVGVZcExsSmJpdlZkVXRvOHg3U2d4RzJmeUF6NkE4WG8waDdJRUFkcXcyWHA0RHVtdFkybmlqTXV5NTduNmlIUlQ4ZnJ6M3FCMVUtN3B3OWFKZGpmT1BEZ2ZZeDMydDBS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5URkhnS2cwNDk1NDBQeEhSZ0JEeWFmWnpvamFLdndVZDhWR2JCTS05TXF0djlnZEc1TWZKTkQyTmlwRW85eHV1N0NHMWU4T2dlMkJicUh2SENUYXBjYXNKRnJlVV9XUEwxWGczRi1KRUpQenJ2MnlZelBiRQ?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Home Secretary grants police request to ban Al Quds Day march - Police Oracle</t>
+          <t>Appeal for witnesses after man dies in A64 collision - North Yorkshire Police</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 10:42:14 GMT</t>
+          <t>Sun, 22 Mar 2026 17:09:00 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNQXVWRDBRd2JNRkc2UDA1Qy1oUkw4T21TT3RuWGw1c1pJVlNwOVpaSzFwY21Xd09LenJOMkppZHo4bkxqNjU2d0k0Z2tTcG1jS1diYzFWNEdrOFFWSlBGNGpBZXlMT1VPMDNOcTdnUm02UUU4RzMyN0l4MjhTUjB1SVlITGxmbUtBNDV5QU1xZnBaSWw5T29NdTYzaWNZTlJoWnNsUDczVDFZNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQUy1LWlNHSmFIbTdPcU9wanhfVkhVbUNkeVhtNWlhbm9YbkhlZ1FYT0hPbGtFQWlzSXRSdF9McWF5TDd1NWlTRTlzeUhISzRuYlBNNHFfV2RYNmpZaFp6TWVaTm1qdFFod3ZQRTdGY0RWYXFyZnpKTnlFSDVRN1hZb3U4QjFMRlpzcDJkak1kZUZQaThLMlpaQzdPZ0RUUS14TFNzSmlIYnhuWUtGT1JJR2lfVlNGTlZvSS1sVE1hNjBIRGhqRTRvVmhTbF9YZjJHTFVGaA?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norfolk Police need your help to identify commercial burglary suspect - City of Norfolk (.gov)</t>
+          <t>Two men arrested and charged after guga hunt protest in Inverness - BBC</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:49:45 GMT</t>
+          <t>Mon, 23 Mar 2026 11:22:01 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5ITlFMLVNuTzRuc2s5NlY4Vm5XTHJjUjBaTVRia2RiMnMxVTBWeVV3dklsRjFBVjVuTVAzMkl5TnpfUk4wNDV2OFQ0ZmRJRDhaNXBIbmlkcmZLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBPWnRjUlJDOVVTeEc4UTVfX1lQNTgxLThhamhqOVBuLWpaM1pYYXR5NjRhQjBwS3VrZUNMQm5EQWRxVXRxYUtUTkQzbUYzMlRXbjhXZHVqZGlRdmhN?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alabama guard Aden Holloway arrested on felony drug charge days before NCAA tournament - Los Angeles Times</t>
+          <t>Cartoon 25 March 26 - Police Oracle</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 19:15:45 GMT</t>
+          <t>Wed, 25 Mar 2026 08:12:30 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOd0h2NkR0WmJRYm94eVA4MHBUMmU3bUhUZlRFd001aVBFcE9nNzQ0V1pXaUtjMXdqbjZRTEJJYkhKa0pZWVotX1ZFY0pEWTlYUWpfcmROcjNMdjYtN3NUYkdrdWwtR29WT2FwdEgyQUFhbkFqMGNDNzBlbHRGNG9ValV3TXN6Y0I1b0hVbUFjRlZCUlpTVmdnSXBJWkZUMzFfeUswRHZCOWUtMGJjU1hCTnpySC1MYlN6eTM0SHM2b3M2b0tyTlY1Y2R5RXlGcU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9lOW1BUzdPTldhYlh5ZkFoSncwTkZNdVhkMzBQa05CYWJzRndxekV5NGtnR0xDT3EwTTVvWC1aaXN6dElqRWE3SDZsMk1yOGNrbHZEN0h5S3h1d3BGMDJ6Qklmel8xTWU3?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Surrey Police vehicle involved in morning collision, no injuries reported - Peace Arch News</t>
+          <t>Lawyer Akhmed Yakoob in police racial abuse arrest - BBC</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 22:34:32 GMT</t>
+          <t>Sun, 22 Mar 2026 15:24:38 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQcHZxT2NfNkZVSXBpbVpKc0NYWFFpX19BUTdTcmtXckRuWjlGSHdDdk1mdEl1aUVUWDRfWUZpbmM1emdhWFJEd1FIbjUtbVdzaU5sS2ZLT2Z2SjRKRUFGa3JESWVOVUxKejJhTXZRQ3ZuY0VkeTNqMkNEVFZ3ZFBBTUg3UnNVZDhsRFBrZW5RWm1ReXh6RnptWVNoZ3pKQ2dMZEJta0RmMlNvMlJFekhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBTS2FWOFpwRFZQN18zTEdhd3I0TVVsNEM4QWMtTk9XSmZGMm1qQm9nMlBnS2hUYUJjR1VKZGhfdkJfRVF6OTM4YV9SN2ZZd0FqNDJjc3N1bVR3Zw?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Trump demands NATO and China police the Strait of Hormuz. So far they aren't joining - NPR</t>
+          <t>Leatherhead : Police seek 38 year old male in connection with 19 March assault – East Surrey News - Leatherhead Living</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:05:59 GMT</t>
+          <t>Tue, 24 Mar 2026 14:41:51 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQRFdvSGxmM01ST1JyV3hvNkxTeTBsd0R0SUZ6MFVYX2lSNjUyQTBaX2xrUDU0QUxWR1pHU2JEZGJQTmdkTEFxc0JETWxXSGpOeWtfcGZ6U1ZVSUk4QjVSZko0Q19nd29zOFhHa1VqaWRQd3hUVWxMWWh2bWtJT25MZ2xJSUVhZ0ZkVlNubVotZXlCZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNSDVKUGhrdnR3N1Vuc29hXzl2bWVXTzAtVW9uWHU3alNyX3FvZ0tLUWU5bGZjaE44MnNSNm5jWHk3Sks3ekJ1VXUtczdrUEFKSFdYY19TTS1EWF80MnFTeUh3QTV2dHpfOVRxSGpreTRkZlhra29aUm1qaTVOdnFoY2k2Qndhb3EycXltY0V0OTAzRDhlXy0xd21zdjdpT09uRzJKcXVEQmZjdHpIcDV0YVZQakhzYTVPNHdFZkdHWVhpSjFYa2V0Z051cw?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Police, fire blotter (March 16) - State-Journal</t>
+          <t>Police helicopter circles over Sandbach to help find missing man - Sandbach Nub News</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 03:27:28 GMT</t>
+          <t>Tue, 24 Mar 2026 17:32:42 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5XcTNfTTFidFJqbThZSlBGMTFRdW1tbjVjWkVlS0o4WS1pT1NMLXEyR28yX0ZhOEEyM290cHVWQlZ1NTBMZWwxdl9iZk8tVm9yU3dpMmZPZmdlcUIzQW0xZUowNmd1bjc2VkJaaHd6dmJmVjQwMllZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNY0dkTHRZdjNkQ0tJMmNnMWNTV2FvQlcxZmZUX1NDVnJ1VG5WRjhMOGJOcEREa3dZeTdmaFotNVk3MkVvVThwdkhOa2FoUXptYXZFRC1CTHY3R1JyajhPckM1ZFVfd0t5MlhDZThWdG0yRzBnVDRvX3dzVEUyT0RBT29OVlBDcU0wOHVSRnZYTzlHWE56a0VuSk1nTEhpYjhHQUE4T3pVajBlYm16c0JJUkhodw?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2851,27 +2851,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UK will win AI race as Chancellor sets out economic ‘big choices’ - GOV.UK</t>
+          <t>BTCUSD Today, March 25: Channel Reclaim Meets Weak Retail, Quiet Whales - Meyka</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 11:14:30 GMT</t>
+          <t>Wed, 25 Mar 2026 05:15:07 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNS2Q1REU1YlB5VFo4Q0stclFISkpVc3p1Qk5UVDQ0b093Mnp2dERSQWVxNHhLaGx0LVpya0I3Rkw1dzVaX3luYm80QkV1ZHVBTHFkV1VVUmUwNHV5blhfc2xWZnNWQVRSY3dNaXZuR1Q1NUdmTUlycUJVZ0V0NnFabFlrSmVwQU9rWmQxRGwxb3poU3lSMDZoX3dGQXdFd00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZnVTT0pyNU9KTmJCR0hxN1hxNFF4TGlVaWdQQk5oS1JmejBKdGJjVl9tVi1iU2Fqc183aV9LWjZmVnhFYVB0NXBleFV2RDEzWFNmVkFoTXgwMlpEbkM2VUJaeEd3MkJIbUo5VTNtVDBMcFFodjhrcURVTzF0bnVfcXEtQUdwQkNRUGxXUzhSQy1lUjN6MUM2YzdlajFQUQ?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2881,27 +2881,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Salesforce reckons software and debt do mix after all - Financial Times</t>
+          <t>Student at Stamford's Westhill High School arrested amid mass walkout, officials say - Stamford Advocate</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 14:42:40 GMT</t>
+          <t>Wed, 25 Mar 2026 00:39:56 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOYThHVlRPVjlNaUROeGlrMmJMdjBQS2wtaVNyNk40MG43UWZMU1JRcVpNenVNM25xRmZFQWxSeG1pUE1jcjNUbGJSbkxpNjdCQ0w2eUc4VWV4ZzdLcDhLX2tpT2hkb0xDWEN4ZEFiR3RLSDM4WkJ0bi1rMU1VM3hvdzUzWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxObTI1VDhGWXQ3VENUVDFlQXFBNkYwMlRmZWVtMzE1NEcyVFFVOGJaemVFU1ZseGZ1X2dSTlFETFFfS3VyQmxOYzJPb3FFbHhEeWpjbjc5Mk1iby1Pb3lKODl4RWozMXRzLXZEUkpZbjFfTTdGSTd4TTFzTkVjNnNBUS1fSlo4QmtFWFZ6MUR5RnkwdENJOWtlR21lQlQtdTRJOG1WbXpJb1NxUQ?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2911,27 +2911,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AI and cyber security: risks and opportunities for organisations - Financier Worldwide</t>
+          <t>Police called after car ploughs into wall outside Crewe dentist - Crewe Nub News</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:53:40 GMT</t>
+          <t>Tue, 24 Mar 2026 19:15:46 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQcUsxdF9IN2NlOTJ4elBmUlA5Y2pGSlJXSk5TT3RjUzYyVzZrcHJhdWVwVW9XWElkQXItZWxIZTJKNzloUG5rY25qVEg4YmhMX0ZqRGwxbzN5SmJHcXdyTlZveVZYSlFVWEU0S1BJcy05NTZMSlFsOXpNMGJUSWJVLUNLR2FOb0IyNGlfT2JIcWROUXJhcVpQRUphdmktcFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNTjRySnZ6VEp5M1lYbFFncUlSaEJibm9SM1IwRm51am5UUVIwY2dKTFp1UEZBMy1kSE1LUnA4WHhjbG0wUFk2Vk9mUXdZSVl3emdyblVndll2UFZxSDBHMkFzOE5CSXY4UnljTnFJVDJaSlFuSkNUdGl0R3gwZFR6RDE2MGVLLWJKSll0d0tacWdJRjBhTWZBVmFwVjB1UlZZcG5uYnhRS2lWeXZkNlE?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2941,27 +2941,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Government probes use of AI in children’s social care - PublicTechnology</t>
+          <t>Iran at war: Scenes from inside the embattled country - Reuters</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 01:15:56 GMT</t>
+          <t>Tue, 24 Mar 2026 15:18:00 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNZ2E0cnlDdllXbzRGYlVLUVZiTVpMWjZUQU5fbWJabG4tLVhYYnRjWnRUUGlralRjM0J3dmlaVXZqX1lTSDJXb01PMmxIc296dkl2YkFzbUl2aEhoNXVVWUp1Y2VjaEN4UVpNMl9LTmxFaTgxcXVFYXRVTUZaa19XdV9tMDlpOWo2d3pzSVlMTXR3NnVpeDZfUElXc1FVLVVaS09tWHdxbVFjUjQwVmhaZTAzblgyenhvT2sxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPbjZqdmh2VXBYS0RWMmMwT1h1V3RRanBoVEFPc0k4RktsOURoRG90aXE3TUNHbEZ4b0VRcVlZZEUwN1BIQmc0NWQxM3RIUFdpSVN2T2tYWWdUNDd1aWxROUs0TXpQNGpSZmJwUXAzT3lHdXNBX0JjeHhiNkhlUmVCY0RZWE1mVkZic0ttUmtB?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2971,27 +2971,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>What could ‘AI-native’ stores look like? - FashionNetwork France</t>
+          <t>LDF and Co-Counsel Defend Protestor of Police Violence Brutalized by the Police in Qualified Immunity Case - Legal Defense Fund</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 04:56:08 GMT</t>
+          <t>Mon, 23 Mar 2026 20:01:22 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNRXdxckY4ajhzTDVId2hCMmVQcHphZDI3N2lFQjhkMk9IV0F0NTFQUDhEU2d4MEk1R0tVQ3FKdGdPQ3lhcmhBMTltUnhUTXUwM2VRNkJrcGJLeElWZTk4RXQ2VkI4c1pZSTZqa0hvYl93dWNDQU5USWFBRHQxN3NTOEExZklKam5iVjdVdFBGaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPM3RkUjlRaGdVQS1wNVNVenRTb2lycGJSQmgyTFRiRXdlMEx6aXJ4eHpfdUVFUFJ4S3FnUTBocmNCd3I0WFh1S0F2eTRBVUtvb2Y0YjI0MEE1Zjc2MFA0QVlOQmtyUjhUeU9VcWdxaTdKZkVTUllLN0RXaGx6cC1YYUx4aWZKaWUwWmk3Wk1RMWhEbnJPSlNyd0tXdkk5SVdsTWFZT3YtMGVVbGllTlZfUUVXZGFFaG5xNl9kTW1BNGJveWkxS1l1TDRNZ0syZjNqRDg3bHkxaXNOdWg4aDJZ?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3001,27 +3001,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Siemens introduces AI agent to automate semiconductor and PCB design workflows - New Electronics</t>
+          <t>Bizarre scenes: Wild act halts CBD march - News.com.au</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 00:02:45 GMT</t>
+          <t>Wed, 25 Mar 2026 05:13:19 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQVm1KNi1hM18xRnBwOEh5V0FIbXdOS1RocWFvbGkwTnRDd3lrN0RUblQ3RFRscjZCQUhRUlR5eWFjU2JQQmhFVDcxU1VYX1BjM2NmVlNxZm5tSkQ3eVdRQXlDUDFTZlpiUm5BbWRPd1BCNXgxNWRyOFJnSDlMUC1KcEJHMlBMOGw4b3NiNnRqdENYUmd6dnlVcnZRRHBCVk5QUDlVcldvWHN4UlJ0cFh1dUhBLWIxQ204NGQzTzVHQkF0dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPbGFrWXZFRXc5b0VUMEVPaHY3cTMyS0R2TmVkRWQzemJjdjRUaExKWFdwcTZwNDEyMXpzaXNqRkVkdnhzajJLMS04Y0t5cFBHejJwNTQ3anJ4WjBtdUdiZDFOQ21FRkVGQWVFWHUtZzRoQUdFUzF4OWNvTkl0TDVISmpHdWZhRVFOMzhscHNWVWVSZ3RaUmpEOWI0cWtibm8tbDVaOVFSRUs4X0ZtQlJUMEg4cGM1NzdFNEZHSU9na1hyaGF5dHVjWVpDV1l5Nmc4Z1hPV3dkRF92MmlUWHY0Q0dLR3RXdHZvUC13NUdzQ2MzQTjSAfgBQVVfeXFMUEw0eS1aODc0cWx6TG5vTnlOdmpnNG5BVlRmd05hRUM4TE54N0dOM2ExdHJRdlIyWFJTYmxqektmelpEd1ljMXJ2UTdWbmdzNUEzYW51NVMwemlJQUZhdTdCbmlYRXdnekNfNG42UUNuUXVsQmZ2ZEdXZ2F2WkRPQTBoU0NBQWdJRnRKNGtTeFBFUkk2WHlDY1VxVjNHUVF0RVJlalV2NjBYNzR6TVo2MEhUeHJfTTlMVGZKdHdVaFZod210Tzg0TEdxaGNqUG1PeUFoSEJGd3V4eVhVR3BpczJrR29hT3pJRUgyZkgwS0JhS2M4azJXOWk?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3031,27 +3031,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MWC 2026: adaptive devices, agentic AI, and always-on companions - verdict.co.uk</t>
+          <t>Seth Rollins gets ARRESTED: Raw highlights, March 23, 2026 - WWE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 14:22:10 GMT</t>
+          <t>Mon, 23 Mar 2026 22:25:29 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOS3U5NWhyQ1U2VDVrTkFjUDRLbU02cFIwYlZPZEh0NHZMVTE1Z1NRTF9jS2tGdzducXNUU1lLb1JLRm5naGVMbmhzcjN2SmhfLTltMDlPUzdaQjh5bXZlVU9obF9Zc2JHU3JZTi1YMV9ad2lETlZldW1GdVRIckxJMHJFUkI0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPOTZCWGNfcDB3RXo0NFlhUW9YRVZaQTVMSlVJZFZrZ3RmSDFmdEtFSk9zQW41WXg5Wll0Y3huTDRqTlkzdk9mcGZ0ODk5VjU0V09uc0tjTG9majhRczNVQ3J2U3YxVGQ5TEZFWVJpY0c0a1BQalZMLXNNZGFFTUQ3SEtpcHRzeVFGa0E?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3061,27 +3061,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Majority of European businesses now use AI, but startups signal early warning on scaling challenges - About Amazon Europe</t>
+          <t>Glen Carbon trustees approve police hires, $1.09M sewer project - The Edwardsville Intelligencer</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 23:11:01 GMT</t>
+          <t>Wed, 25 Mar 2026 04:13:40 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOMlBMTE9pTmtyVGFjbGpobVIzWnRZWXpWbFgwX3hwY0tFbzVzdjkxZ2NyekZQQW0yUi05ODNZdDNtVFBLSXg5aTRHalliWDlaQnItRnR0M2xyQVVkUWdJTV8zNmxNUVVWc1ppNXNDeWYybldPRWNnbFhTOHNnZ2wyc1FYY3JTM0tLQWw4cl9tQ3BGbjh1NEVvcExIcnNMTDBBLUNUczcycGFrM21MaU53eDU3cmpoUUFPcGdPb3RwMnlTR2QxMm9HN05wNTYybkNlcTF2QTVvUTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOeGFGSzZ4N0hfalpySWg0cWlETDF6aUVfNWhVN0ZwckVidnJGc211S29vTHFITWNYZXgySXp5MEJrc19zWkhWSWJ3U2hlMFBBVWVrVnY1eHQ0MzVhVlQ1YklKLWZMQVlvR2FLRXE3a1lDWGh6R1NOdThPX3hHTWZDa1J4RnYzYWJmVmd5ZVVodHY2YVlLZjJVNXpOTQ?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3091,27 +3091,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Europe Has an Edge in Developing Applications for AI - Goldman Sachs</t>
+          <t>UNHCR Somalia Protection and Solutions Monitoring Network Flash Alert 10 | March 2026 - Clashes in Xawaadlay and Yaqbari Villages, Middle and Lower Shabelle Trigger Mass Displacement of Over 8,600 Civilians - ReliefWeb</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 19:00:25 GMT</t>
+          <t>Mon, 23 Mar 2026 14:03:16 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPZk5XNFRtYlNUb0ZhU0w3UGVhVXZqTXh5aDVxUmlIdDJnZUtKVDlXaXQwLWlTLVpudFYzcHdPRGlIZmViUERYWDRCOUJTcVNyWEN5LXYzdEdveTB0ekxETmpoUzV2MHJWR0Fna04xclBZWVpjNnF6SElPYXMyM3BwUUtSRFp1S1NraFFKYWJTN3BDT2ZURDU4NjJDaTRGMFFW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AJBVV95cUxQVUJvSW5rOHl6WnBLcXV5UTFfZEVVeHl3UnFGU3pvM0xPUFFBa0ZTbTdpWjBTMUNibVRhdHpoY29QNTNJeEhyV3ZiVEdvMS1RY3RDLXJrTm8tVk9tMU5Iei01VUZJQlZGSzhWLW9qRU1LVGJSYUoyNnUwdnotaGp6NndDNmNNdk05cUpKMW83Z3E1Nk1ZbHJLXzctSDhLWU9rLXZNU1hKZXdmNHNQeDhya240MTVxVnpQekFHeEFwdFptNlVpdk5pREtIbG0zZTJKcUgzcFVubnZRN2V0ZHRYUmdhc1ZZdXYtWnhQa2NuQzdNZjBvd21BWWRDRS1SMmtvUmk3M1FqcXVraHdTQ1NWLXdfdUdwVE5ONkxnZW9mdnZzM1VqNEVZMk53Skd3N0lWbDZlcmNocmNYZFlJLUVyZ29UNnpQZzYzV0JPYXYyWFo?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>The AI stories we tell – and the ones we don't - Journalism UK</t>
+          <t>UK payments priorities for 2026 include agentic AI and stablecoins - Linklaters</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 18:55:43 GMT</t>
+          <t>Wed, 25 Mar 2026 09:37:28 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBXWkZIVEhlazM2WXRwRUFubjVod1FhN3BLVGhCekx5TzdVNVYwZ2F2U3dnVUgwNno4Q0pwRkc1TWI1MDhfSmhPT05wSVRFLVMwOWhsNXl5Sy1kSTFJOXpjUElQSFpuT05lcDZCcnlEOUc2ZFdIWklVU2JCNTUzUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPYlI1c1NfMWJVU0htZTBoNENha1IzMUV5cGx6RGZsM0dPTVJaUTFqaGFVMjJoWlMyb25ucGRGMGE0TVhESkEwSUVhQmFQX3ctaG94VDFCd2JfajVoSTRfS3k0TllnbVUwbHZFVGRlRy1RSTFsOVhUejNsckZwcVBkYnBfbER2T25feWg5bVo5cTdBcHVka3o5b1lJdjYzVzh1NmVZd1BjbFhyckZreExDd0d5UWZ2MVJMNF9ldHVJQQ?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Node4 reaches Nerdio Gold Partner status in six months - TECHNOLOGY RESELLER</t>
+          <t>Revolut warns it risks backlash over support for energy-intensive AI and crypto - The Guardian</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 07:39:17 GMT</t>
+          <t>Tue, 24 Mar 2026 12:46:00 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOR1RsaDNDMlBwMXNIdWhHcnkxQzFncjdEOXhYLVdVYXVHTGd0ZkpOdjV1NmJEeHFhdGswZnhFaHdiMnVmY1d4QUVmcndJTGNXUmFSR2c1dUc4bElPQld3QkRVN0FIYlpMdnd4WDRRenhBR0QzOURyRzJDemR4dWlXRGdYSjlKc0g5cTBQdlZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOWTFGY2p5am91UUJETXZPRWdDT1Q0ZVBMdFAzZU5oR1d3emwyVUc0TFZyVDdUNmN1VEV5UDVQc1ByWDFCVFFSYkYtODROS05uZ19WMnhjSi1sbHZ2R1U3bVAzbkR2cWNvZTZGeTBwakZ5bGRkY1AyXzdnemprdGRHSDYyNEJkQnNDT28yNktkYTBESkREM2JrRXVDYnQ?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Press release: AI at work - New LRD union guide to shape its future - Labour Research</t>
+          <t>Iress to host mortgage forum focused on AI and connectivity - The Intermediary</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 16:19:31 GMT</t>
+          <t>Wed, 25 Mar 2026 08:57:08 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQQ3A0MTNDNGVjdmNXSDJIUWpDNWhJLVliVVdwaGd0WEUxYXJxd3ZMUkI4V2I3cUhDZTBORHhVOWpERzJNX0ozSTV6MHdweEVoV2gya3pNcGZ1WnhvLWVZTUNpWHJBcHNrQTdEVThSbWNCSGRMc1JBOUNCd3FGS2pNT0c2cWt4cjBiSHVRZ01nSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOSFdvWlAtSGxnenQ3RHFHeGFTSnI1T2pya0k2YnZRRENZdkRCRndjQ2tsVmZLNDd3d2hpbGhsdXVzREtzczU1alNGcnJ4NmJGVC03ZzVDN1I4dHdVSE9RQk1uNFJwTTA0R3paN2dNS09OMzJ2UHctOWtYOF85SkgyZVBUZmY2eWVxSldmZDJVc29rSFdMSG1ja2VfTG9xSkE?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Global Underwater Hub launches underwater robotics and Autonomy Forum ahead of 2026 annual conference - Aberdeen &amp; Grampian Chamber of Commerce</t>
+          <t>AI and the euro area economy - European Central Bank</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 13:00:34 GMT</t>
+          <t>Mon, 23 Mar 2026 16:02:01 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPNFlWdEQ5cG9WRW1WZnhETlRWR21Uci02Smtxdk5XTzlyUm1pbHExVnplcGFyaE8wVWtJWG10cWVwbk1LMTM4bG0yQXVEei0wcmhqMTJpX295QzctZ3VDU3hYaXNFaEdCVms0b0JuSjNxQkxHbUhjSlR6am5JemZYbXdkZFRnUTlBblRCTldxQ2xqaDE5SnplYmRMYWFBR3g2bFk4ZEFIcmNTZVVnV0hxc0ZtcEFObkRhS1d2c3lGTDRTclhTbXk2SlRGeWtycTlOZC1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPVXJOaHZYTU1TVVFqQzZ0NVlfd3h1QTJsN0s1c0xvRVBMb0NnTlZXMjkyUm4zTm4wV1BnUnVHNG1UOUNvN3ZwOENEeUNRUFN4M1ZteGtnVHlRQ2tfaDQwVFpFd3FSeXVpUW5IM0Rfb3l2OWdtS0dHUWUxd2tUOEd1RklEVThnazMzZHoyeg?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cadbury's Phil Warfield: Inspiring Generosity, AI Adoption And LHF Creative - Creative Salon</t>
+          <t>Advancing citizen-first public services through AI and digital transformation - PR Newswire UK</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 07:19:59 GMT</t>
+          <t>Wed, 25 Mar 2026 07:48:00 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNWW9qeXJDck5INS1HSk1FY1JtWHJfVmNua3h2SXQ4aUlVYjhpNTVoNGYxMDBucWRnclM5MVdWaVhCd1dNcm9ZTC1PVk5GYlNmVzIzZ2VYandJUjhxek1UQmpFTW04Nk45VWNyQ1pJUUlEVm54NVAzTnZvLXpHdXJiR25mSXlTZWlWT2JZSWFqRGRzWnVsQ3pMQV8ybE5GQ2JBWFREN0tjYmk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNQXlZTkVvUjhjS3Q3OWNzUmNRbmg1N2pGYko2N3g4bFQyM29NdXBUcGZhVHZFWEJNUXdJczk0d04xcENueXVPQVN1ZGV4dktSbTV6RGZxdmh5djUwY1hoeTFuSUhsbkJZRExxRUJremI4X2JYMUc0d1hVVl9reWZITzlhQ2ZtUlBSN0ViS3ZjUlh3T0pMd3dzZ24ya3pJVTFMQnFFbmwxWWQtb3FBN3pRbkQ0M3dlT3RoQTM3bmo4VGhvRlpkSVVsdUNTYy1jOUND?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Are the winds changing on the AI and copyright debate? (via Passle) - Slaughter and May</t>
+          <t>SafePaaS Announces Federated Identity Governance Architecture for Multi-Cloud and AI NHI - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 15:04:05 GMT</t>
+          <t>Wed, 25 Mar 2026 06:15:00 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQdk5KZUo1WmtQNkJOeFpVRzFNOTEtM3RFSk5aNFNlTHM1VkprcWRkMGpTTlFnYUxoZmtZOE1Jb3RjM2dieXVoUHQ3amF1YXB0aUJNN0tsZkhncE9PcUhNZUtEOThBVlctQ0JBMndnZWtxR20zRGlKYm44VklsdWhQWVNyZm94eXFPMElUcXRMWjF5Y01SRnhHa2EzbHJmTlljaGw4Rw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNWFVRTElZZmVJbUZDUVZXNC1VTkk3emVCOGRjVDhETElpTTMtT0IzMFozMTdrcWZ3bHgydlp5dFNQdTZWY25FWnFzVFZleUVFejYzSzBERGkyVVV2dUdnNTdzMDllYnczUGlDRWh5WlJJek5yYUNZTmltaG5SVHVwa3REYk92SmJMZ2JONjhpdTg2S3lodkctSUY3VVJRUQ?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mayors to gain more spending power under Reeves tax plans - BBC</t>
+          <t>Manchester tech event to focus on AI, trust &amp; risk - IT Brief UK</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 18:26:30 GMT</t>
+          <t>Wed, 25 Mar 2026 09:30:00 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9hdkZCcndvNDBEdXdna1hGOU9ySlFvWHFCVDd5dDJKeF8zQjdiTnl0Z3hjakNWM1dnYjRaTmV0QXNlTGxGSndaaE45X1BMbVExZS1RRVFJS0ViQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQN2hkMEFOR0E5X1pkU1lkVlozSllfN09qTExpYkRvZjFqY1pkNDN1TmpHbWk0bC0tazZwdGdSMjE1WWZWMXRXX09PNmxmczA3d3hfdkVCMm1WNEZJamJXYU5YUldCV1BreVQxbzFSUUVfejc2U2FXejBWb1V0OGlKYQ?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AI workflows keep marketers too busy for the day job - DecisionMarketing</t>
+          <t>White House proposes a national policy framework for artificial intelligence - Norton Rose Fulbright</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:38:00 GMT</t>
+          <t>Tue, 24 Mar 2026 22:32:02 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVlVYazlMMEtHdXVTbEw1WnREYXJVZlQ5UGI1dEhWdUNZOFVJY0xWQUVXTzRQNi1FT2NNb0NjeDFhUFVhYThnRkxYQU10eVpoaGRKclkybW5UNmRSam9BVExQU3BxUWhYZnpHYklxWTBQMHVRT2lPUzZnLU9BTFdPQkNyczVaWl91VTQ3cmNFemlOM0N2ektVaEJac1BRVEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQQ1FGZUNMYS1qTmZrWk9jeHdfVlZVRFlWdkFxRE8zLXJpUGxYa2lWbDJaMU82UGtBOUlIa3pTTjlHUVdaZ1FYQTVxZE1IRi1nalQ4alBLV0VDTmRkeDNkaEpoVlFBYkViR3hta3dyUXlhWFJSUFRxZXBvMkRiN2RmQ3Y1ZkpGQ2QtUHRaMjBVNW9xMWxLU3VBNUdkOERPUXV6cy1Odm9oTFVzaGpkTExqZHVvdmJRUldkR2szWU5hcmdia1ZxMzBoWkdITWJhVVVwZlAxekVkRXNLT3lWNkVWMg?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Taiwan - a critical technology hub - New Electronics</t>
+          <t>Student helps Liverpool manufacturer adopt AI and digital tools - Growth Platform - Liverpool City Region Growth Company</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 00:02:45 GMT</t>
+          <t>Tue, 24 Mar 2026 15:43:09 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNTGN1MGh3SlhEbm84YkM5cjAxRVFISkJVVUR0U2ZtNXltZXAyRUU1aGFyd3RFTzNRanc1OWJvN2E1cXg3YzdaS1ZZalhVSm5JbjVMeUhjMkk2aURSaFl4UXJRbVdIVVlETFJiaFd6bm9HZ3NuS3RySU43RXlhdFFtVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNN2o2NnI3eUM3V0NZY3VlMW42b2dFeHJUMnFCUDVsSzRZUnNObUFSUjJNdHBpWkI4aGZFcFdpcmZGdDJoMkdPc2lHRkllMGRNMTM4Y1BicjFmWFQydFpBUU5UZ00xbHRDN3pxT2V6eWpWM3R3THZWMmRnUlg1V1R2Z1NDSGQ3SW1TaUx2V2FKZ0FGRjM3RmJNa1k4dURLMjlWa1dlTUROOA?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AI and Big Data in Surgery: Emerging Evidence from the Frontline - European Medical Journal</t>
+          <t>Nota AI and SiMa.ai Sign Strategic Partnership for Physical AI Technology Collaboration | Corporate - EQS News</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 07:35:54 GMT</t>
+          <t>Wed, 25 Mar 2026 07:10:25 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNZVJxUTM1ejlNc29mYndhdFl4NUVBeFlPR3VuQ3Z6QTBpdUFFb3RmWExZa3lSMi1CcV9NWHlNcndYQmNfRDJvVExLT1BTWER0VEZSdnlSZjY1WjZ5d3NwRzhJVHhULU95VjVZM1h0TEgtdGVZNjFSZTh4RUlkTVRQWDhUZzRJOVFzRmRSNWg4ZEVFZk9NMW5TRTBONXJWdEdNLUpVZm41c25ZT3U1Q2hJeG03ZHc5emc5dk1QVEREVnBkMjI0WGcwY193aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPdnRBMGN5OGlad2phM1BJZmFINHpabnliTXFmTS05UEpINHJvcU1EYnVMN3pMbzFBcEdTTWdXNkNtWEJxZXRnanhYdVY0ZHc4cklIcFVmb2Zwc1U3QXJydUkyMWRQbmZkVWNGSFZjTV9TUzkxM2p4UkRZek1iNWVNOFpFR2NIWEI1SEExNk1lb3RZRm9hd0xiWGJNWUdpcnNtcHh2aXpOODdHSC1FU0U5RExVbDdNLS1TTUJ3clR5UVZiMlJYUFQ0T3ZDc3FPNlBLX1lZSVNMZXpTZ1hiM2VIN3ZEOFFJWVI3MDE0QTMwR2FBWHRZSUxEQTJaTQ?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>India's outsourcing industry is worth $300bn. Can it survive AI? - BBC</t>
+          <t>AI in Finance Function Gives CFOs Speed, Scale and Control - I by IMD - imd.org</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 01:12:50 GMT</t>
+          <t>Wed, 25 Mar 2026 07:27:49 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4wTHVnbzFpczd5Wk84XzJjRGZmX1JYX2I4M09UeDFtLXpDVUZYTTBvXzl3akhHLUpHWDFqN2RDMTRTLS01bWtnTktlYUFxZ2x5VlMyblRFY0lydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNWUk0OEJfV2ZBbmJLcnRGQy1PLUlxTTFvR0F5aWdHN0ZWSjVtUHRISWdYT0JyaVphOHhvUVkxVjVGdDlTSnVBcm1pY2JGcE00ckdfS1p4dWNua1hqZWNoU0NaTjBCSDd1bU5MT1AzSHpsaUM0V2N1WkdoNTBucG4xV0hCTGliWTBNaHQxckpCQVVlMG94SGdjZVU2MVhaWm9NeDFB?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>7 Factors That Drive Returns on AI Investments, According to a New Survey - Harvard Business Review</t>
+          <t>Openreach Taps Google Cloud AI to Accelerate High-Speed Internet Access and Cut Carbon - PR Newswire</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 22:26:19 GMT</t>
+          <t>Wed, 25 Mar 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPYmVERHhJMlQtMG1pRllpSHR6emdaMlBkV3FOc2xGZk9hZVcxX3NPaGt1alFPLUI1SVlDdURXdU1ndzRSeEV2eUcwTmtPbVoxRGFfeFlGYzRlSnVNWmF5TC1ZZnU0TGhqcDJDbWFKc1M3U215YzVBM0Z2NGU0bTVIUUoxdFZsUjYtM2Y5TlVUd1QteTMzeGFheHBMTjc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWE5WY0R2U2JsV1R0YTdGYzAwVktJYjVjUkRIOUVZZGNDUnhITnUyY0hocVBZVDhPVHFpdzYzM3VDcktJZ094WU1RRVBoMFhDR3JVdWU5YkZNdTFYTldYVHBDRDZwVm1zeHFMRTFfcmNLY1hzcDJvTWFic0R0bTd4SGpPeE5STXpvMFp6RFRrUWtzdm1BQlIxeVYxcTBDalNGbFFyendOMWEteGVzYk9JT1ZFbGJGc3BGZm9yLUJXVW9QdFFPVXp5RWtCazhpdC0yNl8zZW9EN2FsQQ?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IBM Completes Acquisition of Confluent, Making Real Time Data the Engine of Enterprise AI and Agents - IBM Newsroom</t>
+          <t>Oxford school offering specialist AI and performing arts programmes - Oxford Mail</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 13:13:18 GMT</t>
+          <t>Wed, 25 Mar 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPUHFyR1R1NHJSZjA1T0diQUZybERvZ0RqU0YzQXpYbEdvQkhaVTN6QlJtYXRHMjVPLTFPQ2VYWnpHd05rc1JmWFVkOG5hMDUyX3YtWDdUcEhKMWw4WWxvNWtOLUtacVA5c3JrckR1eEJ5ZmQ5VjVMbDVTWXJSMk1iZU9za0dtbGI3RGo0N1Ftb0hjbEpfYm9FQWtrc21mMEhFb1lYNldNa1RDMmVaU19ON0hDX09PN2ZpeTJlMktEblhGQUVsVnFjeTlBNm1SQ2lwTHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOTW5fS21QSjdQUklJMHN6SzM0MnI1eUduZzRJLTM0UnhwMEFhWEY5bnZqNV8wY2tuTWE5cWFNQkZxa0h1NTNMSFdkNFdjVGpobi1HZFRjZzIwTVctbWdxVkVuUDZZY0ZMWjEwcEFjS3BQeFExMVFFSUVGZ25hN29NdWZzTHRNSTM5TlFrSlZUQ2poLUpsQVh6Vw?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>What's On | Alien Intelligence: AI and Architecture - Architectural Association</t>
+          <t>OpenAI to shut Sora app as strategy pivots to coding - National Technology News</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 06:35:34 GMT</t>
+          <t>Wed, 25 Mar 2026 09:36:32 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPVkNIak15Ni1hWkh3cTY5R0Z3SERSYkVOQ18xT1FmbXhpVWhPY0VKSlh6QnBzVnNBcWtnTzNiUWNyRHZJNXRmVFE2ZFNEalhKcDNyWFJkZnlZMzhINV9vaENmb25yMWxGamxCMFZXMjVlVlFzN3pjbjRtT2ZDWmxpcUQ2dkpPRHdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPN1Q3UXJLUGJFSGpreUZObU5EQUdNNjZMRnVaZDdKV2N6eUF6UHh2bkROeHZadVZGbE11d21rendFcFI4SGIwZGtGTlF5eTRmSldSdndSdnlEb3RBRUJFYlZab3c3R0hJbVpvTWxaZncyS3NVU1RXenNUU1Q1cWw0cUU5WHl5VDM1NlpfWXg2VUZUZTg?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Khalifa University is actively building technology capacity - University World News</t>
+          <t>Agile Robots and Google DeepMind announce partnership to advance AI robotics - New Electronics</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 07:03:10 GMT</t>
+          <t>Wed, 25 Mar 2026 08:18:14 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE53WHAwU2hqa292UzUwZ2RfdWlrOXVkTGZOcFVVWDZxZmxjV3lCRW1fVWcxOGI0TDRmQ1hITHJxSXBhdEl1aHc1X29FNUNaUzlwdVdEM2kwcEpTbHhza2txaTk2ckdwUHZGWFFQd0ZHa1BPOVJ0c2Zj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQWUVOdmpfb0JscWVFclFPdVFDY1I5eFlySnhXWkxNNzhhOTM2Z0FEX2hXM1hjcG16eldLUjI5cGVKcHJoV3V0cWxNUGYwc1pjd241SXFrVWktQzhrUXhWRFZockJ4RVB6aWZZR1BNLWYzRjhFc0Y5S3RQdVRZMHhLcjFoRWo5Y3dfOEpUQ1VxM2dueGZtcWlta1lCamhFdm5fWExEc3pOMDFkWFFTWGtCNFdPb1pCb0pjRmlmcFlZOA?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CISO Redefined: Navigating Transactions and the Cybersecurity Landscape - FTI Consulting</t>
+          <t>Clarence Medical Centre launches multilingual AI assistant - IT Brief UK</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 20:22:24 GMT</t>
+          <t>Wed, 25 Mar 2026 08:15:00 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOV3VZVFRsNzBsX2QwSXpGeGR6aXBDOW9Nb2FXaEtlbmdtV04wU29LWFFLQU92T3otbFgtRHVodktOcGU2bXNWQ3VUQzc0dFRkRHZ5Z2VmaUM2dGpUV1gtVlg1eTJrRlc5U1FBN2VsWGZUSmF0anpjOFQ4MDJrc1JxYUlHMGwyc0lmczgtQkFEbVBBTmdfN1dTRjRTUE9XRDUzdHJtZi1Wek5USjNFUVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPQlFYdEh1V0JhVGVUVWZrWmxnWF8wbUlYcjhtb1R4cFpoSlBxZ0Z6VVNUQndxTDhNbS0tS0FwMTRYYkFnRjhESmZiTlZRNnZCQWNMMTBjYUh4QUxEZ3J2aWdPMUpMX2U1SlA4MkhwNzFlb1VqcE56dVRoRWFyTmNlM2tfMU9CcGdDTHdMOXBVbw?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>How technology supports long-term care at different stages of life - telefonica.com</t>
+          <t>Software Stocks Drop on Report Amazon Is Developing AI Tools - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 16:30:00 GMT</t>
+          <t>Tue, 24 Mar 2026 20:10:24 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOajdmQ3FrRWRWMzg0V2xpUFZaTVJGUmc1TG5oZnRySnJuX21vVmlFYll3MHdJMldHaHJNdU91NzdUaFFSa09rTEh3a1VsaUxKblNiUzVwNVVNTlc5SFBZVmJGU0Ezc3hXcXBkMFpWODkzTTV5MUVOOGRzNkMtbzE2VXU1b244cURubjRYaDJBazB5XzBFMjRXMGsxbERocE83c01J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPTmhjTFVRNlQ1VUNJZTB3NTNkeGJrNnJoWFhzRzJRcUNBY0ZIZDQzM0d3Sl9OMy11RXJDODJZT3hQTGJDVHluNzduc01ycTUxakRTX0k1aWVRV3B5TlYzU2sxMlljUHlUYjRZVVdUNEUtZF9fZDNnOTlnZlgzbWo2cEl2Y1lwenRuV1RR?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Singapore opens new entry path in bid to lure AI and tech leaders - Pinsent Masons</t>
+          <t>JAAQ raises £13 million to extend mental health AI innovation - IT Brief UK</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 12:11:39 GMT</t>
+          <t>Wed, 25 Mar 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOWTFKRFc5RjNjUHRFbG50S3RwSDFHZXRCd0lnYzJVWUFndjgzb09Ua2RlREVTN1hiQm5PTW1QZ0pEOFdZUlVSTktma3A2X1FHT1hLbHctRXZmWlZhcWJIdkJHUTlMQ0lURFRkMEJrd1FXRVdnNGJEQWNyZDRzdWdqVkxTSVhUb0dtZ3JWd0dlcjFUXzVOdFVuUkJFTmhWbU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPNUsxTDNtd0RjcllMR2liSjhaS1VNOEpTQWdZOVh0aHIzRXRjTWZ6TTlYRmg1Rlh3eFhjWFBfMGpzRXhVSElHcmMzejEzN3ZTamxPSkUzc1BWWHdWamZIc1ZXQ3ZhbXFTUkZlUXRoQVZZLUk3OGlGcTlyMGJYYTQ0QTlMaF8xMm9mdzNEZUhYNzU5UQ?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rachel Reeves puts £2,500,000,000 towards AI and quantum tech in bid for growth - Metro.co.uk</t>
+          <t>Nasuni partners with Oracle for cloud file storage - IT Brief UK</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 13:47:00 GMT</t>
+          <t>Wed, 25 Mar 2026 08:20:00 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNeEwxemVpR01CZVlpM1c0eS1pUFItV3BqbW9kbXNrSEZ4TE95UG1XMWNOd3BGUjhlZU5YcWdjcS1oTnVpTkVHeHBNcVNJeU5fMDVnWmFzenMzbDQyVUgxSUw2aDVJay1ZeDVoendlQ1NoUm9XbEZGVmE4OWVIbjlYcVRYZDFNa1B2OXBIUlBPUjFRZ1BLd2c2dUw1SmF0QjlCSnpqbzN4dUhabDBZ0gGyAUFVX3lxTE0tc2xITWphZkQ2N1AweGw3TG5VMFpVdmtDWTBGdFIwZ1RWdTN2UHNQd3VvaUlrQnRZTzRLa2lOamxCdk4xSEpCUkplM2Fyb3RsZWFTTm41UUNNcmtEQzFaNnBrc2lrU0pVS20xb1JiUjlmSmd6U242YzRZX2c0Vk5meXhiOHdEcnQ2N0lrQXNoREgtN1JZTkNpMVNOUE9fNWpuQzdtTTNZeVVITEN4T1JKalE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQNXZsaXR5MHplVkR4QjljMlkzNk1jU3BRNzcyeHpWVXlua1RRRXZJRTY0VUhoXy1kWDRwZjFVX0YxdW8yUFVyWHN5YUtXMVBmcGFfSW11ejgzZWR6Vlc0eE01dGdrQ0otTjBXYmc3Z2haQUR4eExjVG9Zb21Gdmp4ZmVsb0g?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>See which jobs are most threatened by AI and who may be able to adapt - The Washington Post</t>
+          <t>SUSE adds AI &amp; virtualisation tools to Rancher Prime - IT Brief UK</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 16:00:00 GMT</t>
+          <t>Tue, 24 Mar 2026 23:30:00 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQLW5fTVYyUm9aS2hCUXU4WGxvZXlkM1FibGRRTDFKZlJNOWJsdDlvMlBzNVRKSmtsXzEwVGFHS1k0VFNhQ0pDeS1zZ3BrcUdFYTFCNkdXVUhPY3FTNVJzZ2EyTVhPZUx3c3VOSkRGNzc1Q2oxOVR2NEFXWjRBbmZrcGVkZ0laQjl5bmFzUnYxNkx5a2ZaMzhj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNc3QwQVAzUTRhWWFMVEl2Ykc1Qk5SeTU1Y2JUWTg2M2xTV1EtQThrUWFXd0FPbzdLbDJLZTFLMUFoMnFVY1F0NFpOVUN1UXAtVmk2MHVpZmlPaVh0MjdFeE5QamhQaG1FVnJITkdCNVphMFhtQlpLcjlwVklHWmlmVGk5Q2o?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Understanding the Complexities in Managing Risk for Artificial Intelligence: The Challenges for Senior Management - Hubbis</t>
+          <t>FDA and Fabian Society launch new AI report - The FDA Trade Union</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 03:35:44 GMT</t>
+          <t>Tue, 24 Mar 2026 16:55:59 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOOEZKQzlXdUxSWTJwRl9oRUFGc0ZmZk9GY3VtXzFMOS16bm1OdGFGbzhIRU9PRGxQSnVtZXhPOWFpekhvUlJ3aEw2anVKQ2JaTE9LTmREYjhnRmR3YXhETmQ2SEU2TmJFU0N1VUZQZlJ3S18xcFN6aEo1S0dqVzY4TUhvQUV6d0lQbHpGd0hYUFEtNW9sX0VXeUtoWlVfckFnREJiNnZOYUhlUDNPTlBpQ3BYRHE1b2RtRFAyUlVWeHY4Q2x2aC1EbzIxRUh3ZXFidkF2ODhrUjhQQXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5UNUpMUjdabFJ6VEZ5OU1IMFVORmZVaFJtR2VFYi1RMDhDdG5IZ2lNenZSd0FlbW1hMk55ZnBXRTlNWFFBdW5OSkx1bzR0bUxSLWlKdHNwSjU?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hefring and Ecomar integrate monitoring technology with electric propulsion - Smart Maritime Network</t>
+          <t>Savanta introduces Virtual Personas for AI-powered consumer research in seconds - PR Newswire UK</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 07:42:43 GMT</t>
+          <t>Wed, 25 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQRHJ4SXNvSVhWYnJJckRoMnBHNE5XeE5ZNVJhY0dNQ0ZoYXc0WnA1S0VHa1ItN3NlcVlJMzRvc2Itb0I0UEJBSFVxejVtZkcxNzc3TFIyQ0dNeGszVzBGdnBMaDVQQVpvWk4zVE5tOC0tcjRycDhickc5WXQ5YmdxdWFIaUlRNXdmSjg1VnROaFo5a1RKWk50dm1QZUN0S2RvQk5kVGVVR2dmenFpWWpNdDJSYmZJbVdmS0dKNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQbjAyWlF0UUUtVlZrWFdtSm10MFh1NUUyMjJPQVBmNzBMdFpwUFVRZlc4Y3VrY1BuS0l1UXhOeVA1WllaWDExdUhEXzg4cHh6SVdjMWlrX3BzNUVNWmg2S2RtdFphNm5yY0d1SG8ta3FWeUhjUkhtT3hZcmJqQUtTS0RxYi1uUExkUVNyQzhLZkJHa3BjR25tWjdaMnRiR0E0dTl6RzdpVnFjOFdfZGp0bHJ0RVJRT25CN3JrZU1Xc0x0elBXcmM5MEQxT050Y3JDR3BB?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Propertymark CEO discusses market resilience, AI and the future of home moving with fellow property guru Phil Spencer - Essex-TV</t>
+          <t>AI roll‑out is outpacing risk controls, Gallagher warns - Insurance Business</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 18:09:01 GMT</t>
+          <t>Wed, 25 Mar 2026 08:59:58 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNV1dLSXBrS0dXdzNsSmF5c2xKZjFRUkNTOU5NMFBHQ2Q5UGxpTjBTOGFZWTlveFdsaEJhZXN6Qk1ycnR4ZlB5SldHNnhiNFBPNlR0VFdoaFVPTHBMRTB0ZjA1c2VQM0FxMG1qVUlnY1lpc0Z0QW1lY0VwUkd1RnE1NkU2M044d3BsTE1rbWdwNGdOUXpiZGZJYnI3QkhCYzB5Sk1MSnJIMlFxREtoSU9zcGNZVWVxYjlHMTd5UzhQaGY3Q19hMGk5elphN3lTbzJNXzMxRHVzWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZVpKRHVqR2tUaGJWemhXQXB6V214bkp0OGpuM3lER2RrUGhHcjFOc0NiT1BBenZzOTMwRUl2dk5zS2RJVFBjaERrY19PSnBOYjJVeWVqSG9kWXhWT0JiWnowMlpRR2plV0FubDhnSG9oUm9oTXB4Mm5FckRXdU1jMEFsRTQwZG5OUWxIWk5RbExpY1Fzczg3Y1dycnlnaXltYTQxbzM5b3NaOWpsay01bXJzOXlHYlE?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Vera CPU by NVIDIA accelerates large-scale AI workloads - Digital Watch Observatory</t>
+          <t>Civil servants should be more involved in shaping AI adoption, report says - Civil Service World</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 07:26:00 GMT</t>
+          <t>Tue, 24 Mar 2026 18:17:00 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1tMnZxaHI3N1k0bElEN2JyT2hfOGJuV0djLU1IakNkY1lIdzBCdG9fS3h6cG9XenNId2FJV2hkNUkyTF85aEF6YzFNQWQzM1VnNVRwQ0FabERsbXYxSVBvLXdmTGptTVowZVpQS2x1ZDNRMnBx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPYkMza0pMVFB2WGVQRlAtc1A4YlJ3MjZtOXRxWEh4WmFpUmRuLW82R2VDSTBMNU5KNTdhNmRINzN4Z0lmYmplM0JjUzdQcUVqN0dldEdqSTZBbmpXcVEzdV93dm9mRHNTbjRsQWF6N1JTTkR3WlpPUncwMk45aDJkN3p0SHFjUGk1OEZScE1tQlUyc2dMX3hvTzRPZG01RHREYk1YTnRWRGlNTzkwZVNhcXVabk44ckRya1NGZnJzTG1pS1hI?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>[Interview] Growth Through HVAC: Samsung Leads the Market With AI and Hyperconnected Solutions - samsung.com</t>
+          <t>Xledger’s finance cloud has a tenant-focused lining - Housing Digital</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 02:02:38 GMT</t>
+          <t>Wed, 25 Mar 2026 09:30:00 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOOUdxRmxleFp0ZXBvUjV5ZnpCYmxRY1B1LXVJWnFwWlpPOWFzMzdOczJRWGQ1ejd6R2ZsZmVmVmpkdXRzRmRTeWFyR29CLXVZSWtVZWdxdWk1UE05cTVud0lLc3Jtc29DZWc0RkVnZnVUQUlDREdzNHkxbjIteUw0QWxWYnRIY00zQTFZOExnLUd4SHBkb1VGY2tPZ0E1Z1lXNERHckJLNHhxU1FsZUE4R04xWEYzZnBmQ2Jz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQY1MxZUQyWjgxU3NqWUVHX0dFb3FVVHNCTWx2VEtHUnJFZFhhcXowdkFHMWdQYkMzaWhwOTQ5bW9qRjFOaV8tNFNnUzhvR3d1RFVzamVJc3V1Y2tMR3Iyak5hSE5xSUdKcG9iX0pZYUcxNEYybW1nZkhKb0gtdFRzY1RPblN1MU0?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Debt investors offloading exposure to software companies is latest sign of pain - Reuters</t>
+          <t>From discovery to decisions: data, AI and the future of mining - BHP</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 14:42:07 GMT</t>
+          <t>Tue, 24 Mar 2026 23:09:53 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQeHV5SWNHd2hFUHd2NDlVZzZrUTlCZ3BuTGUwUFFXaGhfcGo2QmtFbXlWQ3djaGl5UkZOOThpNkJfWldMVTZHWldrTG9CR05HTEJWQW5YOHpyOWl1V29lQkpWWm1JTmFzX24ta1p5enBmMG9EQ2VTdlZWMVM5RW1SUF9PbVdBc1RfV2VoNVBDc25qZUlmUm1BUm1sbFhIaEhPVk1Eakx2Uy1YSndqOW52anp4dFVWaFFDZGlrSDlyaVNQVVo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPWWdRYlh5SHhoMU1idWFyVUxYMGlKcmpNNzNIeWFNT0FraFJTQXdKOVVMT2czY25iSGlWa3FnZmREaFh4ZmFwTWNYZ2JjUHNsMUIzUVRNTWVLNUoxcF9KUzNMOXZnc0xWS3QzRUtLT0hUcEZIV3dkWklUM0ZtVjJadEJSN1ozSGt5SkJuNVVpOTU3RmdDMEw5dVlrY0lHOTlFWEVLUXlaRFJsZw?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>EU delays tech sovereignty package with AI and Chips Act 2 - Digital Watch Observatory</t>
+          <t>Students "must be proficient in emerging digital tools" including AI, says HEAD Genève's Javier Fernández Contreras - Dezeen</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 12:27:57 GMT</t>
+          <t>Wed, 25 Mar 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1RbzRGTGRJZ1JyRlRrdTliLWlRVEFHZGdvOEhrRENJVGN2QnlXWDh6S1dFb0pobkFQVFBKcjRvX2VpQnZVeGtrc2ZBbXF5NW5YR3h6ZF9YYzRMU25fUy1SUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNUE9ELThaaVVORi1jZmh0Y1RTeVgwNC1sNUNOQWJHOGxDOHozaHFyTmRWU1huRnUxSHJZUy1xZFFvN1ZfcnRkTVFmNEZJTnVpMDVLbHk4eXpaQWpnUS1HMjNEMDV5ZG44aEJqOGN0WEZ1ZmFWQ3dLRjg2d01fZmw0NFpPdEE4OWZvVnRBQVpsd0RPMXpFbjNTcVV4cW1STVJIMWtUTGpmVEdoT25I?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Microsoft considers legal action over $50 billion Amazon-OpenAI cloud deal, FT reports - Reuters</t>
+          <t>Arm shares rise as it forecasts revenue boost from in-house AI chip - Financial Times</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 05:07:00 GMT</t>
+          <t>Tue, 24 Mar 2026 17:00:06 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNVFQ4bDFHenlqSFctZWJoMVFBeG54NGlPeXdpNkNGbHVfLXRiLV9VQ0RjMWozRTZWbDBwemoxN0FoUEtJdVF6WkZidDlZQlc5c05Ba09RN2o2U2taejRSMk9NcGc5enVkZGpZU2cyalBrRjJNMTdmSVpRdF96dXRjTkxLbDhHOFFpalVoYUp0LWJtdGE1bnhvcUhQa2g3TVdFWVlRam8zcE5aNS1MTy1vbUhRV1pXQzlDcWFLLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOMmdmcXNZTXlXdmJJRWlhLWNCbUZNU2xjVmlkUzNaZXNnMUg1WXF0UkFnT093TF9iRkNDd3JVdlN2ajJCQlczMWhJYUw2cWxwXzJ6dUh1ZTd5V1dtaEZCSDJNeExnUzgtNGZrWHNsT0VXWGxMcGhTbEZKZXVMZ1djTDJaSUw?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kering Taps Former Auto Exec as Chief Digital, AI and IT Officer - WWD</t>
+          <t>Agentic AI will Split the IT Market into Winners and Losers - The Independent</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 17:33:34 GMT</t>
+          <t>Wed, 25 Mar 2026 09:30:00 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOelVFMVR3QXdKTW83LV94MVhuQ0lPR2ZiNnZtVWFmdElSSEptd2Z5OWR4QzBmcC01Vm5ENFdYSl9xcGtQRll1V2FUbDY4Wkp4YWRFdXV5R1hremdDUWFYX2NLT1dBbjVHeHl2bGs5YTlvMVJSZ0hxck5EdjREVUNUaXJtVE9hUHkwQlg1c3Vsbkc0eXJ2eUNmcGZPNGxkRG1VS1NxUnY4bXhJUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNYVJCS0RNTkY2NUFSb3VQV3BlMmNoaER5QnpNc0VfWDNSMU9PY1ExMjU2aGdyRTJZaTVOWnlFRUtqcHlEZjJmd1JtRWZ6T1VDVkZsRUpiNUJNTzdqb0VuZGtzYWRJQlZMeEhWVTEwSEQ4QWd6bHROR1c4YXRZTkVTaG04YnFvMDlFbG1PNFF5T3NwbTVYNU1YNTluS1NSdzdwd0xPeW5ELVpDbEJqbGQxd282TDRhTElLdklpZlNmSlZrMGxzX1UtLTBTdVo1MkFJYjV3RXVHeEI?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tim Cook talks Apple's 50th anniversary, future of AI and privacy - Good Morning America</t>
+          <t>Saviynt launches AI agent identity security platform - IT Brief UK</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 13:58:41 GMT</t>
+          <t>Tue, 24 Mar 2026 21:49:00 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOXzhGYjlENkhCbFZ5ZE12aFJCRWtUb2g1TnZ3VW1Yd0FidjVsbGQ4Z2FKaGJoMnFjWDRjNEtrX3VOVTEtMW9salNHdWZGWHNYWlJlYjE2V1BaSUxGUW5lTDVHRGdWLWUtajNxS2YxbzJyYk1wbnJmRTUwbnpzUHhta3hhSWdBQ3c0VHZoMXo2aWE0a0t0SmJDT2FOXy1udE9pTnU0bVJGU1RmUmfSAbABQVVfeXFMUEFqdmwtWjFUdGRicUMtRHA1WEtnZzRBdG13c3Z4SmNQQWpac29oRnRIUXU2RktfdEVkM1hxU0VBSk5xYk5nUFZtYy1tX09ocDIzaGNINXVxelNiazh0WVprc3l1MDB6a3dvSlo2Q1hVR2cwU1NJcHN2MGlLaDltaV9RbVlncU0yNDI5cVJ6NzR4NkZhS0lWU1AyY28tc1c5bk1yREktUmgxQm52NXlqTlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxObzZ4SjVoWGN0NTZob1duYk92SFlLSGxvM19meEx5OXFDZUUyRDJtRUtlQzhvcVJISlhQTWZfYXlDaWYtZ01KTjljWE5qWXA2eWdrUUFLLWR5bWptb2p3bDFmenYxTXQ1TmRkUE9jdnVfaEpyOEFmTTZYb3R1M1NIb3VUWnY2Mnc?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Elevate Quantum And Partners Launch Nation’s First Quantum Open Architecture System in Record Time - The Quantum Insider</t>
+          <t>The Intersection of Technology and Psycho-Oncology Care - CancerNetwork</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 07:08:23 GMT</t>
+          <t>Tue, 24 Mar 2026 20:13:35 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNVFJ4OC1aVXp2RVNKLWFoOEdINzdzcnlSODlPNWozb053NkJCR0I3YXZhdHBoRzZfeEdwd0J2T19ndS1BSHNxR1N4aXZISVp4eldfU1lsZFhSalFwcmROQm1ONUlNVWFsVEh2dUdPZTlJTnhHTzYxMFItTGFXYWN1LWVqTm5ZX0JQNm93b2lLRVl2UGZZMUZLNF8zN1NXNFYyZ1dxOVV4Q1AyamZxU1RDYVhQYk9SdFF6WmJCZUtmTDl4bXZoNW9lblNoSFZTVDNHRnBDMDJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNeXM4NjF4UkFlR3J0R2J4Q1A5X2VCSWNkMVZjRzVKVlVQQlF5eFM5bnBzYzBjUTM1dGlxSzFzQkd6STByZ3B0bXBqbndod1ZHc1R3RFhTcUkwa3IzRzJORmUxVjVqeEVoWDBRdmxzdjltakF5YkJCSkpWNC1FaXBjbVotbmNyM3dUb2h4N1NVMHVvYTBs?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4051,27 +4051,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Three men convicted following robbery of mobile phones in Sittingbourne - Kent Police</t>
+          <t>Decoding the hardware-software performance dispersion - LSEG</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 14:15:00 GMT</t>
+          <t>Tue, 24 Mar 2026 06:31:38 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNUEFQNjhaYW03S3hqNF85MTRPWlJteEdaTmxmOG1fRDY5Z2FBZFF1bjFfS2ZuVGxzaDhsRnlwNlh0SGdWclE2RURHWjZCRDQ1QlpQOWxOTVdaZ2ZlMWxSekFRV3h2SEFGWHQySTRZZWhhTDVRa3ZCWHVsZEd2NnhxMXNyT1lQZ0M1NUJKcGJLLUI2NE5UeUphRDV1QXJ6MzFrSUZkeXRVUlpNX0VMdkVnakZDTFBIcHZ2N2M3QXl0UXpwWk0wSkRBYVh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYWp3MUEtMFFlejhzSEZiTXo2Wkc1TWhERVpDcWEtQV80YVhOQ1FkYVYtbWdfdnhoaV9DTk80YlVDUnFKdlZsVlU5OXpTTFNCNzFndlBJTDZnWVhNOTBhQ0IxQ1RxNTliRk9IeHdxWFUxb1BUUWJfTjUwTTV0UVUtTkZsNzNiMWdkd3BZaXBicjkyMnRabUdRZ01mOGZIMTRn?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -4081,27 +4081,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>'I was pursued for fraud for having two council jobs at once' - BBC</t>
+          <t>Deregulating artificial intelligence will not boost EU tech markets - Bruegel</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 05:55:27 GMT</t>
+          <t>Tue, 24 Mar 2026 12:59:05 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9uN2tBVGJ5b2YxakV5SVo1aDhHQld6eXhPd0xWUmNBTU10Q09ydFNTSGllc2lvaTZZMWY1UW5KTEJwV2FqZGF0NWJVZ3h1OVpsaG5WdkdvZld0NFVV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQS29KVk9KWXFUeERBckRWbU9hTU1jY28zTGZib01ydkxRTlpCRzFwbG5ZS3c3aHJEN2ZmdXBvZkpnTm1MXzJwZGFsWWtpR291MFNiV29xaXRmRFFDZTRyTnVUd1NDN3p2S1NtWU9jdUxXNnNhYnF3eW1CcXR6VHVRcVlPU1ZPYXdOY2VVZElwMUdQcDRwcERVcV93LWpqQmozRkNDeWlydw?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4111,27 +4111,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Man jailed for shoplifting and abusing staff in Aldershot | News - Greatest Hits Radio (Surrey &amp; East Hampshire) - Rayo</t>
+          <t>Shy Girl and the ‘uncertain new era’ of AI books - The Week</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 12:53:33 GMT</t>
+          <t>Tue, 24 Mar 2026 23:15:01 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNWWh1YVNDUW1NVmVaZThxdDBjbE93cUFNUzREQWdhU2xMSGRXd0NHWURDVEtpZ0N5TXZpU0ljOGprN2VuUExscG9mdGNrN1pKclo5WDNXWUVyUGdIYlFwSnQzY1Jzc2pBWGYwRmp4RGRsSVRFSUdTNXE3b0pBZFNlOV9ta3RuLU1rekhxVmJPRFFidFRNM0tQSktfQzBUR2toOFNsZ1dJNWdSdm45VGpDX0g2dmNSdEVWcGVEM2s3ZEpaZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBUYmVPV3NSZnh3Mml1YlRidjlONDhWSnp1TG8tRF9LelR5RUZjOEdkZFVXeDVIb2RBVmlzMG5lcENMd3c1MEEtck9hVlRuUnNpWHR4LU1IaC13aGxCVW1yZjBqUUlQdTVVQlBiallUT212bHc?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -4141,27 +4141,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Congleton man sentenced for theft after repeatedly stealing from the same store - Cheshire's Silk 106.9</t>
+          <t>Government backtracks on AI and copyright after outcry from major artists - BBC</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 22:35:13 GMT</t>
+          <t>Wed, 18 Mar 2026 13:24:39 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNdFFUY0k4WUlzVkpQXzFVU1B5aUVNV0pjODZmMlNSSzU4b1JzN1RDWjBQM0FnXy13SzloSjNBN1FHWGk5WV94NDBEVWVpNk5UUGNTNlFqdTF0MUpkZnZmODliem1BUHB2b1lWM1I1elNXQWFNc3VaRTNVQzl1d3RNVm0wUUdoSzJVdjFTNmNxYlRIT1dpOVo0S2RfbVF4MWtkaDlQMG5oeHlLNFFSR2ZBZXVVSHJaUlVIdm0xdld3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE51QnlXcmxnakpyTTZjU19DUFZReDcyOVJpUkNZczU4OTlqcWdrall0RjdxeEZ5bmV5eXZYeUxyekFPdW0xa2xFTm1xMGFrajdkbXJ1SDhPYngyTlFh?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -4171,27 +4171,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>A former Royal Albert Hall worker is convicted of stealing audio equipment worth more than 40.000 pounds - Digital AV Magazine</t>
+          <t>CIQ &amp; AMD unveil tuned Rocky Linux for AI clusters - IT Brief UK</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 11:18:31 GMT</t>
+          <t>Tue, 24 Mar 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOUHdkMnJSNDZqQW8xRm5Ha2hmeVFuN3RvZ1pwczBoUjlTZDNfY0Z6R3cxNHNuMlRUeVRxQzBlLXVuNWdXQVkxa29zWldpblBFN0t2SDhkVjg3TXRIRWxKZDdOSkpUUl8xMWQyek8yY3JESk05bzU5M0hOTzdwYVpGRl9iQ1E0Tml5VFJrVDZjTTBwNTBKTWNFMUNDSWRsTzY4STdhRmJoa25vSTNHTW9r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQVTUxeGpBTnBMcERTTjFpbmgtNExxMmVTaUtXS25VTjNpbExKdktHemNGdDY3MFRCWmY4MjNZVkNaQ1lpMVlKMkFhX1FfNmJkbzMyVUJYQm1JVUlBYVZHZlF0R0dOMXZrdTYxVlJsR2t6WG5pc3FfcDBXTWRVdVNmMm9R?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4201,27 +4201,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>'Prolific' shoplifter who assaulted worker at Co-op in Reading jailed - Reading Chronicle</t>
+          <t>AMD and Hammer Distribution Target UK’s AI “Power Wall” with New CPU-First Infrastructure Strategy - Pressat.co.uk</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 16:36:52 GMT</t>
+          <t>Wed, 25 Mar 2026 00:02:18 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxONXZ1djUxdTliQ1RPM0hYeFhTTHRFR2dtNFVCbE9ackgwSUlzd0EwdmtMQmwxTXVNanNaVkMtMF9vNDRhOXNjZGVIUlFHS3hzWDc1czJST1EtX2hqOS1haFZSMGUzeU5XUFdQNk9rSlo2b0thQVpUNThWZXhoM1pQT2liaW1HSzVKeWFSUWNWbGdiUDZWVUxVNVZxWGpKdm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQcWhVN3k2V25QN2loU1FQZ2ttWDZnY014SElidFI4UzlYNUdGUWQtaTlQb1N6bDNxM3hGM25mNDNQZTVCSUozNzJkV2lZUVZUZHpIOVJELUxHTmlMR2ZaNm1wUS03X1VkdDBSd0FlXzlJRW9HcmZqZ21DU0c5SnB2VW9NcTlfZjJZaGVsaUxWS1hDam9kUGR6NTRKLVVRYm02bDdsYjIzUkJqVDVRTFRyM3NMVkVXejZvWDRQVzhHVFdyeVl1RWNCdVNheUFjUGVRSEJNWE5CRTlWWGlUakw1YWs4Sldybl9KcFBWMUZLdUlTQQ?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -4231,27 +4231,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hunt for two convicted Londoners after over £50,000 worth of phones stolen from shop - Yahoo News UK</t>
+          <t>Divide between Silicon Valley and ordinary people grows ever larger | Technology - The Guardian</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 14:44:23 GMT</t>
+          <t>Tue, 24 Mar 2026 14:06:00 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE40Sk1hTGlTQTZDTUQtcDhncVpKVWl2Z0RQWVE4Qm1EbGswUW9UMnFRR0NvaE9RSGpxS3FTVENVaGhIQ2R0UGc4R05WZTNURnUyWTVRSEFFMjduS2hJeUZEelp0S183bk4tN29waFNBeTJSU0xuaUcyS2ZWSHNNeVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPczYwOFlZNXo3Z1VCYnRFd3QzVVlKcF9oQS1BWFlHRHFPZGpfZ0pYSkN1U1NydHo4Yi0tNFU1UFY2akxaajdhWmdveHFBV29zWDFPaDlKQWh6UW81R3hpU2JPaFl0dWw1T0QyMjRWS2g5VVVZS3Z6VmppeVJTQUxuWjdqYw?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4261,27 +4261,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Logistics Employee Sentenced for Stealing 120 Million Won in Electronics - 조선일보</t>
+          <t>Maximizing ROI in the AI Era: Mainframe Value and TCO explained - IBM Newsroom</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sun, 15 Mar 2026 06:36:59 GMT</t>
+          <t>Tue, 24 Mar 2026 19:55:55 GMT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQTks4Znd0TE5tX0JBcnNJbmVTYjY2NG01UVhma29KT09VTFJXNWZvNm4tUzlzMmRJUkxrQ21BbFZQLUx0YnpvVTNsWGJIUmlUNXljNDRkRnVIel84V1UtWjFRbUFvVXRjc3RWWm1jcVN6XzJlN3h6Sm5JU1gtSmpRNTd0RWFiYmxh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxONTh4dHUwdDFrZXNLQzJFQXo5ZThodUZPc3dWbTZRZXJ6VXZubDJJaWx2YTBWR0xlcDZ6WExhUnJ2engxWnFyVlB3QWp1ZDZOSVRjUG1wYnFITXBkbWdiLUlHTmotWU5vX0FmWTZxWHU3RGFEWHZ6d0EteU9oY3dDeGdIWHBQQjV1WWx2QV80Z2JacG9rLXlV?oc=5</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -4291,27 +4291,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Couple who stole disabled NC Chick-fil-A worker’s phone sentenced after his death - Charlotte Observer</t>
+          <t>AI is reading and repurposing NHS info and that’s a problem - Health Service Journal</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 21:43:00 GMT</t>
+          <t>Tue, 24 Mar 2026 12:35:47 GMT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE0wOG90Q2tFdTdRYXhnaFFRZE56Qy1GcTZzeEYzVlVnRkNUM0x1OTZXM1djSTExWTFhdU9LQ3A0dzg5Qm15TUxXcXg1dnZaZHdtZVRYN1Jycy14OTBldE5uNXBYdUUxOTI3WGZMSElad3ZlR0hmRHlDR2luelDSAXxBVV95cUxPWkk0NjcxaEZGbl9ob0pOT2lyWmNheTVCQ3NTZ0FTd3ZzdTYyZEJRZGk0anRpSDVvVjk1c2ptY1YzUXBZTF9tSmdVcWY3dm9rNVplQjQya3cxaHVDWE9CYjlndk5tNWkydHBnWVVfODZLaUNDTlhhblFxcDFz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQa2hBeC1WbkppdkxwMFBZTFhkelZtOTVFeHd0TFdEUzAwZm9ZVHpMSGFjZ0MwdVpkVzlNVE92TzdXaDdTR204eXFlaTlvOXZFSXEtNUNfbVprOEtBLWJiZzlGZWNVWnNCQlRuN2dNVzAycDU0Vnl3c01kek8welFNUDBRdWRNWXZTUmNrQWtqbGJQLVN1SWRCcVVYNGFzTk5rYy1uaFZ5djNhNVN3VXdNWGQ4TmdCVnY2NlU1Q05CNA?oc=5</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4321,27 +4321,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Stellenbosch law firm employee gets seven years for R13 million fraud - IOL</t>
+          <t>AI fundraising agent smashes targets for London Marathon runner - Third Sector</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Sun, 15 Mar 2026 15:27:29 GMT</t>
+          <t>Tue, 24 Mar 2026 17:00:15 GMT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNRHE4R2pGdmpjM2dKUDlpSjZHLTdDdUZ2Z0NKdjl1RTBfVHNfVHRadE03ZzQ4akxYNDRPdEJhOVBwZldwR2NWNzBnNzljVWU4cmg5M1lpb19vR1hDRTc5SGVfMEs5VVh5QmxHXzNJZEZsRnJWOEFOb1VLbDB2amQyZFVqZmlUQVg3ZkIzeWxjSEhrYnk0Yk4zc1Jla3pSaFRsekRab2YyUjJhREl1Q0xGNGFYT2V6dzBfRFVvRHRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPc2ExY2JTdDlFVjhHZVdTQjNzWEtMSk81cm8za200TUpJNjJxRG1TRlA2eEVvSGgtVDc4dm1zS01xMEU3azh4cXhmams1M05yRTFGVFBwZ0Fta2lYSUF3dm9hbVpQME1mQjBmRElfY2VfdURDSXRFalhLQzk2NHhNNWFReGhwQm5iZHNFX1Y1Y2tUYk5aNmxWTHhZVTJoOHRlMjgwbVlZSURsNUhDcVFGV3RvSGlYMm1R?oc=5</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4351,27 +4351,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Dental employee gets 4 years in prison - DrBicuspid.com</t>
+          <t>Foundations for Achieving Trustworthy AI Outlined in New Research - Homeland Security Today</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 06:05:30 GMT</t>
+          <t>Wed, 25 Mar 2026 08:25:48 GMT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdnF4MzV2ODNETWEwcV9vZjFrUURnM1Y0Yy00LUJQVmdWQnZOU001b0Y4eDV1ZWwzYnN4ZFBpWTVQelJncldlZDlKOFdfVmEyZ1ZMdlQ3cDdiU2ZlMlFua3Rsai1VR0NSQ3BDLWRkV1FLV2RMUlU2T01YbGdyNTZBNmVkR2ZhOHE1OTZCUUQxbDVuSmZhRFl1VVU2eFJ4VUNhY0dWdkRjV3lPWGNFSnYtYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQTDlReGtFYVc2MTB4MFRydHdqV3VLWDdDMmdxQ3ZnbDNrM1JRU3VLQ1MxUEdKRldiSXg3UXBLc0ZrQmlVNlJ2V0VQcGJYelJzN2d6cUV3MlRKcVZ5UVlqVE5SNGtRdWREckdGVmc4QnhiVU5IUDV5MHBIdEVZcVZ3NXdlajJKYmlZdWlGeDF6NEJrVlBZblJZb3VrTlEtRlRrd0hKVy1JN3ZjQTZCckNhbEtkam1xQjZIRzRoVE84M2pMQQ?oc=5</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4381,27 +4381,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Elkins doctor sentenced for nearly $2.5M in tax fraud stolen from employee payroll - WDTV 5</t>
+          <t>Have too much money and not enough taste? Step this way… - Car Magazine</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 18:02:00 GMT</t>
+          <t>Tue, 24 Mar 2026 13:35:04 GMT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQcW9SbHpqc1RHbnZqbXhzUWtYcmxKQkJEX2hPYURqa0hKajFnc1hxUElsNXA3N2VWZm41UXVYNzl0RzU4VmRpbGVTa29MTmlock13UEdWZ3FXRDBtVXRZUXhmQlB4ZVhpYlVZa0duRTZqLUg5TGRRMXZfVDVqZ2s5OF9WTdIBlwFBVV95cUxNVEJsaF8ydDFlYS1TR250TGt2QV9scVNDaG5tazRnVjg1bndWUE5OSElLQ2RfMU1IelpBV3FTQW5KU2ZpUHg2M2twSE1ITVVoRjRET3EzMjQ2dzhtWm5xZUFsbkRvQXFKRGEtTVpNNzNVNUU4ODVsOUF6bmQ1UGVMSUotVXFZQno5T2pLMHRXMmFwalBxTnNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd2VSbGxBWkRYbl80Sk1BLUV4TTVZdHBqWElfN2c4SkpHSWdIOEk0RHV3XzZqQ3BrTFNidzFiVXc3RF9GLWN1ZFQ0c2pjY3FHR0w4d0xBMmdjejZ1VE44Mno5M1BxczNRUXdaZzRPX1VCOTRTSzJEZTA2Z1JIeC15d2F6c2RuUERZS0ZVYWVWYTBVS3hFYUZVRURJZ1kyMk0?oc=5</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -4411,27 +4411,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Two Indian-origin brothers convicted for healthcare, visa fraud in US - Scroll.in</t>
+          <t>As AI Skills Become the Hardest to Find, ManpowerGroup Launches 2026 VivaTech Startup Challenge: "Human First, Digital Always" - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 07:07:00 GMT</t>
+          <t>Tue, 24 Mar 2026 13:32:00 GMT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNSk5MdkltNHFoNGZ3MFpoU1ZCVnVIYjlIRnNzSXA4QlhvWjZYeGJkSjZMX3BDS0lXRVFvTmZpVXJMY0U1aVY1R3hobk94S1FFSktRcXBsZThDeTRTUkJxQ1I4WnhNaWYzYXM0UTlDeXExUXVFRFIxWEtER0JuMXpRYTZFMTRNem5sREczRXpETlFBeE9QYmcwNlBWWkxHX2hBc2s40gGoAUFVX3lxTE5yYWhIcTRuWURkSjlHejB3aVY2blVJYnRwTDNzbGpIV3prY0dISTE1Y1VaOFVvZkRLN0QtTzVjamJiRFluaXlhdl9IZVl6UU40Y2VaQTNKckdhSnhBUzFmNjNFY2lwRDFDT0Y5MElhelJsaUNSWXlGT0lINDJyaW10SklSbDdRZFVHdFhnOG1mUXpZdGxjazVRNm5SaGlabTl0bkZZTkRzVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQaGxVMVdSb2ZjbnE4NGJLNVZxRzJnRlpTMFM2c21JeEU1Rjl5TEgzUGtzXzlaOTRWSnNlRnJKdHhIaEhQcHg0Q2tDR3F3NWhLSFM4WmttSHdmc0x1Sk9Eb2xudTJ1amg2eTNwalNidzg3aWxFLTNSNFBIcnM0bTNDTWtOVDlVT2FPZmxNc2lua3I?oc=5</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4441,27 +4441,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ex-Home Depot worker from Covington gets prison in $4M gift card scam - AOL.com</t>
+          <t>CNCF Welcomes 21 New Silver Members As Global Demand Surges for Observability, AI, and Secure Cloud Native Infrastructure - PR Newswire</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 22:50:05 GMT</t>
+          <t>Wed, 25 Mar 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE0zeXYwaG5KaC1JcEVjTmVreHdwWWRBS2E1ZXR3Nk1GdF9SUFRSSDIzV1ozY3JaeGVUVWtNcDVpdXpZSVBnMGFNLWxoRXQ1WFMzbHg0XzNubmJoS0VSUS01V3Nyd3hrY29xdE1DdnlKYmJwOTNMbFI4RDNHZWJRSTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNMkdzc0lkYXVDSmhJZHJ0dHNROUx4VUlMMW55TWtfWk5xVmpRSHZFTkI3a3pURXNwa2RxMVZlcElEVGRHSzZQbmNHT3RCUXV6LVVMUEVTX3pDYmc1c2lmdlgxOXAwZWxkLThDbzY2SGhzQTNVa2VqWHVRdGNxNjBmV1N6RFBYWmZ1djN1Ukx5aW5TakdzaTFaSXFUSEJXbDh1amhkSncyaU5pel9lT0MzNkxaVFhpVHFWLVdfbmJna29RVTBxSlNsVWY5SzBtb2dMNnJEakZTQ2lRbHVRYllscVdsUW5DbmIySHFPRnp3SFhjd044aUcwMUZienRBcURlSTZjb05R?oc=5</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4471,27 +4471,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tenant Sentenced to 22 Months in Prison for Stealing $65K From Units at Sandy, OR, Self-Storage Facility - Inside Self-Storage</t>
+          <t>Integrating AI and Clinical Trials to Personalize Early Colorectal Cancer Care – Digestive Cancers Europe - Oncodaily</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 22:34:22 GMT</t>
+          <t>Wed, 25 Mar 2026 01:35:15 GMT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOaWJjQlhnRnY3QkJ5dHNGcnRoamRDZUo4WmVORkpkWll0a1puVlRfWklnTEhsUzBRUVlrSVJkVHZOMWtQMURWUTlhS1otd25pNHlCYmxtekZVcU9wa0EzSWZBQThrSW9BbVpEeVBqNmJNbUkydVNqNEtWanl0SEFBQzE3aDdpdXFsbUZVdFVGYl9Na2Q3bnVFdGFfbEdVQWN1bnRNRkd5cjFxa0xYUFBWY3Z1TmEta05PUlN6aElUbGNvME00Q2sxbzVTMkFOX0tGeXZZWGFfb3RkaWd4TUlMSXFUOVRYNk1jVVJiSDNyWTlQUnRS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE1GYnhzWFpFOF9IY2lTczBFLUF5LWRsa2dJTm5XMXJOVnYyX1RvbXRvWW1rVW5kZnJSbHhfVDJBeXk1cXdoWlhIbG82VQ?oc=5</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4501,27 +4501,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Swoyersville woman sentenced for theft from credit union - Times Leader</t>
+          <t>Breakfast Briefing: AI in the world of work - Capital Law</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 19:31:00 GMT</t>
+          <t>Tue, 24 Mar 2026 11:00:39 GMT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOUHg3bXQxZ3FvT1hOU3pwOFp1SlM2V1N6UG9ITTBkdGFJSXdIZGZtcE9Bb0FyVTJwSEVnYlJWamtVdlpTemsySk82UTFiMl91Rl9sYkJwNzJORElCdzRxSmMzQ3g4dzJ5VWxzS0dWSGp6S2VkTkM0SzdDaUtyb3FLbzdneWFJNWVKYWFNdHdJT3NnQTZ1QXloMTZCMG1MZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNVWFGNUY3Tjh1TWlhMUtfV0dXTDFUNjVLOVpVVC1LOWZFTmtYQmp1Y3R6ZzdvQ2JJWlRGaGJZd2J5OEhaTlhHWndxVjFjcmZYN1J0Zjk2VFFCMlZzM2JKbjR6cFoyYXZWV3BCOU0tb0Rma0taOWFnYUVuaEotMzY1VDBYUVZ1SzdJaG5Mbm03WHhXSFE?oc=5</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -4531,27 +4531,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Local HVAC business's former employee sentenced to 8 years for $600K embezzlement scheme - KEZI</t>
+          <t>AI’s new frontier: When business, government interests collide - The Christian Science Monitor</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 17:54:00 GMT</t>
+          <t>Wed, 25 Mar 2026 09:00:09 GMT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxNaWZXWEV0bmk2ZVp1ejV3WThSRmZmV3NqVy1NeWZtaV9LMFpfOWs4Wlc1R0F4MTNKd0ljNk9qVlJObm5yUjBkVTAyZF9qeUlsUDZFQ2hKMFJ1aGowY3RPbU9VTHJsVlVEbjlneG4wUGoxU1F3TmlYbjhDRFBPaFVSMnlUNnhYQ2h6SWhONEJKUm55SUppRjYtLTdSeVM5Rm56Z3B5aTVYTU5OcVNtVTJHZ21XbzMxN1JLeGxqUGdCMU9QSk5qa2MzUndsRk5Cdy00cmRXMGFtdFppSXVBaUFWWDNoRVZHZWRKWk1lS2pxd3J4RzR3RHlkTEVxUTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOQzVQTk1SQTJFOEd2b2FFRmhCTWVwUEMzM1h6VlVPbmI5VjF5eWFxcXRXekdCSzJjakIxWk1yR2d3TVRMQkVvVnFMZTFaeGhIVVpkd0R1SFYwT2lxUEJGakhnSmlfSTBtYWhzZDBfSDZnY2pfdG9pVUwxRzdPZUhLVW5sZGpmNTZ2d0lxN2ptR25ZLWZucmFBY2FHWQ?oc=5</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>For robbing New Orleans postal worker with gun, man sentenced to 12 years in federal prison - NOLA.com</t>
+          <t>'Ashamed' dad sentenced for handling stolen goods after £337k JLR thefts - Birmingham Live</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 09:00:00 GMT</t>
+          <t>Fri, 20 Mar 2026 05:30:00 GMT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQLW9UdUpoek52MnJJWWVkWURzazVUQ045MzhPcHdrTVBJR0E3X1REVWVXRHotQ2R6M2Jxdk5YcHVFS1lHMUpHWl9JVXZMQm1pam1Eb3hmaTh1ZElJRkJ5VzljZWp1RGliUHI4Z004SEt3MHd0QURGc1VPanpLRkhia08wT0tLY1pVQWhJYmNjOThPcF9xdWtUa3psZnNzeFdDNlhOdDk5bmNoWUZ4cmdveHBSdVZPTWY2N3dmMHJKNkFjcVRxRlVTQTF6Q2gtR1MtZzZISnZqWGptSkVuS05EWXBZM0FHTEoxYTRmZlhDdDBkbjFLMmkzN2Nn0gH_AUFVX3lxTFBoUlFWdW1sRGJEWVVNenNSRWc4TUFSNlloLVR0RFdKY1haNFBsUUNRNWlSa216RkdyS2pTUXpLSVY4R1dzbUR2cFJnN004bWVoZUJCMUxjNElqM2pYVGpYTEpncXRzTUlmeDN2XzdBS2tVMWZ3S2xzY3ptaVBhNGM5TWUyYWhaX2dRVlpGY3BHMlVxbG0tWkprM01DWFdubmR6OHg2clhkWGR1R1BTT3Y0OUVGX2U1ck5wRzVMOVU3OGlPVjF3d1lZaDhGRjlrRERsQjJDTTVFZEVIZ1BlY2JXQmJpV3dJVXJOcENDRnk3LTh6cUs0RnpHeFZlUVlhcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOdkE1N1BVNXc4TWZCdzFYeEFPejJoQmYyTEJnNC1XbndrWjVIVkVzY1NBVVNrWDktd0RLdGZrSnI4Ujl6ZHBSZEMtN3VCZXpSemRnemJtb3ZmZU1qVThIdUFWQ3F1VlctS0tiOTNLX1Fnc2NialIybTQ2MktJX2pMaDVzSjY5MnRQVEdWQkVjM29qWXgyZDlxYWh6UVlmRlHSAaQBQVVfeXFMTjVCbWFUWGJ3QU1VekVxelVIUlAzNGJlNjQ2b2tjdFNkQUJnXzBwY015ajRua2c1bk1CVG5NZ2ktdkV4VU5uMW95U1VTVm5xNXluWHN2TjFSX2huei1iREtGVGtYMFhoVTRESFlEZTE0aUFNYzFOT19ILXFDeW1hYktKT0ZEQzkxbWZyWXFNcDgzZ1ZhUlFvbEozSHhfZFdZTlh5djA?oc=5</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Alabama dentist sentenced after setting fire to his own office in insurance fraud scheme - Yellowhammer News</t>
+          <t>Former BetCity Worker Sentenced in €496k Free Bet Fraud Case - iGamingToday.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 15:30:26 GMT</t>
+          <t>Mon, 23 Mar 2026 14:33:57 GMT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVC1XRU9TNXBMLVR2SUVycHdybUFKaU5ZWFJXdmdpRW9MYVR0SlNFbEZfTDlTZ1hFTmd3dVpaRUJVOHFoZTVJeUs2bnp3TGZqd213SFc5SUxYcmFkRnZObW9JY2JYLVFTQkpYR2Nyb1hYQW1NZW1iRS1SZXE2ZThvdU5jd29nWjlUSG1BXzFkaWoya2FSSmNHTTZBMWNEdGhiMVIwRFE0RXN1Q2E4UFFteDFUemp2Z2RlRmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQNnlId1dpZjVVYkhNWjFrUFZOaVhibnBxU0FPbnFzanpfOGhKV2NnZTFhUHBPZmduaDRrSWUxNHZ2d1J2TGJXNFFTMUhrem5zc0RFMUFkazFGUFZHMks2bEZSLS01UkZPQzJZY2dmZ3JPZnAxUWpZN0JFRnVNNHJVdEVHR2hVUTFDOFFoUl93RW9Wc1Br?oc=5</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Former employee sentenced for stealing cash from defunct credit union - 28/22 News</t>
+          <t>Former Kilmarnock social care worker struck off for fraud and theft convictions - Ayrshire Today</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 22:18:29 GMT</t>
+          <t>Mon, 23 Mar 2026 09:25:14 GMT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQTzlTQlA3eHd5ODFsVWZlYy1DLVQ0MlJLVE8wYVBlc2xVbG5xTkluZG4xNzk1MmJ4WXpaMC1yOHdSR0JRZllFRjN4dlVYZjh3Wk1qTENTNnFJUTRrWVpReXBzRWMxWVlPWHp6SU1kUGFYRUpyaGVJNHVuS29pNnRIeERqOHB2bUIwY0RwVl9wa1M0UEtGRExMbDRLeE50Tlg0NHk0dTBnQS11N1lpUEdTSFZzQW5xbG9r0gG4AUFVX3lxTFBPOVNCUDd4d3k4MWxVZmVjLUMtVDQyUktUTzBhUGVzbFVsbnFOSW5kbjE3OTUyYnhZelowLXI4d1JHQlFmWUVGM3h2VVhmOHdaTWpMQ1M2cUlRNGtZWlF5cHNFYzFZWU9YenpJTWRQYVhFSnJoZUk0dW5Lb2k2dEh4RGo4cHZtQjBjRHBWX3BrUzRQS0ZETExsNEt4TnROWDQ0eTR1MGdBLXU3WWlQR1NIVnNBbnFsb2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPNTEyUlR4bnl3OWxZX2JmaVdOcXVtczR3ckRxc0dWTjlCQ3VaQ1NJakJPcmJEbVFlaGRBT0tVdmY0Wjd1bmpuUFQ5Z2Z0Q1Y5MkxlaWwyVFgtZUFNRGx6bl9MN3Jid1F6clVDSzJrV1VpOWJBSXBpbWh2VW5lbjFBdWdLbTk3OUN1dVpxa082eUhsWTYxeGwweEd0ajlrNjNwV1l3?oc=5</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Employee triggered a major alarm at the Lindt Museum - sentenced - blue News</t>
+          <t>Ex-US Soldier Among 3 Sentenced for DPRK IT Worker Scam - GovInfoSecurity</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:46:00 GMT</t>
+          <t>Mon, 23 Mar 2026 21:26:50 GMT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOX0tFcUhzNS1CVG5XZnNIeXJ3ejZ2b1AxLWowS0lydE14NUV3TzBDd3ZIOElmYTRVUmktWldIOTFDOFd6eFo4ZzlLdlc0SVVsV05yZDlPRWtiUFhnUUhLWWJyWjhsci1NeGY5dTJULTB5b1BLUDNxUnRaanBWTjZOR2ZDX2xzQ0w2ckVQS0VLbkFQY1BqNXhTYTFDUzNwMlQ5c0FTaEFBN0dYWkF1eTBaZzlfVmZEOWxYYnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPSU1jVkNsWVN5amZza0xUc0t1RnQzZTd4MXgtMmdmUHgyLVl0SVNDdTZVTEJxNmNpbzZlMVJ4RUlXbHU3Sml2MTRFbHNqZC1mZE01aFJDaGZYenNEdjdYU2RUWUFuTU9mMmlpaFZpbnJSOUlQTjFWY3NldE9Ld3FjTlN1ZXhsZHphTnBBMU1JNWFDMXFZbHBB?oc=5</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Westchester Construction Boss ‘Convicted Of Scamming Workers Is Re-Arrested For $50,000 In Wage Theft’ - WNY Labor Today</t>
+          <t>Trio sentenced for facilitating North Korean IT worker scheme from their homes - CyberScoop</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 20:23:47 GMT</t>
+          <t>Fri, 20 Mar 2026 18:20:59 GMT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPdE1QUnQzT2R4a3BsVW81aFV3UU55VmpHNThvd2tPeGpYYUZUd0UtUlkzSmIxMFZlQ1VpTElEcmN3SkJYejNQWEFtRDFRdXljOGpVV2VGR3c4MjJyMHdYU29LM1lmbzgzWUxBWEQ1MWVLX09SdlpGOWFpT2thOEExODR5UktVdmNfa0ZKc3JEMzZoLUtXcjRJZk5HbnNqZFVTazdtRndNZWEwYXZocjdrLWJDclNDeFhYLXZqc3Y4WHpVU0hZVll4cC1MR0xsY3Brak5NQXR3UUxhZFplSVVsaFA5XzgwLXcwNFd1ekZuc1U0TmE1WmFfUmJwQXBmajBpanc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE14RHpwLWE4MHdKdmFPQXVKYnhqbG9UaU9DQzY5d1didkg2MUFTdmw4OVJMRTYtX3J5UVJ0TkRBQm40M1B4RTRsU292UXBvcXhzc1BrbkdCZ0JCQXdFWHVCVUpoMW9QcjBlbGl2QmNkd25NaVM3WDBV?oc=5</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CAUGHT ON CAM: MKE woman convicted of battery of officer, retail theft after intense Wauwatosa mall incident - TMJ4 News</t>
+          <t>Amazon delivery provider convicted in $9.4M fraud scheme - FreightWaves</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 00:30:43 GMT</t>
+          <t>Wed, 18 Mar 2026 18:58:44 GMT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOMTNqMno0RVBCTDhqV0pPOE1fMk0yYnFOMGFzek5pekt5Um9zTVE4S1FiYzZQd0F4TDRoLWxBa28wNUpSbU54Mmd2VE5KS1BrRm1BZ2w4WnE2WUkxaEREWlVWTHdhTGtaRjFSQVQ0YkpHcUZTSzV6UFdvdGNwNGFCYjYwTGVmSXVmaUNhcmpwWEZxd1dQMnRRX3Q2WWlhUkVRUmtyd1EwNHB2SVR0WGVYVHRNMk5ST3ZCQk9ZUDN0bFhaRVFxUHJWbVgxYkgtQ0dvTU0zeTRkSWlNTnpaakxPc2Nkaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQSndPMWhmQkMxeGVhR2E3MDBTZmh6TXJWOHlkV1FYczJlbVAxbmF5aU96SFYzRktkZ0M5SVU3azJUOXFQV3ZQdm9JMVpPa0Mta1lGRlE4cTN1cGdtVnJJWnBlYmNLbi1wdzRRS3BnTERtd1NQQWVmQlpCWTN3S0NtYk1Fc3JyRjJLNXlxRzFpYUlJeDg?oc=5</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Maine prison official pleads guilty to spending nearly $2.4M in theft and bribery case - Piscataquis Observer</t>
+          <t>Former bank worker sentenced to 26-month prison term for role in mortgage fraud scheme - Yahoo News Canada</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 20:39:25 GMT</t>
+          <t>Mon, 23 Mar 2026 20:50:11 GMT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQLWljLWdyMDh1d0hUVHFCaFdtSHJwOGN2VXJHZXFWZnBVN2xhMlRUYWExU01WSTZRaTdrV1Ftd3FNU1JtaVFzVW5ZV2FCQkZFS19oNnNrdHMyY3JRUDNWR0RxSm5tLUpjMWs3ZHdSTGhSbHRxUjloNHIwOGFBcURyRGFETzB0cm5uRERzWkJzZ3hIam5paGMwaE1TdmxQVW53ZU1nVW5WOXhDOVppRkQwcWdId3lJUGRxUnBXeFQwNXRCeDdN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1LdUhBaHhCc2hVaHNNd1kwcmpUUzZKblgzYTRGTVBOUFg0by1NSU83SzBlTGxFYlZKV09CRW1JMURvb2lqd0lEOW5POXZRdXBUU1N2R09lWnphcHA2RXZIZ3UxOUlWUTZQcHpRZDBMWUNyWVU4N2FqZTdmQy0?oc=5</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Former sex abuse charity worker sentenced after passing sensitive material to prisoner - Civil Society Media</t>
+          <t>Construction Worker Sentenced to 32 Years for Brutal Murder of Customer in Dartford - Hawkinge Gazette</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 13:24:30 GMT</t>
+          <t>Thu, 19 Mar 2026 22:12:37 GMT</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNUVtamhsS296RWVLMm1nU2ZpQkNRejN3TFZ0dEtGeloydzNPZEJzQkhaNzMxejJFWmRyX2wtUERjQThfNl9ZbzQxaFlwRTNNcTJETlE5NnlMd1gwN045bVlvSWZaRFJqZl9uYkpwOGhoMloxS3RXVUstcldGbk5mWVc4Y3ROcnhjemtzTVR1QjJfR09URWVpcy1jZGoxdDRBb1JRT1RxUG14WjRFUmRPS3poZk8zZy0tekN5VzdyQkRrbHJVWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVUVucGVfQjlDNmI2S05RUUpSZmEtTmZNU2J0ZHlsVmxkSmpZZkxWNXlKVE5kR2ZpR2NONjU4bFN6QVh0Z2U3OXRrMjdzNWFzSlFETlUyWWl6emFYODhuUmtfWVpQN1JsODEzQ0pURUk5ekdFdWZYLWVLM0g2UmdRejNzdWtaTDljdXlKZXdOeFoxOURpNFA0eHBmOHhlMHpMUks5aGdNZmpwTHI0bHRwSEQ1VU40T1V1c3VN0gHAAUFVX3lxTFBoNDg5TC12aVJBRjcxVi1tU3E1OVpwM1hGank3bzlEcUNNX2xlclE2TTdGRFpxaXJsT1lsbU03TzhoSVU3UTdKa3JVanJBV3Z2ckJZTnVIUldZdXVENE1tc2E0LWN6M2FmZEhZLWlMWUg2NWNETmt1YWc2M0Q5WlFxM05wd2RtdWxQeC1FNTRKTm1ETmUzZFdtbmY2QjZySnM3cWhJcEhSNmh0eHJ5QXNsaTdaMzNwN0tTR19BZnlyTQ?oc=5</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DStv pirates sentenced as MultiChoice raids intensify - ITWeb</t>
+          <t>Former Cochrane Walmart employee sentenced to house arrest for $7K theft scheme - CochraneNow</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 12:05:00 GMT</t>
+          <t>Thu, 19 Mar 2026 13:04:52 GMT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSkFkdGtuSkFERVJiNlJZMHY1RnZDYkpPZlN5dUpLemplSGt4cURHLW5PbFBpTEtYc3M2dGVIS1UyajhqQkJwVXBNUVViNmJZNUNHUjJJdDlFZ3RyLXNjSU1MN0pwZ043R09nM244Si14Y1ppX056YUdqc1dTSF9LaUJobDBRTDJOYjRnYzA2b19yakRHVEdhZWNjSWtsbU1sWGpiUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNc3RwSE9SV0NMdFZPZU5tUlBVOEc0X09Dbi1JNVdzSEJ1VV9YZmJmMnczdExQVlZXeTFjZWt5UTZzZlA4UnRHTUJrSjhaTFNXdHJqWXVrWHZUZWdudFo1b0w5YmJ5aHo4T2I4a2hhQ1pUUFlfT0lPOFloWUh4Tk9XR1hEanE4MUllSzhvZ2ZiRzYzcVlFektWT1E0T0E2RUd6MXlXMkdPdw?oc=5</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Petal pharmacy owner pleads guilty to tax fraud involving employee paychecks - WDAM-TV</t>
+          <t>MetLife employee convicted in ¥75 million fraud - tokyoreporter.com</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 15:31:00 GMT</t>
+          <t>Fri, 20 Mar 2026 11:47:28 GMT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPZGZ5V2VWRmxxZXpOQ0xkY0FCMmh5eDU3WU8tQmlUNENEMHlwSTdLemhKTWFvRU11cGUzckt2MVoyVm1HdjgyQm1DbERxVVg2N3ZWX1hZUzc5cXJ2NlJaRzJmQll5c3ZNaFhkQkhoUGRiZWtsYlh0eGEyUk9KTzNkWlp1dEl4UDNReU14VzBLcWI4aDJDUU5zUldyZ0d6czE1QzFEaVJmeVZhUdIBvgFBVV95cUxNWmw2T2NWUXV4REdVYTdBNHZia0lXQmQ1OEpNd0txT1ZtYkhSWkgxVjRDVERUZ1dGcS14MEJleTRwYllCb05Qc2ZnTk9Od3hONDZXSlREUGhDd0xOcm1hUE9PSUtiRWppSjV0R1VfUVM3QS1RV3dla2hQUkFuT05CSFJYYWV2ZWYzVElFbjEtbGN4MGZWdXY1M2lSblZYY214VVloY0dpVE5UVWZnd21qZ0JINk9iMkFCbnJhYnNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQLVVHbUpvaUlISlNpNnIzZDVjNE5zU0NZdkRfYW1YYUpPcXQyLXB3Zmk0aDYtSklkdXIwM05LZzM4Y2tJaWhqVUlyeDNNRkgzUnJfN1lKTUFNT3RiT1JSeWlHUnlRRkthWjNPc2NaMl9tOXVYLXhTOWJJWUxIY05sSDJST0N6RzlmOUlkSVdHTzlpdw?oc=5</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Man sentenced in mail theft case - paxtonmedia.com</t>
+          <t>Former employee pleads guilty to embezzling from Eugene Weekly - The Register-Guard</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 06:00:00 GMT</t>
+          <t>Tue, 24 Mar 2026 23:55:00 GMT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOYmpvRzZTM3EteGJxaGlXcFY4ZkVXSTI5cG5aRTVtcjBoUEJMVFpUcllQN1lKX3ZaSXE0Sk9sYzAwT3BhX09BQUNkbHRxa0RwVFlUZ3JFUU15U0ZSVjNlWXVNNUNaRUVYcnNnWmpKRjBmWW1vb0pFTlpYbDFpU0JMZDdiR2RfWFpZNmxaQVY0a0s5NlJ0WnBCUkJseUJCN3BtdnpIUG5YbVdwelJiSnpURDFLZ3J5TEVNajRGLVU0Y3VRSHRxZGlnYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOQWlwN3RkbVRJU0cyZjRUa050U2l6VDdSUnF6Vk9iRWxWdzZQbXhtNzlVcldwajBCdURVaDVVbkxyaDBtZjNTY3d0M19LbXJYX09VTkpyZm9NOUZ1VUppbFFhTjlGaHp3c203NlFGc2JRUURFUGpfUWZuTVhWc1N1RlBUVHBtZmNFcFA5VG1QaGpwMEZBUGJYTnp2ZDNIVXFxQTlxaWxid2ZWYkhlMklwekdONHFOTW5YSmtWcGNjZ2pkQQ?oc=5</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4901,17 +4901,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Former Hillsborough Township School Employee Sentenced to Probation for Embezzlement and Theft of School Funds - TAPinto</t>
+          <t>Local government employee sentenced for stealing thousands of gallons of diesel for personal farm work - AOL.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 16:50:10 GMT</t>
+          <t>Tue, 24 Mar 2026 07:13:26 GMT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxPMXl5bFliZW5Kczc3b2dIcGpGcHJxYVV3aGo0cjdOWmlDdFFHQnFrQnByTFRtSTA1bWJMeVVMRHFYNVZMc2lDeGpRWVFwSG5jT1NlY1IzTkxiU25oR1NrWFVfdGQxVmUyVGU5Y0Z5WTBJUW9ycFRzRWtnUnJreFpHUG50Z3M3Y2taVV8zWUNtajBES3h4V2pmbllYdXZqb1hVb3JWWXduUzVJV2I2MVA3dW5odGV4aHVxV29qUWZCd2pXbzdsV2xmd21ydDBvck90d0I4WE1jMVBWRHA4Tjg5ZVJ2SHY5ejlRZVJNanRSM0xXV2h5YlZ3dlNZWEdfaU9BblB0UTVYanZuSlhOTktmbVVDSDhzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxObE43c3o2NEF4dkstY1FKbFkwZGM2UUZ6OGJKSm1yX0FCRTQ5YTlxaFNXb0c1eTVRYW44MGZPdnlYTElnYmhaOTJNUTJsckNfcHZQbWM3N0p2ZUhRWlk2Y0pqTldUeVdyVm1LMTVmVkg0RjdWWU1yN2dHU1FRZjV0M2tGd2tKMnJoOUlLRA?oc=5</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Habitual fraud Steve Farzam takes plea deal in latest case of impersonating public safety worker - Santa Monica Daily Press</t>
+          <t>Wheeling attorney sentenced for money laundering and fraud - WV News</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 21:11:48 GMT</t>
+          <t>Mon, 23 Mar 2026 20:25:00 GMT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPR1NpVEpkWlY4Tm9MZU04UXdxc1VsbTlHWkVhRUxGYlRONkFhbVdyLTR1anpHTlZ5bDBQNGJDOEk1ODRoZFBwclNXcU9aeXhtTXppTlM0U2dYT2Ria2g1b0d1bkp4RjlaU0VjeGVYdW1VVkFzUXRxNjRtbVM3NkZ3eU5uNXNYZi0xMmdDS1VGdTdub2gtdE1HTUFwck0tcFdReXRvQ0Vmc3o0V2xpQm1uT0lGc0RhalNPVnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNSmFScnhXdWF1dHFfcW9QWXhSUy1DY2FsOE5GTzh1ZE42VGluRVZqWlJkUXFCbGhkckczaVIxZFNlUmN0b0VKRDVobUZ2TTN1R2RfLThwZzA3Wk5BdFR4QUdiYXFKYkJ1cGh5MHRFUkZRVGNHVjQ1M1hkU2EzOVV3TnZEUWtQRnlPTUZlZUU1dTF4QmVYTXZwMlpxMVE3OWxxSjhTNEVCTHNUNzUya1pQTXZGUG04MmU1NGVoSE13UlgtZy1tVFNWdDRQLVFaTTV0NmM0clJVb2ZzQW8?oc=5</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>A Jamaican national was previously deported after drug, assault convictions. Now it’s passport fraud - Hartford Courant</t>
+          <t>CU Robbery Cold Case Leads to Prison Sentence for Former Employee - Credit Union Times</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 09:47:19 GMT</t>
+          <t>Thu, 19 Mar 2026 00:50:33 GMT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNcEl2U2FVQzFCZjctWnJrZjQ3eXhNVElLekpwZVFidV9tc25lYWkweVBXdy1PUEpTTUI3bjRvRlplRERTT3g4cWpCZUV3YmpNLUIyZWpGekQ5dTBLMkE1WXVlMVVZYVVwclU5TmV6QjRMQmg3RUdPWWJINElhbUIyRnpsd1pSdXZoRTBuMDFxbTY1Q21oeTBtM0ZWYzdkZ284MXk1SlFEdklPR0hLWGh2aWZkck1sYzNIUm56ODltODlVVE1PZENfbUpJeFJZZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdVJvSnViMDFzXzlPYnltT1kya2w0QWFNNlVhMUZ3SkVueFlvdk5McG8waG9ESFJOUGNGSnhsUTRsSGNvY0VLMzRJMlJ1ckQtOFY0RUZLSkFkYm9wTzFnZ0xHWE9pLTFBVktLUHV6ZXJ6d1Y1NElsVy1leXdJS2xveHVmampQVUlkYVdPTGpYbHlidFkzRk16cnpZSVNIWmwzR2pn0gGoAUFVX3lxTFA1YndIeDk3Mnl0eHBzcEQzMUdVZGtaX2d1VXlPUWVZTE44SkhWUm5DeHd3TFBjbE96eVBIMWxxczJlakVQd3dJWHljWktkTUE5dk9TT2dTLXQ1WDI4THdDY3BFY0FZMVp1TjlJV09FY19meE14T2d4clo3WHR0SWtDcld0cU9nNmEtX3hvTXlVeU1xaVM2dGN5RXJodlV0VUJMQWZFMzBsQQ?oc=5</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Baltimore County CEO sentenced to 18 months for stealing $2 million in employee payroll taxes - CBS News</t>
+          <t>Man receives prison sentence for killing wife while on LSD - WDTV 5</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Sun, 15 Mar 2026 03:35:38 GMT</t>
+          <t>Thu, 19 Mar 2026 20:30:00 GMT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOclhIM2ZCQlVrX05ubnk3UHBiSEloT3IybUZ5aTlYYjUtQjBHMk9UUEpuNHh2a1EzWHJrVnVDSnJTQ1oxUW4td05JRF9LcXFZb2ZZR1NRWENkby1ySnVpbU5XRjdWblkyZGpJM3R4dlVXQ24waDhpSU1sSENhVm5OMk9YYm9iVGZFdl9QZHFUT0R3QWVZcDNJSWU5YTZicHlOeDlCZ3d3bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQZ1VoTWZpSFlGSzhFYTAyVndwR1QtWm9xakUyOUNOODVKMjd2WjFRbjFWMWVQcFV3VWwtdUJaSmpqeHhxWTlMSk1EWm1BV2ZZMElDZWc0VlpnMGNMZndGTVNEMTNLVF9nUXlrcTcwSDBXdHlZV1ZsLUVucktlQkpxVXp4aXBXdjhhalJtejJrdnpwVUlHOF9FMXpCSmlpVk9f0gGgAUFVX3lxTFBnVWhNZmlIWUZLOEVhMDJWd3BHVC1ab3FqRTI5Q044NUoyN3ZaMVFuMVYxZVBwVXdVbC11QlpKamp4eHFZOUxKTURabUFXZlkwSUNlZzRWWmcwY0xmd0ZNU0QxM0tUX2dReWtxNzBIMFd0eVlXVmwtRW5yS2VCSnFVenhpcFd2OGFqUm16Mmt2enBVSUc4X0UxekJKaWlWT18?oc=5</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -5021,17 +5021,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Randolph Woman Pleads Guilty To Mail Theft - WRFA-LP 107.9 FM</t>
+          <t>Michigan man sentenced in fake campaign signature fraud scheme - Midland Daily News</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 11:42:02 GMT</t>
+          <t>Wed, 18 Mar 2026 21:08:12 GMT</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFAxU1lBemNMbEVCNG9ZV3RJWHJLY2U3NzROZEYzT3haUzgwQl9fYzFNd3lLcnVWVlpVcFhZQWlYZzExOHJUVlhKUUp4LUFtdk1OWDNhZ1lwNG83VXBLOUxOTG1kZllKMVBuRjVGSG12UEYxTGFG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPeUlLdHRBSVgxdDZlRlVCd2VJTExFeVo4OVpyczRUOXVVY1JCTjZJMVR0OF9tVWhZMXlOZm91ZG1vZFFIRk9BWGtHMkhvdXNBc1Vnb3hPZkRpcFlSN2tuYng3TURpV0lPMHR4RVQ0NXF6WUFXVHBGSEEzZnNLQ29xbHhxT1F3TGVjdmpRUl9RT0JrNEI1NE1nM0VONW9oa25sdU93Sm1R?oc=5</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Former USPS employees plead guilty to stealing mail, fraudulently filing PPP loans, authorities say - 11Alive.com</t>
+          <t>Former Rockhill Women’s Care employee sentenced for fraud - MSN</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 23:56:00 GMT</t>
+          <t>Mon, 23 Mar 2026 16:38:36 GMT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPMnZ4U1Q0Q1ZPY3lWMVp6UFBSRmhIS3dwdzNPSUhfLS1sN2pEQzhOTkRxMU1XcjhXR2YxQlhNeDNyWjNab25uRXFla0RJLVAtSFRZbG1tellCSHUwU2pYVEQ5WHN3bUdvdGUxNV9VdFpDNVBwbDk2Vll3X3NTTmdtY1BQRWIwM2ljN2Y4MTdHaGVVdV9rTEd2OS1JZUx0ZTFjeGxMOHJlUTlScXgtNHVPdlRER1NuUU5GTktKc3J4d2N3aV9GM2FCYXIzc3pxMlRvVmdGYXJ5dWJnYWxuVzBYWmxrTktwejRkMGtqV08za2d5bFloc3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAJBVV95cUxNR0FiVEYwWFViXy1fcVRUa29JbmZBeTdab3FiLUdHYUd6dlVWbHFRRml6ZngxTVFFQ3Zkd2RfYnRTbDZ1cDhhd2JXcDZLamdLN3ozVFdmcmZ5LUUzR2dETFBBbmpFTngtWTJfV0tCNEx1TkhPeFpkWkxzNEpHSElqUkhWTl9ELWpRYzlhVHBaUTdZVzR3S1RpWDZIMHdNOXR5cU5JeGlmSE9VT3hzellCSmdGaVJfcWMwNW9PelQ5TnBTQWcwZVhwZEdEdHg0SjZwZlZBbnlXN2tKalRZUVhFLUxRanh2U0JJRGhpcWx3LUNEQlM2cEhiV3RNTUh4R0lQaGhETVl4LW1rUlVOQU8tYkRSYzN3anZXX1hIRHJ1TFo2R183YVl1U084dWxWZzg2MDNIVlBJbUY0RVBLRFlTdQ?oc=5</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -5081,17 +5081,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Two including ex-bank employee get five-year jail in bank fraud case - lokmattimes.com</t>
+          <t>How employee's theft of more than $33,000 from elite school was exposed - The Advocate | Burnie, TAS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 11:38:04 GMT</t>
+          <t>Mon, 23 Mar 2026 00:07:42 GMT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQUlJNdHB0bTZ2RnVQY3ZEc01FTGVOdElBQUFkdXRiVWRXd3QxZ1VQOWJLamJKUVYzeGVTdE9KcWhJdWFfZGQxSFB3REEzY2JNTWZoYWRTQm9FeWVfdHowOUN0a1pvSlRpejN3ejJpcXQweUNWT2NZczFaOGxZaEhrSkNycWtfTVdYM0Y2eHBaWWZwb3NtWlJwZjJVR0RPaGhFVUpRZlZiR0lMQdIBrwFBVV95cUxPSXJHOUlUa2RuZGNPSFhRZlFJa200ZUVqNlFBZnRqSHlGVmsxbEpMVkFEVnlvQ3ltWGFkYlVnQVF1V1pPdWNKemtaN0xDaFpkYVB4OG05R2p5a2RLcDZ5MUd0aXIxMERjdlFmdTdxZkdMWW10Nnc4ekI1RFVZNjAzS2lvV2RDdm12aFhXSkJGNmdsS1Q4UmFZcllSTUdPWGZlVThaeTgtNW1QYUJaWWVv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxORnVROE9xd1VEaDE0UGFDRXlvTk5kc1VaRURuWXBOZENNOHFRTlNxeFFiaDlqcU5DWTRleXByMnMzT3JJNWIzUWFrMHhmLUlWVDIyTmdMVVdhQm1VSksyaUNKYWtMZnBpNVpCR1dyREZEeXJ0VVhmR0JMeFVaNU5Tc2NodWM4N2NTeTl5dTZ2N0RTRGQ3NE9DT0p1cmZHMUJFWEpPMg?oc=5</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -5111,17 +5111,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>The only Glenn Valley worker charged with identity theft sentenced to one year in prison - Omaha World-Herald</t>
+          <t>Alleged fuel thief driver struck worker who tried to stop him, court hears - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 18:24:22 GMT</t>
+          <t>Tue, 24 Mar 2026 06:54:46 GMT</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOc2k5VjZfZTBCV3dxVlZuUHJKeHJqMGhnNU5jd1VrUUVULWt0UzFCV3UwOHZUMDZKbnR5Y0xBdTJHamFUamhpdllvdHRBZXFaQlRPWlFEZEs1MnA2RlhjWWl5Y21aOEpyUkNrc3ZqOWVZQ1FlUkFJZkRQSFRTQ2xFU0NpTWJBZTZST2psTm84QmZESzZ4aEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUjlDVWM2YUZOaHE5bE9xVnJMQ2IzLXg0cUZyeXdteFZDM3Boa1RKRU9CTWszdlVIRlBtUGQyNm1TNjZRdWRsYUZlWVhhQmVoSlRvdS1BczBmcUFEU3k0ejJORG1sSGZJUmFyVEs0aDI5WC1KazExc3lQWnk3amc0aTk2MVdhNnNPU2VrUTViYWVET3hMX0tjUFNHMGJDRXUyVUE?oc=5</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Fake Name, Fake Paychecks, Fake Drowning Stint, Real Taxpayer Money – Connecticut Man Sentenced To 57 Months On Multi-Decade Fraud Charges - The Maine Wire</t>
+          <t>Photos: New Orleans lawyers convicted in brazen staged-wreck fraud scheme - NOLA.com</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 16:18:24 GMT</t>
+          <t>Fri, 20 Mar 2026 22:46:00 GMT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOX0lQX2p0dTVKRlJOaFNGNi0td3R5RDVjOTdZQ0tKbE5IX2Y3NHRwbFdIcnQxNlBka3FkbG02ZmpSWVd3S3ZpalZrMllMamlva1pseUh4RUwxc2lpdEFMX0ZzdlFkUnlmVDF3eFY0MFY2c0xQOXI4Sy1CM3BsSlJZcGkzTWxQMWxnaHFJa09IMHViNzdYZXoxal9uQy1MOS05b3hrWGJjN0JEbEljMDFrR25YN2g2ZDJLQ3FYVXBiM0g1YlAwVlZYaXQ5eXNpWGJmMlAtend2NTFDU2c2anJScGt6RmU4cGI3YWNwY3ZhbnBBZjIxRUUxTE5nVmF0c1B0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxObjJOOHlDd2hJeC0zYWFqLS10UVZxMVZ5a05qRG5fT1dwY1VpSC0tU1JkXzZlRVNQeW1jdkhudk14NTYxcW0tWEF2T09BM3lkQWVBY2tzYzV5aUlsV3l4WGVVTk83bXBwdGhoWE81RGdja3I5WTVYMXBRWXVyUEhQZ0h5MFBfeG5CS2p2c0JNVDhSMVhJT1BuZEFNUWJGR2s4NTlGaHZCUkI4QWhJMnRDLWpXUnduTWVrWEdFOWNEVTgyWTZCekw1andCZ1p2MW1ESDJMTFlGUzh0WVlPeWdPeWtCbzMtT3JsX3RINUtTbm5pNDZpSjRF?oc=5</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Former Weott Water District Employee Pleads Guilty to Grand Theft; District Operator Says Restitution Falls Far Short - Redheaded Blackbelt</t>
+          <t>Woman pleads guilty to fraud - WV MetroNews</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 07:02:23 GMT</t>
+          <t>Thu, 19 Mar 2026 23:32:49 GMT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOZzdyaFpTNXRQWTlweG9SMFJaUHJFdlo1Y0FBVmd3aC1Sc2lzTGNlX0ticlF2Y1NScjEzdVV3cWZWTkRjQm8tZl9mVHZmNjJ2NklhZzBqM2lOMkpFWHdsclIyWkV6TFFWS2N5N0FJd0pLUU00MV9jdXpmRmNOTjNTSE1MbTZ4VWJfdVNFUFExRHF4dElNSHR5R2VmZU14M1VqbHhoeUQzS09kdGdqdjhVZmtUdWRwSzE3M3lnc2g3LUh0VHFrRDFjZ1BTU2cxNW4xdm9hZTlPMlhlc2oteWdoZWNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1xdW1XckpwNWUzSjI2VlZSdmZnNnE1anJGWTlqOVc3S2lmUzY3LTFXTzM5SWc1blpJMXpYUnQyRzMyREtCQ1M0dE1Qd2VPZExrbkJUNnU0WWlyNUVCb05QMDdxcnhGWnhpQTJac200dW5UQQ?oc=5</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -5201,17 +5201,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Former Steinhoff auditor sentenced to R2 million fine in fraud saga - novanews.co.za</t>
+          <t>Body of missing University of Alabama student found in Spain, reports say - WDTV 5</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 03:10:00 GMT</t>
+          <t>Thu, 19 Mar 2026 19:16:00 GMT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQZWNEWi1nUUVrWlAycHRVRWRqNUFyX0s0RjRZMnVVT0hMZ3lhYVFpN1pjSmExbzJuQk91Q0JpNk1CLU9LTTZaQURhQVdYSm5jVEF6amI4Q2JOQVBndjRSYUluTkt6OGQ3WWpvOHdONTdXWng5eHdkWTJ2akotcG1tTHdVa0VzYVdLcVlyb1cxTlJfSGY3aFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPVERnbVVFS3JoTzRmVzhnbHI0X3dESFJUNXVLU0FtU21CRDFFQ3hJdUNUcWhMUjdJdVhCMkZkcTdLdmNEbXk3NTlZUVB5Q0ZkY3ZhVzNvOExrMmVIWkgwZUV2cTBWVWtjUWFncWtWaUFhYVRBeExjaGNYRTBPc0Y0RzJXNGtpdVV5Z0dCWjRkZXpjeEJxZkFEUjE2ZnNSMDUzai1tVWtvaHhkQ0c0RXBkb9IBsAFBVV95cUxPVERnbVVFS3JoTzRmVzhnbHI0X3dESFJUNXVLU0FtU21CRDFFQ3hJdUNUcWhMUjdJdVhCMkZkcTdLdmNEbXk3NTlZUVB5Q0ZkY3ZhVzNvOExrMmVIWkgwZUV2cTBWVWtjUWFncWtWaUFhYVRBeExjaGNYRTBPc0Y0RzJXNGtpdVV5Z0dCWjRkZXpjeEJxZkFEUjE2ZnNSMDUzai1tVWtvaHhkQ0c0RXBkbw?oc=5</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Seasonal Worker at Old Faithful Sentenced to 12 Months for Assault - Montana Outdoor</t>
+          <t>'I wasn't thinking': thief caught on CCTV during $5200 power tool theft - Central Western Daily</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 14:01:27 GMT</t>
+          <t>Thu, 19 Mar 2026 18:01:39 GMT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOT1gxOVdXZU5zckVuaFlicHoyZWdmeDI0TnhvY3lHVm41dlR2R3ViQUNCSGJjWTJJR1dFeWNWeWV2S2s2aGdtVWJvUVhUM2VqcjR6X0NDaHhrNHhLdGp5OHhtdFNWQnpGSEZlTHJlVWZ3VnVCRnZpS2dkdndTSlBwUjNYdlhwYi1SeUFMQkt6bU5PQnBteE9KRlpoYVJsSEl2V0EzWmxIaFFtdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPdW1zUUtKak9xTU44TWVycjJOUWJYYkVkNWo1QmpCSnlqQ000Zmc0Nl9NWGljR19DUm4zZUNxVGktZE1pT2IxTkNRc3BIZ29Rem54M0Y0VEp0aHlEM015c095N3NUOFpzMWxUMWczVTVPZnlYc01QWGE3U1lnczQxSEwyM2NoNGFVSExuWG5KTWY1LWNmT2c5WTVkM0RnQ3hQ?oc=5</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -5261,17 +5261,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>US$186 000 ghost‑worker fraud at United Refineries - heraldonline.co.zw</t>
+          <t>Legislature sends Ivey public corruption penalties bill - Alabama Daily News</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 21:14:32 GMT</t>
+          <t>Sun, 22 Mar 2026 15:53:07 GMT</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPYjZ1X3EyVXVUWjlaZVc3OHJ3UFVkclBHbXpDaTlNcWlUeVI4bE1hMGJxX3IwWGxKTWp5QU5pY0RmZ0RzcEIwVS1lSHo5VzQ2bG50REszT09jU1d1UnhWMjExVWJwcThRV3dGNmIwanVCWVoyVGo1NXRBWFFWVGc0WE44UUlqdDZW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQRU0tdDhXVUthR3k0MF9yaFRqT0dzWDZ5U3I2M1g3TmFCQ2UyZ1htbUtBMTlhS21JZ1hTT1c3SWstdUFIUWFueFFqOGZNR2l3NHlCZmtJMy12eUVxZjE3QS1YamdISF9YbVE5ZktqV21CNnVldW5LWnJ6SFdleHk5UFRyNVZvZjA?oc=5</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -5281,27 +5281,27 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Investigation Black Forest: EPPO carries out searches on suspicion of customs fraud involving the imports of aluminium from China | European Public Prosecutor’s Office - European Public Prosecutor’s Office</t>
+          <t>Elkins Doctor Sentenced for $2.5 Million Tax Fraud, ₹2.1 Crore Stolen from Employee Payroll - The420.in</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 12:00:00 GMT</t>
+          <t>Thu, 19 Mar 2026 05:20:38 GMT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPMnhnVk1nWFptRF9QaV9ZVHpFMldkMmRXdTVzSWlUUkZyMUYxZlNGWVJabF9kQUljNU0zQ2V5WHgzdlRULWZoZEJjdlZ0LVRIc3RVbm5tbW1CQmtIY1NIT2U1SVp5c0RJTVNwa2psLUxSRWNWdV9NVGJJS3NZdDh6Z2ozaWlFNkd1QzgyQTBadkxkUmZQN2xoYlFWMGtKUWkycUtCU0U1RDBPT3Y5Vm5ia2c0Q1A4bFNXMUdlUVZrdkNScVVLREE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5DMmJLdlVfaFlmNHBnaEh6NXhyVmxnU1MzdlRiSEJlbDlNaVBBNklXb2doR2RMNVN3R3NUUnQzLVhxakNteHdXZmkyN1RDX0NOYXdBTE1Eb2RrbnZ0YXpXRTdWVG5RSFBMSUlVWERTTXFMeHpK?oc=5</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -5311,27 +5311,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Global Fraud Summit keynote speech - GOV.UK</t>
+          <t>Richards Bay woman sentenced to eight years in jail for stealing R500,000 - IOL</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 13:56:51 GMT</t>
+          <t>Tue, 24 Mar 2026 04:15:04 GMT</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9Fd1J1bTBtTG1nb3FHMmxjZlp6OXdwVWVodkZPTU9YT3RBSXhoQzZQcTdZbXROMGQxRGRYRWVTMENzSVhZbmZvbHNwTTdmTlVWeTNvMFI2NFJoWGFMYk5LRlVxTS1jRWJ2bDc4Nm9rbWhJNDBIdGhyTWV2dVpwUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPXy1YRXNTelhLNl9FX28tVXItdXNmX1pTR2dwazEyak91dGhTQUV3XzA0dERQUTRSOVBTTXRRc0VoR21tMDZkOHB2R1Y2S00wVGJISnVwMG5VcWljSG85NlNDTlFldGhOVmtEV0w0ZVQ1cTN5UGhMVU44cXpvU2gtYkZJLVh1RzNXWmN3VjIwWGlXVloxa3Vid3BQaEdtc3JKWGZvcjN5ZzF0QXU3OWcwOUhpcmg0N1FEdHkya3FfdXpjWmU0UkN4Q0tKaHVCYVdB?oc=5</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -5341,27 +5341,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Coherent Solutions Releases Research on AI-driven Fraud Prevention in Banking and Finance and the Best AI Models for Banks - PA Media</t>
+          <t>CT man who stole mail from hundreds of mailboxes sentenced for violating supervised release - Hartford Courant</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 14:17:17 GMT</t>
+          <t>Fri, 20 Mar 2026 10:03:01 GMT</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOaHFXN0ZWTG5aUFBGNjNqSmdJT2FqeW1MN3gyZ21adzdEZFRYRjg5a0JGOGx3QW5fbjNuY05UYVBpVXFrUUt3cHVBLS1pREEtNUpsMXFiQ2Jhd0w3a1lHNTctMWpnX2dGN1NHUE5jUk1ZUVNsakxTNzFaX05fZXZibU5QTVYxOHlDdFAyaF9pZ1VKLWZLbVgwTUZwdzlkU3lrVkR3MlljaGR1UXFIR29GaHhVWnVyU2o0a01USjZESEZnU08zTk1yMDRnU3ZkMC1YLTJKaHlmOWtLZDl5X0ZPNXVFd0xGcDJMMnBnR0xqM2Rta0VGSUdaUGxDVXg0c3FOUEgxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPMzBfbzBjS3pSMFl5azRlWjl1T1RwZy0xWGU4NDZDTGVaTFpueWdoLWF5WDV6TEhmN3pvZy0tbkdVX3J0NjhSejJBZDRfQjdpa1hqVnFOajhGN2JoRnZDM2hEQjBvSi1vNWtwMVU5TGcxS25qc2Y1NDQyTGZxb0lrV1NlbVB4dFN2clVjSGJ2QWhBdVM3djg2RzRNZDJ3X1RTdmd3ZFhIcUthSjJiMEJaNXVEcWVFSl9BaDkwbGlJSHR2dU1sRnc?oc=5</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -5371,27 +5371,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>UK launches new anti-fraud strategy - Pinsent Masons</t>
+          <t>Where things stand with the other defendants in the state’s largest welfare fraud scheme - WLBT</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 14:54:33 GMT</t>
+          <t>Fri, 20 Mar 2026 22:41:00 GMT</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNYWl2RUVrX1Z0QkdIUTRfRGtjTGhUMTdzcloyNTlhRXBzWkROUEQwbm5la1VBcHRJak1GQWs2U09NcXJnb0VCQTdITFo0V2NRSzRmYlZPUGMyaE45QW9ZNlI2LXZIcS1tUjZ5Ml9PQ2haTEZtZXFqbDVKcHQybGNzdWF0QWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOaG5LdFZodFcxS3hFSWhQczNvcTFEdWR3WkZQZTJLd252YVJxMjNuV3JGUEFzSG92ZFRheVR5Wi1OUGZLQUlGR0dPa1lnNkk5YVlFZjBRLS1wV0RJaEV0SDhrZUo5ZVJ0QnFwNkFlVVpOQ3huZ0ZnQ1RDNGJDTng1VTIxR2ktYmNKMGpEQm9kNWdvTjh6aW5ncEd0TEE5MHh1VVZxYThnak5nQkZzdHfSAcIBQVVfeXFMUDRMRkVDblJPSUo1dWFRdTRpemxIZHdXTTdXWHBHNVU1T1FiMm1ZSTRXTTBvbmJDc1hfSzVQazFVOVpGSjV2TTRGTVUxR3RkSHZWdmRfZTdlRjhETlJxSXQ1TnU4a3cyQnE5YXUwY2JXZEt1NF9LcG9WZzRXT1Y1OW9BQ0pFeldmSmN1ZkZ2Mkh2djhFcENON3A1eWlxaEFwTzg1dkUxZGl5Z0FOUHRRQy1RYUYzVFNhdDNMaTFqbzZLbHc?oc=5</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -5401,27 +5401,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>VIPRE email security integrates with Microsoft Defender - IT Brief UK</t>
+          <t>Mumbai: Former bank manager, nine others convicted in 2004 home loan fraud - ET Realty</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 16:54:00 GMT</t>
+          <t>Wed, 25 Mar 2026 01:18:16 GMT</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNzI4NVZHc2I0cExfSzBaSVczcUMtQlVKaFFjT3JaTVV4Yy1HSGl1MVk2SEVrMDhmUzJYTGV3VHpGa1c2dHF2MEhLVzJ0NE11WVNER0t2dnZnLTlRSEhSSHdNVC01OEM5ajQ0UEh2U1N0dDZtbEh5LWxRdG8ydnZVeEpVaVY2LUhmd0dv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPMzNCSzE0dmdjTUNlZVB0d05ibzM2MmxhNVdrbFJVd0lrcFhweC1rRW12dlhlQ1V4YURsMGpHWXY0ZzY3LW5XS3NXc1U1emk1dHY5eXJJSlpIN01nN0t6SWJjWmhKbTVoMTFGSTBHcFVDM2lZWnB2QjhDeDJfdzZyNndMTmZCbENuY3VrNTk4TlJ6cDFIUTNXdGlhMmdPM3BTS2t2ZDYyMEpxNTFPZzFSMUJaZG05Umh3TmNJczBaUG1CY191ODcwWFo2cG1jaVU0N05KNW13c2U5aFE3bzd5RdIB5gFBVV95cUxNZXU5Q3VpeUQ5a25IT1ptb2FDWjRlTGxrUlJ6VzROTEhfNXpSLWJGVHpQVUtUMmNVS1lYeE5pQXFnY3RQc2FTLXhES0I0alNrdlFaYXRJcmZtOXFXcWJXNXV2NVJDY2ZsaEk4NThfd3VOZVRZWkZyTG12SFVDTDFCWG5SMUE2eHk4NURSay02aXN6ekpLWkhPRTFzNlNJTDdNVFZXZExDZzQ4cG1oWDFGLUpQempOQ2F2TkVnbGVHS19PUm8ydEkzYVYtMGItRmhHTHQ4cURxY1E3YVF6MUZJdDRUWnlMQQ?oc=5</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -5431,27 +5431,27 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Impersonation Fraud: Woman scammed out of £17k travelled across UK to try to find them - BBC</t>
+          <t>Copper wire, e-scooters: Townsville man’s stealing spree - Townsville Bulletin</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 00:00:38 GMT</t>
+          <t>Tue, 24 Mar 2026 19:19:56 GMT</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9VM1R4VkN2TVp6dUxoRWs3R200eDlzcFZmZlBWRGE5UkU0bmhDenM2RDZ2dF9ZUmdlSVB5cTdteER1OEo3ajJJT1kyYWJmLUJjRUJtOUFpOE1QQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxNeGRIVDNmMVZzM09vVTBKSmRNTEwydks1eGVHNmRiVDFFNTNWVzE2dVI2Mks0NHY4Z21XU0xHaWg1T09oMjA4emNwV3VFT1dIQXp6cS1FZGVjNDRhUWNCM3pmdmFfRGFHWlgyRlo2WkhVMFBlZUJUa043dlAzYUJxeU1wZTZSQkp1OE5KeWNsTTh4ZHhiWmFLVklsTHpULVI4TDU0RGloX0k2R2g1WXV5V0dRckRlcFpzUWhpNl9fakZfSmFtSlZOUTNnWk9YZExBZ3BSUUdWLTliejNjME1OLTNpZmdyOE40T2UxLVYxQm0yYTgtV2ZaWjJ1anRrSWhJMmZacENEYWJleFdkaHpNYVJjSWhfQVZRc01WSEtGWlpBV2dTMkxHNTlXWHcxdUtneE5zeEpnWDLSAbgCQVVfeXFMTXhkSFQzZjFWczNPb1UwSkpkTUxMMnZLNXhlRzZkYlQxRTUzVlcxNnVSNjJLNDR2OGdtV1NMR2loNU9PaDIwOHpjcFd1RU9XSEF6enEtRWRlYzQ0YVFjQjN6ZnZhX0RhR1pYMkZaNlpIVTBQZWVCVGtON3ZQM2FCcXlNcGU2UkJKdThOSnljbE04eGR4YlphS1ZJbEx6VC1SOEw1NERpaF9JNkdoNVl1eVdHUXJEZXBac1FoaTZfX2pGX0phbUpWTlEzZ1pPWGRMQWdwUlFHVi05YnozYzBNTi0zaWZncjhONE9lMS1WMUJtMmE4LVdmWloydWp0a0loSTJmWnBDRGFiZXhXZGh6TWFSY0loX0FWUXNNVkhLRlpaQVdnUzJMRzU5V1h3MXVLZ3hOc3hKZ1gy?oc=5</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5461,27 +5461,27 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Three men accused of 'illegitimate payments' over migrant work visas - EDP24</t>
+          <t>Honduran Worker Sentenced In Tampa For Identity Theft - Hoodline</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 13:23:16 GMT</t>
+          <t>Wed, 18 Mar 2026 20:13:20 GMT</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxONkJzTnpSWk5DQ2hkeDFXTnhCcEIyX21qZmpIQ1VXcDkxSWF1X0c0cXBQd2lUWU5vc1YtY1dfS0ZfWVYtODZSX2sxODZJSzZnSjQ0MTluU21HOHRRcTcxaGJUOU9hbnJZX0M0OUNVRk12MmFKZEIxRnFkb1pLaWJ3YTVSY1Iyb2hUSmpVdGtvdk5YVzB2cm16VV9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOb1pnY21aRUJHTjFJOXFMVVdGd29fY0ZodzBCb1FBdlVkNUlaMkZzZmw1YlQwc09yVW4wZjJrZFpRVnhoeFBpN20tTGtwNmtFWWZ0ZlhOanlvRC1Nb0xkMWRtMVFrQ2VSUW5Zb1hXUWl5dHpWNS1iNEZucmMtU1hhOVpLVkV2YzVxeVRpcEVlQnU5aVVq?oc=5</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5491,27 +5491,27 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FRAUD AND MANIPULATION—Trump signs E.O. formally launches task force to eliminate federal benefit fraud - VitalLaw.com</t>
+          <t>Mexican national sentenced in federal fraud case tied to Nitro restaurant investigation - WV News</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 00:10:36 GMT</t>
+          <t>Tue, 24 Mar 2026 22:53:00 GMT</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQSlBDS3ZBYU5LWV9hanl1Y2tVaUpOakt5OWRNVXFTd09QMlB5Qmx4Y3BZQ0pDZzlyRHQ0SFJCQmM4MGN6UVhBZUxxbXBGYXJQYWl4czdna1o2R3hCem1zaW41c2xmb0dLVnZURzlVMWhoQXloSzVRcWlKdExITzdVcXJfbWpISndSaUJqd1BFZTU5WW1OYkVIaXRFV2p5Q2xkdVZjSmFobkdkNmpMRlYwQmZzNFZ6NDZDanR5V0FTNjJPR3VaY2puNDJOdTFYZFJNNDkyUmFmUTdXbXh6ai1QX3BwU1Q5aWNmaEhUWGZvYjRUM1A2WmJzTm1vNjR3aW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQUjY4OW1VbG8zbVRCNVVHRmg2Y1p5SlZkN21BdHkyLXJkN0JXdGpGakpnYVBrZDF4cnFxWDlQb0swRHp0THZZbHRUMWJKLXROYlZHUDc5ekZQLUt0X09GRDlCZlhwM3BidWZ1Znc3MUxYUzU3ODRmRFp1a3BMYlZXbTQ2VGZDUEd3UGJla3VPTVNmckJDR3VJbVBBbXItQzIyanJfTVNkX0stMVMxeW1FaFcwNDFtZHFjNHJCRHJMTUhlc0ZPQlpReHFtVERPdXdPZHJRb1ZTWUxUSkNLTDl1M2VMRGtUb1ItUjRqY0x5OENfeHRNLVFfQXlvV0tkRlBJTFdWOHFUYw?oc=5</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5521,27 +5521,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Oversight and Intelligence Subcommittee Chairman Cory Mills Delivers Opening Remarks at Hearing on Waste, Fraud, and Abuse in Foreign Assistance - House.gov</t>
+          <t>Accountant-General Sentenced to 72 Years for ₦868 Million Fraud | Tech | Business | Economy - Techeconomy</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 20:27:06 GMT</t>
+          <t>Mon, 23 Mar 2026 12:05:10 GMT</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxPcXFMMVdlQmZOWE4zUFVrR3Bvamx1UWdROUdZbzZKU3dXNzJoQXBkeVFTTVpKUUhwSml0TGxtSXRmbkhOenZ0aWNWM1UwaXk5TFhJUWpwS296M1hpcGtzaW5GR09MaWZkMnpubWR0Tm0tSTdmZFJ5cVk4NWppZTF4OFBzOTRzX3FraldwU2lQVHQxaWVIellXSEpqNnNaTjRkWExzSlRvS2RoR29uOGlzTVBwRTFaLTVNenQ2dDFac3I1VTNadG9meDA3M3Z1cmVWTlk2MXJ2eGlBZjZiY29WUDFibXQ2bVpPdy1jQkNYMXhlVUo2ZVpHY2lUTURxOUJmdWtmMnp3ajhkMlZ0RG1aMHpuM1NQazZCSV9zMUtEQ2k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQZGJHeWJfcWRaT0QxdVZ0RmRZT3NxaEVLZ3FRTXF0MmtoSWdvUjN4U0hlWlZUYWxBS3JqSkpaZjNtdmJOcVY3REZJVmFZNGdrYWN2WXR6ZlNZOE5BWFRpZFNwcEhLSFFxeEFlNk5Db2dMUkxZZFdBdlJDakxoZ19pS1l5NnB2Z0JIbkM5SlFBSENsS2NRbW16Z1RLMA?oc=5</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5551,27 +5551,27 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>The Trump administration has opened the door to waste, fraud and abuse and put national security at risk - Citizens for Responsibility and Ethics in Washington</t>
+          <t>Former BES employee Chernenko was sentenced to 5 years conditionally for attempting fraud worth 700 thousand dollars - antikor.ua</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 17:38:18 GMT</t>
+          <t>Fri, 20 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPNFhqSmhoWmhlVWhSYmpXdDRPTWQtMERSNVVMWGU0ZGxKQi1TSUxyNVR3dk1NdDViRTJOYUtaU1Zzc0NtRXhLWTdGdVBsd21HSmVxX2M0V0JGdFhHQVE5ZTdyWFdqUVRTZ1FHMnFtR2tMeGp3UVhSTjJoandsTGJPVEhZV3pIeGtIY0VqM3NkLU9UWlpMYi1rSmpOR2RQLTl4ZnNsaVhXeU5FOXM1a1RCNjl1aVBZV1dXRDA2VzE0bzBrTW9jemFsYUZiNzZHcUp2WkRQT1hQcVk1WktJcFU2ZXQ0X215UmNUdVlFbjhOTlExRkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPbnZIbXZlZFBzdUI5X3ZwWUdsS09vUm1mSlh2TVpQZ0pQaUxDNmdyY3lzTlBlZ0lZVWEtZzhRSl85VjNkX2hYYU9qeTJqTzRUZnVlelNiMmZHa1FGSk9fX0xuazJmYVJZWGVFdklFZ0JBZUlzZ2lPX1BYUWlKR0ZzZHhXdGl0SDh3ajRNRGpqQm11Y1FSNjZZcVJsS3dJS0NKUmlOVklvUG9KZjI3WUwwaEdUOHViUTRIekZWeHNjcWVkYlpkX3RIdXlDQ1dYeVp5aEozX0lKcDhYWGJIVjFFSTV6cXTSAeoBQVVfeXFMTWx4VDd5dUhyMXdlZHZ1NXdFb2hCOFlmVUtBSktvZVBCRXBaMWRTd2F5NE5LUzU5Q3dEeG5XMmpKM1hNeFhSbXhJZm1Ud1p4dVktMllsdHVZZG1vR2tlZGYzWVFZa01VdVg3cnp2UDJyQUpRdnFOWWZkSldzYWs1NGdiQ1ZEUy1YV1I3cWhnQnZvbHNOYldTajcxV1MxdUVKV3I5R0hiNDhHNmFBMGN5WVJmYjF2N0lVN2ZwRFV6Nk43QWJnUEp0cC1kMEpGNXNrOC00TWx5TmtlNXc2MWZEbUs5bFYtTE5BYVFB?oc=5</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5581,27 +5581,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+          <t>("convicted" OR "sentenced" OR "pleaded guilty") AND ("employee" OR "worker" OR "staff") AND ("data" OR "theft" OR "fraud" OR "stolen")</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Google, Meta, Microsoft Among Signatories of Pact to Combat Scams - SecurityWeek</t>
+          <t>United Refineries worker jailed 10 years for US$186K fraud - newsday.co.zw</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 12:10:52 GMT</t>
+          <t>Mon, 23 Mar 2026 07:00:12 GMT</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNT2ZoYjVadGRvNEVGSHVDMWV4QksyYU90aWVWeW8yMk5Ud05OaFpoOHptQ1habVRoSXE0SE9CV2tpRnViOVB2ZnZCc0llUDJpRmNTejJDN2JIeTJaRS14Rmwxb0xlSFRjWDFCZncyZkxtQ0RxdDB0VHpDdENISGVBd081X0VXRlZDeHRLTktMQmQ5YlBabklXSdIBngFBVV95cUxQMXJBZ1EwbGF0N2swMGE2amlHQTZ1SjdDTTdWTzk3RktKdFV0cmMxWHlKZW9Yc18xX2o0MTJ4Qi1ETE9MVVVIYUhveHk0ZVZuWHlUTEZ3YnVGWkVOM2ttdnlKSGdRM0xhU3FkVXh6X1dlOFRZdVV4WnJVNmxDdFN2QzBjVF8xcEZobFFYeUhSMXFGN1lNcFhmR19kMXMtdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxONXE5akk2Uk5NNmVLd091WjIzOTMzVEZzTWRzcERheFNOV2hqRE54VlVSXzRyUU5hRWxlbXp5ZG5ZamUyNW91QlY1bWM5bUdJV2d6MG9tT0twd2lXMUVoSVBfbGtIbG81bS1oUF9xOG9HREQwQThiQU03bzY2WmRYaUFuQUpOLTYteXFJSnBMYXM2ZWdIdDN0NzVNdlFTOVBPOWpWcWtnZ25QU0xPN1RjS2hhS3VEbFHSAbcBQVVfeXFMTjVxOWpJNlJOTTZlS3dPdVoyMzkzM1RGc01kc3BEYXhTTldoakROeFZVUl80clFOYUVsZW16eWRuWWplMjVvdUJWNW1jOW1HSVdnejBvbU9LcHdpVzFFaElQX2xrSGxvNW0taFBfcThvR0REMEE4YkFNN282NlpkWGlBbkFKTi02LXlxSUpwTGFzNmVnSHQzdDc1TXZRUzlQTzlqVnFrZ2duUFNMTzdUY0toYUt1RGxR?oc=5</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5621,17 +5621,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Anaconda woman shares her story of elder fraud, and how to protect yourself - NonStop Local Billings</t>
+          <t>How fraud became a global business at scale - Follow the Money - Platform for investigative journalism</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 23:53:00 GMT</t>
+          <t>Wed, 25 Mar 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOUUJhTEtHUG8tdTRzQTVXN2NLbUNTYkRLbmlFX0M0dFBiaGwwT3Z6WE12R04xc1p2VHR4R2dKaGs2YV93anpZRURMSHRMbTFCNENVZVlrSFQ1bXVfcHFxM2N4TThKMzdFSUVqYnJta0h1RTdieVh4R2RDeDIyM1RYclJyYlBHbzM4bkJzX2lPWnJ1S2V5VDFnTzBuZ3JPaWhWNEt4TDJFNzEyYkdlc1R6TGlmOWVBRDcyb04xbktrNlpGZm9VME1lX1Z4ZW5vS0hsNHAxaWFTRXZtREQ0dWR3cUJDY243Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9VTHBBTUp2SlhDYmJscHJFU19ZaVpQNVlFZF9OZFg3U09qbDFBTUgxVXZRZnlMbzNUNFd2UGNoZlNIWWVzZVBfNVRLWTIyNlVLSUl6VHBGdWhJYm9ycDVsTEZuajdwNldqb2NIaFNRUnZab001alhCUUZORzV0ZWc?oc=5</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5651,17 +5651,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ex-Shire of Coorow executive charged with fraud and corruption - ABC News</t>
+          <t>Tenancy fraud hitting landlords hard, leading law firm warns - thenegotiator.co.uk</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:36:12 GMT</t>
+          <t>Wed, 25 Mar 2026 05:56:43 GMT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOY0w2Z25ZZWw4ZHZDd2M5UmZxLVRDeHFaR2FCNEp4WlFnX0U5U2R0bzZiSHNxN25kQVNMVnV0MjYyOHFidFZraXNmOS02YVlfdXFYZm9Ca2xaSkh5Sld6UjFIMUVBSC0tY2owSFZSNExBQ1FXRnJ4Tmt3QWNCVmdHVG5ZQjdwN0ZHSFVHeEhjUHJRMlpNQ0lfUjZYMm5BeFBOV2NadDdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNY0wtZnBVblNzUEJ2WTRURHJXajhJV1hWUzc4d0t2RlI0cTY5MzhGMmJSOTZIR3J5WTR5Mll2NWloZzJpT01xZmJmMHJWdGdVLWgzQk5aZlpiS1ZlOVZYcGYwczg4Xy1JSThCOEIwZ08wVl82ZVdCVHJVakxSMDdMM3JfQzdUWGVxNU9KdWJMOGZRMWZZYlpXa2xhSWdfamRkYWZRMkJSZHpZVndwaFg5T2VWTlBxUQ?oc=5</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Scots crooks stole nearly £9m in huge VAT scam – splashing dirty cash on gold bullion - The Scottish Sun</t>
+          <t>Council says £247k recovered in two years as new fraud and bribery policies approved - East Lothian Courier</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 23:03:00 GMT</t>
+          <t>Wed, 25 Mar 2026 09:04:29 GMT</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNaXBfM282Nzl5R1A3TkM4T2NkSHVjdS0xM3o1N2ZTWUxQWWZnUTNrSVdHYkk2bWFBT3FzZ3pqSFVZLUtPemxsMFQtWC1tVzEwSng4NHpoY0M0YlhqdnN0czNUWk80M3N2VXZZbFNQN1o5Zk9GbUFOYTVXVHozbTNpc1R2RGdPU3JxWlh4Zm1LYkZoYUV0TFh1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTGNZejRITEZRSEpMSGdoakV6QlpZTFBXNGoxNW5jbVk4d211YUJpc0MzTXBMQlJKWExURXo0R3UwbkVJWDMtUE5IYjZ3bmNZQi1EVlc1X0lXbDFKWEhOUzRkelZRc3BGcmJrd2hyUnhzdi1vMHBtdjh2WDJkeF8yTGNXSXJzT1ZFNHlpT1ZPcXgwNExwRWFvakJFT1BQZUJEcGF6cElR?oc=5</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5711,17 +5711,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ted DiBiase Jr. welfare fraud trial: Judge denies motion to dismiss as defense begins case - WLBT</t>
+          <t>Insurance fraud goes digital as schemes grow more sophisticated - Mercury Insurance - Insurance Business</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 03:19:00 GMT</t>
+          <t>Wed, 25 Mar 2026 07:29:57 GMT</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNbV9wWFl6TGFpTHpxbzVFOXp6WWV5bUdvZGxGd1dEUkdIMHNUSnZ0dks1SlJuWXZQb3llMEVjMVozWUNob051VVFUSFNrbEx5c3p0R2YzYkFfcmFnb1FsOEt3U3ZUMDdmR2FBZDB0TGNtNjRRQnpuYVRUX1J6TldYQ01INTVHdkJHUzd2cTlXNWlfZFJuUlpsaVJWVEVETkRfdFBQUWxOWWRvb1lKaUFwY0pXZlFXd9IBygFBVV95cUxOWjNEbUlQWTk5UmpnM0xiZ20xMEhIMjB1ZlBMa0xkSmNCUTBoV3pCQWRUc1ljaVVJaGgtaGRHNmdHbUg0elVJWjFob1NPNG13X0w2QmRDckNPUy01QWFEVkFZWExwbW53QUVoRHF6TFdsRGFwSXMtNFVsUmg0dlYxQU5vUk9jXzJ1cmhsR1BBM0JxLXA4MWRRQUQ3VWl1S1dFQmVMekQxYzlFZ3A5alBMYmJBcUJaeGNMT3ZrSVlYSVRDS1NwcXJUY2J3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQc25pejJfZUdkeXk2OUdKa3dBcU1Ua2p4UVQwWFZfMHRMcWRvdzh2SW1RTmNtSDBlR1RMRkhWenNzQ3VBRFpISzRHN0xlOUhIckhJeVZZSnAxQlJYWjRrbFdQaE82a25CTE05ZllBUDJwdFRDZkgyRHZGRTJ4YlNSSGN0OF8yMWFaYjlRMnVwazc3WmswZ2htT210OFZBY1pLTnE5M1lyMThyV2JqVXppN0FzTzBKZnVDNk1jWGs5VkR0dm5TeEJVcUtKWlVSMmNTcG9jajRTQk4tQ3NfckN1bjB5VjU2b04z?oc=5</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Jail time imposed as Albanese Government cracks down on NDIS fraud - MBS Online</t>
+          <t>James Junior Aliyu, Ayobami Omoniyi: How two Nigerians chop prison sentences for US sake of multimillion-dollar wire fraud - BBC</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:18:07 GMT</t>
+          <t>Tue, 24 Mar 2026 18:20:24 GMT</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQVFM4VmRRNThpUjN4SFdmNl94RC04a0dsTk9tR0RObnJ1SllQSl8wb3JfdWlyTkJRdVZMaHdkSEs4MlcyNTU0UTNTNFBKY1BMUm5rSEtNQzg4SGRxcmhxUG5idU4zdTY2V3ktSnoxM0dxcWdENmxLaEYtU3dsNjBXejlfWUlkckpUYXdqWUxZQ1VIbDU1cDduYk9rLVZIM1ZjMFl2ZmNKOF9VN3p1TjA4NDJNMUtYUWlzVk9FTVIzazdWZGhmY3NOR1NGZTBCRzFaU2ZMM3pNNGo2cWZjN09rbXpvNVdRNVFv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBWNW4wOUQ0aFVnbkV6Yk53M2dsbVNFcDhEQ1BzNDduUVhoOVlNa3pYMTBJYnFDU0tUTUNXQ2ZzMmZfcThPNU9xNTRoQURHQlJ1ZGZUa1NaRjMyX1Za0gFiQVVfeXFMTlpMVHRMeS1MSjV5QjNJVHQ0bHA2ZDV0dWdqV1JGT2JsSlJ2RFlkZFJsRTlpYTBFbDlQV0NGWUx0NHpEbm41RUNyTHJPSWE2T3BsQXBWZHY0STRFZDBPUHhGaGc?oc=5</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>International police launch Operation Atlantic to combat crypto approval phishing scams - CoinDesk</t>
+          <t>Friendship fraud: warnings of rise in ‘insidious’ scam targeting older people - The Guardian</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 12:54:51 GMT</t>
+          <t>Sun, 22 Mar 2026 07:02:00 GMT</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPbWJuWG80cy1mSmxYbmVSdUNjZ2VibENib2g2STA5dnNvSGl1Z2JWdVk2QXZkOXJ5V2xwV0llc2JGdml2X2szTDg4RkhRaHZsN01ZamdlbFVMalpFSU0yb0d0WG1TOS0wUE1zTl84d2wtV0JIRWwzQlBiUFJhZkU4VTlkNkRzX0Zwa0k1SlFrVWZHTlI3TGZDaVpzeFMyd0kxdHQ3MUt6ZXA5b2tOYkZJa0pCZF9WNmdEcGJLLXJnYUhNNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQcUlyVzV6dmxtc3V2M1ItLTlyT0hhT3RZRnBKbTlLM05kYWlUb2IxVzhySEYxaWFpbFNOUFB1bFlBc1Q1UTFwZWR0ZlF4bzZfbTU5WVdCTVYxaGRxc29WOERfN1N1TWhOMnRwbU83ZnRCclhNeFZfLVhGVDFkQkpNdFB1Nnl5TFdlS25SWHVkQmlSbHRWMWlUd1hHa1Z3RDVGQkVlQmJ4ZmREdDFETURn?oc=5</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5801,17 +5801,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Georgia resident indicted for targeting athletes in a fraud, sex trafficking scheme - The National News Desk</t>
+          <t>Police’s serious fraud and cyber unit advice session at library - Bishop's Stortford Independent</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 13:41:53 GMT</t>
+          <t>Tue, 24 Mar 2026 09:31:00 GMT</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOZHRBRm9yQlJyVk53eTdQOXZHc2lRT1hSdEdoV1M4eUdISWFsUHVSLTdCdll2czFQVFBYaVl0WnRLd3FBbktXY0ZrdENKcy1fdG9sWWgza05qRnNBeDNtSGVmU3loUEYwOURDdXJNeHo1cHFtcms1WUNpVUw5VnFyR3ZmdzE2VUJnX1JPN0V3ZzdVZTdWSmJrRE5aUmhvbjMxaUpGWllDYmdkSFNWaWdwZlY4c2U1ckRjSkVEUEZXOWc3cmQ0UDZuUjM4MzN0bzVDNGFwWEJIVFNSODlmeHVBdkhYNS1VOENEN1dMX3ljUDhDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOU1doRHF1THBxVWhFT2tzdlFjSzJOdUUzbTc1YW83NU9NcEpHNTlsVjBsQTJzc1RBQS1iSEc0T2Y2SG9mWU1lZWwwSmZJQWdmSGRmRmY3TU0tYTZSSE1HZkZSci1ZSGVhWEt0Q2stQVBFNWN2UGNVYnhWUlAtMHlGM1h3a3RXcGN1T1p4OEFnaW1JUXlWQl9kTm1zTmVSZHJBTTk1Nk85dzhUdWpDVU9RU29NSFF1dnFiNDFN?oc=5</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5831,17 +5831,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>West Virginia doctor sentenced to prison for tax fraud and obstruction, prosecutors say - WCHS</t>
+          <t>Trustmi Expands AI-Driven Platform to Stop Payment Fraud Before Money Moves - Financial IT</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 18:42:58 GMT</t>
+          <t>Mon, 23 Mar 2026 14:28:00 GMT</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOb0JJLUhPa1JNS2V6b3VEbUMwRWl2Z3dCNjJIazVGdlJDeFhfb0ZJQnV2RzVjNC05SWhnWVZLSXI4TDlxb0FXTkVpSm1WODVVeGhibU5PdmtuUnNNVHROYXVxcWd6X2YtalNoNnJSaHVWSkRlanpaTzZQY0RzQ3FwcEdkeU40LTJqMVFhX2hkNHlZMVlweHV0TGJyTDNvOVJsN0hIaENhVC1zdDVnSEtKQk5BMll2Y2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOaDlBdmsxLV9GQnR6MWpnTmstSmZEZkROZlpOWDE3SnNKOWw1UHdvYWxCRFJVbjNyRVlicVA5NktudmU1ZzI4bl9RUGlPT1VfWER6R25TaW8wMkNXUzE4ODJwSVN5M2prYVpYb3pTOFktakdpYk1hQzB0NUt2WmlRVmVJbER1Y3NZLWNIS296YXVjX0tleGVnMEZNMU5YVzJ6dS1mcGVn?oc=5</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Medicare freezes new supplier enrollment as Russian‑linked Texas fraud case unfolds - CBS News</t>
+          <t>Youth Program Hit by $17 Million Scam Had Prior Misconduct, Records Show - The New York Times</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 03:23:35 GMT</t>
+          <t>Wed, 25 Mar 2026 07:00:03 GMT</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNRGtEVlRKLW5LMTFNTU9XcERZQzhEYU1vcDdtNVF4ZlFveWp4bTRLT05FemU1R1NJTDJ3LUZpWGYxc3BHN2VibkJMZXRQRUFpb21FeDBCS09SZ3FKLVRQak91cmNobDByQmFfS1NBS2VjWE45STFvd09vZTdybmJRZEFYVlNUWGo3aF81UmcwT2cwUHVydVloSzBSOUlmLURfdHhTeGZDdFItdDg0d3ZWNXpEOUZkdmR1RVpJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOYTR1a3JMcWxHTGtYUDN5SGc1cF95RGszWDNDRDdPTW9yR2tGbmpLSlNRVzRMLUNfdGJFV25pYXNKM0J0TnVXaWlZcGZVdWlYVmlldHVubVZBNEpuNzBTdkhoZllxZWlUM3hqNXJhM1RBTTNhNU11R0ZPQnFEZ3VQZQ?oc=5</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5891,20 +5891,980 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Skullcandy Taps AI to Fight Fraud, Reduce Decline Rates - Consumer Goods Technology</t>
+          <t>UK businesses hit by cyber breaches as phishing rises - IT Brief UK</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:12:10 GMT</t>
+          <t>Tue, 24 Mar 2026 09:42:00 GMT</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPbmQ0UzZtTzIwdzZyV1hzTTdzWHZyY3JlQXU5ekN5WnpYcnZDV3NYWTNtaHE1T3htcERLMFN4R3AteEE2WlQ2dGVsMENDd2lfeEQ5a0hZVEdVWkRWeTRCZ2dnTV9ua2J0MFl5ekhOMFF4VmVzdDZTQ0xIRzdGRWRLVEktVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNSEhwOU1vV2VOZHNPQ2ZOLVozajdTSjJKaDZxcS1ZeG1BUTRvMXRnNzBTYXN6X2xmdDQ5cHd5cFBLOW94SW4zTlVYX2w4NEc5UGtaSE9Nd1I1NjdLTnFQdDBCRU1GRE91ajhvYVpDa196UHBfZ0gweTJONU5xaDk0MnRLUXF4ZFpB?oc=5</t>
         </is>
       </c>
       <c r="F183" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Infobip, T-Mobile Partner to Enhance User Verification and Fraud Prevention - The Fast Mode</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 01:52:31 GMT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPTXcyeTNkVE9PNFl5YUJMR3lQdDVOZEp1WXJpWVk2UWpCQ3N2WDhqSHFGRGFoaUF6WmtFTlEyUV80eUF6UnF2Umt6X1dwZTNucGRtaFJJMmtwV2ZNMW5KSjBvVUQ5NUdodHpfQWhuMUN1ak5iMFNsZDl1Z1QxaDg5YWdncXlpalhsQWRDR3d4bWFfUGEyanZtRFltM0RJVkVuWlpjRU1ETlRCVEExRUtlQ01UdVB2cXpVQmxldDlGek1ySVZTT0swUg?oc=5</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Palantir Lands Contract With FCA for Fraud Investigations - digit.fyi</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 20:41:09 GMT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNM2NUMkt0MEZEQnA4VjhmU0JPWFk1S2tqOHJ4QXF3U1F0MEhOSl9YOFgwcDNORklfZ0dSZVh0dldPTjdaTHl3cWRNeE1rbFZTWGNrWlJOSTJMNENvdm5kejJ5cms0YmptME11aWxMOUhNbkgxanZ6OXNSUzREeHZ3TTRNaS1nVU0?oc=5</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>As AI Agents Enter Customer Journeys, Enterprises Must Rethink Fraud and Identity - CX Today</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 15:49:43 GMT</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQYWROa1Uxb0NLTGRLVkdTajg1X3llZjB1eDA0UFIxQ2F0RFhTcW1QeUlxNTZaeXZVcWhKTkZTS2JDTDJkVm9xWmRHU2lDM3c5OWZyOVloLXUxQUllQ1VVcVVNelJEM2ZzVlZfSnVMSWpzM1FhZTNBWWthZjV1cjF0RG1iSXRIRl9fclNRdW83V2dfLUNmc2lmUGRVUk55dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tokyo police launch website detailing anonymous criminal groups - The Japan Times</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 05:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOS1dxaEw3dkpQUXlsT183WkVBU1RXcElIM2VnZHJPay1ZLTJZVU1hSEMwZWE1U0JWMUlFcm5lOXQ0N3VNcjRVaS1NMDNYTTJvaGJ2a0w0R3lyRmxRX3VtMFpNc19aQlZ5Q0hlM3VWdnlFZUhxZTVzcFBfNUhUdW9VeTBScWJ0bkZjQVNjV2NoRk1lN29uUW5z?oc=5</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Bail set for gallerist accused of art and antiquities fraud - eKathimerini.com</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 17:16:18 GMT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOd0M2VlFjcnJuVTNDSWpPVnBfYWlMQ1lxY1lraXVYS1VJZW9qMmIybjRnMXpyZ3JXTkJUM09qeVNtekRYNU1Ldm9mVWJ3ZWZnSGxJZUlVUnc5dWluN2k3VHdNRHR3SGlxOGlDcW1XTDQxcl9SZkRNWmRxakl3bHJTeWRVakJ2QmdKVWQtNnB4TUxnMEIwcF9vcXB5Qm9kNmlzM2Q3bA?oc=5</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Tax Agencies Using AI Mainly To Flag Fraud, OECD Says - Law360</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 16:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPTEFicUFCZkY0ZEJDeTVnZnZnWHlyV2RuY3NJVmM4ZmN5WHRDZG9McGxUVGVhSTlXZ3Rnc1ZROTcycXRndHRjU01DVElWckZiQy1EYnQ0aUtiUjZ4enpfX2xDUWxzbEdjeGxoX3Z0ZTRFbV9pek1yVDkxd0lBS0VTWXdlaXUxZzJ6M0lHZEg5RnpRa1hIcGdaREtvTDZFOGJYaU5BNUUzSjNOd9IBaEFVX3lxTFBkUjZkNzNqTDVfRzFSVGlXeDJxT2dsbnF1a0lwX2kySXNVbUsxbWpPYU5ONkhEWV9RTnoydWpXS1VFZVk0NWU1Rjh6Z0g3R1RHUnU2NkU4cTMxMEoyTlp2STJXNlNaSFlz?oc=5</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Feedzai Unveils RiskFM, Aimed at a Frustrating Plague of Financial Fraud - Digital Transactions</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 15:07:42 GMT</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPa2gtOE1vTVBodzdETTVTLXU2WUhWeVlvenpTcEE4dDA0Qzg4YkNMaGlscnpzbzduZFJGYk5ZNUI1VEtpM2g5NFZ4VzZuTHduSC1sei1VT0hkSU5LSkI1Vlp1OEo3bTlHaGNDVE5CQ2lhWDZNdG9jN0FRNzJRMjZ4bGFkOGpxTmN3Q2VqLU5hQnAzcXJsNGtQTjBjQVZRSjBld3p3VGJmNHZJUTZO?oc=5</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Newsom’s failed leadership has let California become a land of fraud and scams - Fox News</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 09:00:15 GMT</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOS2d6Mk5TY3hOTlM4Y1RfMVB0RDUwc2ZZWGVyeWdDZFJqbzdhZUpITG53RUdfU2JzWUFnV29DSFZCN1N3TGtOZUtOaGdMbmQ3OHV1VzFLUFYxWWE3X1p2LVJRUWxHdnAwT2lXZHM5V3FYQnppUkZtWWtnMF9SSFZ4NE5DaVJxNm5FMXR6bktZOEVfdjVQMVY4TEZlYU9YeEN1QlHSAacBQVVfeXFMTzhKOEdmemhqeTdmaXQyWDJXWF9OUllBcjlucXNnS24zRVdISDE2UVh0ZlVtcThTWnpwTUVQOFZXcEN3VkowMHQwVGdKZ0xTODNYNlEzQjl2LXBmMWxqS0U0V3RBZUR2VFdMZmxBc25tOFM1U0J5VFpWRDBMcmkwSlVZUkdDZHpyZHNQaFVfNXZKWlZCQ3kzdVR6dDVMZTBwMUFNZFZiSTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Scam Alert: Stay Safe from Phishing Emails, Text, and Phone Scams - RaleighNC.gov</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNWmNqNW9UaGxSNjA1bGVBLWc5eXFEOWQ5bWlZSGpzTGx6N0N6Y0pmLS1ZUVNqUXV4ODFkQ2s1R25LX3d6ejhqZlVYWktYMDl0LWx4a09nNUQ2QjRGMDZrYms3ZXRfb2NoUTVocEdDY0RxLVVxSU1hTWtlNGJXdXZuZFVhNzl4UG9LalpWX01kRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Couple face trial over €274k theft, fraud and pandemic funds laundering - BreakingNews.ie</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 13:17:23 GMT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQYW54TWZ2dmdQaUtKMWNTdThTZTBGLUZyV18ybU9jTEc2RVlKeUl3WFFFaFhSZ1lPOWlrQ0gtcTNMTElrcHlsX280VTJ2aUs3UDlOWVE5MzlNU21oZUpLSEJJb3hwa3VDalJUaU5IN2V2emhEUXBXS19DaXd2VjNoZWZjOXg2dlc2cmx0Q0RZbXVPeHpXVXNRVlhlYWRaQ1R1aUx6ZWduUjlTeEtNUHFPLUY1S1ExVUJ4YWlJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>TransUnion launches new fraud and personal safety check app - American Banker</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 12:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOZEV3T1A4UDE0alZJZmZxTFV2RDF4T3hRa3lEWmdiVklDRThlUUpfdFNubW1ScFZldU16MG1oR05aZUJFNjZzLTRGNHhiRDh0NXJkYkNUUVZ4Si01T3UyOHcwbVpvRGVVQm5SUVpjbTIyeTFMTGt3WnYxS3hxeTVyd2ZMX1BsSUEzNXpUUjc3OEtJRm1wWDlxS0JJTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>20s Man Sentenced to 4 Years for Voice Phishing, Sending Junior to Cambodia - 조선일보</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 06:19:44 GMT</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQZ2FXMzR4Znh3bmFKSE5VazF0Q3NLTTB3MjdHaFVpX3JTak8yeG1FSjlIRkg1V3AxZHVZQ0s0Z29SZFFhRUI2ZWt6OTNyT1lYcmFRVzNsQWtIazBJbEo1ZGhRUzBJMHVaNnlkVTR5MGhKckJMSmpiSzVZYVVZdlp6NFFWZVVwMF9Y?oc=5</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Elon Did Some Securities Fraud - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 17:59:17 GMT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPNWpoQXZyVG9xcDhubm5LdVBLWE5MOFI0bG1rV3JRVkZLM2s2ajZZYVpJNTZ0cldfT2s1VkFqRGZGOEVtMW4tRXRVYm16V1ZOTjBRTWpDajBtSHlKdWowamdGaTRnRm9MRFRmMkJoaWRDQlotLXR3Sm8xWFMzWDQ2Y0lhblZweUNwUVNTb0xIRHU?oc=5</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Carrot Launches AI-Powered Global Price Monitoring System to Detect Fraud in Fertility Care Worldwide - The AI Journal</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 21:15:57 GMT</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQZVpUSVBqNnVRU0t6am0tSDJJTUVNWW5oTDlvZmNuY0hGazR4aThtSUphNlFOOFRXdXRCTE4wQmh5bjAtVTdZc1lDNWdTbVNtU0hsX00wM0pDYWhzZTJyd2Q4TjliTGk2elZEUnpBVGR1eFNtM1RhYXVxem9fTll6VlVCVjdSMV9IWWdzMFpoUUR4TERDZ0UzbFk3eDB1YmpGbGZvcFpPOVhDOElIYnd4T2wxUnRUZDlib3doRGZSaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>White House Issues Executive Order Targeting Cybercrime, Fraud, and Foreign “Scam Centers” - Consumer Finance Monitor</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 15:21:09 GMT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOMWphY0hqRFVMbUVZVmVUX0FIa0QyaXJoemdoTzkwWUNzX2s2Yml3dWdrOTNWRUhYNGlCZU9pVWZPNGZnREdiRWxSakJHVWRxaTV1eE8tTUwyTGM5a3d1dkZaVVRmU3VCMmhMZF9kM0l2RGJic2d1ZmJqNGp0eVR2YnF3YzhfaU1RZEhXMjIxNmQ4ajBOYkl3X2NQZnFjdm5MY18yU1I2UUZ2Vmd4RUl2cTVtS1FFNzkzTF8zd1J6WExFbGtBUDJtVk9yeXJNLUJnX01N?oc=5</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Protect Yourself Against Romance Scams - ICE | U.S. Immigration and Customs Enforcement (.gov)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 15:41:11 GMT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNZjhHMFRrZ1otVHU3cGVtSXJSTVgyeWFzOXFyUlFFSDRxaFJoclJPR0hPdzR0SGlIWVh1VWo0VW5vWXZQZnB4a3B3ZGozUm5KZW1OT0QwaUtKNzNGMHI2V1hqaTNLdVFlM0ZvZ1J5V3lUMFhBUVNfMTBMSXh0RUlPXy1hLVNQRTdMZlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Judge Rejects Javice’s Bid to Overturn Fraud - Sharecafe</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 08:53:12 GMT</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOX0tfMU5FQWhPbWVETVk2LUh3Zk8yVWxLa3FJUUZUVzZPaFhYTnRjY19GVWJ2R3JaOTFVZWo2VnRBcENzTzZnM0ZvTE5YcFVVRFFFc1pBYjE1eV9zaWJ5VExwUTNITTE4dF9keUstWUxmRENiU01tZldzSnE5eUplN25zbEhlRU9McV9wVA?oc=5</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>The FBI warns Tennessee music lovers about a dangerous surge in AI scams, stolen songs and ticket fraud - News Channel 5 Nashville</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 03:58:14 GMT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQc015WmtabWtGUWhfUDc0cjBSYjhhR0xxQ0dWZXI2cjZwWE1TOWFNWGRmeFdESDhXbkk4aWZvVlhjQlJJOTdnSUh2dFE3MklrUXFqdFNBMkRURUV6X2cwbUNHMElaaXFsYTd6Y2ZRV2J2TW9iVTRaSXJ3MTVtaUlyT1pFSFZxbzBLVTNGWjRQUkFMWWRFTnFiYjQ3OTh4emxaMjUtVEdyNFIxM0NLMTV4VHZIdlBhTFFDa21PazI5dlRpSEFBdlAtM0QtamRCWHozVUxrZXF5dEVQb3U4bm5uQktpZFJZSFF5bk9mNXJDckl6NjRmT1QxRFV2cFQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Medicare is cracking down on rising fraud and improper care at hospice as admissions soar - MarketWatch</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgNBVV95cUxPUkNCQzlPMWtYRU9VUndYXzlQQncwOWJpRUp3SkRQM0dQeVhtdGN0clNPMm8tYk5BVWszeTZpOWwwRkFONVZyZWlvMVlZenJCRS1ZWWEwOW8zVi1MN0JFSUU0WF9OLWlJejhwYXdHNFJQRmNpeXZnd3pRcVkyNlQ0bUQtZHJVVmhLaVY5Tno2WGRXSnNIMm9pemNpQ3RLbEp2M2Q1dUZiUzhfZERJc0VQTVRXbmRjclJCVDE1UEZTWWxCSm50ZXZ0QVVqbndtWTFvd3EtcXJtQ0lyZFJNQ0JVMzFJN2sxQ2RTVXQyR2VLWTF3NnNrVGJsLTFUUEhvcWczdW5mbjloSGxQMW5lVE1ieUVhVUkxaFJuZlRPakdIQVhDbDd2dHJ5V2hmLVZDZkl2cHlINlFNUzZQNFF6d25XYjg0ZGRxamtWUUZDSUxFSnZTYUhMRXZQdmJDN1NaRE4wQWd4SjRtWGllN0FManRTb3ZhdjRlQ2lNQjJCbnBTMWNYZUZmQ29HYmRMLVN0eGtJRWtMeXowTV81bzJ3TzFzSmhPcDNlNUtQRWp5bWIzWDlNMkRJU1VNWWJxWktGVU1oWVhyV0tNYl9XR0RYZEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Layton City bans cryptocurrency kiosks due to fraud and scams - ABC4 Utah</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 21:44:28 GMT</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5TUFdJWWowMkViRXFfRmtYdHV1bFBOUVU2UFhadjhuMkxqRTUtOHdSOHB0SnlPM3dsM0FCRUxlNkNHZ2Y3cHJ2QlI5LWtjQmRpV1ZzUlJPdFNzWlZOUW9iUGFJYkMwQXFTVkFVOFRibXFwNTBFeXQ00gF8QVVfeXFMTzBWakxESE9OQk1USGdsalJyeEdNM05JM215dE9NXzVyZWhkTVVfcU55cW5yS1pWTHZLbUczbmlyUGZybm9kQ1VSSUVsZ1lOd0NGNnZqMUpnWU1GNFdPRUg3QmdnU19nNzU3N2tNTkpIemkwU0tsbjlMc3FPMg?oc=5</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Sky News Australia. . Podcaster Joe Rogan has blasted Gavin Newsom’s Press Office for mocking YouTuber Nick Shirley and his fraud investigations. - Facebook</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 04:48:01 GMT</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOd2ZjQUVwLVdWTF9PNzN6cEo0bWUxU0hsY3AwWnJKWXUtM3dhbWlqT1c4UFJrcFFsbGVqak1fWkI3a0FRSExLdHZVamNacXJmb2hlYWxqblBzcmVJZG5iQ3dZYm9EaUh2d2ZCc2dHbVRxZ3RwMHh1TUF0T2k3VG05NEMxQzBhWmRGa1ZVYW42QkJGNTZIZThrU01hUlRHZVFneXo4dG82enF0SGcwYmRYZ1Jfd0hwNFpxQ1pqcld2S3RZSGk1M0xhOFE4dDhGWnZiSmZYSnBleFN4RGczWXM3MQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>News you won’t see on Fox News: California revoked over 280 hospice licenses, 300 more providers under investigation since Governor Newsom’s hospice moratorium - California State Portal | CA.gov</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 15:14:04 GMT</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNRlUxZ2oxQ3hPNlRfZDFVRjAwVG9xdm5KdXZyd3plcU54bFVGWjNqNzZmazBEdVlaZEZuNWljR0xmUlZqUFBlMnBPdmRXWk9SckExYi1obDZnZ1Q4Qk1iVDFZUk9URWQwQUdQTklEWngwQzI1SnlzRldPSzI5TG1feTRPOEZCUEZ5RXA2eVVDMFVWQWNyVXcwYmhxZXhJRS0zTVl5ZlNHeUJXZzNJcFRsbVBmVjhGMDhqTElqM1YyWGVzd1J2WmYtMk5XdnY5QWlSbl85SmpCbF9qTC1xWC1VYnM2bGY4RTJJMUItcjhKNXBJaXJNczJncnlwQUlBV3dnM0JHbzRMM25qNXZrdFd0TDNxU0ZvLUpadHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Labor Voices: Tax fraud in Michigan construction costs millions - The Detroit News</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 02:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPeDVtVEk5Q29qeFItRHE2QmdENnhWVy1EZHlFbFgtRkNyYW1hMUVNajBPWkJjYXRwdWxzMXBlNjhnUk96dUJUTWdmZHZhNk8wVTBUS2lyU0EyMzhXYjF5MEpMVnNES0FWSXBLNm5mWWRRc0VHUFN6MTVhNFI0WFRQT3dCZUxGNG10WG8yTHFLY3gzQng2WFk2MC1PZWpHWGlUbXJqYVdTZ0lkNlliY2FwTnRLVTRYal9zRUJtNDhta0ZXVDVFVXlQMTdDRWE4aGpkNnozaVNwWThOck9rUjF2ZGlPRGduV1k?oc=5</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>EDMO Launches Student ID Verification to Strengthen Admissions Integrity and Reduce Fraud - The Desert Sun</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 07:51:29 GMT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPWTh0UUpFWmV1SkFwaFZCMDhnZ1J4SGpTN2hSUWVYc2NWRnFpQnhOWkR6akEyOVBISl9wSG9YZHlaa3Ywck1EV0FUMl9mVUNweG1nSnJVXzluTnZBcFpqcFVsVmtKeldnX1VvTS1kVmNUa0xOQkNWMUZudXVmdkI4SGYteXV1UFBUeUhNbnNHTWhEcnd6ejB5REVWQ0hteTdoR1RiV3dKNUY2emVxWjhnTjJsMF9zaFZmN0JucDlIdTI3U1BLQnA0N3JPeGtaaU1oMktrTGR5T2RydTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Detroit woman pleads guilty to wire fraud in student aid scheme - The Detroit News</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 22:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQYUJkaG1xeUFrQmdRMGdRcC03dlNWRlFnWG9rWm4wSHA2UjVWcUV6dU5LWElVVDhkOUFCV2t5amZsXzc0Um4xQ21UVVg3amN4NlBlRGJaTE5EVWJyRnhiY1pOdW5jamNqc2dEZHRsSURMbW1OTmMxQUllMEJBUk1PYUI3SGRQOVZIUV9FYS1CQWNybHUyTmpIdzY3NjFuMjJGYnhDVHlEWkFaNnBlWFRDSVVBRWY1N1NzeEFBWXgxTWNnZzlieUE1LWVrdzdsTmJM?oc=5</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>‘This is a political persecution’: Ex-Nye County commissioner makes not guilty plea - Las Vegas Review-Journal</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 00:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOVEpiSmhwME9heDBSM0l3dEFKMHZJd3B1RV9pTkg5TTFfXzYzX0EtNUtGVDVMb2ZYTHM2MGVBbWFhZHJpWWViekJEMTRTV1RIdFJHMWh3MEhnaG12SnVQdTZuTVB2akU2M09yU1pRMTBPWUVual9EU2xSZ1JLeUZtRGRXblFDMEp0aTdsbGctdklwVkh2cGFzS2FhcG1fQ0w3Q0xrb19GN3k1MFd5bGN2YzZpN2ViNmthUUl6QW42MXJsZGs?oc=5</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Fraud and Loathing in the Mojave Desert - FreightWaves</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 22:30:29 GMT</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ERlpNNVRQOXNNbnFuOFdxQUgwbGo2cGNGbGN2RXpQaFFnSXhOcVJhSzVNMzUtYkZPOGhEMWUtbnRCUnNhLXlDdXA4QWJRREJhZEV6QTVrQXZMeDJ5T0JpZ0JDWXhPQVFlS0NjaUxwZWtXTHZjR2pBcEZhajlxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Phishing Defense: Tracking Adversary-in-the-Middle Attacks - BankInfoSecurity</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 17:32:39 GMT</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPa1R2clV0VFJaeURYX0ozQjY1dUgtQ2R6Zm5FVnBCb25aR0JvU01NaEtKY2JKRGtzR0gyU3NIMnBESmNjRFJlMTlDcGtlY0g3SURCaDJUbm54TGJCN0xOOHFFNF81VVpMX2NZQ1NuV0lPWXNTZTVYdGhKQ3lVN2NGYzBoWlRhenZtVF9UUnI4d3ZUX2poQXA0UWRZUDNnVU0?oc=5</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>When a loved one falls victim to a romance scam - Australian Broadcasting Corporation</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 03:26:11 GMT</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPal9CbXMzaEhaWHo0YkQ3RkZvdGZ5RHFfb1Y3dFJxXzNKZU91U3c0MTI5b2IzdFZmb3QyeU1jN3RPU1puQ3pTQ3B4cGJKckZRbkhuYjdGaFFZaW0xTWN6bV93enZzdFRxcmFWRXhqWDU1czJ0bmVLRFpBeDVfYXdkcXYwWHFlTjNVcFNSRTV2cGE?oc=5</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Credit card fraud surging: Why you should freeze your credit - The Points Guy</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 16:02:33 GMT</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFByRkVBSHIxeGtxVHItNUQwNjUtRFd1NTBkX05pMnBfUXRXa2QwQzNwd3hEVElzbXJBZGp2Zi1sQ2NtUUxpQkdHNTdoYk42R2lzVXFNb2JNQ0lOd01NZWFtRmY0TUJVZzJhaVBWTW5YMndaTDlPUjh3?oc=5</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Conservative activist convicted in voter-fraud case - The Washington Post</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 06:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOSHdjeDBNVnZocFZVeVFiY2gzN19QNUEwTUNoc0ZnOFVSVU5HSWcxMWhEeVNpZm5fdFRhbzJ3RTFWc1VOWTVhZDdMNHBCVTVfWmdsdTdZX2hyRFRxdkRPR1d3ZHpmdnVDYnk1Qm5pbnJtQXUtZU0tc3EzZ1hyS1VidGdoRnEzdEJMY3VMT2ZyOWk?oc=5</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR "identity theft" OR "payment fraud" OR "money laundering" OR "cyber fraud" OR "bank fraud" OR "invoice fraud" OR "romance scam" OR "courier fraud" OR "retail fraud") AND (UK OR Britain OR Europe OR warning OR arrested OR convicted OR victim)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>NINJIO Launches Sensei AI Suite to Advance Security Awareness Training, Phishing Simulation, and Vishing Training for Human Risk Management - PR Newswire</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPOFB3bTJJQTJKckNUTGJZUF9SM2VPRjJSeXFGSXk1b2MyUDk4b2xjQS1SNmhDVUxERU1vSzNQQ3NadGxXUDB1cUdnUDZLMzZuNG03UXRYcUs2NGVTbjhlVjgyclUyWDQ2aGNsejFodkRSbXFidVFUR3hjU2duWnp4ME1paENLV1pycm5qY2FmWWJhLS10R2FJUlVNS0J3Wk5OT2p4X3JXZXZWRWQ1R1RQanh0N0d5WmZpeDJsQzVFOHVtSmxmZGZkSEZGV1pqV0lHUENtSXdDNEZ0NmxFSDlESnlYcmdoZVlGWk9sWGRKcWhEWVpWM2J0RkNRdnRrNmhSQURrY3QwdlJxN25HYXBlZjVaSjVfamlsemZJMjBR?oc=5</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/weekly/topic_feeds_week.xlsx
+++ b/data/weekly/topic_feeds_week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F215"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Changes to UK visa and settlement rules after the 2025 immigration white paper - The House of Commons Library</t>
+          <t>GDP quarterly national accounts, UK: October to December 2025 - Office for National Statistics</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar 2026 07:00:00 GMT</t>
+          <t>Tue, 31 Mar 2026 18:12:01 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBXb3hZSG02UTNOZXFvbVV6aHdkZ1FBcTI5QmlrYnFCX0ZnQ0MyOGFULTlkZ2N1UGloZHd3N0xkT3J6VE1KRFdfN3RxLVV5Q3BEbmhwTVJ2Zld6M2owTTNuZDZnQVZ3cXp5X0ktakVGUEJna29h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSVZ4Uk1NR1cxY19wX1E5Z09aaFltQVBpbFlZSjhnbUxXbngyNWh5NnA5X01fMGZ3ZHdxX1pzeFJ6QVRoWlJhZTZ6RUdQNGVac1JlX2tDUmdYVWpPeFVoNnFyYl9fY212eDlmSXdTRU9iZHJTNS1LQUNQaFh5cndGRVlQNVl4eUl5aTQ5ejdGaUg5blhGc0J6cFN3R0xZTnVucW5uZF80dmRDZDVsS0hTUmh3?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Time to Pay Up: Government unveils toughest crackdown on late payments in over 25 years - GOV.UK</t>
+          <t>Youth involved in nearly half of terrorism probes in Europe and North America, study finds - Euronews.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 00:08:20 GMT</t>
+          <t>Wed, 01 Apr 2026 06:00:30 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNMkRMZUptbzJNdV9UaXJtMWlreTM5WUJ4Y2FseGp3SDVqS083a05XckRPTzdwNjAxYy1iZE91ejhDM3Nfbk85SWJrdTM5Y2Nfb2R0VExCdVdrWmJneGhEYk1TWkZhTnJBdmVVUUo1QlY5VVhoTE1abzlkTUM4alNrcnA3MFZBcDkwdi1VV0RrN2NRZUFPZ21MR0ExZ2ctUE9kYmhwS3R5amJWbmlWVEhpNk1IUUY2RV84aW1sMHh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOd1hkb0J3MFg0NW1nek54eDQtZUltQm1sVnUtSTVoUmFpSnZFcFNyWHNzN1U1ZzBxQ2dwQjBfeW9IS0VGY0E5Z3lGeG5rbFlybEluUUdIMXhHSC1OODZyT2tPZnFiUTlJd08zYzJnR3lNeXpwY0p4ODgtNnFmc1VzMGFBZmtmWTFLRV9BY3JpRmplTno2OE9YWXBDZlNGdHhDSmg2WDBGZ3FfVWR1ZG1NZTB6aWRIeFBTZ2xwcEdOTkNfaWR5UFg3NmcxTHVCR3FI?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BlackRock boss Larry Fink warns of global recession if oil price hits $150 - BBC</t>
+          <t>Apple subsidiary fined by UK government over Moscow sanctions breach - The Guardian</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:04:43 GMT</t>
+          <t>Mon, 30 Mar 2026 18:07:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE50SEhfNnhMQzB0aWFPLUVHcEFyaVA5M2NmWVFEWE0yZmQ4OHg4N3RNd2cxQmtPRFU1a0lKeGFxTzI2UXo1RGlJc3pYN29VRTk1UnhVNm5ZN3NMZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTl83ZVg5a1ZxMzZNQjNsUXBjZWJ2eS1ZSDJ2SWY4eDdndmxwTDRvSFJxaHlEamJSVWRnSlNSRHM3alpJMnFKMGZiMVhMU1pZREdJQThsVzZvS0c0TzctdzBmSTRhaEF0cE1NR3UydWhrWGRwYm9iWTU5SGdyaFBCUkx3UEVoaGJ5b2ZkNnVPZ0lpOElKb3JUUmtIZmd4Yks4NzRSOWx3?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UK inflation held at 3% before global energy price hit from Iran war - The Guardian</t>
+          <t>Track UK's latest migration numbers - including asylum, visas and small boats - BBC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:03:00 GMT</t>
+          <t>Fri, 27 Mar 2026 16:45:39 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQdW9RdlgtdU5kbjBhME9Ca2RXVkVWd0ViSF83UjBJcU1zXzFvU1cwaEVpMTVfenVzaklZRnZnajlqVzZGU2JjdGdjX0liaFdKZHhYckRVNWdrSXZGZm0ydFVGMHNQalRZajZQY0JBckxSSW5zbUdtX2pvWTNjTkl6X1M3eU1QYWlKRDZEaE9oUTlfVGxWQ0VjQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9abkk0V2VWNThMdjNsdG1OMWYteGRuZWpJSmRBeE05TkVScDRxWHpsOTBBbldicVRxVnFWWjV6WkFBTjdZcUQwMVZoMHl5d1E4X0RyVFJIeEh0UQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Keir Starmer to bring forward EU rules legislation in King’s Speech - Financial Times</t>
+          <t>Simpler household recycling rules come into force across England - GOV.UK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 05:00:48 GMT</t>
+          <t>Mon, 30 Mar 2026 23:01:00 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPeHlkN3MwSjVheHB2eXhXRktOY3BxYUhaUHE5Y0ZEZUNuUGQ4UWRwQWpuZWtseEVNY0UxQWxZMmxGVlM0aTBOQnlBQWI5OUZVV3lrLU9ManFQQW9icW1CVjV3dkpjdzFMTDZNZ09wZFBNc3N1NEVSYmhJLVdOSG9tdzhfbGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNR3huem1IZVFmWWxadHppSnFibUVJWl9kczRucWZpTDRtSjdGUE02VHZjeFdiVFFkRUtUS1pzRTZfeUZZX3FLVUh6bDR5cGhDTkN1V1lJbEVhUUt6WC1WZDY2Uk5RUy0zLWlOcWtrTEVZZnJ6dDRUZnhuU05TSW5YQ1l0N0QxbnBqMjlJT1FCcXljOTJIT0JFbklVZ2V4Tmcw?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ECJ advocate general advises on Yemen sanctions - Global Arbitration Review</t>
+          <t>International Crackdown on Online Scam Networks Deepens with New U.K. Sanctions - Kharon</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 21:29:17 GMT</t>
+          <t>Tue, 31 Mar 2026 19:56:37 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPc1FBcFpJdnNsekIwTG1fVkZ1X0RoLTlyaUVDZW1DZm52VlBFMHBfOVdVNFpBblpFWHRwY002U0tKZC1Mdy1JcDdIM1VJY2xhOWg4bmlCbEk0dF95R3p2NlFoN04zdFhBblg5cV8wdWgwaG5BaUhQTDFaYTMyZDlKWVFUYW5vUG1uclZTUVdCTlpLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOZEEwM09UYjNiR2V2bEZvSUVyaV9wUzNiZFFQSmJWaDM4LXRVS25IQ2V2ZGFNZERueUtLLWppMHA0Q01fSFJjVjVubHkweVZNSjNfSVl3UXBkVXp5a192Zzk1STRzdEhCZzU4TWh6QkVhM29JeGJiRk1PUnY1U3JQeFE1N3pvNl9QYU1PNDJXeTNodw?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Middle East Conflict: Situational Updates and Implications for Global Mobility - Newland Chase</t>
+          <t>Sanctions Round-Up: Key UK Legal Developments and Enforcement Trends March 2026 - BCL Solicitors</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 10:28:13 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBnZEN5U3QxTHpnZUV0RVA1dFpHUzMyM05BTEREOUc0LXppakp6YVdTRnZzU1VFbWdVVGFKbXA5MWhnVDV4ZFVvQkRSOUMtT2pLY3NQdHliYlRJM1EtTGVJM090X0MyWmtHdWNFUUNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQZlZxTkNPNXJ5X09iSnZ0UHZpUDJXX3p3RDhsYllqU2d3V2dUeGVkQm9nNEZ2VWNDbVR0NTZiWjU3bHpiTTJBbTNLRURwVVBJUG1YTkpnRE5BdjJKQVBBdFJBZDJDVm16VC1XN2hKRkQtdzFjRmxiS0JCSG5NbDFudGpyajlWblVwTzlPbV9JTGZaWnZHX0x3bmROWFJBOWJ0V1MxNkRR?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russian Sanctions Spark Investigation at a Global Bank - FTI Consulting</t>
+          <t>Timetable of recent and forthcoming legislation - CIPD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 15:39:55 GMT</t>
+          <t>Fri, 27 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPb2hNR29yQl9Lc3EzWkRVa1RKOTJhN0JVM3pDcWxUMEdqTDBKMnZSb0hhMGVWR2IwRHREWlZ6OHg1aFNMdjhOcVlnX0xjNHZ3MnV6NllHYTRDc2dxdk1rTEFzM2tHel9NSFFPeWdKamdkQ0drMmtYNWY0Q0toRFMzUE1MVm84eTNBVHNOdldDR2xJQ1JqLUktQ1dGc3NSRU1zUFhj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE45TGxlbm1lRW1oQXZoS3dkaW40VUtHV3ZzQnRkTjRRUjFraFpDWV91LTYyUml5UUhHYkMtTE43Nm9yaEswTUVOX09fd0xlc0ZQYWVMbmVHdzlnY1BTOGkySlNVdVhZSDF2YmdUTk9SZ2tpdVVTeWN0aw?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How the Iran Conflict Could Drive a New Wave of Terrorism in the West - Vision of Humanity</t>
+          <t>UK Supreme Court confirms broad reach of Russia sanctions and suspends payment obligations under letters of credit - TLT LLP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 00:46:12 GMT</t>
+          <t>Mon, 30 Mar 2026 09:42:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOOG1aa181cGxYSHU4QjllaUk3R1dnZlpHREpCd084d2Fid3BnaFNieGhoclVGdWVWTk42R0F4Q2pnaU11Y0hjbDYwRmlQRVA1M0VSSi0tazN0UG54S1pnY3Z1bm12bmd2VGpqblpiN2xFTXJLUG8wdTVEeWhTYnlQUHFLM3M4Z1lwWEdSWmFzV1VBeWNFYUM5a1NCMC1MS0xJR1puTUN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPRU1MSVpRMGxrOWM0dVlySXhtNUR3U1F6RE9FWEJjOEhVMDZ1VGN4bmRES3Y4ZHdrUXg3UHFsN3J2M0F4VzRILUxSbUYzd0U5UlNvM2FQZnk1eG1sRzhCblpRSk5melpYLXVuN1RwS05ac0N0SFR1LUdUZkJpSnFOSXQ3Z1h1TFk3Z0dpOU9qcUNraWpya3dUc24wYVN1UXVOdGpTdjJMcjlXNE5kYzY5OG44SWVBNVhIb3QwaTAtTmg5Ry1jeEVzSjZCR2RlcGQ4TlN6V0xNU3Y0MDVYOVB4SGVjSUhuczk4a01Bb2VHdGhRcUV4?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>‘The UK’s 'impact economy' definition must put ownership first’ - Pioneers Post</t>
+          <t>Europe’s institutional investors step up bets on the global circular economy - impactalpha.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 11:31:00 GMT</t>
+          <t>Wed, 01 Apr 2026 03:50:45 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOSDVfQUdKUFlfczFGQ3NPbmpadUdiR3VvWUFYWXFSUnFTbXhWODc5MHBPUVZPbXFVaExWNWtPT3Bzd3ROR2Q3bG1SZjd4RW9wMG1rY1FNem9yMjJUMXlzRmdZN0RsaHZoNk5hakxyRGRibjluOGllNVl2aGpkejd5ZDA5R2YxMkVKWU5BYjFSMXc2LXQxRjdhSjVDYkx6ZURmYTd0bTlhRzdwZGVZTUFYSmln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNSl9Ea2J3TVBvZ0FXcDVlZGVEaGxzeHVDNmhwTUtSYy01NzhKUzBWYi1iSTRfVWdZOS1CN2FFLVRsUER6cnNxRllZLXBucl9aZXEwQ1otSGQyT2REdjFJenAwMGswbW8yb3B5VG1kOFRhTlJSUjZYcTFma2RQeW5uYkNlRU8wMDJUX2E0OE50TVdLRUEyWmRNN0tsWUpaT3poZVE?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran conflict jolts UK mortgages: fixed rates jump, lenders pull deals - mpamag.com</t>
+          <t>Accredited British-made construction products worth £5.5bn to UK economy - pwemag.co.uk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:10:00 GMT</t>
+          <t>Wed, 01 Apr 2026 09:10:51 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOeWdNZlFZempuVXQtMm84eUhfSm5tRTlLTjFfa0w5ZXpQUGZoM1hhX0dVMDloMXEyOVZTNXdaUzg4UUVSZTFPWWdQQXc2Q3k0N2VPWFEtXzlfbEJXNmdycEJ2NTlOekZQQWpoS3VpYjlIOVVDVklSME5qenFBZVNrSGpDbDZFemJNZ3dyYnctOFpHS1FHX0ZxdDdfZXBoVi1aTjFBTXBQcHpvbDBHakNDbjFKOGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdjVqUVFMY2dIRExCVl9QcDY2X19yTVkzdktKUGduSFhHbnNtUC05X1lka3JNeXBOaHBSbnUzQ2RZcUFIOXpuVDhHaDQxRC1mRkhtRWQ5d2tlRjBHOTNndlFHb28wZFVNeThTNU4wTW5KRTltd3JpZU5KTGdaWnY0SGdLTV9QejVyc0duODNybDg2TmlXOFQ2bw?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran conflict: TUC calls for emergency taskforce to protect UK from economic shock - Wired-gov.net</t>
+          <t>UK requires closer EU partnerships due to volatile world, Starmer says - Reuters</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:34:55 GMT</t>
+          <t>Wed, 01 Apr 2026 09:50:16 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPOUZ6Qm1Wd19JTXNnR25temJURzdBWUJDTGl3emhlZ0J1N2tETS1HTFp3QmctdjRDYUxJOHVnWHNkUTUzMlNFdjZsNXpYTTVoQWNyWUJ4aEUxa1JOdEVNRmR4VDc5cDJpZHA5OHpmNzhzNm9leVphWDFyNUctUzNsUTVpRkc2NTVsdlFuOEs2SFdYWnZ2SWNEaWcwcV9wRWxWOHBYSUxVWjNVUVh0cXhud1A5NlNNdG54VUI0b3hEN1VrWnZHWGNLLUJlTDFVNGgyd2tMREtVYXlDOW80VGRZa0NR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQY1NvTkdHTjhWWkNGczJQdWhfZ3ZYTnV3QVRla18xSmxHRWU4M0ZvSkQwUmhveGl6ZERLZFRpbDh5N1dGMzJmVGUzdXEyN0wzM0pxcjl3Wks5TE9mMEJ6MUN5eFloNFlVNWgxX3paUV9CUXFxcDdqUUYzeDJ5OTRhME9kSmh3QVg0TC1hUFNVbFZmaVRrSXltZ1Q4UXN5TDExenRlb2pjeGJJeFBqUm5weQ?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UK's Starmer, Saudi crown prince discussed ongoing Middle East conflict, Downing Street says - Reuters</t>
+          <t>The costs and failures of air defence in the Iran conflict and what they mean for Europe - Bruegel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 21:52:24 GMT</t>
+          <t>Mon, 30 Mar 2026 14:31:29 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNNkRCeVVXUV9tMlk0Sm0zWTJ4eUlKcWZQUlhwdm83cjN4X3lTNDhmTDBCRDEwNmtKOFRXT1pfX01YbC1NWTNJOFdabFBGaDMzbkNQRTR1MzZzbVBOSnFkVExPUWZIUlIxM0hsSzVUSXdsRlNIdldzUXQ5UmF4c2tqR3liSDNMOFltX0xnbDVnT2o1WERYYmJDdlE1ay1RR2lKVEkxQ19RTnRLRk5uWHhsd205VHd6QnROeGxDdF9sVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQR211dVNDS21aVlRhVmxIeW54RWZTQU9tbnNXU2MySmVEZ3pLWWdDTmNJNTdqQlpBNWpCWWd1ZEpHYXFsWkVYM0pUR1lfUFpOUUxjS0h2Yi1DZGF6UHRxMXdhbnFTTGY1bE8xRnBUQ1NheTk3a1RzbEx1ZU1tNl9LTUNmOHVkNllZNWFRcFU3T29KWWpCWkI4N3pOZGZ0aEdYeWdoM3FHcUhvLWc?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UK energy supplier flags growing debt burden as Iran conflict drives up prices - Financial Times</t>
+          <t>Economy slows as supply chain disruption and energy costs hit - Metro Global</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 05:00:28 GMT</t>
+          <t>Tue, 31 Mar 2026 19:31:27 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQYVJSOU9DSmdSaHJBWFRScC16c2k2Y2huNkFRdjRPdVIwdVQtSlVtRkFBVFFMUVR4TmtxWnZvUkQxdWNvTEZHMGdkQmJicjVzZVlSdGE2dFBJWUQ5SWJ1R3Znci1RVlByb1V0cm9pMTdKWl81dnVSaGVKRGRjekgtaUFtcHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQMnFwaXFFUE5CbGNWRV9uRDZNdFpxZi1USzdza3hVTkJRZFBSSy1xYmZ0ZkxuZ3FpbkpCUHdCRE9wb3RnaGxlRWFYbFU1eFRiRGNVdTJILUNBVkV4V2E0MTdyVng2bC1UV2kzX2Q2WFctbE1zSVNhMExjWFJlN0ZJckxleU1DOVdOMGlER0dRNjVuSXIzRHZFdjBB?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trump’s sanctions against a UN human rights expert show free speech is dying | - The Guardian</t>
+          <t>IMF warns Middle East conflict will lead to higher prices and slower global growth - The Guardian</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 15:57:00 GMT</t>
+          <t>Mon, 30 Mar 2026 20:28:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPSTBSNHhhb3piU1QtZFBBVmhlM25Ya2pCOVRyQUlxOG9rSFJUR3lmYXlhRHREUmRkYU82WE45S25GaGN5cGJicTZvVlBRSU5rcW5tSzh3WEdWRVFuT01kaWJxVVIydV9aV2pHZFZWZ2N3NjRvYWVWLWdMcWt5Z3RMRkZYZEhwaWNGSHFJU0FRMUM5RVdFRlhYaWJ5TTk3Q0xOWjNKcHFNNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPYm1qMFV5R044TmJCRVdoNERqLUZUa0xxRFJYUFRZSkl5YUNhdnF5ZVQxSEJIa0lRbklnNVlWcXVGR0FGV291NklTZUpoV2prOFQwN1VMeExydTUyZGh2UWZLcl82YjFYT3FHSUZJM3hXRHFmZGcwX3IxODYwNFpDYnZndzhCbE1MQm94cTdPOGN4S3VKVEFMMXlHY2l3ek56NGc4Z0NBQmpQWnBuQi11TTRyeUIyWm4xVVo1d2ZseGxOSEdrUEx3?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philippines declares national energy emergency in wake of Iran conflict - BBC</t>
+          <t>Digital entertainment grew 7x faster than the UK economy - London Business News</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 13:02:54 GMT</t>
+          <t>Wed, 01 Apr 2026 10:10:34 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE11RjAwNTZLQTE3MjFWeTJ3ajdlUFliZlNqaENFUlRub1NDT2FZdzl1VjEyV3hkS0MwczZFc3FZTjNDM05sNGJveGRXV3NsQWJ4RWFhRkdpb21Wc3NM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQUTJoNE10cmxDdzlCaFZua281NWk5aWJHSWFUNkFqc1hTRzZOYk93ZjNRbUltZ0s3R01TY3dLd0NTMldRMWFKWnhLampNRkxMM2JNTEJxa2xZOERMaWdnaUxxV2M5SlVNU0p0YmhVMXpPRGVlOGtmYjZDRmhRWVp1clRnblp0N2xjdlQ5ZFBjaVFnc2M?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reeves plans energy bill help for those 'who need it most' - BBC</t>
+          <t>'Geopolitical realities' | Unilever freezes global hiring amid Middle East conflict pressures - HR Grapevine</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:52:24 GMT</t>
+          <t>Wed, 01 Apr 2026 07:04:58 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE42S3FVTnhnUEVSTEFuaGpJaFRkc19ER0xNeGJiV2dTd1V1S2Ffdk9RNkplempHaUNpa3owQTRNSHg3d3hqYVdEM0Vkb3FCanJoQ09jTGFfQWpHTmI3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNMXlZZEppMFQtQ3FiZDh1S3BZSW1iZlJ1bmZPZzB3N1pXcEhiQi1zY1NheENoaDNiYWMtSHlpZU4wa3RyYlp2MUlBTlRtVHI1X3NEelRNa3dVam1DRTJEdmU5SU9YMldMUm5ndFJWQUZfOTZwdlpEUmlabG4wRUNEbXdSUHJaVDVrTGppZDZjd3NUY19ZaDJsQUtwSTl2ZG5tUTZwUy1oVC1DSHZ4c093SW9BNGZmR0dHX0FyOW9B?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Middle East conflict risks pushing UK food inflation above 8%, warns IGD - Retail Gazette</t>
+          <t>‘Get your own oil’: Trump launches tirade against Europe for not joining Iran war - The Guardian</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:56:05 GMT</t>
+          <t>Tue, 31 Mar 2026 17:06:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQMm9tN1M0MERYdzdmU3gzOFREcThRVjFraGVGc2lFRkF6alVnNkVYeU1SdUN4c0Q0bGxzNGRWOWZrRzFRcmZLTnRJNHFVRncyMktXRU5uSDNhRzdtNmhWZ3JkRkJPR1J4c0hkeHJBSW40N3MyYzZ3YkpFQ1BiaDhycGU3bHJ2d1RuNnhOdEV2bnNLY0h1QWdVRDR3bVZrdHIzN3UyVGNkdGV5SjliOXMtZFFEcUNzbG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPMFFTZjV5RURNSWs1eW1ZOEtzWkdFU1hLSzJYeG5lXzNwRlEtcFR4VmsxdDQyVmtINE4yTjAtRndkR0s3RWd4SVJxb0tMam9QelR3RFhURk1TanhWNnpkakwxdzhfcWRybUQ2REhXUDE3WGpyM2hheWZTcndvTjczcV9zTDVaZjQ0MHg2M0FISmxJY1FvR25sTkZtT1g4ZWJJaTdkY1pXT01zTnA0MGFMR08wSEhHdw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Keir Starmer’s policy on the Iran war is a recipe for catastrophe - Al Jazeera</t>
+          <t>Free webinar on disinformation and AI marks International Fact-Checking Day - LatAm Journalism Review</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:28:47 GMT</t>
+          <t>Tue, 31 Mar 2026 20:23:08 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQWGx2REwtcnpQWjlsWnF0ZkdNRkp6Mnlxa0pEbHJ2MFFraDhhUVVDMll2T1B4clZQYmttU0hNN2ROYTdkcTE3MG8wdEdudTc3dHIzNEcta0NqR1ExMGlUNUsxZ3Y3SzRlOGdDUnIxenFqcW1FT21oMEhiVjJ0aGFUVVVIQnkyUDRtX0t5YTNBSVQ3Y01MODVTSUNGVzM2eUdqREQxX3E4cjdMVXNqcUHSAbMBQVVfeXFMTThrV21mZ01hMjdraDFFZ2RwTTEwQkh0YWhGaEpLQ2tnWXl3NnZmRFdCQzU3cThyaDRBdFBiamx6LVlWTFpXTWhrWUFzbGYyLWZiZUhraVpzaGhwQTdmbXlhOURaWFdLa25PWDZMazBaNWs3RkNvOEV6VlF3NzZUeVNibmp4YXl5V01KQjByUVYtUUFVVkc4dHZuSTd2VVcwdXpub3kyNlZacjlxQ1VsSDU5THM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOZmNWQzBISlhSLVEzOG1wU21SMktHbllnMnJGWS10MWVzV2F3OEFXYlJVclZGZkZ1X3FabWJnX0VlYUFkMV9LbmxpUTlGMk5Ka1BKSk9DbnFnY0wtT1NNSmxhVkhLSHU5U2JLb05NUnM5TVNtME5iYTlHSUh0WHdPb05laHVyY3dXaGhudHNOb3ZsQ0g3Skdpay04S2NiSE1XdXJmczNZVEVTTVQwUGVPRnJWVFBuQmttWm5YLWhPbVg?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PM warns against 'false comfort' of thinking Iran war will end quickly - BBC</t>
+          <t>UK house prices increase in March but Middle East conflict clouds outlook, says Nationwide - Housing Today</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 19:10:55 GMT</t>
+          <t>Tue, 31 Mar 2026 10:57:37 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9RZ3EzbENWYVF2NFdMOHgtOHhjZGtXSFozTTd1MnlJUkFYMThMdWx1Tk84RHVNaElocFV2VDVQbGVXTTRiVDRTUlZsbkdERDB4Y0JpeWN0UXY5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSFExWDJGRlRzUmVlTjlHVnpkTFdhR3BsTTRtMzd1YVdNNFRQcURMNXFFRDRaMTJoLVExRXBqNUtGTUhsX1pSTXRhYy1keDZ6RWhMVWZCX05rZlYyRkJkWUlsYVZDUUlTTXpmS05LRU5tOEstenlWZnhjeHlTSm0zdHBPZHBQMHRnVmFrRTdZS3BQblRxNzNJTUlSSDBXYmQwd3pIN2pSZ0xrblIxeG1YaXNiaWtINmlWYnR2cEdQOG1zWjRnOUNXWFNGYnZPYWNyQ21oY0duOU0?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gulf study interest falls 30% as conflict reshapes student demand - The PIE News</t>
+          <t>Thunes Empowers the Global Economy with Instant Cross-Border Payouts for Gig and Remote Workers - Thunes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 13:53:18 GMT</t>
+          <t>Mon, 30 Mar 2026 16:04:45 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQYjVtUFF2emZkRUQtc0pBTktNejNnckkxRmk0Y1VvUVJQSUhmTVFVY2o3dm51d3hqNmZJOGZKUEo5aDMxRWZaNmJNSXdNX1pOeHRhc05helA0WjFxQ0k5NHY2aTdwcjYwZGZFRW1OQjZvVHZmbWlyOHY2NTYxT1JGYi1razZYcjZpYTg0TjZaTFVhZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNSFRHX3hsUDdpZUtMSGxRTGVuODFrNDJPZVIwYWV6bjZLMDFITld3R3NFVXVUT1lkTGhrckYwWGtBR3ZvR0EyeW8xMWpKaEVZTEYzRlJyYjl0c2xKSEpkNTZUNHlsa1pNQTluMktvcjZRdURnckZSNWRpNFhEQkFzTXMxQUpBb0FSS3Q4Q3hRc2RIZVlrcEFtVHkxMkhHM2tXbVVBUjlITkxrR1Z2Tlp4OVFSS3NSVXY4OVBPWjc3SXpJQQ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tuesday briefing: With the horror of conflict throughout the globe, how likely is world war three? - The Guardian</t>
+          <t>Iran considering RAF Fairford among 'legitimate targets' amid conflict - Yahoo News UK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 06:32:00 GMT</t>
+          <t>Wed, 01 Apr 2026 08:09:12 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOclE5SHJqc2dGZ1ZUYVpvUjc5QlRsT1lkcExBUUxwTXg0S0h3SF84ZzF4ZTZvaVJtcHktOHo3QVE4b21MajlLWVBJODhTOW1NVzJ1dVVzU3BaWnp5bWl6bUdySzNhX2ZQS1NVVG5QSzJVbDdkejVJTE1YT09ZanI0LVNWaTdVeU9vczFOTDl3RVdzV3pGM3NGRlMzYm1tMC1seUhWV3JGbXY0YjI3bmszTU4ydnRxVHFvLXhOVDNubDdDbUlNWVhGQ3lRNzVPMDV1enpheTFCOEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOc0V1UmwwWVpUcjc4TUtsdDg0eG5wYXE2SWExclVhNmd0SzZFMEZ1NVJoVFNVbUZSZFFMNVFFN2VRUF9QRWFCZG01S0QyMFR0Q0ZkLVNGa1FRTjROWDFxc3paR3BhX1V5TTJnS3N1MzJVbElybjNGR2FTbVo3MFZzMHpn?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark's PM Mette Frederiksen, tenacious and tough on migration - Yahoo News UK</t>
+          <t>Australian government must fight climate disinformation, says Senate committee - Global Government Forum</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 01:18:00 GMT</t>
+          <t>Tue, 31 Mar 2026 11:47:17 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPV05XWXc5VUlDdUVEZF9TeVNNaTYxZDZ0ZDV6b012bmRnb0VNam5BSEFvTl9tLVlNWEtCbFpuRUVXYWtqQVd0d3Zpci01NjhvZml2Q1I1X2VMRzZWcW5IZ21kRVozTDEtRjk3TGRmNjI4alhYNUtnU2FlSEVsaFRjVTdWa2NDU3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQdldWSXgtcmNBNnh3S1F4VzVwRkNXc0Jxam5MUkZEeUtXWE13VnQ2V0MwMWJpVXBJZGNwMy1iSGxYS3BKa3otVFRzNXRkMUN5M2pQN0s0aThZUFZpY3ZwVXBxQnY5X3R4UzNtYkc3My1yMFFlLTRpd2VKcUZkUk8xYlFjVEVFWEhBUWp5QmlYQ0Q5djNmdkVwY1dZSzRibkNDSDJwQzMzYmxhQ0hJeDlPd3RJZ0pDYjQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cari’s Legal Exchange — Iran Sanctions: Implications For Global Trade (Video) - Mondaq</t>
+          <t>Oil rises and Asia shares slide as Iran war enters fifth week - BBC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:11:20 GMT</t>
+          <t>Mon, 30 Mar 2026 15:35:40 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNa21ZcnpFcFVtLTQ1VUE5NUpuR29WaUhlU3pQQjNZNzUyZG5iQ3I5aWItRmdRWlpzMnJySGxPdWlYWWVXMzBjVF9xTzUtMWhrREtBRmhoUmRWa293Ynd2OEhpeTg3MTF1RTk0UmtGcmw5cHd4bUNkbDdVSDd2TjlEZGpUZG9RS3BITTNEcHl3U2VnbTh5c0xuSF9ZUkNKMXFkeGptR3pzZEJnYWdFNV9yV200Qkp4VlZERFl4VE9sOGcyV2pldEdWY0FUSHVBNDJzZG90eHdlMHVPelhwUUJBZmZWNkJDbTVMZlBCeER3OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5WT09BMm11ajVYN3ppZUs5NmhMM2cxaXl6NXhQWnlKRFFvNXpLeFhPdHY4bkxEUlNudlRTdC1USUFxU0JHb1ZvdVpvNm0yX0diLUFYUXZRVVN2UQ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Asia’s economy projected to grow 4.5% in 2026, with global GDP share nearing 50% - Human Resources Online</t>
+          <t>UK, France extend Channel migration deal in last-minute agreement - EasternEye</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:40:14 GMT</t>
+          <t>Wed, 01 Apr 2026 09:33:45 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNUJyVnhjQVZ0Y2Q1SVVvNndOMk9sV2NxOUlDM3lBOFVKMW41QVRzZGtTekRaSU9hTjBSalJPSlZTcWYtWXZVR1FLcEpERlR0TEZQS2hmRUpmR3pUTEE1b1FZQUZ6U2NCOTA4SnBsQ0c0bWdPLXlRVUNhZ3I4d1BNNkdoaWU3R1BJRm1oQVE4U2FFNGxMRGxLMDUtc3BMNnZPOFFPc1lfS1c3YTVxbUhBdmxCQks?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOV1lwdWgzODMyaG8wY1RoQjhnb1MwVWstbUY2cC1BRTdKT3ZpSkJvTFozanBodW5neDQ2eTdCNll2cE1kLThFMTVaeEtIaGFKNk50OEIwZnY3R01JS24zZzZjb3dRaFRLTWw4LXRSVVItZWs1QzNBcWtESkV3LXBMcndiZnR5cGVDUkg0dmJvSjdfR0k4YVo0?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Global Terrorism Index 2026: Morocco, a sanctuary of stability in the face of transnational challenges - Atalayar</t>
+          <t>Iran Conflict Sends India-Europe Airfares Soaring, Corporate Travellers Pivot to Short-Haul Asia - VisaHQ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:47:03 GMT</t>
+          <t>Tue, 31 Mar 2026 20:07:04 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxPQURIZU1YQ05GWm1xTE1wNjlBM3BfRHFlamZoZEZZcHVFT3FGeFZ4UDl0dnlCbkExVDEzMktHbm44LXBpd3FGU1MxaTNCNExoMVpvUDYta0VldnB0SFBUVVAwSXB4Q204WTQ0NFRaOFg1bHMza1B6WU01RFRXT3l4OVlaaWs2elpkTTZocmVneExiM1BkYkk0Rl9zc3VhWXFzdzZva2F2Q2YwNy1pSHpxQ2FDbDVqTG5xOWFMOXlCUHlfWnpSZEo3WXdaRU8ycjBZeXFiUklfWERMUzdFekp3ZXEzQ01DbGNtQjkwRno0WWJOWmhqZ1F5UFpuMUQ3LUZucFVFZtIBigJBVV95cUxOMnlMOU00R1FXWHdjc2VXWEtyanU2bkw1OXExRGtBcUpSR2xOMVkzZnVWLXQyTjF6dEwyaVJNZF9MeVVBZVNQaVRsTmU1NTNEYXl1elV3UExDdURPcmFad1RpbTR4MHQ2cF8yZkdlSFZvbzN4bGVqdnhKR3dpOWFLNVJvWW1xNGd3ZHFHczlkVEJJNjJyY3dJay15XzFJTC0zcHZZcmhsVVNrYS1oQ3NPemZwMnM2b0N2T3Fscm0yQkpoMmp4QzI5aDd0QV9nYXdMXzZhSkJNaWc5TU1iZTJ1NlBGWkFvSndxamFHV0p0ZUx2VHFRV05IVnB1M2hXdUxDV25GeG12Q3VEdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQaFgyWkxSQzlNYi1jV0hUcnlUcW0xWHFFdXZSYmdWNGpFTjBjRlN1RmtQTFdCd1pQc0tCNXNQcnBCamtvZjBwV2tlMEZlXy1YZG9KT0ZMT1lUMVI1cW9hQWhDdHJ0emhXNWhEYzNnWERCYTZzMnRoaVBQZUk5cks0ajJEVm5uX3NIeVNtUkxyNEZTWUxxRVlDemhwQ2pHQ0NRMk84RFcyakNvdWxFbjhhclJSczVBTVJ0RkFzV2pFYU95dzhkSlVoVXpMNDlLc2RWNlY0UA?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kuwait says Strait of Hormuz closure is beyond catastrophic, will trigger domino effect across global economy - CNBC</t>
+          <t>UK food waste legislation comes into force - gasworld</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 18:18:54 GMT</t>
+          <t>Tue, 31 Mar 2026 11:13:02 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOc0o0a2UwV0t0Wm1vc25hXzBkd0ZuaUJaaWNuTDBmcFRMak1Ga3hLYmtLb2pCNHpTWWlyUmR4cndUWjA3SHVUUVFfZHdLZzluRVI4RTRoMlhXY2RuM1l2Y21VdDV2RkNmZnRFdU9aZUtTa2tBaTRQWjJXelFmSVQ0bNIBhgFBVV95cUxNMHk0eXIxQjVaaHRNZE5ZSmJPSDBqT1l3YnZKdzNxdXo3ZS10Q0l0d0hQVDdqU0FEeTBMOEZIQ09HVHhaTlo2SFhXNl9KQTVRVjhpZ29Wenlhd2s1MmxHY21aN01GLUtHMlRsV0FfaElKUHQtY3pZcXloSjFhLW5jalJxQm55Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPMTduQ0ZFU205NzlfS04zLW5EOURhcmdZdE1JS1owcTBlSmROYko2LVdkVGNtRHhvRzlIb1F6bW9EU3NHa0VDbnRkSzFudlVSeFdOdkF0VUFNZWJEZ0lWMWs5X20xNUVzczNrMllMQUtLZ3Q4VmtDZXBNQ2xzaGhOY0pEbFhZNUlSbG50aHlIYThMdFI0?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China's growth buoying regional, global economy - China Daily</t>
+          <t>UK deploys air defences across Gulf as conflict intensifies - UK Defence Journal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:21:00 GMT</t>
+          <t>Tue, 31 Mar 2026 18:20:55 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9naUg3ckRzYzF3cGZ5MHN2VDlHRnNLakZ6THhVQjFvSXhJQnhiZ0RnSTgwQVpGYkszUzF6ZnRGTlQteFpDeWY2bl9KWkh5YmNvb3NLdm4xVTV0WEVxZ3EwempMMGtzelpDckstTzBpYkNxY2RHNXI0NGFxZFlfUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQVUx3T3lNTUNodGNhUU9lRVN4TDE1cnFTV1F1cm5VNS1iZlNLNnZ0Z1hlbmpzTzF5OHJ4TzNYYl9zTTh1aXdLdzd4Qnowd0dQM0cxUnM1SDYzVkhzRWFpM2VOaUVOMlFwcVZHQl9MSkVzbWtfaE5aSGk0TXU3MVhXVDV4UmlUNndpTEZXbktCZkZpWEFZdEVB?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nigeria signs digital deal with Finland as Europe backs Africa’s tech talent push with €23million funding - Business Insider Africa</t>
+          <t>UK farmers hit by soaring fuel prices amid Middle East conflict - Farmers Guide</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:06:12 GMT</t>
+          <t>Tue, 31 Mar 2026 10:11:48 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQMGhyM0hTVDlQNGxSZHQ3ZFR4LUZBRnZPaFpVczFJa2psSkRlMS1WTGhja1VhVWNOVTRNM2pTOXZ4dEVrbFc1UGU5SWprdDNSSjlrXzI5Y1ZtYTBnVENPWndoc2Q0ZlJFQVJCdkNiTzI0cmZzRW5QMzIxTjhrV0gtZG9jLVhON082NzZkeTRXYkMyMWNTTE5WZTloem91d0pwekE0aENqLVpiQ0c1TW04aGZ2NThJQkhuNGNwMnpmcVhBQXB5QVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUEdZblphaC1zdGdBTjZ6ZUI4bF80XzZLdk1rNHRBTWtuWU0ta3BmOFBzNWNyZHEydm9kMlBlaDNHVUdOdVJLVUtlc0k1dVNYandBR0FZMlBDZm9lNVVqcFhXaGRZbGJxa0dCRXhKakxCMTBTblBMMlluaU9jT2RnTmxHYVlUcml1NjZhTTJ5MWFZYVhxZlA5eC1pdjFCdGZQNUdkYXpwdEMzUWllamVCUnZHd0h6bmV3VEE?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>International Energy Agency head says global economy faces ‘major, major threat’ from Iran war - AP News</t>
+          <t>Hungary’s Szijjártó admits he liaised with Moscow as EU discussed Russia sanctions - politico.eu</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 08:02:00 GMT</t>
+          <t>Tue, 31 Mar 2026 11:20:00 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNYWpXa0N2MzNVRGRWcV9kZFdEUHpqUmpjRGhSN0lub0ZLdndYLUpsTW8wWFZ4WFhMLVYyV3FsdlpnaFNLdW1ZTWhqVll3aXI1cVRCVnREU0lkMTktcmY5N1Z5X0EtOHZLUkVUNkhycXA5NWZRVzJyZ3ZjZld4V0NfSFdMNzRtWldkQzktdzFtaWxJclJqNW1oa2RfOGVFLUxLRWd1cHZoQ0w1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQWDk4ZHVPbXMzLVNnb1lxUGNxUURQc05nNUE3ZkxOTUx1VkktZWc0a0hxWmRnMlZaLTh5dFZCMVdra3QwbnpteHRyWDFPNGt3akZ6cjNQVTJTTUxKM1BLbEstVi1BakVFWThzSmxoMTc2V1dTbXduV2pSLUFhUnhLdFhzUW40a2lrcEhCTzZDNlFXcUpQZU13bzJjdmtTbWExUElNUnVOb2FxcVNmUFlQdlgwS2Vld00?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ACCC monitoring impact on domestic aviation amid Middle East conflict - ACCC</t>
+          <t>Brit holiday destination prepares for Iranian attack as Middle East conflict threatens Europe - Daily Record</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 22:31:09 GMT</t>
+          <t>Wed, 01 Apr 2026 06:47:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNVlZWVGFuc3A2SW01cUNfekJ1MzR3MVFqa05SVkVHRUIyUk1Dczh1THhNZl9PNVBPajdXc3BFOUg5aGpCbFlMQW84azlqQUlmMkFsRUJYVWdrdjViQ05DblFWY0d5NDNJODAySGIzT0lOOXgzbmxsWTB3NFJndnctRVRzZTlzcmRzWFVBbmgyQWVNQW0xUUdiNE02aVhUaFVoX254akhSVFN0RXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQTjc0RnJqUHRzdVF6Z0xpLTU2OVpWdUc4ME5MQ1FvVEFieUl4OFg2YTMzdi03cXd3MWdiLU16Q1VYSkxqZTRqeDZKb1dNVXZncFhXbEQ2c2s5NnJMaWxNUHVIWDNaRVdkUUZJUzR6YnRMTUtVbkxfcXRqaHdaeS1WOFhqdkNCQmdERjlreXNld3JmZW9Hc0hMcWxabE1mQdIBowFBVV95cUxPNzN5anhReFpLeGxOZjk4bl9OWE93dGNKTTVDeFVwYnhkQ29JajZwcWs3OXVFWEVCMjJrejBDMTYxRTNvRW5uV3poV1VPY2pSOTRtTmdnTUVZeEJuTFJvendmYTkwcXkyWkRlbThsTWZaYTNQMU41MEhIWFhJVC1XT3VhSGZRT2JqXzRKRjhVd0x3N3J5Qlk3RElpT1RSQ2UxeWhF?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nepali traders make global shocks from Iran conflict a pretext to jack up prices - The Kathmandu Post</t>
+          <t>UK PM Starmer to update on cost of living amid Iran conflict impact - London South East</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 01:18:50 GMT</t>
+          <t>Wed, 01 Apr 2026 05:43:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOS3g0ejA5UFM5VjVCVVhHRm0zNTBXakZKSjhJalhrZEwxVFVzbjQ5QThHVjJyaU1UeXAzQUpkdGVvUkp4Y21nS2FBNkJJb0phQlVUeDhZenhuWFRpbXNra0FHbWtvSGdUQVZRYXJRLTFoc29VcTVuSThiN2FYazExLUhXUW9zTmZQSjhWVmY5X3IzVGVPTm1adWp2Z3dlVHVhWFAwajBDU05oQXdqSjRKN2R2dDhoS1RSY3ZXUFo3UEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOZ3hqYkdTRndkUFFwRW40bUNnR3lYUkhZdFNiT0pqd3ZJTk9ROWdVZG1nXzl5TXdvLS1TTmJzRmFWOWV5bUladzNxSDNNYTlBT2dNRnk0V25IbGRkVXgwUkhUUVQzbUlZNUxyTGttV19hTlZ0TUU4NFRrU0FwQndlWEt2QzJKaFpIeU1NaGg4MW44ZnhWQVNGajRUdU9TOWxWZnFnWjFWd1Z1S3ZINzBXUm1OU3BxZw?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1411,27 +1411,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mar 25, 2026: DHL Supply Chain and iglo extend their exclusive logistics partnership - DHL Group</t>
+          <t>Trump's signal to end the conflict revives global optimism - China Daily</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:00:00 GMT</t>
+          <t>Wed, 01 Apr 2026 09:30:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOeU81VE8wZ1hwVWQ5ZWxMeU4zMTVuSkxmREdEUjJGNzRjNWdJUVRQUjQ4VUU5UVZnRVowOHpNX1VGemMwY01OdU9aeVFsRlhyaVA2ZnRLOUV2NEVfRXc0UHNGT3J0cXc4bERLYXdESXloZXhpT1V1R1lNSWRIckRmb294NVJLZHZYUWxQRnB3eTZBbU9KT0hnbDFvd19vTXVRSzJhMEVjMHBoZkJPS3NGLXAzVGRGQWZia2FVcHZGNFU5ZzJUNUFoMUJKYThkMFBndUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1EM0FlU3F6Nm5qOElJRDJ3cENlN1lXbTdHOXRRWll3MFZiSGNNbGtPSnlmQmdWZU9jdnpibFI5YTE5MlBnUlU1blRKdnp3eFZLRjk5M3ZzS0hjR29qVTBNeUFuV2ppQVBITVVrUVNjc1VSeDdvcVRhMTlOMTN1UQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1441,27 +1441,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Doncaster Rovers 1-0 Port Vale | League One highlights - Sky Sports</t>
+          <t>What a geopolitical conflict means for global economy - Xinhua</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 22:16:25 GMT</t>
+          <t>Tue, 31 Mar 2026 12:42:32 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxON1ZXaUQwajF6Q3IybWoycFFaajN2WWNLRU5TMktKVUhWbnlYQUZoZklyekJad1RPcjVQVjJ6SWVrR3cyVFVGaGJIM2RpNUtuREJ3QjVyTVJmbG1rSUlkaVh3b0pVV1ZKTzRIaGRWUHZFRUxpZVlyZmVqLWIxVXc4T0t6MVpCd1FUUHJ2NWpxR1hPRzlETFBmdVNVR2ozQkd6cXJFYVJnN1pFYm9H?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFB4MzhXbVdFaW5vRnFTM3plU3lHd2dzNTFZVmlUdUEzOEROQjltT3NieWZOSHVmZ3NSaFRXeVdLWVBVS0F4TmZSWWxLZkpZOU1ielhFZGR2cFRZMkcxQ1I1TUZ4TkE5aFA4UEdTZ2NFWEpUaFJxdnFuSHlnRkY?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1471,27 +1471,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Contract signed for freight flex vessels - Shippax</t>
+          <t>Syria will stay out of Iran conflict unless it faces aggression, president says - Reuters</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 05:55:41 GMT</t>
+          <t>Tue, 31 Mar 2026 20:24:34 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNQVdqNy1ZY0JuYlViQUtDT2ZDT2lTb3d5NW5hV3NLVDNFVlR0Qmp5QWhpdjZzTlJMY1I0MTQ2LUpUTTR0LXE4aXdzaTlaUHJBUmotNS1CYVRKZzRxa0ZibzliV1ZWbVNJb2JWcUNWbHprbmNQMTRtRXpjUkNtVWxqZkxVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPd0FrY0JmR3NGWTVhMXI1a1BVOUxqd2UtbzFTdjgwclJoRmx1aS14X3ZTRTZ5ckV6d1l2ODZEVWhOclQ0alhFNzRhWkQ4Um1fOENjWFRoSl81clIzNmMtQ1ZUVDBZODdUNlhVbmZua2g3aHpRc0dBcWYzQXFnS0lKTzV0a3JnTVdMR0kydjBGZzh1Q3NGN3FudVpxQWNGWXRhVnppU010OFI1Qi1YZXRkYm56U0VZVkJaTXpuU1RYUklJUQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1501,27 +1501,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Interactive content - The role of tech in Awaab’s Law compliance - Inside Housing</t>
+          <t>Germany’s €8B Climate Push: Can Europe’s Largest Economy Cut Fossil Fuel Use Fast Enough - CarbonCredits.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 07:07:39 GMT</t>
+          <t>Tue, 31 Mar 2026 16:20:57 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSUdLWG93LUFwRGp4cnBfTXRpZVhyaENnc24xSjlUNmNNZVhtdWM4ZjY3aXNCa2ZwV2NxUDZvVlYzc2k5N1JaUXU1cUpYbkpXVE5JOU1FeGpaODNYWDhJY2dvMGpmNlZpQWx2NWRVZnZUR1RUcUttLUVoamk0a0ZER3M2VDJwb25hN0FNN21JTnV6TzlsVnJtUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQWGVOc2VFb1dNdmhoZGxVYU1BYjlwSEJVckUxNDBhYnJXaU5OQjdvNGpXN2xRRFhITC1KSHJtclZWUmFGNGVzVjlraFlLczBycExSU0dZOUdxTkVvSklxWnZCeE02cTdkMDFDOGw5NC14QmtDZ1pnU1NNUlF3cjYxQzdUekFRVXJUZllJZzJWNUV6bHhMSzU3MWZ1ZjdyeWRIUzlueHV1Q2l6aEIxeFM2Q0tB?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1531,27 +1531,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FIREPOWER: Supply chain issues ‘biggest hindrance’ for defence industry scale-up - Euractiv</t>
+          <t>Global Ban on Digital Duties Expires After Stalled Talks at W.T.O. Meeting - The New York Times</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:47:40 GMT</t>
+          <t>Tue, 31 Mar 2026 15:19:47 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxORTl6cUhSelFrTjM4MHl1SlpYdHlTWHYtSWU5MnFxQ2V6a1Rab0dNRzVtWkpSMmJadDl0cHI2dDFNY0haZC1QRndldXRNaVZMVTk1cUJBQk9VVWlPUWJfb1pQZHJNaTcybzZlcFhYcUlZbGZhQmZ4Y1ctNGJ4MDZsdXlnbTI1Xzh4bWRpWTJ1WlYtdFFBNnpjM0xGZWUtLWtzR0l2azVnMFY2bDUy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQUkFLejFCRmRZSUhGRmFGb09laDFWU19kWDBjakdQQm53S0Y3czhmWjhkdWVqTjhXOXhlQkd4VkhEYWNIc1kyYm9zcURrZHQzR3hkYjliUncxWE0wUDVhWXUxZWRJZ01hMzRoNDVXNFBGMFhVZkpyZWlieTNfbHVwMnl3YU5Ba2xraTJzNWotZ0xzbWtfSnNzSg?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR terrorism OR disinformation OR "government policy" OR legislation OR sanctions) AND (Europe OR UK OR "United States" OR global OR international)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Subsidising the supply chain: How China’s industrial policy shapes export competitiveness - CEPR</t>
+          <t>‘Dangerous escalation’: World reacts to Israel passing death penalty law - Al Jazeera</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 00:05:49 GMT</t>
+          <t>Mon, 30 Mar 2026 21:29:48 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNTkVZVkJsUzZBUlpDMHdRaFUyY0p6M0JIWFZieDlrVVN2OGIwWFZ4QlFZRXNiSGZEbDh5WE5TeXlMa19lbXktTU1vX0YxLWpaMkZQZUp2MmNnZkVXYTRHNjBlM2YxS2ttcThWeTMyVzNKV1BZSUxSc0thVU0zQlhBb1pmVWR2X3dZUVRHLVgtYjFCSDBZUjdQLXlWNk1xZ1VkUVhmdlpoeEh1dE10Z1paV0dGVjc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOaHBTS253VlhpRWkzSjZwaE81YjFJY000UW85T2RUclpGdnpXb0JiVWdZR2p5SkJCMlMxQUx6NG11WEpaTHltb29kWUtROE9RSkJHWnktelYwNEtWUF9xbTVfSkdPNG9ldmtDTWhTMHI4NXV3VWVRU0JDaFBZakdLSVg2cnJZSC1HSUVJSTlyemZEcUZMQUZ5TkhVZHVidExxRWoyOHVodEUyTGZqMjNR0gG0AUFVX3lxTFBXeUhCNndVVU52V2k2TmZlSm5sTXAtUFJuZVFtbUNBWDFUalpqcTdnOFRHeWZOeWg2S1hVcS1oT0liZG9zdTJZb080TDAzNmpTRUYySVBIMUprMkdxM01xcU43b3I2N3BXazA5aXF5SDNKMWVmWjQyS09BQ2tpNTVWTlgzRDNUUkVvZ0dkd3dEN3AwdllHYUZ0bXVhUDk4RzRTRl8wUFhFUFZaeXRyQWJrRDVkcg?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Companies House disciplines over 100 staff for compliance breaches - Introducer Today</t>
+          <t>Future RAN: Diversifying the 5G Supply Chain Competition - GOV.UK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 00:07:10 GMT</t>
+          <t>Wed, 01 Apr 2026 07:30:04 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOdW5BcVBncnVzUDZYRGw3ZGNTOFpDQlVhVVJYTnZ6a181TEFwUFg2elRleHNldzBvQzhTNUVDYXhkRkE5UzlYUEt6bFZTV2VyNDJDTjJNRTdnUkJFVmg4XzJBY2JnREJBcGtLR214QzVWT1o2ZTFYRTlSOW1EbkJQV1ljZmFVclNsLTVxSF9aNTRUeHRDQmUyb25IamxXYmw4blluTVFkYVlUZDZxNy1mYUxZd1AtOXFUb2lpTHVXdDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxONnlFeTBXOEZvV1NnaEVxNk9saWswMHdGeEJ4Ny1iVFhyMWpnZlN4OUYyeXlkV0w5WGFKclF2Z0FFX2dETXpQTjlDQlRKdFpZTVVNSU54ZXJYbU0ySmRHQ3N5MWhMNDJxaTNXVm9nWnJZMm5VNE95SjZ2QzAtdGtwcWotZV9aZ0lybUdBVnYxV2NEb2pXZXI3cUJxVEtuZEk?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Berry supply chain must collaborate - Hort News</t>
+          <t>Tilbury freight set for big increase after port expansion approved - Rail Magazine</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 07:03:43 GMT</t>
+          <t>Wed, 01 Apr 2026 04:05:34 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1WMFI2S19IcnRZMnBhaGZPalplZko1cHlXekwzS01lXzV2MERtcXJuNVlaZVZCTTdfY19NX3FlWkUxSjFSXzBfVDVsc3ZzVWZtcVhiQlBVdjFkQkwtbTF1a01aQUVncmpX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxORUZlVkQ2LTRuTndWdE1nb1lQd2ZfaW03T3JhNWlUdUp2eXUycWR0djg1Vm5oeGFQOVdTYW5uQ0hpeDFOREZoaDBpTEYyRldOSHFBQzhuQTFsQzNrdmpjWVRKRmxsVHVxbEtZclhPU2w4T3JPZVZiaGtTZk5xR3daOEw5R2c1akc3d1ZucERGMTZfeGJZUGRYZDBjMWZURnJCdWc?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>McLaughlin &amp; Harvey lands key role in Scottish port upgrade - geplus.co.uk</t>
+          <t>Day 1 of Logistics Regulations Enforcement - Logistics Business</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 06:33:45 GMT</t>
+          <t>Wed, 01 Apr 2026 08:57:06 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNnVfT2F4UXFXUkFBZDdoSVl4NWViREZ0MnI3QzlSSVJFVlpKbFNzZmxfS1hGYnlhQng2QW9fU1dVV2NTMW00WWRwUlBoZURtRnVCSFBuakRSYVVjUVdtWDNkNko0WG5fQzRDcHZEWUwzcVFzSjZ3WDM5SDlVaDByNkJhbGRJdGJjNllWdVQ1eERIU3NOelRjZWhjWEhvT0ww?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPaUJxYkNxMWxKRzhqWFdkVEtWNVFjTXl4OS1meU91aGpUYjU1NzdhNUdXWENCejdXMFdYcWU2VEVfQXFLY1dFQVlIeGFlUkhCTVFhM29GYUZFcVdsWTY2TjR1TWxsWnVXcXlyOFVES3AxejRBc0VOSlg5UnFvTzJnZ2pFT3hWQk4wd3lmZVc0S3pFazhFT2QwcGJrOWFwanE3RVhEQk01eDBCMUxNdXZPeUFMZU5odzU1TEZ3?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>News | M&amp;S logistics warehouse deal underlines confidence in Bristol - CoStar</t>
+          <t>Port of Gothenburg acquires nearby area with focus on future expansion - Logistics Manager</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 07:02:28 GMT</t>
+          <t>Wed, 01 Apr 2026 08:54:16 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPZzRNaFU2TFlaTjRWaVczaUVIMnNrdVJhQ1dXMklLR1A3RW1Kd0piM1pYS25pN080X0VNcHkxRk5Pa2xHWjJlOU00TXd6cGlXS0luNzU1aElSbWRscm9jc3ZWQ2hVUm9RUk5rVC0tN0djSm83REhWbkR3blhsdVpyUlM3azJheUtMUWQzXzZIMXlic3NDMXFKVHRRaWlUWXg2ZmpKRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOQWxtVlpiczd5N1BaTkE0aGtUanlscXpiZ3hvY0xFTzJLS0wyd20xeTEzTk5NTEFjaFdmbUp0SHJ4c25fVHVleS1wUy1HMl9KZndRZ1UyUWxvVW5ZMlpZMFkwV2Njb3A2ZVV4VzhFc3RBODhzZnRXQXBnVU1YNWtnUy1DVnN0VDVSUDk1REM0LVNveXd3RXJOUXhxU19YYnFZTHdGbVhscw?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UK-based sports retailer Stadium to build in-house logistics hub in Sweden - FashionNetwork France</t>
+          <t>EU sets conditions for lowering tariffs on US products in trade deal - EUROMETAL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 18:32:14 GMT</t>
+          <t>Wed, 01 Apr 2026 07:54:21 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNM21RNEhWaGpDMkNVMlpqSW9jZ2hyNGVIVU1NNG0zVGN1NlVMUFh5NnZLQ19hQVNtSDZUN1dONUg4UFh2Y19QYldiQzdLc1FDdWtpZzctQjZ6eTZBRHRGME0tR2g2dG5oSXpiZ3E1LWotRjZRQWVVMzAwb0cwRDY3LURHeWVfLVZkaFlOMUZWV0E1MzU4d2Q5MnE2dFozLTcyalFudlktaExZTDRtZFBHdnBEdHZCN3QydFZ1ZU5MTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQM0l6dTN3V2pUcVdJMjJXMXdLT2lfV1BOY2hlajVTU3FHc0VjbkFFODVhRkFuZm1GTThiRTE2Yl9mS043LUNORlh3SjNMWVNYb1VtQW9MMGZweHVlMlZkTlFjMWxIc1dMYkUtdTZ3V3duRVBldkxTV0d1WHFvYzNmTTI1ckNPbWdDQ0pvUWlMRHV4NlQ3cUE?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cocaine worth £80m found in ceramics load at Thurrock port - BBC</t>
+          <t>Why digitally simulating site logistics matters before you build - Construction Management Magazine</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 06:18:56 GMT</t>
+          <t>Wed, 01 Apr 2026 08:30:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9oYWdfTGxTYW94OXVWb2xlaTVSWm1TcFFsaGV0R29fQ2M0SERCMk85Y0o4Q3VSMXdmbll4TGpVV0Nibm5uTllRWUloYWhURGpVQXl1b090cGF2Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUTVmSWQwNWNBNk9mM3ZMSHZNQUF1TnIxNTF1OWRDUHlSbm9EWE5ySkhxUkN6VU1yMXRpR0puNEZXUmU4c0RnRndTUkxSbXJJYWlUVVIxSU1zbWhZc3YwZFpVajdqVFhCUUJGYUFmS192SC1zd0I2el9yY1JEOHMtUHZ0b3U5NVYyZE5oTDI1dWpoUWZUWjlHQ3E3aFlDNVJiT1lZeQ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia reports fire at Baltic Sea port of Ust-Luga after Ukrainian drone attack - Anadolu Ajansı</t>
+          <t>UK shop price inflation rises to 1.2% as supply chain risks grow - Retail Insight Network</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:20:05 GMT</t>
+          <t>Wed, 01 Apr 2026 06:48:27 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPOWRGNU90YXFCN2NlVXk1S1ZaM1ltY29sWlo2cXM5Rkp3TUhFeUQ1NENHd2pzTzdPeVQycGJTX1dXc0FoanVUZFlDcHhNX01mbnpzYjdTV3E1RWVFMnFBUHNyUU9TdXE1eXFhNDJPcHFjaVBoQzJZeGtpb3lhcVJtVVRwdGV3ZExtOS04bU9Ud0hjdUktaENXQWIwUXNTaG1RYVE5RkZnUnFFWE1Jc0s5aVFkVlhILW1JQ1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNbjNKUFFJeXlhcG10d0FiLWxwTVU3TUF4dm5taHJMZ3Jpc21QMWU1UE5BWnFhUEhKWGwtNG9Xd1VwNXFkbTRRdWNoYThDOHBtYzAwTjhrQnRiTzVGN0xlaUN3a21Yd1FIQmpaZVlxUy10WTh3NUhLUUJKOWFPOEtMbS1pQWtjOVhpbUlWdU50LVpOZUZuSTRDSWZoNnU0VjYzbXM1bUF6Z093YWN5?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saudi logistics group returns for a sixth Posidonia - eKathimerini.com</t>
+          <t>Strikes, street theatre and strangeness in Port Talbot: JON DOYLE's debut novel COMMUNION - Buzz Magazine</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 21:50:47 GMT</t>
+          <t>Wed, 01 Apr 2026 06:02:28 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZjJFdHVPT1VkSFRPR3hLWXQ1V0xDb0piaVdYTUJuM3JaYmh3azlGeW1ub3RLSWlIbmFrNi1YN0x2c013MFc0MXZEa1dnekRFdVVvbllralZ0WGdpRm9ibFlXOEdIX2ZoWHJFa3N3Rk0zckxSdFNwcXFaY0I4UUtpUE5FQWM0VnJUcVBxbnkxSDl2dlU5bktTM29BU204Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBLWU9fUXF6X0RsdzVGU09LUnJ5LUlYSm10TzlmcjFvNjl3UWtoenJPV2JIakwtUmNiSU5hV3MxSUFzWjk2Z19WWWc4aTRMUWxSN3JyVlhxSTkzTXV2bzBLblpmczBXLXNVdEE?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irish metals refinery is in supply chain that feeds Russian war machine, records suggest - The Guardian</t>
+          <t>New free declaration data service means UK businesses have ‘no excuses left’ for non-compliance with customs requirements - export.org.uk</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:58:00 GMT</t>
+          <t>Wed, 01 Apr 2026 09:38:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNMTFjTWR2ckd0a2J5cXhoTXh1aGNLRWljWHhxTnJRVFgydmxoci1UY2Z4T3haRUtDclh2X09CX0RfdHFnak9RRHY1UTQ0MWgtVGNrTHBPeE5CWlVZZ1lJb0hFTnp0d0NzS0VYcTJXS2pnQkpCdmllT25jdGEyNmVxcDVDWV96VHZpaVUycm5ST00tc1YxcXo5dDQ5U3ZuS0dObjVGSm9haHhDcUxtT2l0cC1FOFpyMUNfNkNfNDlPd2dvcHgzWUZNMzlBUEQ1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQd29LRkE3WXlyMUowS1FNUkk2VGdTWHpKUkstbzU1aVJ2ZVdOcV91bS1FdlZlSmhWOU9IVjZaTVRIcDBwRmEzZ2c4aWJZTFlneW9vMnNpQm1tVFdJSFBaQlZXNzRKTTFJQnd2QzJrcXRRbDVNZGM4ZHJUZjZPT0FsMC1pYmZVYjVDU2czU3U4NEpEZUh2X25LZHZ1M2ZkcXBTM3VkM2JiYV84Y0ZXejRPMlVvSTZwX1JVSlBNWGFFc2lMTG03LUItTUNveFpNMHBDMXd4MmVKWHJ0UnpPb25PQkxibm96cVcyOVg0TXZPUWtWZ1BVS2xXRi13?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IFS.ai Logistics to Plug Transport Management Hole - ERP Today</t>
+          <t>UK Factory PMI Shows Worst Supply Chain Stress Since 2022 - Bloomberg.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 06:03:38 GMT</t>
+          <t>Wed, 01 Apr 2026 09:05:51 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1WcFFFSWhGTXExRGdRUS1KVW43c3h3UGhBSlhoYlk5ZE5ENmNUUUpjaVJFRVYzNl9kZGIteXM2OHFZd2MtSU9kVUd2RE55bzI3eGpJV0RrMGV1RHJrbGFBWURORkk3dWJYMDlQTkwtc3g2RHNkWVpjMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQUFVWZjUxZXoycFVUeDZpeVZoRDFRRFE2SUZzSUFGWk1TX0RmTDlaRUJQWVQxbFhWUGIzT0l4TWJobHFBZXk3U0x0ZVctYXFyaDNvZzZPbDlBWGdObzRjbE9ONldVYURTU2pFam9OcWltSThSUENHX2tFYTV5cFpUakFZUExQM2JtckEyalgzUGFnNWc4ZDNNOXNBYjNFLWlGVjBrNVVDNjVHSkJuWGxnUEdUbmE?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jewellery retailer Pandora enlists Hardis Supply Chain for warehouse management system project - Retail Technology Innovation Hub</t>
+          <t>Major progress on Air Products’ new liquid hydrogen facility - Port of Rotterdam</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 05:32:14 GMT</t>
+          <t>Wed, 01 Apr 2026 08:57:45 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPQTM2VFEzWTFoVXNlNXUyV1VFTkZYV2M5MlpDTEJRcHM2OGswY2dXRFhOTVNHSVd6SmZ1VnFON3JIaUVpTHA0VGhid1BjbVpENGp0N1JyekJ1VUVEYkZjaVgyX1FzdU9OMkdOQ2VPUVV5R052OEdjRkc1d21EQ0FPNUNSSzlWakE1bzFfRVdMSl9CRjlHVkIzNTVySzVDbmxwSS1RcTJiQWhwY1hiY3NMbW9vNjBlekpCY1ZMNjNMTXUzQmR0MndDNFc5T0R0NU1ubVdvbEZvVHI2VXZJN0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPdzY5b1JqTmR0aDlGaS1nUks4cWVfb2I5c0l1XzJMWVFPZGljYng1SzRZTzl3THAtdnItTndJbnRubXpSWlA1ODVMUVRWeGt4Uk53S042Tmo1eWZ2TXFGQWFiaE5fclBJMzIwMjM1enN5RDBZeWZlUFdvVEtDTmVIeHFFMzFWNW54VzB3ZEoxc2hObW84R3lwNm5iOHpmNWllRVdwM1lIcERuTEVVMm5lamprZzNSdw?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Greene King Opens New Consolidated Depot To Serve Its Northwest Pubs and Optimise Supply Chain Efficiencies - British Guild of Beer Writers</t>
+          <t>Putin’s War Chest Set To Explode With Iran War, Lifted U.S. Sanctions - Forbes</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 07:30:43 GMT</t>
+          <t>Tue, 31 Mar 2026 12:12:18 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQalBRa1JUQlN5czNfV2JtTmQzUG1jbWVXejJweEVLY2xVN0ZNMElObEFCSS1ZZ1c2S1VUTXMxc3hFUGd3RXIzVHdVZnRKVUh1cVVnRjJuR1Bkb2M1b0cxWUVoOWhnbk5KZ1FtVTRmbEk5dFZmMzFnbUVLUE9tMF9PZ3ZmY2hZQllBaXlvTHNrY0toVC1wR2g0bXpMOTd6S1ZXdXdiUEk5TEFmMUlHNnhHYkhTVjQyMnRkc3hvaDJkZjd0dVBJXzdIOVpyTGM0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxObDB1X0s4dXJhdTlJR0MyaUZuOVYwMWlic2VTZnA2cVBIbDA5UVF6OE5HOUFQNnFXNEYwSzdwTl9paHpIZ2l1RV84MUFCbk15Z0FiaXpESjNUMll5eTBiVEI2cTllLUZ1Vm93TTNob2s4U192bEZqNzZZekNBdmM2X3BKcUZ0R3dmZlhQN0s2cllsd0Q0N1RBMlowWXAxbFkyYy1nLXdVVDBkNUw5OHg5WHFENXFVSDJMRDgtaXVtQno?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stablecoins go mainstream, but compliance hasn’t caught up - Electronic Payments International</t>
+          <t>Phenna expands compliance services with Ventilate deal - Food &amp; Drink International</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 03:44:12 GMT</t>
+          <t>Wed, 01 Apr 2026 09:46:07 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOcl9BNHg2Q1lHcnpqN2pJTGR1N2xER0V2bXlYYTdSeDJkSWpWY1ZheUU3WlhXbEFHb2E2bUdlem1PdWo1MjFPVGZVa2VaWDIyMjJSQVVFSlhIaXI4TkhManZUdThiWXhfZE4xMTVXRVJLWXlYQndseW90MVhzNHBkVGpWSVBwY3owODJ2YWFmU3RvUENZS0pIQXNzcXB5VHR5aE1QZGMzMXdsbzVwVGZHUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXZleF9BSnUyb293NlNTU1JvQUxUcFBxdWpGaEROUUMzaERTcTg2ODhwOVpaMVpRS2VhcHc5Z3NtZVRvQXhBa3RPM20wcjFrZGRGV0FYd3ZmR0ZjNmNjSGViREVQSkRjRHplSDk4dno3bHI1YUJoV3hmSUtNbkJ1WFNsdy1UWllndDFlbHEzZmQ2QTlrOEx5YQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>French bill to push shippers into zero-emission road freight - Trans.INFO</t>
+          <t>Shipping Resilience Tested as Middle East Instability Persists - czapp.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 04:05:54 GMT</t>
+          <t>Wed, 01 Apr 2026 07:30:02 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5DLUpKZGZnZ29vWmF6T19wd3hKRG5zU25kaGRSdjR6LUNoaDlHWGZZNm1pb1NhQldVZV90SE1jNGdOY1o3OEpXNElzckc4WUlIOFY0Z0I1NElZV2FsRXVBVFZ6cGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPNnFmanRsT3V2ak1UWW42MDZJNUJHeGVSR180cmdNeGJ2TFJKdEVwRGdrR2xPLWdaZENDVC1LT25GNjJCRHRHQ2ZEcnpHUG5qYWUtM05tcGpHeDNQQktkX2RxdFQxUE5NdHZnNnBYVXYwV2Z0OEtBcW83VzdQNTRnTkNwZjZjRk9HTC1VRTdCdjRfMDBSUmFsRmg0T2lkUTJuUy15Mw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Middle East instability raises immediate inflation concerns - Furniture News</t>
+          <t>Ralph Lauren targets supply chain improvements in new green strategy - Just Style</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:36:14 GMT</t>
+          <t>Wed, 01 Apr 2026 09:16:20 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPaUhJQUxyYy1NckFWV01BRnRxc0JRZVlJTG93WGNJNlk4X3FlUUZPZFY5UUpHWG52cDVLOGFVM3BmcDhVVGhUUUs1ZlN1aW9JV3YySVh1R2t5M0Z4ZWQyQTlnVzRPdXYwYVdQanFlaHZXUm8zNzZQVElOR2ZOTVpLNXo1UmZ0SlN6Wnp0ZmlaSkh2NWwx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5iOS11OFZyV2NzY0FObm9adjFqYy1LcEsweVJrRWdTa1MySlhUc3N5ODFPMVl4WV9wZzBRN2JsR1FtM2dxR1JWZ2FLNWRWRmZ6cHJLcUdIb2NzUGZxLWd4NXNJS2NOdVQ5Snc?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>To break the pattern of rigid higher education leadership we must move away from compliance and towards curiosity - Wonkhe</t>
+          <t>Port of Dover secures EcoPorts PERS recertification - Port Technology</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 05:05:56 GMT</t>
+          <t>Wed, 01 Apr 2026 09:09:49 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQc3I3U0twTUhheFNXVWwwQldUc0NfX2FrT05uU1FTdXQzRGdQbnBCUUpzWm5FWk5RbkdHaHowSWhMRmlBbWFsX2YtNTJGeXJkYzFwbmFwRjVlcEk0V3FPaFFRSzVRanRYR3lUd1BPY09BSnh3bEFoTWozWndIVjFZaHV6blYwYmZrVERRZDVNbDduWm5JZ2haZW1UOTVVVHhuMk9Ca2s0akRZTzJpVFRSbWRXOFdzc2lvYjJZaWJXTVNOb0xUYnBVSmxfTmRfVndtVk90SFlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNWV2NjY0UVFQRURHdXhISFRuVlhyNWs5a1BwY3gwSE1JNExqTjhLeERXSXFQdGg0cWE1NGpBTUswdG9EZVBxVXlKOW51OV9aSVl4dFhuU0FlbEhMOGQtT0hoUm5WbmtuN1VHZ1ZaYldQQmtIcS1oalZSZXJzb3RtWkNMbGhfeHFqLUw0?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Uncertainty complicates efforts to prioritise shipping investments amid today’s decarbonisation regulations – yet delaying action is not a viable strategy, Wärtsilä survey finds - Wärtsilä</t>
+          <t>UK SMEs prioritise data &amp; AI over compliance digitisation - IT Brief UK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:00:00 GMT</t>
+          <t>Wed, 01 Apr 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wJBVV95cUxPZHZZcUlmUEZQc2pjUzhRbndZcE1hUlMyT0hFZUEycHRXUDdfRnpZTU8zS0haWFF3b0pQVXp1VVZKVzlMUEFDbXRwQnZnTjZfaDY5Qk5XaEdRTXlfbldtWC0xNnRpdDJPdzJRSVN1Q3FmRXVmclIxWmtZT29CSldETzU2b0UwQ1MteFJoT0hFZGFnajhaWXM3aEFCOU9KNEVQcTBPNnlERTM2UnUwbUt6YlFLLVFLRG1hSFhua1hsLTVSRWhDTE5TTHFSWW9CcmYxRHJwdlJJM0JabHA2a2dKeWtHdHNLMjhFbkNkLVpKOThYSHk5MjR2SlNNN19PbEQxTUxGdHZoc1FnSnNyRE02djVXblBlVmY0YjY2Um11VWFPczAtaGFHQ1RIc0g0Q3l3M1Z4QTlOZlJOTDd0RWlCekpzdG02NFAtLTV0OGt2bWo3NzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQUm5pLXFmM2s4SGd5T3N5ZWd0SFhJRWx0WGJvZkVDbFlobWdYQkE4NFpYMzU2SjR6dnY0aUxCejVwR0pyOWV5bW1VV1hUOHVkTkJ5WGlfZmotYWVjR01xSFFOdUtrSHJHU1hraXVzaEIwem9sVGdPYnBkNWhVS3BxaWxZU1NWQnlEOHlB?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Western powers were unable to secure shipping in the Red Sea. Hormuz will be harder - Reuters</t>
+          <t>Equitrans Logistics maintains service despite Middle East delays - Logistics Manager</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 06:02:00 GMT</t>
+          <t>Wed, 01 Apr 2026 09:25:12 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxObXYyUE82WTFKZGx3dy1aLWtwQkJHQ0xtaTdYX1U2b2Nnclp0VmdYY1kwa0lEUEk3dVJDdmdQYXNQeHJmV3hhUExNalF6UHJTLUhhTDlnM3NYZmZQOGswQWpncm9ycjJxN1NvMmc0S1pGa0pJWFBhNjFLTlZ6c1JidTU1bGdaRHRIektUaS1oZlFtZUNBOVUzelJpRTZrckdXTzhOMHBqZnp0M0Jhd1ZvMndEU0NIbEJ6ZjZXTDFXQjNyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaURmSmR6Wk43WnJJdXhWeUJfaDJTcGR1MEh3ZnNPSy1nS3Fia2JRczgwT29fZGRpdXhKaE5TUWdhOWNRb3BRTy1QSmxWekhENVYtRm1jZlRVOEJ6TmE0cFBDWjQ2WXhrUkkxUXhhRFJ1N3FfNkhhUWd2b2tWX0VQTHJkUmRNNEQ5N0R1WEYzTmtYVEdJRFJmVlZjNjgyUjg?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Why is General Motors Investing US$1bn into Mexico? - Supply Chain Digital Magazine</t>
+          <t>East Coast Main Line congestion plan welcomed – but freight operators wary of lack of funding - Rail Magazine</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 17:23:15 GMT</t>
+          <t>Wed, 01 Apr 2026 04:05:34 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOQ2lPaDNDSEJVTTdGczZNME9HeFlTbGdDTjBNNUxYRWREeXMtYkVZQzltaUlFOEI2aFdvdUtsZWhOUWRqY1hUYVMzTTRKazBpUWtWUWtBVE5mWElhYzVTT2V3T294akxJOFJIaVJINE1EZldOeXdEbjNFTjhYM1BfNm5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQQlFuZUktTnczSDRwMXJnVVRBbTBmTWZBa1RGdU5ndXVqeDI4YlJoalhtLTBxaTV2dTR1b2FhenZhXzRGXzdFcjRzR1NjdFRnM2RZS19lZV9ta0NzMFhtTXYwWW1aWTdDN0hDZG9kOFNaRVBsbnBUa0d1cXNrS2doMWRKdzR2YWpfcldjVzBpQ0NwN2E5LU1NZHFwVzZEd3JNa0NlelE0QlM3MUpMSzNDS1lDdXU?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Elliptic selected as compliance partner for Solana Developer Platform - Elliptic</t>
+          <t>IntraLogisteX 2026: packaging and sustainability a strategic focus - Logistics Manager</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:11:48 GMT</t>
+          <t>Wed, 01 Apr 2026 08:00:27 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNM05nQjJLM3hxTF9aNmphU21SN09qNkh3QTZ0YjVTbFI2Z2lhRlFINHNBY0ZmVEp1aGVNNFR6bjVBbmVIMzZKQUZHaDJ6b0ExcEVraVJGY3VjbTZTMnF0VjhjZHNkVUVVYS14dDZLaFZIdWMtb2gwUU9XSF9JTElzTElrUXVBWXRBdnB3VllUZXZ4MWhqcExrOWwwd2VSbV9rc1AwNWxNMHYyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPWGNTa1pzTWZkX05vRm1mRGkzME1JVy1hN2hIXzQ1SXl4MXZwS3h3NzdTQkhFTUk1cFowdzUwSzAwRVFrdlh1UUdtbDlsaVUwWnhCTlVhdDRHbnVqc01GdzhjQU1maV9aV0F4MFBfVFFZMUFoWlo3aDBKdkpmTU93SjJRT01CSWZjdWNKV0lmNGZLS21qb3FWVWdjTnRRNFk5?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Shell shipping boss Karrie Trauth steps up at UK Chamber - Tradewinds News</t>
+          <t>ECommerce Fulfilment Boosts Throughput by 20% - Logistics Business</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:48:44 GMT</t>
+          <t>Wed, 01 Apr 2026 10:22:22 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVE5TN0dNMVM2Z1lieFpZWVItaEdfOUdKVE83SVE4NHdKWlk3Y0tLWUxfVHZKMVpFbzJoZk90STFqYmUzeElZWnFKZFNFdkdodjg1TkxrdkRxMnRNNXFLc1BZcDVlZ2F6TTBUWURBc1FTNmNXMC1SZk5rNE9Ib0JpUFY5Tzc0enRndG5jRzZsOEoyRzAxYUdQVGZIX3dVbjgtajZEdlFpaU5Odw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOdUFWdVozOHl2WVZtMmFhRFBqckdZdmtfY3dnVWZRT2wwR0ZUZXJvMlhXUE9YZ2dfRkN6UkZPZ0RRZzBtdVVWeWQyWkh4R0wxYkoxbnIyX0JyRk1VN0xST2hIc3ZxdTBnd3lIMGNMQnp1NncxV05LTk1vWDlzYklMQ2ZZdjl1YXR5NkZjZ0x2Z2FRb083Z1hNbDAzc2tDMXVPUUt3SzA2VlFlYzI5?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ohio Mayors visit Ellesmere Port - Chester's Dee Radio</t>
+          <t>Force, Vetoes, and Sanctions: Why the ICC Can’t Touch a US President - Jurist.org</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 03:25:45 GMT</t>
+          <t>Wed, 01 Apr 2026 02:41:07 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE8wZlJjMnNmZV9PRTRJS2k1bkRQRjJDeHVRMFdNeHE4RVdsRU85NDkwTmZsekNBY29oQnp0aS02NENJbXg1SUxDM2FFVDdZV25LMXpURlp4Rm5RLUJIbTNSdFZlRlpDWGdiSWdHaV9EWHFnTy1nVXdGd1F5VC1hUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNTmMzcEpxR1NHWWpvVUFSZEVOWW9MejZGVllLTEQ4emhfVG1FUkFsTlFxeElfa1VPVmZCb2FwZFZIV3BHLWpVaHpDMGxEcWE0bnlpM2pMcGpqM3ZFdmdQMmZpcEFMdGFJR2hIOTN0U2VGZTVhUFRFNlk2VzlHVjFpMFdLc1ladC1kcWlTZWFJcWFuSjdDRkdIQjZJT0V4YkZsVEZSQVZPeGVyblk?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>‘Decision intelligence at speed is the breakthrough shipping needs’ - Splash247</t>
+          <t>Next commits £300m to major Yorkshire logistics expansion - BDC Magazine</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 05:48:16 GMT</t>
+          <t>Wed, 01 Apr 2026 10:32:26 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNeE84ck1UTkRNRDRxOV9MMy10ck5IaTl0YjY2NGZGajNMV2g1aHNzNm9tOV9XRFk1MUE0dXB3MGM4RnJOZHg3ZG5HTm1TVWZ1d2M4U2xRYTB0RlJLbEVVWjNSbnBsMHlTV0ZoYjR2XzZySk1EcmliY3lzVHNNclVlYXd4dm5aT2RFaVZ5bE9reGI4dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNeU5FOHNiUGplaDZlTXQ3Z2FNMG52dFlPUTIwU0dmR0ZkN1BOYkJlRFNfN1p5VG5pLUNCaWVNTGNVTkI0a1Y2bG1sd2ZEMDVkcF9BLXpDZFpUSDNiNWR1QTdybkk3UTVHa0NBYWhGMnJfSkFGek9XYlVpOW5qY0NLYm5zZGhGdUxCYUw2VVdjZnkzSDA?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ellesmere Port MP launches petition over stalled shopping centre investment - Chester's Dee Radio</t>
+          <t>Brazil expands pesticide packaging reverse logistics - Packaging Gateway</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 03:25:45 GMT</t>
+          <t>Wed, 01 Apr 2026 06:33:45 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNOVVvekhNNXZ4c2tGZFh6MTJlNmVvbThqVGJKNWR6UEFfWE1XNE14OVd1c1k4NnRYU1J0ZjV4MS1XZmNRZnNDQUtoYXR6S3ExM21UdjhxM3lSSU9YaFZ0aXFvZXRlNjdiZ01aLWM3eGpGTlNZQ2RUdmo5a0c1OGZtNDk5U3V6S19CcnMyclNBcG1Ea0dmUUJXTmpvRjh3NW5wdHplaFhQV3JrZkowUmktQ2tqZC00Mlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNbUozVm9pQUdIYUJrQld0ZFVra2tiU0JtaktURTVhQ3k1OEdtR1hSQXAzVlZJbWZ2b25pd05Ba1VLOUU5dTBLMnljWGk4X0RmMndVX3I0WmZGWjk1WHlHdl9xMW1mZkFKckZibWZmZUFQVEppTE1Va25Fb29HUExGSGlHRlZVam9mODRvWU0xNzFMN2xQb2tz?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kenya flower industry bleeds as Iran war disrupts shipments, drives up freight costs - TRT World</t>
+          <t>Port Talbot set to drive Celtic Sea floating offshore wind with new UK funding - Review Energy</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:21:46 GMT</t>
+          <t>Wed, 01 Apr 2026 02:06:06 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBoY0hGWTQ2ejJhd3VXQnl5VThaRVZVUzBCRXllSkVaV3lYMFp1LVVhOG1VYWhpZGlZdlJxNC1COVNoRjAtRFF2NXdXbEZfSUZBWkZzZVp2YW3SAV5BVV95cUxQOUdhbFlzemdlbTlpUkpKZ29YVWtxTUlSM0Y5aUVsRXdQbzVFanFXOTlpUnVQMDgxeHBINW1aTlhUaHRKMk9tOFZFQWM5Vi1VN1hoODRYX19XMFo1Q1Z3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOXy0tTGw3UW9Gb1lKMW1mQllxaXlQOW1YYlcxcERlNkl6cDlkeFhlTUtDbHBvMjQ5NHBORWpQV2pMUGpJVnNVVm43cmxEcldpZE5zblh3OERPYzIxbmtKY0lKemNRek1OSG16Qmx2OHVBenNqTHNfaFRkX1FEZlQ3QXBLMUQtbXR5VlNIVGNvckN1ZjA4ZThWcURZN3FidmVUaE5xNXFIUDhDU2hTNW5lRWlyMm53dw?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Neath Port Talbot Council Approves Capital Programme for 2026–2029 - Business News Wales</t>
+          <t>US lifts sanctions on 3 Russian-flagged cargo ships - The Kyiv Independent</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 21:39:59 GMT</t>
+          <t>Tue, 31 Mar 2026 16:16:33 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNbF9QUkNZRHdSRXFHVzVJeS1aOVRyN1k4MGNRZ25kc2tnQzFkRUVjb09CUUE4VGVfTlFiTmdkSFNNRE93aXFuUXNUMHdMQkV6em5HMWxtMU9wM2xoc3J2UDc5WXlMOFBTSXdQOEhCdmNLQk9rdzVab09aX2NLdk9nQkYxZXN0UEJkd2FIazVjcVlDMmNfZVE5YUtzbnJmdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1rVmtiRW5wRkowaHdIck9lWnd0NzA4V2xNTjJnVHNZZFBPdDJuVlRadDBTRVFNeHlwN2x1N2VlR1ZrT2RmRWNNeVdGT1E5Y2dRVHduamVpMHBCY2pKNm1zTXBnVGhDSWRLSlJyWFdCWVZRUGZWQlZvZXlfV3dXZw?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>War with Iran drives big swings in shipping stock prices - Lloyd's List</t>
+          <t>India-EU trade deal reduces machinery tariffs to almost zero - Catering Insight</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 22:44:41 GMT</t>
+          <t>Wed, 01 Apr 2026 09:12:16 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNMURCdFJKQkNUckNPdmRIS3BLd3pDU1htUUJ4bEFyUkExcVppQy04R2Z6U19aamY5Y2ljRWllRGNWZ2dUalR4NDVsTUdfOS1pcWc0VXM3UTJJTDZSS2pJdmsxemdTcWRrQnF1Vk9FakpkRTlvUnNsVGdfQ1poTU4xbldJVVB1OUYwbnRDbzN5ZDV1eHpFZ01WcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNTmczZjB5b192STJMTWRLUW9aQ2RjRVFFVHh3X2RCdW1QSVUyVTNwSzl4STM1X1dSMUwwazZwOWtBMHljNUZLcVp6YU1IcUktZDBrRXU5bnp1MXB0Q1huaDZrSHNSRUlXZkNmcGxRWWdfTmhHbV9kYWl6ZkIyRVZpczdNbVJUNWRRa1VQY3hpTFozdE9aTU5Qbw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Promotion: How this Suffolk team guards the nation’s food supply - East Anglian Daily Times</t>
+          <t>£70k confiscation order secured after unsafe meat entered supply chain - Farmers Guide</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:20:54 GMT</t>
+          <t>Wed, 01 Apr 2026 07:44:37 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNU3BCcTJycEJtdFRLWjAxSlR4Z1pjRURQSjBaSW5HY3YwcmotaXNNNExCalFibTRLRnJqSVNrNy0wRnNoelNweWY2WFBTSHdHdzRzSHBjSVlkUDdGTWw1bmx2eWRIYk5GY2JyLWxOVmhmZnZvNTVMVF8wX05rUTg4dXc1SHFvTkZIblpOd2V1bnByeDRNQUtfYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQMGNIYmdhVmZfSG5xSlRjejYtUG0xRVFWRmVSQlAwSmh6N0EzOXBLZS1JY2wzcHVLc2VqUG1zSVlqc05sc000eE5SdkY5Q28xS25oUmNhVzlSTzNaYmJEb2hmSFF5QVlYRUxZaGxMVVZwTXRmS2daNUd1MnFQVDhQc09uN1ZYYWtvOWI3eXNxSGFJREYwbUF4Qy1WQ1pMUEpOaDc1SGZfNUVVVkxLcERJVGxqYXdYckpadDc0?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brentford announce fan behaviour sanctions for first half of 2025/26 season - Brentford FC</t>
+          <t>The Iran Crisis Is Exposing AI’s Supply Chain Blind Spots - Supply Chain Brain</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 16:00:23 GMT</t>
+          <t>Wed, 01 Apr 2026 07:06:04 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOVXV6WDhzRzdIa0VybWNiUnBneHdDblRLT3lQSFZRLXBPeENvaHFvSTNGOTVQV1BydWI4SG0xLWl1d182SzBRTE5veUNNTXlFVnNSR1QxZ3FaX1JLWWpyN1RMQzZLUVgyT3hQTTFCWFNMRFJkS3hUTHZBTzNiSTduTnJId1NMYnJVbEQzNzNLeV9LVVBhRERQVUFJczRQdGZmNDI1U1hKbG5zcWdNNVJrZVdpRlRmSk85YktZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNekJVMi1nQXlJUjU2UmVwaXdVU0dERnphbWx4cTZpVnRtUjJVODVLekNub2xsU3ZvUkJKb3hSUFFnZXpTQ2UyUmpzMlJIeWlXSkFRZ2IzdHZuNkE3LWVsX3BYM2hKR2M2Mk05dGVvNi1oUmJPbWxTTy1uajFjaW5TWG0xNU1BT3Q5Zk1PNnJYLTBzTG9Va2QwOVFra2l6d2dmWUlfV3pkVUxCeHJKMzJHcFBrdzhTeFdjeXpB?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MEDLOG Inaugurates Integrated Logistics Park in Saudi Arabia to Support Vision 2030 - LM - Logistics Manager</t>
+          <t>Gioia Tauro deploys drones to boost port security - Port Technology</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 07:14:29 GMT</t>
+          <t>Wed, 01 Apr 2026 08:54:48 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZWg5MFdBb3V0M3pucUFwMVRSbjBVUi1NR1JRQUhWRVJKbzlBa280MlhGLXdCQnNZQmhHbVI3UG9DQzJBV0ZjZ0FaS19JcDlyaTNWY0FLMmxTZGgwdG1aWjBDQ1hXdWt2NEprOUpDLUxJS0FGWWJUbGdRelU1Q3Q2akVKQzF6VDJIWGkwTmF4dlV0QW1xWnptXzd1NXlsSE82MmZRYXVQQXZsaEtuTS1RMUhuZmg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOeUJGcEpJLUxocVhRNkpTRWY5c2luR3p5Y0EzeWVVNlMzcnNrTEhJYWVCQ1ozdlliM2daM0ZRUjFkNkJBbW16WlJOeS1rTlljeEZLMkE3Q0VhX2NmS1hFUkNITlJHUjJVc2FGT2x4LWpVNE9VRk9qRkFRSlRtTC1oaTFBdVZTUElq?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hutchison Ports unit pushes Panama arbitration claim past $2bn after ‘unlawful’ port takeover - Tradewinds News</t>
+          <t>Rail freight positioned as key enabler of UK cargo flows ‣ - WorldCargo News</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 02:38:35 GMT</t>
+          <t>Wed, 01 Apr 2026 06:17:22 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNVWVIM0Y4OU0wRnAxTEstRkREdTZyTU9oem1qT3V3UHQzdnhsb3NmNWpWSWVvNGEwVjZtd1BhMk9UWHoyRTZIS254R0c0Z3hOak1LTVc5MlVNLWljVUFTZ1VaYk5CRk5GbnE1dXhKeWo4bE5lc1ZxanczTmg1eWFBcGJlRUtzNmdLNjBSOXhXeFlEa1BQYWVFZFVUOWd3UkhCY2ZXdnZya3VlcEdaM01MbzJ6dHFBTTVDRGxDc09wc21yZ2wwc1B5NlVRaUtSOVllM0FDOWF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNaXBHNmc4c2dYWUdtM0RFSkUtWlJjcjVFM3lYR2NLQU5oaWFDQnE1VUxJYWstYVNOZnJOQVA4bElCM2RMWDBlQjJKQzF6ang3OHM4MFBjVTBoQ0xsRjZldzdXR2E3SVVsdUJkOXRTcHNFRFJZRmc1MzVyWVliVVFaUktzR2dCZ2xYaXhvNzQ1SzJZekkyUTl3bWZ1Um5CVmxONzM0?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Man who caused 'permanent damage' in Ellesmere Port pub fight told to expect jail - Chester Standard</t>
+          <t>GeoPura to deliver on-site green hydrogen plant at Port of Tilbury - renewablesnow.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 06:00:00 GMT</t>
+          <t>Wed, 01 Apr 2026 09:27:15 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYzBkYWRsamVQdjQxRnI2Z3U0RWgzQlVpLU5KRXVvR0ZjMjBpOEFEQWhVTXM1dnR2NDY2MDNlZnM5UDlOZ2lqSGZCNTZjZk53c0JfQXA4cm8tV1BHbjFfTTdhMzdPMWZ3ZlhuUmVUUXNFRGV0OVhXOElNN0pUODRvc242M0xBRXBFSDdnbmM5dVBFRWRab09FQVlJT0x3QjJx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOQkUyMFJOQmVmQ2VjMkVISXp4S0FWS0pZaGc3eFFnWWt1V052MEY5aEQ5OGd1RkEzY2prQWdlZ2xBOFpDbFdEcWtEVFA1Qks3YUktSl84eVF5MTdYUWtsS1RsS1VUVGNGRU9kOHpZaEpSYmFKalNvcjhzU0lFMkxCUzZ3ZzNjMDNwZnNoMTJfMldzTTRXd25PUWpRUVRKTHZsQkRLbWRJNXRTQQ?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>£1bn boost to drive UK shift to electric trucks and vans - AirQualityNews</t>
+          <t>ICG's Axel Logistics hires transaction director from Sonar - Green Street News</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:09:27 GMT</t>
+          <t>Wed, 01 Apr 2026 06:49:49 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPdmRDNEZ2QW9iQ1gxME4yLWdmZ0VPd1d4eTYxZ2Z4aXpNdzg3YUpaRmItZTJUN3NCLTFuS0dBNndwRXhlcG0zVWVQMzdYTVRKN3NSSTJYU3J1SUR3cXloU19jZDFNdGRhZkQ5R1NmaGtTNElDQUUySkpUNzcyeWttTVBGdEJPM1lsWjh5dGVGUlMzZmNRNFZNa0pGbnN5RlFaQkNJa3lvN1Bxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPTmplckk0cnVVZUJwNUxiN2ZpUzNZbDZqYUhBMlBfTzdXMUkwMTdEWHhJMGlMckkxLUI5bVd0Zjlqb2Zlb0V6OHlBNlNQMzdrcFA4SFo2TTV1M1M1VUV4c2MxMzBHY3dsWGRGLUJZTWtDaWFBMnlwTG5MVURzdVgtN1hoN2lpNzVfR0w5b0E2T2JXNDZ3NDBEa3l3?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2581,27 +2581,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Man arrested on suspicion of murder following incident in Crumpsall - Greater Manchester Police</t>
+          <t>Industry warns EC guidance on PPWR compliance does not address PFAS and recycling gaps - Packaging Insights</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 21:23:00 GMT</t>
+          <t>Wed, 01 Apr 2026 10:10:55 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQN19OTTlBUE9NNUdYRElZT3IxTkZKYWo1Rkt0SVNjdTItRHRkdWtCbWJXQ2NNbVlEaGVyanMyZmxER3BJeUFCMWY5bkxBbjVuUnkya2V1U1Y1MW12aUk1NkhnZ1Y1NXo1eHFMLVNHeld1QlRubFF1SW1melBiTkVicXBNYzRIYlV5YXBnYVNVdUhvZ0QtcnNSYmotc3JnYWptR0hxSFhCR1NMQ09XVjBtNi1vdW82eGkza3NzYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPUWRDemJ5UXpKbHYtMUdBanY0emljZE1jai1VeFY3Z0dIZXlKSzVMTnJBYmo0SDFZbmsyT3hGbHRidW5BYXJoVzhmV0FVS0FrZUgwVkdfaE5HUHY2ajVnUFIyOTN4OERGVGk3M21BcWN3ZHd0Q2JiN1JVU3JGT29iLWtsblRoQnc0VmU4?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2611,27 +2611,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Appeal for witnesses following sexual assault – Buckingham - thamesvalley.police.uk</t>
+          <t>From Day One: How Almeda Built Its Fresh-Cut Supply Chain Around Reusable Packaging with Tosca - ESM Magazine</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 12:20:00 GMT</t>
+          <t>Wed, 01 Apr 2026 08:21:29 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNczM5cEV5X2VTUWVQNkZMZi0zOEhHVFNFOEh3WTBYblVhYnZ2aTlNNlZxQzhuS0pzNGgwaTNwM0FVV083bjhhempHb3Bob3VRWG1qYW9xZ2RsSUxrc1dkOFRGOXEwejQzdllvbDhsQVFFcHZEY3U2VE9xV1VCdTlrSUNRQURZdHZreGZRX3F5OC1iZDJSUU5UWGMyWWt5R1dFMDBpTVZvVWwtRWFyd2U5TU5taDNPVnVPdzZzWUkwd3haUWY2Zmh4ZjRESHctT0NOZldIR2tR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQdXMyTUV4TEQwTVVmM2FaVU5nZ0huQ0UtamxjcW1fSV8zTjhEZGUzUGgyR3hsTFBrMTJEcWUybEgyV0l3RFQwdEx2d21XRWczTXctRVpFd3ZjVFFrenZ4dnFUYjFmcmlZUWNYbzgzN2R4bU5ON3JWMVYwbWdLSWQxb2dQWUdZWnhKNlNwTWlBZVdzWENEbE5mNUxnSU1UYjl1OUJEUnFrT2w0M3R6eC1GU2p2SmtacUVmazJpOUhNc1kzVWNaQ2NVNXhMSHlVbmstS3JRU0lWdUE4SEpSYVE?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2641,27 +2641,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>March UK retail sales fall, further decline expected - Retail Insight Network</t>
+          <t>Calvin Klein and Tommy Hilfiger owner warns on ‘potential impact’ of Middle East and tariffs - Drapers</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:14:30 GMT</t>
+          <t>Wed, 01 Apr 2026 07:57:21 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5URkhnS2cwNDk1NDBQeEhSZ0JEeWFmWnpvamFLdndVZDhWR2JCTS05TXF0djlnZEc1TWZKTkQyTmlwRW85eHV1N0NHMWU4T2dlMkJicUh2SENUYXBjYXNKRnJlVV9XUEwxWGczRi1KRUpQenJ2MnlZelBiRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNcDNwVGVIanFqcmZLUjhoX3IzeEdJWk9Jc0x2ODNoNG1KTHM5cmRMUlRMYnZNTGVFQnRJRkRRalhybnRtWnpBQnJoR0xxLTZrNW1GR1pxcWhJTUNZZjRyVWxCX3AtaUM2NTAydWczMXg2R1lkT3AxemQzaUFVeC1aaFBreUg3MEd2UnVXRk9Kdm8xbzZCZDZia2ZwWWNnQWt2S3U5UTNXWGxjb3NkOXp0TXVwYzlJQ282cDNOaGxNT1NUWDA?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2671,27 +2671,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Appeal for witnesses after man dies in A64 collision - North Yorkshire Police</t>
+          <t>Iran War Raises Beauty Industry Costs Amid Supply Chain Disruptions - globalbankingandfinance.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sun, 22 Mar 2026 17:09:00 GMT</t>
+          <t>Wed, 01 Apr 2026 10:19:48 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQUy1LWlNHSmFIbTdPcU9wanhfVkhVbUNkeVhtNWlhbm9YbkhlZ1FYT0hPbGtFQWlzSXRSdF9McWF5TDd1NWlTRTlzeUhISzRuYlBNNHFfV2RYNmpZaFp6TWVaTm1qdFFod3ZQRTdGY0RWYXFyZnpKTnlFSDVRN1hZb3U4QjFMRlpzcDJkak1kZUZQaThLMlpaQzdPZ0RUUS14TFNzSmlIYnhuWUtGT1JJR2lfVlNGTlZvSS1sVE1hNjBIRGhqRTRvVmhTbF9YZjJHTFVGaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOZ3ZWSkpvcWRoQi1MbkpWSTA4Vzk3VTZVV0p2VlROelQ4bC10OS01U2V5RVUtSlV5VFFYRDlhc3Y2TlJhaV9YYWxUUndRenpDTWNoZUVoZzFId1hFaXc4a0JOSWl0Z2lpaFlFbUtXei0wZlR3S051el8tTXNsYnV5b08wWmx2aFVHbzFNZXZ6dlpxcEwzbzBUOGsyZkZjLVE?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2701,27 +2701,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Two men arrested and charged after guga hunt protest in Inverness - BBC</t>
+          <t>The key shipping route under Houthi threat that could have a seismic impact on global economy - The Independent</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 11:22:01 GMT</t>
+          <t>Wed, 01 Apr 2026 05:23:00 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBPWnRjUlJDOVVTeEc4UTVfX1lQNTgxLThhamhqOVBuLWpaM1pYYXR5NjRhQjBwS3VrZUNMQm5EQWRxVXRxYUtUTkQzbUYzMlRXbjhXZHVqZGlRdmhN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQd2ZBVHN4VmFFaXRBY0c0TDVaT2VkNU9oa2dXNnVoV2ltaUpTbUtVSUtsZkxMSXNRRHBLUU5XMzVmNngtVG9oeFpUNnJlMTY3VzBYUy1PY1lfaE1pRTRxSUFiQkpLNVhYc2dNeW1iMDJkTzFVcC1ROTlJeXlXUS1EVnhucnl4WlBsMVFyTlM2aGM1bnozWWhvcFZ6TlVjTTl1TDFKMHRqdEM1RlZ3N0pVVnI2N25tWnc?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2731,27 +2731,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cartoon 25 March 26 - Police Oracle</t>
+          <t>IRClass Academy advances port security capacity — SMI DIGITAL - shipmanagementinternational.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 08:12:30 GMT</t>
+          <t>Wed, 01 Apr 2026 09:20:06 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9lOW1BUzdPTldhYlh5ZkFoSncwTkZNdVhkMzBQa05CYWJzRndxekV5NGtnR0xDT3EwTTVvWC1aaXN6dElqRWE3SDZsMk1yOGNrbHZEN0h5S3h1d3BGMDJ6Qklmel8xTWU3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOenN3VzFxXzZYTHZEUU1UNWlwZ3VlTmpUUTZhZExiZ2R3U1g4U1JucnNHOGdSMkZ3M3hzZjFMTjU2VTFNRlBweXFxczd2bWtQQ2FqbW44bHAwZ0dYRGpuTmpzUXhQMWlxcmhDSFZaUHFsTy16SXAzaFRIZ2dDRlN1azBzYU5wUUZPQ0k2WUJSbEp1MVluaWE5aHFn?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2761,27 +2761,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lawyer Akhmed Yakoob in police racial abuse arrest - BBC</t>
+          <t>Address to International Transport and Logistics Forum participants - Президент России</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sun, 22 Mar 2026 15:24:38 GMT</t>
+          <t>Wed, 01 Apr 2026 07:18:11 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBTS2FWOFpwRFZQN18zTEdhd3I0TVVsNEM4QWMtTk9XSmZGMm1qQm9nMlBnS2hUYUJjR1VKZGhfdkJfRVF6OTM4YV9SN2ZZd0FqNDJjc3N1bVR3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1tX05qd1FtakVndXAteG1FOWN1c0s3bTFnd0NhbnlWWHV3SVhhMTkyZ3hPUG9NSWxOZUVlaF83cEFsUGhrY3VNZGRQYkVKa19uLUFNT0hualVBRzJk?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2791,27 +2791,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Leatherhead : Police seek 38 year old male in connection with 19 March assault – East Surrey News - Leatherhead Living</t>
+          <t>UK Needs Closer EU Partnerships Amid Global Instability, Says Starmer - globalbankingandfinance.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:41:51 GMT</t>
+          <t>Wed, 01 Apr 2026 09:56:30 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNSDVKUGhrdnR3N1Vuc29hXzl2bWVXTzAtVW9uWHU3alNyX3FvZ0tLUWU5bGZjaE44MnNSNm5jWHk3Sks3ekJ1VXUtczdrUEFKSFdYY19TTS1EWF80MnFTeUh3QTV2dHpfOVRxSGpreTRkZlhra29aUm1qaTVOdnFoY2k2Qndhb3EycXltY0V0OTAzRDhlXy0xd21zdjdpT09uRzJKcXVEQmZjdHpIcDV0YVZQakhzYTVPNHdFZkdHWVhpSjFYa2V0Z051cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbUF1cFNncVNCb1BWa0s2anExdW1CTTNZLWUzZ0Y0ZDlPQzBuUkg2dWI1emZCOW1HRUVBM1lvOUZ2MGtVeGk5LWt5NC16VVdpTGRIZHJnZTBkT3NFLVVpbWZXVWFlb3YtdjNrYkRheXpLNlVremM5SGRLSERqaTdFVDdLSGpZaDdOQlRiWi1LVXJ4NjBNaHdidFhB?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2821,27 +2821,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Police helicopter circles over Sandbach to help find missing man - Sandbach Nub News</t>
+          <t>Irish lawmaker urges Stripe to flout US sanctions on UN investigator Albanese - politico.eu</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 17:32:42 GMT</t>
+          <t>Tue, 31 Mar 2026 18:17:00 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNY0dkTHRZdjNkQ0tJMmNnMWNTV2FvQlcxZmZUX1NDVnJ1VG5WRjhMOGJOcEREa3dZeTdmaFotNVk3MkVvVThwdkhOa2FoUXptYXZFRC1CTHY3R1JyajhPckM1ZFVfd0t5MlhDZThWdG0yRzBnVDRvX3dzVEUyT0RBT29OVlBDcU0wOHVSRnZYTzlHWE56a0VuSk1nTEhpYjhHQUE4T3pVajBlYm16c0JJUkhodw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPMk1XWTUtUEgydVFJZ3gyYmJvTk90TzNCZHNHRkwwQTY2R29pQXNZa0FZNGwwTmJDekVMOVBkTWZLU05xRWNoeTkzYUNwRXJTLWwyekJYZUh5MF9BMXFoWU1fQ0w5WDdObHN6M05MZWdxOWYwMW5xaG5uSWEwR1VvNFJGS25CTzNzVGhkc2Z2eFhrdkVlR2VLeU5Oa2EyWGxiRHdZ?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2851,27 +2851,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BTCUSD Today, March 25: Channel Reclaim Meets Weak Retail, Quiet Whales - Meyka</t>
+          <t>New Isles of Scilly freight vessel sets off from Vietnam - BBC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 05:15:07 GMT</t>
+          <t>Tue, 31 Mar 2026 05:39:10 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZnVTT0pyNU9KTmJCR0hxN1hxNFF4TGlVaWdQQk5oS1JmejBKdGJjVl9tVi1iU2Fqc183aV9LWjZmVnhFYVB0NXBleFV2RDEzWFNmVkFoTXgwMlpEbkM2VUJaeEd3MkJIbUo5VTNtVDBMcFFodjhrcURVTzF0bnVfcXEtQUdwQkNRUGxXUzhSQy1lUjN6MUM2YzdlajFQUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE84eGRVWWdKQWFadllMOUxJSHlJRWoxbDBmamFKbGhNRjl1Z2UxZWhEeGFnVWhzZzhIMWJRSFBNLVdxY0t0X1JFREp3ZGRPck4zZy1reHhGb1R6NDlu?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2881,27 +2881,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Student at Stamford's Westhill High School arrested amid mass walkout, officials say - Stamford Advocate</t>
+          <t>Jubail Port container terminal begins operations - Port Technology</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 00:39:56 GMT</t>
+          <t>Wed, 01 Apr 2026 09:04:49 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxObTI1VDhGWXQ3VENUVDFlQXFBNkYwMlRmZWVtMzE1NEcyVFFVOGJaemVFU1ZseGZ1X2dSTlFETFFfS3VyQmxOYzJPb3FFbHhEeWpjbjc5Mk1iby1Pb3lKODl4RWozMXRzLXZEUkpZbjFfTTdGSTd4TTFzTkVjNnNBUS1fSlo4QmtFWFZ6MUR5RnkwdENJOWtlR21lQlQtdTRJOG1WbXpJb1NxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPa1NRckxCSExfRG10WlI2SGRERlJRTlc4Wm8waHU3N0w2Uk1JaUI0NEkwaGNUT294SE5leXlIZUdXLTZ4WEJOQ0xkeWRic0FRcTVOTnMwMFFQR1E4ZC1uTzBjYi00WjV5dzRtMHhiN3RGRVVHNkRCOVFtSlZENWh6dnRUdVl2c28?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2911,27 +2911,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Police called after car ploughs into wall outside Crewe dentist - Crewe Nub News</t>
+          <t>Taste of the Med comes to port with opening of new restaurant - Northumberland Gazette</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:15:46 GMT</t>
+          <t>Wed, 01 Apr 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNTjRySnZ6VEp5M1lYbFFncUlSaEJibm9SM1IwRm51am5UUVIwY2dKTFp1UEZBMy1kSE1LUnA4WHhjbG0wUFk2Vk9mUXdZSVl3emdyblVndll2UFZxSDBHMkFzOE5CSXY4UnljTnFJVDJaSlFuSkNUdGl0R3gwZFR6RDE2MGVLLWJKSll0d0tacWdJRjBhTWZBVmFwVjB1UlZZcG5uYnhRS2lWeXZkNlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR2phOHQ5dkQyTWJyQXA4Y1lWTUV4QjF5UlZuTUlpZGNYRFhiX1J3aGZQLUpWRXFJblpYazI1bER3NWM5Z2Njdi1ZOUtNcHlzRjZHNFIwUGFNemVBVmVaNDMwN0NDTHk3MzVFNUFram96VWdxNmNtWllsOFlUY044Tzk2TlhtMVRCaHRDeFNnb1loOXRKN0s4eVRoUU5sdmw1eWU5R3dScFdBRlhkbTg3T0RrVElVbVFPdXZ0U1BvZFVCVEpkNHE3bFk1YXdmS0V5YTlqM0lQVml6cTJHaGtsOEFWc01sQ2hS?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2941,27 +2941,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Iran at war: Scenes from inside the embattled country - Reuters</t>
+          <t>Top 10: Automated Warehouses - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 15:18:00 GMT</t>
+          <t>Wed, 01 Apr 2026 08:55:29 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPbjZqdmh2VXBYS0RWMmMwT1h1V3RRanBoVEFPc0k4RktsOURoRG90aXE3TUNHbEZ4b0VRcVlZZEUwN1BIQmc0NWQxM3RIUFdpSVN2T2tYWWdUNDd1aWxROUs0TXpQNGpSZmJwUXAzT3lHdXNBX0JjeHhiNkhlUmVCY0RZWE1mVkZic0ttUmtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5VRXdzRzczbng1X09PY09JRTZLWngzbXluMDNyWkMtRkpyUFBQSGQxdFVjY3BhcXN2dUE3eUJiM3hmMGQyXzBwRFp6cVk5YXBuQU1Ja1ducTQ2b2kzTWZER3JLcFJLcG5vYVpxbnV2d3Zja0hwV3E0Wg?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2971,27 +2971,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LDF and Co-Counsel Defend Protestor of Police Violence Brutalized by the Police in Qualified Immunity Case - Legal Defense Fund</t>
+          <t>First Thing: Kuwaiti tanker hit by Iranian drone attack in Dubai port - The Guardian</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 20:01:22 GMT</t>
+          <t>Tue, 31 Mar 2026 11:05:00 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPM3RkUjlRaGdVQS1wNVNVenRTb2lycGJSQmgyTFRiRXdlMEx6aXJ4eHpfdUVFUFJ4S3FnUTBocmNCd3I0WFh1S0F2eTRBVUtvb2Y0YjI0MEE1Zjc2MFA0QVlOQmtyUjhUeU9VcWdxaTdKZkVTUllLN0RXaGx6cC1YYUx4aWZKaWUwWmk3Wk1RMWhEbnJPSlNyd0tXdkk5SVdsTWFZT3YtMGVVbGllTlZfUUVXZGFFaG5xNl9kTW1BNGJveWkxS1l1TDRNZ0syZjNqRDg3bHkxaXNOdWg4aDJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNUXFQSHFXQXQzQnJ3bkJESHZOdGRwRTdiQUtBaklBNHlJa19rQmh5SjNmYzlOaEN0bU4ydm1ucnBqRTVsOE5XUU1nRDJGdk9CUm1zc19fejVkY0QxQzZ4aWU5WDRkRjEwaHN2WWVCWW9hVTBtZUVQcGZQRFlyWldGdU5Oa1dkOHBKT0x1M2JoQmZNek44V1lxcFM2YUdMTUdLRmJ3anJfdHBocW1EN2JENDVCNVVWYkU?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3001,27 +3001,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>(protest OR demonstration OR unrest OR boycott OR strike OR march OR "civil unrest") AND (retail OR "shopping centre" OR "town centre" OR luxury OR brand OR police OR arrested OR violence OR clashes)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bizarre scenes: Wild act halts CBD march - News.com.au</t>
+          <t>Tetra Pak urges rapid food innovation to ease supply chain strain - FoodNavigator-Asia.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 05:13:19 GMT</t>
+          <t>Wed, 01 Apr 2026 03:32:42 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPbGFrWXZFRXc5b0VUMEVPaHY3cTMyS0R2TmVkRWQzemJjdjRUaExKWFdwcTZwNDEyMXpzaXNqRkVkdnhzajJLMS04Y0t5cFBHejJwNTQ3anJ4WjBtdUdiZDFOQ21FRkVGQWVFWHUtZzRoQUdFUzF4OWNvTkl0TDVISmpHdWZhRVFOMzhscHNWVWVSZ3RaUmpEOWI0cWtibm8tbDVaOVFSRUs4X0ZtQlJUMEg4cGM1NzdFNEZHSU9na1hyaGF5dHVjWVpDV1l5Nmc4Z1hPV3dkRF92MmlUWHY0Q0dLR3RXdHZvUC13NUdzQ2MzQTjSAfgBQVVfeXFMUEw0eS1aODc0cWx6TG5vTnlOdmpnNG5BVlRmd05hRUM4TE54N0dOM2ExdHJRdlIyWFJTYmxqektmelpEd1ljMXJ2UTdWbmdzNUEzYW51NVMwemlJQUZhdTdCbmlYRXdnekNfNG42UUNuUXVsQmZ2ZEdXZ2F2WkRPQTBoU0NBQWdJRnRKNGtTeFBFUkk2WHlDY1VxVjNHUVF0RVJlalV2NjBYNzR6TVo2MEhUeHJfTTlMVGZKdHdVaFZod210Tzg0TEdxaGNqUG1PeUFoSEJGd3V4eVhVR3BpczJrR29hT3pJRUgyZkgwS0JhS2M4azJXOWk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPUG9lWWxqdHRtZkVrQ3R1U1NCd0h0THZBMWpMSk1JZnZBX0hXdUFpOElHelpwUkVGMFYyTVRPRHpaWklKdnZSbmxaU0JRa0F6dFZUcmFBQ1hxYXQxUUlycHpkM2lzOWdwWmplUEU4WUxLZF9ZTEtiNUFlWEVIem12RzBIYzFuNFpxMnFHN2VtUmdPY3c3bmR1a1lUbmVSdnlFNy0zTzBQOHc3dmcydlp6ODNXWF9LRjVhak54RQ?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seth Rollins gets ARRESTED: Raw highlights, March 23, 2026 - WWE</t>
+          <t>Palestine protest organisers found guilty of breaching police restrictions - Middle East Eye</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 22:25:29 GMT</t>
+          <t>Wed, 01 Apr 2026 09:28:12 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPOTZCWGNfcDB3RXo0NFlhUW9YRVZaQTVMSlVJZFZrZ3RmSDFmdEtFSk9zQW41WXg5Wll0Y3huTDRqTlkzdk9mcGZ0ODk5VjU0V09uc0tjTG9majhRczNVQ3J2U3YxVGQ5TEZFWVJpY0c0a1BQalZMLXNNZGFFTUQ3SEtpcHRzeVFGa0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQcTNmWDdUUEktSlRjQmplYWtYMnJMWUtRR3hubzRzOEZCbWFWZGFRRzBMZEdKU3drQmpNRmVlUXgySkxFTF9DNWNvNG9lV1dYSnVwWDY0SWpDb0xq